--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -2066,22 +2066,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1335.978</v>
+        <v>1333.464</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6528</v>
+        <v>-1.5997</v>
       </c>
       <c r="J14" t="n">
-        <v>1402</v>
+        <v>1401.2</v>
       </c>
       <c r="K14" t="n">
         <v>305</v>
@@ -2102,67 +2102,67 @@
         <v>306</v>
       </c>
       <c r="Q14" t="n">
-        <v>103.424</v>
+        <v>102.203</v>
       </c>
       <c r="R14" t="n">
-        <v>110.596</v>
+        <v>109.944</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.172</v>
+        <v>-7.74</v>
       </c>
       <c r="T14" t="n">
-        <v>0.32396</v>
+        <v>0.3247</v>
       </c>
       <c r="U14" t="n">
-        <v>0.17505</v>
+        <v>0.17681</v>
       </c>
       <c r="V14" t="n">
-        <v>69.31999999999999</v>
+        <v>68.84</v>
       </c>
       <c r="W14" t="n">
-        <v>74.2</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3509</v>
+        <v>0.3305</v>
       </c>
       <c r="Y14" t="n">
-        <v>25.86</v>
+        <v>25.718</v>
       </c>
       <c r="Z14" t="n">
-        <v>58.239</v>
+        <v>58.606</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.612</v>
+        <v>6.362</v>
       </c>
       <c r="AB14" t="n">
-        <v>18.32</v>
+        <v>18.098</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.991</v>
+        <v>11.042</v>
       </c>
       <c r="AD14" t="n">
-        <v>16.016</v>
+        <v>16.283</v>
       </c>
       <c r="AE14" t="n">
-        <v>9.938000000000001</v>
+        <v>10.217</v>
       </c>
       <c r="AF14" t="n">
-        <v>20.562</v>
+        <v>21.088</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.578</v>
+        <v>13.412</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.612</v>
+        <v>7.503</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.329</v>
+        <v>4.389</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15.531</v>
+        <v>15.954</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>-0.5</v>
@@ -2306,22 +2306,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1925.212</v>
+        <v>1932.735</v>
       </c>
       <c r="I16" t="n">
-        <v>7.1116</v>
+        <v>6.7834</v>
       </c>
       <c r="J16" t="n">
-        <v>1726.1</v>
+        <v>1725.9</v>
       </c>
       <c r="K16" t="n">
         <v>20</v>
@@ -2342,70 +2342,70 @@
         <v>19</v>
       </c>
       <c r="Q16" t="n">
-        <v>122.37</v>
+        <v>123.182</v>
       </c>
       <c r="R16" t="n">
-        <v>109.057</v>
+        <v>108.725</v>
       </c>
       <c r="S16" t="n">
-        <v>13.313</v>
+        <v>14.456</v>
       </c>
       <c r="T16" t="n">
-        <v>0.30621</v>
+        <v>0.29751</v>
       </c>
       <c r="U16" t="n">
-        <v>0.11896</v>
+        <v>0.11943</v>
       </c>
       <c r="V16" t="n">
-        <v>89.65000000000001</v>
+        <v>90.45</v>
       </c>
       <c r="W16" t="n">
-        <v>80.01000000000001</v>
+        <v>79.89</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7159</v>
+        <v>0.7361</v>
       </c>
       <c r="Y16" t="n">
-        <v>32.148</v>
+        <v>32.295</v>
       </c>
       <c r="Z16" t="n">
-        <v>64.398</v>
+        <v>64.09</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.057</v>
+        <v>8.228999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>21.591</v>
+        <v>21.573</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.295</v>
+        <v>17.634</v>
       </c>
       <c r="AD16" t="n">
-        <v>23.25</v>
+        <v>23.535</v>
       </c>
       <c r="AE16" t="n">
-        <v>10.011</v>
+        <v>9.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>22.761</v>
+        <v>23.139</v>
       </c>
       <c r="AG16" t="n">
-        <v>16.989</v>
+        <v>17.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.273</v>
+        <v>7.307</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.091</v>
+        <v>5.219</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17.091</v>
+        <v>17.217</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="17">
@@ -3026,22 +3026,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1673.452</v>
+        <v>1671.465</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.3298</v>
+        <v>-6.0193</v>
       </c>
       <c r="J22" t="n">
-        <v>1725.5</v>
+        <v>1739.8</v>
       </c>
       <c r="K22" t="n">
         <v>51</v>
@@ -3062,70 +3062,70 @@
         <v>51</v>
       </c>
       <c r="Q22" t="n">
-        <v>115.761</v>
+        <v>114.756</v>
       </c>
       <c r="R22" t="n">
-        <v>111.17</v>
+        <v>111.243</v>
       </c>
       <c r="S22" t="n">
-        <v>4.59</v>
+        <v>3.513</v>
       </c>
       <c r="T22" t="n">
-        <v>0.32479</v>
+        <v>0.32442</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1611</v>
+        <v>0.16678</v>
       </c>
       <c r="V22" t="n">
-        <v>81.29000000000001</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>77.70999999999999</v>
+        <v>77.58</v>
       </c>
       <c r="X22" t="n">
-        <v>0.5062</v>
+        <v>0.4773</v>
       </c>
       <c r="Y22" t="n">
-        <v>28.695</v>
+        <v>28.42</v>
       </c>
       <c r="Z22" t="n">
-        <v>60.508</v>
+        <v>60.216</v>
       </c>
       <c r="AA22" t="n">
-        <v>8.577</v>
+        <v>8.545</v>
       </c>
       <c r="AB22" t="n">
-        <v>23.847</v>
+        <v>23.909</v>
       </c>
       <c r="AC22" t="n">
-        <v>15.707</v>
+        <v>15.42</v>
       </c>
       <c r="AD22" t="n">
-        <v>21.577</v>
+        <v>21.136</v>
       </c>
       <c r="AE22" t="n">
-        <v>11.273</v>
+        <v>11.295</v>
       </c>
       <c r="AF22" t="n">
-        <v>22.81</v>
+        <v>22.909</v>
       </c>
       <c r="AG22" t="n">
-        <v>15.402</v>
+        <v>15.432</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.139</v>
+        <v>6.17</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.116</v>
+        <v>4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16.587</v>
+        <v>16.58</v>
       </c>
       <c r="AK22" t="n">
-        <v>-5.6</v>
+        <v>-6</v>
       </c>
       <c r="AL22" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="23">
@@ -4586,22 +4586,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1626.746</v>
+        <v>1615.973</v>
       </c>
       <c r="I35" t="n">
-        <v>1.2252</v>
+        <v>1.0517</v>
       </c>
       <c r="J35" t="n">
-        <v>1624.5</v>
+        <v>1623.7</v>
       </c>
       <c r="K35" t="n">
         <v>83</v>
@@ -4622,70 +4622,70 @@
         <v>80</v>
       </c>
       <c r="Q35" t="n">
-        <v>111.734</v>
+        <v>110.534</v>
       </c>
       <c r="R35" t="n">
-        <v>108.992</v>
+        <v>108.804</v>
       </c>
       <c r="S35" t="n">
-        <v>2.743</v>
+        <v>1.73</v>
       </c>
       <c r="T35" t="n">
-        <v>0.30875</v>
+        <v>0.30333</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1503</v>
+        <v>0.15244</v>
       </c>
       <c r="V35" t="n">
-        <v>79.87</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="W35" t="n">
-        <v>77.41</v>
+        <v>77.28</v>
       </c>
       <c r="X35" t="n">
-        <v>0.5102</v>
+        <v>0.4937</v>
       </c>
       <c r="Y35" t="n">
-        <v>27.197</v>
+        <v>27.094</v>
       </c>
       <c r="Z35" t="n">
-        <v>59.871</v>
+        <v>59.876</v>
       </c>
       <c r="AA35" t="n">
-        <v>7.014</v>
+        <v>6.929</v>
       </c>
       <c r="AB35" t="n">
-        <v>21.027</v>
+        <v>21.268</v>
       </c>
       <c r="AC35" t="n">
-        <v>18.463</v>
+        <v>17.895</v>
       </c>
       <c r="AD35" t="n">
-        <v>25.878</v>
+        <v>25.05</v>
       </c>
       <c r="AE35" t="n">
-        <v>10.748</v>
+        <v>10.542</v>
       </c>
       <c r="AF35" t="n">
-        <v>23.51</v>
+        <v>23.655</v>
       </c>
       <c r="AG35" t="n">
-        <v>15.476</v>
+        <v>15.39</v>
       </c>
       <c r="AH35" t="n">
-        <v>6.517</v>
+        <v>6.527</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.095</v>
+        <v>3.223</v>
       </c>
       <c r="AJ35" t="n">
-        <v>15.442</v>
+        <v>15.292</v>
       </c>
       <c r="AK35" t="n">
-        <v>-3.4</v>
+        <v>-4.8</v>
       </c>
       <c r="AL35" t="n">
-        <v>-6.6</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="36">
@@ -5066,22 +5066,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1697.069</v>
+        <v>1728.495</v>
       </c>
       <c r="I39" t="n">
-        <v>8.4321</v>
+        <v>8.044</v>
       </c>
       <c r="J39" t="n">
-        <v>1603.7</v>
+        <v>1599.2</v>
       </c>
       <c r="K39" t="n">
         <v>73</v>
@@ -5102,70 +5102,70 @@
         <v>64</v>
       </c>
       <c r="Q39" t="n">
-        <v>109.388</v>
+        <v>109.407</v>
       </c>
       <c r="R39" t="n">
-        <v>103.548</v>
+        <v>102.709</v>
       </c>
       <c r="S39" t="n">
-        <v>5.84</v>
+        <v>6.698</v>
       </c>
       <c r="T39" t="n">
-        <v>0.22856</v>
+        <v>0.22702</v>
       </c>
       <c r="U39" t="n">
-        <v>0.14744</v>
+        <v>0.14484</v>
       </c>
       <c r="V39" t="n">
-        <v>76.86</v>
+        <v>77.12</v>
       </c>
       <c r="W39" t="n">
-        <v>72.59999999999999</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="X39" t="n">
-        <v>0.6685</v>
+        <v>0.6939</v>
       </c>
       <c r="Y39" t="n">
-        <v>25.674</v>
+        <v>25.823</v>
       </c>
       <c r="Z39" t="n">
-        <v>57.659</v>
+        <v>58.014</v>
       </c>
       <c r="AA39" t="n">
-        <v>9.045999999999999</v>
+        <v>8.912000000000001</v>
       </c>
       <c r="AB39" t="n">
-        <v>24.569</v>
+        <v>24.578</v>
       </c>
       <c r="AC39" t="n">
-        <v>16.47</v>
+        <v>16.565</v>
       </c>
       <c r="AD39" t="n">
-        <v>21.18</v>
+        <v>21.374</v>
       </c>
       <c r="AE39" t="n">
-        <v>7.246</v>
+        <v>7.286</v>
       </c>
       <c r="AF39" t="n">
-        <v>24.181</v>
+        <v>24.585</v>
       </c>
       <c r="AG39" t="n">
-        <v>13.961</v>
+        <v>14.272</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.783</v>
+        <v>5.905</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.211</v>
+        <v>3.252</v>
       </c>
       <c r="AJ39" t="n">
-        <v>18.78</v>
+        <v>18.878</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.4</v>
+        <v>3.2</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="40">
@@ -5546,22 +5546,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F43" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G43" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1454.867</v>
+        <v>1450.905</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.8125</v>
+        <v>-2.6833</v>
       </c>
       <c r="J43" t="n">
-        <v>1359.6</v>
+        <v>1359</v>
       </c>
       <c r="K43" t="n">
         <v>299</v>
@@ -5582,70 +5582,70 @@
         <v>282</v>
       </c>
       <c r="Q43" t="n">
-        <v>108.071</v>
+        <v>107.607</v>
       </c>
       <c r="R43" t="n">
-        <v>109.302</v>
+        <v>109.566</v>
       </c>
       <c r="S43" t="n">
-        <v>-1.23</v>
+        <v>-1.959</v>
       </c>
       <c r="T43" t="n">
-        <v>0.24337</v>
+        <v>0.24558</v>
       </c>
       <c r="U43" t="n">
-        <v>0.15786</v>
+        <v>0.15555</v>
       </c>
       <c r="V43" t="n">
-        <v>70.95</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="W43" t="n">
-        <v>71.97</v>
+        <v>71.95</v>
       </c>
       <c r="X43" t="n">
-        <v>0.5962</v>
+        <v>0.5668</v>
       </c>
       <c r="Y43" t="n">
-        <v>25.311</v>
+        <v>25.153</v>
       </c>
       <c r="Z43" t="n">
-        <v>55.358</v>
+        <v>55.485</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.946</v>
+        <v>6.921</v>
       </c>
       <c r="AB43" t="n">
-        <v>19.406</v>
+        <v>19.338</v>
       </c>
       <c r="AC43" t="n">
-        <v>13.378</v>
+        <v>13.259</v>
       </c>
       <c r="AD43" t="n">
-        <v>17.351</v>
+        <v>17.303</v>
       </c>
       <c r="AE43" t="n">
-        <v>7.596</v>
+        <v>7.697</v>
       </c>
       <c r="AF43" t="n">
-        <v>23.238</v>
+        <v>23.256</v>
       </c>
       <c r="AG43" t="n">
-        <v>13</v>
+        <v>12.783</v>
       </c>
       <c r="AH43" t="n">
-        <v>5.568</v>
+        <v>5.357</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.799</v>
+        <v>3.953</v>
       </c>
       <c r="AJ43" t="n">
-        <v>14.1</v>
+        <v>14.158</v>
       </c>
       <c r="AK43" t="n">
-        <v>-1</v>
+        <v>-4.2</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="44">
@@ -5786,22 +5786,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1439.529</v>
+        <v>1440.393</v>
       </c>
       <c r="I45" t="n">
-        <v>1.3089</v>
+        <v>1.3894</v>
       </c>
       <c r="J45" t="n">
-        <v>1489.4</v>
+        <v>1493.2</v>
       </c>
       <c r="K45" t="n">
         <v>183</v>
@@ -5822,70 +5822,70 @@
         <v>169</v>
       </c>
       <c r="Q45" t="n">
-        <v>112.349</v>
+        <v>112.744</v>
       </c>
       <c r="R45" t="n">
-        <v>112.755</v>
+        <v>113.573</v>
       </c>
       <c r="S45" t="n">
-        <v>-0.406</v>
+        <v>-0.83</v>
       </c>
       <c r="T45" t="n">
-        <v>0.29518</v>
+        <v>0.29636</v>
       </c>
       <c r="U45" t="n">
-        <v>0.16801</v>
+        <v>0.16654</v>
       </c>
       <c r="V45" t="n">
-        <v>73.40000000000001</v>
+        <v>73.39</v>
       </c>
       <c r="W45" t="n">
-        <v>73.76000000000001</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="X45" t="n">
-        <v>0.4926</v>
+        <v>0.4762</v>
       </c>
       <c r="Y45" t="n">
-        <v>25.085</v>
+        <v>25.163</v>
       </c>
       <c r="Z45" t="n">
-        <v>54.787</v>
+        <v>54.694</v>
       </c>
       <c r="AA45" t="n">
-        <v>8.598000000000001</v>
+        <v>8.577999999999999</v>
       </c>
       <c r="AB45" t="n">
-        <v>24.28</v>
+        <v>24.313</v>
       </c>
       <c r="AC45" t="n">
-        <v>14.628</v>
+        <v>14.483</v>
       </c>
       <c r="AD45" t="n">
-        <v>20.337</v>
+        <v>20.197</v>
       </c>
       <c r="AE45" t="n">
-        <v>9.337</v>
+        <v>9.292999999999999</v>
       </c>
       <c r="AF45" t="n">
-        <v>22.104</v>
+        <v>21.857</v>
       </c>
       <c r="AG45" t="n">
-        <v>12.769</v>
+        <v>12.667</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.654</v>
+        <v>4.551</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.463</v>
+        <v>3.476</v>
       </c>
       <c r="AJ45" t="n">
-        <v>17.619</v>
+        <v>17.517</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL45" t="n">
-        <v>-1.8</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="46">
@@ -6026,22 +6026,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F47" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1214.324</v>
+        <v>1215.857</v>
       </c>
       <c r="I47" t="n">
-        <v>-2.1155</v>
+        <v>-2.0217</v>
       </c>
       <c r="J47" t="n">
-        <v>1418.8</v>
+        <v>1419.7</v>
       </c>
       <c r="K47" t="n">
         <v>348</v>
@@ -6062,70 +6062,70 @@
         <v>344</v>
       </c>
       <c r="Q47" t="n">
-        <v>97.01900000000001</v>
+        <v>98.143</v>
       </c>
       <c r="R47" t="n">
-        <v>113.643</v>
+        <v>114.185</v>
       </c>
       <c r="S47" t="n">
-        <v>-16.624</v>
+        <v>-16.042</v>
       </c>
       <c r="T47" t="n">
-        <v>0.28504</v>
+        <v>0.2909</v>
       </c>
       <c r="U47" t="n">
-        <v>0.14328</v>
+        <v>0.14366</v>
       </c>
       <c r="V47" t="n">
-        <v>64.79000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="W47" t="n">
-        <v>76.48</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="X47" t="n">
-        <v>0.1975</v>
+        <v>0.1913</v>
       </c>
       <c r="Y47" t="n">
-        <v>23.177</v>
+        <v>23.29</v>
       </c>
       <c r="Z47" t="n">
-        <v>57.807</v>
+        <v>57.559</v>
       </c>
       <c r="AA47" t="n">
-        <v>5.712</v>
+        <v>5.701</v>
       </c>
       <c r="AB47" t="n">
-        <v>17.843</v>
+        <v>17.742</v>
       </c>
       <c r="AC47" t="n">
-        <v>12.719</v>
+        <v>12.994</v>
       </c>
       <c r="AD47" t="n">
-        <v>16.975</v>
+        <v>17.348</v>
       </c>
       <c r="AE47" t="n">
-        <v>7.901</v>
+        <v>8.035</v>
       </c>
       <c r="AF47" t="n">
-        <v>19.263</v>
+        <v>19.081</v>
       </c>
       <c r="AG47" t="n">
-        <v>11.6</v>
+        <v>11.736</v>
       </c>
       <c r="AH47" t="n">
-        <v>8.243</v>
+        <v>8.135999999999999</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.288</v>
+        <v>1.299</v>
       </c>
       <c r="AJ47" t="n">
-        <v>18.889</v>
+        <v>18.948</v>
       </c>
       <c r="AK47" t="n">
-        <v>-7.2</v>
+        <v>-4.4</v>
       </c>
       <c r="AL47" t="n">
-        <v>-1.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="48">
@@ -6506,22 +6506,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1358.541</v>
+        <v>1356.605</v>
       </c>
       <c r="I51" t="n">
-        <v>-2.6602</v>
+        <v>-2.5339</v>
       </c>
       <c r="J51" t="n">
-        <v>1457.7</v>
+        <v>1460.6</v>
       </c>
       <c r="K51" t="n">
         <v>320</v>
@@ -6542,70 +6542,70 @@
         <v>316</v>
       </c>
       <c r="Q51" t="n">
-        <v>110.861</v>
+        <v>109.789</v>
       </c>
       <c r="R51" t="n">
-        <v>123.995</v>
+        <v>124.458</v>
       </c>
       <c r="S51" t="n">
-        <v>-13.134</v>
+        <v>-14.669</v>
       </c>
       <c r="T51" t="n">
-        <v>0.26541</v>
+        <v>0.26618</v>
       </c>
       <c r="U51" t="n">
-        <v>0.1702</v>
+        <v>0.16812</v>
       </c>
       <c r="V51" t="n">
-        <v>79.42</v>
+        <v>78.38</v>
       </c>
       <c r="W51" t="n">
-        <v>88.59999999999999</v>
+        <v>88.61</v>
       </c>
       <c r="X51" t="n">
-        <v>0.2841</v>
+        <v>0.2639</v>
       </c>
       <c r="Y51" t="n">
-        <v>25.886</v>
+        <v>25.508</v>
       </c>
       <c r="Z51" t="n">
-        <v>57.261</v>
+        <v>57.274</v>
       </c>
       <c r="AA51" t="n">
-        <v>11.034</v>
+        <v>10.859</v>
       </c>
       <c r="AB51" t="n">
-        <v>29.034</v>
+        <v>29.045</v>
       </c>
       <c r="AC51" t="n">
-        <v>16.614</v>
+        <v>16.507</v>
       </c>
       <c r="AD51" t="n">
-        <v>21.909</v>
+        <v>21.64</v>
       </c>
       <c r="AE51" t="n">
-        <v>7.523</v>
+        <v>7.484</v>
       </c>
       <c r="AF51" t="n">
-        <v>20.511</v>
+        <v>20.276</v>
       </c>
       <c r="AG51" t="n">
-        <v>15.159</v>
+        <v>14.697</v>
       </c>
       <c r="AH51" t="n">
-        <v>5.523</v>
+        <v>5.549</v>
       </c>
       <c r="AI51" t="n">
-        <v>2.602</v>
+        <v>2.561</v>
       </c>
       <c r="AJ51" t="n">
-        <v>19.205</v>
+        <v>19.318</v>
       </c>
       <c r="AK51" t="n">
-        <v>-10.4</v>
+        <v>-11.4</v>
       </c>
       <c r="AL51" t="n">
-        <v>-7.4</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="52">
@@ -7106,22 +7106,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1651.887</v>
+        <v>1673.565</v>
       </c>
       <c r="I56" t="n">
-        <v>-5.6123</v>
+        <v>-5.2938</v>
       </c>
       <c r="J56" t="n">
-        <v>1542.5</v>
+        <v>1559.4</v>
       </c>
       <c r="K56" t="n">
         <v>86</v>
@@ -7142,70 +7142,70 @@
         <v>88</v>
       </c>
       <c r="Q56" t="n">
-        <v>120.05</v>
+        <v>119.558</v>
       </c>
       <c r="R56" t="n">
-        <v>113.293</v>
+        <v>112.768</v>
       </c>
       <c r="S56" t="n">
-        <v>6.758</v>
+        <v>6.79</v>
       </c>
       <c r="T56" t="n">
-        <v>0.26154</v>
+        <v>0.25596</v>
       </c>
       <c r="U56" t="n">
-        <v>0.17205</v>
+        <v>0.1771</v>
       </c>
       <c r="V56" t="n">
-        <v>76.13</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="W56" t="n">
-        <v>71.7</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="X56" t="n">
-        <v>0.6481</v>
+        <v>0.6599</v>
       </c>
       <c r="Y56" t="n">
-        <v>25.15</v>
+        <v>25.054</v>
       </c>
       <c r="Z56" t="n">
-        <v>51.087</v>
+        <v>50.694</v>
       </c>
       <c r="AA56" t="n">
-        <v>9.808999999999999</v>
+        <v>9.878</v>
       </c>
       <c r="AB56" t="n">
-        <v>24.741</v>
+        <v>24.864</v>
       </c>
       <c r="AC56" t="n">
-        <v>16.024</v>
+        <v>16.299</v>
       </c>
       <c r="AD56" t="n">
-        <v>20.657</v>
+        <v>21.102</v>
       </c>
       <c r="AE56" t="n">
-        <v>7.694</v>
+        <v>7.524</v>
       </c>
       <c r="AF56" t="n">
-        <v>22.326</v>
+        <v>22.415</v>
       </c>
       <c r="AG56" t="n">
-        <v>15.622</v>
+        <v>15.735</v>
       </c>
       <c r="AH56" t="n">
-        <v>4.976</v>
+        <v>5.129</v>
       </c>
       <c r="AI56" t="n">
-        <v>2.076</v>
+        <v>2.102</v>
       </c>
       <c r="AJ56" t="n">
-        <v>16.678</v>
+        <v>16.66</v>
       </c>
       <c r="AK56" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AL56" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -7706,22 +7706,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F61" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G61" t="b">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>1661.695</v>
+        <v>1672.47</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.7577</v>
+        <v>-1.8294</v>
       </c>
       <c r="J61" t="n">
-        <v>1664.2</v>
+        <v>1663.7</v>
       </c>
       <c r="K61" t="n">
         <v>82</v>
@@ -7742,70 +7742,70 @@
         <v>87</v>
       </c>
       <c r="Q61" t="n">
-        <v>110.254</v>
+        <v>110.125</v>
       </c>
       <c r="R61" t="n">
-        <v>110.824</v>
+        <v>109.574</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.57</v>
+        <v>0.552</v>
       </c>
       <c r="T61" t="n">
-        <v>0.24891</v>
+        <v>0.24808</v>
       </c>
       <c r="U61" t="n">
-        <v>0.1555</v>
+        <v>0.15439</v>
       </c>
       <c r="V61" t="n">
-        <v>75.56999999999999</v>
+        <v>75.59</v>
       </c>
       <c r="W61" t="n">
-        <v>75.70999999999999</v>
+        <v>74.94</v>
       </c>
       <c r="X61" t="n">
-        <v>0.4608</v>
+        <v>0.4899</v>
       </c>
       <c r="Y61" t="n">
-        <v>26.625</v>
+        <v>26.693</v>
       </c>
       <c r="Z61" t="n">
-        <v>58.861</v>
+        <v>59.145</v>
       </c>
       <c r="AA61" t="n">
-        <v>9.888999999999999</v>
+        <v>9.904</v>
       </c>
       <c r="AB61" t="n">
-        <v>28.317</v>
+        <v>28.319</v>
       </c>
       <c r="AC61" t="n">
-        <v>12.433</v>
+        <v>12.296</v>
       </c>
       <c r="AD61" t="n">
-        <v>16.408</v>
+        <v>16.122</v>
       </c>
       <c r="AE61" t="n">
-        <v>8.268000000000001</v>
+        <v>8.266999999999999</v>
       </c>
       <c r="AF61" t="n">
-        <v>24.223</v>
+        <v>24.365</v>
       </c>
       <c r="AG61" t="n">
-        <v>15.486</v>
+        <v>15.577</v>
       </c>
       <c r="AH61" t="n">
-        <v>5.555</v>
+        <v>5.922</v>
       </c>
       <c r="AI61" t="n">
-        <v>2.716</v>
+        <v>2.583</v>
       </c>
       <c r="AJ61" t="n">
-        <v>14.266</v>
+        <v>14.145</v>
       </c>
       <c r="AK61" t="n">
-        <v>-7.4</v>
+        <v>-1.8</v>
       </c>
       <c r="AL61" t="n">
-        <v>-9.6</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="62">
@@ -8426,22 +8426,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G67" t="b">
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1534.835</v>
+        <v>1523.046</v>
       </c>
       <c r="I67" t="n">
-        <v>-2.9764</v>
+        <v>-2.809</v>
       </c>
       <c r="J67" t="n">
-        <v>1538.2</v>
+        <v>1542.6</v>
       </c>
       <c r="K67" t="n">
         <v>106</v>
@@ -8462,70 +8462,70 @@
         <v>105</v>
       </c>
       <c r="Q67" t="n">
-        <v>109.139</v>
+        <v>108.881</v>
       </c>
       <c r="R67" t="n">
-        <v>105.344</v>
+        <v>105.54</v>
       </c>
       <c r="S67" t="n">
-        <v>3.795</v>
+        <v>3.341</v>
       </c>
       <c r="T67" t="n">
-        <v>0.29051</v>
+        <v>0.28454</v>
       </c>
       <c r="U67" t="n">
-        <v>0.16109</v>
+        <v>0.1555</v>
       </c>
       <c r="V67" t="n">
-        <v>70.34</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="W67" t="n">
-        <v>68.36</v>
+        <v>68.48</v>
       </c>
       <c r="X67" t="n">
-        <v>0.5971</v>
+        <v>0.5657</v>
       </c>
       <c r="Y67" t="n">
-        <v>25.073</v>
+        <v>25.071</v>
       </c>
       <c r="Z67" t="n">
-        <v>55.308</v>
+        <v>55.5</v>
       </c>
       <c r="AA67" t="n">
-        <v>8.805999999999999</v>
+        <v>8.823</v>
       </c>
       <c r="AB67" t="n">
-        <v>23.956</v>
+        <v>24.318</v>
       </c>
       <c r="AC67" t="n">
-        <v>11.388</v>
+        <v>11.217</v>
       </c>
       <c r="AD67" t="n">
-        <v>17.63</v>
+        <v>17.52</v>
       </c>
       <c r="AE67" t="n">
-        <v>8.927</v>
+        <v>8.702</v>
       </c>
       <c r="AF67" t="n">
-        <v>21.37</v>
+        <v>21.374</v>
       </c>
       <c r="AG67" t="n">
-        <v>13.341</v>
+        <v>13.227</v>
       </c>
       <c r="AH67" t="n">
-        <v>6.377</v>
+        <v>6.399</v>
       </c>
       <c r="AI67" t="n">
-        <v>3.949</v>
+        <v>3.884</v>
       </c>
       <c r="AJ67" t="n">
-        <v>17.059</v>
+        <v>16.899</v>
       </c>
       <c r="AK67" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="AL67" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -9026,22 +9026,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1605.069</v>
+        <v>1586.703</v>
       </c>
       <c r="I72" t="n">
-        <v>5.8136</v>
+        <v>5.744</v>
       </c>
       <c r="J72" t="n">
-        <v>1597</v>
+        <v>1607.9</v>
       </c>
       <c r="K72" t="n">
         <v>95</v>
@@ -9062,70 +9062,70 @@
         <v>97</v>
       </c>
       <c r="Q72" t="n">
-        <v>105.506</v>
+        <v>104.543</v>
       </c>
       <c r="R72" t="n">
-        <v>102.589</v>
+        <v>103.203</v>
       </c>
       <c r="S72" t="n">
-        <v>2.917</v>
+        <v>1.34</v>
       </c>
       <c r="T72" t="n">
-        <v>0.2994</v>
+        <v>0.29372</v>
       </c>
       <c r="U72" t="n">
-        <v>0.17031</v>
+        <v>0.17239</v>
       </c>
       <c r="V72" t="n">
-        <v>71.05</v>
+        <v>70.53</v>
       </c>
       <c r="W72" t="n">
-        <v>68.93000000000001</v>
+        <v>69.48</v>
       </c>
       <c r="X72" t="n">
-        <v>0.5578</v>
+        <v>0.5266</v>
       </c>
       <c r="Y72" t="n">
-        <v>24.762</v>
+        <v>24.699</v>
       </c>
       <c r="Z72" t="n">
-        <v>56.286</v>
+        <v>56.102</v>
       </c>
       <c r="AA72" t="n">
-        <v>7.34</v>
+        <v>7.102</v>
       </c>
       <c r="AB72" t="n">
-        <v>22.218</v>
+        <v>21.925</v>
       </c>
       <c r="AC72" t="n">
-        <v>14.184</v>
+        <v>14.028</v>
       </c>
       <c r="AD72" t="n">
-        <v>20.395</v>
+        <v>20.213</v>
       </c>
       <c r="AE72" t="n">
-        <v>9.313000000000001</v>
+        <v>9.082000000000001</v>
       </c>
       <c r="AF72" t="n">
-        <v>21.993</v>
+        <v>21.992</v>
       </c>
       <c r="AG72" t="n">
-        <v>15.184</v>
+        <v>14.958</v>
       </c>
       <c r="AH72" t="n">
-        <v>6.966</v>
+        <v>6.876</v>
       </c>
       <c r="AI72" t="n">
-        <v>3.347</v>
+        <v>3.317</v>
       </c>
       <c r="AJ72" t="n">
-        <v>18.061</v>
+        <v>17.942</v>
       </c>
       <c r="AK72" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="AL72" t="n">
-        <v>-1.2</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="73">
@@ -9146,22 +9146,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>1318.546</v>
+        <v>1321.378</v>
       </c>
       <c r="I73" t="n">
-        <v>1.5254</v>
+        <v>1.5671</v>
       </c>
       <c r="J73" t="n">
-        <v>1452.1</v>
+        <v>1448.6</v>
       </c>
       <c r="K73" t="n">
         <v>232</v>
@@ -9182,70 +9182,70 @@
         <v>237</v>
       </c>
       <c r="Q73" t="n">
-        <v>109.416</v>
+        <v>109.832</v>
       </c>
       <c r="R73" t="n">
-        <v>113.933</v>
+        <v>112.816</v>
       </c>
       <c r="S73" t="n">
-        <v>-4.518</v>
+        <v>-2.984</v>
       </c>
       <c r="T73" t="n">
-        <v>0.31799</v>
+        <v>0.31172</v>
       </c>
       <c r="U73" t="n">
-        <v>0.15671</v>
+        <v>0.15656</v>
       </c>
       <c r="V73" t="n">
-        <v>76.95</v>
+        <v>77.05</v>
       </c>
       <c r="W73" t="n">
-        <v>80.41</v>
+        <v>79.47</v>
       </c>
       <c r="X73" t="n">
-        <v>0.4885</v>
+        <v>0.5062</v>
       </c>
       <c r="Y73" t="n">
-        <v>27.263</v>
+        <v>27.319</v>
       </c>
       <c r="Z73" t="n">
-        <v>61.548</v>
+        <v>61.291</v>
       </c>
       <c r="AA73" t="n">
-        <v>6.731</v>
+        <v>6.753</v>
       </c>
       <c r="AB73" t="n">
-        <v>19.215</v>
+        <v>19.247</v>
       </c>
       <c r="AC73" t="n">
-        <v>15.692</v>
+        <v>15.66</v>
       </c>
       <c r="AD73" t="n">
-        <v>19.975</v>
+        <v>19.907</v>
       </c>
       <c r="AE73" t="n">
-        <v>10.9</v>
+        <v>10.739</v>
       </c>
       <c r="AF73" t="n">
-        <v>23.288</v>
+        <v>23.698</v>
       </c>
       <c r="AG73" t="n">
-        <v>13.377</v>
+        <v>13.199</v>
       </c>
       <c r="AH73" t="n">
-        <v>5.758</v>
+        <v>5.658</v>
       </c>
       <c r="AI73" t="n">
-        <v>3.338</v>
+        <v>3.353</v>
       </c>
       <c r="AJ73" t="n">
-        <v>19.429</v>
+        <v>19.388</v>
       </c>
       <c r="AK73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL73" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="74">
@@ -9626,22 +9626,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G77" t="b">
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>1477.395</v>
+        <v>1476.582</v>
       </c>
       <c r="I77" t="n">
-        <v>-2.5766</v>
+        <v>-2.3487</v>
       </c>
       <c r="J77" t="n">
-        <v>1544.2</v>
+        <v>1541.8</v>
       </c>
       <c r="K77" t="n">
         <v>125</v>
@@ -9662,70 +9662,70 @@
         <v>131</v>
       </c>
       <c r="Q77" t="n">
-        <v>109.564</v>
+        <v>108.082</v>
       </c>
       <c r="R77" t="n">
-        <v>107.884</v>
+        <v>107.044</v>
       </c>
       <c r="S77" t="n">
-        <v>1.68</v>
+        <v>1.038</v>
       </c>
       <c r="T77" t="n">
-        <v>0.28088</v>
+        <v>0.28294</v>
       </c>
       <c r="U77" t="n">
-        <v>0.17071</v>
+        <v>0.1768</v>
       </c>
       <c r="V77" t="n">
-        <v>78.48</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="W77" t="n">
-        <v>77.19</v>
+        <v>76.38</v>
       </c>
       <c r="X77" t="n">
-        <v>0.5115</v>
+        <v>0.4938</v>
       </c>
       <c r="Y77" t="n">
-        <v>26.694</v>
+        <v>26.194</v>
       </c>
       <c r="Z77" t="n">
-        <v>58.375</v>
+        <v>57.864</v>
       </c>
       <c r="AA77" t="n">
-        <v>8.84</v>
+        <v>8.667999999999999</v>
       </c>
       <c r="AB77" t="n">
-        <v>25.973</v>
+        <v>25.714</v>
       </c>
       <c r="AC77" t="n">
-        <v>16.256</v>
+        <v>16.199</v>
       </c>
       <c r="AD77" t="n">
-        <v>22.781</v>
+        <v>22.741</v>
       </c>
       <c r="AE77" t="n">
-        <v>8.99</v>
+        <v>9.06</v>
       </c>
       <c r="AF77" t="n">
-        <v>22.919</v>
+        <v>22.857</v>
       </c>
       <c r="AG77" t="n">
-        <v>15.16</v>
+        <v>14.855</v>
       </c>
       <c r="AH77" t="n">
-        <v>7.379</v>
+        <v>7.543</v>
       </c>
       <c r="AI77" t="n">
-        <v>2.977</v>
+        <v>3.012</v>
       </c>
       <c r="AJ77" t="n">
-        <v>20.412</v>
+        <v>20.233</v>
       </c>
       <c r="AK77" t="n">
-        <v>-6.4</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AL77" t="n">
-        <v>-0.5</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="78">
@@ -9746,22 +9746,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F78" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G78" t="b">
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>1285.267</v>
+        <v>1289.133</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.8228</v>
       </c>
       <c r="J78" t="n">
-        <v>1439.3</v>
+        <v>1440.1</v>
       </c>
       <c r="K78" t="n">
         <v>328</v>
@@ -9782,70 +9782,70 @@
         <v>325</v>
       </c>
       <c r="Q78" t="n">
-        <v>96.26600000000001</v>
+        <v>97.13</v>
       </c>
       <c r="R78" t="n">
-        <v>109.224</v>
+        <v>108.819</v>
       </c>
       <c r="S78" t="n">
-        <v>-12.958</v>
+        <v>-11.689</v>
       </c>
       <c r="T78" t="n">
-        <v>0.28693</v>
+        <v>0.29086</v>
       </c>
       <c r="U78" t="n">
-        <v>0.17091</v>
+        <v>0.17086</v>
       </c>
       <c r="V78" t="n">
-        <v>64.04000000000001</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="W78" t="n">
-        <v>72.51000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="X78" t="n">
-        <v>0.3182</v>
+        <v>0.3509</v>
       </c>
       <c r="Y78" t="n">
-        <v>22.384</v>
+        <v>22.453</v>
       </c>
       <c r="Z78" t="n">
-        <v>55.308</v>
+        <v>55.68</v>
       </c>
       <c r="AA78" t="n">
-        <v>5.192</v>
+        <v>5.509</v>
       </c>
       <c r="AB78" t="n">
-        <v>16.667</v>
+        <v>17.224</v>
       </c>
       <c r="AC78" t="n">
-        <v>14.076</v>
+        <v>14.059</v>
       </c>
       <c r="AD78" t="n">
-        <v>18.884</v>
+        <v>18.941</v>
       </c>
       <c r="AE78" t="n">
-        <v>8.460000000000001</v>
+        <v>8.747999999999999</v>
       </c>
       <c r="AF78" t="n">
-        <v>20.5</v>
+        <v>20.686</v>
       </c>
       <c r="AG78" t="n">
-        <v>10.914</v>
+        <v>11.053</v>
       </c>
       <c r="AH78" t="n">
-        <v>7.53</v>
+        <v>7.425</v>
       </c>
       <c r="AI78" t="n">
-        <v>2.813</v>
+        <v>2.873</v>
       </c>
       <c r="AJ78" t="n">
-        <v>16.803</v>
+        <v>16.854</v>
       </c>
       <c r="AK78" t="n">
         <v>-4.4</v>
       </c>
       <c r="AL78" t="n">
-        <v>-6</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="79">
@@ -9866,22 +9866,22 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G79" t="b">
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>1325.108</v>
+        <v>1322.293</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.1187</v>
+        <v>-2.0434</v>
       </c>
       <c r="J79" t="n">
-        <v>1429.6</v>
+        <v>1423.7</v>
       </c>
       <c r="K79" t="n">
         <v>285</v>
@@ -9902,70 +9902,70 @@
         <v>283</v>
       </c>
       <c r="Q79" t="n">
-        <v>111.414</v>
+        <v>111.589</v>
       </c>
       <c r="R79" t="n">
-        <v>118.37</v>
+        <v>119.303</v>
       </c>
       <c r="S79" t="n">
-        <v>-6.956</v>
+        <v>-7.714</v>
       </c>
       <c r="T79" t="n">
-        <v>0.3398</v>
+        <v>0.33873</v>
       </c>
       <c r="U79" t="n">
-        <v>0.16198</v>
+        <v>0.15874</v>
       </c>
       <c r="V79" t="n">
-        <v>77.51000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="W79" t="n">
-        <v>82.73</v>
+        <v>83.14</v>
       </c>
       <c r="X79" t="n">
-        <v>0.3075</v>
+        <v>0.2974</v>
       </c>
       <c r="Y79" t="n">
-        <v>26.469</v>
+        <v>26.713</v>
       </c>
       <c r="Z79" t="n">
-        <v>61.537</v>
+        <v>61.529</v>
       </c>
       <c r="AA79" t="n">
-        <v>10.901</v>
+        <v>10.993</v>
       </c>
       <c r="AB79" t="n">
-        <v>31.286</v>
+        <v>31.231</v>
       </c>
       <c r="AC79" t="n">
-        <v>13.674</v>
+        <v>13.703</v>
       </c>
       <c r="AD79" t="n">
-        <v>18.885</v>
+        <v>18.892</v>
       </c>
       <c r="AE79" t="n">
-        <v>11.233</v>
+        <v>11.157</v>
       </c>
       <c r="AF79" t="n">
-        <v>21.543</v>
+        <v>21.504</v>
       </c>
       <c r="AG79" t="n">
-        <v>14.193</v>
+        <v>14.299</v>
       </c>
       <c r="AH79" t="n">
-        <v>6.134</v>
+        <v>6.332</v>
       </c>
       <c r="AI79" t="n">
-        <v>2.879</v>
+        <v>2.901</v>
       </c>
       <c r="AJ79" t="n">
-        <v>18.646</v>
+        <v>18.536</v>
       </c>
       <c r="AK79" t="n">
-        <v>-4.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AL79" t="n">
-        <v>-3.9</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="80">
@@ -10346,22 +10346,22 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F83" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G83" t="b">
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>1463.777</v>
+        <v>1459.911</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.7166</v>
+        <v>-1.6671</v>
       </c>
       <c r="J83" t="n">
-        <v>1384</v>
+        <v>1380.7</v>
       </c>
       <c r="K83" t="n">
         <v>250</v>
@@ -10382,70 +10382,70 @@
         <v>255</v>
       </c>
       <c r="Q83" t="n">
-        <v>102.226</v>
+        <v>101.962</v>
       </c>
       <c r="R83" t="n">
-        <v>98.389</v>
+        <v>99.179</v>
       </c>
       <c r="S83" t="n">
-        <v>3.837</v>
+        <v>2.783</v>
       </c>
       <c r="T83" t="n">
-        <v>0.27326</v>
+        <v>0.272</v>
       </c>
       <c r="U83" t="n">
-        <v>0.16919</v>
+        <v>0.16794</v>
       </c>
       <c r="V83" t="n">
-        <v>67.69</v>
+        <v>67.73</v>
       </c>
       <c r="W83" t="n">
-        <v>65.31</v>
+        <v>66.02</v>
       </c>
       <c r="X83" t="n">
-        <v>0.5767</v>
+        <v>0.5455</v>
       </c>
       <c r="Y83" t="n">
-        <v>24.58</v>
+        <v>24.795</v>
       </c>
       <c r="Z83" t="n">
-        <v>56.471</v>
+        <v>56.67</v>
       </c>
       <c r="AA83" t="n">
-        <v>7.062</v>
+        <v>6.864</v>
       </c>
       <c r="AB83" t="n">
-        <v>20.263</v>
+        <v>19.852</v>
       </c>
       <c r="AC83" t="n">
-        <v>11.466</v>
+        <v>11.545</v>
       </c>
       <c r="AD83" t="n">
-        <v>17.051</v>
+        <v>17.159</v>
       </c>
       <c r="AE83" t="n">
-        <v>8.824</v>
+        <v>8.83</v>
       </c>
       <c r="AF83" t="n">
-        <v>24.048</v>
+        <v>24.216</v>
       </c>
       <c r="AG83" t="n">
-        <v>12.534</v>
+        <v>12.5</v>
       </c>
       <c r="AH83" t="n">
-        <v>6.942</v>
+        <v>7.023</v>
       </c>
       <c r="AI83" t="n">
-        <v>4.023</v>
+        <v>4.034</v>
       </c>
       <c r="AJ83" t="n">
-        <v>16.541</v>
+        <v>16.648</v>
       </c>
       <c r="AK83" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AL83" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="84">
@@ -10826,22 +10826,22 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F87" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G87" t="b">
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>1260.208</v>
+        <v>1258.741</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.9005</v>
+        <v>-1.7963</v>
       </c>
       <c r="J87" t="n">
-        <v>1389.8</v>
+        <v>1388.9</v>
       </c>
       <c r="K87" t="n">
         <v>333</v>
@@ -10862,70 +10862,70 @@
         <v>333</v>
       </c>
       <c r="Q87" t="n">
-        <v>101.072</v>
+        <v>100.805</v>
       </c>
       <c r="R87" t="n">
-        <v>111.983</v>
+        <v>111.713</v>
       </c>
       <c r="S87" t="n">
-        <v>-10.911</v>
+        <v>-10.909</v>
       </c>
       <c r="T87" t="n">
-        <v>0.31218</v>
+        <v>0.31301</v>
       </c>
       <c r="U87" t="n">
-        <v>0.17355</v>
+        <v>0.17321</v>
       </c>
       <c r="V87" t="n">
-        <v>65.19</v>
+        <v>65.06</v>
       </c>
       <c r="W87" t="n">
-        <v>72.77</v>
+        <v>72.62</v>
       </c>
       <c r="X87" t="n">
-        <v>0.2822</v>
+        <v>0.2727</v>
       </c>
       <c r="Y87" t="n">
-        <v>22.436</v>
+        <v>22.364</v>
       </c>
       <c r="Z87" t="n">
-        <v>55.527</v>
+        <v>55.5</v>
       </c>
       <c r="AA87" t="n">
-        <v>7.67</v>
+        <v>7.557</v>
       </c>
       <c r="AB87" t="n">
-        <v>25.104</v>
+        <v>25.045</v>
       </c>
       <c r="AC87" t="n">
-        <v>12.644</v>
+        <v>12.773</v>
       </c>
       <c r="AD87" t="n">
-        <v>18.007</v>
+        <v>18.239</v>
       </c>
       <c r="AE87" t="n">
-        <v>9.919</v>
+        <v>9.943</v>
       </c>
       <c r="AF87" t="n">
-        <v>21.6</v>
+        <v>21.58</v>
       </c>
       <c r="AG87" t="n">
-        <v>11.566</v>
+        <v>11.375</v>
       </c>
       <c r="AH87" t="n">
-        <v>4.776</v>
+        <v>4.795</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.541</v>
+        <v>1.466</v>
       </c>
       <c r="AJ87" t="n">
-        <v>17.448</v>
+        <v>17.455</v>
       </c>
       <c r="AK87" t="n">
-        <v>-8.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AL87" t="n">
-        <v>-2.1</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="88">
@@ -11075,7 +11075,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1585.017</v>
+        <v>1579.399</v>
       </c>
       <c r="I89" t="n">
         <v>-1.2688</v>
@@ -11186,22 +11186,22 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F90" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G90" t="b">
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>1393.014</v>
+        <v>1395.461</v>
       </c>
       <c r="I90" t="n">
-        <v>-3.8408</v>
+        <v>-3.6887</v>
       </c>
       <c r="J90" t="n">
-        <v>1434</v>
+        <v>1432.7</v>
       </c>
       <c r="K90" t="n">
         <v>264</v>
@@ -11222,70 +11222,70 @@
         <v>262</v>
       </c>
       <c r="Q90" t="n">
-        <v>108.812</v>
+        <v>109.155</v>
       </c>
       <c r="R90" t="n">
-        <v>112.478</v>
+        <v>111.674</v>
       </c>
       <c r="S90" t="n">
-        <v>-3.667</v>
+        <v>-2.518</v>
       </c>
       <c r="T90" t="n">
-        <v>0.29323</v>
+        <v>0.29586</v>
       </c>
       <c r="U90" t="n">
-        <v>0.15483</v>
+        <v>0.15331</v>
       </c>
       <c r="V90" t="n">
-        <v>77.15000000000001</v>
+        <v>76.95</v>
       </c>
       <c r="W90" t="n">
-        <v>79.67</v>
+        <v>78.75</v>
       </c>
       <c r="X90" t="n">
-        <v>0.4091</v>
+        <v>0.4393</v>
       </c>
       <c r="Y90" t="n">
-        <v>27.875</v>
+        <v>28.021</v>
       </c>
       <c r="Z90" t="n">
-        <v>61.193</v>
+        <v>61.318</v>
       </c>
       <c r="AA90" t="n">
-        <v>8.034000000000001</v>
+        <v>7.892</v>
       </c>
       <c r="AB90" t="n">
-        <v>23.477</v>
+        <v>23.234</v>
       </c>
       <c r="AC90" t="n">
-        <v>13.364</v>
+        <v>13.015</v>
       </c>
       <c r="AD90" t="n">
-        <v>18.557</v>
+        <v>18.082</v>
       </c>
       <c r="AE90" t="n">
-        <v>9.409000000000001</v>
+        <v>9.558999999999999</v>
       </c>
       <c r="AF90" t="n">
-        <v>22.602</v>
+        <v>22.67</v>
       </c>
       <c r="AG90" t="n">
-        <v>14.75</v>
+        <v>14.715</v>
       </c>
       <c r="AH90" t="n">
-        <v>7.602</v>
+        <v>7.517</v>
       </c>
       <c r="AI90" t="n">
-        <v>3.523</v>
+        <v>3.495</v>
       </c>
       <c r="AJ90" t="n">
-        <v>19.182</v>
+        <v>18.829</v>
       </c>
       <c r="AK90" t="n">
-        <v>-2.6</v>
+        <v>-0.8</v>
       </c>
       <c r="AL90" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="91">
@@ -11666,22 +11666,22 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F94" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G94" t="b">
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>1598.991</v>
+        <v>1606.048</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.7495</v>
+        <v>-1.2483</v>
       </c>
       <c r="J94" t="n">
-        <v>1651.4</v>
+        <v>1647.5</v>
       </c>
       <c r="K94" t="n">
         <v>71</v>
@@ -11702,70 +11702,70 @@
         <v>77</v>
       </c>
       <c r="Q94" t="n">
-        <v>110.621</v>
+        <v>110.656</v>
       </c>
       <c r="R94" t="n">
-        <v>107.194</v>
+        <v>107.457</v>
       </c>
       <c r="S94" t="n">
-        <v>3.427</v>
+        <v>3.2</v>
       </c>
       <c r="T94" t="n">
-        <v>0.32048</v>
+        <v>0.31773</v>
       </c>
       <c r="U94" t="n">
-        <v>0.15014</v>
+        <v>0.15094</v>
       </c>
       <c r="V94" t="n">
-        <v>79.73</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="W94" t="n">
-        <v>77.53</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="X94" t="n">
-        <v>0.5238</v>
+        <v>0.5392</v>
       </c>
       <c r="Y94" t="n">
-        <v>26.898</v>
+        <v>26.947</v>
       </c>
       <c r="Z94" t="n">
-        <v>62.687</v>
+        <v>62.509</v>
       </c>
       <c r="AA94" t="n">
-        <v>10.027</v>
+        <v>10.111</v>
       </c>
       <c r="AB94" t="n">
-        <v>31.646</v>
+        <v>31.509</v>
       </c>
       <c r="AC94" t="n">
-        <v>15.905</v>
+        <v>15.505</v>
       </c>
       <c r="AD94" t="n">
-        <v>22.02</v>
+        <v>21.558</v>
       </c>
       <c r="AE94" t="n">
-        <v>10.891</v>
+        <v>10.757</v>
       </c>
       <c r="AF94" t="n">
-        <v>22.803</v>
+        <v>22.861</v>
       </c>
       <c r="AG94" t="n">
-        <v>14.15</v>
+        <v>14.177</v>
       </c>
       <c r="AH94" t="n">
-        <v>7.844</v>
+        <v>7.699</v>
       </c>
       <c r="AI94" t="n">
-        <v>3.918</v>
+        <v>3.934</v>
       </c>
       <c r="AJ94" t="n">
-        <v>18.272</v>
+        <v>18.218</v>
       </c>
       <c r="AK94" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AL94" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="95">
@@ -11786,22 +11786,22 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F95" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G95" t="b">
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>1460.717</v>
+        <v>1456.701</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9714</v>
+        <v>1.1066</v>
       </c>
       <c r="J95" t="n">
-        <v>1502.1</v>
+        <v>1494.5</v>
       </c>
       <c r="K95" t="n">
         <v>168</v>
@@ -11822,70 +11822,70 @@
         <v>181</v>
       </c>
       <c r="Q95" t="n">
-        <v>103.917</v>
+        <v>105.16</v>
       </c>
       <c r="R95" t="n">
-        <v>102.396</v>
+        <v>103.587</v>
       </c>
       <c r="S95" t="n">
-        <v>1.521</v>
+        <v>1.573</v>
       </c>
       <c r="T95" t="n">
-        <v>0.31083</v>
+        <v>0.31826</v>
       </c>
       <c r="U95" t="n">
-        <v>0.16279</v>
+        <v>0.15883</v>
       </c>
       <c r="V95" t="n">
-        <v>67.33</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="W95" t="n">
-        <v>66.42</v>
+        <v>67.22</v>
       </c>
       <c r="X95" t="n">
-        <v>0.494</v>
+        <v>0.4762</v>
       </c>
       <c r="Y95" t="n">
-        <v>25.092</v>
+        <v>25.527</v>
       </c>
       <c r="Z95" t="n">
-        <v>58.568</v>
+        <v>59.275</v>
       </c>
       <c r="AA95" t="n">
-        <v>6.366</v>
+        <v>6.52</v>
       </c>
       <c r="AB95" t="n">
-        <v>22.238</v>
+        <v>22.564</v>
       </c>
       <c r="AC95" t="n">
-        <v>10.782</v>
+        <v>10.601</v>
       </c>
       <c r="AD95" t="n">
-        <v>15.478</v>
+        <v>15.117</v>
       </c>
       <c r="AE95" t="n">
-        <v>11.088</v>
+        <v>11.359</v>
       </c>
       <c r="AF95" t="n">
-        <v>24.19</v>
+        <v>23.945</v>
       </c>
       <c r="AG95" t="n">
-        <v>13.176</v>
+        <v>13.337</v>
       </c>
       <c r="AH95" t="n">
-        <v>6.936</v>
+        <v>6.784</v>
       </c>
       <c r="AI95" t="n">
-        <v>2.342</v>
+        <v>2.33</v>
       </c>
       <c r="AJ95" t="n">
-        <v>15.846</v>
+        <v>15.912</v>
       </c>
       <c r="AK95" t="n">
-        <v>-0.8</v>
+        <v>-2.2</v>
       </c>
       <c r="AL95" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="96">
@@ -12146,22 +12146,22 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F98" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G98" t="b">
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>1511.508</v>
+        <v>1540.445</v>
       </c>
       <c r="I98" t="n">
-        <v>-4.4633</v>
+        <v>-4.3148</v>
       </c>
       <c r="J98" t="n">
-        <v>1539</v>
+        <v>1537.4</v>
       </c>
       <c r="K98" t="n">
         <v>76</v>
@@ -12182,70 +12182,70 @@
         <v>86</v>
       </c>
       <c r="Q98" t="n">
-        <v>115.959</v>
+        <v>116.278</v>
       </c>
       <c r="R98" t="n">
-        <v>105.353</v>
+        <v>105.396</v>
       </c>
       <c r="S98" t="n">
-        <v>10.606</v>
+        <v>10.883</v>
       </c>
       <c r="T98" t="n">
-        <v>0.32323</v>
+        <v>0.32287</v>
       </c>
       <c r="U98" t="n">
-        <v>0.17821</v>
+        <v>0.17492</v>
       </c>
       <c r="V98" t="n">
-        <v>82.25</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="W98" t="n">
-        <v>74.63</v>
+        <v>75.11</v>
       </c>
       <c r="X98" t="n">
-        <v>0.5263</v>
+        <v>0.5589</v>
       </c>
       <c r="Y98" t="n">
-        <v>28.316</v>
+        <v>28.507</v>
       </c>
       <c r="Z98" t="n">
-        <v>59.895</v>
+        <v>60.352</v>
       </c>
       <c r="AA98" t="n">
-        <v>9.895</v>
+        <v>9.916</v>
       </c>
       <c r="AB98" t="n">
-        <v>27.825</v>
+        <v>27.766</v>
       </c>
       <c r="AC98" t="n">
-        <v>15.719</v>
+        <v>16.029</v>
       </c>
       <c r="AD98" t="n">
-        <v>21.737</v>
+        <v>22.127</v>
       </c>
       <c r="AE98" t="n">
-        <v>11.228</v>
+        <v>11.27</v>
       </c>
       <c r="AF98" t="n">
-        <v>23.526</v>
+        <v>23.643</v>
       </c>
       <c r="AG98" t="n">
-        <v>15.614</v>
+        <v>15.311</v>
       </c>
       <c r="AH98" t="n">
-        <v>7.246</v>
+        <v>7.388</v>
       </c>
       <c r="AI98" t="n">
-        <v>3.351</v>
+        <v>3.339</v>
       </c>
       <c r="AJ98" t="n">
-        <v>18.211</v>
+        <v>18.154</v>
       </c>
       <c r="AK98" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AL98" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="99">
@@ -12266,22 +12266,22 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F99" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G99" t="b">
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>1421.464</v>
+        <v>1423.665</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9558</v>
+        <v>0.8279</v>
       </c>
       <c r="J99" t="n">
-        <v>1439.2</v>
+        <v>1434.6</v>
       </c>
       <c r="K99" t="n">
         <v>265</v>
@@ -12302,70 +12302,70 @@
         <v>254</v>
       </c>
       <c r="Q99" t="n">
-        <v>109.018</v>
+        <v>109.603</v>
       </c>
       <c r="R99" t="n">
-        <v>110.725</v>
+        <v>111.302</v>
       </c>
       <c r="S99" t="n">
-        <v>-1.708</v>
+        <v>-1.699</v>
       </c>
       <c r="T99" t="n">
-        <v>0.30544</v>
+        <v>0.30437</v>
       </c>
       <c r="U99" t="n">
-        <v>0.1419</v>
+        <v>0.14327</v>
       </c>
       <c r="V99" t="n">
-        <v>79.41</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="W99" t="n">
-        <v>80.67</v>
+        <v>80.81</v>
       </c>
       <c r="X99" t="n">
-        <v>0.4898</v>
+        <v>0.5063</v>
       </c>
       <c r="Y99" t="n">
-        <v>26.095</v>
+        <v>26.045</v>
       </c>
       <c r="Z99" t="n">
-        <v>61.354</v>
+        <v>60.92</v>
       </c>
       <c r="AA99" t="n">
-        <v>9.395</v>
+        <v>9.375</v>
       </c>
       <c r="AB99" t="n">
-        <v>29.197</v>
+        <v>29.003</v>
       </c>
       <c r="AC99" t="n">
-        <v>17.823</v>
+        <v>18.075</v>
       </c>
       <c r="AD99" t="n">
-        <v>24.408</v>
+        <v>24.668</v>
       </c>
       <c r="AE99" t="n">
-        <v>9.558</v>
+        <v>9.526999999999999</v>
       </c>
       <c r="AF99" t="n">
-        <v>21.673</v>
+        <v>21.716</v>
       </c>
       <c r="AG99" t="n">
-        <v>10.429</v>
+        <v>10.428</v>
       </c>
       <c r="AH99" t="n">
-        <v>8.163</v>
+        <v>8.041</v>
       </c>
       <c r="AI99" t="n">
-        <v>3.633</v>
+        <v>3.58</v>
       </c>
       <c r="AJ99" t="n">
-        <v>19.673</v>
+        <v>19.918</v>
       </c>
       <c r="AK99" t="n">
-        <v>-0.4</v>
+        <v>-2.4</v>
       </c>
       <c r="AL99" t="n">
-        <v>-3.5</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="100">
@@ -12386,22 +12386,22 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F100" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G100" t="b">
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>1240.731</v>
+        <v>1246.951</v>
       </c>
       <c r="I100" t="n">
-        <v>-4.8986</v>
+        <v>-4.7199</v>
       </c>
       <c r="J100" t="n">
-        <v>1449.7</v>
+        <v>1444.4</v>
       </c>
       <c r="K100" t="n">
         <v>361</v>
@@ -12422,70 +12422,70 @@
         <v>361</v>
       </c>
       <c r="Q100" t="n">
-        <v>93.236</v>
+        <v>93.643</v>
       </c>
       <c r="R100" t="n">
-        <v>122.448</v>
+        <v>121.606</v>
       </c>
       <c r="S100" t="n">
-        <v>-29.212</v>
+        <v>-27.963</v>
       </c>
       <c r="T100" t="n">
-        <v>0.24216</v>
+        <v>0.2472</v>
       </c>
       <c r="U100" t="n">
-        <v>0.1906</v>
+        <v>0.19404</v>
       </c>
       <c r="V100" t="n">
-        <v>66.38</v>
+        <v>66.39</v>
       </c>
       <c r="W100" t="n">
-        <v>87.43000000000001</v>
+        <v>86.55</v>
       </c>
       <c r="X100" t="n">
-        <v>0.0352</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="Y100" t="n">
-        <v>23.874</v>
+        <v>23.816</v>
       </c>
       <c r="Z100" t="n">
-        <v>57.009</v>
+        <v>56.728</v>
       </c>
       <c r="AA100" t="n">
-        <v>7.156</v>
+        <v>7.231</v>
       </c>
       <c r="AB100" t="n">
-        <v>22.754</v>
+        <v>22.905</v>
       </c>
       <c r="AC100" t="n">
-        <v>11.48</v>
+        <v>11.483</v>
       </c>
       <c r="AD100" t="n">
-        <v>17.007</v>
+        <v>16.993</v>
       </c>
       <c r="AE100" t="n">
-        <v>6.844</v>
+        <v>7.007</v>
       </c>
       <c r="AF100" t="n">
-        <v>20.496</v>
+        <v>20.408</v>
       </c>
       <c r="AG100" t="n">
-        <v>9.83</v>
+        <v>10.15</v>
       </c>
       <c r="AH100" t="n">
-        <v>5.909</v>
+        <v>5.946</v>
       </c>
       <c r="AI100" t="n">
-        <v>2.402</v>
+        <v>2.565</v>
       </c>
       <c r="AJ100" t="n">
-        <v>17.791</v>
+        <v>17.85</v>
       </c>
       <c r="AK100" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="AL100" t="n">
         <v>-12.4</v>
-      </c>
-      <c r="AL100" t="n">
-        <v>-12.3</v>
       </c>
     </row>
     <row r="101">
@@ -12986,22 +12986,22 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F105" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G105" t="b">
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>1479.551</v>
+        <v>1475.095</v>
       </c>
       <c r="I105" t="n">
-        <v>-2.2429</v>
+        <v>-2.2794</v>
       </c>
       <c r="J105" t="n">
-        <v>1600.8</v>
+        <v>1606.5</v>
       </c>
       <c r="K105" t="n">
         <v>166</v>
@@ -13022,70 +13022,70 @@
         <v>168</v>
       </c>
       <c r="Q105" t="n">
-        <v>102.616</v>
+        <v>101.813</v>
       </c>
       <c r="R105" t="n">
-        <v>107.627</v>
+        <v>107.149</v>
       </c>
       <c r="S105" t="n">
-        <v>-5.011</v>
+        <v>-5.336</v>
       </c>
       <c r="T105" t="n">
-        <v>0.27321</v>
+        <v>0.26378</v>
       </c>
       <c r="U105" t="n">
-        <v>0.1736</v>
+        <v>0.17651</v>
       </c>
       <c r="V105" t="n">
-        <v>73.95999999999999</v>
+        <v>73.59</v>
       </c>
       <c r="W105" t="n">
-        <v>77.45</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="X105" t="n">
-        <v>0.3741</v>
+        <v>0.3621</v>
       </c>
       <c r="Y105" t="n">
-        <v>26.524</v>
+        <v>26.287</v>
       </c>
       <c r="Z105" t="n">
-        <v>60.231</v>
+        <v>59.788</v>
       </c>
       <c r="AA105" t="n">
-        <v>7.082</v>
+        <v>6.955</v>
       </c>
       <c r="AB105" t="n">
-        <v>20.007</v>
+        <v>19.861</v>
       </c>
       <c r="AC105" t="n">
-        <v>13.83</v>
+        <v>14.063</v>
       </c>
       <c r="AD105" t="n">
-        <v>19.68</v>
+        <v>19.886</v>
       </c>
       <c r="AE105" t="n">
-        <v>9.286</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AF105" t="n">
-        <v>25.054</v>
+        <v>25.404</v>
       </c>
       <c r="AG105" t="n">
-        <v>15.946</v>
+        <v>15.934</v>
       </c>
       <c r="AH105" t="n">
-        <v>6.034</v>
+        <v>6.053</v>
       </c>
       <c r="AI105" t="n">
-        <v>3.905</v>
+        <v>3.934</v>
       </c>
       <c r="AJ105" t="n">
-        <v>17.844</v>
+        <v>17.926</v>
       </c>
       <c r="AK105" t="n">
-        <v>-16.6</v>
+        <v>-15.6</v>
       </c>
       <c r="AL105" t="n">
-        <v>-14.7</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="106">
@@ -14186,22 +14186,22 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F115" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G115" t="b">
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>2083.138</v>
+        <v>2085.125</v>
       </c>
       <c r="I115" t="n">
-        <v>3.0302</v>
+        <v>2.67</v>
       </c>
       <c r="J115" t="n">
-        <v>1703.5</v>
+        <v>1703.4</v>
       </c>
       <c r="K115" t="n">
         <v>6</v>
@@ -14222,70 +14222,70 @@
         <v>7</v>
       </c>
       <c r="Q115" t="n">
-        <v>118.116</v>
+        <v>117.811</v>
       </c>
       <c r="R115" t="n">
-        <v>94.477</v>
+        <v>94.78</v>
       </c>
       <c r="S115" t="n">
-        <v>23.639</v>
+        <v>23.031</v>
       </c>
       <c r="T115" t="n">
-        <v>0.33823</v>
+        <v>0.34142</v>
       </c>
       <c r="U115" t="n">
-        <v>0.11882</v>
+        <v>0.11932</v>
       </c>
       <c r="V115" t="n">
-        <v>77.84999999999999</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="W115" t="n">
-        <v>62.27</v>
+        <v>62.35</v>
       </c>
       <c r="X115" t="n">
-        <v>0.8299</v>
+        <v>0.8354</v>
       </c>
       <c r="Y115" t="n">
-        <v>27.946</v>
+        <v>27.868</v>
       </c>
       <c r="Z115" t="n">
-        <v>62</v>
+        <v>62.02</v>
       </c>
       <c r="AA115" t="n">
-        <v>8.81</v>
+        <v>8.803000000000001</v>
       </c>
       <c r="AB115" t="n">
-        <v>25.639</v>
+        <v>25.724</v>
       </c>
       <c r="AC115" t="n">
-        <v>13.15</v>
+        <v>12.955</v>
       </c>
       <c r="AD115" t="n">
-        <v>16.952</v>
+        <v>16.724</v>
       </c>
       <c r="AE115" t="n">
-        <v>11.449</v>
+        <v>11.506</v>
       </c>
       <c r="AF115" t="n">
-        <v>22.381</v>
+        <v>22.193</v>
       </c>
       <c r="AG115" t="n">
-        <v>15.136</v>
+        <v>14.839</v>
       </c>
       <c r="AH115" t="n">
-        <v>7.762</v>
+        <v>7.906</v>
       </c>
       <c r="AI115" t="n">
-        <v>3.816</v>
+        <v>3.835</v>
       </c>
       <c r="AJ115" t="n">
-        <v>18.197</v>
+        <v>18.003</v>
       </c>
       <c r="AK115" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AL115" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="116">
@@ -15266,22 +15266,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F124" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G124" t="b">
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>1746.444</v>
+        <v>1752.663</v>
       </c>
       <c r="I124" t="n">
-        <v>-2.8012</v>
+        <v>-2.7312</v>
       </c>
       <c r="J124" t="n">
-        <v>1703.1</v>
+        <v>1695.9</v>
       </c>
       <c r="K124" t="n">
         <v>43</v>
@@ -15302,70 +15302,70 @@
         <v>41</v>
       </c>
       <c r="Q124" t="n">
-        <v>115.783</v>
+        <v>116.395</v>
       </c>
       <c r="R124" t="n">
-        <v>107.653</v>
+        <v>106.139</v>
       </c>
       <c r="S124" t="n">
-        <v>8.130000000000001</v>
+        <v>10.256</v>
       </c>
       <c r="T124" t="n">
-        <v>0.23698</v>
+        <v>0.23404</v>
       </c>
       <c r="U124" t="n">
-        <v>0.14018</v>
+        <v>0.14154</v>
       </c>
       <c r="V124" t="n">
-        <v>78.62</v>
+        <v>78.72</v>
       </c>
       <c r="W124" t="n">
-        <v>72.36</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="X124" t="n">
-        <v>0.5795</v>
+        <v>0.6042</v>
       </c>
       <c r="Y124" t="n">
-        <v>26.5</v>
+        <v>26.745</v>
       </c>
       <c r="Z124" t="n">
-        <v>56.648</v>
+        <v>56.54</v>
       </c>
       <c r="AA124" t="n">
-        <v>10.102</v>
+        <v>10.099</v>
       </c>
       <c r="AB124" t="n">
-        <v>29.273</v>
+        <v>28.981</v>
       </c>
       <c r="AC124" t="n">
-        <v>15.523</v>
+        <v>15.126</v>
       </c>
       <c r="AD124" t="n">
-        <v>19.784</v>
+        <v>19.346</v>
       </c>
       <c r="AE124" t="n">
-        <v>7.148</v>
+        <v>7.132</v>
       </c>
       <c r="AF124" t="n">
-        <v>22.58</v>
+        <v>22.985</v>
       </c>
       <c r="AG124" t="n">
-        <v>16.761</v>
+        <v>16.868</v>
       </c>
       <c r="AH124" t="n">
-        <v>4.682</v>
+        <v>4.616</v>
       </c>
       <c r="AI124" t="n">
-        <v>2.727</v>
+        <v>2.78</v>
       </c>
       <c r="AJ124" t="n">
-        <v>18.398</v>
+        <v>18.265</v>
       </c>
       <c r="AK124" t="n">
-        <v>-9.6</v>
+        <v>-7.2</v>
       </c>
       <c r="AL124" t="n">
-        <v>-2.4</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="125">
@@ -15635,7 +15635,7 @@
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>1821.402</v>
+        <v>1855.288</v>
       </c>
       <c r="I127" t="n">
         <v>4.8208</v>
@@ -16226,22 +16226,22 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F132" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G132" t="b">
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>1364.33</v>
+        <v>1361.102</v>
       </c>
       <c r="I132" t="n">
-        <v>-2.6708</v>
+        <v>-2.5239</v>
       </c>
       <c r="J132" t="n">
-        <v>1403.3</v>
+        <v>1399.1</v>
       </c>
       <c r="K132" t="n">
         <v>294</v>
@@ -16262,70 +16262,70 @@
         <v>296</v>
       </c>
       <c r="Q132" t="n">
-        <v>105.373</v>
+        <v>106.049</v>
       </c>
       <c r="R132" t="n">
-        <v>113.187</v>
+        <v>114.213</v>
       </c>
       <c r="S132" t="n">
-        <v>-7.814</v>
+        <v>-8.164</v>
       </c>
       <c r="T132" t="n">
-        <v>0.30223</v>
+        <v>0.30622</v>
       </c>
       <c r="U132" t="n">
-        <v>0.16987</v>
+        <v>0.16569</v>
       </c>
       <c r="V132" t="n">
-        <v>69.34999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="W132" t="n">
-        <v>74.77</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="X132" t="n">
-        <v>0.3523</v>
+        <v>0.3298</v>
       </c>
       <c r="Y132" t="n">
-        <v>24.727</v>
+        <v>24.811</v>
       </c>
       <c r="Z132" t="n">
-        <v>55.966</v>
+        <v>56.259</v>
       </c>
       <c r="AA132" t="n">
-        <v>6.602</v>
+        <v>6.691</v>
       </c>
       <c r="AB132" t="n">
-        <v>21.057</v>
+        <v>20.979</v>
       </c>
       <c r="AC132" t="n">
-        <v>13.295</v>
+        <v>13.286</v>
       </c>
       <c r="AD132" t="n">
-        <v>18.364</v>
+        <v>18.385</v>
       </c>
       <c r="AE132" t="n">
-        <v>9.489000000000001</v>
+        <v>9.657</v>
       </c>
       <c r="AF132" t="n">
-        <v>21.17</v>
+        <v>21.109</v>
       </c>
       <c r="AG132" t="n">
-        <v>11.102</v>
+        <v>11.087</v>
       </c>
       <c r="AH132" t="n">
-        <v>6.364</v>
+        <v>6.286</v>
       </c>
       <c r="AI132" t="n">
-        <v>2.773</v>
+        <v>2.813</v>
       </c>
       <c r="AJ132" t="n">
-        <v>19.648</v>
+        <v>19.507</v>
       </c>
       <c r="AK132" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AL132" t="n">
-        <v>-1.3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="133">
@@ -16466,22 +16466,22 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F134" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G134" t="b">
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>1505.523</v>
+        <v>1507.281</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3439</v>
+        <v>0.3812</v>
       </c>
       <c r="J134" t="n">
-        <v>1458.7</v>
+        <v>1453.2</v>
       </c>
       <c r="K134" t="n">
         <v>215</v>
@@ -16502,70 +16502,70 @@
         <v>207</v>
       </c>
       <c r="Q134" t="n">
-        <v>110.318</v>
+        <v>110.926</v>
       </c>
       <c r="R134" t="n">
-        <v>110.129</v>
+        <v>109.797</v>
       </c>
       <c r="S134" t="n">
-        <v>0.19</v>
+        <v>1.129</v>
       </c>
       <c r="T134" t="n">
-        <v>0.27281</v>
+        <v>0.27222</v>
       </c>
       <c r="U134" t="n">
-        <v>0.16</v>
+        <v>0.16352</v>
       </c>
       <c r="V134" t="n">
-        <v>74.02</v>
+        <v>74.66</v>
       </c>
       <c r="W134" t="n">
-        <v>74.04000000000001</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="X134" t="n">
-        <v>0.5266</v>
+        <v>0.5536</v>
       </c>
       <c r="Y134" t="n">
-        <v>25.534</v>
+        <v>25.846</v>
       </c>
       <c r="Z134" t="n">
-        <v>56.848</v>
+        <v>56.71</v>
       </c>
       <c r="AA134" t="n">
-        <v>8.856</v>
+        <v>8.612</v>
       </c>
       <c r="AB134" t="n">
-        <v>24.745</v>
+        <v>24.255</v>
       </c>
       <c r="AC134" t="n">
-        <v>14.099</v>
+        <v>14.357</v>
       </c>
       <c r="AD134" t="n">
-        <v>20.144</v>
+        <v>20.388</v>
       </c>
       <c r="AE134" t="n">
-        <v>9.387</v>
+        <v>9.438000000000001</v>
       </c>
       <c r="AF134" t="n">
-        <v>24.638</v>
+        <v>24.867</v>
       </c>
       <c r="AG134" t="n">
-        <v>12.522</v>
+        <v>12.629</v>
       </c>
       <c r="AH134" t="n">
-        <v>5.185</v>
+        <v>5.191</v>
       </c>
       <c r="AI134" t="n">
-        <v>4.008</v>
+        <v>4.032</v>
       </c>
       <c r="AJ134" t="n">
-        <v>18.879</v>
+        <v>18.838</v>
       </c>
       <c r="AK134" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AL134" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="135">
@@ -17186,22 +17186,22 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F140" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G140" t="b">
         <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>1392.119</v>
+        <v>1400.436</v>
       </c>
       <c r="I140" t="n">
-        <v>-2.3737</v>
+        <v>-2.1985</v>
       </c>
       <c r="J140" t="n">
-        <v>1566.7</v>
+        <v>1562.2</v>
       </c>
       <c r="K140" t="n">
         <v>229</v>
@@ -17222,67 +17222,67 @@
         <v>239</v>
       </c>
       <c r="Q140" t="n">
-        <v>98.05500000000001</v>
+        <v>99.501</v>
       </c>
       <c r="R140" t="n">
-        <v>109.646</v>
+        <v>110.346</v>
       </c>
       <c r="S140" t="n">
-        <v>-11.591</v>
+        <v>-10.845</v>
       </c>
       <c r="T140" t="n">
-        <v>0.32452</v>
+        <v>0.32756</v>
       </c>
       <c r="U140" t="n">
-        <v>0.18066</v>
+        <v>0.1795</v>
       </c>
       <c r="V140" t="n">
-        <v>65.34</v>
+        <v>66.39</v>
       </c>
       <c r="W140" t="n">
-        <v>73.29000000000001</v>
+        <v>73.83</v>
       </c>
       <c r="X140" t="n">
-        <v>0.2463</v>
+        <v>0.2857</v>
       </c>
       <c r="Y140" t="n">
-        <v>22.433</v>
+        <v>22.857</v>
       </c>
       <c r="Z140" t="n">
-        <v>55.744</v>
+        <v>56.082</v>
       </c>
       <c r="AA140" t="n">
-        <v>5.281</v>
+        <v>5.32</v>
       </c>
       <c r="AB140" t="n">
-        <v>17.357</v>
+        <v>17.755</v>
       </c>
       <c r="AC140" t="n">
-        <v>15.189</v>
+        <v>15.354</v>
       </c>
       <c r="AD140" t="n">
-        <v>21.124</v>
+        <v>21.129</v>
       </c>
       <c r="AE140" t="n">
-        <v>10.252</v>
+        <v>10.463</v>
       </c>
       <c r="AF140" t="n">
-        <v>21.135</v>
+        <v>21.245</v>
       </c>
       <c r="AG140" t="n">
-        <v>12.956</v>
+        <v>13.095</v>
       </c>
       <c r="AH140" t="n">
-        <v>6.733</v>
+        <v>6.49</v>
       </c>
       <c r="AI140" t="n">
-        <v>2.487</v>
+        <v>2.585</v>
       </c>
       <c r="AJ140" t="n">
-        <v>16.643</v>
+        <v>16.435</v>
       </c>
       <c r="AK140" t="n">
-        <v>-6.2</v>
+        <v>-3.8</v>
       </c>
       <c r="AL140" t="n">
         <v>-7.7</v>
@@ -18026,22 +18026,22 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F147" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G147" t="b">
         <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>1413.12</v>
+        <v>1414.144</v>
       </c>
       <c r="I147" t="n">
-        <v>2.527</v>
+        <v>2.4721</v>
       </c>
       <c r="J147" t="n">
-        <v>1384.3</v>
+        <v>1378.7</v>
       </c>
       <c r="K147" t="n">
         <v>210</v>
@@ -18062,70 +18062,70 @@
         <v>195</v>
       </c>
       <c r="Q147" t="n">
-        <v>108.421</v>
+        <v>109.351</v>
       </c>
       <c r="R147" t="n">
-        <v>103.892</v>
+        <v>104.933</v>
       </c>
       <c r="S147" t="n">
-        <v>4.529</v>
+        <v>4.419</v>
       </c>
       <c r="T147" t="n">
-        <v>0.31539</v>
+        <v>0.32002</v>
       </c>
       <c r="U147" t="n">
-        <v>0.18826</v>
+        <v>0.18848</v>
       </c>
       <c r="V147" t="n">
-        <v>74.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="W147" t="n">
-        <v>71.38</v>
+        <v>71.66</v>
       </c>
       <c r="X147" t="n">
-        <v>0.6812</v>
+        <v>0.6909</v>
       </c>
       <c r="Y147" t="n">
-        <v>27.606</v>
+        <v>27.546</v>
       </c>
       <c r="Z147" t="n">
-        <v>57.557</v>
+        <v>57.285</v>
       </c>
       <c r="AA147" t="n">
-        <v>6.142</v>
+        <v>6.134</v>
       </c>
       <c r="AB147" t="n">
-        <v>16.939</v>
+        <v>16.782</v>
       </c>
       <c r="AC147" t="n">
-        <v>12.742</v>
+        <v>13.075</v>
       </c>
       <c r="AD147" t="n">
-        <v>19.177</v>
+        <v>19.466</v>
       </c>
       <c r="AE147" t="n">
-        <v>10.516</v>
+        <v>10.64</v>
       </c>
       <c r="AF147" t="n">
-        <v>22.304</v>
+        <v>22.173</v>
       </c>
       <c r="AG147" t="n">
-        <v>13.887</v>
+        <v>13.845</v>
       </c>
       <c r="AH147" t="n">
-        <v>7.968</v>
+        <v>7.844</v>
       </c>
       <c r="AI147" t="n">
-        <v>5.243</v>
+        <v>5.331</v>
       </c>
       <c r="AJ147" t="n">
-        <v>17.614</v>
+        <v>17.618</v>
       </c>
       <c r="AK147" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AL147" t="n">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="148">
@@ -18746,22 +18746,22 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F153" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G153" t="b">
         <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>1391.962</v>
+        <v>1390.881</v>
       </c>
       <c r="I153" t="n">
-        <v>-4.4275</v>
+        <v>-4.2873</v>
       </c>
       <c r="J153" t="n">
-        <v>1548.6</v>
+        <v>1562.8</v>
       </c>
       <c r="K153" t="n">
         <v>306</v>
@@ -18782,67 +18782,67 @@
         <v>303</v>
       </c>
       <c r="Q153" t="n">
-        <v>99.747</v>
+        <v>100.15</v>
       </c>
       <c r="R153" t="n">
-        <v>114.413</v>
+        <v>115.522</v>
       </c>
       <c r="S153" t="n">
-        <v>-14.665</v>
+        <v>-15.372</v>
       </c>
       <c r="T153" t="n">
-        <v>0.28375</v>
+        <v>0.28544</v>
       </c>
       <c r="U153" t="n">
-        <v>0.19034</v>
+        <v>0.19015</v>
       </c>
       <c r="V153" t="n">
-        <v>66.83</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="W153" t="n">
-        <v>76.65000000000001</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="X153" t="n">
-        <v>0.2536</v>
+        <v>0.2299</v>
       </c>
       <c r="Y153" t="n">
-        <v>22.916</v>
+        <v>22.982</v>
       </c>
       <c r="Z153" t="n">
-        <v>54.62</v>
+        <v>54.612</v>
       </c>
       <c r="AA153" t="n">
-        <v>7.952</v>
+        <v>8.19</v>
       </c>
       <c r="AB153" t="n">
-        <v>25.771</v>
+        <v>25.887</v>
       </c>
       <c r="AC153" t="n">
-        <v>13.045</v>
+        <v>12.553</v>
       </c>
       <c r="AD153" t="n">
-        <v>19.516</v>
+        <v>18.757</v>
       </c>
       <c r="AE153" t="n">
-        <v>8.885999999999999</v>
+        <v>8.824</v>
       </c>
       <c r="AF153" t="n">
-        <v>22.43</v>
+        <v>21.992</v>
       </c>
       <c r="AG153" t="n">
-        <v>13.896</v>
+        <v>13.726</v>
       </c>
       <c r="AH153" t="n">
-        <v>3.95</v>
+        <v>3.967</v>
       </c>
       <c r="AI153" t="n">
-        <v>3.712</v>
+        <v>3.785</v>
       </c>
       <c r="AJ153" t="n">
-        <v>17.329</v>
+        <v>17.084</v>
       </c>
       <c r="AK153" t="n">
-        <v>-12.2</v>
+        <v>-11</v>
       </c>
       <c r="AL153" t="n">
         <v>-11.2</v>
@@ -19466,22 +19466,22 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F159" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G159" t="b">
         <v>1</v>
       </c>
       <c r="H159" t="n">
-        <v>1496.102</v>
+        <v>1517.593</v>
       </c>
       <c r="I159" t="n">
-        <v>-8.5199</v>
+        <v>-8.0067</v>
       </c>
       <c r="J159" t="n">
-        <v>1661.5</v>
+        <v>1658.7</v>
       </c>
       <c r="K159" t="n">
         <v>100</v>
@@ -19502,70 +19502,70 @@
         <v>109</v>
       </c>
       <c r="Q159" t="n">
-        <v>104.292</v>
+        <v>104.896</v>
       </c>
       <c r="R159" t="n">
-        <v>106.452</v>
+        <v>105.243</v>
       </c>
       <c r="S159" t="n">
-        <v>-2.16</v>
+        <v>-0.348</v>
       </c>
       <c r="T159" t="n">
-        <v>0.30071</v>
+        <v>0.29971</v>
       </c>
       <c r="U159" t="n">
-        <v>0.15675</v>
+        <v>0.15786</v>
       </c>
       <c r="V159" t="n">
-        <v>74.51000000000001</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="W159" t="n">
-        <v>76.25</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="X159" t="n">
-        <v>0.3393</v>
+        <v>0.376</v>
       </c>
       <c r="Y159" t="n">
-        <v>26.618</v>
+        <v>26.722</v>
       </c>
       <c r="Z159" t="n">
-        <v>60.979</v>
+        <v>61.054</v>
       </c>
       <c r="AA159" t="n">
-        <v>7.97</v>
+        <v>8.08</v>
       </c>
       <c r="AB159" t="n">
-        <v>25.291</v>
+        <v>25.471</v>
       </c>
       <c r="AC159" t="n">
-        <v>13.307</v>
+        <v>13.519</v>
       </c>
       <c r="AD159" t="n">
-        <v>19.93</v>
+        <v>19.949</v>
       </c>
       <c r="AE159" t="n">
-        <v>9.477</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AF159" t="n">
-        <v>21.848</v>
+        <v>22.154</v>
       </c>
       <c r="AG159" t="n">
-        <v>15.243</v>
+        <v>15.328</v>
       </c>
       <c r="AH159" t="n">
-        <v>9.304</v>
+        <v>9.500999999999999</v>
       </c>
       <c r="AI159" t="n">
-        <v>3.218</v>
+        <v>3.069</v>
       </c>
       <c r="AJ159" t="n">
-        <v>17.202</v>
+        <v>17.117</v>
       </c>
       <c r="AK159" t="n">
-        <v>-2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL159" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="160">
@@ -19706,22 +19706,22 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F161" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G161" t="b">
         <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>1584.372</v>
+        <v>1598.81</v>
       </c>
       <c r="I161" t="n">
-        <v>-8.259399999999999</v>
+        <v>-7.9559</v>
       </c>
       <c r="J161" t="n">
-        <v>1703.6</v>
+        <v>1712.3</v>
       </c>
       <c r="K161" t="n">
         <v>130</v>
@@ -19742,70 +19742,70 @@
         <v>146</v>
       </c>
       <c r="Q161" t="n">
-        <v>103.793</v>
+        <v>102.768</v>
       </c>
       <c r="R161" t="n">
-        <v>113.485</v>
+        <v>114.807</v>
       </c>
       <c r="S161" t="n">
-        <v>-9.691000000000001</v>
+        <v>-12.039</v>
       </c>
       <c r="T161" t="n">
-        <v>0.31831</v>
+        <v>0.3181</v>
       </c>
       <c r="U161" t="n">
-        <v>0.17894</v>
+        <v>0.17731</v>
       </c>
       <c r="V161" t="n">
-        <v>70.56</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="W161" t="n">
-        <v>76.97</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="X161" t="n">
-        <v>0.3732</v>
+        <v>0.3612</v>
       </c>
       <c r="Y161" t="n">
-        <v>23.321</v>
+        <v>23.01</v>
       </c>
       <c r="Z161" t="n">
-        <v>57.218</v>
+        <v>57.117</v>
       </c>
       <c r="AA161" t="n">
-        <v>8.409000000000001</v>
+        <v>8.475</v>
       </c>
       <c r="AB161" t="n">
-        <v>26.507</v>
+        <v>26.698</v>
       </c>
       <c r="AC161" t="n">
-        <v>15.512</v>
+        <v>14.939</v>
       </c>
       <c r="AD161" t="n">
-        <v>21.429</v>
+        <v>20.731</v>
       </c>
       <c r="AE161" t="n">
-        <v>10.775</v>
+        <v>10.704</v>
       </c>
       <c r="AF161" t="n">
-        <v>22.498</v>
+        <v>22.391</v>
       </c>
       <c r="AG161" t="n">
-        <v>10.577</v>
+        <v>10.511</v>
       </c>
       <c r="AH161" t="n">
-        <v>4.882</v>
+        <v>4.711</v>
       </c>
       <c r="AI161" t="n">
-        <v>2.929</v>
+        <v>2.869</v>
       </c>
       <c r="AJ161" t="n">
-        <v>18.234</v>
+        <v>18.069</v>
       </c>
       <c r="AK161" t="n">
-        <v>-5.6</v>
+        <v>-10</v>
       </c>
       <c r="AL161" t="n">
-        <v>-10.9</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="162">
@@ -20426,22 +20426,22 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F167" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G167" t="b">
         <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>1757.44</v>
+        <v>1773.834</v>
       </c>
       <c r="I167" t="n">
-        <v>13.1837</v>
+        <v>12.7945</v>
       </c>
       <c r="J167" t="n">
-        <v>1596.7</v>
+        <v>1607.1</v>
       </c>
       <c r="K167" t="n">
         <v>32</v>
@@ -20462,70 +20462,70 @@
         <v>30</v>
       </c>
       <c r="Q167" t="n">
-        <v>117.381</v>
+        <v>117.088</v>
       </c>
       <c r="R167" t="n">
-        <v>99.64</v>
+        <v>99.899</v>
       </c>
       <c r="S167" t="n">
-        <v>17.741</v>
+        <v>17.189</v>
       </c>
       <c r="T167" t="n">
-        <v>0.30629</v>
+        <v>0.30613</v>
       </c>
       <c r="U167" t="n">
-        <v>0.15908</v>
+        <v>0.16236</v>
       </c>
       <c r="V167" t="n">
-        <v>82.58</v>
+        <v>82.42</v>
       </c>
       <c r="W167" t="n">
-        <v>69.78</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="X167" t="n">
-        <v>0.7964</v>
+        <v>0.803</v>
       </c>
       <c r="Y167" t="n">
-        <v>30.425</v>
+        <v>30.284</v>
       </c>
       <c r="Z167" t="n">
-        <v>60.239</v>
+        <v>60.12</v>
       </c>
       <c r="AA167" t="n">
-        <v>6.525</v>
+        <v>6.731</v>
       </c>
       <c r="AB167" t="n">
-        <v>19.152</v>
+        <v>19.084</v>
       </c>
       <c r="AC167" t="n">
-        <v>15.207</v>
+        <v>15.12</v>
       </c>
       <c r="AD167" t="n">
-        <v>22.512</v>
+        <v>22.368</v>
       </c>
       <c r="AE167" t="n">
-        <v>10.964</v>
+        <v>10.982</v>
       </c>
       <c r="AF167" t="n">
-        <v>24.613</v>
+        <v>24.672</v>
       </c>
       <c r="AG167" t="n">
-        <v>16.255</v>
+        <v>16.453</v>
       </c>
       <c r="AH167" t="n">
-        <v>8.130000000000001</v>
+        <v>7.985</v>
       </c>
       <c r="AI167" t="n">
-        <v>3.321</v>
+        <v>3.343</v>
       </c>
       <c r="AJ167" t="n">
-        <v>15.545</v>
+        <v>15.177</v>
       </c>
       <c r="AK167" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AL167" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AL167" t="n">
-        <v>6.3</v>
       </c>
     </row>
     <row r="168">
@@ -20906,22 +20906,22 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F171" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G171" t="b">
         <v>1</v>
       </c>
       <c r="H171" t="n">
-        <v>1623.125</v>
+        <v>1616.906</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0378</v>
+        <v>0.1308</v>
       </c>
       <c r="J171" t="n">
-        <v>1677.8</v>
+        <v>1678.8</v>
       </c>
       <c r="K171" t="n">
         <v>64</v>
@@ -20942,70 +20942,70 @@
         <v>68</v>
       </c>
       <c r="Q171" t="n">
-        <v>111.875</v>
+        <v>109.881</v>
       </c>
       <c r="R171" t="n">
-        <v>107.719</v>
+        <v>108.204</v>
       </c>
       <c r="S171" t="n">
-        <v>4.156</v>
+        <v>1.677</v>
       </c>
       <c r="T171" t="n">
-        <v>0.24224</v>
+        <v>0.24826</v>
       </c>
       <c r="U171" t="n">
-        <v>0.15417</v>
+        <v>0.15663</v>
       </c>
       <c r="V171" t="n">
-        <v>71.13</v>
+        <v>69.94</v>
       </c>
       <c r="W171" t="n">
-        <v>68.27</v>
+        <v>68.61</v>
       </c>
       <c r="X171" t="n">
-        <v>0.4898</v>
+        <v>0.4608</v>
       </c>
       <c r="Y171" t="n">
-        <v>24.408</v>
+        <v>24.011</v>
       </c>
       <c r="Z171" t="n">
-        <v>52.789</v>
+        <v>52.835</v>
       </c>
       <c r="AA171" t="n">
-        <v>8.837</v>
+        <v>8.621</v>
       </c>
       <c r="AB171" t="n">
-        <v>25.211</v>
+        <v>25.049</v>
       </c>
       <c r="AC171" t="n">
-        <v>13.476</v>
+        <v>13.299</v>
       </c>
       <c r="AD171" t="n">
-        <v>19.272</v>
+        <v>19.077</v>
       </c>
       <c r="AE171" t="n">
-        <v>7.374</v>
+        <v>7.473</v>
       </c>
       <c r="AF171" t="n">
-        <v>21.776</v>
+        <v>21.563</v>
       </c>
       <c r="AG171" t="n">
-        <v>17.707</v>
+        <v>17.092</v>
       </c>
       <c r="AH171" t="n">
-        <v>6.551</v>
+        <v>6.469</v>
       </c>
       <c r="AI171" t="n">
-        <v>2.823</v>
+        <v>2.666</v>
       </c>
       <c r="AJ171" t="n">
-        <v>14.735</v>
+        <v>14.699</v>
       </c>
       <c r="AK171" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="AL171" t="n">
-        <v>-0.8</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="172">
@@ -21386,22 +21386,22 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F175" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G175" t="b">
         <v>1</v>
       </c>
       <c r="H175" t="n">
-        <v>1231.558</v>
+        <v>1229.143</v>
       </c>
       <c r="I175" t="n">
-        <v>-4.6347</v>
+        <v>-4.4885</v>
       </c>
       <c r="J175" t="n">
-        <v>1439.3</v>
+        <v>1433.1</v>
       </c>
       <c r="K175" t="n">
         <v>356</v>
@@ -21422,70 +21422,70 @@
         <v>357</v>
       </c>
       <c r="Q175" t="n">
-        <v>93.256</v>
+        <v>93.104</v>
       </c>
       <c r="R175" t="n">
-        <v>117.527</v>
+        <v>117.641</v>
       </c>
       <c r="S175" t="n">
-        <v>-24.271</v>
+        <v>-24.536</v>
       </c>
       <c r="T175" t="n">
-        <v>0.29174</v>
+        <v>0.29768</v>
       </c>
       <c r="U175" t="n">
-        <v>0.17676</v>
+        <v>0.17498</v>
       </c>
       <c r="V175" t="n">
-        <v>67.22</v>
+        <v>66.95</v>
       </c>
       <c r="W175" t="n">
-        <v>84.88</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="X175" t="n">
-        <v>0.0366</v>
+        <v>0.0354</v>
       </c>
       <c r="Y175" t="n">
-        <v>24.612</v>
+        <v>24.465</v>
       </c>
       <c r="Z175" t="n">
-        <v>60.359</v>
+        <v>60.48</v>
       </c>
       <c r="AA175" t="n">
-        <v>6.363</v>
+        <v>6.318</v>
       </c>
       <c r="AB175" t="n">
-        <v>22.238</v>
+        <v>22.268</v>
       </c>
       <c r="AC175" t="n">
-        <v>11.63</v>
+        <v>11.702</v>
       </c>
       <c r="AD175" t="n">
-        <v>17.524</v>
+        <v>17.707</v>
       </c>
       <c r="AE175" t="n">
-        <v>8.673999999999999</v>
+        <v>8.898999999999999</v>
       </c>
       <c r="AF175" t="n">
-        <v>20.89</v>
+        <v>20.803</v>
       </c>
       <c r="AG175" t="n">
-        <v>11.425</v>
+        <v>11.298</v>
       </c>
       <c r="AH175" t="n">
-        <v>6.282</v>
+        <v>6.374</v>
       </c>
       <c r="AI175" t="n">
-        <v>3.11</v>
+        <v>3.152</v>
       </c>
       <c r="AJ175" t="n">
-        <v>16.879</v>
+        <v>16.758</v>
       </c>
       <c r="AK175" t="n">
-        <v>-25.8</v>
+        <v>-22.2</v>
       </c>
       <c r="AL175" t="n">
-        <v>-20.5</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="176">
@@ -23066,22 +23066,22 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F189" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G189" t="b">
         <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>1429.382</v>
+        <v>1436.316</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4079</v>
+        <v>0.2848</v>
       </c>
       <c r="J189" t="n">
-        <v>1427.2</v>
+        <v>1430.5</v>
       </c>
       <c r="K189" t="n">
         <v>178</v>
@@ -23102,70 +23102,70 @@
         <v>189</v>
       </c>
       <c r="Q189" t="n">
-        <v>111.782</v>
+        <v>111.931</v>
       </c>
       <c r="R189" t="n">
-        <v>108.535</v>
+        <v>108.718</v>
       </c>
       <c r="S189" t="n">
-        <v>3.247</v>
+        <v>3.213</v>
       </c>
       <c r="T189" t="n">
-        <v>0.32211</v>
+        <v>0.31995</v>
       </c>
       <c r="U189" t="n">
-        <v>0.16153</v>
+        <v>0.15985</v>
       </c>
       <c r="V189" t="n">
-        <v>80.01000000000001</v>
+        <v>80.11</v>
       </c>
       <c r="W189" t="n">
-        <v>77.86</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="X189" t="n">
-        <v>0.5303</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Y189" t="n">
-        <v>27.732</v>
+        <v>27.736</v>
       </c>
       <c r="Z189" t="n">
-        <v>60.869</v>
+        <v>60.863</v>
       </c>
       <c r="AA189" t="n">
-        <v>9.071</v>
+        <v>9.068</v>
       </c>
       <c r="AB189" t="n">
-        <v>27.545</v>
+        <v>27.59</v>
       </c>
       <c r="AC189" t="n">
-        <v>15.47</v>
+        <v>15.575</v>
       </c>
       <c r="AD189" t="n">
-        <v>21.379</v>
+        <v>21.767</v>
       </c>
       <c r="AE189" t="n">
-        <v>10.061</v>
+        <v>10.112</v>
       </c>
       <c r="AF189" t="n">
-        <v>21.323</v>
+        <v>21.689</v>
       </c>
       <c r="AG189" t="n">
-        <v>15.096</v>
+        <v>15.276</v>
       </c>
       <c r="AH189" t="n">
-        <v>8.529999999999999</v>
+        <v>8.468999999999999</v>
       </c>
       <c r="AI189" t="n">
-        <v>3.485</v>
+        <v>3.609</v>
       </c>
       <c r="AJ189" t="n">
-        <v>18.763</v>
+        <v>18.587</v>
       </c>
       <c r="AK189" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AL189" t="n">
-        <v>-0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="190">
@@ -24146,22 +24146,22 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F198" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G198" t="b">
         <v>1</v>
       </c>
       <c r="H198" t="n">
-        <v>1846.973</v>
+        <v>1825.295</v>
       </c>
       <c r="I198" t="n">
-        <v>4.3818</v>
+        <v>4.1386</v>
       </c>
       <c r="J198" t="n">
-        <v>1589.8</v>
+        <v>1590</v>
       </c>
       <c r="K198" t="n">
         <v>46</v>
@@ -24182,70 +24182,70 @@
         <v>42</v>
       </c>
       <c r="Q198" t="n">
-        <v>114.726</v>
+        <v>114.161</v>
       </c>
       <c r="R198" t="n">
-        <v>100.976</v>
+        <v>101.465</v>
       </c>
       <c r="S198" t="n">
-        <v>13.751</v>
+        <v>12.697</v>
       </c>
       <c r="T198" t="n">
-        <v>0.2694</v>
+        <v>0.27207</v>
       </c>
       <c r="U198" t="n">
-        <v>0.14302</v>
+        <v>0.14478</v>
       </c>
       <c r="V198" t="n">
-        <v>80.08</v>
+        <v>79.8</v>
       </c>
       <c r="W198" t="n">
-        <v>70.53</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="X198" t="n">
-        <v>0.7531</v>
+        <v>0.7159</v>
       </c>
       <c r="Y198" t="n">
-        <v>27.422</v>
+        <v>27.489</v>
       </c>
       <c r="Z198" t="n">
-        <v>59.66</v>
+        <v>59.705</v>
       </c>
       <c r="AA198" t="n">
-        <v>9.093</v>
+        <v>8.965999999999999</v>
       </c>
       <c r="AB198" t="n">
-        <v>25.152</v>
+        <v>25.17</v>
       </c>
       <c r="AC198" t="n">
-        <v>16.146</v>
+        <v>15.852</v>
       </c>
       <c r="AD198" t="n">
-        <v>21.961</v>
+        <v>21.705</v>
       </c>
       <c r="AE198" t="n">
-        <v>9.308999999999999</v>
+        <v>9.284000000000001</v>
       </c>
       <c r="AF198" t="n">
-        <v>24.861</v>
+        <v>24.557</v>
       </c>
       <c r="AG198" t="n">
-        <v>14.199</v>
+        <v>14.114</v>
       </c>
       <c r="AH198" t="n">
-        <v>7.422</v>
+        <v>7.852</v>
       </c>
       <c r="AI198" t="n">
-        <v>2.788</v>
+        <v>2.795</v>
       </c>
       <c r="AJ198" t="n">
-        <v>17.365</v>
+        <v>17.523</v>
       </c>
       <c r="AK198" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AL198" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="199">
@@ -25226,22 +25226,22 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F207" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G207" t="b">
         <v>1</v>
       </c>
       <c r="H207" t="n">
-        <v>1302.227</v>
+        <v>1299.893</v>
       </c>
       <c r="I207" t="n">
-        <v>-4.2731</v>
+        <v>-4.0745</v>
       </c>
       <c r="J207" t="n">
-        <v>1462.9</v>
+        <v>1458.7</v>
       </c>
       <c r="K207" t="n">
         <v>334</v>
@@ -25262,70 +25262,70 @@
         <v>336</v>
       </c>
       <c r="Q207" t="n">
-        <v>105.672</v>
+        <v>106.063</v>
       </c>
       <c r="R207" t="n">
-        <v>122.677</v>
+        <v>122.64</v>
       </c>
       <c r="S207" t="n">
-        <v>-17.005</v>
+        <v>-16.577</v>
       </c>
       <c r="T207" t="n">
-        <v>0.26021</v>
+        <v>0.25871</v>
       </c>
       <c r="U207" t="n">
-        <v>0.17703</v>
+        <v>0.17255</v>
       </c>
       <c r="V207" t="n">
-        <v>76.70999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="W207" t="n">
-        <v>89.41</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X207" t="n">
-        <v>0.1708</v>
+        <v>0.1652</v>
       </c>
       <c r="Y207" t="n">
-        <v>26.286</v>
+        <v>26.414</v>
       </c>
       <c r="Z207" t="n">
-        <v>59.86</v>
+        <v>60.193</v>
       </c>
       <c r="AA207" t="n">
-        <v>10.919</v>
+        <v>10.842</v>
       </c>
       <c r="AB207" t="n">
-        <v>30.876</v>
+        <v>31.101</v>
       </c>
       <c r="AC207" t="n">
-        <v>13.224</v>
+        <v>13.532</v>
       </c>
       <c r="AD207" t="n">
-        <v>17.124</v>
+        <v>17.358</v>
       </c>
       <c r="AE207" t="n">
-        <v>7.547</v>
+        <v>7.487</v>
       </c>
       <c r="AF207" t="n">
-        <v>21.345</v>
+        <v>21.313</v>
       </c>
       <c r="AG207" t="n">
-        <v>13.457</v>
+        <v>13.329</v>
       </c>
       <c r="AH207" t="n">
-        <v>4.55</v>
+        <v>4.662</v>
       </c>
       <c r="AI207" t="n">
-        <v>1.472</v>
+        <v>1.388</v>
       </c>
       <c r="AJ207" t="n">
-        <v>18.286</v>
+        <v>18.33</v>
       </c>
       <c r="AK207" t="n">
-        <v>-6.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AL207" t="n">
-        <v>-6.4</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="208">
@@ -25346,22 +25346,22 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F208" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G208" t="b">
         <v>1</v>
       </c>
       <c r="H208" t="n">
-        <v>1548.194</v>
+        <v>1537.165</v>
       </c>
       <c r="I208" t="n">
-        <v>-5.5956</v>
+        <v>-5.3054</v>
       </c>
       <c r="J208" t="n">
-        <v>1512.2</v>
+        <v>1505.6</v>
       </c>
       <c r="K208" t="n">
         <v>139</v>
@@ -25382,70 +25382,70 @@
         <v>143</v>
       </c>
       <c r="Q208" t="n">
-        <v>104.103</v>
+        <v>104.137</v>
       </c>
       <c r="R208" t="n">
-        <v>102.18</v>
+        <v>102.053</v>
       </c>
       <c r="S208" t="n">
-        <v>1.923</v>
+        <v>2.085</v>
       </c>
       <c r="T208" t="n">
-        <v>0.33567</v>
+        <v>0.33668</v>
       </c>
       <c r="U208" t="n">
-        <v>0.15696</v>
+        <v>0.15704</v>
       </c>
       <c r="V208" t="n">
-        <v>68.61</v>
+        <v>68.39</v>
       </c>
       <c r="W208" t="n">
-        <v>67.61</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="X208" t="n">
-        <v>0.5426</v>
+        <v>0.5578</v>
       </c>
       <c r="Y208" t="n">
-        <v>23.874</v>
+        <v>23.816</v>
       </c>
       <c r="Z208" t="n">
-        <v>57.22</v>
+        <v>57.027</v>
       </c>
       <c r="AA208" t="n">
-        <v>5.402</v>
+        <v>5.327</v>
       </c>
       <c r="AB208" t="n">
-        <v>18.513</v>
+        <v>18.415</v>
       </c>
       <c r="AC208" t="n">
-        <v>15.465</v>
+        <v>15.435</v>
       </c>
       <c r="AD208" t="n">
-        <v>21.893</v>
+        <v>22.02</v>
       </c>
       <c r="AE208" t="n">
-        <v>11.041</v>
+        <v>11.116</v>
       </c>
       <c r="AF208" t="n">
-        <v>21.567</v>
+        <v>21.619</v>
       </c>
       <c r="AG208" t="n">
-        <v>11.88</v>
+        <v>11.565</v>
       </c>
       <c r="AH208" t="n">
-        <v>8.794</v>
+        <v>8.878</v>
       </c>
       <c r="AI208" t="n">
-        <v>4.111</v>
+        <v>4.184</v>
       </c>
       <c r="AJ208" t="n">
-        <v>19.272</v>
+        <v>19.211</v>
       </c>
       <c r="AK208" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AL208" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="209">
@@ -25826,22 +25826,22 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F212" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G212" t="b">
         <v>1</v>
       </c>
       <c r="H212" t="n">
-        <v>1595.51</v>
+        <v>1591.668</v>
       </c>
       <c r="I212" t="n">
-        <v>-5.1956</v>
+        <v>-4.6981</v>
       </c>
       <c r="J212" t="n">
-        <v>1692.6</v>
+        <v>1705.7</v>
       </c>
       <c r="K212" t="n">
         <v>68</v>
@@ -25862,70 +25862,70 @@
         <v>72</v>
       </c>
       <c r="Q212" t="n">
-        <v>110.125</v>
+        <v>110.626</v>
       </c>
       <c r="R212" t="n">
-        <v>108.881</v>
+        <v>109.755</v>
       </c>
       <c r="S212" t="n">
-        <v>1.244</v>
+        <v>0.872</v>
       </c>
       <c r="T212" t="n">
-        <v>0.27299</v>
+        <v>0.27194</v>
       </c>
       <c r="U212" t="n">
-        <v>0.12755</v>
+        <v>0.1268</v>
       </c>
       <c r="V212" t="n">
-        <v>73.56999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="W212" t="n">
-        <v>72.36</v>
+        <v>72.37</v>
       </c>
       <c r="X212" t="n">
-        <v>0.4545</v>
+        <v>0.4288</v>
       </c>
       <c r="Y212" t="n">
-        <v>26.261</v>
+        <v>26.177</v>
       </c>
       <c r="Z212" t="n">
-        <v>57.534</v>
+        <v>57.093</v>
       </c>
       <c r="AA212" t="n">
-        <v>6.284</v>
+        <v>6.34</v>
       </c>
       <c r="AB212" t="n">
-        <v>19.511</v>
+        <v>19.397</v>
       </c>
       <c r="AC212" t="n">
-        <v>14.761</v>
+        <v>14.661</v>
       </c>
       <c r="AD212" t="n">
-        <v>19.807</v>
+        <v>19.553</v>
       </c>
       <c r="AE212" t="n">
-        <v>8.034000000000001</v>
+        <v>7.826</v>
       </c>
       <c r="AF212" t="n">
-        <v>21.034</v>
+        <v>20.598</v>
       </c>
       <c r="AG212" t="n">
-        <v>17.102</v>
+        <v>16.969</v>
       </c>
       <c r="AH212" t="n">
-        <v>5.852</v>
+        <v>5.846</v>
       </c>
       <c r="AI212" t="n">
-        <v>3.932</v>
+        <v>3.858</v>
       </c>
       <c r="AJ212" t="n">
-        <v>17.33</v>
+        <v>17.232</v>
       </c>
       <c r="AK212" t="n">
-        <v>-4.4</v>
+        <v>-2.8</v>
       </c>
       <c r="AL212" t="n">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="213">
@@ -26066,22 +26066,22 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F214" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G214" t="b">
         <v>1</v>
       </c>
       <c r="H214" t="n">
-        <v>1575.751</v>
+        <v>1568.181</v>
       </c>
       <c r="I214" t="n">
-        <v>1.2713</v>
+        <v>1.0171</v>
       </c>
       <c r="J214" t="n">
-        <v>1649.1</v>
+        <v>1650.9</v>
       </c>
       <c r="K214" t="n">
         <v>84</v>
@@ -26102,70 +26102,70 @@
         <v>89</v>
       </c>
       <c r="Q214" t="n">
-        <v>109.705</v>
+        <v>110.024</v>
       </c>
       <c r="R214" t="n">
-        <v>110.097</v>
+        <v>111.147</v>
       </c>
       <c r="S214" t="n">
-        <v>-0.392</v>
+        <v>-1.123</v>
       </c>
       <c r="T214" t="n">
-        <v>0.28018</v>
+        <v>0.28102</v>
       </c>
       <c r="U214" t="n">
-        <v>0.16363</v>
+        <v>0.1626</v>
       </c>
       <c r="V214" t="n">
-        <v>74.86</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="W214" t="n">
-        <v>75.14</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="X214" t="n">
-        <v>0.4571</v>
+        <v>0.4269</v>
       </c>
       <c r="Y214" t="n">
-        <v>26.182</v>
+        <v>25.908</v>
       </c>
       <c r="Z214" t="n">
-        <v>58.152</v>
+        <v>57.798</v>
       </c>
       <c r="AA214" t="n">
-        <v>8.98</v>
+        <v>8.933999999999999</v>
       </c>
       <c r="AB214" t="n">
-        <v>25.034</v>
+        <v>24.89</v>
       </c>
       <c r="AC214" t="n">
-        <v>13.518</v>
+        <v>13.933</v>
       </c>
       <c r="AD214" t="n">
-        <v>19.586</v>
+        <v>19.856</v>
       </c>
       <c r="AE214" t="n">
-        <v>9.845000000000001</v>
+        <v>9.803000000000001</v>
       </c>
       <c r="AF214" t="n">
-        <v>24.421</v>
+        <v>24.266</v>
       </c>
       <c r="AG214" t="n">
-        <v>12.421</v>
+        <v>12.314</v>
       </c>
       <c r="AH214" t="n">
-        <v>4.493</v>
+        <v>4.445</v>
       </c>
       <c r="AI214" t="n">
-        <v>2.104</v>
+        <v>2.179</v>
       </c>
       <c r="AJ214" t="n">
-        <v>17.593</v>
+        <v>17.463</v>
       </c>
       <c r="AK214" t="n">
         <v>-7.2</v>
       </c>
       <c r="AL214" t="n">
-        <v>-6.3</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="215">
@@ -26186,22 +26186,22 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F215" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G215" t="b">
         <v>1</v>
       </c>
       <c r="H215" t="n">
-        <v>1510.449</v>
+        <v>1503.515</v>
       </c>
       <c r="I215" t="n">
-        <v>2.8359</v>
+        <v>2.6449</v>
       </c>
       <c r="J215" t="n">
-        <v>1490.2</v>
+        <v>1489.4</v>
       </c>
       <c r="K215" t="n">
         <v>161</v>
@@ -26222,70 +26222,70 @@
         <v>167</v>
       </c>
       <c r="Q215" t="n">
-        <v>113.582</v>
+        <v>113.518</v>
       </c>
       <c r="R215" t="n">
-        <v>115.621</v>
+        <v>115.465</v>
       </c>
       <c r="S215" t="n">
-        <v>-2.039</v>
+        <v>-1.947</v>
       </c>
       <c r="T215" t="n">
-        <v>0.29114</v>
+        <v>0.29379</v>
       </c>
       <c r="U215" t="n">
-        <v>0.14133</v>
+        <v>0.14015</v>
       </c>
       <c r="V215" t="n">
-        <v>81.58</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="W215" t="n">
-        <v>82.86</v>
+        <v>82.83</v>
       </c>
       <c r="X215" t="n">
-        <v>0.4948</v>
+        <v>0.4792</v>
       </c>
       <c r="Y215" t="n">
-        <v>28.427</v>
+        <v>28.508</v>
       </c>
       <c r="Z215" t="n">
-        <v>60.397</v>
+        <v>60.999</v>
       </c>
       <c r="AA215" t="n">
-        <v>7.031</v>
+        <v>7.25</v>
       </c>
       <c r="AB215" t="n">
-        <v>20.306</v>
+        <v>20.839</v>
       </c>
       <c r="AC215" t="n">
-        <v>17.693</v>
+        <v>17.337</v>
       </c>
       <c r="AD215" t="n">
-        <v>23.55</v>
+        <v>23.085</v>
       </c>
       <c r="AE215" t="n">
-        <v>9.087999999999999</v>
+        <v>9.346</v>
       </c>
       <c r="AF215" t="n">
-        <v>21.901</v>
+        <v>22.154</v>
       </c>
       <c r="AG215" t="n">
-        <v>15.658</v>
+        <v>15.649</v>
       </c>
       <c r="AH215" t="n">
-        <v>7.232</v>
+        <v>7.172</v>
       </c>
       <c r="AI215" t="n">
-        <v>3.748</v>
+        <v>3.693</v>
       </c>
       <c r="AJ215" t="n">
-        <v>15.118</v>
+        <v>15.522</v>
       </c>
       <c r="AK215" t="n">
-        <v>-2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL215" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="216">
@@ -26426,22 +26426,22 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F217" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G217" t="b">
         <v>1</v>
       </c>
       <c r="H217" t="n">
-        <v>1782.103</v>
+        <v>1787.388</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1828</v>
+        <v>1.3307</v>
       </c>
       <c r="J217" t="n">
-        <v>1704.7</v>
+        <v>1694.2</v>
       </c>
       <c r="K217" t="n">
         <v>35</v>
@@ -26462,70 +26462,70 @@
         <v>34</v>
       </c>
       <c r="Q217" t="n">
-        <v>117.32</v>
+        <v>118.283</v>
       </c>
       <c r="R217" t="n">
-        <v>108.156</v>
+        <v>107.415</v>
       </c>
       <c r="S217" t="n">
-        <v>9.164</v>
+        <v>10.869</v>
       </c>
       <c r="T217" t="n">
-        <v>0.26007</v>
+        <v>0.25496</v>
       </c>
       <c r="U217" t="n">
-        <v>0.14812</v>
+        <v>0.15006</v>
       </c>
       <c r="V217" t="n">
-        <v>79.65000000000001</v>
+        <v>80.25</v>
       </c>
       <c r="W217" t="n">
-        <v>73.18000000000001</v>
+        <v>72.69</v>
       </c>
       <c r="X217" t="n">
-        <v>0.625</v>
+        <v>0.6372</v>
       </c>
       <c r="Y217" t="n">
-        <v>27.375</v>
+        <v>27.7</v>
       </c>
       <c r="Z217" t="n">
-        <v>56.273</v>
+        <v>56.145</v>
       </c>
       <c r="AA217" t="n">
-        <v>7.807</v>
+        <v>8.15</v>
       </c>
       <c r="AB217" t="n">
-        <v>22.568</v>
+        <v>22.571</v>
       </c>
       <c r="AC217" t="n">
-        <v>17.227</v>
+        <v>16.828</v>
       </c>
       <c r="AD217" t="n">
-        <v>22.352</v>
+        <v>21.927</v>
       </c>
       <c r="AE217" t="n">
-        <v>8.398</v>
+        <v>8.231999999999999</v>
       </c>
       <c r="AF217" t="n">
-        <v>23.307</v>
+        <v>23.525</v>
       </c>
       <c r="AG217" t="n">
-        <v>14.148</v>
+        <v>14.546</v>
       </c>
       <c r="AH217" t="n">
-        <v>4.773</v>
+        <v>4.802</v>
       </c>
       <c r="AI217" t="n">
-        <v>2.625</v>
+        <v>2.507</v>
       </c>
       <c r="AJ217" t="n">
-        <v>17.545</v>
+        <v>17.571</v>
       </c>
       <c r="AK217" t="n">
-        <v>-0.4</v>
+        <v>6.8</v>
       </c>
       <c r="AL217" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="218">
@@ -26786,22 +26786,22 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F220" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G220" t="b">
         <v>1</v>
       </c>
       <c r="H220" t="n">
-        <v>1357.772</v>
+        <v>1355.571</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6592</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J220" t="n">
-        <v>1467.8</v>
+        <v>1469</v>
       </c>
       <c r="K220" t="n">
         <v>243</v>
@@ -26822,70 +26822,70 @@
         <v>253</v>
       </c>
       <c r="Q220" t="n">
-        <v>106.204</v>
+        <v>106.621</v>
       </c>
       <c r="R220" t="n">
-        <v>109.561</v>
+        <v>110.232</v>
       </c>
       <c r="S220" t="n">
-        <v>-3.357</v>
+        <v>-3.611</v>
       </c>
       <c r="T220" t="n">
-        <v>0.24763</v>
+        <v>0.25068</v>
       </c>
       <c r="U220" t="n">
-        <v>0.14636</v>
+        <v>0.14724</v>
       </c>
       <c r="V220" t="n">
-        <v>75.52</v>
+        <v>75.75</v>
       </c>
       <c r="W220" t="n">
-        <v>78.37</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="X220" t="n">
-        <v>0.3623</v>
+        <v>0.3401</v>
       </c>
       <c r="Y220" t="n">
-        <v>26.429</v>
+        <v>26.329</v>
       </c>
       <c r="Z220" t="n">
-        <v>59.809</v>
+        <v>59.648</v>
       </c>
       <c r="AA220" t="n">
-        <v>7.675</v>
+        <v>7.837</v>
       </c>
       <c r="AB220" t="n">
-        <v>21.467</v>
+        <v>21.672</v>
       </c>
       <c r="AC220" t="n">
-        <v>14.988</v>
+        <v>15.25</v>
       </c>
       <c r="AD220" t="n">
-        <v>20.597</v>
+        <v>20.765</v>
       </c>
       <c r="AE220" t="n">
-        <v>7.98</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="AF220" t="n">
-        <v>23.748</v>
+        <v>23.513</v>
       </c>
       <c r="AG220" t="n">
-        <v>12.942</v>
+        <v>12.918</v>
       </c>
       <c r="AH220" t="n">
-        <v>5.69</v>
+        <v>5.638</v>
       </c>
       <c r="AI220" t="n">
-        <v>3.136</v>
+        <v>3.03</v>
       </c>
       <c r="AJ220" t="n">
-        <v>19.281</v>
+        <v>19.341</v>
       </c>
       <c r="AK220" t="n">
-        <v>2.4</v>
+        <v>-0.6</v>
       </c>
       <c r="AL220" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="221">
@@ -26906,22 +26906,22 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F221" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G221" t="b">
         <v>1</v>
       </c>
       <c r="H221" t="n">
-        <v>1259.376</v>
+        <v>1261.791</v>
       </c>
       <c r="I221" t="n">
-        <v>-3.0333</v>
+        <v>-2.8925</v>
       </c>
       <c r="J221" t="n">
-        <v>1438.4</v>
+        <v>1431.5</v>
       </c>
       <c r="K221" t="n">
         <v>315</v>
@@ -26942,70 +26942,70 @@
         <v>318</v>
       </c>
       <c r="Q221" t="n">
-        <v>102.597</v>
+        <v>103.098</v>
       </c>
       <c r="R221" t="n">
-        <v>114.798</v>
+        <v>113.847</v>
       </c>
       <c r="S221" t="n">
-        <v>-12.201</v>
+        <v>-10.75</v>
       </c>
       <c r="T221" t="n">
-        <v>0.28123</v>
+        <v>0.2825</v>
       </c>
       <c r="U221" t="n">
-        <v>0.1742</v>
+        <v>0.1762</v>
       </c>
       <c r="V221" t="n">
-        <v>71.92</v>
+        <v>72.2</v>
       </c>
       <c r="W221" t="n">
-        <v>80.37</v>
+        <v>79.66</v>
       </c>
       <c r="X221" t="n">
-        <v>0.224</v>
+        <v>0.25</v>
       </c>
       <c r="Y221" t="n">
-        <v>24.43</v>
+        <v>24.545</v>
       </c>
       <c r="Z221" t="n">
-        <v>57.578</v>
+        <v>57.648</v>
       </c>
       <c r="AA221" t="n">
-        <v>8.048</v>
+        <v>8.260999999999999</v>
       </c>
       <c r="AB221" t="n">
-        <v>25.762</v>
+        <v>25.875</v>
       </c>
       <c r="AC221" t="n">
-        <v>15.011</v>
+        <v>14.852</v>
       </c>
       <c r="AD221" t="n">
-        <v>20.249</v>
+        <v>20.068</v>
       </c>
       <c r="AE221" t="n">
-        <v>8.622999999999999</v>
+        <v>8.795</v>
       </c>
       <c r="AF221" t="n">
-        <v>21.984</v>
+        <v>22.239</v>
       </c>
       <c r="AG221" t="n">
-        <v>11.393</v>
+        <v>11.364</v>
       </c>
       <c r="AH221" t="n">
-        <v>5.767</v>
+        <v>5.727</v>
       </c>
       <c r="AI221" t="n">
-        <v>3.423</v>
+        <v>3.409</v>
       </c>
       <c r="AJ221" t="n">
-        <v>19.966</v>
+        <v>19.886</v>
       </c>
       <c r="AK221" t="n">
-        <v>4.8</v>
+        <v>12.8</v>
       </c>
       <c r="AL221" t="n">
-        <v>-4.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="222">
@@ -27506,22 +27506,22 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F226" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G226" t="b">
         <v>1</v>
       </c>
       <c r="H226" t="n">
-        <v>1570.599</v>
+        <v>1531.427</v>
       </c>
       <c r="I226" t="n">
-        <v>-7.9364</v>
+        <v>-7.5446</v>
       </c>
       <c r="J226" t="n">
-        <v>1667.7</v>
+        <v>1669.9</v>
       </c>
       <c r="K226" t="n">
         <v>128</v>
@@ -27542,70 +27542,70 @@
         <v>125</v>
       </c>
       <c r="Q226" t="n">
-        <v>110.927</v>
+        <v>110.145</v>
       </c>
       <c r="R226" t="n">
-        <v>117.12</v>
+        <v>118.589</v>
       </c>
       <c r="S226" t="n">
-        <v>-6.193</v>
+        <v>-8.444000000000001</v>
       </c>
       <c r="T226" t="n">
-        <v>0.26821</v>
+        <v>0.26171</v>
       </c>
       <c r="U226" t="n">
-        <v>0.15045</v>
+        <v>0.14917</v>
       </c>
       <c r="V226" t="n">
-        <v>74.7</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="W226" t="n">
-        <v>78.97</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="X226" t="n">
-        <v>0.4232</v>
+        <v>0.3941</v>
       </c>
       <c r="Y226" t="n">
-        <v>26.764</v>
+        <v>26.327</v>
       </c>
       <c r="Z226" t="n">
-        <v>56.541</v>
+        <v>56.217</v>
       </c>
       <c r="AA226" t="n">
-        <v>7.032</v>
+        <v>7.048</v>
       </c>
       <c r="AB226" t="n">
-        <v>21.48</v>
+        <v>21.463</v>
       </c>
       <c r="AC226" t="n">
-        <v>14.137</v>
+        <v>14.45</v>
       </c>
       <c r="AD226" t="n">
-        <v>18.816</v>
+        <v>19.107</v>
       </c>
       <c r="AE226" t="n">
-        <v>7.429</v>
+        <v>7.207</v>
       </c>
       <c r="AF226" t="n">
-        <v>19.761</v>
+        <v>19.404</v>
       </c>
       <c r="AG226" t="n">
-        <v>12.627</v>
+        <v>12.544</v>
       </c>
       <c r="AH226" t="n">
-        <v>7.071</v>
+        <v>7.131</v>
       </c>
       <c r="AI226" t="n">
-        <v>1.661</v>
+        <v>1.576</v>
       </c>
       <c r="AJ226" t="n">
-        <v>15.511</v>
+        <v>15.478</v>
       </c>
       <c r="AK226" t="n">
-        <v>-8.4</v>
+        <v>-15.4</v>
       </c>
       <c r="AL226" t="n">
-        <v>-11</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="227">
@@ -27746,22 +27746,22 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F228" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G228" t="b">
         <v>1</v>
       </c>
       <c r="H228" t="n">
-        <v>1544.746</v>
+        <v>1510.72</v>
       </c>
       <c r="I228" t="n">
-        <v>-5.8166</v>
+        <v>-5.4673</v>
       </c>
       <c r="J228" t="n">
-        <v>1665.2</v>
+        <v>1660.9</v>
       </c>
       <c r="K228" t="n">
         <v>99</v>
@@ -27782,70 +27782,70 @@
         <v>110</v>
       </c>
       <c r="Q228" t="n">
-        <v>106.439</v>
+        <v>106.737</v>
       </c>
       <c r="R228" t="n">
-        <v>108.567</v>
+        <v>109.24</v>
       </c>
       <c r="S228" t="n">
-        <v>-2.128</v>
+        <v>-2.504</v>
       </c>
       <c r="T228" t="n">
-        <v>0.32214</v>
+        <v>0.32571</v>
       </c>
       <c r="U228" t="n">
-        <v>0.16961</v>
+        <v>0.1677</v>
       </c>
       <c r="V228" t="n">
-        <v>70.03</v>
+        <v>70.19</v>
       </c>
       <c r="W228" t="n">
-        <v>70.95999999999999</v>
+        <v>71.39</v>
       </c>
       <c r="X228" t="n">
-        <v>0.3893</v>
+        <v>0.3612</v>
       </c>
       <c r="Y228" t="n">
-        <v>25.05</v>
+        <v>25.08</v>
       </c>
       <c r="Z228" t="n">
-        <v>57.289</v>
+        <v>57.581</v>
       </c>
       <c r="AA228" t="n">
-        <v>8.255000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="AB228" t="n">
-        <v>24.495</v>
+        <v>24.668</v>
       </c>
       <c r="AC228" t="n">
-        <v>11.677</v>
+        <v>11.719</v>
       </c>
       <c r="AD228" t="n">
-        <v>17.425</v>
+        <v>17.427</v>
       </c>
       <c r="AE228" t="n">
-        <v>10.425</v>
+        <v>10.617</v>
       </c>
       <c r="AF228" t="n">
-        <v>21.675</v>
+        <v>21.686</v>
       </c>
       <c r="AG228" t="n">
-        <v>13.287</v>
+        <v>13.548</v>
       </c>
       <c r="AH228" t="n">
-        <v>6.657</v>
+        <v>6.654</v>
       </c>
       <c r="AI228" t="n">
-        <v>3.068</v>
+        <v>3.113</v>
       </c>
       <c r="AJ228" t="n">
-        <v>16.443</v>
+        <v>16.317</v>
       </c>
       <c r="AK228" t="n">
-        <v>-3.4</v>
+        <v>-0.4</v>
       </c>
       <c r="AL228" t="n">
-        <v>-7.2</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="229">
@@ -28466,22 +28466,22 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F234" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G234" t="b">
         <v>1</v>
       </c>
       <c r="H234" t="n">
-        <v>1578.488</v>
+        <v>1568.757</v>
       </c>
       <c r="I234" t="n">
-        <v>1.8443</v>
+        <v>1.8893</v>
       </c>
       <c r="J234" t="n">
-        <v>1644.9</v>
+        <v>1637.9</v>
       </c>
       <c r="K234" t="n">
         <v>63</v>
@@ -28502,70 +28502,70 @@
         <v>74</v>
       </c>
       <c r="Q234" t="n">
-        <v>116.459</v>
+        <v>114.756</v>
       </c>
       <c r="R234" t="n">
-        <v>112.818</v>
+        <v>112.814</v>
       </c>
       <c r="S234" t="n">
-        <v>3.641</v>
+        <v>1.942</v>
       </c>
       <c r="T234" t="n">
-        <v>0.25643</v>
+        <v>0.26274</v>
       </c>
       <c r="U234" t="n">
-        <v>0.15469</v>
+        <v>0.16119</v>
       </c>
       <c r="V234" t="n">
-        <v>86.67</v>
+        <v>85.33</v>
       </c>
       <c r="W234" t="n">
-        <v>84.28</v>
+        <v>84.11</v>
       </c>
       <c r="X234" t="n">
-        <v>0.4911</v>
+        <v>0.4598</v>
       </c>
       <c r="Y234" t="n">
-        <v>30.032</v>
+        <v>29.381</v>
       </c>
       <c r="Z234" t="n">
-        <v>62.491</v>
+        <v>62.126</v>
       </c>
       <c r="AA234" t="n">
-        <v>9.018000000000001</v>
+        <v>8.938000000000001</v>
       </c>
       <c r="AB234" t="n">
-        <v>24.971</v>
+        <v>25.304</v>
       </c>
       <c r="AC234" t="n">
-        <v>17.586</v>
+        <v>17.627</v>
       </c>
       <c r="AD234" t="n">
-        <v>22.962</v>
+        <v>23.102</v>
       </c>
       <c r="AE234" t="n">
-        <v>9.529</v>
+        <v>9.795999999999999</v>
       </c>
       <c r="AF234" t="n">
-        <v>26.73</v>
+        <v>26.627</v>
       </c>
       <c r="AG234" t="n">
-        <v>14.293</v>
+        <v>14.028</v>
       </c>
       <c r="AH234" t="n">
-        <v>5.305</v>
+        <v>5.438</v>
       </c>
       <c r="AI234" t="n">
-        <v>4.086</v>
+        <v>4.051</v>
       </c>
       <c r="AJ234" t="n">
-        <v>18.952</v>
+        <v>18.714</v>
       </c>
       <c r="AK234" t="n">
-        <v>-0.2</v>
+        <v>-3.2</v>
       </c>
       <c r="AL234" t="n">
-        <v>0.4</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="235">
@@ -28586,22 +28586,22 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F235" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G235" t="b">
         <v>1</v>
       </c>
       <c r="H235" t="n">
-        <v>1972.158</v>
+        <v>1976.001</v>
       </c>
       <c r="I235" t="n">
-        <v>1.3222</v>
+        <v>0.8268</v>
       </c>
       <c r="J235" t="n">
-        <v>1747.3</v>
+        <v>1740.2</v>
       </c>
       <c r="K235" t="n">
         <v>8</v>
@@ -28622,70 +28622,70 @@
         <v>9</v>
       </c>
       <c r="Q235" t="n">
-        <v>124.009</v>
+        <v>123.876</v>
       </c>
       <c r="R235" t="n">
-        <v>105.952</v>
+        <v>105.927</v>
       </c>
       <c r="S235" t="n">
-        <v>18.057</v>
+        <v>17.949</v>
       </c>
       <c r="T235" t="n">
-        <v>0.29776</v>
+        <v>0.29772</v>
       </c>
       <c r="U235" t="n">
-        <v>0.13207</v>
+        <v>0.13738</v>
       </c>
       <c r="V235" t="n">
-        <v>82.2</v>
+        <v>81.75</v>
       </c>
       <c r="W235" t="n">
-        <v>70.09999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="X235" t="n">
-        <v>0.7483</v>
+        <v>0.7696</v>
       </c>
       <c r="Y235" t="n">
-        <v>30.075</v>
+        <v>29.917</v>
       </c>
       <c r="Z235" t="n">
-        <v>60.313</v>
+        <v>59.763</v>
       </c>
       <c r="AA235" t="n">
-        <v>9.435</v>
+        <v>9.395</v>
       </c>
       <c r="AB235" t="n">
-        <v>24.612</v>
+        <v>24.527</v>
       </c>
       <c r="AC235" t="n">
-        <v>12.612</v>
+        <v>12.522</v>
       </c>
       <c r="AD235" t="n">
-        <v>17.041</v>
+        <v>16.859</v>
       </c>
       <c r="AE235" t="n">
-        <v>10.272</v>
+        <v>10.218</v>
       </c>
       <c r="AF235" t="n">
-        <v>23.694</v>
+        <v>23.588</v>
       </c>
       <c r="AG235" t="n">
-        <v>19.497</v>
+        <v>19.696</v>
       </c>
       <c r="AH235" t="n">
-        <v>5.782</v>
+        <v>5.621</v>
       </c>
       <c r="AI235" t="n">
-        <v>2.687</v>
+        <v>2.646</v>
       </c>
       <c r="AJ235" t="n">
-        <v>15.143</v>
+        <v>14.942</v>
       </c>
       <c r="AK235" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="AL235" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="236">
@@ -28946,22 +28946,22 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F238" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G238" t="b">
         <v>1</v>
       </c>
       <c r="H238" t="n">
-        <v>1553.447</v>
+        <v>1573.391</v>
       </c>
       <c r="I238" t="n">
-        <v>0.859</v>
+        <v>0.7869</v>
       </c>
       <c r="J238" t="n">
-        <v>1521.9</v>
+        <v>1518.9</v>
       </c>
       <c r="K238" t="n">
         <v>137</v>
@@ -28982,70 +28982,70 @@
         <v>141</v>
       </c>
       <c r="Q238" t="n">
-        <v>105.723</v>
+        <v>105.824</v>
       </c>
       <c r="R238" t="n">
-        <v>102.878</v>
+        <v>102.049</v>
       </c>
       <c r="S238" t="n">
-        <v>2.845</v>
+        <v>3.774</v>
       </c>
       <c r="T238" t="n">
-        <v>0.30658</v>
+        <v>0.3055</v>
       </c>
       <c r="U238" t="n">
-        <v>0.17637</v>
+        <v>0.17887</v>
       </c>
       <c r="V238" t="n">
-        <v>70.84</v>
+        <v>70.77</v>
       </c>
       <c r="W238" t="n">
-        <v>68.91</v>
+        <v>68.22</v>
       </c>
       <c r="X238" t="n">
-        <v>0.5089</v>
+        <v>0.5402</v>
       </c>
       <c r="Y238" t="n">
-        <v>23.82</v>
+        <v>23.934</v>
       </c>
       <c r="Z238" t="n">
-        <v>54.943</v>
+        <v>54.645</v>
       </c>
       <c r="AA238" t="n">
-        <v>7.289</v>
+        <v>7.057</v>
       </c>
       <c r="AB238" t="n">
-        <v>23.738</v>
+        <v>23.273</v>
       </c>
       <c r="AC238" t="n">
-        <v>15.916</v>
+        <v>15.839</v>
       </c>
       <c r="AD238" t="n">
-        <v>21.984</v>
+        <v>21.762</v>
       </c>
       <c r="AE238" t="n">
-        <v>9.504</v>
+        <v>9.394</v>
       </c>
       <c r="AF238" t="n">
-        <v>21.466</v>
+        <v>21.343</v>
       </c>
       <c r="AG238" t="n">
-        <v>11.491</v>
+        <v>11.365</v>
       </c>
       <c r="AH238" t="n">
-        <v>8.343</v>
+        <v>8.727</v>
       </c>
       <c r="AI238" t="n">
-        <v>3.695</v>
+        <v>3.8</v>
       </c>
       <c r="AJ238" t="n">
-        <v>18.188</v>
+        <v>18.054</v>
       </c>
       <c r="AK238" t="n">
-        <v>-7.2</v>
+        <v>-4</v>
       </c>
       <c r="AL238" t="n">
-        <v>-3.7</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="239">
@@ -29066,22 +29066,22 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F239" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G239" t="b">
         <v>1</v>
       </c>
       <c r="H239" t="n">
-        <v>1412.626</v>
+        <v>1395.068</v>
       </c>
       <c r="I239" t="n">
-        <v>0.37</v>
+        <v>0.3717</v>
       </c>
       <c r="J239" t="n">
-        <v>1519.2</v>
+        <v>1520</v>
       </c>
       <c r="K239" t="n">
         <v>230</v>
@@ -29102,70 +29102,70 @@
         <v>243</v>
       </c>
       <c r="Q239" t="n">
-        <v>105.545</v>
+        <v>104.79</v>
       </c>
       <c r="R239" t="n">
-        <v>112.541</v>
+        <v>112.019</v>
       </c>
       <c r="S239" t="n">
-        <v>-6.996</v>
+        <v>-7.229</v>
       </c>
       <c r="T239" t="n">
-        <v>0.33445</v>
+        <v>0.34064</v>
       </c>
       <c r="U239" t="n">
-        <v>0.16779</v>
+        <v>0.17248</v>
       </c>
       <c r="V239" t="n">
-        <v>72.34999999999999</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="W239" t="n">
-        <v>77.45999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="X239" t="n">
-        <v>0.3806</v>
+        <v>0.3519</v>
       </c>
       <c r="Y239" t="n">
-        <v>24.555</v>
+        <v>24.307</v>
       </c>
       <c r="Z239" t="n">
-        <v>59.279</v>
+        <v>59.267</v>
       </c>
       <c r="AA239" t="n">
-        <v>8.911</v>
+        <v>8.98</v>
       </c>
       <c r="AB239" t="n">
-        <v>25.563</v>
+        <v>25.828</v>
       </c>
       <c r="AC239" t="n">
-        <v>14.328</v>
+        <v>13.917</v>
       </c>
       <c r="AD239" t="n">
-        <v>20.713</v>
+        <v>20.454</v>
       </c>
       <c r="AE239" t="n">
-        <v>11.081</v>
+        <v>11.541</v>
       </c>
       <c r="AF239" t="n">
-        <v>21.656</v>
+        <v>21.833</v>
       </c>
       <c r="AG239" t="n">
-        <v>11.413</v>
+        <v>11.252</v>
       </c>
       <c r="AH239" t="n">
-        <v>6.709</v>
+        <v>6.469</v>
       </c>
       <c r="AI239" t="n">
-        <v>3.874</v>
+        <v>3.844</v>
       </c>
       <c r="AJ239" t="n">
-        <v>19.215</v>
+        <v>19.026</v>
       </c>
       <c r="AK239" t="n">
-        <v>-4.2</v>
+        <v>-6.6</v>
       </c>
       <c r="AL239" t="n">
-        <v>-3.4</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="240">
@@ -29426,22 +29426,22 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F242" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G242" t="b">
         <v>1</v>
       </c>
       <c r="H242" t="n">
-        <v>1537.103</v>
+        <v>1539.878</v>
       </c>
       <c r="I242" t="n">
-        <v>-1.4985</v>
+        <v>-1.3829</v>
       </c>
       <c r="J242" t="n">
-        <v>1429.7</v>
+        <v>1429.6</v>
       </c>
       <c r="K242" t="n">
         <v>146</v>
@@ -29462,70 +29462,70 @@
         <v>144</v>
       </c>
       <c r="Q242" t="n">
-        <v>115.599</v>
+        <v>115.297</v>
       </c>
       <c r="R242" t="n">
-        <v>109.781</v>
+        <v>108.919</v>
       </c>
       <c r="S242" t="n">
-        <v>5.817</v>
+        <v>6.378</v>
       </c>
       <c r="T242" t="n">
-        <v>0.33521</v>
+        <v>0.33378</v>
       </c>
       <c r="U242" t="n">
-        <v>0.17171</v>
+        <v>0.17483</v>
       </c>
       <c r="V242" t="n">
-        <v>77.61</v>
+        <v>77.14</v>
       </c>
       <c r="W242" t="n">
-        <v>74.09</v>
+        <v>73.28</v>
       </c>
       <c r="X242" t="n">
-        <v>0.6591</v>
+        <v>0.6702</v>
       </c>
       <c r="Y242" t="n">
-        <v>28.273</v>
+        <v>28.1</v>
       </c>
       <c r="Z242" t="n">
-        <v>59.818</v>
+        <v>59.52</v>
       </c>
       <c r="AA242" t="n">
-        <v>9.307</v>
+        <v>9.34</v>
       </c>
       <c r="AB242" t="n">
-        <v>24.352</v>
+        <v>24.232</v>
       </c>
       <c r="AC242" t="n">
-        <v>11.761</v>
+        <v>11.595</v>
       </c>
       <c r="AD242" t="n">
-        <v>16.795</v>
+        <v>16.628</v>
       </c>
       <c r="AE242" t="n">
-        <v>11.477</v>
+        <v>11.505</v>
       </c>
       <c r="AF242" t="n">
-        <v>23.205</v>
+        <v>23.426</v>
       </c>
       <c r="AG242" t="n">
-        <v>17.864</v>
+        <v>17.661</v>
       </c>
       <c r="AH242" t="n">
-        <v>5.489</v>
+        <v>5.549</v>
       </c>
       <c r="AI242" t="n">
-        <v>2.409</v>
+        <v>2.483</v>
       </c>
       <c r="AJ242" t="n">
-        <v>18.42</v>
+        <v>18.234</v>
       </c>
       <c r="AK242" t="n">
-        <v>16.8</v>
+        <v>16.4</v>
       </c>
       <c r="AL242" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="243">
@@ -31106,22 +31106,22 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F256" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G256" t="b">
         <v>1</v>
       </c>
       <c r="H256" t="n">
-        <v>1291.444</v>
+        <v>1285.224</v>
       </c>
       <c r="I256" t="n">
-        <v>0.343</v>
+        <v>0.3166</v>
       </c>
       <c r="J256" t="n">
-        <v>1423.8</v>
+        <v>1417.8</v>
       </c>
       <c r="K256" t="n">
         <v>296</v>
@@ -31142,70 +31142,70 @@
         <v>292</v>
       </c>
       <c r="Q256" t="n">
-        <v>99.553</v>
+        <v>99.627</v>
       </c>
       <c r="R256" t="n">
-        <v>106.23</v>
+        <v>106.325</v>
       </c>
       <c r="S256" t="n">
-        <v>-6.678</v>
+        <v>-6.698</v>
       </c>
       <c r="T256" t="n">
-        <v>0.28345</v>
+        <v>0.28848</v>
       </c>
       <c r="U256" t="n">
-        <v>0.17204</v>
+        <v>0.17396</v>
       </c>
       <c r="V256" t="n">
-        <v>71.25</v>
+        <v>70.92</v>
       </c>
       <c r="W256" t="n">
-        <v>75.89</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="X256" t="n">
-        <v>0.3651</v>
+        <v>0.3409</v>
       </c>
       <c r="Y256" t="n">
-        <v>25.614</v>
+        <v>25.409</v>
       </c>
       <c r="Z256" t="n">
-        <v>60.002</v>
+        <v>59.648</v>
       </c>
       <c r="AA256" t="n">
-        <v>6.575</v>
+        <v>6.534</v>
       </c>
       <c r="AB256" t="n">
-        <v>21.093</v>
+        <v>20.875</v>
       </c>
       <c r="AC256" t="n">
-        <v>13.444</v>
+        <v>13.614</v>
       </c>
       <c r="AD256" t="n">
-        <v>19.665</v>
+        <v>19.795</v>
       </c>
       <c r="AE256" t="n">
-        <v>9.34</v>
+        <v>9.477</v>
       </c>
       <c r="AF256" t="n">
-        <v>23.369</v>
+        <v>23.136</v>
       </c>
       <c r="AG256" t="n">
-        <v>11.626</v>
+        <v>11.364</v>
       </c>
       <c r="AH256" t="n">
-        <v>6.143</v>
+        <v>6.33</v>
       </c>
       <c r="AI256" t="n">
-        <v>4.683</v>
+        <v>4.602</v>
       </c>
       <c r="AJ256" t="n">
-        <v>18.644</v>
+        <v>18.409</v>
       </c>
       <c r="AK256" t="n">
-        <v>-2.2</v>
+        <v>-1</v>
       </c>
       <c r="AL256" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="257">
@@ -31946,22 +31946,22 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F263" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G263" t="b">
         <v>1</v>
       </c>
       <c r="H263" t="n">
-        <v>1770.075</v>
+        <v>1753.681</v>
       </c>
       <c r="I263" t="n">
-        <v>1.6059</v>
+        <v>1.2979</v>
       </c>
       <c r="J263" t="n">
-        <v>1642.4</v>
+        <v>1646.7</v>
       </c>
       <c r="K263" t="n">
         <v>39</v>
@@ -31982,70 +31982,70 @@
         <v>36</v>
       </c>
       <c r="Q263" t="n">
-        <v>119.377</v>
+        <v>118.531</v>
       </c>
       <c r="R263" t="n">
-        <v>110.1</v>
+        <v>109.669</v>
       </c>
       <c r="S263" t="n">
-        <v>9.276</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="T263" t="n">
-        <v>0.30043</v>
+        <v>0.30293</v>
       </c>
       <c r="U263" t="n">
-        <v>0.14906</v>
+        <v>0.15163</v>
       </c>
       <c r="V263" t="n">
-        <v>85.65000000000001</v>
+        <v>85.03</v>
       </c>
       <c r="W263" t="n">
-        <v>78.23</v>
+        <v>77.95</v>
       </c>
       <c r="X263" t="n">
-        <v>0.6463</v>
+        <v>0.6254</v>
       </c>
       <c r="Y263" t="n">
-        <v>31.082</v>
+        <v>30.904</v>
       </c>
       <c r="Z263" t="n">
-        <v>62.442</v>
+        <v>62.539</v>
       </c>
       <c r="AA263" t="n">
-        <v>8.224</v>
+        <v>8.23</v>
       </c>
       <c r="AB263" t="n">
-        <v>21.673</v>
+        <v>21.828</v>
       </c>
       <c r="AC263" t="n">
-        <v>15.259</v>
+        <v>14.991</v>
       </c>
       <c r="AD263" t="n">
-        <v>20.51</v>
+        <v>20.085</v>
       </c>
       <c r="AE263" t="n">
-        <v>10.456</v>
+        <v>10.564</v>
       </c>
       <c r="AF263" t="n">
-        <v>24.619</v>
+        <v>24.555</v>
       </c>
       <c r="AG263" t="n">
-        <v>17.333</v>
+        <v>17.201</v>
       </c>
       <c r="AH263" t="n">
-        <v>6.966</v>
+        <v>7.169</v>
       </c>
       <c r="AI263" t="n">
-        <v>3.537</v>
+        <v>3.741</v>
       </c>
       <c r="AJ263" t="n">
-        <v>17.327</v>
+        <v>17.016</v>
       </c>
       <c r="AK263" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="AL263" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="264">
@@ -32906,22 +32906,22 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F271" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G271" t="b">
         <v>1</v>
       </c>
       <c r="H271" t="n">
-        <v>1541.694</v>
+        <v>1531.757</v>
       </c>
       <c r="I271" t="n">
-        <v>-9.021100000000001</v>
+        <v>-8.8443</v>
       </c>
       <c r="J271" t="n">
-        <v>1535.2</v>
+        <v>1532.1</v>
       </c>
       <c r="K271" t="n">
         <v>150</v>
@@ -32942,70 +32942,70 @@
         <v>149</v>
       </c>
       <c r="Q271" t="n">
-        <v>111.697</v>
+        <v>111.567</v>
       </c>
       <c r="R271" t="n">
-        <v>110.919</v>
+        <v>111.048</v>
       </c>
       <c r="S271" t="n">
-        <v>0.778</v>
+        <v>0.52</v>
       </c>
       <c r="T271" t="n">
-        <v>0.31867</v>
+        <v>0.31944</v>
       </c>
       <c r="U271" t="n">
-        <v>0.16085</v>
+        <v>0.1633</v>
       </c>
       <c r="V271" t="n">
-        <v>76.26000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="W271" t="n">
-        <v>75.81999999999999</v>
+        <v>76.61</v>
       </c>
       <c r="X271" t="n">
-        <v>0.4926</v>
+        <v>0.4762</v>
       </c>
       <c r="Y271" t="n">
-        <v>28.187</v>
+        <v>28.286</v>
       </c>
       <c r="Z271" t="n">
-        <v>60.376</v>
+        <v>60.687</v>
       </c>
       <c r="AA271" t="n">
-        <v>7.176</v>
+        <v>7.122</v>
       </c>
       <c r="AB271" t="n">
-        <v>19.106</v>
+        <v>19.15</v>
       </c>
       <c r="AC271" t="n">
-        <v>12.711</v>
+        <v>13.102</v>
       </c>
       <c r="AD271" t="n">
-        <v>16.987</v>
+        <v>17.388</v>
       </c>
       <c r="AE271" t="n">
-        <v>10.42</v>
+        <v>10.592</v>
       </c>
       <c r="AF271" t="n">
-        <v>22.065</v>
+        <v>22.32</v>
       </c>
       <c r="AG271" t="n">
-        <v>15.689</v>
+        <v>15.68</v>
       </c>
       <c r="AH271" t="n">
-        <v>7.372</v>
+        <v>7.565</v>
       </c>
       <c r="AI271" t="n">
-        <v>4.493</v>
+        <v>4.524</v>
       </c>
       <c r="AJ271" t="n">
-        <v>16.061</v>
+        <v>16.388</v>
       </c>
       <c r="AK271" t="n">
-        <v>-2.2</v>
+        <v>-3</v>
       </c>
       <c r="AL271" t="n">
-        <v>-4.1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="272">
@@ -33266,22 +33266,22 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F274" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G274" t="b">
         <v>1</v>
       </c>
       <c r="H274" t="n">
-        <v>1618.414</v>
+        <v>1610.154</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2798</v>
+        <v>0.6493</v>
       </c>
       <c r="J274" t="n">
-        <v>1511.9</v>
+        <v>1512.1</v>
       </c>
       <c r="K274" t="n">
         <v>132</v>
@@ -33302,70 +33302,70 @@
         <v>132</v>
       </c>
       <c r="Q274" t="n">
-        <v>104.612</v>
+        <v>104.924</v>
       </c>
       <c r="R274" t="n">
-        <v>102.078</v>
+        <v>102.361</v>
       </c>
       <c r="S274" t="n">
-        <v>2.533</v>
+        <v>2.563</v>
       </c>
       <c r="T274" t="n">
-        <v>0.28857</v>
+        <v>0.28368</v>
       </c>
       <c r="U274" t="n">
-        <v>0.16171</v>
+        <v>0.16317</v>
       </c>
       <c r="V274" t="n">
-        <v>71.73</v>
+        <v>71.77</v>
       </c>
       <c r="W274" t="n">
-        <v>70.27</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="X274" t="n">
-        <v>0.6337</v>
+        <v>0.6465</v>
       </c>
       <c r="Y274" t="n">
-        <v>25.198</v>
+        <v>25.212</v>
       </c>
       <c r="Z274" t="n">
-        <v>60.11</v>
+        <v>59.788</v>
       </c>
       <c r="AA274" t="n">
-        <v>8.212</v>
+        <v>8.247</v>
       </c>
       <c r="AB274" t="n">
-        <v>27.524</v>
+        <v>27.313</v>
       </c>
       <c r="AC274" t="n">
-        <v>13.125</v>
+        <v>13.096</v>
       </c>
       <c r="AD274" t="n">
-        <v>17.707</v>
+        <v>17.535</v>
       </c>
       <c r="AE274" t="n">
-        <v>10.341</v>
+        <v>10.182</v>
       </c>
       <c r="AF274" t="n">
-        <v>25.282</v>
+        <v>25.586</v>
       </c>
       <c r="AG274" t="n">
-        <v>15.245</v>
+        <v>15.157</v>
       </c>
       <c r="AH274" t="n">
-        <v>5.729</v>
+        <v>5.581</v>
       </c>
       <c r="AI274" t="n">
-        <v>4.875</v>
+        <v>4.859</v>
       </c>
       <c r="AJ274" t="n">
-        <v>14.374</v>
+        <v>14.409</v>
       </c>
       <c r="AK274" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AL274" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="275">
@@ -33386,22 +33386,22 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F275" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G275" t="b">
         <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>1828.166</v>
+        <v>1825.867</v>
       </c>
       <c r="I275" t="n">
-        <v>11.0707</v>
+        <v>10.4518</v>
       </c>
       <c r="J275" t="n">
-        <v>1506.9</v>
+        <v>1501.8</v>
       </c>
       <c r="K275" t="n">
         <v>27</v>
@@ -33422,70 +33422,70 @@
         <v>24</v>
       </c>
       <c r="Q275" t="n">
-        <v>121.569</v>
+        <v>121.998</v>
       </c>
       <c r="R275" t="n">
-        <v>96.506</v>
+        <v>96.95099999999999</v>
       </c>
       <c r="S275" t="n">
-        <v>25.063</v>
+        <v>25.047</v>
       </c>
       <c r="T275" t="n">
-        <v>0.23434</v>
+        <v>0.23263</v>
       </c>
       <c r="U275" t="n">
-        <v>0.1691</v>
+        <v>0.16701</v>
       </c>
       <c r="V275" t="n">
-        <v>88.33</v>
+        <v>87.84</v>
       </c>
       <c r="W275" t="n">
-        <v>70.05</v>
+        <v>69.73</v>
       </c>
       <c r="X275" t="n">
-        <v>0.8944</v>
+        <v>0.898</v>
       </c>
       <c r="Y275" t="n">
-        <v>30.73</v>
+        <v>30.701</v>
       </c>
       <c r="Z275" t="n">
-        <v>60.098</v>
+        <v>59.667</v>
       </c>
       <c r="AA275" t="n">
-        <v>11.32</v>
+        <v>11.143</v>
       </c>
       <c r="AB275" t="n">
-        <v>27.156</v>
+        <v>26.66</v>
       </c>
       <c r="AC275" t="n">
-        <v>15.546</v>
+        <v>15.299</v>
       </c>
       <c r="AD275" t="n">
-        <v>21.009</v>
+        <v>20.823</v>
       </c>
       <c r="AE275" t="n">
-        <v>8.92</v>
+        <v>8.776</v>
       </c>
       <c r="AF275" t="n">
-        <v>28.615</v>
+        <v>28.347</v>
       </c>
       <c r="AG275" t="n">
-        <v>18.622</v>
+        <v>18.449</v>
       </c>
       <c r="AH275" t="n">
-        <v>7.287</v>
+        <v>7.116</v>
       </c>
       <c r="AI275" t="n">
-        <v>3.226</v>
+        <v>3.347</v>
       </c>
       <c r="AJ275" t="n">
-        <v>18.824</v>
+        <v>18.449</v>
       </c>
       <c r="AK275" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AL275" t="n">
-        <v>13.7</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="276">
@@ -33746,22 +33746,22 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F278" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G278" t="b">
         <v>1</v>
       </c>
       <c r="H278" t="n">
-        <v>1726.049</v>
+        <v>1733.62</v>
       </c>
       <c r="I278" t="n">
-        <v>3.1148</v>
+        <v>2.8143</v>
       </c>
       <c r="J278" t="n">
-        <v>1626.4</v>
+        <v>1622</v>
       </c>
       <c r="K278" t="n">
         <v>65</v>
@@ -33782,70 +33782,70 @@
         <v>65</v>
       </c>
       <c r="Q278" t="n">
-        <v>111.235</v>
+        <v>111.861</v>
       </c>
       <c r="R278" t="n">
-        <v>106.284</v>
+        <v>106.911</v>
       </c>
       <c r="S278" t="n">
-        <v>4.951</v>
+        <v>4.95</v>
       </c>
       <c r="T278" t="n">
-        <v>0.31596</v>
+        <v>0.31372</v>
       </c>
       <c r="U278" t="n">
-        <v>0.14498</v>
+        <v>0.14388</v>
       </c>
       <c r="V278" t="n">
-        <v>76.02</v>
+        <v>76.22</v>
       </c>
       <c r="W278" t="n">
-        <v>72.45</v>
+        <v>72.67</v>
       </c>
       <c r="X278" t="n">
-        <v>0.6259</v>
+        <v>0.6379</v>
       </c>
       <c r="Y278" t="n">
-        <v>25.286</v>
+        <v>25.582</v>
       </c>
       <c r="Z278" t="n">
-        <v>58.551</v>
+        <v>58.534</v>
       </c>
       <c r="AA278" t="n">
-        <v>9.17</v>
+        <v>9.234999999999999</v>
       </c>
       <c r="AB278" t="n">
-        <v>26.116</v>
+        <v>25.962</v>
       </c>
       <c r="AC278" t="n">
-        <v>16.279</v>
+        <v>15.826</v>
       </c>
       <c r="AD278" t="n">
-        <v>22.102</v>
+        <v>21.694</v>
       </c>
       <c r="AE278" t="n">
-        <v>9.952</v>
+        <v>9.831</v>
       </c>
       <c r="AF278" t="n">
-        <v>21.388</v>
+        <v>21.317</v>
       </c>
       <c r="AG278" t="n">
-        <v>12.088</v>
+        <v>12.078</v>
       </c>
       <c r="AH278" t="n">
-        <v>7.898</v>
+        <v>7.856</v>
       </c>
       <c r="AI278" t="n">
-        <v>3.531</v>
+        <v>3.663</v>
       </c>
       <c r="AJ278" t="n">
-        <v>17.694</v>
+        <v>17.704</v>
       </c>
       <c r="AK278" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AL278" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="279">
@@ -33866,22 +33866,22 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F279" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G279" t="b">
         <v>1</v>
       </c>
       <c r="H279" t="n">
-        <v>1299.897</v>
+        <v>1302.712</v>
       </c>
       <c r="I279" t="n">
-        <v>-1.335</v>
+        <v>-1.2714</v>
       </c>
       <c r="J279" t="n">
-        <v>1414.3</v>
+        <v>1410.3</v>
       </c>
       <c r="K279" t="n">
         <v>317</v>
@@ -33902,70 +33902,70 @@
         <v>320</v>
       </c>
       <c r="Q279" t="n">
-        <v>105.503</v>
+        <v>107.05</v>
       </c>
       <c r="R279" t="n">
-        <v>117.771</v>
+        <v>118.1</v>
       </c>
       <c r="S279" t="n">
-        <v>-12.268</v>
+        <v>-11.05</v>
       </c>
       <c r="T279" t="n">
-        <v>0.27448</v>
+        <v>0.27324</v>
       </c>
       <c r="U279" t="n">
-        <v>0.17964</v>
+        <v>0.17823</v>
       </c>
       <c r="V279" t="n">
-        <v>71.76000000000001</v>
+        <v>72.62</v>
       </c>
       <c r="W279" t="n">
-        <v>80.17</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="X279" t="n">
-        <v>0.3214</v>
+        <v>0.3432</v>
       </c>
       <c r="Y279" t="n">
-        <v>25.098</v>
+        <v>25.08</v>
       </c>
       <c r="Z279" t="n">
-        <v>55.732</v>
+        <v>55.66</v>
       </c>
       <c r="AA279" t="n">
-        <v>8.896000000000001</v>
+        <v>9.010999999999999</v>
       </c>
       <c r="AB279" t="n">
-        <v>24.698</v>
+        <v>24.865</v>
       </c>
       <c r="AC279" t="n">
-        <v>12.664</v>
+        <v>12.69</v>
       </c>
       <c r="AD279" t="n">
-        <v>18.445</v>
+        <v>18.397</v>
       </c>
       <c r="AE279" t="n">
-        <v>7.984</v>
+        <v>7.905</v>
       </c>
       <c r="AF279" t="n">
-        <v>21.434</v>
+        <v>21.296</v>
       </c>
       <c r="AG279" t="n">
-        <v>14.773</v>
+        <v>14.576</v>
       </c>
       <c r="AH279" t="n">
-        <v>5.936</v>
+        <v>5.857</v>
       </c>
       <c r="AI279" t="n">
-        <v>2</v>
+        <v>2.048</v>
       </c>
       <c r="AJ279" t="n">
-        <v>15.325</v>
+        <v>15.409</v>
       </c>
       <c r="AK279" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="AL279" t="n">
-        <v>-2.1</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="280">
@@ -34946,22 +34946,22 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F288" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G288" t="b">
         <v>1</v>
       </c>
       <c r="H288" t="n">
-        <v>1785.054</v>
+        <v>1777.532</v>
       </c>
       <c r="I288" t="n">
-        <v>2.0552</v>
+        <v>2.2904</v>
       </c>
       <c r="J288" t="n">
-        <v>1691.9</v>
+        <v>1700.7</v>
       </c>
       <c r="K288" t="n">
         <v>29</v>
@@ -34982,70 +34982,70 @@
         <v>37</v>
       </c>
       <c r="Q288" t="n">
-        <v>121.103</v>
+        <v>120.672</v>
       </c>
       <c r="R288" t="n">
-        <v>110.258</v>
+        <v>111.462</v>
       </c>
       <c r="S288" t="n">
-        <v>10.846</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="T288" t="n">
-        <v>0.31156</v>
+        <v>0.31228</v>
       </c>
       <c r="U288" t="n">
-        <v>0.15048</v>
+        <v>0.14876</v>
       </c>
       <c r="V288" t="n">
-        <v>82.98</v>
+        <v>83.16</v>
       </c>
       <c r="W288" t="n">
-        <v>75.33</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="X288" t="n">
-        <v>0.612</v>
+        <v>0.5795</v>
       </c>
       <c r="Y288" t="n">
-        <v>27.847</v>
+        <v>28.091</v>
       </c>
       <c r="Z288" t="n">
-        <v>57.45</v>
+        <v>57.83</v>
       </c>
       <c r="AA288" t="n">
-        <v>7.282</v>
+        <v>7.182</v>
       </c>
       <c r="AB288" t="n">
-        <v>20.859</v>
+        <v>20.5</v>
       </c>
       <c r="AC288" t="n">
-        <v>20.009</v>
+        <v>19.795</v>
       </c>
       <c r="AD288" t="n">
-        <v>26.476</v>
+        <v>26.625</v>
       </c>
       <c r="AE288" t="n">
-        <v>10.871</v>
+        <v>10.818</v>
       </c>
       <c r="AF288" t="n">
-        <v>24.132</v>
+        <v>23.932</v>
       </c>
       <c r="AG288" t="n">
-        <v>11.598</v>
+        <v>11.886</v>
       </c>
       <c r="AH288" t="n">
-        <v>5.728</v>
+        <v>5.761</v>
       </c>
       <c r="AI288" t="n">
-        <v>2.933</v>
+        <v>2.818</v>
       </c>
       <c r="AJ288" t="n">
-        <v>18.741</v>
+        <v>18.761</v>
       </c>
       <c r="AK288" t="n">
-        <v>0.4</v>
+        <v>-7</v>
       </c>
       <c r="AL288" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="289">
@@ -36386,22 +36386,22 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F300" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G300" t="b">
         <v>1</v>
       </c>
       <c r="H300" t="n">
-        <v>1577.105</v>
+        <v>1599.905</v>
       </c>
       <c r="I300" t="n">
-        <v>0.6156</v>
+        <v>0.5599</v>
       </c>
       <c r="J300" t="n">
-        <v>1508.7</v>
+        <v>1505.6</v>
       </c>
       <c r="K300" t="n">
         <v>124</v>
@@ -36422,70 +36422,70 @@
         <v>114</v>
       </c>
       <c r="Q300" t="n">
-        <v>107.501</v>
+        <v>108.59</v>
       </c>
       <c r="R300" t="n">
-        <v>102.26</v>
+        <v>102.987</v>
       </c>
       <c r="S300" t="n">
-        <v>5.24</v>
+        <v>5.603</v>
       </c>
       <c r="T300" t="n">
-        <v>0.30102</v>
+        <v>0.30726</v>
       </c>
       <c r="U300" t="n">
-        <v>0.12697</v>
+        <v>0.12453</v>
       </c>
       <c r="V300" t="n">
-        <v>77.39</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="W300" t="n">
-        <v>73.58</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="X300" t="n">
-        <v>0.5981</v>
+        <v>0.6259</v>
       </c>
       <c r="Y300" t="n">
-        <v>27.67</v>
+        <v>27.796</v>
       </c>
       <c r="Z300" t="n">
-        <v>63.631</v>
+        <v>63.878</v>
       </c>
       <c r="AA300" t="n">
-        <v>5.563</v>
+        <v>5.497</v>
       </c>
       <c r="AB300" t="n">
-        <v>19.824</v>
+        <v>19.735</v>
       </c>
       <c r="AC300" t="n">
-        <v>16.483</v>
+        <v>16.701</v>
       </c>
       <c r="AD300" t="n">
-        <v>23.589</v>
+        <v>23.469</v>
       </c>
       <c r="AE300" t="n">
-        <v>11.096</v>
+        <v>11.374</v>
       </c>
       <c r="AF300" t="n">
-        <v>25.452</v>
+        <v>25.313</v>
       </c>
       <c r="AG300" t="n">
-        <v>13.494</v>
+        <v>13.626</v>
       </c>
       <c r="AH300" t="n">
-        <v>7.68</v>
+        <v>7.524</v>
       </c>
       <c r="AI300" t="n">
-        <v>3.522</v>
+        <v>3.476</v>
       </c>
       <c r="AJ300" t="n">
-        <v>14.554</v>
+        <v>14.483</v>
       </c>
       <c r="AK300" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AL300" t="n">
         <v>3.2</v>
-      </c>
-      <c r="AL300" t="n">
-        <v>1.3</v>
       </c>
     </row>
     <row r="301">
@@ -37106,22 +37106,22 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F306" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G306" t="b">
         <v>1</v>
       </c>
       <c r="H306" t="n">
-        <v>1321.723</v>
+        <v>1319.966</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.0421</v>
+        <v>-0.9378</v>
       </c>
       <c r="J306" t="n">
-        <v>1464.5</v>
+        <v>1467.4</v>
       </c>
       <c r="K306" t="n">
         <v>311</v>
@@ -37142,70 +37142,70 @@
         <v>314</v>
       </c>
       <c r="Q306" t="n">
-        <v>99.708</v>
+        <v>99.56</v>
       </c>
       <c r="R306" t="n">
-        <v>109.661</v>
+        <v>110.212</v>
       </c>
       <c r="S306" t="n">
-        <v>-9.952999999999999</v>
+        <v>-10.653</v>
       </c>
       <c r="T306" t="n">
-        <v>0.30272</v>
+        <v>0.30473</v>
       </c>
       <c r="U306" t="n">
-        <v>0.15664</v>
+        <v>0.15517</v>
       </c>
       <c r="V306" t="n">
-        <v>63.63</v>
+        <v>63.75</v>
       </c>
       <c r="W306" t="n">
-        <v>70.20999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="X306" t="n">
-        <v>0.3508</v>
+        <v>0.33</v>
       </c>
       <c r="Y306" t="n">
-        <v>22.352</v>
+        <v>22.46</v>
       </c>
       <c r="Z306" t="n">
-        <v>55.497</v>
+        <v>55.7</v>
       </c>
       <c r="AA306" t="n">
-        <v>7.638</v>
+        <v>7.55</v>
       </c>
       <c r="AB306" t="n">
-        <v>22.657</v>
+        <v>22.45</v>
       </c>
       <c r="AC306" t="n">
-        <v>11.285</v>
+        <v>11.28</v>
       </c>
       <c r="AD306" t="n">
-        <v>16.019</v>
+        <v>16.02</v>
       </c>
       <c r="AE306" t="n">
-        <v>8.632999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AF306" t="n">
-        <v>19.712</v>
+        <v>19.46</v>
       </c>
       <c r="AG306" t="n">
-        <v>10.516</v>
+        <v>10.24</v>
       </c>
       <c r="AH306" t="n">
-        <v>5.743</v>
+        <v>5.81</v>
       </c>
       <c r="AI306" t="n">
-        <v>3.464</v>
+        <v>3.49</v>
       </c>
       <c r="AJ306" t="n">
-        <v>19.042</v>
+        <v>19.03</v>
       </c>
       <c r="AK306" t="n">
-        <v>-7.4</v>
+        <v>-7</v>
       </c>
       <c r="AL306" t="n">
-        <v>-3.5</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="307">
@@ -37946,22 +37946,22 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F313" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G313" t="b">
         <v>1</v>
       </c>
       <c r="H313" t="n">
-        <v>1770.78</v>
+        <v>1755.83</v>
       </c>
       <c r="I313" t="n">
-        <v>2.1219</v>
+        <v>1.5224</v>
       </c>
       <c r="J313" t="n">
-        <v>1691.4</v>
+        <v>1684.4</v>
       </c>
       <c r="K313" t="n">
         <v>67</v>
@@ -37982,70 +37982,70 @@
         <v>63</v>
       </c>
       <c r="Q313" t="n">
-        <v>108.368</v>
+        <v>107.919</v>
       </c>
       <c r="R313" t="n">
-        <v>107.724</v>
+        <v>108.186</v>
       </c>
       <c r="S313" t="n">
-        <v>0.644</v>
+        <v>-0.267</v>
       </c>
       <c r="T313" t="n">
-        <v>0.29238</v>
+        <v>0.29523</v>
       </c>
       <c r="U313" t="n">
-        <v>0.17224</v>
+        <v>0.17118</v>
       </c>
       <c r="V313" t="n">
-        <v>78.19</v>
+        <v>78.05</v>
       </c>
       <c r="W313" t="n">
-        <v>77.5</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="X313" t="n">
-        <v>0.5981</v>
+        <v>0.5782</v>
       </c>
       <c r="Y313" t="n">
-        <v>26.307</v>
+        <v>26.245</v>
       </c>
       <c r="Z313" t="n">
-        <v>58.037</v>
+        <v>58.422</v>
       </c>
       <c r="AA313" t="n">
-        <v>6.322</v>
+        <v>6.245</v>
       </c>
       <c r="AB313" t="n">
-        <v>19.839</v>
+        <v>19.782</v>
       </c>
       <c r="AC313" t="n">
-        <v>19.252</v>
+        <v>19.32</v>
       </c>
       <c r="AD313" t="n">
-        <v>26.444</v>
+        <v>26.497</v>
       </c>
       <c r="AE313" t="n">
-        <v>9.891</v>
+        <v>10.061</v>
       </c>
       <c r="AF313" t="n">
-        <v>23.343</v>
+        <v>23.469</v>
       </c>
       <c r="AG313" t="n">
-        <v>14.713</v>
+        <v>14.265</v>
       </c>
       <c r="AH313" t="n">
-        <v>6.231</v>
+        <v>6.333</v>
       </c>
       <c r="AI313" t="n">
-        <v>5.437</v>
+        <v>5.408</v>
       </c>
       <c r="AJ313" t="n">
-        <v>18.8</v>
+        <v>18.769</v>
       </c>
       <c r="AK313" t="n">
-        <v>-15.6</v>
+        <v>-18</v>
       </c>
       <c r="AL313" t="n">
-        <v>-6.6</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="314">
@@ -39266,22 +39266,22 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F324" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G324" t="b">
         <v>1</v>
       </c>
       <c r="H324" t="n">
-        <v>1813.508</v>
+        <v>1820.115</v>
       </c>
       <c r="I324" t="n">
-        <v>6.893</v>
+        <v>6.5295</v>
       </c>
       <c r="J324" t="n">
-        <v>1649.2</v>
+        <v>1643.5</v>
       </c>
       <c r="K324" t="n">
         <v>34</v>
@@ -39302,70 +39302,70 @@
         <v>33</v>
       </c>
       <c r="Q324" t="n">
-        <v>114.625</v>
+        <v>114.744</v>
       </c>
       <c r="R324" t="n">
-        <v>105.114</v>
+        <v>103.875</v>
       </c>
       <c r="S324" t="n">
-        <v>9.510999999999999</v>
+        <v>10.869</v>
       </c>
       <c r="T324" t="n">
-        <v>0.3173</v>
+        <v>0.31482</v>
       </c>
       <c r="U324" t="n">
-        <v>0.14121</v>
+        <v>0.141</v>
       </c>
       <c r="V324" t="n">
-        <v>76.94</v>
+        <v>77.12</v>
       </c>
       <c r="W324" t="n">
-        <v>70.97</v>
+        <v>70.16</v>
       </c>
       <c r="X324" t="n">
-        <v>0.75</v>
+        <v>0.7691</v>
       </c>
       <c r="Y324" t="n">
-        <v>27.125</v>
+        <v>27.154</v>
       </c>
       <c r="Z324" t="n">
-        <v>59.659</v>
+        <v>59.606</v>
       </c>
       <c r="AA324" t="n">
-        <v>9.659000000000001</v>
+        <v>9.573</v>
       </c>
       <c r="AB324" t="n">
-        <v>27.261</v>
+        <v>27.036</v>
       </c>
       <c r="AC324" t="n">
-        <v>13.034</v>
+        <v>13.24</v>
       </c>
       <c r="AD324" t="n">
-        <v>19</v>
+        <v>19.207</v>
       </c>
       <c r="AE324" t="n">
-        <v>10.148</v>
+        <v>10.111</v>
       </c>
       <c r="AF324" t="n">
-        <v>21.409</v>
+        <v>21.657</v>
       </c>
       <c r="AG324" t="n">
-        <v>15.227</v>
+        <v>15.22</v>
       </c>
       <c r="AH324" t="n">
-        <v>7.477</v>
+        <v>7.669</v>
       </c>
       <c r="AI324" t="n">
-        <v>2.205</v>
+        <v>2.285</v>
       </c>
       <c r="AJ324" t="n">
-        <v>16.091</v>
+        <v>16.153</v>
       </c>
       <c r="AK324" t="n">
-        <v>-3.8</v>
+        <v>-2.2</v>
       </c>
       <c r="AL324" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="325">
@@ -40226,22 +40226,22 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F332" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G332" t="b">
         <v>1</v>
       </c>
       <c r="H332" t="n">
-        <v>1326.263</v>
+        <v>1327.668</v>
       </c>
       <c r="I332" t="n">
-        <v>-2.1472</v>
+        <v>-1.9736</v>
       </c>
       <c r="J332" t="n">
-        <v>1384.3</v>
+        <v>1390.2</v>
       </c>
       <c r="K332" t="n">
         <v>316</v>
@@ -40262,70 +40262,70 @@
         <v>309</v>
       </c>
       <c r="Q332" t="n">
-        <v>105.127</v>
+        <v>105.524</v>
       </c>
       <c r="R332" t="n">
-        <v>109.437</v>
+        <v>109.242</v>
       </c>
       <c r="S332" t="n">
-        <v>-4.31</v>
+        <v>-3.717</v>
       </c>
       <c r="T332" t="n">
-        <v>0.30921</v>
+        <v>0.30663</v>
       </c>
       <c r="U332" t="n">
-        <v>0.1838</v>
+        <v>0.17808</v>
       </c>
       <c r="V332" t="n">
-        <v>70.26000000000001</v>
+        <v>70.11</v>
       </c>
       <c r="W332" t="n">
-        <v>73.34999999999999</v>
+        <v>72.86</v>
       </c>
       <c r="X332" t="n">
-        <v>0.3937</v>
+        <v>0.4154</v>
       </c>
       <c r="Y332" t="n">
-        <v>24.665</v>
+        <v>24.685</v>
       </c>
       <c r="Z332" t="n">
-        <v>56.848</v>
+        <v>56.904</v>
       </c>
       <c r="AA332" t="n">
-        <v>7.741</v>
+        <v>7.658</v>
       </c>
       <c r="AB332" t="n">
-        <v>20.545</v>
+        <v>20.512</v>
       </c>
       <c r="AC332" t="n">
-        <v>13.189</v>
+        <v>13.083</v>
       </c>
       <c r="AD332" t="n">
-        <v>18.425</v>
+        <v>18.138</v>
       </c>
       <c r="AE332" t="n">
-        <v>10.432</v>
+        <v>10.302</v>
       </c>
       <c r="AF332" t="n">
-        <v>23.208</v>
+        <v>23.173</v>
       </c>
       <c r="AG332" t="n">
-        <v>12.307</v>
+        <v>12.033</v>
       </c>
       <c r="AH332" t="n">
-        <v>5.242</v>
+        <v>5.119</v>
       </c>
       <c r="AI332" t="n">
-        <v>2.251</v>
+        <v>2.306</v>
       </c>
       <c r="AJ332" t="n">
-        <v>19.213</v>
+        <v>19.019</v>
       </c>
       <c r="AK332" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AL332" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="333">
@@ -40466,22 +40466,22 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F334" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G334" t="b">
         <v>1</v>
       </c>
       <c r="H334" t="n">
-        <v>1639.275</v>
+        <v>1654.225</v>
       </c>
       <c r="I334" t="n">
-        <v>2.3162</v>
+        <v>2.1014</v>
       </c>
       <c r="J334" t="n">
-        <v>1687.1</v>
+        <v>1689.2</v>
       </c>
       <c r="K334" t="n">
         <v>54</v>
@@ -40502,70 +40502,70 @@
         <v>61</v>
       </c>
       <c r="Q334" t="n">
-        <v>111.084</v>
+        <v>111.564</v>
       </c>
       <c r="R334" t="n">
-        <v>106.695</v>
+        <v>105.957</v>
       </c>
       <c r="S334" t="n">
-        <v>4.389</v>
+        <v>5.606</v>
       </c>
       <c r="T334" t="n">
-        <v>0.29531</v>
+        <v>0.30085</v>
       </c>
       <c r="U334" t="n">
-        <v>0.15002</v>
+        <v>0.15006</v>
       </c>
       <c r="V334" t="n">
-        <v>76.17</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="W334" t="n">
-        <v>72.92</v>
+        <v>72.69</v>
       </c>
       <c r="X334" t="n">
-        <v>0.4773</v>
+        <v>0.5052</v>
       </c>
       <c r="Y334" t="n">
-        <v>27.807</v>
+        <v>28.193</v>
       </c>
       <c r="Z334" t="n">
-        <v>60.58</v>
+        <v>61.267</v>
       </c>
       <c r="AA334" t="n">
-        <v>6.42</v>
+        <v>6.472</v>
       </c>
       <c r="AB334" t="n">
-        <v>20.352</v>
+        <v>20.798</v>
       </c>
       <c r="AC334" t="n">
-        <v>14.136</v>
+        <v>13.991</v>
       </c>
       <c r="AD334" t="n">
-        <v>18.591</v>
+        <v>18.463</v>
       </c>
       <c r="AE334" t="n">
-        <v>10.364</v>
+        <v>10.754</v>
       </c>
       <c r="AF334" t="n">
-        <v>23.989</v>
+        <v>24.097</v>
       </c>
       <c r="AG334" t="n">
-        <v>13.489</v>
+        <v>13.538</v>
       </c>
       <c r="AH334" t="n">
-        <v>5.648</v>
+        <v>5.757</v>
       </c>
       <c r="AI334" t="n">
-        <v>4.205</v>
+        <v>4.241</v>
       </c>
       <c r="AJ334" t="n">
-        <v>16.864</v>
+        <v>17.097</v>
       </c>
       <c r="AK334" t="n">
-        <v>-1</v>
+        <v>3.4</v>
       </c>
       <c r="AL334" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="335">
@@ -41066,22 +41066,22 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F339" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G339" t="b">
         <v>1</v>
       </c>
       <c r="H339" t="n">
-        <v>1396.005</v>
+        <v>1393.173</v>
       </c>
       <c r="I339" t="n">
-        <v>-3.6451</v>
+        <v>-3.5301</v>
       </c>
       <c r="J339" t="n">
-        <v>1460.3</v>
+        <v>1454.8</v>
       </c>
       <c r="K339" t="n">
         <v>262</v>
@@ -41102,70 +41102,70 @@
         <v>247</v>
       </c>
       <c r="Q339" t="n">
-        <v>108.503</v>
+        <v>107.928</v>
       </c>
       <c r="R339" t="n">
-        <v>114.892</v>
+        <v>115.636</v>
       </c>
       <c r="S339" t="n">
-        <v>-6.389</v>
+        <v>-7.709</v>
       </c>
       <c r="T339" t="n">
-        <v>0.3244</v>
+        <v>0.32648</v>
       </c>
       <c r="U339" t="n">
-        <v>0.14992</v>
+        <v>0.14738</v>
       </c>
       <c r="V339" t="n">
-        <v>75.09999999999999</v>
+        <v>74.56</v>
       </c>
       <c r="W339" t="n">
-        <v>79.64</v>
+        <v>79.97</v>
       </c>
       <c r="X339" t="n">
-        <v>0.3733</v>
+        <v>0.3514</v>
       </c>
       <c r="Y339" t="n">
-        <v>26.955</v>
+        <v>26.769</v>
       </c>
       <c r="Z339" t="n">
-        <v>61.255</v>
+        <v>61.329</v>
       </c>
       <c r="AA339" t="n">
-        <v>7.648</v>
+        <v>7.524</v>
       </c>
       <c r="AB339" t="n">
-        <v>23.408</v>
+        <v>23.374</v>
       </c>
       <c r="AC339" t="n">
-        <v>13.54</v>
+        <v>13.501</v>
       </c>
       <c r="AD339" t="n">
-        <v>19.607</v>
+        <v>19.681</v>
       </c>
       <c r="AE339" t="n">
-        <v>10.937</v>
+        <v>11</v>
       </c>
       <c r="AF339" t="n">
-        <v>22.184</v>
+        <v>22.128</v>
       </c>
       <c r="AG339" t="n">
-        <v>12.957</v>
+        <v>12.885</v>
       </c>
       <c r="AH339" t="n">
-        <v>6.613</v>
+        <v>6.501</v>
       </c>
       <c r="AI339" t="n">
-        <v>3.001</v>
+        <v>2.949</v>
       </c>
       <c r="AJ339" t="n">
-        <v>18.597</v>
+        <v>18.681</v>
       </c>
       <c r="AK339" t="n">
-        <v>0.8</v>
+        <v>-4.2</v>
       </c>
       <c r="AL339" t="n">
-        <v>-2.2</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="340">
@@ -41546,22 +41546,22 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F343" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G343" t="b">
         <v>1</v>
       </c>
       <c r="H343" t="n">
-        <v>1833.564</v>
+        <v>1837.727</v>
       </c>
       <c r="I343" t="n">
-        <v>0.5562</v>
+        <v>0.7673</v>
       </c>
       <c r="J343" t="n">
-        <v>1689.3</v>
+        <v>1686</v>
       </c>
       <c r="K343" t="n">
         <v>30</v>
@@ -41582,70 +41582,70 @@
         <v>32</v>
       </c>
       <c r="Q343" t="n">
-        <v>117.739</v>
+        <v>118.38</v>
       </c>
       <c r="R343" t="n">
-        <v>107.724</v>
+        <v>106.471</v>
       </c>
       <c r="S343" t="n">
-        <v>10.015</v>
+        <v>11.909</v>
       </c>
       <c r="T343" t="n">
-        <v>0.27723</v>
+        <v>0.2733</v>
       </c>
       <c r="U343" t="n">
-        <v>0.12636</v>
+        <v>0.12357</v>
       </c>
       <c r="V343" t="n">
-        <v>83.05</v>
+        <v>82.75</v>
       </c>
       <c r="W343" t="n">
-        <v>76</v>
+        <v>74.69</v>
       </c>
       <c r="X343" t="n">
-        <v>0.6932</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="Y343" t="n">
-        <v>27.966</v>
+        <v>27.858</v>
       </c>
       <c r="Z343" t="n">
-        <v>62.273</v>
+        <v>61.871</v>
       </c>
       <c r="AA343" t="n">
-        <v>11.375</v>
+        <v>11.384</v>
       </c>
       <c r="AB343" t="n">
-        <v>31.966</v>
+        <v>31.858</v>
       </c>
       <c r="AC343" t="n">
-        <v>15.739</v>
+        <v>15.651</v>
       </c>
       <c r="AD343" t="n">
-        <v>20.239</v>
+        <v>20.091</v>
       </c>
       <c r="AE343" t="n">
-        <v>9.510999999999999</v>
+        <v>9.375</v>
       </c>
       <c r="AF343" t="n">
-        <v>24.307</v>
+        <v>24.481</v>
       </c>
       <c r="AG343" t="n">
-        <v>15.83</v>
+        <v>15.792</v>
       </c>
       <c r="AH343" t="n">
-        <v>5.591</v>
+        <v>5.691</v>
       </c>
       <c r="AI343" t="n">
-        <v>3.091</v>
+        <v>3.099</v>
       </c>
       <c r="AJ343" t="n">
-        <v>17.318</v>
+        <v>17.069</v>
       </c>
       <c r="AK343" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AL343" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="344">
@@ -41786,22 +41786,22 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F345" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G345" t="b">
         <v>1</v>
       </c>
       <c r="H345" t="n">
-        <v>1462.019</v>
+        <v>1463.954</v>
       </c>
       <c r="I345" t="n">
-        <v>2.7724</v>
+        <v>2.7542</v>
       </c>
       <c r="J345" t="n">
-        <v>1438.5</v>
+        <v>1435.2</v>
       </c>
       <c r="K345" t="n">
         <v>153</v>
@@ -41822,70 +41822,70 @@
         <v>140</v>
       </c>
       <c r="Q345" t="n">
-        <v>115.185</v>
+        <v>115.653</v>
       </c>
       <c r="R345" t="n">
-        <v>110.175</v>
+        <v>109.069</v>
       </c>
       <c r="S345" t="n">
-        <v>5.009</v>
+        <v>6.584</v>
       </c>
       <c r="T345" t="n">
-        <v>0.30107</v>
+        <v>0.29919</v>
       </c>
       <c r="U345" t="n">
-        <v>0.15855</v>
+        <v>0.15797</v>
       </c>
       <c r="V345" t="n">
-        <v>79.43000000000001</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="W345" t="n">
-        <v>75.97</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="X345" t="n">
-        <v>0.6242</v>
+        <v>0.6365</v>
       </c>
       <c r="Y345" t="n">
-        <v>28.099</v>
+        <v>28.241</v>
       </c>
       <c r="Z345" t="n">
-        <v>58.286</v>
+        <v>58.315</v>
       </c>
       <c r="AA345" t="n">
-        <v>7.258</v>
+        <v>7.106</v>
       </c>
       <c r="AB345" t="n">
-        <v>19.811</v>
+        <v>19.626</v>
       </c>
       <c r="AC345" t="n">
-        <v>15.972</v>
+        <v>16.167</v>
       </c>
       <c r="AD345" t="n">
-        <v>21.537</v>
+        <v>21.695</v>
       </c>
       <c r="AE345" t="n">
-        <v>9.696</v>
+        <v>9.753</v>
       </c>
       <c r="AF345" t="n">
-        <v>21.975</v>
+        <v>22.384</v>
       </c>
       <c r="AG345" t="n">
-        <v>13.121</v>
+        <v>13.224</v>
       </c>
       <c r="AH345" t="n">
-        <v>7.214</v>
+        <v>7.073</v>
       </c>
       <c r="AI345" t="n">
-        <v>4.339</v>
+        <v>4.322</v>
       </c>
       <c r="AJ345" t="n">
-        <v>17.36</v>
+        <v>17.289</v>
       </c>
       <c r="AK345" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="AL345" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="346">
@@ -42266,22 +42266,22 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F349" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G349" t="b">
         <v>1</v>
       </c>
       <c r="H349" t="n">
-        <v>1410.7</v>
+        <v>1407.925</v>
       </c>
       <c r="I349" t="n">
-        <v>-3.7547</v>
+        <v>-3.5999</v>
       </c>
       <c r="J349" t="n">
-        <v>1424.4</v>
+        <v>1430.1</v>
       </c>
       <c r="K349" t="n">
         <v>208</v>
@@ -42302,70 +42302,70 @@
         <v>215</v>
       </c>
       <c r="Q349" t="n">
-        <v>109.926</v>
+        <v>108.892</v>
       </c>
       <c r="R349" t="n">
-        <v>109.212</v>
+        <v>108.875</v>
       </c>
       <c r="S349" t="n">
-        <v>0.714</v>
+        <v>0.017</v>
       </c>
       <c r="T349" t="n">
-        <v>0.29697</v>
+        <v>0.3002</v>
       </c>
       <c r="U349" t="n">
-        <v>0.17972</v>
+        <v>0.18106</v>
       </c>
       <c r="V349" t="n">
-        <v>75.73</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="W349" t="n">
-        <v>75.26000000000001</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="X349" t="n">
-        <v>0.4233</v>
+        <v>0.4091</v>
       </c>
       <c r="Y349" t="n">
-        <v>26.363</v>
+        <v>26.011</v>
       </c>
       <c r="Z349" t="n">
-        <v>57.707</v>
+        <v>57.602</v>
       </c>
       <c r="AA349" t="n">
-        <v>9.704000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="AB349" t="n">
-        <v>28.443</v>
+        <v>28.466</v>
       </c>
       <c r="AC349" t="n">
-        <v>13.303</v>
+        <v>13.25</v>
       </c>
       <c r="AD349" t="n">
-        <v>18.21</v>
+        <v>18.057</v>
       </c>
       <c r="AE349" t="n">
-        <v>9.092000000000001</v>
+        <v>9.182</v>
       </c>
       <c r="AF349" t="n">
-        <v>21.646</v>
+        <v>21.557</v>
       </c>
       <c r="AG349" t="n">
-        <v>14.199</v>
+        <v>13.977</v>
       </c>
       <c r="AH349" t="n">
-        <v>6.656</v>
+        <v>6.727</v>
       </c>
       <c r="AI349" t="n">
-        <v>3.54</v>
+        <v>3.455</v>
       </c>
       <c r="AJ349" t="n">
-        <v>18.092</v>
+        <v>18</v>
       </c>
       <c r="AK349" t="n">
-        <v>-2.2</v>
+        <v>-4</v>
       </c>
       <c r="AL349" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
@@ -42506,22 +42506,22 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F351" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G351" t="b">
         <v>1</v>
       </c>
       <c r="H351" t="n">
-        <v>1369.226</v>
+        <v>1366.78</v>
       </c>
       <c r="I351" t="n">
-        <v>-3.6607</v>
+        <v>-3.5941</v>
       </c>
       <c r="J351" t="n">
-        <v>1412.9</v>
+        <v>1412.8</v>
       </c>
       <c r="K351" t="n">
         <v>341</v>
@@ -42542,70 +42542,70 @@
         <v>339</v>
       </c>
       <c r="Q351" t="n">
-        <v>102.22</v>
+        <v>101.867</v>
       </c>
       <c r="R351" t="n">
-        <v>117.269</v>
+        <v>117</v>
       </c>
       <c r="S351" t="n">
-        <v>-15.049</v>
+        <v>-15.132</v>
       </c>
       <c r="T351" t="n">
-        <v>0.3086</v>
+        <v>0.30359</v>
       </c>
       <c r="U351" t="n">
-        <v>0.16701</v>
+        <v>0.16856</v>
       </c>
       <c r="V351" t="n">
-        <v>68.16</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="W351" t="n">
-        <v>78.3</v>
+        <v>77.91</v>
       </c>
       <c r="X351" t="n">
-        <v>0.2564</v>
+        <v>0.2475</v>
       </c>
       <c r="Y351" t="n">
-        <v>23.835</v>
+        <v>23.894</v>
       </c>
       <c r="Z351" t="n">
-        <v>55.795</v>
+        <v>55.687</v>
       </c>
       <c r="AA351" t="n">
-        <v>5.747</v>
+        <v>5.742</v>
       </c>
       <c r="AB351" t="n">
-        <v>18.689</v>
+        <v>18.753</v>
       </c>
       <c r="AC351" t="n">
-        <v>14.747</v>
+        <v>14.227</v>
       </c>
       <c r="AD351" t="n">
-        <v>21.505</v>
+        <v>20.788</v>
       </c>
       <c r="AE351" t="n">
-        <v>9.523999999999999</v>
+        <v>9.359</v>
       </c>
       <c r="AF351" t="n">
-        <v>20.941</v>
+        <v>21.056</v>
       </c>
       <c r="AG351" t="n">
-        <v>9.542</v>
+        <v>9.702</v>
       </c>
       <c r="AH351" t="n">
-        <v>6.414</v>
+        <v>6.298</v>
       </c>
       <c r="AI351" t="n">
-        <v>3.659</v>
+        <v>3.682</v>
       </c>
       <c r="AJ351" t="n">
-        <v>15.161</v>
+        <v>14.995</v>
       </c>
       <c r="AK351" t="n">
-        <v>-6</v>
+        <v>-9.4</v>
       </c>
       <c r="AL351" t="n">
-        <v>-9.4</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="352">
@@ -42746,22 +42746,22 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F353" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G353" t="b">
         <v>1</v>
       </c>
       <c r="H353" t="n">
-        <v>1283.029</v>
+        <v>1286.257</v>
       </c>
       <c r="I353" t="n">
-        <v>1.0009</v>
+        <v>0.9611</v>
       </c>
       <c r="J353" t="n">
-        <v>1434.8</v>
+        <v>1431.3</v>
       </c>
       <c r="K353" t="n">
         <v>275</v>
@@ -42782,67 +42782,67 @@
         <v>285</v>
       </c>
       <c r="Q353" t="n">
-        <v>119.407</v>
+        <v>119.631</v>
       </c>
       <c r="R353" t="n">
-        <v>125.438</v>
+        <v>125.422</v>
       </c>
       <c r="S353" t="n">
-        <v>-6.031</v>
+        <v>-5.792</v>
       </c>
       <c r="T353" t="n">
-        <v>0.22588</v>
+        <v>0.22525</v>
       </c>
       <c r="U353" t="n">
-        <v>0.1446</v>
+        <v>0.14317</v>
       </c>
       <c r="V353" t="n">
-        <v>79.36</v>
+        <v>79.16</v>
       </c>
       <c r="W353" t="n">
-        <v>83.48999999999999</v>
+        <v>83.17</v>
       </c>
       <c r="X353" t="n">
-        <v>0.3636</v>
+        <v>0.3851</v>
       </c>
       <c r="Y353" t="n">
-        <v>27.914</v>
+        <v>27.829</v>
       </c>
       <c r="Z353" t="n">
-        <v>54.045</v>
+        <v>53.966</v>
       </c>
       <c r="AA353" t="n">
-        <v>8.433999999999999</v>
+        <v>8.452999999999999</v>
       </c>
       <c r="AB353" t="n">
-        <v>22.121</v>
+        <v>22.05</v>
       </c>
       <c r="AC353" t="n">
-        <v>15.096</v>
+        <v>15.053</v>
       </c>
       <c r="AD353" t="n">
-        <v>19.152</v>
+        <v>19.043</v>
       </c>
       <c r="AE353" t="n">
-        <v>5.621</v>
+        <v>5.624</v>
       </c>
       <c r="AF353" t="n">
-        <v>19.646</v>
+        <v>19.72</v>
       </c>
       <c r="AG353" t="n">
-        <v>14.894</v>
+        <v>14.699</v>
       </c>
       <c r="AH353" t="n">
-        <v>5.859</v>
+        <v>5.776</v>
       </c>
       <c r="AI353" t="n">
-        <v>1.631</v>
+        <v>1.711</v>
       </c>
       <c r="AJ353" t="n">
-        <v>17.354</v>
+        <v>17.186</v>
       </c>
       <c r="AK353" t="n">
-        <v>-3.4</v>
+        <v>1.2</v>
       </c>
       <c r="AL353" t="n">
         <v>1.8</v>
@@ -43346,22 +43346,22 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F358" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G358" t="b">
         <v>1</v>
       </c>
       <c r="H358" t="n">
-        <v>1350.714</v>
+        <v>1353.227</v>
       </c>
       <c r="I358" t="n">
-        <v>1.4823</v>
+        <v>1.4009</v>
       </c>
       <c r="J358" t="n">
-        <v>1391.8</v>
+        <v>1391.1</v>
       </c>
       <c r="K358" t="n">
         <v>269</v>
@@ -43382,70 +43382,70 @@
         <v>263</v>
       </c>
       <c r="Q358" t="n">
-        <v>102.355</v>
+        <v>101.696</v>
       </c>
       <c r="R358" t="n">
-        <v>103.311</v>
+        <v>102.394</v>
       </c>
       <c r="S358" t="n">
-        <v>-0.956</v>
+        <v>-0.697</v>
       </c>
       <c r="T358" t="n">
-        <v>0.31135</v>
+        <v>0.31199</v>
       </c>
       <c r="U358" t="n">
-        <v>0.1801</v>
+        <v>0.17843</v>
       </c>
       <c r="V358" t="n">
-        <v>74.95</v>
+        <v>74.62</v>
       </c>
       <c r="W358" t="n">
-        <v>75.67</v>
+        <v>75.12</v>
       </c>
       <c r="X358" t="n">
-        <v>0.5062</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="Y358" t="n">
-        <v>27.018</v>
+        <v>26.625</v>
       </c>
       <c r="Z358" t="n">
-        <v>61.065</v>
+        <v>61.068</v>
       </c>
       <c r="AA358" t="n">
-        <v>5.743</v>
+        <v>5.545</v>
       </c>
       <c r="AB358" t="n">
-        <v>19.048</v>
+        <v>18.852</v>
       </c>
       <c r="AC358" t="n">
-        <v>15.173</v>
+        <v>15.83</v>
       </c>
       <c r="AD358" t="n">
-        <v>22.443</v>
+        <v>23.466</v>
       </c>
       <c r="AE358" t="n">
-        <v>10.896</v>
+        <v>11.091</v>
       </c>
       <c r="AF358" t="n">
-        <v>23.684</v>
+        <v>24.023</v>
       </c>
       <c r="AG358" t="n">
-        <v>13.414</v>
+        <v>13.205</v>
       </c>
       <c r="AH358" t="n">
-        <v>8.305</v>
+        <v>8.489000000000001</v>
       </c>
       <c r="AI358" t="n">
-        <v>4.377</v>
+        <v>4.341</v>
       </c>
       <c r="AJ358" t="n">
-        <v>17.623</v>
+        <v>17.614</v>
       </c>
       <c r="AK358" t="n">
-        <v>-3.6</v>
+        <v>0.8</v>
       </c>
       <c r="AL358" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="359">
@@ -43706,22 +43706,22 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F361" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G361" t="b">
         <v>1</v>
       </c>
       <c r="H361" t="n">
-        <v>1284.585</v>
+        <v>1287.953</v>
       </c>
       <c r="I361" t="n">
-        <v>-1.042</v>
+        <v>-0.9737</v>
       </c>
       <c r="J361" t="n">
-        <v>1384.8</v>
+        <v>1382.6</v>
       </c>
       <c r="K361" t="n">
         <v>337</v>
@@ -43742,70 +43742,70 @@
         <v>335</v>
       </c>
       <c r="Q361" t="n">
-        <v>94.735</v>
+        <v>95.73699999999999</v>
       </c>
       <c r="R361" t="n">
-        <v>103.554</v>
+        <v>103.532</v>
       </c>
       <c r="S361" t="n">
-        <v>-8.819000000000001</v>
+        <v>-7.795</v>
       </c>
       <c r="T361" t="n">
-        <v>0.26235</v>
+        <v>0.26104</v>
       </c>
       <c r="U361" t="n">
-        <v>0.18875</v>
+        <v>0.1857</v>
       </c>
       <c r="V361" t="n">
-        <v>64.2</v>
+        <v>64.88</v>
       </c>
       <c r="W361" t="n">
-        <v>70.01000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="X361" t="n">
-        <v>0.3054</v>
+        <v>0.3432</v>
       </c>
       <c r="Y361" t="n">
-        <v>23.152</v>
+        <v>23.322</v>
       </c>
       <c r="Z361" t="n">
-        <v>57.146</v>
+        <v>57.366</v>
       </c>
       <c r="AA361" t="n">
-        <v>7.237</v>
+        <v>7.611</v>
       </c>
       <c r="AB361" t="n">
-        <v>22.663</v>
+        <v>23.466</v>
       </c>
       <c r="AC361" t="n">
-        <v>10.655</v>
+        <v>10.621</v>
       </c>
       <c r="AD361" t="n">
-        <v>15.582</v>
+        <v>15.409</v>
       </c>
       <c r="AE361" t="n">
-        <v>8.98</v>
+        <v>8.933999999999999</v>
       </c>
       <c r="AF361" t="n">
-        <v>25.516</v>
+        <v>25.567</v>
       </c>
       <c r="AG361" t="n">
-        <v>12.014</v>
+        <v>12.158</v>
       </c>
       <c r="AH361" t="n">
-        <v>4.409</v>
+        <v>4.665</v>
       </c>
       <c r="AI361" t="n">
-        <v>4.018</v>
+        <v>3.985</v>
       </c>
       <c r="AJ361" t="n">
-        <v>16.15</v>
+        <v>16.051</v>
       </c>
       <c r="AK361" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="AL361" t="n">
-        <v>-1.6</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="362">
@@ -43946,22 +43946,22 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F363" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G363" t="b">
         <v>1</v>
       </c>
       <c r="H363" t="n">
-        <v>1335.634</v>
+        <v>1332.266</v>
       </c>
       <c r="I363" t="n">
-        <v>1.1375</v>
+        <v>1.0779</v>
       </c>
       <c r="J363" t="n">
-        <v>1382.1</v>
+        <v>1377.7</v>
       </c>
       <c r="K363" t="n">
         <v>289</v>
@@ -43982,70 +43982,70 @@
         <v>287</v>
       </c>
       <c r="Q363" t="n">
-        <v>105.127</v>
+        <v>105.225</v>
       </c>
       <c r="R363" t="n">
-        <v>106.424</v>
+        <v>106.985</v>
       </c>
       <c r="S363" t="n">
-        <v>-1.298</v>
+        <v>-1.76</v>
       </c>
       <c r="T363" t="n">
-        <v>0.2146</v>
+        <v>0.22075</v>
       </c>
       <c r="U363" t="n">
-        <v>0.18263</v>
+        <v>0.18199</v>
       </c>
       <c r="V363" t="n">
-        <v>72.17</v>
+        <v>72.3</v>
       </c>
       <c r="W363" t="n">
-        <v>73.55</v>
+        <v>74</v>
       </c>
       <c r="X363" t="n">
-        <v>0.4598</v>
+        <v>0.4455</v>
       </c>
       <c r="Y363" t="n">
-        <v>24.663</v>
+        <v>24.7</v>
       </c>
       <c r="Z363" t="n">
-        <v>53.803</v>
+        <v>54.264</v>
       </c>
       <c r="AA363" t="n">
-        <v>7.514</v>
+        <v>7.586</v>
       </c>
       <c r="AB363" t="n">
-        <v>21.934</v>
+        <v>22.164</v>
       </c>
       <c r="AC363" t="n">
-        <v>15.328</v>
+        <v>15.318</v>
       </c>
       <c r="AD363" t="n">
-        <v>21.335</v>
+        <v>21.336</v>
       </c>
       <c r="AE363" t="n">
-        <v>6.857</v>
+        <v>7.223</v>
       </c>
       <c r="AF363" t="n">
-        <v>25.286</v>
+        <v>25.418</v>
       </c>
       <c r="AG363" t="n">
-        <v>14.036</v>
+        <v>13.927</v>
       </c>
       <c r="AH363" t="n">
-        <v>5.573</v>
+        <v>5.45</v>
       </c>
       <c r="AI363" t="n">
-        <v>3.233</v>
+        <v>3.3</v>
       </c>
       <c r="AJ363" t="n">
-        <v>17.573</v>
+        <v>17.495</v>
       </c>
       <c r="AK363" t="n">
-        <v>3.6</v>
+        <v>-2</v>
       </c>
       <c r="AL363" t="n">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="364">
@@ -44066,22 +44066,22 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F364" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G364" t="b">
         <v>1</v>
       </c>
       <c r="H364" t="n">
-        <v>1374.829</v>
+        <v>1376.296</v>
       </c>
       <c r="I364" t="n">
-        <v>-1.2655</v>
+        <v>-1.16</v>
       </c>
       <c r="J364" t="n">
-        <v>1383.1</v>
+        <v>1378.9</v>
       </c>
       <c r="K364" t="n">
         <v>286</v>
@@ -44102,70 +44102,70 @@
         <v>278</v>
       </c>
       <c r="Q364" t="n">
-        <v>104.448</v>
+        <v>104.783</v>
       </c>
       <c r="R364" t="n">
-        <v>105.676</v>
+        <v>105.395</v>
       </c>
       <c r="S364" t="n">
-        <v>-1.228</v>
+        <v>-0.612</v>
       </c>
       <c r="T364" t="n">
-        <v>0.26796</v>
+        <v>0.26149</v>
       </c>
       <c r="U364" t="n">
-        <v>0.13424</v>
+        <v>0.13659</v>
       </c>
       <c r="V364" t="n">
-        <v>68.62</v>
+        <v>68.61</v>
       </c>
       <c r="W364" t="n">
-        <v>69.2</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="X364" t="n">
-        <v>0.4545</v>
+        <v>0.4723</v>
       </c>
       <c r="Y364" t="n">
-        <v>25.886</v>
+        <v>25.858</v>
       </c>
       <c r="Z364" t="n">
-        <v>58.352</v>
+        <v>57.807</v>
       </c>
       <c r="AA364" t="n">
-        <v>5.795</v>
+        <v>5.802</v>
       </c>
       <c r="AB364" t="n">
-        <v>18.261</v>
+        <v>18.22</v>
       </c>
       <c r="AC364" t="n">
-        <v>11.057</v>
+        <v>11.097</v>
       </c>
       <c r="AD364" t="n">
-        <v>15.045</v>
+        <v>14.978</v>
       </c>
       <c r="AE364" t="n">
-        <v>8.193</v>
+        <v>7.958</v>
       </c>
       <c r="AF364" t="n">
-        <v>21.727</v>
+        <v>21.909</v>
       </c>
       <c r="AG364" t="n">
-        <v>13.955</v>
+        <v>13.967</v>
       </c>
       <c r="AH364" t="n">
-        <v>7.17</v>
+        <v>7.078</v>
       </c>
       <c r="AI364" t="n">
-        <v>3.807</v>
+        <v>3.813</v>
       </c>
       <c r="AJ364" t="n">
-        <v>18.386</v>
+        <v>18.373</v>
       </c>
       <c r="AK364" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AL364" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="365">
@@ -44186,22 +44186,22 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F365" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G365" t="b">
         <v>1</v>
       </c>
       <c r="H365" t="n">
-        <v>1340.953</v>
+        <v>1343.287</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.6037</v>
+        <v>-0.6063</v>
       </c>
       <c r="J365" t="n">
-        <v>1409.8</v>
+        <v>1405.4</v>
       </c>
       <c r="K365" t="n">
         <v>307</v>
@@ -44222,70 +44222,70 @@
         <v>300</v>
       </c>
       <c r="Q365" t="n">
-        <v>106.153</v>
+        <v>107.117</v>
       </c>
       <c r="R365" t="n">
-        <v>113.64</v>
+        <v>114.063</v>
       </c>
       <c r="S365" t="n">
-        <v>-7.487</v>
+        <v>-6.946</v>
       </c>
       <c r="T365" t="n">
-        <v>0.30594</v>
+        <v>0.30593</v>
       </c>
       <c r="U365" t="n">
-        <v>0.15285</v>
+        <v>0.15279</v>
       </c>
       <c r="V365" t="n">
-        <v>75.14</v>
+        <v>75.95</v>
       </c>
       <c r="W365" t="n">
-        <v>80.45999999999999</v>
+        <v>80.88</v>
       </c>
       <c r="X365" t="n">
-        <v>0.4356</v>
+        <v>0.4545</v>
       </c>
       <c r="Y365" t="n">
-        <v>27.695</v>
+        <v>27.92</v>
       </c>
       <c r="Z365" t="n">
-        <v>62.55</v>
+        <v>62.58</v>
       </c>
       <c r="AA365" t="n">
-        <v>6.882</v>
+        <v>7.034</v>
       </c>
       <c r="AB365" t="n">
-        <v>20.529</v>
+        <v>20.693</v>
       </c>
       <c r="AC365" t="n">
-        <v>12.869</v>
+        <v>13.08</v>
       </c>
       <c r="AD365" t="n">
-        <v>18.337</v>
+        <v>18.636</v>
       </c>
       <c r="AE365" t="n">
-        <v>10.459</v>
+        <v>10.534</v>
       </c>
       <c r="AF365" t="n">
-        <v>23.18</v>
+        <v>23.375</v>
       </c>
       <c r="AG365" t="n">
-        <v>12.649</v>
+        <v>12.489</v>
       </c>
       <c r="AH365" t="n">
-        <v>6.519</v>
+        <v>6.341</v>
       </c>
       <c r="AI365" t="n">
-        <v>4.85</v>
+        <v>4.705</v>
       </c>
       <c r="AJ365" t="n">
-        <v>17.284</v>
+        <v>17.239</v>
       </c>
       <c r="AK365" t="n">
-        <v>-1.4</v>
+        <v>3.6</v>
       </c>
       <c r="AL365" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="366">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -635,13 +635,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1409.551</v>
+        <v>1409.54</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0946</v>
+        <v>0.0979</v>
       </c>
       <c r="J2" t="n">
-        <v>1499.8</v>
+        <v>1500.4</v>
       </c>
       <c r="K2" t="n">
         <v>228</v>
@@ -755,13 +755,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1257.848</v>
+        <v>1257.142</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.3848</v>
+        <v>-2.4029</v>
       </c>
       <c r="J3" t="n">
-        <v>1563.3</v>
+        <v>1561.6</v>
       </c>
       <c r="K3" t="n">
         <v>346</v>
@@ -875,13 +875,13 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1696.621</v>
+        <v>1693.697</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4591</v>
+        <v>1.6325</v>
       </c>
       <c r="J4" t="n">
-        <v>1484.3</v>
+        <v>1484</v>
       </c>
       <c r="K4" t="n">
         <v>61</v>
@@ -995,10 +995,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1966.484</v>
+        <v>1967.128</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6248</v>
+        <v>-1.6145</v>
       </c>
       <c r="J5" t="n">
         <v>1769.4</v>
@@ -1115,13 +1115,13 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1288.656</v>
+        <v>1288.496</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7739</v>
+        <v>0.7742</v>
       </c>
       <c r="J6" t="n">
-        <v>1362.7</v>
+        <v>1362.1</v>
       </c>
       <c r="K6" t="n">
         <v>303</v>
@@ -1235,13 +1235,13 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1290.524</v>
+        <v>1291.479</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4808</v>
+        <v>-2.5457</v>
       </c>
       <c r="J7" t="n">
-        <v>1387.2</v>
+        <v>1386.1</v>
       </c>
       <c r="K7" t="n">
         <v>308</v>
@@ -1355,13 +1355,13 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1297.192</v>
+        <v>1296.992</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1837</v>
+        <v>-2.1772</v>
       </c>
       <c r="J8" t="n">
-        <v>1417.8</v>
+        <v>1416.7</v>
       </c>
       <c r="K8" t="n">
         <v>321</v>
@@ -1475,13 +1475,13 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1267.463</v>
+        <v>1267.327</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4538</v>
+        <v>-1.4578</v>
       </c>
       <c r="J9" t="n">
-        <v>1413.9</v>
+        <v>1413.6</v>
       </c>
       <c r="K9" t="n">
         <v>343</v>
@@ -1595,13 +1595,13 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1407.525</v>
+        <v>1404.655</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4303</v>
+        <v>-0.3441</v>
       </c>
       <c r="J10" t="n">
-        <v>1396.1</v>
+        <v>1396.2</v>
       </c>
       <c r="K10" t="n">
         <v>241</v>
@@ -1715,13 +1715,13 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1495.113</v>
+        <v>1494.4</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.909</v>
       </c>
       <c r="J11" t="n">
-        <v>1425</v>
+        <v>1424.7</v>
       </c>
       <c r="K11" t="n">
         <v>185</v>
@@ -1835,13 +1835,13 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2242.85</v>
+        <v>2252.643</v>
       </c>
       <c r="I12" t="n">
-        <v>8.6394</v>
+        <v>8.169700000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>1747.2</v>
+        <v>1751.1</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
@@ -1955,13 +1955,13 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1681.634</v>
+        <v>1681.478</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7565</v>
+        <v>-1.7205</v>
       </c>
       <c r="J13" t="n">
-        <v>1723.9</v>
+        <v>1725.8</v>
       </c>
       <c r="K13" t="n">
         <v>66</v>
@@ -2075,13 +2075,13 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1333.464</v>
+        <v>1332.971</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5997</v>
+        <v>-1.6057</v>
       </c>
       <c r="J14" t="n">
-        <v>1401.2</v>
+        <v>1400.2</v>
       </c>
       <c r="K14" t="n">
         <v>305</v>
@@ -2195,13 +2195,13 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1257.078</v>
+        <v>1256.783</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5336</v>
+        <v>1.5341</v>
       </c>
       <c r="J15" t="n">
-        <v>1390.1</v>
+        <v>1388.9</v>
       </c>
       <c r="K15" t="n">
         <v>324</v>
@@ -2315,13 +2315,13 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1932.735</v>
+        <v>1940.056</v>
       </c>
       <c r="I16" t="n">
-        <v>6.7834</v>
+        <v>5.7735</v>
       </c>
       <c r="J16" t="n">
-        <v>1725.9</v>
+        <v>1727.6</v>
       </c>
       <c r="K16" t="n">
         <v>20</v>
@@ -2435,13 +2435,13 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1536.683</v>
+        <v>1536.248</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.7379</v>
+        <v>-2.7614</v>
       </c>
       <c r="J17" t="n">
-        <v>1450</v>
+        <v>1449.7</v>
       </c>
       <c r="K17" t="n">
         <v>143</v>
@@ -2555,13 +2555,13 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1308.563</v>
+        <v>1308.968</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7106</v>
+        <v>-0.7184</v>
       </c>
       <c r="J18" t="n">
-        <v>1381</v>
+        <v>1381.7</v>
       </c>
       <c r="K18" t="n">
         <v>336</v>
@@ -2675,13 +2675,13 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1835.829</v>
+        <v>1839.601</v>
       </c>
       <c r="I19" t="n">
-        <v>-7.2849</v>
+        <v>-7.8485</v>
       </c>
       <c r="J19" t="n">
-        <v>1745.4</v>
+        <v>1747.7</v>
       </c>
       <c r="K19" t="n">
         <v>40</v>
@@ -2795,13 +2795,13 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1470.919</v>
+        <v>1470.557</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7965</v>
+        <v>3.7809</v>
       </c>
       <c r="J20" t="n">
-        <v>1407.7</v>
+        <v>1407.6</v>
       </c>
       <c r="K20" t="n">
         <v>165</v>
@@ -2915,13 +2915,13 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1325.397</v>
+        <v>1325.117</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4952</v>
+        <v>-2.4941</v>
       </c>
       <c r="J21" t="n">
-        <v>1444.6</v>
+        <v>1443.3</v>
       </c>
       <c r="K21" t="n">
         <v>302</v>
@@ -3035,13 +3035,13 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1671.465</v>
+        <v>1674.148</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.0193</v>
+        <v>-6.5504</v>
       </c>
       <c r="J22" t="n">
-        <v>1739.8</v>
+        <v>1740.6</v>
       </c>
       <c r="K22" t="n">
         <v>51</v>
@@ -3155,13 +3155,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1753.798</v>
+        <v>1752.259</v>
       </c>
       <c r="I23" t="n">
-        <v>5.6074</v>
+        <v>5.5868</v>
       </c>
       <c r="J23" t="n">
-        <v>1487.2</v>
+        <v>1486</v>
       </c>
       <c r="K23" t="n">
         <v>55</v>
@@ -3275,13 +3275,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1375.93</v>
+        <v>1375.394</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9186</v>
+        <v>0.9205</v>
       </c>
       <c r="J24" t="n">
-        <v>1436.2</v>
+        <v>1436.6</v>
       </c>
       <c r="K24" t="n">
         <v>233</v>
@@ -3395,13 +3395,13 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1244.076</v>
+        <v>1244.292</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.8788</v>
+        <v>-4.8795</v>
       </c>
       <c r="J25" t="n">
-        <v>1366.4</v>
+        <v>1366.7</v>
       </c>
       <c r="K25" t="n">
         <v>359</v>
@@ -3515,13 +3515,13 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1727.678</v>
+        <v>1725.616</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.3169</v>
+        <v>-2.372</v>
       </c>
       <c r="J26" t="n">
-        <v>1623.5</v>
+        <v>1621.6</v>
       </c>
       <c r="K26" t="n">
         <v>60</v>
@@ -3635,13 +3635,13 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1449.736</v>
+        <v>1449.92</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.847</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>1617.9</v>
+        <v>1618.3</v>
       </c>
       <c r="K27" t="n">
         <v>162</v>
@@ -3755,10 +3755,10 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1343.047</v>
+        <v>1343.191</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.6521</v>
+        <v>-2.6522</v>
       </c>
       <c r="J28" t="n">
         <v>1377.3</v>
@@ -3875,13 +3875,13 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1419.283</v>
+        <v>1418.633</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3365</v>
+        <v>1.305</v>
       </c>
       <c r="J29" t="n">
-        <v>1468</v>
+        <v>1467.4</v>
       </c>
       <c r="K29" t="n">
         <v>149</v>
@@ -3995,13 +3995,13 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1625.805</v>
+        <v>1623.586</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4157</v>
+        <v>1.3833</v>
       </c>
       <c r="J30" t="n">
-        <v>1527.8</v>
+        <v>1526.1</v>
       </c>
       <c r="K30" t="n">
         <v>123</v>
@@ -4115,13 +4115,13 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1356.616</v>
+        <v>1356.645</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.7737</v>
+        <v>-2.7758</v>
       </c>
       <c r="J31" t="n">
-        <v>1452.4</v>
+        <v>1452.2</v>
       </c>
       <c r="K31" t="n">
         <v>283</v>
@@ -4235,13 +4235,13 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1320.375</v>
+        <v>1320.344</v>
       </c>
       <c r="I32" t="n">
-        <v>-4.972</v>
+        <v>-4.9488</v>
       </c>
       <c r="J32" t="n">
-        <v>1394.4</v>
+        <v>1395.2</v>
       </c>
       <c r="K32" t="n">
         <v>355</v>
@@ -4355,13 +4355,13 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1305.797</v>
+        <v>1306.005</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.1121</v>
+        <v>-3.1314</v>
       </c>
       <c r="J33" t="n">
-        <v>1411.3</v>
+        <v>1410.7</v>
       </c>
       <c r="K33" t="n">
         <v>335</v>
@@ -4475,13 +4475,13 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1391.429</v>
+        <v>1390.965</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2165</v>
+        <v>-0.2206</v>
       </c>
       <c r="J34" t="n">
-        <v>1459.5</v>
+        <v>1458.9</v>
       </c>
       <c r="K34" t="n">
         <v>194</v>
@@ -4595,13 +4595,13 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1615.973</v>
+        <v>1616.572</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0517</v>
+        <v>1.0682</v>
       </c>
       <c r="J35" t="n">
-        <v>1623.7</v>
+        <v>1624.9</v>
       </c>
       <c r="K35" t="n">
         <v>83</v>
@@ -4715,13 +4715,13 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1901.285</v>
+        <v>1905.773</v>
       </c>
       <c r="I36" t="n">
-        <v>2.827</v>
+        <v>2.2762</v>
       </c>
       <c r="J36" t="n">
-        <v>1712.1</v>
+        <v>1713.1</v>
       </c>
       <c r="K36" t="n">
         <v>23</v>
@@ -4835,13 +4835,13 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1341.289</v>
+        <v>1340.808</v>
       </c>
       <c r="I37" t="n">
-        <v>-2.8296</v>
+        <v>-2.8385</v>
       </c>
       <c r="J37" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K37" t="n">
         <v>263</v>
@@ -4955,13 +4955,13 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1399.228</v>
+        <v>1398.534</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.283</v>
+        <v>-0.3112</v>
       </c>
       <c r="J38" t="n">
-        <v>1499.9</v>
+        <v>1499.6</v>
       </c>
       <c r="K38" t="n">
         <v>214</v>
@@ -5075,13 +5075,13 @@
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1728.495</v>
+        <v>1730.252</v>
       </c>
       <c r="I39" t="n">
-        <v>8.044</v>
+        <v>8.0456</v>
       </c>
       <c r="J39" t="n">
-        <v>1599.2</v>
+        <v>1600</v>
       </c>
       <c r="K39" t="n">
         <v>73</v>
@@ -5195,13 +5195,13 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1390.018</v>
+        <v>1389.48</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1499</v>
+        <v>0.1605</v>
       </c>
       <c r="J40" t="n">
-        <v>1517.7</v>
+        <v>1516.7</v>
       </c>
       <c r="K40" t="n">
         <v>192</v>
@@ -5315,13 +5315,13 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1287.621</v>
+        <v>1287.984</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4761</v>
+        <v>-0.4768</v>
       </c>
       <c r="J41" t="n">
-        <v>1434.3</v>
+        <v>1434.6</v>
       </c>
       <c r="K41" t="n">
         <v>344</v>
@@ -5435,13 +5435,13 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1364.997</v>
+        <v>1365.026</v>
       </c>
       <c r="I42" t="n">
-        <v>3.1006</v>
+        <v>3.0881</v>
       </c>
       <c r="J42" t="n">
-        <v>1443.1</v>
+        <v>1443.7</v>
       </c>
       <c r="K42" t="n">
         <v>154</v>
@@ -5555,13 +5555,13 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1450.905</v>
+        <v>1451.52</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.6833</v>
+        <v>-2.7012</v>
       </c>
       <c r="J43" t="n">
-        <v>1359</v>
+        <v>1359.6</v>
       </c>
       <c r="K43" t="n">
         <v>299</v>
@@ -5675,13 +5675,13 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1330.46</v>
+        <v>1330.459</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0665</v>
+        <v>1.0554</v>
       </c>
       <c r="J44" t="n">
-        <v>1390.3</v>
+        <v>1390</v>
       </c>
       <c r="K44" t="n">
         <v>244</v>
@@ -5795,13 +5795,13 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1440.393</v>
+        <v>1439.346</v>
       </c>
       <c r="I45" t="n">
-        <v>1.3894</v>
+        <v>1.3639</v>
       </c>
       <c r="J45" t="n">
-        <v>1493.2</v>
+        <v>1491.9</v>
       </c>
       <c r="K45" t="n">
         <v>183</v>
@@ -5915,13 +5915,13 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1392.013</v>
+        <v>1392.053</v>
       </c>
       <c r="I46" t="n">
-        <v>-4.0171</v>
+        <v>-4.0162</v>
       </c>
       <c r="J46" t="n">
-        <v>1428.5</v>
+        <v>1429</v>
       </c>
       <c r="K46" t="n">
         <v>298</v>
@@ -6035,13 +6035,13 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1215.857</v>
+        <v>1216.315</v>
       </c>
       <c r="I47" t="n">
-        <v>-2.0217</v>
+        <v>-2.027</v>
       </c>
       <c r="J47" t="n">
-        <v>1419.7</v>
+        <v>1420</v>
       </c>
       <c r="K47" t="n">
         <v>348</v>
@@ -6155,13 +6155,13 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1733.82</v>
+        <v>1733.048</v>
       </c>
       <c r="I48" t="n">
-        <v>0.433</v>
+        <v>0.4193</v>
       </c>
       <c r="J48" t="n">
-        <v>1713</v>
+        <v>1713.8</v>
       </c>
       <c r="K48" t="n">
         <v>44</v>
@@ -6275,13 +6275,13 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1232.051</v>
+        <v>1231.812</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1473</v>
+        <v>-0.1472</v>
       </c>
       <c r="J49" t="n">
-        <v>1417.6</v>
+        <v>1417.3</v>
       </c>
       <c r="K49" t="n">
         <v>351</v>
@@ -6395,13 +6395,13 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1839.653</v>
+        <v>1836.391</v>
       </c>
       <c r="I50" t="n">
-        <v>3.0742</v>
+        <v>3.8425</v>
       </c>
       <c r="J50" t="n">
-        <v>1652.1</v>
+        <v>1652.4</v>
       </c>
       <c r="K50" t="n">
         <v>36</v>
@@ -6515,13 +6515,13 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1356.605</v>
+        <v>1356.663</v>
       </c>
       <c r="I51" t="n">
-        <v>-2.5339</v>
+        <v>-2.5505</v>
       </c>
       <c r="J51" t="n">
-        <v>1460.6</v>
+        <v>1460</v>
       </c>
       <c r="K51" t="n">
         <v>320</v>
@@ -6635,13 +6635,13 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>1428.057</v>
+        <v>1428.244</v>
       </c>
       <c r="I52" t="n">
-        <v>3.9316</v>
+        <v>3.9203</v>
       </c>
       <c r="J52" t="n">
-        <v>1430</v>
+        <v>1429.7</v>
       </c>
       <c r="K52" t="n">
         <v>231</v>
@@ -6755,13 +6755,13 @@
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1580.265</v>
+        <v>1578.343</v>
       </c>
       <c r="I53" t="n">
-        <v>1.5895</v>
+        <v>1.6342</v>
       </c>
       <c r="J53" t="n">
-        <v>1483.9</v>
+        <v>1482.2</v>
       </c>
       <c r="K53" t="n">
         <v>147</v>
@@ -6875,13 +6875,13 @@
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>1421.383</v>
+        <v>1421.786</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1948</v>
+        <v>0.2169</v>
       </c>
       <c r="J54" t="n">
-        <v>1420.4</v>
+        <v>1422</v>
       </c>
       <c r="K54" t="n">
         <v>254</v>
@@ -6995,13 +6995,13 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1613.087</v>
+        <v>1614.086</v>
       </c>
       <c r="I55" t="n">
-        <v>-4.5669</v>
+        <v>-4.609</v>
       </c>
       <c r="J55" t="n">
-        <v>1667.2</v>
+        <v>1668.4</v>
       </c>
       <c r="K55" t="n">
         <v>72</v>
@@ -7115,13 +7115,13 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1673.565</v>
+        <v>1673.239</v>
       </c>
       <c r="I56" t="n">
-        <v>-5.2938</v>
+        <v>-5.7426</v>
       </c>
       <c r="J56" t="n">
-        <v>1559.4</v>
+        <v>1557.5</v>
       </c>
       <c r="K56" t="n">
         <v>86</v>
@@ -7235,13 +7235,13 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>1458.456</v>
+        <v>1459.013</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.273</v>
+        <v>-0.3016</v>
       </c>
       <c r="J57" t="n">
-        <v>1464</v>
+        <v>1464.7</v>
       </c>
       <c r="K57" t="n">
         <v>189</v>
@@ -7355,13 +7355,13 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>2083.797</v>
+        <v>2092.783</v>
       </c>
       <c r="I58" t="n">
-        <v>9.8756</v>
+        <v>9.4907</v>
       </c>
       <c r="J58" t="n">
-        <v>1664.7</v>
+        <v>1667.4</v>
       </c>
       <c r="K58" t="n">
         <v>10</v>
@@ -7475,13 +7475,13 @@
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1180.826</v>
+        <v>1180.884</v>
       </c>
       <c r="I59" t="n">
-        <v>-2.275</v>
+        <v>-2.2819</v>
       </c>
       <c r="J59" t="n">
-        <v>1404.9</v>
+        <v>1404.8</v>
       </c>
       <c r="K59" t="n">
         <v>363</v>
@@ -7595,13 +7595,13 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>1488.865</v>
+        <v>1488.803</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.5084</v>
+        <v>-1.5132</v>
       </c>
       <c r="J60" t="n">
-        <v>1493</v>
+        <v>1493.2</v>
       </c>
       <c r="K60" t="n">
         <v>167</v>
@@ -7715,13 +7715,13 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>1672.47</v>
+        <v>1675.022</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.8294</v>
+        <v>-2.3235</v>
       </c>
       <c r="J61" t="n">
-        <v>1663.7</v>
+        <v>1664.3</v>
       </c>
       <c r="K61" t="n">
         <v>82</v>
@@ -7835,13 +7835,13 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>1310.272</v>
+        <v>1310.189</v>
       </c>
       <c r="I62" t="n">
-        <v>-2.3085</v>
+        <v>-2.3163</v>
       </c>
       <c r="J62" t="n">
-        <v>1471.4</v>
+        <v>1471.2</v>
       </c>
       <c r="K62" t="n">
         <v>326</v>
@@ -7955,13 +7955,13 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>1387.921</v>
+        <v>1387.378</v>
       </c>
       <c r="I63" t="n">
-        <v>2.9774</v>
+        <v>2.9397</v>
       </c>
       <c r="J63" t="n">
-        <v>1481.2</v>
+        <v>1480.3</v>
       </c>
       <c r="K63" t="n">
         <v>171</v>
@@ -8075,13 +8075,13 @@
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>1513.658</v>
+        <v>1512.475</v>
       </c>
       <c r="I64" t="n">
-        <v>1.7826</v>
+        <v>1.7707</v>
       </c>
       <c r="J64" t="n">
-        <v>1453.5</v>
+        <v>1452.8</v>
       </c>
       <c r="K64" t="n">
         <v>164</v>
@@ -8195,13 +8195,13 @@
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>1273.846</v>
+        <v>1273.701</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1269</v>
+        <v>0.1278</v>
       </c>
       <c r="J65" t="n">
-        <v>1444.7</v>
+        <v>1445.1</v>
       </c>
       <c r="K65" t="n">
         <v>268</v>
@@ -8315,13 +8315,13 @@
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>1367.276</v>
+        <v>1367.602</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1568</v>
+        <v>0.1875</v>
       </c>
       <c r="J66" t="n">
-        <v>1471.8</v>
+        <v>1473.1</v>
       </c>
       <c r="K66" t="n">
         <v>267</v>
@@ -8435,13 +8435,13 @@
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1523.046</v>
+        <v>1522.307</v>
       </c>
       <c r="I67" t="n">
-        <v>-2.809</v>
+        <v>-2.8164</v>
       </c>
       <c r="J67" t="n">
-        <v>1542.6</v>
+        <v>1541.6</v>
       </c>
       <c r="K67" t="n">
         <v>106</v>
@@ -8555,13 +8555,13 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1675.017</v>
+        <v>1675.338</v>
       </c>
       <c r="I68" t="n">
-        <v>-2.7831</v>
+        <v>-2.825</v>
       </c>
       <c r="J68" t="n">
-        <v>1553.6</v>
+        <v>1553.3</v>
       </c>
       <c r="K68" t="n">
         <v>75</v>
@@ -8675,13 +8675,13 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>1379.224</v>
+        <v>1379.609</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.4201</v>
+        <v>-1.4438</v>
       </c>
       <c r="J69" t="n">
-        <v>1481.3</v>
+        <v>1481.5</v>
       </c>
       <c r="K69" t="n">
         <v>279</v>
@@ -8795,10 +8795,10 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>1255.917</v>
+        <v>1255.975</v>
       </c>
       <c r="I70" t="n">
-        <v>-3.1804</v>
+        <v>-3.1819</v>
       </c>
       <c r="J70" t="n">
         <v>1357.2</v>
@@ -8915,13 +8915,13 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>1383.339</v>
+        <v>1384.316</v>
       </c>
       <c r="I71" t="n">
-        <v>0.7916</v>
+        <v>0.8096</v>
       </c>
       <c r="J71" t="n">
-        <v>1450.2</v>
+        <v>1451</v>
       </c>
       <c r="K71" t="n">
         <v>224</v>
@@ -9035,13 +9035,13 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1586.703</v>
+        <v>1587.454</v>
       </c>
       <c r="I72" t="n">
-        <v>5.744</v>
+        <v>5.7347</v>
       </c>
       <c r="J72" t="n">
-        <v>1607.9</v>
+        <v>1608.9</v>
       </c>
       <c r="K72" t="n">
         <v>95</v>
@@ -9155,13 +9155,13 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>1321.378</v>
+        <v>1321.596</v>
       </c>
       <c r="I73" t="n">
-        <v>1.5671</v>
+        <v>1.5666</v>
       </c>
       <c r="J73" t="n">
-        <v>1448.6</v>
+        <v>1449.2</v>
       </c>
       <c r="K73" t="n">
         <v>232</v>
@@ -9275,13 +9275,13 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>1501.67</v>
+        <v>1499.496</v>
       </c>
       <c r="I74" t="n">
-        <v>-7.4324</v>
+        <v>-7.1954</v>
       </c>
       <c r="J74" t="n">
-        <v>1522</v>
+        <v>1520.7</v>
       </c>
       <c r="K74" t="n">
         <v>213</v>
@@ -9395,13 +9395,13 @@
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>1421.04</v>
+        <v>1420.912</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0515</v>
+        <v>-0.0564</v>
       </c>
       <c r="J75" t="n">
-        <v>1440.1</v>
+        <v>1439.6</v>
       </c>
       <c r="K75" t="n">
         <v>220</v>
@@ -9515,13 +9515,13 @@
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>2170.059</v>
+        <v>2179.543</v>
       </c>
       <c r="I76" t="n">
-        <v>3.9737</v>
+        <v>3.6659</v>
       </c>
       <c r="J76" t="n">
-        <v>1690.2</v>
+        <v>1692</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
@@ -9635,13 +9635,13 @@
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>1476.582</v>
+        <v>1477.086</v>
       </c>
       <c r="I77" t="n">
-        <v>-2.3487</v>
+        <v>-2.429</v>
       </c>
       <c r="J77" t="n">
-        <v>1541.8</v>
+        <v>1541.5</v>
       </c>
       <c r="K77" t="n">
         <v>125</v>
@@ -9755,13 +9755,13 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>1287.674</v>
+        <v>1287.44</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.7731</v>
+        <v>-0.7794</v>
       </c>
       <c r="J78" t="n">
-        <v>1440.5</v>
+        <v>1439.7</v>
       </c>
       <c r="K78" t="n">
         <v>328</v>
@@ -9875,13 +9875,13 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>1322.293</v>
+        <v>1322.157</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.0434</v>
+        <v>-2.047</v>
       </c>
       <c r="J79" t="n">
-        <v>1423.7</v>
+        <v>1422.5</v>
       </c>
       <c r="K79" t="n">
         <v>285</v>
@@ -9995,13 +9995,13 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>1372.026</v>
+        <v>1372.539</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.3224</v>
+        <v>-1.3602</v>
       </c>
       <c r="J80" t="n">
-        <v>1480.6</v>
+        <v>1479.8</v>
       </c>
       <c r="K80" t="n">
         <v>237</v>
@@ -10115,13 +10115,13 @@
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>1315.909</v>
+        <v>1316.019</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3224</v>
+        <v>-1.332</v>
       </c>
       <c r="J81" t="n">
-        <v>1454.4</v>
+        <v>1454.6</v>
       </c>
       <c r="K81" t="n">
         <v>158</v>
@@ -10235,13 +10235,13 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>1384.025</v>
+        <v>1383.342</v>
       </c>
       <c r="I82" t="n">
-        <v>-2.6614</v>
+        <v>-2.6565</v>
       </c>
       <c r="J82" t="n">
-        <v>1518.5</v>
+        <v>1517.9</v>
       </c>
       <c r="K82" t="n">
         <v>252</v>
@@ -10355,13 +10355,13 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>1459.911</v>
+        <v>1457.934</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.6671</v>
+        <v>-1.6152</v>
       </c>
       <c r="J83" t="n">
-        <v>1380.7</v>
+        <v>1379.3</v>
       </c>
       <c r="K83" t="n">
         <v>250</v>
@@ -10475,13 +10475,13 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>1464.99</v>
+        <v>1464.598</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9038</v>
+        <v>0.8972</v>
       </c>
       <c r="J84" t="n">
-        <v>1490</v>
+        <v>1489.3</v>
       </c>
       <c r="K84" t="n">
         <v>219</v>
@@ -10595,13 +10595,13 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>1515.014</v>
+        <v>1514.772</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5934</v>
+        <v>0.598</v>
       </c>
       <c r="J85" t="n">
-        <v>1424.7</v>
+        <v>1424.6</v>
       </c>
       <c r="K85" t="n">
         <v>140</v>
@@ -10715,13 +10715,13 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>1329.788</v>
+        <v>1329.103</v>
       </c>
       <c r="I86" t="n">
-        <v>-2.036</v>
+        <v>-2.0436</v>
       </c>
       <c r="J86" t="n">
-        <v>1568.2</v>
+        <v>1566.8</v>
       </c>
       <c r="K86" t="n">
         <v>310</v>
@@ -10835,13 +10835,13 @@
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>1258.741</v>
+        <v>1261.746</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.7963</v>
+        <v>-1.8723</v>
       </c>
       <c r="J87" t="n">
-        <v>1388.9</v>
+        <v>1387.9</v>
       </c>
       <c r="K87" t="n">
         <v>333</v>
@@ -10955,13 +10955,13 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1438.411</v>
+        <v>1438.765</v>
       </c>
       <c r="I88" t="n">
-        <v>1.6395</v>
+        <v>1.6325</v>
       </c>
       <c r="J88" t="n">
-        <v>1401.2</v>
+        <v>1401.7</v>
       </c>
       <c r="K88" t="n">
         <v>270</v>
@@ -11075,13 +11075,13 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1579.399</v>
+        <v>1577.292</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2688</v>
+        <v>-1.2377</v>
       </c>
       <c r="J89" t="n">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="K89" t="n">
         <v>121</v>
@@ -11195,13 +11195,13 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>1395.461</v>
+        <v>1394.944</v>
       </c>
       <c r="I90" t="n">
-        <v>-3.6887</v>
+        <v>-3.6949</v>
       </c>
       <c r="J90" t="n">
-        <v>1432.7</v>
+        <v>1432</v>
       </c>
       <c r="K90" t="n">
         <v>264</v>
@@ -11315,13 +11315,13 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>1993.623</v>
+        <v>2002.23</v>
       </c>
       <c r="I91" t="n">
-        <v>4.3059</v>
+        <v>2.5717</v>
       </c>
       <c r="J91" t="n">
-        <v>1699.9</v>
+        <v>1700.4</v>
       </c>
       <c r="K91" t="n">
         <v>4</v>
@@ -11435,13 +11435,13 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1295.076</v>
+        <v>1294.876</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.2209</v>
+        <v>-0.222</v>
       </c>
       <c r="J92" t="n">
-        <v>1380.3</v>
+        <v>1379.3</v>
       </c>
       <c r="K92" t="n">
         <v>314</v>
@@ -11555,13 +11555,13 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>1381.124</v>
+        <v>1380.817</v>
       </c>
       <c r="I93" t="n">
-        <v>1.3949</v>
+        <v>1.3979</v>
       </c>
       <c r="J93" t="n">
-        <v>1494.9</v>
+        <v>1494.4</v>
       </c>
       <c r="K93" t="n">
         <v>198</v>
@@ -11675,13 +11675,13 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>1606.048</v>
+        <v>1607.453</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2483</v>
+        <v>-1.2916</v>
       </c>
       <c r="J94" t="n">
-        <v>1647.5</v>
+        <v>1650</v>
       </c>
       <c r="K94" t="n">
         <v>71</v>
@@ -11795,13 +11795,13 @@
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>1456.701</v>
+        <v>1457.187</v>
       </c>
       <c r="I95" t="n">
-        <v>1.1066</v>
+        <v>1.0971</v>
       </c>
       <c r="J95" t="n">
-        <v>1494.5</v>
+        <v>1494.4</v>
       </c>
       <c r="K95" t="n">
         <v>168</v>
@@ -11915,13 +11915,13 @@
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1423.403</v>
+        <v>1422.518</v>
       </c>
       <c r="I96" t="n">
-        <v>2.4993</v>
+        <v>2.4973</v>
       </c>
       <c r="J96" t="n">
-        <v>1581.4</v>
+        <v>1579.9</v>
       </c>
       <c r="K96" t="n">
         <v>126</v>
@@ -12035,13 +12035,13 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>1529.497</v>
+        <v>1529.522</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1789</v>
+        <v>1.1809</v>
       </c>
       <c r="J97" t="n">
-        <v>1418.9</v>
+        <v>1418.3</v>
       </c>
       <c r="K97" t="n">
         <v>200</v>
@@ -12155,13 +12155,13 @@
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>1540.445</v>
+        <v>1541.693</v>
       </c>
       <c r="I98" t="n">
-        <v>-4.3148</v>
+        <v>-4.2526</v>
       </c>
       <c r="J98" t="n">
-        <v>1537.4</v>
+        <v>1538.6</v>
       </c>
       <c r="K98" t="n">
         <v>76</v>
@@ -12275,13 +12275,13 @@
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>1431.019</v>
+        <v>1430.575</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7327</v>
+        <v>0.7345</v>
       </c>
       <c r="J99" t="n">
-        <v>1440.3</v>
+        <v>1440</v>
       </c>
       <c r="K99" t="n">
         <v>265</v>
@@ -12395,13 +12395,13 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>1246.951</v>
+        <v>1246.565</v>
       </c>
       <c r="I100" t="n">
-        <v>-4.7199</v>
+        <v>-4.7167</v>
       </c>
       <c r="J100" t="n">
-        <v>1444.4</v>
+        <v>1443.2</v>
       </c>
       <c r="K100" t="n">
         <v>361</v>
@@ -12515,13 +12515,13 @@
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>1707.877</v>
+        <v>1707.492</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6563</v>
       </c>
       <c r="J101" t="n">
-        <v>1505.9</v>
+        <v>1505.6</v>
       </c>
       <c r="K101" t="n">
         <v>107</v>
@@ -12635,13 +12635,13 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>1551.364</v>
+        <v>1551.165</v>
       </c>
       <c r="I102" t="n">
-        <v>-4.9935</v>
+        <v>-5.0089</v>
       </c>
       <c r="J102" t="n">
-        <v>1645.5</v>
+        <v>1646.4</v>
       </c>
       <c r="K102" t="n">
         <v>90</v>
@@ -12755,13 +12755,13 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>1810.739</v>
+        <v>1808.83</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8284</v>
+        <v>0.1677</v>
       </c>
       <c r="J103" t="n">
-        <v>1647.3</v>
+        <v>1648.7</v>
       </c>
       <c r="K103" t="n">
         <v>33</v>
@@ -12875,13 +12875,13 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>1332.725</v>
+        <v>1332.386</v>
       </c>
       <c r="I104" t="n">
-        <v>1.1509</v>
+        <v>1.1465</v>
       </c>
       <c r="J104" t="n">
-        <v>1454.7</v>
+        <v>1454.5</v>
       </c>
       <c r="K104" t="n">
         <v>301</v>
@@ -12995,13 +12995,13 @@
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>1475.095</v>
+        <v>1474.55</v>
       </c>
       <c r="I105" t="n">
-        <v>-2.2794</v>
+        <v>-2.29</v>
       </c>
       <c r="J105" t="n">
-        <v>1606.5</v>
+        <v>1605.9</v>
       </c>
       <c r="K105" t="n">
         <v>166</v>
@@ -13115,13 +13115,13 @@
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>2055.072</v>
+        <v>2061.642</v>
       </c>
       <c r="I106" t="n">
-        <v>6.9647</v>
+        <v>6.7538</v>
       </c>
       <c r="J106" t="n">
-        <v>1597.1</v>
+        <v>1597.9</v>
       </c>
       <c r="K106" t="n">
         <v>12</v>
@@ -13235,13 +13235,13 @@
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>1310.567</v>
+        <v>1310.866</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.5193</v>
+        <v>-0.5341</v>
       </c>
       <c r="J107" t="n">
-        <v>1364.2</v>
+        <v>1363.2</v>
       </c>
       <c r="K107" t="n">
         <v>292</v>
@@ -13355,13 +13355,13 @@
         <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>1722.634</v>
+        <v>1718.39</v>
       </c>
       <c r="I108" t="n">
-        <v>6.6005</v>
+        <v>6.6944</v>
       </c>
       <c r="J108" t="n">
-        <v>1577</v>
+        <v>1575.6</v>
       </c>
       <c r="K108" t="n">
         <v>62</v>
@@ -13475,13 +13475,13 @@
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>1351.316</v>
+        <v>1350.882</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4097</v>
+        <v>0.3858</v>
       </c>
       <c r="J109" t="n">
-        <v>1452</v>
+        <v>1451.2</v>
       </c>
       <c r="K109" t="n">
         <v>273</v>
@@ -13595,13 +13595,13 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>1493.255</v>
+        <v>1493.522</v>
       </c>
       <c r="I110" t="n">
-        <v>2.5634</v>
+        <v>2.5383</v>
       </c>
       <c r="J110" t="n">
-        <v>1466.9</v>
+        <v>1466.8</v>
       </c>
       <c r="K110" t="n">
         <v>157</v>
@@ -13715,13 +13715,13 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>1542.675</v>
+        <v>1541.928</v>
       </c>
       <c r="I111" t="n">
-        <v>3.3357</v>
+        <v>3.317</v>
       </c>
       <c r="J111" t="n">
-        <v>1451.5</v>
+        <v>1450.6</v>
       </c>
       <c r="K111" t="n">
         <v>108</v>
@@ -13835,10 +13835,10 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>1623.328</v>
+        <v>1620.837</v>
       </c>
       <c r="I112" t="n">
-        <v>-1.5579</v>
+        <v>-1.4038</v>
       </c>
       <c r="J112" t="n">
         <v>1381.5</v>
@@ -13955,13 +13955,13 @@
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>1568.2</v>
+        <v>1567.789</v>
       </c>
       <c r="I113" t="n">
-        <v>4.0091</v>
+        <v>4.0005</v>
       </c>
       <c r="J113" t="n">
-        <v>1479.4</v>
+        <v>1478.9</v>
       </c>
       <c r="K113" t="n">
         <v>92</v>
@@ -14075,13 +14075,13 @@
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>1289.928</v>
+        <v>1290.108</v>
       </c>
       <c r="I114" t="n">
-        <v>-1.2841</v>
+        <v>-1.2885</v>
       </c>
       <c r="J114" t="n">
-        <v>1381.4</v>
+        <v>1382.1</v>
       </c>
       <c r="K114" t="n">
         <v>332</v>
@@ -14195,13 +14195,13 @@
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>2085.125</v>
+        <v>2099.174</v>
       </c>
       <c r="I115" t="n">
-        <v>2.67</v>
+        <v>1.9173</v>
       </c>
       <c r="J115" t="n">
-        <v>1703.4</v>
+        <v>1706</v>
       </c>
       <c r="K115" t="n">
         <v>6</v>
@@ -14315,13 +14315,13 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>1276.525</v>
+        <v>1276.468</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.832</v>
+        <v>-0.8273</v>
       </c>
       <c r="J116" t="n">
-        <v>1424.5</v>
+        <v>1424.2</v>
       </c>
       <c r="K116" t="n">
         <v>300</v>
@@ -14435,13 +14435,13 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>1410.88</v>
+        <v>1409.029</v>
       </c>
       <c r="I117" t="n">
-        <v>3.2396</v>
+        <v>3.2279</v>
       </c>
       <c r="J117" t="n">
-        <v>1380.9</v>
+        <v>1380.6</v>
       </c>
       <c r="K117" t="n">
         <v>199</v>
@@ -14555,13 +14555,13 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>1398.132</v>
+        <v>1397.445</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3445</v>
+        <v>-0.3407</v>
       </c>
       <c r="J118" t="n">
-        <v>1420.8</v>
+        <v>1419.8</v>
       </c>
       <c r="K118" t="n">
         <v>173</v>
@@ -14675,13 +14675,13 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1330.43</v>
+        <v>1329.993</v>
       </c>
       <c r="I119" t="n">
-        <v>-1.6646</v>
+        <v>-1.6548</v>
       </c>
       <c r="J119" t="n">
-        <v>1428.5</v>
+        <v>1427.6</v>
       </c>
       <c r="K119" t="n">
         <v>238</v>
@@ -14795,13 +14795,13 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>1521.575</v>
+        <v>1520.214</v>
       </c>
       <c r="I120" t="n">
-        <v>1.8755</v>
+        <v>1.8071</v>
       </c>
       <c r="J120" t="n">
-        <v>1504.2</v>
+        <v>1502.8</v>
       </c>
       <c r="K120" t="n">
         <v>110</v>
@@ -14915,13 +14915,13 @@
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>1996.419</v>
+        <v>1999.75</v>
       </c>
       <c r="I121" t="n">
-        <v>8.884600000000001</v>
+        <v>8.6837</v>
       </c>
       <c r="J121" t="n">
-        <v>1710.4</v>
+        <v>1712.9</v>
       </c>
       <c r="K121" t="n">
         <v>5</v>
@@ -15035,13 +15035,13 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>1591.589</v>
+        <v>1589.656</v>
       </c>
       <c r="I122" t="n">
-        <v>2.307</v>
+        <v>2.2669</v>
       </c>
       <c r="J122" t="n">
-        <v>1507.2</v>
+        <v>1505.7</v>
       </c>
       <c r="K122" t="n">
         <v>97</v>
@@ -15155,13 +15155,13 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>1319.932</v>
+        <v>1320.935</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.655</v>
+        <v>-0.6341</v>
       </c>
       <c r="J123" t="n">
-        <v>1432.8</v>
+        <v>1433.7</v>
       </c>
       <c r="K123" t="n">
         <v>266</v>
@@ -15275,13 +15275,13 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>1752.663</v>
+        <v>1752.589</v>
       </c>
       <c r="I124" t="n">
-        <v>-2.7312</v>
+        <v>-2.4765</v>
       </c>
       <c r="J124" t="n">
-        <v>1695.9</v>
+        <v>1696.5</v>
       </c>
       <c r="K124" t="n">
         <v>43</v>
@@ -15395,13 +15395,13 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>1428.46</v>
+        <v>1427.759</v>
       </c>
       <c r="I125" t="n">
-        <v>-3.2579</v>
+        <v>-3.2441</v>
       </c>
       <c r="J125" t="n">
-        <v>1523.5</v>
+        <v>1522.9</v>
       </c>
       <c r="K125" t="n">
         <v>202</v>
@@ -15515,10 +15515,10 @@
         <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>1487.923</v>
+        <v>1487.126</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4117</v>
+        <v>-0.4022</v>
       </c>
       <c r="J126" t="n">
         <v>1426</v>
@@ -15635,13 +15635,13 @@
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>1849.845</v>
+        <v>1851.166</v>
       </c>
       <c r="I127" t="n">
-        <v>4.4435</v>
+        <v>4.4379</v>
       </c>
       <c r="J127" t="n">
-        <v>1706.7</v>
+        <v>1708.5</v>
       </c>
       <c r="K127" t="n">
         <v>24</v>
@@ -15755,13 +15755,13 @@
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>2030.134</v>
+        <v>2024.541</v>
       </c>
       <c r="I128" t="n">
-        <v>3.0314</v>
+        <v>3.6605</v>
       </c>
       <c r="J128" t="n">
-        <v>1692.3</v>
+        <v>1693</v>
       </c>
       <c r="K128" t="n">
         <v>7</v>
@@ -15875,13 +15875,13 @@
         <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>1482.74</v>
+        <v>1482.543</v>
       </c>
       <c r="I129" t="n">
-        <v>3.5282</v>
+        <v>3.5216</v>
       </c>
       <c r="J129" t="n">
-        <v>1441.1</v>
+        <v>1440.7</v>
       </c>
       <c r="K129" t="n">
         <v>257</v>
@@ -15995,10 +15995,10 @@
         <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>1213.343</v>
+        <v>1213.401</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.7358</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="J130" t="n">
         <v>1424.7</v>
@@ -16115,13 +16115,13 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>1300.954</v>
+        <v>1300.886</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.4914</v>
+        <v>-1.469</v>
       </c>
       <c r="J131" t="n">
-        <v>1423.4</v>
+        <v>1425.2</v>
       </c>
       <c r="K131" t="n">
         <v>345</v>
@@ -16235,13 +16235,13 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>1361.102</v>
+        <v>1360.963</v>
       </c>
       <c r="I132" t="n">
-        <v>-2.5239</v>
+        <v>-2.5469</v>
       </c>
       <c r="J132" t="n">
-        <v>1399.1</v>
+        <v>1398.5</v>
       </c>
       <c r="K132" t="n">
         <v>294</v>
@@ -16355,13 +16355,13 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>1459.698</v>
+        <v>1459.096</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0609</v>
+        <v>-0.0599</v>
       </c>
       <c r="J133" t="n">
-        <v>1469.9</v>
+        <v>1469.2</v>
       </c>
       <c r="K133" t="n">
         <v>205</v>
@@ -16475,10 +16475,10 @@
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>1501.28</v>
+        <v>1501.556</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4201</v>
+        <v>0.4005</v>
       </c>
       <c r="J134" t="n">
         <v>1452.5</v>
@@ -16595,13 +16595,13 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>1972.298</v>
+        <v>1971.577</v>
       </c>
       <c r="I135" t="n">
-        <v>11.3738</v>
+        <v>11.9283</v>
       </c>
       <c r="J135" t="n">
-        <v>1777.3</v>
+        <v>1779.6</v>
       </c>
       <c r="K135" t="n">
         <v>16</v>
@@ -16715,13 +16715,13 @@
         <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>1581.015</v>
+        <v>1579.844</v>
       </c>
       <c r="I136" t="n">
-        <v>-5.2381</v>
+        <v>-5.1262</v>
       </c>
       <c r="J136" t="n">
-        <v>1691.8</v>
+        <v>1692.2</v>
       </c>
       <c r="K136" t="n">
         <v>102</v>
@@ -16835,13 +16835,13 @@
         <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>1508.15</v>
+        <v>1507.342</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.4067</v>
+        <v>-0.4075</v>
       </c>
       <c r="J137" t="n">
-        <v>1470.2</v>
+        <v>1469.7</v>
       </c>
       <c r="K137" t="n">
         <v>170</v>
@@ -16955,13 +16955,13 @@
         <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>1606.874</v>
+        <v>1605.462</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4251</v>
+        <v>0.4681</v>
       </c>
       <c r="J138" t="n">
-        <v>1472.9</v>
+        <v>1472.1</v>
       </c>
       <c r="K138" t="n">
         <v>160</v>
@@ -17075,10 +17075,10 @@
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>1893.436</v>
+        <v>1894.362</v>
       </c>
       <c r="I139" t="n">
-        <v>6.006</v>
+        <v>5.7232</v>
       </c>
       <c r="J139" t="n">
         <v>1717.2</v>
@@ -17195,13 +17195,13 @@
         <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>1400.436</v>
+        <v>1400.601</v>
       </c>
       <c r="I140" t="n">
-        <v>-2.1985</v>
+        <v>-2.2046</v>
       </c>
       <c r="J140" t="n">
-        <v>1562.2</v>
+        <v>1562.7</v>
       </c>
       <c r="K140" t="n">
         <v>229</v>
@@ -17315,13 +17315,13 @@
         <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>1265.157</v>
+        <v>1265.122</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.6122</v>
+        <v>-1.6111</v>
       </c>
       <c r="J141" t="n">
-        <v>1389</v>
+        <v>1388.5</v>
       </c>
       <c r="K141" t="n">
         <v>325</v>
@@ -17435,13 +17435,13 @@
         <v>1</v>
       </c>
       <c r="H142" t="n">
-        <v>1352.772</v>
+        <v>1352.5</v>
       </c>
       <c r="I142" t="n">
-        <v>-1.4368</v>
+        <v>-1.4187</v>
       </c>
       <c r="J142" t="n">
-        <v>1401.4</v>
+        <v>1401.8</v>
       </c>
       <c r="K142" t="n">
         <v>223</v>
@@ -17555,13 +17555,13 @@
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>1319.819</v>
+        <v>1320.085</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.6937</v>
+        <v>-0.7048</v>
       </c>
       <c r="J143" t="n">
-        <v>1397.9</v>
+        <v>1399.1</v>
       </c>
       <c r="K143" t="n">
         <v>295</v>
@@ -17675,13 +17675,13 @@
         <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>1732.461</v>
+        <v>1728.988</v>
       </c>
       <c r="I144" t="n">
-        <v>3.2122</v>
+        <v>3.4996</v>
       </c>
       <c r="J144" t="n">
-        <v>1483.4</v>
+        <v>1482.9</v>
       </c>
       <c r="K144" t="n">
         <v>111</v>
@@ -17795,13 +17795,13 @@
         <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>1482.715</v>
+        <v>1481.018</v>
       </c>
       <c r="I145" t="n">
-        <v>1.1762</v>
+        <v>1.2211</v>
       </c>
       <c r="J145" t="n">
-        <v>1422.1</v>
+        <v>1421.5</v>
       </c>
       <c r="K145" t="n">
         <v>179</v>
@@ -17915,13 +17915,13 @@
         <v>1</v>
       </c>
       <c r="H146" t="n">
-        <v>1308.472</v>
+        <v>1307.53</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4338</v>
+        <v>-0.4229</v>
       </c>
       <c r="J146" t="n">
-        <v>1480.1</v>
+        <v>1478.1</v>
       </c>
       <c r="K146" t="n">
         <v>249</v>
@@ -18035,13 +18035,13 @@
         <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>1414.144</v>
+        <v>1414.369</v>
       </c>
       <c r="I147" t="n">
-        <v>2.4721</v>
+        <v>2.4583</v>
       </c>
       <c r="J147" t="n">
-        <v>1378.7</v>
+        <v>1378.6</v>
       </c>
       <c r="K147" t="n">
         <v>210</v>
@@ -18155,13 +18155,13 @@
         <v>1</v>
       </c>
       <c r="H148" t="n">
-        <v>1399.981</v>
+        <v>1399.745</v>
       </c>
       <c r="I148" t="n">
-        <v>-2.9885</v>
+        <v>-2.9584</v>
       </c>
       <c r="J148" t="n">
-        <v>1389.8</v>
+        <v>1389.7</v>
       </c>
       <c r="K148" t="n">
         <v>272</v>
@@ -18275,13 +18275,13 @@
         <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>1503.438</v>
+        <v>1502.677</v>
       </c>
       <c r="I149" t="n">
-        <v>-2.0097</v>
+        <v>-2.0079</v>
       </c>
       <c r="J149" t="n">
-        <v>1471.5</v>
+        <v>1470.5</v>
       </c>
       <c r="K149" t="n">
         <v>246</v>
@@ -18395,13 +18395,13 @@
         <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>1830.183</v>
+        <v>1830.413</v>
       </c>
       <c r="I150" t="n">
-        <v>-3.7351</v>
+        <v>-3.0745</v>
       </c>
       <c r="J150" t="n">
-        <v>1675</v>
+        <v>1677.2</v>
       </c>
       <c r="K150" t="n">
         <v>19</v>
@@ -18515,13 +18515,13 @@
         <v>1</v>
       </c>
       <c r="H151" t="n">
-        <v>1472.7</v>
+        <v>1471.537</v>
       </c>
       <c r="I151" t="n">
-        <v>-5.7748</v>
+        <v>-5.748</v>
       </c>
       <c r="J151" t="n">
-        <v>1516.2</v>
+        <v>1515.5</v>
       </c>
       <c r="K151" t="n">
         <v>148</v>
@@ -18635,13 +18635,13 @@
         <v>1</v>
       </c>
       <c r="H152" t="n">
-        <v>1268.163</v>
+        <v>1268.334</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.8824</v>
+        <v>-0.8812</v>
       </c>
       <c r="J152" t="n">
-        <v>1383.3</v>
+        <v>1383.7</v>
       </c>
       <c r="K152" t="n">
         <v>322</v>
@@ -18755,13 +18755,13 @@
         <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>1390.881</v>
+        <v>1391.352</v>
       </c>
       <c r="I153" t="n">
-        <v>-4.2873</v>
+        <v>-4.2997</v>
       </c>
       <c r="J153" t="n">
-        <v>1562.8</v>
+        <v>1562.7</v>
       </c>
       <c r="K153" t="n">
         <v>306</v>
@@ -18875,13 +18875,13 @@
         <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>1647.846</v>
+        <v>1648.819</v>
       </c>
       <c r="I154" t="n">
-        <v>-1.0692</v>
+        <v>-0.9809</v>
       </c>
       <c r="J154" t="n">
-        <v>1654.3</v>
+        <v>1655</v>
       </c>
       <c r="K154" t="n">
         <v>58</v>
@@ -18995,13 +18995,13 @@
         <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>1347.635</v>
+        <v>1348.264</v>
       </c>
       <c r="I155" t="n">
-        <v>-2.6421</v>
+        <v>-2.662</v>
       </c>
       <c r="J155" t="n">
-        <v>1405.4</v>
+        <v>1406.5</v>
       </c>
       <c r="K155" t="n">
         <v>323</v>
@@ -19115,13 +19115,13 @@
         <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>1286.335</v>
+        <v>1286.572</v>
       </c>
       <c r="I156" t="n">
-        <v>-3.468</v>
+        <v>-3.4847</v>
       </c>
       <c r="J156" t="n">
-        <v>1380.9</v>
+        <v>1380.8</v>
       </c>
       <c r="K156" t="n">
         <v>347</v>
@@ -19235,10 +19235,10 @@
         <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>1343.692</v>
+        <v>1343.873</v>
       </c>
       <c r="I157" t="n">
-        <v>-1.4197</v>
+        <v>-1.4317</v>
       </c>
       <c r="J157" t="n">
         <v>1414.5</v>
@@ -19355,13 +19355,13 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>1490.602</v>
+        <v>1491.176</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1527</v>
+        <v>0.1248</v>
       </c>
       <c r="J158" t="n">
-        <v>1415.8</v>
+        <v>1416.5</v>
       </c>
       <c r="K158" t="n">
         <v>201</v>
@@ -19475,13 +19475,13 @@
         <v>1</v>
       </c>
       <c r="H159" t="n">
-        <v>1517.593</v>
+        <v>1515.683</v>
       </c>
       <c r="I159" t="n">
-        <v>-8.0067</v>
+        <v>-7.4748</v>
       </c>
       <c r="J159" t="n">
-        <v>1658.7</v>
+        <v>1659.8</v>
       </c>
       <c r="K159" t="n">
         <v>100</v>
@@ -19595,13 +19595,13 @@
         <v>1</v>
       </c>
       <c r="H160" t="n">
-        <v>1505.444</v>
+        <v>1505.033</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6728</v>
+        <v>-0.6916</v>
       </c>
       <c r="J160" t="n">
-        <v>1448.7</v>
+        <v>1448.1</v>
       </c>
       <c r="K160" t="n">
         <v>197</v>
@@ -19715,13 +19715,13 @@
         <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>1598.81</v>
+        <v>1601.614</v>
       </c>
       <c r="I161" t="n">
-        <v>-7.9559</v>
+        <v>-8.364800000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>1712.3</v>
+        <v>1713.6</v>
       </c>
       <c r="K161" t="n">
         <v>130</v>
@@ -19835,13 +19835,13 @@
         <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>1478.737</v>
+        <v>1478.94</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0696</v>
+        <v>1.058</v>
       </c>
       <c r="J162" t="n">
-        <v>1451.7</v>
+        <v>1451.3</v>
       </c>
       <c r="K162" t="n">
         <v>203</v>
@@ -19955,13 +19955,13 @@
         <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>1710.286</v>
+        <v>1718.721</v>
       </c>
       <c r="I163" t="n">
-        <v>3.285</v>
+        <v>2.9617</v>
       </c>
       <c r="J163" t="n">
-        <v>1422.9</v>
+        <v>1423</v>
       </c>
       <c r="K163" t="n">
         <v>69</v>
@@ -20075,13 +20075,13 @@
         <v>1</v>
       </c>
       <c r="H164" t="n">
-        <v>1224.127</v>
+        <v>1224.051</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.5205</v>
+        <v>-0.5285</v>
       </c>
       <c r="J164" t="n">
-        <v>1407.2</v>
+        <v>1406.3</v>
       </c>
       <c r="K164" t="n">
         <v>342</v>
@@ -20195,13 +20195,13 @@
         <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>1562.875</v>
+        <v>1560.22</v>
       </c>
       <c r="I165" t="n">
-        <v>-5.6224</v>
+        <v>-5.242</v>
       </c>
       <c r="J165" t="n">
-        <v>1613.5</v>
+        <v>1612.9</v>
       </c>
       <c r="K165" t="n">
         <v>131</v>
@@ -20315,13 +20315,13 @@
         <v>1</v>
       </c>
       <c r="H166" t="n">
-        <v>1455.59</v>
+        <v>1454.946</v>
       </c>
       <c r="I166" t="n">
-        <v>0.903</v>
+        <v>0.8914</v>
       </c>
       <c r="J166" t="n">
-        <v>1455.6</v>
+        <v>1455.1</v>
       </c>
       <c r="K166" t="n">
         <v>182</v>
@@ -20435,13 +20435,13 @@
         <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>1773.834</v>
+        <v>1775.829</v>
       </c>
       <c r="I167" t="n">
-        <v>12.7945</v>
+        <v>12.7773</v>
       </c>
       <c r="J167" t="n">
-        <v>1607.1</v>
+        <v>1609.3</v>
       </c>
       <c r="K167" t="n">
         <v>32</v>
@@ -20555,13 +20555,13 @@
         <v>1</v>
       </c>
       <c r="H168" t="n">
-        <v>1772.698</v>
+        <v>1771.654</v>
       </c>
       <c r="I168" t="n">
-        <v>9.988799999999999</v>
+        <v>9.957599999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>1413.1</v>
+        <v>1412.7</v>
       </c>
       <c r="K168" t="n">
         <v>87</v>
@@ -20675,13 +20675,13 @@
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>2172.447</v>
+        <v>2181.167</v>
       </c>
       <c r="I169" t="n">
-        <v>8.183400000000001</v>
+        <v>7.6139</v>
       </c>
       <c r="J169" t="n">
-        <v>1756.1</v>
+        <v>1758.2</v>
       </c>
       <c r="K169" t="n">
         <v>2</v>
@@ -20795,13 +20795,13 @@
         <v>1</v>
       </c>
       <c r="H170" t="n">
-        <v>2051.509</v>
+        <v>2057.84</v>
       </c>
       <c r="I170" t="n">
-        <v>0.5706</v>
+        <v>0.2001</v>
       </c>
       <c r="J170" t="n">
-        <v>1704.4</v>
+        <v>1707.1</v>
       </c>
       <c r="K170" t="n">
         <v>9</v>
@@ -20915,13 +20915,13 @@
         <v>1</v>
       </c>
       <c r="H171" t="n">
-        <v>1616.906</v>
+        <v>1616.877</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1308</v>
+        <v>0.1361</v>
       </c>
       <c r="J171" t="n">
-        <v>1678.8</v>
+        <v>1679.2</v>
       </c>
       <c r="K171" t="n">
         <v>64</v>
@@ -21035,13 +21035,13 @@
         <v>1</v>
       </c>
       <c r="H172" t="n">
-        <v>1635.363</v>
+        <v>1636.6</v>
       </c>
       <c r="I172" t="n">
-        <v>-8.315899999999999</v>
+        <v>-8.902100000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>1698.7</v>
+        <v>1697.7</v>
       </c>
       <c r="K172" t="n">
         <v>79</v>
@@ -21155,13 +21155,13 @@
         <v>1</v>
       </c>
       <c r="H173" t="n">
-        <v>1633.204</v>
+        <v>1629.748</v>
       </c>
       <c r="I173" t="n">
-        <v>-2.2844</v>
+        <v>-1.5728</v>
       </c>
       <c r="J173" t="n">
-        <v>1702.1</v>
+        <v>1701.8</v>
       </c>
       <c r="K173" t="n">
         <v>96</v>
@@ -21275,13 +21275,13 @@
         <v>1</v>
       </c>
       <c r="H174" t="n">
-        <v>1768.166</v>
+        <v>1767.363</v>
       </c>
       <c r="I174" t="n">
-        <v>-2.8893</v>
+        <v>-2.184</v>
       </c>
       <c r="J174" t="n">
-        <v>1637.7</v>
+        <v>1638.6</v>
       </c>
       <c r="K174" t="n">
         <v>47</v>
@@ -21395,13 +21395,13 @@
         <v>1</v>
       </c>
       <c r="H175" t="n">
-        <v>1229.143</v>
+        <v>1228.63</v>
       </c>
       <c r="I175" t="n">
-        <v>-4.4885</v>
+        <v>-4.4838</v>
       </c>
       <c r="J175" t="n">
-        <v>1433.1</v>
+        <v>1432</v>
       </c>
       <c r="K175" t="n">
         <v>356</v>
@@ -21515,13 +21515,13 @@
         <v>1</v>
       </c>
       <c r="H176" t="n">
-        <v>1399.179</v>
+        <v>1398.778</v>
       </c>
       <c r="I176" t="n">
-        <v>1.4398</v>
+        <v>1.4406</v>
       </c>
       <c r="J176" t="n">
-        <v>1474.7</v>
+        <v>1474.3</v>
       </c>
       <c r="K176" t="n">
         <v>212</v>
@@ -21635,13 +21635,13 @@
         <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>1444.506</v>
+        <v>1443.63</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1442</v>
+        <v>1.1405</v>
       </c>
       <c r="J177" t="n">
-        <v>1459.6</v>
+        <v>1459</v>
       </c>
       <c r="K177" t="n">
         <v>190</v>
@@ -21755,13 +21755,13 @@
         <v>1</v>
       </c>
       <c r="H178" t="n">
-        <v>1460.265</v>
+        <v>1458.848</v>
       </c>
       <c r="I178" t="n">
-        <v>-1.747</v>
+        <v>-1.7046</v>
       </c>
       <c r="J178" t="n">
-        <v>1433.2</v>
+        <v>1432.7</v>
       </c>
       <c r="K178" t="n">
         <v>175</v>
@@ -21875,13 +21875,13 @@
         <v>1</v>
       </c>
       <c r="H179" t="n">
-        <v>1437.98</v>
+        <v>1436.33</v>
       </c>
       <c r="I179" t="n">
-        <v>3.2495</v>
+        <v>3.2578</v>
       </c>
       <c r="J179" t="n">
-        <v>1438.7</v>
+        <v>1437.7</v>
       </c>
       <c r="K179" t="n">
         <v>135</v>
@@ -21995,13 +21995,13 @@
         <v>1</v>
       </c>
       <c r="H180" t="n">
-        <v>1409.083</v>
+        <v>1407.15</v>
       </c>
       <c r="I180" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0138</v>
       </c>
       <c r="J180" t="n">
-        <v>1401.1</v>
+        <v>1398.9</v>
       </c>
       <c r="K180" t="n">
         <v>282</v>
@@ -22115,13 +22115,13 @@
         <v>1</v>
       </c>
       <c r="H181" t="n">
-        <v>1276.705</v>
+        <v>1276.642</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1499</v>
+        <v>-0.1495</v>
       </c>
       <c r="J181" t="n">
-        <v>1359.3</v>
+        <v>1359.2</v>
       </c>
       <c r="K181" t="n">
         <v>353</v>
@@ -22235,13 +22235,13 @@
         <v>1</v>
       </c>
       <c r="H182" t="n">
-        <v>1095.105</v>
+        <v>1094.905</v>
       </c>
       <c r="I182" t="n">
-        <v>-2.9611</v>
+        <v>-2.9612</v>
       </c>
       <c r="J182" t="n">
-        <v>1373.7</v>
+        <v>1372.9</v>
       </c>
       <c r="K182" t="n">
         <v>365</v>
@@ -22355,13 +22355,13 @@
         <v>1</v>
       </c>
       <c r="H183" t="n">
-        <v>1389.558</v>
+        <v>1391.752</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.7751</v>
+        <v>-0.8761</v>
       </c>
       <c r="J183" t="n">
-        <v>1436.1</v>
+        <v>1436.5</v>
       </c>
       <c r="K183" t="n">
         <v>277</v>
@@ -22475,13 +22475,13 @@
         <v>1</v>
       </c>
       <c r="H184" t="n">
-        <v>1485.68</v>
+        <v>1485.849</v>
       </c>
       <c r="I184" t="n">
-        <v>-4.0304</v>
+        <v>-4.0291</v>
       </c>
       <c r="J184" t="n">
-        <v>1526.5</v>
+        <v>1528.1</v>
       </c>
       <c r="K184" t="n">
         <v>180</v>
@@ -22595,13 +22595,13 @@
         <v>1</v>
       </c>
       <c r="H185" t="n">
-        <v>1583.009</v>
+        <v>1581.714</v>
       </c>
       <c r="I185" t="n">
-        <v>4.7153</v>
+        <v>4.703</v>
       </c>
       <c r="J185" t="n">
-        <v>1505.6</v>
+        <v>1504.9</v>
       </c>
       <c r="K185" t="n">
         <v>117</v>
@@ -22715,13 +22715,13 @@
         <v>1</v>
       </c>
       <c r="H186" t="n">
-        <v>1492.704</v>
+        <v>1492.824</v>
       </c>
       <c r="I186" t="n">
-        <v>-2.3487</v>
+        <v>-2.3144</v>
       </c>
       <c r="J186" t="n">
-        <v>1399</v>
+        <v>1399.2</v>
       </c>
       <c r="K186" t="n">
         <v>151</v>
@@ -22835,13 +22835,13 @@
         <v>1</v>
       </c>
       <c r="H187" t="n">
-        <v>1589.861</v>
+        <v>1588.952</v>
       </c>
       <c r="I187" t="n">
-        <v>3.844</v>
+        <v>3.8176</v>
       </c>
       <c r="J187" t="n">
-        <v>1412.7</v>
+        <v>1412.3</v>
       </c>
       <c r="K187" t="n">
         <v>118</v>
@@ -22955,13 +22955,13 @@
         <v>1</v>
       </c>
       <c r="H188" t="n">
-        <v>1278.988</v>
+        <v>1278.591</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.6929</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="J188" t="n">
-        <v>1473.6</v>
+        <v>1472</v>
       </c>
       <c r="K188" t="n">
         <v>331</v>
@@ -23075,13 +23075,13 @@
         <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>1436.316</v>
+        <v>1436.269</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2848</v>
+        <v>0.2764</v>
       </c>
       <c r="J189" t="n">
-        <v>1430.5</v>
+        <v>1430.7</v>
       </c>
       <c r="K189" t="n">
         <v>178</v>
@@ -23195,13 +23195,13 @@
         <v>1</v>
       </c>
       <c r="H190" t="n">
-        <v>1430.484</v>
+        <v>1430.358</v>
       </c>
       <c r="I190" t="n">
-        <v>3.2584</v>
+        <v>3.2549</v>
       </c>
       <c r="J190" t="n">
-        <v>1375.7</v>
+        <v>1375.2</v>
       </c>
       <c r="K190" t="n">
         <v>136</v>
@@ -23315,13 +23315,13 @@
         <v>1</v>
       </c>
       <c r="H191" t="n">
-        <v>1328.742</v>
+        <v>1328.343</v>
       </c>
       <c r="I191" t="n">
-        <v>1.1764</v>
+        <v>1.1591</v>
       </c>
       <c r="J191" t="n">
-        <v>1454.5</v>
+        <v>1453.6</v>
       </c>
       <c r="K191" t="n">
         <v>274</v>
@@ -23435,13 +23435,13 @@
         <v>1</v>
       </c>
       <c r="H192" t="n">
-        <v>1281.865</v>
+        <v>1281.637</v>
       </c>
       <c r="I192" t="n">
-        <v>-1.6079</v>
+        <v>-1.603</v>
       </c>
       <c r="J192" t="n">
-        <v>1390</v>
+        <v>1390.3</v>
       </c>
       <c r="K192" t="n">
         <v>349</v>
@@ -23555,13 +23555,13 @@
         <v>1</v>
       </c>
       <c r="H193" t="n">
-        <v>1751.376</v>
+        <v>1751.703</v>
       </c>
       <c r="I193" t="n">
-        <v>8.2582</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="J193" t="n">
-        <v>1678.8</v>
+        <v>1678.3</v>
       </c>
       <c r="K193" t="n">
         <v>31</v>
@@ -23675,13 +23675,13 @@
         <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>1368.408</v>
+        <v>1367.953</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.5657</v>
+        <v>-0.5425</v>
       </c>
       <c r="J194" t="n">
-        <v>1438.1</v>
+        <v>1438.4</v>
       </c>
       <c r="K194" t="n">
         <v>261</v>
@@ -23795,13 +23795,13 @@
         <v>1</v>
       </c>
       <c r="H195" t="n">
-        <v>1990.637</v>
+        <v>1992.134</v>
       </c>
       <c r="I195" t="n">
-        <v>11.3442</v>
+        <v>11.5554</v>
       </c>
       <c r="J195" t="n">
-        <v>1658</v>
+        <v>1659.3</v>
       </c>
       <c r="K195" t="n">
         <v>11</v>
@@ -23915,13 +23915,13 @@
         <v>1</v>
       </c>
       <c r="H196" t="n">
-        <v>1738.936</v>
+        <v>1735.921</v>
       </c>
       <c r="I196" t="n">
-        <v>7.3067</v>
+        <v>7.2596</v>
       </c>
       <c r="J196" t="n">
-        <v>1614.5</v>
+        <v>1612.8</v>
       </c>
       <c r="K196" t="n">
         <v>70</v>
@@ -24035,13 +24035,13 @@
         <v>1</v>
       </c>
       <c r="H197" t="n">
-        <v>1284.274</v>
+        <v>1284.391</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.2558</v>
+        <v>-0.2563</v>
       </c>
       <c r="J197" t="n">
-        <v>1417.7</v>
+        <v>1416.7</v>
       </c>
       <c r="K197" t="n">
         <v>350</v>
@@ -24155,13 +24155,13 @@
         <v>1</v>
       </c>
       <c r="H198" t="n">
-        <v>1825.295</v>
+        <v>1822.612</v>
       </c>
       <c r="I198" t="n">
-        <v>4.1386</v>
+        <v>3.8299</v>
       </c>
       <c r="J198" t="n">
-        <v>1590</v>
+        <v>1587.8</v>
       </c>
       <c r="K198" t="n">
         <v>46</v>
@@ -24275,13 +24275,13 @@
         <v>1</v>
       </c>
       <c r="H199" t="n">
-        <v>1456.086</v>
+        <v>1455.982</v>
       </c>
       <c r="I199" t="n">
-        <v>-8.1471</v>
+        <v>-8.1896</v>
       </c>
       <c r="J199" t="n">
-        <v>1487.6</v>
+        <v>1487.2</v>
       </c>
       <c r="K199" t="n">
         <v>181</v>
@@ -24395,13 +24395,13 @@
         <v>1</v>
       </c>
       <c r="H200" t="n">
-        <v>1340.232</v>
+        <v>1339.842</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5172</v>
+        <v>0.5343</v>
       </c>
       <c r="J200" t="n">
-        <v>1457.9</v>
+        <v>1459</v>
       </c>
       <c r="K200" t="n">
         <v>176</v>
@@ -24515,13 +24515,13 @@
         <v>1</v>
       </c>
       <c r="H201" t="n">
-        <v>1293.278</v>
+        <v>1293.821</v>
       </c>
       <c r="I201" t="n">
-        <v>-3.5232</v>
+        <v>-3.5334</v>
       </c>
       <c r="J201" t="n">
-        <v>1425.3</v>
+        <v>1425.9</v>
       </c>
       <c r="K201" t="n">
         <v>338</v>
@@ -24635,13 +24635,13 @@
         <v>1</v>
       </c>
       <c r="H202" t="n">
-        <v>1362.216</v>
+        <v>1362.178</v>
       </c>
       <c r="I202" t="n">
-        <v>-1.5288</v>
+        <v>-1.5128</v>
       </c>
       <c r="J202" t="n">
-        <v>1433.8</v>
+        <v>1434.9</v>
       </c>
       <c r="K202" t="n">
         <v>240</v>
@@ -24755,13 +24755,13 @@
         <v>1</v>
       </c>
       <c r="H203" t="n">
-        <v>1307.321</v>
+        <v>1307.929</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3912</v>
+        <v>0.3792</v>
       </c>
       <c r="J203" t="n">
-        <v>1403.8</v>
+        <v>1403.6</v>
       </c>
       <c r="K203" t="n">
         <v>327</v>
@@ -24875,13 +24875,13 @@
         <v>1</v>
       </c>
       <c r="H204" t="n">
-        <v>1364.684</v>
+        <v>1364.479</v>
       </c>
       <c r="I204" t="n">
-        <v>-3.9225</v>
+        <v>-3.9095</v>
       </c>
       <c r="J204" t="n">
-        <v>1376.7</v>
+        <v>1377.4</v>
       </c>
       <c r="K204" t="n">
         <v>313</v>
@@ -24995,13 +24995,13 @@
         <v>1</v>
       </c>
       <c r="H205" t="n">
-        <v>1921.191</v>
+        <v>1921.914</v>
       </c>
       <c r="I205" t="n">
-        <v>2.4067</v>
+        <v>2.4321</v>
       </c>
       <c r="J205" t="n">
-        <v>1655.5</v>
+        <v>1655.6</v>
       </c>
       <c r="K205" t="n">
         <v>28</v>
@@ -25115,13 +25115,13 @@
         <v>1</v>
       </c>
       <c r="H206" t="n">
-        <v>1358.599</v>
+        <v>1358.751</v>
       </c>
       <c r="I206" t="n">
-        <v>0.8176</v>
+        <v>0.8181</v>
       </c>
       <c r="J206" t="n">
-        <v>1463.8</v>
+        <v>1464.2</v>
       </c>
       <c r="K206" t="n">
         <v>290</v>
@@ -25235,13 +25235,13 @@
         <v>1</v>
       </c>
       <c r="H207" t="n">
-        <v>1299.893</v>
+        <v>1299.905</v>
       </c>
       <c r="I207" t="n">
-        <v>-4.0745</v>
+        <v>-4.0723</v>
       </c>
       <c r="J207" t="n">
-        <v>1458.7</v>
+        <v>1460.8</v>
       </c>
       <c r="K207" t="n">
         <v>334</v>
@@ -25355,13 +25355,13 @@
         <v>1</v>
       </c>
       <c r="H208" t="n">
-        <v>1537.165</v>
+        <v>1536.66</v>
       </c>
       <c r="I208" t="n">
-        <v>-5.3054</v>
+        <v>-5.3186</v>
       </c>
       <c r="J208" t="n">
-        <v>1505.6</v>
+        <v>1505</v>
       </c>
       <c r="K208" t="n">
         <v>139</v>
@@ -25475,13 +25475,13 @@
         <v>1</v>
       </c>
       <c r="H209" t="n">
-        <v>1359.583</v>
+        <v>1359.898</v>
       </c>
       <c r="I209" t="n">
-        <v>-3.5538</v>
+        <v>-3.5632</v>
       </c>
       <c r="J209" t="n">
-        <v>1484.3</v>
+        <v>1483.9</v>
       </c>
       <c r="K209" t="n">
         <v>288</v>
@@ -25595,13 +25595,13 @@
         <v>1</v>
       </c>
       <c r="H210" t="n">
-        <v>1320.351</v>
+        <v>1320.172</v>
       </c>
       <c r="I210" t="n">
-        <v>-3.2819</v>
+        <v>-3.2777</v>
       </c>
       <c r="J210" t="n">
-        <v>1438.2</v>
+        <v>1438.1</v>
       </c>
       <c r="K210" t="n">
         <v>319</v>
@@ -25715,13 +25715,13 @@
         <v>1</v>
       </c>
       <c r="H211" t="n">
-        <v>1548.166</v>
+        <v>1547.46</v>
       </c>
       <c r="I211" t="n">
-        <v>-4.3824</v>
+        <v>-4.3733</v>
       </c>
       <c r="J211" t="n">
-        <v>1508.1</v>
+        <v>1507.2</v>
       </c>
       <c r="K211" t="n">
         <v>80</v>
@@ -25835,13 +25835,13 @@
         <v>1</v>
       </c>
       <c r="H212" t="n">
-        <v>1591.668</v>
+        <v>1592.36</v>
       </c>
       <c r="I212" t="n">
-        <v>-4.6981</v>
+        <v>-4.7578</v>
       </c>
       <c r="J212" t="n">
-        <v>1705.7</v>
+        <v>1706.7</v>
       </c>
       <c r="K212" t="n">
         <v>68</v>
@@ -25955,13 +25955,13 @@
         <v>1</v>
       </c>
       <c r="H213" t="n">
-        <v>1288.325</v>
+        <v>1288.065</v>
       </c>
       <c r="I213" t="n">
-        <v>-1.6901</v>
+        <v>-1.681</v>
       </c>
       <c r="J213" t="n">
-        <v>1441.9</v>
+        <v>1441.7</v>
       </c>
       <c r="K213" t="n">
         <v>276</v>
@@ -26075,13 +26075,13 @@
         <v>1</v>
       </c>
       <c r="H214" t="n">
-        <v>1568.181</v>
+        <v>1567.936</v>
       </c>
       <c r="I214" t="n">
-        <v>1.0171</v>
+        <v>1.0015</v>
       </c>
       <c r="J214" t="n">
-        <v>1650.9</v>
+        <v>1651.5</v>
       </c>
       <c r="K214" t="n">
         <v>84</v>
@@ -26195,13 +26195,13 @@
         <v>1</v>
       </c>
       <c r="H215" t="n">
-        <v>1503.515</v>
+        <v>1505.314</v>
       </c>
       <c r="I215" t="n">
-        <v>2.6449</v>
+        <v>2.5419</v>
       </c>
       <c r="J215" t="n">
-        <v>1489.4</v>
+        <v>1491.6</v>
       </c>
       <c r="K215" t="n">
         <v>161</v>
@@ -26315,13 +26315,13 @@
         <v>1</v>
       </c>
       <c r="H216" t="n">
-        <v>1466.528</v>
+        <v>1466.092</v>
       </c>
       <c r="I216" t="n">
-        <v>2.6633</v>
+        <v>2.6549</v>
       </c>
       <c r="J216" t="n">
-        <v>1501.4</v>
+        <v>1500.7</v>
       </c>
       <c r="K216" t="n">
         <v>227</v>
@@ -26435,13 +26435,13 @@
         <v>1</v>
       </c>
       <c r="H217" t="n">
-        <v>1787.388</v>
+        <v>1789.235</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3307</v>
+        <v>1.4042</v>
       </c>
       <c r="J217" t="n">
-        <v>1694.2</v>
+        <v>1696.1</v>
       </c>
       <c r="K217" t="n">
         <v>35</v>
@@ -26555,13 +26555,13 @@
         <v>1</v>
       </c>
       <c r="H218" t="n">
-        <v>1687.398</v>
+        <v>1685.894</v>
       </c>
       <c r="I218" t="n">
-        <v>-3.1749</v>
+        <v>-2.7727</v>
       </c>
       <c r="J218" t="n">
-        <v>1659.4</v>
+        <v>1660.1</v>
       </c>
       <c r="K218" t="n">
         <v>50</v>
@@ -26675,13 +26675,13 @@
         <v>1</v>
       </c>
       <c r="H219" t="n">
-        <v>1713.406</v>
+        <v>1711.936</v>
       </c>
       <c r="I219" t="n">
-        <v>-1.1735</v>
+        <v>-1.0529</v>
       </c>
       <c r="J219" t="n">
-        <v>1678.3</v>
+        <v>1677.8</v>
       </c>
       <c r="K219" t="n">
         <v>74</v>
@@ -26795,13 +26795,13 @@
         <v>1</v>
       </c>
       <c r="H220" t="n">
-        <v>1355.571</v>
+        <v>1355.744</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5648</v>
       </c>
       <c r="J220" t="n">
-        <v>1469</v>
+        <v>1469.1</v>
       </c>
       <c r="K220" t="n">
         <v>243</v>
@@ -26915,13 +26915,13 @@
         <v>1</v>
       </c>
       <c r="H221" t="n">
-        <v>1260.799</v>
+        <v>1260.521</v>
       </c>
       <c r="I221" t="n">
-        <v>-2.7422</v>
+        <v>-2.7439</v>
       </c>
       <c r="J221" t="n">
-        <v>1440.5</v>
+        <v>1440.1</v>
       </c>
       <c r="K221" t="n">
         <v>315</v>
@@ -27035,13 +27035,13 @@
         <v>1</v>
       </c>
       <c r="H222" t="n">
-        <v>1591.289</v>
+        <v>1593.246</v>
       </c>
       <c r="I222" t="n">
-        <v>-9.7958</v>
+        <v>-9.597300000000001</v>
       </c>
       <c r="J222" t="n">
-        <v>1735.8</v>
+        <v>1738.3</v>
       </c>
       <c r="K222" t="n">
         <v>98</v>
@@ -27155,13 +27155,13 @@
         <v>1</v>
       </c>
       <c r="H223" t="n">
-        <v>1544.148</v>
+        <v>1543.318</v>
       </c>
       <c r="I223" t="n">
-        <v>-3.0583</v>
+        <v>-3.0737</v>
       </c>
       <c r="J223" t="n">
-        <v>1540</v>
+        <v>1539.5</v>
       </c>
       <c r="K223" t="n">
         <v>184</v>
@@ -27275,13 +27275,13 @@
         <v>1</v>
       </c>
       <c r="H224" t="n">
-        <v>1432.968</v>
+        <v>1432.666</v>
       </c>
       <c r="I224" t="n">
-        <v>4.1251</v>
+        <v>4.1195</v>
       </c>
       <c r="J224" t="n">
-        <v>1522.5</v>
+        <v>1522.4</v>
       </c>
       <c r="K224" t="n">
         <v>112</v>
@@ -27395,13 +27395,13 @@
         <v>1</v>
       </c>
       <c r="H225" t="n">
-        <v>1421.537</v>
+        <v>1421.929</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9917</v>
+        <v>0.9885</v>
       </c>
       <c r="J225" t="n">
-        <v>1486.8</v>
+        <v>1486.6</v>
       </c>
       <c r="K225" t="n">
         <v>169</v>
@@ -27515,13 +27515,13 @@
         <v>1</v>
       </c>
       <c r="H226" t="n">
-        <v>1531.427</v>
+        <v>1532.755</v>
       </c>
       <c r="I226" t="n">
-        <v>-7.5446</v>
+        <v>-7.5578</v>
       </c>
       <c r="J226" t="n">
-        <v>1669.9</v>
+        <v>1671.8</v>
       </c>
       <c r="K226" t="n">
         <v>128</v>
@@ -27635,13 +27635,13 @@
         <v>1</v>
       </c>
       <c r="H227" t="n">
-        <v>1308.915</v>
+        <v>1308.842</v>
       </c>
       <c r="I227" t="n">
-        <v>-1.8402</v>
+        <v>-1.8484</v>
       </c>
       <c r="J227" t="n">
-        <v>1522.7</v>
+        <v>1523.1</v>
       </c>
       <c r="K227" t="n">
         <v>260</v>
@@ -27755,10 +27755,10 @@
         <v>1</v>
       </c>
       <c r="H228" t="n">
-        <v>1510.72</v>
+        <v>1510.667</v>
       </c>
       <c r="I228" t="n">
-        <v>-5.4673</v>
+        <v>-5.4665</v>
       </c>
       <c r="J228" t="n">
         <v>1660.9</v>
@@ -27875,13 +27875,13 @@
         <v>1</v>
       </c>
       <c r="H229" t="n">
-        <v>1412.642</v>
+        <v>1412.258</v>
       </c>
       <c r="I229" t="n">
-        <v>1.453</v>
+        <v>1.4459</v>
       </c>
       <c r="J229" t="n">
-        <v>1532.3</v>
+        <v>1532.4</v>
       </c>
       <c r="K229" t="n">
         <v>204</v>
@@ -27995,13 +27995,13 @@
         <v>1</v>
       </c>
       <c r="H230" t="n">
-        <v>1458.619</v>
+        <v>1458.268</v>
       </c>
       <c r="I230" t="n">
-        <v>2.1359</v>
+        <v>2.128</v>
       </c>
       <c r="J230" t="n">
-        <v>1417.2</v>
+        <v>1416.6</v>
       </c>
       <c r="K230" t="n">
         <v>159</v>
@@ -28115,13 +28115,13 @@
         <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>1254.63</v>
+        <v>1254.158</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.9082</v>
+        <v>-0.9032</v>
       </c>
       <c r="J231" t="n">
-        <v>1391.5</v>
+        <v>1390.4</v>
       </c>
       <c r="K231" t="n">
         <v>318</v>
@@ -28235,13 +28235,13 @@
         <v>1</v>
       </c>
       <c r="H232" t="n">
-        <v>1327.583</v>
+        <v>1327.678</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.9623</v>
+        <v>-0.9686</v>
       </c>
       <c r="J232" t="n">
-        <v>1410.6</v>
+        <v>1410.8</v>
       </c>
       <c r="K232" t="n">
         <v>278</v>
@@ -28355,13 +28355,13 @@
         <v>1</v>
       </c>
       <c r="H233" t="n">
-        <v>1414.019</v>
+        <v>1413.467</v>
       </c>
       <c r="I233" t="n">
-        <v>-4.6765</v>
+        <v>-4.7095</v>
       </c>
       <c r="J233" t="n">
-        <v>1476.8</v>
+        <v>1475.7</v>
       </c>
       <c r="K233" t="n">
         <v>251</v>
@@ -28475,13 +28475,13 @@
         <v>1</v>
       </c>
       <c r="H234" t="n">
-        <v>1568.757</v>
+        <v>1570.237</v>
       </c>
       <c r="I234" t="n">
-        <v>1.8893</v>
+        <v>1.9346</v>
       </c>
       <c r="J234" t="n">
-        <v>1637.9</v>
+        <v>1639.9</v>
       </c>
       <c r="K234" t="n">
         <v>63</v>
@@ -28595,13 +28595,13 @@
         <v>1</v>
       </c>
       <c r="H235" t="n">
-        <v>1976.001</v>
+        <v>1978.08</v>
       </c>
       <c r="I235" t="n">
-        <v>0.8268</v>
+        <v>0.7736</v>
       </c>
       <c r="J235" t="n">
-        <v>1740.2</v>
+        <v>1741</v>
       </c>
       <c r="K235" t="n">
         <v>8</v>
@@ -28715,13 +28715,13 @@
         <v>1</v>
       </c>
       <c r="H236" t="n">
-        <v>1509.531</v>
+        <v>1509.395</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4836</v>
+        <v>-0.4631</v>
       </c>
       <c r="J236" t="n">
-        <v>1442.7</v>
+        <v>1441.8</v>
       </c>
       <c r="K236" t="n">
         <v>218</v>
@@ -28835,13 +28835,13 @@
         <v>1</v>
       </c>
       <c r="H237" t="n">
-        <v>1373.287</v>
+        <v>1373.073</v>
       </c>
       <c r="I237" t="n">
-        <v>-1.7029</v>
+        <v>-1.7201</v>
       </c>
       <c r="J237" t="n">
-        <v>1424.1</v>
+        <v>1423.5</v>
       </c>
       <c r="K237" t="n">
         <v>255</v>
@@ -28955,13 +28955,13 @@
         <v>1</v>
       </c>
       <c r="H238" t="n">
-        <v>1573.391</v>
+        <v>1573.103</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7869</v>
+        <v>0.7973</v>
       </c>
       <c r="J238" t="n">
-        <v>1518.9</v>
+        <v>1519</v>
       </c>
       <c r="K238" t="n">
         <v>137</v>
@@ -29075,13 +29075,13 @@
         <v>1</v>
       </c>
       <c r="H239" t="n">
-        <v>1395.068</v>
+        <v>1394.644</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3717</v>
+        <v>0.373</v>
       </c>
       <c r="J239" t="n">
-        <v>1520</v>
+        <v>1519.1</v>
       </c>
       <c r="K239" t="n">
         <v>230</v>
@@ -29195,13 +29195,13 @@
         <v>1</v>
       </c>
       <c r="H240" t="n">
-        <v>1471.699</v>
+        <v>1471.33</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.362</v>
+        <v>-0.3741</v>
       </c>
       <c r="J240" t="n">
-        <v>1514.2</v>
+        <v>1513.8</v>
       </c>
       <c r="K240" t="n">
         <v>142</v>
@@ -29315,13 +29315,13 @@
         <v>1</v>
       </c>
       <c r="H241" t="n">
-        <v>1283.083</v>
+        <v>1283.559</v>
       </c>
       <c r="I241" t="n">
-        <v>-3.6533</v>
+        <v>-3.667</v>
       </c>
       <c r="J241" t="n">
-        <v>1465.2</v>
+        <v>1465.9</v>
       </c>
       <c r="K241" t="n">
         <v>357</v>
@@ -29435,13 +29435,13 @@
         <v>1</v>
       </c>
       <c r="H242" t="n">
-        <v>1539.878</v>
+        <v>1538.807</v>
       </c>
       <c r="I242" t="n">
-        <v>-1.3829</v>
+        <v>-1.3441</v>
       </c>
       <c r="J242" t="n">
-        <v>1429.6</v>
+        <v>1429.2</v>
       </c>
       <c r="K242" t="n">
         <v>146</v>
@@ -29555,13 +29555,13 @@
         <v>1</v>
       </c>
       <c r="H243" t="n">
-        <v>1550.636</v>
+        <v>1551.607</v>
       </c>
       <c r="I243" t="n">
-        <v>-3.1151</v>
+        <v>-3.1062</v>
       </c>
       <c r="J243" t="n">
-        <v>1695.2</v>
+        <v>1697.1</v>
       </c>
       <c r="K243" t="n">
         <v>144</v>
@@ -29675,13 +29675,13 @@
         <v>1</v>
       </c>
       <c r="H244" t="n">
-        <v>1259.875</v>
+        <v>1259.415</v>
       </c>
       <c r="I244" t="n">
-        <v>-3.2581</v>
+        <v>-3.2527</v>
       </c>
       <c r="J244" t="n">
-        <v>1394.5</v>
+        <v>1393</v>
       </c>
       <c r="K244" t="n">
         <v>358</v>
@@ -29795,13 +29795,13 @@
         <v>1</v>
       </c>
       <c r="H245" t="n">
-        <v>1389.165</v>
+        <v>1388.955</v>
       </c>
       <c r="I245" t="n">
-        <v>-4.6305</v>
+        <v>-4.6139</v>
       </c>
       <c r="J245" t="n">
-        <v>1460.1</v>
+        <v>1460.2</v>
       </c>
       <c r="K245" t="n">
         <v>216</v>
@@ -29915,13 +29915,13 @@
         <v>1</v>
       </c>
       <c r="H246" t="n">
-        <v>1474.923</v>
+        <v>1473.456</v>
       </c>
       <c r="I246" t="n">
-        <v>0.7808</v>
+        <v>0.7702</v>
       </c>
       <c r="J246" t="n">
-        <v>1518.9</v>
+        <v>1517.4</v>
       </c>
       <c r="K246" t="n">
         <v>114</v>
@@ -30035,13 +30035,13 @@
         <v>1</v>
       </c>
       <c r="H247" t="n">
-        <v>1351.149</v>
+        <v>1351.606</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.0969</v>
+        <v>-0.1043</v>
       </c>
       <c r="J247" t="n">
-        <v>1433.1</v>
+        <v>1433.7</v>
       </c>
       <c r="K247" t="n">
         <v>293</v>
@@ -30155,13 +30155,13 @@
         <v>1</v>
       </c>
       <c r="H248" t="n">
-        <v>1545.235</v>
+        <v>1544.301</v>
       </c>
       <c r="I248" t="n">
-        <v>4.7891</v>
+        <v>4.758</v>
       </c>
       <c r="J248" t="n">
-        <v>1490.8</v>
+        <v>1491.4</v>
       </c>
       <c r="K248" t="n">
         <v>103</v>
@@ -30275,13 +30275,13 @@
         <v>1</v>
       </c>
       <c r="H249" t="n">
-        <v>1444.709</v>
+        <v>1444.918</v>
       </c>
       <c r="I249" t="n">
-        <v>-4.0916</v>
+        <v>-4.0824</v>
       </c>
       <c r="J249" t="n">
-        <v>1433.3</v>
+        <v>1434</v>
       </c>
       <c r="K249" t="n">
         <v>209</v>
@@ -30395,13 +30395,13 @@
         <v>1</v>
       </c>
       <c r="H250" t="n">
-        <v>1363.007</v>
+        <v>1362.04</v>
       </c>
       <c r="I250" t="n">
-        <v>1.825</v>
+        <v>1.7876</v>
       </c>
       <c r="J250" t="n">
-        <v>1528.1</v>
+        <v>1527.7</v>
       </c>
       <c r="K250" t="n">
         <v>235</v>
@@ -30515,13 +30515,13 @@
         <v>1</v>
       </c>
       <c r="H251" t="n">
-        <v>1784.945</v>
+        <v>1781.621</v>
       </c>
       <c r="I251" t="n">
-        <v>5.7312</v>
+        <v>6.1342</v>
       </c>
       <c r="J251" t="n">
-        <v>1653.1</v>
+        <v>1653.2</v>
       </c>
       <c r="K251" t="n">
         <v>42</v>
@@ -30635,13 +30635,13 @@
         <v>1</v>
       </c>
       <c r="H252" t="n">
-        <v>1566.328</v>
+        <v>1564.657</v>
       </c>
       <c r="I252" t="n">
-        <v>-4.2596</v>
+        <v>-4.1724</v>
       </c>
       <c r="J252" t="n">
-        <v>1574.8</v>
+        <v>1573.6</v>
       </c>
       <c r="K252" t="n">
         <v>122</v>
@@ -30755,13 +30755,13 @@
         <v>1</v>
       </c>
       <c r="H253" t="n">
-        <v>1365.067</v>
+        <v>1364.397</v>
       </c>
       <c r="I253" t="n">
-        <v>-3.3076</v>
+        <v>-3.3087</v>
       </c>
       <c r="J253" t="n">
-        <v>1586.5</v>
+        <v>1585.4</v>
       </c>
       <c r="K253" t="n">
         <v>234</v>
@@ -30875,13 +30875,13 @@
         <v>1</v>
       </c>
       <c r="H254" t="n">
-        <v>1501.286</v>
+        <v>1500.315</v>
       </c>
       <c r="I254" t="n">
-        <v>1.1028</v>
+        <v>1.0888</v>
       </c>
       <c r="J254" t="n">
-        <v>1451.8</v>
+        <v>1451.1</v>
       </c>
       <c r="K254" t="n">
         <v>129</v>
@@ -30995,13 +30995,13 @@
         <v>1</v>
       </c>
       <c r="H255" t="n">
-        <v>1765.301</v>
+        <v>1765.908</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5462</v>
+        <v>-0.7176</v>
       </c>
       <c r="J255" t="n">
-        <v>1571</v>
+        <v>1571.8</v>
       </c>
       <c r="K255" t="n">
         <v>37</v>
@@ -31115,13 +31115,13 @@
         <v>1</v>
       </c>
       <c r="H256" t="n">
-        <v>1285.224</v>
+        <v>1285.42</v>
       </c>
       <c r="I256" t="n">
-        <v>0.3166</v>
+        <v>0.3056</v>
       </c>
       <c r="J256" t="n">
-        <v>1417.8</v>
+        <v>1417.1</v>
       </c>
       <c r="K256" t="n">
         <v>296</v>
@@ -31235,13 +31235,13 @@
         <v>1</v>
       </c>
       <c r="H257" t="n">
-        <v>1324.724</v>
+        <v>1324.351</v>
       </c>
       <c r="I257" t="n">
-        <v>-2.4425</v>
+        <v>-2.4332</v>
       </c>
       <c r="J257" t="n">
-        <v>1438.8</v>
+        <v>1439.1</v>
       </c>
       <c r="K257" t="n">
         <v>291</v>
@@ -31355,13 +31355,13 @@
         <v>1</v>
       </c>
       <c r="H258" t="n">
-        <v>1386.614</v>
+        <v>1385.873</v>
       </c>
       <c r="I258" t="n">
-        <v>1.6716</v>
+        <v>1.6769</v>
       </c>
       <c r="J258" t="n">
-        <v>1409.3</v>
+        <v>1408.2</v>
       </c>
       <c r="K258" t="n">
         <v>226</v>
@@ -31475,13 +31475,13 @@
         <v>1</v>
       </c>
       <c r="H259" t="n">
-        <v>1553.402</v>
+        <v>1553.464</v>
       </c>
       <c r="I259" t="n">
-        <v>2.7641</v>
+        <v>2.7763</v>
       </c>
       <c r="J259" t="n">
-        <v>1530.4</v>
+        <v>1530.5</v>
       </c>
       <c r="K259" t="n">
         <v>115</v>
@@ -31595,13 +31595,13 @@
         <v>1</v>
       </c>
       <c r="H260" t="n">
-        <v>1667.349</v>
+        <v>1668.113</v>
       </c>
       <c r="I260" t="n">
-        <v>5.3395</v>
+        <v>5.3546</v>
       </c>
       <c r="J260" t="n">
-        <v>1622.1</v>
+        <v>1623.2</v>
       </c>
       <c r="K260" t="n">
         <v>53</v>
@@ -31715,13 +31715,13 @@
         <v>1</v>
       </c>
       <c r="H261" t="n">
-        <v>1563.168</v>
+        <v>1563.199</v>
       </c>
       <c r="I261" t="n">
-        <v>3.2331</v>
+        <v>3.2741</v>
       </c>
       <c r="J261" t="n">
-        <v>1382.6</v>
+        <v>1383.2</v>
       </c>
       <c r="K261" t="n">
         <v>88</v>
@@ -31835,10 +31835,10 @@
         <v>1</v>
       </c>
       <c r="H262" t="n">
-        <v>1463.89</v>
+        <v>1463.906</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9913</v>
+        <v>0.9788</v>
       </c>
       <c r="J262" t="n">
         <v>1425.2</v>
@@ -31955,13 +31955,13 @@
         <v>1</v>
       </c>
       <c r="H263" t="n">
-        <v>1753.681</v>
+        <v>1752.712</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2979</v>
+        <v>1.268</v>
       </c>
       <c r="J263" t="n">
-        <v>1646.7</v>
+        <v>1646.2</v>
       </c>
       <c r="K263" t="n">
         <v>39</v>
@@ -32075,13 +32075,13 @@
         <v>1</v>
       </c>
       <c r="H264" t="n">
-        <v>1556.349</v>
+        <v>1555.873</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0573</v>
+        <v>0.064</v>
       </c>
       <c r="J264" t="n">
-        <v>1443.2</v>
+        <v>1442.7</v>
       </c>
       <c r="K264" t="n">
         <v>193</v>
@@ -32195,13 +32195,13 @@
         <v>1</v>
       </c>
       <c r="H265" t="n">
-        <v>1538.718</v>
+        <v>1537.929</v>
       </c>
       <c r="I265" t="n">
-        <v>-2.644</v>
+        <v>-2.6339</v>
       </c>
       <c r="J265" t="n">
-        <v>1657.2</v>
+        <v>1657.5</v>
       </c>
       <c r="K265" t="n">
         <v>94</v>
@@ -32315,13 +32315,13 @@
         <v>1</v>
       </c>
       <c r="H266" t="n">
-        <v>1367.158</v>
+        <v>1366.874</v>
       </c>
       <c r="I266" t="n">
-        <v>-1.4109</v>
+        <v>-1.4113</v>
       </c>
       <c r="J266" t="n">
-        <v>1426</v>
+        <v>1425.9</v>
       </c>
       <c r="K266" t="n">
         <v>281</v>
@@ -32435,13 +32435,13 @@
         <v>1</v>
       </c>
       <c r="H267" t="n">
-        <v>1713.424</v>
+        <v>1709.517</v>
       </c>
       <c r="I267" t="n">
-        <v>9.475099999999999</v>
+        <v>9.3651</v>
       </c>
       <c r="J267" t="n">
-        <v>1560.8</v>
+        <v>1558.8</v>
       </c>
       <c r="K267" t="n">
         <v>52</v>
@@ -32555,13 +32555,13 @@
         <v>1</v>
       </c>
       <c r="H268" t="n">
-        <v>1407.494</v>
+        <v>1407.285</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6847</v>
+        <v>0.6829</v>
       </c>
       <c r="J268" t="n">
-        <v>1466.5</v>
+        <v>1466.3</v>
       </c>
       <c r="K268" t="n">
         <v>225</v>
@@ -32675,13 +32675,13 @@
         <v>1</v>
       </c>
       <c r="H269" t="n">
-        <v>1374.214</v>
+        <v>1374.124</v>
       </c>
       <c r="I269" t="n">
-        <v>-2.5602</v>
+        <v>-2.5631</v>
       </c>
       <c r="J269" t="n">
-        <v>1401.1</v>
+        <v>1401.7</v>
       </c>
       <c r="K269" t="n">
         <v>284</v>
@@ -32795,13 +32795,13 @@
         <v>1</v>
       </c>
       <c r="H270" t="n">
-        <v>1325.338</v>
+        <v>1325.265</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2319</v>
+        <v>-0.2329</v>
       </c>
       <c r="J270" t="n">
-        <v>1493.8</v>
+        <v>1494</v>
       </c>
       <c r="K270" t="n">
         <v>256</v>
@@ -32915,13 +32915,13 @@
         <v>1</v>
       </c>
       <c r="H271" t="n">
-        <v>1531.757</v>
+        <v>1531.266</v>
       </c>
       <c r="I271" t="n">
-        <v>-8.8443</v>
+        <v>-8.8599</v>
       </c>
       <c r="J271" t="n">
-        <v>1532.1</v>
+        <v>1531.6</v>
       </c>
       <c r="K271" t="n">
         <v>150</v>
@@ -33035,13 +33035,13 @@
         <v>1</v>
       </c>
       <c r="H272" t="n">
-        <v>1243.869</v>
+        <v>1242.82</v>
       </c>
       <c r="I272" t="n">
-        <v>-1.7832</v>
+        <v>-1.7292</v>
       </c>
       <c r="J272" t="n">
-        <v>1422.9</v>
+        <v>1423.6</v>
       </c>
       <c r="K272" t="n">
         <v>354</v>
@@ -33155,13 +33155,13 @@
         <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>1955.277</v>
+        <v>1955.26</v>
       </c>
       <c r="I273" t="n">
-        <v>4.7636</v>
+        <v>5.539</v>
       </c>
       <c r="J273" t="n">
-        <v>1677.8</v>
+        <v>1679.7</v>
       </c>
       <c r="K273" t="n">
         <v>21</v>
@@ -33275,13 +33275,13 @@
         <v>1</v>
       </c>
       <c r="H274" t="n">
-        <v>1610.154</v>
+        <v>1609.769</v>
       </c>
       <c r="I274" t="n">
-        <v>0.6493</v>
+        <v>0.6471</v>
       </c>
       <c r="J274" t="n">
-        <v>1512.1</v>
+        <v>1511.8</v>
       </c>
       <c r="K274" t="n">
         <v>132</v>
@@ -33395,13 +33395,13 @@
         <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>1825.867</v>
+        <v>1824.481</v>
       </c>
       <c r="I275" t="n">
-        <v>10.4518</v>
+        <v>10.3996</v>
       </c>
       <c r="J275" t="n">
-        <v>1501.8</v>
+        <v>1501.2</v>
       </c>
       <c r="K275" t="n">
         <v>27</v>
@@ -33515,13 +33515,13 @@
         <v>1</v>
       </c>
       <c r="H276" t="n">
-        <v>1877.393</v>
+        <v>1877.369</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2467</v>
+        <v>-0.5286</v>
       </c>
       <c r="J276" t="n">
-        <v>1595.8</v>
+        <v>1595.3</v>
       </c>
       <c r="K276" t="n">
         <v>22</v>
@@ -33635,10 +33635,10 @@
         <v>1</v>
       </c>
       <c r="H277" t="n">
-        <v>1437.45</v>
+        <v>1438.465</v>
       </c>
       <c r="I277" t="n">
-        <v>2.7392</v>
+        <v>2.724</v>
       </c>
       <c r="J277" t="n">
         <v>1429</v>
@@ -33755,13 +33755,13 @@
         <v>1</v>
       </c>
       <c r="H278" t="n">
-        <v>1733.62</v>
+        <v>1734.198</v>
       </c>
       <c r="I278" t="n">
-        <v>2.8143</v>
+        <v>2.838</v>
       </c>
       <c r="J278" t="n">
-        <v>1622</v>
+        <v>1622.2</v>
       </c>
       <c r="K278" t="n">
         <v>65</v>
@@ -33875,13 +33875,13 @@
         <v>1</v>
       </c>
       <c r="H279" t="n">
-        <v>1302.712</v>
+        <v>1302.303</v>
       </c>
       <c r="I279" t="n">
-        <v>-1.2714</v>
+        <v>-1.2838</v>
       </c>
       <c r="J279" t="n">
-        <v>1410.3</v>
+        <v>1409.6</v>
       </c>
       <c r="K279" t="n">
         <v>317</v>
@@ -33995,13 +33995,13 @@
         <v>1</v>
       </c>
       <c r="H280" t="n">
-        <v>1447.485</v>
+        <v>1447.119</v>
       </c>
       <c r="I280" t="n">
-        <v>3.3213</v>
+        <v>3.303</v>
       </c>
       <c r="J280" t="n">
-        <v>1464.4</v>
+        <v>1463.7</v>
       </c>
       <c r="K280" t="n">
         <v>222</v>
@@ -34115,13 +34115,13 @@
         <v>1</v>
       </c>
       <c r="H281" t="n">
-        <v>1593.047</v>
+        <v>1593.426</v>
       </c>
       <c r="I281" t="n">
-        <v>1.2532</v>
+        <v>1.2389</v>
       </c>
       <c r="J281" t="n">
-        <v>1667.2</v>
+        <v>1667.8</v>
       </c>
       <c r="K281" t="n">
         <v>77</v>
@@ -34235,10 +34235,10 @@
         <v>1</v>
       </c>
       <c r="H282" t="n">
-        <v>1376.612</v>
+        <v>1376.177</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.4682</v>
+        <v>-0.451</v>
       </c>
       <c r="J282" t="n">
         <v>1426.5</v>
@@ -34355,13 +34355,13 @@
         <v>1</v>
       </c>
       <c r="H283" t="n">
-        <v>1824.162</v>
+        <v>1827.516</v>
       </c>
       <c r="I283" t="n">
-        <v>6.8019</v>
+        <v>6.8987</v>
       </c>
       <c r="J283" t="n">
-        <v>1678</v>
+        <v>1681.1</v>
       </c>
       <c r="K283" t="n">
         <v>49</v>
@@ -34475,13 +34475,13 @@
         <v>1</v>
       </c>
       <c r="H284" t="n">
-        <v>1509.441</v>
+        <v>1508.173</v>
       </c>
       <c r="I284" t="n">
-        <v>-1.64</v>
+        <v>-1.6583</v>
       </c>
       <c r="J284" t="n">
-        <v>1493.4</v>
+        <v>1492</v>
       </c>
       <c r="K284" t="n">
         <v>174</v>
@@ -34595,13 +34595,13 @@
         <v>1</v>
       </c>
       <c r="H285" t="n">
-        <v>1912.838</v>
+        <v>1915.649</v>
       </c>
       <c r="I285" t="n">
-        <v>-1.7463</v>
+        <v>-1.8805</v>
       </c>
       <c r="J285" t="n">
-        <v>1692.2</v>
+        <v>1693.7</v>
       </c>
       <c r="K285" t="n">
         <v>18</v>
@@ -34715,13 +34715,13 @@
         <v>1</v>
       </c>
       <c r="H286" t="n">
-        <v>1459.28</v>
+        <v>1458.771</v>
       </c>
       <c r="I286" t="n">
-        <v>3.6053</v>
+        <v>3.5917</v>
       </c>
       <c r="J286" t="n">
-        <v>1406.8</v>
+        <v>1406.4</v>
       </c>
       <c r="K286" t="n">
         <v>207</v>
@@ -34835,13 +34835,13 @@
         <v>1</v>
       </c>
       <c r="H287" t="n">
-        <v>1315.495</v>
+        <v>1314.939</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.7748</v>
       </c>
       <c r="J287" t="n">
-        <v>1399.9</v>
+        <v>1398.8</v>
       </c>
       <c r="K287" t="n">
         <v>309</v>
@@ -34955,13 +34955,13 @@
         <v>1</v>
       </c>
       <c r="H288" t="n">
-        <v>1777.532</v>
+        <v>1775.556</v>
       </c>
       <c r="I288" t="n">
-        <v>2.2904</v>
+        <v>2.7602</v>
       </c>
       <c r="J288" t="n">
-        <v>1700.7</v>
+        <v>1702.7</v>
       </c>
       <c r="K288" t="n">
         <v>29</v>
@@ -35075,10 +35075,10 @@
         <v>1</v>
       </c>
       <c r="H289" t="n">
-        <v>1836.851</v>
+        <v>1835.204</v>
       </c>
       <c r="I289" t="n">
-        <v>4.4256</v>
+        <v>4.7779</v>
       </c>
       <c r="J289" t="n">
         <v>1655.1</v>
@@ -35195,13 +35195,13 @@
         <v>1</v>
       </c>
       <c r="H290" t="n">
-        <v>1451.14</v>
+        <v>1450.753</v>
       </c>
       <c r="I290" t="n">
-        <v>0.1801</v>
+        <v>0.1677</v>
       </c>
       <c r="J290" t="n">
-        <v>1427.9</v>
+        <v>1427.4</v>
       </c>
       <c r="K290" t="n">
         <v>242</v>
@@ -35315,13 +35315,13 @@
         <v>1</v>
       </c>
       <c r="H291" t="n">
-        <v>2034.525</v>
+        <v>2044.23</v>
       </c>
       <c r="I291" t="n">
-        <v>11.3167</v>
+        <v>10.5951</v>
       </c>
       <c r="J291" t="n">
-        <v>1753.9</v>
+        <v>1756.8</v>
       </c>
       <c r="K291" t="n">
         <v>13</v>
@@ -35435,13 +35435,13 @@
         <v>1</v>
       </c>
       <c r="H292" t="n">
-        <v>1456.233</v>
+        <v>1455.888</v>
       </c>
       <c r="I292" t="n">
-        <v>0.952</v>
+        <v>0.9448</v>
       </c>
       <c r="J292" t="n">
-        <v>1374</v>
+        <v>1373.6</v>
       </c>
       <c r="K292" t="n">
         <v>217</v>
@@ -35555,13 +35555,13 @@
         <v>1</v>
       </c>
       <c r="H293" t="n">
-        <v>1453.126</v>
+        <v>1452.353</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.6704</v>
+        <v>-0.6824</v>
       </c>
       <c r="J293" t="n">
-        <v>1505.2</v>
+        <v>1505</v>
       </c>
       <c r="K293" t="n">
         <v>145</v>
@@ -35675,13 +35675,13 @@
         <v>1</v>
       </c>
       <c r="H294" t="n">
-        <v>1547.936</v>
+        <v>1546.171</v>
       </c>
       <c r="I294" t="n">
-        <v>-2.8805</v>
+        <v>-2.9255</v>
       </c>
       <c r="J294" t="n">
-        <v>1527.3</v>
+        <v>1527.1</v>
       </c>
       <c r="K294" t="n">
         <v>177</v>
@@ -35795,13 +35795,13 @@
         <v>1</v>
       </c>
       <c r="H295" t="n">
-        <v>1596.75</v>
+        <v>1593.696</v>
       </c>
       <c r="I295" t="n">
-        <v>1.2901</v>
+        <v>1.3343</v>
       </c>
       <c r="J295" t="n">
-        <v>1465.3</v>
+        <v>1464.1</v>
       </c>
       <c r="K295" t="n">
         <v>156</v>
@@ -35915,13 +35915,13 @@
         <v>1</v>
       </c>
       <c r="H296" t="n">
-        <v>1495.313</v>
+        <v>1493.45</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.8165</v>
+        <v>-1.8307</v>
       </c>
       <c r="J296" t="n">
-        <v>1532.1</v>
+        <v>1529.8</v>
       </c>
       <c r="K296" t="n">
         <v>196</v>
@@ -36035,13 +36035,13 @@
         <v>1</v>
       </c>
       <c r="H297" t="n">
-        <v>1677.601</v>
+        <v>1676.214</v>
       </c>
       <c r="I297" t="n">
-        <v>9.6843</v>
+        <v>9.632899999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>1503.6</v>
+        <v>1502.5</v>
       </c>
       <c r="K297" t="n">
         <v>56</v>
@@ -36155,13 +36155,13 @@
         <v>1</v>
       </c>
       <c r="H298" t="n">
-        <v>1394.177</v>
+        <v>1394.986</v>
       </c>
       <c r="I298" t="n">
-        <v>1.5557</v>
+        <v>1.606</v>
       </c>
       <c r="J298" t="n">
-        <v>1425</v>
+        <v>1426.5</v>
       </c>
       <c r="K298" t="n">
         <v>127</v>
@@ -36275,13 +36275,13 @@
         <v>1</v>
       </c>
       <c r="H299" t="n">
-        <v>1290.337</v>
+        <v>1289.804</v>
       </c>
       <c r="I299" t="n">
-        <v>-1.431</v>
+        <v>-1.4248</v>
       </c>
       <c r="J299" t="n">
-        <v>1390.5</v>
+        <v>1389.8</v>
       </c>
       <c r="K299" t="n">
         <v>297</v>
@@ -36395,13 +36395,13 @@
         <v>1</v>
       </c>
       <c r="H300" t="n">
-        <v>1599.905</v>
+        <v>1597.533</v>
       </c>
       <c r="I300" t="n">
-        <v>0.5599</v>
+        <v>0.5946</v>
       </c>
       <c r="J300" t="n">
-        <v>1505.6</v>
+        <v>1504.4</v>
       </c>
       <c r="K300" t="n">
         <v>124</v>
@@ -36515,13 +36515,13 @@
         <v>1</v>
       </c>
       <c r="H301" t="n">
-        <v>1476.874</v>
+        <v>1476.462</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.331</v>
+        <v>-0.3469</v>
       </c>
       <c r="J301" t="n">
-        <v>1449.1</v>
+        <v>1448.5</v>
       </c>
       <c r="K301" t="n">
         <v>155</v>
@@ -36635,13 +36635,13 @@
         <v>1</v>
       </c>
       <c r="H302" t="n">
-        <v>1611.822</v>
+        <v>1610.772</v>
       </c>
       <c r="I302" t="n">
-        <v>2.2597</v>
+        <v>2.2236</v>
       </c>
       <c r="J302" t="n">
-        <v>1470.9</v>
+        <v>1470.2</v>
       </c>
       <c r="K302" t="n">
         <v>109</v>
@@ -36755,10 +36755,10 @@
         <v>1</v>
       </c>
       <c r="H303" t="n">
-        <v>1387.923</v>
+        <v>1387.981</v>
       </c>
       <c r="I303" t="n">
-        <v>-6.1629</v>
+        <v>-6.1627</v>
       </c>
       <c r="J303" t="n">
         <v>1487.6</v>
@@ -36875,13 +36875,13 @@
         <v>1</v>
       </c>
       <c r="H304" t="n">
-        <v>1839.825</v>
+        <v>1838.194</v>
       </c>
       <c r="I304" t="n">
-        <v>7.5365</v>
+        <v>7.6713</v>
       </c>
       <c r="J304" t="n">
-        <v>1687.9</v>
+        <v>1687.7</v>
       </c>
       <c r="K304" t="n">
         <v>48</v>
@@ -36995,13 +36995,13 @@
         <v>1</v>
       </c>
       <c r="H305" t="n">
-        <v>1842.008</v>
+        <v>1845.841</v>
       </c>
       <c r="I305" t="n">
-        <v>2.4672</v>
+        <v>2.0997</v>
       </c>
       <c r="J305" t="n">
-        <v>1687.7</v>
+        <v>1689.8</v>
       </c>
       <c r="K305" t="n">
         <v>41</v>
@@ -37115,13 +37115,13 @@
         <v>1</v>
       </c>
       <c r="H306" t="n">
-        <v>1319.966</v>
+        <v>1319.66</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.9378</v>
+        <v>-0.9332</v>
       </c>
       <c r="J306" t="n">
-        <v>1467.4</v>
+        <v>1467.5</v>
       </c>
       <c r="K306" t="n">
         <v>311</v>
@@ -37235,13 +37235,13 @@
         <v>1</v>
       </c>
       <c r="H307" t="n">
-        <v>1193.541</v>
+        <v>1193.442</v>
       </c>
       <c r="I307" t="n">
-        <v>-2.9969</v>
+        <v>-2.9996</v>
       </c>
       <c r="J307" t="n">
-        <v>1446.4</v>
+        <v>1446.8</v>
       </c>
       <c r="K307" t="n">
         <v>352</v>
@@ -37355,13 +37355,13 @@
         <v>1</v>
       </c>
       <c r="H308" t="n">
-        <v>1390.251</v>
+        <v>1390.224</v>
       </c>
       <c r="I308" t="n">
-        <v>1.1323</v>
+        <v>1.1316</v>
       </c>
       <c r="J308" t="n">
-        <v>1368.2</v>
+        <v>1368.1</v>
       </c>
       <c r="K308" t="n">
         <v>221</v>
@@ -37475,13 +37475,13 @@
         <v>1</v>
       </c>
       <c r="H309" t="n">
-        <v>1375.178</v>
+        <v>1374.882</v>
       </c>
       <c r="I309" t="n">
-        <v>-4.3006</v>
+        <v>-4.2989</v>
       </c>
       <c r="J309" t="n">
-        <v>1419.4</v>
+        <v>1418.9</v>
       </c>
       <c r="K309" t="n">
         <v>253</v>
@@ -37595,13 +37595,13 @@
         <v>1</v>
       </c>
       <c r="H310" t="n">
-        <v>1366.319</v>
+        <v>1366.304</v>
       </c>
       <c r="I310" t="n">
-        <v>-2.834</v>
+        <v>-2.841</v>
       </c>
       <c r="J310" t="n">
-        <v>1427.6</v>
+        <v>1427.7</v>
       </c>
       <c r="K310" t="n">
         <v>304</v>
@@ -37715,13 +37715,13 @@
         <v>1</v>
       </c>
       <c r="H311" t="n">
-        <v>1685.169</v>
+        <v>1681.028</v>
       </c>
       <c r="I311" t="n">
-        <v>1.8461</v>
+        <v>2.0383</v>
       </c>
       <c r="J311" t="n">
-        <v>1429.5</v>
+        <v>1429</v>
       </c>
       <c r="K311" t="n">
         <v>104</v>
@@ -37835,13 +37835,13 @@
         <v>1</v>
       </c>
       <c r="H312" t="n">
-        <v>1653.533</v>
+        <v>1651.123</v>
       </c>
       <c r="I312" t="n">
-        <v>1.5039</v>
+        <v>1.4503</v>
       </c>
       <c r="J312" t="n">
-        <v>1621</v>
+        <v>1619.2</v>
       </c>
       <c r="K312" t="n">
         <v>120</v>
@@ -37955,13 +37955,13 @@
         <v>1</v>
       </c>
       <c r="H313" t="n">
-        <v>1755.83</v>
+        <v>1756.26</v>
       </c>
       <c r="I313" t="n">
-        <v>1.5224</v>
+        <v>1.6277</v>
       </c>
       <c r="J313" t="n">
-        <v>1684.4</v>
+        <v>1685.7</v>
       </c>
       <c r="K313" t="n">
         <v>67</v>
@@ -38075,13 +38075,13 @@
         <v>1</v>
       </c>
       <c r="H314" t="n">
-        <v>1460.197</v>
+        <v>1460.092</v>
       </c>
       <c r="I314" t="n">
-        <v>1.2417</v>
+        <v>1.2384</v>
       </c>
       <c r="J314" t="n">
-        <v>1462.8</v>
+        <v>1462.9</v>
       </c>
       <c r="K314" t="n">
         <v>163</v>
@@ -38195,13 +38195,13 @@
         <v>1</v>
       </c>
       <c r="H315" t="n">
-        <v>1294.163</v>
+        <v>1293.858</v>
       </c>
       <c r="I315" t="n">
-        <v>-4.1527</v>
+        <v>-4.1477</v>
       </c>
       <c r="J315" t="n">
-        <v>1549.5</v>
+        <v>1548.4</v>
       </c>
       <c r="K315" t="n">
         <v>339</v>
@@ -38315,13 +38315,13 @@
         <v>1</v>
       </c>
       <c r="H316" t="n">
-        <v>1524.962</v>
+        <v>1525.926</v>
       </c>
       <c r="I316" t="n">
-        <v>-4.7872</v>
+        <v>-4.671</v>
       </c>
       <c r="J316" t="n">
-        <v>1688.9</v>
+        <v>1690.3</v>
       </c>
       <c r="K316" t="n">
         <v>116</v>
@@ -38435,13 +38435,13 @@
         <v>1</v>
       </c>
       <c r="H317" t="n">
-        <v>1864.304</v>
+        <v>1858.41</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.3251</v>
+        <v>0.4232</v>
       </c>
       <c r="J317" t="n">
-        <v>1591.6</v>
+        <v>1589.9</v>
       </c>
       <c r="K317" t="n">
         <v>26</v>
@@ -38555,13 +38555,13 @@
         <v>1</v>
       </c>
       <c r="H318" t="n">
-        <v>1634.463</v>
+        <v>1633.955</v>
       </c>
       <c r="I318" t="n">
-        <v>3.3289</v>
+        <v>3.3264</v>
       </c>
       <c r="J318" t="n">
-        <v>1457.8</v>
+        <v>1457.5</v>
       </c>
       <c r="K318" t="n">
         <v>85</v>
@@ -38675,13 +38675,13 @@
         <v>1</v>
       </c>
       <c r="H319" t="n">
-        <v>1399.069</v>
+        <v>1398.406</v>
       </c>
       <c r="I319" t="n">
-        <v>-1.8541</v>
+        <v>-1.8368</v>
       </c>
       <c r="J319" t="n">
-        <v>1511</v>
+        <v>1509.3</v>
       </c>
       <c r="K319" t="n">
         <v>280</v>
@@ -38795,13 +38795,13 @@
         <v>1</v>
       </c>
       <c r="H320" t="n">
-        <v>1731.78</v>
+        <v>1727.947</v>
       </c>
       <c r="I320" t="n">
-        <v>2.54</v>
+        <v>2.9027</v>
       </c>
       <c r="J320" t="n">
-        <v>1552.4</v>
+        <v>1551.3</v>
       </c>
       <c r="K320" t="n">
         <v>45</v>
@@ -38915,13 +38915,13 @@
         <v>1</v>
       </c>
       <c r="H321" t="n">
-        <v>1462.274</v>
+        <v>1460.92</v>
       </c>
       <c r="I321" t="n">
-        <v>0.7974</v>
+        <v>0.7665</v>
       </c>
       <c r="J321" t="n">
-        <v>1519.4</v>
+        <v>1518.4</v>
       </c>
       <c r="K321" t="n">
         <v>152</v>
@@ -39035,13 +39035,13 @@
         <v>1</v>
       </c>
       <c r="H322" t="n">
-        <v>1921.037</v>
+        <v>1918.697</v>
       </c>
       <c r="I322" t="n">
-        <v>1.9274</v>
+        <v>2.6895</v>
       </c>
       <c r="J322" t="n">
-        <v>1684</v>
+        <v>1684.4</v>
       </c>
       <c r="K322" t="n">
         <v>14</v>
@@ -39155,13 +39155,13 @@
         <v>1</v>
       </c>
       <c r="H323" t="n">
-        <v>1468.449</v>
+        <v>1467.286</v>
       </c>
       <c r="I323" t="n">
-        <v>-1.865</v>
+        <v>-1.814</v>
       </c>
       <c r="J323" t="n">
-        <v>1394.9</v>
+        <v>1394.3</v>
       </c>
       <c r="K323" t="n">
         <v>245</v>
@@ -39275,13 +39275,13 @@
         <v>1</v>
       </c>
       <c r="H324" t="n">
-        <v>1820.115</v>
+        <v>1821.543</v>
       </c>
       <c r="I324" t="n">
-        <v>6.5295</v>
+        <v>6.4146</v>
       </c>
       <c r="J324" t="n">
-        <v>1643.5</v>
+        <v>1645.7</v>
       </c>
       <c r="K324" t="n">
         <v>34</v>
@@ -39395,13 +39395,13 @@
         <v>1</v>
       </c>
       <c r="H325" t="n">
-        <v>1951.176</v>
+        <v>1951.595</v>
       </c>
       <c r="I325" t="n">
-        <v>13.9718</v>
+        <v>14.014</v>
       </c>
       <c r="J325" t="n">
-        <v>1635.2</v>
+        <v>1635.8</v>
       </c>
       <c r="K325" t="n">
         <v>17</v>
@@ -39515,13 +39515,13 @@
         <v>1</v>
       </c>
       <c r="H326" t="n">
-        <v>1717.963</v>
+        <v>1718.463</v>
       </c>
       <c r="I326" t="n">
-        <v>6.2269</v>
+        <v>6.1973</v>
       </c>
       <c r="J326" t="n">
-        <v>1648</v>
+        <v>1648.5</v>
       </c>
       <c r="K326" t="n">
         <v>57</v>
@@ -39635,13 +39635,13 @@
         <v>1</v>
       </c>
       <c r="H327" t="n">
-        <v>1237.021</v>
+        <v>1236.891</v>
       </c>
       <c r="I327" t="n">
-        <v>-3.5951</v>
+        <v>-3.5993</v>
       </c>
       <c r="J327" t="n">
-        <v>1432.7</v>
+        <v>1431.8</v>
       </c>
       <c r="K327" t="n">
         <v>360</v>
@@ -39755,13 +39755,13 @@
         <v>1</v>
       </c>
       <c r="H328" t="n">
-        <v>1377.522</v>
+        <v>1377.297</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.0451</v>
+        <v>-0.0597</v>
       </c>
       <c r="J328" t="n">
-        <v>1473.2</v>
+        <v>1472.9</v>
       </c>
       <c r="K328" t="n">
         <v>236</v>
@@ -39875,13 +39875,13 @@
         <v>1</v>
       </c>
       <c r="H329" t="n">
-        <v>1230.244</v>
+        <v>1230.004</v>
       </c>
       <c r="I329" t="n">
-        <v>-4.1007</v>
+        <v>-4.103</v>
       </c>
       <c r="J329" t="n">
-        <v>1392.3</v>
+        <v>1391.6</v>
       </c>
       <c r="K329" t="n">
         <v>364</v>
@@ -39995,13 +39995,13 @@
         <v>1</v>
       </c>
       <c r="H330" t="n">
-        <v>1489.079</v>
+        <v>1487.851</v>
       </c>
       <c r="I330" t="n">
-        <v>-3.6149</v>
+        <v>-3.5819</v>
       </c>
       <c r="J330" t="n">
-        <v>1487.7</v>
+        <v>1486.4</v>
       </c>
       <c r="K330" t="n">
         <v>138</v>
@@ -40115,13 +40115,13 @@
         <v>1</v>
       </c>
       <c r="H331" t="n">
-        <v>1338.245</v>
+        <v>1337.936</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4663</v>
+        <v>-0.4778</v>
       </c>
       <c r="J331" t="n">
-        <v>1472.1</v>
+        <v>1471.7</v>
       </c>
       <c r="K331" t="n">
         <v>271</v>
@@ -40235,10 +40235,10 @@
         <v>1</v>
       </c>
       <c r="H332" t="n">
-        <v>1327.668</v>
+        <v>1328.263</v>
       </c>
       <c r="I332" t="n">
-        <v>-1.9736</v>
+        <v>-1.9713</v>
       </c>
       <c r="J332" t="n">
         <v>1390.2</v>
@@ -40355,13 +40355,13 @@
         <v>1</v>
       </c>
       <c r="H333" t="n">
-        <v>1637.259</v>
+        <v>1637.862</v>
       </c>
       <c r="I333" t="n">
-        <v>-2.9629</v>
+        <v>-3.1375</v>
       </c>
       <c r="J333" t="n">
-        <v>1669.8</v>
+        <v>1670.9</v>
       </c>
       <c r="K333" t="n">
         <v>78</v>
@@ -40475,13 +40475,13 @@
         <v>1</v>
       </c>
       <c r="H334" t="n">
-        <v>1654.225</v>
+        <v>1655.835</v>
       </c>
       <c r="I334" t="n">
-        <v>2.1014</v>
+        <v>2.1181</v>
       </c>
       <c r="J334" t="n">
-        <v>1689.2</v>
+        <v>1691.3</v>
       </c>
       <c r="K334" t="n">
         <v>54</v>
@@ -40595,13 +40595,13 @@
         <v>1</v>
       </c>
       <c r="H335" t="n">
-        <v>1458.662</v>
+        <v>1458.161</v>
       </c>
       <c r="I335" t="n">
-        <v>-1.9786</v>
+        <v>-1.9961</v>
       </c>
       <c r="J335" t="n">
-        <v>1567.7</v>
+        <v>1567.6</v>
       </c>
       <c r="K335" t="n">
         <v>134</v>
@@ -40715,13 +40715,13 @@
         <v>1</v>
       </c>
       <c r="H336" t="n">
-        <v>1363.363</v>
+        <v>1362.868</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.0421</v>
+        <v>-0.0298</v>
       </c>
       <c r="J336" t="n">
-        <v>1425.1</v>
+        <v>1423.8</v>
       </c>
       <c r="K336" t="n">
         <v>186</v>
@@ -40835,13 +40835,13 @@
         <v>1</v>
       </c>
       <c r="H337" t="n">
-        <v>1692.66</v>
+        <v>1692.605</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3873</v>
+        <v>0.3731</v>
       </c>
       <c r="J337" t="n">
-        <v>1649.8</v>
+        <v>1650.7</v>
       </c>
       <c r="K337" t="n">
         <v>59</v>
@@ -40955,13 +40955,13 @@
         <v>1</v>
       </c>
       <c r="H338" t="n">
-        <v>1382.087</v>
+        <v>1381.115</v>
       </c>
       <c r="I338" t="n">
-        <v>3.6489</v>
+        <v>3.6336</v>
       </c>
       <c r="J338" t="n">
-        <v>1449.1</v>
+        <v>1448.1</v>
       </c>
       <c r="K338" t="n">
         <v>195</v>
@@ -41075,13 +41075,13 @@
         <v>1</v>
       </c>
       <c r="H339" t="n">
-        <v>1393.173</v>
+        <v>1393.237</v>
       </c>
       <c r="I339" t="n">
-        <v>-3.5301</v>
+        <v>-3.5458</v>
       </c>
       <c r="J339" t="n">
-        <v>1454.8</v>
+        <v>1455</v>
       </c>
       <c r="K339" t="n">
         <v>262</v>
@@ -41195,13 +41195,13 @@
         <v>1</v>
       </c>
       <c r="H340" t="n">
-        <v>1614.619</v>
+        <v>1613.304</v>
       </c>
       <c r="I340" t="n">
-        <v>1.3875</v>
+        <v>1.3577</v>
       </c>
       <c r="J340" t="n">
-        <v>1530.2</v>
+        <v>1529.6</v>
       </c>
       <c r="K340" t="n">
         <v>89</v>
@@ -41315,13 +41315,13 @@
         <v>1</v>
       </c>
       <c r="H341" t="n">
-        <v>1526.698</v>
+        <v>1525.924</v>
       </c>
       <c r="I341" t="n">
-        <v>2.9316</v>
+        <v>2.8777</v>
       </c>
       <c r="J341" t="n">
-        <v>1464</v>
+        <v>1462.6</v>
       </c>
       <c r="K341" t="n">
         <v>133</v>
@@ -41435,13 +41435,13 @@
         <v>1</v>
       </c>
       <c r="H342" t="n">
-        <v>1492.049</v>
+        <v>1492.671</v>
       </c>
       <c r="I342" t="n">
-        <v>1.7239</v>
+        <v>1.7375</v>
       </c>
       <c r="J342" t="n">
-        <v>1432.7</v>
+        <v>1433.9</v>
       </c>
       <c r="K342" t="n">
         <v>141</v>
@@ -41555,13 +41555,13 @@
         <v>1</v>
       </c>
       <c r="H343" t="n">
-        <v>1837.727</v>
+        <v>1837.043</v>
       </c>
       <c r="I343" t="n">
-        <v>0.7673</v>
+        <v>1.4688</v>
       </c>
       <c r="J343" t="n">
-        <v>1686</v>
+        <v>1688.3</v>
       </c>
       <c r="K343" t="n">
         <v>30</v>
@@ -41675,13 +41675,13 @@
         <v>1</v>
       </c>
       <c r="H344" t="n">
-        <v>1486.994</v>
+        <v>1486.769</v>
       </c>
       <c r="I344" t="n">
-        <v>0.4064</v>
+        <v>0.4187</v>
       </c>
       <c r="J344" t="n">
-        <v>1425.7</v>
+        <v>1426.2</v>
       </c>
       <c r="K344" t="n">
         <v>248</v>
@@ -41795,13 +41795,13 @@
         <v>1</v>
       </c>
       <c r="H345" t="n">
-        <v>1463.954</v>
+        <v>1464.47</v>
       </c>
       <c r="I345" t="n">
-        <v>2.7542</v>
+        <v>2.7711</v>
       </c>
       <c r="J345" t="n">
-        <v>1435.2</v>
+        <v>1435.1</v>
       </c>
       <c r="K345" t="n">
         <v>153</v>
@@ -41915,13 +41915,13 @@
         <v>1</v>
       </c>
       <c r="H346" t="n">
-        <v>1524.74</v>
+        <v>1523.832</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.385</v>
+        <v>-0.3879</v>
       </c>
       <c r="J346" t="n">
-        <v>1569.8</v>
+        <v>1568.9</v>
       </c>
       <c r="K346" t="n">
         <v>101</v>
@@ -42035,13 +42035,13 @@
         <v>1</v>
       </c>
       <c r="H347" t="n">
-        <v>1594.869</v>
+        <v>1595.933</v>
       </c>
       <c r="I347" t="n">
-        <v>-2.5518</v>
+        <v>-2.7714</v>
       </c>
       <c r="J347" t="n">
-        <v>1630.7</v>
+        <v>1631</v>
       </c>
       <c r="K347" t="n">
         <v>93</v>
@@ -42155,13 +42155,13 @@
         <v>1</v>
       </c>
       <c r="H348" t="n">
-        <v>1725.297</v>
+        <v>1722.645</v>
       </c>
       <c r="I348" t="n">
-        <v>1.115</v>
+        <v>1.2386</v>
       </c>
       <c r="J348" t="n">
-        <v>1460.6</v>
+        <v>1460.4</v>
       </c>
       <c r="K348" t="n">
         <v>81</v>
@@ -42275,13 +42275,13 @@
         <v>1</v>
       </c>
       <c r="H349" t="n">
-        <v>1407.925</v>
+        <v>1407.461</v>
       </c>
       <c r="I349" t="n">
-        <v>-3.5999</v>
+        <v>-3.5843</v>
       </c>
       <c r="J349" t="n">
-        <v>1430.1</v>
+        <v>1429.8</v>
       </c>
       <c r="K349" t="n">
         <v>208</v>
@@ -42395,13 +42395,13 @@
         <v>1</v>
       </c>
       <c r="H350" t="n">
-        <v>1592.12</v>
+        <v>1592.336</v>
       </c>
       <c r="I350" t="n">
-        <v>1.4758</v>
+        <v>1.4889</v>
       </c>
       <c r="J350" t="n">
-        <v>1460.6</v>
+        <v>1460.9</v>
       </c>
       <c r="K350" t="n">
         <v>119</v>
@@ -42515,13 +42515,13 @@
         <v>1</v>
       </c>
       <c r="H351" t="n">
-        <v>1366.78</v>
+        <v>1365.399</v>
       </c>
       <c r="I351" t="n">
-        <v>-3.5941</v>
+        <v>-3.5673</v>
       </c>
       <c r="J351" t="n">
-        <v>1412.8</v>
+        <v>1410.7</v>
       </c>
       <c r="K351" t="n">
         <v>341</v>
@@ -42635,13 +42635,13 @@
         <v>1</v>
       </c>
       <c r="H352" t="n">
-        <v>1512.449</v>
+        <v>1513.315</v>
       </c>
       <c r="I352" t="n">
-        <v>3.91</v>
+        <v>3.9468</v>
       </c>
       <c r="J352" t="n">
-        <v>1452.7</v>
+        <v>1455.1</v>
       </c>
       <c r="K352" t="n">
         <v>172</v>
@@ -42755,13 +42755,13 @@
         <v>1</v>
       </c>
       <c r="H353" t="n">
-        <v>1286.257</v>
+        <v>1286.086</v>
       </c>
       <c r="I353" t="n">
-        <v>0.9611</v>
+        <v>0.9585</v>
       </c>
       <c r="J353" t="n">
-        <v>1431.3</v>
+        <v>1430.1</v>
       </c>
       <c r="K353" t="n">
         <v>275</v>
@@ -42875,13 +42875,13 @@
         <v>1</v>
       </c>
       <c r="H354" t="n">
-        <v>1381.428</v>
+        <v>1381.57</v>
       </c>
       <c r="I354" t="n">
-        <v>2.3445</v>
+        <v>2.3501</v>
       </c>
       <c r="J354" t="n">
-        <v>1485.2</v>
+        <v>1486.3</v>
       </c>
       <c r="K354" t="n">
         <v>188</v>
@@ -42995,13 +42995,13 @@
         <v>1</v>
       </c>
       <c r="H355" t="n">
-        <v>1383.725</v>
+        <v>1383.62</v>
       </c>
       <c r="I355" t="n">
-        <v>-1.0128</v>
+        <v>-0.9969</v>
       </c>
       <c r="J355" t="n">
-        <v>1470.2</v>
+        <v>1470.7</v>
       </c>
       <c r="K355" t="n">
         <v>211</v>
@@ -43115,13 +43115,13 @@
         <v>1</v>
       </c>
       <c r="H356" t="n">
-        <v>1606.401</v>
+        <v>1603.201</v>
       </c>
       <c r="I356" t="n">
-        <v>-9.214</v>
+        <v>-8.761799999999999</v>
       </c>
       <c r="J356" t="n">
-        <v>1449.9</v>
+        <v>1449.3</v>
       </c>
       <c r="K356" t="n">
         <v>113</v>
@@ -43235,10 +43235,10 @@
         <v>1</v>
       </c>
       <c r="H357" t="n">
-        <v>1570.314</v>
+        <v>1570.246</v>
       </c>
       <c r="I357" t="n">
-        <v>3.1116</v>
+        <v>3.0977</v>
       </c>
       <c r="J357" t="n">
         <v>1396.5</v>
@@ -43355,13 +43355,13 @@
         <v>1</v>
       </c>
       <c r="H358" t="n">
-        <v>1350.836</v>
+        <v>1350.75</v>
       </c>
       <c r="I358" t="n">
-        <v>1.3428</v>
+        <v>1.3326</v>
       </c>
       <c r="J358" t="n">
-        <v>1391.4</v>
+        <v>1391.9</v>
       </c>
       <c r="K358" t="n">
         <v>269</v>
@@ -43475,13 +43475,13 @@
         <v>1</v>
       </c>
       <c r="H359" t="n">
-        <v>1417.451</v>
+        <v>1417.812</v>
       </c>
       <c r="I359" t="n">
-        <v>1.0068</v>
+        <v>1.0097</v>
       </c>
       <c r="J359" t="n">
-        <v>1433.3</v>
+        <v>1434.3</v>
       </c>
       <c r="K359" t="n">
         <v>191</v>
@@ -43595,13 +43595,13 @@
         <v>1</v>
       </c>
       <c r="H360" t="n">
-        <v>1244.905</v>
+        <v>1244.676</v>
       </c>
       <c r="I360" t="n">
-        <v>-2.6101</v>
+        <v>-2.6162</v>
       </c>
       <c r="J360" t="n">
-        <v>1381.2</v>
+        <v>1380.7</v>
       </c>
       <c r="K360" t="n">
         <v>340</v>
@@ -43715,13 +43715,13 @@
         <v>1</v>
       </c>
       <c r="H361" t="n">
-        <v>1287.953</v>
+        <v>1288.644</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.9737</v>
+        <v>-0.9871</v>
       </c>
       <c r="J361" t="n">
-        <v>1382.6</v>
+        <v>1382.3</v>
       </c>
       <c r="K361" t="n">
         <v>337</v>
@@ -43835,13 +43835,13 @@
         <v>1</v>
       </c>
       <c r="H362" t="n">
-        <v>1285.138</v>
+        <v>1285.452</v>
       </c>
       <c r="I362" t="n">
-        <v>-0.6191</v>
+        <v>-0.6216</v>
       </c>
       <c r="J362" t="n">
-        <v>1428.1</v>
+        <v>1429.3</v>
       </c>
       <c r="K362" t="n">
         <v>287</v>
@@ -43955,13 +43955,13 @@
         <v>1</v>
       </c>
       <c r="H363" t="n">
-        <v>1332.266</v>
+        <v>1332.831</v>
       </c>
       <c r="I363" t="n">
-        <v>1.0779</v>
+        <v>1.0626</v>
       </c>
       <c r="J363" t="n">
-        <v>1377.7</v>
+        <v>1378.3</v>
       </c>
       <c r="K363" t="n">
         <v>289</v>
@@ -44075,13 +44075,13 @@
         <v>1</v>
       </c>
       <c r="H364" t="n">
-        <v>1376.296</v>
+        <v>1376.709</v>
       </c>
       <c r="I364" t="n">
-        <v>-1.16</v>
+        <v>-1.1589</v>
       </c>
       <c r="J364" t="n">
-        <v>1378.9</v>
+        <v>1379.4</v>
       </c>
       <c r="K364" t="n">
         <v>286</v>
@@ -44195,13 +44195,13 @@
         <v>1</v>
       </c>
       <c r="H365" t="n">
-        <v>1343.287</v>
+        <v>1342.401</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.6063</v>
+        <v>-0.6218</v>
       </c>
       <c r="J365" t="n">
-        <v>1405.4</v>
+        <v>1404.8</v>
       </c>
       <c r="K365" t="n">
         <v>307</v>
@@ -44315,13 +44315,13 @@
         <v>1</v>
       </c>
       <c r="H366" t="n">
-        <v>1378.844</v>
+        <v>1379.419</v>
       </c>
       <c r="I366" t="n">
-        <v>-3.1475</v>
+        <v>-3.1647</v>
       </c>
       <c r="J366" t="n">
-        <v>1398.2</v>
+        <v>1399.2</v>
       </c>
       <c r="K366" t="n">
         <v>329</v>

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,192 +429,192 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Conf</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>N_games</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>has_box_score</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>POM</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MOR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>WLK</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>BIH</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>NET</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>avg_Score</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>avg_OppScore</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>avg_Won</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>avg_FGM</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>avg_FGA</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>avg_FGM3</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>avg_FGA3</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>avg_FTM</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>avg_FTA</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>avg_OR</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>avg_DR</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>avg_Ast</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>avg_Stl</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>avg_Blk</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>avg_PF</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>last10_Margin</t>
         </is>
@@ -866,22 +878,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1693.697</v>
+        <v>1694.43</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6325</v>
+        <v>1.739</v>
       </c>
       <c r="J4" t="n">
-        <v>1484</v>
+        <v>1476.4</v>
       </c>
       <c r="K4" t="n">
         <v>61</v>
@@ -902,70 +914,70 @@
         <v>57</v>
       </c>
       <c r="Q4" t="n">
-        <v>122.155</v>
+        <v>123.015</v>
       </c>
       <c r="R4" t="n">
-        <v>104.997</v>
+        <v>104.033</v>
       </c>
       <c r="S4" t="n">
-        <v>17.158</v>
+        <v>18.982</v>
       </c>
       <c r="T4" t="n">
-        <v>0.29065</v>
+        <v>0.28459</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1511</v>
+        <v>0.15197</v>
       </c>
       <c r="V4" t="n">
-        <v>87.69</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>75.39</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8236</v>
+        <v>0.8295</v>
       </c>
       <c r="Y4" t="n">
-        <v>31.34</v>
+        <v>31.477</v>
       </c>
       <c r="Z4" t="n">
-        <v>62.824</v>
+        <v>62.557</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.859</v>
+        <v>11.182</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.45</v>
+        <v>28.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.148</v>
+        <v>13.966</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.337</v>
+        <v>18.136</v>
       </c>
       <c r="AE4" t="n">
-        <v>9.944000000000001</v>
+        <v>9.760999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>24.989</v>
+        <v>25.375</v>
       </c>
       <c r="AG4" t="n">
-        <v>18.34</v>
+        <v>18.432</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.414</v>
+        <v>7.432</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.788</v>
+        <v>2.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16.339</v>
+        <v>16.284</v>
       </c>
       <c r="AK4" t="n">
-        <v>15.8</v>
+        <v>20.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>10.5</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="5">
@@ -2786,22 +2798,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1470.557</v>
+        <v>1472.002</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7809</v>
+        <v>3.6601</v>
       </c>
       <c r="J20" t="n">
-        <v>1407.6</v>
+        <v>1404.2</v>
       </c>
       <c r="K20" t="n">
         <v>165</v>
@@ -2822,70 +2834,70 @@
         <v>156</v>
       </c>
       <c r="Q20" t="n">
-        <v>112.964</v>
+        <v>112.692</v>
       </c>
       <c r="R20" t="n">
-        <v>105.909</v>
+        <v>105.061</v>
       </c>
       <c r="S20" t="n">
-        <v>7.055</v>
+        <v>7.631</v>
       </c>
       <c r="T20" t="n">
-        <v>0.28025</v>
+        <v>0.28061</v>
       </c>
       <c r="U20" t="n">
-        <v>0.14955</v>
+        <v>0.15063</v>
       </c>
       <c r="V20" t="n">
-        <v>79.45</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>74.95999999999999</v>
+        <v>73.89</v>
       </c>
       <c r="X20" t="n">
-        <v>0.696</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="Y20" t="n">
-        <v>27.469</v>
+        <v>27.253</v>
       </c>
       <c r="Z20" t="n">
-        <v>59.319</v>
+        <v>59.03</v>
       </c>
       <c r="AA20" t="n">
-        <v>8.121</v>
+        <v>7.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>22.619</v>
+        <v>22.475</v>
       </c>
       <c r="AC20" t="n">
-        <v>16.396</v>
+        <v>16.318</v>
       </c>
       <c r="AD20" t="n">
-        <v>22.234</v>
+        <v>22.051</v>
       </c>
       <c r="AE20" t="n">
-        <v>9.058999999999999</v>
+        <v>9.125999999999999</v>
       </c>
       <c r="AF20" t="n">
-        <v>22.967</v>
+        <v>23.091</v>
       </c>
       <c r="AG20" t="n">
-        <v>15.542</v>
+        <v>15.278</v>
       </c>
       <c r="AH20" t="n">
-        <v>8.648</v>
+        <v>8.590999999999999</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.352</v>
+        <v>2.273</v>
       </c>
       <c r="AJ20" t="n">
-        <v>17.513</v>
+        <v>17.025</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.2</v>
+        <v>-1</v>
       </c>
       <c r="AL20" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="21">
@@ -2906,22 +2918,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1325.117</v>
+        <v>1327.484</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4941</v>
+        <v>-2.2908</v>
       </c>
       <c r="J21" t="n">
-        <v>1443.3</v>
+        <v>1439.8</v>
       </c>
       <c r="K21" t="n">
         <v>302</v>
@@ -2942,70 +2954,70 @@
         <v>307</v>
       </c>
       <c r="Q21" t="n">
-        <v>98.66200000000001</v>
+        <v>99.752</v>
       </c>
       <c r="R21" t="n">
-        <v>107.824</v>
+        <v>107.593</v>
       </c>
       <c r="S21" t="n">
-        <v>-9.162000000000001</v>
+        <v>-7.841</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2837</v>
+        <v>0.28282</v>
       </c>
       <c r="U21" t="n">
-        <v>0.14927</v>
+        <v>0.15089</v>
       </c>
       <c r="V21" t="n">
-        <v>65.5</v>
+        <v>66.28</v>
       </c>
       <c r="W21" t="n">
-        <v>71.45999999999999</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3298</v>
+        <v>0.3523</v>
       </c>
       <c r="Y21" t="n">
-        <v>22.933</v>
+        <v>23.273</v>
       </c>
       <c r="Z21" t="n">
-        <v>56.815</v>
+        <v>56.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.905</v>
+        <v>7.023</v>
       </c>
       <c r="AB21" t="n">
-        <v>22.171</v>
+        <v>22.318</v>
       </c>
       <c r="AC21" t="n">
-        <v>12.728</v>
+        <v>12.716</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.907</v>
+        <v>17.943</v>
       </c>
       <c r="AE21" t="n">
-        <v>8.353</v>
+        <v>8.295</v>
       </c>
       <c r="AF21" t="n">
-        <v>20.439</v>
+        <v>20.386</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.048</v>
+        <v>12.534</v>
       </c>
       <c r="AH21" t="n">
-        <v>7.483</v>
+        <v>7.443</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.541</v>
+        <v>2.693</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16.002</v>
+        <v>15.966</v>
       </c>
       <c r="AK21" t="n">
-        <v>3</v>
+        <v>8.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>-4</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="22">
@@ -3146,22 +3158,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1752.259</v>
+        <v>1736.405</v>
       </c>
       <c r="I23" t="n">
-        <v>5.5868</v>
+        <v>5.3442</v>
       </c>
       <c r="J23" t="n">
-        <v>1486</v>
+        <v>1485.7</v>
       </c>
       <c r="K23" t="n">
         <v>55</v>
@@ -3182,70 +3194,70 @@
         <v>55</v>
       </c>
       <c r="Q23" t="n">
-        <v>118.837</v>
+        <v>118.567</v>
       </c>
       <c r="R23" t="n">
-        <v>104.395</v>
+        <v>105.718</v>
       </c>
       <c r="S23" t="n">
-        <v>14.442</v>
+        <v>12.849</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23891</v>
+        <v>0.23281</v>
       </c>
       <c r="U23" t="n">
-        <v>0.17561</v>
+        <v>0.17334</v>
       </c>
       <c r="V23" t="n">
-        <v>83.53</v>
+        <v>83.44</v>
       </c>
       <c r="W23" t="n">
-        <v>73.34999999999999</v>
+        <v>74.38</v>
       </c>
       <c r="X23" t="n">
-        <v>0.8246</v>
+        <v>0.7986</v>
       </c>
       <c r="Y23" t="n">
-        <v>29.936</v>
+        <v>30.01</v>
       </c>
       <c r="Z23" t="n">
-        <v>57.529</v>
+        <v>57.335</v>
       </c>
       <c r="AA23" t="n">
-        <v>10.736</v>
+        <v>10.744</v>
       </c>
       <c r="AB23" t="n">
-        <v>26.066</v>
+        <v>26.064</v>
       </c>
       <c r="AC23" t="n">
-        <v>12.925</v>
+        <v>13.551</v>
       </c>
       <c r="AD23" t="n">
-        <v>18.87</v>
+        <v>19.404</v>
       </c>
       <c r="AE23" t="n">
-        <v>7.757</v>
+        <v>7.578</v>
       </c>
       <c r="AF23" t="n">
-        <v>24.663</v>
+        <v>24.911</v>
       </c>
       <c r="AG23" t="n">
-        <v>18.286</v>
+        <v>18.413</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.121</v>
+        <v>6.128</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.462</v>
+        <v>3.447</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17.768</v>
+        <v>17.619</v>
       </c>
       <c r="AK23" t="n">
-        <v>13.2</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -3866,22 +3878,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1418.633</v>
+        <v>1421.619</v>
       </c>
       <c r="I29" t="n">
-        <v>1.305</v>
+        <v>1.158</v>
       </c>
       <c r="J29" t="n">
-        <v>1467.4</v>
+        <v>1462.9</v>
       </c>
       <c r="K29" t="n">
         <v>149</v>
@@ -3902,70 +3914,70 @@
         <v>157</v>
       </c>
       <c r="Q29" t="n">
-        <v>108.745</v>
+        <v>108.499</v>
       </c>
       <c r="R29" t="n">
-        <v>101.71</v>
+        <v>101.553</v>
       </c>
       <c r="S29" t="n">
-        <v>7.035</v>
+        <v>6.946</v>
       </c>
       <c r="T29" t="n">
-        <v>0.26867</v>
+        <v>0.2733</v>
       </c>
       <c r="U29" t="n">
-        <v>0.16037</v>
+        <v>0.15836</v>
       </c>
       <c r="V29" t="n">
-        <v>76.83</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>72.56</v>
+        <v>72.53</v>
       </c>
       <c r="X29" t="n">
-        <v>0.525</v>
+        <v>0.5414</v>
       </c>
       <c r="Y29" t="n">
-        <v>26.963</v>
+        <v>26.917</v>
       </c>
       <c r="Z29" t="n">
-        <v>58.631</v>
+        <v>59.016</v>
       </c>
       <c r="AA29" t="n">
-        <v>7.027</v>
+        <v>7</v>
       </c>
       <c r="AB29" t="n">
-        <v>20.333</v>
+        <v>20.235</v>
       </c>
       <c r="AC29" t="n">
-        <v>15.881</v>
+        <v>15.954</v>
       </c>
       <c r="AD29" t="n">
-        <v>21.731</v>
+        <v>21.944</v>
       </c>
       <c r="AE29" t="n">
-        <v>8.561999999999999</v>
+        <v>8.815</v>
       </c>
       <c r="AF29" t="n">
-        <v>23.579</v>
+        <v>23.589</v>
       </c>
       <c r="AG29" t="n">
-        <v>13.16</v>
+        <v>12.998</v>
       </c>
       <c r="AH29" t="n">
-        <v>8.315</v>
+        <v>8.222</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.608</v>
+        <v>3.6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18.225</v>
+        <v>18.139</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AL29" t="n">
-        <v>-1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="30">
@@ -3986,22 +3998,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1623.586</v>
+        <v>1627.68</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3833</v>
+        <v>1.2831</v>
       </c>
       <c r="J30" t="n">
-        <v>1526.1</v>
+        <v>1522.2</v>
       </c>
       <c r="K30" t="n">
         <v>123</v>
@@ -4022,70 +4034,70 @@
         <v>112</v>
       </c>
       <c r="Q30" t="n">
-        <v>111.033</v>
+        <v>110.417</v>
       </c>
       <c r="R30" t="n">
-        <v>106.127</v>
+        <v>105.542</v>
       </c>
       <c r="S30" t="n">
-        <v>4.907</v>
+        <v>4.875</v>
       </c>
       <c r="T30" t="n">
-        <v>0.27325</v>
+        <v>0.27316</v>
       </c>
       <c r="U30" t="n">
-        <v>0.13305</v>
+        <v>0.13273</v>
       </c>
       <c r="V30" t="n">
-        <v>77.31</v>
+        <v>77.75</v>
       </c>
       <c r="W30" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="X30" t="n">
-        <v>0.6388</v>
+        <v>0.65</v>
       </c>
       <c r="Y30" t="n">
-        <v>26.292</v>
+        <v>26.436</v>
       </c>
       <c r="Z30" t="n">
-        <v>59.783</v>
+        <v>60.405</v>
       </c>
       <c r="AA30" t="n">
-        <v>8.81</v>
+        <v>8.645</v>
       </c>
       <c r="AB30" t="n">
-        <v>24.36</v>
+        <v>24.295</v>
       </c>
       <c r="AC30" t="n">
-        <v>15.918</v>
+        <v>16.232</v>
       </c>
       <c r="AD30" t="n">
-        <v>21.616</v>
+        <v>21.973</v>
       </c>
       <c r="AE30" t="n">
-        <v>8.818</v>
+        <v>8.855</v>
       </c>
       <c r="AF30" t="n">
-        <v>23.355</v>
+        <v>23.468</v>
       </c>
       <c r="AG30" t="n">
-        <v>13.205</v>
+        <v>13.309</v>
       </c>
       <c r="AH30" t="n">
-        <v>7.478</v>
+        <v>7.705</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.355</v>
+        <v>3.241</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18.851</v>
+        <v>18.932</v>
       </c>
       <c r="AK30" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="31">
@@ -4106,22 +4118,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1356.645</v>
+        <v>1353.036</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.7758</v>
+        <v>-2.7159</v>
       </c>
       <c r="J31" t="n">
-        <v>1452.2</v>
+        <v>1449</v>
       </c>
       <c r="K31" t="n">
         <v>283</v>
@@ -4142,70 +4154,70 @@
         <v>289</v>
       </c>
       <c r="Q31" t="n">
-        <v>98.83199999999999</v>
+        <v>97.68300000000001</v>
       </c>
       <c r="R31" t="n">
-        <v>105.338</v>
+        <v>105.561</v>
       </c>
       <c r="S31" t="n">
-        <v>-6.506</v>
+        <v>-7.878</v>
       </c>
       <c r="T31" t="n">
-        <v>0.28705</v>
+        <v>0.28627</v>
       </c>
       <c r="U31" t="n">
-        <v>0.18051</v>
+        <v>0.18925</v>
       </c>
       <c r="V31" t="n">
-        <v>67.79000000000001</v>
+        <v>67.05</v>
       </c>
       <c r="W31" t="n">
-        <v>72.41</v>
+        <v>72.66</v>
       </c>
       <c r="X31" t="n">
-        <v>0.2841</v>
+        <v>0.2734</v>
       </c>
       <c r="Y31" t="n">
-        <v>25.075</v>
+        <v>24.859</v>
       </c>
       <c r="Z31" t="n">
-        <v>58.061</v>
+        <v>57.57</v>
       </c>
       <c r="AA31" t="n">
-        <v>6.458</v>
+        <v>6.328</v>
       </c>
       <c r="AB31" t="n">
-        <v>21.093</v>
+        <v>20.914</v>
       </c>
       <c r="AC31" t="n">
-        <v>11.177</v>
+        <v>11.008</v>
       </c>
       <c r="AD31" t="n">
-        <v>16.151</v>
+        <v>16.195</v>
       </c>
       <c r="AE31" t="n">
-        <v>8.890000000000001</v>
+        <v>8.968999999999999</v>
       </c>
       <c r="AF31" t="n">
-        <v>22.055</v>
+        <v>22.328</v>
       </c>
       <c r="AG31" t="n">
-        <v>14.872</v>
+        <v>14.852</v>
       </c>
       <c r="AH31" t="n">
-        <v>7.391</v>
+        <v>7.539</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.771</v>
+        <v>3.742</v>
       </c>
       <c r="AJ31" t="n">
-        <v>18.904</v>
+        <v>18.57</v>
       </c>
       <c r="AK31" t="n">
-        <v>-3</v>
+        <v>-6.6</v>
       </c>
       <c r="AL31" t="n">
-        <v>-7.6</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="32">
@@ -4466,22 +4478,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1390.965</v>
+        <v>1384.851</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2206</v>
+        <v>-0.3277</v>
       </c>
       <c r="J34" t="n">
-        <v>1458.9</v>
+        <v>1459.6</v>
       </c>
       <c r="K34" t="n">
         <v>194</v>
@@ -4502,70 +4514,70 @@
         <v>190</v>
       </c>
       <c r="Q34" t="n">
-        <v>114.441</v>
+        <v>115.04</v>
       </c>
       <c r="R34" t="n">
-        <v>111.829</v>
+        <v>114.085</v>
       </c>
       <c r="S34" t="n">
-        <v>2.612</v>
+        <v>0.954</v>
       </c>
       <c r="T34" t="n">
-        <v>0.27263</v>
+        <v>0.27672</v>
       </c>
       <c r="U34" t="n">
-        <v>0.15683</v>
+        <v>0.15804</v>
       </c>
       <c r="V34" t="n">
-        <v>77.68000000000001</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="W34" t="n">
-        <v>76.28</v>
+        <v>77.38</v>
       </c>
       <c r="X34" t="n">
-        <v>0.5414</v>
+        <v>0.5114</v>
       </c>
       <c r="Y34" t="n">
-        <v>25.716</v>
+        <v>25.989</v>
       </c>
       <c r="Z34" t="n">
-        <v>55.339</v>
+        <v>55.466</v>
       </c>
       <c r="AA34" t="n">
-        <v>9.529</v>
+        <v>9.557</v>
       </c>
       <c r="AB34" t="n">
-        <v>25.164</v>
+        <v>25.125</v>
       </c>
       <c r="AC34" t="n">
-        <v>16.718</v>
+        <v>16.227</v>
       </c>
       <c r="AD34" t="n">
-        <v>22.459</v>
+        <v>21.807</v>
       </c>
       <c r="AE34" t="n">
-        <v>7.963</v>
+        <v>8.090999999999999</v>
       </c>
       <c r="AF34" t="n">
-        <v>20.921</v>
+        <v>20.818</v>
       </c>
       <c r="AG34" t="n">
-        <v>14.222</v>
+        <v>14.102</v>
       </c>
       <c r="AH34" t="n">
-        <v>7.633</v>
+        <v>7.557</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.954</v>
+        <v>2.841</v>
       </c>
       <c r="AJ34" t="n">
-        <v>16.34</v>
+        <v>16.023</v>
       </c>
       <c r="AK34" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="AL34" t="n">
-        <v>-1.7</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="35">
@@ -4826,22 +4838,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1340.808</v>
+        <v>1338.44</v>
       </c>
       <c r="I37" t="n">
-        <v>-2.8385</v>
+        <v>-2.6522</v>
       </c>
       <c r="J37" t="n">
-        <v>1476</v>
+        <v>1466.6</v>
       </c>
       <c r="K37" t="n">
         <v>263</v>
@@ -4862,70 +4874,70 @@
         <v>273</v>
       </c>
       <c r="Q37" t="n">
-        <v>105.755</v>
+        <v>105.894</v>
       </c>
       <c r="R37" t="n">
-        <v>114.354</v>
+        <v>115.091</v>
       </c>
       <c r="S37" t="n">
-        <v>-8.599</v>
+        <v>-9.196999999999999</v>
       </c>
       <c r="T37" t="n">
-        <v>0.29909</v>
+        <v>0.30031</v>
       </c>
       <c r="U37" t="n">
-        <v>0.17267</v>
+        <v>0.17263</v>
       </c>
       <c r="V37" t="n">
-        <v>71.65000000000001</v>
+        <v>71.62</v>
       </c>
       <c r="W37" t="n">
-        <v>77.39</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="X37" t="n">
-        <v>0.2822</v>
+        <v>0.2727</v>
       </c>
       <c r="Y37" t="n">
-        <v>26.164</v>
+        <v>26.307</v>
       </c>
       <c r="Z37" t="n">
-        <v>57.189</v>
+        <v>57.125</v>
       </c>
       <c r="AA37" t="n">
-        <v>6.755</v>
+        <v>6.545</v>
       </c>
       <c r="AB37" t="n">
-        <v>19.755</v>
+        <v>19.364</v>
       </c>
       <c r="AC37" t="n">
-        <v>12.571</v>
+        <v>12.466</v>
       </c>
       <c r="AD37" t="n">
-        <v>17.922</v>
+        <v>17.932</v>
       </c>
       <c r="AE37" t="n">
-        <v>8.997999999999999</v>
+        <v>9.034000000000001</v>
       </c>
       <c r="AF37" t="n">
-        <v>20.728</v>
+        <v>20.716</v>
       </c>
       <c r="AG37" t="n">
-        <v>14.448</v>
+        <v>14.409</v>
       </c>
       <c r="AH37" t="n">
-        <v>6.259</v>
+        <v>6.102</v>
       </c>
       <c r="AI37" t="n">
-        <v>4.175</v>
+        <v>4.068</v>
       </c>
       <c r="AJ37" t="n">
-        <v>17.631</v>
+        <v>17.727</v>
       </c>
       <c r="AK37" t="n">
-        <v>-1.8</v>
+        <v>-2.6</v>
       </c>
       <c r="AL37" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38">
@@ -5426,22 +5438,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F42" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1365.026</v>
+        <v>1367.065</v>
       </c>
       <c r="I42" t="n">
-        <v>3.0881</v>
+        <v>3.1055</v>
       </c>
       <c r="J42" t="n">
-        <v>1443.7</v>
+        <v>1437.1</v>
       </c>
       <c r="K42" t="n">
         <v>154</v>
@@ -5462,70 +5474,70 @@
         <v>164</v>
       </c>
       <c r="Q42" t="n">
-        <v>111.576</v>
+        <v>112.579</v>
       </c>
       <c r="R42" t="n">
-        <v>106.537</v>
+        <v>106.886</v>
       </c>
       <c r="S42" t="n">
-        <v>5.039</v>
+        <v>5.693</v>
       </c>
       <c r="T42" t="n">
-        <v>0.27268</v>
+        <v>0.27216</v>
       </c>
       <c r="U42" t="n">
-        <v>0.1498</v>
+        <v>0.15096</v>
       </c>
       <c r="V42" t="n">
-        <v>78.84999999999999</v>
+        <v>79.11</v>
       </c>
       <c r="W42" t="n">
-        <v>75.8</v>
+        <v>75.64</v>
       </c>
       <c r="X42" t="n">
-        <v>0.625</v>
+        <v>0.6372</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.455</v>
+        <v>27.603</v>
       </c>
       <c r="Z42" t="n">
-        <v>60.795</v>
+        <v>60.454</v>
       </c>
       <c r="AA42" t="n">
-        <v>10.318</v>
+        <v>10.493</v>
       </c>
       <c r="AB42" t="n">
-        <v>29.682</v>
+        <v>29.595</v>
       </c>
       <c r="AC42" t="n">
-        <v>13.625</v>
+        <v>13.408</v>
       </c>
       <c r="AD42" t="n">
-        <v>19.148</v>
+        <v>18.849</v>
       </c>
       <c r="AE42" t="n">
-        <v>8.784000000000001</v>
+        <v>8.682</v>
       </c>
       <c r="AF42" t="n">
-        <v>22.989</v>
+        <v>22.793</v>
       </c>
       <c r="AG42" t="n">
-        <v>16</v>
+        <v>16.12</v>
       </c>
       <c r="AH42" t="n">
-        <v>8.455</v>
+        <v>8.385</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.705</v>
+        <v>1.78</v>
       </c>
       <c r="AJ42" t="n">
-        <v>16.523</v>
+        <v>16.549</v>
       </c>
       <c r="AK42" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AL42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -5666,22 +5678,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G44" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1330.459</v>
+        <v>1319.926</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0554</v>
+        <v>0.9741</v>
       </c>
       <c r="J44" t="n">
-        <v>1390</v>
+        <v>1394.8</v>
       </c>
       <c r="K44" t="n">
         <v>244</v>
@@ -5702,70 +5714,70 @@
         <v>241</v>
       </c>
       <c r="Q44" t="n">
-        <v>107.629</v>
+        <v>107.282</v>
       </c>
       <c r="R44" t="n">
-        <v>106.83</v>
+        <v>107.17</v>
       </c>
       <c r="S44" t="n">
-        <v>0.799</v>
+        <v>0.112</v>
       </c>
       <c r="T44" t="n">
-        <v>0.26419</v>
+        <v>0.26128</v>
       </c>
       <c r="U44" t="n">
-        <v>0.18319</v>
+        <v>0.1772</v>
       </c>
       <c r="V44" t="n">
-        <v>81.09</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="W44" t="n">
-        <v>80.7</v>
+        <v>81.03</v>
       </c>
       <c r="X44" t="n">
-        <v>0.437</v>
+        <v>0.4082</v>
       </c>
       <c r="Y44" t="n">
-        <v>28.678</v>
+        <v>28.612</v>
       </c>
       <c r="Z44" t="n">
-        <v>62.948</v>
+        <v>63.327</v>
       </c>
       <c r="AA44" t="n">
-        <v>11.291</v>
+        <v>11.143</v>
       </c>
       <c r="AB44" t="n">
-        <v>31.324</v>
+        <v>31.299</v>
       </c>
       <c r="AC44" t="n">
-        <v>12.446</v>
+        <v>12.565</v>
       </c>
       <c r="AD44" t="n">
-        <v>19.215</v>
+        <v>19.374</v>
       </c>
       <c r="AE44" t="n">
-        <v>9.82</v>
+        <v>9.755000000000001</v>
       </c>
       <c r="AF44" t="n">
-        <v>27.106</v>
+        <v>27.435</v>
       </c>
       <c r="AG44" t="n">
-        <v>15.848</v>
+        <v>15.701</v>
       </c>
       <c r="AH44" t="n">
-        <v>4.83</v>
+        <v>4.864</v>
       </c>
       <c r="AI44" t="n">
-        <v>4.85</v>
+        <v>4.898</v>
       </c>
       <c r="AJ44" t="n">
-        <v>22.25</v>
+        <v>22.218</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="AL44" t="n">
-        <v>-1.8</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="45">
@@ -5906,22 +5918,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G46" t="b">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1392.053</v>
+        <v>1388.296</v>
       </c>
       <c r="I46" t="n">
-        <v>-4.0162</v>
+        <v>-3.8474</v>
       </c>
       <c r="J46" t="n">
-        <v>1429</v>
+        <v>1422.3</v>
       </c>
       <c r="K46" t="n">
         <v>298</v>
@@ -5942,70 +5954,70 @@
         <v>286</v>
       </c>
       <c r="Q46" t="n">
-        <v>109.829</v>
+        <v>110.697</v>
       </c>
       <c r="R46" t="n">
-        <v>115.429</v>
+        <v>116.423</v>
       </c>
       <c r="S46" t="n">
-        <v>-5.6</v>
+        <v>-5.726</v>
       </c>
       <c r="T46" t="n">
-        <v>0.20552</v>
+        <v>0.20787</v>
       </c>
       <c r="U46" t="n">
-        <v>0.14115</v>
+        <v>0.14024</v>
       </c>
       <c r="V46" t="n">
-        <v>73.87</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="W46" t="n">
-        <v>77.73</v>
+        <v>78.16</v>
       </c>
       <c r="X46" t="n">
-        <v>0.3636</v>
+        <v>0.3416</v>
       </c>
       <c r="Y46" t="n">
-        <v>25.551</v>
+        <v>25.748</v>
       </c>
       <c r="Z46" t="n">
-        <v>56.475</v>
+        <v>56.472</v>
       </c>
       <c r="AA46" t="n">
-        <v>9.702</v>
+        <v>9.91</v>
       </c>
       <c r="AB46" t="n">
-        <v>27.924</v>
+        <v>28.028</v>
       </c>
       <c r="AC46" t="n">
-        <v>13.071</v>
+        <v>12.963</v>
       </c>
       <c r="AD46" t="n">
-        <v>16.909</v>
+        <v>16.826</v>
       </c>
       <c r="AE46" t="n">
-        <v>6.076</v>
+        <v>6.121</v>
       </c>
       <c r="AF46" t="n">
-        <v>23.207</v>
+        <v>23.084</v>
       </c>
       <c r="AG46" t="n">
-        <v>14.167</v>
+        <v>14.345</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.949</v>
+        <v>4.913</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.475</v>
+        <v>2.565</v>
       </c>
       <c r="AJ46" t="n">
-        <v>19.909</v>
+        <v>19.584</v>
       </c>
       <c r="AK46" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AL46" t="n">
-        <v>-2.4</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="47">
@@ -6266,22 +6278,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1231.812</v>
+        <v>1235.569</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1472</v>
+        <v>-0.0387</v>
       </c>
       <c r="J49" t="n">
-        <v>1417.3</v>
+        <v>1415.5</v>
       </c>
       <c r="K49" t="n">
         <v>351</v>
@@ -6302,70 +6314,70 @@
         <v>350</v>
       </c>
       <c r="Q49" t="n">
-        <v>100.858</v>
+        <v>102.254</v>
       </c>
       <c r="R49" t="n">
-        <v>118.134</v>
+        <v>118.782</v>
       </c>
       <c r="S49" t="n">
-        <v>-17.276</v>
+        <v>-16.528</v>
       </c>
       <c r="T49" t="n">
-        <v>0.29617</v>
+        <v>0.2933</v>
       </c>
       <c r="U49" t="n">
-        <v>0.15733</v>
+        <v>0.15537</v>
       </c>
       <c r="V49" t="n">
-        <v>67.58</v>
+        <v>68.22</v>
       </c>
       <c r="W49" t="n">
-        <v>78.65000000000001</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="X49" t="n">
-        <v>0.2576</v>
+        <v>0.2826</v>
       </c>
       <c r="Y49" t="n">
-        <v>23.646</v>
+        <v>23.981</v>
       </c>
       <c r="Z49" t="n">
-        <v>57.303</v>
+        <v>57.36</v>
       </c>
       <c r="AA49" t="n">
-        <v>8.586</v>
+        <v>8.677</v>
       </c>
       <c r="AB49" t="n">
-        <v>27.343</v>
+        <v>27.255</v>
       </c>
       <c r="AC49" t="n">
-        <v>11.702</v>
+        <v>11.45</v>
       </c>
       <c r="AD49" t="n">
-        <v>17.394</v>
+        <v>16.969</v>
       </c>
       <c r="AE49" t="n">
-        <v>8.788</v>
+        <v>8.708</v>
       </c>
       <c r="AF49" t="n">
-        <v>20.46</v>
+        <v>20.575</v>
       </c>
       <c r="AG49" t="n">
-        <v>11.854</v>
+        <v>12.09</v>
       </c>
       <c r="AH49" t="n">
-        <v>5.222</v>
+        <v>5.161</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.47</v>
+        <v>2.444</v>
       </c>
       <c r="AJ49" t="n">
-        <v>16.783</v>
+        <v>16.655</v>
       </c>
       <c r="AK49" t="n">
-        <v>-11.6</v>
+        <v>-7.8</v>
       </c>
       <c r="AL49" t="n">
-        <v>-7.4</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="50">
@@ -7226,22 +7238,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>1459.013</v>
+        <v>1455.135</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3016</v>
+        <v>-0.5597</v>
       </c>
       <c r="J57" t="n">
-        <v>1464.7</v>
+        <v>1462.9</v>
       </c>
       <c r="K57" t="n">
         <v>189</v>
@@ -7262,70 +7274,70 @@
         <v>178</v>
       </c>
       <c r="Q57" t="n">
-        <v>108.773</v>
+        <v>108.916</v>
       </c>
       <c r="R57" t="n">
-        <v>106.304</v>
+        <v>107.165</v>
       </c>
       <c r="S57" t="n">
-        <v>2.469</v>
+        <v>1.75</v>
       </c>
       <c r="T57" t="n">
-        <v>0.30255</v>
+        <v>0.30564</v>
       </c>
       <c r="U57" t="n">
-        <v>0.18527</v>
+        <v>0.18114</v>
       </c>
       <c r="V57" t="n">
-        <v>74.73999999999999</v>
+        <v>74.87</v>
       </c>
       <c r="W57" t="n">
-        <v>73.03</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="X57" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5305</v>
       </c>
       <c r="Y57" t="n">
-        <v>27.375</v>
+        <v>27.613</v>
       </c>
       <c r="Z57" t="n">
-        <v>58.59</v>
+        <v>59.147</v>
       </c>
       <c r="AA57" t="n">
-        <v>8.013999999999999</v>
+        <v>7.918</v>
       </c>
       <c r="AB57" t="n">
-        <v>22.22</v>
+        <v>22.122</v>
       </c>
       <c r="AC57" t="n">
-        <v>11.975</v>
+        <v>11.722</v>
       </c>
       <c r="AD57" t="n">
-        <v>16.949</v>
+        <v>16.76</v>
       </c>
       <c r="AE57" t="n">
-        <v>10.088</v>
+        <v>10.248</v>
       </c>
       <c r="AF57" t="n">
-        <v>23.729</v>
+        <v>23.691</v>
       </c>
       <c r="AG57" t="n">
-        <v>14.917</v>
+        <v>14.918</v>
       </c>
       <c r="AH57" t="n">
-        <v>5.711</v>
+        <v>5.764</v>
       </c>
       <c r="AI57" t="n">
-        <v>3.007</v>
+        <v>2.933</v>
       </c>
       <c r="AJ57" t="n">
-        <v>16.78</v>
+        <v>16.72</v>
       </c>
       <c r="AK57" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL57" t="n">
-        <v>-2.3</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="58">
@@ -8546,22 +8558,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F68" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1675.338</v>
+        <v>1663.379</v>
       </c>
       <c r="I68" t="n">
-        <v>-2.825</v>
+        <v>-2.5466</v>
       </c>
       <c r="J68" t="n">
-        <v>1553.3</v>
+        <v>1562.3</v>
       </c>
       <c r="K68" t="n">
         <v>75</v>
@@ -8582,70 +8594,70 @@
         <v>71</v>
       </c>
       <c r="Q68" t="n">
-        <v>110.379</v>
+        <v>109.989</v>
       </c>
       <c r="R68" t="n">
-        <v>101.852</v>
+        <v>102.288</v>
       </c>
       <c r="S68" t="n">
-        <v>8.526999999999999</v>
+        <v>7.701</v>
       </c>
       <c r="T68" t="n">
-        <v>0.25104</v>
+        <v>0.25309</v>
       </c>
       <c r="U68" t="n">
-        <v>0.17108</v>
+        <v>0.16863</v>
       </c>
       <c r="V68" t="n">
-        <v>75.38</v>
+        <v>74.92</v>
       </c>
       <c r="W68" t="n">
-        <v>70.05</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="X68" t="n">
-        <v>0.7044</v>
+        <v>0.6682</v>
       </c>
       <c r="Y68" t="n">
-        <v>24.218</v>
+        <v>24.3</v>
       </c>
       <c r="Z68" t="n">
-        <v>53.411</v>
+        <v>53.632</v>
       </c>
       <c r="AA68" t="n">
-        <v>7.639</v>
+        <v>7.468</v>
       </c>
       <c r="AB68" t="n">
-        <v>22.149</v>
+        <v>22.159</v>
       </c>
       <c r="AC68" t="n">
-        <v>19.302</v>
+        <v>18.85</v>
       </c>
       <c r="AD68" t="n">
-        <v>25.521</v>
+        <v>25.15</v>
       </c>
       <c r="AE68" t="n">
-        <v>7.773</v>
+        <v>7.855</v>
       </c>
       <c r="AF68" t="n">
-        <v>22.713</v>
+        <v>22.695</v>
       </c>
       <c r="AG68" t="n">
-        <v>14.46</v>
+        <v>14.309</v>
       </c>
       <c r="AH68" t="n">
-        <v>8.616</v>
+        <v>8.486000000000001</v>
       </c>
       <c r="AI68" t="n">
-        <v>4.102</v>
+        <v>4.082</v>
       </c>
       <c r="AJ68" t="n">
-        <v>16.66</v>
+        <v>16.532</v>
       </c>
       <c r="AK68" t="n">
-        <v>9.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AL68" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="69">
@@ -8906,22 +8918,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>1384.316</v>
+        <v>1381.499</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8096</v>
+        <v>0.7654</v>
       </c>
       <c r="J71" t="n">
-        <v>1451</v>
+        <v>1449.1</v>
       </c>
       <c r="K71" t="n">
         <v>224</v>
@@ -8942,70 +8954,70 @@
         <v>234</v>
       </c>
       <c r="Q71" t="n">
-        <v>116.675</v>
+        <v>116.071</v>
       </c>
       <c r="R71" t="n">
-        <v>121.173</v>
+        <v>121.158</v>
       </c>
       <c r="S71" t="n">
-        <v>-4.497</v>
+        <v>-5.087</v>
       </c>
       <c r="T71" t="n">
-        <v>0.2987</v>
+        <v>0.29567</v>
       </c>
       <c r="U71" t="n">
-        <v>0.13262</v>
+        <v>0.13675</v>
       </c>
       <c r="V71" t="n">
-        <v>80.78</v>
+        <v>80.16</v>
       </c>
       <c r="W71" t="n">
-        <v>84.29000000000001</v>
+        <v>84.02</v>
       </c>
       <c r="X71" t="n">
-        <v>0.4233</v>
+        <v>0.4091</v>
       </c>
       <c r="Y71" t="n">
-        <v>28.247</v>
+        <v>27.875</v>
       </c>
       <c r="Z71" t="n">
-        <v>60.672</v>
+        <v>59.977</v>
       </c>
       <c r="AA71" t="n">
-        <v>8.635</v>
+        <v>8.523</v>
       </c>
       <c r="AB71" t="n">
-        <v>23.342</v>
+        <v>23.216</v>
       </c>
       <c r="AC71" t="n">
-        <v>15.647</v>
+        <v>15.886</v>
       </c>
       <c r="AD71" t="n">
-        <v>20.155</v>
+        <v>20.648</v>
       </c>
       <c r="AE71" t="n">
-        <v>9.307</v>
+        <v>9.273</v>
       </c>
       <c r="AF71" t="n">
-        <v>21.914</v>
+        <v>22.136</v>
       </c>
       <c r="AG71" t="n">
-        <v>11.462</v>
+        <v>11.193</v>
       </c>
       <c r="AH71" t="n">
-        <v>4.506</v>
+        <v>4.432</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.882</v>
+        <v>1.943</v>
       </c>
       <c r="AJ71" t="n">
-        <v>18.51</v>
+        <v>18.455</v>
       </c>
       <c r="AK71" t="n">
-        <v>2.2</v>
+        <v>-4.6</v>
       </c>
       <c r="AL71" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="72">
@@ -9266,22 +9278,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G74" t="b">
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>1499.496</v>
+        <v>1515.349</v>
       </c>
       <c r="I74" t="n">
-        <v>-7.1954</v>
+        <v>-6.9278</v>
       </c>
       <c r="J74" t="n">
-        <v>1520.7</v>
+        <v>1530.8</v>
       </c>
       <c r="K74" t="n">
         <v>213</v>
@@ -9302,70 +9314,70 @@
         <v>206</v>
       </c>
       <c r="Q74" t="n">
-        <v>107.72</v>
+        <v>108.966</v>
       </c>
       <c r="R74" t="n">
-        <v>111.359</v>
+        <v>111.357</v>
       </c>
       <c r="S74" t="n">
-        <v>-3.639</v>
+        <v>-2.39</v>
       </c>
       <c r="T74" t="n">
-        <v>0.27276</v>
+        <v>0.27409</v>
       </c>
       <c r="U74" t="n">
-        <v>0.14494</v>
+        <v>0.14506</v>
       </c>
       <c r="V74" t="n">
-        <v>73.73</v>
+        <v>74.89</v>
       </c>
       <c r="W74" t="n">
-        <v>76.19</v>
+        <v>76.44</v>
       </c>
       <c r="X74" t="n">
-        <v>0.3733</v>
+        <v>0.3931</v>
       </c>
       <c r="Y74" t="n">
-        <v>25.658</v>
+        <v>25.69</v>
       </c>
       <c r="Z74" t="n">
-        <v>59.258</v>
+        <v>59.378</v>
       </c>
       <c r="AA74" t="n">
-        <v>8.849</v>
+        <v>9.113</v>
       </c>
       <c r="AB74" t="n">
-        <v>26.451</v>
+        <v>26.906</v>
       </c>
       <c r="AC74" t="n">
-        <v>13.39</v>
+        <v>13.396</v>
       </c>
       <c r="AD74" t="n">
-        <v>19.126</v>
+        <v>19.099</v>
       </c>
       <c r="AE74" t="n">
-        <v>9.093</v>
+        <v>9.01</v>
       </c>
       <c r="AF74" t="n">
-        <v>23.768</v>
+        <v>23.536</v>
       </c>
       <c r="AG74" t="n">
-        <v>12.891</v>
+        <v>13.362</v>
       </c>
       <c r="AH74" t="n">
-        <v>5.208</v>
+        <v>5.025</v>
       </c>
       <c r="AI74" t="n">
-        <v>2.901</v>
+        <v>2.904</v>
       </c>
       <c r="AJ74" t="n">
-        <v>17.397</v>
+        <v>17.582</v>
       </c>
       <c r="AK74" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="AL74" t="n">
-        <v>-10.2</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="75">
@@ -9986,22 +9998,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G80" t="b">
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>1372.539</v>
+        <v>1373.221</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.3602</v>
+        <v>-1.4523</v>
       </c>
       <c r="J80" t="n">
-        <v>1479.8</v>
+        <v>1478.3</v>
       </c>
       <c r="K80" t="n">
         <v>237</v>
@@ -10022,70 +10034,70 @@
         <v>233</v>
       </c>
       <c r="Q80" t="n">
-        <v>102.517</v>
+        <v>102.413</v>
       </c>
       <c r="R80" t="n">
-        <v>108.236</v>
+        <v>108.381</v>
       </c>
       <c r="S80" t="n">
-        <v>-5.719</v>
+        <v>-5.968</v>
       </c>
       <c r="T80" t="n">
-        <v>0.26285</v>
+        <v>0.2617</v>
       </c>
       <c r="U80" t="n">
-        <v>0.1691</v>
+        <v>0.16799</v>
       </c>
       <c r="V80" t="n">
-        <v>70.16</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="W80" t="n">
-        <v>74.23999999999999</v>
+        <v>74.41</v>
       </c>
       <c r="X80" t="n">
-        <v>0.3054</v>
+        <v>0.2956</v>
       </c>
       <c r="Y80" t="n">
-        <v>25.83</v>
+        <v>25.836</v>
       </c>
       <c r="Z80" t="n">
-        <v>58.104</v>
+        <v>58.179</v>
       </c>
       <c r="AA80" t="n">
-        <v>6.037</v>
+        <v>5.956</v>
       </c>
       <c r="AB80" t="n">
-        <v>18.48</v>
+        <v>18.463</v>
       </c>
       <c r="AC80" t="n">
-        <v>12.457</v>
+        <v>12.522</v>
       </c>
       <c r="AD80" t="n">
-        <v>16.984</v>
+        <v>17.095</v>
       </c>
       <c r="AE80" t="n">
-        <v>8.595000000000001</v>
+        <v>8.590999999999999</v>
       </c>
       <c r="AF80" t="n">
-        <v>23.693</v>
+        <v>23.862</v>
       </c>
       <c r="AG80" t="n">
-        <v>12.493</v>
+        <v>12.302</v>
       </c>
       <c r="AH80" t="n">
-        <v>5.714</v>
+        <v>5.722</v>
       </c>
       <c r="AI80" t="n">
-        <v>4.052</v>
+        <v>4.161</v>
       </c>
       <c r="AJ80" t="n">
-        <v>18.066</v>
+        <v>18.176</v>
       </c>
       <c r="AK80" t="n">
-        <v>-7.2</v>
+        <v>-6</v>
       </c>
       <c r="AL80" t="n">
-        <v>-8.5</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="81">
@@ -10946,22 +10958,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F88" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G88" t="b">
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1438.765</v>
+        <v>1442.92</v>
       </c>
       <c r="I88" t="n">
-        <v>1.6325</v>
+        <v>1.62</v>
       </c>
       <c r="J88" t="n">
-        <v>1401.7</v>
+        <v>1403.8</v>
       </c>
       <c r="K88" t="n">
         <v>270</v>
@@ -10982,70 +10994,70 @@
         <v>245</v>
       </c>
       <c r="Q88" t="n">
-        <v>107.41</v>
+        <v>107.862</v>
       </c>
       <c r="R88" t="n">
-        <v>105.929</v>
+        <v>105.351</v>
       </c>
       <c r="S88" t="n">
-        <v>1.481</v>
+        <v>2.512</v>
       </c>
       <c r="T88" t="n">
-        <v>0.34522</v>
+        <v>0.34697</v>
       </c>
       <c r="U88" t="n">
-        <v>0.15302</v>
+        <v>0.15614</v>
       </c>
       <c r="V88" t="n">
-        <v>73.26000000000001</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="W88" t="n">
-        <v>72.20999999999999</v>
+        <v>71.63</v>
       </c>
       <c r="X88" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.629</v>
       </c>
       <c r="Y88" t="n">
-        <v>26.754</v>
+        <v>26.492</v>
       </c>
       <c r="Z88" t="n">
-        <v>62.13</v>
+        <v>61.801</v>
       </c>
       <c r="AA88" t="n">
-        <v>7.417</v>
+        <v>7.329</v>
       </c>
       <c r="AB88" t="n">
-        <v>22.186</v>
+        <v>21.999</v>
       </c>
       <c r="AC88" t="n">
-        <v>12.339</v>
+        <v>12.215</v>
       </c>
       <c r="AD88" t="n">
-        <v>17.455</v>
+        <v>17.505</v>
       </c>
       <c r="AE88" t="n">
-        <v>12.012</v>
+        <v>12.083</v>
       </c>
       <c r="AF88" t="n">
-        <v>23.043</v>
+        <v>22.989</v>
       </c>
       <c r="AG88" t="n">
-        <v>11.991</v>
+        <v>12.011</v>
       </c>
       <c r="AH88" t="n">
-        <v>6.383</v>
+        <v>6.371</v>
       </c>
       <c r="AI88" t="n">
-        <v>3.446</v>
+        <v>3.641</v>
       </c>
       <c r="AJ88" t="n">
-        <v>15.174</v>
+        <v>15.539</v>
       </c>
       <c r="AK88" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="AL88" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -11186,22 +11198,22 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G90" t="b">
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>1394.944</v>
+        <v>1400.088</v>
       </c>
       <c r="I90" t="n">
-        <v>-3.6949</v>
+        <v>-3.5316</v>
       </c>
       <c r="J90" t="n">
-        <v>1432</v>
+        <v>1434.7</v>
       </c>
       <c r="K90" t="n">
         <v>264</v>
@@ -11222,70 +11234,70 @@
         <v>262</v>
       </c>
       <c r="Q90" t="n">
-        <v>109.155</v>
+        <v>109.639</v>
       </c>
       <c r="R90" t="n">
-        <v>111.674</v>
+        <v>110.68</v>
       </c>
       <c r="S90" t="n">
-        <v>-2.518</v>
+        <v>-1.042</v>
       </c>
       <c r="T90" t="n">
-        <v>0.29586</v>
+        <v>0.28901</v>
       </c>
       <c r="U90" t="n">
-        <v>0.15331</v>
+        <v>0.15455</v>
       </c>
       <c r="V90" t="n">
-        <v>76.95</v>
+        <v>77.03</v>
       </c>
       <c r="W90" t="n">
-        <v>78.75</v>
+        <v>77.88</v>
       </c>
       <c r="X90" t="n">
-        <v>0.4393</v>
+        <v>0.4569</v>
       </c>
       <c r="Y90" t="n">
-        <v>28.021</v>
+        <v>27.625</v>
       </c>
       <c r="Z90" t="n">
-        <v>61.318</v>
+        <v>60.829</v>
       </c>
       <c r="AA90" t="n">
-        <v>7.892</v>
+        <v>7.936</v>
       </c>
       <c r="AB90" t="n">
-        <v>23.234</v>
+        <v>23.537</v>
       </c>
       <c r="AC90" t="n">
-        <v>13.015</v>
+        <v>12.846</v>
       </c>
       <c r="AD90" t="n">
-        <v>18.082</v>
+        <v>17.942</v>
       </c>
       <c r="AE90" t="n">
-        <v>9.558999999999999</v>
+        <v>9.260999999999999</v>
       </c>
       <c r="AF90" t="n">
-        <v>22.67</v>
+        <v>22.472</v>
       </c>
       <c r="AG90" t="n">
-        <v>14.715</v>
+        <v>14.578</v>
       </c>
       <c r="AH90" t="n">
-        <v>7.517</v>
+        <v>7.511</v>
       </c>
       <c r="AI90" t="n">
-        <v>3.495</v>
+        <v>3.396</v>
       </c>
       <c r="AJ90" t="n">
-        <v>18.829</v>
+        <v>18.686</v>
       </c>
       <c r="AK90" t="n">
-        <v>-0.8</v>
+        <v>3.6</v>
       </c>
       <c r="AL90" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="91">
@@ -12266,22 +12278,22 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F99" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G99" t="b">
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>1430.575</v>
+        <v>1438.377</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7345</v>
+        <v>0.6965</v>
       </c>
       <c r="J99" t="n">
-        <v>1440</v>
+        <v>1443.7</v>
       </c>
       <c r="K99" t="n">
         <v>265</v>
@@ -12302,70 +12314,70 @@
         <v>254</v>
       </c>
       <c r="Q99" t="n">
-        <v>109.53</v>
+        <v>110.823</v>
       </c>
       <c r="R99" t="n">
-        <v>111.062</v>
+        <v>111.791</v>
       </c>
       <c r="S99" t="n">
-        <v>-1.532</v>
+        <v>-0.968</v>
       </c>
       <c r="T99" t="n">
-        <v>0.31118</v>
+        <v>0.31512</v>
       </c>
       <c r="U99" t="n">
-        <v>0.14484</v>
+        <v>0.144</v>
       </c>
       <c r="V99" t="n">
-        <v>79.45999999999999</v>
+        <v>80.06</v>
       </c>
       <c r="W99" t="n">
-        <v>80.59999999999999</v>
+        <v>80.83</v>
       </c>
       <c r="X99" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5363</v>
       </c>
       <c r="Y99" t="n">
-        <v>26.119</v>
+        <v>26.218</v>
       </c>
       <c r="Z99" t="n">
-        <v>61.336</v>
+        <v>61.247</v>
       </c>
       <c r="AA99" t="n">
-        <v>9.394</v>
+        <v>9.413</v>
       </c>
       <c r="AB99" t="n">
-        <v>29.238</v>
+        <v>28.769</v>
       </c>
       <c r="AC99" t="n">
-        <v>17.696</v>
+        <v>17.742</v>
       </c>
       <c r="AD99" t="n">
-        <v>24.443</v>
+        <v>24.63</v>
       </c>
       <c r="AE99" t="n">
-        <v>9.988</v>
+        <v>10.126</v>
       </c>
       <c r="AF99" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AG99" t="n">
-        <v>10.762</v>
+        <v>10.858</v>
       </c>
       <c r="AH99" t="n">
-        <v>7.933</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="AI99" t="n">
-        <v>3.487</v>
+        <v>3.37</v>
       </c>
       <c r="AJ99" t="n">
-        <v>19.525</v>
+        <v>19.421</v>
       </c>
       <c r="AK99" t="n">
-        <v>-1.4</v>
+        <v>3.4</v>
       </c>
       <c r="AL99" t="n">
-        <v>-2.6</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="100">
@@ -12386,22 +12398,22 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F100" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G100" t="b">
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>1246.565</v>
+        <v>1245.727</v>
       </c>
       <c r="I100" t="n">
-        <v>-4.7167</v>
+        <v>-4.5195</v>
       </c>
       <c r="J100" t="n">
-        <v>1443.2</v>
+        <v>1453.1</v>
       </c>
       <c r="K100" t="n">
         <v>361</v>
@@ -12422,70 +12434,70 @@
         <v>361</v>
       </c>
       <c r="Q100" t="n">
-        <v>93.643</v>
+        <v>93.22199999999999</v>
       </c>
       <c r="R100" t="n">
-        <v>121.606</v>
+        <v>121.763</v>
       </c>
       <c r="S100" t="n">
-        <v>-27.963</v>
+        <v>-28.541</v>
       </c>
       <c r="T100" t="n">
-        <v>0.2472</v>
+        <v>0.24872</v>
       </c>
       <c r="U100" t="n">
-        <v>0.19404</v>
+        <v>0.19297</v>
       </c>
       <c r="V100" t="n">
-        <v>66.39</v>
+        <v>66.08</v>
       </c>
       <c r="W100" t="n">
-        <v>86.55</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="X100" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0658</v>
       </c>
       <c r="Y100" t="n">
-        <v>23.816</v>
+        <v>23.654</v>
       </c>
       <c r="Z100" t="n">
-        <v>56.728</v>
+        <v>56.893</v>
       </c>
       <c r="AA100" t="n">
-        <v>7.231</v>
+        <v>7.152</v>
       </c>
       <c r="AB100" t="n">
-        <v>22.905</v>
+        <v>23.05</v>
       </c>
       <c r="AC100" t="n">
-        <v>11.483</v>
+        <v>11.585</v>
       </c>
       <c r="AD100" t="n">
-        <v>16.993</v>
+        <v>17.033</v>
       </c>
       <c r="AE100" t="n">
-        <v>7.007</v>
+        <v>7.149</v>
       </c>
       <c r="AF100" t="n">
-        <v>20.408</v>
+        <v>20.622</v>
       </c>
       <c r="AG100" t="n">
-        <v>10.15</v>
+        <v>9.975</v>
       </c>
       <c r="AH100" t="n">
-        <v>5.946</v>
+        <v>5.98</v>
       </c>
       <c r="AI100" t="n">
-        <v>2.565</v>
+        <v>2.539</v>
       </c>
       <c r="AJ100" t="n">
-        <v>17.85</v>
+        <v>17.914</v>
       </c>
       <c r="AK100" t="n">
-        <v>-7.2</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AL100" t="n">
-        <v>-12.4</v>
+        <v>-12.7</v>
       </c>
     </row>
     <row r="101">
@@ -13586,22 +13598,22 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F110" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G110" t="b">
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>1493.522</v>
+        <v>1513.711</v>
       </c>
       <c r="I110" t="n">
-        <v>2.5383</v>
+        <v>2.6769</v>
       </c>
       <c r="J110" t="n">
-        <v>1466.8</v>
+        <v>1467.8</v>
       </c>
       <c r="K110" t="n">
         <v>157</v>
@@ -13622,70 +13634,70 @@
         <v>154</v>
       </c>
       <c r="Q110" t="n">
-        <v>108.199</v>
+        <v>109.394</v>
       </c>
       <c r="R110" t="n">
-        <v>104.177</v>
+        <v>104.645</v>
       </c>
       <c r="S110" t="n">
-        <v>4.023</v>
+        <v>4.749</v>
       </c>
       <c r="T110" t="n">
-        <v>0.24657</v>
+        <v>0.24163</v>
       </c>
       <c r="U110" t="n">
-        <v>0.16522</v>
+        <v>0.16367</v>
       </c>
       <c r="V110" t="n">
-        <v>69.54000000000001</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="W110" t="n">
-        <v>67.29000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="X110" t="n">
-        <v>0.5667</v>
+        <v>0.5992</v>
       </c>
       <c r="Y110" t="n">
-        <v>25.247</v>
+        <v>25.413</v>
       </c>
       <c r="Z110" t="n">
-        <v>54.751</v>
+        <v>54.551</v>
       </c>
       <c r="AA110" t="n">
-        <v>7.511</v>
+        <v>7.668</v>
       </c>
       <c r="AB110" t="n">
-        <v>21.713</v>
+        <v>21.725</v>
       </c>
       <c r="AC110" t="n">
-        <v>11.533</v>
+        <v>11.794</v>
       </c>
       <c r="AD110" t="n">
-        <v>14.327</v>
+        <v>14.611</v>
       </c>
       <c r="AE110" t="n">
-        <v>7.282</v>
+        <v>7.15</v>
       </c>
       <c r="AF110" t="n">
-        <v>21.936</v>
+        <v>22.239</v>
       </c>
       <c r="AG110" t="n">
-        <v>13.947</v>
+        <v>14.211</v>
       </c>
       <c r="AH110" t="n">
-        <v>7.34</v>
+        <v>7.275</v>
       </c>
       <c r="AI110" t="n">
-        <v>3.529</v>
+        <v>3.668</v>
       </c>
       <c r="AJ110" t="n">
-        <v>13.736</v>
+        <v>13.482</v>
       </c>
       <c r="AK110" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AL110" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="111">
@@ -13826,22 +13838,22 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F112" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G112" t="b">
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>1620.837</v>
+        <v>1618.025</v>
       </c>
       <c r="I112" t="n">
-        <v>-1.4038</v>
+        <v>-1.2011</v>
       </c>
       <c r="J112" t="n">
-        <v>1381.5</v>
+        <v>1375.9</v>
       </c>
       <c r="K112" t="n">
         <v>91</v>
@@ -13862,70 +13874,70 @@
         <v>76</v>
       </c>
       <c r="Q112" t="n">
-        <v>121.643</v>
+        <v>121.43</v>
       </c>
       <c r="R112" t="n">
-        <v>100.605</v>
+        <v>99.785</v>
       </c>
       <c r="S112" t="n">
-        <v>21.038</v>
+        <v>21.646</v>
       </c>
       <c r="T112" t="n">
-        <v>0.31211</v>
+        <v>0.31365</v>
       </c>
       <c r="U112" t="n">
-        <v>0.12661</v>
+        <v>0.12808</v>
       </c>
       <c r="V112" t="n">
-        <v>86.8</v>
+        <v>86.62</v>
       </c>
       <c r="W112" t="n">
-        <v>72.15000000000001</v>
+        <v>71.55</v>
       </c>
       <c r="X112" t="n">
-        <v>0.8589</v>
+        <v>0.8636</v>
       </c>
       <c r="Y112" t="n">
-        <v>29.116</v>
+        <v>29.136</v>
       </c>
       <c r="Z112" t="n">
-        <v>61.236</v>
+        <v>61.477</v>
       </c>
       <c r="AA112" t="n">
-        <v>9.095000000000001</v>
+        <v>9.023</v>
       </c>
       <c r="AB112" t="n">
-        <v>26.388</v>
+        <v>26.375</v>
       </c>
       <c r="AC112" t="n">
-        <v>19.467</v>
+        <v>19.33</v>
       </c>
       <c r="AD112" t="n">
-        <v>26.245</v>
+        <v>26.091</v>
       </c>
       <c r="AE112" t="n">
-        <v>10.224</v>
+        <v>10.523</v>
       </c>
       <c r="AF112" t="n">
-        <v>22.093</v>
+        <v>22.511</v>
       </c>
       <c r="AG112" t="n">
-        <v>15.494</v>
+        <v>15.432</v>
       </c>
       <c r="AH112" t="n">
-        <v>10.587</v>
+        <v>10.489</v>
       </c>
       <c r="AI112" t="n">
-        <v>3.838</v>
+        <v>3.75</v>
       </c>
       <c r="AJ112" t="n">
-        <v>18.554</v>
+        <v>18.511</v>
       </c>
       <c r="AK112" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="AL112" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="113">
@@ -14786,22 +14798,22 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F120" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G120" t="b">
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>1520.214</v>
+        <v>1529.062</v>
       </c>
       <c r="I120" t="n">
-        <v>1.8071</v>
+        <v>1.9462</v>
       </c>
       <c r="J120" t="n">
-        <v>1502.8</v>
+        <v>1506.7</v>
       </c>
       <c r="K120" t="n">
         <v>110</v>
@@ -14822,70 +14834,70 @@
         <v>116</v>
       </c>
       <c r="Q120" t="n">
-        <v>107.597</v>
+        <v>108.197</v>
       </c>
       <c r="R120" t="n">
-        <v>103.448</v>
+        <v>103.264</v>
       </c>
       <c r="S120" t="n">
-        <v>4.15</v>
+        <v>4.933</v>
       </c>
       <c r="T120" t="n">
-        <v>0.34785</v>
+        <v>0.34541</v>
       </c>
       <c r="U120" t="n">
-        <v>0.16863</v>
+        <v>0.16487</v>
       </c>
       <c r="V120" t="n">
-        <v>73.48999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="W120" t="n">
-        <v>70.63</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="X120" t="n">
-        <v>0.5124</v>
+        <v>0.5374</v>
       </c>
       <c r="Y120" t="n">
-        <v>25.748</v>
+        <v>25.677</v>
       </c>
       <c r="Z120" t="n">
-        <v>58.587</v>
+        <v>58.803</v>
       </c>
       <c r="AA120" t="n">
-        <v>6.236</v>
+        <v>6.264</v>
       </c>
       <c r="AB120" t="n">
-        <v>19.578</v>
+        <v>19.678</v>
       </c>
       <c r="AC120" t="n">
-        <v>15.755</v>
+        <v>16.194</v>
       </c>
       <c r="AD120" t="n">
-        <v>21.696</v>
+        <v>22.378</v>
       </c>
       <c r="AE120" t="n">
-        <v>11.379</v>
+        <v>11.289</v>
       </c>
       <c r="AF120" t="n">
-        <v>21.792</v>
+        <v>21.835</v>
       </c>
       <c r="AG120" t="n">
-        <v>13.739</v>
+        <v>13.76</v>
       </c>
       <c r="AH120" t="n">
-        <v>7.922</v>
+        <v>7.851</v>
       </c>
       <c r="AI120" t="n">
-        <v>3.708</v>
+        <v>3.819</v>
       </c>
       <c r="AJ120" t="n">
-        <v>17.059</v>
+        <v>17.399</v>
       </c>
       <c r="AK120" t="n">
-        <v>10.4</v>
+        <v>7.6</v>
       </c>
       <c r="AL120" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="121">
@@ -15026,22 +15038,22 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F122" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G122" t="b">
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>1589.656</v>
+        <v>1580.626</v>
       </c>
       <c r="I122" t="n">
-        <v>2.2669</v>
+        <v>2.2563</v>
       </c>
       <c r="J122" t="n">
-        <v>1505.7</v>
+        <v>1504.8</v>
       </c>
       <c r="K122" t="n">
         <v>97</v>
@@ -15062,70 +15074,70 @@
         <v>90</v>
       </c>
       <c r="Q122" t="n">
-        <v>110.944</v>
+        <v>109.572</v>
       </c>
       <c r="R122" t="n">
-        <v>101.682</v>
+        <v>102.175</v>
       </c>
       <c r="S122" t="n">
-        <v>9.262</v>
+        <v>7.397</v>
       </c>
       <c r="T122" t="n">
-        <v>0.25983</v>
+        <v>0.25789</v>
       </c>
       <c r="U122" t="n">
-        <v>0.16251</v>
+        <v>0.16388</v>
       </c>
       <c r="V122" t="n">
-        <v>75.36</v>
+        <v>74.33</v>
       </c>
       <c r="W122" t="n">
-        <v>68.98999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="X122" t="n">
-        <v>0.6372</v>
+        <v>0.6069</v>
       </c>
       <c r="Y122" t="n">
-        <v>26.913</v>
+        <v>27.019</v>
       </c>
       <c r="Z122" t="n">
-        <v>57.783</v>
+        <v>57.674</v>
       </c>
       <c r="AA122" t="n">
-        <v>8.702</v>
+        <v>8.638999999999999</v>
       </c>
       <c r="AB122" t="n">
-        <v>24.559</v>
+        <v>24.303</v>
       </c>
       <c r="AC122" t="n">
-        <v>12.832</v>
+        <v>12.568</v>
       </c>
       <c r="AD122" t="n">
-        <v>18.019</v>
+        <v>17.676</v>
       </c>
       <c r="AE122" t="n">
-        <v>8.680999999999999</v>
+        <v>8.638999999999999</v>
       </c>
       <c r="AF122" t="n">
-        <v>24.925</v>
+        <v>25.051</v>
       </c>
       <c r="AG122" t="n">
-        <v>13.526</v>
+        <v>13.812</v>
       </c>
       <c r="AH122" t="n">
-        <v>5.616</v>
+        <v>5.565</v>
       </c>
       <c r="AI122" t="n">
-        <v>2.208</v>
+        <v>2.233</v>
       </c>
       <c r="AJ122" t="n">
-        <v>17.109</v>
+        <v>17.429</v>
       </c>
       <c r="AK122" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AL122" t="n">
-        <v>1</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="123">
@@ -16946,22 +16958,22 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F138" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G138" t="b">
         <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>1605.462</v>
+        <v>1604.405</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4681</v>
+        <v>0.3083</v>
       </c>
       <c r="J138" t="n">
-        <v>1472.1</v>
+        <v>1468.3</v>
       </c>
       <c r="K138" t="n">
         <v>160</v>
@@ -16982,70 +16994,70 @@
         <v>150</v>
       </c>
       <c r="Q138" t="n">
-        <v>112.266</v>
+        <v>112.375</v>
       </c>
       <c r="R138" t="n">
-        <v>108.996</v>
+        <v>109.123</v>
       </c>
       <c r="S138" t="n">
-        <v>3.27</v>
+        <v>3.252</v>
       </c>
       <c r="T138" t="n">
-        <v>0.31622</v>
+        <v>0.3198</v>
       </c>
       <c r="U138" t="n">
-        <v>0.181</v>
+        <v>0.18183</v>
       </c>
       <c r="V138" t="n">
-        <v>83.59</v>
+        <v>83.48</v>
       </c>
       <c r="W138" t="n">
-        <v>81.11</v>
+        <v>81.03</v>
       </c>
       <c r="X138" t="n">
-        <v>0.7178</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="Y138" t="n">
-        <v>26.778</v>
+        <v>26.852</v>
       </c>
       <c r="Z138" t="n">
-        <v>60.436</v>
+        <v>60.5</v>
       </c>
       <c r="AA138" t="n">
-        <v>9.744</v>
+        <v>9.875</v>
       </c>
       <c r="AB138" t="n">
-        <v>27.427</v>
+        <v>27.659</v>
       </c>
       <c r="AC138" t="n">
-        <v>20.287</v>
+        <v>19.898</v>
       </c>
       <c r="AD138" t="n">
-        <v>27.205</v>
+        <v>26.875</v>
       </c>
       <c r="AE138" t="n">
-        <v>11.471</v>
+        <v>11.58</v>
       </c>
       <c r="AF138" t="n">
-        <v>24.591</v>
+        <v>24.42</v>
       </c>
       <c r="AG138" t="n">
-        <v>15.497</v>
+        <v>15.409</v>
       </c>
       <c r="AH138" t="n">
-        <v>6.601</v>
+        <v>6.636</v>
       </c>
       <c r="AI138" t="n">
-        <v>3.471</v>
+        <v>3.443</v>
       </c>
       <c r="AJ138" t="n">
-        <v>19.991</v>
+        <v>19.795</v>
       </c>
       <c r="AK138" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AL138" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="139">
@@ -17786,22 +17798,22 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F145" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G145" t="b">
         <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>1481.018</v>
+        <v>1475.874</v>
       </c>
       <c r="I145" t="n">
-        <v>1.2211</v>
+        <v>1.1224</v>
       </c>
       <c r="J145" t="n">
-        <v>1421.5</v>
+        <v>1421.3</v>
       </c>
       <c r="K145" t="n">
         <v>179</v>
@@ -17822,70 +17834,70 @@
         <v>173</v>
       </c>
       <c r="Q145" t="n">
-        <v>111.947</v>
+        <v>110.673</v>
       </c>
       <c r="R145" t="n">
-        <v>109.05</v>
+        <v>109.605</v>
       </c>
       <c r="S145" t="n">
-        <v>2.897</v>
+        <v>1.067</v>
       </c>
       <c r="T145" t="n">
-        <v>0.25533</v>
+        <v>0.25603</v>
       </c>
       <c r="U145" t="n">
-        <v>0.15023</v>
+        <v>0.15152</v>
       </c>
       <c r="V145" t="n">
-        <v>78.47</v>
+        <v>77.34</v>
       </c>
       <c r="W145" t="n">
         <v>77</v>
       </c>
       <c r="X145" t="n">
-        <v>0.5909</v>
+        <v>0.5607</v>
       </c>
       <c r="Y145" t="n">
-        <v>27.989</v>
+        <v>28.097</v>
       </c>
       <c r="Z145" t="n">
-        <v>61.273</v>
+        <v>61.165</v>
       </c>
       <c r="AA145" t="n">
-        <v>10.523</v>
+        <v>10.331</v>
       </c>
       <c r="AB145" t="n">
-        <v>29.284</v>
+        <v>28.828</v>
       </c>
       <c r="AC145" t="n">
-        <v>11.966</v>
+        <v>11.859</v>
       </c>
       <c r="AD145" t="n">
-        <v>15.909</v>
+        <v>15.663</v>
       </c>
       <c r="AE145" t="n">
-        <v>8.42</v>
+        <v>8.547000000000001</v>
       </c>
       <c r="AF145" t="n">
-        <v>23.534</v>
+        <v>23.789</v>
       </c>
       <c r="AG145" t="n">
-        <v>17.489</v>
+        <v>17.211</v>
       </c>
       <c r="AH145" t="n">
-        <v>6.807</v>
+        <v>6.966</v>
       </c>
       <c r="AI145" t="n">
-        <v>2.659</v>
+        <v>2.583</v>
       </c>
       <c r="AJ145" t="n">
-        <v>16.432</v>
+        <v>16.342</v>
       </c>
       <c r="AK145" t="n">
-        <v>3.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AL145" t="n">
-        <v>1.2</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="146">
@@ -18146,22 +18158,22 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F148" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G148" t="b">
         <v>1</v>
       </c>
       <c r="H148" t="n">
-        <v>1399.745</v>
+        <v>1393.412</v>
       </c>
       <c r="I148" t="n">
-        <v>-2.9584</v>
+        <v>-2.8101</v>
       </c>
       <c r="J148" t="n">
-        <v>1389.7</v>
+        <v>1389.4</v>
       </c>
       <c r="K148" t="n">
         <v>272</v>
@@ -18182,70 +18194,70 @@
         <v>264</v>
       </c>
       <c r="Q148" t="n">
-        <v>106.844</v>
+        <v>106.819</v>
       </c>
       <c r="R148" t="n">
-        <v>107.175</v>
+        <v>107.644</v>
       </c>
       <c r="S148" t="n">
-        <v>-0.33</v>
+        <v>-0.825</v>
       </c>
       <c r="T148" t="n">
-        <v>0.31938</v>
+        <v>0.32367</v>
       </c>
       <c r="U148" t="n">
-        <v>0.18938</v>
+        <v>0.1864</v>
       </c>
       <c r="V148" t="n">
-        <v>75.89</v>
+        <v>75.98</v>
       </c>
       <c r="W148" t="n">
-        <v>75.90000000000001</v>
+        <v>76.36</v>
       </c>
       <c r="X148" t="n">
-        <v>0.4722</v>
+        <v>0.4422</v>
       </c>
       <c r="Y148" t="n">
-        <v>25.774</v>
+        <v>25.844</v>
       </c>
       <c r="Z148" t="n">
-        <v>58.026</v>
+        <v>58.497</v>
       </c>
       <c r="AA148" t="n">
-        <v>6.517</v>
+        <v>6.347</v>
       </c>
       <c r="AB148" t="n">
-        <v>20.241</v>
+        <v>20.347</v>
       </c>
       <c r="AC148" t="n">
-        <v>17.826</v>
+        <v>17.946</v>
       </c>
       <c r="AD148" t="n">
-        <v>23.881</v>
+        <v>24.299</v>
       </c>
       <c r="AE148" t="n">
-        <v>10.819</v>
+        <v>11.177</v>
       </c>
       <c r="AF148" t="n">
-        <v>22.787</v>
+        <v>22.932</v>
       </c>
       <c r="AG148" t="n">
-        <v>12.411</v>
+        <v>12.102</v>
       </c>
       <c r="AH148" t="n">
-        <v>8.281000000000001</v>
+        <v>8.272</v>
       </c>
       <c r="AI148" t="n">
-        <v>1.985</v>
+        <v>1.952</v>
       </c>
       <c r="AJ148" t="n">
-        <v>19.739</v>
+        <v>20.143</v>
       </c>
       <c r="AK148" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AL148" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="149">
@@ -20546,22 +20558,22 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F168" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G168" t="b">
         <v>1</v>
       </c>
       <c r="H168" t="n">
-        <v>1771.654</v>
+        <v>1775.227</v>
       </c>
       <c r="I168" t="n">
-        <v>9.957599999999999</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>1412.7</v>
+        <v>1414.6</v>
       </c>
       <c r="K168" t="n">
         <v>87</v>
@@ -20582,67 +20594,67 @@
         <v>52</v>
       </c>
       <c r="Q168" t="n">
-        <v>120.024</v>
+        <v>120.89</v>
       </c>
       <c r="R168" t="n">
-        <v>103.883</v>
+        <v>105.231</v>
       </c>
       <c r="S168" t="n">
-        <v>16.14</v>
+        <v>15.659</v>
       </c>
       <c r="T168" t="n">
-        <v>0.20705</v>
+        <v>0.21072</v>
       </c>
       <c r="U168" t="n">
-        <v>0.14268</v>
+        <v>0.1402</v>
       </c>
       <c r="V168" t="n">
-        <v>86.41</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="W168" t="n">
-        <v>74.75</v>
+        <v>76.22</v>
       </c>
       <c r="X168" t="n">
         <v>1</v>
       </c>
       <c r="Y168" t="n">
-        <v>29.68</v>
+        <v>29.89</v>
       </c>
       <c r="Z168" t="n">
-        <v>58.332</v>
+        <v>58.746</v>
       </c>
       <c r="AA168" t="n">
-        <v>9.724</v>
+        <v>9.76</v>
       </c>
       <c r="AB168" t="n">
-        <v>26.016</v>
+        <v>25.965</v>
       </c>
       <c r="AC168" t="n">
-        <v>17.325</v>
+        <v>17.998</v>
       </c>
       <c r="AD168" t="n">
-        <v>23.105</v>
+        <v>23.96</v>
       </c>
       <c r="AE168" t="n">
-        <v>6.844</v>
+        <v>7.119</v>
       </c>
       <c r="AF168" t="n">
-        <v>25.587</v>
+        <v>25.871</v>
       </c>
       <c r="AG168" t="n">
-        <v>15.157</v>
+        <v>15.047</v>
       </c>
       <c r="AH168" t="n">
-        <v>7.274</v>
+        <v>7.118</v>
       </c>
       <c r="AI168" t="n">
-        <v>3.238</v>
+        <v>3.169</v>
       </c>
       <c r="AJ168" t="n">
-        <v>16.379</v>
+        <v>16.643</v>
       </c>
       <c r="AK168" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AL168" t="n">
         <v>9.699999999999999</v>
@@ -21986,22 +21998,22 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F180" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G180" t="b">
         <v>1</v>
       </c>
       <c r="H180" t="n">
-        <v>1407.15</v>
+        <v>1409.868</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0138</v>
+        <v>0.1391</v>
       </c>
       <c r="J180" t="n">
-        <v>1398.9</v>
+        <v>1399</v>
       </c>
       <c r="K180" t="n">
         <v>282</v>
@@ -22022,70 +22034,70 @@
         <v>261</v>
       </c>
       <c r="Q180" t="n">
-        <v>108.362</v>
+        <v>108.087</v>
       </c>
       <c r="R180" t="n">
-        <v>112.245</v>
+        <v>111.591</v>
       </c>
       <c r="S180" t="n">
-        <v>-3.884</v>
+        <v>-3.504</v>
       </c>
       <c r="T180" t="n">
-        <v>0.33151</v>
+        <v>0.33067</v>
       </c>
       <c r="U180" t="n">
-        <v>0.17802</v>
+        <v>0.17598</v>
       </c>
       <c r="V180" t="n">
-        <v>72.40000000000001</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="W180" t="n">
-        <v>75.36</v>
+        <v>74.77</v>
       </c>
       <c r="X180" t="n">
-        <v>0.5767</v>
+        <v>0.5909</v>
       </c>
       <c r="Y180" t="n">
-        <v>25.578</v>
+        <v>25.33</v>
       </c>
       <c r="Z180" t="n">
-        <v>57.048</v>
+        <v>56.943</v>
       </c>
       <c r="AA180" t="n">
-        <v>5.635</v>
+        <v>5.523</v>
       </c>
       <c r="AB180" t="n">
-        <v>17.519</v>
+        <v>17.25</v>
       </c>
       <c r="AC180" t="n">
-        <v>15.61</v>
+        <v>15.886</v>
       </c>
       <c r="AD180" t="n">
-        <v>21.116</v>
+        <v>21.591</v>
       </c>
       <c r="AE180" t="n">
-        <v>11.342</v>
+        <v>11.443</v>
       </c>
       <c r="AF180" t="n">
-        <v>22.272</v>
+        <v>22.602</v>
       </c>
       <c r="AG180" t="n">
-        <v>12.354</v>
+        <v>11.989</v>
       </c>
       <c r="AH180" t="n">
-        <v>6.083</v>
+        <v>5.977</v>
       </c>
       <c r="AI180" t="n">
-        <v>2.928</v>
+        <v>3.057</v>
       </c>
       <c r="AJ180" t="n">
-        <v>17.951</v>
+        <v>17.909</v>
       </c>
       <c r="AK180" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AL180" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="181">
@@ -22586,22 +22598,22 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F185" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G185" t="b">
         <v>1</v>
       </c>
       <c r="H185" t="n">
-        <v>1581.714</v>
+        <v>1572.866</v>
       </c>
       <c r="I185" t="n">
-        <v>4.703</v>
+        <v>4.2807</v>
       </c>
       <c r="J185" t="n">
-        <v>1504.9</v>
+        <v>1504.1</v>
       </c>
       <c r="K185" t="n">
         <v>117</v>
@@ -22622,70 +22634,70 @@
         <v>101</v>
       </c>
       <c r="Q185" t="n">
-        <v>116.241</v>
+        <v>115.54</v>
       </c>
       <c r="R185" t="n">
-        <v>111.306</v>
+        <v>111.296</v>
       </c>
       <c r="S185" t="n">
-        <v>4.934</v>
+        <v>4.244</v>
       </c>
       <c r="T185" t="n">
-        <v>0.31205</v>
+        <v>0.30887</v>
       </c>
       <c r="U185" t="n">
-        <v>0.16015</v>
+        <v>0.16111</v>
       </c>
       <c r="V185" t="n">
-        <v>83.41</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="W185" t="n">
-        <v>79.65000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="X185" t="n">
-        <v>0.6364</v>
+        <v>0.6171</v>
       </c>
       <c r="Y185" t="n">
-        <v>28.041</v>
+        <v>28.353</v>
       </c>
       <c r="Z185" t="n">
-        <v>60.686</v>
+        <v>60.809</v>
       </c>
       <c r="AA185" t="n">
-        <v>9.6</v>
+        <v>9.337999999999999</v>
       </c>
       <c r="AB185" t="n">
-        <v>27.4</v>
+        <v>26.792</v>
       </c>
       <c r="AC185" t="n">
-        <v>17.727</v>
+        <v>17.809</v>
       </c>
       <c r="AD185" t="n">
-        <v>23.327</v>
+        <v>23.582</v>
       </c>
       <c r="AE185" t="n">
-        <v>10.759</v>
+        <v>10.753</v>
       </c>
       <c r="AF185" t="n">
-        <v>23.773</v>
+        <v>24.15</v>
       </c>
       <c r="AG185" t="n">
-        <v>13.823</v>
+        <v>13.945</v>
       </c>
       <c r="AH185" t="n">
-        <v>5.955</v>
+        <v>5.926</v>
       </c>
       <c r="AI185" t="n">
-        <v>3.941</v>
+        <v>3.926</v>
       </c>
       <c r="AJ185" t="n">
-        <v>18.541</v>
+        <v>18.736</v>
       </c>
       <c r="AK185" t="n">
-        <v>-5.6</v>
+        <v>-8.6</v>
       </c>
       <c r="AL185" t="n">
-        <v>-6.2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="186">
@@ -22946,22 +22958,22 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F188" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G188" t="b">
         <v>1</v>
       </c>
       <c r="H188" t="n">
-        <v>1278.591</v>
+        <v>1280.349</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.671</v>
       </c>
       <c r="J188" t="n">
-        <v>1472</v>
+        <v>1480.9</v>
       </c>
       <c r="K188" t="n">
         <v>331</v>
@@ -22982,70 +22994,70 @@
         <v>331</v>
       </c>
       <c r="Q188" t="n">
-        <v>96.682</v>
+        <v>95.759</v>
       </c>
       <c r="R188" t="n">
-        <v>113.145</v>
+        <v>113.848</v>
       </c>
       <c r="S188" t="n">
-        <v>-16.462</v>
+        <v>-18.089</v>
       </c>
       <c r="T188" t="n">
-        <v>0.29946</v>
+        <v>0.29511</v>
       </c>
       <c r="U188" t="n">
-        <v>0.20279</v>
+        <v>0.20116</v>
       </c>
       <c r="V188" t="n">
-        <v>66.87</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="W188" t="n">
-        <v>78.62</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="X188" t="n">
-        <v>0.2558</v>
+        <v>0.2469</v>
       </c>
       <c r="Y188" t="n">
-        <v>22.402</v>
+        <v>22.388</v>
       </c>
       <c r="Z188" t="n">
-        <v>55.037</v>
+        <v>55.178</v>
       </c>
       <c r="AA188" t="n">
-        <v>7.754</v>
+        <v>7.646</v>
       </c>
       <c r="AB188" t="n">
-        <v>24.794</v>
+        <v>24.836</v>
       </c>
       <c r="AC188" t="n">
-        <v>14.308</v>
+        <v>13.76</v>
       </c>
       <c r="AD188" t="n">
-        <v>21.64</v>
+        <v>20.995</v>
       </c>
       <c r="AE188" t="n">
-        <v>9.319000000000001</v>
+        <v>9.092000000000001</v>
       </c>
       <c r="AF188" t="n">
-        <v>21.123</v>
+        <v>20.963</v>
       </c>
       <c r="AG188" t="n">
-        <v>11.863</v>
+        <v>11.513</v>
       </c>
       <c r="AH188" t="n">
-        <v>5.362</v>
+        <v>5.626</v>
       </c>
       <c r="AI188" t="n">
-        <v>1.854</v>
+        <v>1.859</v>
       </c>
       <c r="AJ188" t="n">
-        <v>19.19</v>
+        <v>18.725</v>
       </c>
       <c r="AK188" t="n">
-        <v>-15.6</v>
+        <v>-23.8</v>
       </c>
       <c r="AL188" t="n">
-        <v>-13.9</v>
+        <v>-19.8</v>
       </c>
     </row>
     <row r="189">
@@ -23306,22 +23318,22 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F191" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G191" t="b">
         <v>1</v>
       </c>
       <c r="H191" t="n">
-        <v>1328.343</v>
+        <v>1325.956</v>
       </c>
       <c r="I191" t="n">
-        <v>1.1591</v>
+        <v>1.0955</v>
       </c>
       <c r="J191" t="n">
-        <v>1453.6</v>
+        <v>1450.1</v>
       </c>
       <c r="K191" t="n">
         <v>274</v>
@@ -23342,70 +23354,70 @@
         <v>267</v>
       </c>
       <c r="Q191" t="n">
-        <v>107.078</v>
+        <v>106.802</v>
       </c>
       <c r="R191" t="n">
-        <v>113.605</v>
+        <v>113.848</v>
       </c>
       <c r="S191" t="n">
-        <v>-6.526</v>
+        <v>-7.046</v>
       </c>
       <c r="T191" t="n">
-        <v>0.27192</v>
+        <v>0.27335</v>
       </c>
       <c r="U191" t="n">
-        <v>0.17554</v>
+        <v>0.17434</v>
       </c>
       <c r="V191" t="n">
-        <v>73.91</v>
+        <v>73.84</v>
       </c>
       <c r="W191" t="n">
-        <v>78.22</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="X191" t="n">
-        <v>0.3304</v>
+        <v>0.3188</v>
       </c>
       <c r="Y191" t="n">
-        <v>25.503</v>
+        <v>25.721</v>
       </c>
       <c r="Z191" t="n">
-        <v>55.815</v>
+        <v>56.048</v>
       </c>
       <c r="AA191" t="n">
-        <v>5.844</v>
+        <v>6.032</v>
       </c>
       <c r="AB191" t="n">
-        <v>18.414</v>
+        <v>18.643</v>
       </c>
       <c r="AC191" t="n">
-        <v>17.058</v>
+        <v>17.063</v>
       </c>
       <c r="AD191" t="n">
-        <v>23.386</v>
+        <v>23.39</v>
       </c>
       <c r="AE191" t="n">
-        <v>9.292</v>
+        <v>9.335000000000001</v>
       </c>
       <c r="AF191" t="n">
-        <v>24.241</v>
+        <v>24.196</v>
       </c>
       <c r="AG191" t="n">
-        <v>11.687</v>
+        <v>11.899</v>
       </c>
       <c r="AH191" t="n">
-        <v>5.119</v>
+        <v>5.367</v>
       </c>
       <c r="AI191" t="n">
-        <v>3.643</v>
+        <v>3.638</v>
       </c>
       <c r="AJ191" t="n">
-        <v>17.946</v>
+        <v>18.095</v>
       </c>
       <c r="AK191" t="n">
-        <v>-7.4</v>
+        <v>-8</v>
       </c>
       <c r="AL191" t="n">
-        <v>-6.3</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="192">
@@ -23666,22 +23678,22 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F194" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G194" t="b">
         <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>1367.953</v>
+        <v>1373.913</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.5425</v>
+        <v>-0.445</v>
       </c>
       <c r="J194" t="n">
-        <v>1438.4</v>
+        <v>1433.4</v>
       </c>
       <c r="K194" t="n">
         <v>261</v>
@@ -23702,70 +23714,70 @@
         <v>258</v>
       </c>
       <c r="Q194" t="n">
-        <v>107.372</v>
+        <v>108.274</v>
       </c>
       <c r="R194" t="n">
-        <v>112.748</v>
+        <v>112.115</v>
       </c>
       <c r="S194" t="n">
-        <v>-5.376</v>
+        <v>-3.841</v>
       </c>
       <c r="T194" t="n">
-        <v>0.23511</v>
+        <v>0.24288</v>
       </c>
       <c r="U194" t="n">
-        <v>0.15489</v>
+        <v>0.1526</v>
       </c>
       <c r="V194" t="n">
-        <v>74.41</v>
+        <v>74.77</v>
       </c>
       <c r="W194" t="n">
-        <v>78.23</v>
+        <v>77.59</v>
       </c>
       <c r="X194" t="n">
-        <v>0.4019</v>
+        <v>0.4356</v>
       </c>
       <c r="Y194" t="n">
-        <v>26.052</v>
+        <v>25.855</v>
       </c>
       <c r="Z194" t="n">
-        <v>57.246</v>
+        <v>57.545</v>
       </c>
       <c r="AA194" t="n">
-        <v>8.069000000000001</v>
+        <v>8.153</v>
       </c>
       <c r="AB194" t="n">
-        <v>23.123</v>
+        <v>23.344</v>
       </c>
       <c r="AC194" t="n">
-        <v>14.238</v>
+        <v>14.235</v>
       </c>
       <c r="AD194" t="n">
-        <v>19.65</v>
+        <v>19.848</v>
       </c>
       <c r="AE194" t="n">
-        <v>7.256</v>
+        <v>7.675</v>
       </c>
       <c r="AF194" t="n">
-        <v>23.127</v>
+        <v>23.166</v>
       </c>
       <c r="AG194" t="n">
-        <v>12.298</v>
+        <v>12.115</v>
       </c>
       <c r="AH194" t="n">
-        <v>5.754</v>
+        <v>5.598</v>
       </c>
       <c r="AI194" t="n">
-        <v>2.99</v>
+        <v>2.965</v>
       </c>
       <c r="AJ194" t="n">
-        <v>17.125</v>
+        <v>17.164</v>
       </c>
       <c r="AK194" t="n">
-        <v>-2.4</v>
+        <v>-0.4</v>
       </c>
       <c r="AL194" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="195">
@@ -25106,22 +25118,22 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F206" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G206" t="b">
         <v>1</v>
       </c>
       <c r="H206" t="n">
-        <v>1358.751</v>
+        <v>1361.569</v>
       </c>
       <c r="I206" t="n">
-        <v>0.8181</v>
+        <v>0.8397</v>
       </c>
       <c r="J206" t="n">
-        <v>1464.2</v>
+        <v>1459</v>
       </c>
       <c r="K206" t="n">
         <v>290</v>
@@ -25142,70 +25154,70 @@
         <v>284</v>
       </c>
       <c r="Q206" t="n">
-        <v>106.46</v>
+        <v>107.331</v>
       </c>
       <c r="R206" t="n">
-        <v>115.856</v>
+        <v>114.769</v>
       </c>
       <c r="S206" t="n">
-        <v>-9.396000000000001</v>
+        <v>-7.438</v>
       </c>
       <c r="T206" t="n">
-        <v>0.30959</v>
+        <v>0.30819</v>
       </c>
       <c r="U206" t="n">
-        <v>0.13574</v>
+        <v>0.1348</v>
       </c>
       <c r="V206" t="n">
-        <v>74.43000000000001</v>
+        <v>74.97</v>
       </c>
       <c r="W206" t="n">
-        <v>81.06999999999999</v>
+        <v>80.23</v>
       </c>
       <c r="X206" t="n">
-        <v>0.4422</v>
+        <v>0.4734</v>
       </c>
       <c r="Y206" t="n">
-        <v>25.429</v>
+        <v>25.721</v>
       </c>
       <c r="Z206" t="n">
-        <v>59.912</v>
+        <v>59.947</v>
       </c>
       <c r="AA206" t="n">
-        <v>7.85</v>
+        <v>7.914</v>
       </c>
       <c r="AB206" t="n">
-        <v>24.374</v>
+        <v>24.185</v>
       </c>
       <c r="AC206" t="n">
-        <v>15.721</v>
+        <v>15.613</v>
       </c>
       <c r="AD206" t="n">
-        <v>22.49</v>
+        <v>22.506</v>
       </c>
       <c r="AE206" t="n">
-        <v>9.305999999999999</v>
+        <v>9.342000000000001</v>
       </c>
       <c r="AF206" t="n">
-        <v>20.245</v>
+        <v>20.491</v>
       </c>
       <c r="AG206" t="n">
-        <v>10.68</v>
+        <v>10.84</v>
       </c>
       <c r="AH206" t="n">
-        <v>8.013999999999999</v>
+        <v>7.955</v>
       </c>
       <c r="AI206" t="n">
-        <v>2.524</v>
+        <v>2.403</v>
       </c>
       <c r="AJ206" t="n">
-        <v>20.401</v>
+        <v>20.61</v>
       </c>
       <c r="AK206" t="n">
-        <v>-8.4</v>
+        <v>-5.4</v>
       </c>
       <c r="AL206" t="n">
-        <v>-3.3</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="207">
@@ -25466,22 +25478,22 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F209" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G209" t="b">
         <v>1</v>
       </c>
       <c r="H209" t="n">
-        <v>1359.898</v>
+        <v>1362.284</v>
       </c>
       <c r="I209" t="n">
-        <v>-3.5632</v>
+        <v>-3.5491</v>
       </c>
       <c r="J209" t="n">
-        <v>1483.9</v>
+        <v>1477.6</v>
       </c>
       <c r="K209" t="n">
         <v>288</v>
@@ -25502,70 +25514,70 @@
         <v>288</v>
       </c>
       <c r="Q209" t="n">
-        <v>105.803</v>
+        <v>106.52</v>
       </c>
       <c r="R209" t="n">
-        <v>115.606</v>
+        <v>114.903</v>
       </c>
       <c r="S209" t="n">
-        <v>-9.803000000000001</v>
+        <v>-8.382999999999999</v>
       </c>
       <c r="T209" t="n">
-        <v>0.27577</v>
+        <v>0.28003</v>
       </c>
       <c r="U209" t="n">
-        <v>0.15746</v>
+        <v>0.15915</v>
       </c>
       <c r="V209" t="n">
-        <v>74.48</v>
+        <v>74.97</v>
       </c>
       <c r="W209" t="n">
-        <v>81.26000000000001</v>
+        <v>80.77</v>
       </c>
       <c r="X209" t="n">
-        <v>0.2045</v>
+        <v>0.2414</v>
       </c>
       <c r="Y209" t="n">
-        <v>27.511</v>
+        <v>27.255</v>
       </c>
       <c r="Z209" t="n">
-        <v>59.67</v>
+        <v>59.529</v>
       </c>
       <c r="AA209" t="n">
-        <v>7.636</v>
+        <v>7.42</v>
       </c>
       <c r="AB209" t="n">
-        <v>22.557</v>
+        <v>22.159</v>
       </c>
       <c r="AC209" t="n">
-        <v>11.818</v>
+        <v>12.346</v>
       </c>
       <c r="AD209" t="n">
-        <v>17.17</v>
+        <v>17.709</v>
       </c>
       <c r="AE209" t="n">
-        <v>8.034000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="AF209" t="n">
-        <v>21.114</v>
+        <v>21.142</v>
       </c>
       <c r="AG209" t="n">
-        <v>15.364</v>
+        <v>14.96</v>
       </c>
       <c r="AH209" t="n">
-        <v>6.818</v>
+        <v>6.792</v>
       </c>
       <c r="AI209" t="n">
-        <v>2.977</v>
+        <v>3.13</v>
       </c>
       <c r="AJ209" t="n">
-        <v>18.92</v>
+        <v>18.957</v>
       </c>
       <c r="AK209" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="AL209" t="n">
         <v>-9.4</v>
-      </c>
-      <c r="AL209" t="n">
-        <v>-11.5</v>
       </c>
     </row>
     <row r="210">
@@ -25706,22 +25718,22 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F211" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G211" t="b">
         <v>1</v>
       </c>
       <c r="H211" t="n">
-        <v>1547.46</v>
+        <v>1556.49</v>
       </c>
       <c r="I211" t="n">
-        <v>-4.3733</v>
+        <v>-4.1888</v>
       </c>
       <c r="J211" t="n">
-        <v>1507.2</v>
+        <v>1512.2</v>
       </c>
       <c r="K211" t="n">
         <v>80</v>
@@ -25742,70 +25754,70 @@
         <v>81</v>
       </c>
       <c r="Q211" t="n">
-        <v>106.65</v>
+        <v>107.258</v>
       </c>
       <c r="R211" t="n">
-        <v>96.59999999999999</v>
+        <v>96.193</v>
       </c>
       <c r="S211" t="n">
-        <v>10.05</v>
+        <v>11.064</v>
       </c>
       <c r="T211" t="n">
-        <v>0.20593</v>
+        <v>0.20888</v>
       </c>
       <c r="U211" t="n">
-        <v>0.13544</v>
+        <v>0.13732</v>
       </c>
       <c r="V211" t="n">
-        <v>68.29000000000001</v>
+        <v>68.52</v>
       </c>
       <c r="W211" t="n">
-        <v>61.91</v>
+        <v>61.54</v>
       </c>
       <c r="X211" t="n">
-        <v>0.6167</v>
+        <v>0.6284</v>
       </c>
       <c r="Y211" t="n">
-        <v>25.46</v>
+        <v>25.065</v>
       </c>
       <c r="Z211" t="n">
-        <v>55.304</v>
+        <v>54.888</v>
       </c>
       <c r="AA211" t="n">
-        <v>7.438</v>
+        <v>7.274</v>
       </c>
       <c r="AB211" t="n">
-        <v>22.154</v>
+        <v>22.013</v>
       </c>
       <c r="AC211" t="n">
-        <v>9.930999999999999</v>
+        <v>10.236</v>
       </c>
       <c r="AD211" t="n">
-        <v>14.237</v>
+        <v>14.715</v>
       </c>
       <c r="AE211" t="n">
-        <v>6.154</v>
+        <v>6.173</v>
       </c>
       <c r="AF211" t="n">
-        <v>23.371</v>
+        <v>23.141</v>
       </c>
       <c r="AG211" t="n">
-        <v>14.211</v>
+        <v>13.946</v>
       </c>
       <c r="AH211" t="n">
-        <v>6.351</v>
+        <v>6.381</v>
       </c>
       <c r="AI211" t="n">
-        <v>3.115</v>
+        <v>3.093</v>
       </c>
       <c r="AJ211" t="n">
-        <v>15.179</v>
+        <v>15.155</v>
       </c>
       <c r="AK211" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AL211" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="212">
@@ -26306,22 +26318,22 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F216" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G216" t="b">
         <v>1</v>
       </c>
       <c r="H216" t="n">
-        <v>1466.092</v>
+        <v>1462.519</v>
       </c>
       <c r="I216" t="n">
-        <v>2.6549</v>
+        <v>2.3882</v>
       </c>
       <c r="J216" t="n">
-        <v>1500.7</v>
+        <v>1513.3</v>
       </c>
       <c r="K216" t="n">
         <v>227</v>
@@ -26342,70 +26354,70 @@
         <v>222</v>
       </c>
       <c r="Q216" t="n">
-        <v>106.96</v>
+        <v>107.944</v>
       </c>
       <c r="R216" t="n">
-        <v>111.296</v>
+        <v>112.057</v>
       </c>
       <c r="S216" t="n">
-        <v>-4.337</v>
+        <v>-4.113</v>
       </c>
       <c r="T216" t="n">
-        <v>0.29149</v>
+        <v>0.29112</v>
       </c>
       <c r="U216" t="n">
-        <v>0.14661</v>
+        <v>0.14424</v>
       </c>
       <c r="V216" t="n">
-        <v>75.72</v>
+        <v>77.11</v>
       </c>
       <c r="W216" t="n">
-        <v>78.90000000000001</v>
+        <v>80.14</v>
       </c>
       <c r="X216" t="n">
-        <v>0.4586</v>
+        <v>0.4432</v>
       </c>
       <c r="Y216" t="n">
-        <v>26.859</v>
+        <v>27.318</v>
       </c>
       <c r="Z216" t="n">
-        <v>59.628</v>
+        <v>60.284</v>
       </c>
       <c r="AA216" t="n">
-        <v>6.658</v>
+        <v>7.011</v>
       </c>
       <c r="AB216" t="n">
-        <v>22.603</v>
+        <v>22.966</v>
       </c>
       <c r="AC216" t="n">
-        <v>15.346</v>
+        <v>15.466</v>
       </c>
       <c r="AD216" t="n">
-        <v>21.734</v>
+        <v>21.795</v>
       </c>
       <c r="AE216" t="n">
-        <v>8.743</v>
+        <v>8.773</v>
       </c>
       <c r="AF216" t="n">
-        <v>21.257</v>
+        <v>21.364</v>
       </c>
       <c r="AG216" t="n">
-        <v>12.744</v>
+        <v>12.648</v>
       </c>
       <c r="AH216" t="n">
-        <v>5.917</v>
+        <v>5.795</v>
       </c>
       <c r="AI216" t="n">
-        <v>3.317</v>
+        <v>3.398</v>
       </c>
       <c r="AJ216" t="n">
-        <v>17.85</v>
+        <v>18.205</v>
       </c>
       <c r="AK216" t="n">
-        <v>-4</v>
+        <v>-1.2</v>
       </c>
       <c r="AL216" t="n">
-        <v>-3</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="217">
@@ -27386,22 +27398,22 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F225" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G225" t="b">
         <v>1</v>
       </c>
       <c r="H225" t="n">
-        <v>1421.929</v>
+        <v>1419.847</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9885</v>
+        <v>1.0511</v>
       </c>
       <c r="J225" t="n">
-        <v>1486.6</v>
+        <v>1479.6</v>
       </c>
       <c r="K225" t="n">
         <v>169</v>
@@ -27422,70 +27434,70 @@
         <v>159</v>
       </c>
       <c r="Q225" t="n">
-        <v>107.826</v>
+        <v>108.528</v>
       </c>
       <c r="R225" t="n">
-        <v>107.295</v>
+        <v>106.514</v>
       </c>
       <c r="S225" t="n">
-        <v>0.531</v>
+        <v>2.014</v>
       </c>
       <c r="T225" t="n">
-        <v>0.30977</v>
+        <v>0.31197</v>
       </c>
       <c r="U225" t="n">
-        <v>0.1498</v>
+        <v>0.14956</v>
       </c>
       <c r="V225" t="n">
-        <v>74.06999999999999</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="W225" t="n">
-        <v>73.75</v>
+        <v>73.28</v>
       </c>
       <c r="X225" t="n">
-        <v>0.5671</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="Y225" t="n">
-        <v>25.764</v>
+        <v>25.931</v>
       </c>
       <c r="Z225" t="n">
-        <v>59.088</v>
+        <v>59.301</v>
       </c>
       <c r="AA225" t="n">
-        <v>7.771</v>
+        <v>7.916</v>
       </c>
       <c r="AB225" t="n">
-        <v>20.345</v>
+        <v>20.695</v>
       </c>
       <c r="AC225" t="n">
-        <v>14.775</v>
+        <v>14.872</v>
       </c>
       <c r="AD225" t="n">
-        <v>21.569</v>
+        <v>21.615</v>
       </c>
       <c r="AE225" t="n">
-        <v>10.157</v>
+        <v>10.309</v>
       </c>
       <c r="AF225" t="n">
-        <v>22.891</v>
+        <v>22.954</v>
       </c>
       <c r="AG225" t="n">
-        <v>13.486</v>
+        <v>13.531</v>
       </c>
       <c r="AH225" t="n">
-        <v>6.134</v>
+        <v>6.798</v>
       </c>
       <c r="AI225" t="n">
-        <v>3.046</v>
+        <v>3.076</v>
       </c>
       <c r="AJ225" t="n">
-        <v>17.014</v>
+        <v>16.918</v>
       </c>
       <c r="AK225" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AL225" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="226">
@@ -27866,22 +27878,22 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F229" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G229" t="b">
         <v>1</v>
       </c>
       <c r="H229" t="n">
-        <v>1412.258</v>
+        <v>1416.848</v>
       </c>
       <c r="I229" t="n">
-        <v>1.4459</v>
+        <v>1.4725</v>
       </c>
       <c r="J229" t="n">
-        <v>1532.4</v>
+        <v>1531.8</v>
       </c>
       <c r="K229" t="n">
         <v>204</v>
@@ -27902,70 +27914,70 @@
         <v>227</v>
       </c>
       <c r="Q229" t="n">
-        <v>102.442</v>
+        <v>102.469</v>
       </c>
       <c r="R229" t="n">
-        <v>111.35</v>
+        <v>110.885</v>
       </c>
       <c r="S229" t="n">
-        <v>-8.907999999999999</v>
+        <v>-8.416</v>
       </c>
       <c r="T229" t="n">
-        <v>0.26307</v>
+        <v>0.2615</v>
       </c>
       <c r="U229" t="n">
-        <v>0.1902</v>
+        <v>0.18646</v>
       </c>
       <c r="V229" t="n">
-        <v>72.29000000000001</v>
+        <v>72.31</v>
       </c>
       <c r="W229" t="n">
-        <v>78.17</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="X229" t="n">
-        <v>0.4075</v>
+        <v>0.4261</v>
       </c>
       <c r="Y229" t="n">
-        <v>25.873</v>
+        <v>25.797</v>
       </c>
       <c r="Z229" t="n">
-        <v>56.334</v>
+        <v>56.722</v>
       </c>
       <c r="AA229" t="n">
-        <v>6.111</v>
+        <v>6.226</v>
       </c>
       <c r="AB229" t="n">
-        <v>20.127</v>
+        <v>20.638</v>
       </c>
       <c r="AC229" t="n">
-        <v>14.436</v>
+        <v>14.229</v>
       </c>
       <c r="AD229" t="n">
-        <v>19.65</v>
+        <v>19.258</v>
       </c>
       <c r="AE229" t="n">
-        <v>8.016999999999999</v>
+        <v>7.968</v>
       </c>
       <c r="AF229" t="n">
-        <v>22.318</v>
+        <v>22.397</v>
       </c>
       <c r="AG229" t="n">
-        <v>16.285</v>
+        <v>16.409</v>
       </c>
       <c r="AH229" t="n">
-        <v>6.066</v>
+        <v>6.064</v>
       </c>
       <c r="AI229" t="n">
-        <v>2.926</v>
+        <v>2.774</v>
       </c>
       <c r="AJ229" t="n">
-        <v>17.658</v>
+        <v>17.681</v>
       </c>
       <c r="AK229" t="n">
-        <v>-7.8</v>
+        <v>-5</v>
       </c>
       <c r="AL229" t="n">
-        <v>-9.699999999999999</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="230">
@@ -28226,22 +28238,22 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F232" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G232" t="b">
         <v>1</v>
       </c>
       <c r="H232" t="n">
-        <v>1327.678</v>
+        <v>1333.221</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.9686</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J232" t="n">
-        <v>1410.8</v>
+        <v>1408</v>
       </c>
       <c r="K232" t="n">
         <v>278</v>
@@ -28262,70 +28274,70 @@
         <v>266</v>
       </c>
       <c r="Q232" t="n">
-        <v>104.638</v>
+        <v>105.306</v>
       </c>
       <c r="R232" t="n">
-        <v>109.496</v>
+        <v>109.555</v>
       </c>
       <c r="S232" t="n">
-        <v>-4.858</v>
+        <v>-4.248</v>
       </c>
       <c r="T232" t="n">
-        <v>0.29829</v>
+        <v>0.30923</v>
       </c>
       <c r="U232" t="n">
-        <v>0.18528</v>
+        <v>0.18322</v>
       </c>
       <c r="V232" t="n">
-        <v>69.19</v>
+        <v>70.22</v>
       </c>
       <c r="W232" t="n">
-        <v>72.66</v>
+        <v>73.23</v>
       </c>
       <c r="X232" t="n">
-        <v>0.387</v>
+        <v>0.4218</v>
       </c>
       <c r="Y232" t="n">
-        <v>24.894</v>
+        <v>25.041</v>
       </c>
       <c r="Z232" t="n">
-        <v>53.789</v>
+        <v>54.653</v>
       </c>
       <c r="AA232" t="n">
-        <v>4.554</v>
+        <v>4.721</v>
       </c>
       <c r="AB232" t="n">
-        <v>14.865</v>
+        <v>15.565</v>
       </c>
       <c r="AC232" t="n">
-        <v>14.848</v>
+        <v>15.129</v>
       </c>
       <c r="AD232" t="n">
-        <v>21.757</v>
+        <v>22.361</v>
       </c>
       <c r="AE232" t="n">
-        <v>9.478</v>
+        <v>10.048</v>
       </c>
       <c r="AF232" t="n">
-        <v>22.485</v>
+        <v>22.293</v>
       </c>
       <c r="AG232" t="n">
-        <v>11.972</v>
+        <v>11.959</v>
       </c>
       <c r="AH232" t="n">
-        <v>5.422</v>
+        <v>5.741</v>
       </c>
       <c r="AI232" t="n">
-        <v>4.537</v>
+        <v>4.381</v>
       </c>
       <c r="AJ232" t="n">
-        <v>17.515</v>
+        <v>17.197</v>
       </c>
       <c r="AK232" t="n">
-        <v>-0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AL232" t="n">
-        <v>-3.7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="233">
@@ -28826,22 +28838,22 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F237" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G237" t="b">
         <v>1</v>
       </c>
       <c r="H237" t="n">
-        <v>1373.073</v>
+        <v>1373.663</v>
       </c>
       <c r="I237" t="n">
-        <v>-1.7201</v>
+        <v>-1.6094</v>
       </c>
       <c r="J237" t="n">
-        <v>1423.5</v>
+        <v>1419.6</v>
       </c>
       <c r="K237" t="n">
         <v>255</v>
@@ -28862,70 +28874,70 @@
         <v>250</v>
       </c>
       <c r="Q237" t="n">
-        <v>107.902</v>
+        <v>107.889</v>
       </c>
       <c r="R237" t="n">
-        <v>108.681</v>
+        <v>108.719</v>
       </c>
       <c r="S237" t="n">
-        <v>-0.779</v>
+        <v>-0.83</v>
       </c>
       <c r="T237" t="n">
-        <v>0.2779</v>
+        <v>0.276</v>
       </c>
       <c r="U237" t="n">
-        <v>0.16615</v>
+        <v>0.16712</v>
       </c>
       <c r="V237" t="n">
-        <v>79.61</v>
+        <v>79.92</v>
       </c>
       <c r="W237" t="n">
-        <v>80.55</v>
+        <v>80.91</v>
       </c>
       <c r="X237" t="n">
-        <v>0.4586</v>
+        <v>0.4432</v>
       </c>
       <c r="Y237" t="n">
-        <v>26.259</v>
+        <v>26.648</v>
       </c>
       <c r="Z237" t="n">
-        <v>59.705</v>
+        <v>60.091</v>
       </c>
       <c r="AA237" t="n">
-        <v>9.199</v>
+        <v>9.159000000000001</v>
       </c>
       <c r="AB237" t="n">
-        <v>27.259</v>
+        <v>26.875</v>
       </c>
       <c r="AC237" t="n">
-        <v>17.891</v>
+        <v>17.739</v>
       </c>
       <c r="AD237" t="n">
-        <v>25.056</v>
+        <v>24.693</v>
       </c>
       <c r="AE237" t="n">
-        <v>8.952</v>
+        <v>9.010999999999999</v>
       </c>
       <c r="AF237" t="n">
-        <v>22.575</v>
+        <v>23.034</v>
       </c>
       <c r="AG237" t="n">
-        <v>12.116</v>
+        <v>12.5</v>
       </c>
       <c r="AH237" t="n">
-        <v>7.365</v>
+        <v>7.25</v>
       </c>
       <c r="AI237" t="n">
-        <v>3.459</v>
+        <v>3.534</v>
       </c>
       <c r="AJ237" t="n">
-        <v>19.508</v>
+        <v>19.625</v>
       </c>
       <c r="AK237" t="n">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL237" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="238">
@@ -30026,22 +30038,22 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F247" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G247" t="b">
         <v>1</v>
       </c>
       <c r="H247" t="n">
-        <v>1351.606</v>
+        <v>1349.359</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1043</v>
+        <v>-0.03</v>
       </c>
       <c r="J247" t="n">
-        <v>1433.7</v>
+        <v>1436.3</v>
       </c>
       <c r="K247" t="n">
         <v>293</v>
@@ -30062,70 +30074,70 @@
         <v>293</v>
       </c>
       <c r="Q247" t="n">
-        <v>108.852</v>
+        <v>107.521</v>
       </c>
       <c r="R247" t="n">
-        <v>112.581</v>
+        <v>112.659</v>
       </c>
       <c r="S247" t="n">
-        <v>-3.729</v>
+        <v>-5.139</v>
       </c>
       <c r="T247" t="n">
-        <v>0.27999</v>
+        <v>0.27675</v>
       </c>
       <c r="U247" t="n">
-        <v>0.16705</v>
+        <v>0.17065</v>
       </c>
       <c r="V247" t="n">
-        <v>75.31999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="W247" t="n">
-        <v>77.81999999999999</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="X247" t="n">
-        <v>0.424</v>
+        <v>0.4032</v>
       </c>
       <c r="Y247" t="n">
-        <v>25.232</v>
+        <v>24.878</v>
       </c>
       <c r="Z247" t="n">
-        <v>58.64</v>
+        <v>58.174</v>
       </c>
       <c r="AA247" t="n">
-        <v>10.432</v>
+        <v>10.319</v>
       </c>
       <c r="AB247" t="n">
-        <v>29.336</v>
+        <v>29.195</v>
       </c>
       <c r="AC247" t="n">
-        <v>13.984</v>
+        <v>13.731</v>
       </c>
       <c r="AD247" t="n">
-        <v>18.128</v>
+        <v>17.739</v>
       </c>
       <c r="AE247" t="n">
-        <v>9.064</v>
+        <v>8.916</v>
       </c>
       <c r="AF247" t="n">
-        <v>22.992</v>
+        <v>22.962</v>
       </c>
       <c r="AG247" t="n">
-        <v>14.44</v>
+        <v>14.48</v>
       </c>
       <c r="AH247" t="n">
-        <v>5.448</v>
+        <v>5.311</v>
       </c>
       <c r="AI247" t="n">
-        <v>2.736</v>
+        <v>2.867</v>
       </c>
       <c r="AJ247" t="n">
-        <v>15.192</v>
+        <v>14.963</v>
       </c>
       <c r="AK247" t="n">
-        <v>3.6</v>
+        <v>-3</v>
       </c>
       <c r="AL247" t="n">
-        <v>-0.2</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="248">
@@ -30386,22 +30398,22 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F250" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G250" t="b">
         <v>1</v>
       </c>
       <c r="H250" t="n">
-        <v>1362.04</v>
+        <v>1359.68</v>
       </c>
       <c r="I250" t="n">
-        <v>1.7876</v>
+        <v>1.6714</v>
       </c>
       <c r="J250" t="n">
-        <v>1527.7</v>
+        <v>1529.1</v>
       </c>
       <c r="K250" t="n">
         <v>235</v>
@@ -30422,70 +30434,70 @@
         <v>244</v>
       </c>
       <c r="Q250" t="n">
-        <v>104.993</v>
+        <v>104.54</v>
       </c>
       <c r="R250" t="n">
-        <v>113.385</v>
+        <v>112.858</v>
       </c>
       <c r="S250" t="n">
-        <v>-8.391999999999999</v>
+        <v>-8.317</v>
       </c>
       <c r="T250" t="n">
-        <v>0.30574</v>
+        <v>0.30352</v>
       </c>
       <c r="U250" t="n">
-        <v>0.1671</v>
+        <v>0.17017</v>
       </c>
       <c r="V250" t="n">
-        <v>73.3</v>
+        <v>72.67</v>
       </c>
       <c r="W250" t="n">
-        <v>79.38</v>
+        <v>78.67</v>
       </c>
       <c r="X250" t="n">
-        <v>0.3391</v>
+        <v>0.32</v>
       </c>
       <c r="Y250" t="n">
-        <v>26.487</v>
+        <v>26.2</v>
       </c>
       <c r="Z250" t="n">
-        <v>60.28</v>
+        <v>59.808</v>
       </c>
       <c r="AA250" t="n">
-        <v>8.891</v>
+        <v>8.896000000000001</v>
       </c>
       <c r="AB250" t="n">
-        <v>25.848</v>
+        <v>25.776</v>
       </c>
       <c r="AC250" t="n">
-        <v>11.272</v>
+        <v>11.248</v>
       </c>
       <c r="AD250" t="n">
-        <v>15.289</v>
+        <v>15.248</v>
       </c>
       <c r="AE250" t="n">
-        <v>8.728</v>
+        <v>8.712</v>
       </c>
       <c r="AF250" t="n">
-        <v>19.306</v>
+        <v>19.528</v>
       </c>
       <c r="AG250" t="n">
-        <v>15.477</v>
+        <v>15.392</v>
       </c>
       <c r="AH250" t="n">
-        <v>7.851</v>
+        <v>7.832</v>
       </c>
       <c r="AI250" t="n">
-        <v>2.579</v>
+        <v>2.504</v>
       </c>
       <c r="AJ250" t="n">
-        <v>18.685</v>
+        <v>18.552</v>
       </c>
       <c r="AK250" t="n">
-        <v>-8.800000000000001</v>
+        <v>-6.6</v>
       </c>
       <c r="AL250" t="n">
-        <v>-7.6</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="251">
@@ -30506,22 +30518,22 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F251" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G251" t="b">
         <v>1</v>
       </c>
       <c r="H251" t="n">
-        <v>1781.621</v>
+        <v>1788.15</v>
       </c>
       <c r="I251" t="n">
-        <v>6.1342</v>
+        <v>5.5794</v>
       </c>
       <c r="J251" t="n">
-        <v>1653.2</v>
+        <v>1652.6</v>
       </c>
       <c r="K251" t="n">
         <v>42</v>
@@ -30542,70 +30554,70 @@
         <v>44</v>
       </c>
       <c r="Q251" t="n">
-        <v>110.231</v>
+        <v>110.696</v>
       </c>
       <c r="R251" t="n">
-        <v>101.115</v>
+        <v>101.583</v>
       </c>
       <c r="S251" t="n">
-        <v>9.115</v>
+        <v>9.113</v>
       </c>
       <c r="T251" t="n">
-        <v>0.26142</v>
+        <v>0.26053</v>
       </c>
       <c r="U251" t="n">
-        <v>0.16358</v>
+        <v>0.16418</v>
       </c>
       <c r="V251" t="n">
-        <v>77.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="W251" t="n">
-        <v>71.58</v>
+        <v>72.06</v>
       </c>
       <c r="X251" t="n">
-        <v>0.6364</v>
+        <v>0.6584</v>
       </c>
       <c r="Y251" t="n">
-        <v>27.177</v>
+        <v>27.432</v>
       </c>
       <c r="Z251" t="n">
-        <v>57.899</v>
+        <v>58.019</v>
       </c>
       <c r="AA251" t="n">
-        <v>6.884</v>
+        <v>7.028</v>
       </c>
       <c r="AB251" t="n">
-        <v>19.5</v>
+        <v>19.773</v>
       </c>
       <c r="AC251" t="n">
-        <v>16.364</v>
+        <v>16.211</v>
       </c>
       <c r="AD251" t="n">
-        <v>21.768</v>
+        <v>21.665</v>
       </c>
       <c r="AE251" t="n">
-        <v>8.611000000000001</v>
+        <v>8.606</v>
       </c>
       <c r="AF251" t="n">
-        <v>23.182</v>
+        <v>23.404</v>
       </c>
       <c r="AG251" t="n">
-        <v>14.949</v>
+        <v>15.043</v>
       </c>
       <c r="AH251" t="n">
-        <v>7.773</v>
+        <v>7.786</v>
       </c>
       <c r="AI251" t="n">
-        <v>4.419</v>
+        <v>4.531</v>
       </c>
       <c r="AJ251" t="n">
-        <v>19.379</v>
+        <v>19.09</v>
       </c>
       <c r="AK251" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AL251" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="252">
@@ -31346,22 +31358,22 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F258" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G258" t="b">
         <v>1</v>
       </c>
       <c r="H258" t="n">
-        <v>1385.873</v>
+        <v>1383.156</v>
       </c>
       <c r="I258" t="n">
-        <v>1.6769</v>
+        <v>1.6922</v>
       </c>
       <c r="J258" t="n">
-        <v>1408.2</v>
+        <v>1408.8</v>
       </c>
       <c r="K258" t="n">
         <v>226</v>
@@ -31382,70 +31394,70 @@
         <v>220</v>
       </c>
       <c r="Q258" t="n">
-        <v>105.678</v>
+        <v>105.206</v>
       </c>
       <c r="R258" t="n">
-        <v>103.433</v>
+        <v>103.403</v>
       </c>
       <c r="S258" t="n">
-        <v>2.245</v>
+        <v>1.804</v>
       </c>
       <c r="T258" t="n">
-        <v>0.28798</v>
+        <v>0.28961</v>
       </c>
       <c r="U258" t="n">
-        <v>0.16373</v>
+        <v>0.16279</v>
       </c>
       <c r="V258" t="n">
-        <v>73.59</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="W258" t="n">
-        <v>72.41</v>
+        <v>72.2</v>
       </c>
       <c r="X258" t="n">
-        <v>0.5909</v>
+        <v>0.5607</v>
       </c>
       <c r="Y258" t="n">
-        <v>25.784</v>
+        <v>25.541</v>
       </c>
       <c r="Z258" t="n">
-        <v>57.773</v>
+        <v>57.856</v>
       </c>
       <c r="AA258" t="n">
-        <v>6.511</v>
+        <v>6.408</v>
       </c>
       <c r="AB258" t="n">
-        <v>20.864</v>
+        <v>20.781</v>
       </c>
       <c r="AC258" t="n">
-        <v>15.511</v>
+        <v>15.615</v>
       </c>
       <c r="AD258" t="n">
-        <v>22.443</v>
+        <v>22.408</v>
       </c>
       <c r="AE258" t="n">
-        <v>9.284000000000001</v>
+        <v>9.438000000000001</v>
       </c>
       <c r="AF258" t="n">
-        <v>22.955</v>
+        <v>23.108</v>
       </c>
       <c r="AG258" t="n">
-        <v>11.83</v>
+        <v>11.661</v>
       </c>
       <c r="AH258" t="n">
-        <v>6.386</v>
+        <v>6.363</v>
       </c>
       <c r="AI258" t="n">
-        <v>3.58</v>
+        <v>3.615</v>
       </c>
       <c r="AJ258" t="n">
-        <v>20.511</v>
+        <v>20.723</v>
       </c>
       <c r="AK258" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="AL258" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="259">
@@ -31466,22 +31478,22 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F259" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G259" t="b">
         <v>1</v>
       </c>
       <c r="H259" t="n">
-        <v>1553.464</v>
+        <v>1555.824</v>
       </c>
       <c r="I259" t="n">
-        <v>2.7763</v>
+        <v>2.5588</v>
       </c>
       <c r="J259" t="n">
-        <v>1530.5</v>
+        <v>1523.7</v>
       </c>
       <c r="K259" t="n">
         <v>115</v>
@@ -31502,70 +31514,70 @@
         <v>118</v>
       </c>
       <c r="Q259" t="n">
-        <v>101.851</v>
+        <v>101.346</v>
       </c>
       <c r="R259" t="n">
-        <v>98.974</v>
+        <v>98.511</v>
       </c>
       <c r="S259" t="n">
-        <v>2.877</v>
+        <v>2.835</v>
       </c>
       <c r="T259" t="n">
-        <v>0.25643</v>
+        <v>0.25528</v>
       </c>
       <c r="U259" t="n">
-        <v>0.16624</v>
+        <v>0.1673</v>
       </c>
       <c r="V259" t="n">
-        <v>70.52</v>
+        <v>69.97</v>
       </c>
       <c r="W259" t="n">
-        <v>68.62</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="X259" t="n">
-        <v>0.5909</v>
+        <v>0.6042</v>
       </c>
       <c r="Y259" t="n">
-        <v>24.739</v>
+        <v>24.595</v>
       </c>
       <c r="Z259" t="n">
-        <v>56.955</v>
+        <v>56.772</v>
       </c>
       <c r="AA259" t="n">
-        <v>7.364</v>
+        <v>7.156</v>
       </c>
       <c r="AB259" t="n">
-        <v>22.182</v>
+        <v>22.121</v>
       </c>
       <c r="AC259" t="n">
-        <v>13.682</v>
+        <v>13.627</v>
       </c>
       <c r="AD259" t="n">
-        <v>19.602</v>
+        <v>19.364</v>
       </c>
       <c r="AE259" t="n">
-        <v>7.75</v>
+        <v>7.726</v>
       </c>
       <c r="AF259" t="n">
-        <v>21.795</v>
+        <v>21.879</v>
       </c>
       <c r="AG259" t="n">
-        <v>12.898</v>
+        <v>12.934</v>
       </c>
       <c r="AH259" t="n">
-        <v>7.773</v>
+        <v>7.802</v>
       </c>
       <c r="AI259" t="n">
-        <v>4.795</v>
+        <v>4.705</v>
       </c>
       <c r="AJ259" t="n">
-        <v>16.989</v>
+        <v>16.913</v>
       </c>
       <c r="AK259" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AL259" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="260">
@@ -31586,22 +31598,22 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F260" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G260" t="b">
         <v>1</v>
       </c>
       <c r="H260" t="n">
-        <v>1668.113</v>
+        <v>1662.011</v>
       </c>
       <c r="I260" t="n">
-        <v>5.3546</v>
+        <v>4.9773</v>
       </c>
       <c r="J260" t="n">
-        <v>1623.2</v>
+        <v>1637.8</v>
       </c>
       <c r="K260" t="n">
         <v>53</v>
@@ -31622,70 +31634,70 @@
         <v>56</v>
       </c>
       <c r="Q260" t="n">
-        <v>106.106</v>
+        <v>105.771</v>
       </c>
       <c r="R260" t="n">
-        <v>97.43300000000001</v>
+        <v>98.03</v>
       </c>
       <c r="S260" t="n">
-        <v>8.672000000000001</v>
+        <v>7.741</v>
       </c>
       <c r="T260" t="n">
-        <v>0.321</v>
+        <v>0.32326</v>
       </c>
       <c r="U260" t="n">
-        <v>0.15897</v>
+        <v>0.15864</v>
       </c>
       <c r="V260" t="n">
-        <v>70.61</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="W260" t="n">
-        <v>64.87</v>
+        <v>65.14</v>
       </c>
       <c r="X260" t="n">
-        <v>0.6708</v>
+        <v>0.6377</v>
       </c>
       <c r="Y260" t="n">
-        <v>25.478</v>
+        <v>25.328</v>
       </c>
       <c r="Z260" t="n">
-        <v>58.116</v>
+        <v>57.977</v>
       </c>
       <c r="AA260" t="n">
-        <v>4.914</v>
+        <v>4.73</v>
       </c>
       <c r="AB260" t="n">
-        <v>15.865</v>
+        <v>15.591</v>
       </c>
       <c r="AC260" t="n">
-        <v>14.745</v>
+        <v>14.907</v>
       </c>
       <c r="AD260" t="n">
-        <v>20.353</v>
+        <v>20.719</v>
       </c>
       <c r="AE260" t="n">
-        <v>11.005</v>
+        <v>11.099</v>
       </c>
       <c r="AF260" t="n">
-        <v>22.276</v>
+        <v>22.255</v>
       </c>
       <c r="AG260" t="n">
-        <v>13.24</v>
+        <v>12.942</v>
       </c>
       <c r="AH260" t="n">
-        <v>9.436</v>
+        <v>9.272</v>
       </c>
       <c r="AI260" t="n">
-        <v>5.687</v>
+        <v>5.658</v>
       </c>
       <c r="AJ260" t="n">
-        <v>18.6</v>
+        <v>18.562</v>
       </c>
       <c r="AK260" t="n">
-        <v>0.8</v>
+        <v>-2</v>
       </c>
       <c r="AL260" t="n">
-        <v>2.1</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="261">
@@ -32066,22 +32078,22 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F264" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G264" t="b">
         <v>1</v>
       </c>
       <c r="H264" t="n">
-        <v>1555.873</v>
+        <v>1548.072</v>
       </c>
       <c r="I264" t="n">
-        <v>0.064</v>
+        <v>0.0533</v>
       </c>
       <c r="J264" t="n">
-        <v>1442.7</v>
+        <v>1442.8</v>
       </c>
       <c r="K264" t="n">
         <v>193</v>
@@ -32102,70 +32114,70 @@
         <v>176</v>
       </c>
       <c r="Q264" t="n">
-        <v>108.582</v>
+        <v>109.756</v>
       </c>
       <c r="R264" t="n">
-        <v>105.031</v>
+        <v>106.668</v>
       </c>
       <c r="S264" t="n">
-        <v>3.551</v>
+        <v>3.088</v>
       </c>
       <c r="T264" t="n">
-        <v>0.21477</v>
+        <v>0.21373</v>
       </c>
       <c r="U264" t="n">
-        <v>0.125</v>
+        <v>0.12862</v>
       </c>
       <c r="V264" t="n">
-        <v>72.79000000000001</v>
+        <v>73.58</v>
       </c>
       <c r="W264" t="n">
-        <v>70.23999999999999</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="X264" t="n">
-        <v>0.6463</v>
+        <v>0.6254</v>
       </c>
       <c r="Y264" t="n">
-        <v>25.755</v>
+        <v>26.005</v>
       </c>
       <c r="Z264" t="n">
-        <v>55.782</v>
+        <v>55.621</v>
       </c>
       <c r="AA264" t="n">
-        <v>6.925</v>
+        <v>7.694</v>
       </c>
       <c r="AB264" t="n">
-        <v>20.571</v>
+        <v>21.618</v>
       </c>
       <c r="AC264" t="n">
-        <v>14.354</v>
+        <v>14.284</v>
       </c>
       <c r="AD264" t="n">
-        <v>21.803</v>
+        <v>21.542</v>
       </c>
       <c r="AE264" t="n">
-        <v>6.98</v>
+        <v>6.922</v>
       </c>
       <c r="AF264" t="n">
-        <v>24.653</v>
+        <v>24.613</v>
       </c>
       <c r="AG264" t="n">
-        <v>11.619</v>
+        <v>12.191</v>
       </c>
       <c r="AH264" t="n">
-        <v>7.898</v>
+        <v>7.81</v>
       </c>
       <c r="AI264" t="n">
-        <v>2.286</v>
+        <v>2.354</v>
       </c>
       <c r="AJ264" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="AK264" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AL264" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="265">
@@ -32306,22 +32318,22 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F266" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G266" t="b">
         <v>1</v>
       </c>
       <c r="H266" t="n">
-        <v>1366.874</v>
+        <v>1364.284</v>
       </c>
       <c r="I266" t="n">
-        <v>-1.4113</v>
+        <v>-1.3372</v>
       </c>
       <c r="J266" t="n">
-        <v>1425.9</v>
+        <v>1423.8</v>
       </c>
       <c r="K266" t="n">
         <v>281</v>
@@ -32342,70 +32354,70 @@
         <v>281</v>
       </c>
       <c r="Q266" t="n">
-        <v>106.99</v>
+        <v>106.478</v>
       </c>
       <c r="R266" t="n">
-        <v>111.667</v>
+        <v>112.075</v>
       </c>
       <c r="S266" t="n">
-        <v>-4.677</v>
+        <v>-5.596</v>
       </c>
       <c r="T266" t="n">
-        <v>0.27211</v>
+        <v>0.27123</v>
       </c>
       <c r="U266" t="n">
-        <v>0.16158</v>
+        <v>0.15848</v>
       </c>
       <c r="V266" t="n">
-        <v>78.48999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="W266" t="n">
-        <v>81.75</v>
+        <v>81.62</v>
       </c>
       <c r="X266" t="n">
-        <v>0.4709</v>
+        <v>0.4432</v>
       </c>
       <c r="Y266" t="n">
-        <v>25.963</v>
+        <v>26.045</v>
       </c>
       <c r="Z266" t="n">
-        <v>58.16</v>
+        <v>58.284</v>
       </c>
       <c r="AA266" t="n">
-        <v>6.681</v>
+        <v>6.727</v>
       </c>
       <c r="AB266" t="n">
-        <v>20.691</v>
+        <v>20.989</v>
       </c>
       <c r="AC266" t="n">
-        <v>19.885</v>
+        <v>19.602</v>
       </c>
       <c r="AD266" t="n">
-        <v>26.626</v>
+        <v>26.227</v>
       </c>
       <c r="AE266" t="n">
-        <v>8.362</v>
+        <v>8.409000000000001</v>
       </c>
       <c r="AF266" t="n">
-        <v>22.166</v>
+        <v>22.5</v>
       </c>
       <c r="AG266" t="n">
-        <v>12.071</v>
+        <v>11.886</v>
       </c>
       <c r="AH266" t="n">
-        <v>6.247</v>
+        <v>6.102</v>
       </c>
       <c r="AI266" t="n">
-        <v>2.577</v>
+        <v>2.636</v>
       </c>
       <c r="AJ266" t="n">
-        <v>15.728</v>
+        <v>16.034</v>
       </c>
       <c r="AK266" t="n">
-        <v>-0.8</v>
+        <v>-3.4</v>
       </c>
       <c r="AL266" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="267">
@@ -32546,22 +32558,22 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F268" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G268" t="b">
         <v>1</v>
       </c>
       <c r="H268" t="n">
-        <v>1407.285</v>
+        <v>1411.637</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6829</v>
+        <v>0.7741</v>
       </c>
       <c r="J268" t="n">
-        <v>1466.3</v>
+        <v>1465.5</v>
       </c>
       <c r="K268" t="n">
         <v>225</v>
@@ -32582,70 +32594,70 @@
         <v>224</v>
       </c>
       <c r="Q268" t="n">
-        <v>105.466</v>
+        <v>105.9</v>
       </c>
       <c r="R268" t="n">
-        <v>107.01</v>
+        <v>107.224</v>
       </c>
       <c r="S268" t="n">
-        <v>-1.544</v>
+        <v>-1.324</v>
       </c>
       <c r="T268" t="n">
-        <v>0.29217</v>
+        <v>0.29545</v>
       </c>
       <c r="U268" t="n">
-        <v>0.17613</v>
+        <v>0.17677</v>
       </c>
       <c r="V268" t="n">
-        <v>73.52</v>
+        <v>73.72</v>
       </c>
       <c r="W268" t="n">
-        <v>74.73999999999999</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="X268" t="n">
-        <v>0.5034</v>
+        <v>0.5192</v>
       </c>
       <c r="Y268" t="n">
-        <v>25.312</v>
+        <v>25.442</v>
       </c>
       <c r="Z268" t="n">
-        <v>56.623</v>
+        <v>56.692</v>
       </c>
       <c r="AA268" t="n">
-        <v>4.861</v>
+        <v>4.756</v>
       </c>
       <c r="AB268" t="n">
-        <v>16.594</v>
+        <v>16.224</v>
       </c>
       <c r="AC268" t="n">
-        <v>18.036</v>
+        <v>17.929</v>
       </c>
       <c r="AD268" t="n">
-        <v>24.367</v>
+        <v>24.135</v>
       </c>
       <c r="AE268" t="n">
-        <v>9.901</v>
+        <v>9.981</v>
       </c>
       <c r="AF268" t="n">
-        <v>23.65</v>
+        <v>23.494</v>
       </c>
       <c r="AG268" t="n">
-        <v>11.291</v>
+        <v>11.288</v>
       </c>
       <c r="AH268" t="n">
-        <v>7.563</v>
+        <v>7.468</v>
       </c>
       <c r="AI268" t="n">
-        <v>3.629</v>
+        <v>3.494</v>
       </c>
       <c r="AJ268" t="n">
-        <v>19.39</v>
+        <v>19.615</v>
       </c>
       <c r="AK268" t="n">
         <v>4.6</v>
       </c>
       <c r="AL268" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="269">
@@ -33146,22 +33158,22 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F273" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G273" t="b">
         <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>1955.26</v>
+        <v>1961.362</v>
       </c>
       <c r="I273" t="n">
-        <v>5.539</v>
+        <v>5.5897</v>
       </c>
       <c r="J273" t="n">
-        <v>1679.7</v>
+        <v>1680.5</v>
       </c>
       <c r="K273" t="n">
         <v>21</v>
@@ -33182,70 +33194,70 @@
         <v>22</v>
       </c>
       <c r="Q273" t="n">
-        <v>113.733</v>
+        <v>113.791</v>
       </c>
       <c r="R273" t="n">
-        <v>98.581</v>
+        <v>98.702</v>
       </c>
       <c r="S273" t="n">
-        <v>15.153</v>
+        <v>15.089</v>
       </c>
       <c r="T273" t="n">
-        <v>0.32676</v>
+        <v>0.32376</v>
       </c>
       <c r="U273" t="n">
-        <v>0.14108</v>
+        <v>0.14184</v>
       </c>
       <c r="V273" t="n">
-        <v>82.09</v>
+        <v>81.78</v>
       </c>
       <c r="W273" t="n">
-        <v>70.72</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="X273" t="n">
-        <v>0.8021</v>
+        <v>0.8083</v>
       </c>
       <c r="Y273" t="n">
-        <v>27.946</v>
+        <v>27.885</v>
       </c>
       <c r="Z273" t="n">
-        <v>62.042</v>
+        <v>61.583</v>
       </c>
       <c r="AA273" t="n">
-        <v>7.055</v>
+        <v>7.064</v>
       </c>
       <c r="AB273" t="n">
-        <v>21.007</v>
+        <v>20.894</v>
       </c>
       <c r="AC273" t="n">
-        <v>19.145</v>
+        <v>18.942</v>
       </c>
       <c r="AD273" t="n">
-        <v>26.289</v>
+        <v>26.185</v>
       </c>
       <c r="AE273" t="n">
-        <v>11.735</v>
+        <v>11.546</v>
       </c>
       <c r="AF273" t="n">
-        <v>24.538</v>
+        <v>24.428</v>
       </c>
       <c r="AG273" t="n">
-        <v>16.426</v>
+        <v>16.351</v>
       </c>
       <c r="AH273" t="n">
-        <v>7.967</v>
+        <v>7.843</v>
       </c>
       <c r="AI273" t="n">
-        <v>4.759</v>
+        <v>4.818</v>
       </c>
       <c r="AJ273" t="n">
-        <v>17.18</v>
+        <v>17.297</v>
       </c>
       <c r="AK273" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AL273" t="n">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="274">
@@ -33626,22 +33638,22 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F277" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G277" t="b">
         <v>1</v>
       </c>
       <c r="H277" t="n">
-        <v>1438.465</v>
+        <v>1434.31</v>
       </c>
       <c r="I277" t="n">
-        <v>2.724</v>
+        <v>2.6599</v>
       </c>
       <c r="J277" t="n">
-        <v>1429</v>
+        <v>1428.7</v>
       </c>
       <c r="K277" t="n">
         <v>239</v>
@@ -33662,70 +33674,70 @@
         <v>225</v>
       </c>
       <c r="Q277" t="n">
-        <v>106.102</v>
+        <v>105.202</v>
       </c>
       <c r="R277" t="n">
-        <v>104.562</v>
+        <v>105.17</v>
       </c>
       <c r="S277" t="n">
-        <v>1.54</v>
+        <v>0.033</v>
       </c>
       <c r="T277" t="n">
-        <v>0.37335</v>
+        <v>0.37658</v>
       </c>
       <c r="U277" t="n">
-        <v>0.16494</v>
+        <v>0.16475</v>
       </c>
       <c r="V277" t="n">
-        <v>69.67</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="W277" t="n">
-        <v>68.75</v>
+        <v>69.12</v>
       </c>
       <c r="X277" t="n">
-        <v>0.5971</v>
+        <v>0.5657</v>
       </c>
       <c r="Y277" t="n">
-        <v>23.634</v>
+        <v>23.783</v>
       </c>
       <c r="Z277" t="n">
-        <v>58.267</v>
+        <v>58.535</v>
       </c>
       <c r="AA277" t="n">
-        <v>7.026</v>
+        <v>7.035</v>
       </c>
       <c r="AB277" t="n">
-        <v>22.641</v>
+        <v>22.535</v>
       </c>
       <c r="AC277" t="n">
-        <v>15.374</v>
+        <v>15.333</v>
       </c>
       <c r="AD277" t="n">
-        <v>20.714</v>
+        <v>20.833</v>
       </c>
       <c r="AE277" t="n">
-        <v>12.418</v>
+        <v>12.742</v>
       </c>
       <c r="AF277" t="n">
-        <v>20.652</v>
+        <v>20.838</v>
       </c>
       <c r="AG277" t="n">
-        <v>12.509</v>
+        <v>12.641</v>
       </c>
       <c r="AH277" t="n">
-        <v>8.821</v>
+        <v>8.859</v>
       </c>
       <c r="AI277" t="n">
-        <v>3.718</v>
+        <v>3.672</v>
       </c>
       <c r="AJ277" t="n">
-        <v>20.022</v>
+        <v>19.697</v>
       </c>
       <c r="AK277" t="n">
-        <v>1.8</v>
+        <v>-3.8</v>
       </c>
       <c r="AL277" t="n">
-        <v>1.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="278">
@@ -33866,22 +33878,22 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F279" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G279" t="b">
         <v>1</v>
       </c>
       <c r="H279" t="n">
-        <v>1302.303</v>
+        <v>1300.858</v>
       </c>
       <c r="I279" t="n">
-        <v>-1.2838</v>
+        <v>-1.2051</v>
       </c>
       <c r="J279" t="n">
-        <v>1409.6</v>
+        <v>1413.5</v>
       </c>
       <c r="K279" t="n">
         <v>317</v>
@@ -33902,70 +33914,70 @@
         <v>320</v>
       </c>
       <c r="Q279" t="n">
-        <v>107.05</v>
+        <v>106.156</v>
       </c>
       <c r="R279" t="n">
-        <v>118.1</v>
+        <v>117.884</v>
       </c>
       <c r="S279" t="n">
-        <v>-11.05</v>
+        <v>-11.728</v>
       </c>
       <c r="T279" t="n">
-        <v>0.27324</v>
+        <v>0.26966</v>
       </c>
       <c r="U279" t="n">
-        <v>0.17823</v>
+        <v>0.1777</v>
       </c>
       <c r="V279" t="n">
-        <v>72.62</v>
+        <v>71.77</v>
       </c>
       <c r="W279" t="n">
-        <v>80.23999999999999</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="X279" t="n">
-        <v>0.3432</v>
+        <v>0.3182</v>
       </c>
       <c r="Y279" t="n">
-        <v>25.08</v>
+        <v>24.973</v>
       </c>
       <c r="Z279" t="n">
-        <v>55.66</v>
+        <v>55.577</v>
       </c>
       <c r="AA279" t="n">
-        <v>9.010999999999999</v>
+        <v>8.923</v>
       </c>
       <c r="AB279" t="n">
-        <v>24.865</v>
+        <v>24.886</v>
       </c>
       <c r="AC279" t="n">
-        <v>12.69</v>
+        <v>12.395</v>
       </c>
       <c r="AD279" t="n">
-        <v>18.397</v>
+        <v>17.914</v>
       </c>
       <c r="AE279" t="n">
-        <v>7.905</v>
+        <v>7.8</v>
       </c>
       <c r="AF279" t="n">
-        <v>21.296</v>
+        <v>21.377</v>
       </c>
       <c r="AG279" t="n">
-        <v>14.576</v>
+        <v>14.573</v>
       </c>
       <c r="AH279" t="n">
-        <v>5.857</v>
+        <v>5.995</v>
       </c>
       <c r="AI279" t="n">
-        <v>2.048</v>
+        <v>2.032</v>
       </c>
       <c r="AJ279" t="n">
-        <v>15.409</v>
+        <v>15.473</v>
       </c>
       <c r="AK279" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AL279" t="n">
-        <v>-1.2</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="280">
@@ -34706,22 +34718,22 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F286" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G286" t="b">
         <v>1</v>
       </c>
       <c r="H286" t="n">
-        <v>1458.771</v>
+        <v>1463.452</v>
       </c>
       <c r="I286" t="n">
-        <v>3.5917</v>
+        <v>3.459</v>
       </c>
       <c r="J286" t="n">
-        <v>1406.4</v>
+        <v>1408.1</v>
       </c>
       <c r="K286" t="n">
         <v>207</v>
@@ -34742,70 +34754,70 @@
         <v>191</v>
       </c>
       <c r="Q286" t="n">
-        <v>108.599</v>
+        <v>108.827</v>
       </c>
       <c r="R286" t="n">
-        <v>103.648</v>
+        <v>103.433</v>
       </c>
       <c r="S286" t="n">
-        <v>4.951</v>
+        <v>5.394</v>
       </c>
       <c r="T286" t="n">
-        <v>0.3274</v>
+        <v>0.32861</v>
       </c>
       <c r="U286" t="n">
-        <v>0.15664</v>
+        <v>0.16015</v>
       </c>
       <c r="V286" t="n">
-        <v>77.79000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="W286" t="n">
-        <v>74.59999999999999</v>
+        <v>74.02</v>
       </c>
       <c r="X286" t="n">
-        <v>0.6696</v>
+        <v>0.6812</v>
       </c>
       <c r="Y286" t="n">
-        <v>27.771</v>
+        <v>27.7</v>
       </c>
       <c r="Z286" t="n">
-        <v>62.129</v>
+        <v>61.837</v>
       </c>
       <c r="AA286" t="n">
-        <v>5.955</v>
+        <v>6.095</v>
       </c>
       <c r="AB286" t="n">
-        <v>18.652</v>
+        <v>18.812</v>
       </c>
       <c r="AC286" t="n">
-        <v>16.297</v>
+        <v>15.963</v>
       </c>
       <c r="AD286" t="n">
-        <v>21.455</v>
+        <v>20.966</v>
       </c>
       <c r="AE286" t="n">
-        <v>11.082</v>
+        <v>11.158</v>
       </c>
       <c r="AF286" t="n">
-        <v>22.521</v>
+        <v>22.548</v>
       </c>
       <c r="AG286" t="n">
-        <v>12.524</v>
+        <v>12.575</v>
       </c>
       <c r="AH286" t="n">
-        <v>9.218999999999999</v>
+        <v>9.134</v>
       </c>
       <c r="AI286" t="n">
-        <v>3.65</v>
+        <v>3.646</v>
       </c>
       <c r="AJ286" t="n">
-        <v>18.829</v>
+        <v>18.546</v>
       </c>
       <c r="AK286" t="n">
-        <v>12.2</v>
+        <v>16.4</v>
       </c>
       <c r="AL286" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="287">
@@ -35186,22 +35198,22 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F290" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G290" t="b">
         <v>1</v>
       </c>
       <c r="H290" t="n">
-        <v>1450.753</v>
+        <v>1446.401</v>
       </c>
       <c r="I290" t="n">
-        <v>0.1677</v>
+        <v>0.317</v>
       </c>
       <c r="J290" t="n">
-        <v>1427.4</v>
+        <v>1425.5</v>
       </c>
       <c r="K290" t="n">
         <v>242</v>
@@ -35222,70 +35234,70 @@
         <v>236</v>
       </c>
       <c r="Q290" t="n">
-        <v>105.183</v>
+        <v>105.609</v>
       </c>
       <c r="R290" t="n">
-        <v>105.631</v>
+        <v>106.374</v>
       </c>
       <c r="S290" t="n">
-        <v>-0.448</v>
+        <v>-0.765</v>
       </c>
       <c r="T290" t="n">
-        <v>0.30195</v>
+        <v>0.29987</v>
       </c>
       <c r="U290" t="n">
-        <v>0.17846</v>
+        <v>0.17807</v>
       </c>
       <c r="V290" t="n">
-        <v>71.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="W290" t="n">
-        <v>72</v>
+        <v>72.61</v>
       </c>
       <c r="X290" t="n">
-        <v>0.5918</v>
+        <v>0.5596</v>
       </c>
       <c r="Y290" t="n">
-        <v>26.177</v>
+        <v>26.152</v>
       </c>
       <c r="Z290" t="n">
-        <v>56.986</v>
+        <v>56.611</v>
       </c>
       <c r="AA290" t="n">
-        <v>4.599</v>
+        <v>4.547</v>
       </c>
       <c r="AB290" t="n">
-        <v>14.272</v>
+        <v>14.056</v>
       </c>
       <c r="AC290" t="n">
-        <v>14.646</v>
+        <v>15.328</v>
       </c>
       <c r="AD290" t="n">
-        <v>19.354</v>
+        <v>20.213</v>
       </c>
       <c r="AE290" t="n">
-        <v>9.605</v>
+        <v>9.489000000000001</v>
       </c>
       <c r="AF290" t="n">
-        <v>22.136</v>
+        <v>22.041</v>
       </c>
       <c r="AG290" t="n">
-        <v>12.673</v>
+        <v>12.464</v>
       </c>
       <c r="AH290" t="n">
-        <v>8.007</v>
+        <v>7.897</v>
       </c>
       <c r="AI290" t="n">
-        <v>3.735</v>
+        <v>3.724</v>
       </c>
       <c r="AJ290" t="n">
-        <v>18.014</v>
+        <v>17.864</v>
       </c>
       <c r="AK290" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="AL290" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="291">
@@ -35426,22 +35438,22 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F292" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G292" t="b">
         <v>1</v>
       </c>
       <c r="H292" t="n">
-        <v>1455.888</v>
+        <v>1451.207</v>
       </c>
       <c r="I292" t="n">
-        <v>0.9448</v>
+        <v>0.872</v>
       </c>
       <c r="J292" t="n">
-        <v>1373.6</v>
+        <v>1377.9</v>
       </c>
       <c r="K292" t="n">
         <v>217</v>
@@ -35462,70 +35474,70 @@
         <v>199</v>
       </c>
       <c r="Q292" t="n">
-        <v>103.958</v>
+        <v>103.339</v>
       </c>
       <c r="R292" t="n">
-        <v>98.19799999999999</v>
+        <v>98.69799999999999</v>
       </c>
       <c r="S292" t="n">
-        <v>5.761</v>
+        <v>4.641</v>
       </c>
       <c r="T292" t="n">
-        <v>0.32644</v>
+        <v>0.3304</v>
       </c>
       <c r="U292" t="n">
-        <v>0.20132</v>
+        <v>0.20282</v>
       </c>
       <c r="V292" t="n">
-        <v>68.25</v>
+        <v>67.72</v>
       </c>
       <c r="W292" t="n">
-        <v>64.56999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="X292" t="n">
-        <v>0.6584</v>
+        <v>0.6279</v>
       </c>
       <c r="Y292" t="n">
-        <v>23.025</v>
+        <v>22.95</v>
       </c>
       <c r="Z292" t="n">
-        <v>55.258</v>
+        <v>55.273</v>
       </c>
       <c r="AA292" t="n">
-        <v>7.898</v>
+        <v>7.901</v>
       </c>
       <c r="AB292" t="n">
-        <v>25.994</v>
+        <v>26.05</v>
       </c>
       <c r="AC292" t="n">
-        <v>14.307</v>
+        <v>13.922</v>
       </c>
       <c r="AD292" t="n">
-        <v>21.109</v>
+        <v>20.549</v>
       </c>
       <c r="AE292" t="n">
-        <v>12.053</v>
+        <v>12.033</v>
       </c>
       <c r="AF292" t="n">
-        <v>24.009</v>
+        <v>23.667</v>
       </c>
       <c r="AG292" t="n">
-        <v>12.898</v>
+        <v>12.901</v>
       </c>
       <c r="AH292" t="n">
-        <v>8.143000000000001</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="AI292" t="n">
-        <v>4.127</v>
+        <v>4.091</v>
       </c>
       <c r="AJ292" t="n">
-        <v>17.407</v>
+        <v>17.138</v>
       </c>
       <c r="AK292" t="n">
-        <v>-2.4</v>
+        <v>-4.4</v>
       </c>
       <c r="AL292" t="n">
-        <v>1.1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="293">
@@ -35546,22 +35558,22 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F293" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G293" t="b">
         <v>1</v>
       </c>
       <c r="H293" t="n">
-        <v>1452.353</v>
+        <v>1454.799</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.6824</v>
+        <v>-0.6694</v>
       </c>
       <c r="J293" t="n">
-        <v>1505</v>
+        <v>1496.5</v>
       </c>
       <c r="K293" t="n">
         <v>145</v>
@@ -35582,70 +35594,70 @@
         <v>153</v>
       </c>
       <c r="Q293" t="n">
-        <v>113.627</v>
+        <v>115.343</v>
       </c>
       <c r="R293" t="n">
-        <v>111.286</v>
+        <v>111.66</v>
       </c>
       <c r="S293" t="n">
-        <v>2.341</v>
+        <v>3.683</v>
       </c>
       <c r="T293" t="n">
-        <v>0.29463</v>
+        <v>0.29817</v>
       </c>
       <c r="U293" t="n">
-        <v>0.14118</v>
+        <v>0.13885</v>
       </c>
       <c r="V293" t="n">
-        <v>79.34</v>
+        <v>80.27</v>
       </c>
       <c r="W293" t="n">
-        <v>77.73999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="X293" t="n">
-        <v>0.4938</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="Y293" t="n">
-        <v>28.966</v>
+        <v>29.341</v>
       </c>
       <c r="Z293" t="n">
-        <v>60.792</v>
+        <v>60.818</v>
       </c>
       <c r="AA293" t="n">
-        <v>6.988</v>
+        <v>7.227</v>
       </c>
       <c r="AB293" t="n">
-        <v>19.483</v>
+        <v>19.67</v>
       </c>
       <c r="AC293" t="n">
-        <v>14.416</v>
+        <v>14.364</v>
       </c>
       <c r="AD293" t="n">
-        <v>18.861</v>
+        <v>18.886</v>
       </c>
       <c r="AE293" t="n">
-        <v>9.153</v>
+        <v>9.182</v>
       </c>
       <c r="AF293" t="n">
-        <v>21.261</v>
+        <v>21.023</v>
       </c>
       <c r="AG293" t="n">
-        <v>14.988</v>
+        <v>15.5</v>
       </c>
       <c r="AH293" t="n">
-        <v>7.674</v>
+        <v>7.67</v>
       </c>
       <c r="AI293" t="n">
-        <v>2.834</v>
+        <v>2.818</v>
       </c>
       <c r="AJ293" t="n">
-        <v>15.434</v>
+        <v>15.216</v>
       </c>
       <c r="AK293" t="n">
-        <v>5.8</v>
+        <v>11.8</v>
       </c>
       <c r="AL293" t="n">
-        <v>4.3</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="294">
@@ -36866,22 +36878,22 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F304" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G304" t="b">
         <v>1</v>
       </c>
       <c r="H304" t="n">
-        <v>1838.194</v>
+        <v>1820.485</v>
       </c>
       <c r="I304" t="n">
-        <v>7.6713</v>
+        <v>7.025</v>
       </c>
       <c r="J304" t="n">
-        <v>1687.7</v>
+        <v>1687.9</v>
       </c>
       <c r="K304" t="n">
         <v>48</v>
@@ -36902,70 +36914,70 @@
         <v>46</v>
       </c>
       <c r="Q304" t="n">
-        <v>115.827</v>
+        <v>114.766</v>
       </c>
       <c r="R304" t="n">
-        <v>110.451</v>
+        <v>110.491</v>
       </c>
       <c r="S304" t="n">
-        <v>5.375</v>
+        <v>4.275</v>
       </c>
       <c r="T304" t="n">
-        <v>0.30925</v>
+        <v>0.31151</v>
       </c>
       <c r="U304" t="n">
-        <v>0.15406</v>
+        <v>0.1546</v>
       </c>
       <c r="V304" t="n">
-        <v>83.18000000000001</v>
+        <v>81.95</v>
       </c>
       <c r="W304" t="n">
-        <v>79.33</v>
+        <v>78.81</v>
       </c>
       <c r="X304" t="n">
-        <v>0.6803</v>
+        <v>0.6583</v>
       </c>
       <c r="Y304" t="n">
-        <v>29.959</v>
+        <v>29.661</v>
       </c>
       <c r="Z304" t="n">
-        <v>62.755</v>
+        <v>62.671</v>
       </c>
       <c r="AA304" t="n">
-        <v>8.327</v>
+        <v>8.102</v>
       </c>
       <c r="AB304" t="n">
-        <v>21.83</v>
+        <v>21.563</v>
       </c>
       <c r="AC304" t="n">
-        <v>14.939</v>
+        <v>14.522</v>
       </c>
       <c r="AD304" t="n">
-        <v>19.864</v>
+        <v>19.448</v>
       </c>
       <c r="AE304" t="n">
-        <v>10.721</v>
+        <v>10.886</v>
       </c>
       <c r="AF304" t="n">
-        <v>23.245</v>
+        <v>23.334</v>
       </c>
       <c r="AG304" t="n">
-        <v>16.381</v>
+        <v>16.031</v>
       </c>
       <c r="AH304" t="n">
-        <v>5.687</v>
+        <v>5.671</v>
       </c>
       <c r="AI304" t="n">
-        <v>3.068</v>
+        <v>3.02</v>
       </c>
       <c r="AJ304" t="n">
-        <v>17.463</v>
+        <v>17.375</v>
       </c>
       <c r="AK304" t="n">
-        <v>3.6</v>
+        <v>-1.6</v>
       </c>
       <c r="AL304" t="n">
-        <v>-2.2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="305">
@@ -37466,22 +37478,22 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F309" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G309" t="b">
         <v>1</v>
       </c>
       <c r="H309" t="n">
-        <v>1374.882</v>
+        <v>1383.4</v>
       </c>
       <c r="I309" t="n">
-        <v>-4.2989</v>
+        <v>-4.0778</v>
       </c>
       <c r="J309" t="n">
-        <v>1418.9</v>
+        <v>1419.1</v>
       </c>
       <c r="K309" t="n">
         <v>253</v>
@@ -37502,70 +37514,70 @@
         <v>242</v>
       </c>
       <c r="Q309" t="n">
-        <v>106.515</v>
+        <v>106.701</v>
       </c>
       <c r="R309" t="n">
-        <v>110.312</v>
+        <v>109.859</v>
       </c>
       <c r="S309" t="n">
-        <v>-3.796</v>
+        <v>-3.159</v>
       </c>
       <c r="T309" t="n">
-        <v>0.28869</v>
+        <v>0.28374</v>
       </c>
       <c r="U309" t="n">
-        <v>0.15963</v>
+        <v>0.16049</v>
       </c>
       <c r="V309" t="n">
-        <v>71.48999999999999</v>
+        <v>72.09</v>
       </c>
       <c r="W309" t="n">
-        <v>74.09999999999999</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="X309" t="n">
-        <v>0.4019</v>
+        <v>0.4356</v>
       </c>
       <c r="Y309" t="n">
-        <v>25.16</v>
+        <v>25.093</v>
       </c>
       <c r="Z309" t="n">
-        <v>55.744</v>
+        <v>55.563</v>
       </c>
       <c r="AA309" t="n">
-        <v>6.448</v>
+        <v>6.649</v>
       </c>
       <c r="AB309" t="n">
-        <v>18.438</v>
+        <v>18.804</v>
       </c>
       <c r="AC309" t="n">
-        <v>14.725</v>
+        <v>15.254</v>
       </c>
       <c r="AD309" t="n">
-        <v>21.66</v>
+        <v>22.399</v>
       </c>
       <c r="AE309" t="n">
-        <v>8.867000000000001</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="AF309" t="n">
-        <v>21.631</v>
+        <v>21.778</v>
       </c>
       <c r="AG309" t="n">
-        <v>10.142</v>
+        <v>10.224</v>
       </c>
       <c r="AH309" t="n">
-        <v>5.279</v>
+        <v>5.235</v>
       </c>
       <c r="AI309" t="n">
-        <v>3.608</v>
+        <v>3.647</v>
       </c>
       <c r="AJ309" t="n">
-        <v>18.15</v>
+        <v>18.439</v>
       </c>
       <c r="AK309" t="n">
-        <v>-7.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AL309" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="310">
@@ -37586,22 +37598,22 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F310" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G310" t="b">
         <v>1</v>
       </c>
       <c r="H310" t="n">
-        <v>1366.304</v>
+        <v>1371.535</v>
       </c>
       <c r="I310" t="n">
-        <v>-2.841</v>
+        <v>-2.6983</v>
       </c>
       <c r="J310" t="n">
-        <v>1427.7</v>
+        <v>1418.4</v>
       </c>
       <c r="K310" t="n">
         <v>304</v>
@@ -37622,70 +37634,70 @@
         <v>298</v>
       </c>
       <c r="Q310" t="n">
-        <v>109.536</v>
+        <v>110.379</v>
       </c>
       <c r="R310" t="n">
-        <v>118.142</v>
+        <v>117.512</v>
       </c>
       <c r="S310" t="n">
-        <v>-8.606</v>
+        <v>-7.133</v>
       </c>
       <c r="T310" t="n">
-        <v>0.26704</v>
+        <v>0.27244</v>
       </c>
       <c r="U310" t="n">
-        <v>0.14401</v>
+        <v>0.14413</v>
       </c>
       <c r="V310" t="n">
-        <v>76.51000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="W310" t="n">
-        <v>82.76000000000001</v>
+        <v>82.09</v>
       </c>
       <c r="X310" t="n">
-        <v>0.3732</v>
+        <v>0.4089</v>
       </c>
       <c r="Y310" t="n">
-        <v>25.559</v>
+        <v>25.954</v>
       </c>
       <c r="Z310" t="n">
-        <v>57.571</v>
+        <v>57.984</v>
       </c>
       <c r="AA310" t="n">
-        <v>8.387</v>
+        <v>8.233000000000001</v>
       </c>
       <c r="AB310" t="n">
-        <v>23.054</v>
+        <v>23.099</v>
       </c>
       <c r="AC310" t="n">
-        <v>17.002</v>
+        <v>16.7</v>
       </c>
       <c r="AD310" t="n">
-        <v>24.341</v>
+        <v>23.695</v>
       </c>
       <c r="AE310" t="n">
-        <v>8.339</v>
+        <v>8.662000000000001</v>
       </c>
       <c r="AF310" t="n">
-        <v>22.914</v>
+        <v>22.997</v>
       </c>
       <c r="AG310" t="n">
-        <v>11.95</v>
+        <v>12.3</v>
       </c>
       <c r="AH310" t="n">
-        <v>5.557</v>
+        <v>5.54</v>
       </c>
       <c r="AI310" t="n">
-        <v>1.762</v>
+        <v>1.818</v>
       </c>
       <c r="AJ310" t="n">
-        <v>16.446</v>
+        <v>16.383</v>
       </c>
       <c r="AK310" t="n">
-        <v>-4</v>
+        <v>-3.2</v>
       </c>
       <c r="AL310" t="n">
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="311">
@@ -37826,22 +37838,22 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F312" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G312" t="b">
         <v>1</v>
       </c>
       <c r="H312" t="n">
-        <v>1651.123</v>
+        <v>1644.594</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4503</v>
+        <v>1.6162</v>
       </c>
       <c r="J312" t="n">
-        <v>1619.2</v>
+        <v>1623.2</v>
       </c>
       <c r="K312" t="n">
         <v>120</v>
@@ -37862,70 +37874,70 @@
         <v>126</v>
       </c>
       <c r="Q312" t="n">
-        <v>112.07</v>
+        <v>112.135</v>
       </c>
       <c r="R312" t="n">
-        <v>110.89</v>
+        <v>111.678</v>
       </c>
       <c r="S312" t="n">
-        <v>1.18</v>
+        <v>0.457</v>
       </c>
       <c r="T312" t="n">
-        <v>0.29398</v>
+        <v>0.29405</v>
       </c>
       <c r="U312" t="n">
-        <v>0.16157</v>
+        <v>0.15977</v>
       </c>
       <c r="V312" t="n">
-        <v>79.89</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="W312" t="n">
-        <v>79.34999999999999</v>
+        <v>79.98</v>
       </c>
       <c r="X312" t="n">
-        <v>0.5238</v>
+        <v>0.4937</v>
       </c>
       <c r="Y312" t="n">
-        <v>27.844</v>
+        <v>27.861</v>
       </c>
       <c r="Z312" t="n">
-        <v>58.762</v>
+        <v>58.906</v>
       </c>
       <c r="AA312" t="n">
-        <v>7.313</v>
+        <v>7.4</v>
       </c>
       <c r="AB312" t="n">
-        <v>20.918</v>
+        <v>20.959</v>
       </c>
       <c r="AC312" t="n">
-        <v>16.891</v>
+        <v>16.889</v>
       </c>
       <c r="AD312" t="n">
-        <v>24.483</v>
+        <v>24.469</v>
       </c>
       <c r="AE312" t="n">
-        <v>9.653</v>
+        <v>9.613</v>
       </c>
       <c r="AF312" t="n">
-        <v>22.741</v>
+        <v>22.625</v>
       </c>
       <c r="AG312" t="n">
-        <v>14.367</v>
+        <v>14.309</v>
       </c>
       <c r="AH312" t="n">
-        <v>7.435</v>
+        <v>7.461</v>
       </c>
       <c r="AI312" t="n">
-        <v>4.381</v>
+        <v>4.284</v>
       </c>
       <c r="AJ312" t="n">
-        <v>21.83</v>
+        <v>21.674</v>
       </c>
       <c r="AK312" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AL312" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="313">
@@ -38786,22 +38798,22 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F320" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G320" t="b">
         <v>1</v>
       </c>
       <c r="H320" t="n">
-        <v>1727.947</v>
+        <v>1739.907</v>
       </c>
       <c r="I320" t="n">
-        <v>2.9027</v>
+        <v>2.9764</v>
       </c>
       <c r="J320" t="n">
-        <v>1551.3</v>
+        <v>1554.6</v>
       </c>
       <c r="K320" t="n">
         <v>45</v>
@@ -38822,70 +38834,70 @@
         <v>47</v>
       </c>
       <c r="Q320" t="n">
-        <v>118.559</v>
+        <v>118.458</v>
       </c>
       <c r="R320" t="n">
-        <v>103.741</v>
+        <v>103.761</v>
       </c>
       <c r="S320" t="n">
-        <v>14.818</v>
+        <v>14.697</v>
       </c>
       <c r="T320" t="n">
-        <v>0.30399</v>
+        <v>0.29792</v>
       </c>
       <c r="U320" t="n">
-        <v>0.15046</v>
+        <v>0.14971</v>
       </c>
       <c r="V320" t="n">
-        <v>82.73999999999999</v>
+        <v>82.25</v>
       </c>
       <c r="W320" t="n">
-        <v>72.44</v>
+        <v>72.08</v>
       </c>
       <c r="X320" t="n">
-        <v>0.7696</v>
+        <v>0.7768</v>
       </c>
       <c r="Y320" t="n">
-        <v>26.929</v>
+        <v>26.881</v>
       </c>
       <c r="Z320" t="n">
-        <v>58.39</v>
+        <v>58.11</v>
       </c>
       <c r="AA320" t="n">
-        <v>9.403</v>
+        <v>9.371</v>
       </c>
       <c r="AB320" t="n">
-        <v>25.892</v>
+        <v>25.751</v>
       </c>
       <c r="AC320" t="n">
-        <v>19.476</v>
+        <v>19.119</v>
       </c>
       <c r="AD320" t="n">
-        <v>26.32</v>
+        <v>25.817</v>
       </c>
       <c r="AE320" t="n">
-        <v>10.56</v>
+        <v>10.325</v>
       </c>
       <c r="AF320" t="n">
-        <v>24.041</v>
+        <v>24.107</v>
       </c>
       <c r="AG320" t="n">
-        <v>14.15</v>
+        <v>14.168</v>
       </c>
       <c r="AH320" t="n">
-        <v>7.423</v>
+        <v>7.359</v>
       </c>
       <c r="AI320" t="n">
-        <v>4.469</v>
+        <v>4.348</v>
       </c>
       <c r="AJ320" t="n">
-        <v>17.663</v>
+        <v>17.519</v>
       </c>
       <c r="AK320" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AL320" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="321">
@@ -38906,22 +38918,22 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F321" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G321" t="b">
         <v>1</v>
       </c>
       <c r="H321" t="n">
-        <v>1460.92</v>
+        <v>1456.825</v>
       </c>
       <c r="I321" t="n">
-        <v>0.7665</v>
+        <v>0.8941</v>
       </c>
       <c r="J321" t="n">
-        <v>1518.4</v>
+        <v>1523.8</v>
       </c>
       <c r="K321" t="n">
         <v>152</v>
@@ -38942,70 +38954,70 @@
         <v>155</v>
       </c>
       <c r="Q321" t="n">
-        <v>105.92</v>
+        <v>105.545</v>
       </c>
       <c r="R321" t="n">
-        <v>106.149</v>
+        <v>106.076</v>
       </c>
       <c r="S321" t="n">
-        <v>-0.229</v>
+        <v>-0.531</v>
       </c>
       <c r="T321" t="n">
-        <v>0.3118</v>
+        <v>0.30908</v>
       </c>
       <c r="U321" t="n">
-        <v>0.14646</v>
+        <v>0.14964</v>
       </c>
       <c r="V321" t="n">
-        <v>70.68000000000001</v>
+        <v>71.33</v>
       </c>
       <c r="W321" t="n">
-        <v>71.18000000000001</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="X321" t="n">
-        <v>0.5536</v>
+        <v>0.5255</v>
       </c>
       <c r="Y321" t="n">
-        <v>23.806</v>
+        <v>24.012</v>
       </c>
       <c r="Z321" t="n">
-        <v>57.606</v>
+        <v>58.004</v>
       </c>
       <c r="AA321" t="n">
-        <v>7.203</v>
+        <v>7.227</v>
       </c>
       <c r="AB321" t="n">
-        <v>21.278</v>
+        <v>21.331</v>
       </c>
       <c r="AC321" t="n">
-        <v>15.87</v>
+        <v>16.074</v>
       </c>
       <c r="AD321" t="n">
-        <v>22.446</v>
+        <v>22.683</v>
       </c>
       <c r="AE321" t="n">
-        <v>10.325</v>
+        <v>10.331</v>
       </c>
       <c r="AF321" t="n">
-        <v>22.507</v>
+        <v>22.859</v>
       </c>
       <c r="AG321" t="n">
-        <v>11.458</v>
+        <v>11.766</v>
       </c>
       <c r="AH321" t="n">
-        <v>5.864</v>
+        <v>5.929</v>
       </c>
       <c r="AI321" t="n">
-        <v>3.617</v>
+        <v>3.587</v>
       </c>
       <c r="AJ321" t="n">
-        <v>17.58</v>
+        <v>18.077</v>
       </c>
       <c r="AK321" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="AL321" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="322">
@@ -39626,22 +39638,22 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F327" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G327" t="b">
         <v>1</v>
       </c>
       <c r="H327" t="n">
-        <v>1236.891</v>
+        <v>1235.224</v>
       </c>
       <c r="I327" t="n">
-        <v>-3.5993</v>
+        <v>-3.5074</v>
       </c>
       <c r="J327" t="n">
-        <v>1431.8</v>
+        <v>1429.4</v>
       </c>
       <c r="K327" t="n">
         <v>360</v>
@@ -39662,70 +39674,70 @@
         <v>358</v>
       </c>
       <c r="Q327" t="n">
-        <v>101.537</v>
+        <v>101.269</v>
       </c>
       <c r="R327" t="n">
-        <v>123.366</v>
+        <v>123.196</v>
       </c>
       <c r="S327" t="n">
-        <v>-21.829</v>
+        <v>-21.927</v>
       </c>
       <c r="T327" t="n">
-        <v>0.29602</v>
+        <v>0.29837</v>
       </c>
       <c r="U327" t="n">
-        <v>0.14048</v>
+        <v>0.14332</v>
       </c>
       <c r="V327" t="n">
-        <v>68.59</v>
+        <v>68.5</v>
       </c>
       <c r="W327" t="n">
-        <v>83.19</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="X327" t="n">
-        <v>0.1056</v>
+        <v>0.102</v>
       </c>
       <c r="Y327" t="n">
-        <v>22.833</v>
+        <v>22.891</v>
       </c>
       <c r="Z327" t="n">
-        <v>58.446</v>
+        <v>58.469</v>
       </c>
       <c r="AA327" t="n">
-        <v>9.904</v>
+        <v>9.864000000000001</v>
       </c>
       <c r="AB327" t="n">
-        <v>31.456</v>
+        <v>31.293</v>
       </c>
       <c r="AC327" t="n">
-        <v>13.015</v>
+        <v>12.857</v>
       </c>
       <c r="AD327" t="n">
-        <v>18.009</v>
+        <v>17.823</v>
       </c>
       <c r="AE327" t="n">
-        <v>8.346</v>
+        <v>8.401</v>
       </c>
       <c r="AF327" t="n">
-        <v>19.954</v>
+        <v>19.85</v>
       </c>
       <c r="AG327" t="n">
-        <v>11.528</v>
+        <v>11.605</v>
       </c>
       <c r="AH327" t="n">
-        <v>6.609</v>
+        <v>6.599</v>
       </c>
       <c r="AI327" t="n">
-        <v>2.035</v>
+        <v>2.034</v>
       </c>
       <c r="AJ327" t="n">
-        <v>17.378</v>
+        <v>17.218</v>
       </c>
       <c r="AK327" t="n">
-        <v>-13.8</v>
+        <v>-13</v>
       </c>
       <c r="AL327" t="n">
-        <v>-15.9</v>
+        <v>-14.9</v>
       </c>
     </row>
     <row r="328">
@@ -40106,22 +40118,22 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F331" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G331" t="b">
         <v>1</v>
       </c>
       <c r="H331" t="n">
-        <v>1337.936</v>
+        <v>1336.502</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4778</v>
+        <v>-0.5339</v>
       </c>
       <c r="J331" t="n">
-        <v>1471.7</v>
+        <v>1479.4</v>
       </c>
       <c r="K331" t="n">
         <v>271</v>
@@ -40142,70 +40154,70 @@
         <v>277</v>
       </c>
       <c r="Q331" t="n">
-        <v>105.375</v>
+        <v>105.863</v>
       </c>
       <c r="R331" t="n">
-        <v>114.067</v>
+        <v>114.747</v>
       </c>
       <c r="S331" t="n">
-        <v>-8.692</v>
+        <v>-8.884</v>
       </c>
       <c r="T331" t="n">
-        <v>0.27701</v>
+        <v>0.28257</v>
       </c>
       <c r="U331" t="n">
-        <v>0.15732</v>
+        <v>0.15756</v>
       </c>
       <c r="V331" t="n">
-        <v>73.72</v>
+        <v>73.94</v>
       </c>
       <c r="W331" t="n">
-        <v>79.78</v>
+        <v>80.14</v>
       </c>
       <c r="X331" t="n">
-        <v>0.3175</v>
+        <v>0.3068</v>
       </c>
       <c r="Y331" t="n">
-        <v>25.928</v>
+        <v>25.875</v>
       </c>
       <c r="Z331" t="n">
-        <v>59.457</v>
+        <v>59.523</v>
       </c>
       <c r="AA331" t="n">
-        <v>7.376</v>
+        <v>7.648</v>
       </c>
       <c r="AB331" t="n">
-        <v>21.011</v>
+        <v>21.625</v>
       </c>
       <c r="AC331" t="n">
-        <v>14.485</v>
+        <v>14.545</v>
       </c>
       <c r="AD331" t="n">
-        <v>19.45</v>
+        <v>19.557</v>
       </c>
       <c r="AE331" t="n">
-        <v>8.997999999999999</v>
+        <v>9.215999999999999</v>
       </c>
       <c r="AF331" t="n">
-        <v>23.921</v>
+        <v>23.773</v>
       </c>
       <c r="AG331" t="n">
-        <v>12.351</v>
+        <v>12.466</v>
       </c>
       <c r="AH331" t="n">
-        <v>4.104</v>
+        <v>4.136</v>
       </c>
       <c r="AI331" t="n">
-        <v>2.566</v>
+        <v>2.557</v>
       </c>
       <c r="AJ331" t="n">
-        <v>18.679</v>
+        <v>18.534</v>
       </c>
       <c r="AK331" t="n">
-        <v>-5.2</v>
+        <v>-3.4</v>
       </c>
       <c r="AL331" t="n">
-        <v>-7.9</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="332">
@@ -40586,22 +40598,22 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F335" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G335" t="b">
         <v>1</v>
       </c>
       <c r="H335" t="n">
-        <v>1458.161</v>
+        <v>1453.572</v>
       </c>
       <c r="I335" t="n">
-        <v>-1.9961</v>
+        <v>-1.9312</v>
       </c>
       <c r="J335" t="n">
-        <v>1567.6</v>
+        <v>1564</v>
       </c>
       <c r="K335" t="n">
         <v>134</v>
@@ -40622,70 +40634,70 @@
         <v>135</v>
       </c>
       <c r="Q335" t="n">
-        <v>109.85</v>
+        <v>109.462</v>
       </c>
       <c r="R335" t="n">
-        <v>112.208</v>
+        <v>111.982</v>
       </c>
       <c r="S335" t="n">
-        <v>-2.358</v>
+        <v>-2.521</v>
       </c>
       <c r="T335" t="n">
-        <v>0.26586</v>
+        <v>0.25897</v>
       </c>
       <c r="U335" t="n">
-        <v>0.18294</v>
+        <v>0.18131</v>
       </c>
       <c r="V335" t="n">
-        <v>75.94</v>
+        <v>75.56</v>
       </c>
       <c r="W335" t="n">
-        <v>77.5</v>
+        <v>77.22</v>
       </c>
       <c r="X335" t="n">
-        <v>0.3621</v>
+        <v>0.3507</v>
       </c>
       <c r="Y335" t="n">
-        <v>26.749</v>
+        <v>26.701</v>
       </c>
       <c r="Z335" t="n">
-        <v>57.274</v>
+        <v>57.009</v>
       </c>
       <c r="AA335" t="n">
-        <v>9.407999999999999</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="AB335" t="n">
-        <v>25.627</v>
+        <v>25.075</v>
       </c>
       <c r="AC335" t="n">
-        <v>13.033</v>
+        <v>13.249</v>
       </c>
       <c r="AD335" t="n">
-        <v>17.514</v>
+        <v>17.684</v>
       </c>
       <c r="AE335" t="n">
-        <v>8.507999999999999</v>
+        <v>8.295999999999999</v>
       </c>
       <c r="AF335" t="n">
-        <v>23.304</v>
+        <v>23.71</v>
       </c>
       <c r="AG335" t="n">
-        <v>13.577</v>
+        <v>13.51</v>
       </c>
       <c r="AH335" t="n">
-        <v>5.486</v>
+        <v>5.272</v>
       </c>
       <c r="AI335" t="n">
-        <v>2.987</v>
+        <v>3.087</v>
       </c>
       <c r="AJ335" t="n">
-        <v>17.774</v>
+        <v>17.441</v>
       </c>
       <c r="AK335" t="n">
-        <v>-7.8</v>
+        <v>-3</v>
       </c>
       <c r="AL335" t="n">
-        <v>0.5</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="336">
@@ -40826,22 +40838,22 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F337" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G337" t="b">
         <v>1</v>
       </c>
       <c r="H337" t="n">
-        <v>1692.605</v>
+        <v>1710.314</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3731</v>
+        <v>0.4911</v>
       </c>
       <c r="J337" t="n">
-        <v>1650.7</v>
+        <v>1659.8</v>
       </c>
       <c r="K337" t="n">
         <v>59</v>
@@ -40862,70 +40874,70 @@
         <v>58</v>
       </c>
       <c r="Q337" t="n">
-        <v>107.191</v>
+        <v>107.746</v>
       </c>
       <c r="R337" t="n">
-        <v>99.78</v>
+        <v>99.542</v>
       </c>
       <c r="S337" t="n">
-        <v>7.411</v>
+        <v>8.204000000000001</v>
       </c>
       <c r="T337" t="n">
-        <v>0.2944</v>
+        <v>0.28656</v>
       </c>
       <c r="U337" t="n">
-        <v>0.16594</v>
+        <v>0.16296</v>
       </c>
       <c r="V337" t="n">
-        <v>69.55</v>
+        <v>69.95</v>
       </c>
       <c r="W337" t="n">
-        <v>64.73999999999999</v>
+        <v>64.61</v>
       </c>
       <c r="X337" t="n">
-        <v>0.5596</v>
+        <v>0.5855</v>
       </c>
       <c r="Y337" t="n">
-        <v>24.428</v>
+        <v>24.414</v>
       </c>
       <c r="Z337" t="n">
-        <v>55.339</v>
+        <v>55.168</v>
       </c>
       <c r="AA337" t="n">
-        <v>7.777</v>
+        <v>7.809</v>
       </c>
       <c r="AB337" t="n">
-        <v>23.56</v>
+        <v>23.716</v>
       </c>
       <c r="AC337" t="n">
-        <v>12.917</v>
+        <v>13.316</v>
       </c>
       <c r="AD337" t="n">
-        <v>19.259</v>
+        <v>19.548</v>
       </c>
       <c r="AE337" t="n">
-        <v>9.667999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AF337" t="n">
-        <v>22.6</v>
+        <v>22.867</v>
       </c>
       <c r="AG337" t="n">
-        <v>13.038</v>
+        <v>13.043</v>
       </c>
       <c r="AH337" t="n">
-        <v>6.445</v>
+        <v>6.383</v>
       </c>
       <c r="AI337" t="n">
-        <v>2.79</v>
+        <v>2.939</v>
       </c>
       <c r="AJ337" t="n">
-        <v>15.367</v>
+        <v>15.449</v>
       </c>
       <c r="AK337" t="n">
-        <v>-2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AL337" t="n">
-        <v>-1.2</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="338">
@@ -41426,22 +41438,22 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F342" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G342" t="b">
         <v>1</v>
       </c>
       <c r="H342" t="n">
-        <v>1492.671</v>
+        <v>1494.888</v>
       </c>
       <c r="I342" t="n">
-        <v>1.7375</v>
+        <v>1.7613</v>
       </c>
       <c r="J342" t="n">
-        <v>1433.9</v>
+        <v>1430.2</v>
       </c>
       <c r="K342" t="n">
         <v>141</v>
@@ -41462,70 +41474,70 @@
         <v>129</v>
       </c>
       <c r="Q342" t="n">
-        <v>113.502</v>
+        <v>113.463</v>
       </c>
       <c r="R342" t="n">
-        <v>107.201</v>
+        <v>107.147</v>
       </c>
       <c r="S342" t="n">
-        <v>6.301</v>
+        <v>6.316</v>
       </c>
       <c r="T342" t="n">
-        <v>0.31659</v>
+        <v>0.31484</v>
       </c>
       <c r="U342" t="n">
-        <v>0.14079</v>
+        <v>0.13891</v>
       </c>
       <c r="V342" t="n">
-        <v>81.65000000000001</v>
+        <v>82</v>
       </c>
       <c r="W342" t="n">
-        <v>77.19</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="X342" t="n">
-        <v>0.6491</v>
+        <v>0.6607</v>
       </c>
       <c r="Y342" t="n">
-        <v>26.298</v>
+        <v>26.423</v>
       </c>
       <c r="Z342" t="n">
-        <v>61.561</v>
+        <v>62.161</v>
       </c>
       <c r="AA342" t="n">
-        <v>9.333</v>
+        <v>9.189</v>
       </c>
       <c r="AB342" t="n">
-        <v>27.474</v>
+        <v>27.375</v>
       </c>
       <c r="AC342" t="n">
-        <v>19.719</v>
+        <v>19.961</v>
       </c>
       <c r="AD342" t="n">
-        <v>27</v>
+        <v>27.048</v>
       </c>
       <c r="AE342" t="n">
-        <v>11.596</v>
+        <v>11.777</v>
       </c>
       <c r="AF342" t="n">
-        <v>24.298</v>
+        <v>25.021</v>
       </c>
       <c r="AG342" t="n">
-        <v>13.772</v>
+        <v>13.598</v>
       </c>
       <c r="AH342" t="n">
-        <v>6.789</v>
+        <v>6.546</v>
       </c>
       <c r="AI342" t="n">
-        <v>2.544</v>
+        <v>2.743</v>
       </c>
       <c r="AJ342" t="n">
-        <v>19.596</v>
+        <v>19.643</v>
       </c>
       <c r="AK342" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="AL342" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="343">
@@ -42626,22 +42638,22 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F352" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G352" t="b">
         <v>1</v>
       </c>
       <c r="H352" t="n">
-        <v>1513.315</v>
+        <v>1515.562</v>
       </c>
       <c r="I352" t="n">
-        <v>3.9468</v>
+        <v>3.9427</v>
       </c>
       <c r="J352" t="n">
-        <v>1455.1</v>
+        <v>1452.7</v>
       </c>
       <c r="K352" t="n">
         <v>172</v>
@@ -42662,70 +42674,70 @@
         <v>185</v>
       </c>
       <c r="Q352" t="n">
-        <v>107.553</v>
+        <v>107.666</v>
       </c>
       <c r="R352" t="n">
-        <v>104.053</v>
+        <v>102.86</v>
       </c>
       <c r="S352" t="n">
-        <v>3.501</v>
+        <v>4.806</v>
       </c>
       <c r="T352" t="n">
-        <v>0.26408</v>
+        <v>0.2665</v>
       </c>
       <c r="U352" t="n">
-        <v>0.14397</v>
+        <v>0.14358</v>
       </c>
       <c r="V352" t="n">
-        <v>69.34</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="W352" t="n">
-        <v>67.43000000000001</v>
+        <v>66.61</v>
       </c>
       <c r="X352" t="n">
-        <v>0.6818</v>
+        <v>0.6914</v>
       </c>
       <c r="Y352" t="n">
-        <v>22.327</v>
+        <v>22.495</v>
       </c>
       <c r="Z352" t="n">
-        <v>52.968</v>
+        <v>53.36</v>
       </c>
       <c r="AA352" t="n">
-        <v>8.041</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AB352" t="n">
-        <v>24.55</v>
+        <v>24.711</v>
       </c>
       <c r="AC352" t="n">
-        <v>16.645</v>
+        <v>16.201</v>
       </c>
       <c r="AD352" t="n">
-        <v>21.05</v>
+        <v>20.546</v>
       </c>
       <c r="AE352" t="n">
-        <v>6.755</v>
+        <v>6.983</v>
       </c>
       <c r="AF352" t="n">
-        <v>19.009</v>
+        <v>19.236</v>
       </c>
       <c r="AG352" t="n">
-        <v>12.391</v>
+        <v>12.687</v>
       </c>
       <c r="AH352" t="n">
-        <v>8.055</v>
+        <v>8.093</v>
       </c>
       <c r="AI352" t="n">
-        <v>4.923</v>
+        <v>4.851</v>
       </c>
       <c r="AJ352" t="n">
-        <v>16.636</v>
+        <v>16.443</v>
       </c>
       <c r="AK352" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="AL352" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="353">
@@ -42746,22 +42758,22 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F353" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G353" t="b">
         <v>1</v>
       </c>
       <c r="H353" t="n">
-        <v>1286.086</v>
+        <v>1284.047</v>
       </c>
       <c r="I353" t="n">
-        <v>0.9585</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="J353" t="n">
-        <v>1430.1</v>
+        <v>1428</v>
       </c>
       <c r="K353" t="n">
         <v>275</v>
@@ -42782,70 +42794,70 @@
         <v>285</v>
       </c>
       <c r="Q353" t="n">
-        <v>119.631</v>
+        <v>119.459</v>
       </c>
       <c r="R353" t="n">
-        <v>125.422</v>
+        <v>125.976</v>
       </c>
       <c r="S353" t="n">
-        <v>-5.792</v>
+        <v>-6.516</v>
       </c>
       <c r="T353" t="n">
-        <v>0.22525</v>
+        <v>0.22936</v>
       </c>
       <c r="U353" t="n">
-        <v>0.14317</v>
+        <v>0.14555</v>
       </c>
       <c r="V353" t="n">
-        <v>79.16</v>
+        <v>78.88</v>
       </c>
       <c r="W353" t="n">
-        <v>83.17</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="X353" t="n">
-        <v>0.3851</v>
+        <v>0.3635</v>
       </c>
       <c r="Y353" t="n">
-        <v>27.829</v>
+        <v>27.793</v>
       </c>
       <c r="Z353" t="n">
-        <v>53.966</v>
+        <v>53.884</v>
       </c>
       <c r="AA353" t="n">
-        <v>8.452999999999999</v>
+        <v>8.471</v>
       </c>
       <c r="AB353" t="n">
-        <v>22.05</v>
+        <v>22.233</v>
       </c>
       <c r="AC353" t="n">
-        <v>15.053</v>
+        <v>14.825</v>
       </c>
       <c r="AD353" t="n">
-        <v>19.043</v>
+        <v>18.825</v>
       </c>
       <c r="AE353" t="n">
-        <v>5.624</v>
+        <v>5.72</v>
       </c>
       <c r="AF353" t="n">
-        <v>19.72</v>
+        <v>19.578</v>
       </c>
       <c r="AG353" t="n">
-        <v>14.699</v>
+        <v>14.861</v>
       </c>
       <c r="AH353" t="n">
-        <v>5.776</v>
+        <v>5.802</v>
       </c>
       <c r="AI353" t="n">
-        <v>1.711</v>
+        <v>1.703</v>
       </c>
       <c r="AJ353" t="n">
-        <v>17.186</v>
+        <v>17.157</v>
       </c>
       <c r="AK353" t="n">
-        <v>1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="AL353" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="354">
@@ -43466,22 +43478,22 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F359" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G359" t="b">
         <v>1</v>
       </c>
       <c r="H359" t="n">
-        <v>1417.812</v>
+        <v>1419.876</v>
       </c>
       <c r="I359" t="n">
-        <v>1.0097</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="J359" t="n">
-        <v>1434.3</v>
+        <v>1431.2</v>
       </c>
       <c r="K359" t="n">
         <v>191</v>
@@ -43502,70 +43514,70 @@
         <v>201</v>
       </c>
       <c r="Q359" t="n">
-        <v>119.444</v>
+        <v>118.669</v>
       </c>
       <c r="R359" t="n">
-        <v>117.606</v>
+        <v>116.347</v>
       </c>
       <c r="S359" t="n">
-        <v>1.838</v>
+        <v>2.321</v>
       </c>
       <c r="T359" t="n">
-        <v>0.28356</v>
+        <v>0.27908</v>
       </c>
       <c r="U359" t="n">
-        <v>0.14388</v>
+        <v>0.14475</v>
       </c>
       <c r="V359" t="n">
-        <v>84.61</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="W359" t="n">
-        <v>83.51000000000001</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="X359" t="n">
-        <v>0.5607</v>
+        <v>0.5847</v>
       </c>
       <c r="Y359" t="n">
-        <v>29.001</v>
+        <v>28.824</v>
       </c>
       <c r="Z359" t="n">
-        <v>60.034</v>
+        <v>59.897</v>
       </c>
       <c r="AA359" t="n">
-        <v>9.933999999999999</v>
+        <v>9.894</v>
       </c>
       <c r="AB359" t="n">
-        <v>28.162</v>
+        <v>27.971</v>
       </c>
       <c r="AC359" t="n">
-        <v>16.67</v>
+        <v>16.556</v>
       </c>
       <c r="AD359" t="n">
-        <v>21.991</v>
+        <v>21.99</v>
       </c>
       <c r="AE359" t="n">
-        <v>8.946</v>
+        <v>8.843</v>
       </c>
       <c r="AF359" t="n">
-        <v>22.153</v>
+        <v>22.503</v>
       </c>
       <c r="AG359" t="n">
-        <v>15.726</v>
+        <v>15.703</v>
       </c>
       <c r="AH359" t="n">
-        <v>5.648</v>
+        <v>5.857</v>
       </c>
       <c r="AI359" t="n">
-        <v>2.934</v>
+        <v>2.936</v>
       </c>
       <c r="AJ359" t="n">
-        <v>19.988</v>
+        <v>19.718</v>
       </c>
       <c r="AK359" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AL359" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="360">
@@ -44186,22 +44198,22 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F365" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G365" t="b">
         <v>1</v>
       </c>
       <c r="H365" t="n">
-        <v>1342.401</v>
+        <v>1340.338</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.6218</v>
+        <v>-0.6025</v>
       </c>
       <c r="J365" t="n">
-        <v>1404.8</v>
+        <v>1406.5</v>
       </c>
       <c r="K365" t="n">
         <v>307</v>
@@ -44222,70 +44234,70 @@
         <v>300</v>
       </c>
       <c r="Q365" t="n">
-        <v>107.117</v>
+        <v>105.957</v>
       </c>
       <c r="R365" t="n">
-        <v>114.063</v>
+        <v>113.275</v>
       </c>
       <c r="S365" t="n">
-        <v>-6.946</v>
+        <v>-7.317</v>
       </c>
       <c r="T365" t="n">
-        <v>0.30593</v>
+        <v>0.30907</v>
       </c>
       <c r="U365" t="n">
-        <v>0.15279</v>
+        <v>0.15431</v>
       </c>
       <c r="V365" t="n">
-        <v>75.95</v>
+        <v>75.2</v>
       </c>
       <c r="W365" t="n">
-        <v>80.88</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="X365" t="n">
-        <v>0.4545</v>
+        <v>0.4288</v>
       </c>
       <c r="Y365" t="n">
-        <v>27.92</v>
+        <v>27.738</v>
       </c>
       <c r="Z365" t="n">
-        <v>62.58</v>
+        <v>62.996</v>
       </c>
       <c r="AA365" t="n">
-        <v>7.034</v>
+        <v>6.826</v>
       </c>
       <c r="AB365" t="n">
-        <v>20.693</v>
+        <v>20.757</v>
       </c>
       <c r="AC365" t="n">
-        <v>13.08</v>
+        <v>12.903</v>
       </c>
       <c r="AD365" t="n">
-        <v>18.636</v>
+        <v>18.3</v>
       </c>
       <c r="AE365" t="n">
-        <v>10.534</v>
+        <v>10.843</v>
       </c>
       <c r="AF365" t="n">
-        <v>23.375</v>
+        <v>23.601</v>
       </c>
       <c r="AG365" t="n">
-        <v>12.489</v>
+        <v>12.234</v>
       </c>
       <c r="AH365" t="n">
-        <v>6.341</v>
+        <v>6.363</v>
       </c>
       <c r="AI365" t="n">
-        <v>4.705</v>
+        <v>4.649</v>
       </c>
       <c r="AJ365" t="n">
-        <v>17.239</v>
+        <v>17.231</v>
       </c>
       <c r="AK365" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="AL365" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="366">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -3746,22 +3746,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1343.191</v>
+        <v>1346.802</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.6522</v>
+        <v>-2.4681</v>
       </c>
       <c r="J28" t="n">
-        <v>1377.3</v>
+        <v>1379.2</v>
       </c>
       <c r="K28" t="n">
         <v>259</v>
@@ -3782,70 +3782,70 @@
         <v>265</v>
       </c>
       <c r="Q28" t="n">
-        <v>115.3</v>
+        <v>115.453</v>
       </c>
       <c r="R28" t="n">
-        <v>114.059</v>
+        <v>114.218</v>
       </c>
       <c r="S28" t="n">
-        <v>1.241</v>
+        <v>1.235</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23813</v>
+        <v>0.23552</v>
       </c>
       <c r="U28" t="n">
-        <v>0.16822</v>
+        <v>0.16969</v>
       </c>
       <c r="V28" t="n">
-        <v>75.13</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="W28" t="n">
-        <v>74.53</v>
+        <v>74.44</v>
       </c>
       <c r="X28" t="n">
-        <v>0.4899</v>
+        <v>0.5054</v>
       </c>
       <c r="Y28" t="n">
-        <v>26.771</v>
+        <v>26.68</v>
       </c>
       <c r="Z28" t="n">
-        <v>54.275</v>
+        <v>53.987</v>
       </c>
       <c r="AA28" t="n">
-        <v>9.394</v>
+        <v>9.454000000000001</v>
       </c>
       <c r="AB28" t="n">
-        <v>23.814</v>
+        <v>23.876</v>
       </c>
       <c r="AC28" t="n">
-        <v>12.191</v>
+        <v>12.226</v>
       </c>
       <c r="AD28" t="n">
-        <v>16.762</v>
+        <v>16.73</v>
       </c>
       <c r="AE28" t="n">
-        <v>7.275</v>
+        <v>7.195</v>
       </c>
       <c r="AF28" t="n">
-        <v>22.783</v>
+        <v>22.845</v>
       </c>
       <c r="AG28" t="n">
-        <v>14.574</v>
+        <v>14.515</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.829</v>
+        <v>4.679</v>
       </c>
       <c r="AI28" t="n">
-        <v>3.33</v>
+        <v>3.309</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16.07</v>
+        <v>16.165</v>
       </c>
       <c r="AK28" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="AL28" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -5186,22 +5186,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1393.612</v>
+        <v>1405.566</v>
       </c>
       <c r="I40" t="n">
-        <v>0.154</v>
+        <v>0.1743</v>
       </c>
       <c r="J40" t="n">
-        <v>1515.7</v>
+        <v>1523.3</v>
       </c>
       <c r="K40" t="n">
         <v>192</v>
@@ -5222,70 +5222,70 @@
         <v>208</v>
       </c>
       <c r="Q40" t="n">
-        <v>108.933</v>
+        <v>109.09</v>
       </c>
       <c r="R40" t="n">
-        <v>113.237</v>
+        <v>112.484</v>
       </c>
       <c r="S40" t="n">
-        <v>-4.303</v>
+        <v>-3.395</v>
       </c>
       <c r="T40" t="n">
-        <v>0.33922</v>
+        <v>0.34056</v>
       </c>
       <c r="U40" t="n">
-        <v>0.15994</v>
+        <v>0.15989</v>
       </c>
       <c r="V40" t="n">
-        <v>76.37</v>
+        <v>76.53</v>
       </c>
       <c r="W40" t="n">
-        <v>79.37</v>
+        <v>78.88</v>
       </c>
       <c r="X40" t="n">
-        <v>0.4393</v>
+        <v>0.4569</v>
       </c>
       <c r="Y40" t="n">
-        <v>25.712</v>
+        <v>25.681</v>
       </c>
       <c r="Z40" t="n">
-        <v>58.768</v>
+        <v>59.078</v>
       </c>
       <c r="AA40" t="n">
-        <v>7.153</v>
+        <v>6.919</v>
       </c>
       <c r="AB40" t="n">
-        <v>21.846</v>
+        <v>21.674</v>
       </c>
       <c r="AC40" t="n">
-        <v>17.493</v>
+        <v>17.406</v>
       </c>
       <c r="AD40" t="n">
-        <v>23.99</v>
+        <v>23.917</v>
       </c>
       <c r="AE40" t="n">
-        <v>10.495</v>
+        <v>10.729</v>
       </c>
       <c r="AF40" t="n">
-        <v>20.498</v>
+        <v>20.751</v>
       </c>
       <c r="AG40" t="n">
-        <v>11.297</v>
+        <v>11.288</v>
       </c>
       <c r="AH40" t="n">
-        <v>6.691</v>
+        <v>6.556</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.451</v>
+        <v>1.489</v>
       </c>
       <c r="AJ40" t="n">
-        <v>18.565</v>
+        <v>18.707</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="AL40" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="41">
@@ -5426,22 +5426,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1369.938</v>
+        <v>1367.474</v>
       </c>
       <c r="I42" t="n">
-        <v>3.1128</v>
+        <v>3.1174</v>
       </c>
       <c r="J42" t="n">
-        <v>1437.1</v>
+        <v>1437</v>
       </c>
       <c r="K42" t="n">
         <v>154</v>
@@ -5462,70 +5462,70 @@
         <v>164</v>
       </c>
       <c r="Q42" t="n">
-        <v>112.041</v>
+        <v>112.338</v>
       </c>
       <c r="R42" t="n">
-        <v>106.135</v>
+        <v>107.002</v>
       </c>
       <c r="S42" t="n">
-        <v>5.906</v>
+        <v>5.336</v>
       </c>
       <c r="T42" t="n">
-        <v>0.27102</v>
+        <v>0.27465</v>
       </c>
       <c r="U42" t="n">
-        <v>0.15045</v>
+        <v>0.15362</v>
       </c>
       <c r="V42" t="n">
-        <v>78.78</v>
+        <v>79.41</v>
       </c>
       <c r="W42" t="n">
-        <v>75.14</v>
+        <v>76.17</v>
       </c>
       <c r="X42" t="n">
-        <v>0.6486</v>
+        <v>0.6194</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.501</v>
+        <v>27.615</v>
       </c>
       <c r="Z42" t="n">
-        <v>60.511</v>
+        <v>60.695</v>
       </c>
       <c r="AA42" t="n">
-        <v>10.364</v>
+        <v>10.612</v>
       </c>
       <c r="AB42" t="n">
-        <v>29.44</v>
+        <v>29.825</v>
       </c>
       <c r="AC42" t="n">
-        <v>13.415</v>
+        <v>13.763</v>
       </c>
       <c r="AD42" t="n">
-        <v>18.988</v>
+        <v>19.289</v>
       </c>
       <c r="AE42" t="n">
-        <v>8.754</v>
+        <v>9.032</v>
       </c>
       <c r="AF42" t="n">
-        <v>23.174</v>
+        <v>23.333</v>
       </c>
       <c r="AG42" t="n">
-        <v>15.971</v>
+        <v>16.12</v>
       </c>
       <c r="AH42" t="n">
-        <v>8.342000000000001</v>
+        <v>8.301</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.776</v>
+        <v>1.863</v>
       </c>
       <c r="AJ42" t="n">
-        <v>16.636</v>
+        <v>16.668</v>
       </c>
       <c r="AK42" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AL42" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="43">
@@ -5786,22 +5786,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1439.346</v>
+        <v>1437.095</v>
       </c>
       <c r="I45" t="n">
-        <v>1.3639</v>
+        <v>1.3871</v>
       </c>
       <c r="J45" t="n">
-        <v>1491.9</v>
+        <v>1500.4</v>
       </c>
       <c r="K45" t="n">
         <v>183</v>
@@ -5822,70 +5822,70 @@
         <v>169</v>
       </c>
       <c r="Q45" t="n">
-        <v>112.744</v>
+        <v>111.714</v>
       </c>
       <c r="R45" t="n">
-        <v>113.573</v>
+        <v>113.989</v>
       </c>
       <c r="S45" t="n">
-        <v>-0.83</v>
+        <v>-2.275</v>
       </c>
       <c r="T45" t="n">
-        <v>0.29636</v>
+        <v>0.29804</v>
       </c>
       <c r="U45" t="n">
-        <v>0.16654</v>
+        <v>0.1699</v>
       </c>
       <c r="V45" t="n">
-        <v>73.39</v>
+        <v>72.77</v>
       </c>
       <c r="W45" t="n">
-        <v>74.01000000000001</v>
+        <v>74.34</v>
       </c>
       <c r="X45" t="n">
-        <v>0.4762</v>
+        <v>0.4608</v>
       </c>
       <c r="Y45" t="n">
-        <v>25.163</v>
+        <v>25.041</v>
       </c>
       <c r="Z45" t="n">
-        <v>54.694</v>
+        <v>54.84</v>
       </c>
       <c r="AA45" t="n">
-        <v>8.577999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="AB45" t="n">
-        <v>24.313</v>
+        <v>24.536</v>
       </c>
       <c r="AC45" t="n">
-        <v>14.483</v>
+        <v>14.13</v>
       </c>
       <c r="AD45" t="n">
-        <v>20.197</v>
+        <v>19.776</v>
       </c>
       <c r="AE45" t="n">
-        <v>9.292999999999999</v>
+        <v>9.433</v>
       </c>
       <c r="AF45" t="n">
-        <v>21.857</v>
+        <v>21.992</v>
       </c>
       <c r="AG45" t="n">
-        <v>12.667</v>
+        <v>12.658</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.551</v>
+        <v>4.514</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.476</v>
+        <v>3.461</v>
       </c>
       <c r="AJ45" t="n">
-        <v>17.517</v>
+        <v>17.39</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.2</v>
+        <v>-3.4</v>
       </c>
       <c r="AL45" t="n">
-        <v>-2.7</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="46">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1578.343</v>
+        <v>1569.762</v>
       </c>
       <c r="I53" t="n">
-        <v>1.6342</v>
+        <v>1.7549</v>
       </c>
       <c r="J53" t="n">
-        <v>1482.2</v>
+        <v>1482.5</v>
       </c>
       <c r="K53" t="n">
         <v>147</v>
@@ -6782,70 +6782,70 @@
         <v>145</v>
       </c>
       <c r="Q53" t="n">
-        <v>109.208</v>
+        <v>108.385</v>
       </c>
       <c r="R53" t="n">
-        <v>105.836</v>
+        <v>107.002</v>
       </c>
       <c r="S53" t="n">
-        <v>3.372</v>
+        <v>1.384</v>
       </c>
       <c r="T53" t="n">
-        <v>0.2563</v>
+        <v>0.26073</v>
       </c>
       <c r="U53" t="n">
-        <v>0.15334</v>
+        <v>0.15398</v>
       </c>
       <c r="V53" t="n">
-        <v>75.97</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="W53" t="n">
-        <v>73.66</v>
+        <v>73.95</v>
       </c>
       <c r="X53" t="n">
-        <v>0.6708</v>
+        <v>0.6377</v>
       </c>
       <c r="Y53" t="n">
-        <v>25.712</v>
+        <v>26.006</v>
       </c>
       <c r="Z53" t="n">
-        <v>57.317</v>
+        <v>57.623</v>
       </c>
       <c r="AA53" t="n">
-        <v>6.84</v>
+        <v>6.939</v>
       </c>
       <c r="AB53" t="n">
-        <v>21.886</v>
+        <v>21.841</v>
       </c>
       <c r="AC53" t="n">
-        <v>17.708</v>
+        <v>17.203</v>
       </c>
       <c r="AD53" t="n">
-        <v>23.886</v>
+        <v>23.145</v>
       </c>
       <c r="AE53" t="n">
-        <v>8.946999999999999</v>
+        <v>9.284000000000001</v>
       </c>
       <c r="AF53" t="n">
-        <v>25.505</v>
+        <v>25.661</v>
       </c>
       <c r="AG53" t="n">
-        <v>13.448</v>
+        <v>13.533</v>
       </c>
       <c r="AH53" t="n">
-        <v>5.782</v>
+        <v>5.69</v>
       </c>
       <c r="AI53" t="n">
-        <v>4.605</v>
+        <v>4.487</v>
       </c>
       <c r="AJ53" t="n">
-        <v>16.881</v>
+        <v>16.916</v>
       </c>
       <c r="AK53" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AL53" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="54">
@@ -6866,22 +6866,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G54" t="b">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>1421.786</v>
+        <v>1418.774</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2169</v>
+        <v>0.1631</v>
       </c>
       <c r="J54" t="n">
-        <v>1422</v>
+        <v>1419.5</v>
       </c>
       <c r="K54" t="n">
         <v>254</v>
@@ -6902,70 +6902,70 @@
         <v>228</v>
       </c>
       <c r="Q54" t="n">
-        <v>111.409</v>
+        <v>110.531</v>
       </c>
       <c r="R54" t="n">
-        <v>111.987</v>
+        <v>111.789</v>
       </c>
       <c r="S54" t="n">
-        <v>-0.578</v>
+        <v>-1.258</v>
       </c>
       <c r="T54" t="n">
-        <v>0.24946</v>
+        <v>0.24863</v>
       </c>
       <c r="U54" t="n">
-        <v>0.14411</v>
+        <v>0.14247</v>
       </c>
       <c r="V54" t="n">
-        <v>75.98</v>
+        <v>75.5</v>
       </c>
       <c r="W54" t="n">
-        <v>76.20999999999999</v>
+        <v>76.19</v>
       </c>
       <c r="X54" t="n">
-        <v>0.5392</v>
+        <v>0.5101</v>
       </c>
       <c r="Y54" t="n">
-        <v>27.721</v>
+        <v>27.594</v>
       </c>
       <c r="Z54" t="n">
-        <v>58.505</v>
+        <v>58.748</v>
       </c>
       <c r="AA54" t="n">
-        <v>7.408</v>
+        <v>7.296</v>
       </c>
       <c r="AB54" t="n">
-        <v>20.415</v>
+        <v>20.588</v>
       </c>
       <c r="AC54" t="n">
-        <v>13.129</v>
+        <v>13.02</v>
       </c>
       <c r="AD54" t="n">
-        <v>17.602</v>
+        <v>17.423</v>
       </c>
       <c r="AE54" t="n">
-        <v>7.823</v>
+        <v>7.797</v>
       </c>
       <c r="AF54" t="n">
-        <v>23.494</v>
+        <v>23.522</v>
       </c>
       <c r="AG54" t="n">
-        <v>14.359</v>
+        <v>14.157</v>
       </c>
       <c r="AH54" t="n">
-        <v>5.925</v>
+        <v>6.087</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.942</v>
+        <v>2.838</v>
       </c>
       <c r="AJ54" t="n">
-        <v>17.119</v>
+        <v>17.301</v>
       </c>
       <c r="AK54" t="n">
-        <v>-5.6</v>
+        <v>-1.6</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="55">
@@ -9386,22 +9386,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F75" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G75" t="b">
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>1423.201</v>
+        <v>1419.433</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0412</v>
+        <v>0.1348</v>
       </c>
       <c r="J75" t="n">
-        <v>1435.1</v>
+        <v>1436.1</v>
       </c>
       <c r="K75" t="n">
         <v>220</v>
@@ -9422,70 +9422,70 @@
         <v>211</v>
       </c>
       <c r="Q75" t="n">
-        <v>104.38</v>
+        <v>103.567</v>
       </c>
       <c r="R75" t="n">
-        <v>103.892</v>
+        <v>103.688</v>
       </c>
       <c r="S75" t="n">
-        <v>0.488</v>
+        <v>-0.122</v>
       </c>
       <c r="T75" t="n">
-        <v>0.28706</v>
+        <v>0.29096</v>
       </c>
       <c r="U75" t="n">
-        <v>0.18035</v>
+        <v>0.18236</v>
       </c>
       <c r="V75" t="n">
-        <v>67.8</v>
+        <v>67.22</v>
       </c>
       <c r="W75" t="n">
-        <v>67.73999999999999</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="X75" t="n">
-        <v>0.5208</v>
+        <v>0.4955</v>
       </c>
       <c r="Y75" t="n">
-        <v>24.106</v>
+        <v>23.933</v>
       </c>
       <c r="Z75" t="n">
-        <v>54.878</v>
+        <v>55.058</v>
       </c>
       <c r="AA75" t="n">
-        <v>7.776</v>
+        <v>7.823</v>
       </c>
       <c r="AB75" t="n">
-        <v>21.983</v>
+        <v>22.031</v>
       </c>
       <c r="AC75" t="n">
-        <v>11.817</v>
+        <v>11.53</v>
       </c>
       <c r="AD75" t="n">
-        <v>17.747</v>
+        <v>17.326</v>
       </c>
       <c r="AE75" t="n">
-        <v>9.403</v>
+        <v>9.571999999999999</v>
       </c>
       <c r="AF75" t="n">
-        <v>22.956</v>
+        <v>22.898</v>
       </c>
       <c r="AG75" t="n">
-        <v>12.936</v>
+        <v>12.818</v>
       </c>
       <c r="AH75" t="n">
-        <v>5.693</v>
+        <v>5.841</v>
       </c>
       <c r="AI75" t="n">
-        <v>3.553</v>
+        <v>3.486</v>
       </c>
       <c r="AJ75" t="n">
-        <v>16.975</v>
+        <v>16.978</v>
       </c>
       <c r="AK75" t="n">
-        <v>3.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AL75" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="76">
@@ -10226,22 +10226,22 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G82" t="b">
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>1383.342</v>
+        <v>1381.294</v>
       </c>
       <c r="I82" t="n">
-        <v>-2.6565</v>
+        <v>-2.4617</v>
       </c>
       <c r="J82" t="n">
-        <v>1517.9</v>
+        <v>1519.6</v>
       </c>
       <c r="K82" t="n">
         <v>252</v>
@@ -10262,70 +10262,70 @@
         <v>260</v>
       </c>
       <c r="Q82" t="n">
-        <v>101.572</v>
+        <v>101.921</v>
       </c>
       <c r="R82" t="n">
-        <v>110.007</v>
+        <v>110.037</v>
       </c>
       <c r="S82" t="n">
-        <v>-8.433999999999999</v>
+        <v>-8.116</v>
       </c>
       <c r="T82" t="n">
-        <v>0.31665</v>
+        <v>0.31866</v>
       </c>
       <c r="U82" t="n">
-        <v>0.16224</v>
+        <v>0.16102</v>
       </c>
       <c r="V82" t="n">
-        <v>71.08</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="W82" t="n">
-        <v>77.45</v>
+        <v>77.83</v>
       </c>
       <c r="X82" t="n">
-        <v>0.3409</v>
+        <v>0.3298</v>
       </c>
       <c r="Y82" t="n">
-        <v>24.67</v>
+        <v>24.954</v>
       </c>
       <c r="Z82" t="n">
-        <v>58.989</v>
+        <v>59.642</v>
       </c>
       <c r="AA82" t="n">
-        <v>5.398</v>
+        <v>5.45</v>
       </c>
       <c r="AB82" t="n">
-        <v>18.455</v>
+        <v>18.57</v>
       </c>
       <c r="AC82" t="n">
-        <v>16.341</v>
+        <v>16.297</v>
       </c>
       <c r="AD82" t="n">
-        <v>23.42</v>
+        <v>23.276</v>
       </c>
       <c r="AE82" t="n">
-        <v>10.352</v>
+        <v>10.612</v>
       </c>
       <c r="AF82" t="n">
-        <v>22.114</v>
+        <v>22.339</v>
       </c>
       <c r="AG82" t="n">
-        <v>11.682</v>
+        <v>11.79</v>
       </c>
       <c r="AH82" t="n">
-        <v>6.5</v>
+        <v>6.495</v>
       </c>
       <c r="AI82" t="n">
-        <v>4.045</v>
+        <v>3.979</v>
       </c>
       <c r="AJ82" t="n">
-        <v>16.159</v>
+        <v>16.034</v>
       </c>
       <c r="AK82" t="n">
-        <v>-5</v>
+        <v>-5.8</v>
       </c>
       <c r="AL82" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="83">
@@ -10586,22 +10586,22 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F85" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G85" t="b">
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>1515.649</v>
+        <v>1518.466</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.4929</v>
       </c>
       <c r="J85" t="n">
-        <v>1416.1</v>
+        <v>1416.5</v>
       </c>
       <c r="K85" t="n">
         <v>140</v>
@@ -10622,70 +10622,70 @@
         <v>128</v>
       </c>
       <c r="Q85" t="n">
-        <v>116.981</v>
+        <v>116.449</v>
       </c>
       <c r="R85" t="n">
-        <v>105.723</v>
+        <v>105.528</v>
       </c>
       <c r="S85" t="n">
-        <v>11.258</v>
+        <v>10.921</v>
       </c>
       <c r="T85" t="n">
-        <v>0.26961</v>
+        <v>0.26802</v>
       </c>
       <c r="U85" t="n">
-        <v>0.14441</v>
+        <v>0.14557</v>
       </c>
       <c r="V85" t="n">
-        <v>77.66</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="W85" t="n">
-        <v>70.09999999999999</v>
+        <v>69.91</v>
       </c>
       <c r="X85" t="n">
-        <v>0.6702</v>
+        <v>0.6806</v>
       </c>
       <c r="Y85" t="n">
-        <v>27.636</v>
+        <v>27.45</v>
       </c>
       <c r="Z85" t="n">
-        <v>56.583</v>
+        <v>56.367</v>
       </c>
       <c r="AA85" t="n">
-        <v>7.526</v>
+        <v>7.521</v>
       </c>
       <c r="AB85" t="n">
-        <v>21.405</v>
+        <v>21.435</v>
       </c>
       <c r="AC85" t="n">
-        <v>14.859</v>
+        <v>14.821</v>
       </c>
       <c r="AD85" t="n">
-        <v>19.67</v>
+        <v>19.722</v>
       </c>
       <c r="AE85" t="n">
-        <v>8.372999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="AF85" t="n">
-        <v>22.738</v>
+        <v>22.735</v>
       </c>
       <c r="AG85" t="n">
-        <v>14.361</v>
+        <v>14.153</v>
       </c>
       <c r="AH85" t="n">
-        <v>8.616</v>
+        <v>8.606999999999999</v>
       </c>
       <c r="AI85" t="n">
-        <v>3.265</v>
+        <v>3.329</v>
       </c>
       <c r="AJ85" t="n">
-        <v>16.892</v>
+        <v>16.853</v>
       </c>
       <c r="AK85" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="AL85" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="86">
@@ -10946,22 +10946,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F88" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G88" t="b">
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1442.92</v>
+        <v>1438.593</v>
       </c>
       <c r="I88" t="n">
-        <v>1.62</v>
+        <v>1.624</v>
       </c>
       <c r="J88" t="n">
-        <v>1403.8</v>
+        <v>1406</v>
       </c>
       <c r="K88" t="n">
         <v>270</v>
@@ -10982,70 +10982,70 @@
         <v>245</v>
       </c>
       <c r="Q88" t="n">
-        <v>107.862</v>
+        <v>107.307</v>
       </c>
       <c r="R88" t="n">
-        <v>105.351</v>
+        <v>106.134</v>
       </c>
       <c r="S88" t="n">
-        <v>2.512</v>
+        <v>1.173</v>
       </c>
       <c r="T88" t="n">
-        <v>0.34697</v>
+        <v>0.34795</v>
       </c>
       <c r="U88" t="n">
-        <v>0.15614</v>
+        <v>0.15237</v>
       </c>
       <c r="V88" t="n">
-        <v>73.31999999999999</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="W88" t="n">
-        <v>71.63</v>
+        <v>71.98</v>
       </c>
       <c r="X88" t="n">
-        <v>0.629</v>
+        <v>0.6</v>
       </c>
       <c r="Y88" t="n">
-        <v>26.492</v>
+        <v>26.5</v>
       </c>
       <c r="Z88" t="n">
-        <v>61.801</v>
+        <v>62.16</v>
       </c>
       <c r="AA88" t="n">
-        <v>7.329</v>
+        <v>7.29</v>
       </c>
       <c r="AB88" t="n">
-        <v>21.999</v>
+        <v>22.07</v>
       </c>
       <c r="AC88" t="n">
-        <v>12.215</v>
+        <v>11.96</v>
       </c>
       <c r="AD88" t="n">
-        <v>17.505</v>
+        <v>17</v>
       </c>
       <c r="AE88" t="n">
-        <v>12.083</v>
+        <v>12.1</v>
       </c>
       <c r="AF88" t="n">
-        <v>22.989</v>
+        <v>22.92</v>
       </c>
       <c r="AG88" t="n">
-        <v>12.011</v>
+        <v>12</v>
       </c>
       <c r="AH88" t="n">
-        <v>6.371</v>
+        <v>6.36</v>
       </c>
       <c r="AI88" t="n">
-        <v>3.641</v>
+        <v>3.65</v>
       </c>
       <c r="AJ88" t="n">
-        <v>15.539</v>
+        <v>15.61</v>
       </c>
       <c r="AK88" t="n">
-        <v>5.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL88" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="89">
@@ -12026,22 +12026,22 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G97" t="b">
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>1533.703</v>
+        <v>1536.386</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0135</v>
+        <v>0.9002</v>
       </c>
       <c r="J97" t="n">
-        <v>1419.8</v>
+        <v>1417.8</v>
       </c>
       <c r="K97" t="n">
         <v>200</v>
@@ -12062,70 +12062,70 @@
         <v>198</v>
       </c>
       <c r="Q97" t="n">
-        <v>111.251</v>
+        <v>111.677</v>
       </c>
       <c r="R97" t="n">
-        <v>107.479</v>
+        <v>107.709</v>
       </c>
       <c r="S97" t="n">
-        <v>3.772</v>
+        <v>3.968</v>
       </c>
       <c r="T97" t="n">
-        <v>0.25639</v>
+        <v>0.25628</v>
       </c>
       <c r="U97" t="n">
-        <v>0.17087</v>
+        <v>0.17153</v>
       </c>
       <c r="V97" t="n">
-        <v>74.93000000000001</v>
+        <v>75.08</v>
       </c>
       <c r="W97" t="n">
-        <v>72.53</v>
+        <v>72.55</v>
       </c>
       <c r="X97" t="n">
-        <v>0.5901</v>
+        <v>0.6034</v>
       </c>
       <c r="Y97" t="n">
-        <v>26.761</v>
+        <v>26.685</v>
       </c>
       <c r="Z97" t="n">
-        <v>57.05</v>
+        <v>56.691</v>
       </c>
       <c r="AA97" t="n">
-        <v>8.832000000000001</v>
+        <v>8.802</v>
       </c>
       <c r="AB97" t="n">
-        <v>26.882</v>
+        <v>26.576</v>
       </c>
       <c r="AC97" t="n">
-        <v>12.36</v>
+        <v>12.747</v>
       </c>
       <c r="AD97" t="n">
-        <v>18.078</v>
+        <v>18.358</v>
       </c>
       <c r="AE97" t="n">
-        <v>9.109</v>
+        <v>9.007</v>
       </c>
       <c r="AF97" t="n">
-        <v>25.512</v>
+        <v>25.246</v>
       </c>
       <c r="AG97" t="n">
-        <v>14.997</v>
+        <v>15.033</v>
       </c>
       <c r="AH97" t="n">
-        <v>4.283</v>
+        <v>4.348</v>
       </c>
       <c r="AI97" t="n">
-        <v>3.351</v>
+        <v>3.33</v>
       </c>
       <c r="AJ97" t="n">
-        <v>15.394</v>
+        <v>15.572</v>
       </c>
       <c r="AK97" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="AL97" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="98">
@@ -12266,22 +12266,22 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F99" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G99" t="b">
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>1442.26</v>
+        <v>1448.4</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7056</v>
+        <v>0.7301</v>
       </c>
       <c r="J99" t="n">
-        <v>1441.9</v>
+        <v>1444.4</v>
       </c>
       <c r="K99" t="n">
         <v>265</v>
@@ -12302,70 +12302,70 @@
         <v>254</v>
       </c>
       <c r="Q99" t="n">
-        <v>111.698</v>
+        <v>111.539</v>
       </c>
       <c r="R99" t="n">
-        <v>111.372</v>
+        <v>111.349</v>
       </c>
       <c r="S99" t="n">
-        <v>0.326</v>
+        <v>0.191</v>
       </c>
       <c r="T99" t="n">
-        <v>0.31571</v>
+        <v>0.31519</v>
       </c>
       <c r="U99" t="n">
-        <v>0.14654</v>
+        <v>0.14788</v>
       </c>
       <c r="V99" t="n">
-        <v>80.55</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="W99" t="n">
-        <v>80.43000000000001</v>
+        <v>80.42</v>
       </c>
       <c r="X99" t="n">
-        <v>0.55</v>
+        <v>0.5629</v>
       </c>
       <c r="Y99" t="n">
-        <v>25.94</v>
+        <v>26.038</v>
       </c>
       <c r="Z99" t="n">
-        <v>60.92</v>
+        <v>60.962</v>
       </c>
       <c r="AA99" t="n">
-        <v>9.390000000000001</v>
+        <v>9.417</v>
       </c>
       <c r="AB99" t="n">
-        <v>29</v>
+        <v>28.855</v>
       </c>
       <c r="AC99" t="n">
-        <v>17.96</v>
+        <v>17.759</v>
       </c>
       <c r="AD99" t="n">
-        <v>24.81</v>
+        <v>24.536</v>
       </c>
       <c r="AE99" t="n">
-        <v>10.14</v>
+        <v>10.155</v>
       </c>
       <c r="AF99" t="n">
-        <v>21.69</v>
+        <v>21.786</v>
       </c>
       <c r="AG99" t="n">
-        <v>10.74</v>
+        <v>10.767</v>
       </c>
       <c r="AH99" t="n">
-        <v>7.8</v>
+        <v>7.777</v>
       </c>
       <c r="AI99" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="AJ99" t="n">
-        <v>19.33</v>
+        <v>19.503</v>
       </c>
       <c r="AK99" t="n">
-        <v>11.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AL99" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="100">
@@ -13826,22 +13826,22 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F112" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G112" t="b">
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>1620.503</v>
+        <v>1625.523</v>
       </c>
       <c r="I112" t="n">
-        <v>-1.0234</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>1377.7</v>
+        <v>1382.5</v>
       </c>
       <c r="K112" t="n">
         <v>91</v>
@@ -13862,70 +13862,70 @@
         <v>76</v>
       </c>
       <c r="Q112" t="n">
-        <v>121.052</v>
+        <v>121.161</v>
       </c>
       <c r="R112" t="n">
-        <v>100.195</v>
+        <v>100.188</v>
       </c>
       <c r="S112" t="n">
-        <v>20.858</v>
+        <v>20.973</v>
       </c>
       <c r="T112" t="n">
-        <v>0.31142</v>
+        <v>0.30613</v>
       </c>
       <c r="U112" t="n">
-        <v>0.128</v>
+        <v>0.12761</v>
       </c>
       <c r="V112" t="n">
-        <v>86.18000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="W112" t="n">
-        <v>71.66</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="X112" t="n">
-        <v>0.8681</v>
+        <v>0.8722</v>
       </c>
       <c r="Y112" t="n">
-        <v>29.001</v>
+        <v>28.949</v>
       </c>
       <c r="Z112" t="n">
-        <v>61.222</v>
+        <v>61.172</v>
       </c>
       <c r="AA112" t="n">
-        <v>8.99</v>
+        <v>9.042</v>
       </c>
       <c r="AB112" t="n">
-        <v>26.406</v>
+        <v>26.217</v>
       </c>
       <c r="AC112" t="n">
-        <v>19.189</v>
+        <v>19.557</v>
       </c>
       <c r="AD112" t="n">
-        <v>26.045</v>
+        <v>26.314</v>
       </c>
       <c r="AE112" t="n">
-        <v>10.385</v>
+        <v>10.258</v>
       </c>
       <c r="AF112" t="n">
-        <v>22.483</v>
+        <v>22.906</v>
       </c>
       <c r="AG112" t="n">
-        <v>15.255</v>
+        <v>15.246</v>
       </c>
       <c r="AH112" t="n">
-        <v>10.451</v>
+        <v>10.364</v>
       </c>
       <c r="AI112" t="n">
-        <v>3.639</v>
+        <v>3.681</v>
       </c>
       <c r="AJ112" t="n">
-        <v>18.625</v>
+        <v>18.867</v>
       </c>
       <c r="AK112" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AL112" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="113">
@@ -13946,22 +13946,22 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F113" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G113" t="b">
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>1567.789</v>
+        <v>1574.472</v>
       </c>
       <c r="I113" t="n">
-        <v>4.0005</v>
+        <v>3.7174</v>
       </c>
       <c r="J113" t="n">
-        <v>1478.9</v>
+        <v>1481.7</v>
       </c>
       <c r="K113" t="n">
         <v>92</v>
@@ -13982,70 +13982,70 @@
         <v>92</v>
       </c>
       <c r="Q113" t="n">
-        <v>112.703</v>
+        <v>113.985</v>
       </c>
       <c r="R113" t="n">
-        <v>102.707</v>
+        <v>102.458</v>
       </c>
       <c r="S113" t="n">
-        <v>9.996</v>
+        <v>11.527</v>
       </c>
       <c r="T113" t="n">
-        <v>0.30129</v>
+        <v>0.30387</v>
       </c>
       <c r="U113" t="n">
-        <v>0.15494</v>
+        <v>0.15122</v>
       </c>
       <c r="V113" t="n">
-        <v>73.97</v>
+        <v>74.88</v>
       </c>
       <c r="W113" t="n">
-        <v>67.64</v>
+        <v>67.53</v>
       </c>
       <c r="X113" t="n">
-        <v>0.6591</v>
+        <v>0.6702</v>
       </c>
       <c r="Y113" t="n">
-        <v>25.432</v>
+        <v>25.559</v>
       </c>
       <c r="Z113" t="n">
-        <v>58.068</v>
+        <v>58.273</v>
       </c>
       <c r="AA113" t="n">
-        <v>9.125</v>
+        <v>9.382</v>
       </c>
       <c r="AB113" t="n">
-        <v>24.705</v>
+        <v>25.247</v>
       </c>
       <c r="AC113" t="n">
-        <v>13.977</v>
+        <v>14.381</v>
       </c>
       <c r="AD113" t="n">
-        <v>18.5</v>
+        <v>19.049</v>
       </c>
       <c r="AE113" t="n">
-        <v>10.534</v>
+        <v>10.69</v>
       </c>
       <c r="AF113" t="n">
-        <v>24.352</v>
+        <v>24.373</v>
       </c>
       <c r="AG113" t="n">
-        <v>12.466</v>
+        <v>12.495</v>
       </c>
       <c r="AH113" t="n">
-        <v>4.784</v>
+        <v>4.813</v>
       </c>
       <c r="AI113" t="n">
-        <v>3.852</v>
+        <v>3.694</v>
       </c>
       <c r="AJ113" t="n">
-        <v>17.284</v>
+        <v>17.678</v>
       </c>
       <c r="AK113" t="n">
-        <v>13.2</v>
+        <v>20.2</v>
       </c>
       <c r="AL113" t="n">
-        <v>12.3</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="114">
@@ -14306,22 +14306,22 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F116" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G116" t="b">
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>1276.468</v>
+        <v>1274.318</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8273</v>
+        <v>-0.7502</v>
       </c>
       <c r="J116" t="n">
-        <v>1424.2</v>
+        <v>1421.3</v>
       </c>
       <c r="K116" t="n">
         <v>300</v>
@@ -14342,70 +14342,70 @@
         <v>301</v>
       </c>
       <c r="Q116" t="n">
-        <v>103.462</v>
+        <v>102.635</v>
       </c>
       <c r="R116" t="n">
-        <v>112.17</v>
+        <v>112.136</v>
       </c>
       <c r="S116" t="n">
-        <v>-8.708</v>
+        <v>-9.502000000000001</v>
       </c>
       <c r="T116" t="n">
-        <v>0.3045</v>
+        <v>0.29718</v>
       </c>
       <c r="U116" t="n">
-        <v>0.1803</v>
+        <v>0.17965</v>
       </c>
       <c r="V116" t="n">
-        <v>66.56</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="W116" t="n">
-        <v>72.2</v>
+        <v>72.41</v>
       </c>
       <c r="X116" t="n">
-        <v>0.3509</v>
+        <v>0.3305</v>
       </c>
       <c r="Y116" t="n">
-        <v>23.506</v>
+        <v>23.379</v>
       </c>
       <c r="Z116" t="n">
-        <v>53.27</v>
+        <v>53.256</v>
       </c>
       <c r="AA116" t="n">
-        <v>6.127</v>
+        <v>6.174</v>
       </c>
       <c r="AB116" t="n">
-        <v>19.211</v>
+        <v>19.481</v>
       </c>
       <c r="AC116" t="n">
-        <v>13.422</v>
+        <v>13.28</v>
       </c>
       <c r="AD116" t="n">
-        <v>19.183</v>
+        <v>19.174</v>
       </c>
       <c r="AE116" t="n">
-        <v>8.786</v>
+        <v>8.552</v>
       </c>
       <c r="AF116" t="n">
-        <v>20.143</v>
+        <v>20.233</v>
       </c>
       <c r="AG116" t="n">
-        <v>13.814</v>
+        <v>13.718</v>
       </c>
       <c r="AH116" t="n">
-        <v>6.286</v>
+        <v>6.356</v>
       </c>
       <c r="AI116" t="n">
-        <v>3.736</v>
+        <v>3.694</v>
       </c>
       <c r="AJ116" t="n">
-        <v>15.22</v>
+        <v>15.481</v>
       </c>
       <c r="AK116" t="n">
-        <v>-2.4</v>
+        <v>-5.8</v>
       </c>
       <c r="AL116" t="n">
-        <v>-4.2</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="117">
@@ -14546,22 +14546,22 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F118" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G118" t="b">
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>1399.173</v>
+        <v>1403.081</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3774</v>
+        <v>-0.3924</v>
       </c>
       <c r="J118" t="n">
-        <v>1414.5</v>
+        <v>1416.4</v>
       </c>
       <c r="K118" t="n">
         <v>173</v>
@@ -14582,70 +14582,70 @@
         <v>172</v>
       </c>
       <c r="Q118" t="n">
-        <v>110.211</v>
+        <v>110.574</v>
       </c>
       <c r="R118" t="n">
-        <v>107.256</v>
+        <v>107.707</v>
       </c>
       <c r="S118" t="n">
-        <v>2.955</v>
+        <v>2.866</v>
       </c>
       <c r="T118" t="n">
-        <v>0.27607</v>
+        <v>0.27536</v>
       </c>
       <c r="U118" t="n">
-        <v>0.14881</v>
+        <v>0.14631</v>
       </c>
       <c r="V118" t="n">
-        <v>76.39</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="W118" t="n">
-        <v>74.26000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="X118" t="n">
-        <v>0.5208</v>
+        <v>0.5366</v>
       </c>
       <c r="Y118" t="n">
-        <v>25.841</v>
+        <v>25.988</v>
       </c>
       <c r="Z118" t="n">
-        <v>59.763</v>
+        <v>59.935</v>
       </c>
       <c r="AA118" t="n">
-        <v>10.012</v>
+        <v>10.073</v>
       </c>
       <c r="AB118" t="n">
-        <v>28.688</v>
+        <v>28.469</v>
       </c>
       <c r="AC118" t="n">
-        <v>14.692</v>
+        <v>14.302</v>
       </c>
       <c r="AD118" t="n">
-        <v>20.068</v>
+        <v>19.626</v>
       </c>
       <c r="AE118" t="n">
-        <v>9.516</v>
+        <v>9.423</v>
       </c>
       <c r="AF118" t="n">
-        <v>24.439</v>
+        <v>24.291</v>
       </c>
       <c r="AG118" t="n">
-        <v>11.951</v>
+        <v>11.967</v>
       </c>
       <c r="AH118" t="n">
-        <v>5.67</v>
+        <v>5.622</v>
       </c>
       <c r="AI118" t="n">
-        <v>2.372</v>
+        <v>2.331</v>
       </c>
       <c r="AJ118" t="n">
-        <v>18.868</v>
+        <v>18.861</v>
       </c>
       <c r="AK118" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AL118" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="119">
@@ -14666,22 +14666,22 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F119" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G119" t="b">
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1332.544</v>
+        <v>1330.675</v>
       </c>
       <c r="I119" t="n">
-        <v>-1.6577</v>
+        <v>-1.6311</v>
       </c>
       <c r="J119" t="n">
-        <v>1424.5</v>
+        <v>1426.8</v>
       </c>
       <c r="K119" t="n">
         <v>238</v>
@@ -14702,70 +14702,70 @@
         <v>229</v>
       </c>
       <c r="Q119" t="n">
-        <v>110.743</v>
+        <v>110.59</v>
       </c>
       <c r="R119" t="n">
-        <v>116.752</v>
+        <v>116.92</v>
       </c>
       <c r="S119" t="n">
-        <v>-6.01</v>
+        <v>-6.329</v>
       </c>
       <c r="T119" t="n">
-        <v>0.32286</v>
+        <v>0.31844</v>
       </c>
       <c r="U119" t="n">
-        <v>0.16677</v>
+        <v>0.16669</v>
       </c>
       <c r="V119" t="n">
-        <v>73.48</v>
+        <v>73.67</v>
       </c>
       <c r="W119" t="n">
-        <v>77.2</v>
+        <v>77.63</v>
       </c>
       <c r="X119" t="n">
-        <v>0.3509</v>
+        <v>0.3305</v>
       </c>
       <c r="Y119" t="n">
-        <v>25.009</v>
+        <v>25.042</v>
       </c>
       <c r="Z119" t="n">
         <v>55.876</v>
       </c>
       <c r="AA119" t="n">
-        <v>7.888</v>
+        <v>7.859</v>
       </c>
       <c r="AB119" t="n">
-        <v>23.363</v>
+        <v>23.397</v>
       </c>
       <c r="AC119" t="n">
-        <v>15.571</v>
+        <v>15.728</v>
       </c>
       <c r="AD119" t="n">
-        <v>21.022</v>
+        <v>21.259</v>
       </c>
       <c r="AE119" t="n">
-        <v>9.853999999999999</v>
+        <v>9.727</v>
       </c>
       <c r="AF119" t="n">
-        <v>20.73</v>
+        <v>20.994</v>
       </c>
       <c r="AG119" t="n">
-        <v>11.786</v>
+        <v>11.76</v>
       </c>
       <c r="AH119" t="n">
-        <v>5.23</v>
+        <v>5.148</v>
       </c>
       <c r="AI119" t="n">
-        <v>3.938</v>
+        <v>3.967</v>
       </c>
       <c r="AJ119" t="n">
-        <v>17.677</v>
+        <v>18.17</v>
       </c>
       <c r="AK119" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AL119" t="n">
-        <v>-8.1</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="120">
@@ -14786,22 +14786,22 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F120" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G120" t="b">
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>1535.465</v>
+        <v>1528.61</v>
       </c>
       <c r="I120" t="n">
-        <v>2.1038</v>
+        <v>2.2588</v>
       </c>
       <c r="J120" t="n">
-        <v>1506.5</v>
+        <v>1508.7</v>
       </c>
       <c r="K120" t="n">
         <v>110</v>
@@ -14822,70 +14822,70 @@
         <v>116</v>
       </c>
       <c r="Q120" t="n">
-        <v>108.471</v>
+        <v>108.828</v>
       </c>
       <c r="R120" t="n">
-        <v>102.466</v>
+        <v>104.272</v>
       </c>
       <c r="S120" t="n">
-        <v>6.005</v>
+        <v>4.556</v>
       </c>
       <c r="T120" t="n">
-        <v>0.34287</v>
+        <v>0.34057</v>
       </c>
       <c r="U120" t="n">
-        <v>0.16411</v>
+        <v>0.16472</v>
       </c>
       <c r="V120" t="n">
-        <v>74.11</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="W120" t="n">
-        <v>70.04000000000001</v>
+        <v>70.72</v>
       </c>
       <c r="X120" t="n">
-        <v>0.552</v>
+        <v>0.5273</v>
       </c>
       <c r="Y120" t="n">
-        <v>25.752</v>
+        <v>25.944</v>
       </c>
       <c r="Z120" t="n">
-        <v>58.656</v>
+        <v>58.305</v>
       </c>
       <c r="AA120" t="n">
-        <v>6.216</v>
+        <v>6.448</v>
       </c>
       <c r="AB120" t="n">
-        <v>19.76</v>
+        <v>19.867</v>
       </c>
       <c r="AC120" t="n">
-        <v>15.976</v>
+        <v>15.769</v>
       </c>
       <c r="AD120" t="n">
-        <v>22.104</v>
+        <v>21.778</v>
       </c>
       <c r="AE120" t="n">
-        <v>11.288</v>
+        <v>11.125</v>
       </c>
       <c r="AF120" t="n">
-        <v>22.12</v>
+        <v>21.947</v>
       </c>
       <c r="AG120" t="n">
-        <v>13.736</v>
+        <v>14.175</v>
       </c>
       <c r="AH120" t="n">
-        <v>7.792</v>
+        <v>7.622</v>
       </c>
       <c r="AI120" t="n">
-        <v>3.728</v>
+        <v>3.79</v>
       </c>
       <c r="AJ120" t="n">
-        <v>17.12</v>
+        <v>17.04</v>
       </c>
       <c r="AK120" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="AL120" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="121">
@@ -14906,22 +14906,22 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F121" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G121" t="b">
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>1999.75</v>
+        <v>2003.313</v>
       </c>
       <c r="I121" t="n">
-        <v>8.6837</v>
+        <v>8.2525</v>
       </c>
       <c r="J121" t="n">
-        <v>1712.9</v>
+        <v>1709.5</v>
       </c>
       <c r="K121" t="n">
         <v>5</v>
@@ -14942,70 +14942,70 @@
         <v>5</v>
       </c>
       <c r="Q121" t="n">
-        <v>125.293</v>
+        <v>125.482</v>
       </c>
       <c r="R121" t="n">
-        <v>102.127</v>
+        <v>103.074</v>
       </c>
       <c r="S121" t="n">
-        <v>23.166</v>
+        <v>22.408</v>
       </c>
       <c r="T121" t="n">
-        <v>0.32162</v>
+        <v>0.32381</v>
       </c>
       <c r="U121" t="n">
-        <v>0.12962</v>
+        <v>0.12946</v>
       </c>
       <c r="V121" t="n">
-        <v>84.41</v>
+        <v>84.19</v>
       </c>
       <c r="W121" t="n">
-        <v>68.84</v>
+        <v>69.16</v>
       </c>
       <c r="X121" t="n">
-        <v>0.7696</v>
+        <v>0.7768</v>
       </c>
       <c r="Y121" t="n">
-        <v>28.572</v>
+        <v>28.455</v>
       </c>
       <c r="Z121" t="n">
-        <v>62.08</v>
+        <v>61.664</v>
       </c>
       <c r="AA121" t="n">
-        <v>11.152</v>
+        <v>10.899</v>
       </c>
       <c r="AB121" t="n">
-        <v>31.754</v>
+        <v>31.365</v>
       </c>
       <c r="AC121" t="n">
-        <v>16.114</v>
+        <v>16.377</v>
       </c>
       <c r="AD121" t="n">
-        <v>20.32</v>
+        <v>20.643</v>
       </c>
       <c r="AE121" t="n">
-        <v>12.42</v>
+        <v>12.383</v>
       </c>
       <c r="AF121" t="n">
-        <v>26.462</v>
+        <v>26.133</v>
       </c>
       <c r="AG121" t="n">
-        <v>14.646</v>
+        <v>14.638</v>
       </c>
       <c r="AH121" t="n">
-        <v>3.828</v>
+        <v>3.852</v>
       </c>
       <c r="AI121" t="n">
-        <v>4.745</v>
+        <v>4.69</v>
       </c>
       <c r="AJ121" t="n">
-        <v>13.049</v>
+        <v>13.052</v>
       </c>
       <c r="AK121" t="n">
-        <v>13.4</v>
+        <v>10.6</v>
       </c>
       <c r="AL121" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="122">
@@ -15626,22 +15626,22 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F127" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G127" t="b">
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>1851.166</v>
+        <v>1843.67</v>
       </c>
       <c r="I127" t="n">
-        <v>4.4379</v>
+        <v>4.0673</v>
       </c>
       <c r="J127" t="n">
-        <v>1708.5</v>
+        <v>1715.1</v>
       </c>
       <c r="K127" t="n">
         <v>24</v>
@@ -15662,70 +15662,70 @@
         <v>28</v>
       </c>
       <c r="Q127" t="n">
-        <v>119.277</v>
+        <v>118.626</v>
       </c>
       <c r="R127" t="n">
-        <v>103.76</v>
+        <v>104.063</v>
       </c>
       <c r="S127" t="n">
-        <v>15.516</v>
+        <v>14.562</v>
       </c>
       <c r="T127" t="n">
-        <v>0.29249</v>
+        <v>0.28798</v>
       </c>
       <c r="U127" t="n">
-        <v>0.13882</v>
+        <v>0.1446</v>
       </c>
       <c r="V127" t="n">
-        <v>75.34</v>
+        <v>75.41</v>
       </c>
       <c r="W127" t="n">
-        <v>65.31</v>
+        <v>66.05</v>
       </c>
       <c r="X127" t="n">
-        <v>0.6583</v>
+        <v>0.6377</v>
       </c>
       <c r="Y127" t="n">
-        <v>26.547</v>
+        <v>26.586</v>
       </c>
       <c r="Z127" t="n">
-        <v>54.257</v>
+        <v>54.214</v>
       </c>
       <c r="AA127" t="n">
-        <v>7.79</v>
+        <v>7.939</v>
       </c>
       <c r="AB127" t="n">
-        <v>22.215</v>
+        <v>22.507</v>
       </c>
       <c r="AC127" t="n">
-        <v>14.456</v>
+        <v>14.304</v>
       </c>
       <c r="AD127" t="n">
-        <v>18.55</v>
+        <v>18.475</v>
       </c>
       <c r="AE127" t="n">
-        <v>8.090999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="AF127" t="n">
-        <v>19.509</v>
+        <v>19.803</v>
       </c>
       <c r="AG127" t="n">
-        <v>15.132</v>
+        <v>15.214</v>
       </c>
       <c r="AH127" t="n">
-        <v>7.066</v>
+        <v>7.151</v>
       </c>
       <c r="AI127" t="n">
-        <v>2.099</v>
+        <v>2.009</v>
       </c>
       <c r="AJ127" t="n">
-        <v>17.886</v>
+        <v>17.841</v>
       </c>
       <c r="AK127" t="n">
-        <v>0.8</v>
+        <v>-2</v>
       </c>
       <c r="AL127" t="n">
-        <v>1</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="128">
@@ -17546,22 +17546,22 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F143" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G143" t="b">
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>1320.085</v>
+        <v>1323.097</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.7048</v>
+        <v>-0.5849</v>
       </c>
       <c r="J143" t="n">
-        <v>1399.1</v>
+        <v>1401.7</v>
       </c>
       <c r="K143" t="n">
         <v>295</v>
@@ -17582,70 +17582,70 @@
         <v>290</v>
       </c>
       <c r="Q143" t="n">
-        <v>104.373</v>
+        <v>104.757</v>
       </c>
       <c r="R143" t="n">
-        <v>108.739</v>
+        <v>108.578</v>
       </c>
       <c r="S143" t="n">
-        <v>-4.366</v>
+        <v>-3.822</v>
       </c>
       <c r="T143" t="n">
-        <v>0.21826</v>
+        <v>0.21403</v>
       </c>
       <c r="U143" t="n">
-        <v>0.17351</v>
+        <v>0.17293</v>
       </c>
       <c r="V143" t="n">
-        <v>72.15000000000001</v>
+        <v>72.37</v>
       </c>
       <c r="W143" t="n">
-        <v>75.2</v>
+        <v>75.05</v>
       </c>
       <c r="X143" t="n">
-        <v>0.4745</v>
+        <v>0.4909</v>
       </c>
       <c r="Y143" t="n">
-        <v>25.818</v>
+        <v>25.855</v>
       </c>
       <c r="Z143" t="n">
-        <v>55.854</v>
+        <v>55.6</v>
       </c>
       <c r="AA143" t="n">
-        <v>7.708</v>
+        <v>7.7</v>
       </c>
       <c r="AB143" t="n">
-        <v>21.374</v>
+        <v>21.25</v>
       </c>
       <c r="AC143" t="n">
-        <v>12.81</v>
+        <v>12.964</v>
       </c>
       <c r="AD143" t="n">
-        <v>17.452</v>
+        <v>17.782</v>
       </c>
       <c r="AE143" t="n">
-        <v>6.31</v>
+        <v>6.195</v>
       </c>
       <c r="AF143" t="n">
-        <v>22.304</v>
+        <v>22.541</v>
       </c>
       <c r="AG143" t="n">
-        <v>13.956</v>
+        <v>14.045</v>
       </c>
       <c r="AH143" t="n">
-        <v>6.77</v>
+        <v>6.686</v>
       </c>
       <c r="AI143" t="n">
-        <v>3.003</v>
+        <v>3.032</v>
       </c>
       <c r="AJ143" t="n">
-        <v>16.197</v>
+        <v>16.055</v>
       </c>
       <c r="AK143" t="n">
-        <v>-0.4</v>
+        <v>5.6</v>
       </c>
       <c r="AL143" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="144">
@@ -19346,22 +19346,22 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F158" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G158" t="b">
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>1497.499</v>
+        <v>1491.625</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0359</v>
+        <v>0.0074</v>
       </c>
       <c r="J158" t="n">
-        <v>1420.3</v>
+        <v>1423.5</v>
       </c>
       <c r="K158" t="n">
         <v>201</v>
@@ -19382,70 +19382,70 @@
         <v>182</v>
       </c>
       <c r="Q158" t="n">
-        <v>104.471</v>
+        <v>103.772</v>
       </c>
       <c r="R158" t="n">
-        <v>96.88500000000001</v>
+        <v>96.51600000000001</v>
       </c>
       <c r="S158" t="n">
-        <v>7.586</v>
+        <v>7.257</v>
       </c>
       <c r="T158" t="n">
-        <v>0.2682</v>
+        <v>0.27037</v>
       </c>
       <c r="U158" t="n">
-        <v>0.15965</v>
+        <v>0.16537</v>
       </c>
       <c r="V158" t="n">
-        <v>69.37</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="W158" t="n">
-        <v>64.22</v>
+        <v>63.89</v>
       </c>
       <c r="X158" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.5959</v>
       </c>
       <c r="Y158" t="n">
-        <v>25.327</v>
+        <v>25.251</v>
       </c>
       <c r="Z158" t="n">
-        <v>58.106</v>
+        <v>57.906</v>
       </c>
       <c r="AA158" t="n">
-        <v>6.528</v>
+        <v>6.417</v>
       </c>
       <c r="AB158" t="n">
-        <v>20.445</v>
+        <v>20.07</v>
       </c>
       <c r="AC158" t="n">
-        <v>12.101</v>
+        <v>11.833</v>
       </c>
       <c r="AD158" t="n">
-        <v>15.571</v>
+        <v>15.23</v>
       </c>
       <c r="AE158" t="n">
-        <v>9.128</v>
+        <v>9.226000000000001</v>
       </c>
       <c r="AF158" t="n">
-        <v>24.509</v>
+        <v>24.503</v>
       </c>
       <c r="AG158" t="n">
-        <v>14.848</v>
+        <v>14.868</v>
       </c>
       <c r="AH158" t="n">
-        <v>7.144</v>
+        <v>7.012</v>
       </c>
       <c r="AI158" t="n">
-        <v>2.897</v>
+        <v>2.981</v>
       </c>
       <c r="AJ158" t="n">
-        <v>16.973</v>
+        <v>16.847</v>
       </c>
       <c r="AK158" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AL158" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="159">
@@ -19586,22 +19586,22 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F160" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G160" t="b">
         <v>1</v>
       </c>
       <c r="H160" t="n">
-        <v>1505.033</v>
+        <v>1498.893</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6916</v>
+        <v>-0.6787</v>
       </c>
       <c r="J160" t="n">
-        <v>1448.1</v>
+        <v>1448.2</v>
       </c>
       <c r="K160" t="n">
         <v>197</v>
@@ -19622,70 +19622,70 @@
         <v>162</v>
       </c>
       <c r="Q160" t="n">
-        <v>114.099</v>
+        <v>113.862</v>
       </c>
       <c r="R160" t="n">
-        <v>111.782</v>
+        <v>111.607</v>
       </c>
       <c r="S160" t="n">
-        <v>2.317</v>
+        <v>2.255</v>
       </c>
       <c r="T160" t="n">
-        <v>0.29154</v>
+        <v>0.29726</v>
       </c>
       <c r="U160" t="n">
-        <v>0.15801</v>
+        <v>0.158</v>
       </c>
       <c r="V160" t="n">
-        <v>80.55</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="W160" t="n">
-        <v>78.98</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="X160" t="n">
-        <v>0.5937</v>
+        <v>0.575</v>
       </c>
       <c r="Y160" t="n">
-        <v>28.736</v>
+        <v>28.619</v>
       </c>
       <c r="Z160" t="n">
-        <v>61.388</v>
+        <v>61.614</v>
       </c>
       <c r="AA160" t="n">
-        <v>9.978999999999999</v>
+        <v>9.875</v>
       </c>
       <c r="AB160" t="n">
-        <v>27.157</v>
+        <v>27.182</v>
       </c>
       <c r="AC160" t="n">
-        <v>13.097</v>
+        <v>13.481</v>
       </c>
       <c r="AD160" t="n">
-        <v>17.954</v>
+        <v>18.363</v>
       </c>
       <c r="AE160" t="n">
-        <v>9.869999999999999</v>
+        <v>10.238</v>
       </c>
       <c r="AF160" t="n">
-        <v>23.606</v>
+        <v>23.69</v>
       </c>
       <c r="AG160" t="n">
-        <v>16.352</v>
+        <v>16.101</v>
       </c>
       <c r="AH160" t="n">
-        <v>6.088</v>
+        <v>6.054</v>
       </c>
       <c r="AI160" t="n">
-        <v>4.75</v>
+        <v>4.808</v>
       </c>
       <c r="AJ160" t="n">
-        <v>20.397</v>
+        <v>20.207</v>
       </c>
       <c r="AK160" t="n">
-        <v>-1.4</v>
+        <v>-3</v>
       </c>
       <c r="AL160" t="n">
-        <v>-2.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="161">
@@ -19706,22 +19706,22 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F161" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G161" t="b">
         <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>1601.614</v>
+        <v>1598.051</v>
       </c>
       <c r="I161" t="n">
-        <v>-8.364800000000001</v>
+        <v>-8.074299999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>1713.6</v>
+        <v>1724.9</v>
       </c>
       <c r="K161" t="n">
         <v>130</v>
@@ -19742,70 +19742,70 @@
         <v>146</v>
       </c>
       <c r="Q161" t="n">
-        <v>102.768</v>
+        <v>103.933</v>
       </c>
       <c r="R161" t="n">
-        <v>114.807</v>
+        <v>115.229</v>
       </c>
       <c r="S161" t="n">
-        <v>-12.039</v>
+        <v>-11.296</v>
       </c>
       <c r="T161" t="n">
-        <v>0.3181</v>
+        <v>0.32036</v>
       </c>
       <c r="U161" t="n">
-        <v>0.17731</v>
+        <v>0.17539</v>
       </c>
       <c r="V161" t="n">
-        <v>69.43000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="W161" t="n">
-        <v>77.15000000000001</v>
+        <v>77.17</v>
       </c>
       <c r="X161" t="n">
-        <v>0.3612</v>
+        <v>0.35</v>
       </c>
       <c r="Y161" t="n">
-        <v>23.01</v>
+        <v>23.232</v>
       </c>
       <c r="Z161" t="n">
-        <v>57.117</v>
+        <v>57.082</v>
       </c>
       <c r="AA161" t="n">
-        <v>8.475</v>
+        <v>8.491</v>
       </c>
       <c r="AB161" t="n">
-        <v>26.698</v>
+        <v>26.786</v>
       </c>
       <c r="AC161" t="n">
-        <v>14.939</v>
+        <v>14.945</v>
       </c>
       <c r="AD161" t="n">
-        <v>20.731</v>
+        <v>20.695</v>
       </c>
       <c r="AE161" t="n">
-        <v>10.704</v>
+        <v>10.714</v>
       </c>
       <c r="AF161" t="n">
-        <v>22.391</v>
+        <v>22.214</v>
       </c>
       <c r="AG161" t="n">
-        <v>10.511</v>
+        <v>10.418</v>
       </c>
       <c r="AH161" t="n">
-        <v>4.711</v>
+        <v>4.686</v>
       </c>
       <c r="AI161" t="n">
-        <v>2.869</v>
+        <v>2.873</v>
       </c>
       <c r="AJ161" t="n">
-        <v>18.069</v>
+        <v>18.186</v>
       </c>
       <c r="AK161" t="n">
-        <v>-10</v>
+        <v>-10.4</v>
       </c>
       <c r="AL161" t="n">
-        <v>-9.9</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="162">
@@ -20186,22 +20186,22 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F165" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G165" t="b">
         <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>1560.22</v>
+        <v>1567.005</v>
       </c>
       <c r="I165" t="n">
-        <v>-5.242</v>
+        <v>-5.2285</v>
       </c>
       <c r="J165" t="n">
-        <v>1612.9</v>
+        <v>1607.8</v>
       </c>
       <c r="K165" t="n">
         <v>131</v>
@@ -20222,70 +20222,70 @@
         <v>130</v>
       </c>
       <c r="Q165" t="n">
-        <v>103.892</v>
+        <v>104.684</v>
       </c>
       <c r="R165" t="n">
-        <v>105.682</v>
+        <v>106.286</v>
       </c>
       <c r="S165" t="n">
-        <v>-1.789</v>
+        <v>-1.603</v>
       </c>
       <c r="T165" t="n">
-        <v>0.33901</v>
+        <v>0.33967</v>
       </c>
       <c r="U165" t="n">
-        <v>0.18228</v>
+        <v>0.18237</v>
       </c>
       <c r="V165" t="n">
-        <v>74.86</v>
+        <v>75.58</v>
       </c>
       <c r="W165" t="n">
-        <v>76.11</v>
+        <v>76.7</v>
       </c>
       <c r="X165" t="n">
-        <v>0.3966</v>
+        <v>0.424</v>
       </c>
       <c r="Y165" t="n">
-        <v>26.688</v>
+        <v>26.848</v>
       </c>
       <c r="Z165" t="n">
-        <v>61.507</v>
+        <v>61.456</v>
       </c>
       <c r="AA165" t="n">
-        <v>6.545</v>
+        <v>6.584</v>
       </c>
       <c r="AB165" t="n">
-        <v>20.659</v>
+        <v>20.632</v>
       </c>
       <c r="AC165" t="n">
-        <v>14.935</v>
+        <v>15.304</v>
       </c>
       <c r="AD165" t="n">
-        <v>20.596</v>
+        <v>21.184</v>
       </c>
       <c r="AE165" t="n">
-        <v>11.588</v>
+        <v>11.704</v>
       </c>
       <c r="AF165" t="n">
-        <v>22.231</v>
+        <v>22.384</v>
       </c>
       <c r="AG165" t="n">
-        <v>13.481</v>
+        <v>13.496</v>
       </c>
       <c r="AH165" t="n">
-        <v>8.585000000000001</v>
+        <v>8.528</v>
       </c>
       <c r="AI165" t="n">
-        <v>4.174</v>
+        <v>4.24</v>
       </c>
       <c r="AJ165" t="n">
-        <v>20.407</v>
+        <v>20.272</v>
       </c>
       <c r="AK165" t="n">
-        <v>-12.2</v>
+        <v>-7.8</v>
       </c>
       <c r="AL165" t="n">
-        <v>-6.1</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="166">
@@ -20666,22 +20666,22 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F169" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G169" t="b">
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>2181.167</v>
+        <v>2189.25</v>
       </c>
       <c r="I169" t="n">
-        <v>7.6139</v>
+        <v>7.2681</v>
       </c>
       <c r="J169" t="n">
-        <v>1758.2</v>
+        <v>1769.7</v>
       </c>
       <c r="K169" t="n">
         <v>2</v>
@@ -20702,70 +20702,70 @@
         <v>2</v>
       </c>
       <c r="Q169" t="n">
-        <v>121.542</v>
+        <v>121.973</v>
       </c>
       <c r="R169" t="n">
-        <v>95.232</v>
+        <v>95.941</v>
       </c>
       <c r="S169" t="n">
-        <v>26.31</v>
+        <v>26.032</v>
       </c>
       <c r="T169" t="n">
-        <v>0.26417</v>
+        <v>0.26323</v>
       </c>
       <c r="U169" t="n">
-        <v>0.16783</v>
+        <v>0.16569</v>
       </c>
       <c r="V169" t="n">
-        <v>88.18000000000001</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="W169" t="n">
-        <v>68.69</v>
+        <v>69.17</v>
       </c>
       <c r="X169" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9361</v>
       </c>
       <c r="Y169" t="n">
-        <v>30.861</v>
+        <v>30.769</v>
       </c>
       <c r="Z169" t="n">
-        <v>60.37</v>
+        <v>60.303</v>
       </c>
       <c r="AA169" t="n">
-        <v>9.231999999999999</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="AB169" t="n">
-        <v>25.424</v>
+        <v>25.418</v>
       </c>
       <c r="AC169" t="n">
-        <v>17.231</v>
+        <v>17.599</v>
       </c>
       <c r="AD169" t="n">
-        <v>23.319</v>
+        <v>23.569</v>
       </c>
       <c r="AE169" t="n">
-        <v>10.21</v>
+        <v>10.14</v>
       </c>
       <c r="AF169" t="n">
-        <v>28.186</v>
+        <v>28.118</v>
       </c>
       <c r="AG169" t="n">
-        <v>18.981</v>
+        <v>18.74</v>
       </c>
       <c r="AH169" t="n">
-        <v>5.924</v>
+        <v>5.769</v>
       </c>
       <c r="AI169" t="n">
-        <v>5.858</v>
+        <v>5.914</v>
       </c>
       <c r="AJ169" t="n">
-        <v>15.715</v>
+        <v>15.786</v>
       </c>
       <c r="AK169" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AL169" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="170">
@@ -20786,22 +20786,22 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F170" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G170" t="b">
         <v>1</v>
       </c>
       <c r="H170" t="n">
-        <v>2057.84</v>
+        <v>2049.759</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2001</v>
+        <v>0.2376</v>
       </c>
       <c r="J170" t="n">
-        <v>1707.1</v>
+        <v>1729.6</v>
       </c>
       <c r="K170" t="n">
         <v>9</v>
@@ -20822,70 +20822,70 @@
         <v>11</v>
       </c>
       <c r="Q170" t="n">
-        <v>117.414</v>
+        <v>117.051</v>
       </c>
       <c r="R170" t="n">
-        <v>100.056</v>
+        <v>100.921</v>
       </c>
       <c r="S170" t="n">
-        <v>17.358</v>
+        <v>16.13</v>
       </c>
       <c r="T170" t="n">
-        <v>0.29889</v>
+        <v>0.29928</v>
       </c>
       <c r="U170" t="n">
-        <v>0.16503</v>
+        <v>0.16152</v>
       </c>
       <c r="V170" t="n">
-        <v>78.89</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="W170" t="n">
-        <v>67.28</v>
+        <v>68.03</v>
       </c>
       <c r="X170" t="n">
-        <v>0.8354</v>
+        <v>0.7971</v>
       </c>
       <c r="Y170" t="n">
-        <v>27.544</v>
+        <v>27.565</v>
       </c>
       <c r="Z170" t="n">
-        <v>58.168</v>
+        <v>58.528</v>
       </c>
       <c r="AA170" t="n">
-        <v>7.555</v>
+        <v>7.53</v>
       </c>
       <c r="AB170" t="n">
-        <v>21.249</v>
+        <v>21.22</v>
       </c>
       <c r="AC170" t="n">
-        <v>16.245</v>
+        <v>16.128</v>
       </c>
       <c r="AD170" t="n">
-        <v>21.31</v>
+        <v>21.148</v>
       </c>
       <c r="AE170" t="n">
-        <v>11.473</v>
+        <v>11.403</v>
       </c>
       <c r="AF170" t="n">
-        <v>26.56</v>
+        <v>26.368</v>
       </c>
       <c r="AG170" t="n">
-        <v>18.375</v>
+        <v>18.264</v>
       </c>
       <c r="AH170" t="n">
-        <v>5.185</v>
+        <v>5.191</v>
       </c>
       <c r="AI170" t="n">
-        <v>4.235</v>
+        <v>4.148</v>
       </c>
       <c r="AJ170" t="n">
-        <v>16.053</v>
+        <v>16.325</v>
       </c>
       <c r="AK170" t="n">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="AL170" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="171">
@@ -21626,22 +21626,22 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F177" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G177" t="b">
         <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>1443.63</v>
+        <v>1447.398</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1405</v>
+        <v>1.1918</v>
       </c>
       <c r="J177" t="n">
-        <v>1459</v>
+        <v>1458.5</v>
       </c>
       <c r="K177" t="n">
         <v>190</v>
@@ -21662,70 +21662,70 @@
         <v>179</v>
       </c>
       <c r="Q177" t="n">
-        <v>106.983</v>
+        <v>106.485</v>
       </c>
       <c r="R177" t="n">
-        <v>105.894</v>
+        <v>105.001</v>
       </c>
       <c r="S177" t="n">
-        <v>1.089</v>
+        <v>1.484</v>
       </c>
       <c r="T177" t="n">
-        <v>0.31022</v>
+        <v>0.30647</v>
       </c>
       <c r="U177" t="n">
-        <v>0.16246</v>
+        <v>0.16555</v>
       </c>
       <c r="V177" t="n">
-        <v>72.41</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="W177" t="n">
-        <v>71.62</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="X177" t="n">
-        <v>0.5382</v>
+        <v>0.5528</v>
       </c>
       <c r="Y177" t="n">
-        <v>25.676</v>
+        <v>25.46</v>
       </c>
       <c r="Z177" t="n">
-        <v>58.535</v>
+        <v>58.114</v>
       </c>
       <c r="AA177" t="n">
-        <v>7.043</v>
+        <v>6.949</v>
       </c>
       <c r="AB177" t="n">
-        <v>20.066</v>
+        <v>19.939</v>
       </c>
       <c r="AC177" t="n">
-        <v>14.013</v>
+        <v>14.064</v>
       </c>
       <c r="AD177" t="n">
-        <v>18.795</v>
+        <v>18.831</v>
       </c>
       <c r="AE177" t="n">
-        <v>10.165</v>
+        <v>10.076</v>
       </c>
       <c r="AF177" t="n">
-        <v>22.364</v>
+        <v>22.592</v>
       </c>
       <c r="AG177" t="n">
-        <v>13.988</v>
+        <v>13.843</v>
       </c>
       <c r="AH177" t="n">
-        <v>7.417</v>
+        <v>7.508</v>
       </c>
       <c r="AI177" t="n">
-        <v>4.177</v>
+        <v>4.442</v>
       </c>
       <c r="AJ177" t="n">
-        <v>15.958</v>
+        <v>15.917</v>
       </c>
       <c r="AK177" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AL177" t="n">
         <v>2.8</v>
-      </c>
-      <c r="AL177" t="n">
-        <v>2.2</v>
       </c>
     </row>
     <row r="178">
@@ -21866,22 +21866,22 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F179" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G179" t="b">
         <v>1</v>
       </c>
       <c r="H179" t="n">
-        <v>1436.33</v>
+        <v>1432.421</v>
       </c>
       <c r="I179" t="n">
-        <v>3.2578</v>
+        <v>3.1402</v>
       </c>
       <c r="J179" t="n">
-        <v>1437.7</v>
+        <v>1437.1</v>
       </c>
       <c r="K179" t="n">
         <v>135</v>
@@ -21902,70 +21902,70 @@
         <v>134</v>
       </c>
       <c r="Q179" t="n">
-        <v>112.044</v>
+        <v>111.832</v>
       </c>
       <c r="R179" t="n">
-        <v>108.249</v>
+        <v>108.605</v>
       </c>
       <c r="S179" t="n">
-        <v>3.795</v>
+        <v>3.227</v>
       </c>
       <c r="T179" t="n">
-        <v>0.26246</v>
+        <v>0.25636</v>
       </c>
       <c r="U179" t="n">
-        <v>0.14171</v>
+        <v>0.14098</v>
       </c>
       <c r="V179" t="n">
-        <v>75.72</v>
+        <v>75.64</v>
       </c>
       <c r="W179" t="n">
-        <v>73.27</v>
+        <v>73.56</v>
       </c>
       <c r="X179" t="n">
-        <v>0.5404</v>
+        <v>0.5124</v>
       </c>
       <c r="Y179" t="n">
-        <v>26.515</v>
+        <v>26.696</v>
       </c>
       <c r="Z179" t="n">
-        <v>58.111</v>
+        <v>58.006</v>
       </c>
       <c r="AA179" t="n">
-        <v>9.384</v>
+        <v>9.124000000000001</v>
       </c>
       <c r="AB179" t="n">
-        <v>26.192</v>
+        <v>25.702</v>
       </c>
       <c r="AC179" t="n">
-        <v>13.303</v>
+        <v>13.298</v>
       </c>
       <c r="AD179" t="n">
-        <v>17.914</v>
+        <v>17.966</v>
       </c>
       <c r="AE179" t="n">
-        <v>8</v>
+        <v>7.826</v>
       </c>
       <c r="AF179" t="n">
-        <v>22.066</v>
+        <v>22.382</v>
       </c>
       <c r="AG179" t="n">
-        <v>10.566</v>
+        <v>10.503</v>
       </c>
       <c r="AH179" t="n">
-        <v>6.626</v>
+        <v>6.398</v>
       </c>
       <c r="AI179" t="n">
-        <v>2.823</v>
+        <v>2.829</v>
       </c>
       <c r="AJ179" t="n">
-        <v>16.157</v>
+        <v>15.866</v>
       </c>
       <c r="AK179" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AL179" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="180">
@@ -22826,22 +22826,22 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F187" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G187" t="b">
         <v>1</v>
       </c>
       <c r="H187" t="n">
-        <v>1591.399</v>
+        <v>1593.755</v>
       </c>
       <c r="I187" t="n">
-        <v>3.6609</v>
+        <v>3.5257</v>
       </c>
       <c r="J187" t="n">
-        <v>1412</v>
+        <v>1410.6</v>
       </c>
       <c r="K187" t="n">
         <v>118</v>
@@ -22862,70 +22862,70 @@
         <v>117</v>
       </c>
       <c r="Q187" t="n">
-        <v>114.4</v>
+        <v>114.28</v>
       </c>
       <c r="R187" t="n">
-        <v>102.119</v>
+        <v>102.18</v>
       </c>
       <c r="S187" t="n">
-        <v>12.281</v>
+        <v>12.099</v>
       </c>
       <c r="T187" t="n">
-        <v>0.31051</v>
+        <v>0.31044</v>
       </c>
       <c r="U187" t="n">
-        <v>0.14952</v>
+        <v>0.15061</v>
       </c>
       <c r="V187" t="n">
-        <v>79.31999999999999</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="W187" t="n">
-        <v>70.89</v>
+        <v>70.7</v>
       </c>
       <c r="X187" t="n">
-        <v>0.7687</v>
+        <v>0.776</v>
       </c>
       <c r="Y187" t="n">
-        <v>28.181</v>
+        <v>28.072</v>
       </c>
       <c r="Z187" t="n">
-        <v>61.611</v>
+        <v>61.408</v>
       </c>
       <c r="AA187" t="n">
-        <v>9.355</v>
+        <v>9.391999999999999</v>
       </c>
       <c r="AB187" t="n">
-        <v>26.389</v>
+        <v>26.232</v>
       </c>
       <c r="AC187" t="n">
-        <v>13.603</v>
+        <v>13.456</v>
       </c>
       <c r="AD187" t="n">
-        <v>18.852</v>
+        <v>18.84</v>
       </c>
       <c r="AE187" t="n">
-        <v>10.859</v>
+        <v>10.912</v>
       </c>
       <c r="AF187" t="n">
-        <v>23.549</v>
+        <v>23.688</v>
       </c>
       <c r="AG187" t="n">
-        <v>14.991</v>
+        <v>14.88</v>
       </c>
       <c r="AH187" t="n">
-        <v>7.859</v>
+        <v>7.712</v>
       </c>
       <c r="AI187" t="n">
-        <v>2.859</v>
+        <v>2.832</v>
       </c>
       <c r="AJ187" t="n">
-        <v>15.198</v>
+        <v>15.152</v>
       </c>
       <c r="AK187" t="n">
-        <v>16.4</v>
+        <v>10.8</v>
       </c>
       <c r="AL187" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="188">
@@ -23066,22 +23066,22 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F189" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G189" t="b">
         <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>1436.269</v>
+        <v>1439.016</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2764</v>
+        <v>0.2239</v>
       </c>
       <c r="J189" t="n">
-        <v>1430.7</v>
+        <v>1427.9</v>
       </c>
       <c r="K189" t="n">
         <v>178</v>
@@ -23102,70 +23102,70 @@
         <v>189</v>
       </c>
       <c r="Q189" t="n">
-        <v>111.931</v>
+        <v>113.32</v>
       </c>
       <c r="R189" t="n">
-        <v>108.718</v>
+        <v>108.95</v>
       </c>
       <c r="S189" t="n">
-        <v>3.213</v>
+        <v>4.37</v>
       </c>
       <c r="T189" t="n">
-        <v>0.31995</v>
+        <v>0.31536</v>
       </c>
       <c r="U189" t="n">
-        <v>0.15985</v>
+        <v>0.15936</v>
       </c>
       <c r="V189" t="n">
-        <v>80.11</v>
+        <v>80.73</v>
       </c>
       <c r="W189" t="n">
-        <v>77.98999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="X189" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5704</v>
       </c>
       <c r="Y189" t="n">
-        <v>27.736</v>
+        <v>27.694</v>
       </c>
       <c r="Z189" t="n">
-        <v>60.863</v>
+        <v>60.534</v>
       </c>
       <c r="AA189" t="n">
-        <v>9.068</v>
+        <v>8.858000000000001</v>
       </c>
       <c r="AB189" t="n">
-        <v>27.59</v>
+        <v>27.02</v>
       </c>
       <c r="AC189" t="n">
-        <v>15.575</v>
+        <v>15.654</v>
       </c>
       <c r="AD189" t="n">
-        <v>21.767</v>
+        <v>21.578</v>
       </c>
       <c r="AE189" t="n">
-        <v>10.112</v>
+        <v>9.891</v>
       </c>
       <c r="AF189" t="n">
-        <v>21.689</v>
+        <v>21.553</v>
       </c>
       <c r="AG189" t="n">
-        <v>15.276</v>
+        <v>15.356</v>
       </c>
       <c r="AH189" t="n">
-        <v>8.468999999999999</v>
+        <v>8.170999999999999</v>
       </c>
       <c r="AI189" t="n">
-        <v>3.609</v>
+        <v>3.562</v>
       </c>
       <c r="AJ189" t="n">
-        <v>18.587</v>
+        <v>18.511</v>
       </c>
       <c r="AK189" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AL189" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="190">
@@ -23186,22 +23186,22 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F190" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G190" t="b">
         <v>1</v>
       </c>
       <c r="H190" t="n">
-        <v>1430.358</v>
+        <v>1426.747</v>
       </c>
       <c r="I190" t="n">
-        <v>3.2549</v>
+        <v>3.2284</v>
       </c>
       <c r="J190" t="n">
-        <v>1375.2</v>
+        <v>1374.6</v>
       </c>
       <c r="K190" t="n">
         <v>136</v>
@@ -23222,70 +23222,70 @@
         <v>127</v>
       </c>
       <c r="Q190" t="n">
-        <v>113.284</v>
+        <v>113.402</v>
       </c>
       <c r="R190" t="n">
-        <v>98.59399999999999</v>
+        <v>99.34099999999999</v>
       </c>
       <c r="S190" t="n">
-        <v>14.69</v>
+        <v>14.061</v>
       </c>
       <c r="T190" t="n">
-        <v>0.26728</v>
+        <v>0.27695</v>
       </c>
       <c r="U190" t="n">
-        <v>0.16731</v>
+        <v>0.16236</v>
       </c>
       <c r="V190" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="W190" t="n">
-        <v>64.89</v>
+        <v>65.19</v>
       </c>
       <c r="X190" t="n">
-        <v>0.8025</v>
+        <v>0.7652</v>
       </c>
       <c r="Y190" t="n">
-        <v>25.777</v>
+        <v>25.852</v>
       </c>
       <c r="Z190" t="n">
-        <v>54.274</v>
+        <v>54.742</v>
       </c>
       <c r="AA190" t="n">
-        <v>6.721</v>
+        <v>6.464</v>
       </c>
       <c r="AB190" t="n">
-        <v>18.326</v>
+        <v>18.038</v>
       </c>
       <c r="AC190" t="n">
-        <v>15.922</v>
+        <v>15.936</v>
       </c>
       <c r="AD190" t="n">
-        <v>21.547</v>
+        <v>21.629</v>
       </c>
       <c r="AE190" t="n">
-        <v>9.106999999999999</v>
+        <v>9.432</v>
       </c>
       <c r="AF190" t="n">
-        <v>24.917</v>
+        <v>24.62</v>
       </c>
       <c r="AG190" t="n">
-        <v>16.071</v>
+        <v>15.945</v>
       </c>
       <c r="AH190" t="n">
-        <v>7.486</v>
+        <v>7.577</v>
       </c>
       <c r="AI190" t="n">
-        <v>3.346</v>
+        <v>3.287</v>
       </c>
       <c r="AJ190" t="n">
-        <v>14.386</v>
+        <v>14.316</v>
       </c>
       <c r="AK190" t="n">
-        <v>17.8</v>
+        <v>13</v>
       </c>
       <c r="AL190" t="n">
-        <v>14.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="191">
@@ -23786,22 +23786,22 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F195" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G195" t="b">
         <v>1</v>
       </c>
       <c r="H195" t="n">
-        <v>1992.134</v>
+        <v>1999.63</v>
       </c>
       <c r="I195" t="n">
-        <v>11.5554</v>
+        <v>10.6735</v>
       </c>
       <c r="J195" t="n">
-        <v>1659.3</v>
+        <v>1665.7</v>
       </c>
       <c r="K195" t="n">
         <v>11</v>
@@ -23822,70 +23822,70 @@
         <v>12</v>
       </c>
       <c r="Q195" t="n">
-        <v>115.07</v>
+        <v>115.404</v>
       </c>
       <c r="R195" t="n">
-        <v>98.036</v>
+        <v>97.95399999999999</v>
       </c>
       <c r="S195" t="n">
-        <v>17.034</v>
+        <v>17.45</v>
       </c>
       <c r="T195" t="n">
-        <v>0.24188</v>
+        <v>0.23786</v>
       </c>
       <c r="U195" t="n">
-        <v>0.1401</v>
+        <v>0.14019</v>
       </c>
       <c r="V195" t="n">
-        <v>77.38</v>
+        <v>77.97</v>
       </c>
       <c r="W195" t="n">
-        <v>65.75</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="X195" t="n">
-        <v>0.8229</v>
+        <v>0.8406</v>
       </c>
       <c r="Y195" t="n">
-        <v>27.459</v>
+        <v>27.542</v>
       </c>
       <c r="Z195" t="n">
-        <v>59.006</v>
+        <v>58.91</v>
       </c>
       <c r="AA195" t="n">
-        <v>10.497</v>
+        <v>10.542</v>
       </c>
       <c r="AB195" t="n">
-        <v>29.859</v>
+        <v>29.806</v>
       </c>
       <c r="AC195" t="n">
-        <v>11.962</v>
+        <v>12.348</v>
       </c>
       <c r="AD195" t="n">
-        <v>15.893</v>
+        <v>16.351</v>
       </c>
       <c r="AE195" t="n">
-        <v>8.268000000000001</v>
+        <v>8.093</v>
       </c>
       <c r="AF195" t="n">
-        <v>25.403</v>
+        <v>25.371</v>
       </c>
       <c r="AG195" t="n">
-        <v>17.991</v>
+        <v>18.064</v>
       </c>
       <c r="AH195" t="n">
-        <v>7.218</v>
+        <v>7.397</v>
       </c>
       <c r="AI195" t="n">
-        <v>2.646</v>
+        <v>2.551</v>
       </c>
       <c r="AJ195" t="n">
-        <v>14.345</v>
+        <v>14.296</v>
       </c>
       <c r="AK195" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="AL195" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="196">
@@ -24386,22 +24386,22 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F200" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G200" t="b">
         <v>1</v>
       </c>
       <c r="H200" t="n">
-        <v>1339.842</v>
+        <v>1341.993</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5343</v>
+        <v>0.5805</v>
       </c>
       <c r="J200" t="n">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="K200" t="n">
         <v>176</v>
@@ -24422,70 +24422,70 @@
         <v>203</v>
       </c>
       <c r="Q200" t="n">
-        <v>106.226</v>
+        <v>106.165</v>
       </c>
       <c r="R200" t="n">
-        <v>111.076</v>
+        <v>110.071</v>
       </c>
       <c r="S200" t="n">
-        <v>-4.849</v>
+        <v>-3.906</v>
       </c>
       <c r="T200" t="n">
-        <v>0.294</v>
+        <v>0.29265</v>
       </c>
       <c r="U200" t="n">
-        <v>0.1965</v>
+        <v>0.19673</v>
       </c>
       <c r="V200" t="n">
-        <v>75.03</v>
+        <v>74.92</v>
       </c>
       <c r="W200" t="n">
-        <v>78.39</v>
+        <v>77.62</v>
       </c>
       <c r="X200" t="n">
-        <v>0.4472</v>
+        <v>0.4735</v>
       </c>
       <c r="Y200" t="n">
-        <v>24.911</v>
+        <v>24.876</v>
       </c>
       <c r="Z200" t="n">
-        <v>55.889</v>
+        <v>55.805</v>
       </c>
       <c r="AA200" t="n">
-        <v>6.054</v>
+        <v>6.022</v>
       </c>
       <c r="AB200" t="n">
-        <v>18.949</v>
+        <v>18.689</v>
       </c>
       <c r="AC200" t="n">
-        <v>19.153</v>
+        <v>19.146</v>
       </c>
       <c r="AD200" t="n">
-        <v>25.651</v>
+        <v>25.73</v>
       </c>
       <c r="AE200" t="n">
-        <v>10.329</v>
+        <v>10.35</v>
       </c>
       <c r="AF200" t="n">
-        <v>24.592</v>
+        <v>24.846</v>
       </c>
       <c r="AG200" t="n">
-        <v>13.11</v>
+        <v>13.031</v>
       </c>
       <c r="AH200" t="n">
-        <v>5.681</v>
+        <v>5.69</v>
       </c>
       <c r="AI200" t="n">
-        <v>3.85</v>
+        <v>3.805</v>
       </c>
       <c r="AJ200" t="n">
-        <v>19.725</v>
+        <v>19.712</v>
       </c>
       <c r="AK200" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AL200" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="201">
@@ -24626,22 +24626,22 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F202" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G202" t="b">
         <v>1</v>
       </c>
       <c r="H202" t="n">
-        <v>1362.178</v>
+        <v>1364.252</v>
       </c>
       <c r="I202" t="n">
-        <v>-1.5128</v>
+        <v>-1.4633</v>
       </c>
       <c r="J202" t="n">
-        <v>1434.9</v>
+        <v>1425.9</v>
       </c>
       <c r="K202" t="n">
         <v>240</v>
@@ -24662,70 +24662,70 @@
         <v>251</v>
       </c>
       <c r="Q202" t="n">
-        <v>104.426</v>
+        <v>104.332</v>
       </c>
       <c r="R202" t="n">
-        <v>111.13</v>
+        <v>109.702</v>
       </c>
       <c r="S202" t="n">
-        <v>-6.704</v>
+        <v>-5.371</v>
       </c>
       <c r="T202" t="n">
-        <v>0.32341</v>
+        <v>0.32196</v>
       </c>
       <c r="U202" t="n">
-        <v>0.16779</v>
+        <v>0.16798</v>
       </c>
       <c r="V202" t="n">
-        <v>71.33</v>
+        <v>70.97</v>
       </c>
       <c r="W202" t="n">
-        <v>76.29000000000001</v>
+        <v>75.08</v>
       </c>
       <c r="X202" t="n">
-        <v>0.3958</v>
+        <v>0.425</v>
       </c>
       <c r="Y202" t="n">
-        <v>24.729</v>
+        <v>24.808</v>
       </c>
       <c r="Z202" t="n">
-        <v>57.309</v>
+        <v>57.236</v>
       </c>
       <c r="AA202" t="n">
-        <v>8.571</v>
+        <v>8.417999999999999</v>
       </c>
       <c r="AB202" t="n">
-        <v>25.525</v>
+        <v>25.197</v>
       </c>
       <c r="AC202" t="n">
-        <v>13.304</v>
+        <v>12.932</v>
       </c>
       <c r="AD202" t="n">
-        <v>20.237</v>
+        <v>19.711</v>
       </c>
       <c r="AE202" t="n">
-        <v>9.225</v>
+        <v>9.179</v>
       </c>
       <c r="AF202" t="n">
-        <v>19.151</v>
+        <v>19.262</v>
       </c>
       <c r="AG202" t="n">
-        <v>12.849</v>
+        <v>12.987</v>
       </c>
       <c r="AH202" t="n">
-        <v>8.51</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI202" t="n">
-        <v>2.672</v>
+        <v>2.796</v>
       </c>
       <c r="AJ202" t="n">
-        <v>18.208</v>
+        <v>18.067</v>
       </c>
       <c r="AK202" t="n">
-        <v>-1.6</v>
+        <v>2</v>
       </c>
       <c r="AL202" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="203">
@@ -25106,22 +25106,22 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F206" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G206" t="b">
         <v>1</v>
       </c>
       <c r="H206" t="n">
-        <v>1369.221</v>
+        <v>1366.865</v>
       </c>
       <c r="I206" t="n">
-        <v>0.87</v>
+        <v>0.9359</v>
       </c>
       <c r="J206" t="n">
-        <v>1464.7</v>
+        <v>1468.8</v>
       </c>
       <c r="K206" t="n">
         <v>290</v>
@@ -25142,70 +25142,70 @@
         <v>284</v>
       </c>
       <c r="Q206" t="n">
-        <v>107.075</v>
+        <v>106.643</v>
       </c>
       <c r="R206" t="n">
-        <v>114.493</v>
+        <v>114.37</v>
       </c>
       <c r="S206" t="n">
-        <v>-7.418</v>
+        <v>-7.727</v>
       </c>
       <c r="T206" t="n">
-        <v>0.31067</v>
+        <v>0.30476</v>
       </c>
       <c r="U206" t="n">
-        <v>0.1353</v>
+        <v>0.13477</v>
       </c>
       <c r="V206" t="n">
-        <v>74.52</v>
+        <v>74.09</v>
       </c>
       <c r="W206" t="n">
-        <v>79.77</v>
+        <v>79.52</v>
       </c>
       <c r="X206" t="n">
-        <v>0.4899</v>
+        <v>0.4637</v>
       </c>
       <c r="Y206" t="n">
-        <v>25.638</v>
+        <v>25.41</v>
       </c>
       <c r="Z206" t="n">
-        <v>59.936</v>
+        <v>59.73</v>
       </c>
       <c r="AA206" t="n">
-        <v>7.73</v>
+        <v>7.784</v>
       </c>
       <c r="AB206" t="n">
-        <v>24.191</v>
+        <v>24.269</v>
       </c>
       <c r="AC206" t="n">
-        <v>15.475</v>
+        <v>15.453</v>
       </c>
       <c r="AD206" t="n">
-        <v>22.391</v>
+        <v>22.194</v>
       </c>
       <c r="AE206" t="n">
-        <v>9.536</v>
+        <v>9.339</v>
       </c>
       <c r="AF206" t="n">
-        <v>20.632</v>
+        <v>20.848</v>
       </c>
       <c r="AG206" t="n">
-        <v>11.026</v>
+        <v>10.969</v>
       </c>
       <c r="AH206" t="n">
-        <v>7.881</v>
+        <v>7.907</v>
       </c>
       <c r="AI206" t="n">
-        <v>2.328</v>
+        <v>2.465</v>
       </c>
       <c r="AJ206" t="n">
-        <v>20.412</v>
+        <v>20.349</v>
       </c>
       <c r="AK206" t="n">
-        <v>-1.8</v>
+        <v>-6.4</v>
       </c>
       <c r="AL206" t="n">
-        <v>-4</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="207">
@@ -25355,7 +25355,7 @@
         <v>1</v>
       </c>
       <c r="H208" t="n">
-        <v>1536.66</v>
+        <v>1532.285</v>
       </c>
       <c r="I208" t="n">
         <v>-5.3186</v>
@@ -25706,22 +25706,22 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F211" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G211" t="b">
         <v>1</v>
       </c>
       <c r="H211" t="n">
-        <v>1567.024</v>
+        <v>1573.879</v>
       </c>
       <c r="I211" t="n">
-        <v>-3.9617</v>
+        <v>-3.696</v>
       </c>
       <c r="J211" t="n">
-        <v>1516</v>
+        <v>1515.8</v>
       </c>
       <c r="K211" t="n">
         <v>80</v>
@@ -25742,70 +25742,70 @@
         <v>81</v>
       </c>
       <c r="Q211" t="n">
-        <v>107.531</v>
+        <v>108.741</v>
       </c>
       <c r="R211" t="n">
-        <v>96.867</v>
+        <v>97.495</v>
       </c>
       <c r="S211" t="n">
-        <v>10.664</v>
+        <v>11.246</v>
       </c>
       <c r="T211" t="n">
-        <v>0.21397</v>
+        <v>0.22502</v>
       </c>
       <c r="U211" t="n">
-        <v>0.13738</v>
+        <v>0.13537</v>
       </c>
       <c r="V211" t="n">
-        <v>68.64</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="W211" t="n">
-        <v>61.91</v>
+        <v>62.11</v>
       </c>
       <c r="X211" t="n">
-        <v>0.6394</v>
+        <v>0.6498</v>
       </c>
       <c r="Y211" t="n">
-        <v>25.073</v>
+        <v>25.162</v>
       </c>
       <c r="Z211" t="n">
-        <v>54.893</v>
+        <v>55.172</v>
       </c>
       <c r="AA211" t="n">
-        <v>7.339</v>
+        <v>7.284</v>
       </c>
       <c r="AB211" t="n">
-        <v>21.992</v>
+        <v>21.815</v>
       </c>
       <c r="AC211" t="n">
-        <v>10.343</v>
+        <v>10.255</v>
       </c>
       <c r="AD211" t="n">
-        <v>14.725</v>
+        <v>14.486</v>
       </c>
       <c r="AE211" t="n">
-        <v>6.227</v>
+        <v>6.426</v>
       </c>
       <c r="AF211" t="n">
-        <v>22.834</v>
+        <v>22.431</v>
       </c>
       <c r="AG211" t="n">
-        <v>14.038</v>
+        <v>13.992</v>
       </c>
       <c r="AH211" t="n">
-        <v>6.476</v>
+        <v>6.401</v>
       </c>
       <c r="AI211" t="n">
-        <v>3.013</v>
+        <v>2.918</v>
       </c>
       <c r="AJ211" t="n">
-        <v>15.189</v>
+        <v>15.138</v>
       </c>
       <c r="AK211" t="n">
-        <v>11</v>
+        <v>14.4</v>
       </c>
       <c r="AL211" t="n">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="212">
@@ -25946,22 +25946,22 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F213" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G213" t="b">
         <v>1</v>
       </c>
       <c r="H213" t="n">
-        <v>1288.065</v>
+        <v>1285.992</v>
       </c>
       <c r="I213" t="n">
-        <v>-1.681</v>
+        <v>-1.6046</v>
       </c>
       <c r="J213" t="n">
-        <v>1441.7</v>
+        <v>1438.9</v>
       </c>
       <c r="K213" t="n">
         <v>276</v>
@@ -25982,70 +25982,70 @@
         <v>294</v>
       </c>
       <c r="Q213" t="n">
-        <v>102.393</v>
+        <v>101.625</v>
       </c>
       <c r="R213" t="n">
-        <v>112.413</v>
+        <v>112.178</v>
       </c>
       <c r="S213" t="n">
-        <v>-10.02</v>
+        <v>-10.553</v>
       </c>
       <c r="T213" t="n">
-        <v>0.26223</v>
+        <v>0.2687</v>
       </c>
       <c r="U213" t="n">
-        <v>0.17092</v>
+        <v>0.1738</v>
       </c>
       <c r="V213" t="n">
-        <v>66.68000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="W213" t="n">
-        <v>73.31999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="X213" t="n">
-        <v>0.2733</v>
+        <v>0.2644</v>
       </c>
       <c r="Y213" t="n">
-        <v>22.658</v>
+        <v>22.295</v>
       </c>
       <c r="Z213" t="n">
-        <v>52.134</v>
+        <v>52.04</v>
       </c>
       <c r="AA213" t="n">
-        <v>5.801</v>
+        <v>5.876</v>
       </c>
       <c r="AB213" t="n">
-        <v>17.413</v>
+        <v>17.713</v>
       </c>
       <c r="AC213" t="n">
-        <v>15.562</v>
+        <v>15.437</v>
       </c>
       <c r="AD213" t="n">
-        <v>21.043</v>
+        <v>20.866</v>
       </c>
       <c r="AE213" t="n">
-        <v>7.283</v>
+        <v>7.556</v>
       </c>
       <c r="AF213" t="n">
-        <v>20.637</v>
+        <v>20.562</v>
       </c>
       <c r="AG213" t="n">
-        <v>11.438</v>
+        <v>11.313</v>
       </c>
       <c r="AH213" t="n">
-        <v>6.084</v>
+        <v>6.182</v>
       </c>
       <c r="AI213" t="n">
-        <v>2.273</v>
+        <v>2.306</v>
       </c>
       <c r="AJ213" t="n">
-        <v>16.879</v>
+        <v>16.734</v>
       </c>
       <c r="AK213" t="n">
-        <v>-2.4</v>
+        <v>-3</v>
       </c>
       <c r="AL213" t="n">
-        <v>-2</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="214">
@@ -27146,22 +27146,22 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="F223" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G223" t="b">
         <v>1</v>
       </c>
       <c r="H223" t="n">
-        <v>1543.318</v>
+        <v>1551.535</v>
       </c>
       <c r="I223" t="n">
-        <v>-3.0737</v>
+        <v>-2.8876</v>
       </c>
       <c r="J223" t="n">
-        <v>1539.5</v>
+        <v>1538.2</v>
       </c>
       <c r="K223" t="n">
         <v>184</v>
@@ -27182,70 +27182,70 @@
         <v>175</v>
       </c>
       <c r="Q223" t="n">
-        <v>106.94</v>
+        <v>107.333</v>
       </c>
       <c r="R223" t="n">
-        <v>111.937</v>
+        <v>111.753</v>
       </c>
       <c r="S223" t="n">
-        <v>-4.997</v>
+        <v>-4.42</v>
       </c>
       <c r="T223" t="n">
-        <v>0.24478</v>
+        <v>0.24647</v>
       </c>
       <c r="U223" t="n">
-        <v>0.16868</v>
+        <v>0.17043</v>
       </c>
       <c r="V223" t="n">
-        <v>71.39</v>
+        <v>71.66</v>
       </c>
       <c r="W223" t="n">
-        <v>74.56999999999999</v>
+        <v>74.47</v>
       </c>
       <c r="X223" t="n">
-        <v>0.5101</v>
+        <v>0.5363</v>
       </c>
       <c r="Y223" t="n">
-        <v>22.614</v>
+        <v>22.785</v>
       </c>
       <c r="Z223" t="n">
-        <v>52.759</v>
+        <v>52.929</v>
       </c>
       <c r="AA223" t="n">
-        <v>8.145</v>
+        <v>8.31</v>
       </c>
       <c r="AB223" t="n">
-        <v>23.348</v>
+        <v>23.413</v>
       </c>
       <c r="AC223" t="n">
-        <v>18.02</v>
+        <v>17.782</v>
       </c>
       <c r="AD223" t="n">
-        <v>23.472</v>
+        <v>23.028</v>
       </c>
       <c r="AE223" t="n">
-        <v>7.47</v>
+        <v>7.558</v>
       </c>
       <c r="AF223" t="n">
-        <v>22.87</v>
+        <v>22.907</v>
       </c>
       <c r="AG223" t="n">
-        <v>13.864</v>
+        <v>14.012</v>
       </c>
       <c r="AH223" t="n">
-        <v>5.716</v>
+        <v>5.566</v>
       </c>
       <c r="AI223" t="n">
-        <v>3.539</v>
+        <v>3.681</v>
       </c>
       <c r="AJ223" t="n">
-        <v>17.872</v>
+        <v>17.835</v>
       </c>
       <c r="AK223" t="n">
-        <v>3.2</v>
+        <v>-2</v>
       </c>
       <c r="AL223" t="n">
-        <v>-1.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="224">
@@ -27266,22 +27266,22 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F224" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G224" t="b">
         <v>1</v>
       </c>
       <c r="H224" t="n">
-        <v>1440.478</v>
+        <v>1438.055</v>
       </c>
       <c r="I224" t="n">
-        <v>3.9361</v>
+        <v>3.8121</v>
       </c>
       <c r="J224" t="n">
-        <v>1523.4</v>
+        <v>1533.2</v>
       </c>
       <c r="K224" t="n">
         <v>112</v>
@@ -27302,70 +27302,70 @@
         <v>115</v>
       </c>
       <c r="Q224" t="n">
-        <v>107.784</v>
+        <v>108.28</v>
       </c>
       <c r="R224" t="n">
-        <v>104.746</v>
+        <v>105.959</v>
       </c>
       <c r="S224" t="n">
-        <v>3.038</v>
+        <v>2.321</v>
       </c>
       <c r="T224" t="n">
-        <v>0.27275</v>
+        <v>0.28079</v>
       </c>
       <c r="U224" t="n">
-        <v>0.18896</v>
+        <v>0.18753</v>
       </c>
       <c r="V224" t="n">
-        <v>71.36</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="W224" t="n">
-        <v>69.51000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="X224" t="n">
-        <v>0.5382</v>
+        <v>0.5111</v>
       </c>
       <c r="Y224" t="n">
-        <v>25.694</v>
+        <v>25.661</v>
       </c>
       <c r="Z224" t="n">
-        <v>55.922</v>
+        <v>56.071</v>
       </c>
       <c r="AA224" t="n">
-        <v>7.087</v>
+        <v>7.106</v>
       </c>
       <c r="AB224" t="n">
-        <v>19.613</v>
+        <v>19.876</v>
       </c>
       <c r="AC224" t="n">
-        <v>12.882</v>
+        <v>12.894</v>
       </c>
       <c r="AD224" t="n">
-        <v>17.145</v>
+        <v>17.067</v>
       </c>
       <c r="AE224" t="n">
-        <v>9.724</v>
+        <v>10.004</v>
       </c>
       <c r="AF224" t="n">
-        <v>25.625</v>
+        <v>25.325</v>
       </c>
       <c r="AG224" t="n">
-        <v>14.747</v>
+        <v>14.953</v>
       </c>
       <c r="AH224" t="n">
-        <v>5.516</v>
+        <v>5.396</v>
       </c>
       <c r="AI224" t="n">
-        <v>2.208</v>
+        <v>2.192</v>
       </c>
       <c r="AJ224" t="n">
-        <v>18.495</v>
+        <v>18.188</v>
       </c>
       <c r="AK224" t="n">
-        <v>-9</v>
+        <v>-8.4</v>
       </c>
       <c r="AL224" t="n">
-        <v>-0.3</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="225">
@@ -27506,22 +27506,22 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F226" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G226" t="b">
         <v>1</v>
       </c>
       <c r="H226" t="n">
-        <v>1532.755</v>
+        <v>1526.911</v>
       </c>
       <c r="I226" t="n">
-        <v>-7.5578</v>
+        <v>-7.224</v>
       </c>
       <c r="J226" t="n">
-        <v>1671.8</v>
+        <v>1664.7</v>
       </c>
       <c r="K226" t="n">
         <v>128</v>
@@ -27542,70 +27542,70 @@
         <v>125</v>
       </c>
       <c r="Q226" t="n">
-        <v>110.145</v>
+        <v>109.422</v>
       </c>
       <c r="R226" t="n">
-        <v>118.589</v>
+        <v>117.676</v>
       </c>
       <c r="S226" t="n">
-        <v>-8.444000000000001</v>
+        <v>-8.255000000000001</v>
       </c>
       <c r="T226" t="n">
-        <v>0.26171</v>
+        <v>0.26138</v>
       </c>
       <c r="U226" t="n">
-        <v>0.14917</v>
+        <v>0.14889</v>
       </c>
       <c r="V226" t="n">
-        <v>74.15000000000001</v>
+        <v>73.77</v>
       </c>
       <c r="W226" t="n">
-        <v>79.84999999999999</v>
+        <v>79.38</v>
       </c>
       <c r="X226" t="n">
-        <v>0.3941</v>
+        <v>0.3818</v>
       </c>
       <c r="Y226" t="n">
-        <v>26.327</v>
+        <v>26.309</v>
       </c>
       <c r="Z226" t="n">
-        <v>56.217</v>
+        <v>56.382</v>
       </c>
       <c r="AA226" t="n">
-        <v>7.048</v>
+        <v>6.85</v>
       </c>
       <c r="AB226" t="n">
-        <v>21.463</v>
+        <v>21.523</v>
       </c>
       <c r="AC226" t="n">
-        <v>14.45</v>
+        <v>14.305</v>
       </c>
       <c r="AD226" t="n">
-        <v>19.107</v>
+        <v>19.168</v>
       </c>
       <c r="AE226" t="n">
-        <v>7.207</v>
+        <v>7.286</v>
       </c>
       <c r="AF226" t="n">
-        <v>19.404</v>
+        <v>19.932</v>
       </c>
       <c r="AG226" t="n">
-        <v>12.544</v>
+        <v>12.495</v>
       </c>
       <c r="AH226" t="n">
-        <v>7.131</v>
+        <v>7.082</v>
       </c>
       <c r="AI226" t="n">
-        <v>1.576</v>
+        <v>1.755</v>
       </c>
       <c r="AJ226" t="n">
-        <v>15.478</v>
+        <v>15.523</v>
       </c>
       <c r="AK226" t="n">
-        <v>-15.4</v>
+        <v>-15.6</v>
       </c>
       <c r="AL226" t="n">
-        <v>-13.6</v>
+        <v>-12.7</v>
       </c>
     </row>
     <row r="227">
@@ -27986,22 +27986,22 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F230" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G230" t="b">
         <v>1</v>
       </c>
       <c r="H230" t="n">
-        <v>1458.268</v>
+        <v>1460.137</v>
       </c>
       <c r="I230" t="n">
-        <v>2.128</v>
+        <v>2.001</v>
       </c>
       <c r="J230" t="n">
-        <v>1416.6</v>
+        <v>1413.3</v>
       </c>
       <c r="K230" t="n">
         <v>159</v>
@@ -28022,70 +28022,70 @@
         <v>151</v>
       </c>
       <c r="Q230" t="n">
-        <v>105.362</v>
+        <v>105.768</v>
       </c>
       <c r="R230" t="n">
-        <v>101.085</v>
+        <v>101.475</v>
       </c>
       <c r="S230" t="n">
-        <v>4.277</v>
+        <v>4.293</v>
       </c>
       <c r="T230" t="n">
-        <v>0.25917</v>
+        <v>0.25758</v>
       </c>
       <c r="U230" t="n">
-        <v>0.17061</v>
+        <v>0.16607</v>
       </c>
       <c r="V230" t="n">
-        <v>73.65000000000001</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="W230" t="n">
-        <v>70.73</v>
+        <v>71.12</v>
       </c>
       <c r="X230" t="n">
-        <v>0.6182</v>
+        <v>0.6321</v>
       </c>
       <c r="Y230" t="n">
-        <v>26.364</v>
+        <v>26.207</v>
       </c>
       <c r="Z230" t="n">
-        <v>57.716</v>
+        <v>57.532</v>
       </c>
       <c r="AA230" t="n">
-        <v>6.656</v>
+        <v>6.582</v>
       </c>
       <c r="AB230" t="n">
-        <v>19.862</v>
+        <v>19.635</v>
       </c>
       <c r="AC230" t="n">
-        <v>14.269</v>
+        <v>15.077</v>
       </c>
       <c r="AD230" t="n">
-        <v>20.262</v>
+        <v>21.512</v>
       </c>
       <c r="AE230" t="n">
-        <v>8.795</v>
+        <v>8.728999999999999</v>
       </c>
       <c r="AF230" t="n">
-        <v>24.151</v>
+        <v>24.197</v>
       </c>
       <c r="AG230" t="n">
-        <v>13.813</v>
+        <v>13.569</v>
       </c>
       <c r="AH230" t="n">
-        <v>7.22</v>
+        <v>7.271</v>
       </c>
       <c r="AI230" t="n">
-        <v>3.893</v>
+        <v>3.803</v>
       </c>
       <c r="AJ230" t="n">
-        <v>19.545</v>
+        <v>19.849</v>
       </c>
       <c r="AK230" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AL230" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="231">
@@ -29066,22 +29066,22 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F239" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G239" t="b">
         <v>1</v>
       </c>
       <c r="H239" t="n">
-        <v>1394.644</v>
+        <v>1400.544</v>
       </c>
       <c r="I239" t="n">
-        <v>0.373</v>
+        <v>0.3514</v>
       </c>
       <c r="J239" t="n">
-        <v>1519.1</v>
+        <v>1508.3</v>
       </c>
       <c r="K239" t="n">
         <v>230</v>
@@ -29102,70 +29102,70 @@
         <v>243</v>
       </c>
       <c r="Q239" t="n">
-        <v>104.79</v>
+        <v>105.519</v>
       </c>
       <c r="R239" t="n">
-        <v>112.019</v>
+        <v>111.784</v>
       </c>
       <c r="S239" t="n">
-        <v>-7.229</v>
+        <v>-6.265</v>
       </c>
       <c r="T239" t="n">
-        <v>0.34064</v>
+        <v>0.34216</v>
       </c>
       <c r="U239" t="n">
-        <v>0.17248</v>
+        <v>0.16599</v>
       </c>
       <c r="V239" t="n">
-        <v>71.51000000000001</v>
+        <v>72.11</v>
       </c>
       <c r="W239" t="n">
-        <v>76.73999999999999</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="X239" t="n">
-        <v>0.3519</v>
+        <v>0.3878</v>
       </c>
       <c r="Y239" t="n">
-        <v>24.307</v>
+        <v>24.626</v>
       </c>
       <c r="Z239" t="n">
-        <v>59.267</v>
+        <v>60.177</v>
       </c>
       <c r="AA239" t="n">
-        <v>8.98</v>
+        <v>9.109</v>
       </c>
       <c r="AB239" t="n">
-        <v>25.828</v>
+        <v>26.714</v>
       </c>
       <c r="AC239" t="n">
-        <v>13.917</v>
+        <v>13.748</v>
       </c>
       <c r="AD239" t="n">
-        <v>20.454</v>
+        <v>20.224</v>
       </c>
       <c r="AE239" t="n">
-        <v>11.541</v>
+        <v>11.837</v>
       </c>
       <c r="AF239" t="n">
-        <v>21.833</v>
+        <v>22.177</v>
       </c>
       <c r="AG239" t="n">
-        <v>11.252</v>
+        <v>11.367</v>
       </c>
       <c r="AH239" t="n">
-        <v>6.469</v>
+        <v>6.415</v>
       </c>
       <c r="AI239" t="n">
-        <v>3.844</v>
+        <v>3.864</v>
       </c>
       <c r="AJ239" t="n">
-        <v>19.026</v>
+        <v>18.782</v>
       </c>
       <c r="AK239" t="n">
-        <v>-6.6</v>
+        <v>-2.8</v>
       </c>
       <c r="AL239" t="n">
-        <v>-3.2</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="240">
@@ -29546,22 +29546,22 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F243" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G243" t="b">
         <v>1</v>
       </c>
       <c r="H243" t="n">
-        <v>1551.607</v>
+        <v>1557.451</v>
       </c>
       <c r="I243" t="n">
-        <v>-3.1062</v>
+        <v>-2.9475</v>
       </c>
       <c r="J243" t="n">
-        <v>1697.1</v>
+        <v>1684.5</v>
       </c>
       <c r="K243" t="n">
         <v>144</v>
@@ -29582,70 +29582,70 @@
         <v>158</v>
       </c>
       <c r="Q243" t="n">
-        <v>104.855</v>
+        <v>104.804</v>
       </c>
       <c r="R243" t="n">
-        <v>112.839</v>
+        <v>111.665</v>
       </c>
       <c r="S243" t="n">
-        <v>-7.983</v>
+        <v>-6.86</v>
       </c>
       <c r="T243" t="n">
-        <v>0.32469</v>
+        <v>0.31796</v>
       </c>
       <c r="U243" t="n">
-        <v>0.14688</v>
+        <v>0.1454</v>
       </c>
       <c r="V243" t="n">
-        <v>71.04000000000001</v>
+        <v>70.95</v>
       </c>
       <c r="W243" t="n">
-        <v>76.16</v>
+        <v>75.3</v>
       </c>
       <c r="X243" t="n">
-        <v>0.3941</v>
+        <v>0.4273</v>
       </c>
       <c r="Y243" t="n">
-        <v>24.3</v>
+        <v>24.327</v>
       </c>
       <c r="Z243" t="n">
-        <v>58.071</v>
+        <v>58.105</v>
       </c>
       <c r="AA243" t="n">
-        <v>6.552</v>
+        <v>6.477</v>
       </c>
       <c r="AB243" t="n">
-        <v>20.003</v>
+        <v>19.986</v>
       </c>
       <c r="AC243" t="n">
-        <v>15.887</v>
+        <v>15.814</v>
       </c>
       <c r="AD243" t="n">
-        <v>21.529</v>
+        <v>21.359</v>
       </c>
       <c r="AE243" t="n">
-        <v>9.805999999999999</v>
+        <v>9.705</v>
       </c>
       <c r="AF243" t="n">
-        <v>20.619</v>
+        <v>21.109</v>
       </c>
       <c r="AG243" t="n">
-        <v>11.829</v>
+        <v>11.959</v>
       </c>
       <c r="AH243" t="n">
-        <v>6.209</v>
+        <v>6.114</v>
       </c>
       <c r="AI243" t="n">
-        <v>3.266</v>
+        <v>3.332</v>
       </c>
       <c r="AJ243" t="n">
-        <v>16.796</v>
+        <v>16.745</v>
       </c>
       <c r="AK243" t="n">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="AL243" t="n">
-        <v>-5.8</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="244">
@@ -30626,22 +30626,22 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F252" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G252" t="b">
         <v>1</v>
       </c>
       <c r="H252" t="n">
-        <v>1568.082</v>
+        <v>1559.865</v>
       </c>
       <c r="I252" t="n">
-        <v>-4.0664</v>
+        <v>-3.9344</v>
       </c>
       <c r="J252" t="n">
-        <v>1568.4</v>
+        <v>1568.8</v>
       </c>
       <c r="K252" t="n">
         <v>122</v>
@@ -30662,70 +30662,70 @@
         <v>122</v>
       </c>
       <c r="Q252" t="n">
-        <v>109.567</v>
+        <v>109.828</v>
       </c>
       <c r="R252" t="n">
-        <v>108.888</v>
+        <v>109.478</v>
       </c>
       <c r="S252" t="n">
-        <v>0.679</v>
+        <v>0.351</v>
       </c>
       <c r="T252" t="n">
-        <v>0.27471</v>
+        <v>0.27887</v>
       </c>
       <c r="U252" t="n">
-        <v>0.15483</v>
+        <v>0.15469</v>
       </c>
       <c r="V252" t="n">
-        <v>73.92</v>
+        <v>73.97</v>
       </c>
       <c r="W252" t="n">
-        <v>73.56</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="X252" t="n">
-        <v>0.5208</v>
+        <v>0.4955</v>
       </c>
       <c r="Y252" t="n">
-        <v>24.444</v>
+        <v>24.443</v>
       </c>
       <c r="Z252" t="n">
-        <v>56.387</v>
+        <v>56.51</v>
       </c>
       <c r="AA252" t="n">
-        <v>8.936</v>
+        <v>9.018000000000001</v>
       </c>
       <c r="AB252" t="n">
-        <v>26.017</v>
+        <v>26.049</v>
       </c>
       <c r="AC252" t="n">
-        <v>16.093</v>
+        <v>16.062</v>
       </c>
       <c r="AD252" t="n">
-        <v>22.761</v>
+        <v>22.641</v>
       </c>
       <c r="AE252" t="n">
-        <v>9.301</v>
+        <v>9.457000000000001</v>
       </c>
       <c r="AF252" t="n">
-        <v>23.981</v>
+        <v>23.88</v>
       </c>
       <c r="AG252" t="n">
-        <v>13.55</v>
+        <v>13.615</v>
       </c>
       <c r="AH252" t="n">
-        <v>4.882</v>
+        <v>5.116</v>
       </c>
       <c r="AI252" t="n">
-        <v>3.032</v>
+        <v>2.911</v>
       </c>
       <c r="AJ252" t="n">
-        <v>17.137</v>
+        <v>17.204</v>
       </c>
       <c r="AK252" t="n">
-        <v>-0.2</v>
+        <v>-3</v>
       </c>
       <c r="AL252" t="n">
-        <v>-7.2</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="253">
@@ -30986,22 +30986,22 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="F255" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G255" t="b">
         <v>1</v>
       </c>
       <c r="H255" t="n">
-        <v>1765.908</v>
+        <v>1768.33</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.7176</v>
+        <v>-0.4727</v>
       </c>
       <c r="J255" t="n">
-        <v>1571.8</v>
+        <v>1566.6</v>
       </c>
       <c r="K255" t="n">
         <v>37</v>
@@ -31022,70 +31022,70 @@
         <v>40</v>
       </c>
       <c r="Q255" t="n">
-        <v>117.396</v>
+        <v>117.67</v>
       </c>
       <c r="R255" t="n">
-        <v>102.196</v>
+        <v>102.695</v>
       </c>
       <c r="S255" t="n">
-        <v>15.199</v>
+        <v>14.975</v>
       </c>
       <c r="T255" t="n">
-        <v>0.34478</v>
+        <v>0.34723</v>
       </c>
       <c r="U255" t="n">
-        <v>0.14939</v>
+        <v>0.14938</v>
       </c>
       <c r="V255" t="n">
-        <v>83.90000000000001</v>
+        <v>83.47</v>
       </c>
       <c r="W255" t="n">
-        <v>73.06</v>
+        <v>72.86</v>
       </c>
       <c r="X255" t="n">
-        <v>0.7691</v>
+        <v>0.7764</v>
       </c>
       <c r="Y255" t="n">
-        <v>30.462</v>
+        <v>30.322</v>
       </c>
       <c r="Z255" t="n">
-        <v>64.658</v>
+        <v>64.524</v>
       </c>
       <c r="AA255" t="n">
-        <v>9.999000000000001</v>
+        <v>10.176</v>
       </c>
       <c r="AB255" t="n">
-        <v>28.843</v>
+        <v>29.068</v>
       </c>
       <c r="AC255" t="n">
-        <v>12.975</v>
+        <v>12.654</v>
       </c>
       <c r="AD255" t="n">
-        <v>17.304</v>
+        <v>16.932</v>
       </c>
       <c r="AE255" t="n">
-        <v>11.546</v>
+        <v>11.656</v>
       </c>
       <c r="AF255" t="n">
-        <v>21.34</v>
+        <v>21.319</v>
       </c>
       <c r="AG255" t="n">
-        <v>16.822</v>
+        <v>16.943</v>
       </c>
       <c r="AH255" t="n">
-        <v>9.111000000000001</v>
+        <v>8.919</v>
       </c>
       <c r="AI255" t="n">
-        <v>3.715</v>
+        <v>3.703</v>
       </c>
       <c r="AJ255" t="n">
-        <v>19.931</v>
+        <v>19.539</v>
       </c>
       <c r="AK255" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AL255" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="256">
@@ -31826,22 +31826,22 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F262" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G262" t="b">
         <v>1</v>
       </c>
       <c r="H262" t="n">
-        <v>1466.956</v>
+        <v>1471.282</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9509</v>
+        <v>0.9399</v>
       </c>
       <c r="J262" t="n">
-        <v>1425.6</v>
+        <v>1426.7</v>
       </c>
       <c r="K262" t="n">
         <v>206</v>
@@ -31862,67 +31862,67 @@
         <v>194</v>
       </c>
       <c r="Q262" t="n">
-        <v>109.694</v>
+        <v>110.162</v>
       </c>
       <c r="R262" t="n">
-        <v>102.558</v>
+        <v>102.353</v>
       </c>
       <c r="S262" t="n">
-        <v>7.137</v>
+        <v>7.809</v>
       </c>
       <c r="T262" t="n">
-        <v>0.28217</v>
+        <v>0.27995</v>
       </c>
       <c r="U262" t="n">
-        <v>0.15272</v>
+        <v>0.15315</v>
       </c>
       <c r="V262" t="n">
-        <v>70.47</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="W262" t="n">
-        <v>66.08</v>
+        <v>65.97</v>
       </c>
       <c r="X262" t="n">
-        <v>0.6606</v>
+        <v>0.6706</v>
       </c>
       <c r="Y262" t="n">
-        <v>25.4</v>
+        <v>25.408</v>
       </c>
       <c r="Z262" t="n">
-        <v>55.475</v>
+        <v>55.324</v>
       </c>
       <c r="AA262" t="n">
-        <v>5.334</v>
+        <v>5.466</v>
       </c>
       <c r="AB262" t="n">
-        <v>17.842</v>
+        <v>17.719</v>
       </c>
       <c r="AC262" t="n">
-        <v>14.334</v>
+        <v>14.508</v>
       </c>
       <c r="AD262" t="n">
-        <v>18.635</v>
+        <v>18.962</v>
       </c>
       <c r="AE262" t="n">
-        <v>9.007</v>
+        <v>9.012</v>
       </c>
       <c r="AF262" t="n">
-        <v>22.396</v>
+        <v>22.734</v>
       </c>
       <c r="AG262" t="n">
-        <v>13.303</v>
+        <v>13.478</v>
       </c>
       <c r="AH262" t="n">
-        <v>5.987</v>
+        <v>5.875</v>
       </c>
       <c r="AI262" t="n">
-        <v>2.877</v>
+        <v>2.922</v>
       </c>
       <c r="AJ262" t="n">
-        <v>13.919</v>
+        <v>13.803</v>
       </c>
       <c r="AK262" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="AL262" t="n">
         <v>1.7</v>
@@ -32426,22 +32426,22 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F267" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G267" t="b">
         <v>1</v>
       </c>
       <c r="H267" t="n">
-        <v>1709.517</v>
+        <v>1711.768</v>
       </c>
       <c r="I267" t="n">
-        <v>9.3651</v>
+        <v>9.207800000000001</v>
       </c>
       <c r="J267" t="n">
-        <v>1558.8</v>
+        <v>1553.3</v>
       </c>
       <c r="K267" t="n">
         <v>52</v>
@@ -32462,70 +32462,70 @@
         <v>48</v>
       </c>
       <c r="Q267" t="n">
-        <v>115.671</v>
+        <v>116.057</v>
       </c>
       <c r="R267" t="n">
-        <v>102.394</v>
+        <v>101.733</v>
       </c>
       <c r="S267" t="n">
-        <v>13.277</v>
+        <v>14.323</v>
       </c>
       <c r="T267" t="n">
-        <v>0.33601</v>
+        <v>0.33915</v>
       </c>
       <c r="U267" t="n">
-        <v>0.14778</v>
+        <v>0.1453</v>
       </c>
       <c r="V267" t="n">
-        <v>87.87</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="W267" t="n">
-        <v>78.18000000000001</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="X267" t="n">
-        <v>0.7279</v>
+        <v>0.7367</v>
       </c>
       <c r="Y267" t="n">
-        <v>28.769</v>
+        <v>28.782</v>
       </c>
       <c r="Z267" t="n">
-        <v>65.592</v>
+        <v>65.83199999999999</v>
       </c>
       <c r="AA267" t="n">
-        <v>9.429</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AB267" t="n">
-        <v>28.782</v>
+        <v>29.075</v>
       </c>
       <c r="AC267" t="n">
-        <v>20.905</v>
+        <v>20.368</v>
       </c>
       <c r="AD267" t="n">
-        <v>28.136</v>
+        <v>27.475</v>
       </c>
       <c r="AE267" t="n">
-        <v>13.082</v>
+        <v>13.293</v>
       </c>
       <c r="AF267" t="n">
-        <v>25.694</v>
+        <v>25.704</v>
       </c>
       <c r="AG267" t="n">
-        <v>16.796</v>
+        <v>17.121</v>
       </c>
       <c r="AH267" t="n">
-        <v>8.599</v>
+        <v>8.728999999999999</v>
       </c>
       <c r="AI267" t="n">
-        <v>4.238</v>
+        <v>4.139</v>
       </c>
       <c r="AJ267" t="n">
-        <v>20.061</v>
+        <v>19.76</v>
       </c>
       <c r="AK267" t="n">
-        <v>15.4</v>
+        <v>19.6</v>
       </c>
       <c r="AL267" t="n">
-        <v>12.5</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="268">
@@ -32546,22 +32546,22 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F268" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G268" t="b">
         <v>1</v>
       </c>
       <c r="H268" t="n">
-        <v>1417.301</v>
+        <v>1414.022</v>
       </c>
       <c r="I268" t="n">
-        <v>0.8704</v>
+        <v>0.977</v>
       </c>
       <c r="J268" t="n">
-        <v>1466.6</v>
+        <v>1471</v>
       </c>
       <c r="K268" t="n">
         <v>225</v>
@@ -32582,70 +32582,70 @@
         <v>224</v>
       </c>
       <c r="Q268" t="n">
-        <v>106.664</v>
+        <v>106.257</v>
       </c>
       <c r="R268" t="n">
-        <v>107.263</v>
+        <v>107.355</v>
       </c>
       <c r="S268" t="n">
-        <v>-0.599</v>
+        <v>-1.097</v>
       </c>
       <c r="T268" t="n">
-        <v>0.29675</v>
+        <v>0.30373</v>
       </c>
       <c r="U268" t="n">
-        <v>0.17577</v>
+        <v>0.1757</v>
       </c>
       <c r="V268" t="n">
-        <v>74.13</v>
+        <v>73.92</v>
       </c>
       <c r="W268" t="n">
-        <v>74.70999999999999</v>
+        <v>74.84</v>
       </c>
       <c r="X268" t="n">
-        <v>0.5341</v>
+        <v>0.5123</v>
       </c>
       <c r="Y268" t="n">
-        <v>25.33</v>
+        <v>25.439</v>
       </c>
       <c r="Z268" t="n">
-        <v>56.615</v>
+        <v>57.067</v>
       </c>
       <c r="AA268" t="n">
-        <v>4.783</v>
+        <v>4.682</v>
       </c>
       <c r="AB268" t="n">
-        <v>16.465</v>
+        <v>16.529</v>
       </c>
       <c r="AC268" t="n">
-        <v>18.086</v>
+        <v>17.846</v>
       </c>
       <c r="AD268" t="n">
-        <v>24.341</v>
+        <v>24.158</v>
       </c>
       <c r="AE268" t="n">
-        <v>10.006</v>
+        <v>10.321</v>
       </c>
       <c r="AF268" t="n">
-        <v>23.423</v>
+        <v>23.279</v>
       </c>
       <c r="AG268" t="n">
-        <v>11.131</v>
+        <v>11.222</v>
       </c>
       <c r="AH268" t="n">
-        <v>7.429</v>
+        <v>7.458</v>
       </c>
       <c r="AI268" t="n">
-        <v>3.571</v>
+        <v>3.542</v>
       </c>
       <c r="AJ268" t="n">
-        <v>19.744</v>
+        <v>19.907</v>
       </c>
       <c r="AK268" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AL268" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="269">
@@ -34466,22 +34466,22 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F284" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G284" t="b">
         <v>1</v>
       </c>
       <c r="H284" t="n">
-        <v>1508.173</v>
+        <v>1495.489</v>
       </c>
       <c r="I284" t="n">
-        <v>-1.6583</v>
+        <v>-1.6989</v>
       </c>
       <c r="J284" t="n">
-        <v>1492</v>
+        <v>1500.5</v>
       </c>
       <c r="K284" t="n">
         <v>174</v>
@@ -34502,70 +34502,70 @@
         <v>177</v>
       </c>
       <c r="Q284" t="n">
-        <v>111.926</v>
+        <v>111.697</v>
       </c>
       <c r="R284" t="n">
-        <v>108.288</v>
+        <v>108.982</v>
       </c>
       <c r="S284" t="n">
-        <v>3.638</v>
+        <v>2.715</v>
       </c>
       <c r="T284" t="n">
-        <v>0.27166</v>
+        <v>0.26981</v>
       </c>
       <c r="U284" t="n">
-        <v>0.12941</v>
+        <v>0.12888</v>
       </c>
       <c r="V284" t="n">
-        <v>73.63</v>
+        <v>73.5</v>
       </c>
       <c r="W284" t="n">
-        <v>71.06</v>
+        <v>71.56</v>
       </c>
       <c r="X284" t="n">
-        <v>0.525</v>
+        <v>0.4926</v>
       </c>
       <c r="Y284" t="n">
-        <v>24.757</v>
+        <v>24.767</v>
       </c>
       <c r="Z284" t="n">
-        <v>55.659</v>
+        <v>55.782</v>
       </c>
       <c r="AA284" t="n">
-        <v>6.995</v>
+        <v>6.854</v>
       </c>
       <c r="AB284" t="n">
-        <v>20.266</v>
+        <v>20.402</v>
       </c>
       <c r="AC284" t="n">
-        <v>17.121</v>
+        <v>17.117</v>
       </c>
       <c r="AD284" t="n">
-        <v>23.055</v>
+        <v>22.798</v>
       </c>
       <c r="AE284" t="n">
-        <v>8.459</v>
+        <v>8.412000000000001</v>
       </c>
       <c r="AF284" t="n">
-        <v>22.193</v>
+        <v>22.286</v>
       </c>
       <c r="AG284" t="n">
-        <v>12.3</v>
+        <v>12.149</v>
       </c>
       <c r="AH284" t="n">
-        <v>5.389</v>
+        <v>5.409</v>
       </c>
       <c r="AI284" t="n">
-        <v>4.136</v>
+        <v>4.036</v>
       </c>
       <c r="AJ284" t="n">
-        <v>17.359</v>
+        <v>17.632</v>
       </c>
       <c r="AK284" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AL284" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="285">
@@ -35666,22 +35666,22 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F294" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G294" t="b">
         <v>1</v>
       </c>
       <c r="H294" t="n">
-        <v>1548.356</v>
+        <v>1556.938</v>
       </c>
       <c r="I294" t="n">
-        <v>-2.8635</v>
+        <v>-2.7806</v>
       </c>
       <c r="J294" t="n">
-        <v>1520.2</v>
+        <v>1524.4</v>
       </c>
       <c r="K294" t="n">
         <v>177</v>
@@ -35702,70 +35702,70 @@
         <v>180</v>
       </c>
       <c r="Q294" t="n">
-        <v>102.845</v>
+        <v>104.063</v>
       </c>
       <c r="R294" t="n">
-        <v>102.803</v>
+        <v>102.391</v>
       </c>
       <c r="S294" t="n">
-        <v>0.042</v>
+        <v>1.672</v>
       </c>
       <c r="T294" t="n">
-        <v>0.33194</v>
+        <v>0.33571</v>
       </c>
       <c r="U294" t="n">
-        <v>0.15286</v>
+        <v>0.15173</v>
       </c>
       <c r="V294" t="n">
-        <v>66.73999999999999</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="W294" t="n">
-        <v>66.75</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="X294" t="n">
-        <v>0.5382</v>
+        <v>0.5528</v>
       </c>
       <c r="Y294" t="n">
-        <v>24.142</v>
+        <v>24.044</v>
       </c>
       <c r="Z294" t="n">
-        <v>58.486</v>
+        <v>58.428</v>
       </c>
       <c r="AA294" t="n">
-        <v>5.924</v>
+        <v>5.811</v>
       </c>
       <c r="AB294" t="n">
-        <v>20.532</v>
+        <v>20.69</v>
       </c>
       <c r="AC294" t="n">
-        <v>12.535</v>
+        <v>12.322</v>
       </c>
       <c r="AD294" t="n">
-        <v>18.304</v>
+        <v>18.182</v>
       </c>
       <c r="AE294" t="n">
-        <v>11.55</v>
+        <v>11.543</v>
       </c>
       <c r="AF294" t="n">
-        <v>23.372</v>
+        <v>23.028</v>
       </c>
       <c r="AG294" t="n">
-        <v>9.375</v>
+        <v>9.592000000000001</v>
       </c>
       <c r="AH294" t="n">
-        <v>5.999</v>
+        <v>5.801</v>
       </c>
       <c r="AI294" t="n">
-        <v>3.351</v>
+        <v>3.403</v>
       </c>
       <c r="AJ294" t="n">
-        <v>16.096</v>
+        <v>15.949</v>
       </c>
       <c r="AK294" t="n">
-        <v>3.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AL294" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="295">
@@ -35786,22 +35786,22 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F295" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G295" t="b">
         <v>1</v>
       </c>
       <c r="H295" t="n">
-        <v>1593.696</v>
+        <v>1596.975</v>
       </c>
       <c r="I295" t="n">
-        <v>1.3343</v>
+        <v>1.2134</v>
       </c>
       <c r="J295" t="n">
-        <v>1464.1</v>
+        <v>1466.1</v>
       </c>
       <c r="K295" t="n">
         <v>156</v>
@@ -35822,70 +35822,70 @@
         <v>138</v>
       </c>
       <c r="Q295" t="n">
-        <v>112.114</v>
+        <v>111.849</v>
       </c>
       <c r="R295" t="n">
-        <v>106.85</v>
+        <v>106.582</v>
       </c>
       <c r="S295" t="n">
-        <v>5.264</v>
+        <v>5.267</v>
       </c>
       <c r="T295" t="n">
-        <v>0.31618</v>
+        <v>0.31634</v>
       </c>
       <c r="U295" t="n">
-        <v>0.16011</v>
+        <v>0.16365</v>
       </c>
       <c r="V295" t="n">
-        <v>78.37</v>
+        <v>78.33</v>
       </c>
       <c r="W295" t="n">
-        <v>74.94</v>
+        <v>74.86</v>
       </c>
       <c r="X295" t="n">
-        <v>0.6268</v>
+        <v>0.6388</v>
       </c>
       <c r="Y295" t="n">
-        <v>26.691</v>
+        <v>26.401</v>
       </c>
       <c r="Z295" t="n">
-        <v>60.643</v>
+        <v>60.115</v>
       </c>
       <c r="AA295" t="n">
-        <v>9.423</v>
+        <v>9.108000000000001</v>
       </c>
       <c r="AB295" t="n">
-        <v>28.066</v>
+        <v>27.509</v>
       </c>
       <c r="AC295" t="n">
-        <v>15.566</v>
+        <v>16.419</v>
       </c>
       <c r="AD295" t="n">
-        <v>21.229</v>
+        <v>22.171</v>
       </c>
       <c r="AE295" t="n">
-        <v>11.15</v>
+        <v>11.194</v>
       </c>
       <c r="AF295" t="n">
-        <v>23.982</v>
+        <v>24.062</v>
       </c>
       <c r="AG295" t="n">
-        <v>15.284</v>
+        <v>15.054</v>
       </c>
       <c r="AH295" t="n">
-        <v>7.189</v>
+        <v>7.278</v>
       </c>
       <c r="AI295" t="n">
-        <v>3.371</v>
+        <v>3.567</v>
       </c>
       <c r="AJ295" t="n">
-        <v>16.779</v>
+        <v>16.865</v>
       </c>
       <c r="AK295" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AL295" t="n">
-        <v>-0.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="296">
@@ -35906,22 +35906,22 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F296" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G296" t="b">
         <v>1</v>
       </c>
       <c r="H296" t="n">
-        <v>1493.45</v>
+        <v>1495.672</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.8307</v>
+        <v>-1.8275</v>
       </c>
       <c r="J296" t="n">
-        <v>1529.8</v>
+        <v>1531.6</v>
       </c>
       <c r="K296" t="n">
         <v>196</v>
@@ -35942,70 +35942,70 @@
         <v>197</v>
       </c>
       <c r="Q296" t="n">
-        <v>104.531</v>
+        <v>105.566</v>
       </c>
       <c r="R296" t="n">
-        <v>110.322</v>
+        <v>110.647</v>
       </c>
       <c r="S296" t="n">
-        <v>-5.791</v>
+        <v>-5.081</v>
       </c>
       <c r="T296" t="n">
-        <v>0.22717</v>
+        <v>0.23459</v>
       </c>
       <c r="U296" t="n">
-        <v>0.1535</v>
+        <v>0.15187</v>
       </c>
       <c r="V296" t="n">
-        <v>71.19</v>
+        <v>72.42</v>
       </c>
       <c r="W296" t="n">
-        <v>75.43000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="X296" t="n">
-        <v>0.5442</v>
+        <v>0.5266</v>
       </c>
       <c r="Y296" t="n">
-        <v>22.769</v>
+        <v>23.393</v>
       </c>
       <c r="Z296" t="n">
-        <v>53.619</v>
+        <v>54.469</v>
       </c>
       <c r="AA296" t="n">
-        <v>7.599</v>
+        <v>7.683</v>
       </c>
       <c r="AB296" t="n">
-        <v>23.803</v>
+        <v>23.926</v>
       </c>
       <c r="AC296" t="n">
-        <v>18.054</v>
+        <v>17.95</v>
       </c>
       <c r="AD296" t="n">
-        <v>23.81</v>
+        <v>23.661</v>
       </c>
       <c r="AE296" t="n">
-        <v>6.415</v>
+        <v>6.701</v>
       </c>
       <c r="AF296" t="n">
-        <v>21.483</v>
+        <v>21.448</v>
       </c>
       <c r="AG296" t="n">
-        <v>12.769</v>
+        <v>12.782</v>
       </c>
       <c r="AH296" t="n">
-        <v>7.354</v>
+        <v>7.622</v>
       </c>
       <c r="AI296" t="n">
-        <v>4.769</v>
+        <v>4.666</v>
       </c>
       <c r="AJ296" t="n">
-        <v>17.388</v>
+        <v>17.792</v>
       </c>
       <c r="AK296" t="n">
-        <v>-15.8</v>
+        <v>-17.2</v>
       </c>
       <c r="AL296" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="297">
@@ -36026,22 +36026,22 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F297" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G297" t="b">
         <v>1</v>
       </c>
       <c r="H297" t="n">
-        <v>1676.214</v>
+        <v>1679.891</v>
       </c>
       <c r="I297" t="n">
-        <v>9.632899999999999</v>
+        <v>9.1937</v>
       </c>
       <c r="J297" t="n">
-        <v>1502.5</v>
+        <v>1503.5</v>
       </c>
       <c r="K297" t="n">
         <v>56</v>
@@ -36062,70 +36062,70 @@
         <v>50</v>
       </c>
       <c r="Q297" t="n">
-        <v>122.852</v>
+        <v>122.52</v>
       </c>
       <c r="R297" t="n">
-        <v>105.682</v>
+        <v>106.202</v>
       </c>
       <c r="S297" t="n">
-        <v>17.17</v>
+        <v>16.318</v>
       </c>
       <c r="T297" t="n">
-        <v>0.27056</v>
+        <v>0.27118</v>
       </c>
       <c r="U297" t="n">
-        <v>0.14609</v>
+        <v>0.1456</v>
       </c>
       <c r="V297" t="n">
-        <v>84.97</v>
+        <v>84.59</v>
       </c>
       <c r="W297" t="n">
-        <v>73.18000000000001</v>
+        <v>73.37</v>
       </c>
       <c r="X297" t="n">
-        <v>0.7879</v>
+        <v>0.795</v>
       </c>
       <c r="Y297" t="n">
-        <v>28.096</v>
+        <v>27.773</v>
       </c>
       <c r="Z297" t="n">
-        <v>57.843</v>
+        <v>57.612</v>
       </c>
       <c r="AA297" t="n">
-        <v>10.611</v>
+        <v>10.537</v>
       </c>
       <c r="AB297" t="n">
-        <v>26.601</v>
+        <v>26.537</v>
       </c>
       <c r="AC297" t="n">
-        <v>18.172</v>
+        <v>18.509</v>
       </c>
       <c r="AD297" t="n">
-        <v>23.217</v>
+        <v>23.63</v>
       </c>
       <c r="AE297" t="n">
-        <v>9.01</v>
+        <v>9.042999999999999</v>
       </c>
       <c r="AF297" t="n">
-        <v>23.944</v>
+        <v>23.966</v>
       </c>
       <c r="AG297" t="n">
-        <v>15.556</v>
+        <v>15.304</v>
       </c>
       <c r="AH297" t="n">
-        <v>6.667</v>
+        <v>6.441</v>
       </c>
       <c r="AI297" t="n">
-        <v>2.318</v>
+        <v>2.307</v>
       </c>
       <c r="AJ297" t="n">
-        <v>16.399</v>
+        <v>16.289</v>
       </c>
       <c r="AK297" t="n">
-        <v>17.6</v>
+        <v>18.8</v>
       </c>
       <c r="AL297" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="298">
@@ -36386,22 +36386,22 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F300" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G300" t="b">
         <v>1</v>
       </c>
       <c r="H300" t="n">
-        <v>1597.533</v>
+        <v>1599.582</v>
       </c>
       <c r="I300" t="n">
-        <v>0.5946</v>
+        <v>0.5782</v>
       </c>
       <c r="J300" t="n">
-        <v>1504.4</v>
+        <v>1499.7</v>
       </c>
       <c r="K300" t="n">
         <v>124</v>
@@ -36422,70 +36422,70 @@
         <v>114</v>
       </c>
       <c r="Q300" t="n">
-        <v>108.59</v>
+        <v>108.911</v>
       </c>
       <c r="R300" t="n">
-        <v>102.987</v>
+        <v>103.186</v>
       </c>
       <c r="S300" t="n">
-        <v>5.603</v>
+        <v>5.725</v>
       </c>
       <c r="T300" t="n">
-        <v>0.30726</v>
+        <v>0.3013</v>
       </c>
       <c r="U300" t="n">
-        <v>0.12453</v>
+        <v>0.12414</v>
       </c>
       <c r="V300" t="n">
-        <v>77.79000000000001</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="W300" t="n">
-        <v>73.76000000000001</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="X300" t="n">
-        <v>0.6259</v>
+        <v>0.6379</v>
       </c>
       <c r="Y300" t="n">
-        <v>27.796</v>
+        <v>28.121</v>
       </c>
       <c r="Z300" t="n">
-        <v>63.878</v>
+        <v>63.868</v>
       </c>
       <c r="AA300" t="n">
-        <v>5.497</v>
+        <v>5.448</v>
       </c>
       <c r="AB300" t="n">
-        <v>19.735</v>
+        <v>19.406</v>
       </c>
       <c r="AC300" t="n">
-        <v>16.701</v>
+        <v>16.625</v>
       </c>
       <c r="AD300" t="n">
-        <v>23.469</v>
+        <v>23.448</v>
       </c>
       <c r="AE300" t="n">
-        <v>11.374</v>
+        <v>11.114</v>
       </c>
       <c r="AF300" t="n">
-        <v>25.313</v>
+        <v>25.42</v>
       </c>
       <c r="AG300" t="n">
-        <v>13.626</v>
+        <v>13.911</v>
       </c>
       <c r="AH300" t="n">
-        <v>7.524</v>
+        <v>7.605</v>
       </c>
       <c r="AI300" t="n">
-        <v>3.476</v>
+        <v>3.506</v>
       </c>
       <c r="AJ300" t="n">
-        <v>14.483</v>
+        <v>14.494</v>
       </c>
       <c r="AK300" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AL300" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="301">
@@ -37586,22 +37586,22 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F310" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G310" t="b">
         <v>1</v>
       </c>
       <c r="H310" t="n">
-        <v>1376.649</v>
+        <v>1373.966</v>
       </c>
       <c r="I310" t="n">
-        <v>-2.5542</v>
+        <v>-2.3898</v>
       </c>
       <c r="J310" t="n">
-        <v>1424.1</v>
+        <v>1428.1</v>
       </c>
       <c r="K310" t="n">
         <v>304</v>
@@ -37622,70 +37622,70 @@
         <v>298</v>
       </c>
       <c r="Q310" t="n">
-        <v>110.346</v>
+        <v>110.541</v>
       </c>
       <c r="R310" t="n">
-        <v>117.351</v>
+        <v>117.799</v>
       </c>
       <c r="S310" t="n">
-        <v>-7.004</v>
+        <v>-7.257</v>
       </c>
       <c r="T310" t="n">
-        <v>0.27196</v>
+        <v>0.27071</v>
       </c>
       <c r="U310" t="n">
-        <v>0.13909</v>
+        <v>0.14189</v>
       </c>
       <c r="V310" t="n">
-        <v>76.65000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="W310" t="n">
-        <v>81.8</v>
+        <v>81.89</v>
       </c>
       <c r="X310" t="n">
-        <v>0.4273</v>
+        <v>0.4011</v>
       </c>
       <c r="Y310" t="n">
-        <v>25.932</v>
+        <v>25.907</v>
       </c>
       <c r="Z310" t="n">
-        <v>58.159</v>
+        <v>57.67</v>
       </c>
       <c r="AA310" t="n">
-        <v>8.345000000000001</v>
+        <v>8.222</v>
       </c>
       <c r="AB310" t="n">
-        <v>23.232</v>
+        <v>23.011</v>
       </c>
       <c r="AC310" t="n">
-        <v>16.309</v>
+        <v>16.475</v>
       </c>
       <c r="AD310" t="n">
-        <v>23.677</v>
+        <v>23.753</v>
       </c>
       <c r="AE310" t="n">
-        <v>8.632</v>
+        <v>8.499000000000001</v>
       </c>
       <c r="AF310" t="n">
-        <v>23.014</v>
+        <v>22.783</v>
       </c>
       <c r="AG310" t="n">
-        <v>12.236</v>
+        <v>12.086</v>
       </c>
       <c r="AH310" t="n">
-        <v>5.509</v>
+        <v>5.581</v>
       </c>
       <c r="AI310" t="n">
-        <v>1.764</v>
+        <v>1.784</v>
       </c>
       <c r="AJ310" t="n">
-        <v>16.595</v>
+        <v>16.568</v>
       </c>
       <c r="AK310" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL310" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="311">
@@ -37706,22 +37706,22 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F311" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G311" t="b">
         <v>1</v>
       </c>
       <c r="H311" t="n">
-        <v>1681.028</v>
+        <v>1669.074</v>
       </c>
       <c r="I311" t="n">
-        <v>2.0383</v>
+        <v>1.9449</v>
       </c>
       <c r="J311" t="n">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="K311" t="n">
         <v>104</v>
@@ -37742,70 +37742,70 @@
         <v>93</v>
       </c>
       <c r="Q311" t="n">
-        <v>115.349</v>
+        <v>114.725</v>
       </c>
       <c r="R311" t="n">
-        <v>102.31</v>
+        <v>103.357</v>
       </c>
       <c r="S311" t="n">
-        <v>13.04</v>
+        <v>11.368</v>
       </c>
       <c r="T311" t="n">
-        <v>0.31587</v>
+        <v>0.31301</v>
       </c>
       <c r="U311" t="n">
-        <v>0.14142</v>
+        <v>0.13936</v>
       </c>
       <c r="V311" t="n">
-        <v>75.48999999999999</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="W311" t="n">
-        <v>67.06</v>
+        <v>67.95</v>
       </c>
       <c r="X311" t="n">
-        <v>0.8295</v>
+        <v>0.7916</v>
       </c>
       <c r="Y311" t="n">
-        <v>25.398</v>
+        <v>25.373</v>
       </c>
       <c r="Z311" t="n">
-        <v>57.398</v>
+        <v>57.363</v>
       </c>
       <c r="AA311" t="n">
-        <v>8.227</v>
+        <v>8.121</v>
       </c>
       <c r="AB311" t="n">
-        <v>22.739</v>
+        <v>22.594</v>
       </c>
       <c r="AC311" t="n">
-        <v>16.466</v>
+        <v>17.028</v>
       </c>
       <c r="AD311" t="n">
-        <v>23.932</v>
+        <v>24.403</v>
       </c>
       <c r="AE311" t="n">
-        <v>11.716</v>
+        <v>11.606</v>
       </c>
       <c r="AF311" t="n">
-        <v>24.92</v>
+        <v>25.031</v>
       </c>
       <c r="AG311" t="n">
-        <v>13.398</v>
+        <v>13.34</v>
       </c>
       <c r="AH311" t="n">
-        <v>5.125</v>
+        <v>5.109</v>
       </c>
       <c r="AI311" t="n">
-        <v>2.364</v>
+        <v>2.363</v>
       </c>
       <c r="AJ311" t="n">
-        <v>16.898</v>
+        <v>17.097</v>
       </c>
       <c r="AK311" t="n">
-        <v>10.8</v>
+        <v>5.8</v>
       </c>
       <c r="AL311" t="n">
-        <v>8.300000000000001</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="312">
@@ -38186,22 +38186,22 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F315" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G315" t="b">
         <v>1</v>
       </c>
       <c r="H315" t="n">
-        <v>1293.858</v>
+        <v>1292.333</v>
       </c>
       <c r="I315" t="n">
-        <v>-4.1477</v>
+        <v>-4.0185</v>
       </c>
       <c r="J315" t="n">
-        <v>1548.4</v>
+        <v>1541</v>
       </c>
       <c r="K315" t="n">
         <v>339</v>
@@ -38222,70 +38222,70 @@
         <v>341</v>
       </c>
       <c r="Q315" t="n">
-        <v>95.503</v>
+        <v>95.857</v>
       </c>
       <c r="R315" t="n">
-        <v>117.522</v>
+        <v>117.442</v>
       </c>
       <c r="S315" t="n">
-        <v>-22.019</v>
+        <v>-21.584</v>
       </c>
       <c r="T315" t="n">
-        <v>0.3118</v>
+        <v>0.31347</v>
       </c>
       <c r="U315" t="n">
-        <v>0.16787</v>
+        <v>0.16442</v>
       </c>
       <c r="V315" t="n">
-        <v>67.15000000000001</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="W315" t="n">
-        <v>83.05</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="X315" t="n">
-        <v>0.1099</v>
+        <v>0.1061</v>
       </c>
       <c r="Y315" t="n">
-        <v>23.601</v>
+        <v>23.692</v>
       </c>
       <c r="Z315" t="n">
-        <v>60.802</v>
+        <v>61.197</v>
       </c>
       <c r="AA315" t="n">
-        <v>7.344</v>
+        <v>7.354</v>
       </c>
       <c r="AB315" t="n">
-        <v>25.022</v>
+        <v>25.242</v>
       </c>
       <c r="AC315" t="n">
-        <v>12.601</v>
+        <v>12.586</v>
       </c>
       <c r="AD315" t="n">
-        <v>17.927</v>
+        <v>18.051</v>
       </c>
       <c r="AE315" t="n">
-        <v>9.971</v>
+        <v>10.247</v>
       </c>
       <c r="AF315" t="n">
-        <v>21.363</v>
+        <v>21.727</v>
       </c>
       <c r="AG315" t="n">
-        <v>10.106</v>
+        <v>10.131</v>
       </c>
       <c r="AH315" t="n">
-        <v>6.429</v>
+        <v>6.288</v>
       </c>
       <c r="AI315" t="n">
-        <v>4.374</v>
+        <v>4.273</v>
       </c>
       <c r="AJ315" t="n">
-        <v>17.114</v>
+        <v>16.914</v>
       </c>
       <c r="AK315" t="n">
-        <v>-8.6</v>
+        <v>-12.2</v>
       </c>
       <c r="AL315" t="n">
-        <v>-11.9</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="316">
@@ -39746,22 +39746,22 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F328" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G328" t="b">
         <v>1</v>
       </c>
       <c r="H328" t="n">
-        <v>1381.545</v>
+        <v>1378.728</v>
       </c>
       <c r="I328" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.2151</v>
       </c>
       <c r="J328" t="n">
-        <v>1471.4</v>
+        <v>1473.5</v>
       </c>
       <c r="K328" t="n">
         <v>236</v>
@@ -39782,70 +39782,70 @@
         <v>235</v>
       </c>
       <c r="Q328" t="n">
-        <v>110.747</v>
+        <v>110.362</v>
       </c>
       <c r="R328" t="n">
-        <v>113.076</v>
+        <v>112.805</v>
       </c>
       <c r="S328" t="n">
-        <v>-2.328</v>
+        <v>-2.443</v>
       </c>
       <c r="T328" t="n">
-        <v>0.32812</v>
+        <v>0.32863</v>
       </c>
       <c r="U328" t="n">
-        <v>0.1487</v>
+        <v>0.15232</v>
       </c>
       <c r="V328" t="n">
-        <v>76.65000000000001</v>
+        <v>76.22</v>
       </c>
       <c r="W328" t="n">
-        <v>79.29000000000001</v>
+        <v>78.91</v>
       </c>
       <c r="X328" t="n">
-        <v>0.4697</v>
+        <v>0.4441</v>
       </c>
       <c r="Y328" t="n">
-        <v>27.247</v>
+        <v>26.935</v>
       </c>
       <c r="Z328" t="n">
-        <v>62.091</v>
+        <v>61.677</v>
       </c>
       <c r="AA328" t="n">
-        <v>8.494999999999999</v>
+        <v>8.478</v>
       </c>
       <c r="AB328" t="n">
-        <v>24.96</v>
+        <v>25.13</v>
       </c>
       <c r="AC328" t="n">
-        <v>13.475</v>
+        <v>13.739</v>
       </c>
       <c r="AD328" t="n">
-        <v>19.141</v>
+        <v>19.398</v>
       </c>
       <c r="AE328" t="n">
-        <v>11.247</v>
+        <v>11.326</v>
       </c>
       <c r="AF328" t="n">
-        <v>22.914</v>
+        <v>23.009</v>
       </c>
       <c r="AG328" t="n">
-        <v>12.051</v>
+        <v>11.938</v>
       </c>
       <c r="AH328" t="n">
-        <v>5.879</v>
+        <v>5.907</v>
       </c>
       <c r="AI328" t="n">
-        <v>2.389</v>
+        <v>2.332</v>
       </c>
       <c r="AJ328" t="n">
-        <v>18.949</v>
+        <v>18.87</v>
       </c>
       <c r="AK328" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AL328" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="329">
@@ -40946,22 +40946,22 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F338" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G338" t="b">
         <v>1</v>
       </c>
       <c r="H338" t="n">
-        <v>1381.115</v>
+        <v>1378.368</v>
       </c>
       <c r="I338" t="n">
-        <v>3.6336</v>
+        <v>3.5571</v>
       </c>
       <c r="J338" t="n">
-        <v>1448.1</v>
+        <v>1447.2</v>
       </c>
       <c r="K338" t="n">
         <v>195</v>
@@ -40982,70 +40982,70 @@
         <v>209</v>
       </c>
       <c r="Q338" t="n">
-        <v>114.383</v>
+        <v>114.488</v>
       </c>
       <c r="R338" t="n">
-        <v>115.913</v>
+        <v>117.39</v>
       </c>
       <c r="S338" t="n">
-        <v>-1.53</v>
+        <v>-2.902</v>
       </c>
       <c r="T338" t="n">
-        <v>0.22177</v>
+        <v>0.22971</v>
       </c>
       <c r="U338" t="n">
-        <v>0.14623</v>
+        <v>0.14293</v>
       </c>
       <c r="V338" t="n">
-        <v>73.73</v>
+        <v>73.92</v>
       </c>
       <c r="W338" t="n">
-        <v>75</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="X338" t="n">
-        <v>0.5382</v>
+        <v>0.5111</v>
       </c>
       <c r="Y338" t="n">
-        <v>24.936</v>
+        <v>25.301</v>
       </c>
       <c r="Z338" t="n">
-        <v>51.948</v>
+        <v>52.625</v>
       </c>
       <c r="AA338" t="n">
-        <v>7.144</v>
+        <v>7.451</v>
       </c>
       <c r="AB338" t="n">
-        <v>19.55</v>
+        <v>19.918</v>
       </c>
       <c r="AC338" t="n">
-        <v>16.715</v>
+        <v>16.703</v>
       </c>
       <c r="AD338" t="n">
-        <v>21.715</v>
+        <v>21.703</v>
       </c>
       <c r="AE338" t="n">
-        <v>6.297</v>
+        <v>6.663</v>
       </c>
       <c r="AF338" t="n">
-        <v>21.966</v>
+        <v>21.936</v>
       </c>
       <c r="AG338" t="n">
-        <v>13.526</v>
+        <v>13.896</v>
       </c>
       <c r="AH338" t="n">
-        <v>4.319</v>
+        <v>4.444</v>
       </c>
       <c r="AI338" t="n">
-        <v>2.67</v>
+        <v>2.639</v>
       </c>
       <c r="AJ338" t="n">
-        <v>17.025</v>
+        <v>17.054</v>
       </c>
       <c r="AK338" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="AL338" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="339">
@@ -41306,22 +41306,22 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F341" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G341" t="b">
         <v>1</v>
       </c>
       <c r="H341" t="n">
-        <v>1530.758</v>
+        <v>1524.075</v>
       </c>
       <c r="I341" t="n">
-        <v>2.6755</v>
+        <v>2.5272</v>
       </c>
       <c r="J341" t="n">
-        <v>1464.2</v>
+        <v>1468.9</v>
       </c>
       <c r="K341" t="n">
         <v>133</v>
@@ -41342,70 +41342,70 @@
         <v>124</v>
       </c>
       <c r="Q341" t="n">
-        <v>112.386</v>
+        <v>111.684</v>
       </c>
       <c r="R341" t="n">
-        <v>106.607</v>
+        <v>108.491</v>
       </c>
       <c r="S341" t="n">
-        <v>5.779</v>
+        <v>3.194</v>
       </c>
       <c r="T341" t="n">
-        <v>0.23571</v>
+        <v>0.23718</v>
       </c>
       <c r="U341" t="n">
-        <v>0.16184</v>
+        <v>0.16299</v>
       </c>
       <c r="V341" t="n">
-        <v>82.09999999999999</v>
+        <v>81.28</v>
       </c>
       <c r="W341" t="n">
-        <v>78.22</v>
+        <v>79.06</v>
       </c>
       <c r="X341" t="n">
-        <v>0.6259</v>
+        <v>0.5925</v>
       </c>
       <c r="Y341" t="n">
-        <v>27.51</v>
+        <v>27.06</v>
       </c>
       <c r="Z341" t="n">
-        <v>57.932</v>
+        <v>57.455</v>
       </c>
       <c r="AA341" t="n">
-        <v>8.238</v>
+        <v>8.093999999999999</v>
       </c>
       <c r="AB341" t="n">
-        <v>24.694</v>
+        <v>24.633</v>
       </c>
       <c r="AC341" t="n">
-        <v>18.844</v>
+        <v>19.063</v>
       </c>
       <c r="AD341" t="n">
-        <v>25.109</v>
+        <v>25.475</v>
       </c>
       <c r="AE341" t="n">
-        <v>7.571</v>
+        <v>7.618</v>
       </c>
       <c r="AF341" t="n">
-        <v>24.259</v>
+        <v>24.218</v>
       </c>
       <c r="AG341" t="n">
-        <v>17.667</v>
+        <v>17.249</v>
       </c>
       <c r="AH341" t="n">
-        <v>8.17</v>
+        <v>7.826</v>
       </c>
       <c r="AI341" t="n">
-        <v>3.871</v>
+        <v>3.835</v>
       </c>
       <c r="AJ341" t="n">
-        <v>17.646</v>
+        <v>17.853</v>
       </c>
       <c r="AK341" t="n">
-        <v>5.6</v>
+        <v>-0.4</v>
       </c>
       <c r="AL341" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="342">
@@ -41426,22 +41426,22 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F342" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G342" t="b">
         <v>1</v>
       </c>
       <c r="H342" t="n">
-        <v>1493.83</v>
+        <v>1488.81</v>
       </c>
       <c r="I342" t="n">
-        <v>1.7807</v>
+        <v>1.7975</v>
       </c>
       <c r="J342" t="n">
-        <v>1427.2</v>
+        <v>1437.4</v>
       </c>
       <c r="K342" t="n">
         <v>141</v>
@@ -41462,70 +41462,70 @@
         <v>129</v>
       </c>
       <c r="Q342" t="n">
-        <v>113.157</v>
+        <v>112.448</v>
       </c>
       <c r="R342" t="n">
-        <v>107.005</v>
+        <v>107.386</v>
       </c>
       <c r="S342" t="n">
-        <v>6.152</v>
+        <v>5.062</v>
       </c>
       <c r="T342" t="n">
-        <v>0.31303</v>
+        <v>0.31629</v>
       </c>
       <c r="U342" t="n">
-        <v>0.14206</v>
+        <v>0.14235</v>
       </c>
       <c r="V342" t="n">
-        <v>81.51000000000001</v>
+        <v>81.38</v>
       </c>
       <c r="W342" t="n">
-        <v>77.14</v>
+        <v>77.86</v>
       </c>
       <c r="X342" t="n">
-        <v>0.6716</v>
+        <v>0.6364</v>
       </c>
       <c r="Y342" t="n">
-        <v>26.251</v>
+        <v>26.241</v>
       </c>
       <c r="Z342" t="n">
-        <v>61.476</v>
+        <v>62.014</v>
       </c>
       <c r="AA342" t="n">
-        <v>9.039</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AB342" t="n">
-        <v>26.966</v>
+        <v>27.368</v>
       </c>
       <c r="AC342" t="n">
-        <v>19.964</v>
+        <v>19.845</v>
       </c>
       <c r="AD342" t="n">
-        <v>27.19</v>
+        <v>27.309</v>
       </c>
       <c r="AE342" t="n">
-        <v>11.594</v>
+        <v>11.877</v>
       </c>
       <c r="AF342" t="n">
-        <v>24.803</v>
+        <v>24.991</v>
       </c>
       <c r="AG342" t="n">
-        <v>13.609</v>
+        <v>13.514</v>
       </c>
       <c r="AH342" t="n">
-        <v>6.782</v>
+        <v>6.564</v>
       </c>
       <c r="AI342" t="n">
-        <v>2.752</v>
+        <v>2.655</v>
       </c>
       <c r="AJ342" t="n">
-        <v>19.544</v>
+        <v>19.905</v>
       </c>
       <c r="AK342" t="n">
-        <v>1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="AL342" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="343">
@@ -42626,22 +42626,22 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F352" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G352" t="b">
         <v>1</v>
       </c>
       <c r="H352" t="n">
-        <v>1515.562</v>
+        <v>1521.436</v>
       </c>
       <c r="I352" t="n">
-        <v>3.9427</v>
+        <v>3.9296</v>
       </c>
       <c r="J352" t="n">
-        <v>1452.7</v>
+        <v>1455.8</v>
       </c>
       <c r="K352" t="n">
         <v>172</v>
@@ -42662,70 +42662,70 @@
         <v>185</v>
       </c>
       <c r="Q352" t="n">
-        <v>107.666</v>
+        <v>107.026</v>
       </c>
       <c r="R352" t="n">
-        <v>102.86</v>
+        <v>102.734</v>
       </c>
       <c r="S352" t="n">
-        <v>4.806</v>
+        <v>4.291</v>
       </c>
       <c r="T352" t="n">
-        <v>0.2665</v>
+        <v>0.26866</v>
       </c>
       <c r="U352" t="n">
-        <v>0.14358</v>
+        <v>0.14365</v>
       </c>
       <c r="V352" t="n">
-        <v>69.31999999999999</v>
+        <v>68.84</v>
       </c>
       <c r="W352" t="n">
-        <v>66.61</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="X352" t="n">
-        <v>0.6914</v>
+        <v>0.7005</v>
       </c>
       <c r="Y352" t="n">
-        <v>22.495</v>
+        <v>22.336</v>
       </c>
       <c r="Z352" t="n">
-        <v>53.36</v>
+        <v>53.281</v>
       </c>
       <c r="AA352" t="n">
-        <v>8.130000000000001</v>
+        <v>7.965</v>
       </c>
       <c r="AB352" t="n">
-        <v>24.711</v>
+        <v>24.337</v>
       </c>
       <c r="AC352" t="n">
-        <v>16.201</v>
+        <v>16.204</v>
       </c>
       <c r="AD352" t="n">
-        <v>20.546</v>
+        <v>20.564</v>
       </c>
       <c r="AE352" t="n">
-        <v>6.983</v>
+        <v>6.993</v>
       </c>
       <c r="AF352" t="n">
-        <v>19.236</v>
+        <v>19.096</v>
       </c>
       <c r="AG352" t="n">
-        <v>12.687</v>
+        <v>12.527</v>
       </c>
       <c r="AH352" t="n">
-        <v>8.093</v>
+        <v>8.257</v>
       </c>
       <c r="AI352" t="n">
-        <v>4.851</v>
+        <v>5.005</v>
       </c>
       <c r="AJ352" t="n">
-        <v>16.443</v>
+        <v>16.271</v>
       </c>
       <c r="AK352" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AL352" t="n">
-        <v>12.5</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="353">
@@ -43466,22 +43466,22 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F359" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G359" t="b">
         <v>1</v>
       </c>
       <c r="H359" t="n">
-        <v>1424.906</v>
+        <v>1427.37</v>
       </c>
       <c r="I359" t="n">
-        <v>0.9866</v>
+        <v>1.0039</v>
       </c>
       <c r="J359" t="n">
-        <v>1433.6</v>
+        <v>1430.9</v>
       </c>
       <c r="K359" t="n">
         <v>191</v>
@@ -43502,70 +43502,70 @@
         <v>201</v>
       </c>
       <c r="Q359" t="n">
-        <v>119.079</v>
+        <v>119.175</v>
       </c>
       <c r="R359" t="n">
-        <v>116.547</v>
+        <v>116.563</v>
       </c>
       <c r="S359" t="n">
-        <v>2.532</v>
+        <v>2.613</v>
       </c>
       <c r="T359" t="n">
-        <v>0.28019</v>
+        <v>0.2859</v>
       </c>
       <c r="U359" t="n">
-        <v>0.14426</v>
+        <v>0.14407</v>
       </c>
       <c r="V359" t="n">
-        <v>84.45999999999999</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="W359" t="n">
-        <v>82.84999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="X359" t="n">
-        <v>0.5974</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="Y359" t="n">
-        <v>28.916</v>
+        <v>29.025</v>
       </c>
       <c r="Z359" t="n">
-        <v>60.018</v>
+        <v>60.577</v>
       </c>
       <c r="AA359" t="n">
-        <v>9.747</v>
+        <v>9.981999999999999</v>
       </c>
       <c r="AB359" t="n">
-        <v>27.76</v>
+        <v>28.127</v>
       </c>
       <c r="AC359" t="n">
-        <v>16.597</v>
+        <v>16.494</v>
       </c>
       <c r="AD359" t="n">
-        <v>22.24</v>
+        <v>22.103</v>
       </c>
       <c r="AE359" t="n">
-        <v>8.996</v>
+        <v>9.201000000000001</v>
       </c>
       <c r="AF359" t="n">
-        <v>22.763</v>
+        <v>22.584</v>
       </c>
       <c r="AG359" t="n">
-        <v>15.721</v>
+        <v>15.768</v>
       </c>
       <c r="AH359" t="n">
-        <v>5.654</v>
+        <v>5.969</v>
       </c>
       <c r="AI359" t="n">
-        <v>2.818</v>
+        <v>2.927</v>
       </c>
       <c r="AJ359" t="n">
-        <v>19.623</v>
+        <v>19.708</v>
       </c>
       <c r="AK359" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AL359" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="360">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -1226,22 +1226,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1291.479</v>
+        <v>1288.672</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.5457</v>
+        <v>-2.4613</v>
       </c>
       <c r="J7" t="n">
-        <v>1386.1</v>
+        <v>1382</v>
       </c>
       <c r="K7" t="n">
         <v>317</v>
@@ -1262,70 +1262,70 @@
         <v>321</v>
       </c>
       <c r="Q7" t="n">
-        <v>100.633</v>
+        <v>100.336</v>
       </c>
       <c r="R7" t="n">
-        <v>109.066</v>
+        <v>109.176</v>
       </c>
       <c r="S7" t="n">
-        <v>-8.433999999999999</v>
+        <v>-8.840999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3236</v>
+        <v>0.31821</v>
       </c>
       <c r="U7" t="n">
-        <v>0.17943</v>
+        <v>0.17756</v>
       </c>
       <c r="V7" t="n">
-        <v>71.64</v>
+        <v>71.45</v>
       </c>
       <c r="W7" t="n">
-        <v>77.47</v>
+        <v>77.58</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2969</v>
+        <v>0.2875</v>
       </c>
       <c r="Y7" t="n">
-        <v>24.705</v>
+        <v>24.744</v>
       </c>
       <c r="Z7" t="n">
-        <v>60.055</v>
+        <v>59.856</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.385</v>
+        <v>7.258</v>
       </c>
       <c r="AB7" t="n">
-        <v>23.042</v>
+        <v>22.708</v>
       </c>
       <c r="AC7" t="n">
-        <v>14.847</v>
+        <v>15.206</v>
       </c>
       <c r="AD7" t="n">
-        <v>21.022</v>
+        <v>21.407</v>
       </c>
       <c r="AE7" t="n">
-        <v>10.988</v>
+        <v>10.801</v>
       </c>
       <c r="AF7" t="n">
-        <v>22.513</v>
+        <v>22.749</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.649</v>
+        <v>11.806</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.945</v>
+        <v>7.936</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.778</v>
+        <v>3.828</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19.003</v>
+        <v>18.939</v>
       </c>
       <c r="AK7" t="n">
-        <v>-6.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1466,22 +1466,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1267.327</v>
+        <v>1270.134</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4578</v>
+        <v>-1.4276</v>
       </c>
       <c r="J9" t="n">
-        <v>1413.6</v>
+        <v>1410.3</v>
       </c>
       <c r="K9" t="n">
         <v>351</v>
@@ -1502,70 +1502,70 @@
         <v>352</v>
       </c>
       <c r="Q9" t="n">
-        <v>95.94</v>
+        <v>97.167</v>
       </c>
       <c r="R9" t="n">
-        <v>115.854</v>
+        <v>114.964</v>
       </c>
       <c r="S9" t="n">
-        <v>-19.914</v>
+        <v>-17.798</v>
       </c>
       <c r="T9" t="n">
-        <v>0.30273</v>
+        <v>0.30634</v>
       </c>
       <c r="U9" t="n">
-        <v>0.18876</v>
+        <v>0.18556</v>
       </c>
       <c r="V9" t="n">
-        <v>66.65000000000001</v>
+        <v>67.39</v>
       </c>
       <c r="W9" t="n">
-        <v>81.23</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2627</v>
+        <v>0.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>24.01</v>
+        <v>24.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>57.149</v>
+        <v>57.477</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.466</v>
+        <v>6.509</v>
       </c>
       <c r="AB9" t="n">
-        <v>19.35</v>
+        <v>19.791</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.167</v>
+        <v>12.236</v>
       </c>
       <c r="AD9" t="n">
-        <v>17.263</v>
+        <v>17.391</v>
       </c>
       <c r="AE9" t="n">
-        <v>8.295999999999999</v>
+        <v>8.558999999999999</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.315</v>
+        <v>19.464</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.12</v>
+        <v>11.295</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.755</v>
+        <v>7.686</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.266</v>
+        <v>3.377</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17.553</v>
+        <v>17.773</v>
       </c>
       <c r="AK9" t="n">
-        <v>-8</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AL9" t="n">
-        <v>-6.9</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="10">
@@ -5186,22 +5186,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1405.566</v>
+        <v>1402.226</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1743</v>
+        <v>0.2622</v>
       </c>
       <c r="J40" t="n">
-        <v>1523.3</v>
+        <v>1518.8</v>
       </c>
       <c r="K40" t="n">
         <v>177</v>
@@ -5222,70 +5222,70 @@
         <v>192</v>
       </c>
       <c r="Q40" t="n">
-        <v>109.09</v>
+        <v>108.494</v>
       </c>
       <c r="R40" t="n">
-        <v>112.484</v>
+        <v>112.585</v>
       </c>
       <c r="S40" t="n">
-        <v>-3.395</v>
+        <v>-4.091</v>
       </c>
       <c r="T40" t="n">
-        <v>0.34056</v>
+        <v>0.33944</v>
       </c>
       <c r="U40" t="n">
-        <v>0.15989</v>
+        <v>0.16742</v>
       </c>
       <c r="V40" t="n">
-        <v>76.53</v>
+        <v>75.95</v>
       </c>
       <c r="W40" t="n">
-        <v>78.88</v>
+        <v>78.77</v>
       </c>
       <c r="X40" t="n">
-        <v>0.4569</v>
+        <v>0.4335</v>
       </c>
       <c r="Y40" t="n">
-        <v>25.681</v>
+        <v>25.57</v>
       </c>
       <c r="Z40" t="n">
-        <v>59.078</v>
+        <v>58.52</v>
       </c>
       <c r="AA40" t="n">
-        <v>6.919</v>
+        <v>6.809</v>
       </c>
       <c r="AB40" t="n">
-        <v>21.674</v>
+        <v>21.561</v>
       </c>
       <c r="AC40" t="n">
-        <v>17.406</v>
+        <v>17.323</v>
       </c>
       <c r="AD40" t="n">
-        <v>23.917</v>
+        <v>23.738</v>
       </c>
       <c r="AE40" t="n">
-        <v>10.729</v>
+        <v>10.73</v>
       </c>
       <c r="AF40" t="n">
-        <v>20.751</v>
+        <v>20.881</v>
       </c>
       <c r="AG40" t="n">
-        <v>11.288</v>
+        <v>11.199</v>
       </c>
       <c r="AH40" t="n">
-        <v>6.556</v>
+        <v>6.397</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.489</v>
+        <v>1.465</v>
       </c>
       <c r="AJ40" t="n">
-        <v>18.707</v>
+        <v>18.619</v>
       </c>
       <c r="AK40" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AL40" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -9146,22 +9146,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>1321.596</v>
+        <v>1327.669</v>
       </c>
       <c r="I73" t="n">
-        <v>1.5666</v>
+        <v>1.6095</v>
       </c>
       <c r="J73" t="n">
-        <v>1449.2</v>
+        <v>1453.9</v>
       </c>
       <c r="K73" t="n">
         <v>222</v>
@@ -9182,70 +9182,70 @@
         <v>229</v>
       </c>
       <c r="Q73" t="n">
-        <v>109.832</v>
+        <v>109.628</v>
       </c>
       <c r="R73" t="n">
-        <v>112.816</v>
+        <v>112.459</v>
       </c>
       <c r="S73" t="n">
-        <v>-2.984</v>
+        <v>-2.831</v>
       </c>
       <c r="T73" t="n">
-        <v>0.31172</v>
+        <v>0.31612</v>
       </c>
       <c r="U73" t="n">
-        <v>0.15656</v>
+        <v>0.16036</v>
       </c>
       <c r="V73" t="n">
-        <v>77.05</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="W73" t="n">
-        <v>79.47</v>
+        <v>78.97</v>
       </c>
       <c r="X73" t="n">
-        <v>0.5062</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="Y73" t="n">
-        <v>27.319</v>
+        <v>27.182</v>
       </c>
       <c r="Z73" t="n">
-        <v>61.291</v>
+        <v>61.023</v>
       </c>
       <c r="AA73" t="n">
-        <v>6.753</v>
+        <v>6.67</v>
       </c>
       <c r="AB73" t="n">
-        <v>19.247</v>
+        <v>19.375</v>
       </c>
       <c r="AC73" t="n">
-        <v>15.66</v>
+        <v>15.341</v>
       </c>
       <c r="AD73" t="n">
-        <v>19.907</v>
+        <v>19.716</v>
       </c>
       <c r="AE73" t="n">
-        <v>10.739</v>
+        <v>10.841</v>
       </c>
       <c r="AF73" t="n">
-        <v>23.698</v>
+        <v>23.443</v>
       </c>
       <c r="AG73" t="n">
-        <v>13.199</v>
+        <v>13.295</v>
       </c>
       <c r="AH73" t="n">
-        <v>5.658</v>
+        <v>5.648</v>
       </c>
       <c r="AI73" t="n">
-        <v>3.353</v>
+        <v>3.295</v>
       </c>
       <c r="AJ73" t="n">
-        <v>19.388</v>
+        <v>19.239</v>
       </c>
       <c r="AK73" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AL73" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -10106,22 +10106,22 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F81" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G81" t="b">
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>1316.019</v>
+        <v>1318.996</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.332</v>
+        <v>-1.1643</v>
       </c>
       <c r="J81" t="n">
-        <v>1454.6</v>
+        <v>1451.5</v>
       </c>
       <c r="K81" t="n">
         <v>166</v>
@@ -10142,70 +10142,70 @@
         <v>201</v>
       </c>
       <c r="Q81" t="n">
-        <v>111.772</v>
+        <v>112.139</v>
       </c>
       <c r="R81" t="n">
-        <v>113.134</v>
+        <v>113.116</v>
       </c>
       <c r="S81" t="n">
-        <v>-1.362</v>
+        <v>-0.976</v>
       </c>
       <c r="T81" t="n">
-        <v>0.29233</v>
+        <v>0.29289</v>
       </c>
       <c r="U81" t="n">
         <v>0.17069</v>
       </c>
       <c r="V81" t="n">
-        <v>77.79000000000001</v>
+        <v>78.02</v>
       </c>
       <c r="W81" t="n">
-        <v>79.15000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="X81" t="n">
-        <v>0.3966</v>
+        <v>0.424</v>
       </c>
       <c r="Y81" t="n">
-        <v>27.595</v>
+        <v>27.616</v>
       </c>
       <c r="Z81" t="n">
-        <v>57.766</v>
+        <v>57.68</v>
       </c>
       <c r="AA81" t="n">
-        <v>7.289</v>
+        <v>7.368</v>
       </c>
       <c r="AB81" t="n">
-        <v>20.016</v>
+        <v>20.112</v>
       </c>
       <c r="AC81" t="n">
-        <v>15.316</v>
+        <v>15.416</v>
       </c>
       <c r="AD81" t="n">
-        <v>20.474</v>
+        <v>20.704</v>
       </c>
       <c r="AE81" t="n">
-        <v>8.967000000000001</v>
+        <v>9.007999999999999</v>
       </c>
       <c r="AF81" t="n">
-        <v>21.115</v>
+        <v>21.168</v>
       </c>
       <c r="AG81" t="n">
-        <v>13.421</v>
+        <v>13.616</v>
       </c>
       <c r="AH81" t="n">
-        <v>6.165</v>
+        <v>5.96</v>
       </c>
       <c r="AI81" t="n">
-        <v>3.532</v>
+        <v>3.408</v>
       </c>
       <c r="AJ81" t="n">
-        <v>18.108</v>
+        <v>18.216</v>
       </c>
       <c r="AK81" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="AL81" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="82">
@@ -10586,22 +10586,22 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F85" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G85" t="b">
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>1518.466</v>
+        <v>1511.995</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4929</v>
+        <v>0.4694</v>
       </c>
       <c r="J85" t="n">
-        <v>1416.5</v>
+        <v>1421.6</v>
       </c>
       <c r="K85" t="n">
         <v>147</v>
@@ -10622,70 +10622,70 @@
         <v>126</v>
       </c>
       <c r="Q85" t="n">
-        <v>116.449</v>
+        <v>115.903</v>
       </c>
       <c r="R85" t="n">
-        <v>105.528</v>
+        <v>106.335</v>
       </c>
       <c r="S85" t="n">
-        <v>10.921</v>
+        <v>9.568</v>
       </c>
       <c r="T85" t="n">
-        <v>0.26802</v>
+        <v>0.26977</v>
       </c>
       <c r="U85" t="n">
-        <v>0.14557</v>
+        <v>0.14742</v>
       </c>
       <c r="V85" t="n">
-        <v>77.23999999999999</v>
+        <v>76.67</v>
       </c>
       <c r="W85" t="n">
-        <v>69.91</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="X85" t="n">
-        <v>0.6806</v>
+        <v>0.6503</v>
       </c>
       <c r="Y85" t="n">
-        <v>27.45</v>
+        <v>27.465</v>
       </c>
       <c r="Z85" t="n">
-        <v>56.367</v>
+        <v>56.283</v>
       </c>
       <c r="AA85" t="n">
-        <v>7.521</v>
+        <v>7.615</v>
       </c>
       <c r="AB85" t="n">
-        <v>21.435</v>
+        <v>21.603</v>
       </c>
       <c r="AC85" t="n">
-        <v>14.821</v>
+        <v>14.725</v>
       </c>
       <c r="AD85" t="n">
-        <v>19.722</v>
+        <v>19.521</v>
       </c>
       <c r="AE85" t="n">
-        <v>8.31</v>
+        <v>8.43</v>
       </c>
       <c r="AF85" t="n">
-        <v>22.735</v>
+        <v>22.832</v>
       </c>
       <c r="AG85" t="n">
-        <v>14.153</v>
+        <v>14.106</v>
       </c>
       <c r="AH85" t="n">
-        <v>8.606999999999999</v>
+        <v>8.428000000000001</v>
       </c>
       <c r="AI85" t="n">
-        <v>3.329</v>
+        <v>3.31</v>
       </c>
       <c r="AJ85" t="n">
-        <v>16.853</v>
+        <v>16.756</v>
       </c>
       <c r="AK85" t="n">
-        <v>2.4</v>
+        <v>-3</v>
       </c>
       <c r="AL85" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="86">
@@ -12026,22 +12026,22 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F97" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G97" t="b">
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>1536.386</v>
+        <v>1542.857</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9002</v>
+        <v>0.8197</v>
       </c>
       <c r="J97" t="n">
-        <v>1417.8</v>
+        <v>1422.2</v>
       </c>
       <c r="K97" t="n">
         <v>199</v>
@@ -12062,70 +12062,70 @@
         <v>194</v>
       </c>
       <c r="Q97" t="n">
-        <v>111.677</v>
+        <v>112.011</v>
       </c>
       <c r="R97" t="n">
-        <v>107.709</v>
+        <v>107.277</v>
       </c>
       <c r="S97" t="n">
-        <v>3.968</v>
+        <v>4.734</v>
       </c>
       <c r="T97" t="n">
-        <v>0.25628</v>
+        <v>0.25616</v>
       </c>
       <c r="U97" t="n">
-        <v>0.17153</v>
+        <v>0.17102</v>
       </c>
       <c r="V97" t="n">
-        <v>75.08</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="W97" t="n">
-        <v>72.55</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="X97" t="n">
-        <v>0.6034</v>
+        <v>0.616</v>
       </c>
       <c r="Y97" t="n">
-        <v>26.685</v>
+        <v>26.592</v>
       </c>
       <c r="Z97" t="n">
-        <v>56.691</v>
+        <v>56.496</v>
       </c>
       <c r="AA97" t="n">
-        <v>8.802</v>
+        <v>8.568</v>
       </c>
       <c r="AB97" t="n">
-        <v>26.576</v>
+        <v>26.208</v>
       </c>
       <c r="AC97" t="n">
-        <v>12.747</v>
+        <v>12.56</v>
       </c>
       <c r="AD97" t="n">
-        <v>18.358</v>
+        <v>18.288</v>
       </c>
       <c r="AE97" t="n">
-        <v>9.007</v>
+        <v>8.912000000000001</v>
       </c>
       <c r="AF97" t="n">
-        <v>25.246</v>
+        <v>25.008</v>
       </c>
       <c r="AG97" t="n">
-        <v>15.033</v>
+        <v>14.632</v>
       </c>
       <c r="AH97" t="n">
-        <v>4.348</v>
+        <v>4.48</v>
       </c>
       <c r="AI97" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="AJ97" t="n">
-        <v>15.572</v>
+        <v>15.472</v>
       </c>
       <c r="AK97" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AL97" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="98">
@@ -12266,22 +12266,22 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F99" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G99" t="b">
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>1448.4</v>
+        <v>1444.414</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7301</v>
+        <v>0.7778</v>
       </c>
       <c r="J99" t="n">
-        <v>1444.4</v>
+        <v>1449.5</v>
       </c>
       <c r="K99" t="n">
         <v>230</v>
@@ -12302,70 +12302,70 @@
         <v>219</v>
       </c>
       <c r="Q99" t="n">
-        <v>111.539</v>
+        <v>111.045</v>
       </c>
       <c r="R99" t="n">
-        <v>111.349</v>
+        <v>111.873</v>
       </c>
       <c r="S99" t="n">
-        <v>0.191</v>
+        <v>-0.827</v>
       </c>
       <c r="T99" t="n">
-        <v>0.31519</v>
+        <v>0.31381</v>
       </c>
       <c r="U99" t="n">
-        <v>0.14788</v>
+        <v>0.14918</v>
       </c>
       <c r="V99" t="n">
-        <v>80.45999999999999</v>
+        <v>79.72</v>
       </c>
       <c r="W99" t="n">
-        <v>80.42</v>
+        <v>80.31</v>
       </c>
       <c r="X99" t="n">
-        <v>0.5629</v>
+        <v>0.5381</v>
       </c>
       <c r="Y99" t="n">
-        <v>26.038</v>
+        <v>25.769</v>
       </c>
       <c r="Z99" t="n">
-        <v>60.962</v>
+        <v>60.49</v>
       </c>
       <c r="AA99" t="n">
-        <v>9.417</v>
+        <v>9.359</v>
       </c>
       <c r="AB99" t="n">
-        <v>28.855</v>
+        <v>28.85</v>
       </c>
       <c r="AC99" t="n">
-        <v>17.759</v>
+        <v>17.691</v>
       </c>
       <c r="AD99" t="n">
-        <v>24.536</v>
+        <v>24.233</v>
       </c>
       <c r="AE99" t="n">
-        <v>10.155</v>
+        <v>9.956</v>
       </c>
       <c r="AF99" t="n">
-        <v>21.786</v>
+        <v>21.44</v>
       </c>
       <c r="AG99" t="n">
-        <v>10.767</v>
+        <v>10.662</v>
       </c>
       <c r="AH99" t="n">
-        <v>7.777</v>
+        <v>7.913</v>
       </c>
       <c r="AI99" t="n">
-        <v>3.33</v>
+        <v>3.312</v>
       </c>
       <c r="AJ99" t="n">
-        <v>19.503</v>
+        <v>19.342</v>
       </c>
       <c r="AK99" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AL99" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="100">
@@ -13106,22 +13106,22 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F106" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G106" t="b">
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>2061.642</v>
+        <v>2063.153</v>
       </c>
       <c r="I106" t="n">
-        <v>6.7538</v>
+        <v>6.2559</v>
       </c>
       <c r="J106" t="n">
-        <v>1597.9</v>
+        <v>1593.1</v>
       </c>
       <c r="K106" t="n">
         <v>10</v>
@@ -13142,70 +13142,70 @@
         <v>5</v>
       </c>
       <c r="Q106" t="n">
-        <v>120.347</v>
+        <v>120.058</v>
       </c>
       <c r="R106" t="n">
-        <v>93.251</v>
+        <v>92.989</v>
       </c>
       <c r="S106" t="n">
-        <v>27.097</v>
+        <v>27.069</v>
       </c>
       <c r="T106" t="n">
-        <v>0.2992</v>
+        <v>0.2963</v>
       </c>
       <c r="U106" t="n">
-        <v>0.13289</v>
+        <v>0.13371</v>
       </c>
       <c r="V106" t="n">
-        <v>85.66</v>
+        <v>85.09</v>
       </c>
       <c r="W106" t="n">
-        <v>66.3</v>
+        <v>65.83</v>
       </c>
       <c r="X106" t="n">
-        <v>0.8928</v>
+        <v>0.9073</v>
       </c>
       <c r="Y106" t="n">
-        <v>32.586</v>
+        <v>32.388</v>
       </c>
       <c r="Z106" t="n">
-        <v>63.971</v>
+        <v>63.603</v>
       </c>
       <c r="AA106" t="n">
-        <v>6.658</v>
+        <v>6.524</v>
       </c>
       <c r="AB106" t="n">
-        <v>19.614</v>
+        <v>19.41</v>
       </c>
       <c r="AC106" t="n">
-        <v>13.826</v>
+        <v>13.793</v>
       </c>
       <c r="AD106" t="n">
-        <v>19.748</v>
+        <v>19.554</v>
       </c>
       <c r="AE106" t="n">
-        <v>11.017</v>
+        <v>10.895</v>
       </c>
       <c r="AF106" t="n">
-        <v>25.919</v>
+        <v>25.96</v>
       </c>
       <c r="AG106" t="n">
-        <v>18.133</v>
+        <v>18.144</v>
       </c>
       <c r="AH106" t="n">
-        <v>8.587999999999999</v>
+        <v>8.648999999999999</v>
       </c>
       <c r="AI106" t="n">
-        <v>3.681</v>
+        <v>3.691</v>
       </c>
       <c r="AJ106" t="n">
-        <v>17.148</v>
+        <v>17.03</v>
       </c>
       <c r="AK106" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="AL106" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="107">
@@ -13226,22 +13226,22 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F107" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G107" t="b">
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>1310.866</v>
+        <v>1312.041</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.5341</v>
+        <v>-0.5671</v>
       </c>
       <c r="J107" t="n">
-        <v>1363.2</v>
+        <v>1352.3</v>
       </c>
       <c r="K107" t="n">
         <v>298</v>
@@ -13262,70 +13262,70 @@
         <v>301</v>
       </c>
       <c r="Q107" t="n">
-        <v>99.773</v>
+        <v>100.56</v>
       </c>
       <c r="R107" t="n">
-        <v>104.045</v>
+        <v>103.092</v>
       </c>
       <c r="S107" t="n">
-        <v>-4.273</v>
+        <v>-2.532</v>
       </c>
       <c r="T107" t="n">
-        <v>0.29712</v>
+        <v>0.29737</v>
       </c>
       <c r="U107" t="n">
-        <v>0.20505</v>
+        <v>0.20438</v>
       </c>
       <c r="V107" t="n">
-        <v>68.84999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="W107" t="n">
-        <v>71.93000000000001</v>
+        <v>71.16</v>
       </c>
       <c r="X107" t="n">
-        <v>0.3864</v>
+        <v>0.4063</v>
       </c>
       <c r="Y107" t="n">
-        <v>23.091</v>
+        <v>23.142</v>
       </c>
       <c r="Z107" t="n">
-        <v>54.205</v>
+        <v>54.142</v>
       </c>
       <c r="AA107" t="n">
-        <v>6.466</v>
+        <v>6.766</v>
       </c>
       <c r="AB107" t="n">
-        <v>20.83</v>
+        <v>20.867</v>
       </c>
       <c r="AC107" t="n">
-        <v>16.205</v>
+        <v>16.198</v>
       </c>
       <c r="AD107" t="n">
-        <v>22.136</v>
+        <v>22.252</v>
       </c>
       <c r="AE107" t="n">
-        <v>9.034000000000001</v>
+        <v>9.087</v>
       </c>
       <c r="AF107" t="n">
-        <v>21.341</v>
+        <v>21.438</v>
       </c>
       <c r="AG107" t="n">
-        <v>11.83</v>
+        <v>11.999</v>
       </c>
       <c r="AH107" t="n">
-        <v>7.693</v>
+        <v>7.627</v>
       </c>
       <c r="AI107" t="n">
-        <v>2.614</v>
+        <v>2.681</v>
       </c>
       <c r="AJ107" t="n">
-        <v>18.875</v>
+        <v>18.814</v>
       </c>
       <c r="AK107" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="AL107" t="n">
-        <v>-2.3</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="108">
@@ -13946,22 +13946,22 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F113" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G113" t="b">
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>1574.472</v>
+        <v>1582.041</v>
       </c>
       <c r="I113" t="n">
-        <v>3.7174</v>
+        <v>3.5064</v>
       </c>
       <c r="J113" t="n">
-        <v>1481.7</v>
+        <v>1484.4</v>
       </c>
       <c r="K113" t="n">
         <v>84</v>
@@ -13982,70 +13982,70 @@
         <v>88</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.985</v>
+        <v>113.542</v>
       </c>
       <c r="R113" t="n">
-        <v>102.458</v>
+        <v>102.659</v>
       </c>
       <c r="S113" t="n">
-        <v>11.527</v>
+        <v>10.883</v>
       </c>
       <c r="T113" t="n">
-        <v>0.30387</v>
+        <v>0.30742</v>
       </c>
       <c r="U113" t="n">
-        <v>0.15122</v>
+        <v>0.15226</v>
       </c>
       <c r="V113" t="n">
-        <v>74.88</v>
+        <v>74.42</v>
       </c>
       <c r="W113" t="n">
-        <v>67.53</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="X113" t="n">
-        <v>0.6702</v>
+        <v>0.6806</v>
       </c>
       <c r="Y113" t="n">
-        <v>25.559</v>
+        <v>25.469</v>
       </c>
       <c r="Z113" t="n">
-        <v>58.273</v>
+        <v>58.432</v>
       </c>
       <c r="AA113" t="n">
-        <v>9.382</v>
+        <v>9.403</v>
       </c>
       <c r="AB113" t="n">
-        <v>25.247</v>
+        <v>25.336</v>
       </c>
       <c r="AC113" t="n">
-        <v>14.381</v>
+        <v>14.079</v>
       </c>
       <c r="AD113" t="n">
-        <v>19.049</v>
+        <v>18.603</v>
       </c>
       <c r="AE113" t="n">
-        <v>10.69</v>
+        <v>10.857</v>
       </c>
       <c r="AF113" t="n">
-        <v>24.373</v>
+        <v>24.31</v>
       </c>
       <c r="AG113" t="n">
-        <v>12.495</v>
+        <v>12.354</v>
       </c>
       <c r="AH113" t="n">
-        <v>4.813</v>
+        <v>4.683</v>
       </c>
       <c r="AI113" t="n">
-        <v>3.694</v>
+        <v>3.619</v>
       </c>
       <c r="AJ113" t="n">
-        <v>17.678</v>
+        <v>17.45</v>
       </c>
       <c r="AK113" t="n">
-        <v>20.2</v>
+        <v>13.6</v>
       </c>
       <c r="AL113" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="114">
@@ -21626,22 +21626,22 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F177" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G177" t="b">
         <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>1447.398</v>
+        <v>1450.738</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1918</v>
+        <v>1.2494</v>
       </c>
       <c r="J177" t="n">
-        <v>1458.5</v>
+        <v>1456.7</v>
       </c>
       <c r="K177" t="n">
         <v>181</v>
@@ -21662,70 +21662,70 @@
         <v>169</v>
       </c>
       <c r="Q177" t="n">
-        <v>106.485</v>
+        <v>106.718</v>
       </c>
       <c r="R177" t="n">
-        <v>105.001</v>
+        <v>104.796</v>
       </c>
       <c r="S177" t="n">
-        <v>1.484</v>
+        <v>1.922</v>
       </c>
       <c r="T177" t="n">
-        <v>0.30647</v>
+        <v>0.31254</v>
       </c>
       <c r="U177" t="n">
-        <v>0.16555</v>
+        <v>0.16263</v>
       </c>
       <c r="V177" t="n">
-        <v>71.93000000000001</v>
+        <v>72.08</v>
       </c>
       <c r="W177" t="n">
-        <v>70.90000000000001</v>
+        <v>70.75</v>
       </c>
       <c r="X177" t="n">
-        <v>0.5528</v>
+        <v>0.5665</v>
       </c>
       <c r="Y177" t="n">
-        <v>25.46</v>
+        <v>25.465</v>
       </c>
       <c r="Z177" t="n">
-        <v>58.114</v>
+        <v>58.266</v>
       </c>
       <c r="AA177" t="n">
-        <v>6.949</v>
+        <v>6.809</v>
       </c>
       <c r="AB177" t="n">
-        <v>19.939</v>
+        <v>19.889</v>
       </c>
       <c r="AC177" t="n">
-        <v>14.064</v>
+        <v>14.342</v>
       </c>
       <c r="AD177" t="n">
-        <v>18.831</v>
+        <v>19.045</v>
       </c>
       <c r="AE177" t="n">
-        <v>10.076</v>
+        <v>10.133</v>
       </c>
       <c r="AF177" t="n">
-        <v>22.592</v>
+        <v>22.206</v>
       </c>
       <c r="AG177" t="n">
-        <v>13.843</v>
+        <v>13.756</v>
       </c>
       <c r="AH177" t="n">
-        <v>7.508</v>
+        <v>7.705</v>
       </c>
       <c r="AI177" t="n">
-        <v>4.442</v>
+        <v>4.252</v>
       </c>
       <c r="AJ177" t="n">
-        <v>15.917</v>
+        <v>15.898</v>
       </c>
       <c r="AK177" t="n">
-        <v>6.4</v>
+        <v>10.6</v>
       </c>
       <c r="AL177" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="178">
@@ -21746,22 +21746,22 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F178" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G178" t="b">
         <v>1</v>
       </c>
       <c r="H178" t="n">
-        <v>1458.848</v>
+        <v>1464.637</v>
       </c>
       <c r="I178" t="n">
-        <v>-1.7046</v>
+        <v>-1.6217</v>
       </c>
       <c r="J178" t="n">
-        <v>1432.7</v>
+        <v>1434.8</v>
       </c>
       <c r="K178" t="n">
         <v>187</v>
@@ -21782,70 +21782,70 @@
         <v>199</v>
       </c>
       <c r="Q178" t="n">
-        <v>106.424</v>
+        <v>107.791</v>
       </c>
       <c r="R178" t="n">
-        <v>109.34</v>
+        <v>109.828</v>
       </c>
       <c r="S178" t="n">
-        <v>-2.916</v>
+        <v>-2.037</v>
       </c>
       <c r="T178" t="n">
-        <v>0.18347</v>
+        <v>0.18463</v>
       </c>
       <c r="U178" t="n">
-        <v>0.19261</v>
+        <v>0.18961</v>
       </c>
       <c r="V178" t="n">
-        <v>75.17</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="W178" t="n">
-        <v>77.45</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="X178" t="n">
-        <v>0.4762</v>
+        <v>0.5051</v>
       </c>
       <c r="Y178" t="n">
-        <v>26.04</v>
+        <v>26.298</v>
       </c>
       <c r="Z178" t="n">
-        <v>54.212</v>
+        <v>54.323</v>
       </c>
       <c r="AA178" t="n">
-        <v>8.223000000000001</v>
+        <v>8.247</v>
       </c>
       <c r="AB178" t="n">
-        <v>22.476</v>
+        <v>22.414</v>
       </c>
       <c r="AC178" t="n">
-        <v>14.864</v>
+        <v>15.419</v>
       </c>
       <c r="AD178" t="n">
-        <v>19.267</v>
+        <v>19.854</v>
       </c>
       <c r="AE178" t="n">
-        <v>5.502</v>
+        <v>5.586</v>
       </c>
       <c r="AF178" t="n">
-        <v>24.604</v>
+        <v>24.758</v>
       </c>
       <c r="AG178" t="n">
-        <v>14.81</v>
+        <v>14.677</v>
       </c>
       <c r="AH178" t="n">
-        <v>5.601</v>
+        <v>5.465</v>
       </c>
       <c r="AI178" t="n">
-        <v>2.498</v>
+        <v>2.414</v>
       </c>
       <c r="AJ178" t="n">
-        <v>17.498</v>
+        <v>17.52</v>
       </c>
       <c r="AK178" t="n">
-        <v>-7.6</v>
+        <v>-5.6</v>
       </c>
       <c r="AL178" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="179">
@@ -22226,22 +22226,22 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F182" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G182" t="b">
         <v>1</v>
       </c>
       <c r="H182" t="n">
-        <v>1094.905</v>
+        <v>1093.731</v>
       </c>
       <c r="I182" t="n">
-        <v>-2.9612</v>
+        <v>-2.8469</v>
       </c>
       <c r="J182" t="n">
-        <v>1372.9</v>
+        <v>1371.1</v>
       </c>
       <c r="K182" t="n">
         <v>365</v>
@@ -22262,70 +22262,70 @@
         <v>365</v>
       </c>
       <c r="Q182" t="n">
-        <v>91.205</v>
+        <v>90.483</v>
       </c>
       <c r="R182" t="n">
-        <v>119.189</v>
+        <v>119.095</v>
       </c>
       <c r="S182" t="n">
-        <v>-27.984</v>
+        <v>-28.613</v>
       </c>
       <c r="T182" t="n">
-        <v>0.28556</v>
+        <v>0.291</v>
       </c>
       <c r="U182" t="n">
-        <v>0.20728</v>
+        <v>0.2104</v>
       </c>
       <c r="V182" t="n">
-        <v>63.74</v>
+        <v>63.1</v>
       </c>
       <c r="W182" t="n">
-        <v>83.92</v>
+        <v>83.62</v>
       </c>
       <c r="X182" t="n">
-        <v>0.0638</v>
+        <v>0.0618</v>
       </c>
       <c r="Y182" t="n">
-        <v>22.606</v>
+        <v>22.421</v>
       </c>
       <c r="Z182" t="n">
-        <v>55.116</v>
+        <v>55.122</v>
       </c>
       <c r="AA182" t="n">
-        <v>4.951</v>
+        <v>4.907</v>
       </c>
       <c r="AB182" t="n">
-        <v>16.725</v>
+        <v>16.638</v>
       </c>
       <c r="AC182" t="n">
-        <v>13.574</v>
+        <v>13.349</v>
       </c>
       <c r="AD182" t="n">
-        <v>18.872</v>
+        <v>18.669</v>
       </c>
       <c r="AE182" t="n">
-        <v>7.91</v>
+        <v>8.177</v>
       </c>
       <c r="AF182" t="n">
-        <v>19.672</v>
+        <v>19.743</v>
       </c>
       <c r="AG182" t="n">
-        <v>11.843</v>
+        <v>11.898</v>
       </c>
       <c r="AH182" t="n">
-        <v>6.922</v>
+        <v>7.094</v>
       </c>
       <c r="AI182" t="n">
-        <v>2.554</v>
+        <v>2.567</v>
       </c>
       <c r="AJ182" t="n">
-        <v>21.838</v>
+        <v>21.503</v>
       </c>
       <c r="AK182" t="n">
-        <v>-6</v>
+        <v>-11.2</v>
       </c>
       <c r="AL182" t="n">
-        <v>-10.8</v>
+        <v>-11.7</v>
       </c>
     </row>
     <row r="183">
@@ -22706,22 +22706,22 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F186" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G186" t="b">
         <v>1</v>
       </c>
       <c r="H186" t="n">
-        <v>1492.824</v>
+        <v>1487.034</v>
       </c>
       <c r="I186" t="n">
-        <v>-2.3144</v>
+        <v>-2.1857</v>
       </c>
       <c r="J186" t="n">
-        <v>1399.2</v>
+        <v>1401.2</v>
       </c>
       <c r="K186" t="n">
         <v>136</v>
@@ -22742,70 +22742,70 @@
         <v>139</v>
       </c>
       <c r="Q186" t="n">
-        <v>112.556</v>
+        <v>112.831</v>
       </c>
       <c r="R186" t="n">
-        <v>107.837</v>
+        <v>108.911</v>
       </c>
       <c r="S186" t="n">
-        <v>4.718</v>
+        <v>3.92</v>
       </c>
       <c r="T186" t="n">
-        <v>0.22</v>
+        <v>0.22488</v>
       </c>
       <c r="U186" t="n">
-        <v>0.15335</v>
+        <v>0.14965</v>
       </c>
       <c r="V186" t="n">
-        <v>80.56999999999999</v>
+        <v>80.89</v>
       </c>
       <c r="W186" t="n">
-        <v>77.3</v>
+        <v>78.19</v>
       </c>
       <c r="X186" t="n">
-        <v>0.6103</v>
+        <v>0.5818</v>
       </c>
       <c r="Y186" t="n">
-        <v>29.564</v>
+        <v>29.638</v>
       </c>
       <c r="Z186" t="n">
-        <v>60.8</v>
+        <v>61.177</v>
       </c>
       <c r="AA186" t="n">
-        <v>8.91</v>
+        <v>8.856</v>
       </c>
       <c r="AB186" t="n">
-        <v>25.359</v>
+        <v>25.35</v>
       </c>
       <c r="AC186" t="n">
-        <v>12.535</v>
+        <v>12.756</v>
       </c>
       <c r="AD186" t="n">
-        <v>16.519</v>
+        <v>16.839</v>
       </c>
       <c r="AE186" t="n">
-        <v>7.382</v>
+        <v>7.543</v>
       </c>
       <c r="AF186" t="n">
-        <v>26.108</v>
+        <v>25.909</v>
       </c>
       <c r="AG186" t="n">
-        <v>15.815</v>
+        <v>15.787</v>
       </c>
       <c r="AH186" t="n">
-        <v>4.084</v>
+        <v>3.993</v>
       </c>
       <c r="AI186" t="n">
-        <v>2.795</v>
+        <v>2.711</v>
       </c>
       <c r="AJ186" t="n">
-        <v>18.448</v>
+        <v>18.521</v>
       </c>
       <c r="AK186" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AL186" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="187">
@@ -23066,22 +23066,22 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F189" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G189" t="b">
         <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>1439.016</v>
+        <v>1434.798</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2239</v>
+        <v>0.1976</v>
       </c>
       <c r="J189" t="n">
-        <v>1427.9</v>
+        <v>1429.8</v>
       </c>
       <c r="K189" t="n">
         <v>172</v>
@@ -23102,70 +23102,70 @@
         <v>178</v>
       </c>
       <c r="Q189" t="n">
-        <v>113.32</v>
+        <v>113.17</v>
       </c>
       <c r="R189" t="n">
-        <v>108.95</v>
+        <v>109.867</v>
       </c>
       <c r="S189" t="n">
-        <v>4.37</v>
+        <v>3.303</v>
       </c>
       <c r="T189" t="n">
-        <v>0.31536</v>
+        <v>0.32037</v>
       </c>
       <c r="U189" t="n">
-        <v>0.15936</v>
+        <v>0.16094</v>
       </c>
       <c r="V189" t="n">
-        <v>80.73</v>
+        <v>80.98</v>
       </c>
       <c r="W189" t="n">
-        <v>77.84999999999999</v>
+        <v>78.87</v>
       </c>
       <c r="X189" t="n">
-        <v>0.5704</v>
+        <v>0.544</v>
       </c>
       <c r="Y189" t="n">
-        <v>27.694</v>
+        <v>27.752</v>
       </c>
       <c r="Z189" t="n">
-        <v>60.534</v>
+        <v>60.736</v>
       </c>
       <c r="AA189" t="n">
-        <v>8.858000000000001</v>
+        <v>8.904</v>
       </c>
       <c r="AB189" t="n">
-        <v>27.02</v>
+        <v>26.968</v>
       </c>
       <c r="AC189" t="n">
-        <v>15.654</v>
+        <v>15.928</v>
       </c>
       <c r="AD189" t="n">
-        <v>21.578</v>
+        <v>21.936</v>
       </c>
       <c r="AE189" t="n">
-        <v>9.891</v>
+        <v>10.136</v>
       </c>
       <c r="AF189" t="n">
-        <v>21.553</v>
+        <v>21.544</v>
       </c>
       <c r="AG189" t="n">
-        <v>15.356</v>
+        <v>15.36</v>
       </c>
       <c r="AH189" t="n">
-        <v>8.170999999999999</v>
+        <v>8.144</v>
       </c>
       <c r="AI189" t="n">
-        <v>3.562</v>
+        <v>3.584</v>
       </c>
       <c r="AJ189" t="n">
-        <v>18.511</v>
+        <v>18.712</v>
       </c>
       <c r="AK189" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AL189" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="190">
@@ -24386,22 +24386,22 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F200" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G200" t="b">
         <v>1</v>
       </c>
       <c r="H200" t="n">
-        <v>1341.993</v>
+        <v>1339.625</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5805</v>
+        <v>0.6274</v>
       </c>
       <c r="J200" t="n">
-        <v>1453</v>
+        <v>1451.6</v>
       </c>
       <c r="K200" t="n">
         <v>182</v>
@@ -24422,70 +24422,70 @@
         <v>208</v>
       </c>
       <c r="Q200" t="n">
-        <v>106.165</v>
+        <v>106.272</v>
       </c>
       <c r="R200" t="n">
-        <v>110.071</v>
+        <v>111.114</v>
       </c>
       <c r="S200" t="n">
-        <v>-3.906</v>
+        <v>-4.843</v>
       </c>
       <c r="T200" t="n">
-        <v>0.29265</v>
+        <v>0.30559</v>
       </c>
       <c r="U200" t="n">
-        <v>0.19673</v>
+        <v>0.1946</v>
       </c>
       <c r="V200" t="n">
-        <v>74.92</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="W200" t="n">
-        <v>77.62</v>
+        <v>77.64</v>
       </c>
       <c r="X200" t="n">
-        <v>0.4735</v>
+        <v>0.4507</v>
       </c>
       <c r="Y200" t="n">
-        <v>24.876</v>
+        <v>24.611</v>
       </c>
       <c r="Z200" t="n">
-        <v>55.805</v>
+        <v>55.704</v>
       </c>
       <c r="AA200" t="n">
-        <v>6.022</v>
+        <v>5.953</v>
       </c>
       <c r="AB200" t="n">
-        <v>18.689</v>
+        <v>18.798</v>
       </c>
       <c r="AC200" t="n">
-        <v>19.146</v>
+        <v>19.227</v>
       </c>
       <c r="AD200" t="n">
-        <v>25.73</v>
+        <v>25.883</v>
       </c>
       <c r="AE200" t="n">
-        <v>10.35</v>
+        <v>10.638</v>
       </c>
       <c r="AF200" t="n">
-        <v>24.846</v>
+        <v>24.251</v>
       </c>
       <c r="AG200" t="n">
-        <v>13.031</v>
+        <v>12.915</v>
       </c>
       <c r="AH200" t="n">
-        <v>5.69</v>
+        <v>5.815</v>
       </c>
       <c r="AI200" t="n">
-        <v>3.805</v>
+        <v>3.743</v>
       </c>
       <c r="AJ200" t="n">
-        <v>19.712</v>
+        <v>19.576</v>
       </c>
       <c r="AK200" t="n">
-        <v>3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AL200" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="201">
@@ -24626,22 +24626,22 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F202" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G202" t="b">
         <v>1</v>
       </c>
       <c r="H202" t="n">
-        <v>1364.252</v>
+        <v>1361.859</v>
       </c>
       <c r="I202" t="n">
-        <v>-1.4633</v>
+        <v>-1.4014</v>
       </c>
       <c r="J202" t="n">
-        <v>1425.9</v>
+        <v>1426</v>
       </c>
       <c r="K202" t="n">
         <v>232</v>
@@ -24662,70 +24662,70 @@
         <v>246</v>
       </c>
       <c r="Q202" t="n">
-        <v>104.332</v>
+        <v>104.281</v>
       </c>
       <c r="R202" t="n">
-        <v>109.702</v>
+        <v>110.789</v>
       </c>
       <c r="S202" t="n">
-        <v>-5.371</v>
+        <v>-6.508</v>
       </c>
       <c r="T202" t="n">
-        <v>0.32196</v>
+        <v>0.32388</v>
       </c>
       <c r="U202" t="n">
-        <v>0.16798</v>
+        <v>0.16939</v>
       </c>
       <c r="V202" t="n">
-        <v>70.97</v>
+        <v>70.94</v>
       </c>
       <c r="W202" t="n">
-        <v>75.08</v>
+        <v>75.78</v>
       </c>
       <c r="X202" t="n">
-        <v>0.425</v>
+        <v>0.4026</v>
       </c>
       <c r="Y202" t="n">
-        <v>24.808</v>
+        <v>24.774</v>
       </c>
       <c r="Z202" t="n">
-        <v>57.236</v>
+        <v>57.168</v>
       </c>
       <c r="AA202" t="n">
-        <v>8.417999999999999</v>
+        <v>8.314</v>
       </c>
       <c r="AB202" t="n">
-        <v>25.197</v>
+        <v>25.048</v>
       </c>
       <c r="AC202" t="n">
-        <v>12.932</v>
+        <v>13.08</v>
       </c>
       <c r="AD202" t="n">
-        <v>19.711</v>
+        <v>19.694</v>
       </c>
       <c r="AE202" t="n">
-        <v>9.179</v>
+        <v>9.195</v>
       </c>
       <c r="AF202" t="n">
-        <v>19.262</v>
+        <v>19.137</v>
       </c>
       <c r="AG202" t="n">
-        <v>12.987</v>
+        <v>12.889</v>
       </c>
       <c r="AH202" t="n">
-        <v>8.699999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="AI202" t="n">
-        <v>2.796</v>
+        <v>2.743</v>
       </c>
       <c r="AJ202" t="n">
-        <v>18.067</v>
+        <v>17.973</v>
       </c>
       <c r="AK202" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AL202" t="n">
-        <v>-1</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="203">
@@ -27146,22 +27146,22 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F223" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G223" t="b">
         <v>1</v>
       </c>
       <c r="H223" t="n">
-        <v>1551.535</v>
+        <v>1550.024</v>
       </c>
       <c r="I223" t="n">
-        <v>-2.8876</v>
+        <v>-2.6712</v>
       </c>
       <c r="J223" t="n">
-        <v>1538.2</v>
+        <v>1558.8</v>
       </c>
       <c r="K223" t="n">
         <v>179</v>
@@ -27182,70 +27182,70 @@
         <v>171</v>
       </c>
       <c r="Q223" t="n">
-        <v>107.333</v>
+        <v>106.457</v>
       </c>
       <c r="R223" t="n">
-        <v>111.753</v>
+        <v>111.328</v>
       </c>
       <c r="S223" t="n">
-        <v>-4.42</v>
+        <v>-4.871</v>
       </c>
       <c r="T223" t="n">
-        <v>0.24647</v>
+        <v>0.24935</v>
       </c>
       <c r="U223" t="n">
-        <v>0.17043</v>
+        <v>0.17074</v>
       </c>
       <c r="V223" t="n">
-        <v>71.66</v>
+        <v>70.97</v>
       </c>
       <c r="W223" t="n">
-        <v>74.47</v>
+        <v>74.06</v>
       </c>
       <c r="X223" t="n">
-        <v>0.5363</v>
+        <v>0.51</v>
       </c>
       <c r="Y223" t="n">
-        <v>22.785</v>
+        <v>22.6</v>
       </c>
       <c r="Z223" t="n">
-        <v>52.929</v>
+        <v>53.03</v>
       </c>
       <c r="AA223" t="n">
-        <v>8.31</v>
+        <v>8.19</v>
       </c>
       <c r="AB223" t="n">
-        <v>23.413</v>
+        <v>23.47</v>
       </c>
       <c r="AC223" t="n">
-        <v>17.782</v>
+        <v>17.58</v>
       </c>
       <c r="AD223" t="n">
-        <v>23.028</v>
+        <v>22.77</v>
       </c>
       <c r="AE223" t="n">
-        <v>7.558</v>
+        <v>7.67</v>
       </c>
       <c r="AF223" t="n">
-        <v>22.907</v>
+        <v>22.87</v>
       </c>
       <c r="AG223" t="n">
-        <v>14.012</v>
+        <v>13.81</v>
       </c>
       <c r="AH223" t="n">
-        <v>5.566</v>
+        <v>5.49</v>
       </c>
       <c r="AI223" t="n">
-        <v>3.681</v>
+        <v>3.67</v>
       </c>
       <c r="AJ223" t="n">
-        <v>17.835</v>
+        <v>17.73</v>
       </c>
       <c r="AK223" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="AL223" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -29426,22 +29426,22 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F242" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G242" t="b">
         <v>1</v>
       </c>
       <c r="H242" t="n">
-        <v>1538.807</v>
+        <v>1532.735</v>
       </c>
       <c r="I242" t="n">
-        <v>-1.3441</v>
+        <v>-1.224</v>
       </c>
       <c r="J242" t="n">
-        <v>1429.2</v>
+        <v>1424.9</v>
       </c>
       <c r="K242" t="n">
         <v>139</v>
@@ -29462,70 +29462,70 @@
         <v>135</v>
       </c>
       <c r="Q242" t="n">
-        <v>115.297</v>
+        <v>114.922</v>
       </c>
       <c r="R242" t="n">
-        <v>108.919</v>
+        <v>109.407</v>
       </c>
       <c r="S242" t="n">
-        <v>6.378</v>
+        <v>5.514</v>
       </c>
       <c r="T242" t="n">
-        <v>0.33378</v>
+        <v>0.33745</v>
       </c>
       <c r="U242" t="n">
-        <v>0.17483</v>
+        <v>0.1723</v>
       </c>
       <c r="V242" t="n">
-        <v>77.14</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="W242" t="n">
-        <v>73.28</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="X242" t="n">
-        <v>0.6702</v>
+        <v>0.6389</v>
       </c>
       <c r="Y242" t="n">
-        <v>28.1</v>
+        <v>27.961</v>
       </c>
       <c r="Z242" t="n">
-        <v>59.52</v>
+        <v>59.492</v>
       </c>
       <c r="AA242" t="n">
-        <v>9.34</v>
+        <v>9.153</v>
       </c>
       <c r="AB242" t="n">
-        <v>24.232</v>
+        <v>23.881</v>
       </c>
       <c r="AC242" t="n">
-        <v>11.595</v>
+        <v>11.857</v>
       </c>
       <c r="AD242" t="n">
-        <v>16.628</v>
+        <v>16.889</v>
       </c>
       <c r="AE242" t="n">
-        <v>11.505</v>
+        <v>11.604</v>
       </c>
       <c r="AF242" t="n">
-        <v>23.426</v>
+        <v>23.226</v>
       </c>
       <c r="AG242" t="n">
-        <v>17.661</v>
+        <v>17.379</v>
       </c>
       <c r="AH242" t="n">
-        <v>5.549</v>
+        <v>5.678</v>
       </c>
       <c r="AI242" t="n">
-        <v>2.483</v>
+        <v>2.447</v>
       </c>
       <c r="AJ242" t="n">
-        <v>18.234</v>
+        <v>18.204</v>
       </c>
       <c r="AK242" t="n">
-        <v>16.4</v>
+        <v>10.4</v>
       </c>
       <c r="AL242" t="n">
-        <v>11.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="243">
@@ -30986,22 +30986,22 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F255" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G255" t="b">
         <v>1</v>
       </c>
       <c r="H255" t="n">
-        <v>1768.33</v>
+        <v>1787.889</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4727</v>
+        <v>-0.2548</v>
       </c>
       <c r="J255" t="n">
-        <v>1566.6</v>
+        <v>1580.2</v>
       </c>
       <c r="K255" t="n">
         <v>37</v>
@@ -31022,70 +31022,70 @@
         <v>42</v>
       </c>
       <c r="Q255" t="n">
-        <v>117.67</v>
+        <v>117.903</v>
       </c>
       <c r="R255" t="n">
-        <v>102.695</v>
+        <v>103.181</v>
       </c>
       <c r="S255" t="n">
-        <v>14.975</v>
+        <v>14.722</v>
       </c>
       <c r="T255" t="n">
-        <v>0.34723</v>
+        <v>0.34454</v>
       </c>
       <c r="U255" t="n">
-        <v>0.14938</v>
+        <v>0.15002</v>
       </c>
       <c r="V255" t="n">
-        <v>83.47</v>
+        <v>83.25</v>
       </c>
       <c r="W255" t="n">
-        <v>72.86</v>
+        <v>72.83</v>
       </c>
       <c r="X255" t="n">
-        <v>0.7764</v>
+        <v>0.7832</v>
       </c>
       <c r="Y255" t="n">
-        <v>30.322</v>
+        <v>30.101</v>
       </c>
       <c r="Z255" t="n">
-        <v>64.524</v>
+        <v>64.126</v>
       </c>
       <c r="AA255" t="n">
-        <v>10.176</v>
+        <v>9.964</v>
       </c>
       <c r="AB255" t="n">
-        <v>29.068</v>
+        <v>28.64</v>
       </c>
       <c r="AC255" t="n">
-        <v>12.654</v>
+        <v>12.881</v>
       </c>
       <c r="AD255" t="n">
-        <v>16.932</v>
+        <v>17.08</v>
       </c>
       <c r="AE255" t="n">
-        <v>11.656</v>
+        <v>11.628</v>
       </c>
       <c r="AF255" t="n">
-        <v>21.319</v>
+        <v>21.59</v>
       </c>
       <c r="AG255" t="n">
-        <v>16.943</v>
+        <v>16.747</v>
       </c>
       <c r="AH255" t="n">
-        <v>8.919</v>
+        <v>8.648999999999999</v>
       </c>
       <c r="AI255" t="n">
-        <v>3.703</v>
+        <v>3.721</v>
       </c>
       <c r="AJ255" t="n">
-        <v>19.539</v>
+        <v>19.468</v>
       </c>
       <c r="AK255" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AL255" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="256">
@@ -33506,22 +33506,22 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F276" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G276" t="b">
         <v>1</v>
       </c>
       <c r="H276" t="n">
-        <v>1877.369</v>
+        <v>1857.81</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5286</v>
+        <v>-0.2818</v>
       </c>
       <c r="J276" t="n">
-        <v>1595.3</v>
+        <v>1596.9</v>
       </c>
       <c r="K276" t="n">
         <v>22</v>
@@ -33542,70 +33542,70 @@
         <v>20</v>
       </c>
       <c r="Q276" t="n">
-        <v>118.867</v>
+        <v>118.734</v>
       </c>
       <c r="R276" t="n">
-        <v>98.821</v>
+        <v>99.88200000000001</v>
       </c>
       <c r="S276" t="n">
-        <v>20.046</v>
+        <v>18.852</v>
       </c>
       <c r="T276" t="n">
-        <v>0.29664</v>
+        <v>0.2975</v>
       </c>
       <c r="U276" t="n">
-        <v>0.15573</v>
+        <v>0.15247</v>
       </c>
       <c r="V276" t="n">
-        <v>77.73999999999999</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="W276" t="n">
-        <v>64.86</v>
+        <v>65.41</v>
       </c>
       <c r="X276" t="n">
-        <v>0.8683</v>
+        <v>0.829</v>
       </c>
       <c r="Y276" t="n">
-        <v>26.489</v>
+        <v>26.684</v>
       </c>
       <c r="Z276" t="n">
-        <v>57.738</v>
+        <v>57.823</v>
       </c>
       <c r="AA276" t="n">
-        <v>8.166</v>
+        <v>8.194000000000001</v>
       </c>
       <c r="AB276" t="n">
-        <v>20.92</v>
+        <v>20.951</v>
       </c>
       <c r="AC276" t="n">
-        <v>16.591</v>
+        <v>16.191</v>
       </c>
       <c r="AD276" t="n">
-        <v>20.545</v>
+        <v>20.377</v>
       </c>
       <c r="AE276" t="n">
-        <v>11.478</v>
+        <v>11.371</v>
       </c>
       <c r="AF276" t="n">
-        <v>26.44</v>
+        <v>26.154</v>
       </c>
       <c r="AG276" t="n">
-        <v>15.428</v>
+        <v>15.241</v>
       </c>
       <c r="AH276" t="n">
-        <v>5.625</v>
+        <v>5.562</v>
       </c>
       <c r="AI276" t="n">
-        <v>3.572</v>
+        <v>3.586</v>
       </c>
       <c r="AJ276" t="n">
-        <v>15.502</v>
+        <v>15.771</v>
       </c>
       <c r="AK276" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="AL276" t="n">
-        <v>13.7</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="277">
@@ -34226,22 +34226,22 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F282" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G282" t="b">
         <v>1</v>
       </c>
       <c r="H282" t="n">
-        <v>1376.177</v>
+        <v>1378.544</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.451</v>
+        <v>-0.4106</v>
       </c>
       <c r="J282" t="n">
-        <v>1426.5</v>
+        <v>1424</v>
       </c>
       <c r="K282" t="n">
         <v>180</v>
@@ -34262,70 +34262,70 @@
         <v>196</v>
       </c>
       <c r="Q282" t="n">
-        <v>102.165</v>
+        <v>103.004</v>
       </c>
       <c r="R282" t="n">
-        <v>103.54</v>
+        <v>103.532</v>
       </c>
       <c r="S282" t="n">
-        <v>-1.375</v>
+        <v>-0.528</v>
       </c>
       <c r="T282" t="n">
-        <v>0.29116</v>
+        <v>0.29593</v>
       </c>
       <c r="U282" t="n">
-        <v>0.18053</v>
+        <v>0.18515</v>
       </c>
       <c r="V282" t="n">
-        <v>68.84</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="W282" t="n">
-        <v>70.05</v>
+        <v>69.64</v>
       </c>
       <c r="X282" t="n">
-        <v>0.486</v>
+        <v>0.504</v>
       </c>
       <c r="Y282" t="n">
-        <v>23.759</v>
+        <v>23.89</v>
       </c>
       <c r="Z282" t="n">
-        <v>54.512</v>
+        <v>54.417</v>
       </c>
       <c r="AA282" t="n">
-        <v>5.76</v>
+        <v>5.926</v>
       </c>
       <c r="AB282" t="n">
-        <v>17.007</v>
+        <v>17.052</v>
       </c>
       <c r="AC282" t="n">
-        <v>15.559</v>
+        <v>15.227</v>
       </c>
       <c r="AD282" t="n">
-        <v>23.01</v>
+        <v>22.601</v>
       </c>
       <c r="AE282" t="n">
-        <v>9.182</v>
+        <v>9.49</v>
       </c>
       <c r="AF282" t="n">
-        <v>21.678</v>
+        <v>21.768</v>
       </c>
       <c r="AG282" t="n">
-        <v>11.871</v>
+        <v>12.032</v>
       </c>
       <c r="AH282" t="n">
-        <v>7.21</v>
+        <v>7.09</v>
       </c>
       <c r="AI282" t="n">
-        <v>2.642</v>
+        <v>2.646</v>
       </c>
       <c r="AJ282" t="n">
-        <v>20.708</v>
+        <v>20.882</v>
       </c>
       <c r="AK282" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="AL282" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="283">
@@ -35666,22 +35666,22 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F294" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G294" t="b">
         <v>1</v>
       </c>
       <c r="H294" t="n">
-        <v>1556.938</v>
+        <v>1549.369</v>
       </c>
       <c r="I294" t="n">
-        <v>-2.7806</v>
+        <v>-2.6439</v>
       </c>
       <c r="J294" t="n">
-        <v>1524.4</v>
+        <v>1525.9</v>
       </c>
       <c r="K294" t="n">
         <v>157</v>
@@ -35702,70 +35702,70 @@
         <v>160</v>
       </c>
       <c r="Q294" t="n">
-        <v>104.063</v>
+        <v>103.887</v>
       </c>
       <c r="R294" t="n">
-        <v>102.391</v>
+        <v>102.852</v>
       </c>
       <c r="S294" t="n">
-        <v>1.672</v>
+        <v>1.034</v>
       </c>
       <c r="T294" t="n">
-        <v>0.33571</v>
+        <v>0.33827</v>
       </c>
       <c r="U294" t="n">
-        <v>0.15173</v>
+        <v>0.14979</v>
       </c>
       <c r="V294" t="n">
-        <v>67.26000000000001</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="W294" t="n">
-        <v>66.29000000000001</v>
+        <v>66.45</v>
       </c>
       <c r="X294" t="n">
-        <v>0.5528</v>
+        <v>0.5265</v>
       </c>
       <c r="Y294" t="n">
-        <v>24.044</v>
+        <v>24.022</v>
       </c>
       <c r="Z294" t="n">
-        <v>58.428</v>
+        <v>58.594</v>
       </c>
       <c r="AA294" t="n">
-        <v>5.811</v>
+        <v>5.805</v>
       </c>
       <c r="AB294" t="n">
-        <v>20.69</v>
+        <v>20.49</v>
       </c>
       <c r="AC294" t="n">
-        <v>12.322</v>
+        <v>12.421</v>
       </c>
       <c r="AD294" t="n">
-        <v>18.182</v>
+        <v>18.186</v>
       </c>
       <c r="AE294" t="n">
-        <v>11.543</v>
+        <v>11.686</v>
       </c>
       <c r="AF294" t="n">
-        <v>23.028</v>
+        <v>23.013</v>
       </c>
       <c r="AG294" t="n">
-        <v>9.592000000000001</v>
+        <v>9.406000000000001</v>
       </c>
       <c r="AH294" t="n">
-        <v>5.801</v>
+        <v>5.725</v>
       </c>
       <c r="AI294" t="n">
-        <v>3.403</v>
+        <v>3.412</v>
       </c>
       <c r="AJ294" t="n">
-        <v>15.949</v>
+        <v>15.889</v>
       </c>
       <c r="AK294" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AL294" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="295">
@@ -35786,22 +35786,22 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F295" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G295" t="b">
         <v>1</v>
       </c>
       <c r="H295" t="n">
-        <v>1596.975</v>
+        <v>1600.961</v>
       </c>
       <c r="I295" t="n">
-        <v>1.2134</v>
+        <v>1.1284</v>
       </c>
       <c r="J295" t="n">
-        <v>1466.1</v>
+        <v>1466</v>
       </c>
       <c r="K295" t="n">
         <v>153</v>
@@ -35822,70 +35822,70 @@
         <v>132</v>
       </c>
       <c r="Q295" t="n">
-        <v>111.849</v>
+        <v>112.278</v>
       </c>
       <c r="R295" t="n">
-        <v>106.582</v>
+        <v>106.193</v>
       </c>
       <c r="S295" t="n">
-        <v>5.267</v>
+        <v>6.085</v>
       </c>
       <c r="T295" t="n">
-        <v>0.31634</v>
+        <v>0.316</v>
       </c>
       <c r="U295" t="n">
-        <v>0.16365</v>
+        <v>0.16673</v>
       </c>
       <c r="V295" t="n">
-        <v>78.33</v>
+        <v>78.27</v>
       </c>
       <c r="W295" t="n">
-        <v>74.86</v>
+        <v>74.3</v>
       </c>
       <c r="X295" t="n">
-        <v>0.6388</v>
+        <v>0.65</v>
       </c>
       <c r="Y295" t="n">
-        <v>26.401</v>
+        <v>26.627</v>
       </c>
       <c r="Z295" t="n">
-        <v>60.115</v>
+        <v>59.845</v>
       </c>
       <c r="AA295" t="n">
-        <v>9.108000000000001</v>
+        <v>9.009</v>
       </c>
       <c r="AB295" t="n">
-        <v>27.509</v>
+        <v>27.182</v>
       </c>
       <c r="AC295" t="n">
-        <v>16.419</v>
+        <v>16.009</v>
       </c>
       <c r="AD295" t="n">
-        <v>22.171</v>
+        <v>21.709</v>
       </c>
       <c r="AE295" t="n">
-        <v>11.194</v>
+        <v>11.159</v>
       </c>
       <c r="AF295" t="n">
-        <v>24.062</v>
+        <v>24.032</v>
       </c>
       <c r="AG295" t="n">
-        <v>15.054</v>
+        <v>15.186</v>
       </c>
       <c r="AH295" t="n">
-        <v>7.278</v>
+        <v>7.255</v>
       </c>
       <c r="AI295" t="n">
-        <v>3.567</v>
+        <v>3.341</v>
       </c>
       <c r="AJ295" t="n">
-        <v>16.865</v>
+        <v>16.75</v>
       </c>
       <c r="AK295" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AL295" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="296">
@@ -36146,22 +36146,22 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F298" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G298" t="b">
         <v>1</v>
       </c>
       <c r="H298" t="n">
-        <v>1394.986</v>
+        <v>1397.379</v>
       </c>
       <c r="I298" t="n">
-        <v>1.606</v>
+        <v>1.648</v>
       </c>
       <c r="J298" t="n">
-        <v>1426.5</v>
+        <v>1425</v>
       </c>
       <c r="K298" t="n">
         <v>124</v>
@@ -36182,70 +36182,70 @@
         <v>134</v>
       </c>
       <c r="Q298" t="n">
-        <v>109.771</v>
+        <v>110.546</v>
       </c>
       <c r="R298" t="n">
-        <v>105.084</v>
+        <v>105.058</v>
       </c>
       <c r="S298" t="n">
-        <v>4.687</v>
+        <v>5.488</v>
       </c>
       <c r="T298" t="n">
-        <v>0.24194</v>
+        <v>0.23978</v>
       </c>
       <c r="U298" t="n">
-        <v>0.17004</v>
+        <v>0.17131</v>
       </c>
       <c r="V298" t="n">
-        <v>73.11</v>
+        <v>73.62</v>
       </c>
       <c r="W298" t="n">
-        <v>70.18000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="X298" t="n">
-        <v>0.5551</v>
+        <v>0.5697</v>
       </c>
       <c r="Y298" t="n">
-        <v>26.057</v>
+        <v>26.233</v>
       </c>
       <c r="Z298" t="n">
-        <v>56.057</v>
+        <v>55.913</v>
       </c>
       <c r="AA298" t="n">
-        <v>8.863</v>
+        <v>8.988</v>
       </c>
       <c r="AB298" t="n">
-        <v>24.301</v>
+        <v>24.298</v>
       </c>
       <c r="AC298" t="n">
-        <v>12.134</v>
+        <v>12.166</v>
       </c>
       <c r="AD298" t="n">
-        <v>16.058</v>
+        <v>15.939</v>
       </c>
       <c r="AE298" t="n">
-        <v>7.89</v>
+        <v>7.781</v>
       </c>
       <c r="AF298" t="n">
-        <v>23.418</v>
+        <v>23.357</v>
       </c>
       <c r="AG298" t="n">
-        <v>15.624</v>
+        <v>15.796</v>
       </c>
       <c r="AH298" t="n">
-        <v>5.871</v>
+        <v>5.868</v>
       </c>
       <c r="AI298" t="n">
-        <v>2.787</v>
+        <v>2.801</v>
       </c>
       <c r="AJ298" t="n">
-        <v>18.315</v>
+        <v>18.218</v>
       </c>
       <c r="AK298" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="AL298" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="299">
@@ -40706,22 +40706,22 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F336" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G336" t="b">
         <v>1</v>
       </c>
       <c r="H336" t="n">
-        <v>1362.868</v>
+        <v>1359.891</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.0298</v>
+        <v>-0.0016</v>
       </c>
       <c r="J336" t="n">
-        <v>1423.8</v>
+        <v>1419</v>
       </c>
       <c r="K336" t="n">
         <v>193</v>
@@ -40742,70 +40742,70 @@
         <v>197</v>
       </c>
       <c r="Q336" t="n">
-        <v>111.294</v>
+        <v>111.687</v>
       </c>
       <c r="R336" t="n">
-        <v>111.437</v>
+        <v>111.82</v>
       </c>
       <c r="S336" t="n">
-        <v>-0.143</v>
+        <v>-0.132</v>
       </c>
       <c r="T336" t="n">
-        <v>0.3076</v>
+        <v>0.30496</v>
       </c>
       <c r="U336" t="n">
-        <v>0.15521</v>
+        <v>0.15381</v>
       </c>
       <c r="V336" t="n">
-        <v>78.65000000000001</v>
+        <v>78.83</v>
       </c>
       <c r="W336" t="n">
-        <v>78.94</v>
+        <v>79.11</v>
       </c>
       <c r="X336" t="n">
-        <v>0.4783</v>
+        <v>0.4626</v>
       </c>
       <c r="Y336" t="n">
-        <v>27.484</v>
+        <v>27.496</v>
       </c>
       <c r="Z336" t="n">
-        <v>59.916</v>
+        <v>59.734</v>
       </c>
       <c r="AA336" t="n">
-        <v>6.811</v>
+        <v>6.751</v>
       </c>
       <c r="AB336" t="n">
-        <v>19.634</v>
+        <v>19.595</v>
       </c>
       <c r="AC336" t="n">
-        <v>16.873</v>
+        <v>17.092</v>
       </c>
       <c r="AD336" t="n">
-        <v>23.264</v>
+        <v>23.405</v>
       </c>
       <c r="AE336" t="n">
-        <v>10.248</v>
+        <v>10.106</v>
       </c>
       <c r="AF336" t="n">
-        <v>23.332</v>
+        <v>23.247</v>
       </c>
       <c r="AG336" t="n">
-        <v>12.783</v>
+        <v>12.585</v>
       </c>
       <c r="AH336" t="n">
-        <v>6.947</v>
+        <v>6.925</v>
       </c>
       <c r="AI336" t="n">
-        <v>1.503</v>
+        <v>1.537</v>
       </c>
       <c r="AJ336" t="n">
-        <v>18.339</v>
+        <v>18.697</v>
       </c>
       <c r="AK336" t="n">
-        <v>-1.8</v>
+        <v>0.8</v>
       </c>
       <c r="AL336" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="337">
@@ -41786,22 +41786,22 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F345" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G345" t="b">
         <v>1</v>
       </c>
       <c r="H345" t="n">
-        <v>1464.47</v>
+        <v>1468.688</v>
       </c>
       <c r="I345" t="n">
-        <v>2.7711</v>
+        <v>2.7502</v>
       </c>
       <c r="J345" t="n">
-        <v>1435.1</v>
+        <v>1435.9</v>
       </c>
       <c r="K345" t="n">
         <v>144</v>
@@ -41822,70 +41822,70 @@
         <v>133</v>
       </c>
       <c r="Q345" t="n">
-        <v>115.653</v>
+        <v>116.218</v>
       </c>
       <c r="R345" t="n">
-        <v>109.069</v>
+        <v>109.523</v>
       </c>
       <c r="S345" t="n">
-        <v>6.584</v>
+        <v>6.695</v>
       </c>
       <c r="T345" t="n">
-        <v>0.29919</v>
+        <v>0.29519</v>
       </c>
       <c r="U345" t="n">
-        <v>0.15797</v>
+        <v>0.15692</v>
       </c>
       <c r="V345" t="n">
-        <v>79.76000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="W345" t="n">
-        <v>75.20999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="X345" t="n">
-        <v>0.6365</v>
+        <v>0.648</v>
       </c>
       <c r="Y345" t="n">
-        <v>28.241</v>
+        <v>28.392</v>
       </c>
       <c r="Z345" t="n">
-        <v>58.315</v>
+        <v>58.328</v>
       </c>
       <c r="AA345" t="n">
-        <v>7.106</v>
+        <v>7.208</v>
       </c>
       <c r="AB345" t="n">
-        <v>19.626</v>
+        <v>19.72</v>
       </c>
       <c r="AC345" t="n">
-        <v>16.167</v>
+        <v>16.608</v>
       </c>
       <c r="AD345" t="n">
-        <v>21.695</v>
+        <v>22.12</v>
       </c>
       <c r="AE345" t="n">
-        <v>9.753</v>
+        <v>9.584</v>
       </c>
       <c r="AF345" t="n">
-        <v>22.384</v>
+        <v>22.408</v>
       </c>
       <c r="AG345" t="n">
-        <v>13.224</v>
+        <v>13.352</v>
       </c>
       <c r="AH345" t="n">
-        <v>7.073</v>
+        <v>7.216</v>
       </c>
       <c r="AI345" t="n">
-        <v>4.322</v>
+        <v>4.32</v>
       </c>
       <c r="AJ345" t="n">
-        <v>17.289</v>
+        <v>17.528</v>
       </c>
       <c r="AK345" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AL345" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="346">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -1466,22 +1466,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1270.134</v>
+        <v>1267.388</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4276</v>
+        <v>-1.3772</v>
       </c>
       <c r="J9" t="n">
-        <v>1410.3</v>
+        <v>1405.1</v>
       </c>
       <c r="K9" t="n">
         <v>351</v>
@@ -1502,70 +1502,70 @@
         <v>352</v>
       </c>
       <c r="Q9" t="n">
-        <v>97.167</v>
+        <v>96.518</v>
       </c>
       <c r="R9" t="n">
-        <v>114.964</v>
+        <v>114.621</v>
       </c>
       <c r="S9" t="n">
-        <v>-17.798</v>
+        <v>-18.103</v>
       </c>
       <c r="T9" t="n">
-        <v>0.30634</v>
+        <v>0.30128</v>
       </c>
       <c r="U9" t="n">
-        <v>0.18556</v>
+        <v>0.18564</v>
       </c>
       <c r="V9" t="n">
-        <v>67.39</v>
+        <v>66.77</v>
       </c>
       <c r="W9" t="n">
-        <v>80.45999999999999</v>
+        <v>80</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3</v>
+        <v>0.2777</v>
       </c>
       <c r="Y9" t="n">
-        <v>24.05</v>
+        <v>23.714</v>
       </c>
       <c r="Z9" t="n">
-        <v>57.477</v>
+        <v>56.935</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.509</v>
+        <v>6.407</v>
       </c>
       <c r="AB9" t="n">
-        <v>19.791</v>
+        <v>19.431</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.236</v>
+        <v>12.564</v>
       </c>
       <c r="AD9" t="n">
-        <v>17.391</v>
+        <v>17.905</v>
       </c>
       <c r="AE9" t="n">
-        <v>8.558999999999999</v>
+        <v>8.419</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.464</v>
+        <v>19.718</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.295</v>
+        <v>11.029</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.686</v>
+        <v>7.592</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.377</v>
+        <v>3.383</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17.773</v>
+        <v>17.884</v>
       </c>
       <c r="AK9" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10</v>
       </c>
       <c r="AL9" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="10">
@@ -1946,22 +1946,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1678.649</v>
+        <v>1690.003</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4683</v>
+        <v>-1.2702</v>
       </c>
       <c r="J13" t="n">
-        <v>1735.5</v>
+        <v>1729.9</v>
       </c>
       <c r="K13" t="n">
         <v>63</v>
@@ -1982,70 +1982,70 @@
         <v>67</v>
       </c>
       <c r="Q13" t="n">
-        <v>108.23</v>
+        <v>108.881</v>
       </c>
       <c r="R13" t="n">
-        <v>109.086</v>
+        <v>109.142</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.855</v>
+        <v>-0.261</v>
       </c>
       <c r="T13" t="n">
-        <v>0.27782</v>
+        <v>0.27918</v>
       </c>
       <c r="U13" t="n">
-        <v>0.16024</v>
+        <v>0.16072</v>
       </c>
       <c r="V13" t="n">
-        <v>77.08</v>
+        <v>77.47</v>
       </c>
       <c r="W13" t="n">
-        <v>78</v>
+        <v>77.95</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5101</v>
+        <v>0.5363</v>
       </c>
       <c r="Y13" t="n">
-        <v>25.962</v>
+        <v>26.239</v>
       </c>
       <c r="Z13" t="n">
-        <v>58.145</v>
+        <v>58.142</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.606</v>
+        <v>7.629</v>
       </c>
       <c r="AB13" t="n">
-        <v>22.33</v>
+        <v>22.309</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.554</v>
+        <v>17.359</v>
       </c>
       <c r="AD13" t="n">
-        <v>23.212</v>
+        <v>23.175</v>
       </c>
       <c r="AE13" t="n">
-        <v>8.496</v>
+        <v>8.567</v>
       </c>
       <c r="AF13" t="n">
-        <v>21.971</v>
+        <v>22.022</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.02</v>
+        <v>13.906</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.977</v>
+        <v>7.083</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.67</v>
+        <v>4.566</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17.258</v>
+        <v>17.091</v>
       </c>
       <c r="AK13" t="n">
-        <v>-3</v>
+        <v>-1.2</v>
       </c>
       <c r="AL13" t="n">
-        <v>-1.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14">
@@ -3026,19 +3026,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1678.507</v>
+        <v>1667.154</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.2439</v>
+        <v>-5.9263</v>
       </c>
       <c r="J22" t="n">
         <v>1727.4</v>
@@ -3062,70 +3062,70 @@
         <v>48</v>
       </c>
       <c r="Q22" t="n">
-        <v>116.965</v>
+        <v>116.311</v>
       </c>
       <c r="R22" t="n">
-        <v>111.542</v>
+        <v>111.717</v>
       </c>
       <c r="S22" t="n">
-        <v>5.424</v>
+        <v>4.594</v>
       </c>
       <c r="T22" t="n">
-        <v>0.33009</v>
+        <v>0.33352</v>
       </c>
       <c r="U22" t="n">
-        <v>0.16041</v>
+        <v>0.16197</v>
       </c>
       <c r="V22" t="n">
-        <v>81.51000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="W22" t="n">
-        <v>77.47</v>
+        <v>77.73</v>
       </c>
       <c r="X22" t="n">
-        <v>0.5052</v>
+        <v>0.4792</v>
       </c>
       <c r="Y22" t="n">
-        <v>28.984</v>
+        <v>28.831</v>
       </c>
       <c r="Z22" t="n">
-        <v>60.481</v>
+        <v>60.707</v>
       </c>
       <c r="AA22" t="n">
-        <v>8.528</v>
+        <v>8.510999999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>23.64</v>
+        <v>24.088</v>
       </c>
       <c r="AC22" t="n">
-        <v>15.375</v>
+        <v>15.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>20.97</v>
+        <v>20.865</v>
       </c>
       <c r="AE22" t="n">
-        <v>11.307</v>
+        <v>11.496</v>
       </c>
       <c r="AF22" t="n">
-        <v>22.51</v>
+        <v>22.492</v>
       </c>
       <c r="AG22" t="n">
-        <v>15.7</v>
+        <v>15.482</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.339</v>
+        <v>6.413</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.859</v>
+        <v>3.821</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16.256</v>
+        <v>16.486</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.4</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4706,22 +4706,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1924.512</v>
+        <v>1927.75</v>
       </c>
       <c r="I36" t="n">
-        <v>1.6354</v>
+        <v>1.2144</v>
       </c>
       <c r="J36" t="n">
-        <v>1726.9</v>
+        <v>1718</v>
       </c>
       <c r="K36" t="n">
         <v>25</v>
@@ -4742,70 +4742,70 @@
         <v>24</v>
       </c>
       <c r="Q36" t="n">
-        <v>118.392</v>
+        <v>118.903</v>
       </c>
       <c r="R36" t="n">
-        <v>106.817</v>
+        <v>107.055</v>
       </c>
       <c r="S36" t="n">
-        <v>11.575</v>
+        <v>11.848</v>
       </c>
       <c r="T36" t="n">
-        <v>0.30337</v>
+        <v>0.3035</v>
       </c>
       <c r="U36" t="n">
-        <v>0.14189</v>
+        <v>0.14274</v>
       </c>
       <c r="V36" t="n">
-        <v>84.3</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="W36" t="n">
-        <v>75.78</v>
+        <v>76.38</v>
       </c>
       <c r="X36" t="n">
-        <v>0.6806</v>
+        <v>0.6903</v>
       </c>
       <c r="Y36" t="n">
-        <v>29.722</v>
+        <v>30.121</v>
       </c>
       <c r="Z36" t="n">
-        <v>62.397</v>
+        <v>62.75</v>
       </c>
       <c r="AA36" t="n">
-        <v>8.651</v>
+        <v>8.77</v>
       </c>
       <c r="AB36" t="n">
-        <v>25.042</v>
+        <v>25.311</v>
       </c>
       <c r="AC36" t="n">
-        <v>16.204</v>
+        <v>16.137</v>
       </c>
       <c r="AD36" t="n">
-        <v>21.779</v>
+        <v>21.654</v>
       </c>
       <c r="AE36" t="n">
-        <v>10.992</v>
+        <v>11.027</v>
       </c>
       <c r="AF36" t="n">
-        <v>25.121</v>
+        <v>25.195</v>
       </c>
       <c r="AG36" t="n">
-        <v>13.696</v>
+        <v>13.832</v>
       </c>
       <c r="AH36" t="n">
-        <v>7.079</v>
+        <v>7.204</v>
       </c>
       <c r="AI36" t="n">
-        <v>4.418</v>
+        <v>4.474</v>
       </c>
       <c r="AJ36" t="n">
-        <v>15.661</v>
+        <v>15.65</v>
       </c>
       <c r="AK36" t="n">
-        <v>-5.4</v>
+        <v>-4.6</v>
       </c>
       <c r="AL36" t="n">
-        <v>-4.3</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="37">
@@ -6146,22 +6146,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1724.309</v>
+        <v>1728.908</v>
       </c>
       <c r="I48" t="n">
-        <v>0.956</v>
+        <v>1.3367</v>
       </c>
       <c r="J48" t="n">
-        <v>1716.2</v>
+        <v>1706.8</v>
       </c>
       <c r="K48" t="n">
         <v>42</v>
@@ -6182,70 +6182,70 @@
         <v>46</v>
       </c>
       <c r="Q48" t="n">
-        <v>105.275</v>
+        <v>105.7</v>
       </c>
       <c r="R48" t="n">
-        <v>98.18300000000001</v>
+        <v>98.188</v>
       </c>
       <c r="S48" t="n">
-        <v>7.091</v>
+        <v>7.511</v>
       </c>
       <c r="T48" t="n">
-        <v>0.29016</v>
+        <v>0.28945</v>
       </c>
       <c r="U48" t="n">
-        <v>0.16532</v>
+        <v>0.16144</v>
       </c>
       <c r="V48" t="n">
-        <v>73.27</v>
+        <v>73.37</v>
       </c>
       <c r="W48" t="n">
-        <v>67.73999999999999</v>
+        <v>67.61</v>
       </c>
       <c r="X48" t="n">
-        <v>0.542</v>
+        <v>0.5672</v>
       </c>
       <c r="Y48" t="n">
-        <v>26.157</v>
+        <v>26.227</v>
       </c>
       <c r="Z48" t="n">
-        <v>60.354</v>
+        <v>60.433</v>
       </c>
       <c r="AA48" t="n">
-        <v>8.951000000000001</v>
+        <v>8.907</v>
       </c>
       <c r="AB48" t="n">
-        <v>26.6</v>
+        <v>26.401</v>
       </c>
       <c r="AC48" t="n">
-        <v>12.003</v>
+        <v>12.009</v>
       </c>
       <c r="AD48" t="n">
-        <v>17.638</v>
+        <v>17.784</v>
       </c>
       <c r="AE48" t="n">
-        <v>10.075</v>
+        <v>10.103</v>
       </c>
       <c r="AF48" t="n">
-        <v>24.788</v>
+        <v>24.95</v>
       </c>
       <c r="AG48" t="n">
-        <v>16.768</v>
+        <v>16.669</v>
       </c>
       <c r="AH48" t="n">
-        <v>6.412</v>
+        <v>6.266</v>
       </c>
       <c r="AI48" t="n">
-        <v>4.075</v>
+        <v>4.228</v>
       </c>
       <c r="AJ48" t="n">
-        <v>15.959</v>
+        <v>15.855</v>
       </c>
       <c r="AK48" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="AL48" t="n">
-        <v>6.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="49">
@@ -6986,22 +6986,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G55" t="b">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1613.106</v>
+        <v>1605.175</v>
       </c>
       <c r="I55" t="n">
-        <v>-4.3802</v>
+        <v>-4.1723</v>
       </c>
       <c r="J55" t="n">
-        <v>1695.4</v>
+        <v>1689.7</v>
       </c>
       <c r="K55" t="n">
         <v>64</v>
@@ -7022,70 +7022,70 @@
         <v>71</v>
       </c>
       <c r="Q55" t="n">
-        <v>113.992</v>
+        <v>114.138</v>
       </c>
       <c r="R55" t="n">
-        <v>113.317</v>
+        <v>113.853</v>
       </c>
       <c r="S55" t="n">
-        <v>0.675</v>
+        <v>0.285</v>
       </c>
       <c r="T55" t="n">
-        <v>0.28291</v>
+        <v>0.28499</v>
       </c>
       <c r="U55" t="n">
-        <v>0.14112</v>
+        <v>0.13951</v>
       </c>
       <c r="V55" t="n">
-        <v>79.86</v>
+        <v>80</v>
       </c>
       <c r="W55" t="n">
-        <v>79.15000000000001</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="X55" t="n">
-        <v>0.542</v>
+        <v>0.5255</v>
       </c>
       <c r="Y55" t="n">
-        <v>28.009</v>
+        <v>28.073</v>
       </c>
       <c r="Z55" t="n">
-        <v>59.728</v>
+        <v>59.858</v>
       </c>
       <c r="AA55" t="n">
-        <v>7.351</v>
+        <v>7.257</v>
       </c>
       <c r="AB55" t="n">
-        <v>20.82</v>
+        <v>20.648</v>
       </c>
       <c r="AC55" t="n">
-        <v>16.493</v>
+        <v>16.974</v>
       </c>
       <c r="AD55" t="n">
-        <v>21.606</v>
+        <v>22.171</v>
       </c>
       <c r="AE55" t="n">
-        <v>9.074999999999999</v>
+        <v>9.311999999999999</v>
       </c>
       <c r="AF55" t="n">
-        <v>22.797</v>
+        <v>23.065</v>
       </c>
       <c r="AG55" t="n">
-        <v>15.594</v>
+        <v>15.671</v>
       </c>
       <c r="AH55" t="n">
-        <v>6.406</v>
+        <v>6.371</v>
       </c>
       <c r="AI55" t="n">
-        <v>3.339</v>
+        <v>3.423</v>
       </c>
       <c r="AJ55" t="n">
-        <v>17.533</v>
+        <v>17.495</v>
       </c>
       <c r="AK55" t="n">
-        <v>-2.6</v>
+        <v>-7.2</v>
       </c>
       <c r="AL55" t="n">
-        <v>-3.6</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="56">
@@ -9146,22 +9146,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>1327.669</v>
+        <v>1325.858</v>
       </c>
       <c r="I73" t="n">
-        <v>1.6095</v>
+        <v>1.6749</v>
       </c>
       <c r="J73" t="n">
-        <v>1453.9</v>
+        <v>1453.7</v>
       </c>
       <c r="K73" t="n">
         <v>222</v>
@@ -9182,70 +9182,70 @@
         <v>229</v>
       </c>
       <c r="Q73" t="n">
-        <v>109.628</v>
+        <v>108.872</v>
       </c>
       <c r="R73" t="n">
-        <v>112.459</v>
+        <v>111.904</v>
       </c>
       <c r="S73" t="n">
-        <v>-2.831</v>
+        <v>-3.033</v>
       </c>
       <c r="T73" t="n">
-        <v>0.31612</v>
+        <v>0.3151</v>
       </c>
       <c r="U73" t="n">
-        <v>0.16036</v>
+        <v>0.16021</v>
       </c>
       <c r="V73" t="n">
-        <v>76.65000000000001</v>
+        <v>76.13</v>
       </c>
       <c r="W73" t="n">
-        <v>78.97</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="X73" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.4948</v>
       </c>
       <c r="Y73" t="n">
-        <v>27.182</v>
+        <v>26.937</v>
       </c>
       <c r="Z73" t="n">
-        <v>61.023</v>
+        <v>61.055</v>
       </c>
       <c r="AA73" t="n">
-        <v>6.67</v>
+        <v>6.573</v>
       </c>
       <c r="AB73" t="n">
-        <v>19.375</v>
+        <v>18.939</v>
       </c>
       <c r="AC73" t="n">
-        <v>15.341</v>
+        <v>15.483</v>
       </c>
       <c r="AD73" t="n">
-        <v>19.716</v>
+        <v>19.726</v>
       </c>
       <c r="AE73" t="n">
-        <v>10.841</v>
+        <v>10.879</v>
       </c>
       <c r="AF73" t="n">
-        <v>23.443</v>
+        <v>23.636</v>
       </c>
       <c r="AG73" t="n">
-        <v>13.295</v>
+        <v>13.22</v>
       </c>
       <c r="AH73" t="n">
-        <v>5.648</v>
+        <v>5.627</v>
       </c>
       <c r="AI73" t="n">
-        <v>3.295</v>
+        <v>3.253</v>
       </c>
       <c r="AJ73" t="n">
-        <v>19.239</v>
+        <v>19.438</v>
       </c>
       <c r="AK73" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="AL73" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="74">
@@ -10106,22 +10106,22 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F81" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G81" t="b">
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>1318.996</v>
+        <v>1316.994</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.1643</v>
+        <v>-1.0019</v>
       </c>
       <c r="J81" t="n">
-        <v>1451.5</v>
+        <v>1450.3</v>
       </c>
       <c r="K81" t="n">
         <v>166</v>
@@ -10142,70 +10142,70 @@
         <v>201</v>
       </c>
       <c r="Q81" t="n">
-        <v>112.139</v>
+        <v>111.602</v>
       </c>
       <c r="R81" t="n">
-        <v>113.116</v>
+        <v>113.343</v>
       </c>
       <c r="S81" t="n">
-        <v>-0.976</v>
+        <v>-1.741</v>
       </c>
       <c r="T81" t="n">
-        <v>0.29289</v>
+        <v>0.28697</v>
       </c>
       <c r="U81" t="n">
-        <v>0.17069</v>
+        <v>0.16806</v>
       </c>
       <c r="V81" t="n">
-        <v>78.02</v>
+        <v>77.58</v>
       </c>
       <c r="W81" t="n">
-        <v>79.09999999999999</v>
+        <v>79.17</v>
       </c>
       <c r="X81" t="n">
-        <v>0.424</v>
+        <v>0.4032</v>
       </c>
       <c r="Y81" t="n">
-        <v>27.616</v>
+        <v>27.589</v>
       </c>
       <c r="Z81" t="n">
-        <v>57.68</v>
+        <v>57.529</v>
       </c>
       <c r="AA81" t="n">
-        <v>7.368</v>
+        <v>7.341</v>
       </c>
       <c r="AB81" t="n">
-        <v>20.112</v>
+        <v>20.132</v>
       </c>
       <c r="AC81" t="n">
-        <v>15.416</v>
+        <v>15.565</v>
       </c>
       <c r="AD81" t="n">
-        <v>20.704</v>
+        <v>20.967</v>
       </c>
       <c r="AE81" t="n">
-        <v>9.007999999999999</v>
+        <v>8.846</v>
       </c>
       <c r="AF81" t="n">
-        <v>21.168</v>
+        <v>21.501</v>
       </c>
       <c r="AG81" t="n">
-        <v>13.616</v>
+        <v>13.366</v>
       </c>
       <c r="AH81" t="n">
-        <v>5.96</v>
+        <v>6</v>
       </c>
       <c r="AI81" t="n">
-        <v>3.408</v>
+        <v>3.326</v>
       </c>
       <c r="AJ81" t="n">
-        <v>18.216</v>
+        <v>18.34</v>
       </c>
       <c r="AK81" t="n">
-        <v>10.8</v>
+        <v>5.8</v>
       </c>
       <c r="AL81" t="n">
-        <v>10.2</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="82">
@@ -11546,22 +11546,22 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F93" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G93" t="b">
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>1385.503</v>
+        <v>1382.87</v>
       </c>
       <c r="I93" t="n">
-        <v>1.345</v>
+        <v>1.3273</v>
       </c>
       <c r="J93" t="n">
-        <v>1494.2</v>
+        <v>1490.2</v>
       </c>
       <c r="K93" t="n">
         <v>190</v>
@@ -11582,70 +11582,70 @@
         <v>191</v>
       </c>
       <c r="Q93" t="n">
-        <v>107.532</v>
+        <v>107.634</v>
       </c>
       <c r="R93" t="n">
-        <v>108.752</v>
+        <v>109.208</v>
       </c>
       <c r="S93" t="n">
-        <v>-1.22</v>
+        <v>-1.574</v>
       </c>
       <c r="T93" t="n">
-        <v>0.32388</v>
+        <v>0.32124</v>
       </c>
       <c r="U93" t="n">
-        <v>0.17329</v>
+        <v>0.17394</v>
       </c>
       <c r="V93" t="n">
-        <v>78.02</v>
+        <v>77.69</v>
       </c>
       <c r="W93" t="n">
-        <v>79.14</v>
+        <v>79.05</v>
       </c>
       <c r="X93" t="n">
-        <v>0.4321</v>
+        <v>0.4114</v>
       </c>
       <c r="Y93" t="n">
-        <v>27.381</v>
+        <v>27.269</v>
       </c>
       <c r="Z93" t="n">
-        <v>61.02</v>
+        <v>60.486</v>
       </c>
       <c r="AA93" t="n">
-        <v>7.042</v>
+        <v>7.194</v>
       </c>
       <c r="AB93" t="n">
-        <v>20.106</v>
+        <v>20.343</v>
       </c>
       <c r="AC93" t="n">
-        <v>16.211</v>
+        <v>16.08</v>
       </c>
       <c r="AD93" t="n">
-        <v>23.264</v>
+        <v>23.269</v>
       </c>
       <c r="AE93" t="n">
-        <v>11.208</v>
+        <v>11.011</v>
       </c>
       <c r="AF93" t="n">
-        <v>22.559</v>
+        <v>22.4</v>
       </c>
       <c r="AG93" t="n">
-        <v>13.628</v>
+        <v>13.783</v>
       </c>
       <c r="AH93" t="n">
-        <v>8.887</v>
+        <v>8.977</v>
       </c>
       <c r="AI93" t="n">
-        <v>4.474</v>
+        <v>4.406</v>
       </c>
       <c r="AJ93" t="n">
-        <v>18.184</v>
+        <v>18.091</v>
       </c>
       <c r="AK93" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AL93" t="n">
         <v>-0.6</v>
-      </c>
-      <c r="AL93" t="n">
-        <v>0.1</v>
       </c>
     </row>
     <row r="94">
@@ -13106,22 +13106,22 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F106" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G106" t="b">
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>2063.153</v>
+        <v>2068.259</v>
       </c>
       <c r="I106" t="n">
-        <v>6.2559</v>
+        <v>5.8188</v>
       </c>
       <c r="J106" t="n">
-        <v>1593.1</v>
+        <v>1601.3</v>
       </c>
       <c r="K106" t="n">
         <v>10</v>
@@ -13142,70 +13142,70 @@
         <v>5</v>
       </c>
       <c r="Q106" t="n">
-        <v>120.058</v>
+        <v>120.754</v>
       </c>
       <c r="R106" t="n">
-        <v>92.989</v>
+        <v>93.89400000000001</v>
       </c>
       <c r="S106" t="n">
-        <v>27.069</v>
+        <v>26.861</v>
       </c>
       <c r="T106" t="n">
-        <v>0.2963</v>
+        <v>0.29917</v>
       </c>
       <c r="U106" t="n">
-        <v>0.13371</v>
+        <v>0.13348</v>
       </c>
       <c r="V106" t="n">
-        <v>85.09</v>
+        <v>85.06</v>
       </c>
       <c r="W106" t="n">
-        <v>65.83</v>
+        <v>66.02</v>
       </c>
       <c r="X106" t="n">
-        <v>0.9073</v>
+        <v>0.91</v>
       </c>
       <c r="Y106" t="n">
-        <v>32.388</v>
+        <v>32.29</v>
       </c>
       <c r="Z106" t="n">
-        <v>63.603</v>
+        <v>63.29</v>
       </c>
       <c r="AA106" t="n">
-        <v>6.524</v>
+        <v>6.7</v>
       </c>
       <c r="AB106" t="n">
-        <v>19.41</v>
+        <v>19.69</v>
       </c>
       <c r="AC106" t="n">
-        <v>13.793</v>
+        <v>13.78</v>
       </c>
       <c r="AD106" t="n">
-        <v>19.554</v>
+        <v>19.76</v>
       </c>
       <c r="AE106" t="n">
-        <v>10.895</v>
+        <v>10.98</v>
       </c>
       <c r="AF106" t="n">
-        <v>25.96</v>
+        <v>25.82</v>
       </c>
       <c r="AG106" t="n">
-        <v>18.144</v>
+        <v>18.39</v>
       </c>
       <c r="AH106" t="n">
-        <v>8.648999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AI106" t="n">
-        <v>3.691</v>
+        <v>3.7</v>
       </c>
       <c r="AJ106" t="n">
-        <v>17.03</v>
+        <v>16.74</v>
       </c>
       <c r="AK106" t="n">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="AL106" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="107">
@@ -13226,22 +13226,22 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F107" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G107" t="b">
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>1312.041</v>
+        <v>1309.333</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.5671</v>
+        <v>-0.5826</v>
       </c>
       <c r="J107" t="n">
-        <v>1352.3</v>
+        <v>1352.7</v>
       </c>
       <c r="K107" t="n">
         <v>298</v>
@@ -13262,70 +13262,70 @@
         <v>301</v>
       </c>
       <c r="Q107" t="n">
-        <v>100.56</v>
+        <v>100.192</v>
       </c>
       <c r="R107" t="n">
-        <v>103.092</v>
+        <v>103.209</v>
       </c>
       <c r="S107" t="n">
-        <v>-2.532</v>
+        <v>-3.017</v>
       </c>
       <c r="T107" t="n">
-        <v>0.29737</v>
+        <v>0.2968</v>
       </c>
       <c r="U107" t="n">
-        <v>0.20438</v>
+        <v>0.20467</v>
       </c>
       <c r="V107" t="n">
-        <v>69.25</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="W107" t="n">
-        <v>71.16</v>
+        <v>71.23</v>
       </c>
       <c r="X107" t="n">
-        <v>0.4063</v>
+        <v>0.3833</v>
       </c>
       <c r="Y107" t="n">
-        <v>23.142</v>
+        <v>23.044</v>
       </c>
       <c r="Z107" t="n">
-        <v>54.142</v>
+        <v>54.128</v>
       </c>
       <c r="AA107" t="n">
-        <v>6.766</v>
+        <v>6.671</v>
       </c>
       <c r="AB107" t="n">
-        <v>20.867</v>
+        <v>20.59</v>
       </c>
       <c r="AC107" t="n">
-        <v>16.198</v>
+        <v>16.233</v>
       </c>
       <c r="AD107" t="n">
-        <v>22.252</v>
+        <v>22.265</v>
       </c>
       <c r="AE107" t="n">
-        <v>9.087</v>
+        <v>9.106</v>
       </c>
       <c r="AF107" t="n">
-        <v>21.438</v>
+        <v>21.55</v>
       </c>
       <c r="AG107" t="n">
-        <v>11.999</v>
+        <v>11.885</v>
       </c>
       <c r="AH107" t="n">
-        <v>7.627</v>
+        <v>7.649</v>
       </c>
       <c r="AI107" t="n">
         <v>2.681</v>
       </c>
       <c r="AJ107" t="n">
-        <v>18.814</v>
+        <v>18.84</v>
       </c>
       <c r="AK107" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL107" t="n">
-        <v>-0.8</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="108">
@@ -13946,22 +13946,22 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F113" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G113" t="b">
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>1582.041</v>
+        <v>1586.191</v>
       </c>
       <c r="I113" t="n">
-        <v>3.5064</v>
+        <v>3.3583</v>
       </c>
       <c r="J113" t="n">
-        <v>1484.4</v>
+        <v>1482.3</v>
       </c>
       <c r="K113" t="n">
         <v>84</v>
@@ -13982,70 +13982,70 @@
         <v>88</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.542</v>
+        <v>113.557</v>
       </c>
       <c r="R113" t="n">
-        <v>102.659</v>
+        <v>102.691</v>
       </c>
       <c r="S113" t="n">
-        <v>10.883</v>
+        <v>10.866</v>
       </c>
       <c r="T113" t="n">
-        <v>0.30742</v>
+        <v>0.30811</v>
       </c>
       <c r="U113" t="n">
-        <v>0.15226</v>
+        <v>0.15271</v>
       </c>
       <c r="V113" t="n">
-        <v>74.42</v>
+        <v>74.5</v>
       </c>
       <c r="W113" t="n">
-        <v>67.48999999999999</v>
+        <v>67.58</v>
       </c>
       <c r="X113" t="n">
-        <v>0.6806</v>
+        <v>0.6903</v>
       </c>
       <c r="Y113" t="n">
-        <v>25.469</v>
+        <v>25.385</v>
       </c>
       <c r="Z113" t="n">
-        <v>58.432</v>
+        <v>58.372</v>
       </c>
       <c r="AA113" t="n">
-        <v>9.403</v>
+        <v>9.252000000000001</v>
       </c>
       <c r="AB113" t="n">
-        <v>25.336</v>
+        <v>25.159</v>
       </c>
       <c r="AC113" t="n">
-        <v>14.079</v>
+        <v>14.484</v>
       </c>
       <c r="AD113" t="n">
-        <v>18.603</v>
+        <v>19.05</v>
       </c>
       <c r="AE113" t="n">
-        <v>10.857</v>
+        <v>10.974</v>
       </c>
       <c r="AF113" t="n">
-        <v>24.31</v>
+        <v>24.47</v>
       </c>
       <c r="AG113" t="n">
-        <v>12.354</v>
+        <v>12.292</v>
       </c>
       <c r="AH113" t="n">
-        <v>4.683</v>
+        <v>4.801</v>
       </c>
       <c r="AI113" t="n">
-        <v>3.619</v>
+        <v>3.539</v>
       </c>
       <c r="AJ113" t="n">
-        <v>17.45</v>
+        <v>17.585</v>
       </c>
       <c r="AK113" t="n">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="AL113" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="114">
@@ -14546,22 +14546,22 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F118" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G118" t="b">
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>1403.081</v>
+        <v>1405.083</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3924</v>
+        <v>-0.3769</v>
       </c>
       <c r="J118" t="n">
-        <v>1416.4</v>
+        <v>1412.5</v>
       </c>
       <c r="K118" t="n">
         <v>165</v>
@@ -14582,70 +14582,70 @@
         <v>161</v>
       </c>
       <c r="Q118" t="n">
-        <v>110.574</v>
+        <v>110.53</v>
       </c>
       <c r="R118" t="n">
-        <v>107.707</v>
+        <v>107.113</v>
       </c>
       <c r="S118" t="n">
-        <v>2.866</v>
+        <v>3.417</v>
       </c>
       <c r="T118" t="n">
-        <v>0.27536</v>
+        <v>0.27557</v>
       </c>
       <c r="U118" t="n">
-        <v>0.14631</v>
+        <v>0.14578</v>
       </c>
       <c r="V118" t="n">
-        <v>76.51000000000001</v>
+        <v>76.67</v>
       </c>
       <c r="W118" t="n">
-        <v>74.45999999999999</v>
+        <v>74.22</v>
       </c>
       <c r="X118" t="n">
-        <v>0.5366</v>
+        <v>0.5513</v>
       </c>
       <c r="Y118" t="n">
-        <v>25.988</v>
+        <v>25.853</v>
       </c>
       <c r="Z118" t="n">
-        <v>59.935</v>
+        <v>59.981</v>
       </c>
       <c r="AA118" t="n">
-        <v>10.073</v>
+        <v>9.795</v>
       </c>
       <c r="AB118" t="n">
-        <v>28.469</v>
+        <v>28.173</v>
       </c>
       <c r="AC118" t="n">
-        <v>14.302</v>
+        <v>14.545</v>
       </c>
       <c r="AD118" t="n">
-        <v>19.626</v>
+        <v>20.019</v>
       </c>
       <c r="AE118" t="n">
-        <v>9.423</v>
+        <v>9.455</v>
       </c>
       <c r="AF118" t="n">
-        <v>24.291</v>
+        <v>24.365</v>
       </c>
       <c r="AG118" t="n">
-        <v>11.967</v>
+        <v>11.891</v>
       </c>
       <c r="AH118" t="n">
-        <v>5.622</v>
+        <v>5.494</v>
       </c>
       <c r="AI118" t="n">
-        <v>2.331</v>
+        <v>2.359</v>
       </c>
       <c r="AJ118" t="n">
-        <v>18.861</v>
+        <v>19.026</v>
       </c>
       <c r="AK118" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AL118" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -16106,22 +16106,22 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F131" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G131" t="b">
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>1300.886</v>
+        <v>1303.595</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.469</v>
+        <v>-1.4112</v>
       </c>
       <c r="J131" t="n">
-        <v>1425.2</v>
+        <v>1424.2</v>
       </c>
       <c r="K131" t="n">
         <v>342</v>
@@ -16142,70 +16142,70 @@
         <v>348</v>
       </c>
       <c r="Q131" t="n">
-        <v>98.83</v>
+        <v>98.508</v>
       </c>
       <c r="R131" t="n">
-        <v>117.734</v>
+        <v>116.794</v>
       </c>
       <c r="S131" t="n">
-        <v>-18.904</v>
+        <v>-18.286</v>
       </c>
       <c r="T131" t="n">
-        <v>0.30356</v>
+        <v>0.30563</v>
       </c>
       <c r="U131" t="n">
-        <v>0.18255</v>
+        <v>0.18378</v>
       </c>
       <c r="V131" t="n">
-        <v>70.81</v>
+        <v>70.53</v>
       </c>
       <c r="W131" t="n">
-        <v>84.72</v>
+        <v>83.98</v>
       </c>
       <c r="X131" t="n">
-        <v>0.3623</v>
+        <v>0.3817</v>
       </c>
       <c r="Y131" t="n">
-        <v>22.922</v>
+        <v>22.927</v>
       </c>
       <c r="Z131" t="n">
-        <v>58.629</v>
+        <v>58.753</v>
       </c>
       <c r="AA131" t="n">
-        <v>7.988</v>
+        <v>7.958</v>
       </c>
       <c r="AB131" t="n">
-        <v>25.301</v>
+        <v>25.413</v>
       </c>
       <c r="AC131" t="n">
-        <v>16.98</v>
+        <v>16.722</v>
       </c>
       <c r="AD131" t="n">
-        <v>22.101</v>
+        <v>21.95</v>
       </c>
       <c r="AE131" t="n">
-        <v>9.707000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="AF131" t="n">
-        <v>21.168</v>
+        <v>21.352</v>
       </c>
       <c r="AG131" t="n">
-        <v>10.519</v>
+        <v>10.484</v>
       </c>
       <c r="AH131" t="n">
-        <v>6.107</v>
+        <v>6.093</v>
       </c>
       <c r="AI131" t="n">
-        <v>2.913</v>
+        <v>2.938</v>
       </c>
       <c r="AJ131" t="n">
-        <v>19.542</v>
+        <v>19.442</v>
       </c>
       <c r="AK131" t="n">
-        <v>-8.199999999999999</v>
+        <v>-4</v>
       </c>
       <c r="AL131" t="n">
-        <v>-2.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="132">
@@ -16346,22 +16346,22 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F133" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G133" t="b">
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>1462.84</v>
+        <v>1457.955</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0476</v>
+        <v>-0.0097</v>
       </c>
       <c r="J133" t="n">
-        <v>1466.3</v>
+        <v>1466.6</v>
       </c>
       <c r="K133" t="n">
         <v>204</v>
@@ -16382,70 +16382,70 @@
         <v>211</v>
       </c>
       <c r="Q133" t="n">
-        <v>106.291</v>
+        <v>106.037</v>
       </c>
       <c r="R133" t="n">
-        <v>106.842</v>
+        <v>106.928</v>
       </c>
       <c r="S133" t="n">
-        <v>-0.55</v>
+        <v>-0.891</v>
       </c>
       <c r="T133" t="n">
-        <v>0.27989</v>
+        <v>0.28263</v>
       </c>
       <c r="U133" t="n">
-        <v>0.15995</v>
+        <v>0.15928</v>
       </c>
       <c r="V133" t="n">
-        <v>70.13</v>
+        <v>69.88</v>
       </c>
       <c r="W133" t="n">
-        <v>70.59999999999999</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="X133" t="n">
-        <v>0.4332</v>
+        <v>0.4107</v>
       </c>
       <c r="Y133" t="n">
-        <v>23.303</v>
+        <v>23.225</v>
       </c>
       <c r="Z133" t="n">
-        <v>54.436</v>
+        <v>54.528</v>
       </c>
       <c r="AA133" t="n">
-        <v>7.425</v>
+        <v>7.452</v>
       </c>
       <c r="AB133" t="n">
-        <v>20.676</v>
+        <v>20.601</v>
       </c>
       <c r="AC133" t="n">
-        <v>16.098</v>
+        <v>16.186</v>
       </c>
       <c r="AD133" t="n">
-        <v>23.488</v>
+        <v>23.479</v>
       </c>
       <c r="AE133" t="n">
-        <v>9.247999999999999</v>
+        <v>9.365</v>
       </c>
       <c r="AF133" t="n">
-        <v>23.548</v>
+        <v>23.513</v>
       </c>
       <c r="AG133" t="n">
-        <v>11.586</v>
+        <v>11.415</v>
       </c>
       <c r="AH133" t="n">
-        <v>5.76</v>
+        <v>5.885</v>
       </c>
       <c r="AI133" t="n">
-        <v>2.921</v>
+        <v>2.848</v>
       </c>
       <c r="AJ133" t="n">
-        <v>17.33</v>
+        <v>17.342</v>
       </c>
       <c r="AK133" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AL133" t="n">
-        <v>0.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="134">
@@ -16706,22 +16706,22 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F136" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G136" t="b">
         <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>1577.763</v>
+        <v>1574.525</v>
       </c>
       <c r="I136" t="n">
-        <v>-4.9402</v>
+        <v>-4.7707</v>
       </c>
       <c r="J136" t="n">
-        <v>1704.2</v>
+        <v>1710.3</v>
       </c>
       <c r="K136" t="n">
         <v>101</v>
@@ -16742,70 +16742,70 @@
         <v>99</v>
       </c>
       <c r="Q136" t="n">
-        <v>106.78</v>
+        <v>107.267</v>
       </c>
       <c r="R136" t="n">
-        <v>110.178</v>
+        <v>111.05</v>
       </c>
       <c r="S136" t="n">
-        <v>-3.398</v>
+        <v>-3.783</v>
       </c>
       <c r="T136" t="n">
-        <v>0.28922</v>
+        <v>0.29054</v>
       </c>
       <c r="U136" t="n">
-        <v>0.16825</v>
+        <v>0.16907</v>
       </c>
       <c r="V136" t="n">
-        <v>79.26000000000001</v>
+        <v>79.69</v>
       </c>
       <c r="W136" t="n">
-        <v>81.36</v>
+        <v>82.09</v>
       </c>
       <c r="X136" t="n">
-        <v>0.3826</v>
+        <v>0.371</v>
       </c>
       <c r="Y136" t="n">
-        <v>28.948</v>
+        <v>29.063</v>
       </c>
       <c r="Z136" t="n">
-        <v>63.365</v>
+        <v>63.309</v>
       </c>
       <c r="AA136" t="n">
-        <v>9.307</v>
+        <v>9.476000000000001</v>
       </c>
       <c r="AB136" t="n">
-        <v>25.954</v>
+        <v>25.875</v>
       </c>
       <c r="AC136" t="n">
-        <v>12.058</v>
+        <v>12.083</v>
       </c>
       <c r="AD136" t="n">
-        <v>16.919</v>
+        <v>17.043</v>
       </c>
       <c r="AE136" t="n">
-        <v>9.167999999999999</v>
+        <v>9.185</v>
       </c>
       <c r="AF136" t="n">
-        <v>22.371</v>
+        <v>22.288</v>
       </c>
       <c r="AG136" t="n">
-        <v>16.78</v>
+        <v>16.71</v>
       </c>
       <c r="AH136" t="n">
-        <v>7.043</v>
+        <v>7.031</v>
       </c>
       <c r="AI136" t="n">
-        <v>3.53</v>
+        <v>3.526</v>
       </c>
       <c r="AJ136" t="n">
-        <v>19.278</v>
+        <v>19.206</v>
       </c>
       <c r="AK136" t="n">
-        <v>-12.6</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AL136" t="n">
-        <v>-12.6</v>
+        <v>-10.6</v>
       </c>
     </row>
     <row r="137">
@@ -18026,22 +18026,22 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F147" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G147" t="b">
         <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>1416.015</v>
+        <v>1418.21</v>
       </c>
       <c r="I147" t="n">
-        <v>2.4057</v>
+        <v>2.3581</v>
       </c>
       <c r="J147" t="n">
-        <v>1378.3</v>
+        <v>1378.8</v>
       </c>
       <c r="K147" t="n">
         <v>217</v>
@@ -18062,70 +18062,70 @@
         <v>200</v>
       </c>
       <c r="Q147" t="n">
-        <v>108.813</v>
+        <v>109.383</v>
       </c>
       <c r="R147" t="n">
-        <v>104.085</v>
+        <v>104.38</v>
       </c>
       <c r="S147" t="n">
-        <v>4.729</v>
+        <v>5.003</v>
       </c>
       <c r="T147" t="n">
-        <v>0.31667</v>
+        <v>0.31186</v>
       </c>
       <c r="U147" t="n">
-        <v>0.18607</v>
+        <v>0.18305</v>
       </c>
       <c r="V147" t="n">
-        <v>73.84</v>
+        <v>74.13</v>
       </c>
       <c r="W147" t="n">
-        <v>71</v>
+        <v>71.11</v>
       </c>
       <c r="X147" t="n">
-        <v>0.7</v>
+        <v>0.7086</v>
       </c>
       <c r="Y147" t="n">
-        <v>27.34</v>
+        <v>27.456</v>
       </c>
       <c r="Z147" t="n">
-        <v>57.2</v>
+        <v>57.041</v>
       </c>
       <c r="AA147" t="n">
-        <v>5.96</v>
+        <v>5.962</v>
       </c>
       <c r="AB147" t="n">
-        <v>16.74</v>
+        <v>16.459</v>
       </c>
       <c r="AC147" t="n">
-        <v>13.2</v>
+        <v>13.261</v>
       </c>
       <c r="AD147" t="n">
-        <v>19.59</v>
+        <v>19.909</v>
       </c>
       <c r="AE147" t="n">
-        <v>10.56</v>
+        <v>10.4</v>
       </c>
       <c r="AF147" t="n">
-        <v>22.37</v>
+        <v>22.551</v>
       </c>
       <c r="AG147" t="n">
-        <v>13.49</v>
+        <v>13.669</v>
       </c>
       <c r="AH147" t="n">
-        <v>7.84</v>
+        <v>7.816</v>
       </c>
       <c r="AI147" t="n">
-        <v>5.42</v>
+        <v>5.379</v>
       </c>
       <c r="AJ147" t="n">
-        <v>17.72</v>
+        <v>17.593</v>
       </c>
       <c r="AK147" t="n">
-        <v>7</v>
+        <v>10.4</v>
       </c>
       <c r="AL147" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="148">
@@ -18986,22 +18986,22 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F155" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G155" t="b">
         <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>1350.144</v>
+        <v>1348.195</v>
       </c>
       <c r="I155" t="n">
-        <v>-2.5201</v>
+        <v>-2.3753</v>
       </c>
       <c r="J155" t="n">
-        <v>1402.9</v>
+        <v>1403.6</v>
       </c>
       <c r="K155" t="n">
         <v>319</v>
@@ -19022,70 +19022,70 @@
         <v>318</v>
       </c>
       <c r="Q155" t="n">
-        <v>104.971</v>
+        <v>104.608</v>
       </c>
       <c r="R155" t="n">
-        <v>111.755</v>
+        <v>112.642</v>
       </c>
       <c r="S155" t="n">
-        <v>-6.784</v>
+        <v>-8.034000000000001</v>
       </c>
       <c r="T155" t="n">
-        <v>0.30972</v>
+        <v>0.31566</v>
       </c>
       <c r="U155" t="n">
-        <v>0.17143</v>
+        <v>0.17166</v>
       </c>
       <c r="V155" t="n">
-        <v>71.93000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="W155" t="n">
-        <v>76.95</v>
+        <v>77.58</v>
       </c>
       <c r="X155" t="n">
-        <v>0.4205</v>
+        <v>0.3958</v>
       </c>
       <c r="Y155" t="n">
-        <v>26.273</v>
+        <v>26.187</v>
       </c>
       <c r="Z155" t="n">
-        <v>58.216</v>
+        <v>58.643</v>
       </c>
       <c r="AA155" t="n">
-        <v>5.83</v>
+        <v>5.933</v>
       </c>
       <c r="AB155" t="n">
-        <v>18.068</v>
+        <v>18.381</v>
       </c>
       <c r="AC155" t="n">
-        <v>13.557</v>
+        <v>13.397</v>
       </c>
       <c r="AD155" t="n">
-        <v>20.727</v>
+        <v>20.334</v>
       </c>
       <c r="AE155" t="n">
-        <v>10.409</v>
+        <v>10.667</v>
       </c>
       <c r="AF155" t="n">
-        <v>23.102</v>
+        <v>22.969</v>
       </c>
       <c r="AG155" t="n">
-        <v>12.182</v>
+        <v>11.838</v>
       </c>
       <c r="AH155" t="n">
-        <v>5.17</v>
+        <v>5.132</v>
       </c>
       <c r="AI155" t="n">
-        <v>3.011</v>
+        <v>3</v>
       </c>
       <c r="AJ155" t="n">
-        <v>14.909</v>
+        <v>14.957</v>
       </c>
       <c r="AK155" t="n">
-        <v>0.6</v>
+        <v>-6.4</v>
       </c>
       <c r="AL155" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="156">
@@ -19706,22 +19706,22 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F161" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G161" t="b">
         <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>1598.051</v>
+        <v>1607.209</v>
       </c>
       <c r="I161" t="n">
-        <v>-8.074299999999999</v>
+        <v>-7.8093</v>
       </c>
       <c r="J161" t="n">
-        <v>1724.9</v>
+        <v>1715.9</v>
       </c>
       <c r="K161" t="n">
         <v>128</v>
@@ -19742,70 +19742,70 @@
         <v>151</v>
       </c>
       <c r="Q161" t="n">
-        <v>103.933</v>
+        <v>104.081</v>
       </c>
       <c r="R161" t="n">
-        <v>115.229</v>
+        <v>114.203</v>
       </c>
       <c r="S161" t="n">
-        <v>-11.296</v>
+        <v>-10.122</v>
       </c>
       <c r="T161" t="n">
-        <v>0.32036</v>
+        <v>0.31669</v>
       </c>
       <c r="U161" t="n">
-        <v>0.17539</v>
+        <v>0.1739</v>
       </c>
       <c r="V161" t="n">
-        <v>69.90000000000001</v>
+        <v>69.88</v>
       </c>
       <c r="W161" t="n">
-        <v>77.17</v>
+        <v>76.42</v>
       </c>
       <c r="X161" t="n">
-        <v>0.35</v>
+        <v>0.3829</v>
       </c>
       <c r="Y161" t="n">
-        <v>23.232</v>
+        <v>23.011</v>
       </c>
       <c r="Z161" t="n">
-        <v>57.082</v>
+        <v>56.875</v>
       </c>
       <c r="AA161" t="n">
-        <v>8.491</v>
+        <v>8.289</v>
       </c>
       <c r="AB161" t="n">
-        <v>26.786</v>
+        <v>26.492</v>
       </c>
       <c r="AC161" t="n">
-        <v>14.945</v>
+        <v>15.13</v>
       </c>
       <c r="AD161" t="n">
-        <v>20.695</v>
+        <v>20.784</v>
       </c>
       <c r="AE161" t="n">
-        <v>10.714</v>
+        <v>10.548</v>
       </c>
       <c r="AF161" t="n">
-        <v>22.214</v>
+        <v>22.203</v>
       </c>
       <c r="AG161" t="n">
-        <v>10.418</v>
+        <v>10.562</v>
       </c>
       <c r="AH161" t="n">
-        <v>4.686</v>
+        <v>4.809</v>
       </c>
       <c r="AI161" t="n">
-        <v>2.873</v>
+        <v>2.877</v>
       </c>
       <c r="AJ161" t="n">
-        <v>18.186</v>
+        <v>18.067</v>
       </c>
       <c r="AK161" t="n">
-        <v>-10.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AL161" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="162">
@@ -19946,22 +19946,22 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F163" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G163" t="b">
         <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>1718.721</v>
+        <v>1720.824</v>
       </c>
       <c r="I163" t="n">
-        <v>2.9617</v>
+        <v>2.8141</v>
       </c>
       <c r="J163" t="n">
-        <v>1423</v>
+        <v>1422.5</v>
       </c>
       <c r="K163" t="n">
         <v>68</v>
@@ -19982,70 +19982,70 @@
         <v>62</v>
       </c>
       <c r="Q163" t="n">
-        <v>115.407</v>
+        <v>114.819</v>
       </c>
       <c r="R163" t="n">
-        <v>100.479</v>
+        <v>100.313</v>
       </c>
       <c r="S163" t="n">
-        <v>14.929</v>
+        <v>14.507</v>
       </c>
       <c r="T163" t="n">
-        <v>0.34773</v>
+        <v>0.35125</v>
       </c>
       <c r="U163" t="n">
-        <v>0.13762</v>
+        <v>0.1369</v>
       </c>
       <c r="V163" t="n">
-        <v>76.61</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="W163" t="n">
-        <v>66.84</v>
+        <v>67.41</v>
       </c>
       <c r="X163" t="n">
-        <v>0.8292</v>
+        <v>0.8348</v>
       </c>
       <c r="Y163" t="n">
-        <v>26.587</v>
+        <v>26.761</v>
       </c>
       <c r="Z163" t="n">
-        <v>58.373</v>
+        <v>59.313</v>
       </c>
       <c r="AA163" t="n">
-        <v>6.401</v>
+        <v>6.48</v>
       </c>
       <c r="AB163" t="n">
-        <v>20.686</v>
+        <v>20.836</v>
       </c>
       <c r="AC163" t="n">
-        <v>17.031</v>
+        <v>16.925</v>
       </c>
       <c r="AD163" t="n">
-        <v>22.739</v>
+        <v>23.036</v>
       </c>
       <c r="AE163" t="n">
-        <v>10.938</v>
+        <v>11.342</v>
       </c>
       <c r="AF163" t="n">
-        <v>20.59</v>
+        <v>20.895</v>
       </c>
       <c r="AG163" t="n">
-        <v>13.034</v>
+        <v>13.158</v>
       </c>
       <c r="AH163" t="n">
-        <v>10.155</v>
+        <v>10.382</v>
       </c>
       <c r="AI163" t="n">
-        <v>4.289</v>
+        <v>4.297</v>
       </c>
       <c r="AJ163" t="n">
-        <v>19.326</v>
+        <v>19.422</v>
       </c>
       <c r="AK163" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AL163" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="164">
@@ -21506,22 +21506,22 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F176" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G176" t="b">
         <v>1</v>
       </c>
       <c r="H176" t="n">
-        <v>1394.962</v>
+        <v>1397.595</v>
       </c>
       <c r="I176" t="n">
-        <v>1.3277</v>
+        <v>1.1993</v>
       </c>
       <c r="J176" t="n">
-        <v>1474.6</v>
+        <v>1471</v>
       </c>
       <c r="K176" t="n">
         <v>215</v>
@@ -21542,70 +21542,70 @@
         <v>214</v>
       </c>
       <c r="Q176" t="n">
-        <v>107.512</v>
+        <v>107.894</v>
       </c>
       <c r="R176" t="n">
-        <v>109.721</v>
+        <v>109.732</v>
       </c>
       <c r="S176" t="n">
-        <v>-2.209</v>
+        <v>-1.838</v>
       </c>
       <c r="T176" t="n">
-        <v>0.31943</v>
+        <v>0.32401</v>
       </c>
       <c r="U176" t="n">
-        <v>0.1608</v>
+        <v>0.16312</v>
       </c>
       <c r="V176" t="n">
-        <v>73.04000000000001</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="W176" t="n">
-        <v>74.79000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="X176" t="n">
-        <v>0.3904</v>
+        <v>0.4171</v>
       </c>
       <c r="Y176" t="n">
-        <v>24.42</v>
+        <v>24.491</v>
       </c>
       <c r="Z176" t="n">
-        <v>55.958</v>
+        <v>55.926</v>
       </c>
       <c r="AA176" t="n">
-        <v>7.414</v>
+        <v>7.251</v>
       </c>
       <c r="AB176" t="n">
-        <v>22.929</v>
+        <v>22.571</v>
       </c>
       <c r="AC176" t="n">
-        <v>16.792</v>
+        <v>16.829</v>
       </c>
       <c r="AD176" t="n">
-        <v>24.738</v>
+        <v>24.874</v>
       </c>
       <c r="AE176" t="n">
-        <v>9.733000000000001</v>
+        <v>10</v>
       </c>
       <c r="AF176" t="n">
-        <v>20.835</v>
+        <v>20.869</v>
       </c>
       <c r="AG176" t="n">
-        <v>13.799</v>
+        <v>13.474</v>
       </c>
       <c r="AH176" t="n">
-        <v>6.756</v>
+        <v>6.754</v>
       </c>
       <c r="AI176" t="n">
-        <v>3.052</v>
+        <v>3.029</v>
       </c>
       <c r="AJ176" t="n">
-        <v>18.289</v>
+        <v>18.269</v>
       </c>
       <c r="AK176" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
       <c r="AL176" t="n">
-        <v>-1.9</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="177">
@@ -21626,22 +21626,22 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F177" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G177" t="b">
         <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>1450.738</v>
+        <v>1446.589</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2494</v>
+        <v>1.3087</v>
       </c>
       <c r="J177" t="n">
-        <v>1456.7</v>
+        <v>1462</v>
       </c>
       <c r="K177" t="n">
         <v>181</v>
@@ -21662,70 +21662,70 @@
         <v>169</v>
       </c>
       <c r="Q177" t="n">
-        <v>106.718</v>
+        <v>106.67</v>
       </c>
       <c r="R177" t="n">
-        <v>104.796</v>
+        <v>105.293</v>
       </c>
       <c r="S177" t="n">
-        <v>1.922</v>
+        <v>1.377</v>
       </c>
       <c r="T177" t="n">
-        <v>0.31254</v>
+        <v>0.30933</v>
       </c>
       <c r="U177" t="n">
-        <v>0.16263</v>
+        <v>0.16222</v>
       </c>
       <c r="V177" t="n">
-        <v>72.08</v>
+        <v>71.94</v>
       </c>
       <c r="W177" t="n">
-        <v>70.75</v>
+        <v>70.97</v>
       </c>
       <c r="X177" t="n">
-        <v>0.5665</v>
+        <v>0.5409</v>
       </c>
       <c r="Y177" t="n">
-        <v>25.465</v>
+        <v>25.412</v>
       </c>
       <c r="Z177" t="n">
-        <v>58.266</v>
+        <v>58.125</v>
       </c>
       <c r="AA177" t="n">
-        <v>6.809</v>
+        <v>6.85</v>
       </c>
       <c r="AB177" t="n">
-        <v>19.889</v>
+        <v>20.025</v>
       </c>
       <c r="AC177" t="n">
-        <v>14.342</v>
+        <v>14.27</v>
       </c>
       <c r="AD177" t="n">
-        <v>19.045</v>
+        <v>19.038</v>
       </c>
       <c r="AE177" t="n">
-        <v>10.133</v>
+        <v>10.043</v>
       </c>
       <c r="AF177" t="n">
-        <v>22.206</v>
+        <v>22.309</v>
       </c>
       <c r="AG177" t="n">
-        <v>13.756</v>
+        <v>13.674</v>
       </c>
       <c r="AH177" t="n">
-        <v>7.705</v>
+        <v>7.631</v>
       </c>
       <c r="AI177" t="n">
-        <v>4.252</v>
+        <v>4.194</v>
       </c>
       <c r="AJ177" t="n">
-        <v>15.898</v>
+        <v>16.025</v>
       </c>
       <c r="AK177" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="AL177" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="178">
@@ -21746,22 +21746,22 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F178" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G178" t="b">
         <v>1</v>
       </c>
       <c r="H178" t="n">
-        <v>1464.637</v>
+        <v>1469.446</v>
       </c>
       <c r="I178" t="n">
-        <v>-1.6217</v>
+        <v>-1.5005</v>
       </c>
       <c r="J178" t="n">
-        <v>1434.8</v>
+        <v>1435.4</v>
       </c>
       <c r="K178" t="n">
         <v>187</v>
@@ -21782,70 +21782,70 @@
         <v>199</v>
       </c>
       <c r="Q178" t="n">
-        <v>107.791</v>
+        <v>107.303</v>
       </c>
       <c r="R178" t="n">
-        <v>109.828</v>
+        <v>109.175</v>
       </c>
       <c r="S178" t="n">
-        <v>-2.037</v>
+        <v>-1.872</v>
       </c>
       <c r="T178" t="n">
-        <v>0.18463</v>
+        <v>0.19414</v>
       </c>
       <c r="U178" t="n">
-        <v>0.18961</v>
+        <v>0.18613</v>
       </c>
       <c r="V178" t="n">
-        <v>76.26000000000001</v>
+        <v>76.02</v>
       </c>
       <c r="W178" t="n">
-        <v>77.90000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="X178" t="n">
-        <v>0.5051</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="Y178" t="n">
-        <v>26.298</v>
+        <v>26.065</v>
       </c>
       <c r="Z178" t="n">
-        <v>54.323</v>
+        <v>54.969</v>
       </c>
       <c r="AA178" t="n">
-        <v>8.247</v>
+        <v>8.065</v>
       </c>
       <c r="AB178" t="n">
-        <v>22.414</v>
+        <v>22.671</v>
       </c>
       <c r="AC178" t="n">
-        <v>15.419</v>
+        <v>15.699</v>
       </c>
       <c r="AD178" t="n">
-        <v>19.854</v>
+        <v>20.065</v>
       </c>
       <c r="AE178" t="n">
-        <v>5.586</v>
+        <v>5.981</v>
       </c>
       <c r="AF178" t="n">
-        <v>24.758</v>
+        <v>24.596</v>
       </c>
       <c r="AG178" t="n">
-        <v>14.677</v>
+        <v>14.379</v>
       </c>
       <c r="AH178" t="n">
-        <v>5.465</v>
+        <v>5.522</v>
       </c>
       <c r="AI178" t="n">
-        <v>2.414</v>
+        <v>2.41</v>
       </c>
       <c r="AJ178" t="n">
-        <v>17.52</v>
+        <v>17.512</v>
       </c>
       <c r="AK178" t="n">
-        <v>-5.6</v>
+        <v>-1</v>
       </c>
       <c r="AL178" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="179">
@@ -24266,22 +24266,22 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F199" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G199" t="b">
         <v>1</v>
       </c>
       <c r="H199" t="n">
-        <v>1461.453</v>
+        <v>1466.337</v>
       </c>
       <c r="I199" t="n">
-        <v>-7.7933</v>
+        <v>-7.3735</v>
       </c>
       <c r="J199" t="n">
-        <v>1488.4</v>
+        <v>1487.1</v>
       </c>
       <c r="K199" t="n">
         <v>185</v>
@@ -24302,70 +24302,70 @@
         <v>186</v>
       </c>
       <c r="Q199" t="n">
-        <v>109.217</v>
+        <v>109.084</v>
       </c>
       <c r="R199" t="n">
-        <v>108.7</v>
+        <v>108.278</v>
       </c>
       <c r="S199" t="n">
-        <v>0.517</v>
+        <v>0.806</v>
       </c>
       <c r="T199" t="n">
-        <v>0.30891</v>
+        <v>0.30371</v>
       </c>
       <c r="U199" t="n">
-        <v>0.14192</v>
+        <v>0.14467</v>
       </c>
       <c r="V199" t="n">
-        <v>74.59</v>
+        <v>74.27</v>
       </c>
       <c r="W199" t="n">
-        <v>74.38</v>
+        <v>73.88</v>
       </c>
       <c r="X199" t="n">
-        <v>0.4493</v>
+        <v>0.4686</v>
       </c>
       <c r="Y199" t="n">
-        <v>25.743</v>
+        <v>25.578</v>
       </c>
       <c r="Z199" t="n">
-        <v>60.367</v>
+        <v>59.833</v>
       </c>
       <c r="AA199" t="n">
-        <v>7.663</v>
+        <v>7.63</v>
       </c>
       <c r="AB199" t="n">
-        <v>23.537</v>
+        <v>23.472</v>
       </c>
       <c r="AC199" t="n">
-        <v>15.446</v>
+        <v>15.267</v>
       </c>
       <c r="AD199" t="n">
-        <v>20.85</v>
+        <v>20.744</v>
       </c>
       <c r="AE199" t="n">
-        <v>10.759</v>
+        <v>10.543</v>
       </c>
       <c r="AF199" t="n">
-        <v>24.054</v>
+        <v>24.166</v>
       </c>
       <c r="AG199" t="n">
-        <v>12.963</v>
+        <v>12.834</v>
       </c>
       <c r="AH199" t="n">
-        <v>5.624</v>
+        <v>5.733</v>
       </c>
       <c r="AI199" t="n">
-        <v>3.093</v>
+        <v>3.15</v>
       </c>
       <c r="AJ199" t="n">
-        <v>19.853</v>
+        <v>19.728</v>
       </c>
       <c r="AK199" t="n">
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="AL199" t="n">
-        <v>-2.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="200">
@@ -24746,22 +24746,22 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F203" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G203" t="b">
         <v>1</v>
       </c>
       <c r="H203" t="n">
-        <v>1310.022</v>
+        <v>1308.783</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3892</v>
+        <v>0.4078</v>
       </c>
       <c r="J203" t="n">
-        <v>1398.5</v>
+        <v>1403</v>
       </c>
       <c r="K203" t="n">
         <v>332</v>
@@ -24782,70 +24782,70 @@
         <v>327</v>
       </c>
       <c r="Q203" t="n">
-        <v>98.15000000000001</v>
+        <v>97.73699999999999</v>
       </c>
       <c r="R203" t="n">
-        <v>108.469</v>
+        <v>108.415</v>
       </c>
       <c r="S203" t="n">
-        <v>-10.319</v>
+        <v>-10.678</v>
       </c>
       <c r="T203" t="n">
-        <v>0.24997</v>
+        <v>0.25366</v>
       </c>
       <c r="U203" t="n">
-        <v>0.16266</v>
+        <v>0.16287</v>
       </c>
       <c r="V203" t="n">
-        <v>66.45999999999999</v>
+        <v>66</v>
       </c>
       <c r="W203" t="n">
-        <v>73.78</v>
+        <v>73.52</v>
       </c>
       <c r="X203" t="n">
-        <v>0.4909</v>
+        <v>0.4628</v>
       </c>
       <c r="Y203" t="n">
-        <v>23.064</v>
+        <v>22.975</v>
       </c>
       <c r="Z203" t="n">
-        <v>56.459</v>
+        <v>56.612</v>
       </c>
       <c r="AA203" t="n">
-        <v>6.877</v>
+        <v>6.907</v>
       </c>
       <c r="AB203" t="n">
-        <v>22.691</v>
+        <v>22.71</v>
       </c>
       <c r="AC203" t="n">
-        <v>13.455</v>
+        <v>13.146</v>
       </c>
       <c r="AD203" t="n">
-        <v>19.077</v>
+        <v>18.633</v>
       </c>
       <c r="AE203" t="n">
-        <v>8.082000000000001</v>
+        <v>8.223000000000001</v>
       </c>
       <c r="AF203" t="n">
-        <v>23.805</v>
+        <v>23.741</v>
       </c>
       <c r="AG203" t="n">
-        <v>10.605</v>
+        <v>10.456</v>
       </c>
       <c r="AH203" t="n">
-        <v>6.314</v>
+        <v>6.321</v>
       </c>
       <c r="AI203" t="n">
-        <v>3.191</v>
+        <v>3.098</v>
       </c>
       <c r="AJ203" t="n">
-        <v>18.359</v>
+        <v>18.222</v>
       </c>
       <c r="AK203" t="n">
-        <v>-15.6</v>
+        <v>-13.8</v>
       </c>
       <c r="AL203" t="n">
-        <v>-2.7</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="204">
@@ -25826,22 +25826,22 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F212" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G212" t="b">
         <v>1</v>
       </c>
       <c r="H212" t="n">
-        <v>1585.152</v>
+        <v>1591.557</v>
       </c>
       <c r="I212" t="n">
-        <v>-4.3422</v>
+        <v>-4.0194</v>
       </c>
       <c r="J212" t="n">
-        <v>1700.2</v>
+        <v>1694.1</v>
       </c>
       <c r="K212" t="n">
         <v>66</v>
@@ -25862,70 +25862,70 @@
         <v>70</v>
       </c>
       <c r="Q212" t="n">
-        <v>111.005</v>
+        <v>111.473</v>
       </c>
       <c r="R212" t="n">
-        <v>110.165</v>
+        <v>109.981</v>
       </c>
       <c r="S212" t="n">
-        <v>0.841</v>
+        <v>1.492</v>
       </c>
       <c r="T212" t="n">
-        <v>0.28</v>
+        <v>0.28135</v>
       </c>
       <c r="U212" t="n">
-        <v>0.12767</v>
+        <v>0.12765</v>
       </c>
       <c r="V212" t="n">
-        <v>73.12</v>
+        <v>73.31</v>
       </c>
       <c r="W212" t="n">
-        <v>72.17</v>
+        <v>71.98</v>
       </c>
       <c r="X212" t="n">
-        <v>0.4153</v>
+        <v>0.4426</v>
       </c>
       <c r="Y212" t="n">
-        <v>26.067</v>
+        <v>26.133</v>
       </c>
       <c r="Z212" t="n">
-        <v>57.025</v>
+        <v>56.902</v>
       </c>
       <c r="AA212" t="n">
-        <v>6.403</v>
+        <v>6.372</v>
       </c>
       <c r="AB212" t="n">
-        <v>19.582</v>
+        <v>19.606</v>
       </c>
       <c r="AC212" t="n">
-        <v>14.587</v>
+        <v>14.668</v>
       </c>
       <c r="AD212" t="n">
-        <v>19.399</v>
+        <v>19.554</v>
       </c>
       <c r="AE212" t="n">
-        <v>8.081</v>
+        <v>8.111000000000001</v>
       </c>
       <c r="AF212" t="n">
-        <v>20.462</v>
+        <v>20.415</v>
       </c>
       <c r="AG212" t="n">
-        <v>17.042</v>
+        <v>17.191</v>
       </c>
       <c r="AH212" t="n">
-        <v>5.715</v>
+        <v>5.872</v>
       </c>
       <c r="AI212" t="n">
-        <v>3.747</v>
+        <v>3.623</v>
       </c>
       <c r="AJ212" t="n">
-        <v>17.172</v>
+        <v>17.146</v>
       </c>
       <c r="AK212" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="AL212" t="n">
-        <v>-8.699999999999999</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="213">
@@ -26666,22 +26666,22 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F219" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G219" t="b">
         <v>1</v>
       </c>
       <c r="H219" t="n">
-        <v>1708.17</v>
+        <v>1716.101</v>
       </c>
       <c r="I219" t="n">
-        <v>-1.1004</v>
+        <v>-1.1554</v>
       </c>
       <c r="J219" t="n">
-        <v>1693.9</v>
+        <v>1686</v>
       </c>
       <c r="K219" t="n">
         <v>69</v>
@@ -26702,70 +26702,70 @@
         <v>79</v>
       </c>
       <c r="Q219" t="n">
-        <v>110.431</v>
+        <v>111.029</v>
       </c>
       <c r="R219" t="n">
-        <v>109.608</v>
+        <v>109.598</v>
       </c>
       <c r="S219" t="n">
-        <v>0.823</v>
+        <v>1.431</v>
       </c>
       <c r="T219" t="n">
-        <v>0.27916</v>
+        <v>0.27886</v>
       </c>
       <c r="U219" t="n">
-        <v>0.15706</v>
+        <v>0.15495</v>
       </c>
       <c r="V219" t="n">
-        <v>83.8</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="W219" t="n">
-        <v>82.51000000000001</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="X219" t="n">
-        <v>0.5739</v>
+        <v>0.5981</v>
       </c>
       <c r="Y219" t="n">
-        <v>28.783</v>
+        <v>28.97</v>
       </c>
       <c r="Z219" t="n">
-        <v>62.762</v>
+        <v>63.023</v>
       </c>
       <c r="AA219" t="n">
-        <v>7.864</v>
+        <v>7.929</v>
       </c>
       <c r="AB219" t="n">
-        <v>22.986</v>
+        <v>23.157</v>
       </c>
       <c r="AC219" t="n">
-        <v>18.371</v>
+        <v>17.996</v>
       </c>
       <c r="AD219" t="n">
-        <v>24.675</v>
+        <v>24.378</v>
       </c>
       <c r="AE219" t="n">
-        <v>9.843</v>
+        <v>9.815</v>
       </c>
       <c r="AF219" t="n">
-        <v>25.232</v>
+        <v>25.206</v>
       </c>
       <c r="AG219" t="n">
-        <v>14.73</v>
+        <v>14.909</v>
       </c>
       <c r="AH219" t="n">
-        <v>7.296</v>
+        <v>7.226</v>
       </c>
       <c r="AI219" t="n">
-        <v>2.551</v>
+        <v>2.64</v>
       </c>
       <c r="AJ219" t="n">
-        <v>17.122</v>
+        <v>17.31</v>
       </c>
       <c r="AK219" t="n">
-        <v>-6</v>
+        <v>-1.4</v>
       </c>
       <c r="AL219" t="n">
-        <v>-8.4</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="220">
@@ -27026,22 +27026,22 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F222" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G222" t="b">
         <v>1</v>
       </c>
       <c r="H222" t="n">
-        <v>1603.335</v>
+        <v>1594.177</v>
       </c>
       <c r="I222" t="n">
-        <v>-9.083399999999999</v>
+        <v>-8.546799999999999</v>
       </c>
       <c r="J222" t="n">
-        <v>1731.6</v>
+        <v>1726.9</v>
       </c>
       <c r="K222" t="n">
         <v>96</v>
@@ -27062,70 +27062,70 @@
         <v>102</v>
       </c>
       <c r="Q222" t="n">
-        <v>105.705</v>
+        <v>105.074</v>
       </c>
       <c r="R222" t="n">
-        <v>110.423</v>
+        <v>110.424</v>
       </c>
       <c r="S222" t="n">
-        <v>-4.718</v>
+        <v>-5.35</v>
       </c>
       <c r="T222" t="n">
-        <v>0.3115</v>
+        <v>0.31307</v>
       </c>
       <c r="U222" t="n">
-        <v>0.17045</v>
+        <v>0.17062</v>
       </c>
       <c r="V222" t="n">
-        <v>71.34999999999999</v>
+        <v>70.73</v>
       </c>
       <c r="W222" t="n">
-        <v>74.12</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="X222" t="n">
-        <v>0.3942</v>
+        <v>0.371</v>
       </c>
       <c r="Y222" t="n">
-        <v>24.484</v>
+        <v>24.36</v>
       </c>
       <c r="Z222" t="n">
-        <v>57.096</v>
+        <v>57.093</v>
       </c>
       <c r="AA222" t="n">
-        <v>7.971</v>
+        <v>7.98</v>
       </c>
       <c r="AB222" t="n">
-        <v>24.478</v>
+        <v>24.714</v>
       </c>
       <c r="AC222" t="n">
-        <v>14.414</v>
+        <v>14.444</v>
       </c>
       <c r="AD222" t="n">
-        <v>19.872</v>
+        <v>19.793</v>
       </c>
       <c r="AE222" t="n">
-        <v>10.072</v>
+        <v>10.218</v>
       </c>
       <c r="AF222" t="n">
-        <v>22.104</v>
+        <v>22.249</v>
       </c>
       <c r="AG222" t="n">
-        <v>14.443</v>
+        <v>14.298</v>
       </c>
       <c r="AH222" t="n">
-        <v>6.032</v>
+        <v>5.948</v>
       </c>
       <c r="AI222" t="n">
-        <v>3.933</v>
+        <v>4.011</v>
       </c>
       <c r="AJ222" t="n">
-        <v>15.519</v>
+        <v>15.484</v>
       </c>
       <c r="AK222" t="n">
-        <v>-1.2</v>
+        <v>-3.4</v>
       </c>
       <c r="AL222" t="n">
-        <v>-5.2</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="223">
@@ -27506,22 +27506,22 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F226" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G226" t="b">
         <v>1</v>
       </c>
       <c r="H226" t="n">
-        <v>1526.911</v>
+        <v>1520.505</v>
       </c>
       <c r="I226" t="n">
-        <v>-7.224</v>
+        <v>-6.9424</v>
       </c>
       <c r="J226" t="n">
-        <v>1664.7</v>
+        <v>1662.7</v>
       </c>
       <c r="K226" t="n">
         <v>138</v>
@@ -27542,70 +27542,70 @@
         <v>131</v>
       </c>
       <c r="Q226" t="n">
-        <v>109.422</v>
+        <v>109.321</v>
       </c>
       <c r="R226" t="n">
-        <v>117.676</v>
+        <v>117.763</v>
       </c>
       <c r="S226" t="n">
-        <v>-8.255000000000001</v>
+        <v>-8.441000000000001</v>
       </c>
       <c r="T226" t="n">
-        <v>0.26138</v>
+        <v>0.26078</v>
       </c>
       <c r="U226" t="n">
-        <v>0.14889</v>
+        <v>0.1538</v>
       </c>
       <c r="V226" t="n">
-        <v>73.77</v>
+        <v>73.59</v>
       </c>
       <c r="W226" t="n">
-        <v>79.38</v>
+        <v>79.3</v>
       </c>
       <c r="X226" t="n">
-        <v>0.3818</v>
+        <v>0.3703</v>
       </c>
       <c r="Y226" t="n">
-        <v>26.309</v>
+        <v>26.252</v>
       </c>
       <c r="Z226" t="n">
-        <v>56.382</v>
+        <v>55.979</v>
       </c>
       <c r="AA226" t="n">
-        <v>6.85</v>
+        <v>6.907</v>
       </c>
       <c r="AB226" t="n">
-        <v>21.523</v>
+        <v>21.276</v>
       </c>
       <c r="AC226" t="n">
-        <v>14.305</v>
+        <v>14.178</v>
       </c>
       <c r="AD226" t="n">
-        <v>19.168</v>
+        <v>18.906</v>
       </c>
       <c r="AE226" t="n">
-        <v>7.286</v>
+        <v>7.191</v>
       </c>
       <c r="AF226" t="n">
-        <v>19.932</v>
+        <v>19.684</v>
       </c>
       <c r="AG226" t="n">
-        <v>12.495</v>
+        <v>12.755</v>
       </c>
       <c r="AH226" t="n">
-        <v>7.082</v>
+        <v>6.875</v>
       </c>
       <c r="AI226" t="n">
-        <v>1.755</v>
+        <v>1.679</v>
       </c>
       <c r="AJ226" t="n">
-        <v>15.523</v>
+        <v>15.494</v>
       </c>
       <c r="AK226" t="n">
-        <v>-15.6</v>
+        <v>-15</v>
       </c>
       <c r="AL226" t="n">
-        <v>-12.7</v>
+        <v>-13.9</v>
       </c>
     </row>
     <row r="227">
@@ -27746,22 +27746,22 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F228" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G228" t="b">
         <v>1</v>
       </c>
       <c r="H228" t="n">
-        <v>1520.985</v>
+        <v>1536.866</v>
       </c>
       <c r="I228" t="n">
-        <v>-5.1919</v>
+        <v>-4.8733</v>
       </c>
       <c r="J228" t="n">
-        <v>1658.7</v>
+        <v>1663.6</v>
       </c>
       <c r="K228" t="n">
         <v>99</v>
@@ -27782,70 +27782,70 @@
         <v>109</v>
       </c>
       <c r="Q228" t="n">
-        <v>106.555</v>
+        <v>106.774</v>
       </c>
       <c r="R228" t="n">
-        <v>108.825</v>
+        <v>108.939</v>
       </c>
       <c r="S228" t="n">
-        <v>-2.27</v>
+        <v>-2.165</v>
       </c>
       <c r="T228" t="n">
-        <v>0.32297</v>
+        <v>0.32034</v>
       </c>
       <c r="U228" t="n">
-        <v>0.16788</v>
+        <v>0.1682</v>
       </c>
       <c r="V228" t="n">
-        <v>70.17</v>
+        <v>69.89</v>
       </c>
       <c r="W228" t="n">
-        <v>71.23</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="X228" t="n">
-        <v>0.3955</v>
+        <v>0.4137</v>
       </c>
       <c r="Y228" t="n">
-        <v>25.109</v>
+        <v>25.093</v>
       </c>
       <c r="Z228" t="n">
-        <v>57.568</v>
+        <v>57.307</v>
       </c>
       <c r="AA228" t="n">
-        <v>8.195</v>
+        <v>8.215999999999999</v>
       </c>
       <c r="AB228" t="n">
-        <v>24.695</v>
+        <v>24.474</v>
       </c>
       <c r="AC228" t="n">
-        <v>11.759</v>
+        <v>11.449</v>
       </c>
       <c r="AD228" t="n">
-        <v>17.55</v>
+        <v>17.015</v>
       </c>
       <c r="AE228" t="n">
-        <v>10.586</v>
+        <v>10.425</v>
       </c>
       <c r="AF228" t="n">
-        <v>21.955</v>
+        <v>21.833</v>
       </c>
       <c r="AG228" t="n">
-        <v>13.218</v>
+        <v>13.104</v>
       </c>
       <c r="AH228" t="n">
-        <v>6.695</v>
+        <v>6.648</v>
       </c>
       <c r="AI228" t="n">
-        <v>3.05</v>
+        <v>3.279</v>
       </c>
       <c r="AJ228" t="n">
-        <v>16.395</v>
+        <v>16.283</v>
       </c>
       <c r="AK228" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AL228" t="n">
-        <v>-6.6</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="229">
@@ -27986,22 +27986,22 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F230" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G230" t="b">
         <v>1</v>
       </c>
       <c r="H230" t="n">
-        <v>1460.137</v>
+        <v>1455.328</v>
       </c>
       <c r="I230" t="n">
-        <v>2.001</v>
+        <v>1.8991</v>
       </c>
       <c r="J230" t="n">
-        <v>1413.3</v>
+        <v>1416</v>
       </c>
       <c r="K230" t="n">
         <v>141</v>
@@ -28022,70 +28022,70 @@
         <v>136</v>
       </c>
       <c r="Q230" t="n">
-        <v>105.768</v>
+        <v>105.468</v>
       </c>
       <c r="R230" t="n">
-        <v>101.475</v>
+        <v>101.563</v>
       </c>
       <c r="S230" t="n">
-        <v>4.293</v>
+        <v>3.905</v>
       </c>
       <c r="T230" t="n">
-        <v>0.25758</v>
+        <v>0.25082</v>
       </c>
       <c r="U230" t="n">
-        <v>0.16607</v>
+        <v>0.17033</v>
       </c>
       <c r="V230" t="n">
-        <v>74.06999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="W230" t="n">
-        <v>71.12</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="X230" t="n">
-        <v>0.6321</v>
+        <v>0.6034</v>
       </c>
       <c r="Y230" t="n">
-        <v>26.207</v>
+        <v>26.13</v>
       </c>
       <c r="Z230" t="n">
-        <v>57.532</v>
+        <v>57.116</v>
       </c>
       <c r="AA230" t="n">
-        <v>6.582</v>
+        <v>6.776</v>
       </c>
       <c r="AB230" t="n">
-        <v>19.635</v>
+        <v>19.889</v>
       </c>
       <c r="AC230" t="n">
-        <v>15.077</v>
+        <v>15.006</v>
       </c>
       <c r="AD230" t="n">
-        <v>21.512</v>
+        <v>21.361</v>
       </c>
       <c r="AE230" t="n">
-        <v>8.728999999999999</v>
+        <v>8.502000000000001</v>
       </c>
       <c r="AF230" t="n">
-        <v>24.197</v>
+        <v>24.469</v>
       </c>
       <c r="AG230" t="n">
-        <v>13.569</v>
+        <v>13.485</v>
       </c>
       <c r="AH230" t="n">
-        <v>7.271</v>
+        <v>7.082</v>
       </c>
       <c r="AI230" t="n">
-        <v>3.803</v>
+        <v>3.698</v>
       </c>
       <c r="AJ230" t="n">
-        <v>19.849</v>
+        <v>19.823</v>
       </c>
       <c r="AK230" t="n">
-        <v>-0.4</v>
+        <v>1.4</v>
       </c>
       <c r="AL230" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="231">
@@ -28106,22 +28106,22 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F231" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G231" t="b">
         <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>1254.158</v>
+        <v>1256.904</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.9032</v>
+        <v>-0.8365</v>
       </c>
       <c r="J231" t="n">
-        <v>1390.4</v>
+        <v>1386</v>
       </c>
       <c r="K231" t="n">
         <v>312</v>
@@ -28142,70 +28142,70 @@
         <v>316</v>
       </c>
       <c r="Q231" t="n">
-        <v>103.807</v>
+        <v>103.466</v>
       </c>
       <c r="R231" t="n">
-        <v>108.994</v>
+        <v>108.039</v>
       </c>
       <c r="S231" t="n">
-        <v>-5.186</v>
+        <v>-4.573</v>
       </c>
       <c r="T231" t="n">
-        <v>0.27659</v>
+        <v>0.27693</v>
       </c>
       <c r="U231" t="n">
-        <v>0.15535</v>
+        <v>0.1529</v>
       </c>
       <c r="V231" t="n">
-        <v>76.45</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="W231" t="n">
-        <v>80.90000000000001</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="X231" t="n">
-        <v>0.3773</v>
+        <v>0.399</v>
       </c>
       <c r="Y231" t="n">
-        <v>25.355</v>
+        <v>25.172</v>
       </c>
       <c r="Z231" t="n">
-        <v>59.747</v>
+        <v>59.742</v>
       </c>
       <c r="AA231" t="n">
-        <v>6.176</v>
+        <v>5.97</v>
       </c>
       <c r="AB231" t="n">
-        <v>18.689</v>
+        <v>18.556</v>
       </c>
       <c r="AC231" t="n">
-        <v>19.56</v>
+        <v>19.682</v>
       </c>
       <c r="AD231" t="n">
-        <v>25.853</v>
+        <v>26.01</v>
       </c>
       <c r="AE231" t="n">
-        <v>8.827999999999999</v>
+        <v>8.914</v>
       </c>
       <c r="AF231" t="n">
-        <v>22.073</v>
+        <v>22.283</v>
       </c>
       <c r="AG231" t="n">
-        <v>11.165</v>
+        <v>11.106</v>
       </c>
       <c r="AH231" t="n">
-        <v>7.333</v>
+        <v>7.172</v>
       </c>
       <c r="AI231" t="n">
-        <v>4.912</v>
+        <v>4.848</v>
       </c>
       <c r="AJ231" t="n">
-        <v>19.941</v>
+        <v>19.919</v>
       </c>
       <c r="AK231" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AL231" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="232">
@@ -30986,22 +30986,22 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F255" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G255" t="b">
         <v>1</v>
       </c>
       <c r="H255" t="n">
-        <v>1787.889</v>
+        <v>1782.784</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2548</v>
+        <v>0.0374</v>
       </c>
       <c r="J255" t="n">
-        <v>1580.2</v>
+        <v>1596.2</v>
       </c>
       <c r="K255" t="n">
         <v>37</v>
@@ -31022,70 +31022,70 @@
         <v>42</v>
       </c>
       <c r="Q255" t="n">
-        <v>117.903</v>
+        <v>117.619</v>
       </c>
       <c r="R255" t="n">
-        <v>103.181</v>
+        <v>104.107</v>
       </c>
       <c r="S255" t="n">
-        <v>14.722</v>
+        <v>13.513</v>
       </c>
       <c r="T255" t="n">
-        <v>0.34454</v>
+        <v>0.35044</v>
       </c>
       <c r="U255" t="n">
-        <v>0.15002</v>
+        <v>0.14983</v>
       </c>
       <c r="V255" t="n">
-        <v>83.25</v>
+        <v>82.72</v>
       </c>
       <c r="W255" t="n">
-        <v>72.83</v>
+        <v>73.08</v>
       </c>
       <c r="X255" t="n">
-        <v>0.7832</v>
+        <v>0.7512</v>
       </c>
       <c r="Y255" t="n">
-        <v>30.101</v>
+        <v>29.996</v>
       </c>
       <c r="Z255" t="n">
-        <v>64.126</v>
+        <v>64.364</v>
       </c>
       <c r="AA255" t="n">
-        <v>9.964</v>
+        <v>9.962</v>
       </c>
       <c r="AB255" t="n">
-        <v>28.64</v>
+        <v>28.922</v>
       </c>
       <c r="AC255" t="n">
-        <v>12.881</v>
+        <v>12.619</v>
       </c>
       <c r="AD255" t="n">
-        <v>17.08</v>
+        <v>16.714</v>
       </c>
       <c r="AE255" t="n">
-        <v>11.628</v>
+        <v>11.947</v>
       </c>
       <c r="AF255" t="n">
-        <v>21.59</v>
+        <v>21.511</v>
       </c>
       <c r="AG255" t="n">
-        <v>16.747</v>
+        <v>16.636</v>
       </c>
       <c r="AH255" t="n">
-        <v>8.648999999999999</v>
+        <v>8.653</v>
       </c>
       <c r="AI255" t="n">
-        <v>3.721</v>
+        <v>3.614</v>
       </c>
       <c r="AJ255" t="n">
-        <v>19.468</v>
+        <v>19.519</v>
       </c>
       <c r="AK255" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="AL255" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="256">
@@ -31706,22 +31706,22 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F261" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G261" t="b">
         <v>1</v>
       </c>
       <c r="H261" t="n">
-        <v>1563.199</v>
+        <v>1565.83</v>
       </c>
       <c r="I261" t="n">
-        <v>3.2741</v>
+        <v>3.2279</v>
       </c>
       <c r="J261" t="n">
-        <v>1383.2</v>
+        <v>1383.6</v>
       </c>
       <c r="K261" t="n">
         <v>89</v>
@@ -31742,70 +31742,70 @@
         <v>86</v>
       </c>
       <c r="Q261" t="n">
-        <v>113.578</v>
+        <v>112.792</v>
       </c>
       <c r="R261" t="n">
-        <v>98.857</v>
+        <v>98.536</v>
       </c>
       <c r="S261" t="n">
-        <v>14.721</v>
+        <v>14.255</v>
       </c>
       <c r="T261" t="n">
-        <v>0.31095</v>
+        <v>0.30825</v>
       </c>
       <c r="U261" t="n">
-        <v>0.13359</v>
+        <v>0.13209</v>
       </c>
       <c r="V261" t="n">
-        <v>75.69</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="W261" t="n">
-        <v>65.92</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="X261" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8678</v>
       </c>
       <c r="Y261" t="n">
-        <v>27.102</v>
+        <v>27.016</v>
       </c>
       <c r="Z261" t="n">
-        <v>60.475</v>
+        <v>60.371</v>
       </c>
       <c r="AA261" t="n">
-        <v>8.823</v>
+        <v>8.635</v>
       </c>
       <c r="AB261" t="n">
-        <v>24.137</v>
+        <v>23.799</v>
       </c>
       <c r="AC261" t="n">
-        <v>12.665</v>
+        <v>12.369</v>
       </c>
       <c r="AD261" t="n">
-        <v>18.484</v>
+        <v>18.162</v>
       </c>
       <c r="AE261" t="n">
-        <v>10.761</v>
+        <v>10.56</v>
       </c>
       <c r="AF261" t="n">
-        <v>23.525</v>
+        <v>23.296</v>
       </c>
       <c r="AG261" t="n">
-        <v>13.307</v>
+        <v>13.172</v>
       </c>
       <c r="AH261" t="n">
-        <v>6.587</v>
+        <v>6.761</v>
       </c>
       <c r="AI261" t="n">
-        <v>3.59</v>
+        <v>3.603</v>
       </c>
       <c r="AJ261" t="n">
-        <v>16.059</v>
+        <v>15.858</v>
       </c>
       <c r="AK261" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AL261" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="262">
@@ -31826,22 +31826,22 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F262" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G262" t="b">
         <v>1</v>
       </c>
       <c r="H262" t="n">
-        <v>1471.282</v>
+        <v>1478.017</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9399</v>
+        <v>0.9489</v>
       </c>
       <c r="J262" t="n">
-        <v>1426.7</v>
+        <v>1430.3</v>
       </c>
       <c r="K262" t="n">
         <v>195</v>
@@ -31862,70 +31862,70 @@
         <v>188</v>
       </c>
       <c r="Q262" t="n">
-        <v>110.162</v>
+        <v>109.727</v>
       </c>
       <c r="R262" t="n">
-        <v>102.353</v>
+        <v>101.773</v>
       </c>
       <c r="S262" t="n">
-        <v>7.809</v>
+        <v>7.954</v>
       </c>
       <c r="T262" t="n">
-        <v>0.27995</v>
+        <v>0.27993</v>
       </c>
       <c r="U262" t="n">
-        <v>0.15315</v>
+        <v>0.1508</v>
       </c>
       <c r="V262" t="n">
-        <v>70.79000000000001</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="W262" t="n">
-        <v>65.97</v>
+        <v>65.55</v>
       </c>
       <c r="X262" t="n">
-        <v>0.6706</v>
+        <v>0.68</v>
       </c>
       <c r="Y262" t="n">
-        <v>25.408</v>
+        <v>25.087</v>
       </c>
       <c r="Z262" t="n">
-        <v>55.324</v>
+        <v>55.469</v>
       </c>
       <c r="AA262" t="n">
-        <v>5.466</v>
+        <v>5.607</v>
       </c>
       <c r="AB262" t="n">
-        <v>17.719</v>
+        <v>18.258</v>
       </c>
       <c r="AC262" t="n">
-        <v>14.508</v>
+        <v>14.276</v>
       </c>
       <c r="AD262" t="n">
-        <v>18.962</v>
+        <v>18.644</v>
       </c>
       <c r="AE262" t="n">
-        <v>9.012</v>
+        <v>8.92</v>
       </c>
       <c r="AF262" t="n">
-        <v>22.734</v>
+        <v>22.491</v>
       </c>
       <c r="AG262" t="n">
-        <v>13.478</v>
+        <v>13.247</v>
       </c>
       <c r="AH262" t="n">
-        <v>5.875</v>
+        <v>5.993</v>
       </c>
       <c r="AI262" t="n">
-        <v>2.922</v>
+        <v>3.233</v>
       </c>
       <c r="AJ262" t="n">
-        <v>13.803</v>
+        <v>13.935</v>
       </c>
       <c r="AK262" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AL262" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263">
@@ -31946,22 +31946,22 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F263" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G263" t="b">
         <v>1</v>
       </c>
       <c r="H263" t="n">
-        <v>1738.259</v>
+        <v>1744.545</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9109</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="J263" t="n">
-        <v>1643.1</v>
+        <v>1641</v>
       </c>
       <c r="K263" t="n">
         <v>43</v>
@@ -31982,70 +31982,70 @@
         <v>39</v>
       </c>
       <c r="Q263" t="n">
-        <v>118.278</v>
+        <v>119.024</v>
       </c>
       <c r="R263" t="n">
-        <v>110.333</v>
+        <v>110.021</v>
       </c>
       <c r="S263" t="n">
-        <v>7.945</v>
+        <v>9.003</v>
       </c>
       <c r="T263" t="n">
-        <v>0.30642</v>
+        <v>0.31054</v>
       </c>
       <c r="U263" t="n">
-        <v>0.15281</v>
+        <v>0.15051</v>
       </c>
       <c r="V263" t="n">
-        <v>84.92</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="W263" t="n">
-        <v>78.53</v>
+        <v>78</v>
       </c>
       <c r="X263" t="n">
-        <v>0.6058</v>
+        <v>0.629</v>
       </c>
       <c r="Y263" t="n">
-        <v>30.838</v>
+        <v>31.001</v>
       </c>
       <c r="Z263" t="n">
-        <v>62.684</v>
+        <v>63.077</v>
       </c>
       <c r="AA263" t="n">
-        <v>8.397</v>
+        <v>8.465</v>
       </c>
       <c r="AB263" t="n">
-        <v>22.2</v>
+        <v>22.551</v>
       </c>
       <c r="AC263" t="n">
-        <v>14.846</v>
+        <v>14.574</v>
       </c>
       <c r="AD263" t="n">
-        <v>20.061</v>
+        <v>19.593</v>
       </c>
       <c r="AE263" t="n">
-        <v>10.728</v>
+        <v>11.024</v>
       </c>
       <c r="AF263" t="n">
-        <v>24.487</v>
+        <v>24.536</v>
       </c>
       <c r="AG263" t="n">
-        <v>16.994</v>
+        <v>17.187</v>
       </c>
       <c r="AH263" t="n">
-        <v>7.128</v>
+        <v>7.165</v>
       </c>
       <c r="AI263" t="n">
-        <v>3.713</v>
+        <v>3.555</v>
       </c>
       <c r="AJ263" t="n">
-        <v>17.281</v>
+        <v>16.925</v>
       </c>
       <c r="AK263" t="n">
-        <v>-4.2</v>
+        <v>-5.6</v>
       </c>
       <c r="AL263" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="264">
@@ -33746,22 +33746,22 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F278" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G278" t="b">
         <v>1</v>
       </c>
       <c r="H278" t="n">
-        <v>1750.036</v>
+        <v>1734.155</v>
       </c>
       <c r="I278" t="n">
-        <v>2.6234</v>
+        <v>2.5276</v>
       </c>
       <c r="J278" t="n">
-        <v>1628.4</v>
+        <v>1622.5</v>
       </c>
       <c r="K278" t="n">
         <v>59</v>
@@ -33782,70 +33782,70 @@
         <v>59</v>
       </c>
       <c r="Q278" t="n">
-        <v>112.312</v>
+        <v>111.896</v>
       </c>
       <c r="R278" t="n">
-        <v>107.605</v>
+        <v>107.42</v>
       </c>
       <c r="S278" t="n">
-        <v>4.707</v>
+        <v>4.476</v>
       </c>
       <c r="T278" t="n">
-        <v>0.31886</v>
+        <v>0.3248</v>
       </c>
       <c r="U278" t="n">
-        <v>0.14331</v>
+        <v>0.14394</v>
       </c>
       <c r="V278" t="n">
-        <v>76.48999999999999</v>
+        <v>75.83</v>
       </c>
       <c r="W278" t="n">
-        <v>73.09999999999999</v>
+        <v>72.59</v>
       </c>
       <c r="X278" t="n">
-        <v>0.6493</v>
+        <v>0.6183</v>
       </c>
       <c r="Y278" t="n">
-        <v>25.826</v>
+        <v>25.836</v>
       </c>
       <c r="Z278" t="n">
-        <v>58.977</v>
+        <v>59.168</v>
       </c>
       <c r="AA278" t="n">
-        <v>9.278</v>
+        <v>8.997</v>
       </c>
       <c r="AB278" t="n">
-        <v>26.13</v>
+        <v>25.718</v>
       </c>
       <c r="AC278" t="n">
-        <v>15.557</v>
+        <v>15.202</v>
       </c>
       <c r="AD278" t="n">
-        <v>21.299</v>
+        <v>20.902</v>
       </c>
       <c r="AE278" t="n">
-        <v>10.09</v>
+        <v>10.448</v>
       </c>
       <c r="AF278" t="n">
-        <v>21.319</v>
+        <v>21.309</v>
       </c>
       <c r="AG278" t="n">
-        <v>11.977</v>
+        <v>11.875</v>
       </c>
       <c r="AH278" t="n">
-        <v>8.003</v>
+        <v>7.927</v>
       </c>
       <c r="AI278" t="n">
-        <v>3.562</v>
+        <v>3.598</v>
       </c>
       <c r="AJ278" t="n">
-        <v>17.8</v>
+        <v>17.492</v>
       </c>
       <c r="AK278" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AL278" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="279">
@@ -34106,22 +34106,22 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F281" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G281" t="b">
         <v>1</v>
       </c>
       <c r="H281" t="n">
-        <v>1583.107</v>
+        <v>1576.822</v>
       </c>
       <c r="I281" t="n">
-        <v>1.0611</v>
+        <v>0.8467</v>
       </c>
       <c r="J281" t="n">
-        <v>1659</v>
+        <v>1664</v>
       </c>
       <c r="K281" t="n">
         <v>80</v>
@@ -34142,70 +34142,70 @@
         <v>83</v>
       </c>
       <c r="Q281" t="n">
-        <v>108.107</v>
+        <v>107.955</v>
       </c>
       <c r="R281" t="n">
-        <v>106.277</v>
+        <v>107.203</v>
       </c>
       <c r="S281" t="n">
-        <v>1.83</v>
+        <v>0.752</v>
       </c>
       <c r="T281" t="n">
-        <v>0.2758</v>
+        <v>0.27788</v>
       </c>
       <c r="U281" t="n">
-        <v>0.15245</v>
+        <v>0.15298</v>
       </c>
       <c r="V281" t="n">
-        <v>75.12</v>
+        <v>74.94</v>
       </c>
       <c r="W281" t="n">
-        <v>73.84</v>
+        <v>74.38</v>
       </c>
       <c r="X281" t="n">
-        <v>0.4783</v>
+        <v>0.4637</v>
       </c>
       <c r="Y281" t="n">
-        <v>27.177</v>
+        <v>27.258</v>
       </c>
       <c r="Z281" t="n">
-        <v>58.458</v>
+        <v>58.641</v>
       </c>
       <c r="AA281" t="n">
-        <v>7.096</v>
+        <v>7.176</v>
       </c>
       <c r="AB281" t="n">
-        <v>21.417</v>
+        <v>21.913</v>
       </c>
       <c r="AC281" t="n">
-        <v>13.672</v>
+        <v>13.243</v>
       </c>
       <c r="AD281" t="n">
-        <v>20.986</v>
+        <v>20.448</v>
       </c>
       <c r="AE281" t="n">
-        <v>8.776999999999999</v>
+        <v>8.824999999999999</v>
       </c>
       <c r="AF281" t="n">
-        <v>22.959</v>
+        <v>22.855</v>
       </c>
       <c r="AG281" t="n">
-        <v>12.71</v>
+        <v>12.878</v>
       </c>
       <c r="AH281" t="n">
-        <v>6.188</v>
+        <v>6.175</v>
       </c>
       <c r="AI281" t="n">
-        <v>5.988</v>
+        <v>5.875</v>
       </c>
       <c r="AJ281" t="n">
-        <v>16.545</v>
+        <v>16.411</v>
       </c>
       <c r="AK281" t="n">
-        <v>-14.4</v>
+        <v>-10.4</v>
       </c>
       <c r="AL281" t="n">
-        <v>-7.3</v>
+        <v>-10.4</v>
       </c>
     </row>
     <row r="282">
@@ -34226,22 +34226,22 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F282" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G282" t="b">
         <v>1</v>
       </c>
       <c r="H282" t="n">
-        <v>1378.544</v>
+        <v>1375.912</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.4106</v>
+        <v>-0.3578</v>
       </c>
       <c r="J282" t="n">
-        <v>1424</v>
+        <v>1430.4</v>
       </c>
       <c r="K282" t="n">
         <v>180</v>
@@ -34262,67 +34262,67 @@
         <v>196</v>
       </c>
       <c r="Q282" t="n">
-        <v>103.004</v>
+        <v>102.534</v>
       </c>
       <c r="R282" t="n">
-        <v>103.532</v>
+        <v>103.354</v>
       </c>
       <c r="S282" t="n">
-        <v>-0.528</v>
+        <v>-0.821</v>
       </c>
       <c r="T282" t="n">
-        <v>0.29593</v>
+        <v>0.28962</v>
       </c>
       <c r="U282" t="n">
-        <v>0.18515</v>
+        <v>0.18835</v>
       </c>
       <c r="V282" t="n">
-        <v>68.93000000000001</v>
+        <v>68.44</v>
       </c>
       <c r="W282" t="n">
-        <v>69.64</v>
+        <v>69.31</v>
       </c>
       <c r="X282" t="n">
-        <v>0.504</v>
+        <v>0.4792</v>
       </c>
       <c r="Y282" t="n">
-        <v>23.89</v>
+        <v>23.78</v>
       </c>
       <c r="Z282" t="n">
-        <v>54.417</v>
+        <v>54.036</v>
       </c>
       <c r="AA282" t="n">
-        <v>5.926</v>
+        <v>5.939</v>
       </c>
       <c r="AB282" t="n">
-        <v>17.052</v>
+        <v>16.951</v>
       </c>
       <c r="AC282" t="n">
-        <v>15.227</v>
+        <v>14.94</v>
       </c>
       <c r="AD282" t="n">
-        <v>22.601</v>
+        <v>22.15</v>
       </c>
       <c r="AE282" t="n">
-        <v>9.49</v>
+        <v>9.286</v>
       </c>
       <c r="AF282" t="n">
-        <v>21.768</v>
+        <v>22.094</v>
       </c>
       <c r="AG282" t="n">
-        <v>12.032</v>
+        <v>12.083</v>
       </c>
       <c r="AH282" t="n">
-        <v>7.09</v>
+        <v>6.978</v>
       </c>
       <c r="AI282" t="n">
-        <v>2.646</v>
+        <v>2.616</v>
       </c>
       <c r="AJ282" t="n">
-        <v>20.882</v>
+        <v>20.446</v>
       </c>
       <c r="AK282" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AL282" t="n">
         <v>2.9</v>
@@ -36146,22 +36146,22 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F298" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G298" t="b">
         <v>1</v>
       </c>
       <c r="H298" t="n">
-        <v>1397.379</v>
+        <v>1395.275</v>
       </c>
       <c r="I298" t="n">
-        <v>1.648</v>
+        <v>1.687</v>
       </c>
       <c r="J298" t="n">
-        <v>1425</v>
+        <v>1436.7</v>
       </c>
       <c r="K298" t="n">
         <v>124</v>
@@ -36182,70 +36182,70 @@
         <v>134</v>
       </c>
       <c r="Q298" t="n">
-        <v>110.546</v>
+        <v>109.781</v>
       </c>
       <c r="R298" t="n">
-        <v>105.058</v>
+        <v>104.83</v>
       </c>
       <c r="S298" t="n">
-        <v>5.488</v>
+        <v>4.951</v>
       </c>
       <c r="T298" t="n">
-        <v>0.23978</v>
+        <v>0.23747</v>
       </c>
       <c r="U298" t="n">
-        <v>0.17131</v>
+        <v>0.1754</v>
       </c>
       <c r="V298" t="n">
-        <v>73.62</v>
+        <v>73.78</v>
       </c>
       <c r="W298" t="n">
-        <v>70.15000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="X298" t="n">
-        <v>0.5697</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="Y298" t="n">
-        <v>26.233</v>
+        <v>26.192</v>
       </c>
       <c r="Z298" t="n">
-        <v>55.913</v>
+        <v>56.051</v>
       </c>
       <c r="AA298" t="n">
-        <v>8.988</v>
+        <v>9.006</v>
       </c>
       <c r="AB298" t="n">
-        <v>24.298</v>
+        <v>24.519</v>
       </c>
       <c r="AC298" t="n">
-        <v>12.166</v>
+        <v>12.391</v>
       </c>
       <c r="AD298" t="n">
-        <v>15.939</v>
+        <v>16.237</v>
       </c>
       <c r="AE298" t="n">
-        <v>7.781</v>
+        <v>7.808</v>
       </c>
       <c r="AF298" t="n">
-        <v>23.357</v>
+        <v>23.968</v>
       </c>
       <c r="AG298" t="n">
-        <v>15.796</v>
+        <v>15.66</v>
       </c>
       <c r="AH298" t="n">
-        <v>5.868</v>
+        <v>5.949</v>
       </c>
       <c r="AI298" t="n">
-        <v>2.801</v>
+        <v>2.769</v>
       </c>
       <c r="AJ298" t="n">
-        <v>18.218</v>
+        <v>18.378</v>
       </c>
       <c r="AK298" t="n">
-        <v>10.4</v>
+        <v>5.4</v>
       </c>
       <c r="AL298" t="n">
-        <v>10.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="299">
@@ -37346,19 +37346,19 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F308" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G308" t="b">
         <v>1</v>
       </c>
       <c r="H308" t="n">
-        <v>1391.718</v>
+        <v>1393.666</v>
       </c>
       <c r="I308" t="n">
-        <v>1.2162</v>
+        <v>1.2859</v>
       </c>
       <c r="J308" t="n">
         <v>1364.8</v>
@@ -37382,70 +37382,70 @@
         <v>205</v>
       </c>
       <c r="Q308" t="n">
-        <v>112.507</v>
+        <v>113.445</v>
       </c>
       <c r="R308" t="n">
-        <v>102.244</v>
+        <v>102.317</v>
       </c>
       <c r="S308" t="n">
-        <v>10.263</v>
+        <v>11.128</v>
       </c>
       <c r="T308" t="n">
-        <v>0.21264</v>
+        <v>0.21682</v>
       </c>
       <c r="U308" t="n">
-        <v>0.13609</v>
+        <v>0.13443</v>
       </c>
       <c r="V308" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="W308" t="n">
-        <v>68.26000000000001</v>
+        <v>68.28</v>
       </c>
       <c r="X308" t="n">
-        <v>0.7166</v>
+        <v>0.7262</v>
       </c>
       <c r="Y308" t="n">
-        <v>26.469</v>
+        <v>26.737</v>
       </c>
       <c r="Z308" t="n">
-        <v>56.436</v>
+        <v>56.653</v>
       </c>
       <c r="AA308" t="n">
-        <v>7.792</v>
+        <v>7.802</v>
       </c>
       <c r="AB308" t="n">
-        <v>21.871</v>
+        <v>21.746</v>
       </c>
       <c r="AC308" t="n">
-        <v>14.272</v>
+        <v>14.323</v>
       </c>
       <c r="AD308" t="n">
-        <v>18.709</v>
+        <v>18.851</v>
       </c>
       <c r="AE308" t="n">
-        <v>7.082</v>
+        <v>7.269</v>
       </c>
       <c r="AF308" t="n">
-        <v>25.654</v>
+        <v>25.658</v>
       </c>
       <c r="AG308" t="n">
-        <v>12.027</v>
+        <v>12.159</v>
       </c>
       <c r="AH308" t="n">
-        <v>4.709</v>
+        <v>4.935</v>
       </c>
       <c r="AI308" t="n">
-        <v>2.338</v>
+        <v>2.384</v>
       </c>
       <c r="AJ308" t="n">
-        <v>13.744</v>
+        <v>13.677</v>
       </c>
       <c r="AK308" t="n">
-        <v>18.8</v>
+        <v>22.4</v>
       </c>
       <c r="AL308" t="n">
-        <v>16.5</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="309">
@@ -38306,22 +38306,22 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F316" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G316" t="b">
         <v>1</v>
       </c>
       <c r="H316" t="n">
-        <v>1521.567</v>
+        <v>1516.967</v>
       </c>
       <c r="I316" t="n">
-        <v>-4.5566</v>
+        <v>-4.4618</v>
       </c>
       <c r="J316" t="n">
-        <v>1690.8</v>
+        <v>1692.4</v>
       </c>
       <c r="K316" t="n">
         <v>127</v>
@@ -38342,70 +38342,70 @@
         <v>129</v>
       </c>
       <c r="Q316" t="n">
-        <v>108.837</v>
+        <v>108.311</v>
       </c>
       <c r="R316" t="n">
-        <v>116.367</v>
+        <v>115.527</v>
       </c>
       <c r="S316" t="n">
-        <v>-7.53</v>
+        <v>-7.216</v>
       </c>
       <c r="T316" t="n">
-        <v>0.27999</v>
+        <v>0.28027</v>
       </c>
       <c r="U316" t="n">
-        <v>0.16198</v>
+        <v>0.15898</v>
       </c>
       <c r="V316" t="n">
-        <v>74.62</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="W316" t="n">
-        <v>79.59</v>
+        <v>79.02</v>
       </c>
       <c r="X316" t="n">
-        <v>0.3182</v>
+        <v>0.3086</v>
       </c>
       <c r="Y316" t="n">
-        <v>26.645</v>
+        <v>26.456</v>
       </c>
       <c r="Z316" t="n">
-        <v>58.086</v>
+        <v>58.39</v>
       </c>
       <c r="AA316" t="n">
-        <v>7.795</v>
+        <v>7.684</v>
       </c>
       <c r="AB316" t="n">
-        <v>21.891</v>
+        <v>21.826</v>
       </c>
       <c r="AC316" t="n">
-        <v>13.532</v>
+        <v>13.642</v>
       </c>
       <c r="AD316" t="n">
-        <v>18.445</v>
+        <v>18.438</v>
       </c>
       <c r="AE316" t="n">
-        <v>8.641</v>
+        <v>8.778</v>
       </c>
       <c r="AF316" t="n">
-        <v>21.941</v>
+        <v>22.236</v>
       </c>
       <c r="AG316" t="n">
-        <v>13.823</v>
+        <v>13.641</v>
       </c>
       <c r="AH316" t="n">
-        <v>5.386</v>
+        <v>5.314</v>
       </c>
       <c r="AI316" t="n">
-        <v>3.445</v>
+        <v>3.388</v>
       </c>
       <c r="AJ316" t="n">
-        <v>16.164</v>
+        <v>16.142</v>
       </c>
       <c r="AK316" t="n">
-        <v>-14.2</v>
+        <v>-15.2</v>
       </c>
       <c r="AL316" t="n">
-        <v>-10.4</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="317">
@@ -39146,22 +39146,22 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F323" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G323" t="b">
         <v>1</v>
       </c>
       <c r="H323" t="n">
-        <v>1468.715</v>
+        <v>1469.955</v>
       </c>
       <c r="I323" t="n">
-        <v>-1.6744</v>
+        <v>-1.5409</v>
       </c>
       <c r="J323" t="n">
-        <v>1392.4</v>
+        <v>1389.6</v>
       </c>
       <c r="K323" t="n">
         <v>235</v>
@@ -39182,70 +39182,70 @@
         <v>223</v>
       </c>
       <c r="Q323" t="n">
-        <v>112.136</v>
+        <v>111.419</v>
       </c>
       <c r="R323" t="n">
-        <v>105.782</v>
+        <v>105.017</v>
       </c>
       <c r="S323" t="n">
-        <v>6.353</v>
+        <v>6.402</v>
       </c>
       <c r="T323" t="n">
-        <v>0.24151</v>
+        <v>0.24098</v>
       </c>
       <c r="U323" t="n">
-        <v>0.13983</v>
+        <v>0.14061</v>
       </c>
       <c r="V323" t="n">
-        <v>72.91</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="W323" t="n">
-        <v>68.94</v>
+        <v>68.44</v>
       </c>
       <c r="X323" t="n">
-        <v>0.6372</v>
+        <v>0.6486</v>
       </c>
       <c r="Y323" t="n">
-        <v>25.757</v>
+        <v>25.619</v>
       </c>
       <c r="Z323" t="n">
-        <v>55.927</v>
+        <v>55.958</v>
       </c>
       <c r="AA323" t="n">
-        <v>8.505000000000001</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="AB323" t="n">
-        <v>24.915</v>
+        <v>24.968</v>
       </c>
       <c r="AC323" t="n">
-        <v>12.891</v>
+        <v>12.779</v>
       </c>
       <c r="AD323" t="n">
-        <v>17.811</v>
+        <v>17.651</v>
       </c>
       <c r="AE323" t="n">
-        <v>7.825</v>
+        <v>7.84</v>
       </c>
       <c r="AF323" t="n">
-        <v>24.837</v>
+        <v>24.956</v>
       </c>
       <c r="AG323" t="n">
-        <v>12.583</v>
+        <v>12.45</v>
       </c>
       <c r="AH323" t="n">
-        <v>4.471</v>
+        <v>4.582</v>
       </c>
       <c r="AI323" t="n">
-        <v>2.616</v>
+        <v>2.69</v>
       </c>
       <c r="AJ323" t="n">
-        <v>17.153</v>
+        <v>16.878</v>
       </c>
       <c r="AK323" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AL323" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="324">
@@ -39506,22 +39506,22 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F326" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G326" t="b">
         <v>1</v>
       </c>
       <c r="H326" t="n">
-        <v>1713.547</v>
+        <v>1700.034</v>
       </c>
       <c r="I326" t="n">
-        <v>5.7826</v>
+        <v>5.3784</v>
       </c>
       <c r="J326" t="n">
-        <v>1665</v>
+        <v>1660.6</v>
       </c>
       <c r="K326" t="n">
         <v>56</v>
@@ -39542,70 +39542,70 @@
         <v>53</v>
       </c>
       <c r="Q326" t="n">
-        <v>112.338</v>
+        <v>112.713</v>
       </c>
       <c r="R326" t="n">
-        <v>106.803</v>
+        <v>107.616</v>
       </c>
       <c r="S326" t="n">
-        <v>5.536</v>
+        <v>5.097</v>
       </c>
       <c r="T326" t="n">
-        <v>0.29753</v>
+        <v>0.29419</v>
       </c>
       <c r="U326" t="n">
-        <v>0.14583</v>
+        <v>0.14469</v>
       </c>
       <c r="V326" t="n">
-        <v>78.36</v>
+        <v>78.91</v>
       </c>
       <c r="W326" t="n">
-        <v>74.25</v>
+        <v>75.13</v>
       </c>
       <c r="X326" t="n">
-        <v>0.6045</v>
+        <v>0.5863</v>
       </c>
       <c r="Y326" t="n">
-        <v>27.368</v>
+        <v>27.501</v>
       </c>
       <c r="Z326" t="n">
-        <v>60.441</v>
+        <v>60.358</v>
       </c>
       <c r="AA326" t="n">
-        <v>8.573</v>
+        <v>8.555</v>
       </c>
       <c r="AB326" t="n">
-        <v>24.205</v>
+        <v>24.006</v>
       </c>
       <c r="AC326" t="n">
-        <v>15.055</v>
+        <v>15.614</v>
       </c>
       <c r="AD326" t="n">
-        <v>20.391</v>
+        <v>20.867</v>
       </c>
       <c r="AE326" t="n">
-        <v>9.723000000000001</v>
+        <v>9.561</v>
       </c>
       <c r="AF326" t="n">
-        <v>22.705</v>
+        <v>22.666</v>
       </c>
       <c r="AG326" t="n">
-        <v>14.409</v>
+        <v>14.414</v>
       </c>
       <c r="AH326" t="n">
-        <v>6.577</v>
+        <v>6.537</v>
       </c>
       <c r="AI326" t="n">
-        <v>3.127</v>
+        <v>3.254</v>
       </c>
       <c r="AJ326" t="n">
-        <v>16.968</v>
+        <v>17.23</v>
       </c>
       <c r="AK326" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AL326" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="327">
@@ -40346,22 +40346,22 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F333" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G333" t="b">
         <v>1</v>
       </c>
       <c r="H333" t="n">
-        <v>1650.782</v>
+        <v>1664.296</v>
       </c>
       <c r="I333" t="n">
-        <v>-3.0285</v>
+        <v>-2.8429</v>
       </c>
       <c r="J333" t="n">
-        <v>1669.7</v>
+        <v>1670.8</v>
       </c>
       <c r="K333" t="n">
         <v>74</v>
@@ -40382,70 +40382,70 @@
         <v>64</v>
       </c>
       <c r="Q333" t="n">
-        <v>112.134</v>
+        <v>112.871</v>
       </c>
       <c r="R333" t="n">
-        <v>109.4</v>
+        <v>109.995</v>
       </c>
       <c r="S333" t="n">
-        <v>2.734</v>
+        <v>2.877</v>
       </c>
       <c r="T333" t="n">
-        <v>0.29088</v>
+        <v>0.29913</v>
       </c>
       <c r="U333" t="n">
-        <v>0.14881</v>
+        <v>0.14976</v>
       </c>
       <c r="V333" t="n">
-        <v>78.89</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="W333" t="n">
-        <v>76.81999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="X333" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5372</v>
       </c>
       <c r="Y333" t="n">
-        <v>26.85</v>
+        <v>26.994</v>
       </c>
       <c r="Z333" t="n">
-        <v>59.882</v>
+        <v>60.373</v>
       </c>
       <c r="AA333" t="n">
-        <v>8.941000000000001</v>
+        <v>8.926</v>
       </c>
       <c r="AB333" t="n">
-        <v>26.277</v>
+        <v>26.222</v>
       </c>
       <c r="AC333" t="n">
-        <v>16.245</v>
+        <v>16.397</v>
       </c>
       <c r="AD333" t="n">
-        <v>21.064</v>
+        <v>21.137</v>
       </c>
       <c r="AE333" t="n">
-        <v>9.090999999999999</v>
+        <v>9.583</v>
       </c>
       <c r="AF333" t="n">
-        <v>22.132</v>
+        <v>22.056</v>
       </c>
       <c r="AG333" t="n">
-        <v>14.318</v>
+        <v>14.309</v>
       </c>
       <c r="AH333" t="n">
-        <v>7.977</v>
+        <v>7.813</v>
       </c>
       <c r="AI333" t="n">
-        <v>3.459</v>
+        <v>3.519</v>
       </c>
       <c r="AJ333" t="n">
-        <v>18.873</v>
+        <v>18.914</v>
       </c>
       <c r="AK333" t="n">
-        <v>-2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AL333" t="n">
-        <v>-1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="334">
@@ -41786,22 +41786,22 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F345" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G345" t="b">
         <v>1</v>
       </c>
       <c r="H345" t="n">
-        <v>1468.688</v>
+        <v>1470.5</v>
       </c>
       <c r="I345" t="n">
-        <v>2.7502</v>
+        <v>2.7419</v>
       </c>
       <c r="J345" t="n">
-        <v>1435.9</v>
+        <v>1431.7</v>
       </c>
       <c r="K345" t="n">
         <v>144</v>
@@ -41822,70 +41822,70 @@
         <v>133</v>
       </c>
       <c r="Q345" t="n">
-        <v>116.218</v>
+        <v>115.44</v>
       </c>
       <c r="R345" t="n">
-        <v>109.523</v>
+        <v>108.906</v>
       </c>
       <c r="S345" t="n">
-        <v>6.695</v>
+        <v>6.534</v>
       </c>
       <c r="T345" t="n">
-        <v>0.29519</v>
+        <v>0.29712</v>
       </c>
       <c r="U345" t="n">
-        <v>0.15692</v>
+        <v>0.15689</v>
       </c>
       <c r="V345" t="n">
-        <v>80.59999999999999</v>
+        <v>79.86</v>
       </c>
       <c r="W345" t="n">
-        <v>75.92</v>
+        <v>75.31</v>
       </c>
       <c r="X345" t="n">
-        <v>0.648</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="Y345" t="n">
-        <v>28.392</v>
+        <v>28.149</v>
       </c>
       <c r="Z345" t="n">
-        <v>58.328</v>
+        <v>58.31</v>
       </c>
       <c r="AA345" t="n">
-        <v>7.208</v>
+        <v>7.071</v>
       </c>
       <c r="AB345" t="n">
-        <v>19.72</v>
+        <v>19.605</v>
       </c>
       <c r="AC345" t="n">
-        <v>16.608</v>
+        <v>16.496</v>
       </c>
       <c r="AD345" t="n">
-        <v>22.12</v>
+        <v>22.185</v>
       </c>
       <c r="AE345" t="n">
-        <v>9.584</v>
+        <v>9.743</v>
       </c>
       <c r="AF345" t="n">
-        <v>22.408</v>
+        <v>22.565</v>
       </c>
       <c r="AG345" t="n">
-        <v>13.352</v>
+        <v>13.233</v>
       </c>
       <c r="AH345" t="n">
-        <v>7.216</v>
+        <v>7.071</v>
       </c>
       <c r="AI345" t="n">
-        <v>4.32</v>
+        <v>4.387</v>
       </c>
       <c r="AJ345" t="n">
-        <v>17.528</v>
+        <v>17.465</v>
       </c>
       <c r="AK345" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AL345" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="346">
@@ -42626,22 +42626,22 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F352" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G352" t="b">
         <v>1</v>
       </c>
       <c r="H352" t="n">
-        <v>1521.436</v>
+        <v>1514.701</v>
       </c>
       <c r="I352" t="n">
-        <v>3.9296</v>
+        <v>3.9292</v>
       </c>
       <c r="J352" t="n">
-        <v>1455.8</v>
+        <v>1455.9</v>
       </c>
       <c r="K352" t="n">
         <v>174</v>
@@ -42662,70 +42662,70 @@
         <v>173</v>
       </c>
       <c r="Q352" t="n">
-        <v>107.026</v>
+        <v>106.305</v>
       </c>
       <c r="R352" t="n">
-        <v>102.734</v>
+        <v>102.787</v>
       </c>
       <c r="S352" t="n">
-        <v>4.291</v>
+        <v>3.517</v>
       </c>
       <c r="T352" t="n">
-        <v>0.26866</v>
+        <v>0.26903</v>
       </c>
       <c r="U352" t="n">
-        <v>0.14365</v>
+        <v>0.14673</v>
       </c>
       <c r="V352" t="n">
-        <v>68.84</v>
+        <v>68.37</v>
       </c>
       <c r="W352" t="n">
-        <v>66.43000000000001</v>
+        <v>66.44</v>
       </c>
       <c r="X352" t="n">
-        <v>0.7005</v>
+        <v>0.6691</v>
       </c>
       <c r="Y352" t="n">
-        <v>22.336</v>
+        <v>22.309</v>
       </c>
       <c r="Z352" t="n">
-        <v>53.281</v>
+        <v>53.342</v>
       </c>
       <c r="AA352" t="n">
-        <v>7.965</v>
+        <v>7.84</v>
       </c>
       <c r="AB352" t="n">
-        <v>24.337</v>
+        <v>24.087</v>
       </c>
       <c r="AC352" t="n">
-        <v>16.204</v>
+        <v>16.313</v>
       </c>
       <c r="AD352" t="n">
-        <v>20.564</v>
+        <v>20.622</v>
       </c>
       <c r="AE352" t="n">
-        <v>6.993</v>
+        <v>7.291</v>
       </c>
       <c r="AF352" t="n">
-        <v>19.096</v>
+        <v>19.756</v>
       </c>
       <c r="AG352" t="n">
-        <v>12.527</v>
+        <v>12.564</v>
       </c>
       <c r="AH352" t="n">
-        <v>8.257</v>
+        <v>7.964</v>
       </c>
       <c r="AI352" t="n">
-        <v>5.005</v>
+        <v>5.171</v>
       </c>
       <c r="AJ352" t="n">
-        <v>16.271</v>
+        <v>16.12</v>
       </c>
       <c r="AK352" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AL352" t="n">
-        <v>10.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="353">
@@ -44066,22 +44066,22 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F364" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G364" t="b">
         <v>1</v>
       </c>
       <c r="H364" t="n">
-        <v>1378.343</v>
+        <v>1376.148</v>
       </c>
       <c r="I364" t="n">
-        <v>-1.056</v>
+        <v>-0.9555</v>
       </c>
       <c r="J364" t="n">
-        <v>1376.8</v>
+        <v>1379.2</v>
       </c>
       <c r="K364" t="n">
         <v>284</v>
@@ -44102,70 +44102,70 @@
         <v>275</v>
       </c>
       <c r="Q364" t="n">
-        <v>104.016</v>
+        <v>104.231</v>
       </c>
       <c r="R364" t="n">
-        <v>104.426</v>
+        <v>105.246</v>
       </c>
       <c r="S364" t="n">
-        <v>-0.41</v>
+        <v>-1.015</v>
       </c>
       <c r="T364" t="n">
-        <v>0.26035</v>
+        <v>0.25851</v>
       </c>
       <c r="U364" t="n">
-        <v>0.1364</v>
+        <v>0.13572</v>
       </c>
       <c r="V364" t="n">
-        <v>68.08</v>
+        <v>68.27</v>
       </c>
       <c r="W364" t="n">
-        <v>68.15000000000001</v>
+        <v>68.75</v>
       </c>
       <c r="X364" t="n">
-        <v>0.4889</v>
+        <v>0.4645</v>
       </c>
       <c r="Y364" t="n">
-        <v>25.622</v>
+        <v>25.77</v>
       </c>
       <c r="Z364" t="n">
-        <v>57.863</v>
+        <v>57.916</v>
       </c>
       <c r="AA364" t="n">
-        <v>5.767</v>
+        <v>5.783</v>
       </c>
       <c r="AB364" t="n">
-        <v>18.224</v>
+        <v>17.937</v>
       </c>
       <c r="AC364" t="n">
-        <v>11.064</v>
+        <v>10.942</v>
       </c>
       <c r="AD364" t="n">
-        <v>14.885</v>
+        <v>14.787</v>
       </c>
       <c r="AE364" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="AF364" t="n">
-        <v>22.257</v>
+        <v>22.235</v>
       </c>
       <c r="AG364" t="n">
-        <v>13.843</v>
+        <v>13.996</v>
       </c>
       <c r="AH364" t="n">
-        <v>7.054</v>
+        <v>6.942</v>
       </c>
       <c r="AI364" t="n">
-        <v>3.808</v>
+        <v>3.854</v>
       </c>
       <c r="AJ364" t="n">
-        <v>18.185</v>
+        <v>18.417</v>
       </c>
       <c r="AK364" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="AL364" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="365">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -626,22 +626,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1405.523</v>
+        <v>1408.315</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.049</v>
+        <v>-0.1959</v>
       </c>
       <c r="J2" t="n">
-        <v>1497.3</v>
+        <v>1493.1</v>
       </c>
       <c r="K2" t="n">
         <v>246</v>
@@ -662,70 +662,70 @@
         <v>248</v>
       </c>
       <c r="Q2" t="n">
-        <v>97.477</v>
+        <v>98.197</v>
       </c>
       <c r="R2" t="n">
-        <v>106.33</v>
+        <v>106.295</v>
       </c>
       <c r="S2" t="n">
-        <v>-8.853</v>
+        <v>-8.098000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.33021</v>
+        <v>0.32506</v>
       </c>
       <c r="U2" t="n">
-        <v>0.19859</v>
+        <v>0.19923</v>
       </c>
       <c r="V2" t="n">
-        <v>67.04000000000001</v>
+        <v>67.88</v>
       </c>
       <c r="W2" t="n">
-        <v>73.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3535</v>
+        <v>0.3851</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.015</v>
+        <v>23.034</v>
       </c>
       <c r="Z2" t="n">
-        <v>54.803</v>
+        <v>54.438</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.571</v>
+        <v>5.581</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.025</v>
+        <v>17.904</v>
       </c>
       <c r="AC2" t="n">
-        <v>15.439</v>
+        <v>16.227</v>
       </c>
       <c r="AD2" t="n">
-        <v>21.914</v>
+        <v>22.966</v>
       </c>
       <c r="AE2" t="n">
-        <v>9.253</v>
+        <v>9.143000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.631</v>
+        <v>18.929</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.288</v>
+        <v>12.394</v>
       </c>
       <c r="AH2" t="n">
-        <v>9.672000000000001</v>
+        <v>9.475</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.576</v>
+        <v>2.634</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21.136</v>
+        <v>21.407</v>
       </c>
       <c r="AK2" t="n">
-        <v>-10.6</v>
+        <v>-10.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>-5.3</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="3">
@@ -746,22 +746,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1256.606</v>
+        <v>1255.906</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.3635</v>
+        <v>-2.3202</v>
       </c>
       <c r="J3" t="n">
-        <v>1567.3</v>
+        <v>1572.4</v>
       </c>
       <c r="K3" t="n">
         <v>344</v>
@@ -782,70 +782,70 @@
         <v>349</v>
       </c>
       <c r="Q3" t="n">
-        <v>93.432</v>
+        <v>92.197</v>
       </c>
       <c r="R3" t="n">
-        <v>120.309</v>
+        <v>120.132</v>
       </c>
       <c r="S3" t="n">
-        <v>-26.877</v>
+        <v>-27.935</v>
       </c>
       <c r="T3" t="n">
-        <v>0.22224</v>
+        <v>0.22634</v>
       </c>
       <c r="U3" t="n">
-        <v>0.20484</v>
+        <v>0.20738</v>
       </c>
       <c r="V3" t="n">
-        <v>62.02</v>
+        <v>61.32</v>
       </c>
       <c r="W3" t="n">
-        <v>79.79000000000001</v>
+        <v>79.88</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0955</v>
+        <v>0.0926</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.977</v>
+        <v>21.677</v>
       </c>
       <c r="Z3" t="n">
-        <v>50.968</v>
+        <v>51.23</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.614</v>
+        <v>6.474</v>
       </c>
       <c r="AB3" t="n">
-        <v>21.227</v>
+        <v>21.383</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.455</v>
+        <v>11.494</v>
       </c>
       <c r="AD3" t="n">
-        <v>18.145</v>
+        <v>17.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>6.182</v>
+        <v>6.346</v>
       </c>
       <c r="AF3" t="n">
-        <v>20.941</v>
+        <v>21.013</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.223</v>
+        <v>12.091</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.536</v>
+        <v>5.668</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.427</v>
+        <v>2.358</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17.714</v>
+        <v>17.853</v>
       </c>
       <c r="AK3" t="n">
-        <v>-15.2</v>
+        <v>-17.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>-21.8</v>
+        <v>-22.9</v>
       </c>
     </row>
     <row r="4">
@@ -1946,22 +1946,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1690.003</v>
+        <v>1686.239</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2702</v>
+        <v>-1.0352</v>
       </c>
       <c r="J13" t="n">
-        <v>1729.9</v>
+        <v>1742.3</v>
       </c>
       <c r="K13" t="n">
         <v>63</v>
@@ -1982,70 +1982,70 @@
         <v>67</v>
       </c>
       <c r="Q13" t="n">
-        <v>108.881</v>
+        <v>106.954</v>
       </c>
       <c r="R13" t="n">
-        <v>109.142</v>
+        <v>110.224</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.261</v>
+        <v>-3.27</v>
       </c>
       <c r="T13" t="n">
-        <v>0.27918</v>
+        <v>0.27933</v>
       </c>
       <c r="U13" t="n">
-        <v>0.16072</v>
+        <v>0.16761</v>
       </c>
       <c r="V13" t="n">
-        <v>77.47</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>77.95</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5363</v>
+        <v>0.51</v>
       </c>
       <c r="Y13" t="n">
-        <v>26.239</v>
+        <v>25.74</v>
       </c>
       <c r="Z13" t="n">
-        <v>58.142</v>
+        <v>57.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.629</v>
+        <v>7.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>22.309</v>
+        <v>22.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.359</v>
+        <v>17.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>23.175</v>
+        <v>22.74</v>
       </c>
       <c r="AE13" t="n">
-        <v>8.567</v>
+        <v>8.58</v>
       </c>
       <c r="AF13" t="n">
-        <v>22.022</v>
+        <v>22.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.906</v>
+        <v>13.62</v>
       </c>
       <c r="AH13" t="n">
-        <v>7.083</v>
+        <v>6.98</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.566</v>
+        <v>4.57</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17.091</v>
+        <v>17.28</v>
       </c>
       <c r="AK13" t="n">
-        <v>-1.2</v>
+        <v>-8.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.3</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="14">
@@ -2666,22 +2666,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1831.661</v>
+        <v>1837.547</v>
       </c>
       <c r="I19" t="n">
-        <v>-7.7196</v>
+        <v>-7.6154</v>
       </c>
       <c r="J19" t="n">
-        <v>1758.3</v>
+        <v>1750.3</v>
       </c>
       <c r="K19" t="n">
         <v>39</v>
@@ -2702,70 +2702,70 @@
         <v>38</v>
       </c>
       <c r="Q19" t="n">
-        <v>119.162</v>
+        <v>118.87</v>
       </c>
       <c r="R19" t="n">
-        <v>114.916</v>
+        <v>113.503</v>
       </c>
       <c r="S19" t="n">
-        <v>4.246</v>
+        <v>5.367</v>
       </c>
       <c r="T19" t="n">
-        <v>0.34974</v>
+        <v>0.34615</v>
       </c>
       <c r="U19" t="n">
-        <v>0.14587</v>
+        <v>0.14352</v>
       </c>
       <c r="V19" t="n">
-        <v>83.52</v>
+        <v>83.33</v>
       </c>
       <c r="W19" t="n">
-        <v>80.41</v>
+        <v>79.42</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5101</v>
+        <v>0.5363</v>
       </c>
       <c r="Y19" t="n">
-        <v>27.672</v>
+        <v>27.618</v>
       </c>
       <c r="Z19" t="n">
-        <v>59.861</v>
+        <v>60.085</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.872</v>
+        <v>8.000999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>23.223</v>
+        <v>23.508</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.304</v>
+        <v>20.09</v>
       </c>
       <c r="AD19" t="n">
-        <v>27.099</v>
+        <v>26.977</v>
       </c>
       <c r="AE19" t="n">
-        <v>11.901</v>
+        <v>11.897</v>
       </c>
       <c r="AF19" t="n">
-        <v>21.614</v>
+        <v>22.077</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.809</v>
+        <v>12.898</v>
       </c>
       <c r="AH19" t="n">
-        <v>7.519</v>
+        <v>7.651</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.223</v>
+        <v>4.216</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17.362</v>
+        <v>17.257</v>
       </c>
       <c r="AK19" t="n">
-        <v>-3</v>
+        <v>0.4</v>
       </c>
       <c r="AL19" t="n">
-        <v>-5.4</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="20">
@@ -3266,22 +3266,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1375.394</v>
+        <v>1371.906</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9205</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>1436.6</v>
+        <v>1430.6</v>
       </c>
       <c r="K24" t="n">
         <v>238</v>
@@ -3302,70 +3302,70 @@
         <v>255</v>
       </c>
       <c r="Q24" t="n">
-        <v>104.964</v>
+        <v>104.969</v>
       </c>
       <c r="R24" t="n">
-        <v>108.705</v>
+        <v>108.797</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.741</v>
+        <v>-3.829</v>
       </c>
       <c r="T24" t="n">
-        <v>0.27781</v>
+        <v>0.27923</v>
       </c>
       <c r="U24" t="n">
-        <v>0.18622</v>
+        <v>0.18598</v>
       </c>
       <c r="V24" t="n">
-        <v>74.81999999999999</v>
+        <v>74.47</v>
       </c>
       <c r="W24" t="n">
-        <v>77.73</v>
+        <v>77.42</v>
       </c>
       <c r="X24" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5111</v>
       </c>
       <c r="Y24" t="n">
         <v>26.319</v>
       </c>
       <c r="Z24" t="n">
-        <v>57.058</v>
+        <v>56.961</v>
       </c>
       <c r="AA24" t="n">
-        <v>5.694</v>
+        <v>5.828</v>
       </c>
       <c r="AB24" t="n">
-        <v>17.103</v>
+        <v>17.067</v>
       </c>
       <c r="AC24" t="n">
-        <v>16.49</v>
+        <v>16.175</v>
       </c>
       <c r="AD24" t="n">
-        <v>23.633</v>
+        <v>23.386</v>
       </c>
       <c r="AE24" t="n">
-        <v>9.407999999999999</v>
+        <v>9.457000000000001</v>
       </c>
       <c r="AF24" t="n">
-        <v>23.847</v>
+        <v>23.831</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.244</v>
+        <v>13.163</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.802</v>
+        <v>6.642</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.496</v>
+        <v>4.553</v>
       </c>
       <c r="AJ24" t="n">
-        <v>18.405</v>
+        <v>18.351</v>
       </c>
       <c r="AK24" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="AL24" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -3506,22 +3506,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1737.517</v>
+        <v>1724.09</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.1403</v>
+        <v>-1.8566</v>
       </c>
       <c r="J26" t="n">
-        <v>1622.1</v>
+        <v>1610.8</v>
       </c>
       <c r="K26" t="n">
         <v>55</v>
@@ -3542,70 +3542,70 @@
         <v>57</v>
       </c>
       <c r="Q26" t="n">
-        <v>114.39</v>
+        <v>113.98</v>
       </c>
       <c r="R26" t="n">
-        <v>107.179</v>
+        <v>107.778</v>
       </c>
       <c r="S26" t="n">
-        <v>7.211</v>
+        <v>6.202</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28469</v>
+        <v>0.28395</v>
       </c>
       <c r="U26" t="n">
-        <v>0.16036</v>
+        <v>0.15711</v>
       </c>
       <c r="V26" t="n">
-        <v>77.52</v>
+        <v>77.37</v>
       </c>
       <c r="W26" t="n">
-        <v>72.77</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>0.6584</v>
+        <v>0.6279</v>
       </c>
       <c r="Y26" t="n">
-        <v>25.248</v>
+        <v>25.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>55.988</v>
+        <v>56.241</v>
       </c>
       <c r="AA26" t="n">
-        <v>8.391</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="AB26" t="n">
-        <v>24.158</v>
+        <v>24.24</v>
       </c>
       <c r="AC26" t="n">
-        <v>18.634</v>
+        <v>18.47</v>
       </c>
       <c r="AD26" t="n">
         <v>23.736</v>
       </c>
       <c r="AE26" t="n">
-        <v>9.446999999999999</v>
+        <v>9.397</v>
       </c>
       <c r="AF26" t="n">
-        <v>23.693</v>
+        <v>23.661</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.559</v>
+        <v>12.511</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.649</v>
+        <v>4.795</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.196</v>
+        <v>2.323</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17.127</v>
+        <v>17.257</v>
       </c>
       <c r="AK26" t="n">
-        <v>12.2</v>
+        <v>7.2</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="27">
@@ -3746,22 +3746,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1346.802</v>
+        <v>1344.374</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.4681</v>
+        <v>-2.282</v>
       </c>
       <c r="J28" t="n">
-        <v>1379.2</v>
+        <v>1376.4</v>
       </c>
       <c r="K28" t="n">
         <v>254</v>
@@ -3782,70 +3782,70 @@
         <v>257</v>
       </c>
       <c r="Q28" t="n">
-        <v>115.453</v>
+        <v>114.64</v>
       </c>
       <c r="R28" t="n">
-        <v>114.218</v>
+        <v>114.359</v>
       </c>
       <c r="S28" t="n">
-        <v>1.235</v>
+        <v>0.28</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23552</v>
+        <v>0.23959</v>
       </c>
       <c r="U28" t="n">
-        <v>0.16969</v>
+        <v>0.16822</v>
       </c>
       <c r="V28" t="n">
-        <v>75.04000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>74.44</v>
+        <v>74.45</v>
       </c>
       <c r="X28" t="n">
-        <v>0.5054</v>
+        <v>0.48</v>
       </c>
       <c r="Y28" t="n">
-        <v>26.68</v>
+        <v>26.42</v>
       </c>
       <c r="Z28" t="n">
-        <v>53.987</v>
+        <v>54.02</v>
       </c>
       <c r="AA28" t="n">
-        <v>9.454000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>23.876</v>
+        <v>23.56</v>
       </c>
       <c r="AC28" t="n">
-        <v>12.226</v>
+        <v>12.52</v>
       </c>
       <c r="AD28" t="n">
-        <v>16.73</v>
+        <v>17.03</v>
       </c>
       <c r="AE28" t="n">
-        <v>7.195</v>
+        <v>7.33</v>
       </c>
       <c r="AF28" t="n">
-        <v>22.845</v>
+        <v>22.77</v>
       </c>
       <c r="AG28" t="n">
-        <v>14.515</v>
+        <v>14.07</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.679</v>
+        <v>4.73</v>
       </c>
       <c r="AI28" t="n">
-        <v>3.309</v>
+        <v>3.26</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16.165</v>
+        <v>16.23</v>
       </c>
       <c r="AK28" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL28" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -4586,22 +4586,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1626.176</v>
+        <v>1615.75</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8502</v>
+        <v>0.7248</v>
       </c>
       <c r="J35" t="n">
-        <v>1622.8</v>
+        <v>1620.7</v>
       </c>
       <c r="K35" t="n">
         <v>82</v>
@@ -4622,70 +4622,70 @@
         <v>82</v>
       </c>
       <c r="Q35" t="n">
-        <v>110.933</v>
+        <v>111.069</v>
       </c>
       <c r="R35" t="n">
-        <v>108.362</v>
+        <v>109.321</v>
       </c>
       <c r="S35" t="n">
-        <v>2.571</v>
+        <v>1.748</v>
       </c>
       <c r="T35" t="n">
-        <v>0.30799</v>
+        <v>0.30454</v>
       </c>
       <c r="U35" t="n">
-        <v>0.15471</v>
+        <v>0.15282</v>
       </c>
       <c r="V35" t="n">
-        <v>79.34</v>
+        <v>79.39</v>
       </c>
       <c r="W35" t="n">
-        <v>77.03</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="X35" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.4946</v>
       </c>
       <c r="Y35" t="n">
-        <v>27.041</v>
+        <v>27.353</v>
       </c>
       <c r="Z35" t="n">
-        <v>59.948</v>
+        <v>60.147</v>
       </c>
       <c r="AA35" t="n">
-        <v>6.925</v>
+        <v>7.23</v>
       </c>
       <c r="AB35" t="n">
-        <v>21.093</v>
+        <v>21.374</v>
       </c>
       <c r="AC35" t="n">
-        <v>18.336</v>
+        <v>17.872</v>
       </c>
       <c r="AD35" t="n">
-        <v>25.472</v>
+        <v>24.902</v>
       </c>
       <c r="AE35" t="n">
-        <v>10.922</v>
+        <v>10.762</v>
       </c>
       <c r="AF35" t="n">
-        <v>23.878</v>
+        <v>23.981</v>
       </c>
       <c r="AG35" t="n">
-        <v>15.545</v>
+        <v>15.745</v>
       </c>
       <c r="AH35" t="n">
-        <v>6.597</v>
+        <v>6.515</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.278</v>
+        <v>3.247</v>
       </c>
       <c r="AJ35" t="n">
-        <v>15.406</v>
+        <v>15.413</v>
       </c>
       <c r="AK35" t="n">
-        <v>-1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="AL35" t="n">
-        <v>-6.2</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="36">
@@ -4706,22 +4706,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1927.75</v>
+        <v>1934.422</v>
       </c>
       <c r="I36" t="n">
-        <v>1.2144</v>
+        <v>0.879</v>
       </c>
       <c r="J36" t="n">
-        <v>1718</v>
+        <v>1718.9</v>
       </c>
       <c r="K36" t="n">
         <v>25</v>
@@ -4742,70 +4742,70 @@
         <v>24</v>
       </c>
       <c r="Q36" t="n">
-        <v>118.903</v>
+        <v>118.415</v>
       </c>
       <c r="R36" t="n">
-        <v>107.055</v>
+        <v>105.834</v>
       </c>
       <c r="S36" t="n">
-        <v>11.848</v>
+        <v>12.581</v>
       </c>
       <c r="T36" t="n">
-        <v>0.3035</v>
+        <v>0.30424</v>
       </c>
       <c r="U36" t="n">
-        <v>0.14274</v>
+        <v>0.15093</v>
       </c>
       <c r="V36" t="n">
-        <v>85.15000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="W36" t="n">
-        <v>76.38</v>
+        <v>75.16</v>
       </c>
       <c r="X36" t="n">
-        <v>0.6903</v>
+        <v>0.6995</v>
       </c>
       <c r="Y36" t="n">
-        <v>30.121</v>
+        <v>29.492</v>
       </c>
       <c r="Z36" t="n">
-        <v>62.75</v>
+        <v>61.862</v>
       </c>
       <c r="AA36" t="n">
-        <v>8.77</v>
+        <v>8.606</v>
       </c>
       <c r="AB36" t="n">
-        <v>25.311</v>
+        <v>24.971</v>
       </c>
       <c r="AC36" t="n">
-        <v>16.137</v>
+        <v>15.958</v>
       </c>
       <c r="AD36" t="n">
-        <v>21.654</v>
+        <v>21.546</v>
       </c>
       <c r="AE36" t="n">
-        <v>11.027</v>
+        <v>10.962</v>
       </c>
       <c r="AF36" t="n">
-        <v>25.195</v>
+        <v>24.988</v>
       </c>
       <c r="AG36" t="n">
-        <v>13.832</v>
+        <v>13.55</v>
       </c>
       <c r="AH36" t="n">
-        <v>7.204</v>
+        <v>7.18</v>
       </c>
       <c r="AI36" t="n">
-        <v>4.474</v>
+        <v>4.451</v>
       </c>
       <c r="AJ36" t="n">
-        <v>15.65</v>
+        <v>15.631</v>
       </c>
       <c r="AK36" t="n">
-        <v>-4.6</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="n">
-        <v>-2.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="37">
@@ -4946,22 +4946,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1400.166</v>
+        <v>1397.333</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2454</v>
+        <v>-0.1798</v>
       </c>
       <c r="J38" t="n">
-        <v>1490.1</v>
+        <v>1496.9</v>
       </c>
       <c r="K38" t="n">
         <v>211</v>
@@ -4982,70 +4982,70 @@
         <v>228</v>
       </c>
       <c r="Q38" t="n">
-        <v>106.572</v>
+        <v>105.821</v>
       </c>
       <c r="R38" t="n">
-        <v>111.692</v>
+        <v>111.345</v>
       </c>
       <c r="S38" t="n">
-        <v>-5.12</v>
+        <v>-5.524</v>
       </c>
       <c r="T38" t="n">
-        <v>0.28042</v>
+        <v>0.2798</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1916</v>
+        <v>0.1913</v>
       </c>
       <c r="V38" t="n">
-        <v>82.04000000000001</v>
+        <v>81.23</v>
       </c>
       <c r="W38" t="n">
-        <v>85.66</v>
+        <v>85.19</v>
       </c>
       <c r="X38" t="n">
-        <v>0.4063</v>
+        <v>0.3833</v>
       </c>
       <c r="Y38" t="n">
-        <v>26.885</v>
+        <v>26.693</v>
       </c>
       <c r="Z38" t="n">
-        <v>62.442</v>
+        <v>62.381</v>
       </c>
       <c r="AA38" t="n">
-        <v>11.021</v>
+        <v>10.792</v>
       </c>
       <c r="AB38" t="n">
-        <v>32.867</v>
+        <v>32.799</v>
       </c>
       <c r="AC38" t="n">
-        <v>17.252</v>
+        <v>17.057</v>
       </c>
       <c r="AD38" t="n">
-        <v>21.988</v>
+        <v>21.718</v>
       </c>
       <c r="AE38" t="n">
-        <v>9.930999999999999</v>
+        <v>9.914</v>
       </c>
       <c r="AF38" t="n">
-        <v>25.151</v>
+        <v>25.221</v>
       </c>
       <c r="AG38" t="n">
-        <v>13.282</v>
+        <v>13.275</v>
       </c>
       <c r="AH38" t="n">
-        <v>6.481</v>
+        <v>6.374</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.241</v>
+        <v>2.14</v>
       </c>
       <c r="AJ38" t="n">
-        <v>19.54</v>
+        <v>19.668</v>
       </c>
       <c r="AK38" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="39">
@@ -5066,22 +5066,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1717.332</v>
+        <v>1703.272</v>
       </c>
       <c r="I39" t="n">
-        <v>7.7033</v>
+        <v>7.292</v>
       </c>
       <c r="J39" t="n">
-        <v>1603.3</v>
+        <v>1603.7</v>
       </c>
       <c r="K39" t="n">
         <v>71</v>
@@ -5102,70 +5102,70 @@
         <v>65</v>
       </c>
       <c r="Q39" t="n">
-        <v>109.179</v>
+        <v>110.159</v>
       </c>
       <c r="R39" t="n">
-        <v>103.338</v>
+        <v>104.763</v>
       </c>
       <c r="S39" t="n">
-        <v>5.841</v>
+        <v>5.396</v>
       </c>
       <c r="T39" t="n">
-        <v>0.22803</v>
+        <v>0.23512</v>
       </c>
       <c r="U39" t="n">
-        <v>0.14302</v>
+        <v>0.14496</v>
       </c>
       <c r="V39" t="n">
-        <v>76.95</v>
+        <v>77.52</v>
       </c>
       <c r="W39" t="n">
-        <v>72.69</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="X39" t="n">
-        <v>0.6583</v>
+        <v>0.6377</v>
       </c>
       <c r="Y39" t="n">
-        <v>25.575</v>
+        <v>25.867</v>
       </c>
       <c r="Z39" t="n">
-        <v>57.98</v>
+        <v>58.099</v>
       </c>
       <c r="AA39" t="n">
-        <v>8.922000000000001</v>
+        <v>9.023</v>
       </c>
       <c r="AB39" t="n">
-        <v>24.787</v>
+        <v>24.832</v>
       </c>
       <c r="AC39" t="n">
-        <v>16.878</v>
+        <v>16.765</v>
       </c>
       <c r="AD39" t="n">
-        <v>21.68</v>
+        <v>21.704</v>
       </c>
       <c r="AE39" t="n">
-        <v>7.263</v>
+        <v>7.603</v>
       </c>
       <c r="AF39" t="n">
-        <v>24.37</v>
+        <v>24.339</v>
       </c>
       <c r="AG39" t="n">
-        <v>13.879</v>
+        <v>13.838</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.777</v>
+        <v>5.678</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.094</v>
+        <v>3.128</v>
       </c>
       <c r="AJ39" t="n">
-        <v>19.187</v>
+        <v>19.009</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.4</v>
+        <v>-2.8</v>
       </c>
       <c r="AL39" t="n">
-        <v>-1.4</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="40">
@@ -6146,22 +6146,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1728.908</v>
+        <v>1718.336</v>
       </c>
       <c r="I48" t="n">
-        <v>1.3367</v>
+        <v>1.6688</v>
       </c>
       <c r="J48" t="n">
-        <v>1706.8</v>
+        <v>1713.3</v>
       </c>
       <c r="K48" t="n">
         <v>42</v>
@@ -6182,70 +6182,70 @@
         <v>46</v>
       </c>
       <c r="Q48" t="n">
-        <v>105.7</v>
+        <v>104.828</v>
       </c>
       <c r="R48" t="n">
-        <v>98.188</v>
+        <v>97.705</v>
       </c>
       <c r="S48" t="n">
-        <v>7.511</v>
+        <v>7.122</v>
       </c>
       <c r="T48" t="n">
-        <v>0.28945</v>
+        <v>0.28672</v>
       </c>
       <c r="U48" t="n">
-        <v>0.16144</v>
+        <v>0.1656</v>
       </c>
       <c r="V48" t="n">
-        <v>73.37</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="W48" t="n">
-        <v>67.61</v>
+        <v>67.56</v>
       </c>
       <c r="X48" t="n">
-        <v>0.5672</v>
+        <v>0.54</v>
       </c>
       <c r="Y48" t="n">
-        <v>26.227</v>
+        <v>25.97</v>
       </c>
       <c r="Z48" t="n">
-        <v>60.433</v>
+        <v>60.38</v>
       </c>
       <c r="AA48" t="n">
-        <v>8.907</v>
+        <v>8.99</v>
       </c>
       <c r="AB48" t="n">
-        <v>26.401</v>
+        <v>26.42</v>
       </c>
       <c r="AC48" t="n">
-        <v>12.009</v>
+        <v>12.11</v>
       </c>
       <c r="AD48" t="n">
-        <v>17.784</v>
+        <v>17.75</v>
       </c>
       <c r="AE48" t="n">
-        <v>10.103</v>
+        <v>10.09</v>
       </c>
       <c r="AF48" t="n">
-        <v>24.95</v>
+        <v>25.35</v>
       </c>
       <c r="AG48" t="n">
-        <v>16.669</v>
+        <v>16.54</v>
       </c>
       <c r="AH48" t="n">
-        <v>6.266</v>
+        <v>6.26</v>
       </c>
       <c r="AI48" t="n">
-        <v>4.228</v>
+        <v>4.26</v>
       </c>
       <c r="AJ48" t="n">
-        <v>15.855</v>
+        <v>16</v>
       </c>
       <c r="AK48" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AL48" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -6386,22 +6386,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G50" t="b">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1838.213</v>
+        <v>1845.489</v>
       </c>
       <c r="I50" t="n">
-        <v>3.3876</v>
+        <v>3.0058</v>
       </c>
       <c r="J50" t="n">
-        <v>1641.6</v>
+        <v>1644.4</v>
       </c>
       <c r="K50" t="n">
         <v>38</v>
@@ -6422,70 +6422,70 @@
         <v>36</v>
       </c>
       <c r="Q50" t="n">
-        <v>112.83</v>
+        <v>113.176</v>
       </c>
       <c r="R50" t="n">
-        <v>100.583</v>
+        <v>100.702</v>
       </c>
       <c r="S50" t="n">
-        <v>12.247</v>
+        <v>12.474</v>
       </c>
       <c r="T50" t="n">
-        <v>0.2488</v>
+        <v>0.25453</v>
       </c>
       <c r="U50" t="n">
-        <v>0.13952</v>
+        <v>0.13662</v>
       </c>
       <c r="V50" t="n">
-        <v>74.54000000000001</v>
+        <v>74.34</v>
       </c>
       <c r="W50" t="n">
-        <v>66.40000000000001</v>
+        <v>66.11</v>
       </c>
       <c r="X50" t="n">
-        <v>0.713</v>
+        <v>0.7218</v>
       </c>
       <c r="Y50" t="n">
-        <v>25.574</v>
+        <v>25.598</v>
       </c>
       <c r="Z50" t="n">
-        <v>55.872</v>
+        <v>56.21</v>
       </c>
       <c r="AA50" t="n">
-        <v>8.170999999999999</v>
+        <v>8.238</v>
       </c>
       <c r="AB50" t="n">
-        <v>23.991</v>
+        <v>24.261</v>
       </c>
       <c r="AC50" t="n">
-        <v>15.217</v>
+        <v>14.905</v>
       </c>
       <c r="AD50" t="n">
-        <v>20.93</v>
+        <v>20.626</v>
       </c>
       <c r="AE50" t="n">
-        <v>8.289999999999999</v>
+        <v>8.622</v>
       </c>
       <c r="AF50" t="n">
-        <v>23.951</v>
+        <v>23.989</v>
       </c>
       <c r="AG50" t="n">
-        <v>13.003</v>
+        <v>12.886</v>
       </c>
       <c r="AH50" t="n">
-        <v>6.333</v>
+        <v>6.32</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.745</v>
+        <v>2.836</v>
       </c>
       <c r="AJ50" t="n">
-        <v>16.191</v>
+        <v>15.935</v>
       </c>
       <c r="AK50" t="n">
-        <v>-1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL50" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="51">
@@ -7106,22 +7106,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1661.338</v>
+        <v>1664.23</v>
       </c>
       <c r="I56" t="n">
-        <v>-5.2805</v>
+        <v>-4.9476</v>
       </c>
       <c r="J56" t="n">
-        <v>1561.4</v>
+        <v>1553.3</v>
       </c>
       <c r="K56" t="n">
         <v>85</v>
@@ -7142,70 +7142,70 @@
         <v>87</v>
       </c>
       <c r="Q56" t="n">
-        <v>119.17</v>
+        <v>118.834</v>
       </c>
       <c r="R56" t="n">
-        <v>113.564</v>
+        <v>112.903</v>
       </c>
       <c r="S56" t="n">
-        <v>5.606</v>
+        <v>5.931</v>
       </c>
       <c r="T56" t="n">
-        <v>0.25927</v>
+        <v>0.26383</v>
       </c>
       <c r="U56" t="n">
-        <v>0.1744</v>
+        <v>0.1735</v>
       </c>
       <c r="V56" t="n">
-        <v>75.79000000000001</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="W56" t="n">
-        <v>72.04000000000001</v>
+        <v>71.58</v>
       </c>
       <c r="X56" t="n">
-        <v>0.6254</v>
+        <v>0.6493</v>
       </c>
       <c r="Y56" t="n">
-        <v>25.111</v>
+        <v>25.009</v>
       </c>
       <c r="Z56" t="n">
-        <v>50.881</v>
+        <v>51.22</v>
       </c>
       <c r="AA56" t="n">
-        <v>9.686999999999999</v>
+        <v>9.744999999999999</v>
       </c>
       <c r="AB56" t="n">
-        <v>24.641</v>
+        <v>24.93</v>
       </c>
       <c r="AC56" t="n">
-        <v>15.879</v>
+        <v>15.751</v>
       </c>
       <c r="AD56" t="n">
-        <v>20.649</v>
+        <v>20.484</v>
       </c>
       <c r="AE56" t="n">
-        <v>7.514</v>
+        <v>7.771</v>
       </c>
       <c r="AF56" t="n">
-        <v>22.044</v>
+        <v>22.128</v>
       </c>
       <c r="AG56" t="n">
-        <v>15.795</v>
+        <v>15.864</v>
       </c>
       <c r="AH56" t="n">
-        <v>5.19</v>
+        <v>5.203</v>
       </c>
       <c r="AI56" t="n">
-        <v>2.19</v>
+        <v>2.159</v>
       </c>
       <c r="AJ56" t="n">
-        <v>16.671</v>
+        <v>16.507</v>
       </c>
       <c r="AK56" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AL56" t="n">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="57">
@@ -8786,22 +8786,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G70" t="b">
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>1255.975</v>
+        <v>1258.638</v>
       </c>
       <c r="I70" t="n">
-        <v>-3.1819</v>
+        <v>-3.1046</v>
       </c>
       <c r="J70" t="n">
-        <v>1357.2</v>
+        <v>1354.6</v>
       </c>
       <c r="K70" t="n">
         <v>362</v>
@@ -8822,70 +8822,70 @@
         <v>362</v>
       </c>
       <c r="Q70" t="n">
-        <v>90.245</v>
+        <v>90.703</v>
       </c>
       <c r="R70" t="n">
-        <v>108.679</v>
+        <v>108.133</v>
       </c>
       <c r="S70" t="n">
-        <v>-18.434</v>
+        <v>-17.429</v>
       </c>
       <c r="T70" t="n">
-        <v>0.30587</v>
+        <v>0.30644</v>
       </c>
       <c r="U70" t="n">
-        <v>0.18578</v>
+        <v>0.18209</v>
       </c>
       <c r="V70" t="n">
-        <v>59.29</v>
+        <v>60.1</v>
       </c>
       <c r="W70" t="n">
-        <v>71.75</v>
+        <v>71.86</v>
       </c>
       <c r="X70" t="n">
-        <v>0.1711</v>
+        <v>0.202</v>
       </c>
       <c r="Y70" t="n">
-        <v>20.921</v>
+        <v>20.874</v>
       </c>
       <c r="Z70" t="n">
-        <v>54.487</v>
+        <v>54.844</v>
       </c>
       <c r="AA70" t="n">
-        <v>4.658</v>
+        <v>4.558</v>
       </c>
       <c r="AB70" t="n">
-        <v>16.053</v>
+        <v>16.288</v>
       </c>
       <c r="AC70" t="n">
-        <v>12.789</v>
+        <v>13.548</v>
       </c>
       <c r="AD70" t="n">
-        <v>18.487</v>
+        <v>19.432</v>
       </c>
       <c r="AE70" t="n">
-        <v>8.855</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AF70" t="n">
-        <v>19.553</v>
+        <v>19.732</v>
       </c>
       <c r="AG70" t="n">
-        <v>9.711</v>
+        <v>9.596</v>
       </c>
       <c r="AH70" t="n">
-        <v>7.921</v>
+        <v>7.674</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.645</v>
+        <v>1.758</v>
       </c>
       <c r="AJ70" t="n">
-        <v>17.658</v>
+        <v>17.822</v>
       </c>
       <c r="AK70" t="n">
-        <v>-12.2</v>
+        <v>-4.8</v>
       </c>
       <c r="AL70" t="n">
-        <v>-10.3</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -9026,22 +9026,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F72" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1577.85</v>
+        <v>1569.356</v>
       </c>
       <c r="I72" t="n">
-        <v>5.5995</v>
+        <v>5.3969</v>
       </c>
       <c r="J72" t="n">
-        <v>1606.7</v>
+        <v>1604.6</v>
       </c>
       <c r="K72" t="n">
         <v>102</v>
@@ -9062,70 +9062,70 @@
         <v>101</v>
       </c>
       <c r="Q72" t="n">
-        <v>104.505</v>
+        <v>103.998</v>
       </c>
       <c r="R72" t="n">
-        <v>103.47</v>
+        <v>103.311</v>
       </c>
       <c r="S72" t="n">
-        <v>1.035</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="T72" t="n">
-        <v>0.30295</v>
+        <v>0.30033</v>
       </c>
       <c r="U72" t="n">
-        <v>0.17074</v>
+        <v>0.17058</v>
       </c>
       <c r="V72" t="n">
-        <v>70.70999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="W72" t="n">
-        <v>69.90000000000001</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="X72" t="n">
-        <v>0.5101</v>
+        <v>0.4946</v>
       </c>
       <c r="Y72" t="n">
-        <v>24.788</v>
+        <v>24.659</v>
       </c>
       <c r="Z72" t="n">
-        <v>56.768</v>
+        <v>56.587</v>
       </c>
       <c r="AA72" t="n">
-        <v>7.116</v>
+        <v>6.957</v>
       </c>
       <c r="AB72" t="n">
-        <v>22.217</v>
+        <v>21.821</v>
       </c>
       <c r="AC72" t="n">
-        <v>14.02</v>
+        <v>14.114</v>
       </c>
       <c r="AD72" t="n">
-        <v>20.255</v>
+        <v>20.164</v>
       </c>
       <c r="AE72" t="n">
-        <v>9.475</v>
+        <v>9.496</v>
       </c>
       <c r="AF72" t="n">
-        <v>21.838</v>
+        <v>22.21</v>
       </c>
       <c r="AG72" t="n">
-        <v>15.162</v>
+        <v>14.957</v>
       </c>
       <c r="AH72" t="n">
-        <v>6.948</v>
+        <v>6.855</v>
       </c>
       <c r="AI72" t="n">
-        <v>3.406</v>
+        <v>3.413</v>
       </c>
       <c r="AJ72" t="n">
-        <v>18.012</v>
+        <v>17.792</v>
       </c>
       <c r="AK72" t="n">
-        <v>-4</v>
+        <v>-4.8</v>
       </c>
       <c r="AL72" t="n">
-        <v>-3.9</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="73">
@@ -11066,22 +11066,22 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F89" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G89" t="b">
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1570.582</v>
+        <v>1576.085</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.3127</v>
+        <v>-1.4104</v>
       </c>
       <c r="J89" t="n">
-        <v>1561.9</v>
+        <v>1558.4</v>
       </c>
       <c r="K89" t="n">
         <v>125</v>
@@ -11102,70 +11102,70 @@
         <v>123</v>
       </c>
       <c r="Q89" t="n">
-        <v>108.765</v>
+        <v>108.511</v>
       </c>
       <c r="R89" t="n">
-        <v>106.62</v>
+        <v>105.869</v>
       </c>
       <c r="S89" t="n">
-        <v>2.145</v>
+        <v>2.642</v>
       </c>
       <c r="T89" t="n">
-        <v>0.29332</v>
+        <v>0.29221</v>
       </c>
       <c r="U89" t="n">
-        <v>0.16902</v>
+        <v>0.173</v>
       </c>
       <c r="V89" t="n">
-        <v>77.81</v>
+        <v>77.25</v>
       </c>
       <c r="W89" t="n">
-        <v>76.06999999999999</v>
+        <v>75.19</v>
       </c>
       <c r="X89" t="n">
-        <v>0.5114</v>
+        <v>0.5382</v>
       </c>
       <c r="Y89" t="n">
-        <v>27.92</v>
+        <v>27.837</v>
       </c>
       <c r="Z89" t="n">
-        <v>61.034</v>
+        <v>60.621</v>
       </c>
       <c r="AA89" t="n">
-        <v>7.875</v>
+        <v>7.814</v>
       </c>
       <c r="AB89" t="n">
-        <v>23.568</v>
+        <v>23.105</v>
       </c>
       <c r="AC89" t="n">
-        <v>14.091</v>
+        <v>13.762</v>
       </c>
       <c r="AD89" t="n">
-        <v>19.932</v>
+        <v>19.586</v>
       </c>
       <c r="AE89" t="n">
-        <v>10.341</v>
+        <v>10.33</v>
       </c>
       <c r="AF89" t="n">
-        <v>25.045</v>
+        <v>25.153</v>
       </c>
       <c r="AG89" t="n">
-        <v>13.318</v>
+        <v>13.069</v>
       </c>
       <c r="AH89" t="n">
-        <v>5.761</v>
+        <v>5.813</v>
       </c>
       <c r="AI89" t="n">
-        <v>5.375</v>
+        <v>5.352</v>
       </c>
       <c r="AJ89" t="n">
-        <v>17.591</v>
+        <v>17.496</v>
       </c>
       <c r="AK89" t="n">
-        <v>-1.2</v>
+        <v>-2</v>
       </c>
       <c r="AL89" t="n">
-        <v>-4.6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="90">
@@ -11426,22 +11426,22 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F92" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G92" t="b">
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1294.876</v>
+        <v>1297.568</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.222</v>
+        <v>-0.1581</v>
       </c>
       <c r="J92" t="n">
-        <v>1379.3</v>
+        <v>1376.1</v>
       </c>
       <c r="K92" t="n">
         <v>315</v>
@@ -11462,70 +11462,70 @@
         <v>315</v>
       </c>
       <c r="Q92" t="n">
-        <v>99.59099999999999</v>
+        <v>99.547</v>
       </c>
       <c r="R92" t="n">
-        <v>106.666</v>
+        <v>105.787</v>
       </c>
       <c r="S92" t="n">
-        <v>-7.074</v>
+        <v>-6.24</v>
       </c>
       <c r="T92" t="n">
-        <v>0.2982</v>
+        <v>0.30268</v>
       </c>
       <c r="U92" t="n">
-        <v>0.20433</v>
+        <v>0.20622</v>
       </c>
       <c r="V92" t="n">
-        <v>70.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="W92" t="n">
-        <v>75.72</v>
+        <v>75.02</v>
       </c>
       <c r="X92" t="n">
-        <v>0.4493</v>
+        <v>0.4686</v>
       </c>
       <c r="Y92" t="n">
-        <v>24.238</v>
+        <v>24.213</v>
       </c>
       <c r="Z92" t="n">
-        <v>56.245</v>
+        <v>56.395</v>
       </c>
       <c r="AA92" t="n">
-        <v>6.955</v>
+        <v>6.921</v>
       </c>
       <c r="AB92" t="n">
-        <v>21.322</v>
+        <v>21.362</v>
       </c>
       <c r="AC92" t="n">
-        <v>14.666</v>
+        <v>14.654</v>
       </c>
       <c r="AD92" t="n">
-        <v>21.163</v>
+        <v>21.019</v>
       </c>
       <c r="AE92" t="n">
-        <v>9.391999999999999</v>
+        <v>9.667</v>
       </c>
       <c r="AF92" t="n">
-        <v>21.78</v>
+        <v>21.831</v>
       </c>
       <c r="AG92" t="n">
-        <v>12.462</v>
+        <v>12.713</v>
       </c>
       <c r="AH92" t="n">
-        <v>7.86</v>
+        <v>8.170999999999999</v>
       </c>
       <c r="AI92" t="n">
-        <v>2.937</v>
+        <v>3.008</v>
       </c>
       <c r="AJ92" t="n">
-        <v>18.21</v>
+        <v>18.047</v>
       </c>
       <c r="AK92" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AL92" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -11666,22 +11666,22 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F94" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G94" t="b">
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>1621.907</v>
+        <v>1635.967</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.8284</v>
+        <v>-0.3568</v>
       </c>
       <c r="J94" t="n">
-        <v>1656.1</v>
+        <v>1657.6</v>
       </c>
       <c r="K94" t="n">
         <v>65</v>
@@ -11702,70 +11702,70 @@
         <v>69</v>
       </c>
       <c r="Q94" t="n">
-        <v>111.16</v>
+        <v>112.095</v>
       </c>
       <c r="R94" t="n">
-        <v>107.311</v>
+        <v>108.201</v>
       </c>
       <c r="S94" t="n">
-        <v>3.849</v>
+        <v>3.894</v>
       </c>
       <c r="T94" t="n">
-        <v>0.3133</v>
+        <v>0.31106</v>
       </c>
       <c r="U94" t="n">
-        <v>0.15065</v>
+        <v>0.14799</v>
       </c>
       <c r="V94" t="n">
-        <v>80.06</v>
+        <v>80.56</v>
       </c>
       <c r="W94" t="n">
-        <v>77.52</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="X94" t="n">
-        <v>0.5536</v>
+        <v>0.5672</v>
       </c>
       <c r="Y94" t="n">
-        <v>27.067</v>
+        <v>27.364</v>
       </c>
       <c r="Z94" t="n">
-        <v>62.368</v>
+        <v>62.36</v>
       </c>
       <c r="AA94" t="n">
-        <v>10.357</v>
+        <v>10.403</v>
       </c>
       <c r="AB94" t="n">
-        <v>31.672</v>
+        <v>31.493</v>
       </c>
       <c r="AC94" t="n">
-        <v>15.574</v>
+        <v>15.431</v>
       </c>
       <c r="AD94" t="n">
-        <v>21.768</v>
+        <v>21.628</v>
       </c>
       <c r="AE94" t="n">
-        <v>10.559</v>
+        <v>10.421</v>
       </c>
       <c r="AF94" t="n">
-        <v>22.841</v>
+        <v>22.72</v>
       </c>
       <c r="AG94" t="n">
-        <v>14.377</v>
+        <v>14.517</v>
       </c>
       <c r="AH94" t="n">
-        <v>7.832</v>
+        <v>7.815</v>
       </c>
       <c r="AI94" t="n">
-        <v>3.849</v>
+        <v>3.876</v>
       </c>
       <c r="AJ94" t="n">
-        <v>18.223</v>
+        <v>18.258</v>
       </c>
       <c r="AK94" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AL94" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="95">
@@ -11906,22 +11906,22 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F96" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G96" t="b">
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1420.568</v>
+        <v>1417.676</v>
       </c>
       <c r="I96" t="n">
-        <v>2.37</v>
+        <v>2.2387</v>
       </c>
       <c r="J96" t="n">
-        <v>1589</v>
+        <v>1590.6</v>
       </c>
       <c r="K96" t="n">
         <v>131</v>
@@ -11942,70 +11942,70 @@
         <v>149</v>
       </c>
       <c r="Q96" t="n">
-        <v>104.392</v>
+        <v>104.443</v>
       </c>
       <c r="R96" t="n">
-        <v>106.189</v>
+        <v>106.045</v>
       </c>
       <c r="S96" t="n">
-        <v>-1.797</v>
+        <v>-1.602</v>
       </c>
       <c r="T96" t="n">
-        <v>0.26085</v>
+        <v>0.25676</v>
       </c>
       <c r="U96" t="n">
-        <v>0.17001</v>
+        <v>0.17127</v>
       </c>
       <c r="V96" t="n">
-        <v>72.51000000000001</v>
+        <v>72.25</v>
       </c>
       <c r="W96" t="n">
-        <v>73.87</v>
+        <v>73.44</v>
       </c>
       <c r="X96" t="n">
-        <v>0.395</v>
+        <v>0.3826</v>
       </c>
       <c r="Y96" t="n">
-        <v>25.16</v>
+        <v>25.148</v>
       </c>
       <c r="Z96" t="n">
-        <v>57.334</v>
+        <v>57.07</v>
       </c>
       <c r="AA96" t="n">
-        <v>7.502</v>
+        <v>7.51</v>
       </c>
       <c r="AB96" t="n">
-        <v>23.395</v>
+        <v>23.383</v>
       </c>
       <c r="AC96" t="n">
-        <v>14.687</v>
+        <v>14.441</v>
       </c>
       <c r="AD96" t="n">
-        <v>19.641</v>
+        <v>19.191</v>
       </c>
       <c r="AE96" t="n">
-        <v>8.284000000000001</v>
+        <v>8.157</v>
       </c>
       <c r="AF96" t="n">
-        <v>23.382</v>
+        <v>23.513</v>
       </c>
       <c r="AG96" t="n">
-        <v>12.497</v>
+        <v>12.542</v>
       </c>
       <c r="AH96" t="n">
-        <v>6.621</v>
+        <v>6.681</v>
       </c>
       <c r="AI96" t="n">
-        <v>2.111</v>
+        <v>2.226</v>
       </c>
       <c r="AJ96" t="n">
-        <v>16.777</v>
+        <v>16.722</v>
       </c>
       <c r="AK96" t="n">
-        <v>-6.6</v>
+        <v>-7</v>
       </c>
       <c r="AL96" t="n">
-        <v>-3.4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="97">
@@ -12626,22 +12626,22 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F102" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G102" t="b">
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>1558.292</v>
+        <v>1566.786</v>
       </c>
       <c r="I102" t="n">
-        <v>-4.9029</v>
+        <v>-4.7434</v>
       </c>
       <c r="J102" t="n">
-        <v>1640.1</v>
+        <v>1638.3</v>
       </c>
       <c r="K102" t="n">
         <v>87</v>
@@ -12662,70 +12662,70 @@
         <v>95</v>
       </c>
       <c r="Q102" t="n">
-        <v>109.841</v>
+        <v>109.454</v>
       </c>
       <c r="R102" t="n">
-        <v>109.059</v>
+        <v>108.263</v>
       </c>
       <c r="S102" t="n">
-        <v>0.782</v>
+        <v>1.191</v>
       </c>
       <c r="T102" t="n">
-        <v>0.30145</v>
+        <v>0.30234</v>
       </c>
       <c r="U102" t="n">
-        <v>0.14881</v>
+        <v>0.14843</v>
       </c>
       <c r="V102" t="n">
-        <v>74.59999999999999</v>
+        <v>74.09</v>
       </c>
       <c r="W102" t="n">
-        <v>73.98</v>
+        <v>73.22</v>
       </c>
       <c r="X102" t="n">
-        <v>0.4569</v>
+        <v>0.4735</v>
       </c>
       <c r="Y102" t="n">
-        <v>25.793</v>
+        <v>25.512</v>
       </c>
       <c r="Z102" t="n">
-        <v>58.329</v>
+        <v>58.31</v>
       </c>
       <c r="AA102" t="n">
-        <v>6.693</v>
+        <v>6.801</v>
       </c>
       <c r="AB102" t="n">
-        <v>20.718</v>
+        <v>20.783</v>
       </c>
       <c r="AC102" t="n">
-        <v>16.322</v>
+        <v>15.981</v>
       </c>
       <c r="AD102" t="n">
-        <v>22.092</v>
+        <v>21.715</v>
       </c>
       <c r="AE102" t="n">
-        <v>10.207</v>
+        <v>10.208</v>
       </c>
       <c r="AF102" t="n">
-        <v>23.162</v>
+        <v>23.106</v>
       </c>
       <c r="AG102" t="n">
-        <v>15.081</v>
+        <v>14.871</v>
       </c>
       <c r="AH102" t="n">
-        <v>6.771</v>
+        <v>6.681</v>
       </c>
       <c r="AI102" t="n">
-        <v>3.703</v>
+        <v>3.761</v>
       </c>
       <c r="AJ102" t="n">
-        <v>18.297</v>
+        <v>18.199</v>
       </c>
       <c r="AK102" t="n">
-        <v>-5.8</v>
+        <v>-3.6</v>
       </c>
       <c r="AL102" t="n">
-        <v>-2.3</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="103">
@@ -14546,22 +14546,22 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F118" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G118" t="b">
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>1405.083</v>
+        <v>1409.955</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3769</v>
+        <v>-0.3498</v>
       </c>
       <c r="J118" t="n">
-        <v>1412.5</v>
+        <v>1415.2</v>
       </c>
       <c r="K118" t="n">
         <v>165</v>
@@ -14582,70 +14582,70 @@
         <v>161</v>
       </c>
       <c r="Q118" t="n">
-        <v>110.53</v>
+        <v>110.278</v>
       </c>
       <c r="R118" t="n">
-        <v>107.113</v>
+        <v>106.528</v>
       </c>
       <c r="S118" t="n">
-        <v>3.417</v>
+        <v>3.75</v>
       </c>
       <c r="T118" t="n">
-        <v>0.27557</v>
+        <v>0.26932</v>
       </c>
       <c r="U118" t="n">
-        <v>0.14578</v>
+        <v>0.14751</v>
       </c>
       <c r="V118" t="n">
-        <v>76.67</v>
+        <v>76.66</v>
       </c>
       <c r="W118" t="n">
-        <v>74.22</v>
+        <v>73.95</v>
       </c>
       <c r="X118" t="n">
-        <v>0.5513</v>
+        <v>0.5651</v>
       </c>
       <c r="Y118" t="n">
-        <v>25.853</v>
+        <v>25.728</v>
       </c>
       <c r="Z118" t="n">
-        <v>59.981</v>
+        <v>59.747</v>
       </c>
       <c r="AA118" t="n">
-        <v>9.795</v>
+        <v>9.696999999999999</v>
       </c>
       <c r="AB118" t="n">
-        <v>28.173</v>
+        <v>28.106</v>
       </c>
       <c r="AC118" t="n">
-        <v>14.545</v>
+        <v>14.571</v>
       </c>
       <c r="AD118" t="n">
-        <v>20.019</v>
+        <v>20.006</v>
       </c>
       <c r="AE118" t="n">
-        <v>9.455</v>
+        <v>9.212999999999999</v>
       </c>
       <c r="AF118" t="n">
-        <v>24.365</v>
+        <v>24.379</v>
       </c>
       <c r="AG118" t="n">
-        <v>11.891</v>
+        <v>11.722</v>
       </c>
       <c r="AH118" t="n">
-        <v>5.494</v>
+        <v>5.534</v>
       </c>
       <c r="AI118" t="n">
-        <v>2.359</v>
+        <v>2.379</v>
       </c>
       <c r="AJ118" t="n">
-        <v>19.026</v>
+        <v>19.111</v>
       </c>
       <c r="AK118" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AL118" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -15266,22 +15266,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F124" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G124" t="b">
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>1741.914</v>
+        <v>1726.427</v>
       </c>
       <c r="I124" t="n">
-        <v>-2.3683</v>
+        <v>-2.3299</v>
       </c>
       <c r="J124" t="n">
-        <v>1701.1</v>
+        <v>1695.9</v>
       </c>
       <c r="K124" t="n">
         <v>41</v>
@@ -15302,70 +15302,70 @@
         <v>37</v>
       </c>
       <c r="Q124" t="n">
-        <v>116.268</v>
+        <v>115.605</v>
       </c>
       <c r="R124" t="n">
-        <v>107.645</v>
+        <v>107.911</v>
       </c>
       <c r="S124" t="n">
-        <v>8.624000000000001</v>
+        <v>7.693</v>
       </c>
       <c r="T124" t="n">
-        <v>0.23471</v>
+        <v>0.23714</v>
       </c>
       <c r="U124" t="n">
-        <v>0.14284</v>
+        <v>0.14071</v>
       </c>
       <c r="V124" t="n">
-        <v>78.7</v>
+        <v>78</v>
       </c>
       <c r="W124" t="n">
-        <v>72.28</v>
+        <v>72.17</v>
       </c>
       <c r="X124" t="n">
-        <v>0.575</v>
+        <v>0.5574</v>
       </c>
       <c r="Y124" t="n">
-        <v>26.754</v>
+        <v>26.712</v>
       </c>
       <c r="Z124" t="n">
-        <v>56.335</v>
+        <v>56.292</v>
       </c>
       <c r="AA124" t="n">
-        <v>9.887</v>
+        <v>9.778</v>
       </c>
       <c r="AB124" t="n">
-        <v>28.574</v>
+        <v>28.09</v>
       </c>
       <c r="AC124" t="n">
-        <v>15.307</v>
+        <v>15.319</v>
       </c>
       <c r="AD124" t="n">
-        <v>19.531</v>
+        <v>19.575</v>
       </c>
       <c r="AE124" t="n">
-        <v>7.044</v>
+        <v>7.102</v>
       </c>
       <c r="AF124" t="n">
-        <v>22.612</v>
+        <v>22.53</v>
       </c>
       <c r="AG124" t="n">
-        <v>16.789</v>
+        <v>16.734</v>
       </c>
       <c r="AH124" t="n">
-        <v>4.69</v>
+        <v>4.77</v>
       </c>
       <c r="AI124" t="n">
-        <v>2.693</v>
+        <v>2.681</v>
       </c>
       <c r="AJ124" t="n">
-        <v>18.371</v>
+        <v>18.261</v>
       </c>
       <c r="AK124" t="n">
-        <v>-5.8</v>
+        <v>-2.6</v>
       </c>
       <c r="AL124" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="125">
@@ -15626,22 +15626,22 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F127" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G127" t="b">
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>1843.67</v>
+        <v>1848.879</v>
       </c>
       <c r="I127" t="n">
-        <v>4.0673</v>
+        <v>3.6941</v>
       </c>
       <c r="J127" t="n">
-        <v>1715.1</v>
+        <v>1707.5</v>
       </c>
       <c r="K127" t="n">
         <v>24</v>
@@ -15662,70 +15662,70 @@
         <v>25</v>
       </c>
       <c r="Q127" t="n">
-        <v>118.626</v>
+        <v>118.636</v>
       </c>
       <c r="R127" t="n">
-        <v>104.063</v>
+        <v>103.684</v>
       </c>
       <c r="S127" t="n">
-        <v>14.562</v>
+        <v>14.952</v>
       </c>
       <c r="T127" t="n">
-        <v>0.28798</v>
+        <v>0.28843</v>
       </c>
       <c r="U127" t="n">
-        <v>0.1446</v>
+        <v>0.1443</v>
       </c>
       <c r="V127" t="n">
-        <v>75.41</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="W127" t="n">
-        <v>66.05</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="X127" t="n">
-        <v>0.6377</v>
+        <v>0.6599</v>
       </c>
       <c r="Y127" t="n">
-        <v>26.586</v>
+        <v>26.598</v>
       </c>
       <c r="Z127" t="n">
-        <v>54.214</v>
+        <v>54.144</v>
       </c>
       <c r="AA127" t="n">
-        <v>7.939</v>
+        <v>7.949</v>
       </c>
       <c r="AB127" t="n">
-        <v>22.507</v>
+        <v>22.444</v>
       </c>
       <c r="AC127" t="n">
-        <v>14.304</v>
+        <v>14.257</v>
       </c>
       <c r="AD127" t="n">
-        <v>18.475</v>
+        <v>18.578</v>
       </c>
       <c r="AE127" t="n">
-        <v>8.02</v>
+        <v>7.989</v>
       </c>
       <c r="AF127" t="n">
-        <v>19.803</v>
+        <v>19.669</v>
       </c>
       <c r="AG127" t="n">
-        <v>15.214</v>
+        <v>15.352</v>
       </c>
       <c r="AH127" t="n">
-        <v>7.151</v>
+        <v>7.207</v>
       </c>
       <c r="AI127" t="n">
-        <v>2.009</v>
+        <v>1.989</v>
       </c>
       <c r="AJ127" t="n">
-        <v>17.841</v>
+        <v>17.637</v>
       </c>
       <c r="AK127" t="n">
-        <v>-2</v>
+        <v>2.8</v>
       </c>
       <c r="AL127" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="128">
@@ -15746,22 +15746,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F128" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G128" t="b">
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>2027.369</v>
+        <v>2031.132</v>
       </c>
       <c r="I128" t="n">
-        <v>3.1622</v>
+        <v>2.7523</v>
       </c>
       <c r="J128" t="n">
-        <v>1686.9</v>
+        <v>1687.1</v>
       </c>
       <c r="K128" t="n">
         <v>7</v>
@@ -15782,70 +15782,70 @@
         <v>8</v>
       </c>
       <c r="Q128" t="n">
-        <v>118.43</v>
+        <v>118.894</v>
       </c>
       <c r="R128" t="n">
-        <v>96.009</v>
+        <v>94.631</v>
       </c>
       <c r="S128" t="n">
-        <v>22.421</v>
+        <v>24.263</v>
       </c>
       <c r="T128" t="n">
-        <v>0.31841</v>
+        <v>0.31987</v>
       </c>
       <c r="U128" t="n">
-        <v>0.14651</v>
+        <v>0.14543</v>
       </c>
       <c r="V128" t="n">
-        <v>81.81999999999999</v>
+        <v>82.14</v>
       </c>
       <c r="W128" t="n">
-        <v>65.73</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="X128" t="n">
-        <v>0.8083</v>
+        <v>0.8142</v>
       </c>
       <c r="Y128" t="n">
-        <v>29.319</v>
+        <v>29.47</v>
       </c>
       <c r="Z128" t="n">
-        <v>60.09</v>
+        <v>60.231</v>
       </c>
       <c r="AA128" t="n">
-        <v>8.923999999999999</v>
+        <v>8.946999999999999</v>
       </c>
       <c r="AB128" t="n">
-        <v>23.282</v>
+        <v>23.297</v>
       </c>
       <c r="AC128" t="n">
-        <v>14.253</v>
+        <v>14.257</v>
       </c>
       <c r="AD128" t="n">
-        <v>20.946</v>
+        <v>21.098</v>
       </c>
       <c r="AE128" t="n">
-        <v>10.562</v>
+        <v>10.686</v>
       </c>
       <c r="AF128" t="n">
-        <v>22.715</v>
+        <v>22.792</v>
       </c>
       <c r="AG128" t="n">
-        <v>17.425</v>
+        <v>17.443</v>
       </c>
       <c r="AH128" t="n">
-        <v>9.068</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AI128" t="n">
-        <v>2.831</v>
+        <v>2.725</v>
       </c>
       <c r="AJ128" t="n">
-        <v>16.083</v>
+        <v>16.022</v>
       </c>
       <c r="AK128" t="n">
-        <v>0.4</v>
+        <v>12.2</v>
       </c>
       <c r="AL128" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="129">
@@ -16106,22 +16106,22 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F131" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G131" t="b">
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>1303.595</v>
+        <v>1300.904</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.4112</v>
+        <v>-1.3402</v>
       </c>
       <c r="J131" t="n">
-        <v>1424.2</v>
+        <v>1420.2</v>
       </c>
       <c r="K131" t="n">
         <v>342</v>
@@ -16142,70 +16142,70 @@
         <v>348</v>
       </c>
       <c r="Q131" t="n">
-        <v>98.508</v>
+        <v>97.96599999999999</v>
       </c>
       <c r="R131" t="n">
-        <v>116.794</v>
+        <v>116.328</v>
       </c>
       <c r="S131" t="n">
-        <v>-18.286</v>
+        <v>-18.363</v>
       </c>
       <c r="T131" t="n">
-        <v>0.30563</v>
+        <v>0.30936</v>
       </c>
       <c r="U131" t="n">
-        <v>0.18378</v>
+        <v>0.18774</v>
       </c>
       <c r="V131" t="n">
-        <v>70.53</v>
+        <v>70.14</v>
       </c>
       <c r="W131" t="n">
-        <v>83.98</v>
+        <v>83.62</v>
       </c>
       <c r="X131" t="n">
-        <v>0.3817</v>
+        <v>0.36</v>
       </c>
       <c r="Y131" t="n">
-        <v>22.927</v>
+        <v>22.78</v>
       </c>
       <c r="Z131" t="n">
-        <v>58.753</v>
+        <v>58.64</v>
       </c>
       <c r="AA131" t="n">
-        <v>7.958</v>
+        <v>7.97</v>
       </c>
       <c r="AB131" t="n">
-        <v>25.413</v>
+        <v>25.39</v>
       </c>
       <c r="AC131" t="n">
-        <v>16.722</v>
+        <v>16.61</v>
       </c>
       <c r="AD131" t="n">
         <v>21.95</v>
       </c>
       <c r="AE131" t="n">
-        <v>9.91</v>
+        <v>10.09</v>
       </c>
       <c r="AF131" t="n">
-        <v>21.352</v>
+        <v>21.34</v>
       </c>
       <c r="AG131" t="n">
-        <v>10.484</v>
+        <v>10.44</v>
       </c>
       <c r="AH131" t="n">
-        <v>6.093</v>
+        <v>6.37</v>
       </c>
       <c r="AI131" t="n">
-        <v>2.938</v>
+        <v>2.98</v>
       </c>
       <c r="AJ131" t="n">
-        <v>19.442</v>
+        <v>19.33</v>
       </c>
       <c r="AK131" t="n">
-        <v>-4</v>
+        <v>-4.2</v>
       </c>
       <c r="AL131" t="n">
-        <v>-1.8</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="132">
@@ -17066,22 +17066,22 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F139" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G139" t="b">
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>1881.837</v>
+        <v>1887.358</v>
       </c>
       <c r="I139" t="n">
-        <v>5.4881</v>
+        <v>5.1867</v>
       </c>
       <c r="J139" t="n">
-        <v>1728.4</v>
+        <v>1721.6</v>
       </c>
       <c r="K139" t="n">
         <v>27</v>
@@ -17102,70 +17102,70 @@
         <v>28</v>
       </c>
       <c r="Q139" t="n">
-        <v>116.581</v>
+        <v>117.124</v>
       </c>
       <c r="R139" t="n">
-        <v>106.115</v>
+        <v>106.558</v>
       </c>
       <c r="S139" t="n">
-        <v>10.467</v>
+        <v>10.566</v>
       </c>
       <c r="T139" t="n">
-        <v>0.31171</v>
+        <v>0.31218</v>
       </c>
       <c r="U139" t="n">
-        <v>0.14546</v>
+        <v>0.14265</v>
       </c>
       <c r="V139" t="n">
-        <v>81.18000000000001</v>
+        <v>81.47</v>
       </c>
       <c r="W139" t="n">
-        <v>73.83</v>
+        <v>74.06</v>
       </c>
       <c r="X139" t="n">
-        <v>0.6058</v>
+        <v>0.629</v>
       </c>
       <c r="Y139" t="n">
-        <v>28.2</v>
+        <v>28.383</v>
       </c>
       <c r="Z139" t="n">
-        <v>60.675</v>
+        <v>60.754</v>
       </c>
       <c r="AA139" t="n">
-        <v>8.319000000000001</v>
+        <v>8.226000000000001</v>
       </c>
       <c r="AB139" t="n">
-        <v>23.861</v>
+        <v>23.793</v>
       </c>
       <c r="AC139" t="n">
-        <v>16.458</v>
+        <v>16.474</v>
       </c>
       <c r="AD139" t="n">
-        <v>22.722</v>
+        <v>22.753</v>
       </c>
       <c r="AE139" t="n">
-        <v>11.162</v>
+        <v>11.124</v>
       </c>
       <c r="AF139" t="n">
-        <v>24.629</v>
+        <v>24.504</v>
       </c>
       <c r="AG139" t="n">
-        <v>16.203</v>
+        <v>16.144</v>
       </c>
       <c r="AH139" t="n">
-        <v>7.096</v>
+        <v>7.009</v>
       </c>
       <c r="AI139" t="n">
-        <v>4.319</v>
+        <v>4.267</v>
       </c>
       <c r="AJ139" t="n">
-        <v>18.336</v>
+        <v>18.164</v>
       </c>
       <c r="AK139" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="AL139" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="140">
@@ -17186,22 +17186,22 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F140" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G140" t="b">
         <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>1398.339</v>
+        <v>1395.208</v>
       </c>
       <c r="I140" t="n">
-        <v>-2.0204</v>
+        <v>-1.8721</v>
       </c>
       <c r="J140" t="n">
-        <v>1566.1</v>
+        <v>1564.2</v>
       </c>
       <c r="K140" t="n">
         <v>225</v>
@@ -17222,70 +17222,70 @@
         <v>235</v>
       </c>
       <c r="Q140" t="n">
-        <v>99.745</v>
+        <v>100.204</v>
       </c>
       <c r="R140" t="n">
-        <v>111.109</v>
+        <v>112.173</v>
       </c>
       <c r="S140" t="n">
-        <v>-11.364</v>
+        <v>-11.969</v>
       </c>
       <c r="T140" t="n">
-        <v>0.33031</v>
+        <v>0.33313</v>
       </c>
       <c r="U140" t="n">
-        <v>0.17515</v>
+        <v>0.17743</v>
       </c>
       <c r="V140" t="n">
-        <v>66.55</v>
+        <v>67.02</v>
       </c>
       <c r="W140" t="n">
-        <v>74.34</v>
+        <v>75.25</v>
       </c>
       <c r="X140" t="n">
-        <v>0.2633</v>
+        <v>0.2551</v>
       </c>
       <c r="Y140" t="n">
-        <v>22.906</v>
+        <v>23.525</v>
       </c>
       <c r="Z140" t="n">
-        <v>56.5</v>
+        <v>56.829</v>
       </c>
       <c r="AA140" t="n">
-        <v>5.433</v>
+        <v>5.73</v>
       </c>
       <c r="AB140" t="n">
-        <v>17.989</v>
+        <v>18.165</v>
       </c>
       <c r="AC140" t="n">
-        <v>15.218</v>
+        <v>15.006</v>
       </c>
       <c r="AD140" t="n">
-        <v>21.099</v>
+        <v>20.791</v>
       </c>
       <c r="AE140" t="n">
-        <v>10.577</v>
+        <v>10.814</v>
       </c>
       <c r="AF140" t="n">
-        <v>21.197</v>
+        <v>21.322</v>
       </c>
       <c r="AG140" t="n">
-        <v>12.884</v>
+        <v>13.414</v>
       </c>
       <c r="AH140" t="n">
-        <v>6.527</v>
+        <v>6.597</v>
       </c>
       <c r="AI140" t="n">
-        <v>2.481</v>
+        <v>2.565</v>
       </c>
       <c r="AJ140" t="n">
-        <v>16.734</v>
+        <v>16.681</v>
       </c>
       <c r="AK140" t="n">
-        <v>-6</v>
+        <v>-12.4</v>
       </c>
       <c r="AL140" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.300000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -17546,22 +17546,22 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F143" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G143" t="b">
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>1323.097</v>
+        <v>1325.524</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.5849</v>
+        <v>-0.465</v>
       </c>
       <c r="J143" t="n">
-        <v>1401.7</v>
+        <v>1399</v>
       </c>
       <c r="K143" t="n">
         <v>290</v>
@@ -17582,70 +17582,70 @@
         <v>282</v>
       </c>
       <c r="Q143" t="n">
-        <v>104.757</v>
+        <v>105.584</v>
       </c>
       <c r="R143" t="n">
-        <v>108.578</v>
+        <v>108.389</v>
       </c>
       <c r="S143" t="n">
-        <v>-3.822</v>
+        <v>-2.804</v>
       </c>
       <c r="T143" t="n">
-        <v>0.21403</v>
+        <v>0.22286</v>
       </c>
       <c r="U143" t="n">
-        <v>0.17293</v>
+        <v>0.17072</v>
       </c>
       <c r="V143" t="n">
-        <v>72.37</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="W143" t="n">
-        <v>75.05</v>
+        <v>74.47</v>
       </c>
       <c r="X143" t="n">
-        <v>0.4909</v>
+        <v>0.5063</v>
       </c>
       <c r="Y143" t="n">
-        <v>25.855</v>
+        <v>25.759</v>
       </c>
       <c r="Z143" t="n">
-        <v>55.6</v>
+        <v>55.648</v>
       </c>
       <c r="AA143" t="n">
-        <v>7.7</v>
+        <v>7.766</v>
       </c>
       <c r="AB143" t="n">
-        <v>21.25</v>
+        <v>21.222</v>
       </c>
       <c r="AC143" t="n">
-        <v>12.964</v>
+        <v>13.112</v>
       </c>
       <c r="AD143" t="n">
-        <v>17.782</v>
+        <v>17.983</v>
       </c>
       <c r="AE143" t="n">
-        <v>6.195</v>
+        <v>6.564</v>
       </c>
       <c r="AF143" t="n">
-        <v>22.541</v>
+        <v>22.432</v>
       </c>
       <c r="AG143" t="n">
-        <v>14.045</v>
+        <v>13.987</v>
       </c>
       <c r="AH143" t="n">
-        <v>6.686</v>
+        <v>6.635</v>
       </c>
       <c r="AI143" t="n">
-        <v>3.032</v>
+        <v>3.161</v>
       </c>
       <c r="AJ143" t="n">
-        <v>16.055</v>
+        <v>16.136</v>
       </c>
       <c r="AK143" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AL143" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="144">
@@ -17666,22 +17666,22 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F144" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G144" t="b">
         <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>1733.143</v>
+        <v>1719.236</v>
       </c>
       <c r="I144" t="n">
-        <v>3.2041</v>
+        <v>2.9746</v>
       </c>
       <c r="J144" t="n">
-        <v>1485.6</v>
+        <v>1481.5</v>
       </c>
       <c r="K144" t="n">
         <v>116</v>
@@ -17702,70 +17702,70 @@
         <v>100</v>
       </c>
       <c r="Q144" t="n">
-        <v>117.833</v>
+        <v>117.433</v>
       </c>
       <c r="R144" t="n">
-        <v>110.755</v>
+        <v>111.215</v>
       </c>
       <c r="S144" t="n">
-        <v>7.078</v>
+        <v>6.218</v>
       </c>
       <c r="T144" t="n">
-        <v>0.16993</v>
+        <v>0.17119</v>
       </c>
       <c r="U144" t="n">
-        <v>0.13162</v>
+        <v>0.1328</v>
       </c>
       <c r="V144" t="n">
-        <v>76.48</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="W144" t="n">
-        <v>72</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="X144" t="n">
-        <v>0.7874</v>
+        <v>0.753</v>
       </c>
       <c r="Y144" t="n">
-        <v>27.043</v>
+        <v>27.076</v>
       </c>
       <c r="Z144" t="n">
-        <v>53.441</v>
+        <v>53.286</v>
       </c>
       <c r="AA144" t="n">
-        <v>10.316</v>
+        <v>10.19</v>
       </c>
       <c r="AB144" t="n">
-        <v>26.045</v>
+        <v>25.549</v>
       </c>
       <c r="AC144" t="n">
-        <v>12.082</v>
+        <v>12.144</v>
       </c>
       <c r="AD144" t="n">
-        <v>17.058</v>
+        <v>17.311</v>
       </c>
       <c r="AE144" t="n">
-        <v>4.583</v>
+        <v>4.673</v>
       </c>
       <c r="AF144" t="n">
-        <v>21.414</v>
+        <v>21.626</v>
       </c>
       <c r="AG144" t="n">
-        <v>16.67</v>
+        <v>16.533</v>
       </c>
       <c r="AH144" t="n">
-        <v>6.082</v>
+        <v>5.978</v>
       </c>
       <c r="AI144" t="n">
-        <v>3.335</v>
+        <v>3.308</v>
       </c>
       <c r="AJ144" t="n">
-        <v>14.406</v>
+        <v>14.335</v>
       </c>
       <c r="AK144" t="n">
-        <v>-5</v>
+        <v>-2.4</v>
       </c>
       <c r="AL144" t="n">
-        <v>-0.4</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="145">
@@ -18386,22 +18386,22 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F150" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G150" t="b">
         <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>1845.216</v>
+        <v>1855.877</v>
       </c>
       <c r="I150" t="n">
-        <v>-2.9919</v>
+        <v>-2.8167</v>
       </c>
       <c r="J150" t="n">
-        <v>1682.1</v>
+        <v>1683.7</v>
       </c>
       <c r="K150" t="n">
         <v>16</v>
@@ -18422,70 +18422,70 @@
         <v>14</v>
       </c>
       <c r="Q150" t="n">
-        <v>120.186</v>
+        <v>119.153</v>
       </c>
       <c r="R150" t="n">
-        <v>101.95</v>
+        <v>101.26</v>
       </c>
       <c r="S150" t="n">
-        <v>18.236</v>
+        <v>17.893</v>
       </c>
       <c r="T150" t="n">
-        <v>0.28974</v>
+        <v>0.29081</v>
       </c>
       <c r="U150" t="n">
-        <v>0.15782</v>
+        <v>0.15842</v>
       </c>
       <c r="V150" t="n">
-        <v>85.93000000000001</v>
+        <v>84.92</v>
       </c>
       <c r="W150" t="n">
-        <v>72.61</v>
+        <v>71.87</v>
       </c>
       <c r="X150" t="n">
-        <v>0.7125</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="Y150" t="n">
-        <v>28.869</v>
+        <v>28.525</v>
       </c>
       <c r="Z150" t="n">
-        <v>61.753</v>
+        <v>61.485</v>
       </c>
       <c r="AA150" t="n">
-        <v>11.681</v>
+        <v>11.45</v>
       </c>
       <c r="AB150" t="n">
-        <v>32.785</v>
+        <v>32.596</v>
       </c>
       <c r="AC150" t="n">
-        <v>16.076</v>
+        <v>16.013</v>
       </c>
       <c r="AD150" t="n">
-        <v>20.904</v>
+        <v>20.867</v>
       </c>
       <c r="AE150" t="n">
-        <v>10.76</v>
+        <v>10.774</v>
       </c>
       <c r="AF150" t="n">
-        <v>26.158</v>
+        <v>26.088</v>
       </c>
       <c r="AG150" t="n">
-        <v>17.208</v>
+        <v>16.795</v>
       </c>
       <c r="AH150" t="n">
-        <v>6.971</v>
+        <v>6.96</v>
       </c>
       <c r="AI150" t="n">
-        <v>3.268</v>
+        <v>3.239</v>
       </c>
       <c r="AJ150" t="n">
-        <v>18.489</v>
+        <v>18.225</v>
       </c>
       <c r="AK150" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="AL150" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="151">
@@ -18746,22 +18746,22 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F153" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G153" t="b">
         <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>1397.399</v>
+        <v>1402.147</v>
       </c>
       <c r="I153" t="n">
-        <v>-4.1654</v>
+        <v>-3.9937</v>
       </c>
       <c r="J153" t="n">
-        <v>1557.5</v>
+        <v>1553.9</v>
       </c>
       <c r="K153" t="n">
         <v>293</v>
@@ -18782,70 +18782,70 @@
         <v>289</v>
       </c>
       <c r="Q153" t="n">
-        <v>100.546</v>
+        <v>101.204</v>
       </c>
       <c r="R153" t="n">
-        <v>114.659</v>
+        <v>114.468</v>
       </c>
       <c r="S153" t="n">
-        <v>-14.113</v>
+        <v>-13.264</v>
       </c>
       <c r="T153" t="n">
-        <v>0.2832</v>
+        <v>0.28553</v>
       </c>
       <c r="U153" t="n">
-        <v>0.19031</v>
+        <v>0.1854</v>
       </c>
       <c r="V153" t="n">
-        <v>66.79000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="W153" t="n">
-        <v>76.22</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="X153" t="n">
-        <v>0.2682</v>
+        <v>0.2903</v>
       </c>
       <c r="Y153" t="n">
-        <v>22.923</v>
+        <v>22.938</v>
       </c>
       <c r="Z153" t="n">
-        <v>54.455</v>
+        <v>54.711</v>
       </c>
       <c r="AA153" t="n">
-        <v>8.218</v>
+        <v>8.228999999999999</v>
       </c>
       <c r="AB153" t="n">
-        <v>25.95</v>
+        <v>26.199</v>
       </c>
       <c r="AC153" t="n">
-        <v>12.727</v>
+        <v>12.679</v>
       </c>
       <c r="AD153" t="n">
-        <v>18.8</v>
+        <v>18.715</v>
       </c>
       <c r="AE153" t="n">
-        <v>8.827</v>
+        <v>8.802</v>
       </c>
       <c r="AF153" t="n">
-        <v>22.291</v>
+        <v>21.999</v>
       </c>
       <c r="AG153" t="n">
-        <v>13.868</v>
+        <v>13.802</v>
       </c>
       <c r="AH153" t="n">
-        <v>4.105</v>
+        <v>4.062</v>
       </c>
       <c r="AI153" t="n">
-        <v>3.823</v>
+        <v>3.641</v>
       </c>
       <c r="AJ153" t="n">
-        <v>16.777</v>
+        <v>16.877</v>
       </c>
       <c r="AK153" t="n">
-        <v>-4.4</v>
+        <v>-2.2</v>
       </c>
       <c r="AL153" t="n">
-        <v>-9.4</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="154">
@@ -18866,22 +18866,22 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F154" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G154" t="b">
         <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>1640.511</v>
+        <v>1634.991</v>
       </c>
       <c r="I154" t="n">
-        <v>-1.2644</v>
+        <v>-1.5391</v>
       </c>
       <c r="J154" t="n">
-        <v>1660.6</v>
+        <v>1667.8</v>
       </c>
       <c r="K154" t="n">
         <v>62</v>
@@ -18902,70 +18902,70 @@
         <v>77</v>
       </c>
       <c r="Q154" t="n">
-        <v>115.447</v>
+        <v>115.62</v>
       </c>
       <c r="R154" t="n">
-        <v>111.343</v>
+        <v>111.893</v>
       </c>
       <c r="S154" t="n">
-        <v>4.105</v>
+        <v>3.727</v>
       </c>
       <c r="T154" t="n">
-        <v>0.29757</v>
+        <v>0.29877</v>
       </c>
       <c r="U154" t="n">
-        <v>0.1541</v>
+        <v>0.15222</v>
       </c>
       <c r="V154" t="n">
-        <v>81.51000000000001</v>
+        <v>81.44</v>
       </c>
       <c r="W154" t="n">
-        <v>78.38</v>
+        <v>78.58</v>
       </c>
       <c r="X154" t="n">
-        <v>0.4792</v>
+        <v>0.4645</v>
       </c>
       <c r="Y154" t="n">
-        <v>27.933</v>
+        <v>28.067</v>
       </c>
       <c r="Z154" t="n">
-        <v>59.458</v>
+        <v>59.541</v>
       </c>
       <c r="AA154" t="n">
-        <v>6.85</v>
+        <v>6.765</v>
       </c>
       <c r="AB154" t="n">
-        <v>20.589</v>
+        <v>20.495</v>
       </c>
       <c r="AC154" t="n">
-        <v>18.796</v>
+        <v>18.543</v>
       </c>
       <c r="AD154" t="n">
-        <v>24.537</v>
+        <v>24.305</v>
       </c>
       <c r="AE154" t="n">
-        <v>10.572</v>
+        <v>10.566</v>
       </c>
       <c r="AF154" t="n">
-        <v>24.9</v>
+        <v>24.712</v>
       </c>
       <c r="AG154" t="n">
-        <v>14.86</v>
+        <v>14.685</v>
       </c>
       <c r="AH154" t="n">
-        <v>6.157</v>
+        <v>5.924</v>
       </c>
       <c r="AI154" t="n">
-        <v>3.997</v>
+        <v>3.889</v>
       </c>
       <c r="AJ154" t="n">
-        <v>18.783</v>
+        <v>18.672</v>
       </c>
       <c r="AK154" t="n">
-        <v>-6.6</v>
+        <v>-6.2</v>
       </c>
       <c r="AL154" t="n">
-        <v>-8.199999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -19466,22 +19466,22 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F159" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G159" t="b">
         <v>1</v>
       </c>
       <c r="H159" t="n">
-        <v>1544.306</v>
+        <v>1537.357</v>
       </c>
       <c r="I159" t="n">
-        <v>-6.9692</v>
+        <v>-6.3402</v>
       </c>
       <c r="J159" t="n">
-        <v>1680.7</v>
+        <v>1671.3</v>
       </c>
       <c r="K159" t="n">
         <v>86</v>
@@ -19502,70 +19502,70 @@
         <v>91</v>
       </c>
       <c r="Q159" t="n">
-        <v>104.737</v>
+        <v>105.219</v>
       </c>
       <c r="R159" t="n">
-        <v>105.103</v>
+        <v>105.81</v>
       </c>
       <c r="S159" t="n">
-        <v>-0.366</v>
+        <v>-0.591</v>
       </c>
       <c r="T159" t="n">
-        <v>0.2957</v>
+        <v>0.29234</v>
       </c>
       <c r="U159" t="n">
-        <v>0.15907</v>
+        <v>0.15799</v>
       </c>
       <c r="V159" t="n">
-        <v>74.68000000000001</v>
+        <v>75.31</v>
       </c>
       <c r="W159" t="n">
-        <v>75.17</v>
+        <v>75.95</v>
       </c>
       <c r="X159" t="n">
-        <v>0.3955</v>
+        <v>0.3703</v>
       </c>
       <c r="Y159" t="n">
-        <v>26.564</v>
+        <v>26.891</v>
       </c>
       <c r="Z159" t="n">
-        <v>60.505</v>
+        <v>60.822</v>
       </c>
       <c r="AA159" t="n">
-        <v>8.064</v>
+        <v>8.061999999999999</v>
       </c>
       <c r="AB159" t="n">
-        <v>25.232</v>
+        <v>25.191</v>
       </c>
       <c r="AC159" t="n">
-        <v>13.491</v>
+        <v>13.55</v>
       </c>
       <c r="AD159" t="n">
-        <v>20.073</v>
+        <v>19.9</v>
       </c>
       <c r="AE159" t="n">
-        <v>9.327</v>
+        <v>9.282999999999999</v>
       </c>
       <c r="AF159" t="n">
-        <v>21.973</v>
+        <v>22.348</v>
       </c>
       <c r="AG159" t="n">
-        <v>15.364</v>
+        <v>15.6</v>
       </c>
       <c r="AH159" t="n">
-        <v>9.459</v>
+        <v>9.257999999999999</v>
       </c>
       <c r="AI159" t="n">
-        <v>2.959</v>
+        <v>3.087</v>
       </c>
       <c r="AJ159" t="n">
-        <v>17.127</v>
+        <v>16.993</v>
       </c>
       <c r="AK159" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AL159" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="160">
@@ -19706,22 +19706,22 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F161" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G161" t="b">
         <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>1607.209</v>
+        <v>1602</v>
       </c>
       <c r="I161" t="n">
-        <v>-7.8093</v>
+        <v>-7.4945</v>
       </c>
       <c r="J161" t="n">
-        <v>1715.9</v>
+        <v>1722.6</v>
       </c>
       <c r="K161" t="n">
         <v>128</v>
@@ -19742,70 +19742,70 @@
         <v>151</v>
       </c>
       <c r="Q161" t="n">
-        <v>104.081</v>
+        <v>103.793</v>
       </c>
       <c r="R161" t="n">
-        <v>114.203</v>
+        <v>114.527</v>
       </c>
       <c r="S161" t="n">
-        <v>-10.122</v>
+        <v>-10.735</v>
       </c>
       <c r="T161" t="n">
-        <v>0.31669</v>
+        <v>0.31901</v>
       </c>
       <c r="U161" t="n">
-        <v>0.1739</v>
+        <v>0.17758</v>
       </c>
       <c r="V161" t="n">
-        <v>69.88</v>
+        <v>69.63</v>
       </c>
       <c r="W161" t="n">
-        <v>76.42</v>
+        <v>76.56</v>
       </c>
       <c r="X161" t="n">
-        <v>0.3829</v>
+        <v>0.3594</v>
       </c>
       <c r="Y161" t="n">
-        <v>23.011</v>
+        <v>23.018</v>
       </c>
       <c r="Z161" t="n">
-        <v>56.875</v>
+        <v>56.69</v>
       </c>
       <c r="AA161" t="n">
-        <v>8.289</v>
+        <v>8.288</v>
       </c>
       <c r="AB161" t="n">
-        <v>26.492</v>
+        <v>26.331</v>
       </c>
       <c r="AC161" t="n">
-        <v>15.13</v>
+        <v>15.007</v>
       </c>
       <c r="AD161" t="n">
-        <v>20.784</v>
+        <v>20.79</v>
       </c>
       <c r="AE161" t="n">
-        <v>10.548</v>
+        <v>10.652</v>
       </c>
       <c r="AF161" t="n">
-        <v>22.203</v>
+        <v>22.21</v>
       </c>
       <c r="AG161" t="n">
-        <v>10.562</v>
+        <v>10.426</v>
       </c>
       <c r="AH161" t="n">
-        <v>4.809</v>
+        <v>4.874</v>
       </c>
       <c r="AI161" t="n">
-        <v>2.877</v>
+        <v>2.88</v>
       </c>
       <c r="AJ161" t="n">
-        <v>18.067</v>
+        <v>18.09</v>
       </c>
       <c r="AK161" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AL161" t="n">
-        <v>-4.5</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="162">
@@ -19946,22 +19946,22 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F163" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G163" t="b">
         <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>1720.824</v>
+        <v>1726.811</v>
       </c>
       <c r="I163" t="n">
-        <v>2.8141</v>
+        <v>2.6895</v>
       </c>
       <c r="J163" t="n">
-        <v>1422.5</v>
+        <v>1428.4</v>
       </c>
       <c r="K163" t="n">
         <v>68</v>
@@ -19982,70 +19982,70 @@
         <v>62</v>
       </c>
       <c r="Q163" t="n">
-        <v>114.819</v>
+        <v>115.07</v>
       </c>
       <c r="R163" t="n">
-        <v>100.313</v>
+        <v>100.006</v>
       </c>
       <c r="S163" t="n">
-        <v>14.507</v>
+        <v>15.064</v>
       </c>
       <c r="T163" t="n">
-        <v>0.35125</v>
+        <v>0.34832</v>
       </c>
       <c r="U163" t="n">
-        <v>0.1369</v>
+        <v>0.13903</v>
       </c>
       <c r="V163" t="n">
-        <v>76.93000000000001</v>
+        <v>76.83</v>
       </c>
       <c r="W163" t="n">
-        <v>67.41</v>
+        <v>66.97</v>
       </c>
       <c r="X163" t="n">
-        <v>0.8348</v>
+        <v>0.84</v>
       </c>
       <c r="Y163" t="n">
-        <v>26.761</v>
+        <v>26.424</v>
       </c>
       <c r="Z163" t="n">
-        <v>59.313</v>
+        <v>58.808</v>
       </c>
       <c r="AA163" t="n">
-        <v>6.48</v>
+        <v>6.408</v>
       </c>
       <c r="AB163" t="n">
-        <v>20.836</v>
+        <v>20.808</v>
       </c>
       <c r="AC163" t="n">
-        <v>16.925</v>
+        <v>16.896</v>
       </c>
       <c r="AD163" t="n">
-        <v>23.036</v>
+        <v>22.808</v>
       </c>
       <c r="AE163" t="n">
-        <v>11.342</v>
+        <v>11.096</v>
       </c>
       <c r="AF163" t="n">
-        <v>20.895</v>
+        <v>20.68</v>
       </c>
       <c r="AG163" t="n">
-        <v>13.158</v>
+        <v>13.008</v>
       </c>
       <c r="AH163" t="n">
-        <v>10.382</v>
+        <v>10.12</v>
       </c>
       <c r="AI163" t="n">
-        <v>4.297</v>
+        <v>4.248</v>
       </c>
       <c r="AJ163" t="n">
-        <v>19.422</v>
+        <v>19.064</v>
       </c>
       <c r="AK163" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AL163" t="n">
-        <v>10.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="164">
@@ -20186,22 +20186,22 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F165" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G165" t="b">
         <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>1567.005</v>
+        <v>1558.66</v>
       </c>
       <c r="I165" t="n">
-        <v>-5.2285</v>
+        <v>-5.1449</v>
       </c>
       <c r="J165" t="n">
-        <v>1607.8</v>
+        <v>1604.3</v>
       </c>
       <c r="K165" t="n">
         <v>130</v>
@@ -20222,70 +20222,70 @@
         <v>125</v>
       </c>
       <c r="Q165" t="n">
-        <v>104.684</v>
+        <v>104.316</v>
       </c>
       <c r="R165" t="n">
-        <v>106.286</v>
+        <v>106.546</v>
       </c>
       <c r="S165" t="n">
-        <v>-1.603</v>
+        <v>-2.229</v>
       </c>
       <c r="T165" t="n">
-        <v>0.33967</v>
+        <v>0.34083</v>
       </c>
       <c r="U165" t="n">
-        <v>0.18237</v>
+        <v>0.18099</v>
       </c>
       <c r="V165" t="n">
-        <v>75.58</v>
+        <v>75.17</v>
       </c>
       <c r="W165" t="n">
-        <v>76.7</v>
+        <v>76.72</v>
       </c>
       <c r="X165" t="n">
-        <v>0.424</v>
+        <v>0.4032</v>
       </c>
       <c r="Y165" t="n">
-        <v>26.848</v>
+        <v>26.622</v>
       </c>
       <c r="Z165" t="n">
-        <v>61.456</v>
+        <v>61.473</v>
       </c>
       <c r="AA165" t="n">
-        <v>6.584</v>
+        <v>6.866</v>
       </c>
       <c r="AB165" t="n">
-        <v>20.632</v>
+        <v>21.159</v>
       </c>
       <c r="AC165" t="n">
-        <v>15.304</v>
+        <v>15.525</v>
       </c>
       <c r="AD165" t="n">
-        <v>21.184</v>
+        <v>21.331</v>
       </c>
       <c r="AE165" t="n">
-        <v>11.704</v>
+        <v>11.805</v>
       </c>
       <c r="AF165" t="n">
-        <v>22.384</v>
+        <v>22.457</v>
       </c>
       <c r="AG165" t="n">
-        <v>13.496</v>
+        <v>13.465</v>
       </c>
       <c r="AH165" t="n">
-        <v>8.528</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AI165" t="n">
-        <v>4.24</v>
+        <v>4.102</v>
       </c>
       <c r="AJ165" t="n">
-        <v>20.272</v>
+        <v>20.395</v>
       </c>
       <c r="AK165" t="n">
-        <v>-7.8</v>
+        <v>-8</v>
       </c>
       <c r="AL165" t="n">
-        <v>-5.8</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="166">
@@ -20906,22 +20906,22 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F171" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G171" t="b">
         <v>1</v>
       </c>
       <c r="H171" t="n">
-        <v>1624.085</v>
+        <v>1613.709</v>
       </c>
       <c r="I171" t="n">
-        <v>0.236</v>
+        <v>0.3599</v>
       </c>
       <c r="J171" t="n">
-        <v>1674.6</v>
+        <v>1670.6</v>
       </c>
       <c r="K171" t="n">
         <v>72</v>
@@ -20942,70 +20942,70 @@
         <v>74</v>
       </c>
       <c r="Q171" t="n">
-        <v>110.799</v>
+        <v>110.457</v>
       </c>
       <c r="R171" t="n">
-        <v>108.501</v>
+        <v>108.577</v>
       </c>
       <c r="S171" t="n">
-        <v>2.298</v>
+        <v>1.88</v>
       </c>
       <c r="T171" t="n">
-        <v>0.24814</v>
+        <v>0.24991</v>
       </c>
       <c r="U171" t="n">
-        <v>0.15823</v>
+        <v>0.15774</v>
       </c>
       <c r="V171" t="n">
-        <v>70.09</v>
+        <v>70</v>
       </c>
       <c r="W171" t="n">
-        <v>68.39</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="X171" t="n">
-        <v>0.4899</v>
+        <v>0.4637</v>
       </c>
       <c r="Y171" t="n">
-        <v>24.096</v>
+        <v>24.134</v>
       </c>
       <c r="Z171" t="n">
-        <v>52.449</v>
+        <v>52.609</v>
       </c>
       <c r="AA171" t="n">
-        <v>8.551</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB171" t="n">
-        <v>24.748</v>
+        <v>24.762</v>
       </c>
       <c r="AC171" t="n">
-        <v>13.351</v>
+        <v>13.298</v>
       </c>
       <c r="AD171" t="n">
-        <v>19.029</v>
+        <v>18.978</v>
       </c>
       <c r="AE171" t="n">
-        <v>7.446</v>
+        <v>7.474</v>
       </c>
       <c r="AF171" t="n">
-        <v>21.519</v>
+        <v>21.442</v>
       </c>
       <c r="AG171" t="n">
-        <v>17.18</v>
+        <v>17.394</v>
       </c>
       <c r="AH171" t="n">
-        <v>6.478</v>
+        <v>6.505</v>
       </c>
       <c r="AI171" t="n">
-        <v>2.583</v>
+        <v>2.754</v>
       </c>
       <c r="AJ171" t="n">
-        <v>14.571</v>
+        <v>14.462</v>
       </c>
       <c r="AK171" t="n">
-        <v>-3</v>
+        <v>-7.8</v>
       </c>
       <c r="AL171" t="n">
-        <v>-1.4</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="172">
@@ -21026,22 +21026,22 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F172" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G172" t="b">
         <v>1</v>
       </c>
       <c r="H172" t="n">
-        <v>1624.503</v>
+        <v>1640.526</v>
       </c>
       <c r="I172" t="n">
-        <v>-8.4802</v>
+        <v>-8.1568</v>
       </c>
       <c r="J172" t="n">
-        <v>1688.2</v>
+        <v>1692.8</v>
       </c>
       <c r="K172" t="n">
         <v>81</v>
@@ -21062,70 +21062,70 @@
         <v>92</v>
       </c>
       <c r="Q172" t="n">
-        <v>108.773</v>
+        <v>108.94</v>
       </c>
       <c r="R172" t="n">
-        <v>109.587</v>
+        <v>109.083</v>
       </c>
       <c r="S172" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.143</v>
       </c>
       <c r="T172" t="n">
-        <v>0.28176</v>
+        <v>0.28018</v>
       </c>
       <c r="U172" t="n">
-        <v>0.13426</v>
+        <v>0.13619</v>
       </c>
       <c r="V172" t="n">
-        <v>75.12</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="W172" t="n">
-        <v>75.8</v>
+        <v>75.52</v>
       </c>
       <c r="X172" t="n">
-        <v>0.3826</v>
+        <v>0.4126</v>
       </c>
       <c r="Y172" t="n">
-        <v>26.38</v>
+        <v>26.11</v>
       </c>
       <c r="Z172" t="n">
-        <v>59.719</v>
+        <v>59.534</v>
       </c>
       <c r="AA172" t="n">
-        <v>7.09</v>
+        <v>7.155</v>
       </c>
       <c r="AB172" t="n">
-        <v>21.62</v>
+        <v>21.638</v>
       </c>
       <c r="AC172" t="n">
-        <v>15.275</v>
+        <v>15.528</v>
       </c>
       <c r="AD172" t="n">
-        <v>20.316</v>
+        <v>20.548</v>
       </c>
       <c r="AE172" t="n">
-        <v>8.849</v>
+        <v>8.835000000000001</v>
       </c>
       <c r="AF172" t="n">
-        <v>22.47</v>
+        <v>22.641</v>
       </c>
       <c r="AG172" t="n">
-        <v>13.872</v>
+        <v>13.793</v>
       </c>
       <c r="AH172" t="n">
-        <v>7.035</v>
+        <v>6.75</v>
       </c>
       <c r="AI172" t="n">
-        <v>4.223</v>
+        <v>4.3</v>
       </c>
       <c r="AJ172" t="n">
-        <v>19.209</v>
+        <v>19.039</v>
       </c>
       <c r="AK172" t="n">
-        <v>-5.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL172" t="n">
-        <v>-8.9</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="173">
@@ -21146,22 +21146,22 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F173" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G173" t="b">
         <v>1</v>
       </c>
       <c r="H173" t="n">
-        <v>1621.64</v>
+        <v>1615.755</v>
       </c>
       <c r="I173" t="n">
-        <v>-1.5779</v>
+        <v>-1.6216</v>
       </c>
       <c r="J173" t="n">
-        <v>1703.2</v>
+        <v>1707.4</v>
       </c>
       <c r="K173" t="n">
         <v>100</v>
@@ -21182,70 +21182,70 @@
         <v>110</v>
       </c>
       <c r="Q173" t="n">
-        <v>107.606</v>
+        <v>106.637</v>
       </c>
       <c r="R173" t="n">
-        <v>112.471</v>
+        <v>112.302</v>
       </c>
       <c r="S173" t="n">
-        <v>-4.864</v>
+        <v>-5.665</v>
       </c>
       <c r="T173" t="n">
-        <v>0.2773</v>
+        <v>0.27798</v>
       </c>
       <c r="U173" t="n">
-        <v>0.15589</v>
+        <v>0.15546</v>
       </c>
       <c r="V173" t="n">
-        <v>78.33</v>
+        <v>77.47</v>
       </c>
       <c r="W173" t="n">
-        <v>82.09999999999999</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="X173" t="n">
-        <v>0.4153</v>
+        <v>0.4026</v>
       </c>
       <c r="Y173" t="n">
-        <v>28.544</v>
+        <v>28.314</v>
       </c>
       <c r="Z173" t="n">
-        <v>62.988</v>
+        <v>63.009</v>
       </c>
       <c r="AA173" t="n">
-        <v>8.265000000000001</v>
+        <v>8.167999999999999</v>
       </c>
       <c r="AB173" t="n">
-        <v>25.332</v>
+        <v>25.261</v>
       </c>
       <c r="AC173" t="n">
-        <v>12.981</v>
+        <v>12.68</v>
       </c>
       <c r="AD173" t="n">
-        <v>19.389</v>
+        <v>19.274</v>
       </c>
       <c r="AE173" t="n">
-        <v>10.067</v>
+        <v>10.133</v>
       </c>
       <c r="AF173" t="n">
-        <v>25.789</v>
+        <v>25.894</v>
       </c>
       <c r="AG173" t="n">
-        <v>12.933</v>
+        <v>12.747</v>
       </c>
       <c r="AH173" t="n">
-        <v>5.892</v>
+        <v>5.756</v>
       </c>
       <c r="AI173" t="n">
-        <v>4.415</v>
+        <v>4.363</v>
       </c>
       <c r="AJ173" t="n">
-        <v>16.128</v>
+        <v>16.164</v>
       </c>
       <c r="AK173" t="n">
-        <v>-19.4</v>
+        <v>-21.4</v>
       </c>
       <c r="AL173" t="n">
-        <v>-11.3</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="174">
@@ -21506,22 +21506,22 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F176" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G176" t="b">
         <v>1</v>
       </c>
       <c r="H176" t="n">
-        <v>1397.595</v>
+        <v>1411.503</v>
       </c>
       <c r="I176" t="n">
-        <v>1.1993</v>
+        <v>1.1057</v>
       </c>
       <c r="J176" t="n">
-        <v>1471</v>
+        <v>1481.6</v>
       </c>
       <c r="K176" t="n">
         <v>215</v>
@@ -21542,70 +21542,70 @@
         <v>214</v>
       </c>
       <c r="Q176" t="n">
-        <v>107.894</v>
+        <v>108.332</v>
       </c>
       <c r="R176" t="n">
-        <v>109.732</v>
+        <v>109.654</v>
       </c>
       <c r="S176" t="n">
-        <v>-1.838</v>
+        <v>-1.322</v>
       </c>
       <c r="T176" t="n">
-        <v>0.32401</v>
+        <v>0.32511</v>
       </c>
       <c r="U176" t="n">
-        <v>0.16312</v>
+        <v>0.16137</v>
       </c>
       <c r="V176" t="n">
-        <v>73.18000000000001</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="W176" t="n">
-        <v>74.67</v>
+        <v>74.47</v>
       </c>
       <c r="X176" t="n">
-        <v>0.4171</v>
+        <v>0.4363</v>
       </c>
       <c r="Y176" t="n">
-        <v>24.491</v>
+        <v>24.58</v>
       </c>
       <c r="Z176" t="n">
-        <v>55.926</v>
+        <v>56.203</v>
       </c>
       <c r="AA176" t="n">
-        <v>7.251</v>
+        <v>7.342</v>
       </c>
       <c r="AB176" t="n">
-        <v>22.571</v>
+        <v>22.943</v>
       </c>
       <c r="AC176" t="n">
-        <v>16.829</v>
+        <v>16.411</v>
       </c>
       <c r="AD176" t="n">
-        <v>24.874</v>
+        <v>24.252</v>
       </c>
       <c r="AE176" t="n">
-        <v>10</v>
+        <v>10.005</v>
       </c>
       <c r="AF176" t="n">
-        <v>20.869</v>
+        <v>20.79</v>
       </c>
       <c r="AG176" t="n">
-        <v>13.474</v>
+        <v>13.574</v>
       </c>
       <c r="AH176" t="n">
-        <v>6.754</v>
+        <v>6.768</v>
       </c>
       <c r="AI176" t="n">
-        <v>3.029</v>
+        <v>3.033</v>
       </c>
       <c r="AJ176" t="n">
-        <v>18.269</v>
+        <v>18.265</v>
       </c>
       <c r="AK176" t="n">
-        <v>-0.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL176" t="n">
-        <v>-2.3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="177">
@@ -21746,22 +21746,22 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F178" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G178" t="b">
         <v>1</v>
       </c>
       <c r="H178" t="n">
-        <v>1469.446</v>
+        <v>1464.574</v>
       </c>
       <c r="I178" t="n">
-        <v>-1.5005</v>
+        <v>-1.3592</v>
       </c>
       <c r="J178" t="n">
-        <v>1435.4</v>
+        <v>1433.9</v>
       </c>
       <c r="K178" t="n">
         <v>187</v>
@@ -21782,70 +21782,70 @@
         <v>199</v>
       </c>
       <c r="Q178" t="n">
-        <v>107.303</v>
+        <v>106.924</v>
       </c>
       <c r="R178" t="n">
-        <v>109.175</v>
+        <v>109.444</v>
       </c>
       <c r="S178" t="n">
-        <v>-1.872</v>
+        <v>-2.52</v>
       </c>
       <c r="T178" t="n">
-        <v>0.19414</v>
+        <v>0.19704</v>
       </c>
       <c r="U178" t="n">
-        <v>0.18613</v>
+        <v>0.1841</v>
       </c>
       <c r="V178" t="n">
-        <v>76.02</v>
+        <v>75.62</v>
       </c>
       <c r="W178" t="n">
-        <v>77.53</v>
+        <v>77.56</v>
       </c>
       <c r="X178" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.4957</v>
       </c>
       <c r="Y178" t="n">
-        <v>26.065</v>
+        <v>26.016</v>
       </c>
       <c r="Z178" t="n">
-        <v>54.969</v>
+        <v>55.001</v>
       </c>
       <c r="AA178" t="n">
-        <v>8.065</v>
+        <v>7.974</v>
       </c>
       <c r="AB178" t="n">
-        <v>22.671</v>
+        <v>22.553</v>
       </c>
       <c r="AC178" t="n">
-        <v>15.699</v>
+        <v>15.97</v>
       </c>
       <c r="AD178" t="n">
-        <v>20.065</v>
+        <v>20.5</v>
       </c>
       <c r="AE178" t="n">
-        <v>5.981</v>
+        <v>6.193</v>
       </c>
       <c r="AF178" t="n">
-        <v>24.596</v>
+        <v>24.803</v>
       </c>
       <c r="AG178" t="n">
-        <v>14.379</v>
+        <v>14.096</v>
       </c>
       <c r="AH178" t="n">
-        <v>5.522</v>
+        <v>5.621</v>
       </c>
       <c r="AI178" t="n">
-        <v>2.41</v>
+        <v>2.355</v>
       </c>
       <c r="AJ178" t="n">
-        <v>17.512</v>
+        <v>17.412</v>
       </c>
       <c r="AK178" t="n">
-        <v>-1</v>
+        <v>-4.8</v>
       </c>
       <c r="AL178" t="n">
-        <v>-4.3</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="179">
@@ -22106,22 +22106,22 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F181" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G181" t="b">
         <v>1</v>
       </c>
       <c r="H181" t="n">
-        <v>1276.642</v>
+        <v>1266.451</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1495</v>
+        <v>-0.0021</v>
       </c>
       <c r="J181" t="n">
-        <v>1359.2</v>
+        <v>1356.2</v>
       </c>
       <c r="K181" t="n">
         <v>352</v>
@@ -22142,70 +22142,70 @@
         <v>351</v>
       </c>
       <c r="Q181" t="n">
-        <v>100.027</v>
+        <v>99.72799999999999</v>
       </c>
       <c r="R181" t="n">
-        <v>111.787</v>
+        <v>111.487</v>
       </c>
       <c r="S181" t="n">
-        <v>-11.76</v>
+        <v>-11.758</v>
       </c>
       <c r="T181" t="n">
-        <v>0.29449</v>
+        <v>0.29397</v>
       </c>
       <c r="U181" t="n">
-        <v>0.17085</v>
+        <v>0.17056</v>
       </c>
       <c r="V181" t="n">
-        <v>71.78</v>
+        <v>71.72</v>
       </c>
       <c r="W181" t="n">
-        <v>80.06</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="X181" t="n">
-        <v>0.4316</v>
+        <v>0.4019</v>
       </c>
       <c r="Y181" t="n">
-        <v>23.575</v>
+        <v>23.662</v>
       </c>
       <c r="Z181" t="n">
-        <v>58.141</v>
+        <v>58.187</v>
       </c>
       <c r="AA181" t="n">
-        <v>6.651</v>
+        <v>6.335</v>
       </c>
       <c r="AB181" t="n">
-        <v>20.505</v>
+        <v>19.902</v>
       </c>
       <c r="AC181" t="n">
-        <v>17.981</v>
+        <v>18.31</v>
       </c>
       <c r="AD181" t="n">
-        <v>24.202</v>
+        <v>24.665</v>
       </c>
       <c r="AE181" t="n">
-        <v>9.234</v>
+        <v>9.333</v>
       </c>
       <c r="AF181" t="n">
-        <v>21.179</v>
+        <v>21.523</v>
       </c>
       <c r="AG181" t="n">
-        <v>12.364</v>
+        <v>12.265</v>
       </c>
       <c r="AH181" t="n">
-        <v>4.356</v>
+        <v>4.329</v>
       </c>
       <c r="AI181" t="n">
-        <v>3.333</v>
+        <v>3.342</v>
       </c>
       <c r="AJ181" t="n">
-        <v>21.434</v>
+        <v>21.575</v>
       </c>
       <c r="AK181" t="n">
-        <v>1.2</v>
+        <v>-2.6</v>
       </c>
       <c r="AL181" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="182">
@@ -23546,22 +23546,22 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F193" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G193" t="b">
         <v>1</v>
       </c>
       <c r="H193" t="n">
-        <v>1735.865</v>
+        <v>1740.735</v>
       </c>
       <c r="I193" t="n">
-        <v>7.7247</v>
+        <v>7.3141</v>
       </c>
       <c r="J193" t="n">
-        <v>1675.6</v>
+        <v>1669.5</v>
       </c>
       <c r="K193" t="n">
         <v>36</v>
@@ -23582,70 +23582,70 @@
         <v>35</v>
       </c>
       <c r="Q193" t="n">
-        <v>118.752</v>
+        <v>120.031</v>
       </c>
       <c r="R193" t="n">
-        <v>108.163</v>
+        <v>109.136</v>
       </c>
       <c r="S193" t="n">
-        <v>10.589</v>
+        <v>10.895</v>
       </c>
       <c r="T193" t="n">
-        <v>0.28293</v>
+        <v>0.27841</v>
       </c>
       <c r="U193" t="n">
-        <v>0.12958</v>
+        <v>0.1277</v>
       </c>
       <c r="V193" t="n">
-        <v>83.55</v>
+        <v>84.13</v>
       </c>
       <c r="W193" t="n">
-        <v>76.09</v>
+        <v>76.48</v>
       </c>
       <c r="X193" t="n">
-        <v>0.6069</v>
+        <v>0.6284</v>
       </c>
       <c r="Y193" t="n">
-        <v>28.588</v>
+        <v>28.708</v>
       </c>
       <c r="Z193" t="n">
-        <v>61.156</v>
+        <v>60.817</v>
       </c>
       <c r="AA193" t="n">
-        <v>10.226</v>
+        <v>10.368</v>
       </c>
       <c r="AB193" t="n">
-        <v>26.9</v>
+        <v>26.809</v>
       </c>
       <c r="AC193" t="n">
-        <v>16.151</v>
+        <v>16.342</v>
       </c>
       <c r="AD193" t="n">
-        <v>21.254</v>
+        <v>21.364</v>
       </c>
       <c r="AE193" t="n">
-        <v>9.275</v>
+        <v>9.048</v>
       </c>
       <c r="AF193" t="n">
-        <v>23.374</v>
+        <v>23.172</v>
       </c>
       <c r="AG193" t="n">
-        <v>15.644</v>
+        <v>15.721</v>
       </c>
       <c r="AH193" t="n">
-        <v>8.204000000000001</v>
+        <v>8.137</v>
       </c>
       <c r="AI193" t="n">
-        <v>3.319</v>
+        <v>3.23</v>
       </c>
       <c r="AJ193" t="n">
-        <v>18.143</v>
+        <v>18.306</v>
       </c>
       <c r="AK193" t="n">
-        <v>-8.199999999999999</v>
+        <v>-11</v>
       </c>
       <c r="AL193" t="n">
-        <v>-5.5</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="194">
@@ -23906,22 +23906,22 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F196" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G196" t="b">
         <v>1</v>
       </c>
       <c r="H196" t="n">
-        <v>1736.457</v>
+        <v>1737.157</v>
       </c>
       <c r="I196" t="n">
-        <v>6.7862</v>
+        <v>6.361</v>
       </c>
       <c r="J196" t="n">
-        <v>1598.1</v>
+        <v>1587.8</v>
       </c>
       <c r="K196" t="n">
         <v>76</v>
@@ -23942,70 +23942,70 @@
         <v>73</v>
       </c>
       <c r="Q196" t="n">
-        <v>112.993</v>
+        <v>112.926</v>
       </c>
       <c r="R196" t="n">
-        <v>106.432</v>
+        <v>104.737</v>
       </c>
       <c r="S196" t="n">
-        <v>6.561</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="T196" t="n">
-        <v>0.30376</v>
+        <v>0.30288</v>
       </c>
       <c r="U196" t="n">
-        <v>0.14189</v>
+        <v>0.14347</v>
       </c>
       <c r="V196" t="n">
-        <v>75.84999999999999</v>
+        <v>76.05</v>
       </c>
       <c r="W196" t="n">
-        <v>71.76000000000001</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="X196" t="n">
-        <v>0.65</v>
+        <v>0.6606</v>
       </c>
       <c r="Y196" t="n">
-        <v>24.868</v>
+        <v>24.889</v>
       </c>
       <c r="Z196" t="n">
-        <v>56.732</v>
+        <v>56.753</v>
       </c>
       <c r="AA196" t="n">
-        <v>6.768</v>
+        <v>6.728</v>
       </c>
       <c r="AB196" t="n">
-        <v>18.445</v>
+        <v>18.519</v>
       </c>
       <c r="AC196" t="n">
-        <v>19.341</v>
+        <v>19.544</v>
       </c>
       <c r="AD196" t="n">
-        <v>25.727</v>
+        <v>25.989</v>
       </c>
       <c r="AE196" t="n">
-        <v>10.205</v>
+        <v>10.272</v>
       </c>
       <c r="AF196" t="n">
-        <v>23.223</v>
+        <v>23.515</v>
       </c>
       <c r="AG196" t="n">
-        <v>14.205</v>
+        <v>14.316</v>
       </c>
       <c r="AH196" t="n">
-        <v>6.464</v>
+        <v>6.68</v>
       </c>
       <c r="AI196" t="n">
-        <v>3.855</v>
+        <v>3.933</v>
       </c>
       <c r="AJ196" t="n">
-        <v>17.941</v>
+        <v>17.926</v>
       </c>
       <c r="AK196" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="AL196" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="197">
@@ -24266,22 +24266,22 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F199" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G199" t="b">
         <v>1</v>
       </c>
       <c r="H199" t="n">
-        <v>1466.337</v>
+        <v>1461.516</v>
       </c>
       <c r="I199" t="n">
-        <v>-7.3735</v>
+        <v>-6.9468</v>
       </c>
       <c r="J199" t="n">
-        <v>1487.1</v>
+        <v>1489.5</v>
       </c>
       <c r="K199" t="n">
         <v>185</v>
@@ -24302,70 +24302,70 @@
         <v>186</v>
       </c>
       <c r="Q199" t="n">
-        <v>109.084</v>
+        <v>108.097</v>
       </c>
       <c r="R199" t="n">
-        <v>108.278</v>
+        <v>107.846</v>
       </c>
       <c r="S199" t="n">
-        <v>0.806</v>
+        <v>0.251</v>
       </c>
       <c r="T199" t="n">
-        <v>0.30371</v>
+        <v>0.30372</v>
       </c>
       <c r="U199" t="n">
-        <v>0.14467</v>
+        <v>0.14631</v>
       </c>
       <c r="V199" t="n">
-        <v>74.27</v>
+        <v>73.77</v>
       </c>
       <c r="W199" t="n">
-        <v>73.88</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="X199" t="n">
-        <v>0.4686</v>
+        <v>0.4449</v>
       </c>
       <c r="Y199" t="n">
-        <v>25.578</v>
+        <v>25.457</v>
       </c>
       <c r="Z199" t="n">
-        <v>59.833</v>
+        <v>59.89</v>
       </c>
       <c r="AA199" t="n">
-        <v>7.63</v>
+        <v>7.449</v>
       </c>
       <c r="AB199" t="n">
-        <v>23.472</v>
+        <v>23.312</v>
       </c>
       <c r="AC199" t="n">
-        <v>15.267</v>
+        <v>15.232</v>
       </c>
       <c r="AD199" t="n">
-        <v>20.744</v>
+        <v>20.885</v>
       </c>
       <c r="AE199" t="n">
-        <v>10.543</v>
+        <v>10.631</v>
       </c>
       <c r="AF199" t="n">
-        <v>24.166</v>
+        <v>24.387</v>
       </c>
       <c r="AG199" t="n">
-        <v>12.834</v>
+        <v>12.571</v>
       </c>
       <c r="AH199" t="n">
-        <v>5.733</v>
+        <v>5.601</v>
       </c>
       <c r="AI199" t="n">
-        <v>3.15</v>
+        <v>3.095</v>
       </c>
       <c r="AJ199" t="n">
-        <v>19.728</v>
+        <v>20.052</v>
       </c>
       <c r="AK199" t="n">
-        <v>-2.8</v>
+        <v>0.2</v>
       </c>
       <c r="AL199" t="n">
-        <v>0.3</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="200">
@@ -25826,22 +25826,22 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F212" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G212" t="b">
         <v>1</v>
       </c>
       <c r="H212" t="n">
-        <v>1591.557</v>
+        <v>1607.044</v>
       </c>
       <c r="I212" t="n">
-        <v>-4.0194</v>
+        <v>-3.6942</v>
       </c>
       <c r="J212" t="n">
-        <v>1694.1</v>
+        <v>1697.4</v>
       </c>
       <c r="K212" t="n">
         <v>66</v>
@@ -25862,70 +25862,70 @@
         <v>70</v>
       </c>
       <c r="Q212" t="n">
-        <v>111.473</v>
+        <v>111.915</v>
       </c>
       <c r="R212" t="n">
-        <v>109.981</v>
+        <v>109.76</v>
       </c>
       <c r="S212" t="n">
-        <v>1.492</v>
+        <v>2.155</v>
       </c>
       <c r="T212" t="n">
-        <v>0.28135</v>
+        <v>0.27915</v>
       </c>
       <c r="U212" t="n">
-        <v>0.12765</v>
+        <v>0.12991</v>
       </c>
       <c r="V212" t="n">
         <v>73.31</v>
       </c>
       <c r="W212" t="n">
-        <v>71.98</v>
+        <v>71.61</v>
       </c>
       <c r="X212" t="n">
-        <v>0.4426</v>
+        <v>0.4591</v>
       </c>
       <c r="Y212" t="n">
-        <v>26.133</v>
+        <v>25.889</v>
       </c>
       <c r="Z212" t="n">
-        <v>56.902</v>
+        <v>56.478</v>
       </c>
       <c r="AA212" t="n">
-        <v>6.372</v>
+        <v>6.361</v>
       </c>
       <c r="AB212" t="n">
-        <v>19.606</v>
+        <v>19.494</v>
       </c>
       <c r="AC212" t="n">
-        <v>14.668</v>
+        <v>14.669</v>
       </c>
       <c r="AD212" t="n">
-        <v>19.554</v>
+        <v>19.626</v>
       </c>
       <c r="AE212" t="n">
-        <v>8.111000000000001</v>
+        <v>8.052</v>
       </c>
       <c r="AF212" t="n">
-        <v>20.415</v>
+        <v>20.498</v>
       </c>
       <c r="AG212" t="n">
-        <v>17.191</v>
+        <v>16.881</v>
       </c>
       <c r="AH212" t="n">
-        <v>5.872</v>
+        <v>5.773</v>
       </c>
       <c r="AI212" t="n">
-        <v>3.623</v>
+        <v>3.593</v>
       </c>
       <c r="AJ212" t="n">
-        <v>17.146</v>
+        <v>17.112</v>
       </c>
       <c r="AK212" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="AL212" t="n">
-        <v>-6.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="213">
@@ -26546,22 +26546,22 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F218" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G218" t="b">
         <v>1</v>
       </c>
       <c r="H218" t="n">
-        <v>1703.747</v>
+        <v>1709.477</v>
       </c>
       <c r="I218" t="n">
-        <v>-2.4994</v>
+        <v>-2.1526</v>
       </c>
       <c r="J218" t="n">
-        <v>1663.6</v>
+        <v>1657.6</v>
       </c>
       <c r="K218" t="n">
         <v>46</v>
@@ -26582,70 +26582,70 @@
         <v>54</v>
       </c>
       <c r="Q218" t="n">
-        <v>119.555</v>
+        <v>120.332</v>
       </c>
       <c r="R218" t="n">
-        <v>111.752</v>
+        <v>112.013</v>
       </c>
       <c r="S218" t="n">
-        <v>7.803</v>
+        <v>8.319000000000001</v>
       </c>
       <c r="T218" t="n">
-        <v>0.31113</v>
+        <v>0.30719</v>
       </c>
       <c r="U218" t="n">
-        <v>0.14123</v>
+        <v>0.14077</v>
       </c>
       <c r="V218" t="n">
-        <v>82.8</v>
+        <v>82.88</v>
       </c>
       <c r="W218" t="n">
-        <v>77.56999999999999</v>
+        <v>77.34</v>
       </c>
       <c r="X218" t="n">
-        <v>0.5536</v>
+        <v>0.5672</v>
       </c>
       <c r="Y218" t="n">
-        <v>28.243</v>
+        <v>28.331</v>
       </c>
       <c r="Z218" t="n">
-        <v>60.362</v>
+        <v>59.923</v>
       </c>
       <c r="AA218" t="n">
-        <v>9.901</v>
+        <v>9.98</v>
       </c>
       <c r="AB218" t="n">
-        <v>26.664</v>
+        <v>26.669</v>
       </c>
       <c r="AC218" t="n">
-        <v>16.414</v>
+        <v>16.237</v>
       </c>
       <c r="AD218" t="n">
-        <v>22.012</v>
+        <v>21.876</v>
       </c>
       <c r="AE218" t="n">
-        <v>10.319</v>
+        <v>10.101</v>
       </c>
       <c r="AF218" t="n">
-        <v>22.571</v>
+        <v>22.38</v>
       </c>
       <c r="AG218" t="n">
-        <v>14.02</v>
+        <v>14.198</v>
       </c>
       <c r="AH218" t="n">
-        <v>6.342</v>
+        <v>6.392</v>
       </c>
       <c r="AI218" t="n">
-        <v>3.777</v>
+        <v>3.742</v>
       </c>
       <c r="AJ218" t="n">
-        <v>17.728</v>
+        <v>17.608</v>
       </c>
       <c r="AK218" t="n">
-        <v>8.6</v>
+        <v>11.8</v>
       </c>
       <c r="AL218" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="219">
@@ -26666,22 +26666,22 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F219" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G219" t="b">
         <v>1</v>
       </c>
       <c r="H219" t="n">
-        <v>1716.101</v>
+        <v>1706.568</v>
       </c>
       <c r="I219" t="n">
-        <v>-1.1554</v>
+        <v>-1.149</v>
       </c>
       <c r="J219" t="n">
-        <v>1686</v>
+        <v>1692.8</v>
       </c>
       <c r="K219" t="n">
         <v>69</v>
@@ -26702,70 +26702,70 @@
         <v>79</v>
       </c>
       <c r="Q219" t="n">
-        <v>111.029</v>
+        <v>111.498</v>
       </c>
       <c r="R219" t="n">
-        <v>109.598</v>
+        <v>110.641</v>
       </c>
       <c r="S219" t="n">
-        <v>1.431</v>
+        <v>0.857</v>
       </c>
       <c r="T219" t="n">
-        <v>0.27886</v>
+        <v>0.28469</v>
       </c>
       <c r="U219" t="n">
-        <v>0.15495</v>
+        <v>0.15383</v>
       </c>
       <c r="V219" t="n">
-        <v>84.23999999999999</v>
+        <v>84.31</v>
       </c>
       <c r="W219" t="n">
-        <v>82.54000000000001</v>
+        <v>83.03</v>
       </c>
       <c r="X219" t="n">
-        <v>0.5981</v>
+        <v>0.57</v>
       </c>
       <c r="Y219" t="n">
-        <v>28.97</v>
+        <v>29.14</v>
       </c>
       <c r="Z219" t="n">
-        <v>63.023</v>
+        <v>63.21</v>
       </c>
       <c r="AA219" t="n">
-        <v>7.929</v>
+        <v>7.75</v>
       </c>
       <c r="AB219" t="n">
-        <v>23.157</v>
+        <v>22.93</v>
       </c>
       <c r="AC219" t="n">
-        <v>17.996</v>
+        <v>18.01</v>
       </c>
       <c r="AD219" t="n">
-        <v>24.378</v>
+        <v>24.17</v>
       </c>
       <c r="AE219" t="n">
-        <v>9.815</v>
+        <v>10.02</v>
       </c>
       <c r="AF219" t="n">
-        <v>25.206</v>
+        <v>25.01</v>
       </c>
       <c r="AG219" t="n">
-        <v>14.909</v>
+        <v>14.8</v>
       </c>
       <c r="AH219" t="n">
-        <v>7.226</v>
+        <v>7.16</v>
       </c>
       <c r="AI219" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AJ219" t="n">
-        <v>17.31</v>
+        <v>17.39</v>
       </c>
       <c r="AK219" t="n">
-        <v>-1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="AL219" t="n">
-        <v>-8.199999999999999</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="220">
@@ -27746,22 +27746,22 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F228" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G228" t="b">
         <v>1</v>
       </c>
       <c r="H228" t="n">
-        <v>1536.866</v>
+        <v>1531.996</v>
       </c>
       <c r="I228" t="n">
-        <v>-4.8733</v>
+        <v>-4.4929</v>
       </c>
       <c r="J228" t="n">
-        <v>1663.6</v>
+        <v>1665.5</v>
       </c>
       <c r="K228" t="n">
         <v>99</v>
@@ -27782,70 +27782,70 @@
         <v>109</v>
       </c>
       <c r="Q228" t="n">
-        <v>106.774</v>
+        <v>107.914</v>
       </c>
       <c r="R228" t="n">
-        <v>108.939</v>
+        <v>110.677</v>
       </c>
       <c r="S228" t="n">
-        <v>-2.165</v>
+        <v>-2.763</v>
       </c>
       <c r="T228" t="n">
-        <v>0.32034</v>
+        <v>0.31873</v>
       </c>
       <c r="U228" t="n">
-        <v>0.1682</v>
+        <v>0.16818</v>
       </c>
       <c r="V228" t="n">
-        <v>69.89</v>
+        <v>70.72</v>
       </c>
       <c r="W228" t="n">
-        <v>70.90000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="X228" t="n">
-        <v>0.4137</v>
+        <v>0.3893</v>
       </c>
       <c r="Y228" t="n">
-        <v>25.093</v>
+        <v>25.215</v>
       </c>
       <c r="Z228" t="n">
-        <v>57.307</v>
+        <v>57.026</v>
       </c>
       <c r="AA228" t="n">
-        <v>8.215999999999999</v>
+        <v>8.375999999999999</v>
       </c>
       <c r="AB228" t="n">
-        <v>24.474</v>
+        <v>24.634</v>
       </c>
       <c r="AC228" t="n">
-        <v>11.449</v>
+        <v>11.884</v>
       </c>
       <c r="AD228" t="n">
-        <v>17.015</v>
+        <v>17.483</v>
       </c>
       <c r="AE228" t="n">
-        <v>10.425</v>
+        <v>10.283</v>
       </c>
       <c r="AF228" t="n">
-        <v>21.833</v>
+        <v>21.642</v>
       </c>
       <c r="AG228" t="n">
-        <v>13.104</v>
+        <v>13.233</v>
       </c>
       <c r="AH228" t="n">
-        <v>6.648</v>
+        <v>6.462</v>
       </c>
       <c r="AI228" t="n">
-        <v>3.279</v>
+        <v>3.21</v>
       </c>
       <c r="AJ228" t="n">
-        <v>16.283</v>
+        <v>16.341</v>
       </c>
       <c r="AK228" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AL228" t="n">
-        <v>-5.4</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="229">
@@ -28106,22 +28106,22 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F231" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G231" t="b">
         <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>1256.904</v>
+        <v>1260.391</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8365</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="J231" t="n">
-        <v>1386</v>
+        <v>1386.7</v>
       </c>
       <c r="K231" t="n">
         <v>312</v>
@@ -28142,70 +28142,70 @@
         <v>316</v>
       </c>
       <c r="Q231" t="n">
-        <v>103.466</v>
+        <v>103.681</v>
       </c>
       <c r="R231" t="n">
-        <v>108.039</v>
+        <v>107.969</v>
       </c>
       <c r="S231" t="n">
-        <v>-4.573</v>
+        <v>-4.288</v>
       </c>
       <c r="T231" t="n">
-        <v>0.27693</v>
+        <v>0.28121</v>
       </c>
       <c r="U231" t="n">
-        <v>0.1529</v>
+        <v>0.15459</v>
       </c>
       <c r="V231" t="n">
-        <v>75.98999999999999</v>
+        <v>75.89</v>
       </c>
       <c r="W231" t="n">
-        <v>80.01000000000001</v>
+        <v>79.67</v>
       </c>
       <c r="X231" t="n">
-        <v>0.399</v>
+        <v>0.4193</v>
       </c>
       <c r="Y231" t="n">
-        <v>25.172</v>
+        <v>25.248</v>
       </c>
       <c r="Z231" t="n">
-        <v>59.742</v>
+        <v>59.674</v>
       </c>
       <c r="AA231" t="n">
-        <v>5.97</v>
+        <v>5.826</v>
       </c>
       <c r="AB231" t="n">
-        <v>18.556</v>
+        <v>18.242</v>
       </c>
       <c r="AC231" t="n">
-        <v>19.682</v>
+        <v>19.388</v>
       </c>
       <c r="AD231" t="n">
-        <v>26.01</v>
+        <v>25.696</v>
       </c>
       <c r="AE231" t="n">
-        <v>8.914</v>
+        <v>9.028</v>
       </c>
       <c r="AF231" t="n">
-        <v>22.283</v>
+        <v>22.118</v>
       </c>
       <c r="AG231" t="n">
-        <v>11.106</v>
+        <v>11.146</v>
       </c>
       <c r="AH231" t="n">
-        <v>7.172</v>
+        <v>7.161</v>
       </c>
       <c r="AI231" t="n">
-        <v>4.848</v>
+        <v>4.863</v>
       </c>
       <c r="AJ231" t="n">
-        <v>19.919</v>
+        <v>19.845</v>
       </c>
       <c r="AK231" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AL231" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="232">
@@ -28466,22 +28466,22 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F234" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G234" t="b">
         <v>1</v>
       </c>
       <c r="H234" t="n">
-        <v>1563.11</v>
+        <v>1573.536</v>
       </c>
       <c r="I234" t="n">
-        <v>1.8938</v>
+        <v>1.8058</v>
       </c>
       <c r="J234" t="n">
-        <v>1637.8</v>
+        <v>1638.4</v>
       </c>
       <c r="K234" t="n">
         <v>73</v>
@@ -28502,70 +28502,70 @@
         <v>84</v>
       </c>
       <c r="Q234" t="n">
-        <v>115.018</v>
+        <v>115.487</v>
       </c>
       <c r="R234" t="n">
-        <v>112.744</v>
+        <v>112.671</v>
       </c>
       <c r="S234" t="n">
-        <v>2.273</v>
+        <v>2.816</v>
       </c>
       <c r="T234" t="n">
-        <v>0.26603</v>
+        <v>0.26497</v>
       </c>
       <c r="U234" t="n">
-        <v>0.16614</v>
+        <v>0.16182</v>
       </c>
       <c r="V234" t="n">
-        <v>85.45999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="W234" t="n">
-        <v>84.01000000000001</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="X234" t="n">
-        <v>0.4455</v>
+        <v>0.4755</v>
       </c>
       <c r="Y234" t="n">
-        <v>29.45</v>
+        <v>29.506</v>
       </c>
       <c r="Z234" t="n">
-        <v>61.95</v>
+        <v>62.161</v>
       </c>
       <c r="AA234" t="n">
-        <v>9.15</v>
+        <v>8.919</v>
       </c>
       <c r="AB234" t="n">
-        <v>25.45</v>
+        <v>25.022</v>
       </c>
       <c r="AC234" t="n">
-        <v>17.409</v>
+        <v>17.419</v>
       </c>
       <c r="AD234" t="n">
-        <v>22.9</v>
+        <v>22.882</v>
       </c>
       <c r="AE234" t="n">
-        <v>9.927</v>
+        <v>9.833</v>
       </c>
       <c r="AF234" t="n">
-        <v>26.545</v>
+        <v>26.468</v>
       </c>
       <c r="AG234" t="n">
-        <v>14.082</v>
+        <v>14.18</v>
       </c>
       <c r="AH234" t="n">
-        <v>5.382</v>
+        <v>5.327</v>
       </c>
       <c r="AI234" t="n">
-        <v>3.973</v>
+        <v>3.913</v>
       </c>
       <c r="AJ234" t="n">
-        <v>18.627</v>
+        <v>18.474</v>
       </c>
       <c r="AK234" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="AL234" t="n">
-        <v>-1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="235">
@@ -29186,22 +29186,22 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F240" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G240" t="b">
         <v>1</v>
       </c>
       <c r="H240" t="n">
-        <v>1466.935</v>
+        <v>1462.187</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4968</v>
+        <v>-0.6217</v>
       </c>
       <c r="J240" t="n">
-        <v>1510.8</v>
+        <v>1506.6</v>
       </c>
       <c r="K240" t="n">
         <v>143</v>
@@ -29222,67 +29222,67 @@
         <v>152</v>
       </c>
       <c r="Q240" t="n">
-        <v>111.478</v>
+        <v>111.369</v>
       </c>
       <c r="R240" t="n">
-        <v>108.683</v>
+        <v>109.166</v>
       </c>
       <c r="S240" t="n">
-        <v>2.794</v>
+        <v>2.203</v>
       </c>
       <c r="T240" t="n">
-        <v>0.24195</v>
+        <v>0.23982</v>
       </c>
       <c r="U240" t="n">
-        <v>0.13968</v>
+        <v>0.14175</v>
       </c>
       <c r="V240" t="n">
-        <v>76.8</v>
+        <v>76.41</v>
       </c>
       <c r="W240" t="n">
-        <v>74.54000000000001</v>
+        <v>74.52</v>
       </c>
       <c r="X240" t="n">
-        <v>0.4626</v>
+        <v>0.448</v>
       </c>
       <c r="Y240" t="n">
-        <v>25.869</v>
+        <v>25.72</v>
       </c>
       <c r="Z240" t="n">
-        <v>57.31</v>
+        <v>56.824</v>
       </c>
       <c r="AA240" t="n">
-        <v>9.092000000000001</v>
+        <v>9.144</v>
       </c>
       <c r="AB240" t="n">
-        <v>24.164</v>
+        <v>24.352</v>
       </c>
       <c r="AC240" t="n">
-        <v>15.971</v>
+        <v>16.144</v>
       </c>
       <c r="AD240" t="n">
-        <v>21.26</v>
+        <v>21.472</v>
       </c>
       <c r="AE240" t="n">
-        <v>7.461</v>
+        <v>7.44</v>
       </c>
       <c r="AF240" t="n">
-        <v>23.164</v>
+        <v>23.472</v>
       </c>
       <c r="AG240" t="n">
-        <v>14.092</v>
+        <v>14.064</v>
       </c>
       <c r="AH240" t="n">
-        <v>6.917</v>
+        <v>6.776</v>
       </c>
       <c r="AI240" t="n">
-        <v>2.389</v>
+        <v>2.312</v>
       </c>
       <c r="AJ240" t="n">
-        <v>17.809</v>
+        <v>17.72</v>
       </c>
       <c r="AK240" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="AL240" t="n">
         <v>-4.4</v>
@@ -29546,22 +29546,22 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F243" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G243" t="b">
         <v>1</v>
       </c>
       <c r="H243" t="n">
-        <v>1557.451</v>
+        <v>1567.827</v>
       </c>
       <c r="I243" t="n">
-        <v>-2.9475</v>
+        <v>-2.7645</v>
       </c>
       <c r="J243" t="n">
-        <v>1684.5</v>
+        <v>1683.9</v>
       </c>
       <c r="K243" t="n">
         <v>129</v>
@@ -29582,70 +29582,70 @@
         <v>143</v>
       </c>
       <c r="Q243" t="n">
-        <v>104.804</v>
+        <v>105.152</v>
       </c>
       <c r="R243" t="n">
-        <v>111.665</v>
+        <v>111.692</v>
       </c>
       <c r="S243" t="n">
-        <v>-6.86</v>
+        <v>-6.541</v>
       </c>
       <c r="T243" t="n">
-        <v>0.31796</v>
+        <v>0.31413</v>
       </c>
       <c r="U243" t="n">
-        <v>0.1454</v>
+        <v>0.14995</v>
       </c>
       <c r="V243" t="n">
         <v>70.95</v>
       </c>
       <c r="W243" t="n">
-        <v>75.3</v>
+        <v>75.12</v>
       </c>
       <c r="X243" t="n">
-        <v>0.4273</v>
+        <v>0.4446</v>
       </c>
       <c r="Y243" t="n">
-        <v>24.327</v>
+        <v>24.321</v>
       </c>
       <c r="Z243" t="n">
-        <v>58.105</v>
+        <v>57.627</v>
       </c>
       <c r="AA243" t="n">
-        <v>6.477</v>
+        <v>6.593</v>
       </c>
       <c r="AB243" t="n">
-        <v>19.986</v>
+        <v>20.043</v>
       </c>
       <c r="AC243" t="n">
-        <v>15.814</v>
+        <v>15.498</v>
       </c>
       <c r="AD243" t="n">
-        <v>21.359</v>
+        <v>21.01</v>
       </c>
       <c r="AE243" t="n">
-        <v>9.705</v>
+        <v>9.536</v>
       </c>
       <c r="AF243" t="n">
-        <v>21.109</v>
+        <v>21</v>
       </c>
       <c r="AG243" t="n">
-        <v>11.959</v>
+        <v>12.386</v>
       </c>
       <c r="AH243" t="n">
-        <v>6.114</v>
+        <v>6.123</v>
       </c>
       <c r="AI243" t="n">
-        <v>3.332</v>
+        <v>3.352</v>
       </c>
       <c r="AJ243" t="n">
-        <v>16.745</v>
+        <v>16.753</v>
       </c>
       <c r="AK243" t="n">
-        <v>-2.8</v>
+        <v>2</v>
       </c>
       <c r="AL243" t="n">
-        <v>-3.7</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="244">
@@ -30146,22 +30146,22 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F248" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G248" t="b">
         <v>1</v>
       </c>
       <c r="H248" t="n">
-        <v>1540.147</v>
+        <v>1544.967</v>
       </c>
       <c r="I248" t="n">
-        <v>4.6115</v>
+        <v>4.4295</v>
       </c>
       <c r="J248" t="n">
-        <v>1503.4</v>
+        <v>1499.6</v>
       </c>
       <c r="K248" t="n">
         <v>109</v>
@@ -30182,70 +30182,70 @@
         <v>104</v>
       </c>
       <c r="Q248" t="n">
-        <v>113.608</v>
+        <v>112.952</v>
       </c>
       <c r="R248" t="n">
-        <v>107.464</v>
+        <v>106.404</v>
       </c>
       <c r="S248" t="n">
-        <v>6.144</v>
+        <v>6.548</v>
       </c>
       <c r="T248" t="n">
-        <v>0.30916</v>
+        <v>0.31217</v>
       </c>
       <c r="U248" t="n">
-        <v>0.15973</v>
+        <v>0.15871</v>
       </c>
       <c r="V248" t="n">
-        <v>80.45</v>
+        <v>80.03</v>
       </c>
       <c r="W248" t="n">
-        <v>76.34999999999999</v>
+        <v>75.66</v>
       </c>
       <c r="X248" t="n">
-        <v>0.6364</v>
+        <v>0.6584</v>
       </c>
       <c r="Y248" t="n">
-        <v>28.389</v>
+        <v>28.115</v>
       </c>
       <c r="Z248" t="n">
-        <v>61.399</v>
+        <v>61.593</v>
       </c>
       <c r="AA248" t="n">
-        <v>8.460000000000001</v>
+        <v>8.314</v>
       </c>
       <c r="AB248" t="n">
-        <v>21.975</v>
+        <v>22.034</v>
       </c>
       <c r="AC248" t="n">
-        <v>15.212</v>
+        <v>15.491</v>
       </c>
       <c r="AD248" t="n">
-        <v>20.904</v>
+        <v>21.488</v>
       </c>
       <c r="AE248" t="n">
-        <v>10.899</v>
+        <v>11.255</v>
       </c>
       <c r="AF248" t="n">
-        <v>24.369</v>
+        <v>24.637</v>
       </c>
       <c r="AG248" t="n">
-        <v>14.808</v>
+        <v>14.646</v>
       </c>
       <c r="AH248" t="n">
-        <v>6.773</v>
+        <v>6.916</v>
       </c>
       <c r="AI248" t="n">
-        <v>2.793</v>
+        <v>2.699</v>
       </c>
       <c r="AJ248" t="n">
-        <v>17.561</v>
+        <v>17.668</v>
       </c>
       <c r="AK248" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AL248" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="249">
@@ -30746,22 +30746,22 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F253" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G253" t="b">
         <v>1</v>
       </c>
       <c r="H253" t="n">
-        <v>1361.392</v>
+        <v>1374.819</v>
       </c>
       <c r="I253" t="n">
-        <v>-3.1738</v>
+        <v>-3.063</v>
       </c>
       <c r="J253" t="n">
-        <v>1584.5</v>
+        <v>1591.5</v>
       </c>
       <c r="K253" t="n">
         <v>237</v>
@@ -30782,70 +30782,70 @@
         <v>256</v>
       </c>
       <c r="Q253" t="n">
-        <v>107.124</v>
+        <v>107.456</v>
       </c>
       <c r="R253" t="n">
-        <v>120.717</v>
+        <v>119.845</v>
       </c>
       <c r="S253" t="n">
-        <v>-13.593</v>
+        <v>-12.389</v>
       </c>
       <c r="T253" t="n">
-        <v>0.3383</v>
+        <v>0.33606</v>
       </c>
       <c r="U253" t="n">
-        <v>0.14134</v>
+        <v>0.14324</v>
       </c>
       <c r="V253" t="n">
-        <v>70.25</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="W253" t="n">
-        <v>79.03</v>
+        <v>78.73</v>
       </c>
       <c r="X253" t="n">
-        <v>0.2309</v>
+        <v>0.2653</v>
       </c>
       <c r="Y253" t="n">
-        <v>24.393</v>
+        <v>24.236</v>
       </c>
       <c r="Z253" t="n">
-        <v>57.088</v>
+        <v>57.137</v>
       </c>
       <c r="AA253" t="n">
-        <v>7.541</v>
+        <v>7.492</v>
       </c>
       <c r="AB253" t="n">
-        <v>21.435</v>
+        <v>21.626</v>
       </c>
       <c r="AC253" t="n">
-        <v>13.922</v>
+        <v>14.362</v>
       </c>
       <c r="AD253" t="n">
-        <v>18.735</v>
+        <v>19.171</v>
       </c>
       <c r="AE253" t="n">
-        <v>8.999000000000001</v>
+        <v>9.176</v>
       </c>
       <c r="AF253" t="n">
-        <v>17.873</v>
+        <v>18.343</v>
       </c>
       <c r="AG253" t="n">
-        <v>10.123</v>
+        <v>10.035</v>
       </c>
       <c r="AH253" t="n">
-        <v>5.78</v>
+        <v>5.693</v>
       </c>
       <c r="AI253" t="n">
-        <v>2.184</v>
+        <v>2.044</v>
       </c>
       <c r="AJ253" t="n">
-        <v>17.705</v>
+        <v>17.744</v>
       </c>
       <c r="AK253" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="AL253" t="n">
-        <v>-6.9</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="254">
@@ -30866,22 +30866,22 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F254" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G254" t="b">
         <v>1</v>
       </c>
       <c r="H254" t="n">
-        <v>1493.902</v>
+        <v>1488.068</v>
       </c>
       <c r="I254" t="n">
-        <v>1.0793</v>
+        <v>1.0199</v>
       </c>
       <c r="J254" t="n">
-        <v>1456.2</v>
+        <v>1455.5</v>
       </c>
       <c r="K254" t="n">
         <v>126</v>
@@ -30902,70 +30902,70 @@
         <v>137</v>
       </c>
       <c r="Q254" t="n">
-        <v>113.545</v>
+        <v>113.081</v>
       </c>
       <c r="R254" t="n">
-        <v>108.541</v>
+        <v>108.567</v>
       </c>
       <c r="S254" t="n">
-        <v>5.005</v>
+        <v>4.514</v>
       </c>
       <c r="T254" t="n">
-        <v>0.27509</v>
+        <v>0.27631</v>
       </c>
       <c r="U254" t="n">
-        <v>0.18334</v>
+        <v>0.18172</v>
       </c>
       <c r="V254" t="n">
-        <v>76.7</v>
+        <v>76.67</v>
       </c>
       <c r="W254" t="n">
-        <v>73.45999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="X254" t="n">
-        <v>0.5466</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="Y254" t="n">
         <v>25.826</v>
       </c>
       <c r="Z254" t="n">
-        <v>55.345</v>
+        <v>55.688</v>
       </c>
       <c r="AA254" t="n">
-        <v>9.317</v>
+        <v>9.131</v>
       </c>
       <c r="AB254" t="n">
-        <v>24.506</v>
+        <v>24.546</v>
       </c>
       <c r="AC254" t="n">
-        <v>15.73</v>
+        <v>15.885</v>
       </c>
       <c r="AD254" t="n">
-        <v>20.273</v>
+        <v>20.489</v>
       </c>
       <c r="AE254" t="n">
-        <v>8.981</v>
+        <v>9.083</v>
       </c>
       <c r="AF254" t="n">
-        <v>23.481</v>
+        <v>23.596</v>
       </c>
       <c r="AG254" t="n">
-        <v>14.391</v>
+        <v>14.022</v>
       </c>
       <c r="AH254" t="n">
-        <v>6.099</v>
+        <v>6.174</v>
       </c>
       <c r="AI254" t="n">
-        <v>2.23</v>
+        <v>2.315</v>
       </c>
       <c r="AJ254" t="n">
         <v>19.264</v>
       </c>
       <c r="AK254" t="n">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AL254" t="n">
-        <v>0.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="255">
@@ -31706,22 +31706,22 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F261" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G261" t="b">
         <v>1</v>
       </c>
       <c r="H261" t="n">
-        <v>1565.83</v>
+        <v>1559.844</v>
       </c>
       <c r="I261" t="n">
-        <v>3.2279</v>
+        <v>3.1865</v>
       </c>
       <c r="J261" t="n">
-        <v>1383.6</v>
+        <v>1397.1</v>
       </c>
       <c r="K261" t="n">
         <v>89</v>
@@ -31742,70 +31742,70 @@
         <v>86</v>
       </c>
       <c r="Q261" t="n">
-        <v>112.792</v>
+        <v>112.195</v>
       </c>
       <c r="R261" t="n">
-        <v>98.536</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="S261" t="n">
-        <v>14.255</v>
+        <v>12.685</v>
       </c>
       <c r="T261" t="n">
-        <v>0.30825</v>
+        <v>0.3073</v>
       </c>
       <c r="U261" t="n">
-        <v>0.13209</v>
+        <v>0.13545</v>
       </c>
       <c r="V261" t="n">
-        <v>75.04000000000001</v>
+        <v>74.52</v>
       </c>
       <c r="W261" t="n">
-        <v>65.56999999999999</v>
+        <v>66.05</v>
       </c>
       <c r="X261" t="n">
-        <v>0.8678</v>
+        <v>0.832</v>
       </c>
       <c r="Y261" t="n">
-        <v>27.016</v>
+        <v>27.072</v>
       </c>
       <c r="Z261" t="n">
-        <v>60.371</v>
+        <v>60.144</v>
       </c>
       <c r="AA261" t="n">
-        <v>8.635</v>
+        <v>8.68</v>
       </c>
       <c r="AB261" t="n">
-        <v>23.799</v>
+        <v>23.632</v>
       </c>
       <c r="AC261" t="n">
-        <v>12.369</v>
+        <v>12.376</v>
       </c>
       <c r="AD261" t="n">
-        <v>18.162</v>
+        <v>17.984</v>
       </c>
       <c r="AE261" t="n">
-        <v>10.56</v>
+        <v>10.576</v>
       </c>
       <c r="AF261" t="n">
-        <v>23.296</v>
+        <v>23.48</v>
       </c>
       <c r="AG261" t="n">
-        <v>13.172</v>
+        <v>13.232</v>
       </c>
       <c r="AH261" t="n">
-        <v>6.761</v>
+        <v>6.824</v>
       </c>
       <c r="AI261" t="n">
-        <v>3.603</v>
+        <v>3.736</v>
       </c>
       <c r="AJ261" t="n">
-        <v>15.858</v>
+        <v>15.784</v>
       </c>
       <c r="AK261" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AL261" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="262">
@@ -31946,22 +31946,22 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F263" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G263" t="b">
         <v>1</v>
       </c>
       <c r="H263" t="n">
-        <v>1744.545</v>
+        <v>1733.884</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.2411</v>
       </c>
       <c r="J263" t="n">
-        <v>1641</v>
+        <v>1649.8</v>
       </c>
       <c r="K263" t="n">
         <v>43</v>
@@ -31982,70 +31982,70 @@
         <v>39</v>
       </c>
       <c r="Q263" t="n">
-        <v>119.024</v>
+        <v>117.96</v>
       </c>
       <c r="R263" t="n">
-        <v>110.021</v>
+        <v>109.764</v>
       </c>
       <c r="S263" t="n">
-        <v>9.003</v>
+        <v>8.196</v>
       </c>
       <c r="T263" t="n">
-        <v>0.31054</v>
+        <v>0.30979</v>
       </c>
       <c r="U263" t="n">
-        <v>0.15051</v>
+        <v>0.15421</v>
       </c>
       <c r="V263" t="n">
-        <v>85.04000000000001</v>
+        <v>83.95</v>
       </c>
       <c r="W263" t="n">
-        <v>78</v>
+        <v>77.45</v>
       </c>
       <c r="X263" t="n">
-        <v>0.629</v>
+        <v>0.6</v>
       </c>
       <c r="Y263" t="n">
-        <v>31.001</v>
+        <v>30.69</v>
       </c>
       <c r="Z263" t="n">
-        <v>63.077</v>
+        <v>62.69</v>
       </c>
       <c r="AA263" t="n">
-        <v>8.465</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AB263" t="n">
-        <v>22.551</v>
+        <v>22.62</v>
       </c>
       <c r="AC263" t="n">
-        <v>14.574</v>
+        <v>14.11</v>
       </c>
       <c r="AD263" t="n">
-        <v>19.593</v>
+        <v>19.05</v>
       </c>
       <c r="AE263" t="n">
-        <v>11.024</v>
+        <v>10.94</v>
       </c>
       <c r="AF263" t="n">
-        <v>24.536</v>
+        <v>24.47</v>
       </c>
       <c r="AG263" t="n">
-        <v>17.187</v>
+        <v>16.87</v>
       </c>
       <c r="AH263" t="n">
-        <v>7.165</v>
+        <v>7.07</v>
       </c>
       <c r="AI263" t="n">
-        <v>3.555</v>
+        <v>3.65</v>
       </c>
       <c r="AJ263" t="n">
-        <v>16.925</v>
+        <v>16.96</v>
       </c>
       <c r="AK263" t="n">
         <v>-5.6</v>
       </c>
       <c r="AL263" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="264">
@@ -32186,22 +32186,22 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F265" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G265" t="b">
         <v>1</v>
       </c>
       <c r="H265" t="n">
-        <v>1550.024</v>
+        <v>1544.294</v>
       </c>
       <c r="I265" t="n">
-        <v>-2.5273</v>
+        <v>-2.3515</v>
       </c>
       <c r="J265" t="n">
-        <v>1653.5</v>
+        <v>1655.8</v>
       </c>
       <c r="K265" t="n">
         <v>95</v>
@@ -32222,70 +32222,70 @@
         <v>107</v>
       </c>
       <c r="Q265" t="n">
-        <v>108.933</v>
+        <v>109.384</v>
       </c>
       <c r="R265" t="n">
-        <v>110.37</v>
+        <v>111.617</v>
       </c>
       <c r="S265" t="n">
-        <v>-1.437</v>
+        <v>-2.232</v>
       </c>
       <c r="T265" t="n">
-        <v>0.26164</v>
+        <v>0.27064</v>
       </c>
       <c r="U265" t="n">
-        <v>0.1372</v>
+        <v>0.1382</v>
       </c>
       <c r="V265" t="n">
-        <v>74.84</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="W265" t="n">
-        <v>75.98999999999999</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="X265" t="n">
-        <v>0.4261</v>
+        <v>0.4019</v>
       </c>
       <c r="Y265" t="n">
-        <v>25.125</v>
+        <v>25.155</v>
       </c>
       <c r="Z265" t="n">
-        <v>57.826</v>
+        <v>58.001</v>
       </c>
       <c r="AA265" t="n">
-        <v>7.916</v>
+        <v>8.032</v>
       </c>
       <c r="AB265" t="n">
-        <v>25.684</v>
+        <v>25.785</v>
       </c>
       <c r="AC265" t="n">
-        <v>16.675</v>
+        <v>16.586</v>
       </c>
       <c r="AD265" t="n">
-        <v>21.38</v>
+        <v>21.235</v>
       </c>
       <c r="AE265" t="n">
-        <v>7.841</v>
+        <v>8.179</v>
       </c>
       <c r="AF265" t="n">
-        <v>22.206</v>
+        <v>21.988</v>
       </c>
       <c r="AG265" t="n">
-        <v>13.33</v>
+        <v>13.309</v>
       </c>
       <c r="AH265" t="n">
-        <v>5.519</v>
+        <v>5.484</v>
       </c>
       <c r="AI265" t="n">
-        <v>2.438</v>
+        <v>2.36</v>
       </c>
       <c r="AJ265" t="n">
-        <v>17.53</v>
+        <v>17.609</v>
       </c>
       <c r="AK265" t="n">
-        <v>-7.2</v>
+        <v>-11.2</v>
       </c>
       <c r="AL265" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.4</v>
       </c>
     </row>
     <row r="266">
@@ -32906,22 +32906,22 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F271" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G271" t="b">
         <v>1</v>
       </c>
       <c r="H271" t="n">
-        <v>1533.877</v>
+        <v>1537.009</v>
       </c>
       <c r="I271" t="n">
-        <v>-8.699299999999999</v>
+        <v>-8.5665</v>
       </c>
       <c r="J271" t="n">
-        <v>1531.2</v>
+        <v>1525.6</v>
       </c>
       <c r="K271" t="n">
         <v>160</v>
@@ -32942,70 +32942,70 @@
         <v>158</v>
       </c>
       <c r="Q271" t="n">
-        <v>111.12</v>
+        <v>112.488</v>
       </c>
       <c r="R271" t="n">
-        <v>110.825</v>
+        <v>110.943</v>
       </c>
       <c r="S271" t="n">
-        <v>0.294</v>
+        <v>1.545</v>
       </c>
       <c r="T271" t="n">
-        <v>0.31833</v>
+        <v>0.3278</v>
       </c>
       <c r="U271" t="n">
-        <v>0.16326</v>
+        <v>0.16276</v>
       </c>
       <c r="V271" t="n">
-        <v>76.09999999999999</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="W271" t="n">
-        <v>76.03</v>
+        <v>76.3</v>
       </c>
       <c r="X271" t="n">
-        <v>0.4608</v>
+        <v>0.4899</v>
       </c>
       <c r="Y271" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="Z271" t="n">
-        <v>60.287</v>
+        <v>60.568</v>
       </c>
       <c r="AA271" t="n">
-        <v>7.041</v>
+        <v>6.933</v>
       </c>
       <c r="AB271" t="n">
-        <v>19.086</v>
+        <v>18.965</v>
       </c>
       <c r="AC271" t="n">
-        <v>13.26</v>
+        <v>13.496</v>
       </c>
       <c r="AD271" t="n">
-        <v>17.569</v>
+        <v>17.826</v>
       </c>
       <c r="AE271" t="n">
-        <v>10.585</v>
+        <v>10.803</v>
       </c>
       <c r="AF271" t="n">
-        <v>22.458</v>
+        <v>22.035</v>
       </c>
       <c r="AG271" t="n">
-        <v>15.567</v>
+        <v>15.443</v>
       </c>
       <c r="AH271" t="n">
-        <v>7.357</v>
+        <v>7.557</v>
       </c>
       <c r="AI271" t="n">
-        <v>4.312</v>
+        <v>4.394</v>
       </c>
       <c r="AJ271" t="n">
-        <v>16.524</v>
+        <v>16.446</v>
       </c>
       <c r="AK271" t="n">
-        <v>-2.8</v>
+        <v>2</v>
       </c>
       <c r="AL271" t="n">
-        <v>-2.8</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="272">
@@ -34346,22 +34346,22 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F283" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G283" t="b">
         <v>1</v>
       </c>
       <c r="H283" t="n">
-        <v>1836.256</v>
+        <v>1845.79</v>
       </c>
       <c r="I283" t="n">
-        <v>6.8916</v>
+        <v>6.897</v>
       </c>
       <c r="J283" t="n">
-        <v>1679.3</v>
+        <v>1680.3</v>
       </c>
       <c r="K283" t="n">
         <v>44</v>
@@ -34382,70 +34382,70 @@
         <v>40</v>
       </c>
       <c r="Q283" t="n">
-        <v>110.719</v>
+        <v>111.928</v>
       </c>
       <c r="R283" t="n">
-        <v>101.255</v>
+        <v>102.483</v>
       </c>
       <c r="S283" t="n">
-        <v>9.465</v>
+        <v>9.445</v>
       </c>
       <c r="T283" t="n">
-        <v>0.31924</v>
+        <v>0.32551</v>
       </c>
       <c r="U283" t="n">
-        <v>0.15075</v>
+        <v>0.14944</v>
       </c>
       <c r="V283" t="n">
-        <v>77.89</v>
+        <v>78.62</v>
       </c>
       <c r="W283" t="n">
-        <v>71.27</v>
+        <v>72.02</v>
       </c>
       <c r="X283" t="n">
-        <v>0.6806</v>
+        <v>0.6903</v>
       </c>
       <c r="Y283" t="n">
-        <v>26.99</v>
+        <v>27.28</v>
       </c>
       <c r="Z283" t="n">
-        <v>60.278</v>
+        <v>60.559</v>
       </c>
       <c r="AA283" t="n">
-        <v>7.31</v>
+        <v>7.35</v>
       </c>
       <c r="AB283" t="n">
-        <v>22.224</v>
+        <v>22.257</v>
       </c>
       <c r="AC283" t="n">
-        <v>16.597</v>
+        <v>16.708</v>
       </c>
       <c r="AD283" t="n">
-        <v>23.492</v>
+        <v>23.655</v>
       </c>
       <c r="AE283" t="n">
-        <v>10.936</v>
+        <v>11.258</v>
       </c>
       <c r="AF283" t="n">
-        <v>22.482</v>
+        <v>22.415</v>
       </c>
       <c r="AG283" t="n">
-        <v>15.857</v>
+        <v>15.814</v>
       </c>
       <c r="AH283" t="n">
-        <v>7.968</v>
+        <v>7.769</v>
       </c>
       <c r="AI283" t="n">
-        <v>4.418</v>
+        <v>4.594</v>
       </c>
       <c r="AJ283" t="n">
-        <v>16.069</v>
+        <v>16.084</v>
       </c>
       <c r="AK283" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AL283" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="284">
@@ -34466,22 +34466,22 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F284" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G284" t="b">
         <v>1</v>
       </c>
       <c r="H284" t="n">
-        <v>1495.489</v>
+        <v>1489.987</v>
       </c>
       <c r="I284" t="n">
-        <v>-1.6989</v>
+        <v>-1.7447</v>
       </c>
       <c r="J284" t="n">
-        <v>1500.5</v>
+        <v>1501.2</v>
       </c>
       <c r="K284" t="n">
         <v>162</v>
@@ -34502,70 +34502,70 @@
         <v>164</v>
       </c>
       <c r="Q284" t="n">
-        <v>111.697</v>
+        <v>110.657</v>
       </c>
       <c r="R284" t="n">
-        <v>108.982</v>
+        <v>108.259</v>
       </c>
       <c r="S284" t="n">
-        <v>2.715</v>
+        <v>2.398</v>
       </c>
       <c r="T284" t="n">
-        <v>0.26981</v>
+        <v>0.27641</v>
       </c>
       <c r="U284" t="n">
-        <v>0.12888</v>
+        <v>0.13004</v>
       </c>
       <c r="V284" t="n">
-        <v>73.5</v>
+        <v>72.81</v>
       </c>
       <c r="W284" t="n">
-        <v>71.56</v>
+        <v>71.08</v>
       </c>
       <c r="X284" t="n">
-        <v>0.4926</v>
+        <v>0.4773</v>
       </c>
       <c r="Y284" t="n">
-        <v>24.767</v>
+        <v>24.655</v>
       </c>
       <c r="Z284" t="n">
-        <v>55.782</v>
+        <v>55.927</v>
       </c>
       <c r="AA284" t="n">
-        <v>6.854</v>
+        <v>6.645</v>
       </c>
       <c r="AB284" t="n">
-        <v>20.402</v>
+        <v>19.818</v>
       </c>
       <c r="AC284" t="n">
-        <v>17.117</v>
+        <v>16.855</v>
       </c>
       <c r="AD284" t="n">
-        <v>22.798</v>
+        <v>22.586</v>
       </c>
       <c r="AE284" t="n">
-        <v>8.412000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AF284" t="n">
-        <v>22.286</v>
+        <v>21.964</v>
       </c>
       <c r="AG284" t="n">
-        <v>12.149</v>
+        <v>11.795</v>
       </c>
       <c r="AH284" t="n">
-        <v>5.409</v>
+        <v>5.745</v>
       </c>
       <c r="AI284" t="n">
-        <v>4.036</v>
+        <v>3.973</v>
       </c>
       <c r="AJ284" t="n">
-        <v>17.632</v>
+        <v>17.268</v>
       </c>
       <c r="AK284" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="AL284" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="285">
@@ -34946,22 +34946,22 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F288" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G288" t="b">
         <v>1</v>
       </c>
       <c r="H288" t="n">
-        <v>1757.703</v>
+        <v>1741.68</v>
       </c>
       <c r="I288" t="n">
-        <v>2.865</v>
+        <v>2.8164</v>
       </c>
       <c r="J288" t="n">
-        <v>1699.4</v>
+        <v>1696.4</v>
       </c>
       <c r="K288" t="n">
         <v>33</v>
@@ -34982,70 +34982,70 @@
         <v>41</v>
       </c>
       <c r="Q288" t="n">
-        <v>120.366</v>
+        <v>119.505</v>
       </c>
       <c r="R288" t="n">
-        <v>111.344</v>
+        <v>111.341</v>
       </c>
       <c r="S288" t="n">
-        <v>9.023</v>
+        <v>8.164</v>
       </c>
       <c r="T288" t="n">
-        <v>0.30977</v>
+        <v>0.30721</v>
       </c>
       <c r="U288" t="n">
-        <v>0.14945</v>
+        <v>0.145</v>
       </c>
       <c r="V288" t="n">
-        <v>83.22</v>
+        <v>82.48</v>
       </c>
       <c r="W288" t="n">
-        <v>76.92</v>
+        <v>76.77</v>
       </c>
       <c r="X288" t="n">
-        <v>0.5607</v>
+        <v>0.5431</v>
       </c>
       <c r="Y288" t="n">
-        <v>27.903</v>
+        <v>28.019</v>
       </c>
       <c r="Z288" t="n">
-        <v>57.867</v>
+        <v>58.09</v>
       </c>
       <c r="AA288" t="n">
-        <v>7.328</v>
+        <v>7.038</v>
       </c>
       <c r="AB288" t="n">
-        <v>20.996</v>
+        <v>20.446</v>
       </c>
       <c r="AC288" t="n">
-        <v>20.085</v>
+        <v>19.824</v>
       </c>
       <c r="AD288" t="n">
-        <v>26.724</v>
+        <v>26.421</v>
       </c>
       <c r="AE288" t="n">
-        <v>10.748</v>
+        <v>10.651</v>
       </c>
       <c r="AF288" t="n">
-        <v>24.054</v>
+        <v>24.115</v>
       </c>
       <c r="AG288" t="n">
-        <v>11.922</v>
+        <v>11.779</v>
       </c>
       <c r="AH288" t="n">
-        <v>5.726</v>
+        <v>5.994</v>
       </c>
       <c r="AI288" t="n">
-        <v>2.748</v>
+        <v>2.901</v>
       </c>
       <c r="AJ288" t="n">
-        <v>18.987</v>
+        <v>18.853</v>
       </c>
       <c r="AK288" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8</v>
       </c>
       <c r="AL288" t="n">
-        <v>0.9</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="289">
@@ -35906,22 +35906,22 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F296" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G296" t="b">
         <v>1</v>
       </c>
       <c r="H296" t="n">
-        <v>1495.672</v>
+        <v>1504.017</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.8275</v>
+        <v>-1.8568</v>
       </c>
       <c r="J296" t="n">
-        <v>1531.6</v>
+        <v>1532.8</v>
       </c>
       <c r="K296" t="n">
         <v>210</v>
@@ -35942,70 +35942,70 @@
         <v>206</v>
       </c>
       <c r="Q296" t="n">
-        <v>105.566</v>
+        <v>105.806</v>
       </c>
       <c r="R296" t="n">
-        <v>110.647</v>
+        <v>109.965</v>
       </c>
       <c r="S296" t="n">
-        <v>-5.081</v>
+        <v>-4.158</v>
       </c>
       <c r="T296" t="n">
-        <v>0.23459</v>
+        <v>0.23814</v>
       </c>
       <c r="U296" t="n">
-        <v>0.15187</v>
+        <v>0.15333</v>
       </c>
       <c r="V296" t="n">
-        <v>72.42</v>
+        <v>72.52</v>
       </c>
       <c r="W296" t="n">
-        <v>76.18000000000001</v>
+        <v>75.63</v>
       </c>
       <c r="X296" t="n">
-        <v>0.5266</v>
+        <v>0.5536</v>
       </c>
       <c r="Y296" t="n">
-        <v>23.393</v>
+        <v>23.18</v>
       </c>
       <c r="Z296" t="n">
-        <v>54.469</v>
+        <v>54.528</v>
       </c>
       <c r="AA296" t="n">
-        <v>7.683</v>
+        <v>7.551</v>
       </c>
       <c r="AB296" t="n">
-        <v>23.926</v>
+        <v>23.817</v>
       </c>
       <c r="AC296" t="n">
-        <v>17.95</v>
+        <v>18.087</v>
       </c>
       <c r="AD296" t="n">
-        <v>23.661</v>
+        <v>23.962</v>
       </c>
       <c r="AE296" t="n">
-        <v>6.701</v>
+        <v>7.041</v>
       </c>
       <c r="AF296" t="n">
-        <v>21.448</v>
+        <v>21.794</v>
       </c>
       <c r="AG296" t="n">
-        <v>12.782</v>
+        <v>12.516</v>
       </c>
       <c r="AH296" t="n">
-        <v>7.622</v>
+        <v>7.455</v>
       </c>
       <c r="AI296" t="n">
-        <v>4.666</v>
+        <v>4.8</v>
       </c>
       <c r="AJ296" t="n">
-        <v>17.792</v>
+        <v>17.757</v>
       </c>
       <c r="AK296" t="n">
-        <v>-17.2</v>
+        <v>-16</v>
       </c>
       <c r="AL296" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="297">
@@ -36506,22 +36506,22 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F301" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G301" t="b">
         <v>1</v>
       </c>
       <c r="H301" t="n">
-        <v>1472.704</v>
+        <v>1478.537</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3306</v>
+        <v>-0.3411</v>
       </c>
       <c r="J301" t="n">
-        <v>1456.9</v>
+        <v>1457.1</v>
       </c>
       <c r="K301" t="n">
         <v>155</v>
@@ -36542,70 +36542,70 @@
         <v>176</v>
       </c>
       <c r="Q301" t="n">
-        <v>106.711</v>
+        <v>106.915</v>
       </c>
       <c r="R301" t="n">
-        <v>106.156</v>
+        <v>105.912</v>
       </c>
       <c r="S301" t="n">
-        <v>0.555</v>
+        <v>1.003</v>
       </c>
       <c r="T301" t="n">
-        <v>0.25418</v>
+        <v>0.24996</v>
       </c>
       <c r="U301" t="n">
-        <v>0.17526</v>
+        <v>0.17405</v>
       </c>
       <c r="V301" t="n">
-        <v>76.11</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="W301" t="n">
-        <v>75.95999999999999</v>
+        <v>75.81</v>
       </c>
       <c r="X301" t="n">
-        <v>0.5466</v>
+        <v>0.5704</v>
       </c>
       <c r="Y301" t="n">
-        <v>25.102</v>
+        <v>25.224</v>
       </c>
       <c r="Z301" t="n">
-        <v>56.528</v>
+        <v>56.513</v>
       </c>
       <c r="AA301" t="n">
-        <v>8.627000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="AB301" t="n">
-        <v>24.693</v>
+        <v>24.52</v>
       </c>
       <c r="AC301" t="n">
-        <v>17.273</v>
+        <v>17.322</v>
       </c>
       <c r="AD301" t="n">
-        <v>22.938</v>
+        <v>23.024</v>
       </c>
       <c r="AE301" t="n">
-        <v>7.596</v>
+        <v>7.511</v>
       </c>
       <c r="AF301" t="n">
-        <v>22.04</v>
+        <v>22.399</v>
       </c>
       <c r="AG301" t="n">
-        <v>15.283</v>
+        <v>15.181</v>
       </c>
       <c r="AH301" t="n">
-        <v>7.447</v>
+        <v>7.438</v>
       </c>
       <c r="AI301" t="n">
-        <v>2.795</v>
+        <v>2.76</v>
       </c>
       <c r="AJ301" t="n">
-        <v>18.292</v>
+        <v>18.139</v>
       </c>
       <c r="AK301" t="n">
-        <v>-0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AL301" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="302">
@@ -36866,22 +36866,22 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F304" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G304" t="b">
         <v>1</v>
       </c>
       <c r="H304" t="n">
-        <v>1820.485</v>
+        <v>1831.057</v>
       </c>
       <c r="I304" t="n">
-        <v>7.025</v>
+        <v>6.3402</v>
       </c>
       <c r="J304" t="n">
-        <v>1687.9</v>
+        <v>1689.6</v>
       </c>
       <c r="K304" t="n">
         <v>53</v>
@@ -36902,70 +36902,70 @@
         <v>51</v>
       </c>
       <c r="Q304" t="n">
-        <v>114.766</v>
+        <v>113.797</v>
       </c>
       <c r="R304" t="n">
-        <v>110.491</v>
+        <v>109.323</v>
       </c>
       <c r="S304" t="n">
-        <v>4.275</v>
+        <v>4.474</v>
       </c>
       <c r="T304" t="n">
-        <v>0.31151</v>
+        <v>0.31328</v>
       </c>
       <c r="U304" t="n">
-        <v>0.1546</v>
+        <v>0.15363</v>
       </c>
       <c r="V304" t="n">
-        <v>81.95</v>
+        <v>81.5</v>
       </c>
       <c r="W304" t="n">
-        <v>78.81</v>
+        <v>78.23</v>
       </c>
       <c r="X304" t="n">
-        <v>0.6583</v>
+        <v>0.6812</v>
       </c>
       <c r="Y304" t="n">
-        <v>29.661</v>
+        <v>29.528</v>
       </c>
       <c r="Z304" t="n">
-        <v>62.671</v>
+        <v>63.159</v>
       </c>
       <c r="AA304" t="n">
-        <v>8.102</v>
+        <v>7.942</v>
       </c>
       <c r="AB304" t="n">
-        <v>21.563</v>
+        <v>21.736</v>
       </c>
       <c r="AC304" t="n">
-        <v>14.522</v>
+        <v>14.499</v>
       </c>
       <c r="AD304" t="n">
-        <v>19.448</v>
+        <v>19.62</v>
       </c>
       <c r="AE304" t="n">
-        <v>10.886</v>
+        <v>11.145</v>
       </c>
       <c r="AF304" t="n">
-        <v>23.334</v>
+        <v>23.635</v>
       </c>
       <c r="AG304" t="n">
-        <v>16.031</v>
+        <v>15.867</v>
       </c>
       <c r="AH304" t="n">
-        <v>5.671</v>
+        <v>5.725</v>
       </c>
       <c r="AI304" t="n">
-        <v>3.02</v>
+        <v>2.988</v>
       </c>
       <c r="AJ304" t="n">
-        <v>17.375</v>
+        <v>17.307</v>
       </c>
       <c r="AK304" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="AL304" t="n">
-        <v>-4</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="305">
@@ -37826,22 +37826,22 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F312" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G312" t="b">
         <v>1</v>
       </c>
       <c r="H312" t="n">
-        <v>1644.594</v>
+        <v>1650.367</v>
       </c>
       <c r="I312" t="n">
-        <v>1.6162</v>
+        <v>1.6984</v>
       </c>
       <c r="J312" t="n">
-        <v>1623.2</v>
+        <v>1617.1</v>
       </c>
       <c r="K312" t="n">
         <v>104</v>
@@ -37862,70 +37862,70 @@
         <v>111</v>
       </c>
       <c r="Q312" t="n">
-        <v>112.135</v>
+        <v>111.947</v>
       </c>
       <c r="R312" t="n">
-        <v>111.678</v>
+        <v>111.259</v>
       </c>
       <c r="S312" t="n">
-        <v>0.457</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="T312" t="n">
-        <v>0.29405</v>
+        <v>0.29367</v>
       </c>
       <c r="U312" t="n">
-        <v>0.15977</v>
+        <v>0.16043</v>
       </c>
       <c r="V312" t="n">
-        <v>80.01000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="W312" t="n">
-        <v>79.98</v>
+        <v>79.44</v>
       </c>
       <c r="X312" t="n">
-        <v>0.4937</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="Y312" t="n">
-        <v>27.861</v>
+        <v>27.623</v>
       </c>
       <c r="Z312" t="n">
-        <v>58.906</v>
+        <v>58.568</v>
       </c>
       <c r="AA312" t="n">
-        <v>7.4</v>
+        <v>7.394</v>
       </c>
       <c r="AB312" t="n">
-        <v>20.959</v>
+        <v>20.936</v>
       </c>
       <c r="AC312" t="n">
-        <v>16.889</v>
+        <v>16.991</v>
       </c>
       <c r="AD312" t="n">
-        <v>24.469</v>
+        <v>24.783</v>
       </c>
       <c r="AE312" t="n">
-        <v>9.613</v>
+        <v>9.648999999999999</v>
       </c>
       <c r="AF312" t="n">
-        <v>22.625</v>
+        <v>22.78</v>
       </c>
       <c r="AG312" t="n">
-        <v>14.309</v>
+        <v>14.243</v>
       </c>
       <c r="AH312" t="n">
-        <v>7.461</v>
+        <v>7.316</v>
       </c>
       <c r="AI312" t="n">
-        <v>4.284</v>
+        <v>4.635</v>
       </c>
       <c r="AJ312" t="n">
-        <v>21.674</v>
+        <v>21.571</v>
       </c>
       <c r="AK312" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="AL312" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="313">
@@ -37946,22 +37946,22 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F313" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G313" t="b">
         <v>1</v>
       </c>
       <c r="H313" t="n">
-        <v>1742.961</v>
+        <v>1727.904</v>
       </c>
       <c r="I313" t="n">
-        <v>1.0281</v>
+        <v>0.4482</v>
       </c>
       <c r="J313" t="n">
-        <v>1693.6</v>
+        <v>1689.6</v>
       </c>
       <c r="K313" t="n">
         <v>77</v>
@@ -37982,70 +37982,70 @@
         <v>78</v>
       </c>
       <c r="Q313" t="n">
-        <v>108.152</v>
+        <v>107.677</v>
       </c>
       <c r="R313" t="n">
-        <v>109.616</v>
+        <v>108.899</v>
       </c>
       <c r="S313" t="n">
-        <v>-1.464</v>
+        <v>-1.222</v>
       </c>
       <c r="T313" t="n">
-        <v>0.29366</v>
+        <v>0.29051</v>
       </c>
       <c r="U313" t="n">
-        <v>0.16794</v>
+        <v>0.16849</v>
       </c>
       <c r="V313" t="n">
-        <v>77.68000000000001</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="W313" t="n">
-        <v>78.40000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="X313" t="n">
-        <v>0.5596</v>
+        <v>0.542</v>
       </c>
       <c r="Y313" t="n">
-        <v>26.172</v>
+        <v>26.409</v>
       </c>
       <c r="Z313" t="n">
-        <v>58.238</v>
+        <v>58.733</v>
       </c>
       <c r="AA313" t="n">
-        <v>6.309</v>
+        <v>6.33</v>
       </c>
       <c r="AB313" t="n">
-        <v>19.984</v>
+        <v>19.98</v>
       </c>
       <c r="AC313" t="n">
-        <v>19.024</v>
+        <v>18.704</v>
       </c>
       <c r="AD313" t="n">
-        <v>26.039</v>
+        <v>25.812</v>
       </c>
       <c r="AE313" t="n">
-        <v>9.897</v>
+        <v>9.893000000000001</v>
       </c>
       <c r="AF313" t="n">
-        <v>23.246</v>
+        <v>23.722</v>
       </c>
       <c r="AG313" t="n">
-        <v>14.771</v>
+        <v>14.986</v>
       </c>
       <c r="AH313" t="n">
-        <v>6.16</v>
+        <v>6.148</v>
       </c>
       <c r="AI313" t="n">
-        <v>5.486</v>
+        <v>5.577</v>
       </c>
       <c r="AJ313" t="n">
-        <v>18.803</v>
+        <v>18.765</v>
       </c>
       <c r="AK313" t="n">
-        <v>-15</v>
+        <v>-15.6</v>
       </c>
       <c r="AL313" t="n">
-        <v>-10.7</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="314">
@@ -40346,22 +40346,22 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F333" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G333" t="b">
         <v>1</v>
       </c>
       <c r="H333" t="n">
-        <v>1664.296</v>
+        <v>1657.02</v>
       </c>
       <c r="I333" t="n">
-        <v>-2.8429</v>
+        <v>-2.5969</v>
       </c>
       <c r="J333" t="n">
-        <v>1670.8</v>
+        <v>1677.2</v>
       </c>
       <c r="K333" t="n">
         <v>74</v>
@@ -40382,70 +40382,70 @@
         <v>64</v>
       </c>
       <c r="Q333" t="n">
-        <v>112.871</v>
+        <v>112.23</v>
       </c>
       <c r="R333" t="n">
-        <v>109.995</v>
+        <v>110.155</v>
       </c>
       <c r="S333" t="n">
-        <v>2.877</v>
+        <v>2.075</v>
       </c>
       <c r="T333" t="n">
-        <v>0.29913</v>
+        <v>0.29346</v>
       </c>
       <c r="U333" t="n">
-        <v>0.14976</v>
+        <v>0.15144</v>
       </c>
       <c r="V333" t="n">
-        <v>79.56999999999999</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="W333" t="n">
-        <v>77.40000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="X333" t="n">
-        <v>0.5372</v>
+        <v>0.5091</v>
       </c>
       <c r="Y333" t="n">
-        <v>26.994</v>
+        <v>26.762</v>
       </c>
       <c r="Z333" t="n">
-        <v>60.373</v>
+        <v>59.823</v>
       </c>
       <c r="AA333" t="n">
-        <v>8.926</v>
+        <v>8.981999999999999</v>
       </c>
       <c r="AB333" t="n">
-        <v>26.222</v>
+        <v>26.073</v>
       </c>
       <c r="AC333" t="n">
-        <v>16.397</v>
+        <v>15.966</v>
       </c>
       <c r="AD333" t="n">
-        <v>21.137</v>
+        <v>20.727</v>
       </c>
       <c r="AE333" t="n">
-        <v>9.583</v>
+        <v>9.336</v>
       </c>
       <c r="AF333" t="n">
-        <v>22.056</v>
+        <v>22.197</v>
       </c>
       <c r="AG333" t="n">
-        <v>14.309</v>
+        <v>14.216</v>
       </c>
       <c r="AH333" t="n">
-        <v>7.813</v>
+        <v>7.63</v>
       </c>
       <c r="AI333" t="n">
-        <v>3.519</v>
+        <v>3.438</v>
       </c>
       <c r="AJ333" t="n">
-        <v>18.914</v>
+        <v>18.672</v>
       </c>
       <c r="AK333" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="AL333" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="334">
@@ -40466,22 +40466,22 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F334" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G334" t="b">
         <v>1</v>
       </c>
       <c r="H334" t="n">
-        <v>1645.746</v>
+        <v>1660.804</v>
       </c>
       <c r="I334" t="n">
-        <v>2.0254</v>
+        <v>1.8763</v>
       </c>
       <c r="J334" t="n">
-        <v>1686.4</v>
+        <v>1689.5</v>
       </c>
       <c r="K334" t="n">
         <v>54</v>
@@ -40502,70 +40502,70 @@
         <v>61</v>
       </c>
       <c r="Q334" t="n">
-        <v>111.966</v>
+        <v>111.563</v>
       </c>
       <c r="R334" t="n">
-        <v>107.182</v>
+        <v>106.636</v>
       </c>
       <c r="S334" t="n">
-        <v>4.784</v>
+        <v>4.928</v>
       </c>
       <c r="T334" t="n">
-        <v>0.2998</v>
+        <v>0.29778</v>
       </c>
       <c r="U334" t="n">
-        <v>0.14971</v>
+        <v>0.14935</v>
       </c>
       <c r="V334" t="n">
-        <v>76.8</v>
+        <v>77.02</v>
       </c>
       <c r="W334" t="n">
-        <v>73.20999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="X334" t="n">
-        <v>0.4792</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="Y334" t="n">
-        <v>28.054</v>
+        <v>28.102</v>
       </c>
       <c r="Z334" t="n">
-        <v>60.971</v>
+        <v>61.36</v>
       </c>
       <c r="AA334" t="n">
-        <v>6.572</v>
+        <v>6.726</v>
       </c>
       <c r="AB334" t="n">
-        <v>21.046</v>
+        <v>21.289</v>
       </c>
       <c r="AC334" t="n">
-        <v>14.115</v>
+        <v>14.093</v>
       </c>
       <c r="AD334" t="n">
-        <v>18.396</v>
+        <v>18.443</v>
       </c>
       <c r="AE334" t="n">
-        <v>10.639</v>
+        <v>10.619</v>
       </c>
       <c r="AF334" t="n">
-        <v>24.022</v>
+        <v>24.271</v>
       </c>
       <c r="AG334" t="n">
-        <v>13.428</v>
+        <v>13.714</v>
       </c>
       <c r="AH334" t="n">
-        <v>5.744</v>
+        <v>5.792</v>
       </c>
       <c r="AI334" t="n">
-        <v>4.099</v>
+        <v>4.124</v>
       </c>
       <c r="AJ334" t="n">
-        <v>16.981</v>
+        <v>17.08</v>
       </c>
       <c r="AK334" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL334" t="n">
         <v>-0.2</v>
-      </c>
-      <c r="AL334" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="335">
@@ -40826,22 +40826,22 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F337" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G337" t="b">
         <v>1</v>
       </c>
       <c r="H337" t="n">
-        <v>1710.314</v>
+        <v>1703.642</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4911</v>
+        <v>0.6918</v>
       </c>
       <c r="J337" t="n">
-        <v>1659.8</v>
+        <v>1669</v>
       </c>
       <c r="K337" t="n">
         <v>57</v>
@@ -40862,70 +40862,70 @@
         <v>58</v>
       </c>
       <c r="Q337" t="n">
-        <v>107.746</v>
+        <v>106.362</v>
       </c>
       <c r="R337" t="n">
-        <v>99.542</v>
+        <v>99.998</v>
       </c>
       <c r="S337" t="n">
-        <v>8.204000000000001</v>
+        <v>6.364</v>
       </c>
       <c r="T337" t="n">
-        <v>0.28656</v>
+        <v>0.29519</v>
       </c>
       <c r="U337" t="n">
-        <v>0.16296</v>
+        <v>0.16549</v>
       </c>
       <c r="V337" t="n">
-        <v>69.95</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="W337" t="n">
-        <v>64.61</v>
+        <v>64.78</v>
       </c>
       <c r="X337" t="n">
-        <v>0.5855</v>
+        <v>0.5565</v>
       </c>
       <c r="Y337" t="n">
-        <v>24.414</v>
+        <v>24.569</v>
       </c>
       <c r="Z337" t="n">
-        <v>55.168</v>
+        <v>55.435</v>
       </c>
       <c r="AA337" t="n">
-        <v>7.809</v>
+        <v>7.731</v>
       </c>
       <c r="AB337" t="n">
-        <v>23.716</v>
+        <v>23.441</v>
       </c>
       <c r="AC337" t="n">
-        <v>13.316</v>
+        <v>12.925</v>
       </c>
       <c r="AD337" t="n">
-        <v>19.548</v>
+        <v>19.089</v>
       </c>
       <c r="AE337" t="n">
-        <v>9.4</v>
+        <v>9.724</v>
       </c>
       <c r="AF337" t="n">
-        <v>22.867</v>
+        <v>22.648</v>
       </c>
       <c r="AG337" t="n">
-        <v>13.043</v>
+        <v>12.864</v>
       </c>
       <c r="AH337" t="n">
-        <v>6.383</v>
+        <v>6.496</v>
       </c>
       <c r="AI337" t="n">
-        <v>2.939</v>
+        <v>2.949</v>
       </c>
       <c r="AJ337" t="n">
-        <v>15.449</v>
+        <v>15.402</v>
       </c>
       <c r="AK337" t="n">
-        <v>1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AL337" t="n">
-        <v>-0.2</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="338">
@@ -41906,22 +41906,22 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F346" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G346" t="b">
         <v>1</v>
       </c>
       <c r="H346" t="n">
-        <v>1526.838</v>
+        <v>1521.064</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2647</v>
+        <v>-0.1434</v>
       </c>
       <c r="J346" t="n">
-        <v>1558</v>
+        <v>1563.6</v>
       </c>
       <c r="K346" t="n">
         <v>98</v>
@@ -41942,70 +41942,70 @@
         <v>98</v>
       </c>
       <c r="Q346" t="n">
-        <v>113.841</v>
+        <v>113.423</v>
       </c>
       <c r="R346" t="n">
-        <v>109.086</v>
+        <v>109.184</v>
       </c>
       <c r="S346" t="n">
-        <v>4.755</v>
+        <v>4.239</v>
       </c>
       <c r="T346" t="n">
-        <v>0.32308</v>
+        <v>0.32866</v>
       </c>
       <c r="U346" t="n">
-        <v>0.15901</v>
+        <v>0.15531</v>
       </c>
       <c r="V346" t="n">
-        <v>76.72</v>
+        <v>76.33</v>
       </c>
       <c r="W346" t="n">
-        <v>72.95</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="X346" t="n">
-        <v>0.5712</v>
+        <v>0.5431</v>
       </c>
       <c r="Y346" t="n">
-        <v>26.327</v>
+        <v>26.256</v>
       </c>
       <c r="Z346" t="n">
-        <v>58.012</v>
+        <v>58.532</v>
       </c>
       <c r="AA346" t="n">
-        <v>8.439</v>
+        <v>8.207000000000001</v>
       </c>
       <c r="AB346" t="n">
-        <v>25.201</v>
+        <v>25.089</v>
       </c>
       <c r="AC346" t="n">
-        <v>15.627</v>
+        <v>15.607</v>
       </c>
       <c r="AD346" t="n">
-        <v>20.772</v>
+        <v>20.799</v>
       </c>
       <c r="AE346" t="n">
-        <v>10.471</v>
+        <v>10.874</v>
       </c>
       <c r="AF346" t="n">
-        <v>22.244</v>
+        <v>22.287</v>
       </c>
       <c r="AG346" t="n">
-        <v>14.076</v>
+        <v>13.939</v>
       </c>
       <c r="AH346" t="n">
-        <v>6.519</v>
+        <v>6.376</v>
       </c>
       <c r="AI346" t="n">
-        <v>2.342</v>
+        <v>2.351</v>
       </c>
       <c r="AJ346" t="n">
-        <v>21.057</v>
+        <v>21.096</v>
       </c>
       <c r="AK346" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="AL346" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="347">
@@ -42026,22 +42026,22 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F347" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G347" t="b">
         <v>1</v>
       </c>
       <c r="H347" t="n">
-        <v>1591.767</v>
+        <v>1598.716</v>
       </c>
       <c r="I347" t="n">
-        <v>-2.8435</v>
+        <v>-2.9105</v>
       </c>
       <c r="J347" t="n">
-        <v>1639.3</v>
+        <v>1632.7</v>
       </c>
       <c r="K347" t="n">
         <v>97</v>
@@ -42062,67 +42062,67 @@
         <v>97</v>
       </c>
       <c r="Q347" t="n">
-        <v>108.756</v>
+        <v>109.084</v>
       </c>
       <c r="R347" t="n">
-        <v>111.445</v>
+        <v>111.336</v>
       </c>
       <c r="S347" t="n">
-        <v>-2.689</v>
+        <v>-2.252</v>
       </c>
       <c r="T347" t="n">
-        <v>0.2684</v>
+        <v>0.27211</v>
       </c>
       <c r="U347" t="n">
-        <v>0.13549</v>
+        <v>0.13521</v>
       </c>
       <c r="V347" t="n">
-        <v>78.34999999999999</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="W347" t="n">
-        <v>80.18000000000001</v>
+        <v>80.34</v>
       </c>
       <c r="X347" t="n">
-        <v>0.4455</v>
+        <v>0.4755</v>
       </c>
       <c r="Y347" t="n">
-        <v>28.145</v>
+        <v>28.285</v>
       </c>
       <c r="Z347" t="n">
-        <v>63.55</v>
+        <v>63.928</v>
       </c>
       <c r="AA347" t="n">
-        <v>9.427</v>
+        <v>9.488</v>
       </c>
       <c r="AB347" t="n">
-        <v>25.65</v>
+        <v>26.269</v>
       </c>
       <c r="AC347" t="n">
-        <v>12.632</v>
+        <v>12.673</v>
       </c>
       <c r="AD347" t="n">
-        <v>17.245</v>
+        <v>17.365</v>
       </c>
       <c r="AE347" t="n">
-        <v>8.827</v>
+        <v>9.063000000000001</v>
       </c>
       <c r="AF347" t="n">
-        <v>23.786</v>
+        <v>23.889</v>
       </c>
       <c r="AG347" t="n">
-        <v>17.682</v>
+        <v>17.822</v>
       </c>
       <c r="AH347" t="n">
-        <v>6.555</v>
+        <v>6.525</v>
       </c>
       <c r="AI347" t="n">
-        <v>3.991</v>
+        <v>4.074</v>
       </c>
       <c r="AJ347" t="n">
-        <v>17.659</v>
+        <v>17.548</v>
       </c>
       <c r="AK347" t="n">
-        <v>-6</v>
+        <v>-4.6</v>
       </c>
       <c r="AL347" t="n">
         <v>-6</v>
@@ -42986,22 +42986,22 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F355" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G355" t="b">
         <v>1</v>
       </c>
       <c r="H355" t="n">
-        <v>1383.62</v>
+        <v>1386.791</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.9969</v>
+        <v>-1.08</v>
       </c>
       <c r="J355" t="n">
-        <v>1470.7</v>
+        <v>1467.7</v>
       </c>
       <c r="K355" t="n">
         <v>216</v>
@@ -43022,67 +43022,67 @@
         <v>224</v>
       </c>
       <c r="Q355" t="n">
-        <v>100.837</v>
+        <v>100.944</v>
       </c>
       <c r="R355" t="n">
-        <v>105.738</v>
+        <v>105.941</v>
       </c>
       <c r="S355" t="n">
-        <v>-4.901</v>
+        <v>-4.997</v>
       </c>
       <c r="T355" t="n">
-        <v>0.32251</v>
+        <v>0.32108</v>
       </c>
       <c r="U355" t="n">
-        <v>0.19215</v>
+        <v>0.19124</v>
       </c>
       <c r="V355" t="n">
-        <v>72.06</v>
+        <v>72.55</v>
       </c>
       <c r="W355" t="n">
-        <v>75.28</v>
+        <v>75.87</v>
       </c>
       <c r="X355" t="n">
-        <v>0.3644</v>
+        <v>0.3519</v>
       </c>
       <c r="Y355" t="n">
-        <v>25.121</v>
+        <v>25.161</v>
       </c>
       <c r="Z355" t="n">
-        <v>56.547</v>
+        <v>56.769</v>
       </c>
       <c r="AA355" t="n">
-        <v>4.421</v>
+        <v>4.472</v>
       </c>
       <c r="AB355" t="n">
-        <v>13.733</v>
+        <v>13.739</v>
       </c>
       <c r="AC355" t="n">
-        <v>17.397</v>
+        <v>17.752</v>
       </c>
       <c r="AD355" t="n">
-        <v>23.494</v>
+        <v>23.952</v>
       </c>
       <c r="AE355" t="n">
-        <v>9.282999999999999</v>
+        <v>9.311</v>
       </c>
       <c r="AF355" t="n">
-        <v>19.316</v>
+        <v>19.502</v>
       </c>
       <c r="AG355" t="n">
-        <v>10.514</v>
+        <v>10.478</v>
       </c>
       <c r="AH355" t="n">
-        <v>9.664</v>
+        <v>9.704000000000001</v>
       </c>
       <c r="AI355" t="n">
-        <v>3.057</v>
+        <v>3.07</v>
       </c>
       <c r="AJ355" t="n">
-        <v>20.036</v>
+        <v>20.635</v>
       </c>
       <c r="AK355" t="n">
-        <v>-6.2</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AL355" t="n">
         <v>-4.6</v>
@@ -43106,22 +43106,22 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F356" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G356" t="b">
         <v>1</v>
       </c>
       <c r="H356" t="n">
-        <v>1609.612</v>
+        <v>1612.445</v>
       </c>
       <c r="I356" t="n">
-        <v>-8.5106</v>
+        <v>-8.2102</v>
       </c>
       <c r="J356" t="n">
-        <v>1452.2</v>
+        <v>1449.6</v>
       </c>
       <c r="K356" t="n">
         <v>113</v>
@@ -43142,70 +43142,70 @@
         <v>120</v>
       </c>
       <c r="Q356" t="n">
-        <v>107.436</v>
+        <v>107.168</v>
       </c>
       <c r="R356" t="n">
-        <v>101.115</v>
+        <v>100.888</v>
       </c>
       <c r="S356" t="n">
-        <v>6.322</v>
+        <v>6.28</v>
       </c>
       <c r="T356" t="n">
-        <v>0.23662</v>
+        <v>0.2341</v>
       </c>
       <c r="U356" t="n">
-        <v>0.15693</v>
+        <v>0.15836</v>
       </c>
       <c r="V356" t="n">
         <v>74.59</v>
       </c>
       <c r="W356" t="n">
-        <v>70.12</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="X356" t="n">
-        <v>0.6702</v>
+        <v>0.6806</v>
       </c>
       <c r="Y356" t="n">
-        <v>26.979</v>
+        <v>26.917</v>
       </c>
       <c r="Z356" t="n">
-        <v>58.75</v>
+        <v>58.642</v>
       </c>
       <c r="AA356" t="n">
-        <v>8.167999999999999</v>
+        <v>8.099</v>
       </c>
       <c r="AB356" t="n">
-        <v>24.631</v>
+        <v>24.536</v>
       </c>
       <c r="AC356" t="n">
-        <v>12.462</v>
+        <v>12.656</v>
       </c>
       <c r="AD356" t="n">
-        <v>18.132</v>
+        <v>18.419</v>
       </c>
       <c r="AE356" t="n">
-        <v>8.121</v>
+        <v>8.086</v>
       </c>
       <c r="AF356" t="n">
-        <v>25.96</v>
+        <v>26.24</v>
       </c>
       <c r="AG356" t="n">
-        <v>14.772</v>
+        <v>14.84</v>
       </c>
       <c r="AH356" t="n">
-        <v>7.622</v>
+        <v>7.428</v>
       </c>
       <c r="AI356" t="n">
-        <v>2.55</v>
+        <v>2.543</v>
       </c>
       <c r="AJ356" t="n">
-        <v>16.375</v>
+        <v>16.425</v>
       </c>
       <c r="AK356" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AL356" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="357">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -866,22 +866,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1696.501</v>
+        <v>1704.461</v>
       </c>
       <c r="I4" t="n">
-        <v>1.818</v>
+        <v>1.8839</v>
       </c>
       <c r="J4" t="n">
-        <v>1474.6</v>
+        <v>1481.1</v>
       </c>
       <c r="K4" t="n">
         <v>61</v>
@@ -902,70 +902,70 @@
         <v>52</v>
       </c>
       <c r="Q4" t="n">
-        <v>122.156</v>
+        <v>121.819</v>
       </c>
       <c r="R4" t="n">
-        <v>104.236</v>
+        <v>104.079</v>
       </c>
       <c r="S4" t="n">
-        <v>17.92</v>
+        <v>17.74</v>
       </c>
       <c r="T4" t="n">
-        <v>0.28555</v>
+        <v>0.2847</v>
       </c>
       <c r="U4" t="n">
-        <v>0.15211</v>
+        <v>0.1512</v>
       </c>
       <c r="V4" t="n">
-        <v>87.38</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>74.62</v>
+        <v>74.39</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8351</v>
+        <v>0.8403</v>
       </c>
       <c r="Y4" t="n">
-        <v>31.255</v>
+        <v>31.037</v>
       </c>
       <c r="Z4" t="n">
-        <v>62.463</v>
+        <v>62.271</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.969</v>
+        <v>10.875</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.156</v>
+        <v>28.025</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.903</v>
+        <v>14.061</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.198</v>
+        <v>18.567</v>
       </c>
       <c r="AE4" t="n">
-        <v>9.802</v>
+        <v>9.808</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.307</v>
+        <v>25.412</v>
       </c>
       <c r="AG4" t="n">
-        <v>18.135</v>
+        <v>17.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.483</v>
+        <v>7.281</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.726</v>
+        <v>2.869</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16.297</v>
+        <v>16.454</v>
       </c>
       <c r="AK4" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1975.068</v>
+        <v>1949.262</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4869</v>
+        <v>-1.3255</v>
       </c>
       <c r="J5" t="n">
-        <v>1772.1</v>
+        <v>1767</v>
       </c>
       <c r="K5" t="n">
         <v>15</v>
@@ -1022,70 +1022,70 @@
         <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>122.115</v>
+        <v>121.371</v>
       </c>
       <c r="R5" t="n">
-        <v>110.784</v>
+        <v>110.604</v>
       </c>
       <c r="S5" t="n">
-        <v>11.331</v>
+        <v>10.767</v>
       </c>
       <c r="T5" t="n">
-        <v>0.28529</v>
+        <v>0.28088</v>
       </c>
       <c r="U5" t="n">
-        <v>0.12891</v>
+        <v>0.12877</v>
       </c>
       <c r="V5" t="n">
-        <v>92.17</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>83.58</v>
+        <v>83.44</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7444</v>
+        <v>0.7123</v>
       </c>
       <c r="Y5" t="n">
-        <v>30.346</v>
+        <v>30.319</v>
       </c>
       <c r="Z5" t="n">
-        <v>65.965</v>
+        <v>65.97799999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.718</v>
+        <v>12.583</v>
       </c>
       <c r="AB5" t="n">
-        <v>35.465</v>
+        <v>34.886</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.757</v>
+        <v>18.423</v>
       </c>
       <c r="AD5" t="n">
-        <v>24.499</v>
+        <v>24.105</v>
       </c>
       <c r="AE5" t="n">
-        <v>11.014</v>
+        <v>10.858</v>
       </c>
       <c r="AF5" t="n">
-        <v>27.281</v>
+        <v>27.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.153</v>
+        <v>16.106</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.479</v>
+        <v>6.345</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.106</v>
+        <v>5.093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.735</v>
+        <v>18.752</v>
       </c>
       <c r="AK5" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1291.131</v>
+        <v>1288.274</v>
       </c>
       <c r="I6" t="n">
-        <v>0.731</v>
+        <v>0.7093</v>
       </c>
       <c r="J6" t="n">
-        <v>1359</v>
+        <v>1355.6</v>
       </c>
       <c r="K6" t="n">
         <v>301</v>
@@ -1142,70 +1142,70 @@
         <v>308</v>
       </c>
       <c r="Q6" t="n">
-        <v>106.438</v>
+        <v>105.687</v>
       </c>
       <c r="R6" t="n">
-        <v>109.113</v>
+        <v>109.605</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.675</v>
+        <v>-3.918</v>
       </c>
       <c r="T6" t="n">
-        <v>0.26018</v>
+        <v>0.25646</v>
       </c>
       <c r="U6" t="n">
-        <v>0.16095</v>
+        <v>0.15886</v>
       </c>
       <c r="V6" t="n">
-        <v>72.03</v>
+        <v>71.25</v>
       </c>
       <c r="W6" t="n">
-        <v>73.86</v>
+        <v>73.87</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5208</v>
+        <v>0.4966</v>
       </c>
       <c r="Y6" t="n">
-        <v>23.555</v>
+        <v>23.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>54.333</v>
+        <v>54.105</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.198</v>
+        <v>6.079</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.985</v>
+        <v>17.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.262</v>
+        <v>18.272</v>
       </c>
       <c r="AD6" t="n">
-        <v>24.482</v>
+        <v>24.47</v>
       </c>
       <c r="AE6" t="n">
-        <v>8.208</v>
+        <v>8.086</v>
       </c>
       <c r="AF6" t="n">
-        <v>22.912</v>
+        <v>23.061</v>
       </c>
       <c r="AG6" t="n">
-        <v>11.098</v>
+        <v>11.146</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.095</v>
+        <v>6.059</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.92</v>
+        <v>2.941</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18.546</v>
+        <v>18.423</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="7">
@@ -1826,22 +1826,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2256.045</v>
+        <v>2262.937</v>
       </c>
       <c r="I12" t="n">
-        <v>7.4143</v>
+        <v>7.0872</v>
       </c>
       <c r="J12" t="n">
-        <v>1747.3</v>
+        <v>1758.1</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
@@ -1862,70 +1862,70 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>121.007</v>
+        <v>121.14</v>
       </c>
       <c r="R12" t="n">
-        <v>95.60899999999999</v>
+        <v>96.664</v>
       </c>
       <c r="S12" t="n">
-        <v>25.399</v>
+        <v>24.476</v>
       </c>
       <c r="T12" t="n">
-        <v>0.29282</v>
+        <v>0.29415</v>
       </c>
       <c r="U12" t="n">
-        <v>0.14946</v>
+        <v>0.15097</v>
       </c>
       <c r="V12" t="n">
-        <v>86.45</v>
+        <v>86.33</v>
       </c>
       <c r="W12" t="n">
-        <v>68.2</v>
+        <v>68.73</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9381</v>
+        <v>0.9399</v>
       </c>
       <c r="Y12" t="n">
-        <v>30.672</v>
+        <v>30.738</v>
       </c>
       <c r="Z12" t="n">
-        <v>61.146</v>
+        <v>61.035</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.814</v>
+        <v>5.897</v>
       </c>
       <c r="AB12" t="n">
-        <v>16.434</v>
+        <v>16.421</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.292</v>
+        <v>18.954</v>
       </c>
       <c r="AD12" t="n">
-        <v>26.417</v>
+        <v>25.976</v>
       </c>
       <c r="AE12" t="n">
-        <v>12.142</v>
+        <v>12.082</v>
       </c>
       <c r="AF12" t="n">
-        <v>28.978</v>
+        <v>28.701</v>
       </c>
       <c r="AG12" t="n">
-        <v>17.052</v>
+        <v>17.197</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.942</v>
+        <v>8.007999999999999</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.328</v>
+        <v>4.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16.053</v>
+        <v>15.983</v>
       </c>
       <c r="AK12" t="n">
-        <v>15.6</v>
+        <v>14.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>12.2</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2306,22 +2306,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1949.969</v>
+        <v>1956.536</v>
       </c>
       <c r="I16" t="n">
-        <v>5.5428</v>
+        <v>5.3805</v>
       </c>
       <c r="J16" t="n">
-        <v>1728.7</v>
+        <v>1728.4</v>
       </c>
       <c r="K16" t="n">
         <v>18</v>
@@ -2342,70 +2342,70 @@
         <v>18</v>
       </c>
       <c r="Q16" t="n">
-        <v>122.846</v>
+        <v>122.826</v>
       </c>
       <c r="R16" t="n">
-        <v>108.882</v>
+        <v>109.162</v>
       </c>
       <c r="S16" t="n">
-        <v>13.964</v>
+        <v>13.664</v>
       </c>
       <c r="T16" t="n">
-        <v>0.30094</v>
+        <v>0.30257</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1205</v>
+        <v>0.11957</v>
       </c>
       <c r="V16" t="n">
-        <v>90.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>80.01000000000001</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7444</v>
+        <v>0.7523</v>
       </c>
       <c r="Y16" t="n">
-        <v>32.297</v>
+        <v>32.119</v>
       </c>
       <c r="Z16" t="n">
-        <v>64.253</v>
+        <v>64.217</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.192</v>
+        <v>8.186</v>
       </c>
       <c r="AB16" t="n">
-        <v>21.367</v>
+        <v>21.403</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.418</v>
+        <v>17.474</v>
       </c>
       <c r="AD16" t="n">
-        <v>23.406</v>
+        <v>23.363</v>
       </c>
       <c r="AE16" t="n">
-        <v>9.933</v>
+        <v>10.027</v>
       </c>
       <c r="AF16" t="n">
-        <v>23.147</v>
+        <v>23.164</v>
       </c>
       <c r="AG16" t="n">
-        <v>17.025</v>
+        <v>16.902</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.329</v>
+        <v>7.31</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.192</v>
+        <v>5.266</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17.285</v>
+        <v>17.248</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="17">
@@ -5786,22 +5786,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1443.185</v>
+        <v>1452.63</v>
       </c>
       <c r="I45" t="n">
-        <v>1.3825</v>
+        <v>1.4072</v>
       </c>
       <c r="J45" t="n">
-        <v>1498.1</v>
+        <v>1502.2</v>
       </c>
       <c r="K45" t="n">
         <v>191</v>
@@ -5822,70 +5822,70 @@
         <v>183</v>
       </c>
       <c r="Q45" t="n">
-        <v>112.43</v>
+        <v>112.833</v>
       </c>
       <c r="R45" t="n">
-        <v>113.198</v>
+        <v>113.525</v>
       </c>
       <c r="S45" t="n">
-        <v>-0.768</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="T45" t="n">
-        <v>0.29948</v>
+        <v>0.29997</v>
       </c>
       <c r="U45" t="n">
-        <v>0.16971</v>
+        <v>0.16626</v>
       </c>
       <c r="V45" t="n">
-        <v>72.98</v>
+        <v>73.39</v>
       </c>
       <c r="W45" t="n">
-        <v>73.61</v>
+        <v>73.95</v>
       </c>
       <c r="X45" t="n">
-        <v>0.4899</v>
+        <v>0.5054</v>
       </c>
       <c r="Y45" t="n">
-        <v>24.933</v>
+        <v>25.261</v>
       </c>
       <c r="Z45" t="n">
-        <v>54.852</v>
+        <v>55.179</v>
       </c>
       <c r="AA45" t="n">
-        <v>8.715999999999999</v>
+        <v>8.483000000000001</v>
       </c>
       <c r="AB45" t="n">
-        <v>24.794</v>
+        <v>24.472</v>
       </c>
       <c r="AC45" t="n">
-        <v>14.397</v>
+        <v>14.173</v>
       </c>
       <c r="AD45" t="n">
-        <v>19.861</v>
+        <v>19.751</v>
       </c>
       <c r="AE45" t="n">
-        <v>9.643000000000001</v>
+        <v>9.598000000000001</v>
       </c>
       <c r="AF45" t="n">
-        <v>22.272</v>
+        <v>22.144</v>
       </c>
       <c r="AG45" t="n">
-        <v>12.812</v>
+        <v>13.242</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.423</v>
+        <v>4.516</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.533</v>
+        <v>3.536</v>
       </c>
       <c r="AJ45" t="n">
-        <v>17.284</v>
+        <v>17.101</v>
       </c>
       <c r="AK45" t="n">
-        <v>-3</v>
+        <v>-2.2</v>
       </c>
       <c r="AL45" t="n">
-        <v>-5</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="46">
@@ -6386,22 +6386,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G50" t="b">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1863.555</v>
+        <v>1859.484</v>
       </c>
       <c r="I50" t="n">
-        <v>2.7155</v>
+        <v>2.557</v>
       </c>
       <c r="J50" t="n">
-        <v>1655.1</v>
+        <v>1672.9</v>
       </c>
       <c r="K50" t="n">
         <v>38</v>
@@ -6422,70 +6422,70 @@
         <v>36</v>
       </c>
       <c r="Q50" t="n">
-        <v>113.286</v>
+        <v>112.594</v>
       </c>
       <c r="R50" t="n">
-        <v>101.285</v>
+        <v>101.684</v>
       </c>
       <c r="S50" t="n">
-        <v>12.001</v>
+        <v>10.91</v>
       </c>
       <c r="T50" t="n">
-        <v>0.25415</v>
+        <v>0.25542</v>
       </c>
       <c r="U50" t="n">
-        <v>0.13778</v>
+        <v>0.13604</v>
       </c>
       <c r="V50" t="n">
-        <v>74.59999999999999</v>
+        <v>74.02</v>
       </c>
       <c r="W50" t="n">
-        <v>66.67</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="X50" t="n">
-        <v>0.73</v>
+        <v>0.6993</v>
       </c>
       <c r="Y50" t="n">
-        <v>25.73</v>
+        <v>25.401</v>
       </c>
       <c r="Z50" t="n">
-        <v>56.32</v>
+        <v>56.224</v>
       </c>
       <c r="AA50" t="n">
-        <v>8.33</v>
+        <v>8.253</v>
       </c>
       <c r="AB50" t="n">
-        <v>24.42</v>
+        <v>24.388</v>
       </c>
       <c r="AC50" t="n">
-        <v>14.77</v>
+        <v>14.941</v>
       </c>
       <c r="AD50" t="n">
-        <v>20.54</v>
+        <v>20.669</v>
       </c>
       <c r="AE50" t="n">
-        <v>8.630000000000001</v>
+        <v>8.583</v>
       </c>
       <c r="AF50" t="n">
-        <v>24.12</v>
+        <v>23.895</v>
       </c>
       <c r="AG50" t="n">
-        <v>12.99</v>
+        <v>12.855</v>
       </c>
       <c r="AH50" t="n">
-        <v>6.18</v>
+        <v>6.242</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.86</v>
+        <v>2.854</v>
       </c>
       <c r="AJ50" t="n">
-        <v>16.08</v>
+        <v>16.097</v>
       </c>
       <c r="AK50" t="n">
-        <v>2.8</v>
+        <v>-0.6</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="51">
@@ -7346,22 +7346,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F58" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>2066.086</v>
+        <v>2067.868</v>
       </c>
       <c r="I58" t="n">
-        <v>8.2806</v>
+        <v>7.6929</v>
       </c>
       <c r="J58" t="n">
-        <v>1659.9</v>
+        <v>1657.6</v>
       </c>
       <c r="K58" t="n">
         <v>11</v>
@@ -7382,70 +7382,70 @@
         <v>9</v>
       </c>
       <c r="Q58" t="n">
-        <v>117.742</v>
+        <v>117.246</v>
       </c>
       <c r="R58" t="n">
-        <v>97.67400000000001</v>
+        <v>97.10299999999999</v>
       </c>
       <c r="S58" t="n">
-        <v>20.068</v>
+        <v>20.143</v>
       </c>
       <c r="T58" t="n">
-        <v>0.2928</v>
+        <v>0.2963</v>
       </c>
       <c r="U58" t="n">
-        <v>0.15486</v>
+        <v>0.1567</v>
       </c>
       <c r="V58" t="n">
-        <v>78.78</v>
+        <v>78.16</v>
       </c>
       <c r="W58" t="n">
-        <v>65.37</v>
+        <v>64.77</v>
       </c>
       <c r="X58" t="n">
-        <v>0.8763</v>
+        <v>0.88</v>
       </c>
       <c r="Y58" t="n">
-        <v>28.663</v>
+        <v>28.57</v>
       </c>
       <c r="Z58" t="n">
-        <v>58.743</v>
+        <v>58.73</v>
       </c>
       <c r="AA58" t="n">
-        <v>8.538</v>
+        <v>8.48</v>
       </c>
       <c r="AB58" t="n">
-        <v>23.839</v>
+        <v>23.8</v>
       </c>
       <c r="AC58" t="n">
-        <v>12.917</v>
+        <v>12.54</v>
       </c>
       <c r="AD58" t="n">
-        <v>18.07</v>
+        <v>17.56</v>
       </c>
       <c r="AE58" t="n">
-        <v>10.145</v>
+        <v>10.24</v>
       </c>
       <c r="AF58" t="n">
-        <v>24.167</v>
+        <v>24</v>
       </c>
       <c r="AG58" t="n">
-        <v>18.526</v>
+        <v>18.63</v>
       </c>
       <c r="AH58" t="n">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="AI58" t="n">
-        <v>5.34</v>
+        <v>5.37</v>
       </c>
       <c r="AJ58" t="n">
-        <v>18.238</v>
+        <v>18.13</v>
       </c>
       <c r="AK58" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="AL58" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="59">
@@ -7946,22 +7946,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F63" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G63" t="b">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>1399.031</v>
+        <v>1395.89</v>
       </c>
       <c r="I63" t="n">
-        <v>2.9262</v>
+        <v>2.9449</v>
       </c>
       <c r="J63" t="n">
-        <v>1479.9</v>
+        <v>1482.1</v>
       </c>
       <c r="K63" t="n">
         <v>169</v>
@@ -7982,70 +7982,70 @@
         <v>180</v>
       </c>
       <c r="Q63" t="n">
-        <v>107.909</v>
+        <v>107.122</v>
       </c>
       <c r="R63" t="n">
-        <v>109.336</v>
+        <v>109.476</v>
       </c>
       <c r="S63" t="n">
-        <v>-1.426</v>
+        <v>-2.353</v>
       </c>
       <c r="T63" t="n">
-        <v>0.25688</v>
+        <v>0.2559</v>
       </c>
       <c r="U63" t="n">
-        <v>0.1476</v>
+        <v>0.14661</v>
       </c>
       <c r="V63" t="n">
-        <v>80.88</v>
+        <v>80.16</v>
       </c>
       <c r="W63" t="n">
-        <v>82.2</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="X63" t="n">
-        <v>0.5208</v>
+        <v>0.4955</v>
       </c>
       <c r="Y63" t="n">
-        <v>27.283</v>
+        <v>27.181</v>
       </c>
       <c r="Z63" t="n">
-        <v>61.75</v>
+        <v>61.894</v>
       </c>
       <c r="AA63" t="n">
-        <v>9.047000000000001</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="AB63" t="n">
-        <v>26.433</v>
+        <v>26.735</v>
       </c>
       <c r="AC63" t="n">
-        <v>17.268</v>
+        <v>16.662</v>
       </c>
       <c r="AD63" t="n">
-        <v>24.044</v>
+        <v>23.285</v>
       </c>
       <c r="AE63" t="n">
-        <v>8.272</v>
+        <v>8.137</v>
       </c>
       <c r="AF63" t="n">
-        <v>24.274</v>
+        <v>23.964</v>
       </c>
       <c r="AG63" t="n">
-        <v>14.976</v>
+        <v>15.022</v>
       </c>
       <c r="AH63" t="n">
-        <v>7.914</v>
+        <v>7.907</v>
       </c>
       <c r="AI63" t="n">
-        <v>2.757</v>
+        <v>2.823</v>
       </c>
       <c r="AJ63" t="n">
-        <v>18.956</v>
+        <v>18.978</v>
       </c>
       <c r="AK63" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="AL63" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -8066,22 +8066,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F64" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G64" t="b">
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>1515.972</v>
+        <v>1510.213</v>
       </c>
       <c r="I64" t="n">
-        <v>1.7017</v>
+        <v>1.7028</v>
       </c>
       <c r="J64" t="n">
-        <v>1458.3</v>
+        <v>1463.1</v>
       </c>
       <c r="K64" t="n">
         <v>176</v>
@@ -8102,70 +8102,70 @@
         <v>190</v>
       </c>
       <c r="Q64" t="n">
-        <v>105.241</v>
+        <v>105.446</v>
       </c>
       <c r="R64" t="n">
-        <v>105.091</v>
+        <v>106.24</v>
       </c>
       <c r="S64" t="n">
-        <v>0.15</v>
+        <v>-0.795</v>
       </c>
       <c r="T64" t="n">
-        <v>0.27403</v>
+        <v>0.2789</v>
       </c>
       <c r="U64" t="n">
-        <v>0.17019</v>
+        <v>0.16829</v>
       </c>
       <c r="V64" t="n">
-        <v>80.7</v>
+        <v>80.61</v>
       </c>
       <c r="W64" t="n">
-        <v>80.84999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="X64" t="n">
-        <v>0.584</v>
+        <v>0.5583</v>
       </c>
       <c r="Y64" t="n">
-        <v>29.392</v>
+        <v>29.488</v>
       </c>
       <c r="Z64" t="n">
-        <v>64.16800000000001</v>
+        <v>64.34</v>
       </c>
       <c r="AA64" t="n">
-        <v>6.944</v>
+        <v>7.015</v>
       </c>
       <c r="AB64" t="n">
-        <v>21.536</v>
+        <v>21.619</v>
       </c>
       <c r="AC64" t="n">
-        <v>14.976</v>
+        <v>14.615</v>
       </c>
       <c r="AD64" t="n">
-        <v>22.392</v>
+        <v>21.896</v>
       </c>
       <c r="AE64" t="n">
-        <v>10.264</v>
+        <v>10.279</v>
       </c>
       <c r="AF64" t="n">
-        <v>26.952</v>
+        <v>26.515</v>
       </c>
       <c r="AG64" t="n">
-        <v>16.76</v>
+        <v>16.675</v>
       </c>
       <c r="AH64" t="n">
-        <v>6.6</v>
+        <v>6.589</v>
       </c>
       <c r="AI64" t="n">
-        <v>2.864</v>
+        <v>2.806</v>
       </c>
       <c r="AJ64" t="n">
-        <v>18.24</v>
+        <v>18.21</v>
       </c>
       <c r="AK64" t="n">
-        <v>-2.6</v>
+        <v>-5.4</v>
       </c>
       <c r="AL64" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="65">
@@ -8426,22 +8426,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F67" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G67" t="b">
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1533.884</v>
+        <v>1527.507</v>
       </c>
       <c r="I67" t="n">
-        <v>-2.5567</v>
+        <v>-2.3908</v>
       </c>
       <c r="J67" t="n">
-        <v>1535.2</v>
+        <v>1539.4</v>
       </c>
       <c r="K67" t="n">
         <v>107</v>
@@ -8462,70 +8462,70 @@
         <v>106</v>
       </c>
       <c r="Q67" t="n">
-        <v>108.405</v>
+        <v>107.992</v>
       </c>
       <c r="R67" t="n">
-        <v>104.661</v>
+        <v>105.223</v>
       </c>
       <c r="S67" t="n">
-        <v>3.744</v>
+        <v>2.769</v>
       </c>
       <c r="T67" t="n">
-        <v>0.28414</v>
+        <v>0.2874</v>
       </c>
       <c r="U67" t="n">
-        <v>0.15479</v>
+        <v>0.15602</v>
       </c>
       <c r="V67" t="n">
-        <v>69.88</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="W67" t="n">
-        <v>67.89</v>
+        <v>68.05</v>
       </c>
       <c r="X67" t="n">
-        <v>0.6034</v>
+        <v>0.576</v>
       </c>
       <c r="Y67" t="n">
-        <v>24.875</v>
+        <v>24.824</v>
       </c>
       <c r="Z67" t="n">
-        <v>55.43</v>
+        <v>55.456</v>
       </c>
       <c r="AA67" t="n">
-        <v>8.611000000000001</v>
+        <v>8.608000000000001</v>
       </c>
       <c r="AB67" t="n">
-        <v>24.264</v>
+        <v>24.456</v>
       </c>
       <c r="AC67" t="n">
-        <v>11.522</v>
+        <v>11.2</v>
       </c>
       <c r="AD67" t="n">
-        <v>18.019</v>
+        <v>17.568</v>
       </c>
       <c r="AE67" t="n">
-        <v>8.802</v>
+        <v>8.848000000000001</v>
       </c>
       <c r="AF67" t="n">
-        <v>21.754</v>
+        <v>21.552</v>
       </c>
       <c r="AG67" t="n">
-        <v>13.19</v>
+        <v>13.232</v>
       </c>
       <c r="AH67" t="n">
-        <v>6.422</v>
+        <v>6.344</v>
       </c>
       <c r="AI67" t="n">
-        <v>4.085</v>
+        <v>4.032</v>
       </c>
       <c r="AJ67" t="n">
-        <v>16.809</v>
+        <v>16.88</v>
       </c>
       <c r="AK67" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="AL67" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -8546,22 +8546,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1663.379</v>
+        <v>1669.741</v>
       </c>
       <c r="I68" t="n">
-        <v>-2.5466</v>
+        <v>-2.3756</v>
       </c>
       <c r="J68" t="n">
-        <v>1562.3</v>
+        <v>1559.7</v>
       </c>
       <c r="K68" t="n">
         <v>79</v>
@@ -8582,70 +8582,70 @@
         <v>75</v>
       </c>
       <c r="Q68" t="n">
-        <v>109.989</v>
+        <v>109.857</v>
       </c>
       <c r="R68" t="n">
-        <v>102.288</v>
+        <v>101.927</v>
       </c>
       <c r="S68" t="n">
-        <v>7.701</v>
+        <v>7.93</v>
       </c>
       <c r="T68" t="n">
-        <v>0.25309</v>
+        <v>0.25593</v>
       </c>
       <c r="U68" t="n">
-        <v>0.16863</v>
+        <v>0.17025</v>
       </c>
       <c r="V68" t="n">
-        <v>74.92</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="W68" t="n">
-        <v>70.09999999999999</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="X68" t="n">
-        <v>0.6682</v>
+        <v>0.6914</v>
       </c>
       <c r="Y68" t="n">
-        <v>24.3</v>
+        <v>24.017</v>
       </c>
       <c r="Z68" t="n">
-        <v>53.632</v>
+        <v>53.543</v>
       </c>
       <c r="AA68" t="n">
-        <v>7.468</v>
+        <v>7.624</v>
       </c>
       <c r="AB68" t="n">
-        <v>22.159</v>
+        <v>22.241</v>
       </c>
       <c r="AC68" t="n">
-        <v>18.85</v>
+        <v>19.13</v>
       </c>
       <c r="AD68" t="n">
-        <v>25.15</v>
+        <v>25.408</v>
       </c>
       <c r="AE68" t="n">
-        <v>7.855</v>
+        <v>8.02</v>
       </c>
       <c r="AF68" t="n">
-        <v>22.695</v>
+        <v>22.778</v>
       </c>
       <c r="AG68" t="n">
-        <v>14.309</v>
+        <v>14.296</v>
       </c>
       <c r="AH68" t="n">
-        <v>8.486000000000001</v>
+        <v>8.481</v>
       </c>
       <c r="AI68" t="n">
-        <v>4.082</v>
+        <v>4.093</v>
       </c>
       <c r="AJ68" t="n">
-        <v>16.532</v>
+        <v>16.642</v>
       </c>
       <c r="AK68" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AL68" t="n">
-        <v>-0.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="69">
@@ -8786,22 +8786,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F70" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G70" t="b">
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>1258.638</v>
+        <v>1251.618</v>
       </c>
       <c r="I70" t="n">
-        <v>-3.1046</v>
+        <v>-2.9934</v>
       </c>
       <c r="J70" t="n">
-        <v>1354.6</v>
+        <v>1352.4</v>
       </c>
       <c r="K70" t="n">
         <v>362</v>
@@ -8822,70 +8822,70 @@
         <v>362</v>
       </c>
       <c r="Q70" t="n">
-        <v>90.703</v>
+        <v>90.724</v>
       </c>
       <c r="R70" t="n">
-        <v>108.133</v>
+        <v>108.109</v>
       </c>
       <c r="S70" t="n">
-        <v>-17.429</v>
+        <v>-17.385</v>
       </c>
       <c r="T70" t="n">
-        <v>0.30644</v>
+        <v>0.3078</v>
       </c>
       <c r="U70" t="n">
-        <v>0.18209</v>
+        <v>0.18675</v>
       </c>
       <c r="V70" t="n">
-        <v>60.1</v>
+        <v>59.59</v>
       </c>
       <c r="W70" t="n">
-        <v>71.86</v>
+        <v>71.27</v>
       </c>
       <c r="X70" t="n">
-        <v>0.202</v>
+        <v>0.1832</v>
       </c>
       <c r="Y70" t="n">
-        <v>20.874</v>
+        <v>20.985</v>
       </c>
       <c r="Z70" t="n">
-        <v>54.844</v>
+        <v>54.495</v>
       </c>
       <c r="AA70" t="n">
-        <v>4.558</v>
+        <v>4.549</v>
       </c>
       <c r="AB70" t="n">
-        <v>16.288</v>
+        <v>16.172</v>
       </c>
       <c r="AC70" t="n">
-        <v>13.548</v>
+        <v>12.89</v>
       </c>
       <c r="AD70" t="n">
-        <v>19.432</v>
+        <v>18.696</v>
       </c>
       <c r="AE70" t="n">
-        <v>8.960000000000001</v>
+        <v>9.022</v>
       </c>
       <c r="AF70" t="n">
-        <v>19.732</v>
+        <v>19.755</v>
       </c>
       <c r="AG70" t="n">
-        <v>9.596</v>
+        <v>9.634</v>
       </c>
       <c r="AH70" t="n">
-        <v>7.674</v>
+        <v>7.458</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.758</v>
+        <v>1.839</v>
       </c>
       <c r="AJ70" t="n">
-        <v>17.822</v>
+        <v>17.674</v>
       </c>
       <c r="AK70" t="n">
-        <v>-4.8</v>
+        <v>-3.2</v>
       </c>
       <c r="AL70" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10.6</v>
       </c>
     </row>
     <row r="71">
@@ -9506,22 +9506,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F76" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>2185.134</v>
+        <v>2189.206</v>
       </c>
       <c r="I76" t="n">
-        <v>3.7089</v>
+        <v>3.7126</v>
       </c>
       <c r="J76" t="n">
-        <v>1695.7</v>
+        <v>1703.5</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
@@ -9542,70 +9542,70 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>123.041</v>
+        <v>122.893</v>
       </c>
       <c r="R76" t="n">
-        <v>94.116</v>
+        <v>94.026</v>
       </c>
       <c r="S76" t="n">
-        <v>28.925</v>
+        <v>28.866</v>
       </c>
       <c r="T76" t="n">
-        <v>0.2948</v>
+        <v>0.28942</v>
       </c>
       <c r="U76" t="n">
-        <v>0.15466</v>
+        <v>0.1548</v>
       </c>
       <c r="V76" t="n">
-        <v>82.81</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="W76" t="n">
-        <v>63.2</v>
+        <v>62.92</v>
       </c>
       <c r="X76" t="n">
-        <v>0.9383</v>
+        <v>0.9401</v>
       </c>
       <c r="Y76" t="n">
-        <v>28.895</v>
+        <v>28.66</v>
       </c>
       <c r="Z76" t="n">
-        <v>58.539</v>
+        <v>58.116</v>
       </c>
       <c r="AA76" t="n">
-        <v>9.135999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AB76" t="n">
-        <v>26.101</v>
+        <v>25.917</v>
       </c>
       <c r="AC76" t="n">
-        <v>15.882</v>
+        <v>15.993</v>
       </c>
       <c r="AD76" t="n">
-        <v>22.136</v>
+        <v>22.12</v>
       </c>
       <c r="AE76" t="n">
-        <v>11.478</v>
+        <v>11.246</v>
       </c>
       <c r="AF76" t="n">
-        <v>27.024</v>
+        <v>27.268</v>
       </c>
       <c r="AG76" t="n">
-        <v>17.247</v>
+        <v>16.906</v>
       </c>
       <c r="AH76" t="n">
-        <v>7.957</v>
+        <v>7.803</v>
       </c>
       <c r="AI76" t="n">
-        <v>3.414</v>
+        <v>3.306</v>
       </c>
       <c r="AJ76" t="n">
-        <v>15.673</v>
+        <v>15.837</v>
       </c>
       <c r="AK76" t="n">
-        <v>23</v>
+        <v>16.6</v>
       </c>
       <c r="AL76" t="n">
-        <v>18.3</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="77">
@@ -9626,22 +9626,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G77" t="b">
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>1489.773</v>
+        <v>1486.154</v>
       </c>
       <c r="I77" t="n">
-        <v>-2.0712</v>
+        <v>-1.8538</v>
       </c>
       <c r="J77" t="n">
-        <v>1539.9</v>
+        <v>1548</v>
       </c>
       <c r="K77" t="n">
         <v>133</v>
@@ -9662,70 +9662,70 @@
         <v>140</v>
       </c>
       <c r="Q77" t="n">
-        <v>109.054</v>
+        <v>108.657</v>
       </c>
       <c r="R77" t="n">
-        <v>107.321</v>
+        <v>107.403</v>
       </c>
       <c r="S77" t="n">
-        <v>1.733</v>
+        <v>1.254</v>
       </c>
       <c r="T77" t="n">
-        <v>0.29378</v>
+        <v>0.29298</v>
       </c>
       <c r="U77" t="n">
-        <v>0.16761</v>
+        <v>0.17172</v>
       </c>
       <c r="V77" t="n">
-        <v>77.16</v>
+        <v>76.8</v>
       </c>
       <c r="W77" t="n">
-        <v>75.88</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="X77" t="n">
-        <v>0.5382</v>
+        <v>0.5111</v>
       </c>
       <c r="Y77" t="n">
-        <v>26.232</v>
+        <v>26.172</v>
       </c>
       <c r="Z77" t="n">
-        <v>58.372</v>
+        <v>58.194</v>
       </c>
       <c r="AA77" t="n">
-        <v>8.550000000000001</v>
+        <v>8.542999999999999</v>
       </c>
       <c r="AB77" t="n">
-        <v>25.847</v>
+        <v>25.831</v>
       </c>
       <c r="AC77" t="n">
-        <v>16.144</v>
+        <v>15.91</v>
       </c>
       <c r="AD77" t="n">
-        <v>22.691</v>
+        <v>22.222</v>
       </c>
       <c r="AE77" t="n">
-        <v>9.535</v>
+        <v>9.489000000000001</v>
       </c>
       <c r="AF77" t="n">
-        <v>22.703</v>
+        <v>22.713</v>
       </c>
       <c r="AG77" t="n">
-        <v>14.552</v>
+        <v>14.658</v>
       </c>
       <c r="AH77" t="n">
-        <v>7.561</v>
+        <v>7.585</v>
       </c>
       <c r="AI77" t="n">
-        <v>3.01</v>
+        <v>3.042</v>
       </c>
       <c r="AJ77" t="n">
-        <v>19.706</v>
+        <v>19.818</v>
       </c>
       <c r="AK77" t="n">
-        <v>-6</v>
+        <v>-4.8</v>
       </c>
       <c r="AL77" t="n">
-        <v>-2.8</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="78">
@@ -11306,22 +11306,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F91" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G91" t="b">
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>2014.754</v>
+        <v>2024.856</v>
       </c>
       <c r="I91" t="n">
-        <v>2.8716</v>
+        <v>3.1754</v>
       </c>
       <c r="J91" t="n">
-        <v>1709.6</v>
+        <v>1715.4</v>
       </c>
       <c r="K91" t="n">
         <v>4</v>
@@ -11342,70 +11342,70 @@
         <v>4</v>
       </c>
       <c r="Q91" t="n">
-        <v>120.947</v>
+        <v>120.018</v>
       </c>
       <c r="R91" t="n">
-        <v>99.024</v>
+        <v>98.413</v>
       </c>
       <c r="S91" t="n">
-        <v>21.924</v>
+        <v>21.606</v>
       </c>
       <c r="T91" t="n">
-        <v>0.33287</v>
+        <v>0.33391</v>
       </c>
       <c r="U91" t="n">
-        <v>0.15517</v>
+        <v>0.15921</v>
       </c>
       <c r="V91" t="n">
-        <v>87.67</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="W91" t="n">
-        <v>71.73999999999999</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="X91" t="n">
-        <v>0.8087</v>
+        <v>0.8145</v>
       </c>
       <c r="Y91" t="n">
-        <v>31.188</v>
+        <v>30.841</v>
       </c>
       <c r="Z91" t="n">
-        <v>64.794</v>
+        <v>64.554</v>
       </c>
       <c r="AA91" t="n">
-        <v>7.586</v>
+        <v>7.39</v>
       </c>
       <c r="AB91" t="n">
-        <v>24.186</v>
+        <v>24.081</v>
       </c>
       <c r="AC91" t="n">
-        <v>17.704</v>
+        <v>17.941</v>
       </c>
       <c r="AD91" t="n">
-        <v>25.049</v>
+        <v>25.302</v>
       </c>
       <c r="AE91" t="n">
-        <v>14.606</v>
+        <v>14.754</v>
       </c>
       <c r="AF91" t="n">
-        <v>28.594</v>
+        <v>28.754</v>
       </c>
       <c r="AG91" t="n">
-        <v>16.971</v>
+        <v>16.688</v>
       </c>
       <c r="AH91" t="n">
-        <v>6.681</v>
+        <v>6.774</v>
       </c>
       <c r="AI91" t="n">
-        <v>5.107</v>
+        <v>5.134</v>
       </c>
       <c r="AJ91" t="n">
-        <v>17.69</v>
+        <v>17.763</v>
       </c>
       <c r="AK91" t="n">
-        <v>21.4</v>
+        <v>19.2</v>
       </c>
       <c r="AL91" t="n">
-        <v>19.2</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="92">
@@ -11426,22 +11426,22 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F92" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G92" t="b">
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1297.568</v>
+        <v>1295.524</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1581</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>1376.1</v>
+        <v>1376.6</v>
       </c>
       <c r="K92" t="n">
         <v>315</v>
@@ -11462,70 +11462,70 @@
         <v>315</v>
       </c>
       <c r="Q92" t="n">
-        <v>99.547</v>
+        <v>99.462</v>
       </c>
       <c r="R92" t="n">
-        <v>105.787</v>
+        <v>105.779</v>
       </c>
       <c r="S92" t="n">
-        <v>-6.24</v>
+        <v>-6.318</v>
       </c>
       <c r="T92" t="n">
-        <v>0.30268</v>
+        <v>0.30416</v>
       </c>
       <c r="U92" t="n">
-        <v>0.20622</v>
+        <v>0.20442</v>
       </c>
       <c r="V92" t="n">
         <v>70</v>
       </c>
       <c r="W92" t="n">
-        <v>75.02</v>
+        <v>75.05</v>
       </c>
       <c r="X92" t="n">
-        <v>0.4686</v>
+        <v>0.4449</v>
       </c>
       <c r="Y92" t="n">
-        <v>24.213</v>
+        <v>24.497</v>
       </c>
       <c r="Z92" t="n">
-        <v>56.395</v>
+        <v>56.842</v>
       </c>
       <c r="AA92" t="n">
-        <v>6.921</v>
+        <v>6.89</v>
       </c>
       <c r="AB92" t="n">
-        <v>21.362</v>
+        <v>21.384</v>
       </c>
       <c r="AC92" t="n">
-        <v>14.654</v>
+        <v>14.241</v>
       </c>
       <c r="AD92" t="n">
-        <v>21.019</v>
+        <v>20.576</v>
       </c>
       <c r="AE92" t="n">
-        <v>9.667</v>
+        <v>9.749000000000001</v>
       </c>
       <c r="AF92" t="n">
-        <v>21.831</v>
+        <v>21.871</v>
       </c>
       <c r="AG92" t="n">
-        <v>12.713</v>
+        <v>12.984</v>
       </c>
       <c r="AH92" t="n">
-        <v>8.170999999999999</v>
+        <v>8.311</v>
       </c>
       <c r="AI92" t="n">
-        <v>3.008</v>
+        <v>3.167</v>
       </c>
       <c r="AJ92" t="n">
-        <v>18.047</v>
+        <v>17.943</v>
       </c>
       <c r="AK92" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AL92" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="93">
@@ -12146,22 +12146,22 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F98" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G98" t="b">
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>1529.53</v>
+        <v>1525.82</v>
       </c>
       <c r="I98" t="n">
-        <v>-3.9222</v>
+        <v>-3.7537</v>
       </c>
       <c r="J98" t="n">
-        <v>1530.4</v>
+        <v>1543.4</v>
       </c>
       <c r="K98" t="n">
         <v>83</v>
@@ -12182,70 +12182,70 @@
         <v>90</v>
       </c>
       <c r="Q98" t="n">
-        <v>114.99</v>
+        <v>114.986</v>
       </c>
       <c r="R98" t="n">
-        <v>104.966</v>
+        <v>105.766</v>
       </c>
       <c r="S98" t="n">
-        <v>10.024</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="T98" t="n">
-        <v>0.31867</v>
+        <v>0.32427</v>
       </c>
       <c r="U98" t="n">
-        <v>0.17418</v>
+        <v>0.17282</v>
       </c>
       <c r="V98" t="n">
-        <v>81.40000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="W98" t="n">
-        <v>74.19</v>
+        <v>74.95</v>
       </c>
       <c r="X98" t="n">
-        <v>0.5545</v>
+        <v>0.5245</v>
       </c>
       <c r="Y98" t="n">
-        <v>28.059</v>
+        <v>28.123</v>
       </c>
       <c r="Z98" t="n">
-        <v>60.086</v>
+        <v>60.651</v>
       </c>
       <c r="AA98" t="n">
-        <v>9.723000000000001</v>
+        <v>9.914</v>
       </c>
       <c r="AB98" t="n">
-        <v>27.682</v>
+        <v>28.262</v>
       </c>
       <c r="AC98" t="n">
-        <v>15.377</v>
+        <v>15.302</v>
       </c>
       <c r="AD98" t="n">
-        <v>21.314</v>
+        <v>21.327</v>
       </c>
       <c r="AE98" t="n">
-        <v>11.114</v>
+        <v>11.433</v>
       </c>
       <c r="AF98" t="n">
-        <v>23.373</v>
+        <v>23.488</v>
       </c>
       <c r="AG98" t="n">
-        <v>15.25</v>
+        <v>15.309</v>
       </c>
       <c r="AH98" t="n">
-        <v>7.55</v>
+        <v>7.407</v>
       </c>
       <c r="AI98" t="n">
-        <v>3.214</v>
+        <v>3.203</v>
       </c>
       <c r="AJ98" t="n">
-        <v>18.045</v>
+        <v>18.161</v>
       </c>
       <c r="AK98" t="n">
-        <v>6.4</v>
+        <v>-0.4</v>
       </c>
       <c r="AL98" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="99">
@@ -12626,22 +12626,22 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F102" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G102" t="b">
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>1586.19</v>
+        <v>1584.408</v>
       </c>
       <c r="I102" t="n">
-        <v>-4.5368</v>
+        <v>-4.2375</v>
       </c>
       <c r="J102" t="n">
-        <v>1646</v>
+        <v>1660.1</v>
       </c>
       <c r="K102" t="n">
         <v>87</v>
@@ -12662,70 +12662,70 @@
         <v>95</v>
       </c>
       <c r="Q102" t="n">
-        <v>109.929</v>
+        <v>109.001</v>
       </c>
       <c r="R102" t="n">
-        <v>108.045</v>
+        <v>108.358</v>
       </c>
       <c r="S102" t="n">
-        <v>1.884</v>
+        <v>0.643</v>
       </c>
       <c r="T102" t="n">
-        <v>0.30693</v>
+        <v>0.30796</v>
       </c>
       <c r="U102" t="n">
-        <v>0.14631</v>
+        <v>0.14829</v>
       </c>
       <c r="V102" t="n">
-        <v>74.33</v>
+        <v>73.44</v>
       </c>
       <c r="W102" t="n">
-        <v>73.01000000000001</v>
+        <v>72.87</v>
       </c>
       <c r="X102" t="n">
-        <v>0.4892</v>
+        <v>0.4669</v>
       </c>
       <c r="Y102" t="n">
-        <v>25.464</v>
+        <v>25.245</v>
       </c>
       <c r="Z102" t="n">
-        <v>58.416</v>
+        <v>58.083</v>
       </c>
       <c r="AA102" t="n">
-        <v>6.79</v>
+        <v>6.611</v>
       </c>
       <c r="AB102" t="n">
-        <v>21.097</v>
+        <v>20.844</v>
       </c>
       <c r="AC102" t="n">
-        <v>15.868</v>
+        <v>15.727</v>
       </c>
       <c r="AD102" t="n">
-        <v>21.512</v>
+        <v>21.332</v>
       </c>
       <c r="AE102" t="n">
-        <v>10.133</v>
+        <v>10.109</v>
       </c>
       <c r="AF102" t="n">
-        <v>22.659</v>
+        <v>22.507</v>
       </c>
       <c r="AG102" t="n">
-        <v>14.91</v>
+        <v>14.727</v>
       </c>
       <c r="AH102" t="n">
-        <v>6.7</v>
+        <v>6.597</v>
       </c>
       <c r="AI102" t="n">
-        <v>3.644</v>
+        <v>3.568</v>
       </c>
       <c r="AJ102" t="n">
-        <v>18.056</v>
+        <v>17.976</v>
       </c>
       <c r="AK102" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="AL102" t="n">
-        <v>-2.3</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="103">
@@ -13706,22 +13706,22 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F111" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G111" t="b">
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>1535.663</v>
+        <v>1538.805</v>
       </c>
       <c r="I111" t="n">
-        <v>3.2322</v>
+        <v>3.0942</v>
       </c>
       <c r="J111" t="n">
-        <v>1444.6</v>
+        <v>1444.2</v>
       </c>
       <c r="K111" t="n">
         <v>115</v>
@@ -13742,70 +13742,70 @@
         <v>112</v>
       </c>
       <c r="Q111" t="n">
-        <v>108.42</v>
+        <v>108.455</v>
       </c>
       <c r="R111" t="n">
-        <v>97.5</v>
+        <v>96.833</v>
       </c>
       <c r="S111" t="n">
-        <v>10.92</v>
+        <v>11.621</v>
       </c>
       <c r="T111" t="n">
-        <v>0.25241</v>
+        <v>0.25546</v>
       </c>
       <c r="U111" t="n">
-        <v>0.18128</v>
+        <v>0.18434</v>
       </c>
       <c r="V111" t="n">
         <v>78.98999999999999</v>
       </c>
       <c r="W111" t="n">
-        <v>70.95</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="X111" t="n">
-        <v>0.7055</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="Y111" t="n">
-        <v>26.647</v>
+        <v>26.568</v>
       </c>
       <c r="Z111" t="n">
-        <v>57.898</v>
+        <v>57.966</v>
       </c>
       <c r="AA111" t="n">
-        <v>7.411</v>
+        <v>7.227</v>
       </c>
       <c r="AB111" t="n">
-        <v>23.072</v>
+        <v>22.989</v>
       </c>
       <c r="AC111" t="n">
-        <v>18.28</v>
+        <v>18.625</v>
       </c>
       <c r="AD111" t="n">
-        <v>24.951</v>
+        <v>25.045</v>
       </c>
       <c r="AE111" t="n">
-        <v>9.092000000000001</v>
+        <v>9.455</v>
       </c>
       <c r="AF111" t="n">
-        <v>26.303</v>
+        <v>26.841</v>
       </c>
       <c r="AG111" t="n">
-        <v>12.891</v>
+        <v>13.193</v>
       </c>
       <c r="AH111" t="n">
-        <v>6.566</v>
+        <v>6.557</v>
       </c>
       <c r="AI111" t="n">
-        <v>3.799</v>
+        <v>3.875</v>
       </c>
       <c r="AJ111" t="n">
-        <v>18.309</v>
+        <v>18.102</v>
       </c>
       <c r="AK111" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="AL111" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="112">
@@ -14186,22 +14186,22 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F115" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G115" t="b">
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>2111.185</v>
+        <v>2120.903</v>
       </c>
       <c r="I115" t="n">
-        <v>1.4261</v>
+        <v>1.2885</v>
       </c>
       <c r="J115" t="n">
-        <v>1716.1</v>
+        <v>1724.5</v>
       </c>
       <c r="K115" t="n">
         <v>6</v>
@@ -14222,70 +14222,70 @@
         <v>7</v>
       </c>
       <c r="Q115" t="n">
-        <v>117.413</v>
+        <v>117.484</v>
       </c>
       <c r="R115" t="n">
-        <v>95.277</v>
+        <v>94.626</v>
       </c>
       <c r="S115" t="n">
-        <v>22.136</v>
+        <v>22.858</v>
       </c>
       <c r="T115" t="n">
-        <v>0.3403</v>
+        <v>0.33581</v>
       </c>
       <c r="U115" t="n">
-        <v>0.12441</v>
+        <v>0.1237</v>
       </c>
       <c r="V115" t="n">
-        <v>77.45</v>
+        <v>77.16</v>
       </c>
       <c r="W115" t="n">
-        <v>62.88</v>
+        <v>62.21</v>
       </c>
       <c r="X115" t="n">
-        <v>0.8454</v>
+        <v>0.85</v>
       </c>
       <c r="Y115" t="n">
-        <v>27.917</v>
+        <v>27.7</v>
       </c>
       <c r="Z115" t="n">
-        <v>61.895</v>
+        <v>61.58</v>
       </c>
       <c r="AA115" t="n">
-        <v>8.741</v>
+        <v>8.83</v>
       </c>
       <c r="AB115" t="n">
-        <v>25.44</v>
+        <v>25.23</v>
       </c>
       <c r="AC115" t="n">
-        <v>12.878</v>
+        <v>12.93</v>
       </c>
       <c r="AD115" t="n">
-        <v>16.661</v>
+        <v>16.72</v>
       </c>
       <c r="AE115" t="n">
-        <v>11.527</v>
+        <v>11.44</v>
       </c>
       <c r="AF115" t="n">
-        <v>22.32</v>
+        <v>22.7</v>
       </c>
       <c r="AG115" t="n">
-        <v>14.802</v>
+        <v>14.69</v>
       </c>
       <c r="AH115" t="n">
-        <v>8.012</v>
+        <v>7.81</v>
       </c>
       <c r="AI115" t="n">
-        <v>3.887</v>
+        <v>3.88</v>
       </c>
       <c r="AJ115" t="n">
-        <v>18.02</v>
+        <v>17.91</v>
       </c>
       <c r="AK115" t="n">
-        <v>10.8</v>
+        <v>17.8</v>
       </c>
       <c r="AL115" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="116">
@@ -14426,22 +14426,22 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F117" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G117" t="b">
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>1404.399</v>
+        <v>1405.975</v>
       </c>
       <c r="I117" t="n">
-        <v>3.2279</v>
+        <v>3.0696</v>
       </c>
       <c r="J117" t="n">
-        <v>1380.6</v>
+        <v>1374.8</v>
       </c>
       <c r="K117" t="n">
         <v>202</v>
@@ -14462,70 +14462,70 @@
         <v>202</v>
       </c>
       <c r="Q117" t="n">
-        <v>109.075</v>
+        <v>108.811</v>
       </c>
       <c r="R117" t="n">
-        <v>98.807</v>
+        <v>97.937</v>
       </c>
       <c r="S117" t="n">
-        <v>10.268</v>
+        <v>10.874</v>
       </c>
       <c r="T117" t="n">
-        <v>0.31259</v>
+        <v>0.31421</v>
       </c>
       <c r="U117" t="n">
-        <v>0.18549</v>
+        <v>0.18708</v>
       </c>
       <c r="V117" t="n">
-        <v>75.19</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="W117" t="n">
-        <v>68.33</v>
+        <v>67.88</v>
       </c>
       <c r="X117" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6473</v>
       </c>
       <c r="Y117" t="n">
-        <v>25.306</v>
+        <v>25.187</v>
       </c>
       <c r="Z117" t="n">
-        <v>56.175</v>
+        <v>56.056</v>
       </c>
       <c r="AA117" t="n">
-        <v>6.885</v>
+        <v>6.681</v>
       </c>
       <c r="AB117" t="n">
-        <v>19.333</v>
+        <v>19.139</v>
       </c>
       <c r="AC117" t="n">
-        <v>17.698</v>
+        <v>18.159</v>
       </c>
       <c r="AD117" t="n">
-        <v>23.881</v>
+        <v>24.526</v>
       </c>
       <c r="AE117" t="n">
-        <v>10.348</v>
+        <v>10.483</v>
       </c>
       <c r="AF117" t="n">
-        <v>22.612</v>
+        <v>22.755</v>
       </c>
       <c r="AG117" t="n">
-        <v>15.462</v>
+        <v>15.411</v>
       </c>
       <c r="AH117" t="n">
-        <v>8.458</v>
+        <v>8.637</v>
       </c>
       <c r="AI117" t="n">
-        <v>3.827</v>
+        <v>3.907</v>
       </c>
       <c r="AJ117" t="n">
-        <v>18.813</v>
+        <v>18.668</v>
       </c>
       <c r="AK117" t="n">
-        <v>23.6</v>
+        <v>20.6</v>
       </c>
       <c r="AL117" t="n">
-        <v>21.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="118">
@@ -14906,22 +14906,22 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F121" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G121" t="b">
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>2003.313</v>
+        <v>1982.683</v>
       </c>
       <c r="I121" t="n">
-        <v>8.2525</v>
+        <v>7.8712</v>
       </c>
       <c r="J121" t="n">
-        <v>1709.5</v>
+        <v>1717.2</v>
       </c>
       <c r="K121" t="n">
         <v>5</v>
@@ -14942,70 +14942,70 @@
         <v>6</v>
       </c>
       <c r="Q121" t="n">
-        <v>125.482</v>
+        <v>125.113</v>
       </c>
       <c r="R121" t="n">
-        <v>103.074</v>
+        <v>103.663</v>
       </c>
       <c r="S121" t="n">
-        <v>22.408</v>
+        <v>21.45</v>
       </c>
       <c r="T121" t="n">
-        <v>0.32381</v>
+        <v>0.32225</v>
       </c>
       <c r="U121" t="n">
-        <v>0.12946</v>
+        <v>0.12812</v>
       </c>
       <c r="V121" t="n">
-        <v>84.19</v>
+        <v>84.41</v>
       </c>
       <c r="W121" t="n">
-        <v>69.16</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="X121" t="n">
-        <v>0.7768</v>
+        <v>0.7419</v>
       </c>
       <c r="Y121" t="n">
-        <v>28.455</v>
+        <v>28.464</v>
       </c>
       <c r="Z121" t="n">
-        <v>61.664</v>
+        <v>61.919</v>
       </c>
       <c r="AA121" t="n">
-        <v>10.899</v>
+        <v>10.927</v>
       </c>
       <c r="AB121" t="n">
-        <v>31.365</v>
+        <v>31.849</v>
       </c>
       <c r="AC121" t="n">
-        <v>16.377</v>
+        <v>16.684</v>
       </c>
       <c r="AD121" t="n">
-        <v>20.643</v>
+        <v>20.973</v>
       </c>
       <c r="AE121" t="n">
-        <v>12.383</v>
+        <v>12.329</v>
       </c>
       <c r="AF121" t="n">
-        <v>26.133</v>
+        <v>26.185</v>
       </c>
       <c r="AG121" t="n">
-        <v>14.638</v>
+        <v>14.743</v>
       </c>
       <c r="AH121" t="n">
-        <v>3.852</v>
+        <v>3.887</v>
       </c>
       <c r="AI121" t="n">
-        <v>4.69</v>
+        <v>4.597</v>
       </c>
       <c r="AJ121" t="n">
-        <v>13.052</v>
+        <v>13.312</v>
       </c>
       <c r="AK121" t="n">
-        <v>10.6</v>
+        <v>2.8</v>
       </c>
       <c r="AL121" t="n">
-        <v>11.7</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="122">
@@ -15746,22 +15746,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F128" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G128" t="b">
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>2045.888</v>
+        <v>2038.996</v>
       </c>
       <c r="I128" t="n">
-        <v>2.4203</v>
+        <v>2.2111</v>
       </c>
       <c r="J128" t="n">
-        <v>1700.1</v>
+        <v>1718</v>
       </c>
       <c r="K128" t="n">
         <v>7</v>
@@ -15782,70 +15782,70 @@
         <v>8</v>
       </c>
       <c r="Q128" t="n">
-        <v>118.774</v>
+        <v>118.901</v>
       </c>
       <c r="R128" t="n">
-        <v>94.51000000000001</v>
+        <v>95.73399999999999</v>
       </c>
       <c r="S128" t="n">
-        <v>24.264</v>
+        <v>23.167</v>
       </c>
       <c r="T128" t="n">
-        <v>0.31643</v>
+        <v>0.32166</v>
       </c>
       <c r="U128" t="n">
-        <v>0.14618</v>
+        <v>0.14689</v>
       </c>
       <c r="V128" t="n">
-        <v>81.79000000000001</v>
+        <v>81.78</v>
       </c>
       <c r="W128" t="n">
-        <v>64.54000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="X128" t="n">
-        <v>0.8197</v>
+        <v>0.7879</v>
       </c>
       <c r="Y128" t="n">
-        <v>29.036</v>
+        <v>29.191</v>
       </c>
       <c r="Z128" t="n">
-        <v>60.026</v>
+        <v>60.281</v>
       </c>
       <c r="AA128" t="n">
-        <v>8.94</v>
+        <v>9.127000000000001</v>
       </c>
       <c r="AB128" t="n">
-        <v>23.501</v>
+        <v>23.734</v>
       </c>
       <c r="AC128" t="n">
-        <v>13.933</v>
+        <v>13.63</v>
       </c>
       <c r="AD128" t="n">
-        <v>20.637</v>
+        <v>20.256</v>
       </c>
       <c r="AE128" t="n">
-        <v>10.516</v>
+        <v>10.71</v>
       </c>
       <c r="AF128" t="n">
-        <v>22.751</v>
+        <v>22.618</v>
       </c>
       <c r="AG128" t="n">
-        <v>17.19</v>
+        <v>17.122</v>
       </c>
       <c r="AH128" t="n">
-        <v>8.914999999999999</v>
+        <v>8.904999999999999</v>
       </c>
       <c r="AI128" t="n">
-        <v>2.721</v>
+        <v>2.7</v>
       </c>
       <c r="AJ128" t="n">
-        <v>15.838</v>
+        <v>15.883</v>
       </c>
       <c r="AK128" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="AL128" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="129">
@@ -16586,22 +16586,22 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F135" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G135" t="b">
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>1983.374</v>
+        <v>1973.656</v>
       </c>
       <c r="I135" t="n">
-        <v>10.797</v>
+        <v>10.346</v>
       </c>
       <c r="J135" t="n">
-        <v>1778</v>
+        <v>1791.1</v>
       </c>
       <c r="K135" t="n">
         <v>19</v>
@@ -16622,70 +16622,70 @@
         <v>19</v>
       </c>
       <c r="Q135" t="n">
-        <v>111.093</v>
+        <v>109.902</v>
       </c>
       <c r="R135" t="n">
-        <v>100.733</v>
+        <v>101.514</v>
       </c>
       <c r="S135" t="n">
-        <v>10.36</v>
+        <v>8.388999999999999</v>
       </c>
       <c r="T135" t="n">
-        <v>0.24934</v>
+        <v>0.25561</v>
       </c>
       <c r="U135" t="n">
-        <v>0.15162</v>
+        <v>0.15124</v>
       </c>
       <c r="V135" t="n">
-        <v>76.55</v>
+        <v>75.3</v>
       </c>
       <c r="W135" t="n">
-        <v>69.45</v>
+        <v>69.39</v>
       </c>
       <c r="X135" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.6888</v>
       </c>
       <c r="Y135" t="n">
-        <v>27.091</v>
+        <v>26.608</v>
       </c>
       <c r="Z135" t="n">
-        <v>59.08</v>
+        <v>59.007</v>
       </c>
       <c r="AA135" t="n">
-        <v>7.332</v>
+        <v>7.359</v>
       </c>
       <c r="AB135" t="n">
-        <v>20.95</v>
+        <v>21.083</v>
       </c>
       <c r="AC135" t="n">
-        <v>15.035</v>
+        <v>14.725</v>
       </c>
       <c r="AD135" t="n">
-        <v>19.505</v>
+        <v>19.228</v>
       </c>
       <c r="AE135" t="n">
-        <v>9.272</v>
+        <v>9.49</v>
       </c>
       <c r="AF135" t="n">
-        <v>27.748</v>
+        <v>27.48</v>
       </c>
       <c r="AG135" t="n">
-        <v>14.387</v>
+        <v>14.199</v>
       </c>
       <c r="AH135" t="n">
-        <v>5.593</v>
+        <v>5.456</v>
       </c>
       <c r="AI135" t="n">
-        <v>5.833</v>
+        <v>5.684</v>
       </c>
       <c r="AJ135" t="n">
-        <v>14.543</v>
+        <v>14.414</v>
       </c>
       <c r="AK135" t="n">
-        <v>0.8</v>
+        <v>-6.2</v>
       </c>
       <c r="AL135" t="n">
-        <v>-0.2</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="136">
@@ -16826,22 +16826,22 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F137" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G137" t="b">
         <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>1507.336</v>
+        <v>1514.853</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.3139</v>
+        <v>-0.2575</v>
       </c>
       <c r="J137" t="n">
-        <v>1470.6</v>
+        <v>1473.6</v>
       </c>
       <c r="K137" t="n">
         <v>178</v>
@@ -16862,70 +16862,70 @@
         <v>170</v>
       </c>
       <c r="Q137" t="n">
-        <v>111.261</v>
+        <v>111.256</v>
       </c>
       <c r="R137" t="n">
-        <v>108.937</v>
+        <v>108.753</v>
       </c>
       <c r="S137" t="n">
-        <v>2.324</v>
+        <v>2.503</v>
       </c>
       <c r="T137" t="n">
-        <v>0.33323</v>
+        <v>0.33921</v>
       </c>
       <c r="U137" t="n">
-        <v>0.16522</v>
+        <v>0.16722</v>
       </c>
       <c r="V137" t="n">
-        <v>81.06999999999999</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="W137" t="n">
-        <v>79.31</v>
+        <v>78.98</v>
       </c>
       <c r="X137" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5704</v>
       </c>
       <c r="Y137" t="n">
-        <v>26.186</v>
+        <v>26.24</v>
       </c>
       <c r="Z137" t="n">
-        <v>60.739</v>
+        <v>60.843</v>
       </c>
       <c r="AA137" t="n">
-        <v>9.087</v>
+        <v>8.941000000000001</v>
       </c>
       <c r="AB137" t="n">
-        <v>26.562</v>
+        <v>26.52</v>
       </c>
       <c r="AC137" t="n">
-        <v>19.22</v>
+        <v>18.882</v>
       </c>
       <c r="AD137" t="n">
-        <v>27.357</v>
+        <v>26.973</v>
       </c>
       <c r="AE137" t="n">
-        <v>12.016</v>
+        <v>12.241</v>
       </c>
       <c r="AF137" t="n">
-        <v>24.084</v>
+        <v>23.891</v>
       </c>
       <c r="AG137" t="n">
-        <v>13.64</v>
+        <v>13.67</v>
       </c>
       <c r="AH137" t="n">
-        <v>6.478</v>
+        <v>6.754</v>
       </c>
       <c r="AI137" t="n">
-        <v>5.27</v>
+        <v>5.089</v>
       </c>
       <c r="AJ137" t="n">
-        <v>21.106</v>
+        <v>21.024</v>
       </c>
       <c r="AK137" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AL137" t="n">
-        <v>-0.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="138">
@@ -16946,22 +16946,22 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F138" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G138" t="b">
         <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>1608.698</v>
+        <v>1600.738</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1871</v>
+        <v>0.115</v>
       </c>
       <c r="J138" t="n">
-        <v>1469.5</v>
+        <v>1479</v>
       </c>
       <c r="K138" t="n">
         <v>154</v>
@@ -16982,70 +16982,70 @@
         <v>147</v>
       </c>
       <c r="Q138" t="n">
-        <v>112.747</v>
+        <v>112.171</v>
       </c>
       <c r="R138" t="n">
-        <v>109.039</v>
+        <v>109.176</v>
       </c>
       <c r="S138" t="n">
-        <v>3.708</v>
+        <v>2.995</v>
       </c>
       <c r="T138" t="n">
-        <v>0.31737</v>
+        <v>0.32353</v>
       </c>
       <c r="U138" t="n">
-        <v>0.17702</v>
+        <v>0.17631</v>
       </c>
       <c r="V138" t="n">
-        <v>83.56</v>
+        <v>82.89</v>
       </c>
       <c r="W138" t="n">
-        <v>80.81</v>
+        <v>80.62</v>
       </c>
       <c r="X138" t="n">
-        <v>0.7361</v>
+        <v>0.7028</v>
       </c>
       <c r="Y138" t="n">
-        <v>26.922</v>
+        <v>26.612</v>
       </c>
       <c r="Z138" t="n">
-        <v>60.505</v>
+        <v>60.812</v>
       </c>
       <c r="AA138" t="n">
-        <v>9.705</v>
+        <v>9.619</v>
       </c>
       <c r="AB138" t="n">
-        <v>27.256</v>
+        <v>27.319</v>
       </c>
       <c r="AC138" t="n">
-        <v>20.01</v>
+        <v>20.042</v>
       </c>
       <c r="AD138" t="n">
-        <v>27.021</v>
+        <v>26.917</v>
       </c>
       <c r="AE138" t="n">
-        <v>11.441</v>
+        <v>11.864</v>
       </c>
       <c r="AF138" t="n">
-        <v>24.385</v>
+        <v>24.425</v>
       </c>
       <c r="AG138" t="n">
-        <v>15.439</v>
+        <v>14.999</v>
       </c>
       <c r="AH138" t="n">
-        <v>6.724</v>
+        <v>6.671</v>
       </c>
       <c r="AI138" t="n">
-        <v>3.342</v>
+        <v>3.268</v>
       </c>
       <c r="AJ138" t="n">
-        <v>20.009</v>
+        <v>20.135</v>
       </c>
       <c r="AK138" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AL138" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="139">
@@ -17066,22 +17066,22 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F139" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G139" t="b">
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>1896.998</v>
+        <v>1886.896</v>
       </c>
       <c r="I139" t="n">
-        <v>4.9403</v>
+        <v>4.7611</v>
       </c>
       <c r="J139" t="n">
-        <v>1723.9</v>
+        <v>1734.8</v>
       </c>
       <c r="K139" t="n">
         <v>27</v>
@@ -17102,70 +17102,70 @@
         <v>28</v>
       </c>
       <c r="Q139" t="n">
-        <v>116.842</v>
+        <v>115.762</v>
       </c>
       <c r="R139" t="n">
-        <v>106.318</v>
+        <v>106.053</v>
       </c>
       <c r="S139" t="n">
-        <v>10.524</v>
+        <v>9.709</v>
       </c>
       <c r="T139" t="n">
-        <v>0.31204</v>
+        <v>0.31063</v>
       </c>
       <c r="U139" t="n">
-        <v>0.14634</v>
+        <v>0.14646</v>
       </c>
       <c r="V139" t="n">
-        <v>81.27</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="W139" t="n">
-        <v>73.89</v>
+        <v>73.8</v>
       </c>
       <c r="X139" t="n">
-        <v>0.64</v>
+        <v>0.6119</v>
       </c>
       <c r="Y139" t="n">
-        <v>28.25</v>
+        <v>27.993</v>
       </c>
       <c r="Z139" t="n">
-        <v>60.49</v>
+        <v>60.486</v>
       </c>
       <c r="AA139" t="n">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AB139" t="n">
-        <v>23.38</v>
+        <v>23.466</v>
       </c>
       <c r="AC139" t="n">
-        <v>16.41</v>
+        <v>16.408</v>
       </c>
       <c r="AD139" t="n">
-        <v>22.76</v>
+        <v>22.652</v>
       </c>
       <c r="AE139" t="n">
-        <v>11.12</v>
+        <v>11.001</v>
       </c>
       <c r="AF139" t="n">
-        <v>24.51</v>
+        <v>24.38</v>
       </c>
       <c r="AG139" t="n">
-        <v>15.91</v>
+        <v>15.702</v>
       </c>
       <c r="AH139" t="n">
-        <v>7.03</v>
+        <v>7.106</v>
       </c>
       <c r="AI139" t="n">
-        <v>4.19</v>
+        <v>4.204</v>
       </c>
       <c r="AJ139" t="n">
-        <v>18.26</v>
+        <v>18.464</v>
       </c>
       <c r="AK139" t="n">
-        <v>1.4</v>
+        <v>-3</v>
       </c>
       <c r="AL139" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="140">
@@ -18266,22 +18266,22 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F149" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G149" t="b">
         <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>1511.69</v>
+        <v>1515.177</v>
       </c>
       <c r="I149" t="n">
-        <v>-1.5513</v>
+        <v>-1.3208</v>
       </c>
       <c r="J149" t="n">
-        <v>1466</v>
+        <v>1463.6</v>
       </c>
       <c r="K149" t="n">
         <v>208</v>
@@ -18302,70 +18302,70 @@
         <v>213</v>
       </c>
       <c r="Q149" t="n">
-        <v>103.458</v>
+        <v>104.019</v>
       </c>
       <c r="R149" t="n">
-        <v>102.905</v>
+        <v>103.396</v>
       </c>
       <c r="S149" t="n">
-        <v>0.553</v>
+        <v>0.623</v>
       </c>
       <c r="T149" t="n">
-        <v>0.32901</v>
+        <v>0.32986</v>
       </c>
       <c r="U149" t="n">
-        <v>0.17465</v>
+        <v>0.17283</v>
       </c>
       <c r="V149" t="n">
-        <v>68.16</v>
+        <v>68.11</v>
       </c>
       <c r="W149" t="n">
-        <v>67.73</v>
+        <v>67.66</v>
       </c>
       <c r="X149" t="n">
-        <v>0.5551</v>
+        <v>0.5697</v>
       </c>
       <c r="Y149" t="n">
-        <v>24.783</v>
+        <v>24.808</v>
       </c>
       <c r="Z149" t="n">
-        <v>57.555</v>
+        <v>57.41</v>
       </c>
       <c r="AA149" t="n">
-        <v>5.714</v>
+        <v>5.622</v>
       </c>
       <c r="AB149" t="n">
-        <v>19.149</v>
+        <v>19.006</v>
       </c>
       <c r="AC149" t="n">
-        <v>12.878</v>
+        <v>12.868</v>
       </c>
       <c r="AD149" t="n">
-        <v>19.24</v>
+        <v>19.192</v>
       </c>
       <c r="AE149" t="n">
-        <v>11.548</v>
+        <v>11.57</v>
       </c>
       <c r="AF149" t="n">
-        <v>23.225</v>
+        <v>23.192</v>
       </c>
       <c r="AG149" t="n">
-        <v>11.912</v>
+        <v>11.861</v>
       </c>
       <c r="AH149" t="n">
-        <v>6.996</v>
+        <v>6.847</v>
       </c>
       <c r="AI149" t="n">
-        <v>4.685</v>
+        <v>4.542</v>
       </c>
       <c r="AJ149" t="n">
-        <v>16.475</v>
+        <v>16.47</v>
       </c>
       <c r="AK149" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="AL149" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="150">
@@ -19826,22 +19826,22 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F162" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G162" t="b">
         <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>1495.549</v>
+        <v>1489.673</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8792</v>
+        <v>0.828</v>
       </c>
       <c r="J162" t="n">
-        <v>1464.6</v>
+        <v>1461.5</v>
       </c>
       <c r="K162" t="n">
         <v>201</v>
@@ -19862,70 +19862,70 @@
         <v>203</v>
       </c>
       <c r="Q162" t="n">
-        <v>110.008</v>
+        <v>109.253</v>
       </c>
       <c r="R162" t="n">
-        <v>108.117</v>
+        <v>108.044</v>
       </c>
       <c r="S162" t="n">
-        <v>1.892</v>
+        <v>1.209</v>
       </c>
       <c r="T162" t="n">
-        <v>0.29738</v>
+        <v>0.29949</v>
       </c>
       <c r="U162" t="n">
-        <v>0.17118</v>
+        <v>0.17153</v>
       </c>
       <c r="V162" t="n">
-        <v>80.39</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="W162" t="n">
-        <v>78.91</v>
+        <v>78.8</v>
       </c>
       <c r="X162" t="n">
-        <v>0.5208</v>
+        <v>0.4955</v>
       </c>
       <c r="Y162" t="n">
-        <v>28.457</v>
+        <v>28.354</v>
       </c>
       <c r="Z162" t="n">
-        <v>60.671</v>
+        <v>60.77</v>
       </c>
       <c r="AA162" t="n">
-        <v>8.039</v>
+        <v>7.84</v>
       </c>
       <c r="AB162" t="n">
-        <v>22.267</v>
+        <v>22.115</v>
       </c>
       <c r="AC162" t="n">
-        <v>15.268</v>
+        <v>15.119</v>
       </c>
       <c r="AD162" t="n">
-        <v>22.568</v>
+        <v>22.548</v>
       </c>
       <c r="AE162" t="n">
-        <v>10.054</v>
+        <v>10.222</v>
       </c>
       <c r="AF162" t="n">
-        <v>23.306</v>
+        <v>23.412</v>
       </c>
       <c r="AG162" t="n">
-        <v>17.083</v>
+        <v>16.742</v>
       </c>
       <c r="AH162" t="n">
-        <v>6.501</v>
+        <v>6.655</v>
       </c>
       <c r="AI162" t="n">
-        <v>2.224</v>
+        <v>2.217</v>
       </c>
       <c r="AJ162" t="n">
-        <v>21.121</v>
+        <v>20.915</v>
       </c>
       <c r="AK162" t="n">
-        <v>-1.6</v>
+        <v>-2.8</v>
       </c>
       <c r="AL162" t="n">
-        <v>-1.8</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="163">
@@ -20075,7 +20075,7 @@
         <v>1</v>
       </c>
       <c r="H164" t="n">
-        <v>1223.009</v>
+        <v>1226.657</v>
       </c>
       <c r="I164" t="n">
         <v>-0.5586</v>
@@ -20426,22 +20426,22 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F167" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G167" t="b">
         <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>1780.023</v>
+        <v>1772.273</v>
       </c>
       <c r="I167" t="n">
-        <v>12.0727</v>
+        <v>11.776</v>
       </c>
       <c r="J167" t="n">
-        <v>1624.7</v>
+        <v>1635.9</v>
       </c>
       <c r="K167" t="n">
         <v>29</v>
@@ -20462,70 +20462,70 @@
         <v>32</v>
       </c>
       <c r="Q167" t="n">
-        <v>117.746</v>
+        <v>117.066</v>
       </c>
       <c r="R167" t="n">
-        <v>101.581</v>
+        <v>102.955</v>
       </c>
       <c r="S167" t="n">
-        <v>16.165</v>
+        <v>14.111</v>
       </c>
       <c r="T167" t="n">
-        <v>0.3083</v>
+        <v>0.30957</v>
       </c>
       <c r="U167" t="n">
-        <v>0.1583</v>
+        <v>0.15694</v>
       </c>
       <c r="V167" t="n">
-        <v>82.5</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="W167" t="n">
-        <v>70.81</v>
+        <v>71.33</v>
       </c>
       <c r="X167" t="n">
-        <v>0.784</v>
+        <v>0.7487</v>
       </c>
       <c r="Y167" t="n">
-        <v>30.209</v>
+        <v>29.906</v>
       </c>
       <c r="Z167" t="n">
-        <v>59.913</v>
+        <v>59.815</v>
       </c>
       <c r="AA167" t="n">
-        <v>6.635</v>
+        <v>6.546</v>
       </c>
       <c r="AB167" t="n">
-        <v>18.832</v>
+        <v>18.952</v>
       </c>
       <c r="AC167" t="n">
-        <v>15.452</v>
+        <v>15.348</v>
       </c>
       <c r="AD167" t="n">
-        <v>22.736</v>
+        <v>22.337</v>
       </c>
       <c r="AE167" t="n">
-        <v>10.907</v>
+        <v>10.827</v>
       </c>
       <c r="AF167" t="n">
-        <v>24.314</v>
+        <v>24.038</v>
       </c>
       <c r="AG167" t="n">
-        <v>16.338</v>
+        <v>15.973</v>
       </c>
       <c r="AH167" t="n">
-        <v>7.951</v>
+        <v>7.857</v>
       </c>
       <c r="AI167" t="n">
-        <v>3.464</v>
+        <v>3.389</v>
       </c>
       <c r="AJ167" t="n">
-        <v>15.457</v>
+        <v>15.461</v>
       </c>
       <c r="AK167" t="n">
-        <v>8.4</v>
+        <v>2</v>
       </c>
       <c r="AL167" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="168">
@@ -20666,22 +20666,22 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F169" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G169" t="b">
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>2189.25</v>
+        <v>2192.399</v>
       </c>
       <c r="I169" t="n">
-        <v>7.2681</v>
+        <v>6.99</v>
       </c>
       <c r="J169" t="n">
-        <v>1769.7</v>
+        <v>1768.8</v>
       </c>
       <c r="K169" t="n">
         <v>2</v>
@@ -20702,70 +20702,70 @@
         <v>2</v>
       </c>
       <c r="Q169" t="n">
-        <v>121.973</v>
+        <v>121.295</v>
       </c>
       <c r="R169" t="n">
-        <v>95.941</v>
+        <v>95.953</v>
       </c>
       <c r="S169" t="n">
-        <v>26.032</v>
+        <v>25.341</v>
       </c>
       <c r="T169" t="n">
-        <v>0.26323</v>
+        <v>0.26009</v>
       </c>
       <c r="U169" t="n">
-        <v>0.16569</v>
+        <v>0.16468</v>
       </c>
       <c r="V169" t="n">
-        <v>88.43000000000001</v>
+        <v>87.72</v>
       </c>
       <c r="W169" t="n">
-        <v>69.17</v>
+        <v>68.98</v>
       </c>
       <c r="X169" t="n">
-        <v>0.9361</v>
+        <v>0.9381</v>
       </c>
       <c r="Y169" t="n">
-        <v>30.769</v>
+        <v>30.534</v>
       </c>
       <c r="Z169" t="n">
-        <v>60.303</v>
+        <v>60.061</v>
       </c>
       <c r="AA169" t="n">
-        <v>9.297000000000001</v>
+        <v>9.119</v>
       </c>
       <c r="AB169" t="n">
-        <v>25.418</v>
+        <v>25.114</v>
       </c>
       <c r="AC169" t="n">
-        <v>17.599</v>
+        <v>17.535</v>
       </c>
       <c r="AD169" t="n">
-        <v>23.569</v>
+        <v>23.535</v>
       </c>
       <c r="AE169" t="n">
-        <v>10.14</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="AF169" t="n">
-        <v>28.118</v>
+        <v>28.124</v>
       </c>
       <c r="AG169" t="n">
-        <v>18.74</v>
+        <v>18.734</v>
       </c>
       <c r="AH169" t="n">
-        <v>5.769</v>
+        <v>5.854</v>
       </c>
       <c r="AI169" t="n">
-        <v>5.914</v>
+        <v>5.907</v>
       </c>
       <c r="AJ169" t="n">
-        <v>15.786</v>
+        <v>15.783</v>
       </c>
       <c r="AK169" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AL169" t="n">
-        <v>14.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="170">
@@ -20786,22 +20786,22 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F170" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G170" t="b">
         <v>1</v>
       </c>
       <c r="H170" t="n">
-        <v>2049.759</v>
+        <v>2027.394</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2376</v>
+        <v>0.218</v>
       </c>
       <c r="J170" t="n">
-        <v>1729.6</v>
+        <v>1730.1</v>
       </c>
       <c r="K170" t="n">
         <v>9</v>
@@ -20822,70 +20822,70 @@
         <v>11</v>
       </c>
       <c r="Q170" t="n">
-        <v>117.051</v>
+        <v>117.657</v>
       </c>
       <c r="R170" t="n">
-        <v>100.921</v>
+        <v>102.118</v>
       </c>
       <c r="S170" t="n">
-        <v>16.13</v>
+        <v>15.539</v>
       </c>
       <c r="T170" t="n">
-        <v>0.29928</v>
+        <v>0.29627</v>
       </c>
       <c r="U170" t="n">
-        <v>0.16152</v>
+        <v>0.16068</v>
       </c>
       <c r="V170" t="n">
-        <v>78.79000000000001</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="W170" t="n">
-        <v>68.03</v>
+        <v>68.62</v>
       </c>
       <c r="X170" t="n">
-        <v>0.7971</v>
+        <v>0.7728</v>
       </c>
       <c r="Y170" t="n">
-        <v>27.565</v>
+        <v>27.651</v>
       </c>
       <c r="Z170" t="n">
-        <v>58.528</v>
+        <v>58.266</v>
       </c>
       <c r="AA170" t="n">
-        <v>7.53</v>
+        <v>7.776</v>
       </c>
       <c r="AB170" t="n">
-        <v>21.22</v>
+        <v>21.497</v>
       </c>
       <c r="AC170" t="n">
-        <v>16.128</v>
+        <v>16.082</v>
       </c>
       <c r="AD170" t="n">
-        <v>21.148</v>
+        <v>21.071</v>
       </c>
       <c r="AE170" t="n">
-        <v>11.403</v>
+        <v>11.194</v>
       </c>
       <c r="AF170" t="n">
-        <v>26.368</v>
+        <v>26.152</v>
       </c>
       <c r="AG170" t="n">
-        <v>18.264</v>
+        <v>18.362</v>
       </c>
       <c r="AH170" t="n">
-        <v>5.191</v>
+        <v>5.477</v>
       </c>
       <c r="AI170" t="n">
-        <v>4.148</v>
+        <v>4.113</v>
       </c>
       <c r="AJ170" t="n">
-        <v>16.325</v>
+        <v>16.456</v>
       </c>
       <c r="AK170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL170" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="171">
@@ -21026,22 +21026,22 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F172" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G172" t="b">
         <v>1</v>
       </c>
       <c r="H172" t="n">
-        <v>1659.411</v>
+        <v>1685.217</v>
       </c>
       <c r="I172" t="n">
-        <v>-7.7529</v>
+        <v>-7.2757</v>
       </c>
       <c r="J172" t="n">
-        <v>1697.1</v>
+        <v>1706.6</v>
       </c>
       <c r="K172" t="n">
         <v>81</v>
@@ -21062,70 +21062,70 @@
         <v>92</v>
       </c>
       <c r="Q172" t="n">
-        <v>108.809</v>
+        <v>108.929</v>
       </c>
       <c r="R172" t="n">
-        <v>108.874</v>
+        <v>108.993</v>
       </c>
       <c r="S172" t="n">
-        <v>-0.065</v>
+        <v>-0.064</v>
       </c>
       <c r="T172" t="n">
-        <v>0.28475</v>
+        <v>0.28141</v>
       </c>
       <c r="U172" t="n">
-        <v>0.13634</v>
+        <v>0.13361</v>
       </c>
       <c r="V172" t="n">
-        <v>75.34</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="W172" t="n">
-        <v>75.48</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="X172" t="n">
-        <v>0.43</v>
+        <v>0.4464</v>
       </c>
       <c r="Y172" t="n">
-        <v>26.1</v>
+        <v>26.117</v>
       </c>
       <c r="Z172" t="n">
-        <v>59.85</v>
+        <v>59.95</v>
       </c>
       <c r="AA172" t="n">
-        <v>7.23</v>
+        <v>7.281</v>
       </c>
       <c r="AB172" t="n">
-        <v>22.31</v>
+        <v>22.415</v>
       </c>
       <c r="AC172" t="n">
-        <v>15.45</v>
+        <v>15.552</v>
       </c>
       <c r="AD172" t="n">
-        <v>20.68</v>
+        <v>20.804</v>
       </c>
       <c r="AE172" t="n">
-        <v>9.130000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="AF172" t="n">
-        <v>22.73</v>
+        <v>22.901</v>
       </c>
       <c r="AG172" t="n">
-        <v>13.66</v>
+        <v>13.709</v>
       </c>
       <c r="AH172" t="n">
-        <v>6.98</v>
+        <v>6.865</v>
       </c>
       <c r="AI172" t="n">
-        <v>4.23</v>
+        <v>4.233</v>
       </c>
       <c r="AJ172" t="n">
-        <v>18.97</v>
+        <v>18.846</v>
       </c>
       <c r="AK172" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AL172" t="n">
-        <v>-4.6</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="173">
@@ -21506,22 +21506,22 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F176" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G176" t="b">
         <v>1</v>
       </c>
       <c r="H176" t="n">
-        <v>1411.503</v>
+        <v>1408.015</v>
       </c>
       <c r="I176" t="n">
-        <v>1.1057</v>
+        <v>1.1121</v>
       </c>
       <c r="J176" t="n">
-        <v>1481.6</v>
+        <v>1481.4</v>
       </c>
       <c r="K176" t="n">
         <v>215</v>
@@ -21542,70 +21542,70 @@
         <v>214</v>
       </c>
       <c r="Q176" t="n">
-        <v>108.332</v>
+        <v>108.655</v>
       </c>
       <c r="R176" t="n">
-        <v>109.654</v>
+        <v>110.198</v>
       </c>
       <c r="S176" t="n">
-        <v>-1.322</v>
+        <v>-1.544</v>
       </c>
       <c r="T176" t="n">
-        <v>0.32511</v>
+        <v>0.32818</v>
       </c>
       <c r="U176" t="n">
-        <v>0.16137</v>
+        <v>0.15957</v>
       </c>
       <c r="V176" t="n">
-        <v>73.31999999999999</v>
+        <v>73.03</v>
       </c>
       <c r="W176" t="n">
-        <v>74.47</v>
+        <v>74.3</v>
       </c>
       <c r="X176" t="n">
-        <v>0.4363</v>
+        <v>0.4173</v>
       </c>
       <c r="Y176" t="n">
-        <v>24.58</v>
+        <v>24.546</v>
       </c>
       <c r="Z176" t="n">
-        <v>56.203</v>
+        <v>56.123</v>
       </c>
       <c r="AA176" t="n">
-        <v>7.342</v>
+        <v>7.321</v>
       </c>
       <c r="AB176" t="n">
-        <v>22.943</v>
+        <v>23.015</v>
       </c>
       <c r="AC176" t="n">
-        <v>16.411</v>
+        <v>16.264</v>
       </c>
       <c r="AD176" t="n">
-        <v>24.252</v>
+        <v>23.988</v>
       </c>
       <c r="AE176" t="n">
-        <v>10.005</v>
+        <v>10.074</v>
       </c>
       <c r="AF176" t="n">
-        <v>20.79</v>
+        <v>20.659</v>
       </c>
       <c r="AG176" t="n">
-        <v>13.574</v>
+        <v>13.546</v>
       </c>
       <c r="AH176" t="n">
-        <v>6.768</v>
+        <v>6.664</v>
       </c>
       <c r="AI176" t="n">
-        <v>3.033</v>
+        <v>2.995</v>
       </c>
       <c r="AJ176" t="n">
-        <v>18.265</v>
+        <v>18.109</v>
       </c>
       <c r="AK176" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AL176" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="177">
@@ -23426,22 +23426,22 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F192" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G192" t="b">
         <v>1</v>
       </c>
       <c r="H192" t="n">
-        <v>1292.954</v>
+        <v>1291.665</v>
       </c>
       <c r="I192" t="n">
-        <v>-1.46</v>
+        <v>-1.3164</v>
       </c>
       <c r="J192" t="n">
-        <v>1384</v>
+        <v>1379.6</v>
       </c>
       <c r="K192" t="n">
         <v>353</v>
@@ -23462,70 +23462,70 @@
         <v>347</v>
       </c>
       <c r="Q192" t="n">
-        <v>101.786</v>
+        <v>101.75</v>
       </c>
       <c r="R192" t="n">
-        <v>115.959</v>
+        <v>115.018</v>
       </c>
       <c r="S192" t="n">
-        <v>-14.173</v>
+        <v>-13.267</v>
       </c>
       <c r="T192" t="n">
-        <v>0.30517</v>
+        <v>0.31222</v>
       </c>
       <c r="U192" t="n">
-        <v>0.17852</v>
+        <v>0.17585</v>
       </c>
       <c r="V192" t="n">
-        <v>68.33</v>
+        <v>67.72</v>
       </c>
       <c r="W192" t="n">
-        <v>78.47</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="X192" t="n">
-        <v>0.354</v>
+        <v>0.3773</v>
       </c>
       <c r="Y192" t="n">
         <v>23.048</v>
       </c>
       <c r="Z192" t="n">
-        <v>54.672</v>
+        <v>54.755</v>
       </c>
       <c r="AA192" t="n">
-        <v>6.214</v>
+        <v>5.993</v>
       </c>
       <c r="AB192" t="n">
-        <v>18.532</v>
+        <v>18.418</v>
       </c>
       <c r="AC192" t="n">
-        <v>16.022</v>
+        <v>15.63</v>
       </c>
       <c r="AD192" t="n">
-        <v>21.556</v>
+        <v>21.322</v>
       </c>
       <c r="AE192" t="n">
-        <v>8.772</v>
+        <v>9.066000000000001</v>
       </c>
       <c r="AF192" t="n">
-        <v>19.582</v>
+        <v>19.502</v>
       </c>
       <c r="AG192" t="n">
-        <v>12.178</v>
+        <v>12.231</v>
       </c>
       <c r="AH192" t="n">
-        <v>7.746</v>
+        <v>7.791</v>
       </c>
       <c r="AI192" t="n">
-        <v>3.43</v>
+        <v>3.403</v>
       </c>
       <c r="AJ192" t="n">
-        <v>17.58</v>
+        <v>17.37</v>
       </c>
       <c r="AK192" t="n">
-        <v>-4.8</v>
+        <v>3</v>
       </c>
       <c r="AL192" t="n">
-        <v>-3.3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="193">
@@ -23786,22 +23786,22 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F195" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G195" t="b">
         <v>1</v>
       </c>
       <c r="H195" t="n">
-        <v>1999.63</v>
+        <v>1982.884</v>
       </c>
       <c r="I195" t="n">
-        <v>10.6735</v>
+        <v>9.932399999999999</v>
       </c>
       <c r="J195" t="n">
-        <v>1665.7</v>
+        <v>1675.8</v>
       </c>
       <c r="K195" t="n">
         <v>12</v>
@@ -23822,70 +23822,70 @@
         <v>12</v>
       </c>
       <c r="Q195" t="n">
-        <v>115.404</v>
+        <v>114.614</v>
       </c>
       <c r="R195" t="n">
-        <v>97.95399999999999</v>
+        <v>98.94199999999999</v>
       </c>
       <c r="S195" t="n">
-        <v>17.45</v>
+        <v>15.672</v>
       </c>
       <c r="T195" t="n">
-        <v>0.23786</v>
+        <v>0.24333</v>
       </c>
       <c r="U195" t="n">
-        <v>0.14019</v>
+        <v>0.1403</v>
       </c>
       <c r="V195" t="n">
-        <v>77.97</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="W195" t="n">
-        <v>66.06999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="X195" t="n">
-        <v>0.8406</v>
+        <v>0.8038</v>
       </c>
       <c r="Y195" t="n">
-        <v>27.542</v>
+        <v>27.484</v>
       </c>
       <c r="Z195" t="n">
-        <v>58.91</v>
+        <v>58.927</v>
       </c>
       <c r="AA195" t="n">
-        <v>10.542</v>
+        <v>10.526</v>
       </c>
       <c r="AB195" t="n">
-        <v>29.806</v>
+        <v>29.887</v>
       </c>
       <c r="AC195" t="n">
-        <v>12.348</v>
+        <v>12.247</v>
       </c>
       <c r="AD195" t="n">
-        <v>16.351</v>
+        <v>16.133</v>
       </c>
       <c r="AE195" t="n">
-        <v>8.093</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="AF195" t="n">
-        <v>25.371</v>
+        <v>25.329</v>
       </c>
       <c r="AG195" t="n">
-        <v>18.064</v>
+        <v>18.145</v>
       </c>
       <c r="AH195" t="n">
-        <v>7.397</v>
+        <v>7.298</v>
       </c>
       <c r="AI195" t="n">
-        <v>2.551</v>
+        <v>2.556</v>
       </c>
       <c r="AJ195" t="n">
-        <v>14.296</v>
+        <v>14.226</v>
       </c>
       <c r="AK195" t="n">
-        <v>8</v>
+        <v>0.2</v>
       </c>
       <c r="AL195" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="196">
@@ -23906,22 +23906,22 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F196" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G196" t="b">
         <v>1</v>
       </c>
       <c r="H196" t="n">
-        <v>1749.398</v>
+        <v>1739.629</v>
       </c>
       <c r="I196" t="n">
-        <v>5.9785</v>
+        <v>5.6949</v>
       </c>
       <c r="J196" t="n">
-        <v>1597.4</v>
+        <v>1607.1</v>
       </c>
       <c r="K196" t="n">
         <v>76</v>
@@ -23942,70 +23942,70 @@
         <v>73</v>
       </c>
       <c r="Q196" t="n">
-        <v>113.297</v>
+        <v>112.247</v>
       </c>
       <c r="R196" t="n">
-        <v>105.71</v>
+        <v>105.648</v>
       </c>
       <c r="S196" t="n">
-        <v>7.587</v>
+        <v>6.599</v>
       </c>
       <c r="T196" t="n">
-        <v>0.30297</v>
+        <v>0.30122</v>
       </c>
       <c r="U196" t="n">
-        <v>0.14365</v>
+        <v>0.14585</v>
       </c>
       <c r="V196" t="n">
-        <v>76.33</v>
+        <v>75.83</v>
       </c>
       <c r="W196" t="n">
-        <v>71.45999999999999</v>
+        <v>71.67</v>
       </c>
       <c r="X196" t="n">
-        <v>0.6706</v>
+        <v>0.64</v>
       </c>
       <c r="Y196" t="n">
-        <v>24.797</v>
+        <v>24.785</v>
       </c>
       <c r="Z196" t="n">
-        <v>56.385</v>
+        <v>56.585</v>
       </c>
       <c r="AA196" t="n">
-        <v>6.76</v>
+        <v>6.687</v>
       </c>
       <c r="AB196" t="n">
-        <v>18.396</v>
+        <v>18.447</v>
       </c>
       <c r="AC196" t="n">
-        <v>19.812</v>
+        <v>19.458</v>
       </c>
       <c r="AD196" t="n">
-        <v>26.565</v>
+        <v>26.138</v>
       </c>
       <c r="AE196" t="n">
-        <v>10.156</v>
+        <v>10.135</v>
       </c>
       <c r="AF196" t="n">
-        <v>23.223</v>
+        <v>23.382</v>
       </c>
       <c r="AG196" t="n">
-        <v>14.103</v>
+        <v>14.265</v>
       </c>
       <c r="AH196" t="n">
-        <v>6.599</v>
+        <v>6.662</v>
       </c>
       <c r="AI196" t="n">
-        <v>3.827</v>
+        <v>3.735</v>
       </c>
       <c r="AJ196" t="n">
-        <v>18.315</v>
+        <v>18.324</v>
       </c>
       <c r="AK196" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AL196" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="197">
@@ -24146,22 +24146,22 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F198" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G198" t="b">
         <v>1</v>
       </c>
       <c r="H198" t="n">
-        <v>1812.562</v>
+        <v>1796.871</v>
       </c>
       <c r="I198" t="n">
-        <v>3.0887</v>
+        <v>2.7628</v>
       </c>
       <c r="J198" t="n">
-        <v>1586.9</v>
+        <v>1597.3</v>
       </c>
       <c r="K198" t="n">
         <v>49</v>
@@ -24182,70 +24182,70 @@
         <v>45</v>
       </c>
       <c r="Q198" t="n">
-        <v>115.915</v>
+        <v>114.935</v>
       </c>
       <c r="R198" t="n">
-        <v>103.109</v>
+        <v>102.867</v>
       </c>
       <c r="S198" t="n">
-        <v>12.806</v>
+        <v>12.068</v>
       </c>
       <c r="T198" t="n">
-        <v>0.2783</v>
+        <v>0.28396</v>
       </c>
       <c r="U198" t="n">
-        <v>0.14449</v>
+        <v>0.14539</v>
       </c>
       <c r="V198" t="n">
-        <v>80.73</v>
+        <v>79.87</v>
       </c>
       <c r="W198" t="n">
-        <v>71.86</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="X198" t="n">
-        <v>0.7125</v>
+        <v>0.6813</v>
       </c>
       <c r="Y198" t="n">
-        <v>27.969</v>
+        <v>27.556</v>
       </c>
       <c r="Z198" t="n">
-        <v>59.953</v>
+        <v>59.947</v>
       </c>
       <c r="AA198" t="n">
-        <v>9.086</v>
+        <v>9.013</v>
       </c>
       <c r="AB198" t="n">
-        <v>25.121</v>
+        <v>24.995</v>
       </c>
       <c r="AC198" t="n">
-        <v>15.708</v>
+        <v>15.743</v>
       </c>
       <c r="AD198" t="n">
-        <v>21.414</v>
+        <v>21.775</v>
       </c>
       <c r="AE198" t="n">
-        <v>9.582000000000001</v>
+        <v>9.965999999999999</v>
       </c>
       <c r="AF198" t="n">
-        <v>24.521</v>
+        <v>24.575</v>
       </c>
       <c r="AG198" t="n">
-        <v>14.724</v>
+        <v>14.508</v>
       </c>
       <c r="AH198" t="n">
-        <v>7.786</v>
+        <v>7.823</v>
       </c>
       <c r="AI198" t="n">
-        <v>2.661</v>
+        <v>2.69</v>
       </c>
       <c r="AJ198" t="n">
-        <v>17.796</v>
+        <v>17.703</v>
       </c>
       <c r="AK198" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="AL198" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="199">
@@ -25346,22 +25346,22 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F208" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G208" t="b">
         <v>1</v>
       </c>
       <c r="H208" t="n">
-        <v>1540.867</v>
+        <v>1535.095</v>
       </c>
       <c r="I208" t="n">
-        <v>-5.0315</v>
+        <v>-4.7102</v>
       </c>
       <c r="J208" t="n">
-        <v>1509.6</v>
+        <v>1516.2</v>
       </c>
       <c r="K208" t="n">
         <v>140</v>
@@ -25382,70 +25382,70 @@
         <v>145</v>
       </c>
       <c r="Q208" t="n">
-        <v>104.23</v>
+        <v>103.743</v>
       </c>
       <c r="R208" t="n">
-        <v>102.041</v>
+        <v>101.981</v>
       </c>
       <c r="S208" t="n">
-        <v>2.19</v>
+        <v>1.761</v>
       </c>
       <c r="T208" t="n">
-        <v>0.33371</v>
+        <v>0.33301</v>
       </c>
       <c r="U208" t="n">
-        <v>0.15326</v>
+        <v>0.15387</v>
       </c>
       <c r="V208" t="n">
-        <v>68.73</v>
+        <v>69.33</v>
       </c>
       <c r="W208" t="n">
-        <v>67.53</v>
+        <v>68.48</v>
       </c>
       <c r="X208" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.542</v>
       </c>
       <c r="Y208" t="n">
-        <v>23.745</v>
+        <v>23.951</v>
       </c>
       <c r="Z208" t="n">
-        <v>57.02</v>
+        <v>58.032</v>
       </c>
       <c r="AA208" t="n">
-        <v>5.238</v>
+        <v>5.386</v>
       </c>
       <c r="AB208" t="n">
-        <v>18.155</v>
+        <v>18.832</v>
       </c>
       <c r="AC208" t="n">
-        <v>16.006</v>
+        <v>16.046</v>
       </c>
       <c r="AD208" t="n">
-        <v>22.987</v>
+        <v>22.919</v>
       </c>
       <c r="AE208" t="n">
-        <v>11.053</v>
+        <v>11.238</v>
       </c>
       <c r="AF208" t="n">
-        <v>21.832</v>
+        <v>22.342</v>
       </c>
       <c r="AG208" t="n">
-        <v>11.944</v>
+        <v>12.003</v>
       </c>
       <c r="AH208" t="n">
-        <v>8.776999999999999</v>
+        <v>8.896000000000001</v>
       </c>
       <c r="AI208" t="n">
-        <v>4.301</v>
+        <v>4.299</v>
       </c>
       <c r="AJ208" t="n">
-        <v>19.503</v>
+        <v>19.632</v>
       </c>
       <c r="AK208" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="AL208" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="209">
@@ -26426,22 +26426,22 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F217" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G217" t="b">
         <v>1</v>
       </c>
       <c r="H217" t="n">
-        <v>1817.011</v>
+        <v>1813.861</v>
       </c>
       <c r="I217" t="n">
-        <v>1.7194</v>
+        <v>1.9487</v>
       </c>
       <c r="J217" t="n">
-        <v>1705.5</v>
+        <v>1722.9</v>
       </c>
       <c r="K217" t="n">
         <v>26</v>
@@ -26462,70 +26462,70 @@
         <v>30</v>
       </c>
       <c r="Q217" t="n">
-        <v>118.678</v>
+        <v>118</v>
       </c>
       <c r="R217" t="n">
-        <v>108.159</v>
+        <v>108.071</v>
       </c>
       <c r="S217" t="n">
-        <v>10.519</v>
+        <v>9.929</v>
       </c>
       <c r="T217" t="n">
-        <v>0.25262</v>
+        <v>0.25505</v>
       </c>
       <c r="U217" t="n">
-        <v>0.15021</v>
+        <v>0.15026</v>
       </c>
       <c r="V217" t="n">
-        <v>80.11</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="W217" t="n">
-        <v>72.81</v>
+        <v>72.77</v>
       </c>
       <c r="X217" t="n">
-        <v>0.6594</v>
+        <v>0.631</v>
       </c>
       <c r="Y217" t="n">
-        <v>27.61</v>
+        <v>27.409</v>
       </c>
       <c r="Z217" t="n">
-        <v>55.609</v>
+        <v>55.776</v>
       </c>
       <c r="AA217" t="n">
-        <v>8.074999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="AB217" t="n">
-        <v>22.508</v>
+        <v>22.588</v>
       </c>
       <c r="AC217" t="n">
-        <v>16.942</v>
+        <v>16.893</v>
       </c>
       <c r="AD217" t="n">
-        <v>21.973</v>
+        <v>21.846</v>
       </c>
       <c r="AE217" t="n">
-        <v>8.004</v>
+        <v>8.106999999999999</v>
       </c>
       <c r="AF217" t="n">
-        <v>23.061</v>
+        <v>23.082</v>
       </c>
       <c r="AG217" t="n">
-        <v>14.492</v>
+        <v>14.335</v>
       </c>
       <c r="AH217" t="n">
-        <v>4.765</v>
+        <v>4.828</v>
       </c>
       <c r="AI217" t="n">
-        <v>2.415</v>
+        <v>2.498</v>
       </c>
       <c r="AJ217" t="n">
-        <v>17.385</v>
+        <v>17.391</v>
       </c>
       <c r="AK217" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="AL217" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="218">
@@ -26546,22 +26546,22 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F218" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G218" t="b">
         <v>1</v>
       </c>
       <c r="H218" t="n">
-        <v>1729.029</v>
+        <v>1722.461</v>
       </c>
       <c r="I218" t="n">
-        <v>-1.822</v>
+        <v>-1.4338</v>
       </c>
       <c r="J218" t="n">
-        <v>1666.2</v>
+        <v>1675.4</v>
       </c>
       <c r="K218" t="n">
         <v>46</v>
@@ -26582,70 +26582,70 @@
         <v>54</v>
       </c>
       <c r="Q218" t="n">
-        <v>120.404</v>
+        <v>120.005</v>
       </c>
       <c r="R218" t="n">
-        <v>111.311</v>
+        <v>111.633</v>
       </c>
       <c r="S218" t="n">
-        <v>9.093</v>
+        <v>8.372999999999999</v>
       </c>
       <c r="T218" t="n">
-        <v>0.30935</v>
+        <v>0.30897</v>
       </c>
       <c r="U218" t="n">
-        <v>0.14137</v>
+        <v>0.14018</v>
       </c>
       <c r="V218" t="n">
-        <v>82.84999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="W218" t="n">
-        <v>76.8</v>
+        <v>77.13</v>
       </c>
       <c r="X218" t="n">
-        <v>0.58</v>
+        <v>0.5536</v>
       </c>
       <c r="Y218" t="n">
-        <v>28.1</v>
+        <v>28.184</v>
       </c>
       <c r="Z218" t="n">
-        <v>60.03</v>
+        <v>60.221</v>
       </c>
       <c r="AA218" t="n">
-        <v>9.890000000000001</v>
+        <v>9.682</v>
       </c>
       <c r="AB218" t="n">
-        <v>26.86</v>
+        <v>26.402</v>
       </c>
       <c r="AC218" t="n">
-        <v>15.96</v>
+        <v>16.068</v>
       </c>
       <c r="AD218" t="n">
-        <v>21.6</v>
+        <v>21.603</v>
       </c>
       <c r="AE218" t="n">
-        <v>10.19</v>
+        <v>10.213</v>
       </c>
       <c r="AF218" t="n">
-        <v>22.39</v>
+        <v>22.494</v>
       </c>
       <c r="AG218" t="n">
-        <v>14.07</v>
+        <v>14.164</v>
       </c>
       <c r="AH218" t="n">
-        <v>6.32</v>
+        <v>6.205</v>
       </c>
       <c r="AI218" t="n">
-        <v>3.64</v>
+        <v>3.641</v>
       </c>
       <c r="AJ218" t="n">
-        <v>17.48</v>
+        <v>17.534</v>
       </c>
       <c r="AK218" t="n">
-        <v>13.4</v>
+        <v>9.6</v>
       </c>
       <c r="AL218" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="219">
@@ -28106,22 +28106,22 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F231" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G231" t="b">
         <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>1260.391</v>
+        <v>1263.248</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.6629</v>
       </c>
       <c r="J231" t="n">
-        <v>1386.7</v>
+        <v>1382.8</v>
       </c>
       <c r="K231" t="n">
         <v>312</v>
@@ -28142,70 +28142,70 @@
         <v>316</v>
       </c>
       <c r="Q231" t="n">
-        <v>103.681</v>
+        <v>104.259</v>
       </c>
       <c r="R231" t="n">
-        <v>107.969</v>
+        <v>107.197</v>
       </c>
       <c r="S231" t="n">
-        <v>-4.288</v>
+        <v>-2.937</v>
       </c>
       <c r="T231" t="n">
-        <v>0.28121</v>
+        <v>0.2838</v>
       </c>
       <c r="U231" t="n">
-        <v>0.15459</v>
+        <v>0.15457</v>
       </c>
       <c r="V231" t="n">
-        <v>75.89</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="W231" t="n">
-        <v>79.67</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="X231" t="n">
-        <v>0.4193</v>
+        <v>0.4382</v>
       </c>
       <c r="Y231" t="n">
-        <v>25.248</v>
+        <v>24.94</v>
       </c>
       <c r="Z231" t="n">
-        <v>59.674</v>
+        <v>59.453</v>
       </c>
       <c r="AA231" t="n">
-        <v>5.826</v>
+        <v>5.909</v>
       </c>
       <c r="AB231" t="n">
-        <v>18.242</v>
+        <v>18.214</v>
       </c>
       <c r="AC231" t="n">
-        <v>19.388</v>
+        <v>19.138</v>
       </c>
       <c r="AD231" t="n">
-        <v>25.696</v>
+        <v>25.685</v>
       </c>
       <c r="AE231" t="n">
-        <v>9.028</v>
+        <v>9.125</v>
       </c>
       <c r="AF231" t="n">
-        <v>22.118</v>
+        <v>22.091</v>
       </c>
       <c r="AG231" t="n">
-        <v>11.146</v>
+        <v>11.091</v>
       </c>
       <c r="AH231" t="n">
-        <v>7.161</v>
+        <v>7.082</v>
       </c>
       <c r="AI231" t="n">
-        <v>4.863</v>
+        <v>4.743</v>
       </c>
       <c r="AJ231" t="n">
-        <v>19.845</v>
+        <v>19.951</v>
       </c>
       <c r="AK231" t="n">
-        <v>10.8</v>
+        <v>12.8</v>
       </c>
       <c r="AL231" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="232">
@@ -28586,22 +28586,22 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F235" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G235" t="b">
         <v>1</v>
       </c>
       <c r="H235" t="n">
-        <v>1958.996</v>
+        <v>1975.743</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.051</v>
+        <v>-0.3998</v>
       </c>
       <c r="J235" t="n">
-        <v>1740.1</v>
+        <v>1751.8</v>
       </c>
       <c r="K235" t="n">
         <v>8</v>
@@ -28622,70 +28622,70 @@
         <v>10</v>
       </c>
       <c r="Q235" t="n">
-        <v>124.949</v>
+        <v>124.771</v>
       </c>
       <c r="R235" t="n">
-        <v>107.448</v>
+        <v>106.947</v>
       </c>
       <c r="S235" t="n">
-        <v>17.502</v>
+        <v>17.824</v>
       </c>
       <c r="T235" t="n">
-        <v>0.30955</v>
+        <v>0.30942</v>
       </c>
       <c r="U235" t="n">
-        <v>0.13439</v>
+        <v>0.13586</v>
       </c>
       <c r="V235" t="n">
-        <v>82.20999999999999</v>
+        <v>81.89</v>
       </c>
       <c r="W235" t="n">
-        <v>70.56999999999999</v>
+        <v>70.09</v>
       </c>
       <c r="X235" t="n">
-        <v>0.7527</v>
+        <v>0.76</v>
       </c>
       <c r="Y235" t="n">
-        <v>30.093</v>
+        <v>29.77</v>
       </c>
       <c r="Z235" t="n">
-        <v>60.165</v>
+        <v>59.99</v>
       </c>
       <c r="AA235" t="n">
-        <v>9.391</v>
+        <v>9.43</v>
       </c>
       <c r="AB235" t="n">
-        <v>24.484</v>
+        <v>24.76</v>
       </c>
       <c r="AC235" t="n">
-        <v>12.629</v>
+        <v>12.28</v>
       </c>
       <c r="AD235" t="n">
-        <v>17</v>
+        <v>16.68</v>
       </c>
       <c r="AE235" t="n">
-        <v>10.652</v>
+        <v>10.57</v>
       </c>
       <c r="AF235" t="n">
-        <v>23.266</v>
+        <v>23.14</v>
       </c>
       <c r="AG235" t="n">
-        <v>19.899</v>
+        <v>19.65</v>
       </c>
       <c r="AH235" t="n">
-        <v>5.577</v>
+        <v>5.53</v>
       </c>
       <c r="AI235" t="n">
-        <v>2.711</v>
+        <v>2.69</v>
       </c>
       <c r="AJ235" t="n">
-        <v>14.937</v>
+        <v>14.85</v>
       </c>
       <c r="AK235" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="AL235" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="236">
@@ -29666,22 +29666,22 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F244" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G244" t="b">
         <v>1</v>
       </c>
       <c r="H244" t="n">
-        <v>1257.4</v>
+        <v>1255.823</v>
       </c>
       <c r="I244" t="n">
-        <v>-3.0547</v>
+        <v>-2.8499</v>
       </c>
       <c r="J244" t="n">
-        <v>1393.4</v>
+        <v>1394.2</v>
       </c>
       <c r="K244" t="n">
         <v>356</v>
@@ -29702,70 +29702,70 @@
         <v>357</v>
       </c>
       <c r="Q244" t="n">
-        <v>97.12</v>
+        <v>96.22199999999999</v>
       </c>
       <c r="R244" t="n">
-        <v>114.446</v>
+        <v>114.156</v>
       </c>
       <c r="S244" t="n">
-        <v>-17.326</v>
+        <v>-17.934</v>
       </c>
       <c r="T244" t="n">
-        <v>0.34501</v>
+        <v>0.34511</v>
       </c>
       <c r="U244" t="n">
-        <v>0.20089</v>
+        <v>0.2043</v>
       </c>
       <c r="V244" t="n">
-        <v>67.93000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="W244" t="n">
-        <v>80.70999999999999</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="X244" t="n">
-        <v>0.2857</v>
+        <v>0.2633</v>
       </c>
       <c r="Y244" t="n">
-        <v>22.871</v>
+        <v>22.835</v>
       </c>
       <c r="Z244" t="n">
-        <v>55.667</v>
+        <v>55.774</v>
       </c>
       <c r="AA244" t="n">
-        <v>6.272</v>
+        <v>6.354</v>
       </c>
       <c r="AB244" t="n">
-        <v>18.537</v>
+        <v>18.63</v>
       </c>
       <c r="AC244" t="n">
-        <v>15.633</v>
+        <v>15.13</v>
       </c>
       <c r="AD244" t="n">
-        <v>23.088</v>
+        <v>22.487</v>
       </c>
       <c r="AE244" t="n">
-        <v>9.762</v>
+        <v>9.795</v>
       </c>
       <c r="AF244" t="n">
-        <v>18.354</v>
+        <v>18.42</v>
       </c>
       <c r="AG244" t="n">
-        <v>11.939</v>
+        <v>11.967</v>
       </c>
       <c r="AH244" t="n">
-        <v>6.769</v>
+        <v>6.712</v>
       </c>
       <c r="AI244" t="n">
-        <v>3.565</v>
+        <v>3.605</v>
       </c>
       <c r="AJ244" t="n">
-        <v>21.701</v>
+        <v>22.125</v>
       </c>
       <c r="AK244" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AL244" t="n">
-        <v>-2.2</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="245">
@@ -30146,22 +30146,22 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F248" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G248" t="b">
         <v>1</v>
       </c>
       <c r="H248" t="n">
-        <v>1544.967</v>
+        <v>1537.451</v>
       </c>
       <c r="I248" t="n">
-        <v>4.4295</v>
+        <v>4.2853</v>
       </c>
       <c r="J248" t="n">
-        <v>1499.6</v>
+        <v>1500.3</v>
       </c>
       <c r="K248" t="n">
         <v>109</v>
@@ -30182,70 +30182,70 @@
         <v>104</v>
       </c>
       <c r="Q248" t="n">
-        <v>112.952</v>
+        <v>112.785</v>
       </c>
       <c r="R248" t="n">
-        <v>106.404</v>
+        <v>106.917</v>
       </c>
       <c r="S248" t="n">
-        <v>6.548</v>
+        <v>5.867</v>
       </c>
       <c r="T248" t="n">
-        <v>0.31217</v>
+        <v>0.31269</v>
       </c>
       <c r="U248" t="n">
-        <v>0.15871</v>
+        <v>0.16204</v>
       </c>
       <c r="V248" t="n">
-        <v>80.03</v>
+        <v>79.84</v>
       </c>
       <c r="W248" t="n">
-        <v>75.66</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="X248" t="n">
-        <v>0.6584</v>
+        <v>0.6279</v>
       </c>
       <c r="Y248" t="n">
-        <v>28.115</v>
+        <v>28.04</v>
       </c>
       <c r="Z248" t="n">
-        <v>61.593</v>
+        <v>61.154</v>
       </c>
       <c r="AA248" t="n">
-        <v>8.314</v>
+        <v>8.372</v>
       </c>
       <c r="AB248" t="n">
-        <v>22.034</v>
+        <v>22.033</v>
       </c>
       <c r="AC248" t="n">
-        <v>15.491</v>
+        <v>15.638</v>
       </c>
       <c r="AD248" t="n">
-        <v>21.488</v>
+        <v>21.614</v>
       </c>
       <c r="AE248" t="n">
-        <v>11.255</v>
+        <v>11.165</v>
       </c>
       <c r="AF248" t="n">
-        <v>24.637</v>
+        <v>24.437</v>
       </c>
       <c r="AG248" t="n">
-        <v>14.646</v>
+        <v>14.536</v>
       </c>
       <c r="AH248" t="n">
-        <v>6.916</v>
+        <v>6.943</v>
       </c>
       <c r="AI248" t="n">
-        <v>2.699</v>
+        <v>2.694</v>
       </c>
       <c r="AJ248" t="n">
-        <v>17.668</v>
+        <v>17.586</v>
       </c>
       <c r="AK248" t="n">
-        <v>7.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AL248" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="249">
@@ -30506,22 +30506,22 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F251" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G251" t="b">
         <v>1</v>
       </c>
       <c r="H251" t="n">
-        <v>1796.559</v>
+        <v>1812.249</v>
       </c>
       <c r="I251" t="n">
-        <v>5.1383</v>
+        <v>4.8008</v>
       </c>
       <c r="J251" t="n">
-        <v>1653.1</v>
+        <v>1659.4</v>
       </c>
       <c r="K251" t="n">
         <v>47</v>
@@ -30542,70 +30542,70 @@
         <v>47</v>
       </c>
       <c r="Q251" t="n">
-        <v>110.372</v>
+        <v>109.865</v>
       </c>
       <c r="R251" t="n">
-        <v>101.037</v>
+        <v>100.816</v>
       </c>
       <c r="S251" t="n">
-        <v>9.335000000000001</v>
+        <v>9.048999999999999</v>
       </c>
       <c r="T251" t="n">
-        <v>0.26367</v>
+        <v>0.26377</v>
       </c>
       <c r="U251" t="n">
-        <v>0.16537</v>
+        <v>0.16638</v>
       </c>
       <c r="V251" t="n">
-        <v>77.70999999999999</v>
+        <v>77.22</v>
       </c>
       <c r="W251" t="n">
-        <v>71.52</v>
+        <v>71.22</v>
       </c>
       <c r="X251" t="n">
-        <v>0.6695</v>
+        <v>0.68</v>
       </c>
       <c r="Y251" t="n">
-        <v>27.239</v>
+        <v>27.096</v>
       </c>
       <c r="Z251" t="n">
-        <v>57.667</v>
+        <v>57.664</v>
       </c>
       <c r="AA251" t="n">
-        <v>6.75</v>
+        <v>6.728</v>
       </c>
       <c r="AB251" t="n">
-        <v>19.361</v>
+        <v>19.496</v>
       </c>
       <c r="AC251" t="n">
-        <v>16.481</v>
+        <v>16.296</v>
       </c>
       <c r="AD251" t="n">
-        <v>22.536</v>
+        <v>22.312</v>
       </c>
       <c r="AE251" t="n">
-        <v>8.845000000000001</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="AF251" t="n">
-        <v>23.614</v>
+        <v>23.864</v>
       </c>
       <c r="AG251" t="n">
-        <v>14.658</v>
+        <v>14.784</v>
       </c>
       <c r="AH251" t="n">
-        <v>7.843</v>
+        <v>7.92</v>
       </c>
       <c r="AI251" t="n">
-        <v>4.537</v>
+        <v>4.472</v>
       </c>
       <c r="AJ251" t="n">
-        <v>19.007</v>
+        <v>19.232</v>
       </c>
       <c r="AK251" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL251" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="252">
@@ -31586,22 +31586,22 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F260" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G260" t="b">
         <v>1</v>
       </c>
       <c r="H260" t="n">
-        <v>1673.48</v>
+        <v>1669.778</v>
       </c>
       <c r="I260" t="n">
-        <v>4.6016</v>
+        <v>4.331</v>
       </c>
       <c r="J260" t="n">
-        <v>1635.8</v>
+        <v>1648.5</v>
       </c>
       <c r="K260" t="n">
         <v>52</v>
@@ -31622,70 +31622,70 @@
         <v>56</v>
       </c>
       <c r="Q260" t="n">
-        <v>105.774</v>
+        <v>105.592</v>
       </c>
       <c r="R260" t="n">
-        <v>97.474</v>
+        <v>98.3</v>
       </c>
       <c r="S260" t="n">
-        <v>8.300000000000001</v>
+        <v>7.292</v>
       </c>
       <c r="T260" t="n">
-        <v>0.31798</v>
+        <v>0.32634</v>
       </c>
       <c r="U260" t="n">
-        <v>0.15647</v>
+        <v>0.15791</v>
       </c>
       <c r="V260" t="n">
-        <v>70.42</v>
+        <v>70.31</v>
       </c>
       <c r="W260" t="n">
-        <v>64.90000000000001</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="X260" t="n">
-        <v>0.6599</v>
+        <v>0.63</v>
       </c>
       <c r="Y260" t="n">
-        <v>25.298</v>
+        <v>25.38</v>
       </c>
       <c r="Z260" t="n">
-        <v>58.042</v>
+        <v>58.31</v>
       </c>
       <c r="AA260" t="n">
-        <v>4.742</v>
+        <v>4.76</v>
       </c>
       <c r="AB260" t="n">
-        <v>15.41</v>
+        <v>15.65</v>
       </c>
       <c r="AC260" t="n">
-        <v>15.085</v>
+        <v>14.79</v>
       </c>
       <c r="AD260" t="n">
-        <v>20.868</v>
+        <v>20.46</v>
       </c>
       <c r="AE260" t="n">
-        <v>10.978</v>
+        <v>11.16</v>
       </c>
       <c r="AF260" t="n">
-        <v>22.706</v>
+        <v>22.29</v>
       </c>
       <c r="AG260" t="n">
-        <v>13.125</v>
+        <v>13.09</v>
       </c>
       <c r="AH260" t="n">
-        <v>9.183999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AI260" t="n">
-        <v>5.608</v>
+        <v>5.68</v>
       </c>
       <c r="AJ260" t="n">
-        <v>18.598</v>
+        <v>18.85</v>
       </c>
       <c r="AK260" t="n">
-        <v>2.6</v>
+        <v>-0.2</v>
       </c>
       <c r="AL260" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="261">
@@ -32666,22 +32666,22 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F269" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G269" t="b">
         <v>1</v>
       </c>
       <c r="H269" t="n">
-        <v>1375.894</v>
+        <v>1377.937</v>
       </c>
       <c r="I269" t="n">
-        <v>-2.3939</v>
+        <v>-2.2287</v>
       </c>
       <c r="J269" t="n">
-        <v>1396.5</v>
+        <v>1393.5</v>
       </c>
       <c r="K269" t="n">
         <v>275</v>
@@ -32702,70 +32702,70 @@
         <v>277</v>
       </c>
       <c r="Q269" t="n">
-        <v>106.402</v>
+        <v>106.093</v>
       </c>
       <c r="R269" t="n">
-        <v>111.974</v>
+        <v>111.346</v>
       </c>
       <c r="S269" t="n">
-        <v>-5.572</v>
+        <v>-5.253</v>
       </c>
       <c r="T269" t="n">
-        <v>0.32198</v>
+        <v>0.3165</v>
       </c>
       <c r="U269" t="n">
-        <v>0.15896</v>
+        <v>0.16268</v>
       </c>
       <c r="V269" t="n">
-        <v>76.70999999999999</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="W269" t="n">
-        <v>80.86</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="X269" t="n">
-        <v>0.4524</v>
+        <v>0.4703</v>
       </c>
       <c r="Y269" t="n">
-        <v>26.33</v>
+        <v>26.178</v>
       </c>
       <c r="Z269" t="n">
-        <v>60.104</v>
+        <v>59.766</v>
       </c>
       <c r="AA269" t="n">
-        <v>6.851</v>
+        <v>6.794</v>
       </c>
       <c r="AB269" t="n">
-        <v>19.286</v>
+        <v>19.178</v>
       </c>
       <c r="AC269" t="n">
-        <v>17.198</v>
+        <v>17.239</v>
       </c>
       <c r="AD269" t="n">
-        <v>24.746</v>
+        <v>24.568</v>
       </c>
       <c r="AE269" t="n">
-        <v>10.293</v>
+        <v>10.138</v>
       </c>
       <c r="AF269" t="n">
-        <v>21.89</v>
+        <v>22.141</v>
       </c>
       <c r="AG269" t="n">
-        <v>13.763</v>
+        <v>13.735</v>
       </c>
       <c r="AH269" t="n">
-        <v>8.237</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="AI269" t="n">
-        <v>3.616</v>
+        <v>3.596</v>
       </c>
       <c r="AJ269" t="n">
-        <v>19.506</v>
+        <v>19.177</v>
       </c>
       <c r="AK269" t="n">
-        <v>-0.2</v>
+        <v>2.6</v>
       </c>
       <c r="AL269" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="270">
@@ -32906,22 +32906,22 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F271" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G271" t="b">
         <v>1</v>
       </c>
       <c r="H271" t="n">
-        <v>1551.806</v>
+        <v>1545.443</v>
       </c>
       <c r="I271" t="n">
-        <v>-8.3871</v>
+        <v>-8.1075</v>
       </c>
       <c r="J271" t="n">
-        <v>1535.3</v>
+        <v>1538.4</v>
       </c>
       <c r="K271" t="n">
         <v>160</v>
@@ -32942,70 +32942,70 @@
         <v>158</v>
       </c>
       <c r="Q271" t="n">
-        <v>111.9</v>
+        <v>111.407</v>
       </c>
       <c r="R271" t="n">
-        <v>110.283</v>
+        <v>110.254</v>
       </c>
       <c r="S271" t="n">
-        <v>1.616</v>
+        <v>1.152</v>
       </c>
       <c r="T271" t="n">
-        <v>0.32374</v>
+        <v>0.31946</v>
       </c>
       <c r="U271" t="n">
-        <v>0.16305</v>
+        <v>0.16395</v>
       </c>
       <c r="V271" t="n">
-        <v>76.42</v>
+        <v>76.02</v>
       </c>
       <c r="W271" t="n">
-        <v>75.45999999999999</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="X271" t="n">
-        <v>0.5054</v>
+        <v>0.48</v>
       </c>
       <c r="Y271" t="n">
-        <v>27.833</v>
+        <v>27.6</v>
       </c>
       <c r="Z271" t="n">
-        <v>60.37</v>
+        <v>59.83</v>
       </c>
       <c r="AA271" t="n">
-        <v>6.927</v>
+        <v>6.78</v>
       </c>
       <c r="AB271" t="n">
-        <v>19.208</v>
+        <v>18.79</v>
       </c>
       <c r="AC271" t="n">
-        <v>12.985</v>
+        <v>13.29</v>
       </c>
       <c r="AD271" t="n">
-        <v>17.253</v>
+        <v>17.8</v>
       </c>
       <c r="AE271" t="n">
-        <v>10.711</v>
+        <v>10.53</v>
       </c>
       <c r="AF271" t="n">
-        <v>22.249</v>
+        <v>22.25</v>
       </c>
       <c r="AG271" t="n">
-        <v>15.089</v>
+        <v>14.82</v>
       </c>
       <c r="AH271" t="n">
-        <v>7.411</v>
+        <v>7.46</v>
       </c>
       <c r="AI271" t="n">
-        <v>4.329</v>
+        <v>4.41</v>
       </c>
       <c r="AJ271" t="n">
-        <v>16.474</v>
+        <v>16.69</v>
       </c>
       <c r="AK271" t="n">
-        <v>-0.4</v>
+        <v>1.2</v>
       </c>
       <c r="AL271" t="n">
-        <v>0.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="272">
@@ -33146,22 +33146,22 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F273" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G273" t="b">
         <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>1964.079</v>
+        <v>1967.781</v>
       </c>
       <c r="I273" t="n">
-        <v>5.6344</v>
+        <v>5.6546</v>
       </c>
       <c r="J273" t="n">
-        <v>1676.3</v>
+        <v>1677.1</v>
       </c>
       <c r="K273" t="n">
         <v>21</v>
@@ -33182,70 +33182,70 @@
         <v>22</v>
       </c>
       <c r="Q273" t="n">
-        <v>113.751</v>
+        <v>114.058</v>
       </c>
       <c r="R273" t="n">
-        <v>98.538</v>
+        <v>98.849</v>
       </c>
       <c r="S273" t="n">
-        <v>15.213</v>
+        <v>15.209</v>
       </c>
       <c r="T273" t="n">
-        <v>0.32547</v>
+        <v>0.32437</v>
       </c>
       <c r="U273" t="n">
-        <v>0.14079</v>
+        <v>0.14335</v>
       </c>
       <c r="V273" t="n">
-        <v>82</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="W273" t="n">
-        <v>70.61</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="X273" t="n">
-        <v>0.8142</v>
+        <v>0.8197</v>
       </c>
       <c r="Y273" t="n">
-        <v>28.107</v>
+        <v>27.945</v>
       </c>
       <c r="Z273" t="n">
-        <v>62.29</v>
+        <v>61.612</v>
       </c>
       <c r="AA273" t="n">
-        <v>7.062</v>
+        <v>6.945</v>
       </c>
       <c r="AB273" t="n">
-        <v>21.147</v>
+        <v>20.744</v>
       </c>
       <c r="AC273" t="n">
-        <v>18.72</v>
+        <v>18.982</v>
       </c>
       <c r="AD273" t="n">
-        <v>25.857</v>
+        <v>26.094</v>
       </c>
       <c r="AE273" t="n">
-        <v>11.837</v>
+        <v>11.713</v>
       </c>
       <c r="AF273" t="n">
-        <v>24.794</v>
+        <v>24.653</v>
       </c>
       <c r="AG273" t="n">
-        <v>16.421</v>
+        <v>16.352</v>
       </c>
       <c r="AH273" t="n">
-        <v>7.796</v>
+        <v>7.858</v>
       </c>
       <c r="AI273" t="n">
-        <v>4.814</v>
+        <v>4.781</v>
       </c>
       <c r="AJ273" t="n">
-        <v>17.359</v>
+        <v>17.292</v>
       </c>
       <c r="AK273" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AL273" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="274">
@@ -33266,22 +33266,22 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F274" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G274" t="b">
         <v>1</v>
       </c>
       <c r="H274" t="n">
-        <v>1612.03</v>
+        <v>1618.407</v>
       </c>
       <c r="I274" t="n">
-        <v>0.9935</v>
+        <v>1.2818</v>
       </c>
       <c r="J274" t="n">
-        <v>1506.8</v>
+        <v>1508.9</v>
       </c>
       <c r="K274" t="n">
         <v>121</v>
@@ -33302,70 +33302,70 @@
         <v>124</v>
       </c>
       <c r="Q274" t="n">
-        <v>105.941</v>
+        <v>106.146</v>
       </c>
       <c r="R274" t="n">
-        <v>102.745</v>
+        <v>102.385</v>
       </c>
       <c r="S274" t="n">
-        <v>3.196</v>
+        <v>3.761</v>
       </c>
       <c r="T274" t="n">
-        <v>0.2842</v>
+        <v>0.28439</v>
       </c>
       <c r="U274" t="n">
-        <v>0.16209</v>
+        <v>0.16306</v>
       </c>
       <c r="V274" t="n">
-        <v>72.48999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="W274" t="n">
-        <v>70.56999999999999</v>
+        <v>70</v>
       </c>
       <c r="X274" t="n">
-        <v>0.6584</v>
+        <v>0.6695</v>
       </c>
       <c r="Y274" t="n">
-        <v>25.292</v>
+        <v>25.098</v>
       </c>
       <c r="Z274" t="n">
-        <v>59.516</v>
+        <v>59.103</v>
       </c>
       <c r="AA274" t="n">
-        <v>8.326000000000001</v>
+        <v>8.214</v>
       </c>
       <c r="AB274" t="n">
-        <v>27.255</v>
+        <v>26.806</v>
       </c>
       <c r="AC274" t="n">
-        <v>13.581</v>
+        <v>13.838</v>
       </c>
       <c r="AD274" t="n">
-        <v>18.416</v>
+        <v>18.565</v>
       </c>
       <c r="AE274" t="n">
-        <v>10.205</v>
+        <v>10.198</v>
       </c>
       <c r="AF274" t="n">
-        <v>25.565</v>
+        <v>25.529</v>
       </c>
       <c r="AG274" t="n">
-        <v>15.214</v>
+        <v>15.073</v>
       </c>
       <c r="AH274" t="n">
-        <v>5.45</v>
+        <v>5.504</v>
       </c>
       <c r="AI274" t="n">
-        <v>4.82</v>
+        <v>4.71</v>
       </c>
       <c r="AJ274" t="n">
-        <v>14.376</v>
+        <v>14.197</v>
       </c>
       <c r="AK274" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="AL274" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="275">
@@ -33386,22 +33386,22 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F275" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G275" t="b">
         <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>1807.839</v>
+        <v>1811.548</v>
       </c>
       <c r="I275" t="n">
-        <v>9.839</v>
+        <v>9.2125</v>
       </c>
       <c r="J275" t="n">
-        <v>1512.1</v>
+        <v>1510.4</v>
       </c>
       <c r="K275" t="n">
         <v>40</v>
@@ -33422,70 +33422,70 @@
         <v>27</v>
       </c>
       <c r="Q275" t="n">
-        <v>120.357</v>
+        <v>120.632</v>
       </c>
       <c r="R275" t="n">
-        <v>98.52</v>
+        <v>98.514</v>
       </c>
       <c r="S275" t="n">
-        <v>21.837</v>
+        <v>22.118</v>
       </c>
       <c r="T275" t="n">
-        <v>0.24356</v>
+        <v>0.23855</v>
       </c>
       <c r="U275" t="n">
-        <v>0.16865</v>
+        <v>0.16748</v>
       </c>
       <c r="V275" t="n">
-        <v>86.56</v>
+        <v>86.98</v>
       </c>
       <c r="W275" t="n">
-        <v>70.53</v>
+        <v>70.8</v>
       </c>
       <c r="X275" t="n">
-        <v>0.8558</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="Y275" t="n">
-        <v>30.373</v>
+        <v>30.316</v>
       </c>
       <c r="Z275" t="n">
-        <v>59.745</v>
+        <v>59.733</v>
       </c>
       <c r="AA275" t="n">
-        <v>10.846</v>
+        <v>10.893</v>
       </c>
       <c r="AB275" t="n">
-        <v>26.666</v>
+        <v>26.843</v>
       </c>
       <c r="AC275" t="n">
-        <v>14.966</v>
+        <v>15.455</v>
       </c>
       <c r="AD275" t="n">
-        <v>20.459</v>
+        <v>20.803</v>
       </c>
       <c r="AE275" t="n">
-        <v>8.972</v>
+        <v>8.849</v>
       </c>
       <c r="AF275" t="n">
-        <v>27.792</v>
+        <v>28.055</v>
       </c>
       <c r="AG275" t="n">
-        <v>18.052</v>
+        <v>18.203</v>
       </c>
       <c r="AH275" t="n">
-        <v>7.165</v>
+        <v>7.159</v>
       </c>
       <c r="AI275" t="n">
-        <v>3.296</v>
+        <v>3.243</v>
       </c>
       <c r="AJ275" t="n">
-        <v>18.345</v>
+        <v>18.296</v>
       </c>
       <c r="AK275" t="n">
-        <v>-0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="AL275" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276">
@@ -34586,22 +34586,22 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F285" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G285" t="b">
         <v>1</v>
       </c>
       <c r="H285" t="n">
-        <v>1911.024</v>
+        <v>1897.088</v>
       </c>
       <c r="I285" t="n">
-        <v>-1.5912</v>
+        <v>-1.4465</v>
       </c>
       <c r="J285" t="n">
-        <v>1709</v>
+        <v>1716.9</v>
       </c>
       <c r="K285" t="n">
         <v>14</v>
@@ -34622,70 +34622,70 @@
         <v>21</v>
       </c>
       <c r="Q285" t="n">
-        <v>117.138</v>
+        <v>116.86</v>
       </c>
       <c r="R285" t="n">
-        <v>101.718</v>
+        <v>102.568</v>
       </c>
       <c r="S285" t="n">
-        <v>15.421</v>
+        <v>14.292</v>
       </c>
       <c r="T285" t="n">
-        <v>0.35269</v>
+        <v>0.36001</v>
       </c>
       <c r="U285" t="n">
-        <v>0.16427</v>
+        <v>0.16434</v>
       </c>
       <c r="V285" t="n">
-        <v>79.70999999999999</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="W285" t="n">
-        <v>69.09999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="X285" t="n">
-        <v>0.6914</v>
+        <v>0.6589</v>
       </c>
       <c r="Y285" t="n">
-        <v>28.325</v>
+        <v>28.223</v>
       </c>
       <c r="Z285" t="n">
-        <v>60.905</v>
+        <v>61.155</v>
       </c>
       <c r="AA285" t="n">
-        <v>6.53</v>
+        <v>6.456</v>
       </c>
       <c r="AB285" t="n">
-        <v>19.387</v>
+        <v>19.366</v>
       </c>
       <c r="AC285" t="n">
-        <v>16.533</v>
+        <v>16.419</v>
       </c>
       <c r="AD285" t="n">
-        <v>23.7</v>
+        <v>23.694</v>
       </c>
       <c r="AE285" t="n">
-        <v>14.443</v>
+        <v>14.854</v>
       </c>
       <c r="AF285" t="n">
-        <v>25.945</v>
+        <v>25.785</v>
       </c>
       <c r="AG285" t="n">
-        <v>17.036</v>
+        <v>16.852</v>
       </c>
       <c r="AH285" t="n">
-        <v>7.63</v>
+        <v>7.474</v>
       </c>
       <c r="AI285" t="n">
-        <v>3.755</v>
+        <v>3.576</v>
       </c>
       <c r="AJ285" t="n">
-        <v>17.741</v>
+        <v>17.927</v>
       </c>
       <c r="AK285" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AL285" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="286">
@@ -35546,22 +35546,22 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F293" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G293" t="b">
         <v>1</v>
       </c>
       <c r="H293" t="n">
-        <v>1458.551</v>
+        <v>1464.426</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.6373</v>
+        <v>-0.583</v>
       </c>
       <c r="J293" t="n">
-        <v>1494.4</v>
+        <v>1495.2</v>
       </c>
       <c r="K293" t="n">
         <v>135</v>
@@ -35582,70 +35582,70 @@
         <v>146</v>
       </c>
       <c r="Q293" t="n">
-        <v>114.971</v>
+        <v>114.815</v>
       </c>
       <c r="R293" t="n">
-        <v>111.678</v>
+        <v>111.038</v>
       </c>
       <c r="S293" t="n">
-        <v>3.294</v>
+        <v>3.777</v>
       </c>
       <c r="T293" t="n">
-        <v>0.29848</v>
+        <v>0.28982</v>
       </c>
       <c r="U293" t="n">
-        <v>0.1405</v>
+        <v>0.14163</v>
       </c>
       <c r="V293" t="n">
-        <v>79.94</v>
+        <v>79.84</v>
       </c>
       <c r="W293" t="n">
-        <v>77.72</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="X293" t="n">
-        <v>0.5382</v>
+        <v>0.5528</v>
       </c>
       <c r="Y293" t="n">
-        <v>29.318</v>
+        <v>29.371</v>
       </c>
       <c r="Z293" t="n">
-        <v>60.802</v>
+        <v>60.517</v>
       </c>
       <c r="AA293" t="n">
-        <v>7.208</v>
+        <v>7.192</v>
       </c>
       <c r="AB293" t="n">
-        <v>19.463</v>
+        <v>19.521</v>
       </c>
       <c r="AC293" t="n">
-        <v>14.091</v>
+        <v>13.91</v>
       </c>
       <c r="AD293" t="n">
-        <v>18.673</v>
+        <v>18.536</v>
       </c>
       <c r="AE293" t="n">
-        <v>9.252000000000001</v>
+        <v>8.974</v>
       </c>
       <c r="AF293" t="n">
-        <v>21.153</v>
+        <v>21.419</v>
       </c>
       <c r="AG293" t="n">
-        <v>15.189</v>
+        <v>15.474</v>
       </c>
       <c r="AH293" t="n">
-        <v>7.627</v>
+        <v>7.69</v>
       </c>
       <c r="AI293" t="n">
-        <v>2.835</v>
+        <v>2.924</v>
       </c>
       <c r="AJ293" t="n">
-        <v>15.22</v>
+        <v>15.224</v>
       </c>
       <c r="AK293" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AL293" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="294">
@@ -36026,22 +36026,22 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F297" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G297" t="b">
         <v>1</v>
       </c>
       <c r="H297" t="n">
-        <v>1679.891</v>
+        <v>1685.662</v>
       </c>
       <c r="I297" t="n">
-        <v>9.1937</v>
+        <v>8.801299999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>1503.5</v>
+        <v>1505.1</v>
       </c>
       <c r="K297" t="n">
         <v>58</v>
@@ -36062,70 +36062,70 @@
         <v>50</v>
       </c>
       <c r="Q297" t="n">
-        <v>122.52</v>
+        <v>121.598</v>
       </c>
       <c r="R297" t="n">
-        <v>106.202</v>
+        <v>105.564</v>
       </c>
       <c r="S297" t="n">
-        <v>16.318</v>
+        <v>16.035</v>
       </c>
       <c r="T297" t="n">
-        <v>0.27118</v>
+        <v>0.26922</v>
       </c>
       <c r="U297" t="n">
-        <v>0.1456</v>
+        <v>0.14806</v>
       </c>
       <c r="V297" t="n">
-        <v>84.59</v>
+        <v>84.88</v>
       </c>
       <c r="W297" t="n">
-        <v>73.37</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="X297" t="n">
-        <v>0.795</v>
+        <v>0.8017</v>
       </c>
       <c r="Y297" t="n">
-        <v>27.773</v>
+        <v>27.626</v>
       </c>
       <c r="Z297" t="n">
-        <v>57.612</v>
+        <v>58.003</v>
       </c>
       <c r="AA297" t="n">
-        <v>10.537</v>
+        <v>10.612</v>
       </c>
       <c r="AB297" t="n">
-        <v>26.537</v>
+        <v>26.945</v>
       </c>
       <c r="AC297" t="n">
-        <v>18.509</v>
+        <v>19.013</v>
       </c>
       <c r="AD297" t="n">
-        <v>23.63</v>
+        <v>24.195</v>
       </c>
       <c r="AE297" t="n">
-        <v>9.042999999999999</v>
+        <v>9.116</v>
       </c>
       <c r="AF297" t="n">
-        <v>23.966</v>
+        <v>24.509</v>
       </c>
       <c r="AG297" t="n">
-        <v>15.304</v>
+        <v>15.455</v>
       </c>
       <c r="AH297" t="n">
-        <v>6.441</v>
+        <v>6.504</v>
       </c>
       <c r="AI297" t="n">
-        <v>2.307</v>
+        <v>2.381</v>
       </c>
       <c r="AJ297" t="n">
-        <v>16.289</v>
+        <v>16.339</v>
       </c>
       <c r="AK297" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AL297" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="298">
@@ -36386,22 +36386,22 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F300" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G300" t="b">
         <v>1</v>
       </c>
       <c r="H300" t="n">
-        <v>1599.582</v>
+        <v>1590.138</v>
       </c>
       <c r="I300" t="n">
-        <v>0.5782</v>
+        <v>0.5744</v>
       </c>
       <c r="J300" t="n">
-        <v>1499.7</v>
+        <v>1498.7</v>
       </c>
       <c r="K300" t="n">
         <v>122</v>
@@ -36422,70 +36422,70 @@
         <v>117</v>
       </c>
       <c r="Q300" t="n">
-        <v>108.911</v>
+        <v>109.214</v>
       </c>
       <c r="R300" t="n">
-        <v>103.186</v>
+        <v>104.114</v>
       </c>
       <c r="S300" t="n">
-        <v>5.725</v>
+        <v>5.1</v>
       </c>
       <c r="T300" t="n">
-        <v>0.3013</v>
+        <v>0.30054</v>
       </c>
       <c r="U300" t="n">
-        <v>0.12414</v>
+        <v>0.12492</v>
       </c>
       <c r="V300" t="n">
-        <v>78.31999999999999</v>
+        <v>78.16</v>
       </c>
       <c r="W300" t="n">
-        <v>74.18000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="X300" t="n">
-        <v>0.6379</v>
+        <v>0.6058</v>
       </c>
       <c r="Y300" t="n">
-        <v>28.121</v>
+        <v>28.119</v>
       </c>
       <c r="Z300" t="n">
-        <v>63.868</v>
+        <v>63.612</v>
       </c>
       <c r="AA300" t="n">
-        <v>5.448</v>
+        <v>5.838</v>
       </c>
       <c r="AB300" t="n">
-        <v>19.406</v>
+        <v>19.913</v>
       </c>
       <c r="AC300" t="n">
-        <v>16.625</v>
+        <v>16.301</v>
       </c>
       <c r="AD300" t="n">
-        <v>23.448</v>
+        <v>23.186</v>
       </c>
       <c r="AE300" t="n">
-        <v>11.114</v>
+        <v>11.072</v>
       </c>
       <c r="AF300" t="n">
-        <v>25.42</v>
+        <v>25.426</v>
       </c>
       <c r="AG300" t="n">
-        <v>13.911</v>
+        <v>14.145</v>
       </c>
       <c r="AH300" t="n">
-        <v>7.605</v>
+        <v>7.4</v>
       </c>
       <c r="AI300" t="n">
-        <v>3.506</v>
+        <v>3.522</v>
       </c>
       <c r="AJ300" t="n">
-        <v>14.494</v>
+        <v>14.522</v>
       </c>
       <c r="AK300" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AL300" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -36626,22 +36626,22 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F302" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G302" t="b">
         <v>1</v>
       </c>
       <c r="H302" t="n">
-        <v>1614.53</v>
+        <v>1620.289</v>
       </c>
       <c r="I302" t="n">
-        <v>2.2068</v>
+        <v>2.2032</v>
       </c>
       <c r="J302" t="n">
-        <v>1471.2</v>
+        <v>1473</v>
       </c>
       <c r="K302" t="n">
         <v>106</v>
@@ -36662,70 +36662,70 @@
         <v>118</v>
       </c>
       <c r="Q302" t="n">
-        <v>103.588</v>
+        <v>104.721</v>
       </c>
       <c r="R302" t="n">
-        <v>96.37</v>
+        <v>96.983</v>
       </c>
       <c r="S302" t="n">
-        <v>7.218</v>
+        <v>7.738</v>
       </c>
       <c r="T302" t="n">
-        <v>0.26576</v>
+        <v>0.27137</v>
       </c>
       <c r="U302" t="n">
-        <v>0.17116</v>
+        <v>0.17141</v>
       </c>
       <c r="V302" t="n">
-        <v>74.05</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="W302" t="n">
-        <v>68.87</v>
+        <v>69.25</v>
       </c>
       <c r="X302" t="n">
-        <v>0.6702</v>
+        <v>0.6806</v>
       </c>
       <c r="Y302" t="n">
-        <v>26.802</v>
+        <v>27.058</v>
       </c>
       <c r="Z302" t="n">
-        <v>59.531</v>
+        <v>59.783</v>
       </c>
       <c r="AA302" t="n">
-        <v>5.604</v>
+        <v>5.783</v>
       </c>
       <c r="AB302" t="n">
-        <v>16.771</v>
+        <v>17.142</v>
       </c>
       <c r="AC302" t="n">
-        <v>14.844</v>
+        <v>14.892</v>
       </c>
       <c r="AD302" t="n">
-        <v>21.591</v>
+        <v>21.553</v>
       </c>
       <c r="AE302" t="n">
-        <v>9.769</v>
+        <v>10.068</v>
       </c>
       <c r="AF302" t="n">
-        <v>27.214</v>
+        <v>27.096</v>
       </c>
       <c r="AG302" t="n">
-        <v>14.771</v>
+        <v>15.017</v>
       </c>
       <c r="AH302" t="n">
-        <v>7.583</v>
+        <v>7.533</v>
       </c>
       <c r="AI302" t="n">
-        <v>5.88</v>
+        <v>5.863</v>
       </c>
       <c r="AJ302" t="n">
-        <v>16.066</v>
+        <v>15.897</v>
       </c>
       <c r="AK302" t="n">
-        <v>7</v>
+        <v>10.4</v>
       </c>
       <c r="AL302" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="303">
@@ -36986,22 +36986,22 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F305" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G305" t="b">
         <v>1</v>
       </c>
       <c r="H305" t="n">
-        <v>1863.047</v>
+        <v>1885.412</v>
       </c>
       <c r="I305" t="n">
-        <v>2.4395</v>
+        <v>2.6042</v>
       </c>
       <c r="J305" t="n">
-        <v>1683.8</v>
+        <v>1698.9</v>
       </c>
       <c r="K305" t="n">
         <v>28</v>
@@ -37022,70 +37022,70 @@
         <v>34</v>
       </c>
       <c r="Q305" t="n">
-        <v>116.913</v>
+        <v>117.515</v>
       </c>
       <c r="R305" t="n">
-        <v>106.199</v>
+        <v>107.059</v>
       </c>
       <c r="S305" t="n">
-        <v>10.714</v>
+        <v>10.456</v>
       </c>
       <c r="T305" t="n">
-        <v>0.29856</v>
+        <v>0.30517</v>
       </c>
       <c r="U305" t="n">
-        <v>0.12979</v>
+        <v>0.13147</v>
       </c>
       <c r="V305" t="n">
-        <v>77.73</v>
+        <v>78.17</v>
       </c>
       <c r="W305" t="n">
-        <v>70.43000000000001</v>
+        <v>71.05</v>
       </c>
       <c r="X305" t="n">
-        <v>0.6903</v>
+        <v>0.6995</v>
       </c>
       <c r="Y305" t="n">
-        <v>27.428</v>
+        <v>27.489</v>
       </c>
       <c r="Z305" t="n">
-        <v>58.545</v>
+        <v>58.665</v>
       </c>
       <c r="AA305" t="n">
-        <v>7.867</v>
+        <v>7.995</v>
       </c>
       <c r="AB305" t="n">
-        <v>20.801</v>
+        <v>20.867</v>
       </c>
       <c r="AC305" t="n">
-        <v>15.005</v>
+        <v>15.047</v>
       </c>
       <c r="AD305" t="n">
-        <v>19.594</v>
+        <v>19.656</v>
       </c>
       <c r="AE305" t="n">
-        <v>9.151</v>
+        <v>9.388999999999999</v>
       </c>
       <c r="AF305" t="n">
-        <v>21.497</v>
+        <v>21.305</v>
       </c>
       <c r="AG305" t="n">
-        <v>16.173</v>
+        <v>16.458</v>
       </c>
       <c r="AH305" t="n">
-        <v>6.35</v>
+        <v>6.215</v>
       </c>
       <c r="AI305" t="n">
-        <v>2.978</v>
+        <v>2.931</v>
       </c>
       <c r="AJ305" t="n">
-        <v>17.128</v>
+        <v>17.15</v>
       </c>
       <c r="AK305" t="n">
-        <v>13.6</v>
+        <v>10.6</v>
       </c>
       <c r="AL305" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="306">
@@ -38066,22 +38066,22 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F314" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G314" t="b">
         <v>1</v>
       </c>
       <c r="H314" t="n">
-        <v>1459.858</v>
+        <v>1455.907</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9557</v>
+        <v>0.8692</v>
       </c>
       <c r="J314" t="n">
-        <v>1455.6</v>
+        <v>1465</v>
       </c>
       <c r="K314" t="n">
         <v>156</v>
@@ -38102,70 +38102,70 @@
         <v>162</v>
       </c>
       <c r="Q314" t="n">
-        <v>100.633</v>
+        <v>100.873</v>
       </c>
       <c r="R314" t="n">
-        <v>100.344</v>
+        <v>100.828</v>
       </c>
       <c r="S314" t="n">
-        <v>0.29</v>
+        <v>0.045</v>
       </c>
       <c r="T314" t="n">
-        <v>0.31385</v>
+        <v>0.31275</v>
       </c>
       <c r="U314" t="n">
-        <v>0.2045</v>
+        <v>0.20406</v>
       </c>
       <c r="V314" t="n">
-        <v>67.84</v>
+        <v>67.7</v>
       </c>
       <c r="W314" t="n">
-        <v>67.73999999999999</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="X314" t="n">
-        <v>0.5568</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="Y314" t="n">
-        <v>23.148</v>
+        <v>23.132</v>
       </c>
       <c r="Z314" t="n">
-        <v>54.489</v>
+        <v>54.079</v>
       </c>
       <c r="AA314" t="n">
-        <v>4.875</v>
+        <v>4.814</v>
       </c>
       <c r="AB314" t="n">
-        <v>16.864</v>
+        <v>16.52</v>
       </c>
       <c r="AC314" t="n">
-        <v>16.67</v>
+        <v>16.627</v>
       </c>
       <c r="AD314" t="n">
-        <v>22.966</v>
+        <v>23.01</v>
       </c>
       <c r="AE314" t="n">
-        <v>10.864</v>
+        <v>10.682</v>
       </c>
       <c r="AF314" t="n">
-        <v>23.148</v>
+        <v>22.936</v>
       </c>
       <c r="AG314" t="n">
-        <v>10.864</v>
+        <v>10.684</v>
       </c>
       <c r="AH314" t="n">
-        <v>7.295</v>
+        <v>7.361</v>
       </c>
       <c r="AI314" t="n">
-        <v>3.534</v>
+        <v>3.451</v>
       </c>
       <c r="AJ314" t="n">
-        <v>18.568</v>
+        <v>18.801</v>
       </c>
       <c r="AK314" t="n">
-        <v>-1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AL314" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="315">
@@ -38426,22 +38426,22 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F317" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G317" t="b">
         <v>1</v>
       </c>
       <c r="H317" t="n">
-        <v>1875.864</v>
+        <v>1885.633</v>
       </c>
       <c r="I317" t="n">
-        <v>0.1664</v>
+        <v>0.1404</v>
       </c>
       <c r="J317" t="n">
-        <v>1599.4</v>
+        <v>1604.7</v>
       </c>
       <c r="K317" t="n">
         <v>35</v>
@@ -38462,70 +38462,70 @@
         <v>29</v>
       </c>
       <c r="Q317" t="n">
-        <v>120.083</v>
+        <v>119.834</v>
       </c>
       <c r="R317" t="n">
-        <v>104.01</v>
+        <v>103.764</v>
       </c>
       <c r="S317" t="n">
-        <v>16.073</v>
+        <v>16.07</v>
       </c>
       <c r="T317" t="n">
-        <v>0.30497</v>
+        <v>0.3026</v>
       </c>
       <c r="U317" t="n">
-        <v>0.15012</v>
+        <v>0.15009</v>
       </c>
       <c r="V317" t="n">
-        <v>82.05</v>
+        <v>81.95</v>
       </c>
       <c r="W317" t="n">
-        <v>71.2</v>
+        <v>71.09</v>
       </c>
       <c r="X317" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8139</v>
       </c>
       <c r="Y317" t="n">
-        <v>28.84</v>
+        <v>28.653</v>
       </c>
       <c r="Z317" t="n">
-        <v>58.024</v>
+        <v>57.839</v>
       </c>
       <c r="AA317" t="n">
-        <v>8.512</v>
+        <v>8.342000000000001</v>
       </c>
       <c r="AB317" t="n">
-        <v>23.872</v>
+        <v>23.715</v>
       </c>
       <c r="AC317" t="n">
-        <v>15.792</v>
+        <v>16.237</v>
       </c>
       <c r="AD317" t="n">
-        <v>22.384</v>
+        <v>22.872</v>
       </c>
       <c r="AE317" t="n">
-        <v>9.640000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AF317" t="n">
-        <v>21.76</v>
+        <v>22.021</v>
       </c>
       <c r="AG317" t="n">
-        <v>17.232</v>
+        <v>17.14</v>
       </c>
       <c r="AH317" t="n">
-        <v>8.640000000000001</v>
+        <v>8.666</v>
       </c>
       <c r="AI317" t="n">
-        <v>2.872</v>
+        <v>2.876</v>
       </c>
       <c r="AJ317" t="n">
-        <v>19.008</v>
+        <v>19</v>
       </c>
       <c r="AK317" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="AL317" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="318">
@@ -38546,22 +38546,22 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F318" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G318" t="b">
         <v>1</v>
       </c>
       <c r="H318" t="n">
-        <v>1637.012</v>
+        <v>1640.962</v>
       </c>
       <c r="I318" t="n">
-        <v>3.1528</v>
+        <v>3.0131</v>
       </c>
       <c r="J318" t="n">
-        <v>1455.5</v>
+        <v>1456.2</v>
       </c>
       <c r="K318" t="n">
         <v>90</v>
@@ -38582,70 +38582,70 @@
         <v>85</v>
       </c>
       <c r="Q318" t="n">
-        <v>111.579</v>
+        <v>111.372</v>
       </c>
       <c r="R318" t="n">
-        <v>100.455</v>
+        <v>100.517</v>
       </c>
       <c r="S318" t="n">
-        <v>11.123</v>
+        <v>10.854</v>
       </c>
       <c r="T318" t="n">
-        <v>0.30563</v>
+        <v>0.30398</v>
       </c>
       <c r="U318" t="n">
-        <v>0.1962</v>
+        <v>0.19707</v>
       </c>
       <c r="V318" t="n">
-        <v>78.84999999999999</v>
+        <v>78.16</v>
       </c>
       <c r="W318" t="n">
-        <v>71.23999999999999</v>
+        <v>70.75</v>
       </c>
       <c r="X318" t="n">
-        <v>0.752</v>
+        <v>0.7604</v>
       </c>
       <c r="Y318" t="n">
-        <v>28.738</v>
+        <v>28.4</v>
       </c>
       <c r="Z318" t="n">
-        <v>57.794</v>
+        <v>57.192</v>
       </c>
       <c r="AA318" t="n">
-        <v>6.481</v>
+        <v>6.452</v>
       </c>
       <c r="AB318" t="n">
-        <v>19.072</v>
+        <v>19.042</v>
       </c>
       <c r="AC318" t="n">
-        <v>14.89</v>
+        <v>14.905</v>
       </c>
       <c r="AD318" t="n">
-        <v>21.572</v>
+        <v>21.722</v>
       </c>
       <c r="AE318" t="n">
-        <v>10.386</v>
+        <v>10.301</v>
       </c>
       <c r="AF318" t="n">
-        <v>22.926</v>
+        <v>22.939</v>
       </c>
       <c r="AG318" t="n">
-        <v>17.847</v>
+        <v>17.496</v>
       </c>
       <c r="AH318" t="n">
-        <v>9.456</v>
+        <v>9.396000000000001</v>
       </c>
       <c r="AI318" t="n">
-        <v>5.232</v>
+        <v>5.281</v>
       </c>
       <c r="AJ318" t="n">
-        <v>19.089</v>
+        <v>19</v>
       </c>
       <c r="AK318" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="AL318" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="319">
@@ -38786,22 +38786,22 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F320" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G320" t="b">
         <v>1</v>
       </c>
       <c r="H320" t="n">
-        <v>1739.907</v>
+        <v>1743.526</v>
       </c>
       <c r="I320" t="n">
-        <v>2.9764</v>
+        <v>3.091</v>
       </c>
       <c r="J320" t="n">
-        <v>1554.6</v>
+        <v>1550.6</v>
       </c>
       <c r="K320" t="n">
         <v>45</v>
@@ -38822,70 +38822,70 @@
         <v>44</v>
       </c>
       <c r="Q320" t="n">
-        <v>118.458</v>
+        <v>118.247</v>
       </c>
       <c r="R320" t="n">
-        <v>103.761</v>
+        <v>103.782</v>
       </c>
       <c r="S320" t="n">
-        <v>14.697</v>
+        <v>14.465</v>
       </c>
       <c r="T320" t="n">
-        <v>0.29792</v>
+        <v>0.29847</v>
       </c>
       <c r="U320" t="n">
-        <v>0.14971</v>
+        <v>0.15109</v>
       </c>
       <c r="V320" t="n">
-        <v>82.25</v>
+        <v>81.94</v>
       </c>
       <c r="W320" t="n">
-        <v>72.08</v>
+        <v>71.94</v>
       </c>
       <c r="X320" t="n">
-        <v>0.7768</v>
+        <v>0.7836</v>
       </c>
       <c r="Y320" t="n">
-        <v>26.881</v>
+        <v>26.741</v>
       </c>
       <c r="Z320" t="n">
-        <v>58.11</v>
+        <v>57.81</v>
       </c>
       <c r="AA320" t="n">
-        <v>9.371</v>
+        <v>9.288</v>
       </c>
       <c r="AB320" t="n">
-        <v>25.751</v>
+        <v>25.398</v>
       </c>
       <c r="AC320" t="n">
-        <v>19.119</v>
+        <v>19.175</v>
       </c>
       <c r="AD320" t="n">
-        <v>25.817</v>
+        <v>25.927</v>
       </c>
       <c r="AE320" t="n">
-        <v>10.325</v>
+        <v>10.288</v>
       </c>
       <c r="AF320" t="n">
-        <v>24.107</v>
+        <v>23.968</v>
       </c>
       <c r="AG320" t="n">
-        <v>14.168</v>
+        <v>14.06</v>
       </c>
       <c r="AH320" t="n">
-        <v>7.359</v>
+        <v>7.329</v>
       </c>
       <c r="AI320" t="n">
-        <v>4.348</v>
+        <v>4.413</v>
       </c>
       <c r="AJ320" t="n">
-        <v>17.519</v>
+        <v>17.442</v>
       </c>
       <c r="AK320" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AL320" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="321">
@@ -39026,22 +39026,22 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F322" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G322" t="b">
         <v>1</v>
       </c>
       <c r="H322" t="n">
-        <v>1935.713</v>
+        <v>1949.648</v>
       </c>
       <c r="I322" t="n">
-        <v>2.1989</v>
+        <v>1.887</v>
       </c>
       <c r="J322" t="n">
-        <v>1694.9</v>
+        <v>1701.5</v>
       </c>
       <c r="K322" t="n">
         <v>13</v>
@@ -39062,70 +39062,70 @@
         <v>16</v>
       </c>
       <c r="Q322" t="n">
-        <v>121.798</v>
+        <v>121.837</v>
       </c>
       <c r="R322" t="n">
-        <v>105.674</v>
+        <v>105.792</v>
       </c>
       <c r="S322" t="n">
-        <v>16.124</v>
+        <v>16.046</v>
       </c>
       <c r="T322" t="n">
-        <v>0.28022</v>
+        <v>0.28509</v>
       </c>
       <c r="U322" t="n">
-        <v>0.1278</v>
+        <v>0.1258</v>
       </c>
       <c r="V322" t="n">
-        <v>86.92</v>
+        <v>86.44</v>
       </c>
       <c r="W322" t="n">
-        <v>75.20999999999999</v>
+        <v>74.83</v>
       </c>
       <c r="X322" t="n">
-        <v>0.7768</v>
+        <v>0.7836</v>
       </c>
       <c r="Y322" t="n">
-        <v>29.423</v>
+        <v>29.183</v>
       </c>
       <c r="Z322" t="n">
-        <v>61.394</v>
+        <v>61.328</v>
       </c>
       <c r="AA322" t="n">
-        <v>9.496</v>
+        <v>9.442</v>
       </c>
       <c r="AB322" t="n">
-        <v>26.803</v>
+        <v>27</v>
       </c>
       <c r="AC322" t="n">
-        <v>18.583</v>
+        <v>18.63</v>
       </c>
       <c r="AD322" t="n">
-        <v>23.71</v>
+        <v>23.712</v>
       </c>
       <c r="AE322" t="n">
-        <v>9.519</v>
+        <v>9.692</v>
       </c>
       <c r="AF322" t="n">
-        <v>23.968</v>
+        <v>23.844</v>
       </c>
       <c r="AG322" t="n">
-        <v>16.345</v>
+        <v>16.277</v>
       </c>
       <c r="AH322" t="n">
-        <v>8.255000000000001</v>
+        <v>8.164</v>
       </c>
       <c r="AI322" t="n">
-        <v>4.71</v>
+        <v>4.753</v>
       </c>
       <c r="AJ322" t="n">
-        <v>19.542</v>
+        <v>19.526</v>
       </c>
       <c r="AK322" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="AL322" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="323">
@@ -39386,22 +39386,22 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F325" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G325" t="b">
         <v>1</v>
       </c>
       <c r="H325" t="n">
-        <v>1963.233</v>
+        <v>1970.983</v>
       </c>
       <c r="I325" t="n">
-        <v>13.0176</v>
+        <v>12.5889</v>
       </c>
       <c r="J325" t="n">
-        <v>1642.5</v>
+        <v>1646.9</v>
       </c>
       <c r="K325" t="n">
         <v>20</v>
@@ -39422,70 +39422,70 @@
         <v>13</v>
       </c>
       <c r="Q325" t="n">
-        <v>118.864</v>
+        <v>119.48</v>
       </c>
       <c r="R325" t="n">
-        <v>100.312</v>
+        <v>100.211</v>
       </c>
       <c r="S325" t="n">
-        <v>18.552</v>
+        <v>19.27</v>
       </c>
       <c r="T325" t="n">
-        <v>0.31459</v>
+        <v>0.31508</v>
       </c>
       <c r="U325" t="n">
-        <v>0.15269</v>
+        <v>0.15305</v>
       </c>
       <c r="V325" t="n">
-        <v>80.88</v>
+        <v>81</v>
       </c>
       <c r="W325" t="n">
-        <v>68.48999999999999</v>
+        <v>68.19</v>
       </c>
       <c r="X325" t="n">
-        <v>0.8761</v>
+        <v>0.8798</v>
       </c>
       <c r="Y325" t="n">
-        <v>28.226</v>
+        <v>28.326</v>
       </c>
       <c r="Z325" t="n">
-        <v>61.093</v>
+        <v>61.013</v>
       </c>
       <c r="AA325" t="n">
-        <v>10.173</v>
+        <v>10.189</v>
       </c>
       <c r="AB325" t="n">
-        <v>28.19</v>
+        <v>28.133</v>
       </c>
       <c r="AC325" t="n">
-        <v>14.128</v>
+        <v>14.035</v>
       </c>
       <c r="AD325" t="n">
-        <v>19.605</v>
+        <v>19.362</v>
       </c>
       <c r="AE325" t="n">
-        <v>11.911</v>
+        <v>11.94</v>
       </c>
       <c r="AF325" t="n">
-        <v>25.557</v>
+        <v>25.579</v>
       </c>
       <c r="AG325" t="n">
-        <v>16.774</v>
+        <v>16.79</v>
       </c>
       <c r="AH325" t="n">
-        <v>6.65</v>
+        <v>6.593</v>
       </c>
       <c r="AI325" t="n">
-        <v>6.244</v>
+        <v>6.21</v>
       </c>
       <c r="AJ325" t="n">
-        <v>17.929</v>
+        <v>17.825</v>
       </c>
       <c r="AK325" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="AL325" t="n">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="326">
@@ -41546,22 +41546,22 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F343" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G343" t="b">
         <v>1</v>
       </c>
       <c r="H343" t="n">
-        <v>1866.219</v>
+        <v>1886.849</v>
       </c>
       <c r="I343" t="n">
-        <v>1.8886</v>
+        <v>2.1287</v>
       </c>
       <c r="J343" t="n">
-        <v>1697</v>
+        <v>1709.1</v>
       </c>
       <c r="K343" t="n">
         <v>23</v>
@@ -41582,70 +41582,70 @@
         <v>26</v>
       </c>
       <c r="Q343" t="n">
-        <v>119.651</v>
+        <v>119.67</v>
       </c>
       <c r="R343" t="n">
-        <v>108.658</v>
+        <v>108.887</v>
       </c>
       <c r="S343" t="n">
-        <v>10.993</v>
+        <v>10.782</v>
       </c>
       <c r="T343" t="n">
-        <v>0.28108</v>
+        <v>0.27872</v>
       </c>
       <c r="U343" t="n">
-        <v>0.12301</v>
+        <v>0.12218</v>
       </c>
       <c r="V343" t="n">
-        <v>83.33</v>
+        <v>83.61</v>
       </c>
       <c r="W343" t="n">
-        <v>75.84</v>
+        <v>76.25</v>
       </c>
       <c r="X343" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.7296</v>
       </c>
       <c r="Y343" t="n">
-        <v>28.027</v>
+        <v>28.269</v>
       </c>
       <c r="Z343" t="n">
-        <v>61.908</v>
+        <v>62.157</v>
       </c>
       <c r="AA343" t="n">
-        <v>11.717</v>
+        <v>11.584</v>
       </c>
       <c r="AB343" t="n">
-        <v>32.218</v>
+        <v>32.112</v>
       </c>
       <c r="AC343" t="n">
-        <v>15.556</v>
+        <v>15.37</v>
       </c>
       <c r="AD343" t="n">
-        <v>19.799</v>
+        <v>19.718</v>
       </c>
       <c r="AE343" t="n">
-        <v>9.43</v>
+        <v>9.391</v>
       </c>
       <c r="AF343" t="n">
-        <v>23.844</v>
+        <v>24.025</v>
       </c>
       <c r="AG343" t="n">
-        <v>16.027</v>
+        <v>16</v>
       </c>
       <c r="AH343" t="n">
-        <v>5.588</v>
+        <v>5.417</v>
       </c>
       <c r="AI343" t="n">
-        <v>3.071</v>
+        <v>3.022</v>
       </c>
       <c r="AJ343" t="n">
-        <v>17.226</v>
+        <v>17.441</v>
       </c>
       <c r="AK343" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AL343" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="344">
@@ -42386,22 +42386,22 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F350" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G350" t="b">
         <v>1</v>
       </c>
       <c r="H350" t="n">
-        <v>1594.458</v>
+        <v>1597.103</v>
       </c>
       <c r="I350" t="n">
-        <v>1.5103</v>
+        <v>1.5316</v>
       </c>
       <c r="J350" t="n">
-        <v>1455.6</v>
+        <v>1454.2</v>
       </c>
       <c r="K350" t="n">
         <v>112</v>
@@ -42422,70 +42422,70 @@
         <v>103</v>
       </c>
       <c r="Q350" t="n">
-        <v>107.308</v>
+        <v>107.841</v>
       </c>
       <c r="R350" t="n">
-        <v>99.486</v>
+        <v>99.536</v>
       </c>
       <c r="S350" t="n">
-        <v>7.822</v>
+        <v>8.305</v>
       </c>
       <c r="T350" t="n">
-        <v>0.32973</v>
+        <v>0.3313</v>
       </c>
       <c r="U350" t="n">
-        <v>0.17186</v>
+        <v>0.17184</v>
       </c>
       <c r="V350" t="n">
-        <v>73.04000000000001</v>
+        <v>73.48</v>
       </c>
       <c r="W350" t="n">
-        <v>67.73</v>
+        <v>67.83</v>
       </c>
       <c r="X350" t="n">
-        <v>0.7449</v>
+        <v>0.7527</v>
       </c>
       <c r="Y350" t="n">
-        <v>25.591</v>
+        <v>25.786</v>
       </c>
       <c r="Z350" t="n">
-        <v>59.203</v>
+        <v>59.394</v>
       </c>
       <c r="AA350" t="n">
-        <v>6.255</v>
+        <v>6.372</v>
       </c>
       <c r="AB350" t="n">
-        <v>18.87</v>
+        <v>18.824</v>
       </c>
       <c r="AC350" t="n">
-        <v>15.603</v>
+        <v>15.535</v>
       </c>
       <c r="AD350" t="n">
-        <v>21.89</v>
+        <v>21.688</v>
       </c>
       <c r="AE350" t="n">
-        <v>12.519</v>
+        <v>12.567</v>
       </c>
       <c r="AF350" t="n">
-        <v>24.864</v>
+        <v>24.804</v>
       </c>
       <c r="AG350" t="n">
-        <v>10.417</v>
+        <v>10.371</v>
       </c>
       <c r="AH350" t="n">
-        <v>5.316</v>
+        <v>5.465</v>
       </c>
       <c r="AI350" t="n">
-        <v>2.945</v>
+        <v>2.886</v>
       </c>
       <c r="AJ350" t="n">
-        <v>18.757</v>
+        <v>18.628</v>
       </c>
       <c r="AK350" t="n">
-        <v>10.8</v>
+        <v>17.4</v>
       </c>
       <c r="AL350" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="351">
@@ -42866,22 +42866,22 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F354" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G354" t="b">
         <v>1</v>
       </c>
       <c r="H354" t="n">
-        <v>1386.147</v>
+        <v>1383.502</v>
       </c>
       <c r="I354" t="n">
-        <v>2.4009</v>
+        <v>2.4068</v>
       </c>
       <c r="J354" t="n">
-        <v>1489.8</v>
+        <v>1495.4</v>
       </c>
       <c r="K354" t="n">
         <v>184</v>
@@ -42902,70 +42902,70 @@
         <v>175</v>
       </c>
       <c r="Q354" t="n">
-        <v>108.328</v>
+        <v>108.003</v>
       </c>
       <c r="R354" t="n">
-        <v>110.831</v>
+        <v>111.409</v>
       </c>
       <c r="S354" t="n">
-        <v>-2.502</v>
+        <v>-3.406</v>
       </c>
       <c r="T354" t="n">
-        <v>0.26682</v>
+        <v>0.26673</v>
       </c>
       <c r="U354" t="n">
-        <v>0.16996</v>
+        <v>0.17052</v>
       </c>
       <c r="V354" t="n">
-        <v>74.90000000000001</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="W354" t="n">
-        <v>76.67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="X354" t="n">
-        <v>0.5392</v>
+        <v>0.5101</v>
       </c>
       <c r="Y354" t="n">
-        <v>27.02</v>
+        <v>27.032</v>
       </c>
       <c r="Z354" t="n">
-        <v>57.961</v>
+        <v>58.009</v>
       </c>
       <c r="AA354" t="n">
-        <v>7.79</v>
+        <v>7.765</v>
       </c>
       <c r="AB354" t="n">
-        <v>22.176</v>
+        <v>22.168</v>
       </c>
       <c r="AC354" t="n">
-        <v>13.067</v>
+        <v>12.881</v>
       </c>
       <c r="AD354" t="n">
-        <v>17.956</v>
+        <v>17.742</v>
       </c>
       <c r="AE354" t="n">
-        <v>8.502000000000001</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="AF354" t="n">
-        <v>22.592</v>
+        <v>22.53</v>
       </c>
       <c r="AG354" t="n">
-        <v>14.553</v>
+        <v>14.371</v>
       </c>
       <c r="AH354" t="n">
-        <v>6.881</v>
+        <v>6.916</v>
       </c>
       <c r="AI354" t="n">
-        <v>3</v>
+        <v>3.043</v>
       </c>
       <c r="AJ354" t="n">
-        <v>16.202</v>
+        <v>16.029</v>
       </c>
       <c r="AK354" t="n">
-        <v>0.2</v>
+        <v>-4.2</v>
       </c>
       <c r="AL354" t="n">
-        <v>0.6</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="355">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -866,22 +866,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1704.461</v>
+        <v>1707.887</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8839</v>
+        <v>1.9745</v>
       </c>
       <c r="J4" t="n">
-        <v>1481.1</v>
+        <v>1479.2</v>
       </c>
       <c r="K4" t="n">
         <v>61</v>
@@ -902,70 +902,70 @@
         <v>52</v>
       </c>
       <c r="Q4" t="n">
-        <v>121.819</v>
+        <v>121.636</v>
       </c>
       <c r="R4" t="n">
-        <v>104.079</v>
+        <v>104.361</v>
       </c>
       <c r="S4" t="n">
-        <v>17.74</v>
+        <v>17.275</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2847</v>
+        <v>0.28865</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1512</v>
+        <v>0.14997</v>
       </c>
       <c r="V4" t="n">
-        <v>87.01000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="W4" t="n">
-        <v>74.39</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8403</v>
+        <v>0.8452</v>
       </c>
       <c r="Y4" t="n">
-        <v>31.037</v>
+        <v>31.173</v>
       </c>
       <c r="Z4" t="n">
-        <v>62.271</v>
+        <v>62.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.875</v>
+        <v>10.867</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.025</v>
+        <v>28.302</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.061</v>
+        <v>13.591</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.567</v>
+        <v>18.105</v>
       </c>
       <c r="AE4" t="n">
-        <v>9.808</v>
+        <v>9.974</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.412</v>
+        <v>25.292</v>
       </c>
       <c r="AG4" t="n">
-        <v>17.9</v>
+        <v>17.849</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.281</v>
+        <v>7.23</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.869</v>
+        <v>2.885</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16.454</v>
+        <v>16.243</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.8</v>
+        <v>13</v>
       </c>
       <c r="AL4" t="n">
-        <v>12.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="5">
@@ -1826,22 +1826,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2262.937</v>
+        <v>2272.125</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0872</v>
+        <v>6.8151</v>
       </c>
       <c r="J12" t="n">
-        <v>1758.1</v>
+        <v>1769.2</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
@@ -1862,70 +1862,70 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>121.14</v>
+        <v>121.138</v>
       </c>
       <c r="R12" t="n">
-        <v>96.664</v>
+        <v>97.108</v>
       </c>
       <c r="S12" t="n">
-        <v>24.476</v>
+        <v>24.03</v>
       </c>
       <c r="T12" t="n">
-        <v>0.29415</v>
+        <v>0.29246</v>
       </c>
       <c r="U12" t="n">
-        <v>0.15097</v>
+        <v>0.1497</v>
       </c>
       <c r="V12" t="n">
-        <v>86.33</v>
+        <v>86.09</v>
       </c>
       <c r="W12" t="n">
-        <v>68.73</v>
+        <v>68.84</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9399</v>
+        <v>0.9416</v>
       </c>
       <c r="Y12" t="n">
-        <v>30.738</v>
+        <v>30.515</v>
       </c>
       <c r="Z12" t="n">
-        <v>61.035</v>
+        <v>60.799</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.897</v>
+        <v>5.883</v>
       </c>
       <c r="AB12" t="n">
-        <v>16.421</v>
+        <v>16.297</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.954</v>
+        <v>19.177</v>
       </c>
       <c r="AD12" t="n">
-        <v>25.976</v>
+        <v>26.095</v>
       </c>
       <c r="AE12" t="n">
-        <v>12.082</v>
+        <v>11.976</v>
       </c>
       <c r="AF12" t="n">
-        <v>28.701</v>
+        <v>28.655</v>
       </c>
       <c r="AG12" t="n">
-        <v>17.197</v>
+        <v>16.879</v>
       </c>
       <c r="AH12" t="n">
-        <v>8.007999999999999</v>
+        <v>7.778</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.3</v>
+        <v>4.218</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15.983</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>14.6</v>
+        <v>11</v>
       </c>
       <c r="AL12" t="n">
-        <v>8.699999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="13">
@@ -2306,22 +2306,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1956.536</v>
+        <v>1961.738</v>
       </c>
       <c r="I16" t="n">
-        <v>5.3805</v>
+        <v>5.2535</v>
       </c>
       <c r="J16" t="n">
-        <v>1728.4</v>
+        <v>1726.7</v>
       </c>
       <c r="K16" t="n">
         <v>18</v>
@@ -2342,70 +2342,70 @@
         <v>18</v>
       </c>
       <c r="Q16" t="n">
-        <v>122.826</v>
+        <v>122.845</v>
       </c>
       <c r="R16" t="n">
-        <v>109.162</v>
+        <v>109.473</v>
       </c>
       <c r="S16" t="n">
-        <v>13.664</v>
+        <v>13.372</v>
       </c>
       <c r="T16" t="n">
-        <v>0.30257</v>
+        <v>0.30449</v>
       </c>
       <c r="U16" t="n">
-        <v>0.11957</v>
+        <v>0.11969</v>
       </c>
       <c r="V16" t="n">
-        <v>89.90000000000001</v>
+        <v>90.09</v>
       </c>
       <c r="W16" t="n">
-        <v>79.93000000000001</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7523</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>32.119</v>
+        <v>32.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>64.217</v>
+        <v>64.40300000000001</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.186</v>
+        <v>8.103</v>
       </c>
       <c r="AB16" t="n">
-        <v>21.403</v>
+        <v>21.314</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.474</v>
+        <v>17.681</v>
       </c>
       <c r="AD16" t="n">
-        <v>23.363</v>
+        <v>23.668</v>
       </c>
       <c r="AE16" t="n">
-        <v>10.027</v>
+        <v>10.231</v>
       </c>
       <c r="AF16" t="n">
-        <v>23.164</v>
+        <v>23.343</v>
       </c>
       <c r="AG16" t="n">
-        <v>16.902</v>
+        <v>16.863</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.31</v>
+        <v>7.377</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.266</v>
+        <v>5.087</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17.248</v>
+        <v>16.971</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="17">
@@ -5786,22 +5786,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F45" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1452.63</v>
+        <v>1449.52</v>
       </c>
       <c r="I45" t="n">
-        <v>1.4072</v>
+        <v>1.4733</v>
       </c>
       <c r="J45" t="n">
-        <v>1502.2</v>
+        <v>1509.6</v>
       </c>
       <c r="K45" t="n">
         <v>191</v>
@@ -5822,70 +5822,70 @@
         <v>183</v>
       </c>
       <c r="Q45" t="n">
-        <v>112.833</v>
+        <v>111.997</v>
       </c>
       <c r="R45" t="n">
-        <v>113.525</v>
+        <v>114.054</v>
       </c>
       <c r="S45" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-2.057</v>
       </c>
       <c r="T45" t="n">
-        <v>0.29997</v>
+        <v>0.3044</v>
       </c>
       <c r="U45" t="n">
-        <v>0.16626</v>
+        <v>0.16872</v>
       </c>
       <c r="V45" t="n">
-        <v>73.39</v>
+        <v>72.91</v>
       </c>
       <c r="W45" t="n">
-        <v>73.95</v>
+        <v>74.39</v>
       </c>
       <c r="X45" t="n">
-        <v>0.5054</v>
+        <v>0.48</v>
       </c>
       <c r="Y45" t="n">
-        <v>25.261</v>
+        <v>24.94</v>
       </c>
       <c r="Z45" t="n">
-        <v>55.179</v>
+        <v>55.13</v>
       </c>
       <c r="AA45" t="n">
-        <v>8.483000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AB45" t="n">
-        <v>24.472</v>
+        <v>24.71</v>
       </c>
       <c r="AC45" t="n">
-        <v>14.173</v>
+        <v>14.41</v>
       </c>
       <c r="AD45" t="n">
-        <v>19.751</v>
+        <v>20.11</v>
       </c>
       <c r="AE45" t="n">
-        <v>9.598000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="AF45" t="n">
-        <v>22.144</v>
+        <v>22.11</v>
       </c>
       <c r="AG45" t="n">
-        <v>13.242</v>
+        <v>12.92</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.516</v>
+        <v>4.68</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.536</v>
+        <v>3.43</v>
       </c>
       <c r="AJ45" t="n">
-        <v>17.101</v>
+        <v>16.87</v>
       </c>
       <c r="AK45" t="n">
-        <v>-2.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AL45" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="46">
@@ -7346,22 +7346,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F58" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>2067.868</v>
+        <v>2050.719</v>
       </c>
       <c r="I58" t="n">
-        <v>7.6929</v>
+        <v>7.1741</v>
       </c>
       <c r="J58" t="n">
-        <v>1657.6</v>
+        <v>1670.2</v>
       </c>
       <c r="K58" t="n">
         <v>11</v>
@@ -7382,70 +7382,70 @@
         <v>9</v>
       </c>
       <c r="Q58" t="n">
-        <v>117.246</v>
+        <v>116.057</v>
       </c>
       <c r="R58" t="n">
-        <v>97.10299999999999</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="S58" t="n">
-        <v>20.143</v>
+        <v>18.046</v>
       </c>
       <c r="T58" t="n">
-        <v>0.2963</v>
+        <v>0.30128</v>
       </c>
       <c r="U58" t="n">
-        <v>0.1567</v>
+        <v>0.16031</v>
       </c>
       <c r="V58" t="n">
-        <v>78.16</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="W58" t="n">
-        <v>64.77</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="X58" t="n">
-        <v>0.88</v>
+        <v>0.845</v>
       </c>
       <c r="Y58" t="n">
-        <v>28.57</v>
+        <v>28.207</v>
       </c>
       <c r="Z58" t="n">
-        <v>58.73</v>
+        <v>58.622</v>
       </c>
       <c r="AA58" t="n">
-        <v>8.48</v>
+        <v>8.273999999999999</v>
       </c>
       <c r="AB58" t="n">
-        <v>23.8</v>
+        <v>23.604</v>
       </c>
       <c r="AC58" t="n">
-        <v>12.54</v>
+        <v>12.573</v>
       </c>
       <c r="AD58" t="n">
-        <v>17.56</v>
+        <v>17.555</v>
       </c>
       <c r="AE58" t="n">
-        <v>10.24</v>
+        <v>10.473</v>
       </c>
       <c r="AF58" t="n">
-        <v>24</v>
+        <v>23.914</v>
       </c>
       <c r="AG58" t="n">
-        <v>18.63</v>
+        <v>18.314</v>
       </c>
       <c r="AH58" t="n">
-        <v>6.88</v>
+        <v>6.874</v>
       </c>
       <c r="AI58" t="n">
-        <v>5.37</v>
+        <v>5.234</v>
       </c>
       <c r="AJ58" t="n">
-        <v>18.13</v>
+        <v>18.069</v>
       </c>
       <c r="AK58" t="n">
-        <v>14.2</v>
+        <v>3.8</v>
       </c>
       <c r="AL58" t="n">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="59">
@@ -7586,22 +7586,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G60" t="b">
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>1493.851</v>
+        <v>1478.362</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.2607</v>
+        <v>-1.0235</v>
       </c>
       <c r="J60" t="n">
-        <v>1488.6</v>
+        <v>1502.5</v>
       </c>
       <c r="K60" t="n">
         <v>158</v>
@@ -7622,70 +7622,70 @@
         <v>141</v>
       </c>
       <c r="Q60" t="n">
-        <v>119.99</v>
+        <v>120.036</v>
       </c>
       <c r="R60" t="n">
-        <v>116.746</v>
+        <v>118.395</v>
       </c>
       <c r="S60" t="n">
-        <v>3.244</v>
+        <v>1.641</v>
       </c>
       <c r="T60" t="n">
-        <v>0.27858</v>
+        <v>0.29566</v>
       </c>
       <c r="U60" t="n">
-        <v>0.15805</v>
+        <v>0.1555</v>
       </c>
       <c r="V60" t="n">
-        <v>86.56</v>
+        <v>85.63</v>
       </c>
       <c r="W60" t="n">
-        <v>84.56999999999999</v>
+        <v>84.67</v>
       </c>
       <c r="X60" t="n">
-        <v>0.5278</v>
+        <v>0.4926</v>
       </c>
       <c r="Y60" t="n">
-        <v>30.1</v>
+        <v>29.924</v>
       </c>
       <c r="Z60" t="n">
-        <v>61.301</v>
+        <v>61.648</v>
       </c>
       <c r="AA60" t="n">
-        <v>12.31</v>
+        <v>12.137</v>
       </c>
       <c r="AB60" t="n">
-        <v>31.664</v>
+        <v>31.846</v>
       </c>
       <c r="AC60" t="n">
-        <v>14.053</v>
+        <v>13.64</v>
       </c>
       <c r="AD60" t="n">
-        <v>18.935</v>
+        <v>18.421</v>
       </c>
       <c r="AE60" t="n">
-        <v>8.762</v>
+        <v>9.375</v>
       </c>
       <c r="AF60" t="n">
-        <v>22.75</v>
+        <v>22.276</v>
       </c>
       <c r="AG60" t="n">
-        <v>19.884</v>
+        <v>20.021</v>
       </c>
       <c r="AH60" t="n">
-        <v>5.826</v>
+        <v>5.743</v>
       </c>
       <c r="AI60" t="n">
-        <v>2.78</v>
+        <v>2.773</v>
       </c>
       <c r="AJ60" t="n">
-        <v>20.12</v>
+        <v>19.775</v>
       </c>
       <c r="AK60" t="n">
-        <v>1</v>
+        <v>-0.2</v>
       </c>
       <c r="AL60" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="61">
@@ -8546,22 +8546,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F68" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1669.741</v>
+        <v>1688.075</v>
       </c>
       <c r="I68" t="n">
-        <v>-2.3756</v>
+        <v>-2.1851</v>
       </c>
       <c r="J68" t="n">
-        <v>1559.7</v>
+        <v>1570.2</v>
       </c>
       <c r="K68" t="n">
         <v>79</v>
@@ -8582,70 +8582,70 @@
         <v>75</v>
       </c>
       <c r="Q68" t="n">
-        <v>109.857</v>
+        <v>109.548</v>
       </c>
       <c r="R68" t="n">
-        <v>101.927</v>
+        <v>101.885</v>
       </c>
       <c r="S68" t="n">
-        <v>7.93</v>
+        <v>7.662</v>
       </c>
       <c r="T68" t="n">
-        <v>0.25593</v>
+        <v>0.25276</v>
       </c>
       <c r="U68" t="n">
-        <v>0.17025</v>
+        <v>0.1736</v>
       </c>
       <c r="V68" t="n">
-        <v>74.79000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="W68" t="n">
-        <v>69.81999999999999</v>
+        <v>69.87</v>
       </c>
       <c r="X68" t="n">
-        <v>0.6914</v>
+        <v>0.7005</v>
       </c>
       <c r="Y68" t="n">
-        <v>24.017</v>
+        <v>24.007</v>
       </c>
       <c r="Z68" t="n">
-        <v>53.543</v>
+        <v>53.456</v>
       </c>
       <c r="AA68" t="n">
-        <v>7.624</v>
+        <v>7.694</v>
       </c>
       <c r="AB68" t="n">
-        <v>22.241</v>
+        <v>22.46</v>
       </c>
       <c r="AC68" t="n">
-        <v>19.13</v>
+        <v>18.923</v>
       </c>
       <c r="AD68" t="n">
-        <v>25.408</v>
+        <v>25.026</v>
       </c>
       <c r="AE68" t="n">
-        <v>8.02</v>
+        <v>7.928</v>
       </c>
       <c r="AF68" t="n">
-        <v>22.778</v>
+        <v>22.969</v>
       </c>
       <c r="AG68" t="n">
-        <v>14.296</v>
+        <v>14.341</v>
       </c>
       <c r="AH68" t="n">
-        <v>8.481</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="AI68" t="n">
-        <v>4.093</v>
+        <v>4.173</v>
       </c>
       <c r="AJ68" t="n">
-        <v>16.642</v>
+        <v>16.891</v>
       </c>
       <c r="AK68" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL68" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="69">
@@ -9506,22 +9506,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F76" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>2189.206</v>
+        <v>2195.855</v>
       </c>
       <c r="I76" t="n">
-        <v>3.7126</v>
+        <v>3.7176</v>
       </c>
       <c r="J76" t="n">
-        <v>1703.5</v>
+        <v>1712.3</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
@@ -9542,70 +9542,70 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>122.893</v>
+        <v>122.742</v>
       </c>
       <c r="R76" t="n">
-        <v>94.026</v>
+        <v>94.669</v>
       </c>
       <c r="S76" t="n">
-        <v>28.866</v>
+        <v>28.073</v>
       </c>
       <c r="T76" t="n">
-        <v>0.28942</v>
+        <v>0.29815</v>
       </c>
       <c r="U76" t="n">
-        <v>0.1548</v>
+        <v>0.15408</v>
       </c>
       <c r="V76" t="n">
-        <v>82.43000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="W76" t="n">
-        <v>62.92</v>
+        <v>63.22</v>
       </c>
       <c r="X76" t="n">
-        <v>0.9401</v>
+        <v>0.9418</v>
       </c>
       <c r="Y76" t="n">
-        <v>28.66</v>
+        <v>28.578</v>
       </c>
       <c r="Z76" t="n">
-        <v>58.116</v>
+        <v>58.484</v>
       </c>
       <c r="AA76" t="n">
-        <v>9.119999999999999</v>
+        <v>9.076000000000001</v>
       </c>
       <c r="AB76" t="n">
-        <v>25.917</v>
+        <v>25.902</v>
       </c>
       <c r="AC76" t="n">
-        <v>15.993</v>
+        <v>15.971</v>
       </c>
       <c r="AD76" t="n">
-        <v>22.12</v>
+        <v>22.036</v>
       </c>
       <c r="AE76" t="n">
-        <v>11.246</v>
+        <v>11.622</v>
       </c>
       <c r="AF76" t="n">
-        <v>27.268</v>
+        <v>26.964</v>
       </c>
       <c r="AG76" t="n">
-        <v>16.906</v>
+        <v>16.92</v>
       </c>
       <c r="AH76" t="n">
-        <v>7.803</v>
+        <v>7.775</v>
       </c>
       <c r="AI76" t="n">
-        <v>3.306</v>
+        <v>3.24</v>
       </c>
       <c r="AJ76" t="n">
-        <v>15.837</v>
+        <v>15.676</v>
       </c>
       <c r="AK76" t="n">
-        <v>16.6</v>
+        <v>12.2</v>
       </c>
       <c r="AL76" t="n">
-        <v>19.8</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="77">
@@ -11306,22 +11306,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F91" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G91" t="b">
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>2024.856</v>
+        <v>2006.659</v>
       </c>
       <c r="I91" t="n">
-        <v>3.1754</v>
+        <v>3.4651</v>
       </c>
       <c r="J91" t="n">
-        <v>1715.4</v>
+        <v>1722.9</v>
       </c>
       <c r="K91" t="n">
         <v>4</v>
@@ -11342,70 +11342,70 @@
         <v>4</v>
       </c>
       <c r="Q91" t="n">
-        <v>120.018</v>
+        <v>119.994</v>
       </c>
       <c r="R91" t="n">
-        <v>98.413</v>
+        <v>100.186</v>
       </c>
       <c r="S91" t="n">
-        <v>21.606</v>
+        <v>19.808</v>
       </c>
       <c r="T91" t="n">
-        <v>0.33391</v>
+        <v>0.33419</v>
       </c>
       <c r="U91" t="n">
-        <v>0.15921</v>
+        <v>0.15683</v>
       </c>
       <c r="V91" t="n">
-        <v>87.01000000000001</v>
+        <v>86.66</v>
       </c>
       <c r="W91" t="n">
-        <v>71.31999999999999</v>
+        <v>72.19</v>
       </c>
       <c r="X91" t="n">
-        <v>0.8145</v>
+        <v>0.78</v>
       </c>
       <c r="Y91" t="n">
-        <v>30.841</v>
+        <v>30.9</v>
       </c>
       <c r="Z91" t="n">
-        <v>64.554</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AA91" t="n">
-        <v>7.39</v>
+        <v>7.54</v>
       </c>
       <c r="AB91" t="n">
-        <v>24.081</v>
+        <v>24</v>
       </c>
       <c r="AC91" t="n">
-        <v>17.941</v>
+        <v>18</v>
       </c>
       <c r="AD91" t="n">
-        <v>25.302</v>
+        <v>25.13</v>
       </c>
       <c r="AE91" t="n">
-        <v>14.754</v>
+        <v>14.45</v>
       </c>
       <c r="AF91" t="n">
-        <v>28.754</v>
+        <v>28.17</v>
       </c>
       <c r="AG91" t="n">
-        <v>16.688</v>
+        <v>16.92</v>
       </c>
       <c r="AH91" t="n">
-        <v>6.774</v>
+        <v>6.8</v>
       </c>
       <c r="AI91" t="n">
-        <v>5.134</v>
+        <v>5.04</v>
       </c>
       <c r="AJ91" t="n">
-        <v>17.763</v>
+        <v>17.8</v>
       </c>
       <c r="AK91" t="n">
-        <v>19.2</v>
+        <v>13.2</v>
       </c>
       <c r="AL91" t="n">
-        <v>17.7</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="92">
@@ -13586,22 +13586,22 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F110" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G110" t="b">
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>1513.711</v>
+        <v>1490.535</v>
       </c>
       <c r="I110" t="n">
-        <v>2.6769</v>
+        <v>2.799</v>
       </c>
       <c r="J110" t="n">
-        <v>1467.8</v>
+        <v>1465.2</v>
       </c>
       <c r="K110" t="n">
         <v>149</v>
@@ -13622,70 +13622,70 @@
         <v>150</v>
       </c>
       <c r="Q110" t="n">
-        <v>109.394</v>
+        <v>107.967</v>
       </c>
       <c r="R110" t="n">
-        <v>104.645</v>
+        <v>103.76</v>
       </c>
       <c r="S110" t="n">
-        <v>4.749</v>
+        <v>4.207</v>
       </c>
       <c r="T110" t="n">
-        <v>0.24163</v>
+        <v>0.24077</v>
       </c>
       <c r="U110" t="n">
-        <v>0.16367</v>
+        <v>0.16111</v>
       </c>
       <c r="V110" t="n">
-        <v>70.29000000000001</v>
+        <v>69.61</v>
       </c>
       <c r="W110" t="n">
-        <v>67.54000000000001</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="X110" t="n">
-        <v>0.5992</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="Y110" t="n">
-        <v>25.413</v>
+        <v>25.352</v>
       </c>
       <c r="Z110" t="n">
-        <v>54.551</v>
+        <v>55.113</v>
       </c>
       <c r="AA110" t="n">
-        <v>7.668</v>
+        <v>7.598</v>
       </c>
       <c r="AB110" t="n">
-        <v>21.725</v>
+        <v>21.619</v>
       </c>
       <c r="AC110" t="n">
-        <v>11.794</v>
+        <v>11.404</v>
       </c>
       <c r="AD110" t="n">
-        <v>14.611</v>
+        <v>14.228</v>
       </c>
       <c r="AE110" t="n">
-        <v>7.15</v>
+        <v>7.126</v>
       </c>
       <c r="AF110" t="n">
-        <v>22.239</v>
+        <v>22.256</v>
       </c>
       <c r="AG110" t="n">
-        <v>14.211</v>
+        <v>14.141</v>
       </c>
       <c r="AH110" t="n">
-        <v>7.275</v>
+        <v>7.331</v>
       </c>
       <c r="AI110" t="n">
-        <v>3.668</v>
+        <v>3.598</v>
       </c>
       <c r="AJ110" t="n">
-        <v>13.482</v>
+        <v>13.328</v>
       </c>
       <c r="AK110" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AL110" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="111">
@@ -13706,22 +13706,22 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F111" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G111" t="b">
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>1538.805</v>
+        <v>1549.123</v>
       </c>
       <c r="I111" t="n">
-        <v>3.0942</v>
+        <v>2.9832</v>
       </c>
       <c r="J111" t="n">
-        <v>1444.2</v>
+        <v>1452.3</v>
       </c>
       <c r="K111" t="n">
         <v>115</v>
@@ -13742,70 +13742,70 @@
         <v>112</v>
       </c>
       <c r="Q111" t="n">
-        <v>108.455</v>
+        <v>108.144</v>
       </c>
       <c r="R111" t="n">
-        <v>96.833</v>
+        <v>96.693</v>
       </c>
       <c r="S111" t="n">
-        <v>11.621</v>
+        <v>11.451</v>
       </c>
       <c r="T111" t="n">
-        <v>0.25546</v>
+        <v>0.25834</v>
       </c>
       <c r="U111" t="n">
-        <v>0.18434</v>
+        <v>0.18506</v>
       </c>
       <c r="V111" t="n">
-        <v>78.98999999999999</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="W111" t="n">
-        <v>70.43000000000001</v>
+        <v>70.23</v>
       </c>
       <c r="X111" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7361</v>
       </c>
       <c r="Y111" t="n">
-        <v>26.568</v>
+        <v>26.387</v>
       </c>
       <c r="Z111" t="n">
-        <v>57.966</v>
+        <v>58.064</v>
       </c>
       <c r="AA111" t="n">
-        <v>7.227</v>
+        <v>7.177</v>
       </c>
       <c r="AB111" t="n">
-        <v>22.989</v>
+        <v>22.478</v>
       </c>
       <c r="AC111" t="n">
-        <v>18.625</v>
+        <v>18.397</v>
       </c>
       <c r="AD111" t="n">
-        <v>25.045</v>
+        <v>24.685</v>
       </c>
       <c r="AE111" t="n">
-        <v>9.455</v>
+        <v>9.537000000000001</v>
       </c>
       <c r="AF111" t="n">
-        <v>26.841</v>
+        <v>26.693</v>
       </c>
       <c r="AG111" t="n">
-        <v>13.193</v>
+        <v>12.958</v>
       </c>
       <c r="AH111" t="n">
-        <v>6.557</v>
+        <v>6.658</v>
       </c>
       <c r="AI111" t="n">
-        <v>3.875</v>
+        <v>3.955</v>
       </c>
       <c r="AJ111" t="n">
-        <v>18.102</v>
+        <v>18.001</v>
       </c>
       <c r="AK111" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AL111" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="112">
@@ -14186,22 +14186,22 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F115" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G115" t="b">
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>2120.903</v>
+        <v>2111.715</v>
       </c>
       <c r="I115" t="n">
-        <v>1.2885</v>
+        <v>1.2196</v>
       </c>
       <c r="J115" t="n">
-        <v>1724.5</v>
+        <v>1742.7</v>
       </c>
       <c r="K115" t="n">
         <v>6</v>
@@ -14222,70 +14222,70 @@
         <v>7</v>
       </c>
       <c r="Q115" t="n">
-        <v>117.484</v>
+        <v>117.346</v>
       </c>
       <c r="R115" t="n">
-        <v>94.626</v>
+        <v>95.8</v>
       </c>
       <c r="S115" t="n">
-        <v>22.858</v>
+        <v>21.546</v>
       </c>
       <c r="T115" t="n">
-        <v>0.33581</v>
+        <v>0.33855</v>
       </c>
       <c r="U115" t="n">
-        <v>0.1237</v>
+        <v>0.12356</v>
       </c>
       <c r="V115" t="n">
-        <v>77.16</v>
+        <v>77.12</v>
       </c>
       <c r="W115" t="n">
-        <v>62.21</v>
+        <v>63</v>
       </c>
       <c r="X115" t="n">
-        <v>0.85</v>
+        <v>0.8159</v>
       </c>
       <c r="Y115" t="n">
-        <v>27.7</v>
+        <v>27.767</v>
       </c>
       <c r="Z115" t="n">
-        <v>61.58</v>
+        <v>61.756</v>
       </c>
       <c r="AA115" t="n">
-        <v>8.83</v>
+        <v>8.787000000000001</v>
       </c>
       <c r="AB115" t="n">
-        <v>25.23</v>
+        <v>25.138</v>
       </c>
       <c r="AC115" t="n">
-        <v>12.93</v>
+        <v>12.797</v>
       </c>
       <c r="AD115" t="n">
-        <v>16.72</v>
+        <v>16.593</v>
       </c>
       <c r="AE115" t="n">
-        <v>11.44</v>
+        <v>11.514</v>
       </c>
       <c r="AF115" t="n">
-        <v>22.7</v>
+        <v>22.544</v>
       </c>
       <c r="AG115" t="n">
-        <v>14.69</v>
+        <v>14.661</v>
       </c>
       <c r="AH115" t="n">
-        <v>7.81</v>
+        <v>7.7</v>
       </c>
       <c r="AI115" t="n">
-        <v>3.88</v>
+        <v>3.845</v>
       </c>
       <c r="AJ115" t="n">
-        <v>17.91</v>
+        <v>18.057</v>
       </c>
       <c r="AK115" t="n">
-        <v>17.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AL115" t="n">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="116">
@@ -14426,22 +14426,22 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F117" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G117" t="b">
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>1405.975</v>
+        <v>1407.766</v>
       </c>
       <c r="I117" t="n">
-        <v>3.0696</v>
+        <v>2.9318</v>
       </c>
       <c r="J117" t="n">
-        <v>1374.8</v>
+        <v>1372.4</v>
       </c>
       <c r="K117" t="n">
         <v>202</v>
@@ -14462,70 +14462,70 @@
         <v>202</v>
       </c>
       <c r="Q117" t="n">
-        <v>108.811</v>
+        <v>109.065</v>
       </c>
       <c r="R117" t="n">
-        <v>97.937</v>
+        <v>98.31699999999999</v>
       </c>
       <c r="S117" t="n">
-        <v>10.874</v>
+        <v>10.748</v>
       </c>
       <c r="T117" t="n">
-        <v>0.31421</v>
+        <v>0.31905</v>
       </c>
       <c r="U117" t="n">
-        <v>0.18708</v>
+        <v>0.18558</v>
       </c>
       <c r="V117" t="n">
-        <v>75.20999999999999</v>
+        <v>74.94</v>
       </c>
       <c r="W117" t="n">
-        <v>67.88</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="X117" t="n">
-        <v>0.6473</v>
+        <v>0.6591</v>
       </c>
       <c r="Y117" t="n">
-        <v>25.187</v>
+        <v>24.932</v>
       </c>
       <c r="Z117" t="n">
-        <v>56.056</v>
+        <v>55.92</v>
       </c>
       <c r="AA117" t="n">
-        <v>6.681</v>
+        <v>6.636</v>
       </c>
       <c r="AB117" t="n">
-        <v>19.139</v>
+        <v>19.17</v>
       </c>
       <c r="AC117" t="n">
-        <v>18.159</v>
+        <v>18.443</v>
       </c>
       <c r="AD117" t="n">
-        <v>24.526</v>
+        <v>24.841</v>
       </c>
       <c r="AE117" t="n">
-        <v>10.483</v>
+        <v>10.716</v>
       </c>
       <c r="AF117" t="n">
-        <v>22.755</v>
+        <v>22.682</v>
       </c>
       <c r="AG117" t="n">
-        <v>15.411</v>
+        <v>15.227</v>
       </c>
       <c r="AH117" t="n">
-        <v>8.637</v>
+        <v>8.625</v>
       </c>
       <c r="AI117" t="n">
-        <v>3.907</v>
+        <v>3.898</v>
       </c>
       <c r="AJ117" t="n">
-        <v>18.668</v>
+        <v>18.636</v>
       </c>
       <c r="AK117" t="n">
-        <v>20.6</v>
+        <v>15.4</v>
       </c>
       <c r="AL117" t="n">
-        <v>20.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118">
@@ -16826,22 +16826,22 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F137" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G137" t="b">
         <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>1514.853</v>
+        <v>1521.308</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.2575</v>
+        <v>-0.1615</v>
       </c>
       <c r="J137" t="n">
-        <v>1473.6</v>
+        <v>1474.6</v>
       </c>
       <c r="K137" t="n">
         <v>178</v>
@@ -16862,70 +16862,70 @@
         <v>170</v>
       </c>
       <c r="Q137" t="n">
-        <v>111.256</v>
+        <v>111.121</v>
       </c>
       <c r="R137" t="n">
-        <v>108.753</v>
+        <v>108.097</v>
       </c>
       <c r="S137" t="n">
-        <v>2.503</v>
+        <v>3.024</v>
       </c>
       <c r="T137" t="n">
-        <v>0.33921</v>
+        <v>0.34498</v>
       </c>
       <c r="U137" t="n">
-        <v>0.16722</v>
+        <v>0.16501</v>
       </c>
       <c r="V137" t="n">
-        <v>80.84999999999999</v>
+        <v>80.47</v>
       </c>
       <c r="W137" t="n">
-        <v>78.98</v>
+        <v>78.27</v>
       </c>
       <c r="X137" t="n">
-        <v>0.5704</v>
+        <v>0.584</v>
       </c>
       <c r="Y137" t="n">
-        <v>26.24</v>
+        <v>26.064</v>
       </c>
       <c r="Z137" t="n">
-        <v>60.843</v>
+        <v>61.28</v>
       </c>
       <c r="AA137" t="n">
-        <v>8.941000000000001</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="AB137" t="n">
-        <v>26.52</v>
+        <v>26.592</v>
       </c>
       <c r="AC137" t="n">
-        <v>18.882</v>
+        <v>18.736</v>
       </c>
       <c r="AD137" t="n">
-        <v>26.973</v>
+        <v>26.712</v>
       </c>
       <c r="AE137" t="n">
-        <v>12.241</v>
+        <v>12.632</v>
       </c>
       <c r="AF137" t="n">
-        <v>23.891</v>
+        <v>23.856</v>
       </c>
       <c r="AG137" t="n">
-        <v>13.67</v>
+        <v>13.6</v>
       </c>
       <c r="AH137" t="n">
-        <v>6.754</v>
+        <v>6.632</v>
       </c>
       <c r="AI137" t="n">
-        <v>5.089</v>
+        <v>5.128</v>
       </c>
       <c r="AJ137" t="n">
-        <v>21.024</v>
+        <v>20.912</v>
       </c>
       <c r="AK137" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AL137" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="138">
@@ -18266,22 +18266,22 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F149" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G149" t="b">
         <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>1515.177</v>
+        <v>1508.721</v>
       </c>
       <c r="I149" t="n">
-        <v>-1.3208</v>
+        <v>-1.1024</v>
       </c>
       <c r="J149" t="n">
-        <v>1463.6</v>
+        <v>1466</v>
       </c>
       <c r="K149" t="n">
         <v>208</v>
@@ -18302,70 +18302,70 @@
         <v>213</v>
       </c>
       <c r="Q149" t="n">
-        <v>104.019</v>
+        <v>103.618</v>
       </c>
       <c r="R149" t="n">
-        <v>103.396</v>
+        <v>103.731</v>
       </c>
       <c r="S149" t="n">
-        <v>0.623</v>
+        <v>-0.113</v>
       </c>
       <c r="T149" t="n">
-        <v>0.32986</v>
+        <v>0.32926</v>
       </c>
       <c r="U149" t="n">
-        <v>0.17283</v>
+        <v>0.17147</v>
       </c>
       <c r="V149" t="n">
-        <v>68.11</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="W149" t="n">
-        <v>67.66</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="X149" t="n">
-        <v>0.5697</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="Y149" t="n">
         <v>24.808</v>
       </c>
       <c r="Z149" t="n">
-        <v>57.41</v>
+        <v>57.455</v>
       </c>
       <c r="AA149" t="n">
-        <v>5.622</v>
+        <v>5.609</v>
       </c>
       <c r="AB149" t="n">
-        <v>19.006</v>
+        <v>19.032</v>
       </c>
       <c r="AC149" t="n">
-        <v>12.868</v>
+        <v>12.987</v>
       </c>
       <c r="AD149" t="n">
-        <v>19.192</v>
+        <v>19.346</v>
       </c>
       <c r="AE149" t="n">
-        <v>11.57</v>
+        <v>11.66</v>
       </c>
       <c r="AF149" t="n">
-        <v>23.192</v>
+        <v>23.462</v>
       </c>
       <c r="AG149" t="n">
-        <v>11.861</v>
+        <v>11.756</v>
       </c>
       <c r="AH149" t="n">
-        <v>6.847</v>
+        <v>6.872</v>
       </c>
       <c r="AI149" t="n">
-        <v>4.542</v>
+        <v>4.699</v>
       </c>
       <c r="AJ149" t="n">
-        <v>16.47</v>
+        <v>16.526</v>
       </c>
       <c r="AK149" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="AL149" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="150">
@@ -20666,22 +20666,22 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F169" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G169" t="b">
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>2192.399</v>
+        <v>2196.807</v>
       </c>
       <c r="I169" t="n">
-        <v>6.99</v>
+        <v>6.739</v>
       </c>
       <c r="J169" t="n">
-        <v>1768.8</v>
+        <v>1772.9</v>
       </c>
       <c r="K169" t="n">
         <v>2</v>
@@ -20702,70 +20702,70 @@
         <v>2</v>
       </c>
       <c r="Q169" t="n">
-        <v>121.295</v>
+        <v>120.645</v>
       </c>
       <c r="R169" t="n">
-        <v>95.953</v>
+        <v>95.937</v>
       </c>
       <c r="S169" t="n">
-        <v>25.341</v>
+        <v>24.707</v>
       </c>
       <c r="T169" t="n">
-        <v>0.26009</v>
+        <v>0.26043</v>
       </c>
       <c r="U169" t="n">
-        <v>0.16468</v>
+        <v>0.16661</v>
       </c>
       <c r="V169" t="n">
-        <v>87.72</v>
+        <v>87.11</v>
       </c>
       <c r="W169" t="n">
-        <v>68.98</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="X169" t="n">
-        <v>0.9381</v>
+        <v>0.9399</v>
       </c>
       <c r="Y169" t="n">
-        <v>30.534</v>
+        <v>30.379</v>
       </c>
       <c r="Z169" t="n">
-        <v>60.061</v>
+        <v>60.043</v>
       </c>
       <c r="AA169" t="n">
-        <v>9.119</v>
+        <v>9.112</v>
       </c>
       <c r="AB169" t="n">
-        <v>25.114</v>
+        <v>25.18</v>
       </c>
       <c r="AC169" t="n">
-        <v>17.535</v>
+        <v>17.242</v>
       </c>
       <c r="AD169" t="n">
-        <v>23.535</v>
+        <v>23.088</v>
       </c>
       <c r="AE169" t="n">
-        <v>9.994999999999999</v>
+        <v>10.03</v>
       </c>
       <c r="AF169" t="n">
-        <v>28.124</v>
+        <v>28.197</v>
       </c>
       <c r="AG169" t="n">
-        <v>18.734</v>
+        <v>18.529</v>
       </c>
       <c r="AH169" t="n">
-        <v>5.854</v>
+        <v>5.811</v>
       </c>
       <c r="AI169" t="n">
-        <v>5.907</v>
+        <v>5.987</v>
       </c>
       <c r="AJ169" t="n">
-        <v>15.783</v>
+        <v>15.482</v>
       </c>
       <c r="AK169" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AL169" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -21026,22 +21026,22 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F172" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G172" t="b">
         <v>1</v>
       </c>
       <c r="H172" t="n">
-        <v>1685.217</v>
+        <v>1680.016</v>
       </c>
       <c r="I172" t="n">
-        <v>-7.2757</v>
+        <v>-6.7111</v>
       </c>
       <c r="J172" t="n">
-        <v>1706.6</v>
+        <v>1713.4</v>
       </c>
       <c r="K172" t="n">
         <v>81</v>
@@ -21062,70 +21062,70 @@
         <v>92</v>
       </c>
       <c r="Q172" t="n">
-        <v>108.929</v>
+        <v>109.139</v>
       </c>
       <c r="R172" t="n">
-        <v>108.993</v>
+        <v>109.356</v>
       </c>
       <c r="S172" t="n">
-        <v>-0.064</v>
+        <v>-0.217</v>
       </c>
       <c r="T172" t="n">
-        <v>0.28141</v>
+        <v>0.28227</v>
       </c>
       <c r="U172" t="n">
-        <v>0.13361</v>
+        <v>0.13445</v>
       </c>
       <c r="V172" t="n">
-        <v>75.51000000000001</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="W172" t="n">
-        <v>75.65000000000001</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="X172" t="n">
-        <v>0.4464</v>
+        <v>0.4248</v>
       </c>
       <c r="Y172" t="n">
-        <v>26.117</v>
+        <v>26.447</v>
       </c>
       <c r="Z172" t="n">
-        <v>59.95</v>
+        <v>60.285</v>
       </c>
       <c r="AA172" t="n">
-        <v>7.281</v>
+        <v>7.329</v>
       </c>
       <c r="AB172" t="n">
-        <v>22.415</v>
+        <v>22.599</v>
       </c>
       <c r="AC172" t="n">
-        <v>15.552</v>
+        <v>15.362</v>
       </c>
       <c r="AD172" t="n">
-        <v>20.804</v>
+        <v>20.514</v>
       </c>
       <c r="AE172" t="n">
-        <v>9.02</v>
+        <v>9.028</v>
       </c>
       <c r="AF172" t="n">
-        <v>22.901</v>
+        <v>22.821</v>
       </c>
       <c r="AG172" t="n">
-        <v>13.709</v>
+        <v>13.532</v>
       </c>
       <c r="AH172" t="n">
-        <v>6.865</v>
+        <v>6.924</v>
       </c>
       <c r="AI172" t="n">
-        <v>4.233</v>
+        <v>4.264</v>
       </c>
       <c r="AJ172" t="n">
-        <v>18.846</v>
+        <v>18.998</v>
       </c>
       <c r="AK172" t="n">
         <v>1.8</v>
       </c>
       <c r="AL172" t="n">
-        <v>-2.6</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="173">
@@ -23426,22 +23426,22 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F192" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G192" t="b">
         <v>1</v>
       </c>
       <c r="H192" t="n">
-        <v>1291.665</v>
+        <v>1289.874</v>
       </c>
       <c r="I192" t="n">
-        <v>-1.3164</v>
+        <v>-1.1732</v>
       </c>
       <c r="J192" t="n">
-        <v>1379.6</v>
+        <v>1382.1</v>
       </c>
       <c r="K192" t="n">
         <v>353</v>
@@ -23462,70 +23462,70 @@
         <v>347</v>
       </c>
       <c r="Q192" t="n">
-        <v>101.75</v>
+        <v>101.762</v>
       </c>
       <c r="R192" t="n">
-        <v>115.018</v>
+        <v>115.202</v>
       </c>
       <c r="S192" t="n">
-        <v>-13.267</v>
+        <v>-13.44</v>
       </c>
       <c r="T192" t="n">
-        <v>0.31222</v>
+        <v>0.31412</v>
       </c>
       <c r="U192" t="n">
-        <v>0.17585</v>
+        <v>0.17806</v>
       </c>
       <c r="V192" t="n">
-        <v>67.72</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="W192" t="n">
-        <v>77.29000000000001</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="X192" t="n">
-        <v>0.3773</v>
+        <v>0.3535</v>
       </c>
       <c r="Y192" t="n">
-        <v>23.048</v>
+        <v>22.854</v>
       </c>
       <c r="Z192" t="n">
-        <v>54.755</v>
+        <v>54.525</v>
       </c>
       <c r="AA192" t="n">
-        <v>5.993</v>
+        <v>6.035</v>
       </c>
       <c r="AB192" t="n">
-        <v>18.418</v>
+        <v>18.515</v>
       </c>
       <c r="AC192" t="n">
-        <v>15.63</v>
+        <v>15.854</v>
       </c>
       <c r="AD192" t="n">
-        <v>21.322</v>
+        <v>21.444</v>
       </c>
       <c r="AE192" t="n">
-        <v>9.066000000000001</v>
+        <v>9.135999999999999</v>
       </c>
       <c r="AF192" t="n">
-        <v>19.502</v>
+        <v>19.495</v>
       </c>
       <c r="AG192" t="n">
-        <v>12.231</v>
+        <v>12.03</v>
       </c>
       <c r="AH192" t="n">
-        <v>7.791</v>
+        <v>7.697</v>
       </c>
       <c r="AI192" t="n">
-        <v>3.403</v>
+        <v>3.389</v>
       </c>
       <c r="AJ192" t="n">
-        <v>17.37</v>
+        <v>17.616</v>
       </c>
       <c r="AK192" t="n">
-        <v>3</v>
+        <v>-1.2</v>
       </c>
       <c r="AL192" t="n">
-        <v>-2</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="193">
@@ -27386,22 +27386,22 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F225" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G225" t="b">
         <v>1</v>
       </c>
       <c r="H225" t="n">
-        <v>1419.847</v>
+        <v>1431.706</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0511</v>
+        <v>1.1135</v>
       </c>
       <c r="J225" t="n">
-        <v>1479.6</v>
+        <v>1482.7</v>
       </c>
       <c r="K225" t="n">
         <v>163</v>
@@ -27422,70 +27422,70 @@
         <v>148</v>
       </c>
       <c r="Q225" t="n">
-        <v>108.528</v>
+        <v>107.489</v>
       </c>
       <c r="R225" t="n">
-        <v>106.514</v>
+        <v>105.825</v>
       </c>
       <c r="S225" t="n">
-        <v>2.014</v>
+        <v>1.663</v>
       </c>
       <c r="T225" t="n">
-        <v>0.31197</v>
+        <v>0.30844</v>
       </c>
       <c r="U225" t="n">
-        <v>0.14956</v>
+        <v>0.15432</v>
       </c>
       <c r="V225" t="n">
-        <v>74.65000000000001</v>
+        <v>73.91</v>
       </c>
       <c r="W225" t="n">
-        <v>73.28</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="X225" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="Y225" t="n">
-        <v>25.931</v>
+        <v>25.84</v>
       </c>
       <c r="Z225" t="n">
-        <v>59.301</v>
+        <v>59.369</v>
       </c>
       <c r="AA225" t="n">
-        <v>7.916</v>
+        <v>7.89</v>
       </c>
       <c r="AB225" t="n">
-        <v>20.695</v>
+        <v>21.135</v>
       </c>
       <c r="AC225" t="n">
-        <v>14.872</v>
+        <v>14.24</v>
       </c>
       <c r="AD225" t="n">
-        <v>21.615</v>
+        <v>20.671</v>
       </c>
       <c r="AE225" t="n">
-        <v>10.309</v>
+        <v>10.306</v>
       </c>
       <c r="AF225" t="n">
-        <v>22.954</v>
+        <v>23.427</v>
       </c>
       <c r="AG225" t="n">
-        <v>13.531</v>
+        <v>13.662</v>
       </c>
       <c r="AH225" t="n">
-        <v>6.798</v>
+        <v>6.435</v>
       </c>
       <c r="AI225" t="n">
-        <v>3.076</v>
+        <v>3.223</v>
       </c>
       <c r="AJ225" t="n">
-        <v>16.918</v>
+        <v>16.763</v>
       </c>
       <c r="AK225" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AL225" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="226">
@@ -28106,22 +28106,22 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F231" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G231" t="b">
         <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>1263.248</v>
+        <v>1266.708</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6629</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="J231" t="n">
-        <v>1382.8</v>
+        <v>1383.4</v>
       </c>
       <c r="K231" t="n">
         <v>312</v>
@@ -28142,70 +28142,70 @@
         <v>316</v>
       </c>
       <c r="Q231" t="n">
-        <v>104.259</v>
+        <v>104.378</v>
       </c>
       <c r="R231" t="n">
-        <v>107.197</v>
+        <v>107.109</v>
       </c>
       <c r="S231" t="n">
-        <v>-2.937</v>
+        <v>-2.731</v>
       </c>
       <c r="T231" t="n">
-        <v>0.2838</v>
+        <v>0.28778</v>
       </c>
       <c r="U231" t="n">
-        <v>0.15457</v>
+        <v>0.15507</v>
       </c>
       <c r="V231" t="n">
-        <v>75.84999999999999</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="W231" t="n">
-        <v>78.76000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="X231" t="n">
-        <v>0.4382</v>
+        <v>0.456</v>
       </c>
       <c r="Y231" t="n">
-        <v>24.94</v>
+        <v>24.92</v>
       </c>
       <c r="Z231" t="n">
-        <v>59.453</v>
+        <v>59.6</v>
       </c>
       <c r="AA231" t="n">
-        <v>5.909</v>
+        <v>5.864</v>
       </c>
       <c r="AB231" t="n">
-        <v>18.214</v>
+        <v>18.264</v>
       </c>
       <c r="AC231" t="n">
-        <v>19.138</v>
+        <v>19.032</v>
       </c>
       <c r="AD231" t="n">
-        <v>25.685</v>
+        <v>25.432</v>
       </c>
       <c r="AE231" t="n">
-        <v>9.125</v>
+        <v>9.375999999999999</v>
       </c>
       <c r="AF231" t="n">
-        <v>22.091</v>
+        <v>22.176</v>
       </c>
       <c r="AG231" t="n">
-        <v>11.091</v>
+        <v>11.136</v>
       </c>
       <c r="AH231" t="n">
-        <v>7.082</v>
+        <v>7.016</v>
       </c>
       <c r="AI231" t="n">
-        <v>4.743</v>
+        <v>4.816</v>
       </c>
       <c r="AJ231" t="n">
-        <v>19.951</v>
+        <v>19.696</v>
       </c>
       <c r="AK231" t="n">
-        <v>12.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AL231" t="n">
-        <v>8.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -28586,22 +28586,22 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F235" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G235" t="b">
         <v>1</v>
       </c>
       <c r="H235" t="n">
-        <v>1975.743</v>
+        <v>1986.929</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3998</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="J235" t="n">
-        <v>1751.8</v>
+        <v>1754.6</v>
       </c>
       <c r="K235" t="n">
         <v>8</v>
@@ -28622,70 +28622,70 @@
         <v>10</v>
       </c>
       <c r="Q235" t="n">
-        <v>124.771</v>
+        <v>124.757</v>
       </c>
       <c r="R235" t="n">
-        <v>106.947</v>
+        <v>107.247</v>
       </c>
       <c r="S235" t="n">
-        <v>17.824</v>
+        <v>17.51</v>
       </c>
       <c r="T235" t="n">
-        <v>0.30942</v>
+        <v>0.31049</v>
       </c>
       <c r="U235" t="n">
-        <v>0.13586</v>
+        <v>0.13425</v>
       </c>
       <c r="V235" t="n">
-        <v>81.89</v>
+        <v>81.62</v>
       </c>
       <c r="W235" t="n">
-        <v>70.09</v>
+        <v>70.05</v>
       </c>
       <c r="X235" t="n">
-        <v>0.76</v>
+        <v>0.7669</v>
       </c>
       <c r="Y235" t="n">
-        <v>29.77</v>
+        <v>29.662</v>
       </c>
       <c r="Z235" t="n">
-        <v>59.99</v>
+        <v>59.914</v>
       </c>
       <c r="AA235" t="n">
-        <v>9.43</v>
+        <v>9.331</v>
       </c>
       <c r="AB235" t="n">
-        <v>24.76</v>
+        <v>24.516</v>
       </c>
       <c r="AC235" t="n">
-        <v>12.28</v>
+        <v>12.234</v>
       </c>
       <c r="AD235" t="n">
-        <v>16.68</v>
+        <v>16.536</v>
       </c>
       <c r="AE235" t="n">
-        <v>10.57</v>
+        <v>10.515</v>
       </c>
       <c r="AF235" t="n">
-        <v>23.14</v>
+        <v>22.944</v>
       </c>
       <c r="AG235" t="n">
-        <v>19.65</v>
+        <v>19.632</v>
       </c>
       <c r="AH235" t="n">
-        <v>5.53</v>
+        <v>5.64</v>
       </c>
       <c r="AI235" t="n">
-        <v>2.69</v>
+        <v>2.632</v>
       </c>
       <c r="AJ235" t="n">
-        <v>14.85</v>
+        <v>14.883</v>
       </c>
       <c r="AK235" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AL235" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="236">
@@ -30506,22 +30506,22 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F251" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G251" t="b">
         <v>1</v>
       </c>
       <c r="H251" t="n">
-        <v>1812.249</v>
+        <v>1800.371</v>
       </c>
       <c r="I251" t="n">
-        <v>4.8008</v>
+        <v>4.5904</v>
       </c>
       <c r="J251" t="n">
-        <v>1659.4</v>
+        <v>1666.9</v>
       </c>
       <c r="K251" t="n">
         <v>47</v>
@@ -30542,70 +30542,70 @@
         <v>47</v>
       </c>
       <c r="Q251" t="n">
-        <v>109.865</v>
+        <v>109.494</v>
       </c>
       <c r="R251" t="n">
-        <v>100.816</v>
+        <v>101.412</v>
       </c>
       <c r="S251" t="n">
-        <v>9.048999999999999</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="T251" t="n">
-        <v>0.26377</v>
+        <v>0.26363</v>
       </c>
       <c r="U251" t="n">
-        <v>0.16638</v>
+        <v>0.16822</v>
       </c>
       <c r="V251" t="n">
-        <v>77.22</v>
+        <v>76.73</v>
       </c>
       <c r="W251" t="n">
-        <v>71.22</v>
+        <v>71.36</v>
       </c>
       <c r="X251" t="n">
-        <v>0.68</v>
+        <v>0.6514</v>
       </c>
       <c r="Y251" t="n">
-        <v>27.096</v>
+        <v>26.855</v>
       </c>
       <c r="Z251" t="n">
-        <v>57.664</v>
+        <v>57.344</v>
       </c>
       <c r="AA251" t="n">
-        <v>6.728</v>
+        <v>6.675</v>
       </c>
       <c r="AB251" t="n">
-        <v>19.496</v>
+        <v>19.35</v>
       </c>
       <c r="AC251" t="n">
-        <v>16.296</v>
+        <v>16.349</v>
       </c>
       <c r="AD251" t="n">
-        <v>22.312</v>
+        <v>22.387</v>
       </c>
       <c r="AE251" t="n">
-        <v>8.928000000000001</v>
+        <v>8.945</v>
       </c>
       <c r="AF251" t="n">
-        <v>23.864</v>
+        <v>23.968</v>
       </c>
       <c r="AG251" t="n">
-        <v>14.784</v>
+        <v>14.591</v>
       </c>
       <c r="AH251" t="n">
-        <v>7.92</v>
+        <v>7.638</v>
       </c>
       <c r="AI251" t="n">
-        <v>4.472</v>
+        <v>4.658</v>
       </c>
       <c r="AJ251" t="n">
-        <v>19.232</v>
+        <v>18.994</v>
       </c>
       <c r="AK251" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="AL251" t="n">
-        <v>4.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="252">
@@ -32426,22 +32426,22 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F267" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G267" t="b">
         <v>1</v>
       </c>
       <c r="H267" t="n">
-        <v>1711.768</v>
+        <v>1714.878</v>
       </c>
       <c r="I267" t="n">
-        <v>9.207800000000001</v>
+        <v>9.035</v>
       </c>
       <c r="J267" t="n">
-        <v>1553.3</v>
+        <v>1550.3</v>
       </c>
       <c r="K267" t="n">
         <v>51</v>
@@ -32462,70 +32462,70 @@
         <v>49</v>
       </c>
       <c r="Q267" t="n">
-        <v>116.057</v>
+        <v>116.325</v>
       </c>
       <c r="R267" t="n">
-        <v>101.733</v>
+        <v>101.484</v>
       </c>
       <c r="S267" t="n">
-        <v>14.323</v>
+        <v>14.84</v>
       </c>
       <c r="T267" t="n">
-        <v>0.33915</v>
+        <v>0.34115</v>
       </c>
       <c r="U267" t="n">
-        <v>0.1453</v>
+        <v>0.14659</v>
       </c>
       <c r="V267" t="n">
-        <v>87.54000000000001</v>
+        <v>87.53</v>
       </c>
       <c r="W267" t="n">
-        <v>77.20999999999999</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="X267" t="n">
-        <v>0.7367</v>
+        <v>0.7449</v>
       </c>
       <c r="Y267" t="n">
-        <v>28.782</v>
+        <v>28.907</v>
       </c>
       <c r="Z267" t="n">
-        <v>65.83199999999999</v>
+        <v>65.907</v>
       </c>
       <c r="AA267" t="n">
-        <v>9.609999999999999</v>
+        <v>9.672000000000001</v>
       </c>
       <c r="AB267" t="n">
-        <v>29.075</v>
+        <v>29</v>
       </c>
       <c r="AC267" t="n">
-        <v>20.368</v>
+        <v>20.043</v>
       </c>
       <c r="AD267" t="n">
-        <v>27.475</v>
+        <v>26.997</v>
       </c>
       <c r="AE267" t="n">
-        <v>13.293</v>
+        <v>13.397</v>
       </c>
       <c r="AF267" t="n">
-        <v>25.704</v>
+        <v>25.67</v>
       </c>
       <c r="AG267" t="n">
-        <v>17.121</v>
+        <v>16.988</v>
       </c>
       <c r="AH267" t="n">
-        <v>8.728999999999999</v>
+        <v>8.843</v>
       </c>
       <c r="AI267" t="n">
-        <v>4.139</v>
+        <v>4.072</v>
       </c>
       <c r="AJ267" t="n">
-        <v>19.76</v>
+        <v>19.71</v>
       </c>
       <c r="AK267" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AL267" t="n">
-        <v>13.4</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="268">
@@ -32666,22 +32666,22 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F269" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G269" t="b">
         <v>1</v>
       </c>
       <c r="H269" t="n">
-        <v>1377.937</v>
+        <v>1374.476</v>
       </c>
       <c r="I269" t="n">
-        <v>-2.2287</v>
+        <v>-2.0668</v>
       </c>
       <c r="J269" t="n">
-        <v>1393.5</v>
+        <v>1389.2</v>
       </c>
       <c r="K269" t="n">
         <v>275</v>
@@ -32702,70 +32702,70 @@
         <v>277</v>
       </c>
       <c r="Q269" t="n">
-        <v>106.093</v>
+        <v>105.921</v>
       </c>
       <c r="R269" t="n">
-        <v>111.346</v>
+        <v>111.389</v>
       </c>
       <c r="S269" t="n">
-        <v>-5.253</v>
+        <v>-5.468</v>
       </c>
       <c r="T269" t="n">
-        <v>0.3165</v>
+        <v>0.31691</v>
       </c>
       <c r="U269" t="n">
-        <v>0.16268</v>
+        <v>0.1617</v>
       </c>
       <c r="V269" t="n">
-        <v>76.51000000000001</v>
+        <v>76.13</v>
       </c>
       <c r="W269" t="n">
-        <v>80.43000000000001</v>
+        <v>80.17</v>
       </c>
       <c r="X269" t="n">
-        <v>0.4703</v>
+        <v>0.4487</v>
       </c>
       <c r="Y269" t="n">
-        <v>26.178</v>
+        <v>26.231</v>
       </c>
       <c r="Z269" t="n">
-        <v>59.766</v>
+        <v>59.84</v>
       </c>
       <c r="AA269" t="n">
-        <v>6.794</v>
+        <v>6.885</v>
       </c>
       <c r="AB269" t="n">
-        <v>19.178</v>
+        <v>19.154</v>
       </c>
       <c r="AC269" t="n">
-        <v>17.239</v>
+        <v>16.917</v>
       </c>
       <c r="AD269" t="n">
-        <v>24.568</v>
+        <v>24.115</v>
       </c>
       <c r="AE269" t="n">
-        <v>10.138</v>
+        <v>10.16</v>
       </c>
       <c r="AF269" t="n">
-        <v>22.141</v>
+        <v>22.135</v>
       </c>
       <c r="AG269" t="n">
-        <v>13.735</v>
+        <v>13.667</v>
       </c>
       <c r="AH269" t="n">
-        <v>8.265000000000001</v>
+        <v>8.179</v>
       </c>
       <c r="AI269" t="n">
-        <v>3.596</v>
+        <v>3.692</v>
       </c>
       <c r="AJ269" t="n">
-        <v>19.177</v>
+        <v>19.032</v>
       </c>
       <c r="AK269" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AL269" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="270">
@@ -33146,22 +33146,22 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F273" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G273" t="b">
         <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>1967.781</v>
+        <v>1984.929</v>
       </c>
       <c r="I273" t="n">
-        <v>5.6546</v>
+        <v>5.6609</v>
       </c>
       <c r="J273" t="n">
-        <v>1677.1</v>
+        <v>1691.6</v>
       </c>
       <c r="K273" t="n">
         <v>21</v>
@@ -33182,70 +33182,70 @@
         <v>22</v>
       </c>
       <c r="Q273" t="n">
-        <v>114.058</v>
+        <v>113.974</v>
       </c>
       <c r="R273" t="n">
-        <v>98.849</v>
+        <v>98.164</v>
       </c>
       <c r="S273" t="n">
-        <v>15.209</v>
+        <v>15.81</v>
       </c>
       <c r="T273" t="n">
-        <v>0.32437</v>
+        <v>0.3224</v>
       </c>
       <c r="U273" t="n">
-        <v>0.14335</v>
+        <v>0.14223</v>
       </c>
       <c r="V273" t="n">
-        <v>81.81999999999999</v>
+        <v>81.48</v>
       </c>
       <c r="W273" t="n">
-        <v>70.48999999999999</v>
+        <v>69.83</v>
       </c>
       <c r="X273" t="n">
-        <v>0.8197</v>
+        <v>0.8249</v>
       </c>
       <c r="Y273" t="n">
-        <v>27.945</v>
+        <v>27.934</v>
       </c>
       <c r="Z273" t="n">
-        <v>61.612</v>
+        <v>61.515</v>
       </c>
       <c r="AA273" t="n">
-        <v>6.945</v>
+        <v>6.897</v>
       </c>
       <c r="AB273" t="n">
-        <v>20.744</v>
+        <v>20.788</v>
       </c>
       <c r="AC273" t="n">
-        <v>18.982</v>
+        <v>18.719</v>
       </c>
       <c r="AD273" t="n">
-        <v>26.094</v>
+        <v>25.725</v>
       </c>
       <c r="AE273" t="n">
-        <v>11.713</v>
+        <v>11.589</v>
       </c>
       <c r="AF273" t="n">
-        <v>24.653</v>
+        <v>24.568</v>
       </c>
       <c r="AG273" t="n">
-        <v>16.352</v>
+        <v>16.239</v>
       </c>
       <c r="AH273" t="n">
-        <v>7.858</v>
+        <v>7.928</v>
       </c>
       <c r="AI273" t="n">
-        <v>4.781</v>
+        <v>4.907</v>
       </c>
       <c r="AJ273" t="n">
         <v>17.292</v>
       </c>
       <c r="AK273" t="n">
-        <v>13</v>
+        <v>10.6</v>
       </c>
       <c r="AL273" t="n">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="274">
@@ -33266,22 +33266,22 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F274" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G274" t="b">
         <v>1</v>
       </c>
       <c r="H274" t="n">
-        <v>1618.407</v>
+        <v>1610.925</v>
       </c>
       <c r="I274" t="n">
-        <v>1.2818</v>
+        <v>1.549</v>
       </c>
       <c r="J274" t="n">
-        <v>1508.9</v>
+        <v>1518.1</v>
       </c>
       <c r="K274" t="n">
         <v>121</v>
@@ -33302,70 +33302,70 @@
         <v>124</v>
       </c>
       <c r="Q274" t="n">
-        <v>106.146</v>
+        <v>105.807</v>
       </c>
       <c r="R274" t="n">
-        <v>102.385</v>
+        <v>103.141</v>
       </c>
       <c r="S274" t="n">
-        <v>3.761</v>
+        <v>2.666</v>
       </c>
       <c r="T274" t="n">
-        <v>0.28439</v>
+        <v>0.287</v>
       </c>
       <c r="U274" t="n">
-        <v>0.16306</v>
+        <v>0.16199</v>
       </c>
       <c r="V274" t="n">
-        <v>72.25</v>
+        <v>71.94</v>
       </c>
       <c r="W274" t="n">
-        <v>70</v>
+        <v>70.38</v>
       </c>
       <c r="X274" t="n">
-        <v>0.6695</v>
+        <v>0.64</v>
       </c>
       <c r="Y274" t="n">
-        <v>25.098</v>
+        <v>25.168</v>
       </c>
       <c r="Z274" t="n">
-        <v>59.103</v>
+        <v>59.512</v>
       </c>
       <c r="AA274" t="n">
-        <v>8.214</v>
+        <v>8.304</v>
       </c>
       <c r="AB274" t="n">
-        <v>26.806</v>
+        <v>26.944</v>
       </c>
       <c r="AC274" t="n">
-        <v>13.838</v>
+        <v>13.296</v>
       </c>
       <c r="AD274" t="n">
-        <v>18.565</v>
+        <v>17.96</v>
       </c>
       <c r="AE274" t="n">
-        <v>10.198</v>
+        <v>10.352</v>
       </c>
       <c r="AF274" t="n">
-        <v>25.529</v>
+        <v>25.552</v>
       </c>
       <c r="AG274" t="n">
-        <v>15.073</v>
+        <v>15.256</v>
       </c>
       <c r="AH274" t="n">
-        <v>5.504</v>
+        <v>5.4</v>
       </c>
       <c r="AI274" t="n">
-        <v>4.71</v>
+        <v>4.624</v>
       </c>
       <c r="AJ274" t="n">
-        <v>14.197</v>
+        <v>14.144</v>
       </c>
       <c r="AK274" t="n">
-        <v>10.2</v>
+        <v>4</v>
       </c>
       <c r="AL274" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="275">
@@ -33386,22 +33386,22 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F275" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G275" t="b">
         <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>1811.548</v>
+        <v>1793.214</v>
       </c>
       <c r="I275" t="n">
-        <v>9.2125</v>
+        <v>8.666399999999999</v>
       </c>
       <c r="J275" t="n">
-        <v>1510.4</v>
+        <v>1516.9</v>
       </c>
       <c r="K275" t="n">
         <v>40</v>
@@ -33422,70 +33422,70 @@
         <v>27</v>
       </c>
       <c r="Q275" t="n">
-        <v>120.632</v>
+        <v>120.005</v>
       </c>
       <c r="R275" t="n">
-        <v>98.514</v>
+        <v>98.72799999999999</v>
       </c>
       <c r="S275" t="n">
-        <v>22.118</v>
+        <v>21.276</v>
       </c>
       <c r="T275" t="n">
-        <v>0.23855</v>
+        <v>0.24179</v>
       </c>
       <c r="U275" t="n">
-        <v>0.16748</v>
+        <v>0.1658</v>
       </c>
       <c r="V275" t="n">
-        <v>86.98</v>
+        <v>86.22</v>
       </c>
       <c r="W275" t="n">
-        <v>70.8</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="X275" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8347</v>
       </c>
       <c r="Y275" t="n">
-        <v>30.316</v>
+        <v>29.882</v>
       </c>
       <c r="Z275" t="n">
-        <v>59.733</v>
+        <v>59.544</v>
       </c>
       <c r="AA275" t="n">
-        <v>10.893</v>
+        <v>10.782</v>
       </c>
       <c r="AB275" t="n">
-        <v>26.843</v>
+        <v>26.69</v>
       </c>
       <c r="AC275" t="n">
-        <v>15.455</v>
+        <v>15.715</v>
       </c>
       <c r="AD275" t="n">
-        <v>20.803</v>
+        <v>21.086</v>
       </c>
       <c r="AE275" t="n">
-        <v>8.849</v>
+        <v>8.917999999999999</v>
       </c>
       <c r="AF275" t="n">
-        <v>28.055</v>
+        <v>27.823</v>
       </c>
       <c r="AG275" t="n">
-        <v>18.203</v>
+        <v>17.977</v>
       </c>
       <c r="AH275" t="n">
-        <v>7.159</v>
+        <v>7.238</v>
       </c>
       <c r="AI275" t="n">
-        <v>3.243</v>
+        <v>3.206</v>
       </c>
       <c r="AJ275" t="n">
-        <v>18.296</v>
+        <v>18.267</v>
       </c>
       <c r="AK275" t="n">
-        <v>-1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AL275" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276">
@@ -35546,22 +35546,22 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F293" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G293" t="b">
         <v>1</v>
       </c>
       <c r="H293" t="n">
-        <v>1464.426</v>
+        <v>1461</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.583</v>
+        <v>-0.4994</v>
       </c>
       <c r="J293" t="n">
-        <v>1495.2</v>
+        <v>1503.6</v>
       </c>
       <c r="K293" t="n">
         <v>135</v>
@@ -35582,70 +35582,70 @@
         <v>146</v>
       </c>
       <c r="Q293" t="n">
-        <v>114.815</v>
+        <v>114.812</v>
       </c>
       <c r="R293" t="n">
-        <v>111.038</v>
+        <v>111.467</v>
       </c>
       <c r="S293" t="n">
-        <v>3.777</v>
+        <v>3.345</v>
       </c>
       <c r="T293" t="n">
-        <v>0.28982</v>
+        <v>0.28755</v>
       </c>
       <c r="U293" t="n">
-        <v>0.14163</v>
+        <v>0.14226</v>
       </c>
       <c r="V293" t="n">
-        <v>79.84</v>
+        <v>79.72</v>
       </c>
       <c r="W293" t="n">
-        <v>77.29000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="X293" t="n">
-        <v>0.5528</v>
+        <v>0.5265</v>
       </c>
       <c r="Y293" t="n">
-        <v>29.371</v>
+        <v>29.301</v>
       </c>
       <c r="Z293" t="n">
-        <v>60.517</v>
+        <v>60.397</v>
       </c>
       <c r="AA293" t="n">
-        <v>7.192</v>
+        <v>7.306</v>
       </c>
       <c r="AB293" t="n">
-        <v>19.521</v>
+        <v>19.695</v>
       </c>
       <c r="AC293" t="n">
-        <v>13.91</v>
+        <v>13.809</v>
       </c>
       <c r="AD293" t="n">
-        <v>18.536</v>
+        <v>18.357</v>
       </c>
       <c r="AE293" t="n">
-        <v>8.974</v>
+        <v>8.911</v>
       </c>
       <c r="AF293" t="n">
-        <v>21.419</v>
+        <v>21.541</v>
       </c>
       <c r="AG293" t="n">
-        <v>15.474</v>
+        <v>15.523</v>
       </c>
       <c r="AH293" t="n">
-        <v>7.69</v>
+        <v>7.61</v>
       </c>
       <c r="AI293" t="n">
-        <v>2.924</v>
+        <v>2.867</v>
       </c>
       <c r="AJ293" t="n">
-        <v>15.224</v>
+        <v>15.177</v>
       </c>
       <c r="AK293" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="AL293" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="294">
@@ -36026,22 +36026,22 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F297" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G297" t="b">
         <v>1</v>
       </c>
       <c r="H297" t="n">
-        <v>1685.662</v>
+        <v>1673.101</v>
       </c>
       <c r="I297" t="n">
-        <v>8.801299999999999</v>
+        <v>8.4628</v>
       </c>
       <c r="J297" t="n">
-        <v>1505.1</v>
+        <v>1509.4</v>
       </c>
       <c r="K297" t="n">
         <v>58</v>
@@ -36062,70 +36062,70 @@
         <v>50</v>
       </c>
       <c r="Q297" t="n">
-        <v>121.598</v>
+        <v>121.126</v>
       </c>
       <c r="R297" t="n">
-        <v>105.564</v>
+        <v>106.46</v>
       </c>
       <c r="S297" t="n">
-        <v>16.035</v>
+        <v>14.667</v>
       </c>
       <c r="T297" t="n">
-        <v>0.26922</v>
+        <v>0.27526</v>
       </c>
       <c r="U297" t="n">
-        <v>0.14806</v>
+        <v>0.14728</v>
       </c>
       <c r="V297" t="n">
-        <v>84.88</v>
+        <v>84.16</v>
       </c>
       <c r="W297" t="n">
-        <v>73.79000000000001</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="X297" t="n">
-        <v>0.8017</v>
+        <v>0.768</v>
       </c>
       <c r="Y297" t="n">
-        <v>27.626</v>
+        <v>27.48</v>
       </c>
       <c r="Z297" t="n">
-        <v>58.003</v>
+        <v>58.136</v>
       </c>
       <c r="AA297" t="n">
-        <v>10.612</v>
+        <v>10.656</v>
       </c>
       <c r="AB297" t="n">
-        <v>26.945</v>
+        <v>27.032</v>
       </c>
       <c r="AC297" t="n">
-        <v>19.013</v>
+        <v>18.544</v>
       </c>
       <c r="AD297" t="n">
-        <v>24.195</v>
+        <v>23.704</v>
       </c>
       <c r="AE297" t="n">
-        <v>9.116</v>
+        <v>9.295999999999999</v>
       </c>
       <c r="AF297" t="n">
-        <v>24.509</v>
+        <v>24.224</v>
       </c>
       <c r="AG297" t="n">
-        <v>15.455</v>
+        <v>15.336</v>
       </c>
       <c r="AH297" t="n">
-        <v>6.504</v>
+        <v>6.44</v>
       </c>
       <c r="AI297" t="n">
-        <v>2.381</v>
+        <v>2.312</v>
       </c>
       <c r="AJ297" t="n">
-        <v>16.339</v>
+        <v>16.32</v>
       </c>
       <c r="AK297" t="n">
-        <v>19</v>
+        <v>11.2</v>
       </c>
       <c r="AL297" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="298">
@@ -36626,22 +36626,22 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F302" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G302" t="b">
         <v>1</v>
       </c>
       <c r="H302" t="n">
-        <v>1620.289</v>
+        <v>1609.971</v>
       </c>
       <c r="I302" t="n">
-        <v>2.2032</v>
+        <v>2.2217</v>
       </c>
       <c r="J302" t="n">
-        <v>1473</v>
+        <v>1475.3</v>
       </c>
       <c r="K302" t="n">
         <v>106</v>
@@ -36662,70 +36662,70 @@
         <v>118</v>
       </c>
       <c r="Q302" t="n">
-        <v>104.721</v>
+        <v>103.957</v>
       </c>
       <c r="R302" t="n">
-        <v>96.983</v>
+        <v>97.05800000000001</v>
       </c>
       <c r="S302" t="n">
-        <v>7.738</v>
+        <v>6.899</v>
       </c>
       <c r="T302" t="n">
-        <v>0.27137</v>
+        <v>0.27524</v>
       </c>
       <c r="U302" t="n">
-        <v>0.17141</v>
+        <v>0.17235</v>
       </c>
       <c r="V302" t="n">
-        <v>74.79000000000001</v>
+        <v>74.19</v>
       </c>
       <c r="W302" t="n">
-        <v>69.25</v>
+        <v>69.23</v>
       </c>
       <c r="X302" t="n">
-        <v>0.6806</v>
+        <v>0.6503</v>
       </c>
       <c r="Y302" t="n">
-        <v>27.058</v>
+        <v>27</v>
       </c>
       <c r="Z302" t="n">
-        <v>59.783</v>
+        <v>59.992</v>
       </c>
       <c r="AA302" t="n">
-        <v>5.783</v>
+        <v>5.832</v>
       </c>
       <c r="AB302" t="n">
-        <v>17.142</v>
+        <v>17.422</v>
       </c>
       <c r="AC302" t="n">
-        <v>14.892</v>
+        <v>14.636</v>
       </c>
       <c r="AD302" t="n">
-        <v>21.553</v>
+        <v>21.286</v>
       </c>
       <c r="AE302" t="n">
-        <v>10.068</v>
+        <v>10.28</v>
       </c>
       <c r="AF302" t="n">
-        <v>27.096</v>
+        <v>27.053</v>
       </c>
       <c r="AG302" t="n">
-        <v>15.017</v>
+        <v>15.049</v>
       </c>
       <c r="AH302" t="n">
-        <v>7.533</v>
+        <v>7.526</v>
       </c>
       <c r="AI302" t="n">
-        <v>5.863</v>
+        <v>6.036</v>
       </c>
       <c r="AJ302" t="n">
-        <v>15.897</v>
+        <v>15.818</v>
       </c>
       <c r="AK302" t="n">
-        <v>10.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AL302" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="303">
@@ -36986,22 +36986,22 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F305" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G305" t="b">
         <v>1</v>
       </c>
       <c r="H305" t="n">
-        <v>1885.412</v>
+        <v>1874.227</v>
       </c>
       <c r="I305" t="n">
-        <v>2.6042</v>
+        <v>2.8463</v>
       </c>
       <c r="J305" t="n">
-        <v>1698.9</v>
+        <v>1706.3</v>
       </c>
       <c r="K305" t="n">
         <v>28</v>
@@ -37022,70 +37022,70 @@
         <v>34</v>
       </c>
       <c r="Q305" t="n">
-        <v>117.515</v>
+        <v>117.179</v>
       </c>
       <c r="R305" t="n">
-        <v>107.059</v>
+        <v>107.51</v>
       </c>
       <c r="S305" t="n">
-        <v>10.456</v>
+        <v>9.669</v>
       </c>
       <c r="T305" t="n">
-        <v>0.30517</v>
+        <v>0.30552</v>
       </c>
       <c r="U305" t="n">
-        <v>0.13147</v>
+        <v>0.13246</v>
       </c>
       <c r="V305" t="n">
-        <v>78.17</v>
+        <v>77.64</v>
       </c>
       <c r="W305" t="n">
-        <v>71.05</v>
+        <v>71.02</v>
       </c>
       <c r="X305" t="n">
-        <v>0.6995</v>
+        <v>0.6712</v>
       </c>
       <c r="Y305" t="n">
-        <v>27.489</v>
+        <v>27.393</v>
       </c>
       <c r="Z305" t="n">
-        <v>58.665</v>
+        <v>58.465</v>
       </c>
       <c r="AA305" t="n">
-        <v>7.995</v>
+        <v>8.045</v>
       </c>
       <c r="AB305" t="n">
-        <v>20.867</v>
+        <v>21.113</v>
       </c>
       <c r="AC305" t="n">
-        <v>15.047</v>
+        <v>14.955</v>
       </c>
       <c r="AD305" t="n">
-        <v>19.656</v>
+        <v>19.613</v>
       </c>
       <c r="AE305" t="n">
-        <v>9.388999999999999</v>
+        <v>9.468999999999999</v>
       </c>
       <c r="AF305" t="n">
-        <v>21.305</v>
+        <v>21.432</v>
       </c>
       <c r="AG305" t="n">
-        <v>16.458</v>
+        <v>16.565</v>
       </c>
       <c r="AH305" t="n">
-        <v>6.215</v>
+        <v>6.196</v>
       </c>
       <c r="AI305" t="n">
-        <v>2.931</v>
+        <v>2.942</v>
       </c>
       <c r="AJ305" t="n">
-        <v>17.15</v>
+        <v>16.887</v>
       </c>
       <c r="AK305" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="AL305" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="306">
@@ -37346,22 +37346,22 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F308" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G308" t="b">
         <v>1</v>
       </c>
       <c r="H308" t="n">
-        <v>1393.666</v>
+        <v>1397.919</v>
       </c>
       <c r="I308" t="n">
-        <v>1.2859</v>
+        <v>1.3468</v>
       </c>
       <c r="J308" t="n">
-        <v>1364.8</v>
+        <v>1369.1</v>
       </c>
       <c r="K308" t="n">
         <v>198</v>
@@ -37382,70 +37382,70 @@
         <v>205</v>
       </c>
       <c r="Q308" t="n">
-        <v>113.445</v>
+        <v>113.392</v>
       </c>
       <c r="R308" t="n">
-        <v>102.317</v>
+        <v>101.925</v>
       </c>
       <c r="S308" t="n">
-        <v>11.128</v>
+        <v>11.468</v>
       </c>
       <c r="T308" t="n">
-        <v>0.21682</v>
+        <v>0.21757</v>
       </c>
       <c r="U308" t="n">
-        <v>0.13443</v>
+        <v>0.13504</v>
       </c>
       <c r="V308" t="n">
-        <v>75.59999999999999</v>
+        <v>75.42</v>
       </c>
       <c r="W308" t="n">
-        <v>68.28</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="X308" t="n">
-        <v>0.7262</v>
+        <v>0.7352</v>
       </c>
       <c r="Y308" t="n">
-        <v>26.737</v>
+        <v>26.462</v>
       </c>
       <c r="Z308" t="n">
-        <v>56.653</v>
+        <v>56.396</v>
       </c>
       <c r="AA308" t="n">
-        <v>7.802</v>
+        <v>7.881</v>
       </c>
       <c r="AB308" t="n">
-        <v>21.746</v>
+        <v>21.928</v>
       </c>
       <c r="AC308" t="n">
-        <v>14.323</v>
+        <v>14.618</v>
       </c>
       <c r="AD308" t="n">
-        <v>18.851</v>
+        <v>19.114</v>
       </c>
       <c r="AE308" t="n">
-        <v>7.269</v>
+        <v>7.272</v>
       </c>
       <c r="AF308" t="n">
-        <v>25.658</v>
+        <v>25.589</v>
       </c>
       <c r="AG308" t="n">
-        <v>12.159</v>
+        <v>11.892</v>
       </c>
       <c r="AH308" t="n">
-        <v>4.935</v>
+        <v>4.821</v>
       </c>
       <c r="AI308" t="n">
-        <v>2.384</v>
+        <v>2.404</v>
       </c>
       <c r="AJ308" t="n">
-        <v>13.677</v>
+        <v>13.462</v>
       </c>
       <c r="AK308" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="AL308" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="309">
@@ -38426,22 +38426,22 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F317" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G317" t="b">
         <v>1</v>
       </c>
       <c r="H317" t="n">
-        <v>1885.633</v>
+        <v>1897.511</v>
       </c>
       <c r="I317" t="n">
-        <v>0.1404</v>
+        <v>0.1736</v>
       </c>
       <c r="J317" t="n">
-        <v>1604.7</v>
+        <v>1611.4</v>
       </c>
       <c r="K317" t="n">
         <v>35</v>
@@ -38462,70 +38462,70 @@
         <v>29</v>
       </c>
       <c r="Q317" t="n">
-        <v>119.834</v>
+        <v>119.564</v>
       </c>
       <c r="R317" t="n">
-        <v>103.764</v>
+        <v>103.487</v>
       </c>
       <c r="S317" t="n">
-        <v>16.07</v>
+        <v>16.077</v>
       </c>
       <c r="T317" t="n">
-        <v>0.3026</v>
+        <v>0.30319</v>
       </c>
       <c r="U317" t="n">
-        <v>0.15009</v>
+        <v>0.14787</v>
       </c>
       <c r="V317" t="n">
-        <v>81.95</v>
+        <v>81.64</v>
       </c>
       <c r="W317" t="n">
-        <v>71.09</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="X317" t="n">
-        <v>0.8139</v>
+        <v>0.8194</v>
       </c>
       <c r="Y317" t="n">
-        <v>28.653</v>
+        <v>28.736</v>
       </c>
       <c r="Z317" t="n">
-        <v>57.839</v>
+        <v>58.139</v>
       </c>
       <c r="AA317" t="n">
-        <v>8.342000000000001</v>
+        <v>8.287000000000001</v>
       </c>
       <c r="AB317" t="n">
-        <v>23.715</v>
+        <v>23.648</v>
       </c>
       <c r="AC317" t="n">
-        <v>16.237</v>
+        <v>15.817</v>
       </c>
       <c r="AD317" t="n">
-        <v>22.872</v>
+        <v>22.419</v>
       </c>
       <c r="AE317" t="n">
-        <v>9.619999999999999</v>
+        <v>9.676</v>
       </c>
       <c r="AF317" t="n">
-        <v>22.021</v>
+        <v>22.081</v>
       </c>
       <c r="AG317" t="n">
-        <v>17.14</v>
+        <v>17.188</v>
       </c>
       <c r="AH317" t="n">
-        <v>8.666</v>
+        <v>8.669</v>
       </c>
       <c r="AI317" t="n">
-        <v>2.876</v>
+        <v>2.88</v>
       </c>
       <c r="AJ317" t="n">
-        <v>19</v>
+        <v>18.963</v>
       </c>
       <c r="AK317" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AL317" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="318">
@@ -38546,22 +38546,22 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F318" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G318" t="b">
         <v>1</v>
       </c>
       <c r="H318" t="n">
-        <v>1640.962</v>
+        <v>1630.19</v>
       </c>
       <c r="I318" t="n">
-        <v>3.0131</v>
+        <v>2.9069</v>
       </c>
       <c r="J318" t="n">
-        <v>1456.2</v>
+        <v>1461.8</v>
       </c>
       <c r="K318" t="n">
         <v>90</v>
@@ -38582,70 +38582,70 @@
         <v>85</v>
       </c>
       <c r="Q318" t="n">
-        <v>111.372</v>
+        <v>110.639</v>
       </c>
       <c r="R318" t="n">
-        <v>100.517</v>
+        <v>100.286</v>
       </c>
       <c r="S318" t="n">
-        <v>10.854</v>
+        <v>10.353</v>
       </c>
       <c r="T318" t="n">
-        <v>0.30398</v>
+        <v>0.30348</v>
       </c>
       <c r="U318" t="n">
-        <v>0.19707</v>
+        <v>0.19698</v>
       </c>
       <c r="V318" t="n">
-        <v>78.16</v>
+        <v>77.55</v>
       </c>
       <c r="W318" t="n">
-        <v>70.75</v>
+        <v>70.48</v>
       </c>
       <c r="X318" t="n">
-        <v>0.7604</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="Y318" t="n">
-        <v>28.4</v>
+        <v>28.19</v>
       </c>
       <c r="Z318" t="n">
-        <v>57.192</v>
+        <v>57.305</v>
       </c>
       <c r="AA318" t="n">
-        <v>6.452</v>
+        <v>6.55</v>
       </c>
       <c r="AB318" t="n">
-        <v>19.042</v>
+        <v>19.313</v>
       </c>
       <c r="AC318" t="n">
-        <v>14.905</v>
+        <v>14.701</v>
       </c>
       <c r="AD318" t="n">
-        <v>21.722</v>
+        <v>21.262</v>
       </c>
       <c r="AE318" t="n">
-        <v>10.301</v>
+        <v>10.298</v>
       </c>
       <c r="AF318" t="n">
-        <v>22.939</v>
+        <v>23.014</v>
       </c>
       <c r="AG318" t="n">
-        <v>17.496</v>
+        <v>17.21</v>
       </c>
       <c r="AH318" t="n">
-        <v>9.396000000000001</v>
+        <v>9.317</v>
       </c>
       <c r="AI318" t="n">
-        <v>5.281</v>
+        <v>5.145</v>
       </c>
       <c r="AJ318" t="n">
-        <v>19</v>
+        <v>19.04</v>
       </c>
       <c r="AK318" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="AL318" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="319">
@@ -38786,22 +38786,22 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F320" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G320" t="b">
         <v>1</v>
       </c>
       <c r="H320" t="n">
-        <v>1743.526</v>
+        <v>1751.007</v>
       </c>
       <c r="I320" t="n">
-        <v>3.091</v>
+        <v>3.1884</v>
       </c>
       <c r="J320" t="n">
-        <v>1550.6</v>
+        <v>1553.9</v>
       </c>
       <c r="K320" t="n">
         <v>45</v>
@@ -38822,70 +38822,70 @@
         <v>44</v>
       </c>
       <c r="Q320" t="n">
-        <v>118.247</v>
+        <v>118.302</v>
       </c>
       <c r="R320" t="n">
-        <v>103.782</v>
+        <v>103.549</v>
       </c>
       <c r="S320" t="n">
-        <v>14.465</v>
+        <v>14.753</v>
       </c>
       <c r="T320" t="n">
-        <v>0.29847</v>
+        <v>0.29877</v>
       </c>
       <c r="U320" t="n">
-        <v>0.15109</v>
+        <v>0.1491</v>
       </c>
       <c r="V320" t="n">
-        <v>81.94</v>
+        <v>81.86</v>
       </c>
       <c r="W320" t="n">
-        <v>71.94</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="X320" t="n">
-        <v>0.7836</v>
+        <v>0.79</v>
       </c>
       <c r="Y320" t="n">
-        <v>26.741</v>
+        <v>26.87</v>
       </c>
       <c r="Z320" t="n">
-        <v>57.81</v>
+        <v>58.15</v>
       </c>
       <c r="AA320" t="n">
-        <v>9.288</v>
+        <v>9.26</v>
       </c>
       <c r="AB320" t="n">
-        <v>25.398</v>
+        <v>25.44</v>
       </c>
       <c r="AC320" t="n">
-        <v>19.175</v>
+        <v>18.86</v>
       </c>
       <c r="AD320" t="n">
-        <v>25.927</v>
+        <v>25.46</v>
       </c>
       <c r="AE320" t="n">
-        <v>10.288</v>
+        <v>10.38</v>
       </c>
       <c r="AF320" t="n">
-        <v>23.968</v>
+        <v>24.16</v>
       </c>
       <c r="AG320" t="n">
-        <v>14.06</v>
+        <v>14.17</v>
       </c>
       <c r="AH320" t="n">
-        <v>7.329</v>
+        <v>7.33</v>
       </c>
       <c r="AI320" t="n">
-        <v>4.413</v>
+        <v>4.35</v>
       </c>
       <c r="AJ320" t="n">
-        <v>17.442</v>
+        <v>17.21</v>
       </c>
       <c r="AK320" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AL320" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="321">
@@ -39026,22 +39026,22 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F322" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G322" t="b">
         <v>1</v>
       </c>
       <c r="H322" t="n">
-        <v>1949.648</v>
+        <v>1967.845</v>
       </c>
       <c r="I322" t="n">
-        <v>1.887</v>
+        <v>1.6985</v>
       </c>
       <c r="J322" t="n">
-        <v>1701.5</v>
+        <v>1712.2</v>
       </c>
       <c r="K322" t="n">
         <v>13</v>
@@ -39062,70 +39062,70 @@
         <v>16</v>
       </c>
       <c r="Q322" t="n">
-        <v>121.837</v>
+        <v>122.917</v>
       </c>
       <c r="R322" t="n">
-        <v>105.792</v>
+        <v>106.352</v>
       </c>
       <c r="S322" t="n">
-        <v>16.046</v>
+        <v>16.565</v>
       </c>
       <c r="T322" t="n">
-        <v>0.28509</v>
+        <v>0.29372</v>
       </c>
       <c r="U322" t="n">
-        <v>0.1258</v>
+        <v>0.13022</v>
       </c>
       <c r="V322" t="n">
-        <v>86.44</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="W322" t="n">
-        <v>74.83</v>
+        <v>74.87</v>
       </c>
       <c r="X322" t="n">
-        <v>0.7836</v>
+        <v>0.79</v>
       </c>
       <c r="Y322" t="n">
-        <v>29.183</v>
+        <v>29.12</v>
       </c>
       <c r="Z322" t="n">
-        <v>61.328</v>
+        <v>61.2</v>
       </c>
       <c r="AA322" t="n">
-        <v>9.442</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AB322" t="n">
-        <v>27</v>
+        <v>26.6</v>
       </c>
       <c r="AC322" t="n">
-        <v>18.63</v>
+        <v>18.53</v>
       </c>
       <c r="AD322" t="n">
-        <v>23.712</v>
+        <v>23.66</v>
       </c>
       <c r="AE322" t="n">
-        <v>9.692</v>
+        <v>10.07</v>
       </c>
       <c r="AF322" t="n">
-        <v>23.844</v>
+        <v>23.64</v>
       </c>
       <c r="AG322" t="n">
-        <v>16.277</v>
+        <v>16.18</v>
       </c>
       <c r="AH322" t="n">
-        <v>8.164</v>
+        <v>8.06</v>
       </c>
       <c r="AI322" t="n">
-        <v>4.753</v>
+        <v>4.68</v>
       </c>
       <c r="AJ322" t="n">
-        <v>19.526</v>
+        <v>19.59</v>
       </c>
       <c r="AK322" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="AL322" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="323">
@@ -39146,22 +39146,22 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F323" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G323" t="b">
         <v>1</v>
       </c>
       <c r="H323" t="n">
-        <v>1469.955</v>
+        <v>1465.702</v>
       </c>
       <c r="I323" t="n">
-        <v>-1.5409</v>
+        <v>-1.4149</v>
       </c>
       <c r="J323" t="n">
-        <v>1389.6</v>
+        <v>1390.5</v>
       </c>
       <c r="K323" t="n">
         <v>235</v>
@@ -39182,70 +39182,70 @@
         <v>223</v>
       </c>
       <c r="Q323" t="n">
-        <v>111.419</v>
+        <v>110.802</v>
       </c>
       <c r="R323" t="n">
-        <v>105.017</v>
+        <v>105.675</v>
       </c>
       <c r="S323" t="n">
-        <v>6.402</v>
+        <v>5.127</v>
       </c>
       <c r="T323" t="n">
-        <v>0.24098</v>
+        <v>0.24212</v>
       </c>
       <c r="U323" t="n">
-        <v>0.14061</v>
+        <v>0.13988</v>
       </c>
       <c r="V323" t="n">
-        <v>72.45999999999999</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="W323" t="n">
-        <v>68.44</v>
+        <v>68.8</v>
       </c>
       <c r="X323" t="n">
-        <v>0.6486</v>
+        <v>0.6194</v>
       </c>
       <c r="Y323" t="n">
         <v>25.619</v>
       </c>
       <c r="Z323" t="n">
-        <v>55.958</v>
+        <v>56.089</v>
       </c>
       <c r="AA323" t="n">
-        <v>8.438000000000001</v>
+        <v>8.314</v>
       </c>
       <c r="AB323" t="n">
-        <v>24.968</v>
+        <v>25.049</v>
       </c>
       <c r="AC323" t="n">
-        <v>12.779</v>
+        <v>12.454</v>
       </c>
       <c r="AD323" t="n">
-        <v>17.651</v>
+        <v>17.37</v>
       </c>
       <c r="AE323" t="n">
-        <v>7.84</v>
+        <v>7.845</v>
       </c>
       <c r="AF323" t="n">
-        <v>24.956</v>
+        <v>24.818</v>
       </c>
       <c r="AG323" t="n">
-        <v>12.45</v>
+        <v>12.225</v>
       </c>
       <c r="AH323" t="n">
-        <v>4.582</v>
+        <v>4.446</v>
       </c>
       <c r="AI323" t="n">
         <v>2.69</v>
       </c>
       <c r="AJ323" t="n">
-        <v>16.878</v>
+        <v>16.978</v>
       </c>
       <c r="AK323" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AL323" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="324">
@@ -39386,22 +39386,22 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F325" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G325" t="b">
         <v>1</v>
       </c>
       <c r="H325" t="n">
-        <v>1970.983</v>
+        <v>1964.334</v>
       </c>
       <c r="I325" t="n">
-        <v>12.5889</v>
+        <v>12.2076</v>
       </c>
       <c r="J325" t="n">
-        <v>1646.9</v>
+        <v>1665.9</v>
       </c>
       <c r="K325" t="n">
         <v>20</v>
@@ -39422,70 +39422,70 @@
         <v>13</v>
       </c>
       <c r="Q325" t="n">
-        <v>119.48</v>
+        <v>119.042</v>
       </c>
       <c r="R325" t="n">
-        <v>100.211</v>
+        <v>100.852</v>
       </c>
       <c r="S325" t="n">
-        <v>19.27</v>
+        <v>18.19</v>
       </c>
       <c r="T325" t="n">
-        <v>0.31508</v>
+        <v>0.31535</v>
       </c>
       <c r="U325" t="n">
-        <v>0.15305</v>
+        <v>0.15437</v>
       </c>
       <c r="V325" t="n">
-        <v>81</v>
+        <v>80.56</v>
       </c>
       <c r="W325" t="n">
-        <v>68.19</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="X325" t="n">
-        <v>0.8798</v>
+        <v>0.8462</v>
       </c>
       <c r="Y325" t="n">
-        <v>28.326</v>
+        <v>28.144</v>
       </c>
       <c r="Z325" t="n">
-        <v>61.013</v>
+        <v>60.77</v>
       </c>
       <c r="AA325" t="n">
-        <v>10.189</v>
+        <v>10.101</v>
       </c>
       <c r="AB325" t="n">
-        <v>28.133</v>
+        <v>27.998</v>
       </c>
       <c r="AC325" t="n">
-        <v>14.035</v>
+        <v>14.058</v>
       </c>
       <c r="AD325" t="n">
-        <v>19.362</v>
+        <v>19.297</v>
       </c>
       <c r="AE325" t="n">
-        <v>11.94</v>
+        <v>11.868</v>
       </c>
       <c r="AF325" t="n">
-        <v>25.579</v>
+        <v>25.406</v>
       </c>
       <c r="AG325" t="n">
-        <v>16.79</v>
+        <v>16.499</v>
       </c>
       <c r="AH325" t="n">
-        <v>6.593</v>
+        <v>6.473</v>
       </c>
       <c r="AI325" t="n">
-        <v>6.21</v>
+        <v>6.426</v>
       </c>
       <c r="AJ325" t="n">
-        <v>17.825</v>
+        <v>17.854</v>
       </c>
       <c r="AK325" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="AL325" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="326">
@@ -41186,22 +41186,22 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F340" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G340" t="b">
         <v>1</v>
       </c>
       <c r="H340" t="n">
-        <v>1620.014</v>
+        <v>1632.575</v>
       </c>
       <c r="I340" t="n">
-        <v>1.5141</v>
+        <v>1.6748</v>
       </c>
       <c r="J340" t="n">
-        <v>1534.8</v>
+        <v>1540.9</v>
       </c>
       <c r="K340" t="n">
         <v>88</v>
@@ -41222,70 +41222,70 @@
         <v>80</v>
       </c>
       <c r="Q340" t="n">
-        <v>112.547</v>
+        <v>113.009</v>
       </c>
       <c r="R340" t="n">
-        <v>102.003</v>
+        <v>102.222</v>
       </c>
       <c r="S340" t="n">
-        <v>10.544</v>
+        <v>10.787</v>
       </c>
       <c r="T340" t="n">
-        <v>0.34769</v>
+        <v>0.34609</v>
       </c>
       <c r="U340" t="n">
-        <v>0.14168</v>
+        <v>0.14266</v>
       </c>
       <c r="V340" t="n">
-        <v>77.83</v>
+        <v>77.84</v>
       </c>
       <c r="W340" t="n">
-        <v>70.56</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="X340" t="n">
-        <v>0.6708</v>
+        <v>0.6812</v>
       </c>
       <c r="Y340" t="n">
-        <v>27.594</v>
+        <v>27.522</v>
       </c>
       <c r="Z340" t="n">
-        <v>62.68</v>
+        <v>62.443</v>
       </c>
       <c r="AA340" t="n">
-        <v>7.066</v>
+        <v>7.281</v>
       </c>
       <c r="AB340" t="n">
-        <v>21.114</v>
+        <v>21.377</v>
       </c>
       <c r="AC340" t="n">
-        <v>15.575</v>
+        <v>15.519</v>
       </c>
       <c r="AD340" t="n">
-        <v>22.599</v>
+        <v>22.528</v>
       </c>
       <c r="AE340" t="n">
-        <v>13.317</v>
+        <v>13.319</v>
       </c>
       <c r="AF340" t="n">
-        <v>24.909</v>
+        <v>25.11</v>
       </c>
       <c r="AG340" t="n">
-        <v>11.466</v>
+        <v>11.588</v>
       </c>
       <c r="AH340" t="n">
-        <v>6.207</v>
+        <v>6.041</v>
       </c>
       <c r="AI340" t="n">
-        <v>3.967</v>
+        <v>3.881</v>
       </c>
       <c r="AJ340" t="n">
-        <v>17.563</v>
+        <v>17.475</v>
       </c>
       <c r="AK340" t="n">
-        <v>11.2</v>
+        <v>13.2</v>
       </c>
       <c r="AL340" t="n">
-        <v>6.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="341">
@@ -41546,22 +41546,22 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F343" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G343" t="b">
         <v>1</v>
       </c>
       <c r="H343" t="n">
-        <v>1886.849</v>
+        <v>1882.441</v>
       </c>
       <c r="I343" t="n">
-        <v>2.1287</v>
+        <v>2.4266</v>
       </c>
       <c r="J343" t="n">
-        <v>1709.1</v>
+        <v>1724.6</v>
       </c>
       <c r="K343" t="n">
         <v>23</v>
@@ -41582,70 +41582,70 @@
         <v>26</v>
       </c>
       <c r="Q343" t="n">
-        <v>119.67</v>
+        <v>118.801</v>
       </c>
       <c r="R343" t="n">
-        <v>108.887</v>
+        <v>108.528</v>
       </c>
       <c r="S343" t="n">
-        <v>10.782</v>
+        <v>10.273</v>
       </c>
       <c r="T343" t="n">
-        <v>0.27872</v>
+        <v>0.27758</v>
       </c>
       <c r="U343" t="n">
-        <v>0.12218</v>
+        <v>0.12395</v>
       </c>
       <c r="V343" t="n">
-        <v>83.61</v>
+        <v>82.86</v>
       </c>
       <c r="W343" t="n">
-        <v>76.25</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="X343" t="n">
-        <v>0.7296</v>
+        <v>0.7003</v>
       </c>
       <c r="Y343" t="n">
-        <v>28.269</v>
+        <v>28.019</v>
       </c>
       <c r="Z343" t="n">
-        <v>62.157</v>
+        <v>62.051</v>
       </c>
       <c r="AA343" t="n">
-        <v>11.584</v>
+        <v>11.769</v>
       </c>
       <c r="AB343" t="n">
-        <v>32.112</v>
+        <v>32.339</v>
       </c>
       <c r="AC343" t="n">
-        <v>15.37</v>
+        <v>14.964</v>
       </c>
       <c r="AD343" t="n">
-        <v>19.718</v>
+        <v>19.211</v>
       </c>
       <c r="AE343" t="n">
-        <v>9.391</v>
+        <v>9.305</v>
       </c>
       <c r="AF343" t="n">
-        <v>24.025</v>
+        <v>23.926</v>
       </c>
       <c r="AG343" t="n">
-        <v>16</v>
+        <v>15.926</v>
       </c>
       <c r="AH343" t="n">
-        <v>5.417</v>
+        <v>5.586</v>
       </c>
       <c r="AI343" t="n">
-        <v>3.022</v>
+        <v>3.103</v>
       </c>
       <c r="AJ343" t="n">
-        <v>17.441</v>
+        <v>17.268</v>
       </c>
       <c r="AK343" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AL343" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="344">
@@ -42146,22 +42146,22 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F348" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G348" t="b">
         <v>1</v>
       </c>
       <c r="H348" t="n">
-        <v>1720.17</v>
+        <v>1727.414</v>
       </c>
       <c r="I348" t="n">
-        <v>1.1161</v>
+        <v>1.0257</v>
       </c>
       <c r="J348" t="n">
-        <v>1457.4</v>
+        <v>1459.8</v>
       </c>
       <c r="K348" t="n">
         <v>78</v>
@@ -42182,70 +42182,70 @@
         <v>66</v>
       </c>
       <c r="Q348" t="n">
-        <v>120.934</v>
+        <v>122.206</v>
       </c>
       <c r="R348" t="n">
-        <v>107.169</v>
+        <v>108.541</v>
       </c>
       <c r="S348" t="n">
-        <v>13.765</v>
+        <v>13.665</v>
       </c>
       <c r="T348" t="n">
-        <v>0.28465</v>
+        <v>0.29232</v>
       </c>
       <c r="U348" t="n">
-        <v>0.13619</v>
+        <v>0.13558</v>
       </c>
       <c r="V348" t="n">
-        <v>80.15000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="W348" t="n">
-        <v>70.87</v>
+        <v>71.45</v>
       </c>
       <c r="X348" t="n">
-        <v>0.8111</v>
+        <v>0.8178</v>
       </c>
       <c r="Y348" t="n">
-        <v>28.02</v>
+        <v>28.405</v>
       </c>
       <c r="Z348" t="n">
-        <v>57.3</v>
+        <v>57.623</v>
       </c>
       <c r="AA348" t="n">
-        <v>8.191000000000001</v>
+        <v>8.324</v>
       </c>
       <c r="AB348" t="n">
-        <v>20.584</v>
+        <v>20.81</v>
       </c>
       <c r="AC348" t="n">
-        <v>15.922</v>
+        <v>15.47</v>
       </c>
       <c r="AD348" t="n">
-        <v>20.864</v>
+        <v>20.449</v>
       </c>
       <c r="AE348" t="n">
-        <v>9.244</v>
+        <v>9.587</v>
       </c>
       <c r="AF348" t="n">
-        <v>23.144</v>
+        <v>22.984</v>
       </c>
       <c r="AG348" t="n">
-        <v>15.322</v>
+        <v>15.644</v>
       </c>
       <c r="AH348" t="n">
-        <v>5.336</v>
+        <v>5.202</v>
       </c>
       <c r="AI348" t="n">
-        <v>2.962</v>
+        <v>3.121</v>
       </c>
       <c r="AJ348" t="n">
-        <v>16.284</v>
+        <v>16.028</v>
       </c>
       <c r="AK348" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AL348" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="349">
@@ -42386,22 +42386,22 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F350" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G350" t="b">
         <v>1</v>
       </c>
       <c r="H350" t="n">
-        <v>1597.103</v>
+        <v>1607.876</v>
       </c>
       <c r="I350" t="n">
-        <v>1.5316</v>
+        <v>1.5554</v>
       </c>
       <c r="J350" t="n">
-        <v>1454.2</v>
+        <v>1462.4</v>
       </c>
       <c r="K350" t="n">
         <v>112</v>
@@ -42422,70 +42422,70 @@
         <v>103</v>
       </c>
       <c r="Q350" t="n">
-        <v>107.841</v>
+        <v>107.215</v>
       </c>
       <c r="R350" t="n">
-        <v>99.536</v>
+        <v>99.24299999999999</v>
       </c>
       <c r="S350" t="n">
-        <v>8.305</v>
+        <v>7.972</v>
       </c>
       <c r="T350" t="n">
-        <v>0.3313</v>
+        <v>0.32874</v>
       </c>
       <c r="U350" t="n">
-        <v>0.17184</v>
+        <v>0.17351</v>
       </c>
       <c r="V350" t="n">
-        <v>73.48</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="W350" t="n">
-        <v>67.83</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="X350" t="n">
-        <v>0.7527</v>
+        <v>0.76</v>
       </c>
       <c r="Y350" t="n">
-        <v>25.786</v>
+        <v>25.57</v>
       </c>
       <c r="Z350" t="n">
-        <v>59.394</v>
+        <v>58.97</v>
       </c>
       <c r="AA350" t="n">
-        <v>6.372</v>
+        <v>6.21</v>
       </c>
       <c r="AB350" t="n">
-        <v>18.824</v>
+        <v>18.41</v>
       </c>
       <c r="AC350" t="n">
-        <v>15.535</v>
+        <v>15.5</v>
       </c>
       <c r="AD350" t="n">
-        <v>21.688</v>
+        <v>21.84</v>
       </c>
       <c r="AE350" t="n">
-        <v>12.567</v>
+        <v>12.42</v>
       </c>
       <c r="AF350" t="n">
-        <v>24.804</v>
+        <v>24.78</v>
       </c>
       <c r="AG350" t="n">
-        <v>10.371</v>
+        <v>10.4</v>
       </c>
       <c r="AH350" t="n">
-        <v>5.465</v>
+        <v>5.46</v>
       </c>
       <c r="AI350" t="n">
-        <v>2.886</v>
+        <v>2.91</v>
       </c>
       <c r="AJ350" t="n">
-        <v>18.628</v>
+        <v>18.35</v>
       </c>
       <c r="AK350" t="n">
-        <v>17.4</v>
+        <v>15.4</v>
       </c>
       <c r="AL350" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="351">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -2306,22 +2306,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1961.738</v>
+        <v>1977.002</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2535</v>
+        <v>5.1479</v>
       </c>
       <c r="J16" t="n">
-        <v>1726.7</v>
+        <v>1736</v>
       </c>
       <c r="K16" t="n">
         <v>18</v>
@@ -2342,70 +2342,70 @@
         <v>18</v>
       </c>
       <c r="Q16" t="n">
-        <v>122.845</v>
+        <v>122.871</v>
       </c>
       <c r="R16" t="n">
-        <v>109.473</v>
+        <v>109.332</v>
       </c>
       <c r="S16" t="n">
-        <v>13.372</v>
+        <v>13.539</v>
       </c>
       <c r="T16" t="n">
-        <v>0.30449</v>
+        <v>0.29787</v>
       </c>
       <c r="U16" t="n">
-        <v>0.11969</v>
+        <v>0.12058</v>
       </c>
       <c r="V16" t="n">
-        <v>90.09</v>
+        <v>89.91</v>
       </c>
       <c r="W16" t="n">
-        <v>80.31999999999999</v>
+        <v>80.05</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>32.15</v>
+        <v>32.072</v>
       </c>
       <c r="Z16" t="n">
-        <v>64.40300000000001</v>
+        <v>64.128</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.103</v>
+        <v>8.375999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>21.314</v>
+        <v>21.432</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.681</v>
+        <v>17.391</v>
       </c>
       <c r="AD16" t="n">
-        <v>23.668</v>
+        <v>23.287</v>
       </c>
       <c r="AE16" t="n">
-        <v>10.231</v>
+        <v>9.99</v>
       </c>
       <c r="AF16" t="n">
-        <v>23.343</v>
+        <v>23.588</v>
       </c>
       <c r="AG16" t="n">
-        <v>16.863</v>
+        <v>17.031</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.377</v>
+        <v>7.239</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.087</v>
+        <v>5.117</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16.971</v>
+        <v>16.881</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="17">
@@ -8546,22 +8546,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F68" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1688.075</v>
+        <v>1677.744</v>
       </c>
       <c r="I68" t="n">
-        <v>-2.1851</v>
+        <v>-1.9174</v>
       </c>
       <c r="J68" t="n">
-        <v>1570.2</v>
+        <v>1574.7</v>
       </c>
       <c r="K68" t="n">
         <v>79</v>
@@ -8582,70 +8582,70 @@
         <v>75</v>
       </c>
       <c r="Q68" t="n">
-        <v>109.548</v>
+        <v>109.173</v>
       </c>
       <c r="R68" t="n">
-        <v>101.885</v>
+        <v>102.25</v>
       </c>
       <c r="S68" t="n">
-        <v>7.662</v>
+        <v>6.923</v>
       </c>
       <c r="T68" t="n">
-        <v>0.25276</v>
+        <v>0.25145</v>
       </c>
       <c r="U68" t="n">
-        <v>0.1736</v>
+        <v>0.17261</v>
       </c>
       <c r="V68" t="n">
-        <v>74.67</v>
+        <v>74.22</v>
       </c>
       <c r="W68" t="n">
-        <v>69.87</v>
+        <v>69.88</v>
       </c>
       <c r="X68" t="n">
-        <v>0.7005</v>
+        <v>0.6691</v>
       </c>
       <c r="Y68" t="n">
-        <v>24.007</v>
+        <v>23.989</v>
       </c>
       <c r="Z68" t="n">
-        <v>53.456</v>
+        <v>53.465</v>
       </c>
       <c r="AA68" t="n">
-        <v>7.694</v>
+        <v>7.64</v>
       </c>
       <c r="AB68" t="n">
-        <v>22.46</v>
+        <v>22.338</v>
       </c>
       <c r="AC68" t="n">
-        <v>18.923</v>
+        <v>18.571</v>
       </c>
       <c r="AD68" t="n">
-        <v>25.026</v>
+        <v>24.796</v>
       </c>
       <c r="AE68" t="n">
-        <v>7.928</v>
+        <v>7.942</v>
       </c>
       <c r="AF68" t="n">
-        <v>22.969</v>
+        <v>23.233</v>
       </c>
       <c r="AG68" t="n">
-        <v>14.341</v>
+        <v>14.4</v>
       </c>
       <c r="AH68" t="n">
-        <v>8.311999999999999</v>
+        <v>8.148999999999999</v>
       </c>
       <c r="AI68" t="n">
-        <v>4.173</v>
+        <v>4.145</v>
       </c>
       <c r="AJ68" t="n">
-        <v>16.891</v>
+        <v>16.865</v>
       </c>
       <c r="AK68" t="n">
-        <v>1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="AL68" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="69">
@@ -20666,22 +20666,22 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F169" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G169" t="b">
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>2196.807</v>
+        <v>2173.708</v>
       </c>
       <c r="I169" t="n">
-        <v>6.739</v>
+        <v>6.5185</v>
       </c>
       <c r="J169" t="n">
-        <v>1772.9</v>
+        <v>1779.9</v>
       </c>
       <c r="K169" t="n">
         <v>2</v>
@@ -20702,70 +20702,70 @@
         <v>2</v>
       </c>
       <c r="Q169" t="n">
-        <v>120.645</v>
+        <v>120.66</v>
       </c>
       <c r="R169" t="n">
-        <v>95.937</v>
+        <v>97.182</v>
       </c>
       <c r="S169" t="n">
-        <v>24.707</v>
+        <v>23.477</v>
       </c>
       <c r="T169" t="n">
-        <v>0.26043</v>
+        <v>0.25981</v>
       </c>
       <c r="U169" t="n">
-        <v>0.16661</v>
+        <v>0.1613</v>
       </c>
       <c r="V169" t="n">
-        <v>87.11</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="W169" t="n">
-        <v>68.84999999999999</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="X169" t="n">
-        <v>0.9399</v>
+        <v>0.9046</v>
       </c>
       <c r="Y169" t="n">
-        <v>30.379</v>
+        <v>30.409</v>
       </c>
       <c r="Z169" t="n">
-        <v>60.043</v>
+        <v>59.947</v>
       </c>
       <c r="AA169" t="n">
-        <v>9.112</v>
+        <v>8.932</v>
       </c>
       <c r="AB169" t="n">
-        <v>25.18</v>
+        <v>24.768</v>
       </c>
       <c r="AC169" t="n">
-        <v>17.242</v>
+        <v>17.255</v>
       </c>
       <c r="AD169" t="n">
-        <v>23.088</v>
+        <v>23.138</v>
       </c>
       <c r="AE169" t="n">
-        <v>10.03</v>
+        <v>9.917999999999999</v>
       </c>
       <c r="AF169" t="n">
-        <v>28.197</v>
+        <v>27.953</v>
       </c>
       <c r="AG169" t="n">
-        <v>18.529</v>
+        <v>18.666</v>
       </c>
       <c r="AH169" t="n">
-        <v>5.811</v>
+        <v>5.751</v>
       </c>
       <c r="AI169" t="n">
-        <v>5.987</v>
+        <v>5.934</v>
       </c>
       <c r="AJ169" t="n">
-        <v>15.482</v>
+        <v>15.451</v>
       </c>
       <c r="AK169" t="n">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="AL169" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="170">
@@ -27386,22 +27386,22 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F225" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G225" t="b">
         <v>1</v>
       </c>
       <c r="H225" t="n">
-        <v>1431.706</v>
+        <v>1458.418</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1135</v>
+        <v>1.2024</v>
       </c>
       <c r="J225" t="n">
-        <v>1482.7</v>
+        <v>1493.7</v>
       </c>
       <c r="K225" t="n">
         <v>163</v>
@@ -27422,70 +27422,70 @@
         <v>148</v>
       </c>
       <c r="Q225" t="n">
-        <v>107.489</v>
+        <v>108.543</v>
       </c>
       <c r="R225" t="n">
-        <v>105.825</v>
+        <v>106.705</v>
       </c>
       <c r="S225" t="n">
-        <v>1.663</v>
+        <v>1.838</v>
       </c>
       <c r="T225" t="n">
-        <v>0.30844</v>
+        <v>0.31426</v>
       </c>
       <c r="U225" t="n">
-        <v>0.15432</v>
+        <v>0.15185</v>
       </c>
       <c r="V225" t="n">
-        <v>73.91</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="W225" t="n">
-        <v>72.79000000000001</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="X225" t="n">
-        <v>0.5981</v>
+        <v>0.612</v>
       </c>
       <c r="Y225" t="n">
-        <v>25.84</v>
+        <v>26.097</v>
       </c>
       <c r="Z225" t="n">
-        <v>59.369</v>
+        <v>59.889</v>
       </c>
       <c r="AA225" t="n">
-        <v>7.89</v>
+        <v>7.942</v>
       </c>
       <c r="AB225" t="n">
-        <v>21.135</v>
+        <v>21.143</v>
       </c>
       <c r="AC225" t="n">
-        <v>14.24</v>
+        <v>14.34</v>
       </c>
       <c r="AD225" t="n">
-        <v>20.671</v>
+        <v>20.739</v>
       </c>
       <c r="AE225" t="n">
-        <v>10.306</v>
+        <v>10.616</v>
       </c>
       <c r="AF225" t="n">
-        <v>23.427</v>
+        <v>23.33</v>
       </c>
       <c r="AG225" t="n">
-        <v>13.662</v>
+        <v>14.076</v>
       </c>
       <c r="AH225" t="n">
-        <v>6.435</v>
+        <v>6.601</v>
       </c>
       <c r="AI225" t="n">
-        <v>3.223</v>
+        <v>3.224</v>
       </c>
       <c r="AJ225" t="n">
-        <v>16.763</v>
+        <v>16.776</v>
       </c>
       <c r="AK225" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AL225" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="226">
@@ -28586,22 +28586,22 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F235" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G235" t="b">
         <v>1</v>
       </c>
       <c r="H235" t="n">
-        <v>1986.929</v>
+        <v>2010.028</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.7024</v>
       </c>
       <c r="J235" t="n">
-        <v>1754.6</v>
+        <v>1769.7</v>
       </c>
       <c r="K235" t="n">
         <v>8</v>
@@ -28622,70 +28622,70 @@
         <v>10</v>
       </c>
       <c r="Q235" t="n">
-        <v>124.757</v>
+        <v>124.873</v>
       </c>
       <c r="R235" t="n">
-        <v>107.247</v>
+        <v>107.488</v>
       </c>
       <c r="S235" t="n">
-        <v>17.51</v>
+        <v>17.385</v>
       </c>
       <c r="T235" t="n">
-        <v>0.31049</v>
+        <v>0.31102</v>
       </c>
       <c r="U235" t="n">
-        <v>0.13425</v>
+        <v>0.13371</v>
       </c>
       <c r="V235" t="n">
-        <v>81.62</v>
+        <v>81.64</v>
       </c>
       <c r="W235" t="n">
-        <v>70.05</v>
+        <v>70.16</v>
       </c>
       <c r="X235" t="n">
-        <v>0.7669</v>
+        <v>0.7734</v>
       </c>
       <c r="Y235" t="n">
-        <v>29.662</v>
+        <v>29.717</v>
       </c>
       <c r="Z235" t="n">
-        <v>59.914</v>
+        <v>60.092</v>
       </c>
       <c r="AA235" t="n">
-        <v>9.331</v>
+        <v>9.266</v>
       </c>
       <c r="AB235" t="n">
-        <v>24.516</v>
+        <v>24.538</v>
       </c>
       <c r="AC235" t="n">
-        <v>12.234</v>
+        <v>11.996</v>
       </c>
       <c r="AD235" t="n">
-        <v>16.536</v>
+        <v>16.196</v>
       </c>
       <c r="AE235" t="n">
-        <v>10.515</v>
+        <v>10.547</v>
       </c>
       <c r="AF235" t="n">
-        <v>22.944</v>
+        <v>22.963</v>
       </c>
       <c r="AG235" t="n">
-        <v>19.632</v>
+        <v>19.475</v>
       </c>
       <c r="AH235" t="n">
-        <v>5.64</v>
+        <v>5.484</v>
       </c>
       <c r="AI235" t="n">
-        <v>2.632</v>
+        <v>2.66</v>
       </c>
       <c r="AJ235" t="n">
-        <v>14.883</v>
+        <v>14.998</v>
       </c>
       <c r="AK235" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AL235" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="236">
@@ -32426,22 +32426,22 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F267" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G267" t="b">
         <v>1</v>
       </c>
       <c r="H267" t="n">
-        <v>1714.878</v>
+        <v>1723.482</v>
       </c>
       <c r="I267" t="n">
-        <v>9.035</v>
+        <v>8.857799999999999</v>
       </c>
       <c r="J267" t="n">
-        <v>1550.3</v>
+        <v>1554.8</v>
       </c>
       <c r="K267" t="n">
         <v>51</v>
@@ -32462,70 +32462,70 @@
         <v>49</v>
       </c>
       <c r="Q267" t="n">
-        <v>116.325</v>
+        <v>115.66</v>
       </c>
       <c r="R267" t="n">
-        <v>101.484</v>
+        <v>100.714</v>
       </c>
       <c r="S267" t="n">
-        <v>14.84</v>
+        <v>14.946</v>
       </c>
       <c r="T267" t="n">
-        <v>0.34115</v>
+        <v>0.33977</v>
       </c>
       <c r="U267" t="n">
-        <v>0.14659</v>
+        <v>0.14645</v>
       </c>
       <c r="V267" t="n">
-        <v>87.53</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="W267" t="n">
-        <v>76.84999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="X267" t="n">
-        <v>0.7449</v>
+        <v>0.7527</v>
       </c>
       <c r="Y267" t="n">
-        <v>28.907</v>
+        <v>28.626</v>
       </c>
       <c r="Z267" t="n">
-        <v>65.907</v>
+        <v>65.66800000000001</v>
       </c>
       <c r="AA267" t="n">
-        <v>9.672000000000001</v>
+        <v>9.493</v>
       </c>
       <c r="AB267" t="n">
-        <v>29</v>
+        <v>28.708</v>
       </c>
       <c r="AC267" t="n">
-        <v>20.043</v>
+        <v>20.071</v>
       </c>
       <c r="AD267" t="n">
-        <v>26.997</v>
+        <v>26.988</v>
       </c>
       <c r="AE267" t="n">
-        <v>13.397</v>
+        <v>13.34</v>
       </c>
       <c r="AF267" t="n">
-        <v>25.67</v>
+        <v>25.733</v>
       </c>
       <c r="AG267" t="n">
-        <v>16.988</v>
+        <v>16.833</v>
       </c>
       <c r="AH267" t="n">
-        <v>8.843</v>
+        <v>8.856</v>
       </c>
       <c r="AI267" t="n">
-        <v>4.072</v>
+        <v>4.051</v>
       </c>
       <c r="AJ267" t="n">
-        <v>19.71</v>
+        <v>19.753</v>
       </c>
       <c r="AK267" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="AL267" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="268">
@@ -38786,22 +38786,22 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F320" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G320" t="b">
         <v>1</v>
       </c>
       <c r="H320" t="n">
-        <v>1751.007</v>
+        <v>1761.339</v>
       </c>
       <c r="I320" t="n">
-        <v>3.1884</v>
+        <v>3.2921</v>
       </c>
       <c r="J320" t="n">
-        <v>1553.9</v>
+        <v>1558.4</v>
       </c>
       <c r="K320" t="n">
         <v>45</v>
@@ -38822,70 +38822,70 @@
         <v>44</v>
       </c>
       <c r="Q320" t="n">
-        <v>118.302</v>
+        <v>117.937</v>
       </c>
       <c r="R320" t="n">
-        <v>103.549</v>
+        <v>103.323</v>
       </c>
       <c r="S320" t="n">
-        <v>14.753</v>
+        <v>14.613</v>
       </c>
       <c r="T320" t="n">
-        <v>0.29877</v>
+        <v>0.29406</v>
       </c>
       <c r="U320" t="n">
-        <v>0.1491</v>
+        <v>0.14675</v>
       </c>
       <c r="V320" t="n">
-        <v>81.86</v>
+        <v>81.45</v>
       </c>
       <c r="W320" t="n">
-        <v>71.68000000000001</v>
+        <v>71.38</v>
       </c>
       <c r="X320" t="n">
-        <v>0.79</v>
+        <v>0.796</v>
       </c>
       <c r="Y320" t="n">
-        <v>26.87</v>
+        <v>26.7</v>
       </c>
       <c r="Z320" t="n">
-        <v>58.15</v>
+        <v>58.049</v>
       </c>
       <c r="AA320" t="n">
-        <v>9.26</v>
+        <v>9.339</v>
       </c>
       <c r="AB320" t="n">
-        <v>25.44</v>
+        <v>25.399</v>
       </c>
       <c r="AC320" t="n">
-        <v>18.86</v>
+        <v>18.711</v>
       </c>
       <c r="AD320" t="n">
-        <v>25.46</v>
+        <v>25.323</v>
       </c>
       <c r="AE320" t="n">
-        <v>10.38</v>
+        <v>10.196</v>
       </c>
       <c r="AF320" t="n">
-        <v>24.16</v>
+        <v>24.27</v>
       </c>
       <c r="AG320" t="n">
-        <v>14.17</v>
+        <v>14.069</v>
       </c>
       <c r="AH320" t="n">
-        <v>7.33</v>
+        <v>7.397</v>
       </c>
       <c r="AI320" t="n">
         <v>4.35</v>
       </c>
       <c r="AJ320" t="n">
-        <v>17.21</v>
+        <v>17.301</v>
       </c>
       <c r="AK320" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AL320" t="n">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="321">
@@ -39026,22 +39026,22 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F322" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G322" t="b">
         <v>1</v>
       </c>
       <c r="H322" t="n">
-        <v>1967.845</v>
+        <v>1952.581</v>
       </c>
       <c r="I322" t="n">
-        <v>1.6985</v>
+        <v>1.6305</v>
       </c>
       <c r="J322" t="n">
-        <v>1712.2</v>
+        <v>1718.8</v>
       </c>
       <c r="K322" t="n">
         <v>13</v>
@@ -39062,70 +39062,70 @@
         <v>16</v>
       </c>
       <c r="Q322" t="n">
-        <v>122.917</v>
+        <v>122.082</v>
       </c>
       <c r="R322" t="n">
-        <v>106.352</v>
+        <v>106.871</v>
       </c>
       <c r="S322" t="n">
-        <v>16.565</v>
+        <v>15.211</v>
       </c>
       <c r="T322" t="n">
-        <v>0.29372</v>
+        <v>0.29148</v>
       </c>
       <c r="U322" t="n">
-        <v>0.13022</v>
+        <v>0.12812</v>
       </c>
       <c r="V322" t="n">
-        <v>86.73999999999999</v>
+        <v>86.25</v>
       </c>
       <c r="W322" t="n">
-        <v>74.87</v>
+        <v>75.31</v>
       </c>
       <c r="X322" t="n">
-        <v>0.79</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="Y322" t="n">
-        <v>29.12</v>
+        <v>28.992</v>
       </c>
       <c r="Z322" t="n">
-        <v>61.2</v>
+        <v>61.425</v>
       </c>
       <c r="AA322" t="n">
-        <v>9.289999999999999</v>
+        <v>9.359</v>
       </c>
       <c r="AB322" t="n">
-        <v>26.6</v>
+        <v>26.593</v>
       </c>
       <c r="AC322" t="n">
-        <v>18.53</v>
+        <v>18.409</v>
       </c>
       <c r="AD322" t="n">
-        <v>23.66</v>
+        <v>23.333</v>
       </c>
       <c r="AE322" t="n">
-        <v>10.07</v>
+        <v>9.971</v>
       </c>
       <c r="AF322" t="n">
-        <v>23.64</v>
+        <v>23.709</v>
       </c>
       <c r="AG322" t="n">
-        <v>16.18</v>
+        <v>16.127</v>
       </c>
       <c r="AH322" t="n">
-        <v>8.06</v>
+        <v>8.048999999999999</v>
       </c>
       <c r="AI322" t="n">
-        <v>4.68</v>
+        <v>4.555</v>
       </c>
       <c r="AJ322" t="n">
-        <v>19.59</v>
+        <v>19.323</v>
       </c>
       <c r="AK322" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AL322" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="323">
@@ -41186,22 +41186,22 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F340" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G340" t="b">
         <v>1</v>
       </c>
       <c r="H340" t="n">
-        <v>1632.575</v>
+        <v>1623.971</v>
       </c>
       <c r="I340" t="n">
-        <v>1.6748</v>
+        <v>1.8722</v>
       </c>
       <c r="J340" t="n">
-        <v>1540.9</v>
+        <v>1546.5</v>
       </c>
       <c r="K340" t="n">
         <v>88</v>
@@ -41222,70 +41222,70 @@
         <v>80</v>
       </c>
       <c r="Q340" t="n">
-        <v>113.009</v>
+        <v>111.577</v>
       </c>
       <c r="R340" t="n">
-        <v>102.222</v>
+        <v>102.283</v>
       </c>
       <c r="S340" t="n">
-        <v>10.787</v>
+        <v>9.295</v>
       </c>
       <c r="T340" t="n">
-        <v>0.34609</v>
+        <v>0.34458</v>
       </c>
       <c r="U340" t="n">
-        <v>0.14266</v>
+        <v>0.14529</v>
       </c>
       <c r="V340" t="n">
-        <v>77.84</v>
+        <v>76.86</v>
       </c>
       <c r="W340" t="n">
         <v>70.45999999999999</v>
       </c>
       <c r="X340" t="n">
-        <v>0.6812</v>
+        <v>0.6492</v>
       </c>
       <c r="Y340" t="n">
-        <v>27.522</v>
+        <v>27.161</v>
       </c>
       <c r="Z340" t="n">
-        <v>62.443</v>
+        <v>62.214</v>
       </c>
       <c r="AA340" t="n">
-        <v>7.281</v>
+        <v>7.091</v>
       </c>
       <c r="AB340" t="n">
-        <v>21.377</v>
+        <v>21.226</v>
       </c>
       <c r="AC340" t="n">
-        <v>15.519</v>
+        <v>15.442</v>
       </c>
       <c r="AD340" t="n">
-        <v>22.528</v>
+        <v>22.473</v>
       </c>
       <c r="AE340" t="n">
-        <v>13.319</v>
+        <v>13.267</v>
       </c>
       <c r="AF340" t="n">
-        <v>25.11</v>
+        <v>25.187</v>
       </c>
       <c r="AG340" t="n">
-        <v>11.588</v>
+        <v>11.401</v>
       </c>
       <c r="AH340" t="n">
-        <v>6.041</v>
+        <v>6.103</v>
       </c>
       <c r="AI340" t="n">
-        <v>3.881</v>
+        <v>4.032</v>
       </c>
       <c r="AJ340" t="n">
-        <v>17.475</v>
+        <v>17.578</v>
       </c>
       <c r="AK340" t="n">
-        <v>13.2</v>
+        <v>7.8</v>
       </c>
       <c r="AL340" t="n">
-        <v>8.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="341">
@@ -42146,22 +42146,22 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F348" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G348" t="b">
         <v>1</v>
       </c>
       <c r="H348" t="n">
-        <v>1727.414</v>
+        <v>1684.172</v>
       </c>
       <c r="I348" t="n">
-        <v>1.0257</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="J348" t="n">
-        <v>1459.8</v>
+        <v>1457.5</v>
       </c>
       <c r="K348" t="n">
         <v>78</v>
@@ -42182,70 +42182,70 @@
         <v>66</v>
       </c>
       <c r="Q348" t="n">
-        <v>122.206</v>
+        <v>121.507</v>
       </c>
       <c r="R348" t="n">
-        <v>108.541</v>
+        <v>108.892</v>
       </c>
       <c r="S348" t="n">
-        <v>13.665</v>
+        <v>12.615</v>
       </c>
       <c r="T348" t="n">
-        <v>0.29232</v>
+        <v>0.29055</v>
       </c>
       <c r="U348" t="n">
-        <v>0.13558</v>
+        <v>0.13803</v>
       </c>
       <c r="V348" t="n">
-        <v>80.59999999999999</v>
+        <v>80.66</v>
       </c>
       <c r="W348" t="n">
-        <v>71.45</v>
+        <v>72.2</v>
       </c>
       <c r="X348" t="n">
-        <v>0.8178</v>
+        <v>0.7741</v>
       </c>
       <c r="Y348" t="n">
-        <v>28.405</v>
+        <v>28.331</v>
       </c>
       <c r="Z348" t="n">
-        <v>57.623</v>
+        <v>57.843</v>
       </c>
       <c r="AA348" t="n">
-        <v>8.324</v>
+        <v>8.581</v>
       </c>
       <c r="AB348" t="n">
-        <v>20.81</v>
+        <v>21.104</v>
       </c>
       <c r="AC348" t="n">
-        <v>15.47</v>
+        <v>15.613</v>
       </c>
       <c r="AD348" t="n">
-        <v>20.449</v>
+        <v>20.328</v>
       </c>
       <c r="AE348" t="n">
-        <v>9.587</v>
+        <v>9.557</v>
       </c>
       <c r="AF348" t="n">
-        <v>22.984</v>
+        <v>23.15</v>
       </c>
       <c r="AG348" t="n">
-        <v>15.644</v>
+        <v>15.628</v>
       </c>
       <c r="AH348" t="n">
-        <v>5.202</v>
+        <v>5.211</v>
       </c>
       <c r="AI348" t="n">
-        <v>3.121</v>
+        <v>3.12</v>
       </c>
       <c r="AJ348" t="n">
-        <v>16.028</v>
+        <v>16.106</v>
       </c>
       <c r="AK348" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AL348" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="349">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,192 +429,192 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Conf</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>N_games</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>has_box_score</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>POM</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MOR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>WLK</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>BIH</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>NET</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>avg_Score</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>avg_OppScore</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>avg_Won</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>avg_FGM</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>avg_FGA</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>avg_FGM3</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>avg_FGA3</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>avg_FTM</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>avg_FTA</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>avg_OR</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>avg_DR</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>avg_Ast</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>avg_Stl</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>avg_Blk</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>avg_PF</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>last10_Margin</t>
         </is>
@@ -644,19 +656,19 @@
         <v>1489.4</v>
       </c>
       <c r="K2" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="L2" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="M2" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="N2" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="O2" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P2" t="n">
         <v>248</v>
@@ -764,16 +776,16 @@
         <v>1572.4</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L3" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M3" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="N3" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="O3" t="n">
         <v>346</v>
@@ -884,19 +896,19 @@
         <v>1479.2</v>
       </c>
       <c r="K4" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L4" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="N4" t="n">
         <v>54</v>
       </c>
       <c r="O4" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P4" t="n">
         <v>52</v>
@@ -1004,16 +1016,16 @@
         <v>1767</v>
       </c>
       <c r="K5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L5" t="n">
+        <v>11</v>
+      </c>
+      <c r="M5" t="n">
+        <v>16</v>
+      </c>
+      <c r="N5" t="n">
         <v>15</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" t="n">
-        <v>12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>12</v>
       </c>
       <c r="O5" t="n">
         <v>14</v>
@@ -1124,16 +1136,16 @@
         <v>1355.6</v>
       </c>
       <c r="K6" t="n">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="L6" t="n">
         <v>319</v>
       </c>
       <c r="M6" t="n">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="N6" t="n">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="O6" t="n">
         <v>265</v>
@@ -1244,19 +1256,19 @@
         <v>1382</v>
       </c>
       <c r="K7" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L7" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="M7" t="n">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="N7" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="O7" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="P7" t="n">
         <v>321</v>
@@ -1364,10 +1376,10 @@
         <v>1413.3</v>
       </c>
       <c r="K8" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L8" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M8" t="n">
         <v>292</v>
@@ -1379,7 +1391,7 @@
         <v>340</v>
       </c>
       <c r="P8" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q8" t="n">
         <v>104.333</v>
@@ -1484,19 +1496,19 @@
         <v>1405.1</v>
       </c>
       <c r="K9" t="n">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="L9" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="M9" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="N9" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="O9" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P9" t="n">
         <v>352</v>
@@ -1604,16 +1616,16 @@
         <v>1396.2</v>
       </c>
       <c r="K10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L10" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M10" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="O10" t="n">
         <v>258</v>
@@ -1724,22 +1736,22 @@
         <v>1423.8</v>
       </c>
       <c r="K11" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L11" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M11" t="n">
+        <v>193</v>
+      </c>
+      <c r="N11" t="n">
         <v>195</v>
       </c>
-      <c r="N11" t="n">
-        <v>193</v>
-      </c>
       <c r="O11" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="P11" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="Q11" t="n">
         <v>108.198</v>
@@ -1844,19 +1856,19 @@
         <v>1769.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1964,19 +1976,19 @@
         <v>1742.3</v>
       </c>
       <c r="K13" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L13" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M13" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="N13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P13" t="n">
         <v>67</v>
@@ -2084,22 +2096,22 @@
         <v>1400.2</v>
       </c>
       <c r="K14" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L14" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M14" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N14" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O14" t="n">
         <v>311</v>
       </c>
       <c r="P14" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Q14" t="n">
         <v>102.203</v>
@@ -2204,19 +2216,19 @@
         <v>1389.8</v>
       </c>
       <c r="K15" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L15" t="n">
         <v>335</v>
       </c>
       <c r="M15" t="n">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="N15" t="n">
         <v>312</v>
       </c>
       <c r="O15" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P15" t="n">
         <v>317</v>
@@ -2324,23 +2336,21 @@
         <v>1736</v>
       </c>
       <c r="K16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L16" t="n">
+        <v>12</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15</v>
+      </c>
+      <c r="N16" t="n">
         <v>14</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>20</v>
       </c>
-      <c r="N16" t="n">
-        <v>16</v>
-      </c>
-      <c r="O16" t="n">
-        <v>21</v>
-      </c>
-      <c r="P16" t="n">
-        <v>18</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
         <v>122.871</v>
       </c>
@@ -2444,22 +2454,22 @@
         <v>1449.7</v>
       </c>
       <c r="K17" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L17" t="n">
+        <v>146</v>
+      </c>
+      <c r="M17" t="n">
+        <v>166</v>
+      </c>
+      <c r="N17" t="n">
+        <v>145</v>
+      </c>
+      <c r="O17" t="n">
         <v>142</v>
       </c>
-      <c r="M17" t="n">
-        <v>172</v>
-      </c>
-      <c r="N17" t="n">
-        <v>146</v>
-      </c>
-      <c r="O17" t="n">
-        <v>143</v>
-      </c>
       <c r="P17" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="Q17" t="n">
         <v>111.178</v>
@@ -2567,10 +2577,10 @@
         <v>337</v>
       </c>
       <c r="L18" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M18" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N18" t="n">
         <v>338</v>
@@ -2579,7 +2589,7 @@
         <v>339</v>
       </c>
       <c r="P18" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q18" t="n">
         <v>102.472</v>
@@ -2684,19 +2694,19 @@
         <v>1757.6</v>
       </c>
       <c r="K19" t="n">
+        <v>38</v>
+      </c>
+      <c r="L19" t="n">
+        <v>29</v>
+      </c>
+      <c r="M19" t="n">
+        <v>38</v>
+      </c>
+      <c r="N19" t="n">
         <v>39</v>
       </c>
-      <c r="L19" t="n">
-        <v>31</v>
-      </c>
-      <c r="M19" t="n">
-        <v>44</v>
-      </c>
-      <c r="N19" t="n">
-        <v>40</v>
-      </c>
       <c r="O19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P19" t="n">
         <v>38</v>
@@ -2804,22 +2814,22 @@
         <v>1405.9</v>
       </c>
       <c r="K20" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L20" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="M20" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N20" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O20" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="P20" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="Q20" t="n">
         <v>112.877</v>
@@ -2924,22 +2934,22 @@
         <v>1439.8</v>
       </c>
       <c r="K21" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L21" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M21" t="n">
         <v>266</v>
       </c>
       <c r="N21" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O21" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P21" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="Q21" t="n">
         <v>99.752</v>
@@ -3044,19 +3054,19 @@
         <v>1727.4</v>
       </c>
       <c r="K22" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L22" t="n">
+        <v>46</v>
+      </c>
+      <c r="M22" t="n">
         <v>44</v>
       </c>
-      <c r="M22" t="n">
-        <v>40</v>
-      </c>
       <c r="N22" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O22" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P22" t="n">
         <v>48</v>
@@ -3164,22 +3174,22 @@
         <v>1485.7</v>
       </c>
       <c r="K23" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L23" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="M23" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N23" t="n">
         <v>61</v>
       </c>
       <c r="O23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P23" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="Q23" t="n">
         <v>118.567</v>
@@ -3284,19 +3294,19 @@
         <v>1430.6</v>
       </c>
       <c r="K24" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="L24" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="M24" t="n">
         <v>268</v>
       </c>
       <c r="N24" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="O24" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P24" t="n">
         <v>255</v>
@@ -3410,7 +3420,7 @@
         <v>361</v>
       </c>
       <c r="M25" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N25" t="n">
         <v>358</v>
@@ -3524,19 +3534,19 @@
         <v>1610.8</v>
       </c>
       <c r="K26" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="L26" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="M26" t="n">
+        <v>85</v>
+      </c>
+      <c r="N26" t="n">
         <v>76</v>
       </c>
-      <c r="N26" t="n">
-        <v>69</v>
-      </c>
       <c r="O26" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="P26" t="n">
         <v>57</v>
@@ -3644,22 +3654,22 @@
         <v>1614.9</v>
       </c>
       <c r="K27" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L27" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M27" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N27" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O27" t="n">
         <v>206</v>
       </c>
       <c r="P27" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Q27" t="n">
         <v>100.075</v>
@@ -3764,19 +3774,19 @@
         <v>1376.4</v>
       </c>
       <c r="K28" t="n">
+        <v>261</v>
+      </c>
+      <c r="L28" t="n">
+        <v>277</v>
+      </c>
+      <c r="M28" t="n">
         <v>254</v>
       </c>
-      <c r="L28" t="n">
-        <v>276</v>
-      </c>
-      <c r="M28" t="n">
-        <v>231</v>
-      </c>
       <c r="N28" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="O28" t="n">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="P28" t="n">
         <v>257</v>
@@ -3884,19 +3894,19 @@
         <v>1463.5</v>
       </c>
       <c r="K29" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L29" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="M29" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="N29" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="O29" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="P29" t="n">
         <v>155</v>
@@ -4007,19 +4017,19 @@
         <v>123</v>
       </c>
       <c r="L30" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M30" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="N30" t="n">
         <v>108</v>
       </c>
       <c r="O30" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="P30" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Q30" t="n">
         <v>110.424</v>
@@ -4124,22 +4134,22 @@
         <v>1449</v>
       </c>
       <c r="K31" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L31" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M31" t="n">
         <v>275</v>
       </c>
       <c r="N31" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O31" t="n">
         <v>318</v>
       </c>
       <c r="P31" t="n">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="Q31" t="n">
         <v>97.68300000000001</v>
@@ -4253,13 +4263,13 @@
         <v>352</v>
       </c>
       <c r="N32" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O32" t="n">
         <v>349</v>
       </c>
       <c r="P32" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="Q32" t="n">
         <v>95.277</v>
@@ -4373,13 +4383,13 @@
         <v>325</v>
       </c>
       <c r="N33" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O33" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P33" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q33" t="n">
         <v>99.30200000000001</v>
@@ -4484,19 +4494,19 @@
         <v>1469.9</v>
       </c>
       <c r="K34" t="n">
+        <v>199</v>
+      </c>
+      <c r="L34" t="n">
+        <v>226</v>
+      </c>
+      <c r="M34" t="n">
         <v>207</v>
       </c>
-      <c r="L34" t="n">
-        <v>224</v>
-      </c>
-      <c r="M34" t="n">
-        <v>229</v>
-      </c>
       <c r="N34" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O34" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P34" t="n">
         <v>198</v>
@@ -4604,16 +4614,16 @@
         <v>1620.7</v>
       </c>
       <c r="K35" t="n">
+        <v>86</v>
+      </c>
+      <c r="L35" t="n">
+        <v>79</v>
+      </c>
+      <c r="M35" t="n">
+        <v>73</v>
+      </c>
+      <c r="N35" t="n">
         <v>82</v>
-      </c>
-      <c r="L35" t="n">
-        <v>71</v>
-      </c>
-      <c r="M35" t="n">
-        <v>67</v>
-      </c>
-      <c r="N35" t="n">
-        <v>81</v>
       </c>
       <c r="O35" t="n">
         <v>86</v>
@@ -4724,10 +4734,10 @@
         <v>1733.2</v>
       </c>
       <c r="K36" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L36" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M36" t="n">
         <v>22</v>
@@ -4736,7 +4746,7 @@
         <v>22</v>
       </c>
       <c r="O36" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P36" t="n">
         <v>24</v>
@@ -4844,7 +4854,7 @@
         <v>1466.6</v>
       </c>
       <c r="K37" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L37" t="n">
         <v>279</v>
@@ -4853,13 +4863,13 @@
         <v>281</v>
       </c>
       <c r="N37" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O37" t="n">
         <v>294</v>
       </c>
       <c r="P37" t="n">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="Q37" t="n">
         <v>105.894</v>
@@ -4964,19 +4974,19 @@
         <v>1496.9</v>
       </c>
       <c r="K38" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L38" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M38" t="n">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="N38" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="O38" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P38" t="n">
         <v>228</v>
@@ -5084,19 +5094,19 @@
         <v>1603.7</v>
       </c>
       <c r="K39" t="n">
+        <v>73</v>
+      </c>
+      <c r="L39" t="n">
+        <v>72</v>
+      </c>
+      <c r="M39" t="n">
         <v>71</v>
-      </c>
-      <c r="L39" t="n">
-        <v>65</v>
-      </c>
-      <c r="M39" t="n">
-        <v>73</v>
       </c>
       <c r="N39" t="n">
         <v>71</v>
       </c>
       <c r="O39" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P39" t="n">
         <v>65</v>
@@ -5204,19 +5214,19 @@
         <v>1518.8</v>
       </c>
       <c r="K40" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="L40" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="M40" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="N40" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="O40" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="P40" t="n">
         <v>192</v>
@@ -5324,22 +5334,22 @@
         <v>1434.6</v>
       </c>
       <c r="K41" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L41" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M41" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N41" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O41" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P41" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q41" t="n">
         <v>96.16800000000001</v>
@@ -5444,19 +5454,19 @@
         <v>1437</v>
       </c>
       <c r="K42" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L42" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M42" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N42" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O42" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P42" t="n">
         <v>166</v>
@@ -5564,22 +5574,22 @@
         <v>1359.6</v>
       </c>
       <c r="K43" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L43" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M43" t="n">
         <v>274</v>
       </c>
       <c r="N43" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O43" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P43" t="n">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Q43" t="n">
         <v>107.607</v>
@@ -5684,22 +5694,22 @@
         <v>1394.8</v>
       </c>
       <c r="K44" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L44" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M44" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N44" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O44" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P44" t="n">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Q44" t="n">
         <v>107.282</v>
@@ -5804,19 +5814,19 @@
         <v>1509.6</v>
       </c>
       <c r="K45" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="L45" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="M45" t="n">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="N45" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O45" t="n">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="P45" t="n">
         <v>183</v>
@@ -5924,22 +5934,22 @@
         <v>1422.3</v>
       </c>
       <c r="K46" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L46" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M46" t="n">
         <v>288</v>
       </c>
       <c r="N46" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O46" t="n">
         <v>304</v>
       </c>
       <c r="P46" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q46" t="n">
         <v>110.697</v>
@@ -6044,22 +6054,22 @@
         <v>1420</v>
       </c>
       <c r="K47" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L47" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M47" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N47" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O47" t="n">
         <v>350</v>
       </c>
       <c r="P47" t="n">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q47" t="n">
         <v>98.143</v>
@@ -6164,19 +6174,19 @@
         <v>1713.3</v>
       </c>
       <c r="K48" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L48" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M48" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N48" t="n">
         <v>43</v>
       </c>
       <c r="O48" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P48" t="n">
         <v>46</v>
@@ -6284,22 +6294,22 @@
         <v>1419.9</v>
       </c>
       <c r="K49" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L49" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M49" t="n">
         <v>349</v>
       </c>
       <c r="N49" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O49" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P49" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="Q49" t="n">
         <v>102.551</v>
@@ -6404,19 +6414,19 @@
         <v>1672.9</v>
       </c>
       <c r="K50" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L50" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M50" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N50" t="n">
         <v>35</v>
       </c>
       <c r="O50" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P50" t="n">
         <v>36</v>
@@ -6524,22 +6534,22 @@
         <v>1460</v>
       </c>
       <c r="K51" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L51" t="n">
         <v>288</v>
       </c>
       <c r="M51" t="n">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="N51" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="O51" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P51" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="Q51" t="n">
         <v>109.789</v>
@@ -6647,19 +6657,19 @@
         <v>247</v>
       </c>
       <c r="L52" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="M52" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N52" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O52" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="P52" t="n">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="Q52" t="n">
         <v>103.612</v>
@@ -6764,19 +6774,19 @@
         <v>1482.5</v>
       </c>
       <c r="K53" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L53" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="M53" t="n">
         <v>183</v>
       </c>
       <c r="N53" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="O53" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P53" t="n">
         <v>163</v>
@@ -6884,13 +6894,13 @@
         <v>1419.5</v>
       </c>
       <c r="K54" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L54" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M54" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N54" t="n">
         <v>224</v>
@@ -7004,19 +7014,19 @@
         <v>1689.7</v>
       </c>
       <c r="K55" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="L55" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M55" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="N55" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O55" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P55" t="n">
         <v>71</v>
@@ -7124,19 +7134,19 @@
         <v>1564.6</v>
       </c>
       <c r="K56" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L56" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M56" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N56" t="n">
         <v>85</v>
       </c>
       <c r="O56" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P56" t="n">
         <v>87</v>
@@ -7247,19 +7257,19 @@
         <v>189</v>
       </c>
       <c r="L57" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M57" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N57" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O57" t="n">
         <v>185</v>
       </c>
       <c r="P57" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="Q57" t="n">
         <v>108.916</v>
@@ -7367,13 +7377,13 @@
         <v>11</v>
       </c>
       <c r="L58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M58" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O58" t="n">
         <v>4</v>
@@ -7604,19 +7614,19 @@
         <v>1502.5</v>
       </c>
       <c r="K60" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="L60" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="M60" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="N60" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="O60" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="P60" t="n">
         <v>141</v>
@@ -7724,16 +7734,16 @@
         <v>1664.6</v>
       </c>
       <c r="K61" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L61" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M61" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="N61" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O61" t="n">
         <v>84</v>
@@ -7844,16 +7854,16 @@
         <v>1467.6</v>
       </c>
       <c r="K62" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L62" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M62" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="N62" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O62" t="n">
         <v>333</v>
@@ -7964,19 +7974,19 @@
         <v>1482.1</v>
       </c>
       <c r="K63" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L63" t="n">
         <v>195</v>
       </c>
       <c r="M63" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="N63" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O63" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P63" t="n">
         <v>180</v>
@@ -8084,19 +8094,19 @@
         <v>1463.1</v>
       </c>
       <c r="K64" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L64" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="M64" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="N64" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O64" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="P64" t="n">
         <v>190</v>
@@ -8207,7 +8217,7 @@
         <v>265</v>
       </c>
       <c r="L65" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="M65" t="n">
         <v>305</v>
@@ -8219,7 +8229,7 @@
         <v>292</v>
       </c>
       <c r="P65" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q65" t="n">
         <v>104.279</v>
@@ -8327,19 +8337,19 @@
         <v>274</v>
       </c>
       <c r="L66" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M66" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N66" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O66" t="n">
         <v>257</v>
       </c>
       <c r="P66" t="n">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="Q66" t="n">
         <v>105.276</v>
@@ -8444,19 +8454,19 @@
         <v>1539.4</v>
       </c>
       <c r="K67" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L67" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M67" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="N67" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="O67" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P67" t="n">
         <v>106</v>
@@ -8564,23 +8574,21 @@
         <v>1574.7</v>
       </c>
       <c r="K68" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L68" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="M68" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N68" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O68" t="n">
-        <v>66</v>
-      </c>
-      <c r="P68" t="n">
-        <v>75</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
         <v>109.173</v>
       </c>
@@ -8684,10 +8692,10 @@
         <v>1481.8</v>
       </c>
       <c r="K69" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L69" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M69" t="n">
         <v>291</v>
@@ -8699,7 +8707,7 @@
         <v>283</v>
       </c>
       <c r="P69" t="n">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="Q69" t="n">
         <v>104.493</v>
@@ -8810,10 +8818,10 @@
         <v>364</v>
       </c>
       <c r="M70" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N70" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O70" t="n">
         <v>362</v>
@@ -8924,10 +8932,10 @@
         <v>1449.1</v>
       </c>
       <c r="K71" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L71" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M71" t="n">
         <v>304</v>
@@ -8936,10 +8944,10 @@
         <v>249</v>
       </c>
       <c r="O71" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P71" t="n">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="Q71" t="n">
         <v>116.071</v>
@@ -9047,16 +9055,16 @@
         <v>102</v>
       </c>
       <c r="L72" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M72" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N72" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O72" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="P72" t="n">
         <v>101</v>
@@ -9164,19 +9172,19 @@
         <v>1453.7</v>
       </c>
       <c r="K73" t="n">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="L73" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M73" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="N73" t="n">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="O73" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P73" t="n">
         <v>229</v>
@@ -9284,22 +9292,22 @@
         <v>1528.6</v>
       </c>
       <c r="K74" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L74" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="M74" t="n">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="N74" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="O74" t="n">
         <v>230</v>
       </c>
       <c r="P74" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="Q74" t="n">
         <v>107.643</v>
@@ -9404,19 +9412,19 @@
         <v>1436.1</v>
       </c>
       <c r="K75" t="n">
+        <v>222</v>
+      </c>
+      <c r="L75" t="n">
         <v>221</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
+        <v>192</v>
+      </c>
+      <c r="N75" t="n">
+        <v>211</v>
+      </c>
+      <c r="O75" t="n">
         <v>219</v>
-      </c>
-      <c r="M75" t="n">
-        <v>194</v>
-      </c>
-      <c r="N75" t="n">
-        <v>210</v>
-      </c>
-      <c r="O75" t="n">
-        <v>221</v>
       </c>
       <c r="P75" t="n">
         <v>210</v>
@@ -9527,16 +9535,16 @@
         <v>1</v>
       </c>
       <c r="L76" t="n">
+        <v>2</v>
+      </c>
+      <c r="M76" t="n">
         <v>1</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2</v>
       </c>
       <c r="N76" t="n">
         <v>2</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P76" t="n">
         <v>1</v>
@@ -9644,19 +9652,19 @@
         <v>1548</v>
       </c>
       <c r="K77" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L77" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M77" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N77" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O77" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="P77" t="n">
         <v>140</v>
@@ -9764,22 +9772,22 @@
         <v>1439.7</v>
       </c>
       <c r="K78" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L78" t="n">
         <v>317</v>
       </c>
       <c r="M78" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N78" t="n">
         <v>317</v>
       </c>
       <c r="O78" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P78" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q78" t="n">
         <v>97.188</v>
@@ -9884,13 +9892,13 @@
         <v>1422.5</v>
       </c>
       <c r="K79" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L79" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M79" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N79" t="n">
         <v>293</v>
@@ -9899,7 +9907,7 @@
         <v>302</v>
       </c>
       <c r="P79" t="n">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="Q79" t="n">
         <v>111.589</v>
@@ -10004,22 +10012,22 @@
         <v>1478.3</v>
       </c>
       <c r="K80" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L80" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M80" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N80" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O80" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P80" t="n">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="Q80" t="n">
         <v>102.413</v>
@@ -10124,19 +10132,19 @@
         <v>1450.3</v>
       </c>
       <c r="K81" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="L81" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M81" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N81" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O81" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P81" t="n">
         <v>201</v>
@@ -10244,13 +10252,13 @@
         <v>1519.6</v>
       </c>
       <c r="K82" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L82" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M82" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N82" t="n">
         <v>274</v>
@@ -10370,16 +10378,16 @@
         <v>259</v>
       </c>
       <c r="M83" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N83" t="n">
         <v>246</v>
       </c>
       <c r="O83" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P83" t="n">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="Q83" t="n">
         <v>101.962</v>
@@ -10484,22 +10492,22 @@
         <v>1489.2</v>
       </c>
       <c r="K84" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L84" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M84" t="n">
         <v>218</v>
       </c>
       <c r="N84" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O84" t="n">
         <v>236</v>
       </c>
       <c r="P84" t="n">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="Q84" t="n">
         <v>111.233</v>
@@ -10604,19 +10612,19 @@
         <v>1421.6</v>
       </c>
       <c r="K85" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="L85" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="M85" t="n">
+        <v>173</v>
+      </c>
+      <c r="N85" t="n">
+        <v>146</v>
+      </c>
+      <c r="O85" t="n">
         <v>162</v>
-      </c>
-      <c r="N85" t="n">
-        <v>138</v>
-      </c>
-      <c r="O85" t="n">
-        <v>154</v>
       </c>
       <c r="P85" t="n">
         <v>126</v>
@@ -10724,22 +10732,22 @@
         <v>1566.8</v>
       </c>
       <c r="K86" t="n">
+        <v>308</v>
+      </c>
+      <c r="L86" t="n">
+        <v>275</v>
+      </c>
+      <c r="M86" t="n">
+        <v>243</v>
+      </c>
+      <c r="N86" t="n">
         <v>307</v>
-      </c>
-      <c r="L86" t="n">
-        <v>278</v>
-      </c>
-      <c r="M86" t="n">
-        <v>247</v>
-      </c>
-      <c r="N86" t="n">
-        <v>308</v>
       </c>
       <c r="O86" t="n">
         <v>305</v>
       </c>
       <c r="P86" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q86" t="n">
         <v>97.123</v>
@@ -10847,19 +10855,19 @@
         <v>336</v>
       </c>
       <c r="L87" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M87" t="n">
         <v>339</v>
       </c>
       <c r="N87" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O87" t="n">
         <v>345</v>
       </c>
       <c r="P87" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q87" t="n">
         <v>100.805</v>
@@ -10964,19 +10972,19 @@
         <v>1406</v>
       </c>
       <c r="K88" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L88" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M88" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N88" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O88" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P88" t="n">
         <v>242</v>
@@ -11084,19 +11092,19 @@
         <v>1558</v>
       </c>
       <c r="K89" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L89" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M89" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N89" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O89" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="P89" t="n">
         <v>123</v>
@@ -11204,22 +11212,22 @@
         <v>1431.6</v>
       </c>
       <c r="K90" t="n">
+        <v>244</v>
+      </c>
+      <c r="L90" t="n">
+        <v>248</v>
+      </c>
+      <c r="M90" t="n">
+        <v>230</v>
+      </c>
+      <c r="N90" t="n">
         <v>243</v>
-      </c>
-      <c r="L90" t="n">
-        <v>251</v>
-      </c>
-      <c r="M90" t="n">
-        <v>233</v>
-      </c>
-      <c r="N90" t="n">
-        <v>241</v>
       </c>
       <c r="O90" t="n">
         <v>260</v>
       </c>
       <c r="P90" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="Q90" t="n">
         <v>108.76</v>
@@ -11327,7 +11335,7 @@
         <v>4</v>
       </c>
       <c r="L91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M91" t="n">
         <v>4</v>
@@ -11336,7 +11344,7 @@
         <v>4</v>
       </c>
       <c r="O91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P91" t="n">
         <v>4</v>
@@ -11444,19 +11452,19 @@
         <v>1376.6</v>
       </c>
       <c r="K92" t="n">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="L92" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="M92" t="n">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="N92" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="O92" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P92" t="n">
         <v>315</v>
@@ -11564,19 +11572,19 @@
         <v>1490.2</v>
       </c>
       <c r="K93" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="L93" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="M93" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="N93" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O93" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P93" t="n">
         <v>191</v>
@@ -11684,19 +11692,19 @@
         <v>1678</v>
       </c>
       <c r="K94" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="L94" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M94" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N94" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="O94" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P94" t="n">
         <v>69</v>
@@ -11804,19 +11812,19 @@
         <v>1499.4</v>
       </c>
       <c r="K95" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L95" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="M95" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N95" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O95" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="P95" t="n">
         <v>174</v>
@@ -11924,19 +11932,19 @@
         <v>1590.6</v>
       </c>
       <c r="K96" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L96" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M96" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="N96" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O96" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="P96" t="n">
         <v>149</v>
@@ -12044,19 +12052,19 @@
         <v>1422.2</v>
       </c>
       <c r="K97" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="L97" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="M97" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="N97" t="n">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="O97" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="P97" t="n">
         <v>194</v>
@@ -12164,19 +12172,19 @@
         <v>1543.4</v>
       </c>
       <c r="K98" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L98" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M98" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N98" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O98" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P98" t="n">
         <v>90</v>
@@ -12284,19 +12292,19 @@
         <v>1449.5</v>
       </c>
       <c r="K99" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="L99" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="M99" t="n">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="N99" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="O99" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P99" t="n">
         <v>219</v>
@@ -12524,19 +12532,19 @@
         <v>1514.4</v>
       </c>
       <c r="K101" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L101" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="M101" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="N101" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="O101" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P101" t="n">
         <v>89</v>
@@ -12644,19 +12652,19 @@
         <v>1660.1</v>
       </c>
       <c r="K102" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="L102" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="M102" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N102" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O102" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P102" t="n">
         <v>95</v>
@@ -12764,19 +12772,19 @@
         <v>1643.1</v>
       </c>
       <c r="K103" t="n">
+        <v>32</v>
+      </c>
+      <c r="L103" t="n">
+        <v>34</v>
+      </c>
+      <c r="M103" t="n">
         <v>31</v>
       </c>
-      <c r="L103" t="n">
-        <v>28</v>
-      </c>
-      <c r="M103" t="n">
-        <v>28</v>
-      </c>
       <c r="N103" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="O103" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="P103" t="n">
         <v>31</v>
@@ -12887,19 +12895,19 @@
         <v>310</v>
       </c>
       <c r="L104" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M104" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N104" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O104" t="n">
         <v>319</v>
       </c>
       <c r="P104" t="n">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="Q104" t="n">
         <v>99.483</v>
@@ -13004,22 +13012,22 @@
         <v>1614.5</v>
       </c>
       <c r="K105" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L105" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M105" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N105" t="n">
         <v>167</v>
       </c>
       <c r="O105" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="P105" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q105" t="n">
         <v>102.629</v>
@@ -13127,10 +13135,10 @@
         <v>10</v>
       </c>
       <c r="L106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M106" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N106" t="n">
         <v>11</v>
@@ -13247,16 +13255,16 @@
         <v>298</v>
       </c>
       <c r="L107" t="n">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="M107" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="N107" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O107" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="P107" t="n">
         <v>301</v>
@@ -13364,19 +13372,19 @@
         <v>1581.4</v>
       </c>
       <c r="K108" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L108" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="M108" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="N108" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O108" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P108" t="n">
         <v>68</v>
@@ -13490,7 +13498,7 @@
         <v>282</v>
       </c>
       <c r="M109" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="N109" t="n">
         <v>260</v>
@@ -13499,7 +13507,7 @@
         <v>266</v>
       </c>
       <c r="P109" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Q109" t="n">
         <v>101.655</v>
@@ -13604,19 +13612,19 @@
         <v>1465.2</v>
       </c>
       <c r="K110" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L110" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="M110" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="N110" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O110" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P110" t="n">
         <v>150</v>
@@ -13724,19 +13732,19 @@
         <v>1452.3</v>
       </c>
       <c r="K111" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L111" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="M111" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="N111" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="O111" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="P111" t="n">
         <v>112</v>
@@ -13844,19 +13852,19 @@
         <v>1382.5</v>
       </c>
       <c r="K112" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L112" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M112" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="N112" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O112" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P112" t="n">
         <v>76</v>
@@ -13964,16 +13972,16 @@
         <v>1482.3</v>
       </c>
       <c r="K113" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L113" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="M113" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N113" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O113" t="n">
         <v>92</v>
@@ -14084,22 +14092,22 @@
         <v>1382.1</v>
       </c>
       <c r="K114" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L114" t="n">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="M114" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="N114" t="n">
         <v>332</v>
       </c>
       <c r="O114" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P114" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q114" t="n">
         <v>102.844</v>
@@ -14204,16 +14212,16 @@
         <v>1742.7</v>
       </c>
       <c r="K115" t="n">
+        <v>5</v>
+      </c>
+      <c r="L115" t="n">
+        <v>4</v>
+      </c>
+      <c r="M115" t="n">
         <v>6</v>
       </c>
-      <c r="L115" t="n">
-        <v>5</v>
-      </c>
-      <c r="M115" t="n">
-        <v>7</v>
-      </c>
       <c r="N115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O115" t="n">
         <v>6</v>
@@ -14324,16 +14332,16 @@
         <v>1421.3</v>
       </c>
       <c r="K116" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L116" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M116" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N116" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O116" t="n">
         <v>293</v>
@@ -14444,19 +14452,19 @@
         <v>1372.4</v>
       </c>
       <c r="K117" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="L117" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="M117" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N117" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O117" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P117" t="n">
         <v>202</v>
@@ -14564,19 +14572,19 @@
         <v>1415.2</v>
       </c>
       <c r="K118" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="L118" t="n">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="M118" t="n">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="N118" t="n">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="O118" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="P118" t="n">
         <v>161</v>
@@ -14684,16 +14692,16 @@
         <v>1426.8</v>
       </c>
       <c r="K119" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L119" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M119" t="n">
         <v>285</v>
       </c>
       <c r="N119" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O119" t="n">
         <v>267</v>
@@ -14807,16 +14815,16 @@
         <v>105</v>
       </c>
       <c r="L120" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M120" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N120" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O120" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="P120" t="n">
         <v>113</v>
@@ -14924,19 +14932,19 @@
         <v>1717.2</v>
       </c>
       <c r="K121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L121" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M121" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O121" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P121" t="n">
         <v>6</v>
@@ -15050,16 +15058,16 @@
         <v>113</v>
       </c>
       <c r="M122" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N122" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O122" t="n">
         <v>102</v>
       </c>
       <c r="P122" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="Q122" t="n">
         <v>109.572</v>
@@ -15167,19 +15175,19 @@
         <v>266</v>
       </c>
       <c r="L123" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M123" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N123" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O123" t="n">
         <v>287</v>
       </c>
       <c r="P123" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q123" t="n">
         <v>106.705</v>
@@ -15284,19 +15292,19 @@
         <v>1695.9</v>
       </c>
       <c r="K124" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L124" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M124" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N124" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O124" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P124" t="n">
         <v>37</v>
@@ -15404,22 +15412,22 @@
         <v>1522.9</v>
       </c>
       <c r="K125" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L125" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M125" t="n">
         <v>182</v>
       </c>
       <c r="N125" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O125" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P125" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q125" t="n">
         <v>102.445</v>
@@ -15527,19 +15535,19 @@
         <v>259</v>
       </c>
       <c r="L126" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="M126" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="N126" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O126" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P126" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="Q126" t="n">
         <v>106.375</v>
@@ -15644,13 +15652,13 @@
         <v>1712.2</v>
       </c>
       <c r="K127" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L127" t="n">
         <v>33</v>
       </c>
       <c r="M127" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N127" t="n">
         <v>28</v>
@@ -15764,19 +15772,19 @@
         <v>1718</v>
       </c>
       <c r="K128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L128" t="n">
+        <v>8</v>
+      </c>
+      <c r="M128" t="n">
+        <v>5</v>
+      </c>
+      <c r="N128" t="n">
+        <v>5</v>
+      </c>
+      <c r="O128" t="n">
         <v>10</v>
-      </c>
-      <c r="M128" t="n">
-        <v>6</v>
-      </c>
-      <c r="N128" t="n">
-        <v>6</v>
-      </c>
-      <c r="O128" t="n">
-        <v>11</v>
       </c>
       <c r="P128" t="n">
         <v>8</v>
@@ -15884,22 +15892,22 @@
         <v>1440.7</v>
       </c>
       <c r="K129" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L129" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="M129" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N129" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O129" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P129" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q129" t="n">
         <v>107.117</v>
@@ -16004,22 +16012,22 @@
         <v>1424.7</v>
       </c>
       <c r="K130" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L130" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M130" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="N130" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O130" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P130" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="Q130" t="n">
         <v>106.37</v>
@@ -16124,13 +16132,13 @@
         <v>1420.2</v>
       </c>
       <c r="K131" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L131" t="n">
         <v>331</v>
       </c>
       <c r="M131" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N131" t="n">
         <v>335</v>
@@ -16244,7 +16252,7 @@
         <v>1398.5</v>
       </c>
       <c r="K132" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L132" t="n">
         <v>293</v>
@@ -16253,13 +16261,13 @@
         <v>264</v>
       </c>
       <c r="N132" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="O132" t="n">
         <v>297</v>
       </c>
       <c r="P132" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q132" t="n">
         <v>106.049</v>
@@ -16364,19 +16372,19 @@
         <v>1466.6</v>
       </c>
       <c r="K133" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="L133" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="M133" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="N133" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O133" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P133" t="n">
         <v>211</v>
@@ -16484,19 +16492,19 @@
         <v>1452.5</v>
       </c>
       <c r="K134" t="n">
+        <v>213</v>
+      </c>
+      <c r="L134" t="n">
+        <v>193</v>
+      </c>
+      <c r="M134" t="n">
         <v>212</v>
-      </c>
-      <c r="L134" t="n">
-        <v>188</v>
-      </c>
-      <c r="M134" t="n">
-        <v>214</v>
       </c>
       <c r="N134" t="n">
         <v>207</v>
       </c>
       <c r="O134" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="P134" t="n">
         <v>207</v>
@@ -16604,19 +16612,19 @@
         <v>1791.1</v>
       </c>
       <c r="K135" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L135" t="n">
         <v>18</v>
       </c>
       <c r="M135" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N135" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O135" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P135" t="n">
         <v>19</v>
@@ -16727,16 +16735,16 @@
         <v>101</v>
       </c>
       <c r="L136" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M136" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="N136" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O136" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P136" t="n">
         <v>99</v>
@@ -16844,19 +16852,19 @@
         <v>1474.6</v>
       </c>
       <c r="K137" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="L137" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="M137" t="n">
+        <v>132</v>
+      </c>
+      <c r="N137" t="n">
+        <v>165</v>
+      </c>
+      <c r="O137" t="n">
         <v>149</v>
-      </c>
-      <c r="N137" t="n">
-        <v>184</v>
-      </c>
-      <c r="O137" t="n">
-        <v>170</v>
       </c>
       <c r="P137" t="n">
         <v>170</v>
@@ -16964,19 +16972,19 @@
         <v>1479</v>
       </c>
       <c r="K138" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="L138" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M138" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N138" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="O138" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P138" t="n">
         <v>147</v>
@@ -17084,16 +17092,16 @@
         <v>1734.8</v>
       </c>
       <c r="K139" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L139" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M139" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N139" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O139" t="n">
         <v>31</v>
@@ -17204,19 +17212,19 @@
         <v>1564.2</v>
       </c>
       <c r="K140" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="L140" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="M140" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="N140" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="O140" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P140" t="n">
         <v>235</v>
@@ -17324,22 +17332,22 @@
         <v>1388.5</v>
       </c>
       <c r="K141" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L141" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M141" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="N141" t="n">
         <v>325</v>
       </c>
       <c r="O141" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P141" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q141" t="n">
         <v>103.025</v>
@@ -17444,22 +17452,22 @@
         <v>1401.8</v>
       </c>
       <c r="K142" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L142" t="n">
         <v>270</v>
       </c>
       <c r="M142" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="N142" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O142" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P142" t="n">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="Q142" t="n">
         <v>102.79</v>
@@ -17564,19 +17572,19 @@
         <v>1399</v>
       </c>
       <c r="K143" t="n">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="L143" t="n">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="M143" t="n">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="N143" t="n">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="O143" t="n">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="P143" t="n">
         <v>282</v>
@@ -17684,19 +17692,19 @@
         <v>1481.5</v>
       </c>
       <c r="K144" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="L144" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M144" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="N144" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="O144" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P144" t="n">
         <v>100</v>
@@ -17804,22 +17812,22 @@
         <v>1421.3</v>
       </c>
       <c r="K145" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L145" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="M145" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N145" t="n">
+        <v>183</v>
+      </c>
+      <c r="O145" t="n">
         <v>182</v>
       </c>
-      <c r="O145" t="n">
-        <v>180</v>
-      </c>
       <c r="P145" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="Q145" t="n">
         <v>110.673</v>
@@ -17924,22 +17932,22 @@
         <v>1480.9</v>
       </c>
       <c r="K146" t="n">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="L146" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M146" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N146" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O146" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P146" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="Q146" t="n">
         <v>101.905</v>
@@ -18044,19 +18052,19 @@
         <v>1378.8</v>
       </c>
       <c r="K147" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L147" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M147" t="n">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="N147" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O147" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P147" t="n">
         <v>200</v>
@@ -18167,19 +18175,19 @@
         <v>271</v>
       </c>
       <c r="L148" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M148" t="n">
         <v>289</v>
       </c>
       <c r="N148" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O148" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P148" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Q148" t="n">
         <v>106.819</v>
@@ -18284,19 +18292,19 @@
         <v>1466</v>
       </c>
       <c r="K149" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="L149" t="n">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="M149" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="N149" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="O149" t="n">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="P149" t="n">
         <v>213</v>
@@ -18404,19 +18412,19 @@
         <v>1686.1</v>
       </c>
       <c r="K150" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L150" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M150" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N150" t="n">
         <v>21</v>
       </c>
       <c r="O150" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P150" t="n">
         <v>14</v>
@@ -18527,19 +18535,19 @@
         <v>161</v>
       </c>
       <c r="L151" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="M151" t="n">
         <v>141</v>
       </c>
       <c r="N151" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O151" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P151" t="n">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="Q151" t="n">
         <v>105.07</v>
@@ -18644,19 +18652,19 @@
         <v>1383.7</v>
       </c>
       <c r="K152" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L152" t="n">
         <v>332</v>
       </c>
       <c r="M152" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N152" t="n">
         <v>322</v>
       </c>
       <c r="O152" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P152" t="n">
         <v>328</v>
@@ -18764,19 +18772,19 @@
         <v>1554</v>
       </c>
       <c r="K153" t="n">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="L153" t="n">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M153" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N153" t="n">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="O153" t="n">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="P153" t="n">
         <v>289</v>
@@ -18884,16 +18892,16 @@
         <v>1667.8</v>
       </c>
       <c r="K154" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L154" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M154" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N154" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O154" t="n">
         <v>88</v>
@@ -19004,19 +19012,19 @@
         <v>1403.6</v>
       </c>
       <c r="K155" t="n">
+        <v>321</v>
+      </c>
+      <c r="L155" t="n">
+        <v>306</v>
+      </c>
+      <c r="M155" t="n">
         <v>319</v>
       </c>
-      <c r="L155" t="n">
-        <v>303</v>
-      </c>
-      <c r="M155" t="n">
-        <v>306</v>
-      </c>
       <c r="N155" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="O155" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P155" t="n">
         <v>318</v>
@@ -19124,7 +19132,7 @@
         <v>1378</v>
       </c>
       <c r="K156" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L156" t="n">
         <v>347</v>
@@ -19133,13 +19141,13 @@
         <v>347</v>
       </c>
       <c r="N156" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O156" t="n">
         <v>352</v>
       </c>
       <c r="P156" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q156" t="n">
         <v>94.974</v>
@@ -19244,19 +19252,19 @@
         <v>1414.5</v>
       </c>
       <c r="K157" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L157" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M157" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N157" t="n">
         <v>329</v>
       </c>
       <c r="O157" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P157" t="n">
         <v>329</v>
@@ -19364,19 +19372,19 @@
         <v>1423.5</v>
       </c>
       <c r="K158" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L158" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M158" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="N158" t="n">
         <v>181</v>
       </c>
       <c r="O158" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P158" t="n">
         <v>182</v>
@@ -19484,19 +19492,19 @@
         <v>1671.3</v>
       </c>
       <c r="K159" t="n">
+        <v>84</v>
+      </c>
+      <c r="L159" t="n">
         <v>86</v>
       </c>
-      <c r="L159" t="n">
-        <v>83</v>
-      </c>
       <c r="M159" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="N159" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O159" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="P159" t="n">
         <v>91</v>
@@ -19604,16 +19612,16 @@
         <v>1448.2</v>
       </c>
       <c r="K160" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L160" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="M160" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N160" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O160" t="n">
         <v>157</v>
@@ -19724,19 +19732,19 @@
         <v>1722.6</v>
       </c>
       <c r="K161" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="L161" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="M161" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="N161" t="n">
+        <v>116</v>
+      </c>
+      <c r="O161" t="n">
         <v>121</v>
-      </c>
-      <c r="O161" t="n">
-        <v>123</v>
       </c>
       <c r="P161" t="n">
         <v>151</v>
@@ -19844,19 +19852,19 @@
         <v>1461.5</v>
       </c>
       <c r="K162" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="L162" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M162" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="N162" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="O162" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P162" t="n">
         <v>203</v>
@@ -19970,13 +19978,13 @@
         <v>87</v>
       </c>
       <c r="M163" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N163" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O163" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="P163" t="n">
         <v>62</v>
@@ -20084,19 +20092,19 @@
         <v>1403.1</v>
       </c>
       <c r="K164" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L164" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M164" t="n">
         <v>345</v>
       </c>
       <c r="N164" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="O164" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P164" t="n">
         <v>350</v>
@@ -20204,19 +20212,19 @@
         <v>1604.3</v>
       </c>
       <c r="K165" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="L165" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M165" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="N165" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="O165" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="P165" t="n">
         <v>125</v>
@@ -20324,22 +20332,22 @@
         <v>1450.7</v>
       </c>
       <c r="K166" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L166" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M166" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N166" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O166" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P166" t="n">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="Q166" t="n">
         <v>114.816</v>
@@ -20444,16 +20452,16 @@
         <v>1635.9</v>
       </c>
       <c r="K167" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L167" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M167" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N167" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O167" t="n">
         <v>26</v>
@@ -20564,19 +20572,19 @@
         <v>1416.9</v>
       </c>
       <c r="K168" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L168" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="M168" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N168" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O168" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P168" t="n">
         <v>55</v>
@@ -20684,23 +20692,21 @@
         <v>1779.9</v>
       </c>
       <c r="K169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
       </c>
       <c r="M169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O169" t="n">
         <v>3</v>
       </c>
-      <c r="P169" t="n">
-        <v>2</v>
-      </c>
+      <c r="P169" t="inlineStr"/>
       <c r="Q169" t="n">
         <v>120.66</v>
       </c>
@@ -20807,16 +20813,16 @@
         <v>9</v>
       </c>
       <c r="L170" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M170" t="n">
+        <v>12</v>
+      </c>
+      <c r="N170" t="n">
         <v>10</v>
       </c>
-      <c r="N170" t="n">
+      <c r="O170" t="n">
         <v>9</v>
-      </c>
-      <c r="O170" t="n">
-        <v>7</v>
       </c>
       <c r="P170" t="n">
         <v>11</v>
@@ -20924,19 +20930,19 @@
         <v>1670.6</v>
       </c>
       <c r="K171" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L171" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="M171" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N171" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O171" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="P171" t="n">
         <v>74</v>
@@ -21044,19 +21050,19 @@
         <v>1713.4</v>
       </c>
       <c r="K172" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="L172" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M172" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="N172" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="O172" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="P172" t="n">
         <v>92</v>
@@ -21167,16 +21173,16 @@
         <v>100</v>
       </c>
       <c r="L173" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M173" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N173" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O173" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="P173" t="n">
         <v>110</v>
@@ -21284,16 +21290,16 @@
         <v>1658.3</v>
       </c>
       <c r="K174" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L174" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M174" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N174" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O174" t="n">
         <v>43</v>
@@ -21407,19 +21413,19 @@
         <v>358</v>
       </c>
       <c r="L175" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M175" t="n">
         <v>362</v>
       </c>
       <c r="N175" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O175" t="n">
         <v>363</v>
       </c>
       <c r="P175" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q175" t="n">
         <v>93.104</v>
@@ -21524,19 +21530,19 @@
         <v>1481.4</v>
       </c>
       <c r="K176" t="n">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="L176" t="n">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="M176" t="n">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="N176" t="n">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="O176" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P176" t="n">
         <v>214</v>
@@ -21644,19 +21650,19 @@
         <v>1462</v>
       </c>
       <c r="K177" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L177" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="M177" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N177" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O177" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="P177" t="n">
         <v>169</v>
@@ -21764,19 +21770,19 @@
         <v>1433.9</v>
       </c>
       <c r="K178" t="n">
+        <v>186</v>
+      </c>
+      <c r="L178" t="n">
         <v>187</v>
       </c>
-      <c r="L178" t="n">
-        <v>200</v>
-      </c>
       <c r="M178" t="n">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="N178" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="O178" t="n">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="P178" t="n">
         <v>199</v>
@@ -21884,19 +21890,19 @@
         <v>1437.1</v>
       </c>
       <c r="K179" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L179" t="n">
+        <v>167</v>
+      </c>
+      <c r="M179" t="n">
         <v>163</v>
       </c>
-      <c r="M179" t="n">
-        <v>167</v>
-      </c>
       <c r="N179" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O179" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="P179" t="n">
         <v>127</v>
@@ -22004,13 +22010,13 @@
         <v>1402</v>
       </c>
       <c r="K180" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L180" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M180" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N180" t="n">
         <v>269</v>
@@ -22019,7 +22025,7 @@
         <v>223</v>
       </c>
       <c r="P180" t="n">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="Q180" t="n">
         <v>107.598</v>
@@ -22124,19 +22130,19 @@
         <v>1356.2</v>
       </c>
       <c r="K181" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L181" t="n">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="M181" t="n">
         <v>358</v>
       </c>
       <c r="N181" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O181" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P181" t="n">
         <v>351</v>
@@ -22250,7 +22256,7 @@
         <v>365</v>
       </c>
       <c r="M182" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N182" t="n">
         <v>365</v>
@@ -22364,19 +22370,19 @@
         <v>1437.6</v>
       </c>
       <c r="K183" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L183" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M183" t="n">
         <v>290</v>
       </c>
       <c r="N183" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O183" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P183" t="n">
         <v>279</v>
@@ -22484,19 +22490,19 @@
         <v>1524.2</v>
       </c>
       <c r="K184" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="L184" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="M184" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="N184" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="O184" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="P184" t="n">
         <v>154</v>
@@ -22604,22 +22610,22 @@
         <v>1504.1</v>
       </c>
       <c r="K185" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L185" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M185" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N185" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O185" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P185" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="Q185" t="n">
         <v>115.54</v>
@@ -22724,19 +22730,19 @@
         <v>1401.2</v>
       </c>
       <c r="K186" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="L186" t="n">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="M186" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="N186" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="O186" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="P186" t="n">
         <v>139</v>
@@ -22844,16 +22850,16 @@
         <v>1410.6</v>
       </c>
       <c r="K187" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L187" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="M187" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="N187" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O187" t="n">
         <v>98</v>
@@ -22970,16 +22976,16 @@
         <v>312</v>
       </c>
       <c r="M188" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N188" t="n">
+        <v>330</v>
+      </c>
+      <c r="O188" t="n">
+        <v>321</v>
+      </c>
+      <c r="P188" t="n">
         <v>331</v>
-      </c>
-      <c r="O188" t="n">
-        <v>320</v>
-      </c>
-      <c r="P188" t="n">
-        <v>336</v>
       </c>
       <c r="Q188" t="n">
         <v>95.759</v>
@@ -23084,19 +23090,19 @@
         <v>1429.8</v>
       </c>
       <c r="K189" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="L189" t="n">
         <v>183</v>
       </c>
       <c r="M189" t="n">
+        <v>186</v>
+      </c>
+      <c r="N189" t="n">
         <v>173</v>
       </c>
-      <c r="N189" t="n">
-        <v>166</v>
-      </c>
       <c r="O189" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="P189" t="n">
         <v>178</v>
@@ -23207,16 +23213,16 @@
         <v>142</v>
       </c>
       <c r="L190" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M190" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N190" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="O190" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P190" t="n">
         <v>138</v>
@@ -23324,22 +23330,22 @@
         <v>1450.1</v>
       </c>
       <c r="K191" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L191" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M191" t="n">
         <v>283</v>
       </c>
       <c r="N191" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O191" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P191" t="n">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="Q191" t="n">
         <v>106.802</v>
@@ -23444,19 +23450,19 @@
         <v>1382.1</v>
       </c>
       <c r="K192" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L192" t="n">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="M192" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N192" t="n">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="O192" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="P192" t="n">
         <v>347</v>
@@ -23564,19 +23570,19 @@
         <v>1681.7</v>
       </c>
       <c r="K193" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L193" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M193" t="n">
         <v>34</v>
       </c>
       <c r="N193" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O193" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P193" t="n">
         <v>35</v>
@@ -23690,13 +23696,13 @@
         <v>244</v>
       </c>
       <c r="M194" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N194" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O194" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P194" t="n">
         <v>258</v>
@@ -23804,19 +23810,19 @@
         <v>1675.8</v>
       </c>
       <c r="K195" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L195" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M195" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N195" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O195" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P195" t="n">
         <v>12</v>
@@ -23924,19 +23930,19 @@
         <v>1607.1</v>
       </c>
       <c r="K196" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L196" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M196" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N196" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O196" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P196" t="n">
         <v>73</v>
@@ -24050,16 +24056,16 @@
         <v>349</v>
       </c>
       <c r="M197" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N197" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O197" t="n">
         <v>348</v>
       </c>
       <c r="P197" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q197" t="n">
         <v>96.61499999999999</v>
@@ -24164,19 +24170,19 @@
         <v>1597.3</v>
       </c>
       <c r="K198" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L198" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M198" t="n">
         <v>55</v>
       </c>
       <c r="N198" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O198" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P198" t="n">
         <v>45</v>
@@ -24284,19 +24290,19 @@
         <v>1489.5</v>
       </c>
       <c r="K199" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L199" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M199" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N199" t="n">
         <v>209</v>
       </c>
       <c r="O199" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="P199" t="n">
         <v>186</v>
@@ -24404,19 +24410,19 @@
         <v>1451.6</v>
       </c>
       <c r="K200" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L200" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="M200" t="n">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="N200" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="O200" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="P200" t="n">
         <v>208</v>
@@ -24527,19 +24533,19 @@
         <v>338</v>
       </c>
       <c r="L201" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M201" t="n">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="N201" t="n">
         <v>339</v>
       </c>
       <c r="O201" t="n">
+        <v>342</v>
+      </c>
+      <c r="P201" t="n">
         <v>343</v>
-      </c>
-      <c r="P201" t="n">
-        <v>341</v>
       </c>
       <c r="Q201" t="n">
         <v>100.711</v>
@@ -24644,19 +24650,19 @@
         <v>1426</v>
       </c>
       <c r="K202" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L202" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="M202" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="N202" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="O202" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P202" t="n">
         <v>246</v>
@@ -24767,7 +24773,7 @@
         <v>332</v>
       </c>
       <c r="L203" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M203" t="n">
         <v>337</v>
@@ -24776,7 +24782,7 @@
         <v>319</v>
       </c>
       <c r="O203" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="P203" t="n">
         <v>327</v>
@@ -24884,19 +24890,19 @@
         <v>1371.6</v>
       </c>
       <c r="K204" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L204" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="M204" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="N204" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="O204" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P204" t="n">
         <v>313</v>
@@ -25004,19 +25010,19 @@
         <v>1677.4</v>
       </c>
       <c r="K205" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L205" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M205" t="n">
         <v>24</v>
       </c>
       <c r="N205" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O205" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P205" t="n">
         <v>23</v>
@@ -25124,19 +25130,19 @@
         <v>1468.8</v>
       </c>
       <c r="K206" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L206" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="M206" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N206" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O206" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P206" t="n">
         <v>272</v>
@@ -25247,7 +25253,7 @@
         <v>335</v>
       </c>
       <c r="L207" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M207" t="n">
         <v>293</v>
@@ -25259,7 +25265,7 @@
         <v>347</v>
       </c>
       <c r="P207" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q207" t="n">
         <v>106.063</v>
@@ -25364,19 +25370,19 @@
         <v>1516.2</v>
       </c>
       <c r="K208" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="L208" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="M208" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="N208" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O208" t="n">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="P208" t="n">
         <v>145</v>
@@ -25484,22 +25490,22 @@
         <v>1476.8</v>
       </c>
       <c r="K209" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L209" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M209" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N209" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O209" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P209" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q209" t="n">
         <v>106.615</v>
@@ -25604,22 +25610,22 @@
         <v>1433.8</v>
       </c>
       <c r="K210" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L210" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M210" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N210" t="n">
         <v>327</v>
       </c>
       <c r="O210" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P210" t="n">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="Q210" t="n">
         <v>104.506</v>
@@ -25724,19 +25730,19 @@
         <v>1515.8</v>
       </c>
       <c r="K211" t="n">
+        <v>72</v>
+      </c>
+      <c r="L211" t="n">
+        <v>93</v>
+      </c>
+      <c r="M211" t="n">
         <v>70</v>
       </c>
-      <c r="L211" t="n">
-        <v>100</v>
-      </c>
-      <c r="M211" t="n">
-        <v>72</v>
-      </c>
       <c r="N211" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O211" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P211" t="n">
         <v>72</v>
@@ -25844,19 +25850,19 @@
         <v>1706.6</v>
       </c>
       <c r="K212" t="n">
+        <v>57</v>
+      </c>
+      <c r="L212" t="n">
+        <v>59</v>
+      </c>
+      <c r="M212" t="n">
+        <v>60</v>
+      </c>
+      <c r="N212" t="n">
         <v>66</v>
       </c>
-      <c r="L212" t="n">
-        <v>70</v>
-      </c>
-      <c r="M212" t="n">
-        <v>65</v>
-      </c>
-      <c r="N212" t="n">
-        <v>74</v>
-      </c>
       <c r="O212" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="P212" t="n">
         <v>70</v>
@@ -25964,19 +25970,19 @@
         <v>1438.9</v>
       </c>
       <c r="K213" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L213" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M213" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N213" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="O213" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P213" t="n">
         <v>300</v>
@@ -26084,22 +26090,22 @@
         <v>1641.3</v>
       </c>
       <c r="K214" t="n">
+        <v>89</v>
+      </c>
+      <c r="L214" t="n">
+        <v>99</v>
+      </c>
+      <c r="M214" t="n">
+        <v>87</v>
+      </c>
+      <c r="N214" t="n">
         <v>92</v>
       </c>
-      <c r="L214" t="n">
-        <v>101</v>
-      </c>
-      <c r="M214" t="n">
-        <v>92</v>
-      </c>
-      <c r="N214" t="n">
-        <v>91</v>
-      </c>
       <c r="O214" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P214" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="Q214" t="n">
         <v>108.974</v>
@@ -26204,22 +26210,22 @@
         <v>1491.6</v>
       </c>
       <c r="K215" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L215" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M215" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N215" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O215" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P215" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="Q215" t="n">
         <v>113.518</v>
@@ -26324,19 +26330,19 @@
         <v>1514.4</v>
       </c>
       <c r="K216" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L216" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M216" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N216" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="O216" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P216" t="n">
         <v>227</v>
@@ -26447,13 +26453,13 @@
         <v>26</v>
       </c>
       <c r="L217" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M217" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N217" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O217" t="n">
         <v>38</v>
@@ -26564,19 +26570,19 @@
         <v>1675.4</v>
       </c>
       <c r="K218" t="n">
+        <v>40</v>
+      </c>
+      <c r="L218" t="n">
+        <v>38</v>
+      </c>
+      <c r="M218" t="n">
         <v>46</v>
       </c>
-      <c r="L218" t="n">
-        <v>43</v>
-      </c>
-      <c r="M218" t="n">
-        <v>47</v>
-      </c>
       <c r="N218" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="O218" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="P218" t="n">
         <v>54</v>
@@ -26684,19 +26690,19 @@
         <v>1692.8</v>
       </c>
       <c r="K219" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L219" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M219" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N219" t="n">
         <v>60</v>
       </c>
       <c r="O219" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P219" t="n">
         <v>79</v>
@@ -26807,19 +26813,19 @@
         <v>248</v>
       </c>
       <c r="L220" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M220" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N220" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O220" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P220" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q220" t="n">
         <v>106.621</v>
@@ -26924,22 +26930,22 @@
         <v>1440.1</v>
       </c>
       <c r="K221" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L221" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M221" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="N221" t="n">
         <v>324</v>
       </c>
       <c r="O221" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P221" t="n">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="Q221" t="n">
         <v>102.735</v>
@@ -27044,19 +27050,19 @@
         <v>1726.9</v>
       </c>
       <c r="K222" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L222" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="M222" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N222" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="O222" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P222" t="n">
         <v>102</v>
@@ -27164,19 +27170,19 @@
         <v>1558.8</v>
       </c>
       <c r="K223" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L223" t="n">
         <v>126</v>
       </c>
       <c r="M223" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="N223" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="O223" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P223" t="n">
         <v>171</v>
@@ -27284,19 +27290,19 @@
         <v>1533.2</v>
       </c>
       <c r="K224" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L224" t="n">
         <v>137</v>
       </c>
       <c r="M224" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N224" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O224" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P224" t="n">
         <v>116</v>
@@ -27404,23 +27410,21 @@
         <v>1493.7</v>
       </c>
       <c r="K225" t="n">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="L225" t="n">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="M225" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="N225" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="O225" t="n">
-        <v>141</v>
-      </c>
-      <c r="P225" t="n">
-        <v>148</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="P225" t="inlineStr"/>
       <c r="Q225" t="n">
         <v>108.543</v>
       </c>
@@ -27527,16 +27531,16 @@
         <v>138</v>
       </c>
       <c r="L226" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M226" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N226" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O226" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="P226" t="n">
         <v>131</v>
@@ -27644,22 +27648,22 @@
         <v>1523.1</v>
       </c>
       <c r="K227" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L227" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M227" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N227" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O227" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P227" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Q227" t="n">
         <v>100.545</v>
@@ -27764,19 +27768,19 @@
         <v>1665.5</v>
       </c>
       <c r="K228" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="L228" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="M228" t="n">
         <v>81</v>
       </c>
       <c r="N228" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O228" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="P228" t="n">
         <v>109</v>
@@ -27884,22 +27888,22 @@
         <v>1534</v>
       </c>
       <c r="K229" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="L229" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M229" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N229" t="n">
         <v>217</v>
       </c>
       <c r="O229" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P229" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Q229" t="n">
         <v>102.178</v>
@@ -28004,19 +28008,19 @@
         <v>1416</v>
       </c>
       <c r="K230" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="L230" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="M230" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="N230" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="O230" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="P230" t="n">
         <v>136</v>
@@ -28124,19 +28128,19 @@
         <v>1383.4</v>
       </c>
       <c r="K231" t="n">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="L231" t="n">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="M231" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="N231" t="n">
+        <v>281</v>
+      </c>
+      <c r="O231" t="n">
         <v>306</v>
-      </c>
-      <c r="O231" t="n">
-        <v>325</v>
       </c>
       <c r="P231" t="n">
         <v>316</v>
@@ -28244,22 +28248,22 @@
         <v>1412.3</v>
       </c>
       <c r="K232" t="n">
+        <v>270</v>
+      </c>
+      <c r="L232" t="n">
         <v>269</v>
       </c>
-      <c r="L232" t="n">
-        <v>268</v>
-      </c>
       <c r="M232" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N232" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O232" t="n">
         <v>273</v>
       </c>
       <c r="P232" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q232" t="n">
         <v>105.189</v>
@@ -28364,19 +28368,19 @@
         <v>1490.2</v>
       </c>
       <c r="K233" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L233" t="n">
         <v>256</v>
       </c>
       <c r="M233" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N233" t="n">
         <v>257</v>
       </c>
       <c r="O233" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P233" t="n">
         <v>249</v>
@@ -28484,16 +28488,16 @@
         <v>1652.1</v>
       </c>
       <c r="K234" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L234" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="M234" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N234" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O234" t="n">
         <v>94</v>
@@ -28607,20 +28611,18 @@
         <v>8</v>
       </c>
       <c r="L235" t="n">
+        <v>7</v>
+      </c>
+      <c r="M235" t="n">
+        <v>7</v>
+      </c>
+      <c r="N235" t="n">
+        <v>7</v>
+      </c>
+      <c r="O235" t="n">
         <v>12</v>
       </c>
-      <c r="M235" t="n">
-        <v>8</v>
-      </c>
-      <c r="N235" t="n">
-        <v>8</v>
-      </c>
-      <c r="O235" t="n">
-        <v>13</v>
-      </c>
-      <c r="P235" t="n">
-        <v>10</v>
-      </c>
+      <c r="P235" t="inlineStr"/>
       <c r="Q235" t="n">
         <v>124.873</v>
       </c>
@@ -28724,19 +28726,19 @@
         <v>1445.4</v>
       </c>
       <c r="K236" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L236" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M236" t="n">
         <v>196</v>
       </c>
       <c r="N236" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O236" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P236" t="n">
         <v>212</v>
@@ -28844,22 +28846,22 @@
         <v>1419.6</v>
       </c>
       <c r="K237" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L237" t="n">
         <v>257</v>
       </c>
       <c r="M237" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N237" t="n">
         <v>258</v>
       </c>
       <c r="O237" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P237" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q237" t="n">
         <v>107.889</v>
@@ -28964,19 +28966,19 @@
         <v>1516</v>
       </c>
       <c r="K238" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L238" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="M238" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N238" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="O238" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="P238" t="n">
         <v>144</v>
@@ -29090,13 +29092,13 @@
         <v>211</v>
       </c>
       <c r="M239" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N239" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O239" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P239" t="n">
         <v>244</v>
@@ -29204,19 +29206,19 @@
         <v>1506.6</v>
       </c>
       <c r="K240" t="n">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="L240" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="M240" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="N240" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="O240" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="P240" t="n">
         <v>152</v>
@@ -29327,7 +29329,7 @@
         <v>357</v>
       </c>
       <c r="L241" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M241" t="n">
         <v>348</v>
@@ -29444,19 +29446,19 @@
         <v>1424.9</v>
       </c>
       <c r="K242" t="n">
+        <v>144</v>
+      </c>
+      <c r="L242" t="n">
+        <v>158</v>
+      </c>
+      <c r="M242" t="n">
+        <v>159</v>
+      </c>
+      <c r="N242" t="n">
+        <v>149</v>
+      </c>
+      <c r="O242" t="n">
         <v>139</v>
-      </c>
-      <c r="L242" t="n">
-        <v>146</v>
-      </c>
-      <c r="M242" t="n">
-        <v>143</v>
-      </c>
-      <c r="N242" t="n">
-        <v>145</v>
-      </c>
-      <c r="O242" t="n">
-        <v>126</v>
       </c>
       <c r="P242" t="n">
         <v>135</v>
@@ -29564,19 +29566,19 @@
         <v>1691.9</v>
       </c>
       <c r="K243" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L243" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="M243" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N243" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="O243" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P243" t="n">
         <v>143</v>
@@ -29687,7 +29689,7 @@
         <v>356</v>
       </c>
       <c r="L244" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M244" t="n">
         <v>363</v>
@@ -29696,7 +29698,7 @@
         <v>357</v>
       </c>
       <c r="O244" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="P244" t="n">
         <v>357</v>
@@ -29804,13 +29806,13 @@
         <v>1460.2</v>
       </c>
       <c r="K245" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L245" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M245" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N245" t="n">
         <v>237</v>
@@ -29819,7 +29821,7 @@
         <v>256</v>
       </c>
       <c r="P245" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q245" t="n">
         <v>109.059</v>
@@ -29927,19 +29929,19 @@
         <v>117</v>
       </c>
       <c r="L246" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M246" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="N246" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O246" t="n">
         <v>158</v>
       </c>
       <c r="P246" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="Q246" t="n">
         <v>102.605</v>
@@ -30044,22 +30046,22 @@
         <v>1436.3</v>
       </c>
       <c r="K247" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L247" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M247" t="n">
         <v>280</v>
       </c>
       <c r="N247" t="n">
+        <v>280</v>
+      </c>
+      <c r="O247" t="n">
         <v>278</v>
       </c>
-      <c r="O247" t="n">
-        <v>277</v>
-      </c>
       <c r="P247" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q247" t="n">
         <v>107.521</v>
@@ -30164,19 +30166,19 @@
         <v>1500.3</v>
       </c>
       <c r="K248" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L248" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M248" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N248" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O248" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="P248" t="n">
         <v>104</v>
@@ -30284,22 +30286,22 @@
         <v>1439.5</v>
       </c>
       <c r="K249" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L249" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="M249" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="N249" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O249" t="n">
         <v>215</v>
       </c>
       <c r="P249" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Q249" t="n">
         <v>112.221</v>
@@ -30407,19 +30409,19 @@
         <v>224</v>
       </c>
       <c r="L250" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="M250" t="n">
+        <v>251</v>
+      </c>
+      <c r="N250" t="n">
         <v>253</v>
-      </c>
-      <c r="N250" t="n">
-        <v>254</v>
       </c>
       <c r="O250" t="n">
         <v>247</v>
       </c>
       <c r="P250" t="n">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="Q250" t="n">
         <v>104.54</v>
@@ -30524,19 +30526,19 @@
         <v>1666.9</v>
       </c>
       <c r="K251" t="n">
+        <v>48</v>
+      </c>
+      <c r="L251" t="n">
         <v>47</v>
       </c>
-      <c r="L251" t="n">
-        <v>50</v>
-      </c>
       <c r="M251" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N251" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O251" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P251" t="n">
         <v>47</v>
@@ -30644,19 +30646,19 @@
         <v>1568.8</v>
       </c>
       <c r="K252" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L252" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M252" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N252" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O252" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P252" t="n">
         <v>119</v>
@@ -30764,19 +30766,19 @@
         <v>1598.9</v>
       </c>
       <c r="K253" t="n">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="L253" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="M253" t="n">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="N253" t="n">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="O253" t="n">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="P253" t="n">
         <v>256</v>
@@ -30884,19 +30886,19 @@
         <v>1455.5</v>
       </c>
       <c r="K254" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L254" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="M254" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N254" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O254" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="P254" t="n">
         <v>137</v>
@@ -31004,19 +31006,19 @@
         <v>1596.2</v>
       </c>
       <c r="K255" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L255" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M255" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N255" t="n">
         <v>36</v>
       </c>
       <c r="O255" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P255" t="n">
         <v>42</v>
@@ -31127,19 +31129,19 @@
         <v>302</v>
       </c>
       <c r="L256" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M256" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N256" t="n">
         <v>288</v>
       </c>
       <c r="O256" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P256" t="n">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="Q256" t="n">
         <v>99.627</v>
@@ -31247,10 +31249,10 @@
         <v>285</v>
       </c>
       <c r="L257" t="n">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M257" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N257" t="n">
         <v>302</v>
@@ -31259,7 +31261,7 @@
         <v>312</v>
       </c>
       <c r="P257" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="Q257" t="n">
         <v>99.092</v>
@@ -31364,22 +31366,22 @@
         <v>1408.8</v>
       </c>
       <c r="K258" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L258" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M258" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N258" t="n">
         <v>219</v>
       </c>
       <c r="O258" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P258" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="Q258" t="n">
         <v>105.206</v>
@@ -31484,22 +31486,22 @@
         <v>1521.6</v>
       </c>
       <c r="K259" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L259" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M259" t="n">
         <v>134</v>
       </c>
       <c r="N259" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="O259" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P259" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="Q259" t="n">
         <v>100.946</v>
@@ -31604,19 +31606,19 @@
         <v>1648.5</v>
       </c>
       <c r="K260" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L260" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M260" t="n">
         <v>50</v>
       </c>
       <c r="N260" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O260" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P260" t="n">
         <v>56</v>
@@ -31724,19 +31726,19 @@
         <v>1397.1</v>
       </c>
       <c r="K261" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L261" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M261" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="N261" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="O261" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P261" t="n">
         <v>86</v>
@@ -31844,19 +31846,19 @@
         <v>1430.3</v>
       </c>
       <c r="K262" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="L262" t="n">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="M262" t="n">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="N262" t="n">
+        <v>170</v>
+      </c>
+      <c r="O262" t="n">
         <v>172</v>
-      </c>
-      <c r="O262" t="n">
-        <v>177</v>
       </c>
       <c r="P262" t="n">
         <v>188</v>
@@ -31964,16 +31966,16 @@
         <v>1649.8</v>
       </c>
       <c r="K263" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L263" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M263" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N263" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O263" t="n">
         <v>44</v>
@@ -32084,22 +32086,22 @@
         <v>1442.8</v>
       </c>
       <c r="K264" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L264" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="M264" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N264" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O264" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P264" t="n">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="Q264" t="n">
         <v>109.756</v>
@@ -32207,16 +32209,16 @@
         <v>95</v>
       </c>
       <c r="L265" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M265" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N265" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O265" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="P265" t="n">
         <v>107</v>
@@ -32324,22 +32326,22 @@
         <v>1423.8</v>
       </c>
       <c r="K266" t="n">
+        <v>282</v>
+      </c>
+      <c r="L266" t="n">
+        <v>266</v>
+      </c>
+      <c r="M266" t="n">
+        <v>334</v>
+      </c>
+      <c r="N266" t="n">
+        <v>292</v>
+      </c>
+      <c r="O266" t="n">
+        <v>254</v>
+      </c>
+      <c r="P266" t="n">
         <v>281</v>
-      </c>
-      <c r="L266" t="n">
-        <v>263</v>
-      </c>
-      <c r="M266" t="n">
-        <v>336</v>
-      </c>
-      <c r="N266" t="n">
-        <v>291</v>
-      </c>
-      <c r="O266" t="n">
-        <v>252</v>
-      </c>
-      <c r="P266" t="n">
-        <v>284</v>
       </c>
       <c r="Q266" t="n">
         <v>106.478</v>
@@ -32444,23 +32446,21 @@
         <v>1554.8</v>
       </c>
       <c r="K267" t="n">
+        <v>47</v>
+      </c>
+      <c r="L267" t="n">
+        <v>58</v>
+      </c>
+      <c r="M267" t="n">
+        <v>49</v>
+      </c>
+      <c r="N267" t="n">
+        <v>45</v>
+      </c>
+      <c r="O267" t="n">
         <v>51</v>
       </c>
-      <c r="L267" t="n">
-        <v>64</v>
-      </c>
-      <c r="M267" t="n">
-        <v>51</v>
-      </c>
-      <c r="N267" t="n">
-        <v>49</v>
-      </c>
-      <c r="O267" t="n">
-        <v>54</v>
-      </c>
-      <c r="P267" t="n">
-        <v>49</v>
-      </c>
+      <c r="P267" t="inlineStr"/>
       <c r="Q267" t="n">
         <v>115.66</v>
       </c>
@@ -32564,19 +32564,19 @@
         <v>1471</v>
       </c>
       <c r="K268" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L268" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M268" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N268" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O268" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P268" t="n">
         <v>218</v>
@@ -32684,19 +32684,19 @@
         <v>1389.2</v>
       </c>
       <c r="K269" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="L269" t="n">
         <v>280</v>
       </c>
       <c r="M269" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="N269" t="n">
         <v>259</v>
       </c>
       <c r="O269" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P269" t="n">
         <v>277</v>
@@ -32804,19 +32804,19 @@
         <v>1494</v>
       </c>
       <c r="K270" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L270" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M270" t="n">
         <v>265</v>
       </c>
       <c r="N270" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O270" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P270" t="n">
         <v>271</v>
@@ -32924,19 +32924,19 @@
         <v>1538.4</v>
       </c>
       <c r="K271" t="n">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="L271" t="n">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="M271" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="N271" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="O271" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="P271" t="n">
         <v>158</v>
@@ -33164,19 +33164,19 @@
         <v>1691.6</v>
       </c>
       <c r="K273" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L273" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M273" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="N273" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O273" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P273" t="n">
         <v>22</v>
@@ -33284,19 +33284,19 @@
         <v>1518.1</v>
       </c>
       <c r="K274" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L274" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M274" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N274" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="O274" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P274" t="n">
         <v>124</v>
@@ -33404,19 +33404,19 @@
         <v>1516.9</v>
       </c>
       <c r="K275" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L275" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M275" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N275" t="n">
+        <v>34</v>
+      </c>
+      <c r="O275" t="n">
         <v>30</v>
-      </c>
-      <c r="O275" t="n">
-        <v>28</v>
       </c>
       <c r="P275" t="n">
         <v>27</v>
@@ -33524,19 +33524,19 @@
         <v>1596.9</v>
       </c>
       <c r="K276" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L276" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M276" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N276" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O276" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P276" t="n">
         <v>20</v>
@@ -33644,22 +33644,22 @@
         <v>1428.7</v>
       </c>
       <c r="K277" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L277" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M277" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="N277" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O277" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P277" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="Q277" t="n">
         <v>105.202</v>
@@ -33764,19 +33764,19 @@
         <v>1622.5</v>
       </c>
       <c r="K278" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L278" t="n">
+        <v>62</v>
+      </c>
+      <c r="M278" t="n">
         <v>58</v>
-      </c>
-      <c r="M278" t="n">
-        <v>56</v>
       </c>
       <c r="N278" t="n">
         <v>58</v>
       </c>
       <c r="O278" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="P278" t="n">
         <v>59</v>
@@ -33887,19 +33887,19 @@
         <v>303</v>
       </c>
       <c r="L279" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M279" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="N279" t="n">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="O279" t="n">
         <v>303</v>
       </c>
       <c r="P279" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="Q279" t="n">
         <v>106.156</v>
@@ -34004,22 +34004,22 @@
         <v>1459.9</v>
       </c>
       <c r="K280" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L280" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M280" t="n">
         <v>188</v>
       </c>
       <c r="N280" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O280" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P280" t="n">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="Q280" t="n">
         <v>104.116</v>
@@ -34124,19 +34124,19 @@
         <v>1664</v>
       </c>
       <c r="K281" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L281" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M281" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N281" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O281" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P281" t="n">
         <v>83</v>
@@ -34244,19 +34244,19 @@
         <v>1430.4</v>
       </c>
       <c r="K282" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="L282" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M282" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N282" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O282" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="P282" t="n">
         <v>196</v>
@@ -34364,16 +34364,16 @@
         <v>1691.3</v>
       </c>
       <c r="K283" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L283" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M283" t="n">
         <v>43</v>
       </c>
       <c r="N283" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O283" t="n">
         <v>35</v>
@@ -34484,19 +34484,19 @@
         <v>1501.2</v>
       </c>
       <c r="K284" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L284" t="n">
+        <v>149</v>
+      </c>
+      <c r="M284" t="n">
         <v>144</v>
       </c>
-      <c r="M284" t="n">
-        <v>142</v>
-      </c>
       <c r="N284" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="O284" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="P284" t="n">
         <v>164</v>
@@ -34604,19 +34604,19 @@
         <v>1716.9</v>
       </c>
       <c r="K285" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L285" t="n">
         <v>17</v>
       </c>
       <c r="M285" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N285" t="n">
         <v>20</v>
       </c>
       <c r="O285" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P285" t="n">
         <v>21</v>
@@ -34724,10 +34724,10 @@
         <v>1407.8</v>
       </c>
       <c r="K286" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L286" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="M286" t="n">
         <v>187</v>
@@ -34736,10 +34736,10 @@
         <v>168</v>
       </c>
       <c r="O286" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P286" t="n">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="Q286" t="n">
         <v>109.904</v>
@@ -34844,13 +34844,13 @@
         <v>1398.8</v>
       </c>
       <c r="K287" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L287" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M287" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N287" t="n">
         <v>304</v>
@@ -34859,7 +34859,7 @@
         <v>310</v>
       </c>
       <c r="P287" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="Q287" t="n">
         <v>103.121</v>
@@ -34964,19 +34964,19 @@
         <v>1696.4</v>
       </c>
       <c r="K288" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L288" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M288" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N288" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O288" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P288" t="n">
         <v>41</v>
@@ -35084,19 +35084,19 @@
         <v>1653.7</v>
       </c>
       <c r="K289" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L289" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M289" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N289" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O289" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P289" t="n">
         <v>43</v>
@@ -35207,19 +35207,19 @@
         <v>245</v>
       </c>
       <c r="L290" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M290" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N290" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O290" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P290" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q290" t="n">
         <v>105.609</v>
@@ -35324,16 +35324,16 @@
         <v>1772.3</v>
       </c>
       <c r="K291" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L291" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M291" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N291" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O291" t="n">
         <v>17</v>
@@ -35447,7 +35447,7 @@
         <v>223</v>
       </c>
       <c r="L292" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M292" t="n">
         <v>222</v>
@@ -35456,10 +35456,10 @@
         <v>202</v>
       </c>
       <c r="O292" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P292" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="Q292" t="n">
         <v>103.339</v>
@@ -35564,19 +35564,19 @@
         <v>1503.6</v>
       </c>
       <c r="K293" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L293" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="M293" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N293" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="O293" t="n">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="P293" t="n">
         <v>146</v>
@@ -35690,13 +35690,13 @@
         <v>165</v>
       </c>
       <c r="M294" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="N294" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O294" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P294" t="n">
         <v>160</v>
@@ -35804,19 +35804,19 @@
         <v>1466</v>
       </c>
       <c r="K295" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="L295" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M295" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N295" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="O295" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P295" t="n">
         <v>132</v>
@@ -35924,19 +35924,19 @@
         <v>1528.4</v>
       </c>
       <c r="K296" t="n">
+        <v>211</v>
+      </c>
+      <c r="L296" t="n">
+        <v>138</v>
+      </c>
+      <c r="M296" t="n">
         <v>210</v>
       </c>
-      <c r="L296" t="n">
+      <c r="N296" t="n">
+        <v>213</v>
+      </c>
+      <c r="O296" t="n">
         <v>141</v>
-      </c>
-      <c r="M296" t="n">
-        <v>211</v>
-      </c>
-      <c r="N296" t="n">
-        <v>216</v>
-      </c>
-      <c r="O296" t="n">
-        <v>142</v>
       </c>
       <c r="P296" t="n">
         <v>206</v>
@@ -36044,19 +36044,19 @@
         <v>1509.4</v>
       </c>
       <c r="K297" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L297" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M297" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="N297" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O297" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P297" t="n">
         <v>50</v>
@@ -36164,16 +36164,16 @@
         <v>1436.7</v>
       </c>
       <c r="K298" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="L298" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M298" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N298" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="O298" t="n">
         <v>167</v>
@@ -36284,19 +36284,19 @@
         <v>1386.6</v>
       </c>
       <c r="K299" t="n">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="L299" t="n">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="M299" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N299" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="O299" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="P299" t="n">
         <v>320</v>
@@ -36404,19 +36404,19 @@
         <v>1498.7</v>
       </c>
       <c r="K300" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L300" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M300" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="N300" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="O300" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="P300" t="n">
         <v>117</v>
@@ -36524,19 +36524,19 @@
         <v>1454.3</v>
       </c>
       <c r="K301" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="L301" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M301" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N301" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="O301" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P301" t="n">
         <v>176</v>
@@ -36644,19 +36644,19 @@
         <v>1475.3</v>
       </c>
       <c r="K302" t="n">
+        <v>104</v>
+      </c>
+      <c r="L302" t="n">
+        <v>123</v>
+      </c>
+      <c r="M302" t="n">
         <v>106</v>
       </c>
-      <c r="L302" t="n">
-        <v>120</v>
-      </c>
-      <c r="M302" t="n">
-        <v>105</v>
-      </c>
       <c r="N302" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O302" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P302" t="n">
         <v>118</v>
@@ -36764,22 +36764,22 @@
         <v>1487.6</v>
       </c>
       <c r="K303" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L303" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M303" t="n">
         <v>294</v>
       </c>
       <c r="N303" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="O303" t="n">
         <v>282</v>
       </c>
       <c r="P303" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q303" t="n">
         <v>100.877</v>
@@ -36884,19 +36884,19 @@
         <v>1712.7</v>
       </c>
       <c r="K304" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L304" t="n">
         <v>42</v>
       </c>
       <c r="M304" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N304" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O304" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P304" t="n">
         <v>51</v>
@@ -37004,16 +37004,16 @@
         <v>1706.3</v>
       </c>
       <c r="K305" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L305" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M305" t="n">
+        <v>32</v>
+      </c>
+      <c r="N305" t="n">
         <v>31</v>
-      </c>
-      <c r="N305" t="n">
-        <v>34</v>
       </c>
       <c r="O305" t="n">
         <v>33</v>
@@ -37127,10 +37127,10 @@
         <v>313</v>
       </c>
       <c r="L306" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="M306" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N306" t="n">
         <v>321</v>
@@ -37139,7 +37139,7 @@
         <v>291</v>
       </c>
       <c r="P306" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q306" t="n">
         <v>99.56</v>
@@ -37244,7 +37244,7 @@
         <v>1446.8</v>
       </c>
       <c r="K307" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L307" t="n">
         <v>359</v>
@@ -37364,19 +37364,19 @@
         <v>1369.1</v>
       </c>
       <c r="K308" t="n">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="L308" t="n">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="M308" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="N308" t="n">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O308" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="P308" t="n">
         <v>205</v>
@@ -37484,7 +37484,7 @@
         <v>1428.4</v>
       </c>
       <c r="K309" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L309" t="n">
         <v>247</v>
@@ -37496,10 +37496,10 @@
         <v>251</v>
       </c>
       <c r="O309" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P309" t="n">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q309" t="n">
         <v>106.648</v>
@@ -37604,19 +37604,19 @@
         <v>1428.1</v>
       </c>
       <c r="K310" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L310" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M310" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N310" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O310" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P310" t="n">
         <v>293</v>
@@ -37727,16 +37727,16 @@
         <v>110</v>
       </c>
       <c r="L311" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="M311" t="n">
         <v>133</v>
       </c>
       <c r="N311" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O311" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P311" t="n">
         <v>96</v>
@@ -37844,16 +37844,16 @@
         <v>1628.6</v>
       </c>
       <c r="K312" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L312" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M312" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N312" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O312" t="n">
         <v>106</v>
@@ -37964,19 +37964,19 @@
         <v>1689.6</v>
       </c>
       <c r="K313" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L313" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M313" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N313" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O313" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P313" t="n">
         <v>78</v>
@@ -38084,19 +38084,19 @@
         <v>1465</v>
       </c>
       <c r="K314" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L314" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M314" t="n">
         <v>156</v>
       </c>
       <c r="N314" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O314" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P314" t="n">
         <v>162</v>
@@ -38207,13 +38207,13 @@
         <v>340</v>
       </c>
       <c r="L315" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M315" t="n">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="N315" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="O315" t="n">
         <v>344</v>
@@ -38324,19 +38324,19 @@
         <v>1692.4</v>
       </c>
       <c r="K316" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L316" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M316" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="N316" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O316" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P316" t="n">
         <v>129</v>
@@ -38444,19 +38444,19 @@
         <v>1611.4</v>
       </c>
       <c r="K317" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L317" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="M317" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N317" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="O317" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P317" t="n">
         <v>29</v>
@@ -38567,16 +38567,16 @@
         <v>90</v>
       </c>
       <c r="L318" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M318" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N318" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="O318" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P318" t="n">
         <v>85</v>
@@ -38684,22 +38684,22 @@
         <v>1507.2</v>
       </c>
       <c r="K319" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L319" t="n">
         <v>240</v>
       </c>
       <c r="M319" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="N319" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O319" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P319" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q319" t="n">
         <v>100.368</v>
@@ -38807,20 +38807,18 @@
         <v>45</v>
       </c>
       <c r="L320" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M320" t="n">
         <v>48</v>
       </c>
       <c r="N320" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="O320" t="n">
         <v>40</v>
       </c>
-      <c r="P320" t="n">
-        <v>44</v>
-      </c>
+      <c r="P320" t="inlineStr"/>
       <c r="Q320" t="n">
         <v>117.937</v>
       </c>
@@ -38924,22 +38922,22 @@
         <v>1523.8</v>
       </c>
       <c r="K321" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L321" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M321" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N321" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="O321" t="n">
         <v>151</v>
       </c>
       <c r="P321" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Q321" t="n">
         <v>105.545</v>
@@ -39044,23 +39042,21 @@
         <v>1718.8</v>
       </c>
       <c r="K322" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L322" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M322" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N322" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O322" t="n">
-        <v>22</v>
-      </c>
-      <c r="P322" t="n">
-        <v>16</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="P322" t="inlineStr"/>
       <c r="Q322" t="n">
         <v>122.082</v>
       </c>
@@ -39164,19 +39160,19 @@
         <v>1390.5</v>
       </c>
       <c r="K323" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L323" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="M323" t="n">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="N323" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="O323" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P323" t="n">
         <v>223</v>
@@ -39284,19 +39280,19 @@
         <v>1641.5</v>
       </c>
       <c r="K324" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L324" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M324" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N324" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O324" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P324" t="n">
         <v>33</v>
@@ -39404,19 +39400,19 @@
         <v>1665.9</v>
       </c>
       <c r="K325" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L325" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M325" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N325" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O325" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P325" t="n">
         <v>13</v>
@@ -39524,19 +39520,19 @@
         <v>1660.6</v>
       </c>
       <c r="K326" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L326" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M326" t="n">
         <v>45</v>
       </c>
       <c r="N326" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O326" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="P326" t="n">
         <v>53</v>
@@ -39647,7 +39643,7 @@
         <v>360</v>
       </c>
       <c r="L327" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M327" t="n">
         <v>353</v>
@@ -39659,7 +39655,7 @@
         <v>358</v>
       </c>
       <c r="P327" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q327" t="n">
         <v>101.269</v>
@@ -39764,19 +39760,19 @@
         <v>1473.5</v>
       </c>
       <c r="K328" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L328" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="M328" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N328" t="n">
         <v>232</v>
       </c>
       <c r="O328" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P328" t="n">
         <v>226</v>
@@ -39899,7 +39895,7 @@
         <v>364</v>
       </c>
       <c r="P329" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="Q329" t="n">
         <v>93.68600000000001</v>
@@ -40004,19 +40000,19 @@
         <v>1484.4</v>
       </c>
       <c r="K330" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L330" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="M330" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N330" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="O330" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="P330" t="n">
         <v>156</v>
@@ -40133,13 +40129,13 @@
         <v>286</v>
       </c>
       <c r="N331" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O331" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P331" t="n">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="Q331" t="n">
         <v>105.863</v>
@@ -40244,22 +40240,22 @@
         <v>1390.5</v>
       </c>
       <c r="K332" t="n">
+        <v>305</v>
+      </c>
+      <c r="L332" t="n">
+        <v>323</v>
+      </c>
+      <c r="M332" t="n">
+        <v>327</v>
+      </c>
+      <c r="N332" t="n">
         <v>306</v>
-      </c>
-      <c r="L332" t="n">
-        <v>326</v>
-      </c>
-      <c r="M332" t="n">
-        <v>328</v>
-      </c>
-      <c r="N332" t="n">
-        <v>307</v>
       </c>
       <c r="O332" t="n">
         <v>316</v>
       </c>
       <c r="P332" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q332" t="n">
         <v>104.549</v>
@@ -40370,13 +40366,13 @@
         <v>67</v>
       </c>
       <c r="M333" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N333" t="n">
         <v>70</v>
       </c>
       <c r="O333" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P333" t="n">
         <v>64</v>
@@ -40484,19 +40480,19 @@
         <v>1695.6</v>
       </c>
       <c r="K334" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L334" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M334" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N334" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O334" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P334" t="n">
         <v>61</v>
@@ -40607,19 +40603,19 @@
         <v>137</v>
       </c>
       <c r="L335" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="M335" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N335" t="n">
         <v>164</v>
       </c>
       <c r="O335" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P335" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q335" t="n">
         <v>109.462</v>
@@ -40724,19 +40720,19 @@
         <v>1419</v>
       </c>
       <c r="K336" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="L336" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="M336" t="n">
+        <v>208</v>
+      </c>
+      <c r="N336" t="n">
         <v>212</v>
       </c>
-      <c r="N336" t="n">
-        <v>208</v>
-      </c>
       <c r="O336" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="P336" t="n">
         <v>197</v>
@@ -40844,19 +40840,19 @@
         <v>1669</v>
       </c>
       <c r="K337" t="n">
+        <v>59</v>
+      </c>
+      <c r="L337" t="n">
+        <v>53</v>
+      </c>
+      <c r="M337" t="n">
+        <v>61</v>
+      </c>
+      <c r="N337" t="n">
         <v>57</v>
       </c>
-      <c r="L337" t="n">
-        <v>51</v>
-      </c>
-      <c r="M337" t="n">
-        <v>54</v>
-      </c>
-      <c r="N337" t="n">
-        <v>55</v>
-      </c>
       <c r="O337" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P337" t="n">
         <v>58</v>
@@ -40964,10 +40960,10 @@
         <v>1447.2</v>
       </c>
       <c r="K338" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L338" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M338" t="n">
         <v>217</v>
@@ -40976,7 +40972,7 @@
         <v>203</v>
       </c>
       <c r="O338" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P338" t="n">
         <v>216</v>
@@ -41087,19 +41083,19 @@
         <v>268</v>
       </c>
       <c r="L339" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M339" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N339" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O339" t="n">
         <v>259</v>
       </c>
       <c r="P339" t="n">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="Q339" t="n">
         <v>107.928</v>
@@ -41204,23 +41200,21 @@
         <v>1546.5</v>
       </c>
       <c r="K340" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L340" t="n">
         <v>91</v>
       </c>
       <c r="M340" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N340" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O340" t="n">
-        <v>85</v>
-      </c>
-      <c r="P340" t="n">
-        <v>80</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="P340" t="inlineStr"/>
       <c r="Q340" t="n">
         <v>111.577</v>
       </c>
@@ -41324,19 +41318,19 @@
         <v>1468.9</v>
       </c>
       <c r="K341" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L341" t="n">
         <v>173</v>
       </c>
       <c r="M341" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N341" t="n">
+        <v>135</v>
+      </c>
+      <c r="O341" t="n">
         <v>132</v>
-      </c>
-      <c r="O341" t="n">
-        <v>133</v>
       </c>
       <c r="P341" t="n">
         <v>128</v>
@@ -41444,16 +41438,16 @@
         <v>1437.4</v>
       </c>
       <c r="K342" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L342" t="n">
         <v>151</v>
       </c>
       <c r="M342" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N342" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O342" t="n">
         <v>125</v>
@@ -41564,19 +41558,19 @@
         <v>1724.6</v>
       </c>
       <c r="K343" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L343" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M343" t="n">
         <v>23</v>
       </c>
       <c r="N343" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O343" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P343" t="n">
         <v>26</v>
@@ -41687,19 +41681,19 @@
         <v>253</v>
       </c>
       <c r="L344" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M344" t="n">
         <v>282</v>
       </c>
       <c r="N344" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O344" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P344" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="Q344" t="n">
         <v>114.069</v>
@@ -41804,19 +41798,19 @@
         <v>1431.7</v>
       </c>
       <c r="K345" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L345" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="M345" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N345" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="O345" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="P345" t="n">
         <v>133</v>
@@ -41927,16 +41921,16 @@
         <v>98</v>
       </c>
       <c r="L346" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M346" t="n">
         <v>102</v>
       </c>
       <c r="N346" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="O346" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P346" t="n">
         <v>98</v>
@@ -42047,7 +42041,7 @@
         <v>97</v>
       </c>
       <c r="L347" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="M347" t="n">
         <v>101</v>
@@ -42056,7 +42050,7 @@
         <v>95</v>
       </c>
       <c r="O347" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P347" t="n">
         <v>97</v>
@@ -42164,23 +42158,21 @@
         <v>1457.5</v>
       </c>
       <c r="K348" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L348" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M348" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N348" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O348" t="n">
-        <v>62</v>
-      </c>
-      <c r="P348" t="n">
-        <v>66</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="P348" t="inlineStr"/>
       <c r="Q348" t="n">
         <v>121.507</v>
       </c>
@@ -42287,19 +42279,19 @@
         <v>214</v>
       </c>
       <c r="L349" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M349" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N349" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O349" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P349" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="Q349" t="n">
         <v>108.892</v>
@@ -42404,19 +42396,19 @@
         <v>1462.4</v>
       </c>
       <c r="K350" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L350" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="M350" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="N350" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="O350" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P350" t="n">
         <v>103</v>
@@ -42524,22 +42516,22 @@
         <v>1410.7</v>
       </c>
       <c r="K351" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L351" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M351" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N351" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O351" t="n">
         <v>334</v>
       </c>
       <c r="P351" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q351" t="n">
         <v>101.867</v>
@@ -42644,19 +42636,19 @@
         <v>1455.9</v>
       </c>
       <c r="K352" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="L352" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="M352" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="N352" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="O352" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="P352" t="n">
         <v>173</v>
@@ -42770,10 +42762,10 @@
         <v>287</v>
       </c>
       <c r="M353" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N353" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O353" t="n">
         <v>286</v>
@@ -42884,19 +42876,19 @@
         <v>1495.4</v>
       </c>
       <c r="K354" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L354" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M354" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N354" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="O354" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="P354" t="n">
         <v>175</v>
@@ -43004,19 +42996,19 @@
         <v>1467.7</v>
       </c>
       <c r="K355" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L355" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="M355" t="n">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="N355" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="O355" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P355" t="n">
         <v>224</v>
@@ -43124,19 +43116,19 @@
         <v>1452.3</v>
       </c>
       <c r="K356" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L356" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="M356" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N356" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="O356" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P356" t="n">
         <v>120</v>
@@ -43244,22 +43236,22 @@
         <v>1395</v>
       </c>
       <c r="K357" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L357" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M357" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N357" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O357" t="n">
         <v>117</v>
       </c>
       <c r="P357" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q357" t="n">
         <v>117.765</v>
@@ -43370,13 +43362,13 @@
         <v>284</v>
       </c>
       <c r="M358" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N358" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O358" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P358" t="n">
         <v>263</v>
@@ -43484,16 +43476,16 @@
         <v>1430.9</v>
       </c>
       <c r="K359" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L359" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="M359" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="N359" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O359" t="n">
         <v>171</v>
@@ -43607,10 +43599,10 @@
         <v>339</v>
       </c>
       <c r="L360" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M360" t="n">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="N360" t="n">
         <v>352</v>
@@ -43619,7 +43611,7 @@
         <v>354</v>
       </c>
       <c r="P360" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q360" t="n">
         <v>96.282</v>
@@ -43727,19 +43719,19 @@
         <v>334</v>
       </c>
       <c r="L361" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M361" t="n">
         <v>324</v>
       </c>
       <c r="N361" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O361" t="n">
         <v>341</v>
       </c>
       <c r="P361" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q361" t="n">
         <v>94.59999999999999</v>
@@ -43844,22 +43836,22 @@
         <v>1429.3</v>
       </c>
       <c r="K362" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L362" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M362" t="n">
         <v>284</v>
       </c>
       <c r="N362" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O362" t="n">
         <v>298</v>
       </c>
       <c r="P362" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="Q362" t="n">
         <v>98.67700000000001</v>
@@ -43964,22 +43956,22 @@
         <v>1378.3</v>
       </c>
       <c r="K363" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L363" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M363" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N363" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O363" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P363" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Q363" t="n">
         <v>105.225</v>
@@ -44084,19 +44076,19 @@
         <v>1379.2</v>
       </c>
       <c r="K364" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L364" t="n">
         <v>311</v>
       </c>
       <c r="M364" t="n">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="N364" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O364" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P364" t="n">
         <v>275</v>
@@ -44207,19 +44199,19 @@
         <v>304</v>
       </c>
       <c r="L365" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="M365" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N365" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O365" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P365" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q365" t="n">
         <v>105.957</v>
@@ -44327,19 +44319,19 @@
         <v>328</v>
       </c>
       <c r="L366" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M366" t="n">
+        <v>311</v>
+      </c>
+      <c r="N366" t="n">
         <v>313</v>
-      </c>
-      <c r="N366" t="n">
-        <v>315</v>
       </c>
       <c r="O366" t="n">
         <v>324</v>
       </c>
       <c r="P366" t="n">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="Q366" t="n">
         <v>97.51300000000001</v>

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,192 +417,192 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Conf</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>N_games</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>has_box_score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>POM</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MOR</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>WLK</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>BIH</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>NET</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>avg_Score</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>avg_OppScore</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>avg_Won</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>avg_FGM</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>avg_FGA</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>avg_FGM3</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>avg_FGA3</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>avg_FTM</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>avg_FTA</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>avg_OR</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>avg_DR</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>avg_Ast</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>avg_Stl</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>avg_Blk</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>avg_PF</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>last10_Margin</t>
         </is>
@@ -791,7 +779,7 @@
         <v>346</v>
       </c>
       <c r="P3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q3" t="n">
         <v>92.197</v>
@@ -908,10 +896,10 @@
         <v>54</v>
       </c>
       <c r="O4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q4" t="n">
         <v>121.636</v>
@@ -1031,7 +1019,7 @@
         <v>14</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q5" t="n">
         <v>121.371</v>
@@ -1151,7 +1139,7 @@
         <v>265</v>
       </c>
       <c r="P6" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q6" t="n">
         <v>105.687</v>
@@ -1271,7 +1259,7 @@
         <v>332</v>
       </c>
       <c r="P7" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q7" t="n">
         <v>100.336</v>
@@ -1511,7 +1499,7 @@
         <v>336</v>
       </c>
       <c r="P9" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q9" t="n">
         <v>96.518</v>
@@ -1631,7 +1619,7 @@
         <v>258</v>
       </c>
       <c r="P10" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q10" t="n">
         <v>108.04</v>
@@ -1751,7 +1739,7 @@
         <v>175</v>
       </c>
       <c r="P11" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="Q11" t="n">
         <v>108.198</v>
@@ -1988,10 +1976,10 @@
         <v>64</v>
       </c>
       <c r="O13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P13" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q13" t="n">
         <v>106.954</v>
@@ -2111,7 +2099,7 @@
         <v>311</v>
       </c>
       <c r="P14" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q14" t="n">
         <v>102.203</v>
@@ -2231,7 +2219,7 @@
         <v>301</v>
       </c>
       <c r="P15" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q15" t="n">
         <v>104.367</v>
@@ -2348,9 +2336,11 @@
         <v>14</v>
       </c>
       <c r="O16" t="n">
-        <v>20</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="P16" t="n">
+        <v>15</v>
+      </c>
       <c r="Q16" t="n">
         <v>122.871</v>
       </c>
@@ -2469,7 +2459,7 @@
         <v>142</v>
       </c>
       <c r="P17" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="Q17" t="n">
         <v>111.178</v>
@@ -2589,7 +2579,7 @@
         <v>339</v>
       </c>
       <c r="P18" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q18" t="n">
         <v>102.472</v>
@@ -2706,7 +2696,7 @@
         <v>39</v>
       </c>
       <c r="O19" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P19" t="n">
         <v>38</v>
@@ -2826,10 +2816,10 @@
         <v>147</v>
       </c>
       <c r="O20" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P20" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="Q20" t="n">
         <v>112.877</v>
@@ -2949,7 +2939,7 @@
         <v>295</v>
       </c>
       <c r="P21" t="n">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="Q21" t="n">
         <v>99.752</v>
@@ -3069,7 +3059,7 @@
         <v>70</v>
       </c>
       <c r="P22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q22" t="n">
         <v>116.311</v>
@@ -3186,10 +3176,10 @@
         <v>61</v>
       </c>
       <c r="O23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P23" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="Q23" t="n">
         <v>118.567</v>
@@ -3309,7 +3299,7 @@
         <v>221</v>
       </c>
       <c r="P24" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Q24" t="n">
         <v>104.969</v>
@@ -3549,7 +3539,7 @@
         <v>59</v>
       </c>
       <c r="P26" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q26" t="n">
         <v>113.98</v>
@@ -3669,7 +3659,7 @@
         <v>206</v>
       </c>
       <c r="P27" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="Q27" t="n">
         <v>100.075</v>
@@ -3789,7 +3779,7 @@
         <v>270</v>
       </c>
       <c r="P28" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q28" t="n">
         <v>114.64</v>
@@ -3909,7 +3899,7 @@
         <v>178</v>
       </c>
       <c r="P29" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q29" t="n">
         <v>108.629</v>
@@ -4029,7 +4019,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q30" t="n">
         <v>110.424</v>
@@ -4149,7 +4139,7 @@
         <v>318</v>
       </c>
       <c r="P31" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="Q31" t="n">
         <v>97.68300000000001</v>
@@ -4269,7 +4259,7 @@
         <v>349</v>
       </c>
       <c r="P32" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q32" t="n">
         <v>95.277</v>
@@ -4389,7 +4379,7 @@
         <v>328</v>
       </c>
       <c r="P33" t="n">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Q33" t="n">
         <v>99.30200000000001</v>
@@ -4509,7 +4499,7 @@
         <v>196</v>
       </c>
       <c r="P34" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Q34" t="n">
         <v>114.269</v>
@@ -4629,7 +4619,7 @@
         <v>86</v>
       </c>
       <c r="P35" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q35" t="n">
         <v>111.069</v>
@@ -4749,7 +4739,7 @@
         <v>23</v>
       </c>
       <c r="P36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q36" t="n">
         <v>117.675</v>
@@ -4869,7 +4859,7 @@
         <v>294</v>
       </c>
       <c r="P37" t="n">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="Q37" t="n">
         <v>105.894</v>
@@ -4989,7 +4979,7 @@
         <v>232</v>
       </c>
       <c r="P38" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q38" t="n">
         <v>105.821</v>
@@ -5109,7 +5099,7 @@
         <v>56</v>
       </c>
       <c r="P39" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q39" t="n">
         <v>110.159</v>
@@ -5229,7 +5219,7 @@
         <v>201</v>
       </c>
       <c r="P40" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="Q40" t="n">
         <v>108.494</v>
@@ -5349,7 +5339,7 @@
         <v>329</v>
       </c>
       <c r="P41" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q41" t="n">
         <v>96.16800000000001</v>
@@ -5589,7 +5579,7 @@
         <v>252</v>
       </c>
       <c r="P43" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="Q43" t="n">
         <v>107.607</v>
@@ -5706,10 +5696,10 @@
         <v>255</v>
       </c>
       <c r="O44" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P44" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q44" t="n">
         <v>107.282</v>
@@ -5829,7 +5819,7 @@
         <v>176</v>
       </c>
       <c r="P45" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="Q45" t="n">
         <v>111.997</v>
@@ -5949,7 +5939,7 @@
         <v>304</v>
       </c>
       <c r="P46" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q46" t="n">
         <v>110.697</v>
@@ -6069,7 +6059,7 @@
         <v>350</v>
       </c>
       <c r="P47" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="Q47" t="n">
         <v>98.143</v>
@@ -6186,10 +6176,10 @@
         <v>43</v>
       </c>
       <c r="O48" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P48" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q48" t="n">
         <v>104.828</v>
@@ -6309,7 +6299,7 @@
         <v>338</v>
       </c>
       <c r="P49" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="Q49" t="n">
         <v>102.551</v>
@@ -6429,7 +6419,7 @@
         <v>32</v>
       </c>
       <c r="P50" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Q50" t="n">
         <v>112.594</v>
@@ -6549,7 +6539,7 @@
         <v>308</v>
       </c>
       <c r="P51" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q51" t="n">
         <v>109.789</v>
@@ -6669,7 +6659,7 @@
         <v>181</v>
       </c>
       <c r="P52" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="Q52" t="n">
         <v>103.612</v>
@@ -6789,7 +6779,7 @@
         <v>113</v>
       </c>
       <c r="P53" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q53" t="n">
         <v>108.385</v>
@@ -6909,7 +6899,7 @@
         <v>240</v>
       </c>
       <c r="P54" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="Q54" t="n">
         <v>110.531</v>
@@ -7029,7 +7019,7 @@
         <v>68</v>
       </c>
       <c r="P55" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="Q55" t="n">
         <v>114.138</v>
@@ -7269,7 +7259,7 @@
         <v>185</v>
       </c>
       <c r="P57" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Q57" t="n">
         <v>108.916</v>
@@ -7389,7 +7379,7 @@
         <v>4</v>
       </c>
       <c r="P58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q58" t="n">
         <v>116.057</v>
@@ -7629,7 +7619,7 @@
         <v>188</v>
       </c>
       <c r="P60" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="Q60" t="n">
         <v>120.036</v>
@@ -7749,7 +7739,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q61" t="n">
         <v>109.303</v>
@@ -7986,10 +7976,10 @@
         <v>192</v>
       </c>
       <c r="O63" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P63" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q63" t="n">
         <v>107.122</v>
@@ -8109,7 +8099,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Q64" t="n">
         <v>105.446</v>
@@ -8229,7 +8219,7 @@
         <v>292</v>
       </c>
       <c r="P65" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="Q65" t="n">
         <v>104.279</v>
@@ -8349,7 +8339,7 @@
         <v>257</v>
       </c>
       <c r="P66" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="Q66" t="n">
         <v>105.276</v>
@@ -8469,7 +8459,7 @@
         <v>110</v>
       </c>
       <c r="P67" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="Q67" t="n">
         <v>107.992</v>
@@ -8586,9 +8576,11 @@
         <v>72</v>
       </c>
       <c r="O68" t="n">
-        <v>64</v>
-      </c>
-      <c r="P68" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="P68" t="n">
+        <v>69</v>
+      </c>
       <c r="Q68" t="n">
         <v>109.173</v>
       </c>
@@ -8707,7 +8699,7 @@
         <v>283</v>
       </c>
       <c r="P69" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="Q69" t="n">
         <v>104.493</v>
@@ -8947,7 +8939,7 @@
         <v>242</v>
       </c>
       <c r="P71" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="Q71" t="n">
         <v>116.071</v>
@@ -9067,7 +9059,7 @@
         <v>95</v>
       </c>
       <c r="P72" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q72" t="n">
         <v>103.998</v>
@@ -9187,7 +9179,7 @@
         <v>210</v>
       </c>
       <c r="P73" t="n">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="Q73" t="n">
         <v>108.872</v>
@@ -9304,10 +9296,10 @@
         <v>204</v>
       </c>
       <c r="O74" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P74" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="Q74" t="n">
         <v>107.643</v>
@@ -9427,7 +9419,7 @@
         <v>219</v>
       </c>
       <c r="P75" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q75" t="n">
         <v>103.567</v>
@@ -9664,10 +9656,10 @@
         <v>137</v>
       </c>
       <c r="O77" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P77" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="Q77" t="n">
         <v>108.657</v>
@@ -9787,7 +9779,7 @@
         <v>314</v>
       </c>
       <c r="P78" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="Q78" t="n">
         <v>97.188</v>
@@ -9907,7 +9899,7 @@
         <v>302</v>
       </c>
       <c r="P79" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="Q79" t="n">
         <v>111.589</v>
@@ -10027,7 +10019,7 @@
         <v>268</v>
       </c>
       <c r="P80" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q80" t="n">
         <v>102.413</v>
@@ -10147,7 +10139,7 @@
         <v>226</v>
       </c>
       <c r="P81" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q81" t="n">
         <v>111.602</v>
@@ -10267,7 +10259,7 @@
         <v>255</v>
       </c>
       <c r="P82" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q82" t="n">
         <v>101.921</v>
@@ -10387,7 +10379,7 @@
         <v>249</v>
       </c>
       <c r="P83" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q83" t="n">
         <v>101.962</v>
@@ -10507,7 +10499,7 @@
         <v>236</v>
       </c>
       <c r="P84" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="Q84" t="n">
         <v>111.233</v>
@@ -10627,7 +10619,7 @@
         <v>162</v>
       </c>
       <c r="P85" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="Q85" t="n">
         <v>115.903</v>
@@ -10747,7 +10739,7 @@
         <v>305</v>
       </c>
       <c r="P86" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q86" t="n">
         <v>97.123</v>
@@ -10867,7 +10859,7 @@
         <v>345</v>
       </c>
       <c r="P87" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q87" t="n">
         <v>100.805</v>
@@ -10987,7 +10979,7 @@
         <v>211</v>
       </c>
       <c r="P88" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q88" t="n">
         <v>107.307</v>
@@ -11104,7 +11096,7 @@
         <v>129</v>
       </c>
       <c r="O89" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P89" t="n">
         <v>123</v>
@@ -11227,7 +11219,7 @@
         <v>260</v>
       </c>
       <c r="P90" t="n">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="Q90" t="n">
         <v>108.76</v>
@@ -11467,7 +11459,7 @@
         <v>289</v>
       </c>
       <c r="P92" t="n">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="Q92" t="n">
         <v>99.462</v>
@@ -11587,7 +11579,7 @@
         <v>228</v>
       </c>
       <c r="P93" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="Q93" t="n">
         <v>107.634</v>
@@ -11707,7 +11699,7 @@
         <v>72</v>
       </c>
       <c r="P94" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="Q94" t="n">
         <v>112.145</v>
@@ -11947,7 +11939,7 @@
         <v>179</v>
       </c>
       <c r="P96" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Q96" t="n">
         <v>104.443</v>
@@ -12067,7 +12059,7 @@
         <v>183</v>
       </c>
       <c r="P97" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="Q97" t="n">
         <v>112.011</v>
@@ -12187,7 +12179,7 @@
         <v>118</v>
       </c>
       <c r="P98" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q98" t="n">
         <v>114.986</v>
@@ -12307,7 +12299,7 @@
         <v>227</v>
       </c>
       <c r="P99" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q99" t="n">
         <v>111.045</v>
@@ -12547,7 +12539,7 @@
         <v>78</v>
       </c>
       <c r="P101" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Q101" t="n">
         <v>111.945</v>
@@ -12667,7 +12659,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Q102" t="n">
         <v>109.001</v>
@@ -12787,7 +12779,7 @@
         <v>37</v>
       </c>
       <c r="P103" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q103" t="n">
         <v>119.916</v>
@@ -12907,7 +12899,7 @@
         <v>319</v>
       </c>
       <c r="P104" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="Q104" t="n">
         <v>99.483</v>
@@ -13027,7 +13019,7 @@
         <v>204</v>
       </c>
       <c r="P105" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q105" t="n">
         <v>102.629</v>
@@ -13144,10 +13136,10 @@
         <v>11</v>
       </c>
       <c r="O106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P106" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q106" t="n">
         <v>120.754</v>
@@ -13267,7 +13259,7 @@
         <v>320</v>
       </c>
       <c r="P107" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q107" t="n">
         <v>100.192</v>
@@ -13387,7 +13379,7 @@
         <v>74</v>
       </c>
       <c r="P108" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q108" t="n">
         <v>110.214</v>
@@ -13507,7 +13499,7 @@
         <v>266</v>
       </c>
       <c r="P109" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q109" t="n">
         <v>101.655</v>
@@ -13624,10 +13616,10 @@
         <v>151</v>
       </c>
       <c r="O110" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P110" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q110" t="n">
         <v>107.967</v>
@@ -13747,7 +13739,7 @@
         <v>93</v>
       </c>
       <c r="P111" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="Q111" t="n">
         <v>108.144</v>
@@ -13867,7 +13859,7 @@
         <v>75</v>
       </c>
       <c r="P112" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q112" t="n">
         <v>121.161</v>
@@ -14107,7 +14099,7 @@
         <v>337</v>
       </c>
       <c r="P114" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q114" t="n">
         <v>102.844</v>
@@ -14224,10 +14216,10 @@
         <v>6</v>
       </c>
       <c r="O115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P115" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q115" t="n">
         <v>117.346</v>
@@ -14464,10 +14456,10 @@
         <v>196</v>
       </c>
       <c r="O117" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P117" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q117" t="n">
         <v>109.065</v>
@@ -14587,7 +14579,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="Q118" t="n">
         <v>110.278</v>
@@ -14824,10 +14816,10 @@
         <v>109</v>
       </c>
       <c r="O120" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P120" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q120" t="n">
         <v>108.828</v>
@@ -14947,7 +14939,7 @@
         <v>13</v>
       </c>
       <c r="P121" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q121" t="n">
         <v>125.113</v>
@@ -15067,7 +15059,7 @@
         <v>102</v>
       </c>
       <c r="P122" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q122" t="n">
         <v>109.572</v>
@@ -15187,7 +15179,7 @@
         <v>287</v>
       </c>
       <c r="P123" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q123" t="n">
         <v>106.705</v>
@@ -15307,7 +15299,7 @@
         <v>58</v>
       </c>
       <c r="P124" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q124" t="n">
         <v>115.605</v>
@@ -15427,7 +15419,7 @@
         <v>253</v>
       </c>
       <c r="P125" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q125" t="n">
         <v>102.445</v>
@@ -15547,7 +15539,7 @@
         <v>216</v>
       </c>
       <c r="P126" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q126" t="n">
         <v>106.375</v>
@@ -15664,10 +15656,10 @@
         <v>28</v>
       </c>
       <c r="O127" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P127" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q127" t="n">
         <v>118.924</v>
@@ -15787,7 +15779,7 @@
         <v>10</v>
       </c>
       <c r="P128" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q128" t="n">
         <v>118.901</v>
@@ -15907,7 +15899,7 @@
         <v>217</v>
       </c>
       <c r="P129" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q129" t="n">
         <v>107.117</v>
@@ -16027,7 +16019,7 @@
         <v>343</v>
       </c>
       <c r="P130" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q130" t="n">
         <v>106.37</v>
@@ -16147,7 +16139,7 @@
         <v>315</v>
       </c>
       <c r="P131" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q131" t="n">
         <v>97.96599999999999</v>
@@ -16267,7 +16259,7 @@
         <v>297</v>
       </c>
       <c r="P132" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q132" t="n">
         <v>106.049</v>
@@ -16387,7 +16379,7 @@
         <v>235</v>
       </c>
       <c r="P133" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Q133" t="n">
         <v>106.037</v>
@@ -16507,7 +16499,7 @@
         <v>193</v>
       </c>
       <c r="P134" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q134" t="n">
         <v>110.849</v>
@@ -16627,7 +16619,7 @@
         <v>15</v>
       </c>
       <c r="P135" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q135" t="n">
         <v>109.902</v>
@@ -16747,7 +16739,7 @@
         <v>111</v>
       </c>
       <c r="P136" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q136" t="n">
         <v>107.267</v>
@@ -16867,7 +16859,7 @@
         <v>149</v>
       </c>
       <c r="P137" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="Q137" t="n">
         <v>111.121</v>
@@ -16987,7 +16979,7 @@
         <v>87</v>
       </c>
       <c r="P138" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="Q138" t="n">
         <v>112.171</v>
@@ -17227,7 +17219,7 @@
         <v>243</v>
       </c>
       <c r="P140" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="Q140" t="n">
         <v>100.204</v>
@@ -17347,7 +17339,7 @@
         <v>330</v>
       </c>
       <c r="P141" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q141" t="n">
         <v>103.025</v>
@@ -17467,7 +17459,7 @@
         <v>280</v>
       </c>
       <c r="P142" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="Q142" t="n">
         <v>102.79</v>
@@ -17587,7 +17579,7 @@
         <v>263</v>
       </c>
       <c r="P143" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="Q143" t="n">
         <v>105.584</v>
@@ -17707,7 +17699,7 @@
         <v>77</v>
       </c>
       <c r="P144" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="Q144" t="n">
         <v>117.433</v>
@@ -17827,7 +17819,7 @@
         <v>182</v>
       </c>
       <c r="P145" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="Q145" t="n">
         <v>110.673</v>
@@ -17947,7 +17939,7 @@
         <v>288</v>
       </c>
       <c r="P146" t="n">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="Q146" t="n">
         <v>101.905</v>
@@ -18067,7 +18059,7 @@
         <v>165</v>
       </c>
       <c r="P147" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Q147" t="n">
         <v>109.383</v>
@@ -18184,10 +18176,10 @@
         <v>264</v>
       </c>
       <c r="O148" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P148" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q148" t="n">
         <v>106.819</v>
@@ -18307,7 +18299,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="Q149" t="n">
         <v>103.618</v>
@@ -18427,7 +18419,7 @@
         <v>28</v>
       </c>
       <c r="P150" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q150" t="n">
         <v>118.896</v>
@@ -18547,7 +18539,7 @@
         <v>187</v>
       </c>
       <c r="P151" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="Q151" t="n">
         <v>105.07</v>
@@ -18787,7 +18779,7 @@
         <v>276</v>
       </c>
       <c r="P153" t="n">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="Q153" t="n">
         <v>100.517</v>
@@ -19027,7 +19019,7 @@
         <v>317</v>
       </c>
       <c r="P155" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q155" t="n">
         <v>104.608</v>
@@ -19147,7 +19139,7 @@
         <v>352</v>
       </c>
       <c r="P156" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q156" t="n">
         <v>94.974</v>
@@ -19387,7 +19379,7 @@
         <v>202</v>
       </c>
       <c r="P158" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q158" t="n">
         <v>103.772</v>
@@ -19504,10 +19496,10 @@
         <v>94</v>
       </c>
       <c r="O159" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P159" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q159" t="n">
         <v>105.219</v>
@@ -19627,7 +19619,7 @@
         <v>157</v>
       </c>
       <c r="P160" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q160" t="n">
         <v>113.862</v>
@@ -19747,7 +19739,7 @@
         <v>121</v>
       </c>
       <c r="P161" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="Q161" t="n">
         <v>103.793</v>
@@ -19867,7 +19859,7 @@
         <v>208</v>
       </c>
       <c r="P162" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q162" t="n">
         <v>109.253</v>
@@ -19984,10 +19976,10 @@
         <v>63</v>
       </c>
       <c r="O163" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P163" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Q163" t="n">
         <v>115.07</v>
@@ -20107,7 +20099,7 @@
         <v>353</v>
       </c>
       <c r="P164" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q164" t="n">
         <v>95.45399999999999</v>
@@ -20227,7 +20219,7 @@
         <v>163</v>
       </c>
       <c r="P165" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="Q165" t="n">
         <v>104.316</v>
@@ -20347,7 +20339,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="Q166" t="n">
         <v>114.816</v>
@@ -20464,7 +20456,7 @@
         <v>33</v>
       </c>
       <c r="O167" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P167" t="n">
         <v>32</v>
@@ -20587,7 +20579,7 @@
         <v>22</v>
       </c>
       <c r="P168" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="Q168" t="n">
         <v>120.742</v>
@@ -20706,7 +20698,9 @@
       <c r="O169" t="n">
         <v>3</v>
       </c>
-      <c r="P169" t="inlineStr"/>
+      <c r="P169" t="n">
+        <v>2</v>
+      </c>
       <c r="Q169" t="n">
         <v>120.66</v>
       </c>
@@ -20945,7 +20939,7 @@
         <v>91</v>
       </c>
       <c r="P171" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q171" t="n">
         <v>110.457</v>
@@ -21065,7 +21059,7 @@
         <v>103</v>
       </c>
       <c r="P172" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="Q172" t="n">
         <v>109.139</v>
@@ -21185,7 +21179,7 @@
         <v>107</v>
       </c>
       <c r="P173" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q173" t="n">
         <v>106.637</v>
@@ -21305,7 +21299,7 @@
         <v>43</v>
       </c>
       <c r="P174" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q174" t="n">
         <v>114.923</v>
@@ -21425,7 +21419,7 @@
         <v>363</v>
       </c>
       <c r="P175" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q175" t="n">
         <v>93.104</v>
@@ -21545,7 +21539,7 @@
         <v>234</v>
       </c>
       <c r="P176" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="Q176" t="n">
         <v>108.655</v>
@@ -21665,7 +21659,7 @@
         <v>173</v>
       </c>
       <c r="P177" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q177" t="n">
         <v>106.67</v>
@@ -21785,7 +21779,7 @@
         <v>186</v>
       </c>
       <c r="P178" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="Q178" t="n">
         <v>106.924</v>
@@ -21905,7 +21899,7 @@
         <v>166</v>
       </c>
       <c r="P179" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q179" t="n">
         <v>111.832</v>
@@ -22025,7 +22019,7 @@
         <v>223</v>
       </c>
       <c r="P180" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q180" t="n">
         <v>107.598</v>
@@ -22145,7 +22139,7 @@
         <v>327</v>
       </c>
       <c r="P181" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q181" t="n">
         <v>99.72799999999999</v>
@@ -22385,7 +22379,7 @@
         <v>250</v>
       </c>
       <c r="P183" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q183" t="n">
         <v>99.91200000000001</v>
@@ -22505,7 +22499,7 @@
         <v>170</v>
       </c>
       <c r="P184" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="Q184" t="n">
         <v>107.743</v>
@@ -22625,7 +22619,7 @@
         <v>99</v>
       </c>
       <c r="P185" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Q185" t="n">
         <v>115.54</v>
@@ -22745,7 +22739,7 @@
         <v>156</v>
       </c>
       <c r="P186" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="Q186" t="n">
         <v>112.831</v>
@@ -22865,7 +22859,7 @@
         <v>98</v>
       </c>
       <c r="P187" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q187" t="n">
         <v>114.28</v>
@@ -22985,7 +22979,7 @@
         <v>321</v>
       </c>
       <c r="P188" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q188" t="n">
         <v>95.759</v>
@@ -23105,7 +23099,7 @@
         <v>195</v>
       </c>
       <c r="P189" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="Q189" t="n">
         <v>113.17</v>
@@ -23225,7 +23219,7 @@
         <v>123</v>
       </c>
       <c r="P190" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q190" t="n">
         <v>113.402</v>
@@ -23345,7 +23339,7 @@
         <v>285</v>
       </c>
       <c r="P191" t="n">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="Q191" t="n">
         <v>106.802</v>
@@ -23465,7 +23459,7 @@
         <v>335</v>
       </c>
       <c r="P192" t="n">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="Q192" t="n">
         <v>101.762</v>
@@ -23585,7 +23579,7 @@
         <v>41</v>
       </c>
       <c r="P193" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q193" t="n">
         <v>119.356</v>
@@ -23825,7 +23819,7 @@
         <v>11</v>
       </c>
       <c r="P195" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q195" t="n">
         <v>114.614</v>
@@ -23945,7 +23939,7 @@
         <v>69</v>
       </c>
       <c r="P196" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q196" t="n">
         <v>112.247</v>
@@ -24065,7 +24059,7 @@
         <v>348</v>
       </c>
       <c r="P197" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q197" t="n">
         <v>96.61499999999999</v>
@@ -24182,10 +24176,10 @@
         <v>51</v>
       </c>
       <c r="O198" t="n">
+        <v>45</v>
+      </c>
+      <c r="P198" t="n">
         <v>46</v>
-      </c>
-      <c r="P198" t="n">
-        <v>45</v>
       </c>
       <c r="Q198" t="n">
         <v>114.935</v>
@@ -24305,7 +24299,7 @@
         <v>222</v>
       </c>
       <c r="P199" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q199" t="n">
         <v>108.097</v>
@@ -24425,7 +24419,7 @@
         <v>213</v>
       </c>
       <c r="P200" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q200" t="n">
         <v>106.272</v>
@@ -24545,7 +24539,7 @@
         <v>342</v>
       </c>
       <c r="P201" t="n">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="Q201" t="n">
         <v>100.711</v>
@@ -24665,7 +24659,7 @@
         <v>238</v>
       </c>
       <c r="P202" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q202" t="n">
         <v>104.281</v>
@@ -24905,7 +24899,7 @@
         <v>325</v>
       </c>
       <c r="P204" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q204" t="n">
         <v>103.072</v>
@@ -25025,7 +25019,7 @@
         <v>19</v>
       </c>
       <c r="P205" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q205" t="n">
         <v>115.28</v>
@@ -25145,7 +25139,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q206" t="n">
         <v>106.643</v>
@@ -25265,7 +25259,7 @@
         <v>347</v>
       </c>
       <c r="P207" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q207" t="n">
         <v>106.063</v>
@@ -25385,7 +25379,7 @@
         <v>127</v>
       </c>
       <c r="P208" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="Q208" t="n">
         <v>103.743</v>
@@ -25505,7 +25499,7 @@
         <v>323</v>
       </c>
       <c r="P209" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q209" t="n">
         <v>106.615</v>
@@ -25625,7 +25619,7 @@
         <v>322</v>
       </c>
       <c r="P210" t="n">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q210" t="n">
         <v>104.506</v>
@@ -25865,7 +25859,7 @@
         <v>90</v>
       </c>
       <c r="P212" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q212" t="n">
         <v>111.958</v>
@@ -25985,7 +25979,7 @@
         <v>307</v>
       </c>
       <c r="P213" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q213" t="n">
         <v>101.625</v>
@@ -26105,7 +26099,7 @@
         <v>105</v>
       </c>
       <c r="P214" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="Q214" t="n">
         <v>108.974</v>
@@ -26225,7 +26219,7 @@
         <v>184</v>
       </c>
       <c r="P215" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="Q215" t="n">
         <v>113.518</v>
@@ -26345,7 +26339,7 @@
         <v>214</v>
       </c>
       <c r="P216" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q216" t="n">
         <v>107.677</v>
@@ -26465,7 +26459,7 @@
         <v>38</v>
       </c>
       <c r="P217" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q217" t="n">
         <v>118</v>
@@ -26585,7 +26579,7 @@
         <v>67</v>
       </c>
       <c r="P218" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="Q218" t="n">
         <v>120.005</v>
@@ -26705,7 +26699,7 @@
         <v>55</v>
       </c>
       <c r="P219" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Q219" t="n">
         <v>111.498</v>
@@ -26825,7 +26819,7 @@
         <v>262</v>
       </c>
       <c r="P220" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q220" t="n">
         <v>106.621</v>
@@ -26945,7 +26939,7 @@
         <v>326</v>
       </c>
       <c r="P221" t="n">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="Q221" t="n">
         <v>102.735</v>
@@ -27065,7 +27059,7 @@
         <v>116</v>
       </c>
       <c r="P222" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="Q222" t="n">
         <v>105.074</v>
@@ -27182,10 +27176,10 @@
         <v>166</v>
       </c>
       <c r="O223" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P223" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q223" t="n">
         <v>106.457</v>
@@ -27302,7 +27296,7 @@
         <v>120</v>
       </c>
       <c r="O224" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="P224" t="n">
         <v>116</v>
@@ -27422,9 +27416,11 @@
         <v>139</v>
       </c>
       <c r="O225" t="n">
-        <v>138</v>
-      </c>
-      <c r="P225" t="inlineStr"/>
+        <v>128</v>
+      </c>
+      <c r="P225" t="n">
+        <v>139</v>
+      </c>
       <c r="Q225" t="n">
         <v>108.543</v>
       </c>
@@ -27540,10 +27536,10 @@
         <v>131</v>
       </c>
       <c r="O226" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P226" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="Q226" t="n">
         <v>109.321</v>
@@ -27663,7 +27659,7 @@
         <v>290</v>
       </c>
       <c r="P227" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q227" t="n">
         <v>100.545</v>
@@ -27783,7 +27779,7 @@
         <v>126</v>
       </c>
       <c r="P228" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="Q228" t="n">
         <v>107.914</v>
@@ -27903,7 +27899,7 @@
         <v>205</v>
       </c>
       <c r="P229" t="n">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Q229" t="n">
         <v>102.178</v>
@@ -28023,7 +28019,7 @@
         <v>143</v>
       </c>
       <c r="P230" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="Q230" t="n">
         <v>105.468</v>
@@ -28143,7 +28139,7 @@
         <v>306</v>
       </c>
       <c r="P231" t="n">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="Q231" t="n">
         <v>104.378</v>
@@ -28263,7 +28259,7 @@
         <v>273</v>
       </c>
       <c r="P232" t="n">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="Q232" t="n">
         <v>105.189</v>
@@ -28503,7 +28499,7 @@
         <v>94</v>
       </c>
       <c r="P234" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q234" t="n">
         <v>114.622</v>
@@ -28622,7 +28618,9 @@
       <c r="O235" t="n">
         <v>12</v>
       </c>
-      <c r="P235" t="inlineStr"/>
+      <c r="P235" t="n">
+        <v>9</v>
+      </c>
       <c r="Q235" t="n">
         <v>124.873</v>
       </c>
@@ -28861,7 +28859,7 @@
         <v>261</v>
       </c>
       <c r="P237" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q237" t="n">
         <v>107.889</v>
@@ -28981,7 +28979,7 @@
         <v>159</v>
       </c>
       <c r="P238" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="Q238" t="n">
         <v>104.755</v>
@@ -29101,7 +29099,7 @@
         <v>241</v>
       </c>
       <c r="P239" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q239" t="n">
         <v>105.519</v>
@@ -29221,7 +29219,7 @@
         <v>190</v>
       </c>
       <c r="P240" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="Q240" t="n">
         <v>111.369</v>
@@ -29341,7 +29339,7 @@
         <v>357</v>
       </c>
       <c r="P241" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q241" t="n">
         <v>94.77500000000001</v>
@@ -29461,7 +29459,7 @@
         <v>139</v>
       </c>
       <c r="P242" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="Q242" t="n">
         <v>114.922</v>
@@ -29581,7 +29579,7 @@
         <v>119</v>
       </c>
       <c r="P243" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="Q243" t="n">
         <v>104.259</v>
@@ -29701,7 +29699,7 @@
         <v>351</v>
       </c>
       <c r="P244" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q244" t="n">
         <v>96.22199999999999</v>
@@ -29821,7 +29819,7 @@
         <v>256</v>
       </c>
       <c r="P245" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Q245" t="n">
         <v>109.059</v>
@@ -29941,7 +29939,7 @@
         <v>158</v>
       </c>
       <c r="P246" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="Q246" t="n">
         <v>102.605</v>
@@ -30181,7 +30179,7 @@
         <v>101</v>
       </c>
       <c r="P248" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q248" t="n">
         <v>112.785</v>
@@ -30301,7 +30299,7 @@
         <v>215</v>
       </c>
       <c r="P249" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q249" t="n">
         <v>112.221</v>
@@ -30421,7 +30419,7 @@
         <v>247</v>
       </c>
       <c r="P250" t="n">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="Q250" t="n">
         <v>104.54</v>
@@ -30781,7 +30779,7 @@
         <v>244</v>
       </c>
       <c r="P253" t="n">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="Q253" t="n">
         <v>107.527</v>
@@ -30901,7 +30899,7 @@
         <v>164</v>
       </c>
       <c r="P254" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="Q254" t="n">
         <v>113.081</v>
@@ -31021,7 +31019,7 @@
         <v>34</v>
       </c>
       <c r="P255" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q255" t="n">
         <v>117.619</v>
@@ -31141,7 +31139,7 @@
         <v>299</v>
       </c>
       <c r="P256" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="Q256" t="n">
         <v>99.627</v>
@@ -31261,7 +31259,7 @@
         <v>312</v>
       </c>
       <c r="P257" t="n">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="Q257" t="n">
         <v>99.092</v>
@@ -31381,7 +31379,7 @@
         <v>220</v>
       </c>
       <c r="P258" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q258" t="n">
         <v>105.206</v>
@@ -31501,7 +31499,7 @@
         <v>114</v>
       </c>
       <c r="P259" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="Q259" t="n">
         <v>100.946</v>
@@ -31621,7 +31619,7 @@
         <v>54</v>
       </c>
       <c r="P260" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="Q260" t="n">
         <v>105.592</v>
@@ -31741,7 +31739,7 @@
         <v>66</v>
       </c>
       <c r="P261" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q261" t="n">
         <v>112.195</v>
@@ -31861,7 +31859,7 @@
         <v>172</v>
       </c>
       <c r="P262" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="Q262" t="n">
         <v>109.727</v>
@@ -31981,7 +31979,7 @@
         <v>44</v>
       </c>
       <c r="P263" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q263" t="n">
         <v>117.96</v>
@@ -32101,7 +32099,7 @@
         <v>154</v>
       </c>
       <c r="P264" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="Q264" t="n">
         <v>109.756</v>
@@ -32221,7 +32219,7 @@
         <v>135</v>
       </c>
       <c r="P265" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q265" t="n">
         <v>109.384</v>
@@ -32341,7 +32339,7 @@
         <v>254</v>
       </c>
       <c r="P266" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q266" t="n">
         <v>106.478</v>
@@ -32458,9 +32456,11 @@
         <v>45</v>
       </c>
       <c r="O267" t="n">
-        <v>51</v>
-      </c>
-      <c r="P267" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="P267" t="n">
+        <v>45</v>
+      </c>
       <c r="Q267" t="n">
         <v>115.66</v>
       </c>
@@ -32579,7 +32579,7 @@
         <v>212</v>
       </c>
       <c r="P268" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Q268" t="n">
         <v>106.257</v>
@@ -32699,7 +32699,7 @@
         <v>271</v>
       </c>
       <c r="P269" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q269" t="n">
         <v>105.921</v>
@@ -32819,7 +32819,7 @@
         <v>264</v>
       </c>
       <c r="P270" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q270" t="n">
         <v>101.359</v>
@@ -32939,7 +32939,7 @@
         <v>161</v>
       </c>
       <c r="P271" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="Q271" t="n">
         <v>111.407</v>
@@ -33179,7 +33179,7 @@
         <v>16</v>
       </c>
       <c r="P273" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q273" t="n">
         <v>113.974</v>
@@ -33299,7 +33299,7 @@
         <v>89</v>
       </c>
       <c r="P274" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q274" t="n">
         <v>105.807</v>
@@ -33419,7 +33419,7 @@
         <v>30</v>
       </c>
       <c r="P275" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q275" t="n">
         <v>120.005</v>
@@ -33539,7 +33539,7 @@
         <v>21</v>
       </c>
       <c r="P276" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q276" t="n">
         <v>118.734</v>
@@ -33656,10 +33656,10 @@
         <v>225</v>
       </c>
       <c r="O277" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P277" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="Q277" t="n">
         <v>105.202</v>
@@ -33779,7 +33779,7 @@
         <v>57</v>
       </c>
       <c r="P278" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q278" t="n">
         <v>111.896</v>
@@ -33899,7 +33899,7 @@
         <v>303</v>
       </c>
       <c r="P279" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="Q279" t="n">
         <v>106.156</v>
@@ -34019,7 +34019,7 @@
         <v>209</v>
       </c>
       <c r="P280" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="Q280" t="n">
         <v>104.116</v>
@@ -34139,7 +34139,7 @@
         <v>85</v>
       </c>
       <c r="P281" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q281" t="n">
         <v>107.955</v>
@@ -34259,7 +34259,7 @@
         <v>198</v>
       </c>
       <c r="P282" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="Q282" t="n">
         <v>102.534</v>
@@ -34379,7 +34379,7 @@
         <v>35</v>
       </c>
       <c r="P283" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q283" t="n">
         <v>111.157</v>
@@ -34496,10 +34496,10 @@
         <v>174</v>
       </c>
       <c r="O284" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P284" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q284" t="n">
         <v>110.657</v>
@@ -34616,10 +34616,10 @@
         <v>20</v>
       </c>
       <c r="O285" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P285" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q285" t="n">
         <v>116.86</v>
@@ -34739,7 +34739,7 @@
         <v>152</v>
       </c>
       <c r="P286" t="n">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="Q286" t="n">
         <v>109.904</v>
@@ -34859,7 +34859,7 @@
         <v>310</v>
       </c>
       <c r="P287" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="Q287" t="n">
         <v>103.121</v>
@@ -34979,7 +34979,7 @@
         <v>47</v>
       </c>
       <c r="P288" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q288" t="n">
         <v>119.505</v>
@@ -35099,7 +35099,7 @@
         <v>42</v>
       </c>
       <c r="P289" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q289" t="n">
         <v>117.135</v>
@@ -35219,7 +35219,7 @@
         <v>197</v>
       </c>
       <c r="P290" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q290" t="n">
         <v>105.609</v>
@@ -35339,7 +35339,7 @@
         <v>17</v>
       </c>
       <c r="P291" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q291" t="n">
         <v>117.198</v>
@@ -35459,7 +35459,7 @@
         <v>192</v>
       </c>
       <c r="P292" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="Q292" t="n">
         <v>103.339</v>
@@ -35579,7 +35579,7 @@
         <v>148</v>
       </c>
       <c r="P293" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="Q293" t="n">
         <v>114.812</v>
@@ -35699,7 +35699,7 @@
         <v>155</v>
       </c>
       <c r="P294" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q294" t="n">
         <v>103.887</v>
@@ -35819,7 +35819,7 @@
         <v>120</v>
       </c>
       <c r="P295" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="Q295" t="n">
         <v>112.278</v>
@@ -35936,10 +35936,10 @@
         <v>213</v>
       </c>
       <c r="O296" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P296" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q296" t="n">
         <v>105.424</v>
@@ -36056,10 +36056,10 @@
         <v>59</v>
       </c>
       <c r="O297" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P297" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q297" t="n">
         <v>121.126</v>
@@ -36179,7 +36179,7 @@
         <v>167</v>
       </c>
       <c r="P298" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="Q298" t="n">
         <v>109.781</v>
@@ -36299,7 +36299,7 @@
         <v>313</v>
       </c>
       <c r="P299" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q299" t="n">
         <v>103.586</v>
@@ -36419,7 +36419,7 @@
         <v>115</v>
       </c>
       <c r="P300" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q300" t="n">
         <v>109.214</v>
@@ -36539,7 +36539,7 @@
         <v>160</v>
       </c>
       <c r="P301" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q301" t="n">
         <v>105.97</v>
@@ -36659,7 +36659,7 @@
         <v>109</v>
       </c>
       <c r="P302" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q302" t="n">
         <v>103.957</v>
@@ -36779,7 +36779,7 @@
         <v>282</v>
       </c>
       <c r="P303" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Q303" t="n">
         <v>100.877</v>
@@ -37019,7 +37019,7 @@
         <v>33</v>
       </c>
       <c r="P305" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q305" t="n">
         <v>117.179</v>
@@ -37139,7 +37139,7 @@
         <v>291</v>
       </c>
       <c r="P306" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q306" t="n">
         <v>99.56</v>
@@ -37379,7 +37379,7 @@
         <v>189</v>
       </c>
       <c r="P308" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="Q308" t="n">
         <v>113.392</v>
@@ -37499,7 +37499,7 @@
         <v>248</v>
       </c>
       <c r="P309" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q309" t="n">
         <v>106.648</v>
@@ -37619,7 +37619,7 @@
         <v>279</v>
       </c>
       <c r="P310" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q310" t="n">
         <v>110.541</v>
@@ -37976,10 +37976,10 @@
         <v>74</v>
       </c>
       <c r="O313" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P313" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q313" t="n">
         <v>107.677</v>
@@ -38099,7 +38099,7 @@
         <v>150</v>
       </c>
       <c r="P314" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q314" t="n">
         <v>100.873</v>
@@ -38219,7 +38219,7 @@
         <v>344</v>
       </c>
       <c r="P315" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q315" t="n">
         <v>95.857</v>
@@ -38339,7 +38339,7 @@
         <v>147</v>
       </c>
       <c r="P316" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q316" t="n">
         <v>108.311</v>
@@ -38459,7 +38459,7 @@
         <v>29</v>
       </c>
       <c r="P317" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q317" t="n">
         <v>119.564</v>
@@ -38699,7 +38699,7 @@
         <v>277</v>
       </c>
       <c r="P319" t="n">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Q319" t="n">
         <v>100.368</v>
@@ -38816,9 +38816,11 @@
         <v>41</v>
       </c>
       <c r="O320" t="n">
-        <v>40</v>
-      </c>
-      <c r="P320" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="P320" t="n">
+        <v>43</v>
+      </c>
       <c r="Q320" t="n">
         <v>117.937</v>
       </c>
@@ -38937,7 +38939,7 @@
         <v>151</v>
       </c>
       <c r="P321" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q321" t="n">
         <v>105.545</v>
@@ -39054,9 +39056,11 @@
         <v>12</v>
       </c>
       <c r="O322" t="n">
-        <v>18</v>
-      </c>
-      <c r="P322" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="P322" t="n">
+        <v>13</v>
+      </c>
       <c r="Q322" t="n">
         <v>122.082</v>
       </c>
@@ -39175,7 +39179,7 @@
         <v>225</v>
       </c>
       <c r="P323" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q323" t="n">
         <v>110.802</v>
@@ -39295,7 +39299,7 @@
         <v>24</v>
       </c>
       <c r="P324" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q324" t="n">
         <v>114.594</v>
@@ -39415,7 +39419,7 @@
         <v>8</v>
       </c>
       <c r="P325" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q325" t="n">
         <v>119.042</v>
@@ -39535,7 +39539,7 @@
         <v>52</v>
       </c>
       <c r="P326" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q326" t="n">
         <v>112.713</v>
@@ -39655,7 +39659,7 @@
         <v>358</v>
       </c>
       <c r="P327" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q327" t="n">
         <v>101.269</v>
@@ -39775,7 +39779,7 @@
         <v>239</v>
       </c>
       <c r="P328" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q328" t="n">
         <v>110.362</v>
@@ -39895,7 +39899,7 @@
         <v>364</v>
       </c>
       <c r="P329" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q329" t="n">
         <v>93.68600000000001</v>
@@ -40015,7 +40019,7 @@
         <v>145</v>
       </c>
       <c r="P330" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="Q330" t="n">
         <v>108.18</v>
@@ -40135,7 +40139,7 @@
         <v>272</v>
       </c>
       <c r="P331" t="n">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="Q331" t="n">
         <v>105.863</v>
@@ -40255,7 +40259,7 @@
         <v>316</v>
       </c>
       <c r="P332" t="n">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="Q332" t="n">
         <v>104.549</v>
@@ -40375,7 +40379,7 @@
         <v>79</v>
       </c>
       <c r="P333" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q333" t="n">
         <v>112.23</v>
@@ -40495,7 +40499,7 @@
         <v>82</v>
       </c>
       <c r="P334" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="Q334" t="n">
         <v>112.2</v>
@@ -40615,7 +40619,7 @@
         <v>203</v>
       </c>
       <c r="P335" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="Q335" t="n">
         <v>109.462</v>
@@ -40735,7 +40739,7 @@
         <v>224</v>
       </c>
       <c r="P336" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Q336" t="n">
         <v>111.687</v>
@@ -40855,7 +40859,7 @@
         <v>71</v>
       </c>
       <c r="P337" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q337" t="n">
         <v>106.362</v>
@@ -40975,7 +40979,7 @@
         <v>177</v>
       </c>
       <c r="P338" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q338" t="n">
         <v>114.488</v>
@@ -41095,7 +41099,7 @@
         <v>259</v>
       </c>
       <c r="P339" t="n">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q339" t="n">
         <v>107.928</v>
@@ -41214,7 +41218,9 @@
       <c r="O340" t="n">
         <v>83</v>
       </c>
-      <c r="P340" t="inlineStr"/>
+      <c r="P340" t="n">
+        <v>78</v>
+      </c>
       <c r="Q340" t="n">
         <v>111.577</v>
       </c>
@@ -41330,10 +41336,10 @@
         <v>135</v>
       </c>
       <c r="O341" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P341" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q341" t="n">
         <v>111.684</v>
@@ -41453,7 +41459,7 @@
         <v>125</v>
       </c>
       <c r="P342" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q342" t="n">
         <v>112.448</v>
@@ -41573,7 +41579,7 @@
         <v>27</v>
       </c>
       <c r="P343" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q343" t="n">
         <v>118.801</v>
@@ -41693,7 +41699,7 @@
         <v>218</v>
       </c>
       <c r="P344" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q344" t="n">
         <v>114.069</v>
@@ -41813,7 +41819,7 @@
         <v>124</v>
       </c>
       <c r="P345" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="Q345" t="n">
         <v>115.44</v>
@@ -41933,7 +41939,7 @@
         <v>100</v>
       </c>
       <c r="P346" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q346" t="n">
         <v>113.423</v>
@@ -42170,9 +42176,11 @@
         <v>73</v>
       </c>
       <c r="O348" t="n">
-        <v>60</v>
-      </c>
-      <c r="P348" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="P348" t="n">
+        <v>68</v>
+      </c>
       <c r="Q348" t="n">
         <v>121.507</v>
       </c>
@@ -42291,7 +42299,7 @@
         <v>245</v>
       </c>
       <c r="P349" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q349" t="n">
         <v>108.892</v>
@@ -42411,7 +42419,7 @@
         <v>81</v>
       </c>
       <c r="P350" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="Q350" t="n">
         <v>107.215</v>
@@ -42531,7 +42539,7 @@
         <v>334</v>
       </c>
       <c r="P351" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q351" t="n">
         <v>101.867</v>
@@ -42648,10 +42656,10 @@
         <v>155</v>
       </c>
       <c r="O352" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P352" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Q352" t="n">
         <v>106.305</v>
@@ -42891,7 +42899,7 @@
         <v>144</v>
       </c>
       <c r="P354" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q354" t="n">
         <v>108.003</v>
@@ -43011,7 +43019,7 @@
         <v>231</v>
       </c>
       <c r="P355" t="n">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q355" t="n">
         <v>100.944</v>
@@ -43131,7 +43139,7 @@
         <v>112</v>
       </c>
       <c r="P356" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Q356" t="n">
         <v>106.759</v>
@@ -43251,7 +43259,7 @@
         <v>117</v>
       </c>
       <c r="P357" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q357" t="n">
         <v>117.765</v>
@@ -43371,7 +43379,7 @@
         <v>251</v>
       </c>
       <c r="P358" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q358" t="n">
         <v>101.565</v>
@@ -43491,7 +43499,7 @@
         <v>171</v>
       </c>
       <c r="P359" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q359" t="n">
         <v>119.175</v>
@@ -43611,7 +43619,7 @@
         <v>354</v>
       </c>
       <c r="P360" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q360" t="n">
         <v>96.282</v>
@@ -43731,7 +43739,7 @@
         <v>341</v>
       </c>
       <c r="P361" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q361" t="n">
         <v>94.59999999999999</v>
@@ -43851,7 +43859,7 @@
         <v>298</v>
       </c>
       <c r="P362" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="Q362" t="n">
         <v>98.67700000000001</v>
@@ -43971,7 +43979,7 @@
         <v>300</v>
       </c>
       <c r="P363" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q363" t="n">
         <v>105.225</v>
@@ -44091,7 +44099,7 @@
         <v>296</v>
       </c>
       <c r="P364" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q364" t="n">
         <v>104.231</v>
@@ -44211,7 +44219,7 @@
         <v>269</v>
       </c>
       <c r="P365" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q365" t="n">
         <v>105.957</v>
@@ -44331,7 +44339,7 @@
         <v>324</v>
       </c>
       <c r="P366" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q366" t="n">
         <v>97.51300000000001</v>

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -2666,22 +2666,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1825.157</v>
+        <v>1830.518</v>
       </c>
       <c r="I19" t="n">
-        <v>-7.4529</v>
+        <v>-7.3446</v>
       </c>
       <c r="J19" t="n">
-        <v>1757.6</v>
+        <v>1748.1</v>
       </c>
       <c r="K19" t="n">
         <v>38</v>
@@ -2702,70 +2702,70 @@
         <v>38</v>
       </c>
       <c r="Q19" t="n">
-        <v>118.016</v>
+        <v>118.347</v>
       </c>
       <c r="R19" t="n">
-        <v>113.691</v>
+        <v>113.34</v>
       </c>
       <c r="S19" t="n">
-        <v>4.325</v>
+        <v>5.007</v>
       </c>
       <c r="T19" t="n">
-        <v>0.34924</v>
+        <v>0.34722</v>
       </c>
       <c r="U19" t="n">
-        <v>0.14565</v>
+        <v>0.14503</v>
       </c>
       <c r="V19" t="n">
-        <v>82.52</v>
+        <v>82.55</v>
       </c>
       <c r="W19" t="n">
-        <v>79.31999999999999</v>
+        <v>78.92</v>
       </c>
       <c r="X19" t="n">
-        <v>0.51</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>27.36</v>
+        <v>27.293</v>
       </c>
       <c r="Z19" t="n">
-        <v>60.03</v>
+        <v>60.068</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.93</v>
+        <v>8.249000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>23.54</v>
+        <v>24.303</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.87</v>
+        <v>19.711</v>
       </c>
       <c r="AD19" t="n">
-        <v>26.75</v>
+        <v>26.441</v>
       </c>
       <c r="AE19" t="n">
-        <v>12.07</v>
+        <v>12.068</v>
       </c>
       <c r="AF19" t="n">
-        <v>22.05</v>
+        <v>22.298</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.6</v>
+        <v>12.872</v>
       </c>
       <c r="AH19" t="n">
-        <v>7.4</v>
+        <v>7.322</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.17</v>
+        <v>4.213</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17.59</v>
+        <v>17.303</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>-3.4</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="20">
@@ -8426,22 +8426,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G67" t="b">
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1527.507</v>
+        <v>1520.481</v>
       </c>
       <c r="I67" t="n">
-        <v>-2.3908</v>
+        <v>-2.2791</v>
       </c>
       <c r="J67" t="n">
-        <v>1539.4</v>
+        <v>1545.3</v>
       </c>
       <c r="K67" t="n">
         <v>114</v>
@@ -8462,70 +8462,70 @@
         <v>115</v>
       </c>
       <c r="Q67" t="n">
-        <v>107.992</v>
+        <v>108.143</v>
       </c>
       <c r="R67" t="n">
-        <v>105.223</v>
+        <v>105.516</v>
       </c>
       <c r="S67" t="n">
-        <v>2.769</v>
+        <v>2.627</v>
       </c>
       <c r="T67" t="n">
-        <v>0.2874</v>
+        <v>0.28302</v>
       </c>
       <c r="U67" t="n">
-        <v>0.15602</v>
+        <v>0.15297</v>
       </c>
       <c r="V67" t="n">
-        <v>69.45999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="W67" t="n">
-        <v>68.05</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="X67" t="n">
-        <v>0.576</v>
+        <v>0.5583</v>
       </c>
       <c r="Y67" t="n">
-        <v>24.824</v>
+        <v>25.037</v>
       </c>
       <c r="Z67" t="n">
-        <v>55.456</v>
+        <v>56.011</v>
       </c>
       <c r="AA67" t="n">
-        <v>8.608000000000001</v>
+        <v>8.859</v>
       </c>
       <c r="AB67" t="n">
-        <v>24.456</v>
+        <v>25.019</v>
       </c>
       <c r="AC67" t="n">
-        <v>11.2</v>
+        <v>11.017</v>
       </c>
       <c r="AD67" t="n">
-        <v>17.568</v>
+        <v>17.236</v>
       </c>
       <c r="AE67" t="n">
-        <v>8.848000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="AF67" t="n">
-        <v>21.552</v>
+        <v>21.751</v>
       </c>
       <c r="AG67" t="n">
-        <v>13.232</v>
+        <v>13.448</v>
       </c>
       <c r="AH67" t="n">
-        <v>6.344</v>
+        <v>6.38</v>
       </c>
       <c r="AI67" t="n">
-        <v>4.032</v>
+        <v>4.108</v>
       </c>
       <c r="AJ67" t="n">
-        <v>16.88</v>
+        <v>16.991</v>
       </c>
       <c r="AK67" t="n">
-        <v>0.4</v>
+        <v>-1.8</v>
       </c>
       <c r="AL67" t="n">
-        <v>2</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="68">
@@ -12506,22 +12506,22 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F101" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G101" t="b">
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>1709.338</v>
+        <v>1685.089</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.2025</v>
+        <v>-1.4337</v>
       </c>
       <c r="J101" t="n">
-        <v>1514.4</v>
+        <v>1522.7</v>
       </c>
       <c r="K101" t="n">
         <v>96</v>
@@ -12542,67 +12542,67 @@
         <v>92</v>
       </c>
       <c r="Q101" t="n">
-        <v>111.945</v>
+        <v>112.217</v>
       </c>
       <c r="R101" t="n">
-        <v>104.412</v>
+        <v>105.202</v>
       </c>
       <c r="S101" t="n">
-        <v>7.533</v>
+        <v>7.015</v>
       </c>
       <c r="T101" t="n">
-        <v>0.26281</v>
+        <v>0.26936</v>
       </c>
       <c r="U101" t="n">
-        <v>0.15292</v>
+        <v>0.1523</v>
       </c>
       <c r="V101" t="n">
-        <v>72.75</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="W101" t="n">
-        <v>67.62</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="X101" t="n">
-        <v>0.7014</v>
+        <v>0.6801</v>
       </c>
       <c r="Y101" t="n">
-        <v>25.177</v>
+        <v>25.133</v>
       </c>
       <c r="Z101" t="n">
-        <v>53.487</v>
+        <v>53.745</v>
       </c>
       <c r="AA101" t="n">
-        <v>6.22</v>
+        <v>6.206</v>
       </c>
       <c r="AB101" t="n">
-        <v>18.525</v>
+        <v>18.546</v>
       </c>
       <c r="AC101" t="n">
-        <v>16.438</v>
+        <v>16.569</v>
       </c>
       <c r="AD101" t="n">
-        <v>22.736</v>
+        <v>22.763</v>
       </c>
       <c r="AE101" t="n">
-        <v>8.606</v>
+        <v>8.879</v>
       </c>
       <c r="AF101" t="n">
-        <v>23.745</v>
+        <v>23.628</v>
       </c>
       <c r="AG101" t="n">
-        <v>12.87</v>
+        <v>12.657</v>
       </c>
       <c r="AH101" t="n">
-        <v>5.142</v>
+        <v>5.093</v>
       </c>
       <c r="AI101" t="n">
-        <v>3.023</v>
+        <v>3.042</v>
       </c>
       <c r="AJ101" t="n">
-        <v>15.371</v>
+        <v>15.413</v>
       </c>
       <c r="AK101" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="AL101" t="n">
         <v>-3.1</v>
@@ -14426,22 +14426,22 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F117" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G117" t="b">
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>1407.766</v>
+        <v>1413.012</v>
       </c>
       <c r="I117" t="n">
-        <v>2.9318</v>
+        <v>2.8128</v>
       </c>
       <c r="J117" t="n">
-        <v>1372.4</v>
+        <v>1374.4</v>
       </c>
       <c r="K117" t="n">
         <v>207</v>
@@ -14462,70 +14462,70 @@
         <v>203</v>
       </c>
       <c r="Q117" t="n">
-        <v>109.065</v>
+        <v>109.768</v>
       </c>
       <c r="R117" t="n">
-        <v>98.31699999999999</v>
+        <v>99.30200000000001</v>
       </c>
       <c r="S117" t="n">
-        <v>10.748</v>
+        <v>10.466</v>
       </c>
       <c r="T117" t="n">
-        <v>0.31905</v>
+        <v>0.31778</v>
       </c>
       <c r="U117" t="n">
-        <v>0.18558</v>
+        <v>0.18288</v>
       </c>
       <c r="V117" t="n">
-        <v>74.94</v>
+        <v>75.48</v>
       </c>
       <c r="W117" t="n">
-        <v>67.73999999999999</v>
+        <v>68.45</v>
       </c>
       <c r="X117" t="n">
-        <v>0.6591</v>
+        <v>0.6702</v>
       </c>
       <c r="Y117" t="n">
-        <v>24.932</v>
+        <v>25.174</v>
       </c>
       <c r="Z117" t="n">
-        <v>55.92</v>
+        <v>56.184</v>
       </c>
       <c r="AA117" t="n">
-        <v>6.636</v>
+        <v>6.801</v>
       </c>
       <c r="AB117" t="n">
-        <v>19.17</v>
+        <v>19.252</v>
       </c>
       <c r="AC117" t="n">
-        <v>18.443</v>
+        <v>18.33</v>
       </c>
       <c r="AD117" t="n">
-        <v>24.841</v>
+        <v>24.736</v>
       </c>
       <c r="AE117" t="n">
-        <v>10.716</v>
+        <v>10.714</v>
       </c>
       <c r="AF117" t="n">
-        <v>22.682</v>
+        <v>22.834</v>
       </c>
       <c r="AG117" t="n">
-        <v>15.227</v>
+        <v>15.22</v>
       </c>
       <c r="AH117" t="n">
-        <v>8.625</v>
+        <v>8.375999999999999</v>
       </c>
       <c r="AI117" t="n">
-        <v>3.898</v>
+        <v>3.771</v>
       </c>
       <c r="AJ117" t="n">
-        <v>18.636</v>
+        <v>18.714</v>
       </c>
       <c r="AK117" t="n">
-        <v>15.4</v>
+        <v>11</v>
       </c>
       <c r="AL117" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="118">
@@ -17666,22 +17666,22 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F144" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G144" t="b">
         <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>1719.236</v>
+        <v>1743.485</v>
       </c>
       <c r="I144" t="n">
-        <v>2.9746</v>
+        <v>2.673</v>
       </c>
       <c r="J144" t="n">
-        <v>1481.5</v>
+        <v>1491.2</v>
       </c>
       <c r="K144" t="n">
         <v>125</v>
@@ -17702,70 +17702,70 @@
         <v>106</v>
       </c>
       <c r="Q144" t="n">
-        <v>117.433</v>
+        <v>117.773</v>
       </c>
       <c r="R144" t="n">
-        <v>111.215</v>
+        <v>111.278</v>
       </c>
       <c r="S144" t="n">
-        <v>6.218</v>
+        <v>6.495</v>
       </c>
       <c r="T144" t="n">
-        <v>0.17119</v>
+        <v>0.17409</v>
       </c>
       <c r="U144" t="n">
-        <v>0.1328</v>
+        <v>0.13118</v>
       </c>
       <c r="V144" t="n">
-        <v>76.15000000000001</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="W144" t="n">
-        <v>72.20999999999999</v>
+        <v>72.13</v>
       </c>
       <c r="X144" t="n">
-        <v>0.753</v>
+        <v>0.7683</v>
       </c>
       <c r="Y144" t="n">
-        <v>27.076</v>
+        <v>27.066</v>
       </c>
       <c r="Z144" t="n">
-        <v>53.286</v>
+        <v>53.378</v>
       </c>
       <c r="AA144" t="n">
-        <v>10.19</v>
+        <v>10.039</v>
       </c>
       <c r="AB144" t="n">
-        <v>25.549</v>
+        <v>25.276</v>
       </c>
       <c r="AC144" t="n">
-        <v>12.144</v>
+        <v>12.332</v>
       </c>
       <c r="AD144" t="n">
-        <v>17.311</v>
+        <v>17.385</v>
       </c>
       <c r="AE144" t="n">
-        <v>4.673</v>
+        <v>4.789</v>
       </c>
       <c r="AF144" t="n">
-        <v>21.626</v>
+        <v>21.683</v>
       </c>
       <c r="AG144" t="n">
-        <v>16.533</v>
+        <v>16.53</v>
       </c>
       <c r="AH144" t="n">
-        <v>5.978</v>
+        <v>6.04</v>
       </c>
       <c r="AI144" t="n">
-        <v>3.308</v>
+        <v>3.298</v>
       </c>
       <c r="AJ144" t="n">
-        <v>14.335</v>
+        <v>14.451</v>
       </c>
       <c r="AK144" t="n">
-        <v>-2.4</v>
+        <v>0.6</v>
       </c>
       <c r="AL144" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="145">
@@ -23546,19 +23546,19 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F193" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G193" t="b">
         <v>1</v>
       </c>
       <c r="H193" t="n">
-        <v>1734.013</v>
+        <v>1711.533</v>
       </c>
       <c r="I193" t="n">
-        <v>6.962</v>
+        <v>6.597</v>
       </c>
       <c r="J193" t="n">
         <v>1681.7</v>
@@ -23582,70 +23582,70 @@
         <v>36</v>
       </c>
       <c r="Q193" t="n">
-        <v>119.356</v>
+        <v>118.677</v>
       </c>
       <c r="R193" t="n">
-        <v>109.318</v>
+        <v>108.955</v>
       </c>
       <c r="S193" t="n">
-        <v>10.038</v>
+        <v>9.722</v>
       </c>
       <c r="T193" t="n">
-        <v>0.2802</v>
+        <v>0.28198</v>
       </c>
       <c r="U193" t="n">
-        <v>0.12879</v>
+        <v>0.13052</v>
       </c>
       <c r="V193" t="n">
-        <v>83.62</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="W193" t="n">
-        <v>76.55</v>
+        <v>76.2</v>
       </c>
       <c r="X193" t="n">
-        <v>0.601</v>
+        <v>0.5836</v>
       </c>
       <c r="Y193" t="n">
-        <v>28.392</v>
+        <v>28.178</v>
       </c>
       <c r="Z193" t="n">
-        <v>60.756</v>
+        <v>60.648</v>
       </c>
       <c r="AA193" t="n">
-        <v>10.369</v>
+        <v>10.165</v>
       </c>
       <c r="AB193" t="n">
-        <v>26.657</v>
+        <v>26.338</v>
       </c>
       <c r="AC193" t="n">
-        <v>16.463</v>
+        <v>16.594</v>
       </c>
       <c r="AD193" t="n">
-        <v>21.416</v>
+        <v>21.676</v>
       </c>
       <c r="AE193" t="n">
-        <v>9.129</v>
+        <v>9.339</v>
       </c>
       <c r="AF193" t="n">
-        <v>23.21</v>
+        <v>23.464</v>
       </c>
       <c r="AG193" t="n">
-        <v>15.576</v>
+        <v>15.398</v>
       </c>
       <c r="AH193" t="n">
-        <v>8.035</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="AI193" t="n">
-        <v>3.394</v>
+        <v>3.424</v>
       </c>
       <c r="AJ193" t="n">
-        <v>18.117</v>
+        <v>18.072</v>
       </c>
       <c r="AK193" t="n">
-        <v>-6.6</v>
+        <v>-5.8</v>
       </c>
       <c r="AL193" t="n">
-        <v>-7.1</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -26666,22 +26666,22 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F219" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G219" t="b">
         <v>1</v>
       </c>
       <c r="H219" t="n">
-        <v>1706.568</v>
+        <v>1713.594</v>
       </c>
       <c r="I219" t="n">
-        <v>-1.149</v>
+        <v>-1.1886</v>
       </c>
       <c r="J219" t="n">
-        <v>1692.8</v>
+        <v>1685</v>
       </c>
       <c r="K219" t="n">
         <v>66</v>
@@ -26702,70 +26702,70 @@
         <v>74</v>
       </c>
       <c r="Q219" t="n">
-        <v>111.498</v>
+        <v>111.537</v>
       </c>
       <c r="R219" t="n">
-        <v>110.641</v>
+        <v>110.394</v>
       </c>
       <c r="S219" t="n">
-        <v>0.857</v>
+        <v>1.144</v>
       </c>
       <c r="T219" t="n">
-        <v>0.28469</v>
+        <v>0.27727</v>
       </c>
       <c r="U219" t="n">
-        <v>0.15383</v>
+        <v>0.15255</v>
       </c>
       <c r="V219" t="n">
-        <v>84.31</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="W219" t="n">
-        <v>83.03</v>
+        <v>82.8</v>
       </c>
       <c r="X219" t="n">
-        <v>0.57</v>
+        <v>0.5921</v>
       </c>
       <c r="Y219" t="n">
-        <v>29.14</v>
+        <v>29.049</v>
       </c>
       <c r="Z219" t="n">
-        <v>63.21</v>
+        <v>62.876</v>
       </c>
       <c r="AA219" t="n">
-        <v>7.75</v>
+        <v>7.758</v>
       </c>
       <c r="AB219" t="n">
-        <v>22.93</v>
+        <v>22.663</v>
       </c>
       <c r="AC219" t="n">
-        <v>18.01</v>
+        <v>18.145</v>
       </c>
       <c r="AD219" t="n">
-        <v>24.17</v>
+        <v>24.464</v>
       </c>
       <c r="AE219" t="n">
-        <v>10.02</v>
+        <v>9.779</v>
       </c>
       <c r="AF219" t="n">
-        <v>25.01</v>
+        <v>25.404</v>
       </c>
       <c r="AG219" t="n">
-        <v>14.8</v>
+        <v>14.748</v>
       </c>
       <c r="AH219" t="n">
-        <v>7.16</v>
+        <v>7.098</v>
       </c>
       <c r="AI219" t="n">
-        <v>2.6</v>
+        <v>2.544</v>
       </c>
       <c r="AJ219" t="n">
-        <v>17.39</v>
+        <v>17.08</v>
       </c>
       <c r="AK219" t="n">
-        <v>-4.2</v>
+        <v>1.2</v>
       </c>
       <c r="AL219" t="n">
-        <v>-5.2</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="220">
@@ -27395,7 +27395,7 @@
         <v>1</v>
       </c>
       <c r="H225" t="n">
-        <v>1458.418</v>
+        <v>1435.396</v>
       </c>
       <c r="I225" t="n">
         <v>1.2024</v>
@@ -31466,22 +31466,22 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F259" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G259" t="b">
         <v>1</v>
       </c>
       <c r="H259" t="n">
-        <v>1548.014</v>
+        <v>1560.056</v>
       </c>
       <c r="I259" t="n">
-        <v>2.3807</v>
+        <v>2.1732</v>
       </c>
       <c r="J259" t="n">
-        <v>1521.6</v>
+        <v>1524.1</v>
       </c>
       <c r="K259" t="n">
         <v>119</v>
@@ -31502,70 +31502,70 @@
         <v>122</v>
       </c>
       <c r="Q259" t="n">
-        <v>100.946</v>
+        <v>100.859</v>
       </c>
       <c r="R259" t="n">
-        <v>98.42700000000001</v>
+        <v>97.512</v>
       </c>
       <c r="S259" t="n">
-        <v>2.519</v>
+        <v>3.347</v>
       </c>
       <c r="T259" t="n">
-        <v>0.2559</v>
+        <v>0.25248</v>
       </c>
       <c r="U259" t="n">
-        <v>0.16862</v>
+        <v>0.16788</v>
       </c>
       <c r="V259" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="W259" t="n">
-        <v>67.93000000000001</v>
+        <v>67.36</v>
       </c>
       <c r="X259" t="n">
-        <v>0.575</v>
+        <v>0.5974</v>
       </c>
       <c r="Y259" t="n">
-        <v>24.315</v>
+        <v>24.212</v>
       </c>
       <c r="Z259" t="n">
-        <v>56.549</v>
+        <v>56.508</v>
       </c>
       <c r="AA259" t="n">
-        <v>7.192</v>
+        <v>7.266</v>
       </c>
       <c r="AB259" t="n">
-        <v>22.044</v>
+        <v>22.022</v>
       </c>
       <c r="AC259" t="n">
-        <v>13.774</v>
+        <v>13.912</v>
       </c>
       <c r="AD259" t="n">
-        <v>19.592</v>
+        <v>19.646</v>
       </c>
       <c r="AE259" t="n">
-        <v>7.786</v>
+        <v>7.663</v>
       </c>
       <c r="AF259" t="n">
-        <v>21.997</v>
+        <v>22.049</v>
       </c>
       <c r="AG259" t="n">
-        <v>12.894</v>
+        <v>12.987</v>
       </c>
       <c r="AH259" t="n">
-        <v>7.767</v>
+        <v>7.823</v>
       </c>
       <c r="AI259" t="n">
-        <v>4.786</v>
+        <v>4.863</v>
       </c>
       <c r="AJ259" t="n">
-        <v>16.769</v>
+        <v>16.574</v>
       </c>
       <c r="AK259" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AL259" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="260">
@@ -31706,22 +31706,22 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F261" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G261" t="b">
         <v>1</v>
       </c>
       <c r="H261" t="n">
-        <v>1559.844</v>
+        <v>1550.507</v>
       </c>
       <c r="I261" t="n">
-        <v>3.1865</v>
+        <v>3.0971</v>
       </c>
       <c r="J261" t="n">
-        <v>1397.1</v>
+        <v>1405.2</v>
       </c>
       <c r="K261" t="n">
         <v>91</v>
@@ -31742,70 +31742,70 @@
         <v>89</v>
       </c>
       <c r="Q261" t="n">
-        <v>112.195</v>
+        <v>112.155</v>
       </c>
       <c r="R261" t="n">
-        <v>99.51000000000001</v>
+        <v>99.89400000000001</v>
       </c>
       <c r="S261" t="n">
-        <v>12.685</v>
+        <v>12.261</v>
       </c>
       <c r="T261" t="n">
-        <v>0.3073</v>
+        <v>0.30966</v>
       </c>
       <c r="U261" t="n">
-        <v>0.13545</v>
+        <v>0.13657</v>
       </c>
       <c r="V261" t="n">
-        <v>74.52</v>
+        <v>75</v>
       </c>
       <c r="W261" t="n">
-        <v>66.05</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="X261" t="n">
-        <v>0.832</v>
+        <v>0.8065</v>
       </c>
       <c r="Y261" t="n">
-        <v>27.072</v>
+        <v>27.254</v>
       </c>
       <c r="Z261" t="n">
-        <v>60.144</v>
+        <v>60.571</v>
       </c>
       <c r="AA261" t="n">
-        <v>8.68</v>
+        <v>8.728</v>
       </c>
       <c r="AB261" t="n">
-        <v>23.632</v>
+        <v>23.998</v>
       </c>
       <c r="AC261" t="n">
-        <v>12.376</v>
+        <v>12.295</v>
       </c>
       <c r="AD261" t="n">
-        <v>17.984</v>
+        <v>17.954</v>
       </c>
       <c r="AE261" t="n">
-        <v>10.576</v>
+        <v>10.674</v>
       </c>
       <c r="AF261" t="n">
-        <v>23.48</v>
+        <v>23.434</v>
       </c>
       <c r="AG261" t="n">
-        <v>13.232</v>
+        <v>13.179</v>
       </c>
       <c r="AH261" t="n">
-        <v>6.824</v>
+        <v>7.045</v>
       </c>
       <c r="AI261" t="n">
-        <v>3.736</v>
+        <v>3.798</v>
       </c>
       <c r="AJ261" t="n">
-        <v>15.784</v>
+        <v>16.045</v>
       </c>
       <c r="AK261" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AL261" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="262">
@@ -32066,22 +32066,22 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F264" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G264" t="b">
         <v>1</v>
       </c>
       <c r="H264" t="n">
-        <v>1548.072</v>
+        <v>1542.711</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0533</v>
+        <v>-0.006</v>
       </c>
       <c r="J264" t="n">
-        <v>1442.8</v>
+        <v>1459.5</v>
       </c>
       <c r="K264" t="n">
         <v>205</v>
@@ -32102,70 +32102,70 @@
         <v>187</v>
       </c>
       <c r="Q264" t="n">
-        <v>109.756</v>
+        <v>109.4</v>
       </c>
       <c r="R264" t="n">
-        <v>106.668</v>
+        <v>107.005</v>
       </c>
       <c r="S264" t="n">
-        <v>3.088</v>
+        <v>2.395</v>
       </c>
       <c r="T264" t="n">
-        <v>0.21373</v>
+        <v>0.21434</v>
       </c>
       <c r="U264" t="n">
-        <v>0.12862</v>
+        <v>0.12568</v>
       </c>
       <c r="V264" t="n">
-        <v>73.58</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="W264" t="n">
-        <v>71.34999999999999</v>
+        <v>71.37</v>
       </c>
       <c r="X264" t="n">
-        <v>0.6254</v>
+        <v>0.6058</v>
       </c>
       <c r="Y264" t="n">
-        <v>26.005</v>
+        <v>26.012</v>
       </c>
       <c r="Z264" t="n">
-        <v>55.621</v>
+        <v>55.855</v>
       </c>
       <c r="AA264" t="n">
-        <v>7.694</v>
+        <v>7.478</v>
       </c>
       <c r="AB264" t="n">
-        <v>21.618</v>
+        <v>21.275</v>
       </c>
       <c r="AC264" t="n">
-        <v>14.284</v>
+        <v>13.939</v>
       </c>
       <c r="AD264" t="n">
-        <v>21.542</v>
+        <v>21.139</v>
       </c>
       <c r="AE264" t="n">
-        <v>6.922</v>
+        <v>6.936</v>
       </c>
       <c r="AF264" t="n">
-        <v>24.613</v>
+        <v>24.606</v>
       </c>
       <c r="AG264" t="n">
-        <v>12.191</v>
+        <v>12.194</v>
       </c>
       <c r="AH264" t="n">
-        <v>7.81</v>
+        <v>7.797</v>
       </c>
       <c r="AI264" t="n">
-        <v>2.354</v>
+        <v>2.319</v>
       </c>
       <c r="AJ264" t="n">
-        <v>13.26</v>
+        <v>13.148</v>
       </c>
       <c r="AK264" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AL264" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="265">
@@ -34946,22 +34946,22 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F288" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G288" t="b">
         <v>1</v>
       </c>
       <c r="H288" t="n">
-        <v>1741.68</v>
+        <v>1764.159</v>
       </c>
       <c r="I288" t="n">
-        <v>2.8164</v>
+        <v>2.6628</v>
       </c>
       <c r="J288" t="n">
-        <v>1696.4</v>
+        <v>1698.6</v>
       </c>
       <c r="K288" t="n">
         <v>37</v>
@@ -34982,70 +34982,70 @@
         <v>42</v>
       </c>
       <c r="Q288" t="n">
-        <v>119.505</v>
+        <v>118.998</v>
       </c>
       <c r="R288" t="n">
-        <v>111.341</v>
+        <v>110.826</v>
       </c>
       <c r="S288" t="n">
-        <v>8.164</v>
+        <v>8.173</v>
       </c>
       <c r="T288" t="n">
-        <v>0.30721</v>
+        <v>0.30408</v>
       </c>
       <c r="U288" t="n">
-        <v>0.145</v>
+        <v>0.14433</v>
       </c>
       <c r="V288" t="n">
-        <v>82.48</v>
+        <v>82.06</v>
       </c>
       <c r="W288" t="n">
-        <v>76.77</v>
+        <v>76.34</v>
       </c>
       <c r="X288" t="n">
-        <v>0.5431</v>
+        <v>0.5665</v>
       </c>
       <c r="Y288" t="n">
-        <v>28.019</v>
+        <v>27.8</v>
       </c>
       <c r="Z288" t="n">
-        <v>58.09</v>
+        <v>58.071</v>
       </c>
       <c r="AA288" t="n">
-        <v>7.038</v>
+        <v>7.053</v>
       </c>
       <c r="AB288" t="n">
-        <v>20.446</v>
+        <v>20.366</v>
       </c>
       <c r="AC288" t="n">
-        <v>19.824</v>
+        <v>19.636</v>
       </c>
       <c r="AD288" t="n">
-        <v>26.421</v>
+        <v>26.145</v>
       </c>
       <c r="AE288" t="n">
-        <v>10.651</v>
+        <v>10.53</v>
       </c>
       <c r="AF288" t="n">
-        <v>24.115</v>
+        <v>24.173</v>
       </c>
       <c r="AG288" t="n">
-        <v>11.779</v>
+        <v>11.734</v>
       </c>
       <c r="AH288" t="n">
-        <v>5.994</v>
+        <v>6.018</v>
       </c>
       <c r="AI288" t="n">
-        <v>2.901</v>
+        <v>2.956</v>
       </c>
       <c r="AJ288" t="n">
-        <v>18.853</v>
+        <v>18.996</v>
       </c>
       <c r="AK288" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="AL288" t="n">
-        <v>-1.1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="289">
@@ -36026,22 +36026,22 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F297" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G297" t="b">
         <v>1</v>
       </c>
       <c r="H297" t="n">
-        <v>1673.101</v>
+        <v>1682.437</v>
       </c>
       <c r="I297" t="n">
-        <v>8.4628</v>
+        <v>8.0585</v>
       </c>
       <c r="J297" t="n">
-        <v>1509.4</v>
+        <v>1510.5</v>
       </c>
       <c r="K297" t="n">
         <v>63</v>
@@ -36062,70 +36062,70 @@
         <v>52</v>
       </c>
       <c r="Q297" t="n">
-        <v>121.126</v>
+        <v>121.034</v>
       </c>
       <c r="R297" t="n">
-        <v>106.46</v>
+        <v>106.412</v>
       </c>
       <c r="S297" t="n">
-        <v>14.667</v>
+        <v>14.622</v>
       </c>
       <c r="T297" t="n">
-        <v>0.27526</v>
+        <v>0.28053</v>
       </c>
       <c r="U297" t="n">
-        <v>0.14728</v>
+        <v>0.14866</v>
       </c>
       <c r="V297" t="n">
-        <v>84.16</v>
+        <v>84.47</v>
       </c>
       <c r="W297" t="n">
-        <v>73.98999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="X297" t="n">
-        <v>0.768</v>
+        <v>0.7829</v>
       </c>
       <c r="Y297" t="n">
-        <v>27.48</v>
+        <v>27.381</v>
       </c>
       <c r="Z297" t="n">
-        <v>58.136</v>
+        <v>58.439</v>
       </c>
       <c r="AA297" t="n">
-        <v>10.656</v>
+        <v>10.582</v>
       </c>
       <c r="AB297" t="n">
-        <v>27.032</v>
+        <v>27.231</v>
       </c>
       <c r="AC297" t="n">
-        <v>18.544</v>
+        <v>19.128</v>
       </c>
       <c r="AD297" t="n">
-        <v>23.704</v>
+        <v>24.437</v>
       </c>
       <c r="AE297" t="n">
-        <v>9.295999999999999</v>
+        <v>9.747999999999999</v>
       </c>
       <c r="AF297" t="n">
-        <v>24.224</v>
+        <v>24.402</v>
       </c>
       <c r="AG297" t="n">
-        <v>15.336</v>
+        <v>15.226</v>
       </c>
       <c r="AH297" t="n">
-        <v>6.44</v>
+        <v>6.665</v>
       </c>
       <c r="AI297" t="n">
-        <v>2.312</v>
+        <v>2.387</v>
       </c>
       <c r="AJ297" t="n">
-        <v>16.32</v>
+        <v>16.156</v>
       </c>
       <c r="AK297" t="n">
-        <v>11.2</v>
+        <v>5.4</v>
       </c>
       <c r="AL297" t="n">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="298">
@@ -36626,22 +36626,22 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F302" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G302" t="b">
         <v>1</v>
       </c>
       <c r="H302" t="n">
-        <v>1609.971</v>
+        <v>1592.022</v>
       </c>
       <c r="I302" t="n">
-        <v>2.2217</v>
+        <v>2.1658</v>
       </c>
       <c r="J302" t="n">
-        <v>1475.3</v>
+        <v>1481.2</v>
       </c>
       <c r="K302" t="n">
         <v>104</v>
@@ -36662,70 +36662,70 @@
         <v>117</v>
       </c>
       <c r="Q302" t="n">
-        <v>103.957</v>
+        <v>103.857</v>
       </c>
       <c r="R302" t="n">
-        <v>97.05800000000001</v>
+        <v>97.233</v>
       </c>
       <c r="S302" t="n">
-        <v>6.899</v>
+        <v>6.624</v>
       </c>
       <c r="T302" t="n">
-        <v>0.27524</v>
+        <v>0.27504</v>
       </c>
       <c r="U302" t="n">
-        <v>0.17235</v>
+        <v>0.17126</v>
       </c>
       <c r="V302" t="n">
         <v>74.19</v>
       </c>
       <c r="W302" t="n">
-        <v>69.23</v>
+        <v>69.44</v>
       </c>
       <c r="X302" t="n">
-        <v>0.6503</v>
+        <v>0.631</v>
       </c>
       <c r="Y302" t="n">
-        <v>27</v>
+        <v>26.923</v>
       </c>
       <c r="Z302" t="n">
-        <v>59.992</v>
+        <v>60.017</v>
       </c>
       <c r="AA302" t="n">
-        <v>5.832</v>
+        <v>5.704</v>
       </c>
       <c r="AB302" t="n">
-        <v>17.422</v>
+        <v>17.177</v>
       </c>
       <c r="AC302" t="n">
-        <v>14.636</v>
+        <v>14.853</v>
       </c>
       <c r="AD302" t="n">
-        <v>21.286</v>
+        <v>21.484</v>
       </c>
       <c r="AE302" t="n">
-        <v>10.28</v>
+        <v>10.249</v>
       </c>
       <c r="AF302" t="n">
-        <v>27.053</v>
+        <v>27.022</v>
       </c>
       <c r="AG302" t="n">
-        <v>15.049</v>
+        <v>14.992</v>
       </c>
       <c r="AH302" t="n">
-        <v>7.526</v>
+        <v>7.819</v>
       </c>
       <c r="AI302" t="n">
-        <v>6.036</v>
+        <v>5.885</v>
       </c>
       <c r="AJ302" t="n">
-        <v>15.818</v>
+        <v>15.927</v>
       </c>
       <c r="AK302" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AL302" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="303">
@@ -37346,22 +37346,22 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F308" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G308" t="b">
         <v>1</v>
       </c>
       <c r="H308" t="n">
-        <v>1397.919</v>
+        <v>1392.673</v>
       </c>
       <c r="I308" t="n">
-        <v>1.3468</v>
+        <v>1.415</v>
       </c>
       <c r="J308" t="n">
-        <v>1369.1</v>
+        <v>1369.9</v>
       </c>
       <c r="K308" t="n">
         <v>185</v>
@@ -37382,70 +37382,70 @@
         <v>196</v>
       </c>
       <c r="Q308" t="n">
-        <v>113.392</v>
+        <v>113.599</v>
       </c>
       <c r="R308" t="n">
-        <v>101.925</v>
+        <v>102.819</v>
       </c>
       <c r="S308" t="n">
-        <v>11.468</v>
+        <v>10.78</v>
       </c>
       <c r="T308" t="n">
-        <v>0.21757</v>
+        <v>0.21619</v>
       </c>
       <c r="U308" t="n">
-        <v>0.13504</v>
+        <v>0.13477</v>
       </c>
       <c r="V308" t="n">
-        <v>75.42</v>
+        <v>75.72</v>
       </c>
       <c r="W308" t="n">
-        <v>67.90000000000001</v>
+        <v>68.66</v>
       </c>
       <c r="X308" t="n">
-        <v>0.7352</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="Y308" t="n">
-        <v>26.462</v>
+        <v>26.596</v>
       </c>
       <c r="Z308" t="n">
-        <v>56.396</v>
+        <v>56.417</v>
       </c>
       <c r="AA308" t="n">
-        <v>7.881</v>
+        <v>7.91</v>
       </c>
       <c r="AB308" t="n">
-        <v>21.928</v>
+        <v>21.904</v>
       </c>
       <c r="AC308" t="n">
-        <v>14.618</v>
+        <v>14.622</v>
       </c>
       <c r="AD308" t="n">
-        <v>19.114</v>
+        <v>19.256</v>
       </c>
       <c r="AE308" t="n">
-        <v>7.272</v>
+        <v>7.218</v>
       </c>
       <c r="AF308" t="n">
-        <v>25.589</v>
+        <v>25.615</v>
       </c>
       <c r="AG308" t="n">
-        <v>11.892</v>
+        <v>11.897</v>
       </c>
       <c r="AH308" t="n">
-        <v>4.821</v>
+        <v>4.878</v>
       </c>
       <c r="AI308" t="n">
-        <v>2.404</v>
+        <v>2.385</v>
       </c>
       <c r="AJ308" t="n">
-        <v>13.462</v>
+        <v>13.75</v>
       </c>
       <c r="AK308" t="n">
-        <v>23</v>
+        <v>17.6</v>
       </c>
       <c r="AL308" t="n">
-        <v>18.2</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="309">
@@ -37706,22 +37706,22 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F311" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G311" t="b">
         <v>1</v>
       </c>
       <c r="H311" t="n">
-        <v>1669.074</v>
+        <v>1694.511</v>
       </c>
       <c r="I311" t="n">
-        <v>1.9449</v>
+        <v>1.7793</v>
       </c>
       <c r="J311" t="n">
-        <v>1427</v>
+        <v>1439.1</v>
       </c>
       <c r="K311" t="n">
         <v>110</v>
@@ -37742,70 +37742,70 @@
         <v>96</v>
       </c>
       <c r="Q311" t="n">
-        <v>114.725</v>
+        <v>114.505</v>
       </c>
       <c r="R311" t="n">
-        <v>103.357</v>
+        <v>103.212</v>
       </c>
       <c r="S311" t="n">
-        <v>11.368</v>
+        <v>11.293</v>
       </c>
       <c r="T311" t="n">
-        <v>0.31301</v>
+        <v>0.31717</v>
       </c>
       <c r="U311" t="n">
-        <v>0.13936</v>
+        <v>0.139</v>
       </c>
       <c r="V311" t="n">
-        <v>75.23999999999999</v>
+        <v>75</v>
       </c>
       <c r="W311" t="n">
-        <v>67.95</v>
+        <v>67.73</v>
       </c>
       <c r="X311" t="n">
-        <v>0.7916</v>
+        <v>0.8083</v>
       </c>
       <c r="Y311" t="n">
-        <v>25.373</v>
+        <v>25.351</v>
       </c>
       <c r="Z311" t="n">
-        <v>57.363</v>
+        <v>57.851</v>
       </c>
       <c r="AA311" t="n">
-        <v>8.121</v>
+        <v>8.211</v>
       </c>
       <c r="AB311" t="n">
-        <v>22.594</v>
+        <v>22.742</v>
       </c>
       <c r="AC311" t="n">
-        <v>17.028</v>
+        <v>16.561</v>
       </c>
       <c r="AD311" t="n">
-        <v>24.403</v>
+        <v>23.903</v>
       </c>
       <c r="AE311" t="n">
-        <v>11.606</v>
+        <v>11.94</v>
       </c>
       <c r="AF311" t="n">
-        <v>25.031</v>
+        <v>25.167</v>
       </c>
       <c r="AG311" t="n">
-        <v>13.34</v>
+        <v>13.403</v>
       </c>
       <c r="AH311" t="n">
-        <v>5.109</v>
+        <v>5.054</v>
       </c>
       <c r="AI311" t="n">
-        <v>2.363</v>
+        <v>2.351</v>
       </c>
       <c r="AJ311" t="n">
-        <v>17.097</v>
+        <v>17.106</v>
       </c>
       <c r="AK311" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AL311" t="n">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="312">
@@ -37826,22 +37826,22 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F312" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G312" t="b">
         <v>1</v>
       </c>
       <c r="H312" t="n">
-        <v>1644.282</v>
+        <v>1662.23</v>
       </c>
       <c r="I312" t="n">
-        <v>1.7904</v>
+        <v>1.8215</v>
       </c>
       <c r="J312" t="n">
-        <v>1628.6</v>
+        <v>1625.4</v>
       </c>
       <c r="K312" t="n">
         <v>107</v>
@@ -37862,70 +37862,70 @@
         <v>111</v>
       </c>
       <c r="Q312" t="n">
-        <v>111.008</v>
+        <v>110.869</v>
       </c>
       <c r="R312" t="n">
-        <v>111.624</v>
+        <v>110.996</v>
       </c>
       <c r="S312" t="n">
-        <v>-0.616</v>
+        <v>-0.126</v>
       </c>
       <c r="T312" t="n">
-        <v>0.29551</v>
+        <v>0.29015</v>
       </c>
       <c r="U312" t="n">
-        <v>0.16541</v>
+        <v>0.16844</v>
       </c>
       <c r="V312" t="n">
-        <v>78.89</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="W312" t="n">
-        <v>79.56999999999999</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="X312" t="n">
-        <v>0.4946</v>
+        <v>0.52</v>
       </c>
       <c r="Y312" t="n">
-        <v>27.441</v>
+        <v>27.56</v>
       </c>
       <c r="Z312" t="n">
-        <v>58.452</v>
+        <v>58.32</v>
       </c>
       <c r="AA312" t="n">
-        <v>7.413</v>
+        <v>7.55</v>
       </c>
       <c r="AB312" t="n">
-        <v>21.022</v>
+        <v>21.12</v>
       </c>
       <c r="AC312" t="n">
-        <v>16.594</v>
+        <v>16.26</v>
       </c>
       <c r="AD312" t="n">
-        <v>24.305</v>
+        <v>23.95</v>
       </c>
       <c r="AE312" t="n">
-        <v>9.743</v>
+        <v>9.57</v>
       </c>
       <c r="AF312" t="n">
-        <v>22.794</v>
+        <v>23.03</v>
       </c>
       <c r="AG312" t="n">
-        <v>14.081</v>
+        <v>14.24</v>
       </c>
       <c r="AH312" t="n">
-        <v>7.257</v>
+        <v>7.23</v>
       </c>
       <c r="AI312" t="n">
-        <v>4.567</v>
+        <v>4.7</v>
       </c>
       <c r="AJ312" t="n">
-        <v>21.671</v>
+        <v>21.55</v>
       </c>
       <c r="AK312" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AL312" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="313">
@@ -41186,22 +41186,22 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F340" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G340" t="b">
         <v>1</v>
       </c>
       <c r="H340" t="n">
-        <v>1623.971</v>
+        <v>1632.359</v>
       </c>
       <c r="I340" t="n">
-        <v>1.8722</v>
+        <v>1.9753</v>
       </c>
       <c r="J340" t="n">
-        <v>1546.5</v>
+        <v>1543.7</v>
       </c>
       <c r="K340" t="n">
         <v>82</v>
@@ -41222,70 +41222,70 @@
         <v>78</v>
       </c>
       <c r="Q340" t="n">
-        <v>111.577</v>
+        <v>111.467</v>
       </c>
       <c r="R340" t="n">
-        <v>102.283</v>
+        <v>101.995</v>
       </c>
       <c r="S340" t="n">
-        <v>9.295</v>
+        <v>9.473000000000001</v>
       </c>
       <c r="T340" t="n">
-        <v>0.34458</v>
+        <v>0.34362</v>
       </c>
       <c r="U340" t="n">
-        <v>0.14529</v>
+        <v>0.14702</v>
       </c>
       <c r="V340" t="n">
-        <v>76.86</v>
+        <v>76.97</v>
       </c>
       <c r="W340" t="n">
-        <v>70.45999999999999</v>
+        <v>70.45</v>
       </c>
       <c r="X340" t="n">
-        <v>0.6492</v>
+        <v>0.67</v>
       </c>
       <c r="Y340" t="n">
-        <v>27.161</v>
+        <v>27.28</v>
       </c>
       <c r="Z340" t="n">
-        <v>62.214</v>
+        <v>62.39</v>
       </c>
       <c r="AA340" t="n">
-        <v>7.091</v>
+        <v>7.04</v>
       </c>
       <c r="AB340" t="n">
-        <v>21.226</v>
+        <v>21.12</v>
       </c>
       <c r="AC340" t="n">
-        <v>15.442</v>
+        <v>15.37</v>
       </c>
       <c r="AD340" t="n">
-        <v>22.473</v>
+        <v>22.52</v>
       </c>
       <c r="AE340" t="n">
-        <v>13.267</v>
+        <v>13.43</v>
       </c>
       <c r="AF340" t="n">
-        <v>25.187</v>
+        <v>25.67</v>
       </c>
       <c r="AG340" t="n">
-        <v>11.401</v>
+        <v>11.42</v>
       </c>
       <c r="AH340" t="n">
-        <v>6.103</v>
+        <v>6.01</v>
       </c>
       <c r="AI340" t="n">
-        <v>4.032</v>
+        <v>3.92</v>
       </c>
       <c r="AJ340" t="n">
-        <v>17.578</v>
+        <v>17.46</v>
       </c>
       <c r="AK340" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AL340" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="341">
@@ -41906,22 +41906,22 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F346" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G346" t="b">
         <v>1</v>
       </c>
       <c r="H346" t="n">
-        <v>1521.064</v>
+        <v>1512.677</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.1434</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="J346" t="n">
-        <v>1563.6</v>
+        <v>1565.2</v>
       </c>
       <c r="K346" t="n">
         <v>98</v>
@@ -41942,70 +41942,70 @@
         <v>99</v>
       </c>
       <c r="Q346" t="n">
-        <v>113.423</v>
+        <v>112.648</v>
       </c>
       <c r="R346" t="n">
-        <v>109.184</v>
+        <v>108.708</v>
       </c>
       <c r="S346" t="n">
-        <v>4.239</v>
+        <v>3.94</v>
       </c>
       <c r="T346" t="n">
-        <v>0.32866</v>
+        <v>0.3246</v>
       </c>
       <c r="U346" t="n">
-        <v>0.15531</v>
+        <v>0.15516</v>
       </c>
       <c r="V346" t="n">
-        <v>76.33</v>
+        <v>76.13</v>
       </c>
       <c r="W346" t="n">
-        <v>72.90000000000001</v>
+        <v>72.95</v>
       </c>
       <c r="X346" t="n">
-        <v>0.5431</v>
+        <v>0.5265</v>
       </c>
       <c r="Y346" t="n">
-        <v>26.256</v>
+        <v>26.208</v>
       </c>
       <c r="Z346" t="n">
-        <v>58.532</v>
+        <v>58.683</v>
       </c>
       <c r="AA346" t="n">
-        <v>8.207000000000001</v>
+        <v>8.327999999999999</v>
       </c>
       <c r="AB346" t="n">
-        <v>25.089</v>
+        <v>25.244</v>
       </c>
       <c r="AC346" t="n">
-        <v>15.607</v>
+        <v>15.388</v>
       </c>
       <c r="AD346" t="n">
-        <v>20.799</v>
+        <v>20.774</v>
       </c>
       <c r="AE346" t="n">
-        <v>10.874</v>
+        <v>10.703</v>
       </c>
       <c r="AF346" t="n">
-        <v>22.287</v>
+        <v>22.399</v>
       </c>
       <c r="AG346" t="n">
-        <v>13.939</v>
+        <v>14.129</v>
       </c>
       <c r="AH346" t="n">
-        <v>6.376</v>
+        <v>6.603</v>
       </c>
       <c r="AI346" t="n">
-        <v>2.351</v>
+        <v>2.381</v>
       </c>
       <c r="AJ346" t="n">
-        <v>21.096</v>
+        <v>21.173</v>
       </c>
       <c r="AK346" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AL346" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="347">
@@ -42146,22 +42146,22 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F348" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G348" t="b">
         <v>1</v>
       </c>
       <c r="H348" t="n">
-        <v>1684.172</v>
+        <v>1681.756</v>
       </c>
       <c r="I348" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.8274</v>
       </c>
       <c r="J348" t="n">
-        <v>1457.5</v>
+        <v>1468</v>
       </c>
       <c r="K348" t="n">
         <v>81</v>
@@ -42182,70 +42182,70 @@
         <v>68</v>
       </c>
       <c r="Q348" t="n">
-        <v>121.507</v>
+        <v>120.747</v>
       </c>
       <c r="R348" t="n">
-        <v>108.892</v>
+        <v>108.547</v>
       </c>
       <c r="S348" t="n">
-        <v>12.615</v>
+        <v>12.199</v>
       </c>
       <c r="T348" t="n">
-        <v>0.29055</v>
+        <v>0.29606</v>
       </c>
       <c r="U348" t="n">
-        <v>0.13803</v>
+        <v>0.13678</v>
       </c>
       <c r="V348" t="n">
-        <v>80.66</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="W348" t="n">
-        <v>72.2</v>
+        <v>71.78</v>
       </c>
       <c r="X348" t="n">
-        <v>0.7741</v>
+        <v>0.7483</v>
       </c>
       <c r="Y348" t="n">
-        <v>28.331</v>
+        <v>28.163</v>
       </c>
       <c r="Z348" t="n">
-        <v>57.843</v>
+        <v>58.19</v>
       </c>
       <c r="AA348" t="n">
-        <v>8.581</v>
+        <v>8.476000000000001</v>
       </c>
       <c r="AB348" t="n">
-        <v>21.104</v>
+        <v>21.286</v>
       </c>
       <c r="AC348" t="n">
-        <v>15.613</v>
+        <v>15.293</v>
       </c>
       <c r="AD348" t="n">
-        <v>20.328</v>
+        <v>20.469</v>
       </c>
       <c r="AE348" t="n">
-        <v>9.557</v>
+        <v>10.034</v>
       </c>
       <c r="AF348" t="n">
-        <v>23.15</v>
+        <v>23.388</v>
       </c>
       <c r="AG348" t="n">
-        <v>15.628</v>
+        <v>15.626</v>
       </c>
       <c r="AH348" t="n">
-        <v>5.211</v>
+        <v>5.204</v>
       </c>
       <c r="AI348" t="n">
-        <v>3.12</v>
+        <v>3.197</v>
       </c>
       <c r="AJ348" t="n">
-        <v>16.106</v>
+        <v>16.054</v>
       </c>
       <c r="AK348" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AL348" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="349">
@@ -43226,22 +43226,22 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F357" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G357" t="b">
         <v>1</v>
       </c>
       <c r="H357" t="n">
-        <v>1562.594</v>
+        <v>1550.552</v>
       </c>
       <c r="I357" t="n">
-        <v>2.9745</v>
+        <v>2.8057</v>
       </c>
       <c r="J357" t="n">
-        <v>1395</v>
+        <v>1402</v>
       </c>
       <c r="K357" t="n">
         <v>109</v>
@@ -43262,70 +43262,70 @@
         <v>103</v>
       </c>
       <c r="Q357" t="n">
-        <v>117.765</v>
+        <v>116.064</v>
       </c>
       <c r="R357" t="n">
-        <v>105.683</v>
+        <v>105.279</v>
       </c>
       <c r="S357" t="n">
-        <v>12.082</v>
+        <v>10.785</v>
       </c>
       <c r="T357" t="n">
-        <v>0.17386</v>
+        <v>0.17931</v>
       </c>
       <c r="U357" t="n">
-        <v>0.13275</v>
+        <v>0.14</v>
       </c>
       <c r="V357" t="n">
-        <v>81.67</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="W357" t="n">
-        <v>73.22</v>
+        <v>73.03</v>
       </c>
       <c r="X357" t="n">
-        <v>0.6912</v>
+        <v>0.6696</v>
       </c>
       <c r="Y357" t="n">
-        <v>29.077</v>
+        <v>28.812</v>
       </c>
       <c r="Z357" t="n">
-        <v>56.738</v>
+        <v>56.861</v>
       </c>
       <c r="AA357" t="n">
-        <v>9.798</v>
+        <v>9.622999999999999</v>
       </c>
       <c r="AB357" t="n">
-        <v>26.472</v>
+        <v>26.368</v>
       </c>
       <c r="AC357" t="n">
-        <v>13.762</v>
+        <v>13.354</v>
       </c>
       <c r="AD357" t="n">
-        <v>20.042</v>
+        <v>19.446</v>
       </c>
       <c r="AE357" t="n">
-        <v>5.476</v>
+        <v>5.771</v>
       </c>
       <c r="AF357" t="n">
-        <v>24.165</v>
+        <v>24.464</v>
       </c>
       <c r="AG357" t="n">
-        <v>16.406</v>
+        <v>16.13</v>
       </c>
       <c r="AH357" t="n">
-        <v>7.436</v>
+        <v>7.403</v>
       </c>
       <c r="AI357" t="n">
-        <v>2.613</v>
+        <v>2.606</v>
       </c>
       <c r="AJ357" t="n">
-        <v>16.149</v>
+        <v>16.183</v>
       </c>
       <c r="AK357" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="AL357" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="358">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -3986,22 +3986,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1617.146</v>
+        <v>1599.461</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2181</v>
+        <v>1.0977</v>
       </c>
       <c r="J30" t="n">
-        <v>1524.5</v>
+        <v>1530.5</v>
       </c>
       <c r="K30" t="n">
         <v>123</v>
@@ -4022,70 +4022,70 @@
         <v>113</v>
       </c>
       <c r="Q30" t="n">
-        <v>110.424</v>
+        <v>110.575</v>
       </c>
       <c r="R30" t="n">
-        <v>106.062</v>
+        <v>107.267</v>
       </c>
       <c r="S30" t="n">
-        <v>4.362</v>
+        <v>3.308</v>
       </c>
       <c r="T30" t="n">
-        <v>0.26313</v>
+        <v>0.26698</v>
       </c>
       <c r="U30" t="n">
-        <v>0.13661</v>
+        <v>0.13706</v>
       </c>
       <c r="V30" t="n">
-        <v>77.20999999999999</v>
+        <v>76.84</v>
       </c>
       <c r="W30" t="n">
-        <v>74.02</v>
+        <v>74.28</v>
       </c>
       <c r="X30" t="n">
-        <v>0.6171</v>
+        <v>0.599</v>
       </c>
       <c r="Y30" t="n">
-        <v>26.501</v>
+        <v>26.324</v>
       </c>
       <c r="Z30" t="n">
-        <v>59.551</v>
+        <v>59.385</v>
       </c>
       <c r="AA30" t="n">
-        <v>8.592000000000001</v>
+        <v>8.682</v>
       </c>
       <c r="AB30" t="n">
-        <v>23.687</v>
+        <v>23.797</v>
       </c>
       <c r="AC30" t="n">
-        <v>15.788</v>
+        <v>15.63</v>
       </c>
       <c r="AD30" t="n">
-        <v>21.511</v>
+        <v>21.277</v>
       </c>
       <c r="AE30" t="n">
-        <v>8.497999999999999</v>
+        <v>8.611000000000001</v>
       </c>
       <c r="AF30" t="n">
-        <v>23.401</v>
+        <v>23.348</v>
       </c>
       <c r="AG30" t="n">
-        <v>13.377</v>
+        <v>13.329</v>
       </c>
       <c r="AH30" t="n">
-        <v>7.617</v>
+        <v>7.307</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18.864</v>
+        <v>18.88</v>
       </c>
       <c r="AK30" t="n">
-        <v>3.6</v>
+        <v>-2</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31">
@@ -5066,22 +5066,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1703.272</v>
+        <v>1710.414</v>
       </c>
       <c r="I39" t="n">
-        <v>7.292</v>
+        <v>6.8262</v>
       </c>
       <c r="J39" t="n">
-        <v>1603.7</v>
+        <v>1600.4</v>
       </c>
       <c r="K39" t="n">
         <v>73</v>
@@ -5102,70 +5102,70 @@
         <v>67</v>
       </c>
       <c r="Q39" t="n">
-        <v>110.159</v>
+        <v>110.668</v>
       </c>
       <c r="R39" t="n">
-        <v>104.763</v>
+        <v>104.285</v>
       </c>
       <c r="S39" t="n">
-        <v>5.396</v>
+        <v>6.383</v>
       </c>
       <c r="T39" t="n">
-        <v>0.23512</v>
+        <v>0.23394</v>
       </c>
       <c r="U39" t="n">
-        <v>0.14496</v>
+        <v>0.14794</v>
       </c>
       <c r="V39" t="n">
-        <v>77.52</v>
+        <v>77.95</v>
       </c>
       <c r="W39" t="n">
-        <v>73.56999999999999</v>
+        <v>73.31</v>
       </c>
       <c r="X39" t="n">
-        <v>0.6377</v>
+        <v>0.6599</v>
       </c>
       <c r="Y39" t="n">
-        <v>25.867</v>
+        <v>26.065</v>
       </c>
       <c r="Z39" t="n">
-        <v>58.099</v>
+        <v>58.02</v>
       </c>
       <c r="AA39" t="n">
-        <v>9.023</v>
+        <v>9.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>24.832</v>
+        <v>24.94</v>
       </c>
       <c r="AC39" t="n">
-        <v>16.765</v>
+        <v>16.575</v>
       </c>
       <c r="AD39" t="n">
-        <v>21.704</v>
+        <v>21.274</v>
       </c>
       <c r="AE39" t="n">
-        <v>7.603</v>
+        <v>7.495</v>
       </c>
       <c r="AF39" t="n">
-        <v>24.339</v>
+        <v>24.215</v>
       </c>
       <c r="AG39" t="n">
-        <v>13.838</v>
+        <v>14.168</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.678</v>
+        <v>5.888</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.128</v>
+        <v>2.999</v>
       </c>
       <c r="AJ39" t="n">
-        <v>19.009</v>
+        <v>18.864</v>
       </c>
       <c r="AK39" t="n">
-        <v>-2.8</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>-2.1</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="40">
@@ -7106,22 +7106,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1655.821</v>
+        <v>1633.654</v>
       </c>
       <c r="I56" t="n">
-        <v>-4.6276</v>
+        <v>-4.3855</v>
       </c>
       <c r="J56" t="n">
-        <v>1564.6</v>
+        <v>1564.1</v>
       </c>
       <c r="K56" t="n">
         <v>88</v>
@@ -7142,70 +7142,70 @@
         <v>87</v>
       </c>
       <c r="Q56" t="n">
-        <v>117.701</v>
+        <v>117.184</v>
       </c>
       <c r="R56" t="n">
-        <v>112.562</v>
+        <v>112.366</v>
       </c>
       <c r="S56" t="n">
-        <v>5.14</v>
+        <v>4.819</v>
       </c>
       <c r="T56" t="n">
-        <v>0.26372</v>
+        <v>0.26623</v>
       </c>
       <c r="U56" t="n">
-        <v>0.17614</v>
+        <v>0.17522</v>
       </c>
       <c r="V56" t="n">
-        <v>75.05</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="W56" t="n">
-        <v>71.65000000000001</v>
+        <v>71.55</v>
       </c>
       <c r="X56" t="n">
-        <v>0.6183</v>
+        <v>0.6</v>
       </c>
       <c r="Y56" t="n">
-        <v>24.781</v>
+        <v>24.69</v>
       </c>
       <c r="Z56" t="n">
-        <v>51.374</v>
+        <v>51.58</v>
       </c>
       <c r="AA56" t="n">
-        <v>9.878</v>
+        <v>9.73</v>
       </c>
       <c r="AB56" t="n">
-        <v>25.251</v>
+        <v>25.35</v>
       </c>
       <c r="AC56" t="n">
-        <v>15.606</v>
+        <v>15.63</v>
       </c>
       <c r="AD56" t="n">
-        <v>20.234</v>
+        <v>20.3</v>
       </c>
       <c r="AE56" t="n">
-        <v>7.763</v>
+        <v>7.92</v>
       </c>
       <c r="AF56" t="n">
-        <v>22.124</v>
+        <v>22.2</v>
       </c>
       <c r="AG56" t="n">
-        <v>15.595</v>
+        <v>15.51</v>
       </c>
       <c r="AH56" t="n">
-        <v>5.185</v>
+        <v>5.22</v>
       </c>
       <c r="AI56" t="n">
-        <v>2.155</v>
+        <v>2.15</v>
       </c>
       <c r="AJ56" t="n">
-        <v>16.984</v>
+        <v>16.92</v>
       </c>
       <c r="AK56" t="n">
-        <v>0.8</v>
+        <v>-2.6</v>
       </c>
       <c r="AL56" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="57">
@@ -8546,22 +8546,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F68" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1677.744</v>
+        <v>1695.429</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.9174</v>
+        <v>-1.7367</v>
       </c>
       <c r="J68" t="n">
-        <v>1574.7</v>
+        <v>1574.5</v>
       </c>
       <c r="K68" t="n">
         <v>78</v>
@@ -8582,70 +8582,70 @@
         <v>69</v>
       </c>
       <c r="Q68" t="n">
-        <v>109.173</v>
+        <v>110.224</v>
       </c>
       <c r="R68" t="n">
-        <v>102.25</v>
+        <v>102.463</v>
       </c>
       <c r="S68" t="n">
-        <v>6.923</v>
+        <v>7.761</v>
       </c>
       <c r="T68" t="n">
-        <v>0.25145</v>
+        <v>0.24689</v>
       </c>
       <c r="U68" t="n">
-        <v>0.17261</v>
+        <v>0.16853</v>
       </c>
       <c r="V68" t="n">
-        <v>74.22</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="W68" t="n">
-        <v>69.88</v>
+        <v>69.73</v>
       </c>
       <c r="X68" t="n">
-        <v>0.6691</v>
+        <v>0.6889</v>
       </c>
       <c r="Y68" t="n">
-        <v>23.989</v>
+        <v>24.038</v>
       </c>
       <c r="Z68" t="n">
-        <v>53.465</v>
+        <v>53.26</v>
       </c>
       <c r="AA68" t="n">
-        <v>7.64</v>
+        <v>7.699</v>
       </c>
       <c r="AB68" t="n">
-        <v>22.338</v>
+        <v>22.186</v>
       </c>
       <c r="AC68" t="n">
-        <v>18.571</v>
+        <v>18.766</v>
       </c>
       <c r="AD68" t="n">
-        <v>24.796</v>
+        <v>24.887</v>
       </c>
       <c r="AE68" t="n">
-        <v>7.942</v>
+        <v>7.751</v>
       </c>
       <c r="AF68" t="n">
-        <v>23.233</v>
+        <v>23.103</v>
       </c>
       <c r="AG68" t="n">
-        <v>14.4</v>
+        <v>14.291</v>
       </c>
       <c r="AH68" t="n">
-        <v>8.148999999999999</v>
+        <v>8.083</v>
       </c>
       <c r="AI68" t="n">
-        <v>4.145</v>
+        <v>4.064</v>
       </c>
       <c r="AJ68" t="n">
-        <v>16.865</v>
+        <v>16.82</v>
       </c>
       <c r="AK68" t="n">
-        <v>-0.6</v>
+        <v>1.2</v>
       </c>
       <c r="AL68" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="69">
@@ -12146,22 +12146,22 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F98" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G98" t="b">
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>1525.82</v>
+        <v>1546.505</v>
       </c>
       <c r="I98" t="n">
-        <v>-3.7537</v>
+        <v>-3.6146</v>
       </c>
       <c r="J98" t="n">
-        <v>1543.4</v>
+        <v>1543.8</v>
       </c>
       <c r="K98" t="n">
         <v>85</v>
@@ -12185,67 +12185,67 @@
         <v>114.986</v>
       </c>
       <c r="R98" t="n">
-        <v>105.766</v>
+        <v>105.859</v>
       </c>
       <c r="S98" t="n">
-        <v>9.220000000000001</v>
+        <v>9.127000000000001</v>
       </c>
       <c r="T98" t="n">
-        <v>0.32427</v>
+        <v>0.32167</v>
       </c>
       <c r="U98" t="n">
-        <v>0.17282</v>
+        <v>0.17626</v>
       </c>
       <c r="V98" t="n">
-        <v>81.59</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="W98" t="n">
-        <v>74.95</v>
+        <v>74.92</v>
       </c>
       <c r="X98" t="n">
-        <v>0.5245</v>
+        <v>0.5508</v>
       </c>
       <c r="Y98" t="n">
-        <v>28.123</v>
+        <v>28.036</v>
       </c>
       <c r="Z98" t="n">
-        <v>60.651</v>
+        <v>60.217</v>
       </c>
       <c r="AA98" t="n">
-        <v>9.914</v>
+        <v>9.922000000000001</v>
       </c>
       <c r="AB98" t="n">
-        <v>28.262</v>
+        <v>27.995</v>
       </c>
       <c r="AC98" t="n">
-        <v>15.302</v>
+        <v>15.371</v>
       </c>
       <c r="AD98" t="n">
-        <v>21.327</v>
+        <v>21.246</v>
       </c>
       <c r="AE98" t="n">
-        <v>11.433</v>
+        <v>11.276</v>
       </c>
       <c r="AF98" t="n">
-        <v>23.488</v>
+        <v>23.449</v>
       </c>
       <c r="AG98" t="n">
-        <v>15.309</v>
+        <v>15.424</v>
       </c>
       <c r="AH98" t="n">
-        <v>7.407</v>
+        <v>7.461</v>
       </c>
       <c r="AI98" t="n">
-        <v>3.203</v>
+        <v>3.335</v>
       </c>
       <c r="AJ98" t="n">
         <v>18.161</v>
       </c>
       <c r="AK98" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL98" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="99">
@@ -14786,22 +14786,22 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F120" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G120" t="b">
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>1528.61</v>
+        <v>1521.468</v>
       </c>
       <c r="I120" t="n">
-        <v>2.2588</v>
+        <v>2.3348</v>
       </c>
       <c r="J120" t="n">
-        <v>1508.7</v>
+        <v>1515.5</v>
       </c>
       <c r="K120" t="n">
         <v>105</v>
@@ -14822,70 +14822,70 @@
         <v>110</v>
       </c>
       <c r="Q120" t="n">
-        <v>108.828</v>
+        <v>108.58</v>
       </c>
       <c r="R120" t="n">
-        <v>104.272</v>
+        <v>104.924</v>
       </c>
       <c r="S120" t="n">
-        <v>4.556</v>
+        <v>3.656</v>
       </c>
       <c r="T120" t="n">
-        <v>0.34057</v>
+        <v>0.33986</v>
       </c>
       <c r="U120" t="n">
-        <v>0.16472</v>
+        <v>0.16596</v>
       </c>
       <c r="V120" t="n">
         <v>73.93000000000001</v>
       </c>
       <c r="W120" t="n">
-        <v>70.72</v>
+        <v>71.38</v>
       </c>
       <c r="X120" t="n">
-        <v>0.5273</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="Y120" t="n">
-        <v>25.944</v>
+        <v>26.021</v>
       </c>
       <c r="Z120" t="n">
-        <v>58.305</v>
+        <v>58.324</v>
       </c>
       <c r="AA120" t="n">
-        <v>6.448</v>
+        <v>6.317</v>
       </c>
       <c r="AB120" t="n">
-        <v>19.867</v>
+        <v>19.664</v>
       </c>
       <c r="AC120" t="n">
-        <v>15.769</v>
+        <v>15.634</v>
       </c>
       <c r="AD120" t="n">
-        <v>21.778</v>
+        <v>21.627</v>
       </c>
       <c r="AE120" t="n">
-        <v>11.125</v>
+        <v>11.039</v>
       </c>
       <c r="AF120" t="n">
-        <v>21.947</v>
+        <v>21.822</v>
       </c>
       <c r="AG120" t="n">
-        <v>14.175</v>
+        <v>14.35</v>
       </c>
       <c r="AH120" t="n">
-        <v>7.622</v>
+        <v>7.558</v>
       </c>
       <c r="AI120" t="n">
-        <v>3.79</v>
+        <v>3.826</v>
       </c>
       <c r="AJ120" t="n">
-        <v>17.04</v>
+        <v>16.949</v>
       </c>
       <c r="AK120" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="AL120" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="121">
@@ -15026,22 +15026,22 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F122" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G122" t="b">
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>1580.626</v>
+        <v>1594.577</v>
       </c>
       <c r="I122" t="n">
-        <v>2.2563</v>
+        <v>2.1793</v>
       </c>
       <c r="J122" t="n">
-        <v>1504.8</v>
+        <v>1508.2</v>
       </c>
       <c r="K122" t="n">
         <v>103</v>
@@ -15062,70 +15062,70 @@
         <v>95</v>
       </c>
       <c r="Q122" t="n">
-        <v>109.572</v>
+        <v>110.094</v>
       </c>
       <c r="R122" t="n">
-        <v>102.175</v>
+        <v>101.357</v>
       </c>
       <c r="S122" t="n">
-        <v>7.397</v>
+        <v>8.738</v>
       </c>
       <c r="T122" t="n">
-        <v>0.25789</v>
+        <v>0.25529</v>
       </c>
       <c r="U122" t="n">
-        <v>0.16388</v>
+        <v>0.15942</v>
       </c>
       <c r="V122" t="n">
-        <v>74.33</v>
+        <v>74.73</v>
       </c>
       <c r="W122" t="n">
-        <v>69.14</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="X122" t="n">
-        <v>0.6069</v>
+        <v>0.6284</v>
       </c>
       <c r="Y122" t="n">
-        <v>27.019</v>
+        <v>27</v>
       </c>
       <c r="Z122" t="n">
-        <v>57.674</v>
+        <v>57.961</v>
       </c>
       <c r="AA122" t="n">
-        <v>8.638999999999999</v>
+        <v>8.819000000000001</v>
       </c>
       <c r="AB122" t="n">
-        <v>24.303</v>
+        <v>24.781</v>
       </c>
       <c r="AC122" t="n">
-        <v>12.568</v>
+        <v>12.588</v>
       </c>
       <c r="AD122" t="n">
-        <v>17.676</v>
+        <v>17.752</v>
       </c>
       <c r="AE122" t="n">
-        <v>8.638999999999999</v>
+        <v>8.619</v>
       </c>
       <c r="AF122" t="n">
-        <v>25.051</v>
+        <v>25.431</v>
       </c>
       <c r="AG122" t="n">
-        <v>13.812</v>
+        <v>14.032</v>
       </c>
       <c r="AH122" t="n">
-        <v>5.565</v>
+        <v>5.637</v>
       </c>
       <c r="AI122" t="n">
-        <v>2.233</v>
+        <v>2.257</v>
       </c>
       <c r="AJ122" t="n">
-        <v>17.429</v>
+        <v>17.221</v>
       </c>
       <c r="AK122" t="n">
-        <v>-2</v>
+        <v>-1.2</v>
       </c>
       <c r="AL122" t="n">
-        <v>-1.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="123">
@@ -16946,22 +16946,22 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F138" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G138" t="b">
         <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>1600.738</v>
+        <v>1586.787</v>
       </c>
       <c r="I138" t="n">
-        <v>0.115</v>
+        <v>0.0072</v>
       </c>
       <c r="J138" t="n">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K138" t="n">
         <v>148</v>
@@ -16982,70 +16982,70 @@
         <v>141</v>
       </c>
       <c r="Q138" t="n">
-        <v>112.171</v>
+        <v>111.134</v>
       </c>
       <c r="R138" t="n">
-        <v>109.176</v>
+        <v>109.344</v>
       </c>
       <c r="S138" t="n">
-        <v>2.995</v>
+        <v>1.79</v>
       </c>
       <c r="T138" t="n">
-        <v>0.32353</v>
+        <v>0.31864</v>
       </c>
       <c r="U138" t="n">
-        <v>0.17631</v>
+        <v>0.17543</v>
       </c>
       <c r="V138" t="n">
-        <v>82.89</v>
+        <v>82.03</v>
       </c>
       <c r="W138" t="n">
-        <v>80.62</v>
+        <v>80.61</v>
       </c>
       <c r="X138" t="n">
-        <v>0.7028</v>
+        <v>0.6813</v>
       </c>
       <c r="Y138" t="n">
-        <v>26.612</v>
+        <v>26.45</v>
       </c>
       <c r="Z138" t="n">
-        <v>60.812</v>
+        <v>60.872</v>
       </c>
       <c r="AA138" t="n">
-        <v>9.619</v>
+        <v>9.539</v>
       </c>
       <c r="AB138" t="n">
-        <v>27.319</v>
+        <v>27.35</v>
       </c>
       <c r="AC138" t="n">
-        <v>20.042</v>
+        <v>19.591</v>
       </c>
       <c r="AD138" t="n">
-        <v>26.917</v>
+        <v>26.338</v>
       </c>
       <c r="AE138" t="n">
-        <v>11.864</v>
+        <v>11.703</v>
       </c>
       <c r="AF138" t="n">
-        <v>24.425</v>
+        <v>24.763</v>
       </c>
       <c r="AG138" t="n">
-        <v>14.999</v>
+        <v>15.133</v>
       </c>
       <c r="AH138" t="n">
-        <v>6.671</v>
+        <v>6.49</v>
       </c>
       <c r="AI138" t="n">
-        <v>3.268</v>
+        <v>3.239</v>
       </c>
       <c r="AJ138" t="n">
-        <v>20.135</v>
+        <v>19.933</v>
       </c>
       <c r="AK138" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AL138" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="139">
@@ -17546,22 +17546,22 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F143" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G143" t="b">
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>1325.524</v>
+        <v>1320.16</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.465</v>
+        <v>-0.3498</v>
       </c>
       <c r="J143" t="n">
-        <v>1399</v>
+        <v>1394.1</v>
       </c>
       <c r="K143" t="n">
         <v>284</v>
@@ -17582,70 +17582,70 @@
         <v>275</v>
       </c>
       <c r="Q143" t="n">
-        <v>105.584</v>
+        <v>104.495</v>
       </c>
       <c r="R143" t="n">
-        <v>108.389</v>
+        <v>108.288</v>
       </c>
       <c r="S143" t="n">
-        <v>-2.804</v>
+        <v>-3.793</v>
       </c>
       <c r="T143" t="n">
-        <v>0.22286</v>
+        <v>0.22012</v>
       </c>
       <c r="U143" t="n">
-        <v>0.17072</v>
+        <v>0.17007</v>
       </c>
       <c r="V143" t="n">
-        <v>72.40000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="W143" t="n">
-        <v>74.47</v>
+        <v>74.34</v>
       </c>
       <c r="X143" t="n">
-        <v>0.5063</v>
+        <v>0.4792</v>
       </c>
       <c r="Y143" t="n">
-        <v>25.759</v>
+        <v>25.832</v>
       </c>
       <c r="Z143" t="n">
-        <v>55.648</v>
+        <v>55.712</v>
       </c>
       <c r="AA143" t="n">
-        <v>7.766</v>
+        <v>7.552</v>
       </c>
       <c r="AB143" t="n">
-        <v>21.222</v>
+        <v>20.74</v>
       </c>
       <c r="AC143" t="n">
-        <v>13.112</v>
+        <v>12.935</v>
       </c>
       <c r="AD143" t="n">
-        <v>17.983</v>
+        <v>17.66</v>
       </c>
       <c r="AE143" t="n">
-        <v>6.564</v>
+        <v>6.491</v>
       </c>
       <c r="AF143" t="n">
-        <v>22.432</v>
+        <v>22.628</v>
       </c>
       <c r="AG143" t="n">
-        <v>13.987</v>
+        <v>13.625</v>
       </c>
       <c r="AH143" t="n">
-        <v>6.635</v>
+        <v>6.879</v>
       </c>
       <c r="AI143" t="n">
-        <v>3.161</v>
+        <v>3.37</v>
       </c>
       <c r="AJ143" t="n">
-        <v>16.136</v>
+        <v>15.911</v>
       </c>
       <c r="AK143" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="AL143" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="144">
@@ -20546,22 +20546,22 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F168" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G168" t="b">
         <v>1</v>
       </c>
       <c r="H168" t="n">
-        <v>1758.619</v>
+        <v>1780.382</v>
       </c>
       <c r="I168" t="n">
-        <v>9.362500000000001</v>
+        <v>8.9497</v>
       </c>
       <c r="J168" t="n">
-        <v>1416.9</v>
+        <v>1429.2</v>
       </c>
       <c r="K168" t="n">
         <v>93</v>
@@ -20582,70 +20582,70 @@
         <v>64</v>
       </c>
       <c r="Q168" t="n">
-        <v>120.742</v>
+        <v>121.342</v>
       </c>
       <c r="R168" t="n">
-        <v>105.875</v>
+        <v>106.311</v>
       </c>
       <c r="S168" t="n">
-        <v>14.867</v>
+        <v>15.031</v>
       </c>
       <c r="T168" t="n">
-        <v>0.21861</v>
+        <v>0.22217</v>
       </c>
       <c r="U168" t="n">
-        <v>0.14132</v>
+        <v>0.1392</v>
       </c>
       <c r="V168" t="n">
-        <v>87.18000000000001</v>
+        <v>87.28</v>
       </c>
       <c r="W168" t="n">
-        <v>76.42</v>
+        <v>76.45</v>
       </c>
       <c r="X168" t="n">
-        <v>0.9583</v>
+        <v>0.9669</v>
       </c>
       <c r="Y168" t="n">
-        <v>30.071</v>
+        <v>30.073</v>
       </c>
       <c r="Z168" t="n">
-        <v>59.025</v>
+        <v>59.207</v>
       </c>
       <c r="AA168" t="n">
-        <v>9.468999999999999</v>
+        <v>9.337</v>
       </c>
       <c r="AB168" t="n">
-        <v>25.507</v>
+        <v>25.403</v>
       </c>
       <c r="AC168" t="n">
-        <v>17.731</v>
+        <v>17.528</v>
       </c>
       <c r="AD168" t="n">
-        <v>23.579</v>
+        <v>23.276</v>
       </c>
       <c r="AE168" t="n">
-        <v>7.485</v>
+        <v>7.597</v>
       </c>
       <c r="AF168" t="n">
-        <v>25.746</v>
+        <v>25.648</v>
       </c>
       <c r="AG168" t="n">
-        <v>15.068</v>
+        <v>15.066</v>
       </c>
       <c r="AH168" t="n">
-        <v>7.012</v>
+        <v>6.913</v>
       </c>
       <c r="AI168" t="n">
-        <v>3.088</v>
+        <v>2.979</v>
       </c>
       <c r="AJ168" t="n">
-        <v>16.665</v>
+        <v>16.709</v>
       </c>
       <c r="AK168" t="n">
         <v>2.4</v>
       </c>
       <c r="AL168" t="n">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="169">
@@ -22586,22 +22586,22 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F185" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G185" t="b">
         <v>1</v>
       </c>
       <c r="H185" t="n">
-        <v>1572.866</v>
+        <v>1564.521</v>
       </c>
       <c r="I185" t="n">
-        <v>4.2807</v>
+        <v>3.8582</v>
       </c>
       <c r="J185" t="n">
-        <v>1504.1</v>
+        <v>1513.7</v>
       </c>
       <c r="K185" t="n">
         <v>122</v>
@@ -22622,70 +22622,70 @@
         <v>105</v>
       </c>
       <c r="Q185" t="n">
-        <v>115.54</v>
+        <v>115.201</v>
       </c>
       <c r="R185" t="n">
-        <v>111.296</v>
+        <v>111.68</v>
       </c>
       <c r="S185" t="n">
-        <v>4.244</v>
+        <v>3.521</v>
       </c>
       <c r="T185" t="n">
-        <v>0.30887</v>
+        <v>0.30569</v>
       </c>
       <c r="U185" t="n">
-        <v>0.16111</v>
+        <v>0.16293</v>
       </c>
       <c r="V185" t="n">
-        <v>83.29000000000001</v>
+        <v>83</v>
       </c>
       <c r="W185" t="n">
-        <v>80.09</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="X185" t="n">
-        <v>0.6171</v>
+        <v>0.599</v>
       </c>
       <c r="Y185" t="n">
-        <v>28.353</v>
+        <v>28.27</v>
       </c>
       <c r="Z185" t="n">
-        <v>60.809</v>
+        <v>60.707</v>
       </c>
       <c r="AA185" t="n">
-        <v>9.337999999999999</v>
+        <v>9.473000000000001</v>
       </c>
       <c r="AB185" t="n">
-        <v>26.792</v>
+        <v>26.97</v>
       </c>
       <c r="AC185" t="n">
-        <v>17.809</v>
+        <v>17.374</v>
       </c>
       <c r="AD185" t="n">
-        <v>23.582</v>
+        <v>23.062</v>
       </c>
       <c r="AE185" t="n">
-        <v>10.753</v>
+        <v>10.594</v>
       </c>
       <c r="AF185" t="n">
-        <v>24.15</v>
+        <v>24.102</v>
       </c>
       <c r="AG185" t="n">
-        <v>13.945</v>
+        <v>13.827</v>
       </c>
       <c r="AH185" t="n">
-        <v>5.926</v>
+        <v>5.815</v>
       </c>
       <c r="AI185" t="n">
-        <v>3.926</v>
+        <v>3.982</v>
       </c>
       <c r="AJ185" t="n">
-        <v>18.736</v>
+        <v>18.296</v>
       </c>
       <c r="AK185" t="n">
-        <v>-8.6</v>
+        <v>-8</v>
       </c>
       <c r="AL185" t="n">
-        <v>-7</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="186">
@@ -23186,22 +23186,22 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F190" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G190" t="b">
         <v>1</v>
       </c>
       <c r="H190" t="n">
-        <v>1426.747</v>
+        <v>1422.529</v>
       </c>
       <c r="I190" t="n">
-        <v>3.2284</v>
+        <v>3.1653</v>
       </c>
       <c r="J190" t="n">
-        <v>1374.6</v>
+        <v>1386.7</v>
       </c>
       <c r="K190" t="n">
         <v>142</v>
@@ -23222,70 +23222,70 @@
         <v>137</v>
       </c>
       <c r="Q190" t="n">
-        <v>113.402</v>
+        <v>113.124</v>
       </c>
       <c r="R190" t="n">
-        <v>99.34099999999999</v>
+        <v>100.097</v>
       </c>
       <c r="S190" t="n">
-        <v>14.061</v>
+        <v>13.027</v>
       </c>
       <c r="T190" t="n">
-        <v>0.27695</v>
+        <v>0.28323</v>
       </c>
       <c r="U190" t="n">
-        <v>0.16236</v>
+        <v>0.16355</v>
       </c>
       <c r="V190" t="n">
-        <v>74.09999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="W190" t="n">
-        <v>65.19</v>
+        <v>65.8</v>
       </c>
       <c r="X190" t="n">
-        <v>0.7652</v>
+        <v>0.7419</v>
       </c>
       <c r="Y190" t="n">
-        <v>25.852</v>
+        <v>25.929</v>
       </c>
       <c r="Z190" t="n">
-        <v>54.742</v>
+        <v>55.077</v>
       </c>
       <c r="AA190" t="n">
-        <v>6.464</v>
+        <v>6.536</v>
       </c>
       <c r="AB190" t="n">
-        <v>18.038</v>
+        <v>18.259</v>
       </c>
       <c r="AC190" t="n">
-        <v>15.936</v>
+        <v>15.647</v>
       </c>
       <c r="AD190" t="n">
-        <v>21.629</v>
+        <v>21.254</v>
       </c>
       <c r="AE190" t="n">
-        <v>9.432</v>
+        <v>9.59</v>
       </c>
       <c r="AF190" t="n">
-        <v>24.62</v>
+        <v>24.347</v>
       </c>
       <c r="AG190" t="n">
-        <v>15.945</v>
+        <v>15.802</v>
       </c>
       <c r="AH190" t="n">
-        <v>7.577</v>
+        <v>7.442</v>
       </c>
       <c r="AI190" t="n">
-        <v>3.287</v>
+        <v>3.237</v>
       </c>
       <c r="AJ190" t="n">
-        <v>14.316</v>
+        <v>14.423</v>
       </c>
       <c r="AK190" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="AL190" t="n">
-        <v>13.2</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="191">
@@ -23906,22 +23906,22 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F196" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G196" t="b">
         <v>1</v>
       </c>
       <c r="H196" t="n">
-        <v>1739.629</v>
+        <v>1747.974</v>
       </c>
       <c r="I196" t="n">
-        <v>5.6949</v>
+        <v>5.3805</v>
       </c>
       <c r="J196" t="n">
-        <v>1607.1</v>
+        <v>1602.9</v>
       </c>
       <c r="K196" t="n">
         <v>75</v>
@@ -23942,70 +23942,70 @@
         <v>70</v>
       </c>
       <c r="Q196" t="n">
-        <v>112.247</v>
+        <v>112.996</v>
       </c>
       <c r="R196" t="n">
-        <v>105.648</v>
+        <v>105.635</v>
       </c>
       <c r="S196" t="n">
-        <v>6.599</v>
+        <v>7.361</v>
       </c>
       <c r="T196" t="n">
-        <v>0.30122</v>
+        <v>0.30095</v>
       </c>
       <c r="U196" t="n">
-        <v>0.14585</v>
+        <v>0.14234</v>
       </c>
       <c r="V196" t="n">
-        <v>75.83</v>
+        <v>76.44</v>
       </c>
       <c r="W196" t="n">
-        <v>71.67</v>
+        <v>71.72</v>
       </c>
       <c r="X196" t="n">
-        <v>0.64</v>
+        <v>0.6606</v>
       </c>
       <c r="Y196" t="n">
-        <v>24.785</v>
+        <v>25.264</v>
       </c>
       <c r="Z196" t="n">
-        <v>56.585</v>
+        <v>57.191</v>
       </c>
       <c r="AA196" t="n">
-        <v>6.687</v>
+        <v>6.717</v>
       </c>
       <c r="AB196" t="n">
-        <v>18.447</v>
+        <v>18.54</v>
       </c>
       <c r="AC196" t="n">
-        <v>19.458</v>
+        <v>19.086</v>
       </c>
       <c r="AD196" t="n">
-        <v>26.138</v>
+        <v>25.544</v>
       </c>
       <c r="AE196" t="n">
-        <v>10.135</v>
+        <v>10.18</v>
       </c>
       <c r="AF196" t="n">
-        <v>23.382</v>
+        <v>23.532</v>
       </c>
       <c r="AG196" t="n">
-        <v>14.265</v>
+        <v>14.457</v>
       </c>
       <c r="AH196" t="n">
-        <v>6.662</v>
+        <v>6.738</v>
       </c>
       <c r="AI196" t="n">
-        <v>3.735</v>
+        <v>3.697</v>
       </c>
       <c r="AJ196" t="n">
-        <v>18.324</v>
+        <v>18.052</v>
       </c>
       <c r="AK196" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AL196" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="197">
@@ -24146,22 +24146,22 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F198" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G198" t="b">
         <v>1</v>
       </c>
       <c r="H198" t="n">
-        <v>1796.871</v>
+        <v>1802.429</v>
       </c>
       <c r="I198" t="n">
-        <v>2.7628</v>
+        <v>2.3893</v>
       </c>
       <c r="J198" t="n">
-        <v>1597.3</v>
+        <v>1593.2</v>
       </c>
       <c r="K198" t="n">
         <v>50</v>
@@ -24182,70 +24182,70 @@
         <v>46</v>
       </c>
       <c r="Q198" t="n">
-        <v>114.935</v>
+        <v>116.178</v>
       </c>
       <c r="R198" t="n">
-        <v>102.867</v>
+        <v>103.208</v>
       </c>
       <c r="S198" t="n">
-        <v>12.068</v>
+        <v>12.971</v>
       </c>
       <c r="T198" t="n">
-        <v>0.28396</v>
+        <v>0.28453</v>
       </c>
       <c r="U198" t="n">
-        <v>0.14539</v>
+        <v>0.14214</v>
       </c>
       <c r="V198" t="n">
-        <v>79.87</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="W198" t="n">
-        <v>71.48999999999999</v>
+        <v>72</v>
       </c>
       <c r="X198" t="n">
-        <v>0.6813</v>
+        <v>0.6995</v>
       </c>
       <c r="Y198" t="n">
-        <v>27.556</v>
+        <v>28.062</v>
       </c>
       <c r="Z198" t="n">
-        <v>59.947</v>
+        <v>60.478</v>
       </c>
       <c r="AA198" t="n">
-        <v>9.013</v>
+        <v>9.183999999999999</v>
       </c>
       <c r="AB198" t="n">
-        <v>24.995</v>
+        <v>25.376</v>
       </c>
       <c r="AC198" t="n">
-        <v>15.743</v>
+        <v>15.76</v>
       </c>
       <c r="AD198" t="n">
-        <v>21.775</v>
+        <v>21.653</v>
       </c>
       <c r="AE198" t="n">
-        <v>9.965999999999999</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="AF198" t="n">
-        <v>24.575</v>
+        <v>24.618</v>
       </c>
       <c r="AG198" t="n">
-        <v>14.508</v>
+        <v>14.78</v>
       </c>
       <c r="AH198" t="n">
-        <v>7.823</v>
+        <v>7.935</v>
       </c>
       <c r="AI198" t="n">
-        <v>2.69</v>
+        <v>2.776</v>
       </c>
       <c r="AJ198" t="n">
-        <v>17.703</v>
+        <v>17.614</v>
       </c>
       <c r="AK198" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="AL198" t="n">
-        <v>4.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="199">
@@ -28106,22 +28106,22 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F231" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G231" t="b">
         <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>1266.708</v>
+        <v>1272.073</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.4587</v>
       </c>
       <c r="J231" t="n">
-        <v>1383.4</v>
+        <v>1381.2</v>
       </c>
       <c r="K231" t="n">
         <v>288</v>
@@ -28142,70 +28142,70 @@
         <v>300</v>
       </c>
       <c r="Q231" t="n">
-        <v>104.378</v>
+        <v>104.266</v>
       </c>
       <c r="R231" t="n">
-        <v>107.109</v>
+        <v>106.277</v>
       </c>
       <c r="S231" t="n">
-        <v>-2.731</v>
+        <v>-2.011</v>
       </c>
       <c r="T231" t="n">
-        <v>0.28778</v>
+        <v>0.28965</v>
       </c>
       <c r="U231" t="n">
-        <v>0.15507</v>
+        <v>0.15843</v>
       </c>
       <c r="V231" t="n">
-        <v>75.70999999999999</v>
+        <v>75.41</v>
       </c>
       <c r="W231" t="n">
-        <v>78.45</v>
+        <v>77.64</v>
       </c>
       <c r="X231" t="n">
-        <v>0.456</v>
+        <v>0.4727</v>
       </c>
       <c r="Y231" t="n">
-        <v>24.92</v>
+        <v>24.784</v>
       </c>
       <c r="Z231" t="n">
-        <v>59.6</v>
+        <v>59.52</v>
       </c>
       <c r="AA231" t="n">
-        <v>5.864</v>
+        <v>5.876</v>
       </c>
       <c r="AB231" t="n">
-        <v>18.264</v>
+        <v>18.479</v>
       </c>
       <c r="AC231" t="n">
-        <v>19.032</v>
+        <v>18.6</v>
       </c>
       <c r="AD231" t="n">
-        <v>25.432</v>
+        <v>24.965</v>
       </c>
       <c r="AE231" t="n">
-        <v>9.375999999999999</v>
+        <v>9.502000000000001</v>
       </c>
       <c r="AF231" t="n">
-        <v>22.176</v>
+        <v>22.27</v>
       </c>
       <c r="AG231" t="n">
-        <v>11.136</v>
+        <v>11.124</v>
       </c>
       <c r="AH231" t="n">
-        <v>7.016</v>
+        <v>6.954</v>
       </c>
       <c r="AI231" t="n">
-        <v>4.816</v>
+        <v>4.66</v>
       </c>
       <c r="AJ231" t="n">
-        <v>19.696</v>
+        <v>19.406</v>
       </c>
       <c r="AK231" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AL231" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="232">
@@ -30146,22 +30146,22 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F248" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G248" t="b">
         <v>1</v>
       </c>
       <c r="H248" t="n">
-        <v>1537.451</v>
+        <v>1531.893</v>
       </c>
       <c r="I248" t="n">
-        <v>4.2853</v>
+        <v>4.0919</v>
       </c>
       <c r="J248" t="n">
-        <v>1500.3</v>
+        <v>1512.1</v>
       </c>
       <c r="K248" t="n">
         <v>111</v>
@@ -30182,70 +30182,70 @@
         <v>107</v>
       </c>
       <c r="Q248" t="n">
-        <v>112.785</v>
+        <v>112.703</v>
       </c>
       <c r="R248" t="n">
-        <v>106.917</v>
+        <v>108.213</v>
       </c>
       <c r="S248" t="n">
-        <v>5.867</v>
+        <v>4.49</v>
       </c>
       <c r="T248" t="n">
-        <v>0.31269</v>
+        <v>0.31466</v>
       </c>
       <c r="U248" t="n">
-        <v>0.16204</v>
+        <v>0.16234</v>
       </c>
       <c r="V248" t="n">
-        <v>79.84</v>
+        <v>80.02</v>
       </c>
       <c r="W248" t="n">
-        <v>75.93000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="X248" t="n">
-        <v>0.6279</v>
+        <v>0.608</v>
       </c>
       <c r="Y248" t="n">
-        <v>28.04</v>
+        <v>28.264</v>
       </c>
       <c r="Z248" t="n">
-        <v>61.154</v>
+        <v>61.504</v>
       </c>
       <c r="AA248" t="n">
-        <v>8.372</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="AB248" t="n">
-        <v>22.033</v>
+        <v>22.032</v>
       </c>
       <c r="AC248" t="n">
-        <v>15.638</v>
+        <v>15.376</v>
       </c>
       <c r="AD248" t="n">
-        <v>21.614</v>
+        <v>21.424</v>
       </c>
       <c r="AE248" t="n">
-        <v>11.165</v>
+        <v>11.28</v>
       </c>
       <c r="AF248" t="n">
-        <v>24.437</v>
+        <v>24.448</v>
       </c>
       <c r="AG248" t="n">
-        <v>14.536</v>
+        <v>14.824</v>
       </c>
       <c r="AH248" t="n">
-        <v>6.943</v>
+        <v>6.816</v>
       </c>
       <c r="AI248" t="n">
-        <v>2.694</v>
+        <v>2.712</v>
       </c>
       <c r="AJ248" t="n">
-        <v>17.586</v>
+        <v>17.536</v>
       </c>
       <c r="AK248" t="n">
-        <v>-0.6</v>
+        <v>-6.4</v>
       </c>
       <c r="AL248" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="249">
@@ -31946,22 +31946,22 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F263" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G263" t="b">
         <v>1</v>
       </c>
       <c r="H263" t="n">
-        <v>1733.884</v>
+        <v>1712.121</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2411</v>
+        <v>-0.0531</v>
       </c>
       <c r="J263" t="n">
-        <v>1649.8</v>
+        <v>1652.1</v>
       </c>
       <c r="K263" t="n">
         <v>42</v>
@@ -31982,70 +31982,70 @@
         <v>37</v>
       </c>
       <c r="Q263" t="n">
-        <v>117.96</v>
+        <v>118.261</v>
       </c>
       <c r="R263" t="n">
-        <v>109.764</v>
+        <v>110.821</v>
       </c>
       <c r="S263" t="n">
-        <v>8.196</v>
+        <v>7.44</v>
       </c>
       <c r="T263" t="n">
-        <v>0.30979</v>
+        <v>0.31093</v>
       </c>
       <c r="U263" t="n">
-        <v>0.15421</v>
+        <v>0.14986</v>
       </c>
       <c r="V263" t="n">
-        <v>83.95</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="W263" t="n">
-        <v>77.45</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="X263" t="n">
-        <v>0.6</v>
+        <v>0.5828</v>
       </c>
       <c r="Y263" t="n">
         <v>30.69</v>
       </c>
       <c r="Z263" t="n">
-        <v>62.69</v>
+        <v>62.805</v>
       </c>
       <c r="AA263" t="n">
-        <v>8.460000000000001</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="AB263" t="n">
-        <v>22.62</v>
+        <v>23.284</v>
       </c>
       <c r="AC263" t="n">
-        <v>14.11</v>
+        <v>14.272</v>
       </c>
       <c r="AD263" t="n">
-        <v>19.05</v>
+        <v>19.319</v>
       </c>
       <c r="AE263" t="n">
-        <v>10.94</v>
+        <v>10.98</v>
       </c>
       <c r="AF263" t="n">
-        <v>24.47</v>
+        <v>24.428</v>
       </c>
       <c r="AG263" t="n">
-        <v>16.87</v>
+        <v>17.057</v>
       </c>
       <c r="AH263" t="n">
-        <v>7.07</v>
+        <v>6.972</v>
       </c>
       <c r="AI263" t="n">
-        <v>3.65</v>
+        <v>3.573</v>
       </c>
       <c r="AJ263" t="n">
-        <v>16.96</v>
+        <v>16.971</v>
       </c>
       <c r="AK263" t="n">
-        <v>-5.6</v>
+        <v>-3.6</v>
       </c>
       <c r="AL263" t="n">
-        <v>0.9</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="264">
@@ -33266,22 +33266,22 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F274" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G274" t="b">
         <v>1</v>
       </c>
       <c r="H274" t="n">
-        <v>1610.925</v>
+        <v>1633.092</v>
       </c>
       <c r="I274" t="n">
-        <v>1.549</v>
+        <v>1.7131</v>
       </c>
       <c r="J274" t="n">
-        <v>1518.1</v>
+        <v>1521.6</v>
       </c>
       <c r="K274" t="n">
         <v>116</v>
@@ -33302,70 +33302,70 @@
         <v>121</v>
       </c>
       <c r="Q274" t="n">
-        <v>105.807</v>
+        <v>105.758</v>
       </c>
       <c r="R274" t="n">
-        <v>103.141</v>
+        <v>102.729</v>
       </c>
       <c r="S274" t="n">
-        <v>2.666</v>
+        <v>3.029</v>
       </c>
       <c r="T274" t="n">
-        <v>0.287</v>
+        <v>0.28861</v>
       </c>
       <c r="U274" t="n">
-        <v>0.16199</v>
+        <v>0.16399</v>
       </c>
       <c r="V274" t="n">
-        <v>71.94</v>
+        <v>71.88</v>
       </c>
       <c r="W274" t="n">
-        <v>70.38</v>
+        <v>70.08</v>
       </c>
       <c r="X274" t="n">
-        <v>0.64</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="Y274" t="n">
-        <v>25.168</v>
+        <v>25.078</v>
       </c>
       <c r="Z274" t="n">
-        <v>59.512</v>
+        <v>59.396</v>
       </c>
       <c r="AA274" t="n">
-        <v>8.304</v>
+        <v>8.241</v>
       </c>
       <c r="AB274" t="n">
-        <v>26.944</v>
+        <v>26.784</v>
       </c>
       <c r="AC274" t="n">
-        <v>13.296</v>
+        <v>13.488</v>
       </c>
       <c r="AD274" t="n">
-        <v>17.96</v>
+        <v>18.139</v>
       </c>
       <c r="AE274" t="n">
-        <v>10.352</v>
+        <v>10.464</v>
       </c>
       <c r="AF274" t="n">
-        <v>25.552</v>
+        <v>25.604</v>
       </c>
       <c r="AG274" t="n">
-        <v>15.256</v>
+        <v>15.025</v>
       </c>
       <c r="AH274" t="n">
-        <v>5.4</v>
+        <v>5.519</v>
       </c>
       <c r="AI274" t="n">
-        <v>4.624</v>
+        <v>4.659</v>
       </c>
       <c r="AJ274" t="n">
-        <v>14.144</v>
+        <v>14.232</v>
       </c>
       <c r="AK274" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AL274" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="275">
@@ -38546,22 +38546,22 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F318" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G318" t="b">
         <v>1</v>
       </c>
       <c r="H318" t="n">
-        <v>1630.19</v>
+        <v>1609.505</v>
       </c>
       <c r="I318" t="n">
-        <v>2.9069</v>
+        <v>2.7323</v>
       </c>
       <c r="J318" t="n">
-        <v>1461.8</v>
+        <v>1463.4</v>
       </c>
       <c r="K318" t="n">
         <v>90</v>
@@ -38582,70 +38582,70 @@
         <v>85</v>
       </c>
       <c r="Q318" t="n">
-        <v>110.639</v>
+        <v>110.974</v>
       </c>
       <c r="R318" t="n">
-        <v>100.286</v>
+        <v>100.987</v>
       </c>
       <c r="S318" t="n">
-        <v>10.353</v>
+        <v>9.987</v>
       </c>
       <c r="T318" t="n">
-        <v>0.30348</v>
+        <v>0.30707</v>
       </c>
       <c r="U318" t="n">
-        <v>0.19698</v>
+        <v>0.19627</v>
       </c>
       <c r="V318" t="n">
-        <v>77.55</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="W318" t="n">
-        <v>70.48</v>
+        <v>70.86</v>
       </c>
       <c r="X318" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="Y318" t="n">
-        <v>28.19</v>
+        <v>28.147</v>
       </c>
       <c r="Z318" t="n">
-        <v>57.305</v>
+        <v>57.327</v>
       </c>
       <c r="AA318" t="n">
-        <v>6.55</v>
+        <v>6.59</v>
       </c>
       <c r="AB318" t="n">
-        <v>19.313</v>
+        <v>19.372</v>
       </c>
       <c r="AC318" t="n">
-        <v>14.701</v>
+        <v>14.859</v>
       </c>
       <c r="AD318" t="n">
-        <v>21.262</v>
+        <v>21.397</v>
       </c>
       <c r="AE318" t="n">
-        <v>10.298</v>
+        <v>10.404</v>
       </c>
       <c r="AF318" t="n">
-        <v>23.014</v>
+        <v>22.885</v>
       </c>
       <c r="AG318" t="n">
-        <v>17.21</v>
+        <v>17.449</v>
       </c>
       <c r="AH318" t="n">
-        <v>9.317</v>
+        <v>9.359</v>
       </c>
       <c r="AI318" t="n">
-        <v>5.145</v>
+        <v>5.006</v>
       </c>
       <c r="AJ318" t="n">
-        <v>19.04</v>
+        <v>18.917</v>
       </c>
       <c r="AK318" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="AL318" t="n">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="319">
@@ -40346,22 +40346,22 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F333" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G333" t="b">
         <v>1</v>
       </c>
       <c r="H333" t="n">
-        <v>1657.02</v>
+        <v>1661.239</v>
       </c>
       <c r="I333" t="n">
-        <v>-2.5969</v>
+        <v>-2.4181</v>
       </c>
       <c r="J333" t="n">
-        <v>1677.2</v>
+        <v>1665.4</v>
       </c>
       <c r="K333" t="n">
         <v>74</v>
@@ -40382,70 +40382,70 @@
         <v>66</v>
       </c>
       <c r="Q333" t="n">
-        <v>112.23</v>
+        <v>112.962</v>
       </c>
       <c r="R333" t="n">
         <v>110.155</v>
       </c>
       <c r="S333" t="n">
-        <v>2.075</v>
+        <v>2.807</v>
       </c>
       <c r="T333" t="n">
-        <v>0.29346</v>
+        <v>0.2982</v>
       </c>
       <c r="U333" t="n">
-        <v>0.15144</v>
+        <v>0.15295</v>
       </c>
       <c r="V333" t="n">
-        <v>78.65000000000001</v>
+        <v>78.97</v>
       </c>
       <c r="W333" t="n">
-        <v>76.98999999999999</v>
+        <v>76.86</v>
       </c>
       <c r="X333" t="n">
-        <v>0.5091</v>
+        <v>0.5345</v>
       </c>
       <c r="Y333" t="n">
-        <v>26.762</v>
+        <v>26.825</v>
       </c>
       <c r="Z333" t="n">
-        <v>59.823</v>
+        <v>59.782</v>
       </c>
       <c r="AA333" t="n">
-        <v>8.981999999999999</v>
+        <v>8.930999999999999</v>
       </c>
       <c r="AB333" t="n">
-        <v>26.073</v>
+        <v>26.276</v>
       </c>
       <c r="AC333" t="n">
-        <v>15.966</v>
+        <v>16.218</v>
       </c>
       <c r="AD333" t="n">
-        <v>20.727</v>
+        <v>20.825</v>
       </c>
       <c r="AE333" t="n">
-        <v>9.336</v>
+        <v>9.548999999999999</v>
       </c>
       <c r="AF333" t="n">
-        <v>22.197</v>
+        <v>22.145</v>
       </c>
       <c r="AG333" t="n">
-        <v>14.216</v>
+        <v>14.353</v>
       </c>
       <c r="AH333" t="n">
-        <v>7.63</v>
+        <v>7.589</v>
       </c>
       <c r="AI333" t="n">
-        <v>3.438</v>
+        <v>3.516</v>
       </c>
       <c r="AJ333" t="n">
-        <v>18.672</v>
+        <v>18.578</v>
       </c>
       <c r="AK333" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="AL333" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="334">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -2306,22 +2306,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1977.002</v>
+        <v>1980.818</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1479</v>
+        <v>5.1109</v>
       </c>
       <c r="J16" t="n">
-        <v>1736</v>
+        <v>1727.5</v>
       </c>
       <c r="K16" t="n">
         <v>15</v>
@@ -2342,70 +2342,70 @@
         <v>15</v>
       </c>
       <c r="Q16" t="n">
-        <v>122.871</v>
+        <v>122.949</v>
       </c>
       <c r="R16" t="n">
-        <v>109.332</v>
+        <v>109.035</v>
       </c>
       <c r="S16" t="n">
-        <v>13.539</v>
+        <v>13.914</v>
       </c>
       <c r="T16" t="n">
-        <v>0.29787</v>
+        <v>0.2989</v>
       </c>
       <c r="U16" t="n">
-        <v>0.12058</v>
+        <v>0.12071</v>
       </c>
       <c r="V16" t="n">
-        <v>89.91</v>
+        <v>90.19</v>
       </c>
       <c r="W16" t="n">
-        <v>80.05</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7731</v>
       </c>
       <c r="Y16" t="n">
-        <v>32.072</v>
+        <v>32.335</v>
       </c>
       <c r="Z16" t="n">
-        <v>64.128</v>
+        <v>64.456</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.375999999999999</v>
+        <v>8.169</v>
       </c>
       <c r="AB16" t="n">
-        <v>21.432</v>
+        <v>21.397</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.391</v>
+        <v>17.354</v>
       </c>
       <c r="AD16" t="n">
-        <v>23.287</v>
+        <v>23.126</v>
       </c>
       <c r="AE16" t="n">
-        <v>9.99</v>
+        <v>10.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>23.588</v>
+        <v>23.725</v>
       </c>
       <c r="AG16" t="n">
-        <v>17.031</v>
+        <v>17.321</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.239</v>
+        <v>7.291</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.117</v>
+        <v>5.113</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16.881</v>
+        <v>16.665</v>
       </c>
       <c r="AK16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="17">
@@ -4706,22 +4706,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F36" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1926.176</v>
+        <v>1888.501</v>
       </c>
       <c r="I36" t="n">
-        <v>0.632</v>
+        <v>0.3813</v>
       </c>
       <c r="J36" t="n">
-        <v>1733.2</v>
+        <v>1731.5</v>
       </c>
       <c r="K36" t="n">
         <v>23</v>
@@ -4742,70 +4742,70 @@
         <v>23</v>
       </c>
       <c r="Q36" t="n">
-        <v>117.675</v>
+        <v>117.423</v>
       </c>
       <c r="R36" t="n">
-        <v>106.1</v>
+        <v>106.522</v>
       </c>
       <c r="S36" t="n">
-        <v>11.575</v>
+        <v>10.901</v>
       </c>
       <c r="T36" t="n">
-        <v>0.30384</v>
+        <v>0.30731</v>
       </c>
       <c r="U36" t="n">
-        <v>0.15342</v>
+        <v>0.1519</v>
       </c>
       <c r="V36" t="n">
-        <v>83.77</v>
+        <v>83.45</v>
       </c>
       <c r="W36" t="n">
-        <v>75.31</v>
+        <v>75.45</v>
       </c>
       <c r="X36" t="n">
-        <v>0.6712</v>
+        <v>0.6523</v>
       </c>
       <c r="Y36" t="n">
-        <v>29.287</v>
+        <v>29.412</v>
       </c>
       <c r="Z36" t="n">
-        <v>61.622</v>
+        <v>61.859</v>
       </c>
       <c r="AA36" t="n">
-        <v>8.613</v>
+        <v>8.596</v>
       </c>
       <c r="AB36" t="n">
-        <v>24.733</v>
+        <v>24.694</v>
       </c>
       <c r="AC36" t="n">
-        <v>16</v>
+        <v>15.75</v>
       </c>
       <c r="AD36" t="n">
-        <v>21.48</v>
+        <v>21.375</v>
       </c>
       <c r="AE36" t="n">
-        <v>10.897</v>
+        <v>11.093</v>
       </c>
       <c r="AF36" t="n">
-        <v>24.881</v>
+        <v>24.879</v>
       </c>
       <c r="AG36" t="n">
-        <v>13.398</v>
+        <v>13.461</v>
       </c>
       <c r="AH36" t="n">
-        <v>7.138</v>
+        <v>7.106</v>
       </c>
       <c r="AI36" t="n">
-        <v>4.438</v>
+        <v>4.461</v>
       </c>
       <c r="AJ36" t="n">
-        <v>15.798</v>
+        <v>15.88</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="37">
@@ -9506,22 +9506,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F76" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>2195.855</v>
+        <v>2196.684</v>
       </c>
       <c r="I76" t="n">
-        <v>3.7176</v>
+        <v>3.7365</v>
       </c>
       <c r="J76" t="n">
-        <v>1712.3</v>
+        <v>1700.6</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
@@ -9542,70 +9542,70 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>122.742</v>
+        <v>122.606</v>
       </c>
       <c r="R76" t="n">
-        <v>94.669</v>
+        <v>94.999</v>
       </c>
       <c r="S76" t="n">
-        <v>28.073</v>
+        <v>27.607</v>
       </c>
       <c r="T76" t="n">
-        <v>0.29815</v>
+        <v>0.29898</v>
       </c>
       <c r="U76" t="n">
-        <v>0.15408</v>
+        <v>0.15337</v>
       </c>
       <c r="V76" t="n">
-        <v>82.2</v>
+        <v>81.86</v>
       </c>
       <c r="W76" t="n">
         <v>63.22</v>
       </c>
       <c r="X76" t="n">
-        <v>0.9418</v>
+        <v>0.9434</v>
       </c>
       <c r="Y76" t="n">
-        <v>28.578</v>
+        <v>28.44</v>
       </c>
       <c r="Z76" t="n">
-        <v>58.484</v>
+        <v>58.434</v>
       </c>
       <c r="AA76" t="n">
-        <v>9.076000000000001</v>
+        <v>8.930999999999999</v>
       </c>
       <c r="AB76" t="n">
-        <v>25.902</v>
+        <v>25.915</v>
       </c>
       <c r="AC76" t="n">
-        <v>15.971</v>
+        <v>16.049</v>
       </c>
       <c r="AD76" t="n">
-        <v>22.036</v>
+        <v>22.018</v>
       </c>
       <c r="AE76" t="n">
-        <v>11.622</v>
+        <v>11.701</v>
       </c>
       <c r="AF76" t="n">
-        <v>26.964</v>
+        <v>27.028</v>
       </c>
       <c r="AG76" t="n">
-        <v>16.92</v>
+        <v>16.713</v>
       </c>
       <c r="AH76" t="n">
-        <v>7.775</v>
+        <v>7.61</v>
       </c>
       <c r="AI76" t="n">
-        <v>3.24</v>
+        <v>3.255</v>
       </c>
       <c r="AJ76" t="n">
-        <v>15.676</v>
+        <v>15.486</v>
       </c>
       <c r="AK76" t="n">
-        <v>12.2</v>
+        <v>7.6</v>
       </c>
       <c r="AL76" t="n">
-        <v>18.6</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="77">
@@ -12746,22 +12746,22 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F103" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G103" t="b">
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>1798.055</v>
+        <v>1771.672</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2861</v>
+        <v>0.2428</v>
       </c>
       <c r="J103" t="n">
-        <v>1643.1</v>
+        <v>1649.4</v>
       </c>
       <c r="K103" t="n">
         <v>32</v>
@@ -12782,70 +12782,70 @@
         <v>33</v>
       </c>
       <c r="Q103" t="n">
-        <v>119.916</v>
+        <v>119.281</v>
       </c>
       <c r="R103" t="n">
-        <v>106.588</v>
+        <v>107.6</v>
       </c>
       <c r="S103" t="n">
-        <v>13.328</v>
+        <v>11.68</v>
       </c>
       <c r="T103" t="n">
-        <v>0.31812</v>
+        <v>0.31594</v>
       </c>
       <c r="U103" t="n">
-        <v>0.14104</v>
+        <v>0.14131</v>
       </c>
       <c r="V103" t="n">
-        <v>89.59</v>
+        <v>89.28</v>
       </c>
       <c r="W103" t="n">
-        <v>79.12</v>
+        <v>80.11</v>
       </c>
       <c r="X103" t="n">
-        <v>0.6788</v>
+        <v>0.6589</v>
       </c>
       <c r="Y103" t="n">
-        <v>30.919</v>
+        <v>31.428</v>
       </c>
       <c r="Z103" t="n">
-        <v>65.276</v>
+        <v>65.621</v>
       </c>
       <c r="AA103" t="n">
-        <v>9.802</v>
+        <v>9.779</v>
       </c>
       <c r="AB103" t="n">
-        <v>28.115</v>
+        <v>28.21</v>
       </c>
       <c r="AC103" t="n">
-        <v>18.122</v>
+        <v>17.805</v>
       </c>
       <c r="AD103" t="n">
-        <v>23.924</v>
+        <v>23.458</v>
       </c>
       <c r="AE103" t="n">
-        <v>11.579</v>
+        <v>11.599</v>
       </c>
       <c r="AF103" t="n">
-        <v>24.446</v>
+        <v>24.859</v>
       </c>
       <c r="AG103" t="n">
-        <v>14.813</v>
+        <v>15.38</v>
       </c>
       <c r="AH103" t="n">
-        <v>8.278</v>
+        <v>8.27</v>
       </c>
       <c r="AI103" t="n">
-        <v>6.098</v>
+        <v>6.12</v>
       </c>
       <c r="AJ103" t="n">
-        <v>17.192</v>
+        <v>17.275</v>
       </c>
       <c r="AK103" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="AL103" t="n">
-        <v>1.8</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="104">
@@ -13106,22 +13106,22 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F106" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G106" t="b">
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>2068.259</v>
+        <v>2070.396</v>
       </c>
       <c r="I106" t="n">
-        <v>5.8188</v>
+        <v>5.4527</v>
       </c>
       <c r="J106" t="n">
-        <v>1601.3</v>
+        <v>1596.4</v>
       </c>
       <c r="K106" t="n">
         <v>10</v>
@@ -13142,70 +13142,70 @@
         <v>7</v>
       </c>
       <c r="Q106" t="n">
-        <v>120.754</v>
+        <v>120.168</v>
       </c>
       <c r="R106" t="n">
-        <v>93.89400000000001</v>
+        <v>93.744</v>
       </c>
       <c r="S106" t="n">
-        <v>26.861</v>
+        <v>26.424</v>
       </c>
       <c r="T106" t="n">
-        <v>0.29917</v>
+        <v>0.30091</v>
       </c>
       <c r="U106" t="n">
-        <v>0.13348</v>
+        <v>0.13405</v>
       </c>
       <c r="V106" t="n">
-        <v>85.06</v>
+        <v>84.66</v>
       </c>
       <c r="W106" t="n">
-        <v>66.02</v>
+        <v>65.92</v>
       </c>
       <c r="X106" t="n">
-        <v>0.91</v>
+        <v>0.9126</v>
       </c>
       <c r="Y106" t="n">
-        <v>32.29</v>
+        <v>32.051</v>
       </c>
       <c r="Z106" t="n">
-        <v>63.29</v>
+        <v>63.379</v>
       </c>
       <c r="AA106" t="n">
-        <v>6.7</v>
+        <v>6.526</v>
       </c>
       <c r="AB106" t="n">
-        <v>19.69</v>
+        <v>19.573</v>
       </c>
       <c r="AC106" t="n">
-        <v>13.78</v>
+        <v>14.027</v>
       </c>
       <c r="AD106" t="n">
-        <v>19.76</v>
+        <v>19.853</v>
       </c>
       <c r="AE106" t="n">
-        <v>10.98</v>
+        <v>11.163</v>
       </c>
       <c r="AF106" t="n">
-        <v>25.82</v>
+        <v>25.97</v>
       </c>
       <c r="AG106" t="n">
-        <v>18.39</v>
+        <v>18.282</v>
       </c>
       <c r="AH106" t="n">
-        <v>8.470000000000001</v>
+        <v>8.457000000000001</v>
       </c>
       <c r="AI106" t="n">
-        <v>3.7</v>
+        <v>3.747</v>
       </c>
       <c r="AJ106" t="n">
-        <v>16.74</v>
+        <v>16.902</v>
       </c>
       <c r="AK106" t="n">
         <v>11.8</v>
       </c>
       <c r="AL106" t="n">
-        <v>13.1</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="107">
@@ -13595,7 +13595,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>1490.535</v>
+        <v>1500.659</v>
       </c>
       <c r="I110" t="n">
         <v>2.799</v>
@@ -13706,22 +13706,22 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F111" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G111" t="b">
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>1549.123</v>
+        <v>1545.307</v>
       </c>
       <c r="I111" t="n">
-        <v>2.9832</v>
+        <v>2.9403</v>
       </c>
       <c r="J111" t="n">
-        <v>1452.3</v>
+        <v>1472.5</v>
       </c>
       <c r="K111" t="n">
         <v>108</v>
@@ -13742,70 +13742,70 @@
         <v>101</v>
       </c>
       <c r="Q111" t="n">
-        <v>108.144</v>
+        <v>108.056</v>
       </c>
       <c r="R111" t="n">
-        <v>96.693</v>
+        <v>98.124</v>
       </c>
       <c r="S111" t="n">
-        <v>11.451</v>
+        <v>9.932</v>
       </c>
       <c r="T111" t="n">
-        <v>0.25834</v>
+        <v>0.2616</v>
       </c>
       <c r="U111" t="n">
-        <v>0.18506</v>
+        <v>0.18375</v>
       </c>
       <c r="V111" t="n">
-        <v>78.65000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="W111" t="n">
-        <v>70.23</v>
+        <v>71.41</v>
       </c>
       <c r="X111" t="n">
-        <v>0.7361</v>
+        <v>0.7028</v>
       </c>
       <c r="Y111" t="n">
-        <v>26.387</v>
+        <v>26.624</v>
       </c>
       <c r="Z111" t="n">
-        <v>58.064</v>
+        <v>58.49</v>
       </c>
       <c r="AA111" t="n">
-        <v>7.177</v>
+        <v>7.317</v>
       </c>
       <c r="AB111" t="n">
-        <v>22.478</v>
+        <v>22.908</v>
       </c>
       <c r="AC111" t="n">
-        <v>18.397</v>
+        <v>17.915</v>
       </c>
       <c r="AD111" t="n">
-        <v>24.685</v>
+        <v>24.193</v>
       </c>
       <c r="AE111" t="n">
-        <v>9.537000000000001</v>
+        <v>9.561999999999999</v>
       </c>
       <c r="AF111" t="n">
-        <v>26.693</v>
+        <v>26.421</v>
       </c>
       <c r="AG111" t="n">
-        <v>12.958</v>
+        <v>13.083</v>
       </c>
       <c r="AH111" t="n">
-        <v>6.658</v>
+        <v>6.565</v>
       </c>
       <c r="AI111" t="n">
-        <v>3.955</v>
+        <v>3.853</v>
       </c>
       <c r="AJ111" t="n">
-        <v>18.001</v>
+        <v>17.824</v>
       </c>
       <c r="AK111" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="AL111" t="n">
-        <v>2.1</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="112">
@@ -13826,22 +13826,22 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F112" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G112" t="b">
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>1625.523</v>
+        <v>1664.344</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.6842</v>
       </c>
       <c r="J112" t="n">
-        <v>1382.5</v>
+        <v>1401.4</v>
       </c>
       <c r="K112" t="n">
         <v>92</v>
@@ -13862,70 +13862,70 @@
         <v>75</v>
       </c>
       <c r="Q112" t="n">
-        <v>121.161</v>
+        <v>120.784</v>
       </c>
       <c r="R112" t="n">
-        <v>100.188</v>
+        <v>100.586</v>
       </c>
       <c r="S112" t="n">
-        <v>20.973</v>
+        <v>20.197</v>
       </c>
       <c r="T112" t="n">
-        <v>0.30613</v>
+        <v>0.30161</v>
       </c>
       <c r="U112" t="n">
-        <v>0.12761</v>
+        <v>0.12796</v>
       </c>
       <c r="V112" t="n">
-        <v>86.5</v>
+        <v>86.31</v>
       </c>
       <c r="W112" t="n">
-        <v>71.84999999999999</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="X112" t="n">
-        <v>0.8722</v>
+        <v>0.8761</v>
       </c>
       <c r="Y112" t="n">
-        <v>28.949</v>
+        <v>29.049</v>
       </c>
       <c r="Z112" t="n">
-        <v>61.172</v>
+        <v>61.346</v>
       </c>
       <c r="AA112" t="n">
-        <v>9.042</v>
+        <v>9.031000000000001</v>
       </c>
       <c r="AB112" t="n">
-        <v>26.217</v>
+        <v>26.128</v>
       </c>
       <c r="AC112" t="n">
-        <v>19.557</v>
+        <v>19.145</v>
       </c>
       <c r="AD112" t="n">
-        <v>26.314</v>
+        <v>25.688</v>
       </c>
       <c r="AE112" t="n">
-        <v>10.258</v>
+        <v>10.119</v>
       </c>
       <c r="AF112" t="n">
-        <v>22.906</v>
+        <v>23.134</v>
       </c>
       <c r="AG112" t="n">
-        <v>15.246</v>
+        <v>15.328</v>
       </c>
       <c r="AH112" t="n">
-        <v>10.364</v>
+        <v>10.052</v>
       </c>
       <c r="AI112" t="n">
-        <v>3.681</v>
+        <v>3.69</v>
       </c>
       <c r="AJ112" t="n">
-        <v>18.867</v>
+        <v>18.534</v>
       </c>
       <c r="AK112" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AL112" t="n">
-        <v>15.9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="113">
@@ -14186,22 +14186,22 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F115" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G115" t="b">
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>2111.715</v>
+        <v>2112.552</v>
       </c>
       <c r="I115" t="n">
-        <v>1.2196</v>
+        <v>1.1096</v>
       </c>
       <c r="J115" t="n">
-        <v>1742.7</v>
+        <v>1725.6</v>
       </c>
       <c r="K115" t="n">
         <v>5</v>
@@ -14222,70 +14222,70 @@
         <v>5</v>
       </c>
       <c r="Q115" t="n">
-        <v>117.346</v>
+        <v>117.422</v>
       </c>
       <c r="R115" t="n">
-        <v>95.8</v>
+        <v>94.66500000000001</v>
       </c>
       <c r="S115" t="n">
-        <v>21.546</v>
+        <v>22.757</v>
       </c>
       <c r="T115" t="n">
-        <v>0.33855</v>
+        <v>0.33192</v>
       </c>
       <c r="U115" t="n">
-        <v>0.12356</v>
+        <v>0.12292</v>
       </c>
       <c r="V115" t="n">
-        <v>77.12</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="W115" t="n">
-        <v>63</v>
+        <v>62.27</v>
       </c>
       <c r="X115" t="n">
-        <v>0.8159</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="Y115" t="n">
-        <v>27.767</v>
+        <v>27.885</v>
       </c>
       <c r="Z115" t="n">
-        <v>61.756</v>
+        <v>61.745</v>
       </c>
       <c r="AA115" t="n">
-        <v>8.787000000000001</v>
+        <v>8.765000000000001</v>
       </c>
       <c r="AB115" t="n">
-        <v>25.138</v>
+        <v>24.8</v>
       </c>
       <c r="AC115" t="n">
-        <v>12.797</v>
+        <v>12.645</v>
       </c>
       <c r="AD115" t="n">
-        <v>16.593</v>
+        <v>16.41</v>
       </c>
       <c r="AE115" t="n">
-        <v>11.514</v>
+        <v>11.37</v>
       </c>
       <c r="AF115" t="n">
-        <v>22.544</v>
+        <v>23.168</v>
       </c>
       <c r="AG115" t="n">
-        <v>14.661</v>
+        <v>14.503</v>
       </c>
       <c r="AH115" t="n">
-        <v>7.7</v>
+        <v>7.745</v>
       </c>
       <c r="AI115" t="n">
-        <v>3.845</v>
+        <v>3.747</v>
       </c>
       <c r="AJ115" t="n">
-        <v>18.057</v>
+        <v>17.917</v>
       </c>
       <c r="AK115" t="n">
-        <v>8.800000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="AL115" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -14426,22 +14426,22 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F117" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G117" t="b">
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>1413.012</v>
+        <v>1412.371</v>
       </c>
       <c r="I117" t="n">
-        <v>2.8128</v>
+        <v>2.7318</v>
       </c>
       <c r="J117" t="n">
-        <v>1374.4</v>
+        <v>1406.7</v>
       </c>
       <c r="K117" t="n">
         <v>207</v>
@@ -14462,70 +14462,70 @@
         <v>203</v>
       </c>
       <c r="Q117" t="n">
-        <v>109.768</v>
+        <v>109.688</v>
       </c>
       <c r="R117" t="n">
-        <v>99.30200000000001</v>
+        <v>100.821</v>
       </c>
       <c r="S117" t="n">
-        <v>10.466</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="T117" t="n">
-        <v>0.31778</v>
+        <v>0.31724</v>
       </c>
       <c r="U117" t="n">
-        <v>0.18288</v>
+        <v>0.18058</v>
       </c>
       <c r="V117" t="n">
-        <v>75.48</v>
+        <v>75.56</v>
       </c>
       <c r="W117" t="n">
-        <v>68.45</v>
+        <v>69.66</v>
       </c>
       <c r="X117" t="n">
-        <v>0.6702</v>
+        <v>0.6389</v>
       </c>
       <c r="Y117" t="n">
-        <v>25.174</v>
+        <v>25.211</v>
       </c>
       <c r="Z117" t="n">
-        <v>56.184</v>
+        <v>56.419</v>
       </c>
       <c r="AA117" t="n">
-        <v>6.801</v>
+        <v>7.068</v>
       </c>
       <c r="AB117" t="n">
-        <v>19.252</v>
+        <v>19.64</v>
       </c>
       <c r="AC117" t="n">
-        <v>18.33</v>
+        <v>18.069</v>
       </c>
       <c r="AD117" t="n">
-        <v>24.736</v>
+        <v>24.411</v>
       </c>
       <c r="AE117" t="n">
-        <v>10.714</v>
+        <v>10.546</v>
       </c>
       <c r="AF117" t="n">
-        <v>22.834</v>
+        <v>22.517</v>
       </c>
       <c r="AG117" t="n">
-        <v>15.22</v>
+        <v>15.182</v>
       </c>
       <c r="AH117" t="n">
-        <v>8.375999999999999</v>
+        <v>8.207000000000001</v>
       </c>
       <c r="AI117" t="n">
-        <v>3.771</v>
+        <v>3.642</v>
       </c>
       <c r="AJ117" t="n">
-        <v>18.714</v>
+        <v>18.546</v>
       </c>
       <c r="AK117" t="n">
-        <v>11</v>
+        <v>2.8</v>
       </c>
       <c r="AL117" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118">
@@ -14546,22 +14546,22 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F118" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G118" t="b">
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>1409.955</v>
+        <v>1409.118</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3498</v>
+        <v>-0.2978</v>
       </c>
       <c r="J118" t="n">
-        <v>1415.2</v>
+        <v>1439.8</v>
       </c>
       <c r="K118" t="n">
         <v>145</v>
@@ -14582,70 +14582,70 @@
         <v>145</v>
       </c>
       <c r="Q118" t="n">
-        <v>110.278</v>
+        <v>108.976</v>
       </c>
       <c r="R118" t="n">
-        <v>106.528</v>
+        <v>107.138</v>
       </c>
       <c r="S118" t="n">
-        <v>3.75</v>
+        <v>1.838</v>
       </c>
       <c r="T118" t="n">
-        <v>0.26932</v>
+        <v>0.26845</v>
       </c>
       <c r="U118" t="n">
-        <v>0.14751</v>
+        <v>0.14698</v>
       </c>
       <c r="V118" t="n">
-        <v>76.66</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="W118" t="n">
-        <v>73.95</v>
+        <v>74.14</v>
       </c>
       <c r="X118" t="n">
-        <v>0.5651</v>
+        <v>0.5424</v>
       </c>
       <c r="Y118" t="n">
-        <v>25.728</v>
+        <v>25.402</v>
       </c>
       <c r="Z118" t="n">
-        <v>59.747</v>
+        <v>59.646</v>
       </c>
       <c r="AA118" t="n">
-        <v>9.696999999999999</v>
+        <v>9.586</v>
       </c>
       <c r="AB118" t="n">
-        <v>28.106</v>
+        <v>28.192</v>
       </c>
       <c r="AC118" t="n">
-        <v>14.571</v>
+        <v>14.364</v>
       </c>
       <c r="AD118" t="n">
-        <v>20.006</v>
+        <v>19.821</v>
       </c>
       <c r="AE118" t="n">
-        <v>9.212999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="AF118" t="n">
-        <v>24.379</v>
+        <v>24.397</v>
       </c>
       <c r="AG118" t="n">
-        <v>11.722</v>
+        <v>11.616</v>
       </c>
       <c r="AH118" t="n">
-        <v>5.534</v>
+        <v>5.512</v>
       </c>
       <c r="AI118" t="n">
-        <v>2.379</v>
+        <v>2.469</v>
       </c>
       <c r="AJ118" t="n">
-        <v>19.111</v>
+        <v>18.876</v>
       </c>
       <c r="AK118" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AL118" t="n">
-        <v>9.199999999999999</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="119">
@@ -14906,22 +14906,22 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F121" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G121" t="b">
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>1982.683</v>
+        <v>1984.447</v>
       </c>
       <c r="I121" t="n">
-        <v>7.8712</v>
+        <v>7.3951</v>
       </c>
       <c r="J121" t="n">
-        <v>1717.2</v>
+        <v>1704.4</v>
       </c>
       <c r="K121" t="n">
         <v>7</v>
@@ -14942,70 +14942,70 @@
         <v>8</v>
       </c>
       <c r="Q121" t="n">
-        <v>125.113</v>
+        <v>126.534</v>
       </c>
       <c r="R121" t="n">
-        <v>103.663</v>
+        <v>103.563</v>
       </c>
       <c r="S121" t="n">
-        <v>21.45</v>
+        <v>22.971</v>
       </c>
       <c r="T121" t="n">
-        <v>0.32225</v>
+        <v>0.32629</v>
       </c>
       <c r="U121" t="n">
-        <v>0.12812</v>
+        <v>0.12517</v>
       </c>
       <c r="V121" t="n">
-        <v>84.41</v>
+        <v>85.2</v>
       </c>
       <c r="W121" t="n">
-        <v>70.04000000000001</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="X121" t="n">
-        <v>0.7419</v>
+        <v>0.76</v>
       </c>
       <c r="Y121" t="n">
-        <v>28.464</v>
+        <v>28.81</v>
       </c>
       <c r="Z121" t="n">
-        <v>61.919</v>
+        <v>62.36</v>
       </c>
       <c r="AA121" t="n">
-        <v>10.927</v>
+        <v>11.1</v>
       </c>
       <c r="AB121" t="n">
-        <v>31.849</v>
+        <v>31.92</v>
       </c>
       <c r="AC121" t="n">
-        <v>16.684</v>
+        <v>16.57</v>
       </c>
       <c r="AD121" t="n">
-        <v>20.973</v>
+        <v>20.88</v>
       </c>
       <c r="AE121" t="n">
-        <v>12.329</v>
+        <v>12.65</v>
       </c>
       <c r="AF121" t="n">
-        <v>26.185</v>
+        <v>26.26</v>
       </c>
       <c r="AG121" t="n">
-        <v>14.743</v>
+        <v>14.73</v>
       </c>
       <c r="AH121" t="n">
-        <v>3.887</v>
+        <v>3.8</v>
       </c>
       <c r="AI121" t="n">
-        <v>4.597</v>
+        <v>4.52</v>
       </c>
       <c r="AJ121" t="n">
-        <v>13.312</v>
+        <v>13.12</v>
       </c>
       <c r="AK121" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="AL121" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122">
@@ -16826,22 +16826,22 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F137" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G137" t="b">
         <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>1521.308</v>
+        <v>1519.171</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1615</v>
+        <v>-0.0429</v>
       </c>
       <c r="J137" t="n">
-        <v>1474.6</v>
+        <v>1497.2</v>
       </c>
       <c r="K137" t="n">
         <v>163</v>
@@ -16862,70 +16862,70 @@
         <v>155</v>
       </c>
       <c r="Q137" t="n">
-        <v>111.121</v>
+        <v>110.411</v>
       </c>
       <c r="R137" t="n">
-        <v>108.097</v>
+        <v>108.109</v>
       </c>
       <c r="S137" t="n">
-        <v>3.024</v>
+        <v>2.302</v>
       </c>
       <c r="T137" t="n">
-        <v>0.34498</v>
+        <v>0.34286</v>
       </c>
       <c r="U137" t="n">
-        <v>0.16501</v>
+        <v>0.16508</v>
       </c>
       <c r="V137" t="n">
-        <v>80.47</v>
+        <v>79.91</v>
       </c>
       <c r="W137" t="n">
-        <v>78.27</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="X137" t="n">
-        <v>0.584</v>
+        <v>0.5583</v>
       </c>
       <c r="Y137" t="n">
-        <v>26.064</v>
+        <v>25.901</v>
       </c>
       <c r="Z137" t="n">
-        <v>61.28</v>
+        <v>61.071</v>
       </c>
       <c r="AA137" t="n">
-        <v>8.688000000000001</v>
+        <v>8.521000000000001</v>
       </c>
       <c r="AB137" t="n">
-        <v>26.592</v>
+        <v>26.212</v>
       </c>
       <c r="AC137" t="n">
-        <v>18.736</v>
+        <v>18.783</v>
       </c>
       <c r="AD137" t="n">
-        <v>26.712</v>
+        <v>26.744</v>
       </c>
       <c r="AE137" t="n">
-        <v>12.632</v>
+        <v>12.489</v>
       </c>
       <c r="AF137" t="n">
-        <v>23.856</v>
+        <v>23.837</v>
       </c>
       <c r="AG137" t="n">
-        <v>13.6</v>
+        <v>13.359</v>
       </c>
       <c r="AH137" t="n">
-        <v>6.632</v>
+        <v>6.736</v>
       </c>
       <c r="AI137" t="n">
-        <v>5.128</v>
+        <v>5.086</v>
       </c>
       <c r="AJ137" t="n">
-        <v>20.912</v>
+        <v>20.823</v>
       </c>
       <c r="AK137" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AL137" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="138">
@@ -18386,22 +18386,22 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F150" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G150" t="b">
         <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>1836.881</v>
+        <v>1854.143</v>
       </c>
       <c r="I150" t="n">
-        <v>-2.5958</v>
+        <v>-2.5004</v>
       </c>
       <c r="J150" t="n">
-        <v>1686.1</v>
+        <v>1686.9</v>
       </c>
       <c r="K150" t="n">
         <v>19</v>
@@ -18422,70 +18422,70 @@
         <v>17</v>
       </c>
       <c r="Q150" t="n">
-        <v>118.896</v>
+        <v>118.734</v>
       </c>
       <c r="R150" t="n">
-        <v>101.876</v>
+        <v>101.945</v>
       </c>
       <c r="S150" t="n">
-        <v>17.02</v>
+        <v>16.789</v>
       </c>
       <c r="T150" t="n">
-        <v>0.28905</v>
+        <v>0.2886</v>
       </c>
       <c r="U150" t="n">
-        <v>0.15971</v>
+        <v>0.16453</v>
       </c>
       <c r="V150" t="n">
-        <v>84.66</v>
+        <v>84.69</v>
       </c>
       <c r="W150" t="n">
-        <v>72.23</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="X150" t="n">
-        <v>0.6911</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="Y150" t="n">
-        <v>28.532</v>
+        <v>28.525</v>
       </c>
       <c r="Z150" t="n">
-        <v>61.349</v>
+        <v>61.046</v>
       </c>
       <c r="AA150" t="n">
-        <v>11.288</v>
+        <v>11.395</v>
       </c>
       <c r="AB150" t="n">
-        <v>32.323</v>
+        <v>32.12</v>
       </c>
       <c r="AC150" t="n">
-        <v>15.915</v>
+        <v>15.868</v>
       </c>
       <c r="AD150" t="n">
-        <v>20.726</v>
+        <v>20.915</v>
       </c>
       <c r="AE150" t="n">
-        <v>10.713</v>
+        <v>10.737</v>
       </c>
       <c r="AF150" t="n">
-        <v>26.159</v>
+        <v>26.294</v>
       </c>
       <c r="AG150" t="n">
-        <v>16.841</v>
+        <v>16.854</v>
       </c>
       <c r="AH150" t="n">
-        <v>6.893</v>
+        <v>6.838</v>
       </c>
       <c r="AI150" t="n">
-        <v>3.394</v>
+        <v>3.35</v>
       </c>
       <c r="AJ150" t="n">
-        <v>18.347</v>
+        <v>18.284</v>
       </c>
       <c r="AK150" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="AL150" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="151">
@@ -19946,22 +19946,22 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F163" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G163" t="b">
         <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>1726.811</v>
+        <v>1715.565</v>
       </c>
       <c r="I163" t="n">
-        <v>2.6895</v>
+        <v>2.6075</v>
       </c>
       <c r="J163" t="n">
-        <v>1428.4</v>
+        <v>1447.5</v>
       </c>
       <c r="K163" t="n">
         <v>68</v>
@@ -19982,70 +19982,70 @@
         <v>56</v>
       </c>
       <c r="Q163" t="n">
-        <v>115.07</v>
+        <v>114.775</v>
       </c>
       <c r="R163" t="n">
-        <v>100.006</v>
+        <v>100.989</v>
       </c>
       <c r="S163" t="n">
-        <v>15.064</v>
+        <v>13.786</v>
       </c>
       <c r="T163" t="n">
-        <v>0.34832</v>
+        <v>0.35346</v>
       </c>
       <c r="U163" t="n">
-        <v>0.13903</v>
+        <v>0.13698</v>
       </c>
       <c r="V163" t="n">
-        <v>76.83</v>
+        <v>76.5</v>
       </c>
       <c r="W163" t="n">
-        <v>66.97</v>
+        <v>67.45</v>
       </c>
       <c r="X163" t="n">
-        <v>0.84</v>
+        <v>0.8065</v>
       </c>
       <c r="Y163" t="n">
-        <v>26.424</v>
+        <v>26.427</v>
       </c>
       <c r="Z163" t="n">
-        <v>58.808</v>
+        <v>59.261</v>
       </c>
       <c r="AA163" t="n">
-        <v>6.408</v>
+        <v>6.519</v>
       </c>
       <c r="AB163" t="n">
-        <v>20.808</v>
+        <v>21.006</v>
       </c>
       <c r="AC163" t="n">
-        <v>16.896</v>
+        <v>16.599</v>
       </c>
       <c r="AD163" t="n">
-        <v>22.808</v>
+        <v>22.306</v>
       </c>
       <c r="AE163" t="n">
-        <v>11.096</v>
+        <v>11.316</v>
       </c>
       <c r="AF163" t="n">
-        <v>20.68</v>
+        <v>20.605</v>
       </c>
       <c r="AG163" t="n">
-        <v>13.008</v>
+        <v>12.954</v>
       </c>
       <c r="AH163" t="n">
-        <v>10.12</v>
+        <v>10.117</v>
       </c>
       <c r="AI163" t="n">
-        <v>4.248</v>
+        <v>4.287</v>
       </c>
       <c r="AJ163" t="n">
-        <v>19.064</v>
+        <v>19.047</v>
       </c>
       <c r="AK163" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AL163" t="n">
-        <v>13.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="164">
@@ -20666,22 +20666,22 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F169" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G169" t="b">
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>2173.708</v>
+        <v>2174.35</v>
       </c>
       <c r="I169" t="n">
-        <v>6.5185</v>
+        <v>6.1854</v>
       </c>
       <c r="J169" t="n">
-        <v>1779.9</v>
+        <v>1765.3</v>
       </c>
       <c r="K169" t="n">
         <v>3</v>
@@ -20702,70 +20702,70 @@
         <v>2</v>
       </c>
       <c r="Q169" t="n">
-        <v>120.66</v>
+        <v>121.548</v>
       </c>
       <c r="R169" t="n">
-        <v>97.182</v>
+        <v>97.557</v>
       </c>
       <c r="S169" t="n">
-        <v>23.477</v>
+        <v>23.992</v>
       </c>
       <c r="T169" t="n">
-        <v>0.25981</v>
+        <v>0.25476</v>
       </c>
       <c r="U169" t="n">
-        <v>0.1613</v>
+        <v>0.16164</v>
       </c>
       <c r="V169" t="n">
-        <v>86.70999999999999</v>
+        <v>87.33</v>
       </c>
       <c r="W169" t="n">
-        <v>69.29000000000001</v>
+        <v>69.59</v>
       </c>
       <c r="X169" t="n">
-        <v>0.9046</v>
+        <v>0.9149</v>
       </c>
       <c r="Y169" t="n">
-        <v>30.409</v>
+        <v>30.647</v>
       </c>
       <c r="Z169" t="n">
-        <v>59.947</v>
+        <v>59.793</v>
       </c>
       <c r="AA169" t="n">
-        <v>8.932</v>
+        <v>9.042999999999999</v>
       </c>
       <c r="AB169" t="n">
-        <v>24.768</v>
+        <v>24.822</v>
       </c>
       <c r="AC169" t="n">
-        <v>17.255</v>
+        <v>17.22</v>
       </c>
       <c r="AD169" t="n">
-        <v>23.138</v>
+        <v>23.035</v>
       </c>
       <c r="AE169" t="n">
-        <v>9.917999999999999</v>
+        <v>9.728999999999999</v>
       </c>
       <c r="AF169" t="n">
-        <v>27.953</v>
+        <v>28.107</v>
       </c>
       <c r="AG169" t="n">
-        <v>18.666</v>
+        <v>18.945</v>
       </c>
       <c r="AH169" t="n">
-        <v>5.751</v>
+        <v>5.702</v>
       </c>
       <c r="AI169" t="n">
-        <v>5.934</v>
+        <v>6.015</v>
       </c>
       <c r="AJ169" t="n">
-        <v>15.451</v>
+        <v>15.382</v>
       </c>
       <c r="AK169" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="AL169" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="170">
@@ -20786,22 +20786,22 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F170" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G170" t="b">
         <v>1</v>
       </c>
       <c r="H170" t="n">
-        <v>2027.394</v>
+        <v>2031.39</v>
       </c>
       <c r="I170" t="n">
-        <v>0.218</v>
+        <v>0.0735</v>
       </c>
       <c r="J170" t="n">
-        <v>1730.1</v>
+        <v>1723.2</v>
       </c>
       <c r="K170" t="n">
         <v>9</v>
@@ -20822,70 +20822,70 @@
         <v>11</v>
       </c>
       <c r="Q170" t="n">
-        <v>117.657</v>
+        <v>117.934</v>
       </c>
       <c r="R170" t="n">
-        <v>102.118</v>
+        <v>101.399</v>
       </c>
       <c r="S170" t="n">
-        <v>15.539</v>
+        <v>16.535</v>
       </c>
       <c r="T170" t="n">
-        <v>0.29627</v>
+        <v>0.28968</v>
       </c>
       <c r="U170" t="n">
-        <v>0.16068</v>
+        <v>0.1613</v>
       </c>
       <c r="V170" t="n">
-        <v>78.98999999999999</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="W170" t="n">
-        <v>68.62</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="X170" t="n">
-        <v>0.7728</v>
+        <v>0.79</v>
       </c>
       <c r="Y170" t="n">
-        <v>27.651</v>
+        <v>27.84</v>
       </c>
       <c r="Z170" t="n">
-        <v>58.266</v>
+        <v>58.22</v>
       </c>
       <c r="AA170" t="n">
-        <v>7.776</v>
+        <v>7.81</v>
       </c>
       <c r="AB170" t="n">
-        <v>21.497</v>
+        <v>21.38</v>
       </c>
       <c r="AC170" t="n">
-        <v>16.082</v>
+        <v>16.09</v>
       </c>
       <c r="AD170" t="n">
-        <v>21.071</v>
+        <v>20.97</v>
       </c>
       <c r="AE170" t="n">
-        <v>11.194</v>
+        <v>10.96</v>
       </c>
       <c r="AF170" t="n">
-        <v>26.152</v>
+        <v>26.41</v>
       </c>
       <c r="AG170" t="n">
-        <v>18.362</v>
+        <v>18.65</v>
       </c>
       <c r="AH170" t="n">
-        <v>5.477</v>
+        <v>5.39</v>
       </c>
       <c r="AI170" t="n">
-        <v>4.113</v>
+        <v>4.2</v>
       </c>
       <c r="AJ170" t="n">
-        <v>16.456</v>
+        <v>16.31</v>
       </c>
       <c r="AK170" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="AL170" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="171">
@@ -22826,22 +22826,22 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F187" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G187" t="b">
         <v>1</v>
       </c>
       <c r="H187" t="n">
-        <v>1593.755</v>
+        <v>1589.758</v>
       </c>
       <c r="I187" t="n">
-        <v>3.5257</v>
+        <v>3.408</v>
       </c>
       <c r="J187" t="n">
-        <v>1410.6</v>
+        <v>1434.7</v>
       </c>
       <c r="K187" t="n">
         <v>113</v>
@@ -22862,70 +22862,70 @@
         <v>114</v>
       </c>
       <c r="Q187" t="n">
-        <v>114.28</v>
+        <v>113.469</v>
       </c>
       <c r="R187" t="n">
-        <v>102.18</v>
+        <v>103.166</v>
       </c>
       <c r="S187" t="n">
-        <v>12.099</v>
+        <v>10.303</v>
       </c>
       <c r="T187" t="n">
-        <v>0.31044</v>
+        <v>0.30533</v>
       </c>
       <c r="U187" t="n">
-        <v>0.15061</v>
+        <v>0.15101</v>
       </c>
       <c r="V187" t="n">
-        <v>78.98999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="W187" t="n">
-        <v>70.7</v>
+        <v>71.59</v>
       </c>
       <c r="X187" t="n">
-        <v>0.776</v>
+        <v>0.7444</v>
       </c>
       <c r="Y187" t="n">
-        <v>28.072</v>
+        <v>27.978</v>
       </c>
       <c r="Z187" t="n">
-        <v>61.408</v>
+        <v>61.28</v>
       </c>
       <c r="AA187" t="n">
-        <v>9.391999999999999</v>
+        <v>9.257</v>
       </c>
       <c r="AB187" t="n">
-        <v>26.232</v>
+        <v>26.21</v>
       </c>
       <c r="AC187" t="n">
-        <v>13.456</v>
+        <v>13.388</v>
       </c>
       <c r="AD187" t="n">
-        <v>18.84</v>
+        <v>18.768</v>
       </c>
       <c r="AE187" t="n">
-        <v>10.912</v>
+        <v>10.638</v>
       </c>
       <c r="AF187" t="n">
-        <v>23.688</v>
+        <v>23.467</v>
       </c>
       <c r="AG187" t="n">
-        <v>14.88</v>
+        <v>14.83</v>
       </c>
       <c r="AH187" t="n">
-        <v>7.712</v>
+        <v>7.675</v>
       </c>
       <c r="AI187" t="n">
-        <v>2.832</v>
+        <v>2.768</v>
       </c>
       <c r="AJ187" t="n">
-        <v>15.152</v>
+        <v>15.232</v>
       </c>
       <c r="AK187" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="AL187" t="n">
-        <v>11.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="188">
@@ -23786,22 +23786,22 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F195" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G195" t="b">
         <v>1</v>
       </c>
       <c r="H195" t="n">
-        <v>1982.884</v>
+        <v>1988.043</v>
       </c>
       <c r="I195" t="n">
-        <v>9.932399999999999</v>
+        <v>9.170199999999999</v>
       </c>
       <c r="J195" t="n">
-        <v>1675.8</v>
+        <v>1669.8</v>
       </c>
       <c r="K195" t="n">
         <v>14</v>
@@ -23822,70 +23822,70 @@
         <v>14</v>
       </c>
       <c r="Q195" t="n">
-        <v>114.614</v>
+        <v>115.233</v>
       </c>
       <c r="R195" t="n">
-        <v>98.94199999999999</v>
+        <v>97.834</v>
       </c>
       <c r="S195" t="n">
-        <v>15.672</v>
+        <v>17.399</v>
       </c>
       <c r="T195" t="n">
-        <v>0.24333</v>
+        <v>0.24652</v>
       </c>
       <c r="U195" t="n">
-        <v>0.1403</v>
+        <v>0.13855</v>
       </c>
       <c r="V195" t="n">
-        <v>77.06999999999999</v>
+        <v>77.23</v>
       </c>
       <c r="W195" t="n">
-        <v>66.3</v>
+        <v>65.45</v>
       </c>
       <c r="X195" t="n">
-        <v>0.8038</v>
+        <v>0.82</v>
       </c>
       <c r="Y195" t="n">
-        <v>27.484</v>
+        <v>27.52</v>
       </c>
       <c r="Z195" t="n">
-        <v>58.927</v>
+        <v>59.18</v>
       </c>
       <c r="AA195" t="n">
-        <v>10.526</v>
+        <v>10.67</v>
       </c>
       <c r="AB195" t="n">
-        <v>29.887</v>
+        <v>30.24</v>
       </c>
       <c r="AC195" t="n">
-        <v>12.247</v>
+        <v>12</v>
       </c>
       <c r="AD195" t="n">
-        <v>16.133</v>
+        <v>15.75</v>
       </c>
       <c r="AE195" t="n">
-        <v>8.332000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AF195" t="n">
-        <v>25.329</v>
+        <v>25.29</v>
       </c>
       <c r="AG195" t="n">
-        <v>18.145</v>
+        <v>18.2</v>
       </c>
       <c r="AH195" t="n">
-        <v>7.298</v>
+        <v>7.42</v>
       </c>
       <c r="AI195" t="n">
-        <v>2.556</v>
+        <v>2.5</v>
       </c>
       <c r="AJ195" t="n">
-        <v>14.226</v>
+        <v>14.12</v>
       </c>
       <c r="AK195" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="AL195" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="196">
@@ -24986,22 +24986,22 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F205" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G205" t="b">
         <v>1</v>
       </c>
       <c r="H205" t="n">
-        <v>1899.484</v>
+        <v>1863.313</v>
       </c>
       <c r="I205" t="n">
-        <v>2.2848</v>
+        <v>2.0961</v>
       </c>
       <c r="J205" t="n">
-        <v>1677.4</v>
+        <v>1679</v>
       </c>
       <c r="K205" t="n">
         <v>29</v>
@@ -25022,70 +25022,70 @@
         <v>24</v>
       </c>
       <c r="Q205" t="n">
-        <v>115.28</v>
+        <v>114.782</v>
       </c>
       <c r="R205" t="n">
-        <v>103.723</v>
+        <v>103.763</v>
       </c>
       <c r="S205" t="n">
-        <v>11.556</v>
+        <v>11.019</v>
       </c>
       <c r="T205" t="n">
-        <v>0.25957</v>
+        <v>0.258</v>
       </c>
       <c r="U205" t="n">
-        <v>0.13749</v>
+        <v>0.13763</v>
       </c>
       <c r="V205" t="n">
-        <v>79.77</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="W205" t="n">
-        <v>71.41</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="X205" t="n">
-        <v>0.7419</v>
+        <v>0.72</v>
       </c>
       <c r="Y205" t="n">
-        <v>27.927</v>
+        <v>28.02</v>
       </c>
       <c r="Z205" t="n">
-        <v>58.988</v>
+        <v>59.31</v>
       </c>
       <c r="AA205" t="n">
-        <v>8.567</v>
+        <v>8.66</v>
       </c>
       <c r="AB205" t="n">
-        <v>24.626</v>
+        <v>24.74</v>
       </c>
       <c r="AC205" t="n">
-        <v>15.392</v>
+        <v>15.2</v>
       </c>
       <c r="AD205" t="n">
-        <v>22.351</v>
+        <v>22.09</v>
       </c>
       <c r="AE205" t="n">
-        <v>9.214</v>
+        <v>9.19</v>
       </c>
       <c r="AF205" t="n">
-        <v>26.155</v>
+        <v>26.39</v>
       </c>
       <c r="AG205" t="n">
-        <v>15.792</v>
+        <v>15.69</v>
       </c>
       <c r="AH205" t="n">
-        <v>5.444</v>
+        <v>5.42</v>
       </c>
       <c r="AI205" t="n">
-        <v>3.402</v>
+        <v>3.47</v>
       </c>
       <c r="AJ205" t="n">
-        <v>14.578</v>
+        <v>14.66</v>
       </c>
       <c r="AK205" t="n">
-        <v>-0.4</v>
+        <v>-1.8</v>
       </c>
       <c r="AL205" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="206">
@@ -26426,22 +26426,22 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F217" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G217" t="b">
         <v>1</v>
       </c>
       <c r="H217" t="n">
-        <v>1813.861</v>
+        <v>1789.287</v>
       </c>
       <c r="I217" t="n">
-        <v>1.9487</v>
+        <v>2.1115</v>
       </c>
       <c r="J217" t="n">
-        <v>1722.9</v>
+        <v>1723.3</v>
       </c>
       <c r="K217" t="n">
         <v>26</v>
@@ -26462,70 +26462,70 @@
         <v>29</v>
       </c>
       <c r="Q217" t="n">
-        <v>118</v>
+        <v>117.639</v>
       </c>
       <c r="R217" t="n">
-        <v>108.071</v>
+        <v>108.068</v>
       </c>
       <c r="S217" t="n">
-        <v>9.929</v>
+        <v>9.571</v>
       </c>
       <c r="T217" t="n">
-        <v>0.25505</v>
+        <v>0.25683</v>
       </c>
       <c r="U217" t="n">
-        <v>0.15026</v>
+        <v>0.14892</v>
       </c>
       <c r="V217" t="n">
-        <v>79.68000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="W217" t="n">
-        <v>72.77</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="X217" t="n">
-        <v>0.631</v>
+        <v>0.6128</v>
       </c>
       <c r="Y217" t="n">
-        <v>27.409</v>
+        <v>27.327</v>
       </c>
       <c r="Z217" t="n">
-        <v>55.776</v>
+        <v>55.915</v>
       </c>
       <c r="AA217" t="n">
-        <v>8.09</v>
+        <v>8.125</v>
       </c>
       <c r="AB217" t="n">
-        <v>22.588</v>
+        <v>22.591</v>
       </c>
       <c r="AC217" t="n">
-        <v>16.893</v>
+        <v>16.616</v>
       </c>
       <c r="AD217" t="n">
-        <v>21.846</v>
+        <v>21.587</v>
       </c>
       <c r="AE217" t="n">
-        <v>8.106999999999999</v>
+        <v>8.236000000000001</v>
       </c>
       <c r="AF217" t="n">
-        <v>23.082</v>
+        <v>23.199</v>
       </c>
       <c r="AG217" t="n">
-        <v>14.335</v>
+        <v>14.276</v>
       </c>
       <c r="AH217" t="n">
-        <v>4.828</v>
+        <v>4.788</v>
       </c>
       <c r="AI217" t="n">
-        <v>2.498</v>
+        <v>2.541</v>
       </c>
       <c r="AJ217" t="n">
-        <v>17.391</v>
+        <v>17.231</v>
       </c>
       <c r="AK217" t="n">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="AL217" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218">
@@ -27386,22 +27386,22 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F225" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G225" t="b">
         <v>1</v>
       </c>
       <c r="H225" t="n">
-        <v>1435.396</v>
+        <v>1433.632</v>
       </c>
       <c r="I225" t="n">
-        <v>1.2024</v>
+        <v>1.3668</v>
       </c>
       <c r="J225" t="n">
-        <v>1493.7</v>
+        <v>1513.2</v>
       </c>
       <c r="K225" t="n">
         <v>150</v>
@@ -27422,70 +27422,70 @@
         <v>139</v>
       </c>
       <c r="Q225" t="n">
-        <v>108.543</v>
+        <v>108.034</v>
       </c>
       <c r="R225" t="n">
-        <v>106.705</v>
+        <v>108.635</v>
       </c>
       <c r="S225" t="n">
-        <v>1.838</v>
+        <v>-0.601</v>
       </c>
       <c r="T225" t="n">
-        <v>0.31426</v>
+        <v>0.3115</v>
       </c>
       <c r="U225" t="n">
-        <v>0.15185</v>
+        <v>0.15052</v>
       </c>
       <c r="V225" t="n">
-        <v>74.73999999999999</v>
+        <v>74.36</v>
       </c>
       <c r="W225" t="n">
-        <v>73.48999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="X225" t="n">
-        <v>0.612</v>
+        <v>0.5795</v>
       </c>
       <c r="Y225" t="n">
-        <v>26.097</v>
+        <v>26.216</v>
       </c>
       <c r="Z225" t="n">
-        <v>59.889</v>
+        <v>60.08</v>
       </c>
       <c r="AA225" t="n">
-        <v>7.942</v>
+        <v>7.977</v>
       </c>
       <c r="AB225" t="n">
-        <v>21.143</v>
+        <v>21.511</v>
       </c>
       <c r="AC225" t="n">
-        <v>14.34</v>
+        <v>13.75</v>
       </c>
       <c r="AD225" t="n">
-        <v>20.739</v>
+        <v>19.932</v>
       </c>
       <c r="AE225" t="n">
-        <v>10.616</v>
+        <v>10.375</v>
       </c>
       <c r="AF225" t="n">
-        <v>23.33</v>
+        <v>23.08</v>
       </c>
       <c r="AG225" t="n">
-        <v>14.076</v>
+        <v>13.92</v>
       </c>
       <c r="AH225" t="n">
-        <v>6.601</v>
+        <v>6.364</v>
       </c>
       <c r="AI225" t="n">
-        <v>3.224</v>
+        <v>3.205</v>
       </c>
       <c r="AJ225" t="n">
-        <v>16.776</v>
+        <v>17.023</v>
       </c>
       <c r="AK225" t="n">
-        <v>7.8</v>
+        <v>-1</v>
       </c>
       <c r="AL225" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="226">
@@ -31826,22 +31826,22 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F262" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G262" t="b">
         <v>1</v>
       </c>
       <c r="H262" t="n">
-        <v>1478.017</v>
+        <v>1477.189</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9489</v>
+        <v>0.9855</v>
       </c>
       <c r="J262" t="n">
-        <v>1430.3</v>
+        <v>1458.8</v>
       </c>
       <c r="K262" t="n">
         <v>192</v>
@@ -31862,70 +31862,70 @@
         <v>183</v>
       </c>
       <c r="Q262" t="n">
-        <v>109.727</v>
+        <v>109.579</v>
       </c>
       <c r="R262" t="n">
-        <v>101.773</v>
+        <v>102.384</v>
       </c>
       <c r="S262" t="n">
-        <v>7.954</v>
+        <v>7.195</v>
       </c>
       <c r="T262" t="n">
-        <v>0.27993</v>
+        <v>0.28293</v>
       </c>
       <c r="U262" t="n">
-        <v>0.1508</v>
+        <v>0.14927</v>
       </c>
       <c r="V262" t="n">
-        <v>70.45999999999999</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="W262" t="n">
-        <v>65.55</v>
+        <v>65.88</v>
       </c>
       <c r="X262" t="n">
-        <v>0.68</v>
+        <v>0.6505</v>
       </c>
       <c r="Y262" t="n">
-        <v>25.087</v>
+        <v>25.17</v>
       </c>
       <c r="Z262" t="n">
-        <v>55.469</v>
+        <v>55.809</v>
       </c>
       <c r="AA262" t="n">
-        <v>5.607</v>
+        <v>5.691</v>
       </c>
       <c r="AB262" t="n">
-        <v>18.258</v>
+        <v>18.421</v>
       </c>
       <c r="AC262" t="n">
-        <v>14.276</v>
+        <v>14.003</v>
       </c>
       <c r="AD262" t="n">
-        <v>18.644</v>
+        <v>18.217</v>
       </c>
       <c r="AE262" t="n">
-        <v>8.92</v>
+        <v>9.02</v>
       </c>
       <c r="AF262" t="n">
-        <v>22.491</v>
+        <v>22.432</v>
       </c>
       <c r="AG262" t="n">
-        <v>13.247</v>
+        <v>13.36</v>
       </c>
       <c r="AH262" t="n">
-        <v>5.993</v>
+        <v>5.933</v>
       </c>
       <c r="AI262" t="n">
-        <v>3.233</v>
+        <v>3.103</v>
       </c>
       <c r="AJ262" t="n">
-        <v>13.935</v>
+        <v>13.992</v>
       </c>
       <c r="AK262" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AL262" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="263">
@@ -32426,22 +32426,22 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F267" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G267" t="b">
         <v>1</v>
       </c>
       <c r="H267" t="n">
-        <v>1723.482</v>
+        <v>1706.22</v>
       </c>
       <c r="I267" t="n">
-        <v>8.857799999999999</v>
+        <v>8.7103</v>
       </c>
       <c r="J267" t="n">
-        <v>1554.8</v>
+        <v>1565.3</v>
       </c>
       <c r="K267" t="n">
         <v>47</v>
@@ -32462,70 +32462,70 @@
         <v>45</v>
       </c>
       <c r="Q267" t="n">
-        <v>115.66</v>
+        <v>115.379</v>
       </c>
       <c r="R267" t="n">
-        <v>100.714</v>
+        <v>101.318</v>
       </c>
       <c r="S267" t="n">
-        <v>14.946</v>
+        <v>14.062</v>
       </c>
       <c r="T267" t="n">
-        <v>0.33977</v>
+        <v>0.34579</v>
       </c>
       <c r="U267" t="n">
-        <v>0.14645</v>
+        <v>0.14539</v>
       </c>
       <c r="V267" t="n">
-        <v>86.81999999999999</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="W267" t="n">
-        <v>76.08</v>
+        <v>76.58</v>
       </c>
       <c r="X267" t="n">
-        <v>0.7527</v>
+        <v>0.72</v>
       </c>
       <c r="Y267" t="n">
-        <v>28.626</v>
+        <v>28.74</v>
       </c>
       <c r="Z267" t="n">
-        <v>65.66800000000001</v>
+        <v>66.17</v>
       </c>
       <c r="AA267" t="n">
-        <v>9.493</v>
+        <v>9.35</v>
       </c>
       <c r="AB267" t="n">
-        <v>28.708</v>
+        <v>28.95</v>
       </c>
       <c r="AC267" t="n">
-        <v>20.071</v>
+        <v>19.85</v>
       </c>
       <c r="AD267" t="n">
-        <v>26.988</v>
+        <v>26.59</v>
       </c>
       <c r="AE267" t="n">
-        <v>13.34</v>
+        <v>13.53</v>
       </c>
       <c r="AF267" t="n">
-        <v>25.733</v>
+        <v>25.45</v>
       </c>
       <c r="AG267" t="n">
-        <v>16.833</v>
+        <v>16.76</v>
       </c>
       <c r="AH267" t="n">
-        <v>8.856</v>
+        <v>9.09</v>
       </c>
       <c r="AI267" t="n">
-        <v>4.051</v>
+        <v>4.02</v>
       </c>
       <c r="AJ267" t="n">
-        <v>19.753</v>
+        <v>19.8</v>
       </c>
       <c r="AK267" t="n">
-        <v>19</v>
+        <v>12.6</v>
       </c>
       <c r="AL267" t="n">
-        <v>15.1</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="268">
@@ -33386,22 +33386,22 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F275" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G275" t="b">
         <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>1793.214</v>
+        <v>1819.597</v>
       </c>
       <c r="I275" t="n">
-        <v>8.666399999999999</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="J275" t="n">
-        <v>1516.9</v>
+        <v>1526.5</v>
       </c>
       <c r="K275" t="n">
         <v>41</v>
@@ -33422,70 +33422,70 @@
         <v>31</v>
       </c>
       <c r="Q275" t="n">
-        <v>120.005</v>
+        <v>120.498</v>
       </c>
       <c r="R275" t="n">
-        <v>98.72799999999999</v>
+        <v>98.57599999999999</v>
       </c>
       <c r="S275" t="n">
-        <v>21.276</v>
+        <v>21.922</v>
       </c>
       <c r="T275" t="n">
-        <v>0.24179</v>
+        <v>0.24815</v>
       </c>
       <c r="U275" t="n">
-        <v>0.1658</v>
+        <v>0.16516</v>
       </c>
       <c r="V275" t="n">
-        <v>86.22</v>
+        <v>87.03</v>
       </c>
       <c r="W275" t="n">
-        <v>70.65000000000001</v>
+        <v>70.91</v>
       </c>
       <c r="X275" t="n">
-        <v>0.8347</v>
+        <v>0.85</v>
       </c>
       <c r="Y275" t="n">
-        <v>29.882</v>
+        <v>29.8</v>
       </c>
       <c r="Z275" t="n">
-        <v>59.544</v>
+        <v>60.09</v>
       </c>
       <c r="AA275" t="n">
-        <v>10.782</v>
+        <v>10.78</v>
       </c>
       <c r="AB275" t="n">
-        <v>26.69</v>
+        <v>27.21</v>
       </c>
       <c r="AC275" t="n">
-        <v>15.715</v>
+        <v>15.68</v>
       </c>
       <c r="AD275" t="n">
-        <v>21.086</v>
+        <v>21.2</v>
       </c>
       <c r="AE275" t="n">
-        <v>8.917999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="AF275" t="n">
-        <v>27.823</v>
+        <v>27.6</v>
       </c>
       <c r="AG275" t="n">
-        <v>17.977</v>
+        <v>17.67</v>
       </c>
       <c r="AH275" t="n">
-        <v>7.238</v>
+        <v>7.29</v>
       </c>
       <c r="AI275" t="n">
-        <v>3.206</v>
+        <v>3.25</v>
       </c>
       <c r="AJ275" t="n">
-        <v>18.267</v>
+        <v>18.11</v>
       </c>
       <c r="AK275" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="AL275" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="276">
@@ -33506,22 +33506,22 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F276" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G276" t="b">
         <v>1</v>
       </c>
       <c r="H276" t="n">
-        <v>1857.81</v>
+        <v>1829.011</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2818</v>
+        <v>-0.1963</v>
       </c>
       <c r="J276" t="n">
-        <v>1596.9</v>
+        <v>1604.4</v>
       </c>
       <c r="K276" t="n">
         <v>24</v>
@@ -33542,70 +33542,70 @@
         <v>22</v>
       </c>
       <c r="Q276" t="n">
-        <v>118.734</v>
+        <v>117.386</v>
       </c>
       <c r="R276" t="n">
-        <v>99.88200000000001</v>
+        <v>99.93899999999999</v>
       </c>
       <c r="S276" t="n">
-        <v>18.852</v>
+        <v>17.447</v>
       </c>
       <c r="T276" t="n">
-        <v>0.2975</v>
+        <v>0.2968</v>
       </c>
       <c r="U276" t="n">
-        <v>0.15247</v>
+        <v>0.1542</v>
       </c>
       <c r="V276" t="n">
-        <v>77.54000000000001</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="W276" t="n">
-        <v>65.41</v>
+        <v>65.19</v>
       </c>
       <c r="X276" t="n">
-        <v>0.829</v>
+        <v>0.8038</v>
       </c>
       <c r="Y276" t="n">
-        <v>26.684</v>
+        <v>26.493</v>
       </c>
       <c r="Z276" t="n">
-        <v>57.823</v>
+        <v>57.534</v>
       </c>
       <c r="AA276" t="n">
-        <v>8.194000000000001</v>
+        <v>8.154999999999999</v>
       </c>
       <c r="AB276" t="n">
-        <v>20.951</v>
+        <v>20.991</v>
       </c>
       <c r="AC276" t="n">
-        <v>16.191</v>
+        <v>16.017</v>
       </c>
       <c r="AD276" t="n">
-        <v>20.377</v>
+        <v>20.141</v>
       </c>
       <c r="AE276" t="n">
-        <v>11.371</v>
+        <v>11.288</v>
       </c>
       <c r="AF276" t="n">
-        <v>26.154</v>
+        <v>26.05</v>
       </c>
       <c r="AG276" t="n">
-        <v>15.241</v>
+        <v>15.278</v>
       </c>
       <c r="AH276" t="n">
-        <v>5.562</v>
+        <v>5.848</v>
       </c>
       <c r="AI276" t="n">
-        <v>3.586</v>
+        <v>3.473</v>
       </c>
       <c r="AJ276" t="n">
-        <v>15.771</v>
+        <v>15.722</v>
       </c>
       <c r="AK276" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="AL276" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="277">
@@ -34346,22 +34346,22 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F283" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G283" t="b">
         <v>1</v>
       </c>
       <c r="H283" t="n">
-        <v>1836.074</v>
+        <v>1860.648</v>
       </c>
       <c r="I283" t="n">
-        <v>6.9164</v>
+        <v>6.8435</v>
       </c>
       <c r="J283" t="n">
-        <v>1691.3</v>
+        <v>1693.5</v>
       </c>
       <c r="K283" t="n">
         <v>43</v>
@@ -34382,70 +34382,70 @@
         <v>39</v>
       </c>
       <c r="Q283" t="n">
-        <v>111.157</v>
+        <v>111.032</v>
       </c>
       <c r="R283" t="n">
-        <v>102.345</v>
+        <v>102.3</v>
       </c>
       <c r="S283" t="n">
-        <v>8.813000000000001</v>
+        <v>8.731</v>
       </c>
       <c r="T283" t="n">
-        <v>0.32311</v>
+        <v>0.31828</v>
       </c>
       <c r="U283" t="n">
-        <v>0.15137</v>
+        <v>0.14957</v>
       </c>
       <c r="V283" t="n">
-        <v>78.26000000000001</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="W283" t="n">
-        <v>72.11</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="X283" t="n">
-        <v>0.6611</v>
+        <v>0.679</v>
       </c>
       <c r="Y283" t="n">
-        <v>27.133</v>
+        <v>27.035</v>
       </c>
       <c r="Z283" t="n">
-        <v>60.635</v>
+        <v>60.473</v>
       </c>
       <c r="AA283" t="n">
-        <v>7.407</v>
+        <v>7.342</v>
       </c>
       <c r="AB283" t="n">
-        <v>22.356</v>
+        <v>22.358</v>
       </c>
       <c r="AC283" t="n">
-        <v>16.584</v>
+        <v>16.361</v>
       </c>
       <c r="AD283" t="n">
-        <v>23.409</v>
+        <v>22.993</v>
       </c>
       <c r="AE283" t="n">
-        <v>11.219</v>
+        <v>11.019</v>
       </c>
       <c r="AF283" t="n">
-        <v>22.651</v>
+        <v>22.732</v>
       </c>
       <c r="AG283" t="n">
-        <v>15.589</v>
+        <v>15.724</v>
       </c>
       <c r="AH283" t="n">
-        <v>7.666</v>
+        <v>7.56</v>
       </c>
       <c r="AI283" t="n">
-        <v>4.541</v>
+        <v>4.488</v>
       </c>
       <c r="AJ283" t="n">
-        <v>16.359</v>
+        <v>16.07</v>
       </c>
       <c r="AK283" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="AL283" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="284">
@@ -34946,22 +34946,22 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F288" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G288" t="b">
         <v>1</v>
       </c>
       <c r="H288" t="n">
-        <v>1764.159</v>
+        <v>1801.834</v>
       </c>
       <c r="I288" t="n">
-        <v>2.6628</v>
+        <v>2.6488</v>
       </c>
       <c r="J288" t="n">
-        <v>1698.6</v>
+        <v>1706</v>
       </c>
       <c r="K288" t="n">
         <v>37</v>
@@ -34982,70 +34982,70 @@
         <v>42</v>
       </c>
       <c r="Q288" t="n">
-        <v>118.998</v>
+        <v>119.208</v>
       </c>
       <c r="R288" t="n">
-        <v>110.826</v>
+        <v>110.835</v>
       </c>
       <c r="S288" t="n">
-        <v>8.173</v>
+        <v>8.372999999999999</v>
       </c>
       <c r="T288" t="n">
-        <v>0.30408</v>
+        <v>0.30312</v>
       </c>
       <c r="U288" t="n">
-        <v>0.14433</v>
+        <v>0.14324</v>
       </c>
       <c r="V288" t="n">
         <v>82.06</v>
       </c>
       <c r="W288" t="n">
-        <v>76.34</v>
+        <v>76.23</v>
       </c>
       <c r="X288" t="n">
-        <v>0.5665</v>
+        <v>0.5793</v>
       </c>
       <c r="Y288" t="n">
-        <v>27.8</v>
+        <v>27.696</v>
       </c>
       <c r="Z288" t="n">
-        <v>58.071</v>
+        <v>57.983</v>
       </c>
       <c r="AA288" t="n">
-        <v>7.053</v>
+        <v>6.945</v>
       </c>
       <c r="AB288" t="n">
-        <v>20.366</v>
+        <v>20.468</v>
       </c>
       <c r="AC288" t="n">
-        <v>19.636</v>
+        <v>19.661</v>
       </c>
       <c r="AD288" t="n">
-        <v>26.145</v>
+        <v>26.133</v>
       </c>
       <c r="AE288" t="n">
-        <v>10.53</v>
+        <v>10.464</v>
       </c>
       <c r="AF288" t="n">
-        <v>24.173</v>
+        <v>24.112</v>
       </c>
       <c r="AG288" t="n">
-        <v>11.734</v>
+        <v>11.529</v>
       </c>
       <c r="AH288" t="n">
-        <v>6.018</v>
+        <v>6</v>
       </c>
       <c r="AI288" t="n">
-        <v>2.956</v>
+        <v>2.978</v>
       </c>
       <c r="AJ288" t="n">
-        <v>18.996</v>
+        <v>18.97</v>
       </c>
       <c r="AK288" t="n">
-        <v>-5</v>
+        <v>-4.6</v>
       </c>
       <c r="AL288" t="n">
-        <v>-1.8</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="289">
@@ -35066,22 +35066,22 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F289" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G289" t="b">
         <v>1</v>
       </c>
       <c r="H289" t="n">
-        <v>1823.96</v>
+        <v>1852.759</v>
       </c>
       <c r="I289" t="n">
-        <v>4.3608</v>
+        <v>4.0806</v>
       </c>
       <c r="J289" t="n">
-        <v>1653.7</v>
+        <v>1661.5</v>
       </c>
       <c r="K289" t="n">
         <v>39</v>
@@ -35102,70 +35102,70 @@
         <v>44</v>
       </c>
       <c r="Q289" t="n">
-        <v>117.135</v>
+        <v>116.943</v>
       </c>
       <c r="R289" t="n">
-        <v>107.431</v>
+        <v>106.221</v>
       </c>
       <c r="S289" t="n">
-        <v>9.702999999999999</v>
+        <v>10.722</v>
       </c>
       <c r="T289" t="n">
-        <v>0.30978</v>
+        <v>0.31014</v>
       </c>
       <c r="U289" t="n">
-        <v>0.13892</v>
+        <v>0.14624</v>
       </c>
       <c r="V289" t="n">
-        <v>87.41</v>
+        <v>86.69</v>
       </c>
       <c r="W289" t="n">
-        <v>79.61</v>
+        <v>78.33</v>
       </c>
       <c r="X289" t="n">
-        <v>0.648</v>
+        <v>0.6706</v>
       </c>
       <c r="Y289" t="n">
-        <v>29.827</v>
+        <v>29.32</v>
       </c>
       <c r="Z289" t="n">
-        <v>64.822</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="AA289" t="n">
-        <v>10.777</v>
+        <v>10.779</v>
       </c>
       <c r="AB289" t="n">
-        <v>29.846</v>
+        <v>29.559</v>
       </c>
       <c r="AC289" t="n">
-        <v>17.844</v>
+        <v>17.327</v>
       </c>
       <c r="AD289" t="n">
-        <v>24.14</v>
+        <v>23.668</v>
       </c>
       <c r="AE289" t="n">
-        <v>11.317</v>
+        <v>11.21</v>
       </c>
       <c r="AF289" t="n">
-        <v>24.495</v>
+        <v>24.294</v>
       </c>
       <c r="AG289" t="n">
-        <v>18.222</v>
+        <v>17.823</v>
       </c>
       <c r="AH289" t="n">
-        <v>8.129</v>
+        <v>8.025</v>
       </c>
       <c r="AI289" t="n">
-        <v>3.365</v>
+        <v>3.329</v>
       </c>
       <c r="AJ289" t="n">
-        <v>19.233</v>
+        <v>18.924</v>
       </c>
       <c r="AK289" t="n">
-        <v>-5.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL289" t="n">
-        <v>-5.3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="290">
@@ -35786,22 +35786,22 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F295" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G295" t="b">
         <v>1</v>
       </c>
       <c r="H295" t="n">
-        <v>1600.961</v>
+        <v>1595.802</v>
       </c>
       <c r="I295" t="n">
-        <v>1.1284</v>
+        <v>1.0762</v>
       </c>
       <c r="J295" t="n">
-        <v>1466</v>
+        <v>1488.7</v>
       </c>
       <c r="K295" t="n">
         <v>143</v>
@@ -35822,70 +35822,70 @@
         <v>125</v>
       </c>
       <c r="Q295" t="n">
-        <v>112.278</v>
+        <v>110.674</v>
       </c>
       <c r="R295" t="n">
-        <v>106.193</v>
+        <v>107.202</v>
       </c>
       <c r="S295" t="n">
-        <v>6.085</v>
+        <v>3.471</v>
       </c>
       <c r="T295" t="n">
-        <v>0.316</v>
+        <v>0.31414</v>
       </c>
       <c r="U295" t="n">
-        <v>0.16673</v>
+        <v>0.17064</v>
       </c>
       <c r="V295" t="n">
-        <v>78.27</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="W295" t="n">
-        <v>74.3</v>
+        <v>74.55</v>
       </c>
       <c r="X295" t="n">
-        <v>0.65</v>
+        <v>0.6171</v>
       </c>
       <c r="Y295" t="n">
-        <v>26.627</v>
+        <v>25.99</v>
       </c>
       <c r="Z295" t="n">
-        <v>59.845</v>
+        <v>59.36</v>
       </c>
       <c r="AA295" t="n">
-        <v>9.009</v>
+        <v>9.018000000000001</v>
       </c>
       <c r="AB295" t="n">
-        <v>27.182</v>
+        <v>27.352</v>
       </c>
       <c r="AC295" t="n">
-        <v>16.009</v>
+        <v>15.931</v>
       </c>
       <c r="AD295" t="n">
-        <v>21.709</v>
+        <v>21.436</v>
       </c>
       <c r="AE295" t="n">
-        <v>11.159</v>
+        <v>11.067</v>
       </c>
       <c r="AF295" t="n">
-        <v>24.032</v>
+        <v>24.031</v>
       </c>
       <c r="AG295" t="n">
-        <v>15.186</v>
+        <v>14.98</v>
       </c>
       <c r="AH295" t="n">
-        <v>7.255</v>
+        <v>7.16</v>
       </c>
       <c r="AI295" t="n">
-        <v>3.341</v>
+        <v>3.327</v>
       </c>
       <c r="AJ295" t="n">
-        <v>16.75</v>
+        <v>16.567</v>
       </c>
       <c r="AK295" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AL295" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="296">
@@ -38786,22 +38786,22 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F320" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G320" t="b">
         <v>1</v>
       </c>
       <c r="H320" t="n">
-        <v>1761.339</v>
+        <v>1797.509</v>
       </c>
       <c r="I320" t="n">
-        <v>3.2921</v>
+        <v>3.4141</v>
       </c>
       <c r="J320" t="n">
-        <v>1558.4</v>
+        <v>1569.9</v>
       </c>
       <c r="K320" t="n">
         <v>45</v>
@@ -38822,70 +38822,70 @@
         <v>43</v>
       </c>
       <c r="Q320" t="n">
-        <v>117.937</v>
+        <v>117.658</v>
       </c>
       <c r="R320" t="n">
-        <v>103.323</v>
+        <v>103.371</v>
       </c>
       <c r="S320" t="n">
-        <v>14.613</v>
+        <v>14.287</v>
       </c>
       <c r="T320" t="n">
-        <v>0.29406</v>
+        <v>0.29349</v>
       </c>
       <c r="U320" t="n">
-        <v>0.14675</v>
+        <v>0.14585</v>
       </c>
       <c r="V320" t="n">
-        <v>81.45</v>
+        <v>81.58</v>
       </c>
       <c r="W320" t="n">
-        <v>71.38</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="X320" t="n">
-        <v>0.796</v>
+        <v>0.8017</v>
       </c>
       <c r="Y320" t="n">
-        <v>26.7</v>
+        <v>26.819</v>
       </c>
       <c r="Z320" t="n">
-        <v>58.049</v>
+        <v>58.501</v>
       </c>
       <c r="AA320" t="n">
-        <v>9.339</v>
+        <v>9.275</v>
       </c>
       <c r="AB320" t="n">
-        <v>25.399</v>
+        <v>25.545</v>
       </c>
       <c r="AC320" t="n">
-        <v>18.711</v>
+        <v>18.514</v>
       </c>
       <c r="AD320" t="n">
-        <v>25.323</v>
+        <v>25.183</v>
       </c>
       <c r="AE320" t="n">
-        <v>10.196</v>
+        <v>10.264</v>
       </c>
       <c r="AF320" t="n">
-        <v>24.27</v>
+        <v>24.56</v>
       </c>
       <c r="AG320" t="n">
-        <v>14.069</v>
+        <v>14.233</v>
       </c>
       <c r="AH320" t="n">
-        <v>7.397</v>
+        <v>7.405</v>
       </c>
       <c r="AI320" t="n">
-        <v>4.35</v>
+        <v>4.229</v>
       </c>
       <c r="AJ320" t="n">
-        <v>17.301</v>
+        <v>17.283</v>
       </c>
       <c r="AK320" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AL320" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="321">
@@ -39026,22 +39026,22 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F322" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G322" t="b">
         <v>1</v>
       </c>
       <c r="H322" t="n">
-        <v>1952.581</v>
+        <v>1963.829</v>
       </c>
       <c r="I322" t="n">
-        <v>1.6305</v>
+        <v>1.4886</v>
       </c>
       <c r="J322" t="n">
-        <v>1718.8</v>
+        <v>1716.9</v>
       </c>
       <c r="K322" t="n">
         <v>12</v>
@@ -39062,70 +39062,70 @@
         <v>13</v>
       </c>
       <c r="Q322" t="n">
-        <v>122.082</v>
+        <v>122.218</v>
       </c>
       <c r="R322" t="n">
-        <v>106.871</v>
+        <v>106.709</v>
       </c>
       <c r="S322" t="n">
-        <v>15.211</v>
+        <v>15.509</v>
       </c>
       <c r="T322" t="n">
-        <v>0.29148</v>
+        <v>0.28967</v>
       </c>
       <c r="U322" t="n">
-        <v>0.12812</v>
+        <v>0.13117</v>
       </c>
       <c r="V322" t="n">
-        <v>86.25</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="W322" t="n">
-        <v>75.31</v>
+        <v>74.94</v>
       </c>
       <c r="X322" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7734</v>
       </c>
       <c r="Y322" t="n">
-        <v>28.992</v>
+        <v>28.917</v>
       </c>
       <c r="Z322" t="n">
-        <v>61.425</v>
+        <v>60.998</v>
       </c>
       <c r="AA322" t="n">
-        <v>9.359</v>
+        <v>9.34</v>
       </c>
       <c r="AB322" t="n">
-        <v>26.593</v>
+        <v>26.521</v>
       </c>
       <c r="AC322" t="n">
-        <v>18.409</v>
+        <v>18.388</v>
       </c>
       <c r="AD322" t="n">
-        <v>23.333</v>
+        <v>23.285</v>
       </c>
       <c r="AE322" t="n">
-        <v>9.971</v>
+        <v>9.935</v>
       </c>
       <c r="AF322" t="n">
-        <v>23.709</v>
+        <v>23.865</v>
       </c>
       <c r="AG322" t="n">
-        <v>16.127</v>
+        <v>16.105</v>
       </c>
       <c r="AH322" t="n">
-        <v>8.048999999999999</v>
+        <v>7.871</v>
       </c>
       <c r="AI322" t="n">
-        <v>4.555</v>
+        <v>4.529</v>
       </c>
       <c r="AJ322" t="n">
-        <v>19.323</v>
+        <v>19.072</v>
       </c>
       <c r="AK322" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AL322" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="323">
@@ -41546,22 +41546,22 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F343" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G343" t="b">
         <v>1</v>
       </c>
       <c r="H343" t="n">
-        <v>1882.441</v>
+        <v>1843.62</v>
       </c>
       <c r="I343" t="n">
-        <v>2.4266</v>
+        <v>2.6405</v>
       </c>
       <c r="J343" t="n">
-        <v>1724.6</v>
+        <v>1717.5</v>
       </c>
       <c r="K343" t="n">
         <v>22</v>
@@ -41582,70 +41582,70 @@
         <v>25</v>
       </c>
       <c r="Q343" t="n">
-        <v>118.801</v>
+        <v>118.854</v>
       </c>
       <c r="R343" t="n">
-        <v>108.528</v>
+        <v>108.886</v>
       </c>
       <c r="S343" t="n">
-        <v>10.273</v>
+        <v>9.968</v>
       </c>
       <c r="T343" t="n">
-        <v>0.27758</v>
+        <v>0.27955</v>
       </c>
       <c r="U343" t="n">
-        <v>0.12395</v>
+        <v>0.12224</v>
       </c>
       <c r="V343" t="n">
-        <v>82.86</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="W343" t="n">
-        <v>75.84999999999999</v>
+        <v>76.16</v>
       </c>
       <c r="X343" t="n">
-        <v>0.7003</v>
+        <v>0.6807</v>
       </c>
       <c r="Y343" t="n">
-        <v>28.019</v>
+        <v>28.164</v>
       </c>
       <c r="Z343" t="n">
-        <v>62.051</v>
+        <v>62.485</v>
       </c>
       <c r="AA343" t="n">
-        <v>11.769</v>
+        <v>11.852</v>
       </c>
       <c r="AB343" t="n">
-        <v>32.339</v>
+        <v>32.569</v>
       </c>
       <c r="AC343" t="n">
-        <v>14.964</v>
+        <v>14.735</v>
       </c>
       <c r="AD343" t="n">
-        <v>19.211</v>
+        <v>18.955</v>
       </c>
       <c r="AE343" t="n">
-        <v>9.305</v>
+        <v>9.455</v>
       </c>
       <c r="AF343" t="n">
-        <v>23.926</v>
+        <v>24.05</v>
       </c>
       <c r="AG343" t="n">
-        <v>15.926</v>
+        <v>16.015</v>
       </c>
       <c r="AH343" t="n">
-        <v>5.586</v>
+        <v>5.575</v>
       </c>
       <c r="AI343" t="n">
-        <v>3.103</v>
+        <v>3.157</v>
       </c>
       <c r="AJ343" t="n">
-        <v>17.268</v>
+        <v>17.212</v>
       </c>
       <c r="AK343" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="AL343" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="344">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -866,22 +866,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1707.887</v>
+        <v>1700.07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9745</v>
+        <v>2.0575</v>
       </c>
       <c r="J4" t="n">
-        <v>1479.2</v>
+        <v>1499.8</v>
       </c>
       <c r="K4" t="n">
         <v>64</v>
@@ -902,70 +902,70 @@
         <v>54</v>
       </c>
       <c r="Q4" t="n">
-        <v>121.636</v>
+        <v>121.234</v>
       </c>
       <c r="R4" t="n">
-        <v>104.361</v>
+        <v>105.697</v>
       </c>
       <c r="S4" t="n">
-        <v>17.275</v>
+        <v>15.537</v>
       </c>
       <c r="T4" t="n">
-        <v>0.28865</v>
+        <v>0.29368</v>
       </c>
       <c r="U4" t="n">
-        <v>0.14997</v>
+        <v>0.14984</v>
       </c>
       <c r="V4" t="n">
-        <v>86.8</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>74.51000000000001</v>
+        <v>75.13</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8452</v>
+        <v>0.8113</v>
       </c>
       <c r="Y4" t="n">
-        <v>31.173</v>
+        <v>30.919</v>
       </c>
       <c r="Z4" t="n">
-        <v>62.67</v>
+        <v>62.417</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.867</v>
+        <v>10.649</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.302</v>
+        <v>27.894</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.591</v>
+        <v>13.776</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.105</v>
+        <v>18.257</v>
       </c>
       <c r="AE4" t="n">
-        <v>9.974</v>
+        <v>9.978</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.292</v>
+        <v>24.877</v>
       </c>
       <c r="AG4" t="n">
-        <v>17.849</v>
+        <v>17.649</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.23</v>
+        <v>7.163</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.885</v>
+        <v>2.918</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16.243</v>
+        <v>16.155</v>
       </c>
       <c r="AK4" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>13.8</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="5">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1949.262</v>
+        <v>1954.667</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3255</v>
+        <v>-1.3316</v>
       </c>
       <c r="J5" t="n">
-        <v>1767</v>
+        <v>1760.9</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -1022,70 +1022,70 @@
         <v>18</v>
       </c>
       <c r="Q5" t="n">
-        <v>121.371</v>
+        <v>121.89</v>
       </c>
       <c r="R5" t="n">
-        <v>110.604</v>
+        <v>110.305</v>
       </c>
       <c r="S5" t="n">
-        <v>10.767</v>
+        <v>11.585</v>
       </c>
       <c r="T5" t="n">
-        <v>0.28088</v>
+        <v>0.28487</v>
       </c>
       <c r="U5" t="n">
-        <v>0.12877</v>
+        <v>0.1295</v>
       </c>
       <c r="V5" t="n">
-        <v>91.59999999999999</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>83.44</v>
+        <v>82.95</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7123</v>
+        <v>0.7296</v>
       </c>
       <c r="Y5" t="n">
-        <v>30.319</v>
+        <v>30.377</v>
       </c>
       <c r="Z5" t="n">
-        <v>65.97799999999999</v>
+        <v>66.008</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.583</v>
+        <v>12.601</v>
       </c>
       <c r="AB5" t="n">
-        <v>34.886</v>
+        <v>35.069</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.423</v>
+        <v>18.327</v>
       </c>
       <c r="AD5" t="n">
-        <v>24.105</v>
+        <v>23.988</v>
       </c>
       <c r="AE5" t="n">
-        <v>10.858</v>
+        <v>11.111</v>
       </c>
       <c r="AF5" t="n">
-        <v>27.55</v>
+        <v>27.558</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.106</v>
+        <v>16.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.345</v>
+        <v>6.361</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.093</v>
+        <v>5.129</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.752</v>
+        <v>18.529</v>
       </c>
       <c r="AK5" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1826,22 +1826,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2272.125</v>
+        <v>2272.508</v>
       </c>
       <c r="I12" t="n">
-        <v>6.8151</v>
+        <v>6.6001</v>
       </c>
       <c r="J12" t="n">
-        <v>1769.2</v>
+        <v>1753.9</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1862,70 +1862,70 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>121.138</v>
+        <v>121.602</v>
       </c>
       <c r="R12" t="n">
-        <v>97.108</v>
+        <v>96.53400000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>24.03</v>
+        <v>25.069</v>
       </c>
       <c r="T12" t="n">
-        <v>0.29246</v>
+        <v>0.29327</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1497</v>
+        <v>0.14976</v>
       </c>
       <c r="V12" t="n">
-        <v>86.09</v>
+        <v>86.36</v>
       </c>
       <c r="W12" t="n">
-        <v>68.84</v>
+        <v>68.41</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9416</v>
+        <v>0.9433</v>
       </c>
       <c r="Y12" t="n">
-        <v>30.515</v>
+        <v>30.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>60.799</v>
+        <v>60.822</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.883</v>
+        <v>5.887</v>
       </c>
       <c r="AB12" t="n">
-        <v>16.297</v>
+        <v>16.205</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.177</v>
+        <v>19.249</v>
       </c>
       <c r="AD12" t="n">
-        <v>26.095</v>
+        <v>26.335</v>
       </c>
       <c r="AE12" t="n">
-        <v>11.976</v>
+        <v>12.143</v>
       </c>
       <c r="AF12" t="n">
-        <v>28.655</v>
+        <v>28.938</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.879</v>
+        <v>16.908</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.778</v>
+        <v>7.687</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.218</v>
+        <v>4.441</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16</v>
+        <v>15.857</v>
       </c>
       <c r="AK12" t="n">
-        <v>11</v>
+        <v>14.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>9.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="13">
@@ -6386,22 +6386,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F50" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G50" t="b">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1859.484</v>
+        <v>1831.145</v>
       </c>
       <c r="I50" t="n">
-        <v>2.557</v>
+        <v>2.3914</v>
       </c>
       <c r="J50" t="n">
-        <v>1672.9</v>
+        <v>1674.2</v>
       </c>
       <c r="K50" t="n">
         <v>36</v>
@@ -6422,70 +6422,70 @@
         <v>34</v>
       </c>
       <c r="Q50" t="n">
-        <v>112.594</v>
+        <v>112.781</v>
       </c>
       <c r="R50" t="n">
-        <v>101.684</v>
+        <v>102.417</v>
       </c>
       <c r="S50" t="n">
-        <v>10.91</v>
+        <v>10.363</v>
       </c>
       <c r="T50" t="n">
-        <v>0.25542</v>
+        <v>0.25948</v>
       </c>
       <c r="U50" t="n">
-        <v>0.13604</v>
+        <v>0.1369</v>
       </c>
       <c r="V50" t="n">
-        <v>74.02</v>
+        <v>73.66</v>
       </c>
       <c r="W50" t="n">
-        <v>66.79000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="X50" t="n">
-        <v>0.6993</v>
+        <v>0.6797</v>
       </c>
       <c r="Y50" t="n">
-        <v>25.401</v>
+        <v>25.194</v>
       </c>
       <c r="Z50" t="n">
-        <v>56.224</v>
+        <v>55.893</v>
       </c>
       <c r="AA50" t="n">
-        <v>8.253</v>
+        <v>8.218</v>
       </c>
       <c r="AB50" t="n">
-        <v>24.388</v>
+        <v>24.405</v>
       </c>
       <c r="AC50" t="n">
-        <v>14.941</v>
+        <v>15.248</v>
       </c>
       <c r="AD50" t="n">
-        <v>20.669</v>
+        <v>21.031</v>
       </c>
       <c r="AE50" t="n">
-        <v>8.583</v>
+        <v>8.826000000000001</v>
       </c>
       <c r="AF50" t="n">
-        <v>23.895</v>
+        <v>23.98</v>
       </c>
       <c r="AG50" t="n">
-        <v>12.855</v>
+        <v>12.59</v>
       </c>
       <c r="AH50" t="n">
-        <v>6.242</v>
+        <v>6.115</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.854</v>
+        <v>2.784</v>
       </c>
       <c r="AJ50" t="n">
-        <v>16.097</v>
+        <v>16.011</v>
       </c>
       <c r="AK50" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="AL50" t="n">
-        <v>-3.4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="51">
@@ -7346,22 +7346,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F58" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>2050.719</v>
+        <v>2053.381</v>
       </c>
       <c r="I58" t="n">
-        <v>7.1741</v>
+        <v>6.6189</v>
       </c>
       <c r="J58" t="n">
-        <v>1670.2</v>
+        <v>1662.8</v>
       </c>
       <c r="K58" t="n">
         <v>11</v>
@@ -7382,70 +7382,70 @@
         <v>10</v>
       </c>
       <c r="Q58" t="n">
-        <v>116.057</v>
+        <v>116.791</v>
       </c>
       <c r="R58" t="n">
-        <v>98.01000000000001</v>
+        <v>98.316</v>
       </c>
       <c r="S58" t="n">
-        <v>18.046</v>
+        <v>18.475</v>
       </c>
       <c r="T58" t="n">
-        <v>0.30128</v>
+        <v>0.30395</v>
       </c>
       <c r="U58" t="n">
-        <v>0.16031</v>
+        <v>0.15867</v>
       </c>
       <c r="V58" t="n">
-        <v>77.26000000000001</v>
+        <v>77.67</v>
       </c>
       <c r="W58" t="n">
-        <v>65.18000000000001</v>
+        <v>65.34</v>
       </c>
       <c r="X58" t="n">
-        <v>0.845</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="Y58" t="n">
-        <v>28.207</v>
+        <v>28.431</v>
       </c>
       <c r="Z58" t="n">
-        <v>58.622</v>
+        <v>58.882</v>
       </c>
       <c r="AA58" t="n">
-        <v>8.273999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB58" t="n">
-        <v>23.604</v>
+        <v>23.697</v>
       </c>
       <c r="AC58" t="n">
-        <v>12.573</v>
+        <v>12.603</v>
       </c>
       <c r="AD58" t="n">
-        <v>17.555</v>
+        <v>17.603</v>
       </c>
       <c r="AE58" t="n">
-        <v>10.473</v>
+        <v>10.693</v>
       </c>
       <c r="AF58" t="n">
-        <v>23.914</v>
+        <v>24.017</v>
       </c>
       <c r="AG58" t="n">
-        <v>18.314</v>
+        <v>18.516</v>
       </c>
       <c r="AH58" t="n">
-        <v>6.874</v>
+        <v>6.887</v>
       </c>
       <c r="AI58" t="n">
-        <v>5.234</v>
+        <v>5.107</v>
       </c>
       <c r="AJ58" t="n">
-        <v>18.069</v>
+        <v>18.048</v>
       </c>
       <c r="AK58" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="AL58" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="59">
@@ -11306,22 +11306,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F91" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G91" t="b">
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>2006.659</v>
+        <v>2007.171</v>
       </c>
       <c r="I91" t="n">
-        <v>3.4651</v>
+        <v>3.5894</v>
       </c>
       <c r="J91" t="n">
-        <v>1722.9</v>
+        <v>1703.3</v>
       </c>
       <c r="K91" t="n">
         <v>4</v>
@@ -11342,70 +11342,70 @@
         <v>4</v>
       </c>
       <c r="Q91" t="n">
-        <v>119.994</v>
+        <v>121.802</v>
       </c>
       <c r="R91" t="n">
-        <v>100.186</v>
+        <v>99.018</v>
       </c>
       <c r="S91" t="n">
-        <v>19.808</v>
+        <v>22.784</v>
       </c>
       <c r="T91" t="n">
-        <v>0.33419</v>
+        <v>0.3326</v>
       </c>
       <c r="U91" t="n">
-        <v>0.15683</v>
+        <v>0.15503</v>
       </c>
       <c r="V91" t="n">
-        <v>86.66</v>
+        <v>87.83</v>
       </c>
       <c r="W91" t="n">
-        <v>72.19</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="X91" t="n">
-        <v>0.78</v>
+        <v>0.796</v>
       </c>
       <c r="Y91" t="n">
-        <v>30.9</v>
+        <v>31.451</v>
       </c>
       <c r="Z91" t="n">
-        <v>64.23999999999999</v>
+        <v>64.551</v>
       </c>
       <c r="AA91" t="n">
-        <v>7.54</v>
+        <v>7.611</v>
       </c>
       <c r="AB91" t="n">
-        <v>24</v>
+        <v>23.952</v>
       </c>
       <c r="AC91" t="n">
+        <v>17.817</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>24.876</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>14.572</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>28.676</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>17.345</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>6.681</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>5.135</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>17.681</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="AL91" t="n">
         <v>18</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>25.13</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>28.17</v>
-      </c>
-      <c r="AG91" t="n">
-        <v>16.92</v>
-      </c>
-      <c r="AH91" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AI91" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="AJ91" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="AK91" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AL91" t="n">
-        <v>14.1</v>
       </c>
     </row>
     <row r="92">
@@ -12026,22 +12026,22 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F97" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G97" t="b">
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>1542.857</v>
+        <v>1540.197</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8197</v>
+        <v>0.788</v>
       </c>
       <c r="J97" t="n">
-        <v>1422.2</v>
+        <v>1445.6</v>
       </c>
       <c r="K97" t="n">
         <v>191</v>
@@ -12062,70 +12062,70 @@
         <v>186</v>
       </c>
       <c r="Q97" t="n">
-        <v>112.011</v>
+        <v>111.793</v>
       </c>
       <c r="R97" t="n">
-        <v>107.277</v>
+        <v>108.038</v>
       </c>
       <c r="S97" t="n">
-        <v>4.734</v>
+        <v>3.754</v>
       </c>
       <c r="T97" t="n">
-        <v>0.25616</v>
+        <v>0.25304</v>
       </c>
       <c r="U97" t="n">
-        <v>0.17102</v>
+        <v>0.17098</v>
       </c>
       <c r="V97" t="n">
-        <v>75.06999999999999</v>
+        <v>74.91</v>
       </c>
       <c r="W97" t="n">
-        <v>72.06999999999999</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="X97" t="n">
-        <v>0.616</v>
+        <v>0.5893</v>
       </c>
       <c r="Y97" t="n">
-        <v>26.592</v>
+        <v>26.397</v>
       </c>
       <c r="Z97" t="n">
-        <v>56.496</v>
+        <v>56.181</v>
       </c>
       <c r="AA97" t="n">
-        <v>8.568</v>
+        <v>8.628</v>
       </c>
       <c r="AB97" t="n">
-        <v>26.208</v>
+        <v>26.202</v>
       </c>
       <c r="AC97" t="n">
-        <v>12.56</v>
+        <v>12.866</v>
       </c>
       <c r="AD97" t="n">
-        <v>18.288</v>
+        <v>18.587</v>
       </c>
       <c r="AE97" t="n">
-        <v>8.912000000000001</v>
+        <v>8.746</v>
       </c>
       <c r="AF97" t="n">
-        <v>25.008</v>
+        <v>24.831</v>
       </c>
       <c r="AG97" t="n">
-        <v>14.632</v>
+        <v>14.682</v>
       </c>
       <c r="AH97" t="n">
-        <v>4.48</v>
+        <v>4.396</v>
       </c>
       <c r="AI97" t="n">
-        <v>3.28</v>
+        <v>3.279</v>
       </c>
       <c r="AJ97" t="n">
-        <v>15.472</v>
+        <v>15.465</v>
       </c>
       <c r="AK97" t="n">
-        <v>5.6</v>
+        <v>-0.8</v>
       </c>
       <c r="AL97" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -13946,22 +13946,22 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F113" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G113" t="b">
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>1586.191</v>
+        <v>1580.784</v>
       </c>
       <c r="I113" t="n">
-        <v>3.3583</v>
+        <v>3.2408</v>
       </c>
       <c r="J113" t="n">
-        <v>1482.3</v>
+        <v>1500.6</v>
       </c>
       <c r="K113" t="n">
         <v>87</v>
@@ -13982,70 +13982,70 @@
         <v>88</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.557</v>
+        <v>113.029</v>
       </c>
       <c r="R113" t="n">
-        <v>102.691</v>
+        <v>103.66</v>
       </c>
       <c r="S113" t="n">
-        <v>10.866</v>
+        <v>9.369</v>
       </c>
       <c r="T113" t="n">
-        <v>0.30811</v>
+        <v>0.31061</v>
       </c>
       <c r="U113" t="n">
-        <v>0.15271</v>
+        <v>0.1533</v>
       </c>
       <c r="V113" t="n">
-        <v>74.5</v>
+        <v>74.33</v>
       </c>
       <c r="W113" t="n">
-        <v>67.58</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="X113" t="n">
-        <v>0.6903</v>
+        <v>0.6611</v>
       </c>
       <c r="Y113" t="n">
-        <v>25.385</v>
+        <v>25.506</v>
       </c>
       <c r="Z113" t="n">
-        <v>58.372</v>
+        <v>58.784</v>
       </c>
       <c r="AA113" t="n">
-        <v>9.252000000000001</v>
+        <v>9.347</v>
       </c>
       <c r="AB113" t="n">
-        <v>25.159</v>
+        <v>25.142</v>
       </c>
       <c r="AC113" t="n">
-        <v>14.484</v>
+        <v>13.968</v>
       </c>
       <c r="AD113" t="n">
-        <v>19.05</v>
+        <v>18.431</v>
       </c>
       <c r="AE113" t="n">
-        <v>10.974</v>
+        <v>11.017</v>
       </c>
       <c r="AF113" t="n">
-        <v>24.47</v>
+        <v>24.305</v>
       </c>
       <c r="AG113" t="n">
-        <v>12.292</v>
+        <v>12.3</v>
       </c>
       <c r="AH113" t="n">
-        <v>4.801</v>
+        <v>4.828</v>
       </c>
       <c r="AI113" t="n">
-        <v>3.539</v>
+        <v>3.541</v>
       </c>
       <c r="AJ113" t="n">
-        <v>17.585</v>
+        <v>17.425</v>
       </c>
       <c r="AK113" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="AL113" t="n">
-        <v>13.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
@@ -15626,22 +15626,22 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F127" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G127" t="b">
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>1831.779</v>
+        <v>1860.117</v>
       </c>
       <c r="I127" t="n">
-        <v>3.3952</v>
+        <v>3.0379</v>
       </c>
       <c r="J127" t="n">
-        <v>1712.2</v>
+        <v>1717.1</v>
       </c>
       <c r="K127" t="n">
         <v>25</v>
@@ -15662,70 +15662,70 @@
         <v>27</v>
       </c>
       <c r="Q127" t="n">
-        <v>118.924</v>
+        <v>119.224</v>
       </c>
       <c r="R127" t="n">
-        <v>104.806</v>
+        <v>105.017</v>
       </c>
       <c r="S127" t="n">
-        <v>14.118</v>
+        <v>14.206</v>
       </c>
       <c r="T127" t="n">
-        <v>0.28864</v>
+        <v>0.29176</v>
       </c>
       <c r="U127" t="n">
-        <v>0.14551</v>
+        <v>0.14178</v>
       </c>
       <c r="V127" t="n">
-        <v>75.15000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="W127" t="n">
-        <v>66.03</v>
+        <v>65.78</v>
       </c>
       <c r="X127" t="n">
-        <v>0.63</v>
+        <v>0.6503</v>
       </c>
       <c r="Y127" t="n">
-        <v>26.41</v>
+        <v>26.283</v>
       </c>
       <c r="Z127" t="n">
-        <v>53.75</v>
+        <v>53.854</v>
       </c>
       <c r="AA127" t="n">
-        <v>8.02</v>
+        <v>8.038</v>
       </c>
       <c r="AB127" t="n">
-        <v>22.38</v>
+        <v>22.533</v>
       </c>
       <c r="AC127" t="n">
-        <v>14.31</v>
+        <v>14.061</v>
       </c>
       <c r="AD127" t="n">
-        <v>18.58</v>
+        <v>18.323</v>
       </c>
       <c r="AE127" t="n">
-        <v>7.96</v>
+        <v>8.048</v>
       </c>
       <c r="AF127" t="n">
-        <v>19.58</v>
+        <v>19.506</v>
       </c>
       <c r="AG127" t="n">
-        <v>15.34</v>
+        <v>15.205</v>
       </c>
       <c r="AH127" t="n">
-        <v>7.1</v>
+        <v>7.001</v>
       </c>
       <c r="AI127" t="n">
         <v>2</v>
       </c>
       <c r="AJ127" t="n">
-        <v>17.62</v>
+        <v>17.766</v>
       </c>
       <c r="AK127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL127" t="n">
         <v>-1.2</v>
-      </c>
-      <c r="AL127" t="n">
-        <v>-2.5</v>
       </c>
     </row>
     <row r="128">
@@ -15746,22 +15746,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F128" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G128" t="b">
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>2038.996</v>
+        <v>2040.699</v>
       </c>
       <c r="I128" t="n">
-        <v>2.2111</v>
+        <v>1.9908</v>
       </c>
       <c r="J128" t="n">
-        <v>1718</v>
+        <v>1704.9</v>
       </c>
       <c r="K128" t="n">
         <v>6</v>
@@ -15782,70 +15782,70 @@
         <v>6</v>
       </c>
       <c r="Q128" t="n">
-        <v>118.901</v>
+        <v>119.647</v>
       </c>
       <c r="R128" t="n">
-        <v>95.73399999999999</v>
+        <v>95.52800000000001</v>
       </c>
       <c r="S128" t="n">
-        <v>23.167</v>
+        <v>24.119</v>
       </c>
       <c r="T128" t="n">
-        <v>0.32166</v>
+        <v>0.32421</v>
       </c>
       <c r="U128" t="n">
-        <v>0.14689</v>
+        <v>0.14659</v>
       </c>
       <c r="V128" t="n">
-        <v>81.78</v>
+        <v>82.73</v>
       </c>
       <c r="W128" t="n">
-        <v>65.28</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="X128" t="n">
-        <v>0.7879</v>
+        <v>0.8015</v>
       </c>
       <c r="Y128" t="n">
-        <v>29.191</v>
+        <v>29.492</v>
       </c>
       <c r="Z128" t="n">
-        <v>60.281</v>
+        <v>60.655</v>
       </c>
       <c r="AA128" t="n">
-        <v>9.127000000000001</v>
+        <v>9.157</v>
       </c>
       <c r="AB128" t="n">
-        <v>23.734</v>
+        <v>23.688</v>
       </c>
       <c r="AC128" t="n">
-        <v>13.63</v>
+        <v>13.966</v>
       </c>
       <c r="AD128" t="n">
-        <v>20.256</v>
+        <v>20.59</v>
       </c>
       <c r="AE128" t="n">
-        <v>10.71</v>
+        <v>10.938</v>
       </c>
       <c r="AF128" t="n">
-        <v>22.618</v>
+        <v>22.731</v>
       </c>
       <c r="AG128" t="n">
-        <v>17.122</v>
+        <v>17.392</v>
       </c>
       <c r="AH128" t="n">
-        <v>8.904999999999999</v>
+        <v>8.914999999999999</v>
       </c>
       <c r="AI128" t="n">
-        <v>2.7</v>
+        <v>2.788</v>
       </c>
       <c r="AJ128" t="n">
-        <v>15.883</v>
+        <v>15.922</v>
       </c>
       <c r="AK128" t="n">
-        <v>14.8</v>
+        <v>24.8</v>
       </c>
       <c r="AL128" t="n">
-        <v>9.199999999999999</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="129">
@@ -16586,22 +16586,22 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F135" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G135" t="b">
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>1973.656</v>
+        <v>1979.25</v>
       </c>
       <c r="I135" t="n">
-        <v>10.346</v>
+        <v>9.864800000000001</v>
       </c>
       <c r="J135" t="n">
-        <v>1791.1</v>
+        <v>1780.1</v>
       </c>
       <c r="K135" t="n">
         <v>21</v>
@@ -16622,70 +16622,70 @@
         <v>21</v>
       </c>
       <c r="Q135" t="n">
-        <v>109.902</v>
+        <v>109.767</v>
       </c>
       <c r="R135" t="n">
-        <v>101.514</v>
+        <v>100.723</v>
       </c>
       <c r="S135" t="n">
-        <v>8.388999999999999</v>
+        <v>9.044</v>
       </c>
       <c r="T135" t="n">
-        <v>0.25561</v>
+        <v>0.25343</v>
       </c>
       <c r="U135" t="n">
-        <v>0.15124</v>
+        <v>0.14997</v>
       </c>
       <c r="V135" t="n">
-        <v>75.3</v>
+        <v>75.33</v>
       </c>
       <c r="W135" t="n">
-        <v>69.39</v>
+        <v>69.02</v>
       </c>
       <c r="X135" t="n">
-        <v>0.6888</v>
+        <v>0.7091</v>
       </c>
       <c r="Y135" t="n">
-        <v>26.608</v>
+        <v>26.727</v>
       </c>
       <c r="Z135" t="n">
-        <v>59.007</v>
+        <v>59.269</v>
       </c>
       <c r="AA135" t="n">
-        <v>7.359</v>
+        <v>7.229</v>
       </c>
       <c r="AB135" t="n">
-        <v>21.083</v>
+        <v>20.978</v>
       </c>
       <c r="AC135" t="n">
-        <v>14.725</v>
+        <v>14.647</v>
       </c>
       <c r="AD135" t="n">
-        <v>19.228</v>
+        <v>19.033</v>
       </c>
       <c r="AE135" t="n">
-        <v>9.49</v>
+        <v>9.446999999999999</v>
       </c>
       <c r="AF135" t="n">
-        <v>27.48</v>
+        <v>27.684</v>
       </c>
       <c r="AG135" t="n">
-        <v>14.199</v>
+        <v>14.022</v>
       </c>
       <c r="AH135" t="n">
-        <v>5.456</v>
+        <v>5.465</v>
       </c>
       <c r="AI135" t="n">
-        <v>5.684</v>
+        <v>5.658</v>
       </c>
       <c r="AJ135" t="n">
-        <v>14.414</v>
+        <v>14.436</v>
       </c>
       <c r="AK135" t="n">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
       <c r="AL135" t="n">
-        <v>-3.6</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="136">
@@ -17066,22 +17066,22 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F139" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G139" t="b">
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>1886.896</v>
+        <v>1905.506</v>
       </c>
       <c r="I139" t="n">
-        <v>4.7611</v>
+        <v>4.5369</v>
       </c>
       <c r="J139" t="n">
-        <v>1734.8</v>
+        <v>1734</v>
       </c>
       <c r="K139" t="n">
         <v>28</v>
@@ -17102,70 +17102,70 @@
         <v>28</v>
       </c>
       <c r="Q139" t="n">
-        <v>115.762</v>
+        <v>116.168</v>
       </c>
       <c r="R139" t="n">
-        <v>106.053</v>
+        <v>106.38</v>
       </c>
       <c r="S139" t="n">
-        <v>9.709</v>
+        <v>9.788</v>
       </c>
       <c r="T139" t="n">
-        <v>0.31063</v>
+        <v>0.30777</v>
       </c>
       <c r="U139" t="n">
-        <v>0.14646</v>
+        <v>0.14633</v>
       </c>
       <c r="V139" t="n">
-        <v>80.59999999999999</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="W139" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="X139" t="n">
-        <v>0.6119</v>
+        <v>0.6318</v>
       </c>
       <c r="Y139" t="n">
-        <v>27.993</v>
+        <v>28.205</v>
       </c>
       <c r="Z139" t="n">
-        <v>60.486</v>
+        <v>60.593</v>
       </c>
       <c r="AA139" t="n">
-        <v>8.029999999999999</v>
+        <v>8.131</v>
       </c>
       <c r="AB139" t="n">
-        <v>23.466</v>
+        <v>23.638</v>
       </c>
       <c r="AC139" t="n">
-        <v>16.408</v>
+        <v>16.359</v>
       </c>
       <c r="AD139" t="n">
-        <v>22.652</v>
+        <v>22.614</v>
       </c>
       <c r="AE139" t="n">
-        <v>11.001</v>
+        <v>10.954</v>
       </c>
       <c r="AF139" t="n">
-        <v>24.38</v>
+        <v>24.656</v>
       </c>
       <c r="AG139" t="n">
-        <v>15.702</v>
+        <v>15.885</v>
       </c>
       <c r="AH139" t="n">
-        <v>7.106</v>
+        <v>7.011</v>
       </c>
       <c r="AI139" t="n">
-        <v>4.204</v>
+        <v>4.458</v>
       </c>
       <c r="AJ139" t="n">
-        <v>18.464</v>
+        <v>18.359</v>
       </c>
       <c r="AK139" t="n">
-        <v>-3</v>
+        <v>0.2</v>
       </c>
       <c r="AL139" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="140">
@@ -18026,22 +18026,22 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F147" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G147" t="b">
         <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>1418.21</v>
+        <v>1417.828</v>
       </c>
       <c r="I147" t="n">
-        <v>2.3581</v>
+        <v>2.3176</v>
       </c>
       <c r="J147" t="n">
-        <v>1378.8</v>
+        <v>1411.9</v>
       </c>
       <c r="K147" t="n">
         <v>216</v>
@@ -18062,70 +18062,70 @@
         <v>198</v>
       </c>
       <c r="Q147" t="n">
-        <v>109.383</v>
+        <v>108.226</v>
       </c>
       <c r="R147" t="n">
-        <v>104.38</v>
+        <v>105.253</v>
       </c>
       <c r="S147" t="n">
-        <v>5.003</v>
+        <v>2.973</v>
       </c>
       <c r="T147" t="n">
-        <v>0.31186</v>
+        <v>0.31587</v>
       </c>
       <c r="U147" t="n">
-        <v>0.18305</v>
+        <v>0.18279</v>
       </c>
       <c r="V147" t="n">
-        <v>74.13</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="W147" t="n">
-        <v>71.11</v>
+        <v>71.89</v>
       </c>
       <c r="X147" t="n">
-        <v>0.7086</v>
+        <v>0.6797</v>
       </c>
       <c r="Y147" t="n">
-        <v>27.456</v>
+        <v>27.24</v>
       </c>
       <c r="Z147" t="n">
-        <v>57.041</v>
+        <v>57.492</v>
       </c>
       <c r="AA147" t="n">
-        <v>5.962</v>
+        <v>6.046</v>
       </c>
       <c r="AB147" t="n">
-        <v>16.459</v>
+        <v>16.917</v>
       </c>
       <c r="AC147" t="n">
-        <v>13.261</v>
+        <v>12.967</v>
       </c>
       <c r="AD147" t="n">
-        <v>19.909</v>
+        <v>19.46</v>
       </c>
       <c r="AE147" t="n">
-        <v>10.4</v>
+        <v>10.499</v>
       </c>
       <c r="AF147" t="n">
-        <v>22.551</v>
+        <v>22.37</v>
       </c>
       <c r="AG147" t="n">
-        <v>13.669</v>
+        <v>13.697</v>
       </c>
       <c r="AH147" t="n">
-        <v>7.816</v>
+        <v>7.756</v>
       </c>
       <c r="AI147" t="n">
-        <v>5.379</v>
+        <v>5.368</v>
       </c>
       <c r="AJ147" t="n">
-        <v>17.593</v>
+        <v>17.78</v>
       </c>
       <c r="AK147" t="n">
-        <v>10.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL147" t="n">
-        <v>7.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="148">
@@ -20426,22 +20426,22 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F167" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G167" t="b">
         <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>1772.273</v>
+        <v>1794.728</v>
       </c>
       <c r="I167" t="n">
-        <v>11.776</v>
+        <v>11.4257</v>
       </c>
       <c r="J167" t="n">
-        <v>1635.9</v>
+        <v>1636.7</v>
       </c>
       <c r="K167" t="n">
         <v>31</v>
@@ -20462,70 +20462,70 @@
         <v>32</v>
       </c>
       <c r="Q167" t="n">
-        <v>117.066</v>
+        <v>117.437</v>
       </c>
       <c r="R167" t="n">
-        <v>102.955</v>
+        <v>102.471</v>
       </c>
       <c r="S167" t="n">
-        <v>14.111</v>
+        <v>14.966</v>
       </c>
       <c r="T167" t="n">
-        <v>0.30957</v>
+        <v>0.31068</v>
       </c>
       <c r="U167" t="n">
-        <v>0.15694</v>
+        <v>0.15663</v>
       </c>
       <c r="V167" t="n">
-        <v>81.70999999999999</v>
+        <v>81.86</v>
       </c>
       <c r="W167" t="n">
-        <v>71.33</v>
+        <v>70.97</v>
       </c>
       <c r="X167" t="n">
-        <v>0.7487</v>
+        <v>0.7673</v>
       </c>
       <c r="Y167" t="n">
-        <v>29.906</v>
+        <v>29.84</v>
       </c>
       <c r="Z167" t="n">
-        <v>59.815</v>
+        <v>59.855</v>
       </c>
       <c r="AA167" t="n">
-        <v>6.546</v>
+        <v>6.753</v>
       </c>
       <c r="AB167" t="n">
-        <v>18.952</v>
+        <v>19.142</v>
       </c>
       <c r="AC167" t="n">
-        <v>15.348</v>
+        <v>15.429</v>
       </c>
       <c r="AD167" t="n">
-        <v>22.337</v>
+        <v>22.687</v>
       </c>
       <c r="AE167" t="n">
-        <v>10.827</v>
+        <v>11.055</v>
       </c>
       <c r="AF167" t="n">
-        <v>24.038</v>
+        <v>24.356</v>
       </c>
       <c r="AG167" t="n">
-        <v>15.973</v>
+        <v>16.207</v>
       </c>
       <c r="AH167" t="n">
-        <v>7.857</v>
+        <v>7.844</v>
       </c>
       <c r="AI167" t="n">
-        <v>3.389</v>
+        <v>3.338</v>
       </c>
       <c r="AJ167" t="n">
-        <v>15.461</v>
+        <v>15.476</v>
       </c>
       <c r="AK167" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="AL167" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="168">
@@ -20546,22 +20546,22 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F168" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G168" t="b">
         <v>1</v>
       </c>
       <c r="H168" t="n">
-        <v>1780.382</v>
+        <v>1762.633</v>
       </c>
       <c r="I168" t="n">
-        <v>8.9497</v>
+        <v>8.696899999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>1429.2</v>
+        <v>1434.9</v>
       </c>
       <c r="K168" t="n">
         <v>93</v>
@@ -20582,70 +20582,70 @@
         <v>64</v>
       </c>
       <c r="Q168" t="n">
-        <v>121.342</v>
+        <v>119.936</v>
       </c>
       <c r="R168" t="n">
-        <v>106.311</v>
+        <v>106.804</v>
       </c>
       <c r="S168" t="n">
-        <v>15.031</v>
+        <v>13.132</v>
       </c>
       <c r="T168" t="n">
-        <v>0.22217</v>
+        <v>0.22513</v>
       </c>
       <c r="U168" t="n">
-        <v>0.1392</v>
+        <v>0.14135</v>
       </c>
       <c r="V168" t="n">
-        <v>87.28</v>
+        <v>86.06</v>
       </c>
       <c r="W168" t="n">
-        <v>76.45</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="X168" t="n">
-        <v>0.9669</v>
+        <v>0.9295</v>
       </c>
       <c r="Y168" t="n">
-        <v>30.073</v>
+        <v>29.641</v>
       </c>
       <c r="Z168" t="n">
-        <v>59.207</v>
+        <v>58.968</v>
       </c>
       <c r="AA168" t="n">
-        <v>9.337</v>
+        <v>9.276</v>
       </c>
       <c r="AB168" t="n">
-        <v>25.403</v>
+        <v>25.571</v>
       </c>
       <c r="AC168" t="n">
-        <v>17.528</v>
+        <v>17.314</v>
       </c>
       <c r="AD168" t="n">
-        <v>23.276</v>
+        <v>22.974</v>
       </c>
       <c r="AE168" t="n">
-        <v>7.597</v>
+        <v>7.583</v>
       </c>
       <c r="AF168" t="n">
-        <v>25.648</v>
+        <v>25.333</v>
       </c>
       <c r="AG168" t="n">
-        <v>15.066</v>
+        <v>14.795</v>
       </c>
       <c r="AH168" t="n">
-        <v>6.913</v>
+        <v>6.974</v>
       </c>
       <c r="AI168" t="n">
-        <v>2.979</v>
+        <v>3</v>
       </c>
       <c r="AJ168" t="n">
-        <v>16.709</v>
+        <v>16.596</v>
       </c>
       <c r="AK168" t="n">
-        <v>2.4</v>
+        <v>-2.4</v>
       </c>
       <c r="AL168" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="169">
@@ -21266,22 +21266,22 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F174" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G174" t="b">
         <v>1</v>
       </c>
       <c r="H174" t="n">
-        <v>1747.812</v>
+        <v>1725.357</v>
       </c>
       <c r="I174" t="n">
-        <v>-1.7576</v>
+        <v>-1.6662</v>
       </c>
       <c r="J174" t="n">
-        <v>1658.3</v>
+        <v>1660.3</v>
       </c>
       <c r="K174" t="n">
         <v>52</v>
@@ -21302,70 +21302,70 @@
         <v>58</v>
       </c>
       <c r="Q174" t="n">
-        <v>114.923</v>
+        <v>114.338</v>
       </c>
       <c r="R174" t="n">
-        <v>109.478</v>
+        <v>109.815</v>
       </c>
       <c r="S174" t="n">
-        <v>5.446</v>
+        <v>4.523</v>
       </c>
       <c r="T174" t="n">
-        <v>0.29962</v>
+        <v>0.29735</v>
       </c>
       <c r="U174" t="n">
-        <v>0.16854</v>
+        <v>0.16754</v>
       </c>
       <c r="V174" t="n">
-        <v>79.56</v>
+        <v>79.09</v>
       </c>
       <c r="W174" t="n">
-        <v>75.38</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="X174" t="n">
-        <v>0.6171</v>
+        <v>0.599</v>
       </c>
       <c r="Y174" t="n">
-        <v>27.957</v>
+        <v>27.637</v>
       </c>
       <c r="Z174" t="n">
-        <v>56.944</v>
+        <v>56.97</v>
       </c>
       <c r="AA174" t="n">
-        <v>7.203</v>
+        <v>7.335</v>
       </c>
       <c r="AB174" t="n">
-        <v>20.784</v>
+        <v>21.082</v>
       </c>
       <c r="AC174" t="n">
-        <v>16.704</v>
+        <v>16.659</v>
       </c>
       <c r="AD174" t="n">
-        <v>24.173</v>
+        <v>23.93</v>
       </c>
       <c r="AE174" t="n">
-        <v>10.116</v>
+        <v>10.025</v>
       </c>
       <c r="AF174" t="n">
-        <v>22.777</v>
+        <v>22.82</v>
       </c>
       <c r="AG174" t="n">
-        <v>14.421</v>
+        <v>14.443</v>
       </c>
       <c r="AH174" t="n">
-        <v>6.748</v>
+        <v>6.647</v>
       </c>
       <c r="AI174" t="n">
-        <v>3.755</v>
+        <v>3.742</v>
       </c>
       <c r="AJ174" t="n">
-        <v>17.742</v>
+        <v>17.826</v>
       </c>
       <c r="AK174" t="n">
-        <v>0.4</v>
+        <v>-3.2</v>
       </c>
       <c r="AL174" t="n">
-        <v>-0.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="175">
@@ -25706,22 +25706,22 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F211" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G211" t="b">
         <v>1</v>
       </c>
       <c r="H211" t="n">
-        <v>1573.879</v>
+        <v>1569.56</v>
       </c>
       <c r="I211" t="n">
-        <v>-3.696</v>
+        <v>-3.4213</v>
       </c>
       <c r="J211" t="n">
-        <v>1515.8</v>
+        <v>1532.4</v>
       </c>
       <c r="K211" t="n">
         <v>72</v>
@@ -25742,70 +25742,70 @@
         <v>72</v>
       </c>
       <c r="Q211" t="n">
-        <v>108.741</v>
+        <v>107.639</v>
       </c>
       <c r="R211" t="n">
-        <v>97.495</v>
+        <v>98.39400000000001</v>
       </c>
       <c r="S211" t="n">
-        <v>11.246</v>
+        <v>9.244999999999999</v>
       </c>
       <c r="T211" t="n">
-        <v>0.22502</v>
+        <v>0.22193</v>
       </c>
       <c r="U211" t="n">
-        <v>0.13537</v>
+        <v>0.13436</v>
       </c>
       <c r="V211" t="n">
-        <v>69.18000000000001</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="W211" t="n">
-        <v>62.11</v>
+        <v>62.66</v>
       </c>
       <c r="X211" t="n">
-        <v>0.6498</v>
+        <v>0.6239</v>
       </c>
       <c r="Y211" t="n">
-        <v>25.162</v>
+        <v>25.035</v>
       </c>
       <c r="Z211" t="n">
-        <v>55.172</v>
+        <v>55.185</v>
       </c>
       <c r="AA211" t="n">
-        <v>7.284</v>
+        <v>7.141</v>
       </c>
       <c r="AB211" t="n">
-        <v>21.815</v>
+        <v>21.572</v>
       </c>
       <c r="AC211" t="n">
-        <v>10.255</v>
+        <v>10.112</v>
       </c>
       <c r="AD211" t="n">
-        <v>14.486</v>
+        <v>14.439</v>
       </c>
       <c r="AE211" t="n">
-        <v>6.426</v>
+        <v>6.369</v>
       </c>
       <c r="AF211" t="n">
-        <v>22.431</v>
+        <v>22.546</v>
       </c>
       <c r="AG211" t="n">
-        <v>13.992</v>
+        <v>13.786</v>
       </c>
       <c r="AH211" t="n">
-        <v>6.401</v>
+        <v>6.397</v>
       </c>
       <c r="AI211" t="n">
-        <v>2.918</v>
+        <v>2.908</v>
       </c>
       <c r="AJ211" t="n">
-        <v>15.138</v>
+        <v>15.249</v>
       </c>
       <c r="AK211" t="n">
-        <v>14.4</v>
+        <v>4.8</v>
       </c>
       <c r="AL211" t="n">
-        <v>10.8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="212">
@@ -28106,22 +28106,22 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F231" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G231" t="b">
         <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>1272.073</v>
+        <v>1271.561</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4587</v>
+        <v>-0.3388</v>
       </c>
       <c r="J231" t="n">
-        <v>1381.2</v>
+        <v>1406.5</v>
       </c>
       <c r="K231" t="n">
         <v>288</v>
@@ -28142,70 +28142,70 @@
         <v>300</v>
       </c>
       <c r="Q231" t="n">
-        <v>104.266</v>
+        <v>103.391</v>
       </c>
       <c r="R231" t="n">
-        <v>106.277</v>
+        <v>108.666</v>
       </c>
       <c r="S231" t="n">
-        <v>-2.011</v>
+        <v>-5.275</v>
       </c>
       <c r="T231" t="n">
-        <v>0.28965</v>
+        <v>0.29509</v>
       </c>
       <c r="U231" t="n">
-        <v>0.15843</v>
+        <v>0.15573</v>
       </c>
       <c r="V231" t="n">
-        <v>75.41</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="W231" t="n">
-        <v>77.64</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="X231" t="n">
-        <v>0.4727</v>
+        <v>0.4514</v>
       </c>
       <c r="Y231" t="n">
-        <v>24.784</v>
+        <v>24.523</v>
       </c>
       <c r="Z231" t="n">
-        <v>59.52</v>
+        <v>59.66</v>
       </c>
       <c r="AA231" t="n">
-        <v>5.876</v>
+        <v>5.88</v>
       </c>
       <c r="AB231" t="n">
-        <v>18.479</v>
+        <v>18.569</v>
       </c>
       <c r="AC231" t="n">
-        <v>18.6</v>
+        <v>18.551</v>
       </c>
       <c r="AD231" t="n">
-        <v>24.965</v>
+        <v>24.764</v>
       </c>
       <c r="AE231" t="n">
-        <v>9.502000000000001</v>
+        <v>9.451000000000001</v>
       </c>
       <c r="AF231" t="n">
-        <v>22.27</v>
+        <v>21.833</v>
       </c>
       <c r="AG231" t="n">
-        <v>11.124</v>
+        <v>10.935</v>
       </c>
       <c r="AH231" t="n">
-        <v>6.954</v>
+        <v>6.822</v>
       </c>
       <c r="AI231" t="n">
-        <v>4.66</v>
+        <v>4.625</v>
       </c>
       <c r="AJ231" t="n">
-        <v>19.406</v>
+        <v>19.34</v>
       </c>
       <c r="AK231" t="n">
-        <v>10</v>
+        <v>-3.6</v>
       </c>
       <c r="AL231" t="n">
-        <v>9.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
@@ -28586,22 +28586,22 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F235" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G235" t="b">
         <v>1</v>
       </c>
       <c r="H235" t="n">
-        <v>2010.028</v>
+        <v>2011.512</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.7024</v>
+        <v>-0.6772</v>
       </c>
       <c r="J235" t="n">
-        <v>1769.7</v>
+        <v>1753.9</v>
       </c>
       <c r="K235" t="n">
         <v>8</v>
@@ -28622,70 +28622,70 @@
         <v>9</v>
       </c>
       <c r="Q235" t="n">
-        <v>124.873</v>
+        <v>125.909</v>
       </c>
       <c r="R235" t="n">
-        <v>107.488</v>
+        <v>107.355</v>
       </c>
       <c r="S235" t="n">
-        <v>17.385</v>
+        <v>18.555</v>
       </c>
       <c r="T235" t="n">
-        <v>0.31102</v>
+        <v>0.31279</v>
       </c>
       <c r="U235" t="n">
-        <v>0.13371</v>
+        <v>0.13549</v>
       </c>
       <c r="V235" t="n">
-        <v>81.64</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="W235" t="n">
-        <v>70.16</v>
+        <v>70.17</v>
       </c>
       <c r="X235" t="n">
-        <v>0.7734</v>
+        <v>0.7796</v>
       </c>
       <c r="Y235" t="n">
-        <v>29.717</v>
+        <v>30.117</v>
       </c>
       <c r="Z235" t="n">
-        <v>60.092</v>
+        <v>60.234</v>
       </c>
       <c r="AA235" t="n">
-        <v>9.266</v>
+        <v>9.454000000000001</v>
       </c>
       <c r="AB235" t="n">
-        <v>24.538</v>
+        <v>24.523</v>
       </c>
       <c r="AC235" t="n">
-        <v>11.996</v>
+        <v>11.912</v>
       </c>
       <c r="AD235" t="n">
-        <v>16.196</v>
+        <v>16.133</v>
       </c>
       <c r="AE235" t="n">
-        <v>10.547</v>
+        <v>10.702</v>
       </c>
       <c r="AF235" t="n">
-        <v>22.963</v>
+        <v>23.08</v>
       </c>
       <c r="AG235" t="n">
-        <v>19.475</v>
+        <v>19.674</v>
       </c>
       <c r="AH235" t="n">
-        <v>5.484</v>
+        <v>5.496</v>
       </c>
       <c r="AI235" t="n">
-        <v>2.66</v>
+        <v>2.777</v>
       </c>
       <c r="AJ235" t="n">
-        <v>14.998</v>
+        <v>14.901</v>
       </c>
       <c r="AK235" t="n">
-        <v>8</v>
+        <v>15.4</v>
       </c>
       <c r="AL235" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="236">
@@ -30986,22 +30986,22 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F255" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G255" t="b">
         <v>1</v>
       </c>
       <c r="H255" t="n">
-        <v>1782.784</v>
+        <v>1764.174</v>
       </c>
       <c r="I255" t="n">
-        <v>0.0374</v>
+        <v>0.252</v>
       </c>
       <c r="J255" t="n">
-        <v>1596.2</v>
+        <v>1603.2</v>
       </c>
       <c r="K255" t="n">
         <v>35</v>
@@ -31022,70 +31022,70 @@
         <v>40</v>
       </c>
       <c r="Q255" t="n">
-        <v>117.619</v>
+        <v>117.526</v>
       </c>
       <c r="R255" t="n">
-        <v>104.107</v>
+        <v>104.506</v>
       </c>
       <c r="S255" t="n">
-        <v>13.513</v>
+        <v>13.02</v>
       </c>
       <c r="T255" t="n">
-        <v>0.35044</v>
+        <v>0.34803</v>
       </c>
       <c r="U255" t="n">
-        <v>0.14983</v>
+        <v>0.14781</v>
       </c>
       <c r="V255" t="n">
-        <v>82.72</v>
+        <v>82.89</v>
       </c>
       <c r="W255" t="n">
-        <v>73.08</v>
+        <v>73.62</v>
       </c>
       <c r="X255" t="n">
-        <v>0.7512</v>
+        <v>0.7295</v>
       </c>
       <c r="Y255" t="n">
-        <v>29.996</v>
+        <v>30.029</v>
       </c>
       <c r="Z255" t="n">
-        <v>64.364</v>
+        <v>64.654</v>
       </c>
       <c r="AA255" t="n">
-        <v>9.962</v>
+        <v>10.045</v>
       </c>
       <c r="AB255" t="n">
-        <v>28.922</v>
+        <v>29.031</v>
       </c>
       <c r="AC255" t="n">
-        <v>12.619</v>
+        <v>12.642</v>
       </c>
       <c r="AD255" t="n">
-        <v>16.714</v>
+        <v>16.648</v>
       </c>
       <c r="AE255" t="n">
-        <v>11.947</v>
+        <v>11.883</v>
       </c>
       <c r="AF255" t="n">
-        <v>21.511</v>
+        <v>21.681</v>
       </c>
       <c r="AG255" t="n">
-        <v>16.636</v>
+        <v>16.679</v>
       </c>
       <c r="AH255" t="n">
-        <v>8.653</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="AI255" t="n">
-        <v>3.614</v>
+        <v>3.576</v>
       </c>
       <c r="AJ255" t="n">
-        <v>19.519</v>
+        <v>19.533</v>
       </c>
       <c r="AK255" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="AL255" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="256">
@@ -33146,22 +33146,22 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F273" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G273" t="b">
         <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>1984.929</v>
+        <v>1989.246</v>
       </c>
       <c r="I273" t="n">
-        <v>5.6609</v>
+        <v>5.7241</v>
       </c>
       <c r="J273" t="n">
-        <v>1691.6</v>
+        <v>1684.5</v>
       </c>
       <c r="K273" t="n">
         <v>17</v>
@@ -33182,70 +33182,70 @@
         <v>16</v>
       </c>
       <c r="Q273" t="n">
-        <v>113.974</v>
+        <v>114.409</v>
       </c>
       <c r="R273" t="n">
-        <v>98.164</v>
+        <v>97.80200000000001</v>
       </c>
       <c r="S273" t="n">
-        <v>15.81</v>
+        <v>16.607</v>
       </c>
       <c r="T273" t="n">
-        <v>0.3224</v>
+        <v>0.32084</v>
       </c>
       <c r="U273" t="n">
-        <v>0.14223</v>
+        <v>0.14183</v>
       </c>
       <c r="V273" t="n">
-        <v>81.48</v>
+        <v>81.47</v>
       </c>
       <c r="W273" t="n">
-        <v>69.83</v>
+        <v>69.36</v>
       </c>
       <c r="X273" t="n">
-        <v>0.8249</v>
+        <v>0.8298</v>
       </c>
       <c r="Y273" t="n">
-        <v>27.934</v>
+        <v>27.908</v>
       </c>
       <c r="Z273" t="n">
-        <v>61.515</v>
+        <v>61.396</v>
       </c>
       <c r="AA273" t="n">
-        <v>6.897</v>
+        <v>7.022</v>
       </c>
       <c r="AB273" t="n">
-        <v>20.788</v>
+        <v>21.087</v>
       </c>
       <c r="AC273" t="n">
-        <v>18.719</v>
+        <v>18.63</v>
       </c>
       <c r="AD273" t="n">
-        <v>25.725</v>
+        <v>25.659</v>
       </c>
       <c r="AE273" t="n">
-        <v>11.589</v>
+        <v>11.631</v>
       </c>
       <c r="AF273" t="n">
-        <v>24.568</v>
+        <v>24.889</v>
       </c>
       <c r="AG273" t="n">
-        <v>16.239</v>
+        <v>16.148</v>
       </c>
       <c r="AH273" t="n">
-        <v>7.928</v>
+        <v>7.736</v>
       </c>
       <c r="AI273" t="n">
-        <v>4.907</v>
+        <v>4.922</v>
       </c>
       <c r="AJ273" t="n">
-        <v>17.292</v>
+        <v>17.105</v>
       </c>
       <c r="AK273" t="n">
-        <v>10.6</v>
+        <v>15.2</v>
       </c>
       <c r="AL273" t="n">
-        <v>9.800000000000001</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="274">
@@ -34586,19 +34586,19 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F285" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G285" t="b">
         <v>1</v>
       </c>
       <c r="H285" t="n">
-        <v>1897.088</v>
+        <v>1914.838</v>
       </c>
       <c r="I285" t="n">
-        <v>-1.4465</v>
+        <v>-1.3934</v>
       </c>
       <c r="J285" t="n">
         <v>1716.9</v>
@@ -34622,70 +34622,70 @@
         <v>20</v>
       </c>
       <c r="Q285" t="n">
-        <v>116.86</v>
+        <v>116.955</v>
       </c>
       <c r="R285" t="n">
-        <v>102.568</v>
+        <v>101.617</v>
       </c>
       <c r="S285" t="n">
-        <v>14.292</v>
+        <v>15.338</v>
       </c>
       <c r="T285" t="n">
-        <v>0.36001</v>
+        <v>0.35639</v>
       </c>
       <c r="U285" t="n">
-        <v>0.16434</v>
+        <v>0.16761</v>
       </c>
       <c r="V285" t="n">
-        <v>79.31999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="W285" t="n">
-        <v>69.43000000000001</v>
+        <v>68.83</v>
       </c>
       <c r="X285" t="n">
-        <v>0.6589</v>
+        <v>0.68</v>
       </c>
       <c r="Y285" t="n">
-        <v>28.223</v>
+        <v>28.382</v>
       </c>
       <c r="Z285" t="n">
-        <v>61.155</v>
+        <v>61.036</v>
       </c>
       <c r="AA285" t="n">
-        <v>6.456</v>
+        <v>6.585</v>
       </c>
       <c r="AB285" t="n">
-        <v>19.366</v>
+        <v>19.418</v>
       </c>
       <c r="AC285" t="n">
-        <v>16.419</v>
+        <v>16.047</v>
       </c>
       <c r="AD285" t="n">
-        <v>23.694</v>
+        <v>23.12</v>
       </c>
       <c r="AE285" t="n">
-        <v>14.854</v>
+        <v>14.687</v>
       </c>
       <c r="AF285" t="n">
-        <v>25.785</v>
+        <v>25.945</v>
       </c>
       <c r="AG285" t="n">
-        <v>16.852</v>
+        <v>16.993</v>
       </c>
       <c r="AH285" t="n">
-        <v>7.474</v>
+        <v>7.415</v>
       </c>
       <c r="AI285" t="n">
-        <v>3.576</v>
+        <v>3.542</v>
       </c>
       <c r="AJ285" t="n">
-        <v>17.927</v>
+        <v>17.724</v>
       </c>
       <c r="AK285" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="AL285" t="n">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="286">
@@ -34706,22 +34706,22 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F286" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G286" t="b">
         <v>1</v>
       </c>
       <c r="H286" t="n">
-        <v>1466.924</v>
+        <v>1465.222</v>
       </c>
       <c r="I286" t="n">
-        <v>3.3618</v>
+        <v>3.2842</v>
       </c>
       <c r="J286" t="n">
-        <v>1407.8</v>
+        <v>1433</v>
       </c>
       <c r="K286" t="n">
         <v>187</v>
@@ -34742,70 +34742,70 @@
         <v>172</v>
       </c>
       <c r="Q286" t="n">
-        <v>109.904</v>
+        <v>109.103</v>
       </c>
       <c r="R286" t="n">
-        <v>103.284</v>
+        <v>104.707</v>
       </c>
       <c r="S286" t="n">
-        <v>6.621</v>
+        <v>4.396</v>
       </c>
       <c r="T286" t="n">
-        <v>0.328</v>
+        <v>0.33012</v>
       </c>
       <c r="U286" t="n">
-        <v>0.15886</v>
+        <v>0.16077</v>
       </c>
       <c r="V286" t="n">
-        <v>78.18000000000001</v>
+        <v>77.91</v>
       </c>
       <c r="W286" t="n">
-        <v>73.88</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="X286" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="Y286" t="n">
-        <v>27.935</v>
+        <v>27.901</v>
       </c>
       <c r="Z286" t="n">
-        <v>62.106</v>
+        <v>62.186</v>
       </c>
       <c r="AA286" t="n">
-        <v>6.485</v>
+        <v>6.357</v>
       </c>
       <c r="AB286" t="n">
-        <v>19.086</v>
+        <v>19.113</v>
       </c>
       <c r="AC286" t="n">
-        <v>15.826</v>
+        <v>15.748</v>
       </c>
       <c r="AD286" t="n">
-        <v>20.735</v>
+        <v>20.721</v>
       </c>
       <c r="AE286" t="n">
-        <v>11.262</v>
+        <v>11.232</v>
       </c>
       <c r="AF286" t="n">
-        <v>22.847</v>
+        <v>22.601</v>
       </c>
       <c r="AG286" t="n">
-        <v>12.673</v>
+        <v>12.709</v>
       </c>
       <c r="AH286" t="n">
-        <v>9.012</v>
+        <v>8.993</v>
       </c>
       <c r="AI286" t="n">
-        <v>3.616</v>
+        <v>3.836</v>
       </c>
       <c r="AJ286" t="n">
-        <v>18.499</v>
+        <v>18.657</v>
       </c>
       <c r="AK286" t="n">
-        <v>19.8</v>
+        <v>7.6</v>
       </c>
       <c r="AL286" t="n">
-        <v>13.8</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="287">
@@ -35306,22 +35306,22 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F291" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G291" t="b">
         <v>1</v>
       </c>
       <c r="H291" t="n">
-        <v>2010.735</v>
+        <v>2018.552</v>
       </c>
       <c r="I291" t="n">
-        <v>9.579599999999999</v>
+        <v>8.9857</v>
       </c>
       <c r="J291" t="n">
-        <v>1772.3</v>
+        <v>1767</v>
       </c>
       <c r="K291" t="n">
         <v>20</v>
@@ -35342,70 +35342,70 @@
         <v>19</v>
       </c>
       <c r="Q291" t="n">
-        <v>117.198</v>
+        <v>118.539</v>
       </c>
       <c r="R291" t="n">
-        <v>106.696</v>
+        <v>106.753</v>
       </c>
       <c r="S291" t="n">
-        <v>10.501</v>
+        <v>11.786</v>
       </c>
       <c r="T291" t="n">
-        <v>0.28931</v>
+        <v>0.28763</v>
       </c>
       <c r="U291" t="n">
-        <v>0.155</v>
+        <v>0.15503</v>
       </c>
       <c r="V291" t="n">
-        <v>80.11</v>
+        <v>80.83</v>
       </c>
       <c r="W291" t="n">
-        <v>72.65000000000001</v>
+        <v>72.56</v>
       </c>
       <c r="X291" t="n">
-        <v>0.6801</v>
+        <v>0.7</v>
       </c>
       <c r="Y291" t="n">
-        <v>28.887</v>
+        <v>29.08</v>
       </c>
       <c r="Z291" t="n">
-        <v>60.977</v>
+        <v>60.71</v>
       </c>
       <c r="AA291" t="n">
-        <v>11.421</v>
+        <v>11.45</v>
       </c>
       <c r="AB291" t="n">
-        <v>28.851</v>
+        <v>28.61</v>
       </c>
       <c r="AC291" t="n">
-        <v>11.833</v>
+        <v>11.88</v>
       </c>
       <c r="AD291" t="n">
-        <v>16.628</v>
+        <v>16.75</v>
       </c>
       <c r="AE291" t="n">
-        <v>10.493</v>
+        <v>10.39</v>
       </c>
       <c r="AF291" t="n">
-        <v>24.642</v>
+        <v>24.58</v>
       </c>
       <c r="AG291" t="n">
-        <v>15.917</v>
+        <v>15.98</v>
       </c>
       <c r="AH291" t="n">
-        <v>5.867</v>
+        <v>5.97</v>
       </c>
       <c r="AI291" t="n">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="AJ291" t="n">
-        <v>16.442</v>
+        <v>16.45</v>
       </c>
       <c r="AK291" t="n">
-        <v>-3</v>
+        <v>-1.4</v>
       </c>
       <c r="AL291" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="292">
@@ -36866,22 +36866,22 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F304" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G304" t="b">
         <v>1</v>
       </c>
       <c r="H304" t="n">
-        <v>1828.635</v>
+        <v>1805.81</v>
       </c>
       <c r="I304" t="n">
-        <v>5.8051</v>
+        <v>5.3176</v>
       </c>
       <c r="J304" t="n">
-        <v>1712.7</v>
+        <v>1713.5</v>
       </c>
       <c r="K304" t="n">
         <v>54</v>
@@ -36902,70 +36902,70 @@
         <v>51</v>
       </c>
       <c r="Q304" t="n">
-        <v>112.997</v>
+        <v>112.743</v>
       </c>
       <c r="R304" t="n">
-        <v>110.03</v>
+        <v>109.749</v>
       </c>
       <c r="S304" t="n">
-        <v>2.967</v>
+        <v>2.994</v>
       </c>
       <c r="T304" t="n">
-        <v>0.31466</v>
+        <v>0.32046</v>
       </c>
       <c r="U304" t="n">
-        <v>0.15426</v>
+        <v>0.15757</v>
       </c>
       <c r="V304" t="n">
-        <v>80.73</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="W304" t="n">
-        <v>78.5</v>
+        <v>78.33</v>
       </c>
       <c r="X304" t="n">
-        <v>0.6492</v>
+        <v>0.63</v>
       </c>
       <c r="Y304" t="n">
-        <v>29.306</v>
+        <v>29.28</v>
       </c>
       <c r="Z304" t="n">
-        <v>63.031</v>
+        <v>63.39</v>
       </c>
       <c r="AA304" t="n">
-        <v>7.792</v>
+        <v>8.01</v>
       </c>
       <c r="AB304" t="n">
-        <v>21.68</v>
+        <v>22.1</v>
       </c>
       <c r="AC304" t="n">
-        <v>14.328</v>
+        <v>14</v>
       </c>
       <c r="AD304" t="n">
-        <v>19.39</v>
+        <v>19.3</v>
       </c>
       <c r="AE304" t="n">
-        <v>11.145</v>
+        <v>11.68</v>
       </c>
       <c r="AF304" t="n">
-        <v>23.526</v>
+        <v>23.71</v>
       </c>
       <c r="AG304" t="n">
-        <v>15.688</v>
+        <v>15.72</v>
       </c>
       <c r="AH304" t="n">
-        <v>5.638</v>
+        <v>5.55</v>
       </c>
       <c r="AI304" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AJ304" t="n">
-        <v>17.601</v>
+        <v>17.51</v>
       </c>
       <c r="AK304" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.4</v>
       </c>
       <c r="AL304" t="n">
-        <v>-4.5</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="305">
@@ -36986,22 +36986,22 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F305" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G305" t="b">
         <v>1</v>
       </c>
       <c r="H305" t="n">
-        <v>1874.227</v>
+        <v>1897.052</v>
       </c>
       <c r="I305" t="n">
-        <v>2.8463</v>
+        <v>2.9774</v>
       </c>
       <c r="J305" t="n">
-        <v>1706.3</v>
+        <v>1708.6</v>
       </c>
       <c r="K305" t="n">
         <v>27</v>
@@ -37022,70 +37022,70 @@
         <v>30</v>
       </c>
       <c r="Q305" t="n">
-        <v>117.179</v>
+        <v>116.926</v>
       </c>
       <c r="R305" t="n">
-        <v>107.51</v>
+        <v>107.231</v>
       </c>
       <c r="S305" t="n">
-        <v>9.669</v>
+        <v>9.695</v>
       </c>
       <c r="T305" t="n">
-        <v>0.30552</v>
+        <v>0.30733</v>
       </c>
       <c r="U305" t="n">
-        <v>0.13246</v>
+        <v>0.1316</v>
       </c>
       <c r="V305" t="n">
         <v>77.64</v>
       </c>
       <c r="W305" t="n">
-        <v>71.02</v>
+        <v>71</v>
       </c>
       <c r="X305" t="n">
-        <v>0.6712</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="Y305" t="n">
-        <v>27.393</v>
+        <v>27.397</v>
       </c>
       <c r="Z305" t="n">
-        <v>58.465</v>
+        <v>58.839</v>
       </c>
       <c r="AA305" t="n">
-        <v>8.045</v>
+        <v>7.957</v>
       </c>
       <c r="AB305" t="n">
-        <v>21.113</v>
+        <v>21.057</v>
       </c>
       <c r="AC305" t="n">
-        <v>14.955</v>
+        <v>14.9</v>
       </c>
       <c r="AD305" t="n">
-        <v>19.613</v>
+        <v>19.56</v>
       </c>
       <c r="AE305" t="n">
-        <v>9.468999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AF305" t="n">
-        <v>21.432</v>
+        <v>21.576</v>
       </c>
       <c r="AG305" t="n">
-        <v>16.565</v>
+        <v>16.332</v>
       </c>
       <c r="AH305" t="n">
-        <v>6.196</v>
+        <v>6.449</v>
       </c>
       <c r="AI305" t="n">
-        <v>2.942</v>
+        <v>3.158</v>
       </c>
       <c r="AJ305" t="n">
-        <v>16.887</v>
+        <v>16.872</v>
       </c>
       <c r="AK305" t="n">
-        <v>10.2</v>
+        <v>7</v>
       </c>
       <c r="AL305" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="306">
@@ -38426,22 +38426,22 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F317" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G317" t="b">
         <v>1</v>
       </c>
       <c r="H317" t="n">
-        <v>1897.511</v>
+        <v>1917.024</v>
       </c>
       <c r="I317" t="n">
-        <v>0.1736</v>
+        <v>0.2638</v>
       </c>
       <c r="J317" t="n">
-        <v>1611.4</v>
+        <v>1617</v>
       </c>
       <c r="K317" t="n">
         <v>30</v>
@@ -38462,70 +38462,70 @@
         <v>26</v>
       </c>
       <c r="Q317" t="n">
-        <v>119.564</v>
+        <v>119.887</v>
       </c>
       <c r="R317" t="n">
-        <v>103.487</v>
+        <v>103.861</v>
       </c>
       <c r="S317" t="n">
-        <v>16.077</v>
+        <v>16.026</v>
       </c>
       <c r="T317" t="n">
-        <v>0.30319</v>
+        <v>0.30557</v>
       </c>
       <c r="U317" t="n">
-        <v>0.14787</v>
+        <v>0.14772</v>
       </c>
       <c r="V317" t="n">
-        <v>81.64</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="W317" t="n">
-        <v>70.79000000000001</v>
+        <v>71.03</v>
       </c>
       <c r="X317" t="n">
-        <v>0.8194</v>
+        <v>0.8247</v>
       </c>
       <c r="Y317" t="n">
-        <v>28.736</v>
+        <v>28.701</v>
       </c>
       <c r="Z317" t="n">
-        <v>58.139</v>
+        <v>58.266</v>
       </c>
       <c r="AA317" t="n">
-        <v>8.287000000000001</v>
+        <v>8.506</v>
       </c>
       <c r="AB317" t="n">
-        <v>23.648</v>
+        <v>23.893</v>
       </c>
       <c r="AC317" t="n">
-        <v>15.817</v>
+        <v>15.526</v>
       </c>
       <c r="AD317" t="n">
-        <v>22.419</v>
+        <v>22.146</v>
       </c>
       <c r="AE317" t="n">
-        <v>9.676</v>
+        <v>9.679</v>
       </c>
       <c r="AF317" t="n">
-        <v>22.081</v>
+        <v>21.88</v>
       </c>
       <c r="AG317" t="n">
-        <v>17.188</v>
+        <v>17.14</v>
       </c>
       <c r="AH317" t="n">
-        <v>8.669</v>
+        <v>8.571</v>
       </c>
       <c r="AI317" t="n">
-        <v>2.88</v>
+        <v>2.776</v>
       </c>
       <c r="AJ317" t="n">
-        <v>18.963</v>
+        <v>19.042</v>
       </c>
       <c r="AK317" t="n">
-        <v>4.2</v>
+        <v>11.6</v>
       </c>
       <c r="AL317" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="318">
@@ -39266,22 +39266,22 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F324" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G324" t="b">
         <v>1</v>
       </c>
       <c r="H324" t="n">
-        <v>1806.305</v>
+        <v>1786.792</v>
       </c>
       <c r="I324" t="n">
-        <v>5.8793</v>
+        <v>5.5318</v>
       </c>
       <c r="J324" t="n">
-        <v>1641.5</v>
+        <v>1652</v>
       </c>
       <c r="K324" t="n">
         <v>33</v>
@@ -39302,70 +39302,70 @@
         <v>35</v>
       </c>
       <c r="Q324" t="n">
-        <v>114.594</v>
+        <v>114.709</v>
       </c>
       <c r="R324" t="n">
-        <v>104.935</v>
+        <v>105.725</v>
       </c>
       <c r="S324" t="n">
-        <v>9.659000000000001</v>
+        <v>8.984</v>
       </c>
       <c r="T324" t="n">
-        <v>0.31301</v>
+        <v>0.31015</v>
       </c>
       <c r="U324" t="n">
-        <v>0.14469</v>
+        <v>0.1437</v>
       </c>
       <c r="V324" t="n">
-        <v>77.04000000000001</v>
+        <v>77.11</v>
       </c>
       <c r="W324" t="n">
-        <v>70.84999999999999</v>
+        <v>71.37</v>
       </c>
       <c r="X324" t="n">
-        <v>0.7432</v>
+        <v>0.7212</v>
       </c>
       <c r="Y324" t="n">
-        <v>27.523</v>
+        <v>27.519</v>
       </c>
       <c r="Z324" t="n">
-        <v>59.681</v>
+        <v>59.353</v>
       </c>
       <c r="AA324" t="n">
-        <v>9.641</v>
+        <v>9.362</v>
       </c>
       <c r="AB324" t="n">
-        <v>26.937</v>
+        <v>26.577</v>
       </c>
       <c r="AC324" t="n">
-        <v>12.911</v>
+        <v>13.517</v>
       </c>
       <c r="AD324" t="n">
-        <v>18.685</v>
+        <v>19.383</v>
       </c>
       <c r="AE324" t="n">
-        <v>10.222</v>
+        <v>10.142</v>
       </c>
       <c r="AF324" t="n">
-        <v>22.147</v>
+        <v>22.321</v>
       </c>
       <c r="AG324" t="n">
-        <v>15.495</v>
+        <v>15.635</v>
       </c>
       <c r="AH324" t="n">
-        <v>7.274</v>
+        <v>7.185</v>
       </c>
       <c r="AI324" t="n">
-        <v>2.177</v>
+        <v>2.103</v>
       </c>
       <c r="AJ324" t="n">
-        <v>15.933</v>
+        <v>15.893</v>
       </c>
       <c r="AK324" t="n">
-        <v>-1</v>
+        <v>-4.8</v>
       </c>
       <c r="AL324" t="n">
-        <v>0.9</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="325">
@@ -39386,22 +39386,22 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F325" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G325" t="b">
         <v>1</v>
       </c>
       <c r="H325" t="n">
-        <v>1964.334</v>
+        <v>1966.747</v>
       </c>
       <c r="I325" t="n">
-        <v>12.2076</v>
+        <v>11.7947</v>
       </c>
       <c r="J325" t="n">
-        <v>1665.9</v>
+        <v>1654.9</v>
       </c>
       <c r="K325" t="n">
         <v>13</v>
@@ -39422,70 +39422,70 @@
         <v>12</v>
       </c>
       <c r="Q325" t="n">
-        <v>119.042</v>
+        <v>119.416</v>
       </c>
       <c r="R325" t="n">
-        <v>100.852</v>
+        <v>101.187</v>
       </c>
       <c r="S325" t="n">
-        <v>18.19</v>
+        <v>18.229</v>
       </c>
       <c r="T325" t="n">
-        <v>0.31535</v>
+        <v>0.31319</v>
       </c>
       <c r="U325" t="n">
-        <v>0.15437</v>
+        <v>0.15637</v>
       </c>
       <c r="V325" t="n">
-        <v>80.56</v>
+        <v>80.7</v>
       </c>
       <c r="W325" t="n">
-        <v>68.45999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="X325" t="n">
-        <v>0.8462</v>
+        <v>0.8582</v>
       </c>
       <c r="Y325" t="n">
-        <v>28.144</v>
+        <v>28.17</v>
       </c>
       <c r="Z325" t="n">
-        <v>60.77</v>
+        <v>60.58</v>
       </c>
       <c r="AA325" t="n">
-        <v>10.101</v>
+        <v>10.221</v>
       </c>
       <c r="AB325" t="n">
-        <v>27.998</v>
+        <v>27.957</v>
       </c>
       <c r="AC325" t="n">
-        <v>14.058</v>
+        <v>14.021</v>
       </c>
       <c r="AD325" t="n">
-        <v>19.297</v>
+        <v>19.133</v>
       </c>
       <c r="AE325" t="n">
-        <v>11.868</v>
+        <v>11.815</v>
       </c>
       <c r="AF325" t="n">
-        <v>25.406</v>
+        <v>25.568</v>
       </c>
       <c r="AG325" t="n">
-        <v>16.499</v>
+        <v>16.396</v>
       </c>
       <c r="AH325" t="n">
-        <v>6.473</v>
+        <v>6.411</v>
       </c>
       <c r="AI325" t="n">
-        <v>6.426</v>
+        <v>6.333</v>
       </c>
       <c r="AJ325" t="n">
-        <v>17.854</v>
+        <v>17.572</v>
       </c>
       <c r="AK325" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AL325" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="326">
@@ -41786,22 +41786,22 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F345" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G345" t="b">
         <v>1</v>
       </c>
       <c r="H345" t="n">
-        <v>1470.5</v>
+        <v>1468.087</v>
       </c>
       <c r="I345" t="n">
-        <v>2.7419</v>
+        <v>2.7298</v>
       </c>
       <c r="J345" t="n">
-        <v>1431.7</v>
+        <v>1452.2</v>
       </c>
       <c r="K345" t="n">
         <v>140</v>
@@ -41822,70 +41822,70 @@
         <v>127</v>
       </c>
       <c r="Q345" t="n">
-        <v>115.44</v>
+        <v>115.45</v>
       </c>
       <c r="R345" t="n">
-        <v>108.906</v>
+        <v>109.658</v>
       </c>
       <c r="S345" t="n">
-        <v>6.534</v>
+        <v>5.792</v>
       </c>
       <c r="T345" t="n">
-        <v>0.29712</v>
+        <v>0.29826</v>
       </c>
       <c r="U345" t="n">
-        <v>0.15689</v>
+        <v>0.15513</v>
       </c>
       <c r="V345" t="n">
-        <v>79.86</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="W345" t="n">
-        <v>75.31</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="X345" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6319</v>
       </c>
       <c r="Y345" t="n">
-        <v>28.149</v>
+        <v>28.069</v>
       </c>
       <c r="Z345" t="n">
-        <v>58.31</v>
+        <v>58.412</v>
       </c>
       <c r="AA345" t="n">
-        <v>7.071</v>
+        <v>7.312</v>
       </c>
       <c r="AB345" t="n">
-        <v>19.605</v>
+        <v>20.046</v>
       </c>
       <c r="AC345" t="n">
-        <v>16.496</v>
+        <v>16.259</v>
       </c>
       <c r="AD345" t="n">
-        <v>22.185</v>
+        <v>21.743</v>
       </c>
       <c r="AE345" t="n">
-        <v>9.743</v>
+        <v>9.654999999999999</v>
       </c>
       <c r="AF345" t="n">
-        <v>22.565</v>
+        <v>22.289</v>
       </c>
       <c r="AG345" t="n">
-        <v>13.233</v>
+        <v>13.167</v>
       </c>
       <c r="AH345" t="n">
-        <v>7.071</v>
+        <v>7.127</v>
       </c>
       <c r="AI345" t="n">
-        <v>4.387</v>
+        <v>4.361</v>
       </c>
       <c r="AJ345" t="n">
-        <v>17.465</v>
+        <v>17.34</v>
       </c>
       <c r="AK345" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AL345" t="n">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="346">
@@ -42386,22 +42386,22 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F350" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G350" t="b">
         <v>1</v>
       </c>
       <c r="H350" t="n">
-        <v>1607.876</v>
+        <v>1602.282</v>
       </c>
       <c r="I350" t="n">
-        <v>1.5554</v>
+        <v>1.6245</v>
       </c>
       <c r="J350" t="n">
-        <v>1462.4</v>
+        <v>1480.3</v>
       </c>
       <c r="K350" t="n">
         <v>106</v>
@@ -42422,70 +42422,70 @@
         <v>98</v>
       </c>
       <c r="Q350" t="n">
-        <v>107.215</v>
+        <v>106.575</v>
       </c>
       <c r="R350" t="n">
-        <v>99.24299999999999</v>
+        <v>99.312</v>
       </c>
       <c r="S350" t="n">
-        <v>7.972</v>
+        <v>7.264</v>
       </c>
       <c r="T350" t="n">
-        <v>0.32874</v>
+        <v>0.32763</v>
       </c>
       <c r="U350" t="n">
-        <v>0.17351</v>
+        <v>0.17095</v>
       </c>
       <c r="V350" t="n">
-        <v>72.93000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="W350" t="n">
-        <v>67.51000000000001</v>
+        <v>67.59</v>
       </c>
       <c r="X350" t="n">
-        <v>0.76</v>
+        <v>0.7284</v>
       </c>
       <c r="Y350" t="n">
-        <v>25.57</v>
+        <v>25.506</v>
       </c>
       <c r="Z350" t="n">
-        <v>58.97</v>
+        <v>59.251</v>
       </c>
       <c r="AA350" t="n">
-        <v>6.21</v>
+        <v>6.156</v>
       </c>
       <c r="AB350" t="n">
-        <v>18.41</v>
+        <v>18.457</v>
       </c>
       <c r="AC350" t="n">
-        <v>15.5</v>
+        <v>15.303</v>
       </c>
       <c r="AD350" t="n">
-        <v>21.84</v>
+        <v>21.71</v>
       </c>
       <c r="AE350" t="n">
-        <v>12.42</v>
+        <v>12.437</v>
       </c>
       <c r="AF350" t="n">
-        <v>24.78</v>
+        <v>24.988</v>
       </c>
       <c r="AG350" t="n">
-        <v>10.4</v>
+        <v>10.186</v>
       </c>
       <c r="AH350" t="n">
-        <v>5.46</v>
+        <v>5.476</v>
       </c>
       <c r="AI350" t="n">
-        <v>2.91</v>
+        <v>2.874</v>
       </c>
       <c r="AJ350" t="n">
-        <v>18.35</v>
+        <v>18.177</v>
       </c>
       <c r="AK350" t="n">
-        <v>15.4</v>
+        <v>10.8</v>
       </c>
       <c r="AL350" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="351">
@@ -43466,22 +43466,22 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F359" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G359" t="b">
         <v>1</v>
       </c>
       <c r="H359" t="n">
-        <v>1427.37</v>
+        <v>1425.887</v>
       </c>
       <c r="I359" t="n">
-        <v>1.0039</v>
+        <v>1.0261</v>
       </c>
       <c r="J359" t="n">
-        <v>1430.9</v>
+        <v>1452.8</v>
       </c>
       <c r="K359" t="n">
         <v>181</v>
@@ -43502,70 +43502,70 @@
         <v>189</v>
       </c>
       <c r="Q359" t="n">
-        <v>119.175</v>
+        <v>118.645</v>
       </c>
       <c r="R359" t="n">
-        <v>116.563</v>
+        <v>117.977</v>
       </c>
       <c r="S359" t="n">
-        <v>2.613</v>
+        <v>0.667</v>
       </c>
       <c r="T359" t="n">
-        <v>0.2859</v>
+        <v>0.28974</v>
       </c>
       <c r="U359" t="n">
-        <v>0.14407</v>
+        <v>0.14319</v>
       </c>
       <c r="V359" t="n">
-        <v>84.93000000000001</v>
+        <v>84.31</v>
       </c>
       <c r="W359" t="n">
-        <v>83.23</v>
+        <v>83.92</v>
       </c>
       <c r="X359" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.5836</v>
       </c>
       <c r="Y359" t="n">
-        <v>29.025</v>
+        <v>29.037</v>
       </c>
       <c r="Z359" t="n">
-        <v>60.577</v>
+        <v>60.623</v>
       </c>
       <c r="AA359" t="n">
-        <v>9.981999999999999</v>
+        <v>9.831</v>
       </c>
       <c r="AB359" t="n">
-        <v>28.127</v>
+        <v>27.947</v>
       </c>
       <c r="AC359" t="n">
-        <v>16.494</v>
+        <v>16.052</v>
       </c>
       <c r="AD359" t="n">
-        <v>22.103</v>
+        <v>21.487</v>
       </c>
       <c r="AE359" t="n">
-        <v>9.201000000000001</v>
+        <v>9.109</v>
       </c>
       <c r="AF359" t="n">
-        <v>22.584</v>
+        <v>22.176</v>
       </c>
       <c r="AG359" t="n">
-        <v>15.768</v>
+        <v>15.915</v>
       </c>
       <c r="AH359" t="n">
-        <v>5.969</v>
+        <v>6.061</v>
       </c>
       <c r="AI359" t="n">
-        <v>2.927</v>
+        <v>2.912</v>
       </c>
       <c r="AJ359" t="n">
-        <v>19.708</v>
+        <v>19.412</v>
       </c>
       <c r="AK359" t="n">
-        <v>6.4</v>
+        <v>-3.6</v>
       </c>
       <c r="AL359" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="360">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -2306,22 +2306,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1980.818</v>
+        <v>1988.127</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1109</v>
+        <v>5.0738</v>
       </c>
       <c r="J16" t="n">
-        <v>1727.5</v>
+        <v>1731.7</v>
       </c>
       <c r="K16" t="n">
         <v>15</v>
@@ -2342,70 +2342,70 @@
         <v>15</v>
       </c>
       <c r="Q16" t="n">
-        <v>122.949</v>
+        <v>122.969</v>
       </c>
       <c r="R16" t="n">
-        <v>109.035</v>
+        <v>109.338</v>
       </c>
       <c r="S16" t="n">
-        <v>13.914</v>
+        <v>13.631</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2989</v>
+        <v>0.29609</v>
       </c>
       <c r="U16" t="n">
-        <v>0.12071</v>
+        <v>0.11967</v>
       </c>
       <c r="V16" t="n">
-        <v>90.19</v>
+        <v>90.28</v>
       </c>
       <c r="W16" t="n">
-        <v>80.01000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7731</v>
+        <v>0.7793</v>
       </c>
       <c r="Y16" t="n">
-        <v>32.335</v>
+        <v>32.379</v>
       </c>
       <c r="Z16" t="n">
-        <v>64.456</v>
+        <v>64.524</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.169</v>
+        <v>8.228</v>
       </c>
       <c r="AB16" t="n">
-        <v>21.397</v>
+        <v>21.214</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.354</v>
+        <v>17.29</v>
       </c>
       <c r="AD16" t="n">
-        <v>23.126</v>
+        <v>23.062</v>
       </c>
       <c r="AE16" t="n">
-        <v>10.1</v>
+        <v>10.014</v>
       </c>
       <c r="AF16" t="n">
-        <v>23.725</v>
+        <v>23.869</v>
       </c>
       <c r="AG16" t="n">
-        <v>17.321</v>
+        <v>17.283</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.291</v>
+        <v>7.31</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.113</v>
+        <v>5.145</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16.665</v>
+        <v>16.448</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="17">
@@ -8546,22 +8546,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F68" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1695.429</v>
+        <v>1719.075</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.7367</v>
+        <v>-1.4928</v>
       </c>
       <c r="J68" t="n">
-        <v>1574.5</v>
+        <v>1578.5</v>
       </c>
       <c r="K68" t="n">
         <v>78</v>
@@ -8582,70 +8582,70 @@
         <v>69</v>
       </c>
       <c r="Q68" t="n">
-        <v>110.224</v>
+        <v>110.613</v>
       </c>
       <c r="R68" t="n">
-        <v>102.463</v>
+        <v>102.177</v>
       </c>
       <c r="S68" t="n">
-        <v>7.761</v>
+        <v>8.436</v>
       </c>
       <c r="T68" t="n">
-        <v>0.24689</v>
+        <v>0.24972</v>
       </c>
       <c r="U68" t="n">
-        <v>0.16853</v>
+        <v>0.16976</v>
       </c>
       <c r="V68" t="n">
-        <v>74.56999999999999</v>
+        <v>74.72</v>
       </c>
       <c r="W68" t="n">
-        <v>69.73</v>
+        <v>69.45</v>
       </c>
       <c r="X68" t="n">
-        <v>0.6889</v>
+        <v>0.6974</v>
       </c>
       <c r="Y68" t="n">
-        <v>24.038</v>
+        <v>24.213</v>
       </c>
       <c r="Z68" t="n">
-        <v>53.26</v>
+        <v>53.414</v>
       </c>
       <c r="AA68" t="n">
-        <v>7.699</v>
+        <v>7.734</v>
       </c>
       <c r="AB68" t="n">
-        <v>22.186</v>
+        <v>22.331</v>
       </c>
       <c r="AC68" t="n">
-        <v>18.766</v>
+        <v>18.53</v>
       </c>
       <c r="AD68" t="n">
-        <v>24.887</v>
+        <v>24.557</v>
       </c>
       <c r="AE68" t="n">
-        <v>7.751</v>
+        <v>7.919</v>
       </c>
       <c r="AF68" t="n">
-        <v>23.103</v>
+        <v>23.258</v>
       </c>
       <c r="AG68" t="n">
-        <v>14.291</v>
+        <v>14.377</v>
       </c>
       <c r="AH68" t="n">
-        <v>8.083</v>
+        <v>8.073</v>
       </c>
       <c r="AI68" t="n">
-        <v>4.064</v>
+        <v>3.971</v>
       </c>
       <c r="AJ68" t="n">
-        <v>16.82</v>
+        <v>16.761</v>
       </c>
       <c r="AK68" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="AL68" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="69">
@@ -9506,22 +9506,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F76" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>2196.684</v>
+        <v>2203.313</v>
       </c>
       <c r="I76" t="n">
-        <v>3.7365</v>
+        <v>3.7385</v>
       </c>
       <c r="J76" t="n">
-        <v>1700.6</v>
+        <v>1715.1</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
@@ -9542,70 +9542,70 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>122.606</v>
+        <v>122.582</v>
       </c>
       <c r="R76" t="n">
-        <v>94.999</v>
+        <v>94.554</v>
       </c>
       <c r="S76" t="n">
-        <v>27.607</v>
+        <v>28.028</v>
       </c>
       <c r="T76" t="n">
-        <v>0.29898</v>
+        <v>0.29512</v>
       </c>
       <c r="U76" t="n">
-        <v>0.15337</v>
+        <v>0.15728</v>
       </c>
       <c r="V76" t="n">
-        <v>81.86</v>
+        <v>81.94</v>
       </c>
       <c r="W76" t="n">
-        <v>63.22</v>
+        <v>63.01</v>
       </c>
       <c r="X76" t="n">
-        <v>0.9434</v>
+        <v>0.945</v>
       </c>
       <c r="Y76" t="n">
-        <v>28.44</v>
+        <v>28.431</v>
       </c>
       <c r="Z76" t="n">
-        <v>58.434</v>
+        <v>58.079</v>
       </c>
       <c r="AA76" t="n">
-        <v>8.930999999999999</v>
+        <v>8.898</v>
       </c>
       <c r="AB76" t="n">
-        <v>25.915</v>
+        <v>25.732</v>
       </c>
       <c r="AC76" t="n">
-        <v>16.049</v>
+        <v>16.176</v>
       </c>
       <c r="AD76" t="n">
-        <v>22.018</v>
+        <v>22.065</v>
       </c>
       <c r="AE76" t="n">
-        <v>11.701</v>
+        <v>11.559</v>
       </c>
       <c r="AF76" t="n">
-        <v>27.028</v>
+        <v>27.25</v>
       </c>
       <c r="AG76" t="n">
-        <v>16.713</v>
+        <v>16.78</v>
       </c>
       <c r="AH76" t="n">
-        <v>7.61</v>
+        <v>7.559</v>
       </c>
       <c r="AI76" t="n">
-        <v>3.255</v>
+        <v>3.285</v>
       </c>
       <c r="AJ76" t="n">
-        <v>15.486</v>
+        <v>15.523</v>
       </c>
       <c r="AK76" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AL76" t="n">
-        <v>17.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="77">
@@ -13106,22 +13106,22 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F106" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G106" t="b">
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>2070.396</v>
+        <v>2027.119</v>
       </c>
       <c r="I106" t="n">
-        <v>5.4527</v>
+        <v>5.1307</v>
       </c>
       <c r="J106" t="n">
-        <v>1596.4</v>
+        <v>1606.9</v>
       </c>
       <c r="K106" t="n">
         <v>10</v>
@@ -13142,70 +13142,70 @@
         <v>7</v>
       </c>
       <c r="Q106" t="n">
-        <v>120.168</v>
+        <v>119.759</v>
       </c>
       <c r="R106" t="n">
-        <v>93.744</v>
+        <v>94.54300000000001</v>
       </c>
       <c r="S106" t="n">
-        <v>26.424</v>
+        <v>25.216</v>
       </c>
       <c r="T106" t="n">
-        <v>0.30091</v>
+        <v>0.29566</v>
       </c>
       <c r="U106" t="n">
-        <v>0.13405</v>
+        <v>0.13185</v>
       </c>
       <c r="V106" t="n">
-        <v>84.66</v>
+        <v>84.14</v>
       </c>
       <c r="W106" t="n">
-        <v>65.92</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="X106" t="n">
-        <v>0.9126</v>
+        <v>0.878</v>
       </c>
       <c r="Y106" t="n">
-        <v>32.051</v>
+        <v>32.076</v>
       </c>
       <c r="Z106" t="n">
-        <v>63.379</v>
+        <v>63.257</v>
       </c>
       <c r="AA106" t="n">
-        <v>6.526</v>
+        <v>6.501</v>
       </c>
       <c r="AB106" t="n">
-        <v>19.573</v>
+        <v>19.418</v>
       </c>
       <c r="AC106" t="n">
-        <v>14.027</v>
+        <v>13.712</v>
       </c>
       <c r="AD106" t="n">
-        <v>19.853</v>
+        <v>19.423</v>
       </c>
       <c r="AE106" t="n">
-        <v>11.163</v>
+        <v>10.891</v>
       </c>
       <c r="AF106" t="n">
-        <v>25.97</v>
+        <v>25.869</v>
       </c>
       <c r="AG106" t="n">
-        <v>18.282</v>
+        <v>18.357</v>
       </c>
       <c r="AH106" t="n">
-        <v>8.457000000000001</v>
+        <v>8.305</v>
       </c>
       <c r="AI106" t="n">
-        <v>3.747</v>
+        <v>3.671</v>
       </c>
       <c r="AJ106" t="n">
-        <v>16.902</v>
+        <v>16.664</v>
       </c>
       <c r="AK106" t="n">
-        <v>11.8</v>
+        <v>2.4</v>
       </c>
       <c r="AL106" t="n">
-        <v>14.7</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="107">
@@ -13826,22 +13826,22 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F112" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G112" t="b">
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>1664.344</v>
+        <v>1657.036</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.6842</v>
+        <v>-0.3178</v>
       </c>
       <c r="J112" t="n">
-        <v>1401.4</v>
+        <v>1404.4</v>
       </c>
       <c r="K112" t="n">
         <v>92</v>
@@ -13862,70 +13862,70 @@
         <v>75</v>
       </c>
       <c r="Q112" t="n">
-        <v>120.784</v>
+        <v>120.565</v>
       </c>
       <c r="R112" t="n">
-        <v>100.586</v>
+        <v>101.276</v>
       </c>
       <c r="S112" t="n">
-        <v>20.197</v>
+        <v>19.289</v>
       </c>
       <c r="T112" t="n">
-        <v>0.30161</v>
+        <v>0.30298</v>
       </c>
       <c r="U112" t="n">
-        <v>0.12796</v>
+        <v>0.12743</v>
       </c>
       <c r="V112" t="n">
-        <v>86.31</v>
+        <v>86.41</v>
       </c>
       <c r="W112" t="n">
-        <v>72.20999999999999</v>
+        <v>72.97</v>
       </c>
       <c r="X112" t="n">
-        <v>0.8761</v>
+        <v>0.8413</v>
       </c>
       <c r="Y112" t="n">
-        <v>29.049</v>
+        <v>29.222</v>
       </c>
       <c r="Z112" t="n">
-        <v>61.346</v>
+        <v>61.839</v>
       </c>
       <c r="AA112" t="n">
-        <v>9.031000000000001</v>
+        <v>9.069000000000001</v>
       </c>
       <c r="AB112" t="n">
-        <v>26.128</v>
+        <v>26.612</v>
       </c>
       <c r="AC112" t="n">
-        <v>19.145</v>
+        <v>18.864</v>
       </c>
       <c r="AD112" t="n">
-        <v>25.688</v>
+        <v>25.243</v>
       </c>
       <c r="AE112" t="n">
-        <v>10.119</v>
+        <v>10.189</v>
       </c>
       <c r="AF112" t="n">
-        <v>23.134</v>
+        <v>23.137</v>
       </c>
       <c r="AG112" t="n">
-        <v>15.328</v>
+        <v>15.377</v>
       </c>
       <c r="AH112" t="n">
-        <v>10.052</v>
+        <v>9.928000000000001</v>
       </c>
       <c r="AI112" t="n">
-        <v>3.69</v>
+        <v>3.584</v>
       </c>
       <c r="AJ112" t="n">
-        <v>18.534</v>
+        <v>18.532</v>
       </c>
       <c r="AK112" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AL112" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
@@ -14186,22 +14186,22 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F115" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G115" t="b">
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>2112.552</v>
+        <v>2122.165</v>
       </c>
       <c r="I115" t="n">
-        <v>1.1096</v>
+        <v>1.0162</v>
       </c>
       <c r="J115" t="n">
-        <v>1725.6</v>
+        <v>1741.9</v>
       </c>
       <c r="K115" t="n">
         <v>5</v>
@@ -14222,70 +14222,70 @@
         <v>5</v>
       </c>
       <c r="Q115" t="n">
-        <v>117.422</v>
+        <v>117.91</v>
       </c>
       <c r="R115" t="n">
-        <v>94.66500000000001</v>
+        <v>94.52</v>
       </c>
       <c r="S115" t="n">
-        <v>22.757</v>
+        <v>23.39</v>
       </c>
       <c r="T115" t="n">
-        <v>0.33192</v>
+        <v>0.33619</v>
       </c>
       <c r="U115" t="n">
-        <v>0.12292</v>
+        <v>0.12241</v>
       </c>
       <c r="V115" t="n">
-        <v>77.18000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="W115" t="n">
-        <v>62.27</v>
+        <v>62.21</v>
       </c>
       <c r="X115" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8347</v>
       </c>
       <c r="Y115" t="n">
-        <v>27.885</v>
+        <v>27.934</v>
       </c>
       <c r="Z115" t="n">
-        <v>61.745</v>
+        <v>61.966</v>
       </c>
       <c r="AA115" t="n">
-        <v>8.765000000000001</v>
+        <v>8.744</v>
       </c>
       <c r="AB115" t="n">
-        <v>24.8</v>
+        <v>25.104</v>
       </c>
       <c r="AC115" t="n">
-        <v>12.645</v>
+        <v>12.947</v>
       </c>
       <c r="AD115" t="n">
-        <v>16.41</v>
+        <v>16.762</v>
       </c>
       <c r="AE115" t="n">
-        <v>11.37</v>
+        <v>11.671</v>
       </c>
       <c r="AF115" t="n">
-        <v>23.168</v>
+        <v>23.17</v>
       </c>
       <c r="AG115" t="n">
-        <v>14.503</v>
+        <v>14.523</v>
       </c>
       <c r="AH115" t="n">
-        <v>7.745</v>
+        <v>7.609</v>
       </c>
       <c r="AI115" t="n">
-        <v>3.747</v>
+        <v>3.887</v>
       </c>
       <c r="AJ115" t="n">
-        <v>17.917</v>
+        <v>17.873</v>
       </c>
       <c r="AK115" t="n">
-        <v>12.4</v>
+        <v>17.2</v>
       </c>
       <c r="AL115" t="n">
-        <v>9.199999999999999</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="116">
@@ -14906,22 +14906,22 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F121" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G121" t="b">
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>1984.447</v>
+        <v>1997.795</v>
       </c>
       <c r="I121" t="n">
-        <v>7.3951</v>
+        <v>6.9704</v>
       </c>
       <c r="J121" t="n">
-        <v>1704.4</v>
+        <v>1718.8</v>
       </c>
       <c r="K121" t="n">
         <v>7</v>
@@ -14942,70 +14942,70 @@
         <v>8</v>
       </c>
       <c r="Q121" t="n">
-        <v>126.534</v>
+        <v>125.89</v>
       </c>
       <c r="R121" t="n">
-        <v>103.563</v>
+        <v>102.84</v>
       </c>
       <c r="S121" t="n">
-        <v>22.971</v>
+        <v>23.05</v>
       </c>
       <c r="T121" t="n">
-        <v>0.32629</v>
+        <v>0.32312</v>
       </c>
       <c r="U121" t="n">
-        <v>0.12517</v>
+        <v>0.12769</v>
       </c>
       <c r="V121" t="n">
-        <v>85.2</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="W121" t="n">
-        <v>69.81999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="X121" t="n">
-        <v>0.76</v>
+        <v>0.7669</v>
       </c>
       <c r="Y121" t="n">
-        <v>28.81</v>
+        <v>28.699</v>
       </c>
       <c r="Z121" t="n">
-        <v>62.36</v>
+        <v>62.079</v>
       </c>
       <c r="AA121" t="n">
-        <v>11.1</v>
+        <v>10.981</v>
       </c>
       <c r="AB121" t="n">
-        <v>31.92</v>
+        <v>31.576</v>
       </c>
       <c r="AC121" t="n">
-        <v>16.57</v>
+        <v>16.361</v>
       </c>
       <c r="AD121" t="n">
-        <v>20.88</v>
+        <v>20.73</v>
       </c>
       <c r="AE121" t="n">
-        <v>12.65</v>
+        <v>12.554</v>
       </c>
       <c r="AF121" t="n">
-        <v>26.26</v>
+        <v>26.502</v>
       </c>
       <c r="AG121" t="n">
-        <v>14.73</v>
+        <v>14.738</v>
       </c>
       <c r="AH121" t="n">
-        <v>3.8</v>
+        <v>3.864</v>
       </c>
       <c r="AI121" t="n">
-        <v>4.52</v>
+        <v>4.563</v>
       </c>
       <c r="AJ121" t="n">
-        <v>13.12</v>
+        <v>13.184</v>
       </c>
       <c r="AK121" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AL121" t="n">
-        <v>10</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="122">
@@ -17666,22 +17666,22 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F144" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G144" t="b">
         <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>1743.485</v>
+        <v>1723.725</v>
       </c>
       <c r="I144" t="n">
-        <v>2.673</v>
+        <v>2.567</v>
       </c>
       <c r="J144" t="n">
-        <v>1491.2</v>
+        <v>1499.6</v>
       </c>
       <c r="K144" t="n">
         <v>125</v>
@@ -17702,70 +17702,70 @@
         <v>106</v>
       </c>
       <c r="Q144" t="n">
-        <v>117.773</v>
+        <v>117.103</v>
       </c>
       <c r="R144" t="n">
-        <v>111.278</v>
+        <v>111.5</v>
       </c>
       <c r="S144" t="n">
-        <v>6.495</v>
+        <v>5.603</v>
       </c>
       <c r="T144" t="n">
-        <v>0.17409</v>
+        <v>0.17692</v>
       </c>
       <c r="U144" t="n">
-        <v>0.13118</v>
+        <v>0.12885</v>
       </c>
       <c r="V144" t="n">
-        <v>76.23999999999999</v>
+        <v>75.72</v>
       </c>
       <c r="W144" t="n">
-        <v>72.13</v>
+        <v>72.17</v>
       </c>
       <c r="X144" t="n">
-        <v>0.7683</v>
+        <v>0.7372</v>
       </c>
       <c r="Y144" t="n">
-        <v>27.066</v>
+        <v>26.91</v>
       </c>
       <c r="Z144" t="n">
-        <v>53.378</v>
+        <v>53.506</v>
       </c>
       <c r="AA144" t="n">
-        <v>10.039</v>
+        <v>9.872</v>
       </c>
       <c r="AB144" t="n">
-        <v>25.276</v>
+        <v>25.205</v>
       </c>
       <c r="AC144" t="n">
-        <v>12.332</v>
+        <v>12.288</v>
       </c>
       <c r="AD144" t="n">
-        <v>17.385</v>
+        <v>17.314</v>
       </c>
       <c r="AE144" t="n">
-        <v>4.789</v>
+        <v>4.814</v>
       </c>
       <c r="AF144" t="n">
-        <v>21.683</v>
+        <v>21.487</v>
       </c>
       <c r="AG144" t="n">
-        <v>16.53</v>
+        <v>16.474</v>
       </c>
       <c r="AH144" t="n">
-        <v>6.04</v>
+        <v>6.032</v>
       </c>
       <c r="AI144" t="n">
-        <v>3.298</v>
+        <v>3.288</v>
       </c>
       <c r="AJ144" t="n">
-        <v>14.451</v>
+        <v>14.647</v>
       </c>
       <c r="AK144" t="n">
-        <v>0.6</v>
+        <v>-2</v>
       </c>
       <c r="AL144" t="n">
-        <v>-1.5</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="145">
@@ -18386,22 +18386,22 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F150" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G150" t="b">
         <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>1854.143</v>
+        <v>1840.231</v>
       </c>
       <c r="I150" t="n">
-        <v>-2.5004</v>
+        <v>-2.3212</v>
       </c>
       <c r="J150" t="n">
-        <v>1686.9</v>
+        <v>1697.9</v>
       </c>
       <c r="K150" t="n">
         <v>19</v>
@@ -18422,70 +18422,70 @@
         <v>17</v>
       </c>
       <c r="Q150" t="n">
-        <v>118.734</v>
+        <v>118.298</v>
       </c>
       <c r="R150" t="n">
-        <v>101.945</v>
+        <v>102.457</v>
       </c>
       <c r="S150" t="n">
-        <v>16.789</v>
+        <v>15.841</v>
       </c>
       <c r="T150" t="n">
-        <v>0.2886</v>
+        <v>0.29073</v>
       </c>
       <c r="U150" t="n">
-        <v>0.16453</v>
+        <v>0.16363</v>
       </c>
       <c r="V150" t="n">
-        <v>84.69</v>
+        <v>84.14</v>
       </c>
       <c r="W150" t="n">
-        <v>72.43000000000001</v>
+        <v>72.55</v>
       </c>
       <c r="X150" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.6807</v>
       </c>
       <c r="Y150" t="n">
-        <v>28.525</v>
+        <v>28.439</v>
       </c>
       <c r="Z150" t="n">
-        <v>61.046</v>
+        <v>61.185</v>
       </c>
       <c r="AA150" t="n">
-        <v>11.395</v>
+        <v>11.44</v>
       </c>
       <c r="AB150" t="n">
-        <v>32.12</v>
+        <v>32.349</v>
       </c>
       <c r="AC150" t="n">
-        <v>15.868</v>
+        <v>15.458</v>
       </c>
       <c r="AD150" t="n">
-        <v>20.915</v>
+        <v>20.351</v>
       </c>
       <c r="AE150" t="n">
-        <v>10.737</v>
+        <v>10.745</v>
       </c>
       <c r="AF150" t="n">
-        <v>26.294</v>
+        <v>26.077</v>
       </c>
       <c r="AG150" t="n">
-        <v>16.854</v>
+        <v>16.822</v>
       </c>
       <c r="AH150" t="n">
-        <v>6.838</v>
+        <v>6.787</v>
       </c>
       <c r="AI150" t="n">
-        <v>3.35</v>
+        <v>3.305</v>
       </c>
       <c r="AJ150" t="n">
-        <v>18.284</v>
+        <v>18.391</v>
       </c>
       <c r="AK150" t="n">
-        <v>4.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AL150" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="151">
@@ -20666,22 +20666,22 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F169" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G169" t="b">
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>2174.35</v>
+        <v>2180.38</v>
       </c>
       <c r="I169" t="n">
-        <v>6.1854</v>
+        <v>5.8798</v>
       </c>
       <c r="J169" t="n">
-        <v>1765.3</v>
+        <v>1779.7</v>
       </c>
       <c r="K169" t="n">
         <v>3</v>
@@ -20702,70 +20702,70 @@
         <v>2</v>
       </c>
       <c r="Q169" t="n">
-        <v>121.548</v>
+        <v>121.931</v>
       </c>
       <c r="R169" t="n">
-        <v>97.557</v>
+        <v>97.663</v>
       </c>
       <c r="S169" t="n">
-        <v>23.992</v>
+        <v>24.268</v>
       </c>
       <c r="T169" t="n">
-        <v>0.25476</v>
+        <v>0.25601</v>
       </c>
       <c r="U169" t="n">
-        <v>0.16164</v>
+        <v>0.16069</v>
       </c>
       <c r="V169" t="n">
-        <v>87.33</v>
+        <v>87.5</v>
       </c>
       <c r="W169" t="n">
-        <v>69.59</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="X169" t="n">
-        <v>0.9149</v>
+        <v>0.9172</v>
       </c>
       <c r="Y169" t="n">
-        <v>30.647</v>
+        <v>30.717</v>
       </c>
       <c r="Z169" t="n">
-        <v>59.793</v>
+        <v>59.869</v>
       </c>
       <c r="AA169" t="n">
-        <v>9.042999999999999</v>
+        <v>9.097</v>
       </c>
       <c r="AB169" t="n">
-        <v>24.822</v>
+        <v>24.766</v>
       </c>
       <c r="AC169" t="n">
-        <v>17.22</v>
+        <v>17.186</v>
       </c>
       <c r="AD169" t="n">
-        <v>23.035</v>
+        <v>23.055</v>
       </c>
       <c r="AE169" t="n">
-        <v>9.728999999999999</v>
+        <v>9.814</v>
       </c>
       <c r="AF169" t="n">
-        <v>28.107</v>
+        <v>28.186</v>
       </c>
       <c r="AG169" t="n">
-        <v>18.945</v>
+        <v>18.924</v>
       </c>
       <c r="AH169" t="n">
-        <v>5.702</v>
+        <v>5.586</v>
       </c>
       <c r="AI169" t="n">
-        <v>6.015</v>
+        <v>6.103</v>
       </c>
       <c r="AJ169" t="n">
-        <v>15.382</v>
+        <v>15.317</v>
       </c>
       <c r="AK169" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AL169" t="n">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="170">
@@ -20786,22 +20786,22 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F170" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G170" t="b">
         <v>1</v>
       </c>
       <c r="H170" t="n">
-        <v>2031.39</v>
+        <v>2045.301</v>
       </c>
       <c r="I170" t="n">
-        <v>0.0735</v>
+        <v>-0.0252</v>
       </c>
       <c r="J170" t="n">
-        <v>1723.2</v>
+        <v>1733.5</v>
       </c>
       <c r="K170" t="n">
         <v>9</v>
@@ -20822,70 +20822,70 @@
         <v>11</v>
       </c>
       <c r="Q170" t="n">
-        <v>117.934</v>
+        <v>117.697</v>
       </c>
       <c r="R170" t="n">
-        <v>101.399</v>
+        <v>101.519</v>
       </c>
       <c r="S170" t="n">
-        <v>16.535</v>
+        <v>16.178</v>
       </c>
       <c r="T170" t="n">
-        <v>0.28968</v>
+        <v>0.29109</v>
       </c>
       <c r="U170" t="n">
-        <v>0.1613</v>
+        <v>0.16361</v>
       </c>
       <c r="V170" t="n">
-        <v>79.45999999999999</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="W170" t="n">
-        <v>68.34999999999999</v>
+        <v>68.39</v>
       </c>
       <c r="X170" t="n">
-        <v>0.79</v>
+        <v>0.796</v>
       </c>
       <c r="Y170" t="n">
-        <v>27.84</v>
+        <v>27.719</v>
       </c>
       <c r="Z170" t="n">
-        <v>58.22</v>
+        <v>58.118</v>
       </c>
       <c r="AA170" t="n">
-        <v>7.81</v>
+        <v>7.911</v>
       </c>
       <c r="AB170" t="n">
-        <v>21.38</v>
+        <v>21.571</v>
       </c>
       <c r="AC170" t="n">
-        <v>16.09</v>
+        <v>16.01</v>
       </c>
       <c r="AD170" t="n">
-        <v>20.97</v>
+        <v>20.923</v>
       </c>
       <c r="AE170" t="n">
-        <v>10.96</v>
+        <v>11.029</v>
       </c>
       <c r="AF170" t="n">
-        <v>26.41</v>
+        <v>26.427</v>
       </c>
       <c r="AG170" t="n">
-        <v>18.65</v>
+        <v>18.707</v>
       </c>
       <c r="AH170" t="n">
-        <v>5.39</v>
+        <v>5.34</v>
       </c>
       <c r="AI170" t="n">
-        <v>4.2</v>
+        <v>4.213</v>
       </c>
       <c r="AJ170" t="n">
-        <v>16.31</v>
+        <v>16.128</v>
       </c>
       <c r="AK170" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AL170" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="171">
@@ -23786,22 +23786,22 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F195" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G195" t="b">
         <v>1</v>
       </c>
       <c r="H195" t="n">
-        <v>1988.043</v>
+        <v>2012.467</v>
       </c>
       <c r="I195" t="n">
-        <v>9.170199999999999</v>
+        <v>8.516999999999999</v>
       </c>
       <c r="J195" t="n">
-        <v>1669.8</v>
+        <v>1683.9</v>
       </c>
       <c r="K195" t="n">
         <v>14</v>
@@ -23822,70 +23822,70 @@
         <v>14</v>
       </c>
       <c r="Q195" t="n">
-        <v>115.233</v>
+        <v>115.192</v>
       </c>
       <c r="R195" t="n">
-        <v>97.834</v>
+        <v>98.636</v>
       </c>
       <c r="S195" t="n">
-        <v>17.399</v>
+        <v>16.556</v>
       </c>
       <c r="T195" t="n">
-        <v>0.24652</v>
+        <v>0.24223</v>
       </c>
       <c r="U195" t="n">
-        <v>0.13855</v>
+        <v>0.14089</v>
       </c>
       <c r="V195" t="n">
-        <v>77.23</v>
+        <v>77.12</v>
       </c>
       <c r="W195" t="n">
-        <v>65.45</v>
+        <v>65.88</v>
       </c>
       <c r="X195" t="n">
-        <v>0.82</v>
+        <v>0.8252</v>
       </c>
       <c r="Y195" t="n">
-        <v>27.52</v>
+        <v>27.572</v>
       </c>
       <c r="Z195" t="n">
-        <v>59.18</v>
+        <v>58.847</v>
       </c>
       <c r="AA195" t="n">
-        <v>10.67</v>
+        <v>10.573</v>
       </c>
       <c r="AB195" t="n">
-        <v>30.24</v>
+        <v>29.723</v>
       </c>
       <c r="AC195" t="n">
-        <v>12</v>
+        <v>11.866</v>
       </c>
       <c r="AD195" t="n">
-        <v>15.75</v>
+        <v>15.624</v>
       </c>
       <c r="AE195" t="n">
-        <v>8.470000000000001</v>
+        <v>8.292999999999999</v>
       </c>
       <c r="AF195" t="n">
-        <v>25.29</v>
+        <v>25.33</v>
       </c>
       <c r="AG195" t="n">
-        <v>18.2</v>
+        <v>18.098</v>
       </c>
       <c r="AH195" t="n">
-        <v>7.42</v>
+        <v>7.302</v>
       </c>
       <c r="AI195" t="n">
-        <v>2.5</v>
+        <v>2.418</v>
       </c>
       <c r="AJ195" t="n">
-        <v>14.12</v>
+        <v>14.3</v>
       </c>
       <c r="AK195" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="AL195" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="196">
@@ -23906,22 +23906,22 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F196" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G196" t="b">
         <v>1</v>
       </c>
       <c r="H196" t="n">
-        <v>1747.974</v>
+        <v>1767.735</v>
       </c>
       <c r="I196" t="n">
-        <v>5.3805</v>
+        <v>5.1312</v>
       </c>
       <c r="J196" t="n">
-        <v>1602.9</v>
+        <v>1608.4</v>
       </c>
       <c r="K196" t="n">
         <v>75</v>
@@ -23942,70 +23942,70 @@
         <v>70</v>
       </c>
       <c r="Q196" t="n">
-        <v>112.996</v>
+        <v>113.135</v>
       </c>
       <c r="R196" t="n">
-        <v>105.635</v>
+        <v>105.56</v>
       </c>
       <c r="S196" t="n">
-        <v>7.361</v>
+        <v>7.575</v>
       </c>
       <c r="T196" t="n">
-        <v>0.30095</v>
+        <v>0.30057</v>
       </c>
       <c r="U196" t="n">
-        <v>0.14234</v>
+        <v>0.14388</v>
       </c>
       <c r="V196" t="n">
-        <v>76.44</v>
+        <v>76.19</v>
       </c>
       <c r="W196" t="n">
-        <v>71.72</v>
+        <v>71.36</v>
       </c>
       <c r="X196" t="n">
-        <v>0.6606</v>
+        <v>0.6698</v>
       </c>
       <c r="Y196" t="n">
-        <v>25.264</v>
+        <v>25.138</v>
       </c>
       <c r="Z196" t="n">
-        <v>57.191</v>
+        <v>56.916</v>
       </c>
       <c r="AA196" t="n">
-        <v>6.717</v>
+        <v>6.614</v>
       </c>
       <c r="AB196" t="n">
-        <v>18.54</v>
+        <v>18.458</v>
       </c>
       <c r="AC196" t="n">
-        <v>19.086</v>
+        <v>19.193</v>
       </c>
       <c r="AD196" t="n">
-        <v>25.544</v>
+        <v>25.503</v>
       </c>
       <c r="AE196" t="n">
-        <v>10.18</v>
+        <v>10.239</v>
       </c>
       <c r="AF196" t="n">
-        <v>23.532</v>
+        <v>23.727</v>
       </c>
       <c r="AG196" t="n">
-        <v>14.457</v>
+        <v>14.533</v>
       </c>
       <c r="AH196" t="n">
-        <v>6.738</v>
+        <v>6.577</v>
       </c>
       <c r="AI196" t="n">
-        <v>3.697</v>
+        <v>3.725</v>
       </c>
       <c r="AJ196" t="n">
-        <v>18.052</v>
+        <v>17.999</v>
       </c>
       <c r="AK196" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL196" t="n">
-        <v>3.7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="197">
@@ -33386,22 +33386,22 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F275" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G275" t="b">
         <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>1819.597</v>
+        <v>1813.568</v>
       </c>
       <c r="I275" t="n">
-        <v>8.063000000000001</v>
+        <v>7.6609</v>
       </c>
       <c r="J275" t="n">
-        <v>1526.5</v>
+        <v>1540.5</v>
       </c>
       <c r="K275" t="n">
         <v>41</v>
@@ -33422,70 +33422,70 @@
         <v>31</v>
       </c>
       <c r="Q275" t="n">
-        <v>120.498</v>
+        <v>119.709</v>
       </c>
       <c r="R275" t="n">
-        <v>98.57599999999999</v>
+        <v>99.976</v>
       </c>
       <c r="S275" t="n">
-        <v>21.922</v>
+        <v>19.733</v>
       </c>
       <c r="T275" t="n">
-        <v>0.24815</v>
+        <v>0.24409</v>
       </c>
       <c r="U275" t="n">
-        <v>0.16516</v>
+        <v>0.16343</v>
       </c>
       <c r="V275" t="n">
-        <v>87.03</v>
+        <v>86.31</v>
       </c>
       <c r="W275" t="n">
-        <v>70.91</v>
+        <v>71.78</v>
       </c>
       <c r="X275" t="n">
-        <v>0.85</v>
+        <v>0.8159</v>
       </c>
       <c r="Y275" t="n">
-        <v>29.8</v>
+        <v>29.739</v>
       </c>
       <c r="Z275" t="n">
-        <v>60.09</v>
+        <v>60.009</v>
       </c>
       <c r="AA275" t="n">
-        <v>10.78</v>
+        <v>10.758</v>
       </c>
       <c r="AB275" t="n">
-        <v>27.21</v>
+        <v>27.28</v>
       </c>
       <c r="AC275" t="n">
-        <v>15.68</v>
+        <v>15.372</v>
       </c>
       <c r="AD275" t="n">
-        <v>21.2</v>
+        <v>20.915</v>
       </c>
       <c r="AE275" t="n">
-        <v>9.15</v>
+        <v>8.933999999999999</v>
       </c>
       <c r="AF275" t="n">
-        <v>27.6</v>
+        <v>27.449</v>
       </c>
       <c r="AG275" t="n">
-        <v>17.67</v>
+        <v>17.69</v>
       </c>
       <c r="AH275" t="n">
-        <v>7.29</v>
+        <v>7.262</v>
       </c>
       <c r="AI275" t="n">
-        <v>3.25</v>
+        <v>3.156</v>
       </c>
       <c r="AJ275" t="n">
-        <v>18.11</v>
+        <v>18.107</v>
       </c>
       <c r="AK275" t="n">
-        <v>3.2</v>
+        <v>-4.2</v>
       </c>
       <c r="AL275" t="n">
-        <v>5.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="276">
@@ -34346,22 +34346,22 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F283" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G283" t="b">
         <v>1</v>
       </c>
       <c r="H283" t="n">
-        <v>1860.648</v>
+        <v>1854.019</v>
       </c>
       <c r="I283" t="n">
-        <v>6.8435</v>
+        <v>6.8722</v>
       </c>
       <c r="J283" t="n">
-        <v>1693.5</v>
+        <v>1707</v>
       </c>
       <c r="K283" t="n">
         <v>43</v>
@@ -34382,70 +34382,70 @@
         <v>39</v>
       </c>
       <c r="Q283" t="n">
-        <v>111.032</v>
+        <v>110.055</v>
       </c>
       <c r="R283" t="n">
-        <v>102.3</v>
+        <v>102.759</v>
       </c>
       <c r="S283" t="n">
-        <v>8.731</v>
+        <v>7.295</v>
       </c>
       <c r="T283" t="n">
-        <v>0.31828</v>
+        <v>0.32362</v>
       </c>
       <c r="U283" t="n">
-        <v>0.14957</v>
+        <v>0.14858</v>
       </c>
       <c r="V283" t="n">
-        <v>77.84999999999999</v>
+        <v>77.23</v>
       </c>
       <c r="W283" t="n">
-        <v>71.76000000000001</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="X283" t="n">
-        <v>0.679</v>
+        <v>0.6523</v>
       </c>
       <c r="Y283" t="n">
-        <v>27.035</v>
+        <v>26.914</v>
       </c>
       <c r="Z283" t="n">
-        <v>60.473</v>
+        <v>60.804</v>
       </c>
       <c r="AA283" t="n">
-        <v>7.342</v>
+        <v>7.34</v>
       </c>
       <c r="AB283" t="n">
-        <v>22.358</v>
+        <v>22.412</v>
       </c>
       <c r="AC283" t="n">
-        <v>16.361</v>
+        <v>16.004</v>
       </c>
       <c r="AD283" t="n">
-        <v>22.993</v>
+        <v>22.621</v>
       </c>
       <c r="AE283" t="n">
-        <v>11.019</v>
+        <v>11.057</v>
       </c>
       <c r="AF283" t="n">
-        <v>22.732</v>
+        <v>22.395</v>
       </c>
       <c r="AG283" t="n">
-        <v>15.724</v>
+        <v>15.574</v>
       </c>
       <c r="AH283" t="n">
-        <v>7.56</v>
+        <v>7.746</v>
       </c>
       <c r="AI283" t="n">
-        <v>4.488</v>
+        <v>4.446</v>
       </c>
       <c r="AJ283" t="n">
-        <v>16.07</v>
+        <v>16.256</v>
       </c>
       <c r="AK283" t="n">
-        <v>4.4</v>
+        <v>-1.8</v>
       </c>
       <c r="AL283" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="284">
@@ -34946,22 +34946,22 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F288" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G288" t="b">
         <v>1</v>
       </c>
       <c r="H288" t="n">
-        <v>1801.834</v>
+        <v>1845.111</v>
       </c>
       <c r="I288" t="n">
-        <v>2.6488</v>
+        <v>2.8244</v>
       </c>
       <c r="J288" t="n">
-        <v>1706</v>
+        <v>1711</v>
       </c>
       <c r="K288" t="n">
         <v>37</v>
@@ -34982,70 +34982,70 @@
         <v>42</v>
       </c>
       <c r="Q288" t="n">
-        <v>119.208</v>
+        <v>119.114</v>
       </c>
       <c r="R288" t="n">
-        <v>110.835</v>
+        <v>110.731</v>
       </c>
       <c r="S288" t="n">
-        <v>8.372999999999999</v>
+        <v>8.382999999999999</v>
       </c>
       <c r="T288" t="n">
-        <v>0.30312</v>
+        <v>0.30206</v>
       </c>
       <c r="U288" t="n">
-        <v>0.14324</v>
+        <v>0.14233</v>
       </c>
       <c r="V288" t="n">
-        <v>82.06</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="W288" t="n">
-        <v>76.23</v>
+        <v>75.97</v>
       </c>
       <c r="X288" t="n">
-        <v>0.5793</v>
+        <v>0.5915</v>
       </c>
       <c r="Y288" t="n">
-        <v>27.696</v>
+        <v>27.7</v>
       </c>
       <c r="Z288" t="n">
-        <v>57.983</v>
+        <v>58.074</v>
       </c>
       <c r="AA288" t="n">
-        <v>6.945</v>
+        <v>6.86</v>
       </c>
       <c r="AB288" t="n">
-        <v>20.468</v>
+        <v>20.29</v>
       </c>
       <c r="AC288" t="n">
-        <v>19.661</v>
+        <v>19.309</v>
       </c>
       <c r="AD288" t="n">
-        <v>26.133</v>
+        <v>25.627</v>
       </c>
       <c r="AE288" t="n">
-        <v>10.464</v>
+        <v>10.43</v>
       </c>
       <c r="AF288" t="n">
-        <v>24.112</v>
+        <v>24.154</v>
       </c>
       <c r="AG288" t="n">
-        <v>11.529</v>
+        <v>11.925</v>
       </c>
       <c r="AH288" t="n">
-        <v>6</v>
+        <v>5.963</v>
       </c>
       <c r="AI288" t="n">
-        <v>2.978</v>
+        <v>2.897</v>
       </c>
       <c r="AJ288" t="n">
-        <v>18.97</v>
+        <v>18.6</v>
       </c>
       <c r="AK288" t="n">
-        <v>-4.6</v>
+        <v>0.6</v>
       </c>
       <c r="AL288" t="n">
-        <v>-2.1</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="289">
@@ -35066,22 +35066,22 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F289" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G289" t="b">
         <v>1</v>
       </c>
       <c r="H289" t="n">
-        <v>1852.759</v>
+        <v>1843.146</v>
       </c>
       <c r="I289" t="n">
-        <v>4.0806</v>
+        <v>3.9805</v>
       </c>
       <c r="J289" t="n">
-        <v>1661.5</v>
+        <v>1671.3</v>
       </c>
       <c r="K289" t="n">
         <v>39</v>
@@ -35102,70 +35102,70 @@
         <v>44</v>
       </c>
       <c r="Q289" t="n">
-        <v>116.943</v>
+        <v>116.034</v>
       </c>
       <c r="R289" t="n">
-        <v>106.221</v>
+        <v>107.859</v>
       </c>
       <c r="S289" t="n">
-        <v>10.722</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="T289" t="n">
-        <v>0.31014</v>
+        <v>0.30977</v>
       </c>
       <c r="U289" t="n">
-        <v>0.14624</v>
+        <v>0.14563</v>
       </c>
       <c r="V289" t="n">
-        <v>86.69</v>
+        <v>85.77</v>
       </c>
       <c r="W289" t="n">
-        <v>78.33</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="X289" t="n">
-        <v>0.6706</v>
+        <v>0.64</v>
       </c>
       <c r="Y289" t="n">
-        <v>29.32</v>
+        <v>28.996</v>
       </c>
       <c r="Z289" t="n">
-        <v>64.04000000000001</v>
+        <v>63.753</v>
       </c>
       <c r="AA289" t="n">
-        <v>10.779</v>
+        <v>10.596</v>
       </c>
       <c r="AB289" t="n">
-        <v>29.559</v>
+        <v>29.411</v>
       </c>
       <c r="AC289" t="n">
-        <v>17.327</v>
+        <v>17.385</v>
       </c>
       <c r="AD289" t="n">
-        <v>23.668</v>
+        <v>23.625</v>
       </c>
       <c r="AE289" t="n">
-        <v>11.21</v>
+        <v>11.124</v>
       </c>
       <c r="AF289" t="n">
-        <v>24.294</v>
+        <v>24.16</v>
       </c>
       <c r="AG289" t="n">
-        <v>17.823</v>
+        <v>17.582</v>
       </c>
       <c r="AH289" t="n">
-        <v>8.025</v>
+        <v>7.898</v>
       </c>
       <c r="AI289" t="n">
-        <v>3.329</v>
+        <v>3.2</v>
       </c>
       <c r="AJ289" t="n">
-        <v>18.924</v>
+        <v>19.109</v>
       </c>
       <c r="AK289" t="n">
-        <v>0.2</v>
+        <v>-4.8</v>
       </c>
       <c r="AL289" t="n">
-        <v>-2.1</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="290">
@@ -37706,22 +37706,22 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F311" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G311" t="b">
         <v>1</v>
       </c>
       <c r="H311" t="n">
-        <v>1694.511</v>
+        <v>1670.865</v>
       </c>
       <c r="I311" t="n">
-        <v>1.7793</v>
+        <v>1.7868</v>
       </c>
       <c r="J311" t="n">
-        <v>1439.1</v>
+        <v>1446.8</v>
       </c>
       <c r="K311" t="n">
         <v>110</v>
@@ -37742,70 +37742,70 @@
         <v>96</v>
       </c>
       <c r="Q311" t="n">
-        <v>114.505</v>
+        <v>113.876</v>
       </c>
       <c r="R311" t="n">
-        <v>103.212</v>
+        <v>104.148</v>
       </c>
       <c r="S311" t="n">
-        <v>11.293</v>
+        <v>9.728</v>
       </c>
       <c r="T311" t="n">
-        <v>0.31717</v>
+        <v>0.31802</v>
       </c>
       <c r="U311" t="n">
-        <v>0.139</v>
+        <v>0.13928</v>
       </c>
       <c r="V311" t="n">
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="W311" t="n">
-        <v>67.73</v>
+        <v>68.23</v>
       </c>
       <c r="X311" t="n">
-        <v>0.8083</v>
+        <v>0.7742</v>
       </c>
       <c r="Y311" t="n">
-        <v>25.351</v>
+        <v>25.301</v>
       </c>
       <c r="Z311" t="n">
-        <v>57.851</v>
+        <v>57.712</v>
       </c>
       <c r="AA311" t="n">
-        <v>8.211</v>
+        <v>7.986</v>
       </c>
       <c r="AB311" t="n">
-        <v>22.742</v>
+        <v>22.641</v>
       </c>
       <c r="AC311" t="n">
-        <v>16.561</v>
+        <v>16.379</v>
       </c>
       <c r="AD311" t="n">
-        <v>23.903</v>
+        <v>23.68</v>
       </c>
       <c r="AE311" t="n">
-        <v>11.94</v>
+        <v>11.796</v>
       </c>
       <c r="AF311" t="n">
-        <v>25.167</v>
+        <v>24.844</v>
       </c>
       <c r="AG311" t="n">
-        <v>13.403</v>
+        <v>13.132</v>
       </c>
       <c r="AH311" t="n">
-        <v>5.054</v>
+        <v>5.182</v>
       </c>
       <c r="AI311" t="n">
-        <v>2.351</v>
+        <v>2.421</v>
       </c>
       <c r="AJ311" t="n">
-        <v>17.106</v>
+        <v>17.093</v>
       </c>
       <c r="AK311" t="n">
-        <v>5</v>
+        <v>-3.4</v>
       </c>
       <c r="AL311" t="n">
-        <v>6.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="312">
@@ -38786,22 +38786,22 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F320" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G320" t="b">
         <v>1</v>
       </c>
       <c r="H320" t="n">
-        <v>1797.509</v>
+        <v>1784.161</v>
       </c>
       <c r="I320" t="n">
-        <v>3.4141</v>
+        <v>3.6722</v>
       </c>
       <c r="J320" t="n">
-        <v>1569.9</v>
+        <v>1572.5</v>
       </c>
       <c r="K320" t="n">
         <v>45</v>
@@ -38822,70 +38822,70 @@
         <v>43</v>
       </c>
       <c r="Q320" t="n">
-        <v>117.658</v>
+        <v>116.484</v>
       </c>
       <c r="R320" t="n">
-        <v>103.371</v>
+        <v>103.756</v>
       </c>
       <c r="S320" t="n">
-        <v>14.287</v>
+        <v>12.728</v>
       </c>
       <c r="T320" t="n">
-        <v>0.29349</v>
+        <v>0.29816</v>
       </c>
       <c r="U320" t="n">
-        <v>0.14585</v>
+        <v>0.14635</v>
       </c>
       <c r="V320" t="n">
-        <v>81.58</v>
+        <v>80.62</v>
       </c>
       <c r="W320" t="n">
-        <v>71.70999999999999</v>
+        <v>71.81</v>
       </c>
       <c r="X320" t="n">
-        <v>0.8017</v>
+        <v>0.7714</v>
       </c>
       <c r="Y320" t="n">
-        <v>26.819</v>
+        <v>26.664</v>
       </c>
       <c r="Z320" t="n">
-        <v>58.501</v>
+        <v>58.671</v>
       </c>
       <c r="AA320" t="n">
-        <v>9.275</v>
+        <v>9.204000000000001</v>
       </c>
       <c r="AB320" t="n">
-        <v>25.545</v>
+        <v>25.746</v>
       </c>
       <c r="AC320" t="n">
-        <v>18.514</v>
+        <v>17.98</v>
       </c>
       <c r="AD320" t="n">
-        <v>25.183</v>
+        <v>24.542</v>
       </c>
       <c r="AE320" t="n">
-        <v>10.264</v>
+        <v>10.319</v>
       </c>
       <c r="AF320" t="n">
-        <v>24.56</v>
+        <v>24.218</v>
       </c>
       <c r="AG320" t="n">
-        <v>14.233</v>
+        <v>13.979</v>
       </c>
       <c r="AH320" t="n">
-        <v>7.405</v>
+        <v>7.421</v>
       </c>
       <c r="AI320" t="n">
-        <v>4.229</v>
+        <v>4.177</v>
       </c>
       <c r="AJ320" t="n">
-        <v>17.283</v>
+        <v>17.204</v>
       </c>
       <c r="AK320" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="AL320" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="321">
@@ -39026,22 +39026,22 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F322" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G322" t="b">
         <v>1</v>
       </c>
       <c r="H322" t="n">
-        <v>1963.829</v>
+        <v>1939.405</v>
       </c>
       <c r="I322" t="n">
-        <v>1.4886</v>
+        <v>1.4161</v>
       </c>
       <c r="J322" t="n">
-        <v>1716.9</v>
+        <v>1726.2</v>
       </c>
       <c r="K322" t="n">
         <v>12</v>
@@ -39062,70 +39062,70 @@
         <v>13</v>
       </c>
       <c r="Q322" t="n">
-        <v>122.218</v>
+        <v>121.911</v>
       </c>
       <c r="R322" t="n">
-        <v>106.709</v>
+        <v>107.07</v>
       </c>
       <c r="S322" t="n">
-        <v>15.509</v>
+        <v>14.841</v>
       </c>
       <c r="T322" t="n">
-        <v>0.28967</v>
+        <v>0.29281</v>
       </c>
       <c r="U322" t="n">
-        <v>0.13117</v>
+        <v>0.13038</v>
       </c>
       <c r="V322" t="n">
-        <v>86.04000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="W322" t="n">
-        <v>74.94</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="X322" t="n">
-        <v>0.7734</v>
+        <v>0.7439</v>
       </c>
       <c r="Y322" t="n">
-        <v>28.917</v>
+        <v>28.766</v>
       </c>
       <c r="Z322" t="n">
-        <v>60.998</v>
+        <v>60.976</v>
       </c>
       <c r="AA322" t="n">
-        <v>9.34</v>
+        <v>9.473000000000001</v>
       </c>
       <c r="AB322" t="n">
-        <v>26.521</v>
+        <v>26.916</v>
       </c>
       <c r="AC322" t="n">
-        <v>18.388</v>
+        <v>18.136</v>
       </c>
       <c r="AD322" t="n">
-        <v>23.285</v>
+        <v>23.16</v>
       </c>
       <c r="AE322" t="n">
-        <v>9.935</v>
+        <v>9.981</v>
       </c>
       <c r="AF322" t="n">
-        <v>23.865</v>
+        <v>23.656</v>
       </c>
       <c r="AG322" t="n">
-        <v>16.105</v>
+        <v>16.074</v>
       </c>
       <c r="AH322" t="n">
-        <v>7.871</v>
+        <v>7.846</v>
       </c>
       <c r="AI322" t="n">
-        <v>4.529</v>
+        <v>4.523</v>
       </c>
       <c r="AJ322" t="n">
-        <v>19.072</v>
+        <v>19.031</v>
       </c>
       <c r="AK322" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AL322" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="323">

--- a/team_snapshot_2026.xlsx
+++ b/team_snapshot_2026.xlsx
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1954.667</v>
+        <v>1985.69</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3316</v>
+        <v>-1.3006</v>
       </c>
       <c r="J5" t="n">
-        <v>1760.9</v>
+        <v>1777.2</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -1022,70 +1022,70 @@
         <v>18</v>
       </c>
       <c r="Q5" t="n">
-        <v>121.89</v>
+        <v>122.085</v>
       </c>
       <c r="R5" t="n">
-        <v>110.305</v>
+        <v>109.744</v>
       </c>
       <c r="S5" t="n">
-        <v>11.585</v>
+        <v>12.341</v>
       </c>
       <c r="T5" t="n">
-        <v>0.28487</v>
+        <v>0.28781</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1295</v>
+        <v>0.13149</v>
       </c>
       <c r="V5" t="n">
-        <v>91.65000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>82.95</v>
+        <v>82.39</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7296</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>30.377</v>
+        <v>30.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>66.008</v>
+        <v>66.074</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.601</v>
+        <v>12.843</v>
       </c>
       <c r="AB5" t="n">
-        <v>35.069</v>
+        <v>35.318</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.327</v>
+        <v>18.091</v>
       </c>
       <c r="AD5" t="n">
-        <v>23.988</v>
+        <v>23.696</v>
       </c>
       <c r="AE5" t="n">
-        <v>11.111</v>
+        <v>11.318</v>
       </c>
       <c r="AF5" t="n">
-        <v>27.558</v>
+        <v>27.599</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.12</v>
+        <v>16.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.361</v>
+        <v>6.424</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.129</v>
+        <v>5.117</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.529</v>
+        <v>18.666</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AL5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6">
@@ -1826,22 +1826,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2272.508</v>
+        <v>2278.515</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6001</v>
+        <v>6.3904</v>
       </c>
       <c r="J12" t="n">
-        <v>1753.9</v>
+        <v>1771.6</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1862,70 +1862,70 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>121.602</v>
+        <v>121.646</v>
       </c>
       <c r="R12" t="n">
-        <v>96.53400000000001</v>
+        <v>96.95099999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>25.069</v>
+        <v>24.694</v>
       </c>
       <c r="T12" t="n">
-        <v>0.29327</v>
+        <v>0.29711</v>
       </c>
       <c r="U12" t="n">
-        <v>0.14976</v>
+        <v>0.15073</v>
       </c>
       <c r="V12" t="n">
-        <v>86.36</v>
+        <v>86.03</v>
       </c>
       <c r="W12" t="n">
-        <v>68.41</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9433</v>
+        <v>0.9448</v>
       </c>
       <c r="Y12" t="n">
-        <v>30.61</v>
+        <v>30.303</v>
       </c>
       <c r="Z12" t="n">
-        <v>60.822</v>
+        <v>60.662</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.887</v>
+        <v>5.924</v>
       </c>
       <c r="AB12" t="n">
-        <v>16.205</v>
+        <v>16.255</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.249</v>
+        <v>19.497</v>
       </c>
       <c r="AD12" t="n">
-        <v>26.335</v>
+        <v>26.724</v>
       </c>
       <c r="AE12" t="n">
-        <v>12.143</v>
+        <v>12.455</v>
       </c>
       <c r="AF12" t="n">
-        <v>28.938</v>
+        <v>28.993</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.908</v>
+        <v>16.607</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.687</v>
+        <v>7.448</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.441</v>
+        <v>4.421</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15.857</v>
+        <v>15.821</v>
       </c>
       <c r="AK12" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="AL12" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="13">
@@ -2666,22 +2666,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1830.518</v>
+        <v>1836.183</v>
       </c>
       <c r="I19" t="n">
-        <v>-7.3446</v>
+        <v>-7.1903</v>
       </c>
       <c r="J19" t="n">
-        <v>1748.1</v>
+        <v>1743</v>
       </c>
       <c r="K19" t="n">
         <v>38</v>
@@ -2702,70 +2702,70 @@
         <v>38</v>
       </c>
       <c r="Q19" t="n">
-        <v>118.347</v>
+        <v>118.616</v>
       </c>
       <c r="R19" t="n">
-        <v>113.34</v>
+        <v>113.595</v>
       </c>
       <c r="S19" t="n">
-        <v>5.007</v>
+        <v>5.021</v>
       </c>
       <c r="T19" t="n">
-        <v>0.34722</v>
+        <v>0.34374</v>
       </c>
       <c r="U19" t="n">
-        <v>0.14503</v>
+        <v>0.14484</v>
       </c>
       <c r="V19" t="n">
-        <v>82.55</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>78.92</v>
+        <v>79.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.5468</v>
       </c>
       <c r="Y19" t="n">
-        <v>27.293</v>
+        <v>27.386</v>
       </c>
       <c r="Z19" t="n">
-        <v>60.068</v>
+        <v>59.983</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.249000000000001</v>
+        <v>8.207000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>24.303</v>
+        <v>24.187</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.711</v>
+        <v>19.922</v>
       </c>
       <c r="AD19" t="n">
-        <v>26.441</v>
+        <v>26.732</v>
       </c>
       <c r="AE19" t="n">
-        <v>12.068</v>
+        <v>11.983</v>
       </c>
       <c r="AF19" t="n">
-        <v>22.298</v>
+        <v>22.56</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.872</v>
+        <v>12.904</v>
       </c>
       <c r="AH19" t="n">
-        <v>7.322</v>
+        <v>7.229</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.213</v>
+        <v>4.198</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17.303</v>
+        <v>17.155</v>
       </c>
       <c r="AK19" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
@@ -5066,22 +5066,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1710.414</v>
+        <v>1684.049</v>
       </c>
       <c r="I39" t="n">
-        <v>6.8262</v>
+        <v>6.4442</v>
       </c>
       <c r="J39" t="n">
-        <v>1600.4</v>
+        <v>1602.4</v>
       </c>
       <c r="K39" t="n">
         <v>73</v>
@@ -5102,70 +5102,70 @@
         <v>67</v>
       </c>
       <c r="Q39" t="n">
-        <v>110.668</v>
+        <v>110.457</v>
       </c>
       <c r="R39" t="n">
-        <v>104.285</v>
+        <v>104.585</v>
       </c>
       <c r="S39" t="n">
-        <v>6.383</v>
+        <v>5.872</v>
       </c>
       <c r="T39" t="n">
-        <v>0.23394</v>
+        <v>0.23672</v>
       </c>
       <c r="U39" t="n">
-        <v>0.14794</v>
+        <v>0.14591</v>
       </c>
       <c r="V39" t="n">
-        <v>77.95</v>
+        <v>77.7</v>
       </c>
       <c r="W39" t="n">
-        <v>73.31</v>
+        <v>73.42</v>
       </c>
       <c r="X39" t="n">
-        <v>0.6599</v>
+        <v>0.63</v>
       </c>
       <c r="Y39" t="n">
-        <v>26.065</v>
+        <v>26.08</v>
       </c>
       <c r="Z39" t="n">
-        <v>58.02</v>
+        <v>58.39</v>
       </c>
       <c r="AA39" t="n">
-        <v>9.25</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB39" t="n">
-        <v>24.94</v>
+        <v>25.19</v>
       </c>
       <c r="AC39" t="n">
-        <v>16.575</v>
+        <v>16.24</v>
       </c>
       <c r="AD39" t="n">
-        <v>21.274</v>
+        <v>21</v>
       </c>
       <c r="AE39" t="n">
-        <v>7.495</v>
+        <v>7.68</v>
       </c>
       <c r="AF39" t="n">
-        <v>24.215</v>
+        <v>24.36</v>
       </c>
       <c r="AG39" t="n">
-        <v>14.168</v>
+        <v>14.09</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.888</v>
+        <v>5.93</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.999</v>
+        <v>3.03</v>
       </c>
       <c r="AJ39" t="n">
-        <v>18.864</v>
+        <v>18.67</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="40">
@@ -7346,22 +7346,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F58" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>2053.381</v>
+        <v>2068.556</v>
       </c>
       <c r="I58" t="n">
-        <v>6.6189</v>
+        <v>6.1349</v>
       </c>
       <c r="J58" t="n">
-        <v>1662.8</v>
+        <v>1675.6</v>
       </c>
       <c r="K58" t="n">
         <v>11</v>
@@ -7382,70 +7382,70 @@
         <v>10</v>
       </c>
       <c r="Q58" t="n">
-        <v>116.791</v>
+        <v>116.645</v>
       </c>
       <c r="R58" t="n">
-        <v>98.316</v>
+        <v>97.91500000000001</v>
       </c>
       <c r="S58" t="n">
-        <v>18.475</v>
+        <v>18.73</v>
       </c>
       <c r="T58" t="n">
-        <v>0.30395</v>
+        <v>0.30311</v>
       </c>
       <c r="U58" t="n">
-        <v>0.15867</v>
+        <v>0.16219</v>
       </c>
       <c r="V58" t="n">
-        <v>77.67</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="W58" t="n">
-        <v>65.34</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="X58" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8622</v>
       </c>
       <c r="Y58" t="n">
-        <v>28.431</v>
+        <v>28.207</v>
       </c>
       <c r="Z58" t="n">
-        <v>58.882</v>
+        <v>58.478</v>
       </c>
       <c r="AA58" t="n">
-        <v>8.199999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB58" t="n">
         <v>23.697</v>
       </c>
       <c r="AC58" t="n">
-        <v>12.603</v>
+        <v>12.829</v>
       </c>
       <c r="AD58" t="n">
-        <v>17.603</v>
+        <v>17.721</v>
       </c>
       <c r="AE58" t="n">
-        <v>10.693</v>
+        <v>10.642</v>
       </c>
       <c r="AF58" t="n">
-        <v>24.017</v>
+        <v>24.036</v>
       </c>
       <c r="AG58" t="n">
-        <v>18.516</v>
+        <v>18.397</v>
       </c>
       <c r="AH58" t="n">
-        <v>6.887</v>
+        <v>6.89</v>
       </c>
       <c r="AI58" t="n">
-        <v>5.107</v>
+        <v>5.138</v>
       </c>
       <c r="AJ58" t="n">
-        <v>18.048</v>
+        <v>18.127</v>
       </c>
       <c r="AK58" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AL58" t="n">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="59">
@@ -11306,22 +11306,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F91" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G91" t="b">
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>2007.171</v>
+        <v>1970.43</v>
       </c>
       <c r="I91" t="n">
-        <v>3.5894</v>
+        <v>3.6774</v>
       </c>
       <c r="J91" t="n">
-        <v>1703.3</v>
+        <v>1725.7</v>
       </c>
       <c r="K91" t="n">
         <v>4</v>
@@ -11342,70 +11342,70 @@
         <v>4</v>
       </c>
       <c r="Q91" t="n">
-        <v>121.802</v>
+        <v>121.291</v>
       </c>
       <c r="R91" t="n">
-        <v>99.018</v>
+        <v>99.98099999999999</v>
       </c>
       <c r="S91" t="n">
-        <v>22.784</v>
+        <v>21.31</v>
       </c>
       <c r="T91" t="n">
-        <v>0.3326</v>
+        <v>0.33433</v>
       </c>
       <c r="U91" t="n">
-        <v>0.15503</v>
+        <v>0.15588</v>
       </c>
       <c r="V91" t="n">
-        <v>87.83</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="W91" t="n">
-        <v>71.34999999999999</v>
+        <v>71.56</v>
       </c>
       <c r="X91" t="n">
-        <v>0.796</v>
+        <v>0.7647</v>
       </c>
       <c r="Y91" t="n">
-        <v>31.451</v>
+        <v>31.126</v>
       </c>
       <c r="Z91" t="n">
-        <v>64.551</v>
+        <v>64</v>
       </c>
       <c r="AA91" t="n">
-        <v>7.611</v>
+        <v>7.566</v>
       </c>
       <c r="AB91" t="n">
-        <v>23.952</v>
+        <v>23.972</v>
       </c>
       <c r="AC91" t="n">
-        <v>17.817</v>
+        <v>17.71</v>
       </c>
       <c r="AD91" t="n">
-        <v>24.876</v>
+        <v>24.832</v>
       </c>
       <c r="AE91" t="n">
-        <v>14.572</v>
+        <v>14.39</v>
       </c>
       <c r="AF91" t="n">
-        <v>28.676</v>
+        <v>28.159</v>
       </c>
       <c r="AG91" t="n">
-        <v>17.345</v>
+        <v>17.115</v>
       </c>
       <c r="AH91" t="n">
-        <v>6.681</v>
+        <v>6.606</v>
       </c>
       <c r="AI91" t="n">
-        <v>5.135</v>
+        <v>4.928</v>
       </c>
       <c r="AJ91" t="n">
-        <v>17.681</v>
+        <v>17.754</v>
       </c>
       <c r="AK91" t="n">
-        <v>18.2</v>
+        <v>11.2</v>
       </c>
       <c r="AL91" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92">
@@ -12146,22 +12146,22 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F98" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G98" t="b">
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>1546.505</v>
+        <v>1540.737</v>
       </c>
       <c r="I98" t="n">
-        <v>-3.6146</v>
+        <v>-3.3693</v>
       </c>
       <c r="J98" t="n">
-        <v>1543.8</v>
+        <v>1553.1</v>
       </c>
       <c r="K98" t="n">
         <v>85</v>
@@ -12182,70 +12182,70 @@
         <v>91</v>
       </c>
       <c r="Q98" t="n">
-        <v>114.986</v>
+        <v>113.989</v>
       </c>
       <c r="R98" t="n">
-        <v>105.859</v>
+        <v>106.612</v>
       </c>
       <c r="S98" t="n">
-        <v>9.127000000000001</v>
+        <v>7.378</v>
       </c>
       <c r="T98" t="n">
-        <v>0.32167</v>
+        <v>0.3226</v>
       </c>
       <c r="U98" t="n">
-        <v>0.17626</v>
+        <v>0.17667</v>
       </c>
       <c r="V98" t="n">
-        <v>81.48999999999999</v>
+        <v>80.69</v>
       </c>
       <c r="W98" t="n">
-        <v>74.92</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="X98" t="n">
-        <v>0.5508</v>
+        <v>0.5236</v>
       </c>
       <c r="Y98" t="n">
-        <v>28.036</v>
+        <v>27.778</v>
       </c>
       <c r="Z98" t="n">
-        <v>60.217</v>
+        <v>60.371</v>
       </c>
       <c r="AA98" t="n">
-        <v>9.922000000000001</v>
+        <v>9.952999999999999</v>
       </c>
       <c r="AB98" t="n">
-        <v>27.995</v>
+        <v>28.309</v>
       </c>
       <c r="AC98" t="n">
-        <v>15.371</v>
+        <v>15.069</v>
       </c>
       <c r="AD98" t="n">
-        <v>21.246</v>
+        <v>20.782</v>
       </c>
       <c r="AE98" t="n">
-        <v>11.276</v>
+        <v>11.331</v>
       </c>
       <c r="AF98" t="n">
-        <v>23.449</v>
+        <v>23.476</v>
       </c>
       <c r="AG98" t="n">
-        <v>15.424</v>
+        <v>15.218</v>
       </c>
       <c r="AH98" t="n">
-        <v>7.461</v>
+        <v>7.356</v>
       </c>
       <c r="AI98" t="n">
-        <v>3.335</v>
+        <v>3.371</v>
       </c>
       <c r="AJ98" t="n">
-        <v>18.161</v>
+        <v>18.105</v>
       </c>
       <c r="AK98" t="n">
-        <v>0.2</v>
+        <v>-6.6</v>
       </c>
       <c r="AL98" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="99">
@@ -15026,22 +15026,22 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F122" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G122" t="b">
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>1594.577</v>
+        <v>1617.365</v>
       </c>
       <c r="I122" t="n">
-        <v>2.1793</v>
+        <v>2.1828</v>
       </c>
       <c r="J122" t="n">
-        <v>1508.2</v>
+        <v>1513.3</v>
       </c>
       <c r="K122" t="n">
         <v>103</v>
@@ -15062,70 +15062,70 @@
         <v>95</v>
       </c>
       <c r="Q122" t="n">
-        <v>110.094</v>
+        <v>110.138</v>
       </c>
       <c r="R122" t="n">
-        <v>101.357</v>
+        <v>101.764</v>
       </c>
       <c r="S122" t="n">
-        <v>8.738</v>
+        <v>8.374000000000001</v>
       </c>
       <c r="T122" t="n">
-        <v>0.25529</v>
+        <v>0.25849</v>
       </c>
       <c r="U122" t="n">
-        <v>0.15942</v>
+        <v>0.15917</v>
       </c>
       <c r="V122" t="n">
-        <v>74.73</v>
+        <v>74.81</v>
       </c>
       <c r="W122" t="n">
-        <v>68.65000000000001</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="X122" t="n">
-        <v>0.6284</v>
+        <v>0.6394</v>
       </c>
       <c r="Y122" t="n">
-        <v>27</v>
+        <v>26.923</v>
       </c>
       <c r="Z122" t="n">
-        <v>57.961</v>
+        <v>58.025</v>
       </c>
       <c r="AA122" t="n">
-        <v>8.819000000000001</v>
+        <v>8.827999999999999</v>
       </c>
       <c r="AB122" t="n">
-        <v>24.781</v>
+        <v>25.007</v>
       </c>
       <c r="AC122" t="n">
-        <v>12.588</v>
+        <v>12.802</v>
       </c>
       <c r="AD122" t="n">
-        <v>17.752</v>
+        <v>17.875</v>
       </c>
       <c r="AE122" t="n">
-        <v>8.619</v>
+        <v>8.678000000000001</v>
       </c>
       <c r="AF122" t="n">
-        <v>25.431</v>
+        <v>25.177</v>
       </c>
       <c r="AG122" t="n">
-        <v>14.032</v>
+        <v>13.893</v>
       </c>
       <c r="AH122" t="n">
-        <v>5.637</v>
+        <v>5.639</v>
       </c>
       <c r="AI122" t="n">
-        <v>2.257</v>
+        <v>2.24</v>
       </c>
       <c r="AJ122" t="n">
-        <v>17.221</v>
+        <v>17.279</v>
       </c>
       <c r="AK122" t="n">
-        <v>-1.2</v>
+        <v>2.2</v>
       </c>
       <c r="AL122" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="123">
@@ -15626,22 +15626,22 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F127" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G127" t="b">
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>1860.117</v>
+        <v>1896.858</v>
       </c>
       <c r="I127" t="n">
-        <v>3.0379</v>
+        <v>2.8676</v>
       </c>
       <c r="J127" t="n">
-        <v>1717.1</v>
+        <v>1722.3</v>
       </c>
       <c r="K127" t="n">
         <v>25</v>
@@ -15662,70 +15662,70 @@
         <v>27</v>
       </c>
       <c r="Q127" t="n">
-        <v>119.224</v>
+        <v>119.243</v>
       </c>
       <c r="R127" t="n">
-        <v>105.017</v>
+        <v>105.476</v>
       </c>
       <c r="S127" t="n">
-        <v>14.206</v>
+        <v>13.767</v>
       </c>
       <c r="T127" t="n">
-        <v>0.29176</v>
+        <v>0.29258</v>
       </c>
       <c r="U127" t="n">
-        <v>0.14178</v>
+        <v>0.1441</v>
       </c>
       <c r="V127" t="n">
         <v>74.90000000000001</v>
       </c>
       <c r="W127" t="n">
-        <v>65.78</v>
+        <v>66.05</v>
       </c>
       <c r="X127" t="n">
-        <v>0.6503</v>
+        <v>0.6601</v>
       </c>
       <c r="Y127" t="n">
-        <v>26.283</v>
+        <v>26.2</v>
       </c>
       <c r="Z127" t="n">
-        <v>53.854</v>
+        <v>53.562</v>
       </c>
       <c r="AA127" t="n">
-        <v>8.038</v>
+        <v>7.954</v>
       </c>
       <c r="AB127" t="n">
-        <v>22.533</v>
+        <v>22.37</v>
       </c>
       <c r="AC127" t="n">
-        <v>14.061</v>
+        <v>14.336</v>
       </c>
       <c r="AD127" t="n">
-        <v>18.323</v>
+        <v>18.702</v>
       </c>
       <c r="AE127" t="n">
-        <v>8.048</v>
+        <v>8.065</v>
       </c>
       <c r="AF127" t="n">
-        <v>19.506</v>
+        <v>19.473</v>
       </c>
       <c r="AG127" t="n">
-        <v>15.205</v>
+        <v>15.338</v>
       </c>
       <c r="AH127" t="n">
-        <v>7.001</v>
+        <v>7.028</v>
       </c>
       <c r="AI127" t="n">
-        <v>2</v>
+        <v>1.963</v>
       </c>
       <c r="AJ127" t="n">
-        <v>17.766</v>
+        <v>17.745</v>
       </c>
       <c r="AK127" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="AL127" t="n">
-        <v>-1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -15746,22 +15746,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F128" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G128" t="b">
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>2040.699</v>
+        <v>2057.221</v>
       </c>
       <c r="I128" t="n">
-        <v>1.9908</v>
+        <v>1.8048</v>
       </c>
       <c r="J128" t="n">
-        <v>1704.9</v>
+        <v>1720.3</v>
       </c>
       <c r="K128" t="n">
         <v>6</v>
@@ -15782,70 +15782,70 @@
         <v>6</v>
       </c>
       <c r="Q128" t="n">
-        <v>119.647</v>
+        <v>119.437</v>
       </c>
       <c r="R128" t="n">
-        <v>95.52800000000001</v>
+        <v>95.352</v>
       </c>
       <c r="S128" t="n">
-        <v>24.119</v>
+        <v>24.085</v>
       </c>
       <c r="T128" t="n">
-        <v>0.32421</v>
+        <v>0.32237</v>
       </c>
       <c r="U128" t="n">
-        <v>0.14659</v>
+        <v>0.14503</v>
       </c>
       <c r="V128" t="n">
-        <v>82.73</v>
+        <v>82.52</v>
       </c>
       <c r="W128" t="n">
-        <v>65.45999999999999</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="X128" t="n">
-        <v>0.8015</v>
+        <v>0.8069</v>
       </c>
       <c r="Y128" t="n">
-        <v>29.492</v>
+        <v>29.379</v>
       </c>
       <c r="Z128" t="n">
-        <v>60.655</v>
+        <v>60.586</v>
       </c>
       <c r="AA128" t="n">
-        <v>9.157</v>
+        <v>9.138</v>
       </c>
       <c r="AB128" t="n">
-        <v>23.688</v>
+        <v>23.834</v>
       </c>
       <c r="AC128" t="n">
-        <v>13.966</v>
+        <v>14.021</v>
       </c>
       <c r="AD128" t="n">
-        <v>20.59</v>
+        <v>20.662</v>
       </c>
       <c r="AE128" t="n">
-        <v>10.938</v>
+        <v>10.821</v>
       </c>
       <c r="AF128" t="n">
-        <v>22.731</v>
+        <v>22.69</v>
       </c>
       <c r="AG128" t="n">
-        <v>17.392</v>
+        <v>17.331</v>
       </c>
       <c r="AH128" t="n">
-        <v>8.914999999999999</v>
+        <v>9.021000000000001</v>
       </c>
       <c r="AI128" t="n">
-        <v>2.788</v>
+        <v>2.676</v>
       </c>
       <c r="AJ128" t="n">
-        <v>15.922</v>
+        <v>15.917</v>
       </c>
       <c r="AK128" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="AL128" t="n">
-        <v>10.8</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="129">
@@ -16586,22 +16586,22 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F135" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G135" t="b">
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>1979.25</v>
+        <v>1953.755</v>
       </c>
       <c r="I135" t="n">
-        <v>9.864800000000001</v>
+        <v>9.4422</v>
       </c>
       <c r="J135" t="n">
-        <v>1780.1</v>
+        <v>1795</v>
       </c>
       <c r="K135" t="n">
         <v>21</v>
@@ -16622,70 +16622,70 @@
         <v>21</v>
       </c>
       <c r="Q135" t="n">
-        <v>109.767</v>
+        <v>109.195</v>
       </c>
       <c r="R135" t="n">
-        <v>100.723</v>
+        <v>100.635</v>
       </c>
       <c r="S135" t="n">
-        <v>9.044</v>
+        <v>8.561</v>
       </c>
       <c r="T135" t="n">
-        <v>0.25343</v>
+        <v>0.25554</v>
       </c>
       <c r="U135" t="n">
-        <v>0.14997</v>
+        <v>0.14891</v>
       </c>
       <c r="V135" t="n">
-        <v>75.33</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="W135" t="n">
-        <v>69.02</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="X135" t="n">
-        <v>0.7091</v>
+        <v>0.6787</v>
       </c>
       <c r="Y135" t="n">
-        <v>26.727</v>
+        <v>26.669</v>
       </c>
       <c r="Z135" t="n">
-        <v>59.269</v>
+        <v>59.583</v>
       </c>
       <c r="AA135" t="n">
-        <v>7.229</v>
+        <v>7.408</v>
       </c>
       <c r="AB135" t="n">
-        <v>20.978</v>
+        <v>21.538</v>
       </c>
       <c r="AC135" t="n">
-        <v>14.647</v>
+        <v>14.343</v>
       </c>
       <c r="AD135" t="n">
-        <v>19.033</v>
+        <v>18.777</v>
       </c>
       <c r="AE135" t="n">
-        <v>9.446999999999999</v>
+        <v>9.500999999999999</v>
       </c>
       <c r="AF135" t="n">
-        <v>27.684</v>
+        <v>27.545</v>
       </c>
       <c r="AG135" t="n">
-        <v>14.022</v>
+        <v>14.008</v>
       </c>
       <c r="AH135" t="n">
-        <v>5.465</v>
+        <v>5.529</v>
       </c>
       <c r="AI135" t="n">
-        <v>5.658</v>
+        <v>5.574</v>
       </c>
       <c r="AJ135" t="n">
-        <v>14.436</v>
+        <v>14.54</v>
       </c>
       <c r="AK135" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL135" t="n">
-        <v>-3.2</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="136">
@@ -17066,22 +17066,22 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F139" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G139" t="b">
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>1905.506</v>
+        <v>1888.985</v>
       </c>
       <c r="I139" t="n">
-        <v>4.5369</v>
+        <v>4.416</v>
       </c>
       <c r="J139" t="n">
-        <v>1734</v>
+        <v>1743.2</v>
       </c>
       <c r="K139" t="n">
         <v>28</v>
@@ -17102,70 +17102,70 @@
         <v>28</v>
       </c>
       <c r="Q139" t="n">
-        <v>116.168</v>
+        <v>115.322</v>
       </c>
       <c r="R139" t="n">
-        <v>106.38</v>
+        <v>106.864</v>
       </c>
       <c r="S139" t="n">
-        <v>9.788</v>
+        <v>8.458</v>
       </c>
       <c r="T139" t="n">
-        <v>0.30777</v>
+        <v>0.30343</v>
       </c>
       <c r="U139" t="n">
-        <v>0.14633</v>
+        <v>0.15168</v>
       </c>
       <c r="V139" t="n">
-        <v>81.06999999999999</v>
+        <v>80.36</v>
       </c>
       <c r="W139" t="n">
-        <v>74.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="X139" t="n">
-        <v>0.6318</v>
+        <v>0.6061</v>
       </c>
       <c r="Y139" t="n">
-        <v>28.205</v>
+        <v>27.915</v>
       </c>
       <c r="Z139" t="n">
-        <v>60.593</v>
+        <v>60.015</v>
       </c>
       <c r="AA139" t="n">
-        <v>8.131</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="AB139" t="n">
-        <v>23.638</v>
+        <v>23.65</v>
       </c>
       <c r="AC139" t="n">
-        <v>16.359</v>
+        <v>16.215</v>
       </c>
       <c r="AD139" t="n">
-        <v>22.614</v>
+        <v>22.428</v>
       </c>
       <c r="AE139" t="n">
-        <v>10.954</v>
+        <v>10.758</v>
       </c>
       <c r="AF139" t="n">
-        <v>24.656</v>
+        <v>24.614</v>
       </c>
       <c r="AG139" t="n">
-        <v>15.885</v>
+        <v>15.684</v>
       </c>
       <c r="AH139" t="n">
-        <v>7.011</v>
+        <v>6.92</v>
       </c>
       <c r="AI139" t="n">
-        <v>4.458</v>
+        <v>4.35</v>
       </c>
       <c r="AJ139" t="n">
-        <v>18.359</v>
+        <v>18.358</v>
       </c>
       <c r="AK139" t="n">
-        <v>0.2</v>
+        <v>-2.2</v>
       </c>
       <c r="AL139" t="n">
-        <v>0.4</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="140">
@@ -20426,22 +20426,22 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F167" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G167" t="b">
         <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>1794.728</v>
+        <v>1783.017</v>
       </c>
       <c r="I167" t="n">
-        <v>11.4257</v>
+        <v>11.1893</v>
       </c>
       <c r="J167" t="n">
-        <v>1636.7</v>
+        <v>1646.6</v>
       </c>
       <c r="K167" t="n">
         <v>31</v>
@@ -20462,70 +20462,70 @@
         <v>32</v>
       </c>
       <c r="Q167" t="n">
-        <v>117.437</v>
+        <v>116.933</v>
       </c>
       <c r="R167" t="n">
-        <v>102.471</v>
+        <v>103.198</v>
       </c>
       <c r="S167" t="n">
-        <v>14.966</v>
+        <v>13.735</v>
       </c>
       <c r="T167" t="n">
-        <v>0.31068</v>
+        <v>0.31465</v>
       </c>
       <c r="U167" t="n">
-        <v>0.15663</v>
+        <v>0.15787</v>
       </c>
       <c r="V167" t="n">
-        <v>81.86</v>
+        <v>81.39</v>
       </c>
       <c r="W167" t="n">
-        <v>70.97</v>
+        <v>71.34</v>
       </c>
       <c r="X167" t="n">
-        <v>0.7673</v>
+        <v>0.7353</v>
       </c>
       <c r="Y167" t="n">
-        <v>29.84</v>
+        <v>29.81</v>
       </c>
       <c r="Z167" t="n">
-        <v>59.855</v>
+        <v>59.974</v>
       </c>
       <c r="AA167" t="n">
-        <v>6.753</v>
+        <v>6.64</v>
       </c>
       <c r="AB167" t="n">
-        <v>19.142</v>
+        <v>19.085</v>
       </c>
       <c r="AC167" t="n">
-        <v>15.429</v>
+        <v>15.127</v>
       </c>
       <c r="AD167" t="n">
-        <v>22.687</v>
+        <v>22.132</v>
       </c>
       <c r="AE167" t="n">
-        <v>11.055</v>
+        <v>11.115</v>
       </c>
       <c r="AF167" t="n">
-        <v>24.356</v>
+        <v>24.09</v>
       </c>
       <c r="AG167" t="n">
-        <v>16.207</v>
+        <v>16.208</v>
       </c>
       <c r="AH167" t="n">
-        <v>7.844</v>
+        <v>7.897</v>
       </c>
       <c r="AI167" t="n">
-        <v>3.338</v>
+        <v>3.301</v>
       </c>
       <c r="AJ167" t="n">
-        <v>15.476</v>
+        <v>15.491</v>
       </c>
       <c r="AK167" t="n">
-        <v>0.4</v>
+        <v>-3.2</v>
       </c>
       <c r="AL167" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="168">
@@ -24146,22 +24146,22 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F198" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G198" t="b">
         <v>1</v>
       </c>
       <c r="H198" t="n">
-        <v>1802.429</v>
+        <v>1808.195</v>
       </c>
       <c r="I198" t="n">
-        <v>2.3893</v>
+        <v>2.0968</v>
       </c>
       <c r="J198" t="n">
-        <v>1593.2</v>
+        <v>1592</v>
       </c>
       <c r="K198" t="n">
         <v>50</v>
@@ -24182,70 +24182,70 @@
         <v>46</v>
       </c>
       <c r="Q198" t="n">
-        <v>116.178</v>
+        <v>116.354</v>
       </c>
       <c r="R198" t="n">
-        <v>103.208</v>
+        <v>102.654</v>
       </c>
       <c r="S198" t="n">
-        <v>12.971</v>
+        <v>13.7</v>
       </c>
       <c r="T198" t="n">
-        <v>0.28453</v>
+        <v>0.28594</v>
       </c>
       <c r="U198" t="n">
-        <v>0.14214</v>
+        <v>0.14241</v>
       </c>
       <c r="V198" t="n">
-        <v>81.06999999999999</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="W198" t="n">
-        <v>72</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="X198" t="n">
-        <v>0.6995</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="Y198" t="n">
-        <v>28.062</v>
+        <v>28.082</v>
       </c>
       <c r="Z198" t="n">
-        <v>60.478</v>
+        <v>60.535</v>
       </c>
       <c r="AA198" t="n">
-        <v>9.183999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AB198" t="n">
-        <v>25.376</v>
+        <v>25.366</v>
       </c>
       <c r="AC198" t="n">
-        <v>15.76</v>
+        <v>15.655</v>
       </c>
       <c r="AD198" t="n">
-        <v>21.653</v>
+        <v>21.605</v>
       </c>
       <c r="AE198" t="n">
-        <v>9.994999999999999</v>
+        <v>10.156</v>
       </c>
       <c r="AF198" t="n">
-        <v>24.618</v>
+        <v>24.806</v>
       </c>
       <c r="AG198" t="n">
-        <v>14.78</v>
+        <v>14.886</v>
       </c>
       <c r="AH198" t="n">
-        <v>7.935</v>
+        <v>7.987</v>
       </c>
       <c r="AI198" t="n">
-        <v>2.776</v>
+        <v>2.878</v>
       </c>
       <c r="AJ198" t="n">
-        <v>17.614</v>
+        <v>17.316</v>
       </c>
       <c r="AK198" t="n">
-        <v>5.2</v>
+        <v>11.8</v>
       </c>
       <c r="AL198" t="n">
-        <v>6.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="199">
@@ -26666,22 +26666,22 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F219" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G219" t="b">
         <v>1</v>
       </c>
       <c r="H219" t="n">
-        <v>1713.594</v>
+        <v>1686.949</v>
       </c>
       <c r="I219" t="n">
-        <v>-1.1886</v>
+        <v>-1.1802</v>
       </c>
       <c r="J219" t="n">
-        <v>1685</v>
+        <v>1684.5</v>
       </c>
       <c r="K219" t="n">
         <v>66</v>
@@ -26702,70 +26702,70 @@
         <v>74</v>
       </c>
       <c r="Q219" t="n">
-        <v>111.537</v>
+        <v>110.918</v>
       </c>
       <c r="R219" t="n">
-        <v>110.394</v>
+        <v>111.177</v>
       </c>
       <c r="S219" t="n">
-        <v>1.144</v>
+        <v>-0.259</v>
       </c>
       <c r="T219" t="n">
-        <v>0.27727</v>
+        <v>0.27908</v>
       </c>
       <c r="U219" t="n">
-        <v>0.15255</v>
+        <v>0.15287</v>
       </c>
       <c r="V219" t="n">
-        <v>84.26000000000001</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="W219" t="n">
-        <v>82.8</v>
+        <v>83.31</v>
       </c>
       <c r="X219" t="n">
-        <v>0.5921</v>
+        <v>0.5664</v>
       </c>
       <c r="Y219" t="n">
-        <v>29.049</v>
+        <v>28.983</v>
       </c>
       <c r="Z219" t="n">
-        <v>62.876</v>
+        <v>63.017</v>
       </c>
       <c r="AA219" t="n">
-        <v>7.758</v>
+        <v>7.699</v>
       </c>
       <c r="AB219" t="n">
-        <v>22.663</v>
+        <v>22.634</v>
       </c>
       <c r="AC219" t="n">
-        <v>18.145</v>
+        <v>17.817</v>
       </c>
       <c r="AD219" t="n">
-        <v>24.464</v>
+        <v>24.174</v>
       </c>
       <c r="AE219" t="n">
-        <v>9.779</v>
+        <v>9.867000000000001</v>
       </c>
       <c r="AF219" t="n">
-        <v>25.404</v>
+        <v>25.386</v>
       </c>
       <c r="AG219" t="n">
-        <v>14.748</v>
+        <v>14.551</v>
       </c>
       <c r="AH219" t="n">
-        <v>7.098</v>
+        <v>7.002</v>
       </c>
       <c r="AI219" t="n">
-        <v>2.544</v>
+        <v>2.649</v>
       </c>
       <c r="AJ219" t="n">
-        <v>17.08</v>
+        <v>16.993</v>
       </c>
       <c r="AK219" t="n">
-        <v>1.2</v>
+        <v>-5.4</v>
       </c>
       <c r="AL219" t="n">
-        <v>-3.9</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="220">
@@ -28586,22 +28586,22 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F235" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G235" t="b">
         <v>1</v>
       </c>
       <c r="H235" t="n">
-        <v>2011.512</v>
+        <v>2023.223</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6772</v>
+        <v>-0.6463</v>
       </c>
       <c r="J235" t="n">
-        <v>1753.9</v>
+        <v>1767</v>
       </c>
       <c r="K235" t="n">
         <v>8</v>
@@ -28622,70 +28622,70 @@
         <v>9</v>
       </c>
       <c r="Q235" t="n">
-        <v>125.909</v>
+        <v>125.552</v>
       </c>
       <c r="R235" t="n">
-        <v>107.355</v>
+        <v>107.346</v>
       </c>
       <c r="S235" t="n">
-        <v>18.555</v>
+        <v>18.206</v>
       </c>
       <c r="T235" t="n">
-        <v>0.31279</v>
+        <v>0.3071</v>
       </c>
       <c r="U235" t="n">
-        <v>0.13549</v>
+        <v>0.13688</v>
       </c>
       <c r="V235" t="n">
-        <v>82.45999999999999</v>
+        <v>82.16</v>
       </c>
       <c r="W235" t="n">
-        <v>70.17</v>
+        <v>70.13</v>
       </c>
       <c r="X235" t="n">
-        <v>0.7796</v>
+        <v>0.7854</v>
       </c>
       <c r="Y235" t="n">
-        <v>30.117</v>
+        <v>29.854</v>
       </c>
       <c r="Z235" t="n">
-        <v>60.234</v>
+        <v>59.739</v>
       </c>
       <c r="AA235" t="n">
-        <v>9.454000000000001</v>
+        <v>9.368</v>
       </c>
       <c r="AB235" t="n">
-        <v>24.523</v>
+        <v>24.165</v>
       </c>
       <c r="AC235" t="n">
-        <v>11.912</v>
+        <v>12.257</v>
       </c>
       <c r="AD235" t="n">
-        <v>16.133</v>
+        <v>16.368</v>
       </c>
       <c r="AE235" t="n">
-        <v>10.702</v>
+        <v>10.437</v>
       </c>
       <c r="AF235" t="n">
-        <v>23.08</v>
+        <v>22.985</v>
       </c>
       <c r="AG235" t="n">
-        <v>19.674</v>
+        <v>19.548</v>
       </c>
       <c r="AH235" t="n">
-        <v>5.496</v>
+        <v>5.586</v>
       </c>
       <c r="AI235" t="n">
-        <v>2.777</v>
+        <v>2.759</v>
       </c>
       <c r="AJ235" t="n">
-        <v>14.901</v>
+        <v>14.713</v>
       </c>
       <c r="AK235" t="n">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="AL235" t="n">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="236">
@@ -31466,22 +31466,22 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F259" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G259" t="b">
         <v>1</v>
       </c>
       <c r="H259" t="n">
-        <v>1560.056</v>
+        <v>1554.391</v>
       </c>
       <c r="I259" t="n">
-        <v>2.1732</v>
+        <v>2.0584</v>
       </c>
       <c r="J259" t="n">
-        <v>1524.1</v>
+        <v>1535.5</v>
       </c>
       <c r="K259" t="n">
         <v>119</v>
@@ -31502,70 +31502,70 @@
         <v>122</v>
       </c>
       <c r="Q259" t="n">
-        <v>100.859</v>
+        <v>101.572</v>
       </c>
       <c r="R259" t="n">
-        <v>97.512</v>
+        <v>98.834</v>
       </c>
       <c r="S259" t="n">
-        <v>3.347</v>
+        <v>2.738</v>
       </c>
       <c r="T259" t="n">
-        <v>0.25248</v>
+        <v>0.24514</v>
       </c>
       <c r="U259" t="n">
-        <v>0.16788</v>
+        <v>0.1658</v>
       </c>
       <c r="V259" t="n">
-        <v>69.59999999999999</v>
+        <v>70.22</v>
       </c>
       <c r="W259" t="n">
-        <v>67.36</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="X259" t="n">
-        <v>0.5974</v>
+        <v>0.5709</v>
       </c>
       <c r="Y259" t="n">
-        <v>24.212</v>
+        <v>24.51</v>
       </c>
       <c r="Z259" t="n">
-        <v>56.508</v>
+        <v>56.665</v>
       </c>
       <c r="AA259" t="n">
-        <v>7.266</v>
+        <v>7.587</v>
       </c>
       <c r="AB259" t="n">
-        <v>22.022</v>
+        <v>22.376</v>
       </c>
       <c r="AC259" t="n">
-        <v>13.912</v>
+        <v>13.611</v>
       </c>
       <c r="AD259" t="n">
-        <v>19.646</v>
+        <v>19.293</v>
       </c>
       <c r="AE259" t="n">
-        <v>7.663</v>
+        <v>7.43</v>
       </c>
       <c r="AF259" t="n">
-        <v>22.049</v>
+        <v>22.03</v>
       </c>
       <c r="AG259" t="n">
-        <v>12.987</v>
+        <v>13.201</v>
       </c>
       <c r="AH259" t="n">
-        <v>7.823</v>
+        <v>7.82</v>
       </c>
       <c r="AI259" t="n">
-        <v>4.863</v>
+        <v>4.85</v>
       </c>
       <c r="AJ259" t="n">
-        <v>16.574</v>
+        <v>16.678</v>
       </c>
       <c r="AK259" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="AL259" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="260">
@@ -33146,22 +33146,22 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F273" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G273" t="b">
         <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>1989.246</v>
+        <v>2014.742</v>
       </c>
       <c r="I273" t="n">
-        <v>5.7241</v>
+        <v>5.7703</v>
       </c>
       <c r="J273" t="n">
-        <v>1684.5</v>
+        <v>1698.7</v>
       </c>
       <c r="K273" t="n">
         <v>17</v>
@@ -33182,70 +33182,70 @@
         <v>16</v>
       </c>
       <c r="Q273" t="n">
-        <v>114.409</v>
+        <v>113.755</v>
       </c>
       <c r="R273" t="n">
-        <v>97.80200000000001</v>
+        <v>97.798</v>
       </c>
       <c r="S273" t="n">
-        <v>16.607</v>
+        <v>15.957</v>
       </c>
       <c r="T273" t="n">
-        <v>0.32084</v>
+        <v>0.31722</v>
       </c>
       <c r="U273" t="n">
-        <v>0.14183</v>
+        <v>0.1451</v>
       </c>
       <c r="V273" t="n">
-        <v>81.47</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="W273" t="n">
-        <v>69.36</v>
+        <v>69.33</v>
       </c>
       <c r="X273" t="n">
-        <v>0.8298</v>
+        <v>0.8345</v>
       </c>
       <c r="Y273" t="n">
-        <v>27.908</v>
+        <v>27.779</v>
       </c>
       <c r="Z273" t="n">
-        <v>61.396</v>
+        <v>61.172</v>
       </c>
       <c r="AA273" t="n">
-        <v>7.022</v>
+        <v>6.931</v>
       </c>
       <c r="AB273" t="n">
-        <v>21.087</v>
+        <v>20.786</v>
       </c>
       <c r="AC273" t="n">
-        <v>18.63</v>
+        <v>18.428</v>
       </c>
       <c r="AD273" t="n">
-        <v>25.659</v>
+        <v>25.386</v>
       </c>
       <c r="AE273" t="n">
-        <v>11.631</v>
+        <v>11.538</v>
       </c>
       <c r="AF273" t="n">
-        <v>24.889</v>
+        <v>25.179</v>
       </c>
       <c r="AG273" t="n">
-        <v>16.148</v>
+        <v>15.924</v>
       </c>
       <c r="AH273" t="n">
-        <v>7.736</v>
+        <v>7.607</v>
       </c>
       <c r="AI273" t="n">
-        <v>4.922</v>
+        <v>5.055</v>
       </c>
       <c r="AJ273" t="n">
-        <v>17.105</v>
+        <v>17.034</v>
       </c>
       <c r="AK273" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
       <c r="AL273" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="274">
@@ -33266,22 +33266,22 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F274" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G274" t="b">
         <v>1</v>
       </c>
       <c r="H274" t="n">
-        <v>1633.092</v>
+        <v>1659.458</v>
       </c>
       <c r="I274" t="n">
-        <v>1.7131</v>
+        <v>1.9645</v>
       </c>
       <c r="J274" t="n">
-        <v>1521.6</v>
+        <v>1527.6</v>
       </c>
       <c r="K274" t="n">
         <v>116</v>
@@ -33302,70 +33302,70 @@
         <v>121</v>
       </c>
       <c r="Q274" t="n">
-        <v>105.758</v>
+        <v>106.077</v>
       </c>
       <c r="R274" t="n">
-        <v>102.729</v>
+        <v>103.137</v>
       </c>
       <c r="S274" t="n">
-        <v>3.029</v>
+        <v>2.94</v>
       </c>
       <c r="T274" t="n">
-        <v>0.28861</v>
+        <v>0.29071</v>
       </c>
       <c r="U274" t="n">
-        <v>0.16399</v>
+        <v>0.16258</v>
       </c>
       <c r="V274" t="n">
-        <v>71.88</v>
+        <v>72.06</v>
       </c>
       <c r="W274" t="n">
-        <v>70.08</v>
+        <v>70.31</v>
       </c>
       <c r="X274" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.669</v>
       </c>
       <c r="Y274" t="n">
-        <v>25.078</v>
+        <v>25.275</v>
       </c>
       <c r="Z274" t="n">
-        <v>59.396</v>
+        <v>59.725</v>
       </c>
       <c r="AA274" t="n">
-        <v>8.241</v>
+        <v>8.278</v>
       </c>
       <c r="AB274" t="n">
-        <v>26.784</v>
+        <v>26.782</v>
       </c>
       <c r="AC274" t="n">
-        <v>13.488</v>
+        <v>13.229</v>
       </c>
       <c r="AD274" t="n">
-        <v>18.139</v>
+        <v>17.935</v>
       </c>
       <c r="AE274" t="n">
-        <v>10.464</v>
+        <v>10.644</v>
       </c>
       <c r="AF274" t="n">
-        <v>25.604</v>
+        <v>25.72</v>
       </c>
       <c r="AG274" t="n">
-        <v>15.025</v>
+        <v>15.171</v>
       </c>
       <c r="AH274" t="n">
-        <v>5.519</v>
+        <v>5.481</v>
       </c>
       <c r="AI274" t="n">
-        <v>4.659</v>
+        <v>4.558</v>
       </c>
       <c r="AJ274" t="n">
-        <v>14.232</v>
+        <v>14.137</v>
       </c>
       <c r="AK274" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AL274" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="275">
@@ -34586,22 +34586,22 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F285" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G285" t="b">
         <v>1</v>
       </c>
       <c r="H285" t="n">
-        <v>1914.838</v>
+        <v>1944.981</v>
       </c>
       <c r="I285" t="n">
-        <v>-1.3934</v>
+        <v>-1.2526</v>
       </c>
       <c r="J285" t="n">
-        <v>1716.9</v>
+        <v>1724</v>
       </c>
       <c r="K285" t="n">
         <v>16</v>
@@ -34622,70 +34622,70 @@
         <v>20</v>
       </c>
       <c r="Q285" t="n">
-        <v>116.955</v>
+        <v>117.137</v>
       </c>
       <c r="R285" t="n">
-        <v>101.617</v>
+        <v>102.163</v>
       </c>
       <c r="S285" t="n">
-        <v>15.338</v>
+        <v>14.975</v>
       </c>
       <c r="T285" t="n">
-        <v>0.35639</v>
+        <v>0.36076</v>
       </c>
       <c r="U285" t="n">
-        <v>0.16761</v>
+        <v>0.16454</v>
       </c>
       <c r="V285" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="W285" t="n">
-        <v>68.83</v>
+        <v>69.09</v>
       </c>
       <c r="X285" t="n">
-        <v>0.68</v>
+        <v>0.6889</v>
       </c>
       <c r="Y285" t="n">
-        <v>28.382</v>
+        <v>28.301</v>
       </c>
       <c r="Z285" t="n">
-        <v>61.036</v>
+        <v>61.364</v>
       </c>
       <c r="AA285" t="n">
-        <v>6.585</v>
+        <v>6.768</v>
       </c>
       <c r="AB285" t="n">
-        <v>19.418</v>
+        <v>20.011</v>
       </c>
       <c r="AC285" t="n">
-        <v>16.047</v>
+        <v>15.757</v>
       </c>
       <c r="AD285" t="n">
-        <v>23.12</v>
+        <v>22.793</v>
       </c>
       <c r="AE285" t="n">
-        <v>14.687</v>
+        <v>14.756</v>
       </c>
       <c r="AF285" t="n">
-        <v>25.945</v>
+        <v>25.646</v>
       </c>
       <c r="AG285" t="n">
-        <v>16.993</v>
+        <v>16.779</v>
       </c>
       <c r="AH285" t="n">
-        <v>7.415</v>
+        <v>7.347</v>
       </c>
       <c r="AI285" t="n">
-        <v>3.542</v>
+        <v>3.614</v>
       </c>
       <c r="AJ285" t="n">
-        <v>17.724</v>
+        <v>17.812</v>
       </c>
       <c r="AK285" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AL285" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="286">
@@ -35306,22 +35306,22 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F291" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G291" t="b">
         <v>1</v>
       </c>
       <c r="H291" t="n">
-        <v>2018.552</v>
+        <v>1987.529</v>
       </c>
       <c r="I291" t="n">
-        <v>8.9857</v>
+        <v>8.4871</v>
       </c>
       <c r="J291" t="n">
-        <v>1767</v>
+        <v>1776.6</v>
       </c>
       <c r="K291" t="n">
         <v>20</v>
@@ -35342,70 +35342,70 @@
         <v>19</v>
       </c>
       <c r="Q291" t="n">
-        <v>118.539</v>
+        <v>117.459</v>
       </c>
       <c r="R291" t="n">
-        <v>106.753</v>
+        <v>107.736</v>
       </c>
       <c r="S291" t="n">
-        <v>11.786</v>
+        <v>9.722</v>
       </c>
       <c r="T291" t="n">
-        <v>0.28763</v>
+        <v>0.29262</v>
       </c>
       <c r="U291" t="n">
-        <v>0.15503</v>
+        <v>0.15476</v>
       </c>
       <c r="V291" t="n">
-        <v>80.83</v>
+        <v>80.12</v>
       </c>
       <c r="W291" t="n">
-        <v>72.56</v>
+        <v>73.25</v>
       </c>
       <c r="X291" t="n">
-        <v>0.7</v>
+        <v>0.6702</v>
       </c>
       <c r="Y291" t="n">
-        <v>29.08</v>
+        <v>28.721</v>
       </c>
       <c r="Z291" t="n">
-        <v>60.71</v>
+        <v>60.796</v>
       </c>
       <c r="AA291" t="n">
-        <v>11.45</v>
+        <v>11.168</v>
       </c>
       <c r="AB291" t="n">
-        <v>28.61</v>
+        <v>28.555</v>
       </c>
       <c r="AC291" t="n">
-        <v>11.88</v>
+        <v>12.153</v>
       </c>
       <c r="AD291" t="n">
-        <v>16.75</v>
+        <v>17.007</v>
       </c>
       <c r="AE291" t="n">
-        <v>10.39</v>
+        <v>10.562</v>
       </c>
       <c r="AF291" t="n">
-        <v>24.58</v>
+        <v>24.438</v>
       </c>
       <c r="AG291" t="n">
-        <v>15.98</v>
+        <v>15.663</v>
       </c>
       <c r="AH291" t="n">
-        <v>5.97</v>
+        <v>6.057</v>
       </c>
       <c r="AI291" t="n">
-        <v>3.77</v>
+        <v>3.767</v>
       </c>
       <c r="AJ291" t="n">
-        <v>16.45</v>
+        <v>16.36</v>
       </c>
       <c r="AK291" t="n">
-        <v>-1.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AL291" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="292">
@@ -36026,22 +36026,22 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F297" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G297" t="b">
         <v>1</v>
       </c>
       <c r="H297" t="n">
-        <v>1682.437</v>
+        <v>1698.087</v>
       </c>
       <c r="I297" t="n">
-        <v>8.0585</v>
+        <v>7.7327</v>
       </c>
       <c r="J297" t="n">
-        <v>1510.5</v>
+        <v>1515.8</v>
       </c>
       <c r="K297" t="n">
         <v>63</v>
@@ -36062,70 +36062,70 @@
         <v>52</v>
       </c>
       <c r="Q297" t="n">
-        <v>121.034</v>
+        <v>121</v>
       </c>
       <c r="R297" t="n">
-        <v>106.412</v>
+        <v>106.231</v>
       </c>
       <c r="S297" t="n">
-        <v>14.622</v>
+        <v>14.769</v>
       </c>
       <c r="T297" t="n">
-        <v>0.28053</v>
+        <v>0.2826</v>
       </c>
       <c r="U297" t="n">
-        <v>0.14866</v>
+        <v>0.15151</v>
       </c>
       <c r="V297" t="n">
-        <v>84.47</v>
+        <v>84.16</v>
       </c>
       <c r="W297" t="n">
-        <v>74.31999999999999</v>
+        <v>73.94</v>
       </c>
       <c r="X297" t="n">
-        <v>0.7829</v>
+        <v>0.7894</v>
       </c>
       <c r="Y297" t="n">
-        <v>27.381</v>
+        <v>27.391</v>
       </c>
       <c r="Z297" t="n">
-        <v>58.439</v>
+        <v>58.361</v>
       </c>
       <c r="AA297" t="n">
-        <v>10.582</v>
+        <v>10.572</v>
       </c>
       <c r="AB297" t="n">
-        <v>27.231</v>
+        <v>27.218</v>
       </c>
       <c r="AC297" t="n">
-        <v>19.128</v>
+        <v>18.808</v>
       </c>
       <c r="AD297" t="n">
-        <v>24.437</v>
+        <v>24.227</v>
       </c>
       <c r="AE297" t="n">
-        <v>9.747999999999999</v>
+        <v>9.965</v>
       </c>
       <c r="AF297" t="n">
-        <v>24.402</v>
+        <v>24.62</v>
       </c>
       <c r="AG297" t="n">
-        <v>15.226</v>
+        <v>15.278</v>
       </c>
       <c r="AH297" t="n">
-        <v>6.665</v>
+        <v>6.528</v>
       </c>
       <c r="AI297" t="n">
-        <v>2.387</v>
+        <v>2.287</v>
       </c>
       <c r="AJ297" t="n">
-        <v>16.156</v>
+        <v>16.032</v>
       </c>
       <c r="AK297" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL297" t="n">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="298">
@@ -36986,22 +36986,22 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F305" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G305" t="b">
         <v>1</v>
       </c>
       <c r="H305" t="n">
-        <v>1897.052</v>
+        <v>1881.876</v>
       </c>
       <c r="I305" t="n">
-        <v>2.9774</v>
+        <v>3.1818</v>
       </c>
       <c r="J305" t="n">
-        <v>1708.6</v>
+        <v>1716.2</v>
       </c>
       <c r="K305" t="n">
         <v>27</v>
@@ -37022,70 +37022,70 @@
         <v>30</v>
       </c>
       <c r="Q305" t="n">
-        <v>116.926</v>
+        <v>116.161</v>
       </c>
       <c r="R305" t="n">
-        <v>107.231</v>
+        <v>107.674</v>
       </c>
       <c r="S305" t="n">
-        <v>9.695</v>
+        <v>8.487</v>
       </c>
       <c r="T305" t="n">
-        <v>0.30733</v>
+        <v>0.30781</v>
       </c>
       <c r="U305" t="n">
-        <v>0.1316</v>
+        <v>0.13337</v>
       </c>
       <c r="V305" t="n">
-        <v>77.64</v>
+        <v>76.94</v>
       </c>
       <c r="W305" t="n">
-        <v>71</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="X305" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="Y305" t="n">
-        <v>27.397</v>
+        <v>27.11</v>
       </c>
       <c r="Z305" t="n">
-        <v>58.839</v>
+        <v>58.434</v>
       </c>
       <c r="AA305" t="n">
-        <v>7.957</v>
+        <v>7.869</v>
       </c>
       <c r="AB305" t="n">
-        <v>21.057</v>
+        <v>20.779</v>
       </c>
       <c r="AC305" t="n">
-        <v>14.9</v>
+        <v>14.883</v>
       </c>
       <c r="AD305" t="n">
-        <v>19.56</v>
+        <v>19.621</v>
       </c>
       <c r="AE305" t="n">
-        <v>9.640000000000001</v>
+        <v>9.545</v>
       </c>
       <c r="AF305" t="n">
-        <v>21.576</v>
+        <v>21.352</v>
       </c>
       <c r="AG305" t="n">
-        <v>16.332</v>
+        <v>16.29</v>
       </c>
       <c r="AH305" t="n">
-        <v>6.449</v>
+        <v>6.317</v>
       </c>
       <c r="AI305" t="n">
-        <v>3.158</v>
+        <v>3.041</v>
       </c>
       <c r="AJ305" t="n">
-        <v>16.872</v>
+        <v>16.89</v>
       </c>
       <c r="AK305" t="n">
-        <v>7</v>
+        <v>-0.4</v>
       </c>
       <c r="AL305" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="306">
@@ -37826,22 +37826,22 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F312" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G312" t="b">
         <v>1</v>
       </c>
       <c r="H312" t="n">
-        <v>1662.23</v>
+        <v>1646.58</v>
       </c>
       <c r="I312" t="n">
-        <v>1.8215</v>
+        <v>1.9334</v>
       </c>
       <c r="J312" t="n">
-        <v>1625.4</v>
+        <v>1627.7</v>
       </c>
       <c r="K312" t="n">
         <v>107</v>
@@ -37862,70 +37862,70 @@
         <v>111</v>
       </c>
       <c r="Q312" t="n">
-        <v>110.869</v>
+        <v>110.556</v>
       </c>
       <c r="R312" t="n">
-        <v>110.996</v>
+        <v>111.362</v>
       </c>
       <c r="S312" t="n">
-        <v>-0.126</v>
+        <v>-0.806</v>
       </c>
       <c r="T312" t="n">
-        <v>0.29015</v>
+        <v>0.29018</v>
       </c>
       <c r="U312" t="n">
-        <v>0.16844</v>
+        <v>0.16506</v>
       </c>
       <c r="V312" t="n">
-        <v>78.93000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="W312" t="n">
-        <v>79.26000000000001</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="X312" t="n">
-        <v>0.52</v>
+        <v>0.4953</v>
       </c>
       <c r="Y312" t="n">
-        <v>27.56</v>
+        <v>27.524</v>
       </c>
       <c r="Z312" t="n">
-        <v>58.32</v>
+        <v>58.388</v>
       </c>
       <c r="AA312" t="n">
-        <v>7.55</v>
+        <v>7.457</v>
       </c>
       <c r="AB312" t="n">
-        <v>21.12</v>
+        <v>21.28</v>
       </c>
       <c r="AC312" t="n">
-        <v>16.26</v>
+        <v>15.965</v>
       </c>
       <c r="AD312" t="n">
-        <v>23.95</v>
+        <v>23.635</v>
       </c>
       <c r="AE312" t="n">
-        <v>9.57</v>
+        <v>9.467000000000001</v>
       </c>
       <c r="AF312" t="n">
-        <v>23.03</v>
+        <v>22.74</v>
       </c>
       <c r="AG312" t="n">
-        <v>14.24</v>
+        <v>14.089</v>
       </c>
       <c r="AH312" t="n">
-        <v>7.23</v>
+        <v>7.31</v>
       </c>
       <c r="AI312" t="n">
-        <v>4.7</v>
+        <v>4.641</v>
       </c>
       <c r="AJ312" t="n">
-        <v>21.55</v>
+        <v>21.438</v>
       </c>
       <c r="AK312" t="n">
-        <v>2</v>
+        <v>-5.6</v>
       </c>
       <c r="AL312" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="313">
@@ -38426,22 +38426,22 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F317" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G317" t="b">
         <v>1</v>
       </c>
       <c r="H317" t="n">
-        <v>1917.024</v>
+        <v>1911.017</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2638</v>
+        <v>0.436</v>
       </c>
       <c r="J317" t="n">
-        <v>1617</v>
+        <v>1632.8</v>
       </c>
       <c r="K317" t="n">
         <v>30</v>
@@ -38462,70 +38462,70 @@
         <v>26</v>
       </c>
       <c r="Q317" t="n">
-        <v>119.887</v>
+        <v>119.218</v>
       </c>
       <c r="R317" t="n">
-        <v>103.861</v>
+        <v>104.375</v>
       </c>
       <c r="S317" t="n">
-        <v>16.026</v>
+        <v>14.843</v>
       </c>
       <c r="T317" t="n">
-        <v>0.30557</v>
+        <v>0.30523</v>
       </c>
       <c r="U317" t="n">
-        <v>0.14772</v>
+        <v>0.14484</v>
       </c>
       <c r="V317" t="n">
-        <v>81.84999999999999</v>
+        <v>81.28</v>
       </c>
       <c r="W317" t="n">
-        <v>71.03</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="X317" t="n">
-        <v>0.8247</v>
+        <v>0.7951</v>
       </c>
       <c r="Y317" t="n">
-        <v>28.701</v>
+        <v>28.578</v>
       </c>
       <c r="Z317" t="n">
-        <v>58.266</v>
+        <v>58.434</v>
       </c>
       <c r="AA317" t="n">
-        <v>8.506</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="AB317" t="n">
-        <v>23.893</v>
+        <v>24.134</v>
       </c>
       <c r="AC317" t="n">
-        <v>15.526</v>
+        <v>15.327</v>
       </c>
       <c r="AD317" t="n">
-        <v>22.146</v>
+        <v>21.819</v>
       </c>
       <c r="AE317" t="n">
-        <v>9.679</v>
+        <v>9.619</v>
       </c>
       <c r="AF317" t="n">
-        <v>21.88</v>
+        <v>21.777</v>
       </c>
       <c r="AG317" t="n">
-        <v>17.14</v>
+        <v>17.039</v>
       </c>
       <c r="AH317" t="n">
-        <v>8.571</v>
+        <v>8.602</v>
       </c>
       <c r="AI317" t="n">
-        <v>2.776</v>
+        <v>2.87</v>
       </c>
       <c r="AJ317" t="n">
-        <v>19.042</v>
+        <v>19.235</v>
       </c>
       <c r="AK317" t="n">
-        <v>11.6</v>
+        <v>8.4</v>
       </c>
       <c r="AL317" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="318">
@@ -39386,22 +39386,22 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F325" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G325" t="b">
         <v>1</v>
       </c>
       <c r="H325" t="n">
-        <v>1966.747</v>
+        <v>1936.604</v>
       </c>
       <c r="I325" t="n">
-        <v>11.7947</v>
+        <v>11.404</v>
       </c>
       <c r="J325" t="n">
-        <v>1654.9</v>
+        <v>1670.5</v>
       </c>
       <c r="K325" t="n">
         <v>13</v>
@@ -39422,70 +39422,70 @@
         <v>12</v>
       </c>
       <c r="Q325" t="n">
-        <v>119.416</v>
+        <v>119.058</v>
       </c>
       <c r="R325" t="n">
-        <v>101.187</v>
+        <v>101.799</v>
       </c>
       <c r="S325" t="n">
-        <v>18.229</v>
+        <v>17.259</v>
       </c>
       <c r="T325" t="n">
-        <v>0.31319</v>
+        <v>0.31252</v>
       </c>
       <c r="U325" t="n">
-        <v>0.15637</v>
+        <v>0.15584</v>
       </c>
       <c r="V325" t="n">
-        <v>80.7</v>
+        <v>80.39</v>
       </c>
       <c r="W325" t="n">
-        <v>68.58</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="X325" t="n">
-        <v>0.8582</v>
+        <v>0.8276</v>
       </c>
       <c r="Y325" t="n">
-        <v>28.17</v>
+        <v>28.097</v>
       </c>
       <c r="Z325" t="n">
-        <v>60.58</v>
+        <v>60.434</v>
       </c>
       <c r="AA325" t="n">
-        <v>10.221</v>
+        <v>10.124</v>
       </c>
       <c r="AB325" t="n">
-        <v>27.957</v>
+        <v>27.662</v>
       </c>
       <c r="AC325" t="n">
-        <v>14.021</v>
+        <v>14.2</v>
       </c>
       <c r="AD325" t="n">
-        <v>19.133</v>
+        <v>19.372</v>
       </c>
       <c r="AE325" t="n">
-        <v>11.815</v>
+        <v>11.8</v>
       </c>
       <c r="AF325" t="n">
-        <v>25.568</v>
+        <v>25.628</v>
       </c>
       <c r="AG325" t="n">
-        <v>16.396</v>
+        <v>16.552</v>
       </c>
       <c r="AH325" t="n">
-        <v>6.411</v>
+        <v>6.345</v>
       </c>
       <c r="AI325" t="n">
-        <v>6.333</v>
+        <v>6.331</v>
       </c>
       <c r="AJ325" t="n">
-        <v>17.572</v>
+        <v>17.503</v>
       </c>
       <c r="AK325" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="AL325" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="326">
@@ -40346,22 +40346,22 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F333" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G333" t="b">
         <v>1</v>
       </c>
       <c r="H333" t="n">
-        <v>1661.239</v>
+        <v>1638.451</v>
       </c>
       <c r="I333" t="n">
-        <v>-2.4181</v>
+        <v>-2.2356</v>
       </c>
       <c r="J333" t="n">
-        <v>1665.4</v>
+        <v>1665.2</v>
       </c>
       <c r="K333" t="n">
         <v>74</v>
@@ -40382,70 +40382,70 @@
         <v>66</v>
       </c>
       <c r="Q333" t="n">
-        <v>112.962</v>
+        <v>112.689</v>
       </c>
       <c r="R333" t="n">
-        <v>110.155</v>
+        <v>110.294</v>
       </c>
       <c r="S333" t="n">
-        <v>2.807</v>
+        <v>2.395</v>
       </c>
       <c r="T333" t="n">
-        <v>0.2982</v>
+        <v>0.29456</v>
       </c>
       <c r="U333" t="n">
-        <v>0.15295</v>
+        <v>0.15274</v>
       </c>
       <c r="V333" t="n">
-        <v>78.97</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="W333" t="n">
-        <v>76.86</v>
+        <v>76.95</v>
       </c>
       <c r="X333" t="n">
-        <v>0.5345</v>
+        <v>0.509</v>
       </c>
       <c r="Y333" t="n">
-        <v>26.825</v>
+        <v>26.869</v>
       </c>
       <c r="Z333" t="n">
-        <v>59.782</v>
+        <v>59.676</v>
       </c>
       <c r="AA333" t="n">
-        <v>8.930999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AB333" t="n">
-        <v>26.276</v>
+        <v>25.842</v>
       </c>
       <c r="AC333" t="n">
-        <v>16.218</v>
+        <v>16.093</v>
       </c>
       <c r="AD333" t="n">
-        <v>20.825</v>
+        <v>20.83</v>
       </c>
       <c r="AE333" t="n">
-        <v>9.548999999999999</v>
+        <v>9.442</v>
       </c>
       <c r="AF333" t="n">
-        <v>22.145</v>
+        <v>22.334</v>
       </c>
       <c r="AG333" t="n">
-        <v>14.353</v>
+        <v>14.35</v>
       </c>
       <c r="AH333" t="n">
-        <v>7.589</v>
+        <v>7.594</v>
       </c>
       <c